--- a/scraped_data/05-01-2025_05-31-2025_Koninklijk besluit__scraping_results.xlsx
+++ b/scraped_data/05-01-2025_05-31-2025_Koninklijk besluit__scraping_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,28 +461,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025000798</t>
+          <t>2025201467</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19 mei 2025</t>
+          <t>22 mei 2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 11 maart 2024, gesloten in het Paritair Comité voor de bedienden der metaalfabrikatennijverheid, betreffende de wijziging van het sociaal sectoraal pensioenstelsel en van de sectorale technische nota (1)</t>
+          <t>17 mei 2025. - Koninklijk besluit tot benoeming van de leden van de Administratieve Commissie ter regeling van de arbeidsrelatie</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-19&amp;numac_search=2025000798&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025000798=0&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-22&amp;numac_search=2025201467&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201467=0&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de bedienden der metaalfabrikatennijverheid;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 11 maart 2024, gesloten in het Paritair Comité voor de bedienden der metaalfabrikatennijverheid, betreffende de wijziging van het sociaal sectoraal pensioenstelsel en van de sectorale technische nota.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de bedienden der metaalfabrikatennijverheidCollectieve arbeidsovereenkomst van 11 maart 2024Wijziging van het sociaal sectoraal pensioenstelsel en van de sectorale technische nota (Overeenkomst geregistreerd op 29 maart 2024 onder het nummer 187003/CO/209)HOOFDSTUK I. - ToepassingsgebiedArtikel 1.  § 1. Deze overeenkomst is van toepassing op de werkgevers, die onder de bevoegdheid vallen van het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid, en op de werknemers met een arbeidsovereenkomst voor bedienden die deze werkgevers tewerkstellen. § 2. Onder "werkgevers" wordt verstaan : zowel de juridische entiteit (op basis van het ondernemingsnummer) als de vestigingseenheden (op basis van het vestigingseenheidnummer) indien de juridische entiteit over meerdere vestigingseenheden beschikt.HOOFDSTUK II. - VoorwerpArt. 2. Deze collectieve arbeidsovereenkomst wijzigt de collectieve arbeidsovereenkomst van 4 juli 2022 (met registratienummer 174721/CO/209) tot wijziging van het sociaal sectoraal pensioenstelsel, het pensioenreglement, het solidariteitsreglement en van de sectorale technische nota.Deze collectieve arbeidsovereenkomst heeft als voorwerp :a) de coördinatie van de basiskenmerken en de regels inzake het beheer en de uitvoering van het sociaal sectoraal pensioenstelsel en de verduidelijking van een aantal aspecten van het sociaal sectoraal pensioenstelsel, zoals vastgelegd in de sectorale collectieve arbeidsovereenkomsten, opgesomd in artikel 18 van deze collectieve arbeidsovereenkomst;b) de wijziging met ingang van 1 september 2023 van de technische nota, opgenomen in bijlage 1 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174121/CO/209.Art. 3. Deze collectieve arbeidsovereenkomst wordt gesloten met toepassing van artikel 10 van de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid.De wet van 28 april 2003 zal verder kortweg de "WAP" genoemd worden.Deze collectieve arbeidsovereenkomst wordt gesloten in uitvoering van de beslissing van de representatieve organisaties in het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid en heeft als enig voorwerp de instelling van een sectoraal pensioenstel :-vanaf 1 april 2002 voor de bedienden van de werkgevers, die niet vrijgesteld zijn van de deelname aan het sectoraal pensioenstelsel of geen gebruik hebben gemaakt van "opting-out" (zie hoofdstuk X van deze collectieve arbeidsovereenkomst);- vanaf 1 juli 2007 voor de kaderleden van de werkgevers, die niet vrijgesteld zijn van de deelname aan het sectoraal pensioenstelsel of geen gebruik hebben gemaakt van "opting-out" (zie hoofdstuk X van deze collectieve arbeidsovereenkomst).Met ingang van 1 januari 2017 werd het sectoraal pensioenstelsel omgevormd tot een sociaal sectoraal pensioenstelsel via de invoering van een solidariteitstoezegging. Vanaf 1 januari 2017 geldt de solidariteitstoezegging eveneens voor de bedienden en de kaderleden van de werkgevers die destijds gebruik hebben gemaakt van "opting-out" (zie hoofdstuk X van deze collectieve arbeidsovereenkomst).In artikel 18 van deze collectieve arbeidsovereenkomst wordt de historiek weergegeven van de verschillende sectorale collectieve arbeidsovereenkomsten die in de loop van de jaren binnen het Paritair Comité 209 voor de bedienden van metaalfabrikatennijverheid werden gesloten ter invoering, wijziging en verduidelijking van het sociaal sectoraal pensioenstelsel.HOOFDSTUK III. - Aanduiding van de InrichterArt. 4. Overeenkomstig artikel 3, § 1, 5°  van de WAP, wordt het "Sociaal Fonds voor de Bedienden Metaal-BIS - Fonds voor Bestaanszekerheid", afgekort SFBM-BIS, met ondernemingsnummer KBO 0682.891.282, opgericht op 1 januari 2017 via de collectieve arbeidsovereenkomst van 9 oktober 2017 van het Paritair Comité 209 (met registratienummer 142818/CO/209), aangeduid als Inrichter van het sociaal sectoraal pensioenstelsel.Het SFBM-BIS zal hierna de "Inrichter" genoemd worden.HOOFDSTUK IV. - De pensioentoezeggingArt. 5.  § 1. Het sociaal sectoraal pensioenstelsel bestaat enerzijds uit een pensioentoezegging die is vastgelegd in het pensioenreglement (zie sectie 1 met de bijzondere voorwaarden en de algemene voorwaarden van het groepsverzekeringsreglement, zoals opgenomen in bijlage 2 en bijlage 3 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209), en anderzijds uit een solidariteitstoezegging, die verbonden is aan de pensioentoezegging en is vastgelegd in het solidariteitsreglement (zie sectie 2 met de bijzondere voorwaarden en de algemene voorwaarden van het groepsverzekeringsreglement, opgenomen in bijlage 2 en in bijlage 3 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209). § 2. De pensioentoezegging is van het type vaste bijdragen zonder rendementsgarantie van de Inrichter, doch zonder afbreuk te doen aan het wettelijk minimum rendement opgelegd door de WAP.De sectorale pensioentoezegging moet sinds de aanvang beschouwd worden als één globale pensioentoezegging. De wettelijke minimum rendementsgarantie wordt berekend op de totaliteit van de verworven reserves, opgebouwd vanaf 1 januari 2004.Bij de kapitalisatie van de aanvullende pensioenpremies en de toepassing van de wettelijke minimum rendementsgarantie wordt de horizontale methode toegepast.De pensioentoezegging voorziet in :- de opbouw van een aanvullend pensioenkapitaal, dat overeenkomstig de regels en de modaliteiten van het pensioenreglement wordt uitbetaald aan de aangesloten werknemer op moment van pensionering (in zoverre de betrokken werknemer bij zijn uittreding uit de sector zijn verworven reserves niet heeft overgedragen naar een andere pensioeninstelling). Dit aanvullend pensioenkapitaal kan op verzoek van de aangesloten werknemer worden omgezet in een levenslange pensioenrente;- een overlijdenskapitaal in geval van overlijden van de aangesloten werknemer vóór pensionering, dat gelijk is aan de verworven reserves die de aangesloten werknemer heeft opgebouwd in het sociaal sectoraal pensioenstelsel tot op het moment van zijn overlijden en dat wordt uitbetaald aan de begunstigden van de overleden aangesloten werknemer, overeenkomstig de regels en modaliteiten van het pensioenreglement. § 3. Deze pensioentoezegging is een verbintenis van de Inrichter ten aanzien van de aangesloten werknemers. § 4. De regels en modaliteiten betreffende de pensioentoezegging worden verder vastgelegd in sectie 1 met de bijzondere en de algemene voorwaarden van het groepsverzekeringsreglement (het pensioenreglement), opgenomen in de bijlagen 2 en 3 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209. Het pensioenreglement moet steeds gelezen worden in overeenstemming met deze sectorale collectieve arbeidsovereenkomst, die voorrang heeft.HOOFDSTUK V. - Beheer en aanduiding van de pensioeninstellingArt. 6.  § 1. Het beheer en de uitvoering van de pensioentoezegging werden aanvankelijk door de Inrichter toevertrouwd aan de verzekeringsonderneming Integrale NV. Met ingang van 15 december 2021 heeft de verzekeringsonderneming Monument Assurance Belgium NV, met maatschappelijke zetel te 1210 Sint-Joost-ten-Node, Koning Albert II - Laan, 19 en onder het codenummer 1644 en met ondernemingsnummer 0478.291.162, alle rechten en verplichtingen met betrekking tot de pensioentoezegging overgenomen van Integrale NV. Monument Assurance Belgium NV vervangt met andere woorden Integrale NV met ingang van 15 december 2021 als pensioeninstelling en staat vanaf 15 december 2021 in voor het beheer en de uitvoering van de pensioentoezegging. § 2. De beheers- en werkingsregels die worden afgesproken tussen de Inrichter en Monument Assurance Belgium NV als pensioeninstelling evenals de door Monument Assurance Belgium NV aangerekende beheerskosten worden vastgelegd in een beheers- en verzekeringsovereenkomst, en zijn ook beschreven in de technische nota, opgenomen in bijlage 1 bij deze collectieve overeenkomst.HOOFDSTUK VI. - Verwerving van pensioenrechtenArt. 7. Overeenkomstig artikel 17 van de WAP en het pensioenreglement in sectie 1 met de bijzondere en de algemene voorwaarden van het groepsverzekeringsreglement (zoals bepaald in de bijlagen 2 en 3 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209), kunnen alle werknemers, tewerkgesteld bij een werkgever bedoeld in artikel 1, die niet aangesloten zijn bij een evenwaardig ondernemingspensioenstelsel in het kader van een opting-out of een buiten toepassingsgebied (zie hoofdstuk X van deze collectieve arbeidsovereenkomst), hun recht op een sectoraal aanvullend pensioen laten gelden binnen de voorwaarden van het pensioen- en solidariteitsreglement.HOOFDSTUK VII. - SolidariteitstoezeggingArt. 8.  § 1. De solidariteitstoezegging voorziet, in uitvoering van artikel 43 van de WAP en het koninklijk besluit van 14 november 2003 tot vaststelling van de solidariteitsprestaties verbonden met de sociale aanvullende pensioenstelsels in de volgende solidariteitsprestaties :- de financiering van de opbouw van het aanvullend pensioen tijdens de periodes van tijdelijke werkloosheid in de zin van hoofdstuk II/1 "Regeling van schorsing van de uitvoering van de overeenkomst en regeling van gedeeltelijke arbeid" van titel III van de wet van 3 juli 1978 betreffende de arbeidsovereenkomsten;- de financiering van de opbouw van het aanvullend pensioen tijdens de periodes van arbeidsongeschiktheid ten gevolge van ziekte of ongeval van gemeen recht (met uitzondering van een arbeidsongeval of een beroepsziekte);- de financiering van de opbouw van het aanvullend pensioen tijdens periodes voorafgaand aan het faillissement, de ontbinding en invereffeningstelling, sluiting of de gerechtelijke reorganisatie (in de zin van Boek XX van het Wetboek Economisch Recht) van de onderneming alsook de financiering van de opbouw van het aanvullend pensioen indien het faillissement of invereffeningstelling van de onderneming zich voordeed in de periode sinds 1 januari 2019 en de betrokken failliete/vereffende onderneming in de periode vóór 2019 de werknemers niet had aangesloten aan het sectoraal pensioenstelsel en geen aanvullende pensioenpremies had betaald, met dien verstande dat in alle gevallen deze solidariteitsprestatie slechts voor een maximumperiode van 12 maanden wordt toegekend;- de financiering van een extra uitkering in de vorm van een rente aan de begunstigden in geval van overlijden van de aangesloten werknemer tijdens zijn beroepsloopbaan in de sector vóór de datum van pensionering. § 2. De bedragen van deze solidariteitsprestaties worden door het Paritair Comité 209 bepaald in een aparte collectieve arbeidsovereenkomst. § 3. Deze solidariteitstoezegging is een verbintenis van de Inrichter ten aanzien van de aangesloten werknemers. § 4. De regels en de modaliteiten betreffende de solidariteitstoezegging worden verder vastgelegd in sectie 2 met de bijzondere en de algemene voorwaarden van het groepsverzekeringsreglement (het solidariteitsreglement), opgenomen in de bijlagen 2 en 3 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209. Het solidariteitsreglement moet steeds gelezen worden in overeenstemming met deze sectorale collectieve arbeidsovereenkomst, die voorrang heeft.HOOFDSTUK VIII. - Beheer en aanduiding van de solidariteitsinstellingArt. 9.  § 1. Het beheer en de uitvoering van de solidariteitstoezegging werden aanvankelijk door de Inrichter toevertrouwd aan de verzekeringsonderneming Integrale NV. Met ingang van 15 december 2021 heeft de verzekeringsonderneming Monument Assurance Belgium NV, met maatschappelijke zetel te 1210 Sint-Joost-ten-Node, Koning Albert II-Laan, 19, toegelaten onder het codenummer 1644 en met ondernemingsnummer 0478.291.162, alle rechten en verplichtingen met betrekking tot de solidariteitstoezegging overgenomen van Integrale NV. Monument Assurance Belgium NV vervangt met andere woorden Integrale NV met ingang van 15 december 2021 als solidariteitsinstelling en staat vanaf 15 december 2021 in voor het beheer en de uitvoering van de solidariteitstoezegging. § 2. De beheers- en werkingsregels die worden afgesproken tussen de Inrichter en Monument Assurance Belgium NV als solidariteitsinstelling evenals de door Monument Assurance Belgium NV aangerekende beheerskosten worden vastgelegd in een beheers- en verzekeringsovereenkomst, en zijn ook beschreven in de technische nota, opgenomen in bijlage 1 bij deze collectieve overeenkomst.HOOFDSTUK IX. - Bijdragen en inningsmodaliteitenArt. 10. Algemene principes § 1. In het voordeel van de werknemers, die rechten kunnen laten gelden met betrekking tot het sociaal sectoraal pensioenstelsel, zal het "Sociaal Fonds voor de Bedienden Metaal - Fonds voor Bestaanszekerheid", afgekort "SFBM", met ondernemingsnummer KBO 0541.831.805, opgericht op 1 januari 2014 via de collectieve arbeidsovereenkomst van 4 november 2013 van het Paritair Comité 209 (met registratienummer 118373/CO/209), met ingang van 1 januari 2019 zowel de aanvullende pensioenpremies als de solidariteitsbijdragen innen ter financiering van het sociaal sectoraal pensioenstelsel. § 2. Het SFBM int de aanvullende pensioenpremies en de solidariteitsbijdragen in naam en voor rekening van de Inrichter bij alle werkgevers op wie het sociaal sectoraal pensioenstelsel in haar geheel van toepassing is.Het SFBM int ook de solidariteitsbijdragen in naam en voor rekening van de Inrichter bij de werkgevers op wie enkel de solidariteitstoezegging van toepassing is (omdat ze voor wat betreft de pensioentoezegging genieten van een "opting-out").De premies tot financiering van de pensioentoezegging en de bijdragen tot financiering van de solidariteitstoezegging worden geïnd onder de vorm van procentuele kwartaalbijdragen.Dit betekent dat de aanvullende pensioenpremies en de solidariteitsbijdragen door het SFBM driemaandelijks worden geïnd bij de betrokken werkgevers op basis van de DmfA-aangiftes.Daarnaast int het SFBM bij de werkgever die de aangeslotene tewerkstelt op het moment van zijn uittreding, pensionering of overlijden, in naam en voor rekening van de Inrichter, de nodige premies die nodig zijn voor de aanzuivering van de tekorten van de gewaarborgde pensioenreserves alsook van de tekorten ten opzichte van de wettelijke rendementsgarantie, zoals bepaald in de artikelen 24 en 30 van de WAP. Dit omvat ook dat het SFBM, in naam en voor rekening van de Inrichter, de achterstallige pensioenpremies (verhoogd met een bijkomende administratiekost) int bij de werkgevers, die in het verleden nagelaten hebben om hun bedienden aan te sluiten bij het sociaal sectoraal pensioenstelsel en de nodige pensioenpremies te betalen, zoals bepaald in de sectorale collectieve arbeidsovereenkomsten met betrekking tot het sociaal sectoraal pensioenstelsel en uitgewerkt in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst (en in de vorige versies van de technische nota). § 3. De eventuele taksen en sociale bijdragen zijn ten laste van de werkgever en komen bovenop de aanvullende pensioenpremies.Het SFBM int, in naam en voor rekening van de Inrichter, bij de werkgevers de sociale bijdragen, met inbegrip van de eventuele Wijninckxbijdrage, zoals bedoeld in artikel 38, §  3duodecies en § 3terdecies van de wet van 29 juni 1981, die verschuldigd zijn op de aanvullende pensioenpremies en stort deze door aan de Rijksdienst voor Sociale Zekerheid (RSZ). § 4. Het percentage van de aanvullende pensioenpremies en de solidariteitsbijdragen, alsook de modaliteiten van de inning worden vastgelegd in de sectorale collectieve arbeidsovereenkomsten tot vaststelling van de statuten van het SFBM, en in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst. § 5. De concrete afspraken omtrent de inning en de doorstorting van deze aanvullende pensioenpremies en solidariteitsbijdragen worden verder uitgewerkt in een beheersovereenkomst tussen het SFBM en de Inrichter. Omdat het SFBM bij de inning ondersteuning krijgt van het "Fonds voor bestaanszekerheid van de metaalverwerkende nijverheid", met ondernemingsnummer KBO 0855.690.646, (opgericht bij beslissing van 13 januari 1965 van het Nationaal Paritair Comité 111, algemeen verbindend verklaard bij koninklijk besluit van 10 februari 1965), afgekort "FBZMN", is het FBZMN ook partij bij deze beheersovereenkomst. § 6. De praktische aspecten van de inning en de doorstorting van de aanvullende pensioenpremies en solidariteitsbijdragen naar de pensioen- en solidariteitsinstelling worden vastgelegd in een beheersovereenkomst tussen de Inrichter, het SFBM en Monument Assurance Belgium NV.Art. 11. Financiering van de pensioentoezegging § 1. De financiering van de pensioentoezegging zal gebeuren via een patronale pensioenpremie, die gelijk is aan een percentage van het referentieloon van de aangesloten werknemers. Het referentieloon is gelijk aan het bij de RSZ aangegeven brutojaarloon, exclusief het enkel en het dubbel vakantiegeld. § 2. Met ingang van 1 januari 2020 bedraagt de patronale pensioenpremie 2,29 pct. van het referentieloon.Meer concreet, betreft het 2,29 pct. op basis van de brutoloonmassa, waarbij de brutoloonmassa gelijk is aan de som van 1/1,08 op DmfA-bezoldigingscode 1 met de DmfA-bezoldigingscodes 2, 3, 4. § 3. De aanvullende pensioenpremies worden per kwartaal geïnd door het SFBM.Binnen de 4 maanden volgend op het einde van het betreffende kwartaal stort het SFBM de aanvullende pensioenpremies, na inhouding van de administratiekosten voor de inning ervan, in naam en voor rekening van de Inrichter, door naar de pensioeninstelling (Monument Assurance Belgium NV).Met ingang van 1 januari 2020 houdt het SFBM bij elk verlopen kwartaal een forfaitair percentage in op de geïnde aanvullende pensioenpremies. Dit forfaitair kostenpercentage wordt jaarlijks bepaald door de raad van bestuur van de Inrichter. Voor 2023 en 2024 is dit forfaitair kostenpercentage vastgelegd op 1 pct. van de geïnde aanvullende pensioenpremies.Art. 12. Financiering van de solidariteitstoezegging § 1. De financiering van de solidariteitstoezegging zal gebeuren via een solidariteitsbijdrage, die gelijk is aan een percentage van het referentieloon van de aangesloten werknemers. Het referentieloon is gelijk aan het bij de RSZ aangegeven brutojaarloon, exclusief het enkel en het dubbel vakantiegeld. § 2. Met ingang van 1 januari 2020 bedraagt de solidariteitsbijdrage 0,10 pct. van het referentieloon.Meer concreet, betreft het 0,10 pct. op basis van de brutoloonmassa, waarbij de brutoloonmassa gelijk is aan de som van 1/1,08 op DmfA-bezoldigingscode 1 met de DmfA-bezoldigingscodes 2, 3, 4. § 3. De solidariteitsbijdragen worden per kwartaal geïnd door het SFBM.Binnen de 4 maanden volgend op het einde van het betreffende kwartaal stort het SFBM 95 pct. en vanaf 1 januari 2021 96 pct. van de geïnde solidariteitsbijdragen, in naam en voor rekening van de Inrichter door naar de solidariteitsinstelling. De overige 5 pct. en vanaf 1 januari 2021 de overige 4 pct. van de geïnde solidariteitsbijdragen worden tegelijkertijd doorgestort naar de Inrichter ter dekking van de administratiekosten voor de inning van de solidariteitsbijdragen en diens algemene werkingskosten. Deze bepalingen zijn eveneens van toepassing indien de Inrichter (of het SFBM in naam en voor rekening van de Inrichter) nog bedragen zou ontvangen via het Fonds van Sluiting van Onderneming (FSO), de curator, de vereffenaar(s) of van de onderneming in gerechtelijke reorganisatie voor aangeslotenen voor wie de opbouw van het aanvullend pensioen tijdens periodes voorafgaand aan het faillissement, de ontbinding en invereffeningstelling, sluiting of de gerechtelijke reorganisatie (in de zin van Boek XX van het Wetboek Economisch Recht) van de onderneming reeds via de solidariteitspensioentoezegging gebeurde.HOOFDSTUK X. - Buiten toepassingsgebied en mogelijkheid tot opting-outArt. 13. Buiten toepassingsgebied § 1. Werkgevers, die voor hun bedienden een aanvullend pensioenstelsel op ondernemingsniveau hebben ingericht vóór 11 juni 2001, dat zonder onderbreking nog steeds van toepassing is en minstens evenwaardig is aan het sectoraal aanvullend pensioenstelsel, moeten niet deelnemen aan het sociaal sectoraal pensioenstelsel en worden bijgevolg uitgesloten uit het toepassingsgebied van het sociaal sectoraal pensioenstelsel in zoverre ze voldoen aan de jaarlijkse attesteringsplicht overeenkomstig § 3 van dit artikel.Werkgevers, die voor hun kaderleden een aanvullend pensioenstelsel op ondernemingsniveau hebben ingericht vóór 31 december 2006, dat zonder onderbreking nog steeds van toepassing is en minstens evenwaardig is aan het sectoraal pensioenstelsel, moeten niet deelnemen aan het sociaal sectoraal pensioenstelsel en worden bijgevolg uitgesloten uit het toepassingsgebied van het sociaal sectoraal pensioenstelsel in zoverre zij voldoen aan de jaarlijkse attesteringsplicht overeenkomstig § 3 van dit artikel.De vrijstelling van deelname aan het sociaal sectoraal pensioenstelsel wegens buiten toepassingsgebied geldt zowel voor de pensioentoezegging als voor de solidariteitstoezegging. § 2. De voorwaarden en modaliteiten omtrent het "buiten toepassingsgebied" worden verder vastgelegd in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst. § 3. Er geldt een jaarlijkse attesteringsplicht voor de werkgevers bedoeld in § 1 van dit artikel, waarvan de modaliteiten wordt vastgelegd in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst.Art. 14. Opting-out § 1. Werkgevers, die vóór 1 april 2011 op basis van de toepasselijke sectorale collectieve arbeidsovereenkomsten binnen het Paritair Comité 209, gebruik hebben gemaakt van de geboden mogelijkheid tot opting-out (dit wil zeggen de mogelijkheid om voor een deel of het geheel van de werknemers de uitvoering van sectoraal pensioenstelsel zelf te organiseren in een pensioenstelsel op het niveau van de onderneming, zoals bepaald in artikel 9 van de WAP), kunnen de opting-out verderzetten, op voorwaarde dat ze blijven voldoen aan de voorwaarden en modaliteiten met inbegrip van de jaarlijkse attesteringsplicht, zoals vastgelegd in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst. § 3. Werkgevers die vóór 1 april 2011 gebruik hebben gemaakt van de mogelijkheid tot opting-out, zijn wel verplicht om zich aan te sluiten bij de solidariteitstoezegging die werd ingevoerd door de Inrichter binnen de sector en dit voor alle werknemers, die aangesloten zijn bij het pensioenstelsel op het niveau van de onderneming.Art. 15. Reorganisaties - nieuwe ondernemingenIn het kader van de overgang van een onderneming, vestiging of deel van een onderneming of een vestiging, als gevolg van een conventionele overdracht of een fusie, splitsing of andere transactie in de zin van de collectieve arbeidsovereenkomst nr. 32bis van 7 juni 1985 betreffende het behoud van de rechten van de werknemers bij wijziging van werkgever ingevolge de overgang van ondernemingen krachtens overeenkomst en tot regeling van de rechten van de werknemers die overgenomen worden bij overname van activa na faillissement of gerechtelijk akkoord door boedelafstand (zoals nadien gewijzigd), kan de werkgever voor de overgenomen of bij de reorganisatie betrokken werknemers eveneens vrijgesteld worden van deelname aan het sociaal sectoraal pensioenstelsel, mits voldaan is aan de voorwaarden voor opting-out (hoofdstuk B) of van buiten toepassingsgebied (hoofdstuk C), zoals voorzien in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst.Indien een werkgever ten gevolge van een wijziging van paritair comité onder de bevoegdheid valt van het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid, kan de werkgever voor de betrokken werknemers eveneens vrijgesteld worden van deelname aan het sociaal sectoraal pensioenstelsel, mits voldaan is aan de voorwaarden van buiten toepassingsgebied (hoofdstuk C) op het moment dat de werkgever onder de bevoegdheid van het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid valt, zoals voorzien in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst.Indien de onderneming pas op moment van of na de inwerkingtreding van deze collectieve arbeidsovereenkomst is opgericht en onder de bevoegdheid valt van het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid, kan de werkgever voor de betrokken werknemers eveneens vrijgesteld worden van deelname aan het sociaal sectoraal pensioenstelsel indien deze vanaf de oprichting reeds een evenwaardig ondernemingsplan heeft en mits voldaan is aan de voorwaarden van buiten toepassingsgebied (hoofdstuk C) op het moment van de oprichting, zoals voorzien in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst.Art. 16. Alle werknemers van een werkgever, bedoeld in artikel 1 van deze collectieve arbeidsovereenkomst, die niet aangesloten zijn bij een ander evenwaardig ondernemingspensioenstelsel in het kader van een opting-out of een buiten toepassingsgebied, zijn verplicht aangesloten aan het sectoraal sociaal pensioenstelsel.HOOFDSTUK XI. - Wijziging van het pensioenreglement, solidariteitsreglement en de technische notaArt. 17.  § 1. Het reglement van de groepsverzekering die het sociaal sectoraal pensioenstelsel uitvoert, zoals opgenomen in bijlage 2 en bijlage 3 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209 blijft verder van toepassing. § 2. De technische nota, opgenomen in bijlage 1 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209, wordt met ingang van 1 september 2023 gewijzigd door de technische nota opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst. § 3. De technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst, maakt integraal deel uit van deze collectieve arbeidsovereenkomst.HOOFDSTUK XII. - Vervanging van de collectieve arbeidsovereenkomstArt. 18.  § 1. Deze collectieve arbeidsovereenkomst vervangt vanaf 1 september 2023 de collectieve arbeidsovereenkomst van 4 juli 2022 tot wijziging van het sociaal sectoraal pensioenstelsel, het pensioenreglement en het solidariteitsreglement en van de sectorale technische nota (met registratienummer 174721/CO/209), met uitzondering van de bijlagen 2 en 3, die ongewijzigd behouden blijven. § 2. Deze collectieve arbeidsovereenkomst coördineert de basiskenmerken en de regels inzake het beheer en uitvoering van het sociaal sectoraal pensioenstelsel en verduidelijkt een aantal aspecten van het sociaal sectoraal pensioenstelsel, zoals vastgelegd in de sectorale collectieve arbeidsovereenkomsten, die binnen het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid werden gesloten met betrekking tot het sociaal sectoraal pensioenstelsel, zoals onder meer :- de collectieve arbeidsovereenkomst van 11 juni 2001 (met registratienummer 57918/CO/209) betreffende het nationaal akkoord 2001-2002, gesloten in het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid;- de collectieve arbeidsovereenkomst van 17 december 2001 (met registratienummer 60649/CO/209) betreffende de uitvoering van artikel 4, §§ 2, 3 en 4 van de collectieve arbeidsovereenkomst van 11 juni 2001 betreffende het nationaal akkoord 2001-2002;- de collectieve arbeidsovereenkomst van 21 maart 2002 (met registratienummer 62481/CO/209) betreffende de uitvoering van hoofdstuk II, artikel 4, §§ 1 en 5 van de collectieve arbeidsovereenkomst van 11 juni 2001 betreffende het nationaal akkoord 2001-2002;- de collectieve arbeidsovereenkomst van 8 maart 2004 (met registratienummer 70726/CO/209) tot wijziging van de collectieve arbeidsovereenkomst van 21 maart 2002 betreffende de uitvoering van hoofdstuk II, artikel 4, §§ 1 en 5 van de collectieve arbeidsovereenkomst van 11 juni 2001 betreffende het nationaal akkoord 2001-2002;- de collectieve arbeidsovereenkomst van 18 januari 2007 (met registratienummer 82045/CO/209) gesloten in uitvoering van het nationaal akkoord 2007-2008, tot wijziging en vervanging van de collectieve arbeidsovereenkomst van 21 maart 2002 tot uitvoering van hoofdstuk II, artikel 4, §§ 1 en 5 van de collectieve arbeidsovereenkomst van 11 juni 2001 betreffende het nationaal akkoord 2001-2002 (sectoraal aanvullend pensioen);- de collectieve arbeidsovereenkomst van 24 september 2007 (met registratienummer 85840/CO/209) betreffende het nationaal akkoord 2007-2008, gesloten in het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid;- de collectieve arbeidsovereenkomst van 6 juli 2009 (met registratienummer 95215/CO/209) betreffende het nationaal akkoord 2009-2010, gesloten in het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid;- de collectieve arbeidsovereenkomst van 20 december 2010 (met registratienummer 102881/CO/209) tot wijziging van artikel 3, § 2b van het nationaal akkoord 2009-2010;- de collectieve arbeidsovereenkomst van 20 december 2010 (met registratienummer 102882/CO/209) tot uitvoering van artikel 3, § 4, 4de alinea van het nationaal akkoord 2009-2010;- de collectieve arbeidsovereenkomst van 4 juli 2011 (met registratienummer 105349/CO/209) betreffende het nationaal akkoord 2011-2012, gesloten in het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid;- de collectieve arbeidsovereenkomst van 5 maart 2012 (met registratienummer 109294/CO/209) tot wijziging van het reglement van de groepsverzekering die het sectorale pensioenstelsel uitvoert en van de sectorale technische nota;- de collectieve arbeidsovereenkomst van 10 juli 2013 (met registratienummer 116303/CO/209) tot wijziging van het reglement van de groepsverzekering die het sectorale pensioenstelsel uitvoert en van de sectorale technische nota;- de collectieve arbeidsovereenkomst van 4 november 2013 (met registratienummer 118405/CO/209) tot verhoging van het bedrag van de pensioenbijdragen;- de collectieve arbeidsovereenkomst van 4 juli 2016 (met registratienummer 134523/CO/209) tot wijziging van het reglement van de groepsverzekering die het sectorale pensioenstelsel uitvoert en van de sectorale technische nota, en opheffing van het nivelleringsfonds;- de collectieve arbeidsovereenkomst van 13 november 2017 (met registratienummer 144393/CO/209) tot wijziging van het reglement van de groepsverzekering die het sectorale pensioenstelsel uitvoert en van de sectorale technische nota;- de collectieve arbeidsovereenkomst van 11 december 2017 (met registratienummer 144375/CO/209) betreffende de solidariteitsuitkeringen;- de collectieve arbeidsovereenkomst van 9 december 2019 (met registratienummer 157451/CO/209) tot wijziging van het reglement van de groepsverzekering die het sociale sectorale pensioenstelsel uitvoert en van de sectorale technische nota en tot verduidelijking van een aantal aspecten van het sectorale pensioenstelsel;- de collectieve arbeidsovereenkomst van 14 december 2020 tot wijziging van het sociaal sectoraal pensioenstelsel, het pensioenreglement, het solidariteitsreglement en van de sectorale technische nota (met registratienummer 162728/CO/209);- de collectieve arbeidsovereenkomst van 4 juli 2022 tot wijziging van het sociaal sectoraal pensioenstelsel, het pensioenreglement, het solidariteitsreglement en van de sectorale technische nota (met registratienummer 17</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op artikelen 37 en 107, tweede lid, van de Grondwet; Gelet op de programmawet (I) van 27 december 2006 betreffende de Administratieve Commissie ter regeling van de arbeidsrelatie, artikel 329, vervangen bij de wet van 25 augustus 2012 en gewijzigd bij de wetten van 7 mei 2019 en van 3 oktober 2022; Gelet op het koninklijk besluit van 11 februari 2013 houdende samenstelling en werking van de kamers van de Administratieve Commissie ter regeling van de arbeidsrelatie, artikel 2, § 1, gewijzigd bij de koninklijke besluiten van 23 juni 2019 en 28 maart 2024 en artikel 3, § 1, gewijzigd bij het koninklijk besluit van 28 maart 2024; Op de voordracht van de Minister van Werk, van de Minister van Sociale Zaken, van de Minister van Sociale Fraudebestrijding en van de Minister van Zelfstandigen, Hebben Wij besloten en besluiten Wij : Artikel 1. Ontslag uit het mandaat van plaatsvervangend voorzitter van de Franstalige kamer van de Administratieve Commissie ter regeling van de arbeidsrelatie wordt verleend aan Pascal Hubain. Art. 2. De volgende personen worden benoemd als Franstalige leden van de Administratieve Commissie ter regeling van de arbeidsrelatie: a) als voorzitter: Pascal Hubain, rechter in de Franstalige arbeidsrechtbank te Brussel; b) als vaste leden: Marie-Hélène Vrielinck als vertegenwoordiger van de Rijksdienst voor sociale zekerheid; Anne Zimmermann als vertegenwoordiger van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg; Doris Mulombe-Mwanza, Baleja Lydia Mukadi en Stephane Schütz als vertegenwoordigers van het Rijksinstituut voor de sociale verzekeringen der zelfstandigen. c) als plaatsvervangers: Julie Delforge als vertegenwoordiger van de Federale Overheidsdienst Sociale Zekerheid, Directie-generaal Zelfstandigen; Sarah Yumusak en Eva Polizzi als vertegenwoordiger van het Rijksinstituut voor de sociale verzekeringen der zelfstandigen; Aurore Léonet als vertegenwoordiger van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg;Mathilde Henkinbrant en Laurélie Vandenameele, als vertegenwoordigers van de Federale Overheidsdienst Sociale Zekerheid, Directie-generaal Juridische Expertise; Quentin Delattre als vertegenwoordiger van de Rijksdienst voor sociale zekerheid. Art. 3. De volgende personen worden benoemd als Nederlandstalige leden van de Administratieve Commissie ter regeling van de arbeidsrelatie: a) als voorzitter: Koen Nevens, rechter in de arbeidsrechtbank te Gent; b) als vaste leden: Pascale Mylemans als vertegenwoordiger van de Federale Overheidsdienst Sociale Zekerheid, Directie-generaal Juridische Expertise; Wim Brouckaert als vertegenwoordiger van de Rijksdienst voor sociale zekerheid; Sven Vanhuysse als vertegenwoordiger van de Federale Overheidsdienst Sociale Zekerheid, Directie-generaal Zelfstandigen; Erwin Tavernier als vertegenwoordiger van het Rijksinstituut voor de sociale verzekeringen der zelfstandigen. c) als plaatsvervangers: Steven Boelens als vertegenwoordiger van de Federale Overheidsdienst Sociale Zekerheid, Directie-generaal Juridische Expertise; Annick Floreal als vertegenwoordiger van de Federale Overheidsdienst Sociale Zekerheid, Directie-generaal Zelfstandigen; Riet Vanden Driessche en Nathalie De Groot als vertegenwoordigers van het Rijksinstituut voor de sociale verzekeringen der zelfstandigen; Lisa Verschingel en Claudio Vandersnickt als vertegenwoordigers van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg. Art. 4. Dit besluit heeft uitwerking met ingang van 3 maart 2025. Art. 5. De minister bevoegd voor Werk, de minister bevoegd voor Sociale Zaken, de minister bevoegd voor Sociale Fraudebestrijding en de minister bevoegd voor Zelfstandigen zijn, ieder wat hem betreft, belast met de uitvoering van dit besluit. Gegeven te Brussel, op 17 mei 2025. FILIPVan Koningswege :De Minister van Werk, D. CLARINVAL De Minister van Sociale Zaken, F. VANDENBROUCKE De Minister van Sociale Fraudebestrijding, R. BEENDERS De Minister van Zelfstandigen, E. SIMONET 
+</t>
         </is>
       </c>
     </row>
@@ -492,28 +493,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025201258</t>
+          <t>2025003991</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19 mei 2025</t>
+          <t>26 mei 2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 23 januari 2025, gesloten in het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap, betreffende het statuut van de zonale busbegeleiders (1)</t>
+          <t>17 mei 2025. - Koninklijk besluit tot wijziging van de bijlage III van het KB/WIB 92 op het stuk van studentenarbeid</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-19&amp;numac_search=2025201258&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025201258=1&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-26&amp;numac_search=2025003991&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003991=1&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 23 januari 2025, gesloten in het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap, betreffende het statuut van de zonale busbegeleiders. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 5 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap Collectieve arbeidsovereenkomst van 23 januari 2025 Statuut van de zonale busbegeleiders (Overeenkomst geregistreerd op 31 januari 2025 onder het nummer 191704/CO/152.01) HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de busbegeleiders en busbegeleidsters, hierna "busbegeleider" genoemd, die ressorteren onder het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap, en die behoren tot het zonaal leerlingenvervoer, zoals gedefinieerd bij wet van 15 juli 1983 houdende de oprichting van de Nationale Dienst voor Leerlingenvervoer. HOOFDSTUK II. - Duur van contracten Art. 2. Deze collectieve arbeidsovereenkomst is afgesloten ter verbetering van het statuut van de busbegeleider zoals gedefinieerd in artikel 1. Alle zonale busbegeleiders krijgen een arbeidsovereenkomst aangeboden van ten minste tien maanden met ingang van 1 september 2008. Met uitzondering van de jaarlijkse betaalde vakantiedagen worden volgende dagen doorbetaald zonder dat prestaties dienen geleverd te worden : - de schoolvakantiedagen die vallen tussen 1 september en 30 juni; - de facultatieve vrije dagen bepaald door de school, de inrichtende macht of het Vlaams Ministerie van Onderwijs; - de dagen waarop de school voorziet in een alternatief lessenpakket en er zodoende geen leerlingenvervoer nodig is. Art. 3. Deze collectieve arbeidsovereenkomst doet geen afbreuk aan de bestaande loon- en arbeidsvoorwaarden.Art. 4. Tijdens de maanden juli en augustus kan de busbegeleider aanspraak maken op een bestaanszekerheidsvergoeding indien voldaan is aan de voorwaarden zoals vastgelegd bij collectieve arbeidsovereenkomst van 28 september 2016 betreffende de bestaanszekerheidsvergoeding. HOOFDSTUK III. - Geldigheidsduur Art. 5. Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst van 28 september 2016 betreffende het statuut van de zonale busbegeleiders (overeenkomst geregistreerd op 29 november 2016 onder het nummer 136155/CO/152.01) en treedt in werking op datum van sluiting en is gesloten voor onbepaalde duur. Elk van de partijen kan ze opzeggen mits een opzeggingstermijn van drie maanden. Deze opzegging wordt bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap. Art. 6. Overeenkomstig artikel 14 van de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités worden, voor wat betreft de ondertekening van deze collectieve arbeidsovereenkomst, de handtekeningen van de personen die deze aangaan namens de werknemersorganisaties enerzijds en namens de werkgeversorganisaties anderzijds, vervangen door de, door de voorzitter en de secretaris ondertekende en door de leden goedgekeurde notulen van de vergadering. Gezien om te worden gevoegd bij het koninklijk besluit van 5 mei 2025. De Minister van Werk, D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op het Wetboek van de inkomstenbelastingen 1992, artikel 275, §§ 1 en 2, gewijzigd bij de wet van 23 augustus 2023;Gelet op het KB/WIB 92:- artikel 88, gewijzigd bij het koninklijk besluit van 19 december 2022;- bijlage III, vervangen bij het koninklijk besluit van 12 december 2024;Overwegende de wet van 10 april 2025 strekkende tot het vaststellen van de grens voor studentenarbeid op 650 uur, artikel 2;Gelet op de wetten op de Raad van State, gecoördineerd op 12 januari 1973, artikel 3, § 1;Gelet op de dringende noodzakelijkheid;Overwegende:- dat de wet van 10 april 2025 strekkende tot het vaststellen van de grens voor studentenarbeid op 650 uur de maximale grens voor studentenarbeid permanent heeft verhoogd van 475 tot 650 uren vanaf 1 januari 2025;- dat met de verhoging van het aantal fiscaal vrijgestelde uren studentenarbeid zo snel mogelijk rekening moet kunnen worden gehouden voor de toepassing van de bedrijfsvoorheffing;- dat dit besluit dus van toepassing moet zijn vanaf 1 januari 2025;- dat het ten spoedigste ter kennis moet worden gebracht van de schuldenaars van de bedrijfsvoorheffing;- dat dit besluit dus dringend moet worden getroffen;Op de voordracht van de Minister van Financiën,Hebben Wij besloten en besluiten Wij :Artikel 1. In nummer 71. van de toepassingsregels van de bijlage III van het KB/WIB 92, vervangen bij het koninklijk besluit van 12 december 2024, worden de woorden "gedurende 475 aangegeven uren" vervangen door de woorden "gedurende 650 aangegeven uren".Art. 2. Dit besluit heeft uitwerking met ingang van 1 januari 2025.Art. 3. De minister die bevoegd is voor Financiën, is belast met de uitvoering van dit besluit.Gegeven te Brussel, 17 mei 2025.FILIPVan Koningswege :De Minister van Financiën,J. JAMBON 
 </t>
         </is>
       </c>
@@ -524,28 +525,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025201248</t>
+          <t>2025003953</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 10 februari 2025, gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, tot vaststelling van het percentage van de bijdragen tot bijkomende financiering van de tweede pensioenpijler voor het jaar 2025 (1)</t>
+          <t>17 mei 2025. - Koninklijk besluit tot wijziging van artikel 7 van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-19&amp;numac_search=2025201248&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025201248=2&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025003953&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003953=2&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de gezondheidsinrichtingen en -diensten; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 10 februari 2025, gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, tot vaststelling van het percentage van de bijdragen tot bijkomende financiering van de tweede pensioenpijler voor het jaar 2025. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 5 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.Bijlage Paritair Comité voor de gezondheidsinrichtingen en -diensten Collectieve arbeidsovereenkomst van 10 februari 2025 Vaststelling van het percentage van de bijdragen tot bijkomende financiering van de tweede pensioenpijler voor het jaar 2025 (Overeenkomst geregistreerd op 20 maart 2025 onder het nummer 192673/CO/330) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de werknemers die ressorteren onder het Paritair Comité voor de gezondheidsinrichtingen en -diensten en die behoren tot de onderstaande sectoren onder de bevoegdheid van de Vlaamse Gemeenschap en/of de Vlaamse Gemeenschapscommissie van het Brusselse Hoofdstedelijk Gewest : - de categorale ziekenhuizen (dit is elk ziekenhuis dat uitsluitend beschikt over een G-dienst (revalidatie van geriatrische patiënten) en/of een Sp-dienst (gespecialiseerde dienst voor behandeling en revalidatie) als vermeld in artikel 5, § 1, I, eerste lid, 3° en 4° van de bijzondere wet van 8 augustus 1980 tot hervorming der instellingen); - de rusthuizen voor bejaarden, de rust- en verzorgingstehuizen, de dagverzorgingscentra, de assistentiewoningen, de centra voor kortverblijf voor bejaarden; - de psychiatrische verzorgingstehuizen; - de initiatieven voor beschut wonen; - de revalidatiecentra met uitsluiting van de instellingen waarmee het Verzekeringscomité van het RIZIV op voorstel van het College van geneesheren-directeurs, in uitvoering van artikel 22, 6° van de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen gecoördineerd op 14 juli 1994, een overeenkomst heeft gesloten en die niet vallen onder de toepassing van artikel 5, § 1, I, 5° van de bijzondere wet van 8 augustus 1980 tot hervorming van de instellingen. Onder "werknemers" wordt verstaan : het mannelijk en vrouwelijk werklieden- en bediendepersoneel. Art. 2. In toepassing van artikelen 3 en 4 van de collectieve arbeidsovereenkomst van 12 november 2018 tot financiering van de tweede pensioenpijler en de jaarlijkse vaststelling van het percentage van de bijdragen (registratienummer 149441/CO/330), gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, wordt het percentage van de bijdragen voor het jaar 2025 op jaarbasis bepaald als volgt : per kwartaal 0,22 pct. van het brutobedrag van de bezoldigingen, vóór inhouding van de persoonlijke socialezekerheidsbijdragen. De inning van deze bijdragen geschiedt voor het jaar 2025 als volgt : - geen inning in het eerste en het tweede kwartaal; - 0,44 pct. van het brutobedrag van de bezoldigingen, vóór inhouding van de persoonlijke socialezekerheidsbijdragen, tijdens het derde en het vierde kwartaal. Art. 3. Deze collectieve arbeidsovereenkomst gaat in vanaf de datum van ondertekening. Zij is gesloten voor onbepaalde tijd en kan worden opgezegd door elk van de partijen, mits een opzeggingstermijn van zes maanden, bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Comité voor de gezondheidsinrichtingen en -diensten die alle ondertekenende organisaties hiervan in kennis stelt. De opzeggingstermijn begint te lopen vanaf de eerste dag van de maand die volgt op de datum waarop de voorzitter van het Paritair Comité voor de gezondheidsinrichtingen en -diensten de betrokken organisaties in kennis heeft gesteld van de opzegging. Gezien om te worden gevoegd bij het koninklijk besluit van 5 mei 2025. De Minister van Werk, D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, artikel 35, § 1, vijfde lid en § 2, eerste lid, 1°,  gewijzigd bij het koninklijk besluit van 25 april 1997, bekrachtigd bij de wet van 12 december 1997;Gelet op het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen;Gelet op de voorstellen van de Technische raad voor kinesitherapie, gedaan op 8 november 2024 en 10 januari 2025;Gelet op de adviezen van de Dienst voor geneeskundige evaluatie en controle gegeven op 8 november 2024 en10 januari 2025;Gelet op de beslissing van de Overeenkomstencommissie kinesitherapeuten - verzekeringsinstellingen van 28 januari 2025;Gelet op het advies van de Commissie voor begrotingscontrole van 12 februari 2025;Gelet op de beslissing van het Comité van de verzekering voor geneeskundige verzorging van het Rijksinstituut voor ziekte- en invaliditeitsverzekering van 17 februari 2025;Gelet op het advies van de inspecteur van financiën, gegeven op 3 maart 2025;Gelet op de akkoordbevinding van de Minister van Begroting, gegeven op 21 maart 2025;Gelet op het advies 77.612/2 van de Raad van State, gegeven op 24 april 2025 met toepassing van artikel 84, § 1, eerste lid, 2°  van de wetten op de Raad van State gecoördineerd op 12 januari 1973;Op de voordracht van de Minister van Sociale Zaken,Hebben Wij besloten en besluiten Wij :Artikel 1. In artikel 7 van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen, vervangen bij het koninklijk besluit van 18 december 2002 en laatstelijk gewijzigd bij het koninklijk besluit van 29 mei 2024 worden de volgende wijzigingen aangebracht :1°  § 8 wordt aangevuld als volgt:"In dit artikel 7, moet worden verstaan :Onder "pathologische situatie" : een pathologische medisch-functionele situatie waarvoor de rechthebbende een kinesitherapeutische behandeling nodig heeft. Deze pathologische situatie kan het gevolg zijn van een acute of chronische pathologie.Onder "nieuwe pathologische situatie" : een pathologische medisch-functionele situatie van een rechthebbende waarvan de behandeling geen verlenging is van de behandeling van ofwel :- een of meerdere pathologische situaties uit § 10, die tijdens hetzelfde kalenderjaar al werden behandeld met kinesitherapie, of- een pathologische situatie uit § 14, 5°, A of § 14, 5°, B tijdens de lopende kennisgevingsperiode.Om te kunnen spreken van een nieuwe pathologische situatie moet de diagnose of pathologie niet nieuw zijn, dit kan dus gaan om een herval/recidief maar geen verlenging van een bestaande situatie. Tijdens een lopende kennisgevingsperiode § 14, 5°, A kan evenwel geen herval/recidief worden aangevraagd voor dezelfde diagnose of pathologie als deze waarvoor de kennisgevingsperiode lopende is "2°  In § 10 wordt de bepaling "Onder nieuwe pathologische situatie moet worden verstaan, een situatie die optreedt na het begin van de kinesitherapeutische behandeling, tijdens hetzelfde kalenderjaar en die losstaat van de oorspronkelijke pathologische situatie. » geschrapt.3°  In § 11, 1ste lid worden de woorden "14ter, 14quater of 14quinquies" vervangen door de woorden "of 14ter".4°  In § 11 wordt de bepaling "De verstrekkingen 560755, 560873, 560991, 561116, 561212, 564476 en 561304 mogen alleen worden geattesteerd voor patiënten die lijden aan een letsel van encefale oorsprong :" vervangen als volgt :"De verstrekkingen 560755, 560873, 560991, 561116, 561212, 564476 en 561304 mogen slechts eenmaal per dag worden geattesteerd en mogen niet op dezelfde dag worden gecumuleerd met andere verstrekkingen van artikel 7, § 1, van de nomenclatuur van de geneeskundige verstrekkingen, met uitzondering van de verstrekkingen "schriftelijk verslag" (560711, 560836, 560954, 561072, 561190, 564454 en 561411) waarmee wel mag worden gecumuleerd. Deze verstrekkingen 560755, 560873, 560991, 561116, 561212, 564476 en 561304 mogen alleen worden geattesteerd voor patiënten die lijden aan een letsel van encefale oorsprong :"5°  In § 11 wordt de bepaling "Tot 31 december van het kalenderjaar waarin de patiënt zijn 21ste verjaardag bereikt mogen de verstrekkingen 560755, 560873, 560991, 561116, 561212, 564476 en 561304 slechts eenmaal per dag worden geattesteerd. Deze mogen niet op dezelfde dag worden gecumuleerd met andere verstrekkingen van artikel 7, § 1, van de nomenclatuur van de geneeskundige verstrekkingen, met uitzondering van de verstrekkingen "schriftelijk verslag" (560711, 560836, 560954, 561072, 561190, 564454 en 561411) waarmee wel mag worden gecumuleerd." vervangen als volgt :"Tot 31 december van het kalenderjaar waarin de patiënt zijn 21ste verjaardag bereikt zijn er geen beperkingen op het aantal verstrekkingen 560755, 560873, 560991, 561116, 561212, 564476 en 561304 per kalenderjaar."6°  In § 14 wordt de bepaling "Onder nieuwe pathologische situatie moet worden verstaan, een situatie die optreedt na het begin van de kinesitherapeutische behandeling en die losstaat van de oorspronkelijke pathologische situatie" geschrapt.7°   § 14, 5°,  B, e) wordt vervangen als volgt:"e) Chronischevermoeidheidssyndroom/ Myalgische encephalomyelitis:Het initiële voorschrift met vermelding van de diagnose moet worden opgemaakt door een arts-specialist in de reumatologie, in de fysische geneeskunde en revalidatie, in de neurologie of in de inwendige geneeskunde, na klinisch onderzoek en overeenkomstig de meest recente criteria die op internationaal niveau van toepassing zijn.Voor het einde van het eerste jaar dat volgt op het jaar waarin de eerste verstrekking van de behandeling heeft plaatsgehad, zal voornoemde arts-specialist de evolutie van de symptomen van de patiënt opnieuw beoordelen, teneinde te bevestigen dat het noodzakelijk is dat de behandeling wordt voortgezet in het kader van § 14. Deze bevestiging, getekend door de arts-specialist, moet voorkomen in het individuele kinesitherapiedossier.Art. 2. Dit besluit treedt in werking op de eerste dag van de tweede maand na die waarin het is bekendgemaakt in het Belgisch Staatsblad.Art. 3. De minister bevoegd voor Sociale Zaken is belast met de uitvoering van dit besluit.Gegeven te Brussel, 17 mei 2025.FILIPVan Koningswege :De Minister van Sociale Zaken en Volksgezondheid,F. VANDENBROUCKE 
 </t>
         </is>
       </c>
@@ -556,29 +557,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025003811</t>
+          <t>2025004032</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5 mei 2025. - Koninklijk besluit houdende toekenning van een toelage aan de vzw "Çavaria" voor het budgettair jaar 2025</t>
+          <t>17 mei 2025. - Koninklijk besluit betreffende de toekenning van een subsidie voor de verlenging van 53 projecten voor digitale inclusie van kwetsbare groepen, uitgevoerd door 51 OCMW's en 2 verenigingen van OCMW's die in 2022 en 2023 werden geselecteerd uit de kandidaturen van de projectoproep "e-inclusion for Belgium - OCMW's" in het kader van het Europese herstel- en veerkrachtplan, onder het project "e-inclusion for Belgium"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-20&amp;numac_search=2025003811&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003811=3&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025004032&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025004032=3&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 22 mei 2003 houdende organisatie van de begroting en van de comptabiliteit van de federale Staat, op de artikelen 121 tot 124;Gelet op de wet van 10 mei 2007 ter bestrijding van bepaalde vormen van discriminatie, artikel 32/1;Gelet op de financiewet voor begrotingsjaar van 20 december 2024 op sectie 12 - FOD Justitie, programma 58/5 - Diversiteit, Interculturaliteit en Gelijkheid van Kansen;Gelet op het koninklijk besluit van 20 mei 2022 betreffende de administratieve, begrotings- en beheerscontrole;Gelet op het koninklijk besluit van 2 oktober 2023 betreffende de modaliteiten voor de toekenning van de jaarlijkse subsidies voor de koepels van niet-gouvernementele organisaties die actief zijn in het domein van de bestrijding van discriminatie op grond van seksuele oriëntatie voor wat betreft de materies die behoren tot de bevoegdheid van de federale overheid;Gelet op het ministerieel besluit van 22 maart 2024 tot erkenning van de koepels van niet-gouvernementele organisaties die actief zijn in het domein van de bestrijding van discriminatie op grond van seksuele oriëntatie voor wat betreft de materies die behoren tot de bevoegdheid van de federale overheid, voor de erkenningscyclus van 2024-2028;Gelet de instemming van de Minister van Begroting gegeven op 4 april 2025;Gelet op het advies van de inspecteur van Financiën, gegeven op 10 januari 2025;Overwegende dat een krediet van vierhonderdéénennegentigduizend euro (491.000,00 euro) op de organisatieafdeling 12.58.52, activiteitenprogramma 58/5, basisallocatie 33.00.41 van de administratieve begroting van de FOD justitie voor het begrotingsjaar 2025 is ingeschreven;Overwegende de aanvraag voor een subsidie die de vzw "Çavaria" indiende op 1 oktober 2024 overeenkomstig artikel 13 van het voornoemde koninklijk besluit van 2 oktober 2023;Overwegende dat de vzw "Çavaria" voldoet aan de criteria vastgelegd in artikelen 8 en 10 van het voornoemde koninklijk besluit van 2 oktober 2023 en is erkend als een koepel van organisaties;Op de voordracht van de Minister van Gelijke Kansen;Hebben Wij besloten en besluiten Wij :Artikel 1.  § 1. Een toelage van zevenenveertigduizend tweehonderdtweeënvijftig euro en zeventig cent (47.252,70 euro) wordt toegekend aan de vzw "Çavaria", met zetel gevestigd te Kammerstraat 22, 9000 Gent (ondernemingsnummer 0415 652 423 en rekeningnummer IBAN BE 84 0682 1326 7459). § 2. De toelage is bedoeld ter financiële ondersteuning van de jaarlijkse werkingskosten in verband met de uitvoering van een werkprogramma in het kader van het federale beleid inzake bestrijding van discriminatie op grond van seksuele oriëntatie. Art. 2. De toelage bedoeld in artikel 1, wordt aangerekend op het activiteitenprogramma 58/5, basisallocatie 33.00.41, organisatieafdeling 12.58.52 van de administratieve begroting van de FOD Justitie voor het begrotingsjaar 2025.Art. 3. De periode waarop de toelage betrekking heeft, begint op 1 januari 2025 en eindigt op 31 maart 2025.Art. 4. De toelage bedoeld in artikel 1 wordt in twee schijven betaald, verdeeld op de volgende wijze:- een eerste schijf van negentig percent na ondertekening van dit besluit;- het saldo van tien percent na de voorlegging van het eindverslag van de activiteiten en de bewijsstukken voor de volledige toelage. Art. 5.  § 1. Worden aanvaard als subsidieerbare kosten:1°  de kosten voor de huur, de huurlasten en het onderhoud van de gebouwen;2°  de personeelskosten en de kosten voor de aanwerving van het personeel en voor het personeelsbeheer;3°  de missiekosten en reiskosten;4°  de opleidingskosten;5°  de kosten voor administratief en boekhoudkundig beheer;6°  de kantoor- en informaticakosten;7°  de kosten inzake logistiek, communicatie en kantooruitrusting. § 2. De subsidie dekt geen kosten die reeds gedekt zijn door een andere vorm van subsidiering.Art. 6.  § 1. De vereniging verstuurt uiterlijk op 3A maart 2026 het eindverslag van de activiteiten alsook de financiële bewijsstukken naar de dienst Gelijke Kansen (Waterloolaan 115, 1000 Brussel of naar het e-mailadres: equal@just.fgov.be). § 2. Het eindverslag van de activiteiten bevat minstens een algemene beschrijving van de verwezenlijkte werkzaamheden, een synthese van de gevoerde acties, een evaluatie van de behaalde doelstellingen, een beschrijving van de eventuele ondervonden problemen met inbegrip van de obstakels bij de tenuitvoerlegging van de acties, een beschrijving van de faciliterende factoren, alsook alle noodzakelijke informatie die de dienst Gelijke Kansen in staat moet stellen om de verwezenlijking van die activiteiten te evalueren. § 3. De vereniging verstuurt eveneens een samenvattende tabel van alle bewijsstukken van de op deze toelage aangerekende uitgaven, met referentie naar de uitgavencategorieën. § 4. Bij ontstentenis van de volledige overlevering van de documenten, namelijk het eindverslag van de activiteiten en de bewijsstukken voor de volledige toelage, wordt de tweede schijf van de toelage niet uitbetaald en wordt, in voorkomend geval, de eerste schijf teruggevorderd voor het gedeelte van het bedrag dat niet naar behoren, overeenkomstig dit artikel, is gemotiveerd.Art. 7.  § 1. De begunstigde moet:- de bepalingen van de toekenning van de toelage volledig nakomen. Indien dat niet het geval is, kan hem een volledige of gedeeltelijke terugbetaling van de toegekende toelage worden gevraagd;- met betrekking tot het goede besteding van deze toelage enige controle van stukken en/of ter plekke aanvaarden;- het publiek in elk bericht of bij elke publiciteit op de hoogte brengen van de financiële hulp die ze in het kader van deze toelage hebben ontvangen. § 2. In het geval dat de toelage onrechtmatig werd gebruikt, is de dienst Gelijke Kansen van de FOD Justitie belast met de terugvordering van de bedragen. § 3. Indien blijkt dat te veel toelage werd toegekend voor het afgelopen jaar, wordt een beslissing tot terugvordering ter kennis gebracht bij aangetekende brief. Na verloop van een termijn van dertig dagen wordt de beslissing tot terugvordering definitief, tenzij de vereniging opmerkingen heeft laten toekomen. In dat geval wordt de definitieve beslissing uiterlijk twee maanden na ontvangst van de opmerkingen ter kennis van de vereniging gebracht. De vereniging stort het verschuldigde bedrag uiterlijk drie maanden na de definitieve beslissing tot terugvordering terug.Art. 8. Dit besluit heeft uitwerking met ingang van 1 januari 2025.Art. 9. Het lid van de regering dat bevoegd is voor Gelijke Kansen is belast met de uitvoering van dit besluitGegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister voor Gelijke Kansen,R. BEENDERS 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 22 mei 2003 betreffende de organisatie van de begroting en van de comptabiliteit van de federale Staat, artikelen 121 tot 124 ;Gelet op de programmawet van 20 december 2020, artikel 91;Gelet op de wet van 23 december 2021 betreffende de Algemene uitgavenbegroting voor het begrotingsjaar 2022, artikel 2.06.4 ;Gelet op de wet van 26 december 2022 betreffende de Algemene uitgavenbegroting voor het begrotingsjaar 2023, artikel 2.06.4 ;Gelet op de wet van 22 december 2023 betreffende de Algemene uitgavenbegroting voor het begrotingsjaar 2024, artikel 2.06.4 ;Gelet op de wet van 29 november 2024 houdende de tweede aanpassing van de Algemene Uitgavenbegroting voor het begrotingsjaar 2024;Gelet op de financiënwet van 20 december 2024 voor het begrotingsjaar 2025 ;Gelet op de financiënwet van 25 maart 2025 voor het begrotingsjaar 2025 ;Gelet op het koninklijk besluit van 20 mei 2022 betreffende de administratieve, begrotings- en beheerscontrole, artikel 20 ;Gelet op het Nationaal herstel- en veerkrachtplan zoals goedgekeurd door de Ministerraad op 30 april 2021.Gelet op de verordening (EU) 2023/435 van het Europees parlement en de Raad van 27 februari 2023 tot wijziging van Verordening (EU) 2021/241 wat betreft REPowerEU-hoofdstukken in herstel- en veerkrachtplannen en tot wijziging van Verordeningen (EU) nr. 1303/2013, (EU) 2021/1060 en (EU) 2021/1755 en Richtlijn 2003/87/EGGelet op de uitvoeringsbeslissing van de Raad van de Europese unie van 6 juli 2021 betreffende de goedkeuring van de evaluatie van het Belgische herstel- en veerkrachtplan;Gelet op de uitvoeringsbeslissing van de Europese Raad van 13 juli 2021 (en zijn bijlage) met betrekking tot de goedkeuring van de evaluatie van het Belgische plan voor Herstel en Veerkracht;Gelet op het uitvoeringsbesluit van de Raad van de Unie van 8 december 2023 (en bijlage) dat het uitvoeringsbesluit van 13 juli 2021 wijzigt betreffende de goedkeuring van de beoordeling van het plan voor herstel en veerkracht voor België.Gelet op de verordening (EU) 2021/241 van het Europees parlement en van de Raad van de Europese unie van 12 februari 2021 tot instelling van de herstel- en veerkrachtfaciliteit.Gelet op de uitvoeringsbeslissing van de Europese Raad van 13 juli 2021 (en zijn bijlage) met betrekking tot de goedkeuring van de evaluatie van het Belgische plan voor Herstel en Veerkracht;Gelet op het uitvoeringsbesluit van de Raad van de Unie van 8 december 2023 (en bijlage) dat het uitvoeringsbesluit van 13 juli 2021 wijzigt betreffende de goedkeuring van de beoordeling van het plan voor herstel en veerkracht voor België.Gelet op het advies van de Inspectie van Financiën, gegeven op 10 oktober 2022 ;Gelet op het advies van de Inspectie van Financiën, gegeven op 18 oktober 2022 ;Gelet op het advies van de Inspectie van Financiën, gegeven op 7 november 2022 ;Gelet op het advies van de Inspectie van Financiën, gegeven op 24 juli 2023 ;Gelet op het advies van de Inspectie van Financiën, gegeven op 28 juli 2023;Gelet op het advies van de Inspectie van Financiën, gegeven op 16 november 2023;Gelet op het advies van de Inspectie van Financiën, gegeven op 19 december 2024Gelet op het advies van de Inspectie van Financiën, gegeven op 27 januari 2025;Overwegende het belang van een snelle uitvoering van het project dat is opgenomen in het door de Ministerraad van 30 april 2021 goedgekeurde Nationaal Plan voor Herstel en Veerkracht betreffende de investeringen in digitaliseringOp de voordracht van de Minister van Asiel en Migratie, en Maatschappelijke Integratie, belast met Grootstedenbeleid;Hebben Wij besloten en besluiten Wij :Artikel 1.  § 1. Er wordt in het kader van het "e-inclusion for Belgium" project (referentie I408034vBE-C[42]-I[I-4.08]) van het Europees herstel- en veerkrachtplan aan 51 OCMW's en 2 verenigingen van OCMW's een subsidie van samen maximaal vijf miljoen negenhonderdvierennegentig duizend vijfhonderdeenenvijftig euro (€ 5.994.551,00 EUR) toegekend ter dekking van de kosten die gepaard gaan met de verwezenlijking van projecten inzake digitale inclusie van kwetsbare groepen in onze maatschappij. § 2. De subsidie van vijf miljoen negenhonderdvierennegentig duizend vijfhonderdeenenvijftig euro (€ 5.994.551,00 EUR) wordt aan de 51 OCMW's en de 2 verenigingen van OCMW's verdeeld zoals vermeld in de bijlage van dit Koninklijk Besluit. § 3. Het bedrag van de subsidie komt overeen met het goedgekeurde bedrag voor het laatste werkingsjaar van het uit te voeren project. § 4. Het subsidiebedrag werd uitgesplitst in een bedrag exclusief en een bedrag inclusief btw. In geval van onduidelijkheid werd een correctie doorgevoerd om de btw te berekenen zonder het maximumbedrag van de toegekende subsidiebedrag te overschrijden. § 5. Alleen bedragen exclusief btw kunnen ten laste van het herstel- en veerkrachtplan worden gebracht. De btw wordt gedragen door de Belgische staat. § 6. Het subsidiebedrag zal worden aangerekend op de basisallocatie 06.41.14.43.52 van de Algemene uitgavenbegroting van het begrotingsjaar 2024.Art. 2. Het Digilab team van de POD Maatschappelijke Integratie, Administratief Centrum Kruidtuin - Finance Tower, Kruidtuinlaan 50 bus 165, 1000 Brussel, is belast met het administratieve beheer van het project "e-inclusion for Belgium".Art. 3.  § 1. Binnen drie maanden na de ondertekening van dit koninklijk besluit wordt een protocol, opgesteld op basis van de gegevens in het aanvraagdossier, gesloten tussen de begunstigde van de subsidie en de POD Maatschappelijke Integratie. Daarin worden de doelstellingen van het project, de wijze van uitvoering, de samenwerking tussen de partijen, de sancties, de verslaglegging en de verplichtingen van de begunstigde gespecificeerd in het kader van Herstel- en veerkrachtfaciliteit. § 2. De uitvoering van het project moet geschieden op de in het protocol beschreven wijze.Art. 4. De subsidie dekt de uitgaven in de periode van 1 november 2024 tot en met 31 oktober 2025.Art. 5.  § 1. De subsidie kan alleen de kosten in verband met het project dekken die zijn aangegeven in het aanvraagdossier ingediende financiële plan of waarvoor een wijzigingsverzoek is goedgekeurd door Digilab en die kunnen worden gefinancierd in het kader van het Europees herstel- en veerkrachtplan. § 2. Dubbele financiering van projectkosten is strikt verboden. § 3. Het betreft kosten die verband houden met de uitvoering van volgende goedgekeurde projecten:1. Het project "Digiclusie Gent" van het OCMW van Gent 2. Het project "Digikar" van het OCMW van Puurs-Sint-Amands 3. Het project "Allemaal Digitaal!" van het OCMW van Bilzen 4. Het project "E-Trust" van het OCMW van Oostende 5. Het project "De Welzijnsapp #VANRSL" van het OCMW van Roeselare 6. Het project "Digiplek" van het OCMW van Halle 7. Het project "W(ijze)W(eb)Wijkfiguren" van het OCMW van Wingene 8. Het project "Eeklo digitaal sterker" van het OCMW van Eeklo 9. Het project "Vlotte Balie" van het OCMW van Genk 10. Het project "Digitaal voor elke Maldegemnaar" van het OCMW van Maldegem 11. Het project "Digit-Help" van het OCMW van Waterloo 12. Het project "cyber(wo)man" van het OCMW van Eigenbrakel 13. Het project "l'e-inclusion pour tous" van het OCMW van Ans 14. Het project "Le monde numérique et moi" van het OCMW van Anderlues 15. Het project "Digi-Connect 2.0" van het OCMW van Luik 16. Het project "Femmes Connectées" van het OCMW van Lessen 17. Het project "E-Wel" van het OCMW van Welkenraedt 18. Het project "Soutien Numérique pour tous" van het OCMW van Montigny-le-Tilleul 19. Het project "Connect&amp;Vous@Fléron" van het OCMW van Fléron 20. Het project "Projet POINT.com" van het OCMW van Plombières 21. Het project "L'Atelier numérique" van het OCMW van Doornik 22. Het project "L'Appui numérique" van het OCMW van Flémalle 23. Het project "SPOT en réseau" van de Vereniging van OCMW's Hoofdstuk XII bestaande uit Aywaille, Beyne-Heusay, Chaudfontaine, Fléron, Sprimont en Trooz 24. Het project "Numérique pour tous" van het OCMW van Jemeppe-sur-Sambre 25. Het project "Clic'Mobile" van het OCMW van Oudergem 26. Het projet "Tous Connectées" van het OCMW van Ganshoren 27. Het project "Digiscan Brugge" van het OCMW Brugge 28. Het project "Digivaardig Sint-Niklaas" van het OCMW Sint-Niklaas 29. Het project "Digitale Brugfiguren" van het OCMW Kortrijk 30. Het project "Regionaal Samenwerken W13" van de welzijnsvereniging W13 31. Het project "Reach out for e-inclusion" van het OCMW van Beerse 32. Het project "Lokaal Digitaal" van het OCMW van Oud-Heverlee 33. Het project "DIGI Care" van het OCMW Temse 34. Het project "Cyber Rogier et Formations" van het OCMW van Schaarbeek 35. Het project "Num@tic" van het OCMW van de Stad Brussel 36. Het project "TIC@Jette" van het OCMW van Jette 37. Het project "Molenbeek e-inclusion" van het OCMW van Molenbeek 38. Het project "La Maison du Numérique 1190" van het OCMW van Vorst 39. Het project "Connect1060" van het OCMW van Sint-Gillis 40. Het project "Digital Buddies" van het OCMW van Evere 41. Het project "Informaticien pour tous!" van het OCMW van Sint-Agatha-Berchem 42. Het project "Numéri'Bus" van het OCMW van Yvoir 43. Het project "Ensemble, pour le numérique!" van het OCMW van Ottignies - Louvain-la-Neuve 44. Het project "Digital pour Tous" van het OCMW van Morlanwelz 45. Het project "Inclusion numérique à Ramillies et Perwez" van het OCMW van Ramillies 46. Het project "E-inclusion pour tou(te)s" van het OCMW van La Louvière 47. Het project "DigiCap" van het OCMW van Zinnik 48. Het project "E-inclusion - CPAS Namur" van het OCMW van Namen 49. Het project "En marche pour l'e-inclusion" van het OCMW van Marche-en-Famenne 50. Het project "Digithurlu" van het OCMW van Moeskroen 51. Het project "e-permanences" van het OCMW van Les Bons Villers 52. Het OCMW-project "Clic... Tous connectés" van Charleroi 53. Het project "Auberge digit@le" van het OCMW van Thuin § 4. De organisaties zijn verplicht naast de subsidie een cofinanciering te voorzien. Deze cofinanciering moet bijdragen aan de verduurzaming van het project na afloop van de subsidie, zoals beoogd in de doelstellingen van de projectoproepen "e-inclusion for Belgium" uit 2022 en 2023 gericht op OCMW's. Het bedrag van de cofinanciering dient 20% te bedragen van de totale uitgaven die in het lopende jaar voor dit project worden gemaakt. § 5. Het niet voorzien in de vereiste cofinanciering zal resulteren in een vermindering van de toegekende subsidie. De vermindering zal proportioneel worden berekend op basis van het tekort aan de vereiste cofinanciering. § 6. Het inzetten van cofinanciering afkomstig uit andere Europese bronnen is strikt verboden.Art. 6.  § 1. Voor het laatste werkingsjaar wordt er geen voorschot uitbetaald. § 2. De subsidie wordt aan de begunstigde betaald, evenredig met de gedane uitgaven en met inachtneming van de bepalingen in artikel 7 en artikel 8, onder voorbehoud van : a) de verwezenlijking van de in het protocol opgenomen doelstellingen van het project en de conformiteit ervan met betrekking tot de in het herstel- en veerkrachtplan bepaalde mijlpalen/doelstellingen van het project "e-inclusion for Belgium"; b) De verwezenlijking van gepaste maatregelen om de financiële belangen van de Unie te beschermen en erover waken dat het gebruik van de fondsen in het kader van de door de faciliteit ondersteunde maatregelen het Belgisch en Europees juridisch kader respecteren, in het bijzonder wat de preventie, de opsporing en de bestrijding van de fraude, de corruptie en de belangenconflicten in artikel 22 van het Europees reglement (EU) 2021/241 betreft, vormt een verplichting en een voorwaarde voor de toekenning van de toelage. c) In geval van fraude, corruptie, belangenconflicten en dubbele financiering ten nadele van de financiële belangen van de Unie wordt de subsidie in haar geheel of gedeeltelijk verminderd. Bij de vaststelling van het bedrag van de terugvordering en de verlaging, of van het bedrag dat vroegtijdig moet worden terugbetaald, neemt de staat het evenredigheidsbeginsel in acht en houdt hij rekening met de ernst van de fraude, de corruptie en de belangenconflicten die de financiële belangen van de Unie schaden, of met de niet-nakoming van een verplichting. Bij het vaststellen van de toe te passen financiële correcties zal rekening worden gehouden met de richtsnoeren van de Europese Commissie voor het bepalen van de financiële correcties die moeten worden toegepast in geval van niet-naleving van de regels inzake overheidsopdrachten.het opmaken van terugbetalingsaanvragen vergezeld van de in artikel 7 paragraaf 4 genoemde documenten, waaruit onder meer de materialiteit en het bedrag van de aangegeven kosten blijkt.Art. 7.  § 1. Om de subsidie te verkrijgen, moet de organisatie twee terugbetalingsaanvragen indienen. § 2. De eerste terugbetalingsaanvraag heeft betrekking op uitgaven tussen 1 november 2024 en april 2025. Deze moet uiterlijk op 15 mei 2025 aan Digilab worden verzonden.Deze eerste terugbetalingsaanvraag moet vergezeld gaan van de in artikel 7 paragraaf 4 beschreven documenten om verificatie van die uitgaven mogelijk te maken.Het bedrag van de eerste terugbetalingsaanvraag wordt betaald, na goedkeuring van de door de begunstigde ingediende documenten en mits aan de in artikel 7 paragraaf 8 genoemde eisen wordt voldaan.De hoogte van het bedrag van de eerste terugbetalingsaanvraag mag niet meer bedragen dan 60% van het totale subsidiebedrag. Indien het ingediende bedrag van de terugbetalingsaanvraag het vastgestelde percentage overschrijdt, zal het terugbetalingsbedrag worden aangepast en beperkt tot maximaal 60% van het totale subsidiebedrag, rekening houdend met de door de administratie goedgekeurde kosten. § 3. De tweede terugbetalingsaanvraag heeft betrekking op uitgaven die zijn gedaan tussen 1 november 2024 en oktober 2025 en die niet zijn opgenomen in de eerste terugbetalingsaanvraag.Deze tweede terugbetalingsaanvraag moet uiterlijk op 17 november 2025 aan Digilab worden verzonden. Deze moet ook vergezeld gaan van de in artikel 7 paragraaf 4 beschreven documenten met betrekking tot de in deze terugbetalingsaanvraag opgegeven uitgaven (om verificatie van die uitgaven mogelijk te maken).Het bedrag van de tweede terugbetalingsaanvraag, dat ten hoogste overeenkomt met het saldo van de subsidie, wordt betaald na goedkeuring van de door de begunstigde ingediende documenten en mits aan de in artikel 7 paragraaf 8 genoemde eisen wordt voldaan. § 4. Om ontvankelijk te zijn moet elke aanvraag vergezeld gaan van de volgende documenten : - een financieel verslag over de uitgaven die in het kader van het project zijn gedaan. De inhoud van het financieel verslag wordt in artikel 7 paragraaf 5 nader toegelicht; - alle boekhoudkundige documenten, originelen of leesbare kopieën, die de in het financieel verslag vermelde uitgaven rechtvaardigen. Al deze documenten moeten worden genummerd volgens een voorgeschreven methode (toegelicht in het protocol) zodat deze gemakkelijk gelinkt kunnen worden met de gegevens in het financieel verslag. De aanvrager verbindt zich ertoe de originelen gedurende de wettelijk voorgeschreven termijnen te bewaren en op verzoek van de administratie ter beschikking te stellen. - alle aanvullende bewijsstukken die nodig zijn om aan te tonen dat de gedane uitgaven rechtstreeks verband houden met de mijlpalen/doelstellingen van het "e-inclusion for Belgium" project zoals goedgekeurd in het herstel- en veerkrachtplan ; - een verklaring op eer dat : e) de projectuitgaven niet dubbel worden gefinancierd ; f) alle ingediende facturen zijn betaald.Indien dit niet het geval is, moet Digilab hiervan onverwijld in kennis worden gesteld. Dit deel van de subsidie wordt dan niet betaald of moet worden terugbetaald. - een document met de naam, voornaam en geboortedatum van de wettelijke vertegenwoordigers van de dienstverleners aan wie in het kader van het project een betaling is gedaan en wie vrijgesteld zijn van registratie in het UBO register.een activiteitenverslag in waarin onder meer de in het kader van het project ondernomen acties en de mate waarin de doelstellingen en resultaten zijn bereikt, worden aangetoond. § 5. De financiële verslagen dienen een gedetailleerde overzichtstabel te bevatten van de gemaakte uitgaven, inclusief de bijbehorende betalingsbewijzen, waarmee de organisaties waaraan de betalingen zijn verricht kunnen worden geïdentificeerd (naam, KBO-nummer, adres), met vermelding van het bedrag exclusief btw en het btw-bedrag. Daarnaast dient een grondige toelichting te worden verstrekt over de relevantie van de uitgaven en het verband met het project. § 6. De financiële verslagen en activiteitenverslagen worden uitsluitend opgesteld op basis van het door Digilab verstrekte modellen en voldoen aan de in het protocol gespecifieerde vereisten. § 7. Terugbetalingsaanvragen en andere in artikel 7 paragraaf 4 genoemde documenten moeten bij Digilab worden ingediend via het elektronische systeem voor projecttoezicht. § 8. De uitbetaling van de terugbetalingsaanvraag zal worden geweigerd of het gevorderde bedrag zal niet volledig worden betaald: - in geval van niet-naleving van de bepalingen van dit koninklijk besluit ; - in geval van één of meerdere ontbrekende, onvolledige of buiten de termijn verzonden document (in het kader van de in artikel 7 paragraaf 4 gevraagde documenten) ;in geval van één of meerdere bewijsstukken, financiële verslagen of activiteitenverslagen die geen onweerlegbaar bewijs leveren dat de subsidie overeenkomstig de voorschriften is gebruikt.Art. 8. De begunstigde van de subsidie is verplicht de betaalde bedragen onverwijld terug te betalen : - in geval van onaanvaardbare, onvolledige of niet-conforme uitvoering van het project met betrekking tot de mijlpalen/doelstellingen van het project "e-inclusion for Belgium" zoals goedgekeurd in het herstel- en veerkrachtplan;in geval van niet-naleving van de voorwaarden van dit koninklijk besluit of het protocol.Art. 9.  § 1. Digilab zal één of meer controles ter plaatse uitvoeren om na te gaan of de uitvoering van het project beantwoordt aan de in het protocol omschreven doelstellingen en dat de subsidie wordt gebruikt overeenkomstig de geldende regelgeving. § 2. Een externe audit kan worden verricht door de bevoegde federale of Europese autoriteiten. § 3. Indien de begunstigde van de subsidie de controle(s) belemmert, is hij verplicht de betaalde bedragen onverwijld terug te betalen.Art. 10. Op het einde van het laatste jaar van het project vindt een evaluatie plaats. Digilab is belast met deze evaluatie.Art. 11.  § 1. Het Belgische en Europese juridische kader betreffende het gebruik van middelen in het kader van het herstel- en herstelplan moeten door de organisatie en diens partners worden nageleefd.Het is de verantwoordelijkheid van organisatie ervoor te zorgen dat de wettelijke kaders door diens partners worden nageleefd. § 2. Bij de uitvoering van het project moet met name het DNSH-beginsel ("Do No Significant Harm") in acht worden genomen.Het niet naleven van het DNSH-beginsel kan ertoe leiden dat de subsidie moet worden terugbetaald.Art. 12. De Minister voor Maatschappelijke Integratie is belast met de uitvoering van dit besluit.Gegeven te Brussel, 17 mei 2025.FILIPVan Koningswege :De Minister van Asiel en Migratie, en Maatschappelijke Integratie, belast met GrootstedenbeleidA. VAN BOSSUYT   </t>
         </is>
       </c>
     </row>
@@ -588,28 +588,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025003812</t>
+          <t>2025003952</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5 mei 2025. - Koninklijk besluit houdende toekenning van een toelage aan de vzw "Prisme" voor het budgettair jaar 2025</t>
+          <t>17 mei 2025. - Koninklijk besluit tot bepaling van de voorwaarden en de modaliteiten overeenkomstig dewelke de verplichte verzekering voor geneeskundige verzorging en uitkeringen een financiële tegemoetkoming verleent aan de vroedvrouwen voor gebruik van telematica en het elektronisch beheer van de medische dossiers in 2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-20&amp;numac_search=2025003812&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003812=4&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025003952&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003952=4&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 22 mei 2003 houdende organisatie van de begroting en van de comptabiliteit van de federale Staat, op de artikelen 121 tot 124;Gelet op de wet van 10 mei 2007 ter bestrijding van bepaalde vormen van discriminatie, artikel 32/1;Gelet op de financiewet voor begrotingsjaar van 20 december 2024 op sectie 12 - FOD Justitie, programma 58/5 - Diversiteit, Interculturaliteit en Gelijkheid van Kansen;Gelet op het koninklijk besluit van 20 mei 2022 betreffende de administratieve, begrotings- en beheerscontrole;Gelet op het koninklijk besluit van 2 oktober 2023 betreffende de modaliteiten voor de toekenning van de jaarlijkse subsidies voor de koepels van niet-gouvernementele organisaties die actief zijn in het domein van de bestrijding van discriminatie op grond van seksuele oriëntatie voor wat betreft de materies die behoren tot de bevoegdheid van de federale overheid;Gelet op het ministerieel besluit van 22 maart 2024 tot erkenning van de koepels van niet-gouvernementele organisaties die actief zijn in het domein van de bestrijding van discriminatie op grond van seksuele oriëntatie voor wat betreft de materies die behoren tot de bevoegdheid van de federale overheid, voor de erkenningscyclus van 2024-2028;Gelet de instemming van de Minister van Begroting gegeven op 4 april 2025;Gelet op het advies van de inspecteur van Financiën, gegeven op 10 januari 2025;Overwegende dat een krediet van vierhonderdéénennegentigduizend euro (491.000,00 euro) op de organisatieafdeling 12.58.52, activiteitenprogramma 58/5, basisallocatie 33.00.41 van de administratieve begroting van de FOD justitie voor het begrotingsjaar 2025 is ingeschreven;Overwegende de aanvraag voor een subsidie die de vzw "Prisme" indiende op 1 oktober 2024 overeenkomstig artikel 13 van het voornoemde koninklijk besluit van 2 oktober 2023;Overwegende dat de vzw "Prisme" voldoet aan de criteria vastgelegd in artikelen 8 en 10 van het voornoemde koninklijk besluit van 2 oktober 2023 en is erkend als een koepel van organisaties;Op de voordracht van de Minister van Gelijke Kansen;Hebben Wij besloten en besluiten Wij :Artikel 1.  § 1. Een toelage van vierenveertigduizend zeshonderdzevenentwintig euro en vijfenvijftig cent euro (44.627,55 euro) wordt toegekend aan de vzw "Prisme", met zetel gevestigd te Rue Pierreuse 25, 4000 Luik (ondernemingsnummer 0890 447 429 en rekeningnummer IBAN BE 82 0682 4796 5268). § 2. De toelage is bedoeld ter financiële ondersteuning van de jaarlijkse werkingskosten in verband met de uitvoering van een werkprogramma in het kader van het federale beleid inzake bestrijding van discriminatie op grond van seksuele oriëntatie. Art. 2. De toelage bedoeld in artikel 1, wordt aangerekend op het activiteitenprogramma 58/5, basisallocatie 33.00.41, organisatieafdeling 12.58.52 van de administratieve begroting van de FOD Justitie voor het begrotingsjaar 2025.Art. 3. De periode waarop de toelage betrekking heeft, begint op 1 januari 2025 en eindigt op 31 maart 2025.Art. 4. De toelage bedoeld in artikel 1 wordt in twee schijven betaald, verdeeld op de volgende wijze:- een eerste schijf van negentig procent na ondertekening van dit besluit;- de tweede schijf van tien procent na de voorlegging van het eindverslag van de activiteiten en de bewijsstukken voor de volledige toelage. Art. 5.  § 1. Worden aanvaard als subsidieerbare kosten:1°  de kosten voor de huur, de huurlasten en het onderhoud van de gebouwen;2°  de personeelskosten en de kosten voor de aanwerving van het personeel en voor het personeelsbeheer;3°  de missiekosten en reiskosten;4°  de opleidingskosten;5°  de kosten voor administratief en boekhoudkundig beheer;6°  de kantoor- en informaticakosten;7°  de kosten inzake logistiek, communicatie en kantooruitrusting. § 2. De subsidie dekt geen kosten die reeds gedekt zijn door een andere vorm van subsidiering.Art. 6.  § 1. De vereniging verstuurt uiterlijk op 31 maart 2026 het eindverslag van de activiteiten alsook de financiële bewijsstukken naar de dienst Gelijke Kansen (Waterloolaan 115, 1000 Brussel of naar het e-mailadres: equal@just.fgov.be). § 2. Het eindverslag van de activiteiten bevat minstens een algemene beschrijving van de verwezenlijkte werkzaamheden, een synthese van de gevoerde acties, een evaluatie van de behaalde doelstellingen, een beschrijving van de eventuele ondervonden problemen met inbegrip van de obstakels bij de tenuitvoerlegging van de acties, een beschrijving van de faciliterende factoren, alsook alle noodzakelijke informatie die de dienst Gelijke Kansen in staat moet stellen om de verwezenlijking van die activiteiten te evalueren. § 3. De vereniging verstuurt eveneens een samenvattende tabel van alle bewijsstukken van de op deze toelage aangerekende uitgaven, met referentie naar de uitgavencategorieën. § 4. Bij ontstentenis van de volledige overlevering van de documenten, namelijk het eindverslag van de activiteiten en de bewijsstukken voor de volledige toelage, wordt de tweede schijf van de toelage niet uitbetaald en wordt, in voorkomend geval, de eerste schijf teruggevorderd voor het gedeelte van het bedrag dat niet naar behoren, overeenkomstig dit artikel, is gemotiveerd.Art. 7.  § 1. De begunstigde moet:- de bepalingen van de toekenning van de toelage volledig nakomen. Indien dat niet het geval is, kan hem een volledige of gedeeltelijke terugbetaling van de toegekende toelage worden gevraagd;- met betrekking tot het goede besteding van deze toelage enige controle van stukken en/of ter plekke aanvaarden;- het publiek in elk bericht of bij elke publiciteit op de hoogte brengen van de financiële hulp die ze in het kader van deze toelage hebben ontvangen. § 2. In het geval dat de toelage onrechtmatig werd gebruikt, is de dienst Gelijke Kansen van de FOD Justitie belast met de terugvordering van de bedragen. § 3. Indien blijkt dat te veel toelage werd toegekend voor het afgelopen jaar, wordt een beslissing tot terugvordering ter kennis gebracht bij aangetekende brief. Na verloop van een termijn van dertig dagen wordt de beslissing tot terugvordering definitief, tenzij de vereniging opmerkingen heeft laten toekomen. In dat geval wordt de definitieve beslissing uiterlijk twee maanden na ontvangst van de opmerkingen ter kennis van de vereniging gebracht. De vereniging stort het verschuldigde bedrag uiterlijk drie maanden na de definitieve beslissing tot terugvordering terug.Art. 8. Dit besluit heeft uitwerking met ingang van 1 januari 2025.Art. 9. Het lid van de regering dat bevoegd is voor Gelijke Kansen is belast met de uitvoering van dit besluitGegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister voor Gelijke Kansen,R. BEENDERS 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, artikel 36sexies, ingevoegd bij de wet van 22 augustus 2002 en gewijzigd bij de wet van 22 december 2003;Gelet op het voorstel van de Overeenkomstencommissie vroedvrouwen - verzekeringsinstellingen, gedaan op 21 mei 2024;Gelet op het advies van de Commissie voor begrotingscontrole, gegeven op 5 juni 2024;Gelet op het advies van het Comité van de verzekering voor geneeskundige verzorging, gegeven op 10 juni 2024;Gelet op het advies van de inspecteur van Financiën, gegeven op 26 juni 2024;Gelet op de weigering van akkoordbevinding van de Staatssecretaris voor Begroting van 26 juli 2024; Gelet op de regelgevingsimpactanalyse, uitgevoerd overeenkomstig de artikelen 6 en 7 van de wet van 15 december 2013 houdende diverse bepalingen inzake administratieve vereenvoudiging;Gelet op het besluit van de Ministerraad van 20 december 2024 om voorbij te gaan aan de weigering van akkoordbevinding van de Staatssecretaris voor Begroting;Gelet op advies 77.382/2 van de Raad van State, gegeven op 6 februari 2025, met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Gelet op het advies nr. 21/2025 van 9 april 2025 van de Gegevensbeschermingsautoriteit, gegeven op 9 april 2025;Op de voordracht van de Minister van Sociale Zaken en op het advies van de in Raad vergaderde Ministers,Hebben Wij besloten en besluiten Wij :HOOFDSTUK 1. - Inleidende bepalingArtikel 1. Dit besluit bepaalt de voorwaarden en de modaliteiten waaronder een vroedvrouw een tegemoetkoming van het RIZIV kan krijgen in de kosten verbonden aan het gebruik van telematica en het elektronisch beheer van de dossiers van de rechthebbende in 2024.HOOFDSTUK 2. - DefinitiesArt. 2. Voor de toepassing van dit besluit wordt verstaan onder:1°  de vroedvrouw : De vroedvrouw die door de bevoegde Minister is erkend en over een RIZIV-nummer beschikt dat aan de vroedvrouw is voorbehouden;2°  premiejaar: het kalenderjaar 2024 waarvoor de tegemoetkoming toegekend wordt;3°  MyCareNet : het elektronisch netwerk bedoeld in artikel 5 van het koninklijk besluit van 18 september 2015 tot uitvoering van artikel 53, § 1 van de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, betreffende de derdebetalersregeling.HOOFDSTUK 3. - ToekenningsvoorwaardenAfdeling 1. - Voorwaarden inzake de effectieve activiteit als vroedvrouwArt. 3. Om deze tegemoetkoming te genieten moet de vroedvrouw beantwoorden aan volgende voorwaarden:1°  individueel toetreden tot de nationale overeenkomst tussen de vroedvrouwen en de verzekeringsinstellingen, die is gesloten door de Overeenkomstencommissie die is bedoeld in artikel 26 van de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, voor het volledig premiejaar ; voor het premiejaar waarin de vroedvrouw voor het eerst geregistreerd is bij het RIZIV, volstaat het om zich tijdens dat jaar aan te sluiten bij de overeenkomst;2°  een minimumactiviteit hebben van 250 verstrekkingen die in het premiejaar 2024 terugbetaald zijn door de verplichte verzekering voor geneeskundige verzorging en uitkeringen, op basis van artikel 9 a) van de nomenclatuur van de geneeskundige verstrekkingen; of een activiteit hebben van minimum 3.750 V-waarden aan terugbetaalde verstrekkingen in het premiejaar 2024, opgenomen in artikel 9, a) van de nomenclatuur van de geneeskundige verstrekkingen.Afdeling 2. - Voorwaarden inzake het effectief gebruik van telematica en het elektronisch beheer van dossiers van de rechthebbendeArt. 4. In het premiejaar 2024 moet de vroedvrouw de volgende gebruiksdrempels bereiken:De vroedvrouw maakt gedurende het premiejaar via zijn softwarepakket gebruik van de dienst MyCareNet voor de raadpleging van de verzekerbaarheid van de patiënten en voldoet aan de minimale drempel van minstens 150 raadplegingen gedurende het premiejaar;De vroedvrouw maakt gedurende het premiejaar via zijn softwarepakket gebruik van de dienst MyCareNet voor het elektronisch factureren. Gedurende het premiejaar rekent hij minstens 40% van de verstrekkingen aangerekend via derdebetalersregeling, aan via elektronische weg.HOOFDSTUK 4. - Bedrag van de tegemoetkomingArt. 5. Het bedrag van het premiejaar bedraagt 800 euro.HOOFDSTUK 5. - ToekenningsmodaliteitenArt. 6. Voor het bekomen van de tegemoetkoming dient de vroedvrouw een aanvraag tot tegemoetkoming in bij de Dienst voor geneeskundige verzorging van het RIZIV, die volgende elementen bevat:1°  Het RIZIV-nummer van de betrokken vroedvrouw;2°  Het premiejaar waarvoor zij de tegemoetkoming vraagt;3°  Het rekeningnummer waarop de tegemoetkoming moet gestort worden.Art. 7. Op straffe van verval moet de aanvraag bedoeld in artikel 6, uiterlijk op 31 oktober van het jaar volgend op het premiejaar aan de Dienst voor geneeskundige verzorging van het RIZIV overgemaakt worden, volgens de modaliteiten gepubliceerd op de website van dit Instituut. De aanvraag wordt elektronisch ingediend via een door het RIZIV ter beschikking gestelde webtoepassing.Art. 8. Het RIZIV zal de bij haar beschikbare informatie inzake `effectieve activiteit als vroedvrouw' (her)gebruiken voor de verificatie van de in artikel 3, 2°  bedoelde voorwaarden voor het premiejaar.De gegevens die toelaten na te gaan of de vroedvrouw de in artikel 4 bedoelde minimumdrempel bereikt, worden aangeleverd via de in voornoemd artikel vermelde dienst.Art. 9. Na het indienen van de aanvraag tot tegemoetkoming, beslist de Dienst voor geneeskundige verzorging van het RIZIV of de vroedvrouw in aanmerking komt en deelt deze beslissing aan de vroedvrouw mee.Art. 10. De premie wordt aan de vroedvrouw die in aanmerking komt voor een tegemoetkoming uiterlijk op 31 december van het jaar volgend op het premiejaar betaald.Art. 11. De vroedvrouw heeft de mogelijkheid om de in artikel 9 bedoelde beslissing te betwisten bij de leidend ambtenaar van de Dienst voor geneeskundige verzorging van het RIZIV volgens de modaliteiten gepubliceerd op voornoemde website van het RIZIV, op straffe van onontvankelijkheid binnen de zestig dagen te rekenen vanaf de datum van de kennisgeving van de beslissing. Art. 12. Persoonsgegevens die in het kader van deze premie worden verwerkt, worden bewaard gedurende een periode van tien jaar vanaf de datum van betaling van de premie of, in geval van een besluit om de premie niet toe te kennen, vanaf de datum van dat besluit.HOOFDSTUK 6. - SlotbepalingenArt. 13. Dit besluit is van toepassing voor het premiejaar 2024.Art. 14. De Minister bevoegd voor Sociale Zaken is belast met de uitvoering van dit besluit.Gegeven te Brussel, 17 mei 2025.FILIPVan Koningswege :De Minister van Sociale Zaken en Volksgezondheid,F. VANDENBROUCKE 
 </t>
         </is>
       </c>
@@ -620,28 +620,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025003735</t>
+          <t>2025004014</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21 mei 2025</t>
+          <t>30 mei 2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5 mei 2025. - Koninklijk besluit houdende benoeming van de vertegenwoordiger van de Minister van Financiën bij de Nationale Bank van België</t>
+          <t>17 mei 2025. - Koninklijk besluit houdende uitvoering van artikel 147, vierde lid, van het Wetboek van de inkomstenbelastingen 1992 voor het aanslagjaar 2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-21&amp;numac_search=2025003735&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003735=5&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-30&amp;numac_search=2025004014&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025004014=5&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 22 februari 1998 tot vaststelling van het organiek statuut van de Nationale Bank van België, artikel 22;Gelet op artikel 41 van de statuten van de Nationale Bank van België, goedgekeurd bij koninklijk besluit van 18 september 2022;Gelet op het koninklijk besluit van 9 februari 2024 houdende benoeming van de vertegenwoordiger van de Minister van Financiën bij de Nationale Bank van België;Op de voordracht van de Vice-eersteminister en Minister van Financiën,Hebben Wij besloten en besluiten Wij :Artikel 1. Wesley De Visscher wordt benoemd tot vertegenwoordiger van de Minister van Financiën bij de Nationale Bank van België ter vervanging van de heer Filip Van de Velde.Art. 2. Dit besluit treedt in werking op 1 mei 2025.Art. 3. De Minister bevoegd voor Financiën is belast met de uitvoering van dit besluit.Gegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Vice-eersteminister en Minister van Financiën,J. JAMBON 
+VERSLAG AAN DE KONINGSire,Artikel 147, vierde lid, van het Wetboek van de inkomstenbelastingen 1992 (WIB 92) bepaalt dat wanneer voor een bepaald aanslagjaar de belasting op pensioenen en andere vervangingsinkomsten of op werkloosheidsuitkeringen na toepassing van de basisvermindering en de aanvullende vermindering voor pensioenen en vervangingsinkomsten of voor werkloosheidsuitkeringen niet tot nul is teruggebracht voor een belastingplichtige met een belastbaar inkomen dat gelijk is aan 10.160 euro (basisbedrag) en uitsluitend bestaat uit pensioenen en andere vervangingsinkomsten of werkloosheidsuitkeringen, de Koning het bedrag van de aanvullende vermindering verhoogt tot het bedrag dat nodig is om de belasting alsnog tot nul terug te brengen.Voor het aanslagjaar 2026 is het bedrag van de basisvermindering voor pensioenen en andere vervangingsinkomsten en van de basisvermindering voor werkloosheidsuitkeringen gelijk aan 2.219,27 euro (basisbedrag: 1.148,93 euro) en het bedrag van de aanvullende vermindering gelijk aan 456,59 euro (basisbedrag: 236,38 euro). Het in artikel 147, vierde lid, WIB 92 vermelde bedrag van het belastbare inkomen is voor het aanslagjaar 2026 gelijk aan 19.630 euro. De basisbelasting op dat inkomen bedraagt (16.320 x 25 pct.) + ((19.630 - 16.320) x 40 pct.) of 4.080 + 1.324 = 5.404 euro. Voor aanslagjaar 2026 bedraagt het bedrag van de belastingvrije som 10.910 euro. De basisbelasting wordt zo verminderd met 2.727,50 euro (10.910 euro x 25 pct.) tot 2.676,50 euro (om te slane belasting). De som van de basisvermindering en de aanvullende vermindering voor pensioenen en andere vervangingsinkomsten of van de basisvermindering en de aanvullende vermindering voor werkloosheidsuitkeringen, i.c. 2.219,27 + 456,59 = 2.675,86 euro, volstaat net niet om het bedrag van de verschuldigde belasting na toepassing van de verminderingen voor pensioenen en andere vervangingsinkomsten of voor werkloosheidsuitkeringen op nul te brengen. Overeenkomstig artikel 147, vierde lid, WIB 92 moet het geïndexeerde bedrag van de aanvullende vermindering voor pensioenen en andere vervangingsinkomsten en van de aanvullende vermindering voor werkloosheidsuitkeringen derhalve voor het aanslagjaar 2026 met 0,64 euro worden verhoogd tot 457,23 euro. Dit besluit geeft hieraan uitvoering.Het in artikel 147, eerste lid, 1°,  en 7°,  WIB 92 vermelde basisbedrag van de aanvullende vermindering wordt geïndexeerd aan de hand van de coëfficiënt als bedoeld in artikel 178, § 3, derde lid, 2°,  WIB 92 en na toepassing van de indexeringscoëfficiënt afgerond tot de hogere of lagere cent naargelang het cijfer van de duizendsten al dan niet 5 bereikt (artikel 178, § 2, derde lid, WIB 92). De in artikel 178, § 3, derde lid, 2°,  WIB 92 bedoelde indexeringscoëfficiënt is voor het aanslagjaar 2026 gelijk aan 1,9316. Om tot een geïndexeerd bedrag van 457,23 euro te komen, moet het basisbedrag van 236,38 euro worden verhoogd tot 236,71 euro.Het nieuwe basisbedrag van 236,71 euro geldt overeenkomstig artikel 147, vierde lid, laatste zin, WIB 92 enkel voor het aanslagjaar 2026.Dit is, Sire, de draagwijdte van het besluit dat U wordt voorgelegd.Ik heb de eer te zijn,Sire,Van Uwe Majesteit,de zeer eerbiedige en zeer getrouwe dienaar,De Minister van Financiën,J. JAMBONADVIES 77.591/3 VAN 25 APRIL 2025 OVER EEN ONTWERP VAN KONINKLIJK BESLUIT `HOUDENDE UITVOERING VAN ARTIKEL 147, VIERDE LID, VAN HET WETBOEK VAN DE INKOMSTENBELASTINGEN 1992 VOOR HET AANSLAGJAAR 2026'Op 27 maart 2025 is de Raad van State, afdeling Wetgeving, door de Minister van Financiën verzocht binnen een termijn van dertig dagen een advies te verstrekken over een ontwerp van koninklijk besluit `houdende uitvoering van artikel 147, vierde lid, van het Wetboek van de inkomstenbelastingen 1992 voor het aanslagjaar 2026'.Het ontwerp is door de derde kamer onderzocht op 22 april 2025. De kamer was samengesteld uit Jeroen Van Nieuwenhove, kamervoorzitter, Koen Muylle en Elly Van De Velde, staatsraden, Jan Velaers en Bruno Peeters, assessoren, en Yves Depoorter, griffier.Het verslag is uitgebracht door Allan Magerotte, adjunct-auditeur.De overeenstemming tussen de Franse en de Nederlandse tekst van het advies is nagezien onder toezicht van Elly Van De Velde, staatsraad.Het advies, waarvan de tekst hierna volgt, is gegeven op 25 april 2025.1. Over het voor advies voorgelegde ontwerp van koninklijk besluit is slechts de volgende opmerking te maken.Luidens het vijfde lid van de aanhef betreft de uitvoering van artikel 147, vierde lid, van het Wetboek van de inkomstenbelastingen 1992 een gebonden bevoegdheid. Het zesde lid van de aanhef preciseert dat de geregelde aangelegenheid in lopende zaken moet worden voortgezet.Beide leden moeten uit de aanhef worden weggelaten, gelet op het feit dat de regering thans over de volheid van haar bevoegdheid beschikt.De griffier   De voorzitterY. Depoorter   J. Van Nieuwenhove17 MEI 2025. - Koninklijk besluit houdende uitvoering van artikel 147, vierde lid, van het Wetboek van de inkomstenbelastingen 1992 voor het aanslagjaar 2026FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op het Wetboek van de inkomstenbelastingen 1992, artikel 147, vierde lid, ingevoegd bij de wet van 23 maart 2019 en gewijzigd bij de wet van 17 maart 2022;Gelet op het KB/WIB 92;Gelet op het advies van de Inspecteur van Financiën, gegeven op 17 januari 2025;Gelet op de akkoordbevinding van de Staatssecretaris voor Begroting, d.d. 19 maart 2025;Gelet op het advies 77.591/3 van de Raad van State, gegeven op 25 april 2025, met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Op de voordracht van de Minister van Financiën,Hebben Wij besloten en besluiten Wij :Artikel 1. Artikel 6318/18, enig lid, van het KB/WIB 92, ingevoegd bij het koninklijk besluit van 28 juni 2019, vervangen bij het koninklijk besluit van 2 mei 2021 en gewijzigd bij de koninklijke besluiten van 6 juni 2022, 25 april 2023 en 25 februari 2024, wordt aangevuld met een bepaling onder een zesde streepje, luidende:"- voor het aanslagjaar 2026: 236,71 euro.".Art. 2. Dit besluit is van toepassing vanaf aanslagjaar 2026.Art. 3. De minister die bevoegd is voor Financiën, is belast met de uitvoering van dit besluit.Gegeven te Brussel, 17 mei 2025.FILIPVan Koningswege :De Minister van Financiën,J. JAMBON 
 </t>
         </is>
       </c>
@@ -652,28 +652,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025003813</t>
+          <t>2025004085</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>26 mei 2025</t>
+          <t>30 mei 2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5 mei 2025. - Koninklijk besluit houdende toekenning van een toelage aan de vzw "Rainbow House" voor het budgettair jaar 2025</t>
+          <t>17 mei 2025. - Koninklijk besluit houdende aanstelling van een Regeringscommissaris bij het Instituut voor de gelijkheid van vrouwen en mannen</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-26&amp;numac_search=2025003813&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003813=6&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-30&amp;numac_search=2025004085&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025004085=6&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 22 mei 2003 houdende organisatie van de begroting en van de comptabiliteit van de federale Staat, op de artikelen 121 tot 124;Gelet op de wet van 10 mei 2007 ter bestrijding van bepaalde vormen van discriminatie, artikel 32/1;Gelet op de financiewet voor begrotingsjaar van 20 december 2024 op sectie 12 - FOD Justitie, programma 58/5 - Diversiteit, Interculturaliteit en Gelijkheid van Kansen;Gelet op het koninklijk besluit van 20 mei 2022 betreffende de administratieve, begrotings- en beheerscontrole;Gelet op het koninklijk besluit van 2 oktober 2023 betreffende de modaliteiten voor de toekenning van de jaarlijkse subsidies voor de koepels van niet-gouvernementele organisaties die actief zijn in het domein van de bestrijding van discriminatie op grond van seksuele oriëntatie voor wat betreft de materies die behoren tot de bevoegdheid van de federale overheid;Gelet op het ministerieel besluit van 22 maart 2024 tot erkenning van de koepels van niet-gouvernementele organisaties die actief zijn in het domein van de bestrijding van discriminatie op grond van seksuele oriëntatie voor wat betreft de materies die behoren tot de bevoegdheid van de federale overheid, voor de erkenningscyclus van 2024-2028;Gelet de instemming van de Minister van Begroting gegeven op 4 april 2025;Gelet op het advies van de inspecteur van Financiën, gegeven op 10 januari 2025;Overwegende dat een krediet van vierhonderdéénennegentigduizend euro (491.000,00 euro) op de organisatieafdeling 12.58.52, activiteitenprogramma 58/5, basisallocatie 33.00.41 van de administratieve begroting van de FOD justitie voor het begrotingsjaar 2025 is ingeschreven;Overwegende de aanvraag voor een subsidie die de vzw "Rainbow House" indiende op 1 oktober 2024 overeenkomstig artikel 13 van het voornoemde koninklijk besluit van 2 oktober 2023;Overwegende dat de vzw "Rainbow House" voldoet aan de criteria vastgelegd in artikelen 8 en 10 van het voornoemde koninklijk besluit van 2 oktober 2023 en is erkend als een koepel van organisaties;Op de voordracht van de Minister van Gelijke Kansen;Hebben Wij besloten en besluiten Wij :Artikel 1.  § 1. Een toelage van negenendertigduizend driehonderdzevenenzeventig euro en vijfentwintig cent (39.377,25 euro) wordt toegekend aan de vzw "Rainbow House", met zetel gevestigd te Kolenmarkt 42, 1000 Brussel (ondernemings-nummer 478 920 276 en rekeningnummer IBAN BE91 0689 4623 0276). § 2. De toelage is bedoeld ter financiële ondersteuning van de jaarlijkse werkingskosten in verband met de uitvoering van een werkprogramma in het kader van het federale beleid inzake bestrijding van discriminatie op grond van seksuele oriëntatie.Art. 2. De toelage bedoeld in artikel 1, wordt aangerekend op het activiteitenprogramma 58/5, basisallocatie 33.00.41, organisatieafdeling 12.58.52 van de administratieve begroting van de FOD Justitie voor het begrotingsjaar 2025.Art. 3. De periode waarop de toelage betrekking heeft, begint op 1 januari 2025 en eindigt op 31 maart 2025.Art. 4. De toelage bedoeld in artikel 1 wordt in twee schijven betaald, verdeeld op de volgende wijze:- een eerste schijf van negentig procent na ondertekening van dit besluit;- de tweede schijf van tien procent na de voorlegging van het eindverslag van de activiteiten en de bewijsstukken voor de volledige toelage.Art. 5.  § 1. Worden aanvaard als subsidieerbare kosten:1°  de kosten voor de huur, de huurlasten en het onderhoud van de gebouwen;2°  de personeelskosten en de kosten voor de aanwerving van het personeel en voor het personeelsbeheer;3°  de missiekosten en reiskosten;4°  de opleidingskosten;5°  de kosten voor administratief en boekhoudkundig beheer;6°  de kantoor- en informaticakosten;7°  de kosten inzake logistiek, communicatie en kantooruitrusting. § 2. De subsidie dekt geen kosten die reeds gedekt zijn door een andere vorm van subsidiering.Art. 6.  § 1. De vereniging verstuurt uiterlijk op 31 maart 2026 het eindverslag van de activiteiten alsook de financiële bewijsstukken naar de dienst Gelijke Kansen (Waterloolaan 115, 1000 Brussel of naar het e-mailadres: equal@just.fgov.be). § 2. Het eindverslag van de activiteiten bevat minstens een algemene beschrijving van de verwezenlijkte werkzaamheden, een synthese van de gevoerde acties, een evaluatie van de behaalde doelstellingen, een beschrijving van de eventuele ondervonden problemen met inbegrip van de obstakels bij de tenuitvoerlegging van de acties, een beschrijving van de faciliterende factoren, alsook alle noodzakelijke informatie die de dienst Gelijke Kansen in staat moet stellen om de verwezenlijking van die activiteiten te evalueren. § 3. De vereniging verstuurt eveneens een samenvattende tabel van alle bewijsstukken van de op deze toelage aangerekende uitgaven, met referentie naar de uitgavencategorieën. § 4. Bij ontstentenis van de volledige overlevering van de documenten, namelijk het eindverslag van de activiteiten en de bewijsstukken voor de volledige toelage, wordt de tweede schijf van de toelage niet uitbetaald en wordt, in voorkomend geval, de eerste schijf teruggevorderd voor het gedeelte van het bedrag dat niet naar behoren, overeenkomstig dit artikel, is gemotiveerd.Art. 7.  § 1. De begunstigde moet:- de bepalingen van de toekenning van de toelage volledig nakomen. Indien dat niet het geval is, kan hem een volledige of gedeeltelijke terugbetaling van de toegekende toelage worden gevraagd;- met betrekking tot het goede besteding van deze toelage enige controle van stukken en/of ter plekke aanvaarden;- het publiek in elk bericht of bij elke publiciteit op de hoogte brengen van de financiële hulp die ze in het kader van deze toelage hebben ontvangen. § 2. In het geval dat de toelage onrechtmatig werd gebruikt, is de dienst Gelijke Kansen van de FOD Justitie belast met de terugvordering van de bedragen. § 3. Indien blijkt dat te veel toelage werd toegekend voor het afgelopen jaar, wordt een beslissing tot terugvordering ter kennis gebracht bij aangetekende brief. Na verloop van een termijn van dertig dagen wordt de beslissing tot terugvordering definitief, tenzij de vereniging opmerkingen heeft laten toekomen. In dat geval wordt de definitieve beslissing uiterlijk twee maanden na ontvangst van de opmerkingen ter kennis van de vereniging gebracht. De vereniging stort het verschuldigde bedrag uiterlijk drie maanden na de definitieve beslissing tot terugvordering terug.Art. 8. Dit besluit heeft uitwerking met ingang van 1 januari 2025.Art. 9. Het lid van de regering dat bevoegd is voor Gelijke Kansen is belast met de uitvoering van dit besluitGegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister voor Gelijke Kansen,R. BEENDERS 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 16 december 2002 houdende oprichting van het Instituut voor de gelijkheid van vrouwen en mannen;Gelet op de wet van 16 maart 1954 betreffende de controle op sommige instellingen van openbaar nut, inzonderheid op artikel 9;Overwegend dat het past om te voorzien in de functie van Regeringscommissaris belast met het oefenen van de controle namens de Minister van Begroting bij het Instituut voor gelijkheid van vrouwen en mannen;Op de voordracht van de minister van Begroting,Hebben Wij besloten en besluiten Wij :Artikel 1. De heer VAN SANDE Maarten wordt ontheven uit zijn functie van Regeringscommissaris bij het Instituut voor de gelijkheid van vrouwen en mannen.Art. 2. Mevr. DEKKERS Laura wordt aangesteld in de hoedanigheid van Regeringscommissaris bij het Instituut voor de gelijkheid van vrouwen en mannen.Art. 3. Dit besluit treedt in werking de dag waarop het in het Belgisch Staatsblad wordt bekendgemaakt.Art. 4. De minister bevoegd voor Begroting is belast met de uitvoering van dit besluit.Gegeven te Brussel, 17 mei 2025.FILIPVan Koningswege :De Minister van Begroting,V. VAN PETEGHEM 
 </t>
         </is>
       </c>
@@ -684,7 +684,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025003893</t>
+          <t>2025004066</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -694,19 +694,18 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5 mei 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur en van het koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur</t>
+          <t>16 mei 2025. - Koninklijk besluit tot vaststelling van de taalkaders van het personeel van de centrale diensten van de Centrale Dienst voor Sociale en Culturele Actie van het Ministerie van Landsverdediging</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-27&amp;numac_search=2025003893&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003893=7&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025004066&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025004066=7&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t xml:space="preserve">
-VERSLAG AAN DE KONINGSire,AlgemeenHet koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur (hierna "KB toegankelijkheid"), zette richtlijn (EU) 2019/882 van het Europees Parlement en de Raad van 17 april 2019 betreffende de toegankelijkheidsvoorschriften voor producten en diensten, gedeeltelijk om. Volgens artikel 31 van deze richtlijn diende deze tegen 28 juni 2022 te zijn omgezet en vanaf 28 juni 2025 te worden toegepast.Het koninklijk besluit van 13 maart 2024 tot wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur (hierna "KB universele lader"), zette Richtlijn (EU) 2022/2380 van het Europees Parlement en de Raad van 23 november 2022 tot wijziging van Richtlijn 2014/53/EU betreffende de harmonisatie van de wetgevingen van de lidstaten inzake het op de markt aanbieden van radioapparatuur, gedeeltelijk om. Volgens artikel 2 van deze richtlijn diende deze tegen 28 december 2023 te zijn omgezet en vanaf 28 december 2024 te worden toegepast (voor bepaalde radioapparatuur).Er worden dus twee Europese richtlijnen omgezet door wijziging van hetzelfde koninklijk besluit, waarbij de volgens de Europese deadline eerste omzetting later moet in werking treden dan de tweede. Aangezien de eerste omzetting nog niet in werking was ten tijde van de tweede omzetting, kon het niet anders dan bij de tweede omzetting uit te gaan van het koninklijk besluit zoals nog niet gewijzigd door de eerste omzetting. Tegen dat de eerste omzetting in werking treedt, is echter ook de tweede omzetting al in werking getreden. Bijgevolg is het uitgangspunt bij de inwerkingtreding van de eerste omzetting het koninklijk besluit zoals gewijzigd door de tweede omzetting. Daardoor klopt de formulering van bepaalde wijzigingen van de eerste omzetting niet meer. Die was immers gebaseerd op de tekst zoals nog niet gewijzigd door de tweede omzetting. Vandaar wijzigt het voorliggende koninklijk besluit die formulering (artikelen 5 en 6) en laat deze in werking treden samen met de eerste omzetting. Ook wordt het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur zelf (hierna "KB radioapparatuur") gewijzigd om de tekst ingevoegd door de tweede omzetting waar nodig aan te passen aan de eerste omzetting. Aangezien ten tijde van de tweede omzetting de eerste omzetting nog niet in werking was getreden, kon daar geen rekening mee worden gehouden (artikelen 2 en 4). Verder worden met het voorliggende koninklijk besluit ook een paar materiële vergissingen rechtgezet (artikelen 1, 3, 7 en 8). Het gaat hier dus louter om wetstechnische wijzigingen en niet om inhoudelijke.Advies 77.399/4 van de Raad van State van 12 februari 2025 werd integraal gevolgd.Artikelsgewijze besprekingArtikel 1 Dit artikel zet een vergissing in de Franse tekst van het KB radioapparatuur recht: er dient te worden verwezen naar "alinéa" en niet naar "paragraphe". Artikelen 2 en 4In de tekst van het KB radioapparatuur die toegevoegd werd door het KB universele lader wordt op verschillende plaatsen verwezen naar artikel 4 § 8, derde lid ervan. Aangezien het KB toegankelijkheid een nieuw lid invoegt tussen het eerste en tweede lid van artikel 4 § 8, wijzigt vanaf dan het derde lid in het vierde lid en dient dus de verwijzing naar artikel 4, § 8, derde lid te wijzigen naar artikel 4, § 8, vierde lid. Waar in de Franse tekst per vergissing naar « paragraphe » in plaats van naar « alinéa » verwezen werd, wordt dit ook rechtgezet (artikel 2).Artikel 3Dit artikel wijzigt artikel 26, § 7, van het KB radioapparatuur. In artikel 26, § 7, wordt verwezen naar paragraaf 4, tweede lid. Het KB toegankelijkheid voegt een nieuw lid in tussen het eerste en tweede lid van paragraaf 4 zodat het tweede lid het derde lid wordt. De verwijzing in artikel 26, § 7, wordt in die zin aangepast.Artikel 5Het lid van artikel 4, § 8, dat gewijzigd wordt door artikel 5, 9°,  c) van het KB toegankelijkheid werd eerder al gewijzigd door het KB universele lader. De wijziging die het KB toegankelijkheid doorvoert, dient dus te gebeuren op de tekst zoals gewijzigd door het KB universele lader. Aangezien dat niet het geval was, wordt de formulering van de wijziging die artikel 5, 9°,  c) van het KB toegankelijkheid doorvoert in die zin aangepast.Artikel 6Dit betreft de rechtzetting van een vergissing in het KB toegankelijkheid. De aangegeven wijziging is bedoeld voor het opschrift van hoofdstuk 3, afdeling 5 van het KB radioapparatuur en niet hoofdstuk 4. Artikel 7Door de toepassing van artikel 23, 1°,  van het KB toegankelijkheid in zijn huidige vorm zouden in de Franse tekst van artikel 28 § 1 van het KB radioapparatuur de woorden "l'article 26" twee keer na elkaar komen te staan, wat niet de bedoeling is. Deze wijziging dient dus om dit te voorkomen.Artikel 8Deze rechtzettingen i.v.m. het KB toegankelijkheid krijgen logischerwijze dezelfde datum van inwerkingtreding als het KB toegankelijkheid zelf. Enkel artikel 1 dient vroeger in werking te treden rekening houdend met de opmerking van de Raad van State (voetnoot 7 van zijn advies). Dit om verwarring te vermijden over de in artikel 1 bedoelde verbetering. Deze slaat op artikel 4, § 8, derde lid, van het KB radioapparatuur dat door de inwerkingtreding van het KB toegankelijkheid echter het vierde lid zal worden. Artikel 9Deze bepaling behoeft geen commentaar.Ik heb de eer te zijn,Sire,Van Uwe Majesteit,de zeer eerbiedige en zeer getrouwe dienaar,De Minister van Telecommunicatie,V. MATZRAAD VAN STATEAfdeling WetgevingAdvies 77.399/4 van 12 februari 2025 over een ontwerp van koninklijk besluit `houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur en van het koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur'Op 14 januari 2025 is de Raad van State, afdeling Wetgeving, door de Vice-eersteminister en Minister van Ambtenarenzaken, Overheidsbedrijven, Telecommunicatie en Post verzocht binnen een termijn van dertig dagen een advies te verstrekken over een ontwerp van koninklijk besluit `houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur en van het koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur'.Het ontwerp is door de vierde kamer onderzocht op 12 februari 2025. De kamer was samengesteld uit Bernard BLERO, kamervoorzitter, Géraldine ROSOUX en Dimitri YERNAULT, staatsraden, Christian BEHRENDT en Jacques ENGLEBERT, assessoren, en Anne-Catherine VAN GEERSDAELE, griffier.Het verslag is uitgebracht door Julien GAUL, auditeur.De overeenstemming tussen de Franse en de Nederlandse tekst van het advies is nagezien onder toezicht van Géraldine ROSOUX.Het advies, waarvan de tekst hierna volgt, is gegeven op 12 februari 2025.Aangezien de adviesaanvraag ingediend is op basis van artikel 84, § 1, eerste lid, 2°,  van de wetten `op de Raad van State', gecoördineerd op 12 januari 1973, beperkt de afdeling Wetgeving zich, overeenkomstig artikel 84, § 3, van de gecoördineerde wetten, voornamelijk tot het onderzoek van de bevoegdheid van de steller van de handeling, de rechtsgrond en de vraag of de voorgeschreven vormvereisten zijn vervuld.VOORAFGAANDE VORMVEREISTEN1. De gemachtigde beaamt dat sommige bepalingen van het ontwerp rechtsgrond vinden in artikel 32, § 3, tweede lid, en § 4, derde lid, van de wet van 13 juni 2005 `betreffende de elektronische communicatie', welk artikel ertoe verplicht het advies in te winnen van het Belgisch Instituut voor postdiensten en telecommunicatie.Er moet op toegezien worden dat dit vormvereiste naar behoren vervuld wordt.2. Artikel 9, tweede lid, van het samenwerkingsakkoord van 17 november 2006 `tussen de Federale Staat, de Vlaamse Gemeenschap, de Franstalige Gemeenschap en de Duitstalige Gemeenschap betreffende het wederzijds consulteren bij het opstellen van regelgeving inzake elektronische communicatienetwerken, het uitwisselen van informatie en de uitoefening van de bevoegdheden met betrekking tot elektronische communicatienetwerken door de regulerende instanties bevoegd voor telecommunicatie of radio-omroep en televisie' luidt als volgt:"Het Interministerieel Comité voor Telecommunicatie en Radio-omroep en Televisie heeft tot taak om in onderling overleg en met respect voor ieders bevoegdheid, volgens de modaliteiten en procedures zoals vastgelegd binnen het Overlegcomité, de wederzijdse consultatie te organiseren omtrent mekaars initiatieven inzake het opstellen van ontwerpregelgeving met betrekking tot omroep en telecommunicatie."Aangezien het ontwerp het op de markt aanbieden van radioapparatuur betreft, vormt het een "ontwerpregelgeving met betrekking tot omroep en telecommunicatie" in de zin van het samenwerkingsakkoord van 17 november 2006.De afdeling Wetgeving heeft aan de hand van het dossier dat haar voorgelegd is niet kunnen vaststellen of die wederzijdse consultatie plaatsgevonden heeft.Er moet op toegezien worden dat dit vormvereiste naar behoren vervuld wordt.3. Indien de aan de Raad van State voorgelegde tekst naar aanleiding van het vervullen van die vormvereisten nog wijzigingen zou ondergaan die niet louter vormelijk zijn en die niet het resultaat zijn van het gevolg dat aan dit advies wordt gegeven, moeten de gewijzigde of toegevoegde bepalingen op hun beurt om advies aan de afdeling Wetgeving worden voorgelegd, overeenkomstig artikel 3, § 1, eerste lid, van de gecoördineerde wetten `op de Raad van State'.De vervulling van die vormvereisten moet bovendien in de aanhef vermeld worden.ALGEMENE OPMERKINGEN1. Voor elk gewijzigd artikel dienen de opeenvolgende vroegere wijzigingen daarvan opgegeven te worden, overeenkomstig de regels opgenomen in de Handleiding voor het opstellen van wetgevende en reglementaire teksten.1 Bijgevolg dienen de volgende preciseringen aangebracht te worden:- artikel 4, § 8, derde lid, van het koninklijk besluit van 25 maart 2016 `betreffende het op de markt aanbieden van radioapparatuur' is ingevoegd bij het koninklijk besluit van 13 maart 2024 `tot wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur'2 (artikel 1 van het ontwerp);- de artikelen 6, § 4, tweede lid, en 7, § 2, tweede lid (lees derde lid), van het koninklijk besluit van 25 maart 2016 zijn ingevoegd bij het koninklijk besluit van 13 maart 20243 (artikel 2 van het ontwerp);- artikel 28, eerste lid, h), van het koninklijk besluit van 25 maart 2016 is vervangen bij het koninklijk besluit van 13 maart 20244 (artikel 4 van het ontwerp);- artikel 4, § 8, tweede lid5, van het koninklijk besluit van 25 maart 2016 is gewijzigd bij het koninklijk besluit van 13 maart 20246 (artikel 5 van het ontwerp).2. Gelet op de wijze waarop het ontwerpbesluit gesteld is7, moet de steller zich ervan vergewissen of het feit dat de inwerkingtreding van dat besluit samenvalt met die van het koninklijk besluit van 13 september 2023 `houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur', te weten 28 juni 2025, een duidelijke en coherente samenhang waarborgt tussen de wijzigingen die respectievelijk aangebracht worden bij het ontwerp en bij het koninklijk besluit van 13 september 2023.BIJZONDERE OPMERKINGENAANHEFIn het eerste lid moet eveneens verwezen worden naar artikel 32, § 3, tweede lid, en § 4, derde lid, van de wet van 13 juni 2005, dat vervangen is bij de wet van 18 december 2015.DISPOSITIEFArtikel 6Bij artikel 6 van het koninklijk besluit van 13 maart 2024 wordt geen tweede lid ingevoegd in artikel 7, § 2, van het koninklijk besluit van 25 maart 2016 maar wordt dat artikel aangevuld met een lid. De gemachtigde is het ermee eens dat de bij artikel 6 van het ontwerp beoogde wijziging geen bestaansgrond heeft. De bepaling moet weggelaten worden.De Griffier   De VoorzitterAnne-Catherine VAN GEERSDAELE   Bernard BLERO_______Nota's1 Beginselen van de wetgevingstechniek-Handleiding voor het opstellen van wetgevende en reglementaire teksten, www.raadvst-consetat.be, tab "Wetgevingstechniek", aanbeveling 113 en volgende.2 Artikel 4, 2°,  van het koninklijk besluit van 13 maart 2024. Behalve wat laptops betreft, is dat koninklijk besluit van 13 maart 2024 in werking getreden op 28 december 2024 (zie artikel 12 van dat besluit).3 Respectievelijk bij de artikelen 5 en 6 van het koninklijk besluit van 13 maart 2024.4 Artikel 10, 2°,  van het koninklijk besluit van 13 maart 2024.5 Dat het derde lid zal worden bij de inwerkingtreding van artikel 5, 9°,  b), van het koninklijk besluit van 13 september 2023 `houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur'.6 Artikel 4, 1°,  van het koninklijk besluit van 13 maart 2024.7 Zo worden bij artikel 1 van het ontwerp wijzigingen aangebracht in artikel 4, § 8, derde lid, van het koninklijk besluit van 25 maart 2016 (ingevoegd bij artikel 4, 2°,  van het koninklijk besluit van 13 maart 2024) terwijl bij artikel 5, 9°,  b), van het koninklijk besluit van 13 september 2023 een nieuw lid ingevoegd zal worden tussen het eerste lid en het tweede lid van artikel 4, § 8, waardoor het huidige derde lid het vierde lid zal worden. Bovendien worden bij het ontwerpbesluit wijzigingen aangebracht in het koninklijk besluit van 13 september 2023.5 MEI 2025. - Koninklijk besluit houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur en van het koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuurFILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 13 juni 2005 betreffende de elektronische communicatie, artikel 32, § 2/1, ingevoegd bij de wet van 6 februari 2024, § 3, tweede lid, § 4, derde lid, vervangen bij de wet van 18 december 2015 en artikel 38/1, ingevoegd bij de wet van 20 juli 2023;Gelet op het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur;Gelet op het koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur;Gelet op advies 77.399/4 van de Raad van State, gegeven op 12 februari 2025, met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Gelet op het advies van het Belgisch Instituut voor postdiensten en telecommunicatie van 7 april 2025;Gelet op de raadpleging van 16 april 2025 tot 25 april 2025 van het Interministerieel Comité voor Telecommunicatie en Radio-omroep en Televisie;Op de voordracht van de Minister van Telecommunicatie,Hebben Wij besloten en besluiten Wij :Artikel 1. In artikel 4, § 8, derde lid, van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur, ingevoegd bij het koninklijk besluit van 13 maart 2024, wordt in de Franse tekst het woord "paragraphe" vervangen door het woord "alinéa".Art. 2. In artikel 6, § 4, tweede lid en in artikel 7, § 2, derde lid, van hetzelfde besluit, ingevoegd bij het koninklijk besluit van 13 maart 2024, worden de woorden "derde lid" vervangen door de woorden "vierde lid".Art. 3. In artikel 26 § 7 van hetzelfde besluit, worden de woorden "tweede lid" vervangen door de woorden "derde lid".Art. 4. In artikel 28, eerste lid, bepaling onder h), van hetzelfde besluit, vervangen bij het koninklijk besluit van 13 maart 2024, worden de woorden "derde lid" vervangen door de woorden "vierde lid".Art. 5. Artikel 5, 9°,  c) van het koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur wordt vervangen als volgt: "c) in het vroegere tweede lid, gewijzigd bij het koninklijk besluit van 13 maart 2024, dat het derde lid wordt, worden de woorden "De instructies bevatten" vervangen door de woorden "Wat de essentiële eisen betreft, bevatten de instructies".Art. 6. In artikel 9 van hetzelfde besluit worden de woorden "hoofdstuk 4" vervangen door de woorden "hoofdstuk 3".Art. 7. In artikel 23, 1°  van hetzelfde besluit worden in de Franse tekst de woorden "l'article 26" geschrapt.Art. 8. Artikel 1 treedt in werking op 27 juni 2025.De artikelen 2 tot 7 treden in werking op 28 juni 2025.Art. 9. De minister bevoegd voor Telecommunicatie wordt belast met de uitvoering van dit besluit.Gegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister van Telecommunicatie,V. MATZ 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 16 maart 1954 betreffende de controle op sommige instellingen van openbaar nut, inzonderheid op artikel 11, § 2;Gelet op de wetten op het gebruik van de talen in bestuurszaken, gecoördineerd op 18 juli 1966, artikel 43, laatst gewijzigd bij de wet van 4 april 2006;Gelet op het koninklijk besluit van 16 november 2006 betreffende de aanduiding en de uitoefening van de management- en staffuncties in sommige instellingen van openbaar nut;Gelet op het koninklijk besluit van 13 maart 2007 tot vaststelling, met het oog op de toepassing van artikel 43 van de wetten op het gebruik van de talen in bestuurszaken, gecoördineerd op 18 juli 1966, van de betrekkingen van de ambtenaren in sommige instellingen van openbaar nut, die eenzelfde trap van de hiërarchie vormen;Gelet op het koninklijk besluit van 26 oktober 2018 tot vaststelling van de taalkaders van de Centrale Dienst voor sociale en culturele actie van het Ministerie van Landsverdediging;Gelet op het Personeelsplan 2024 van de Centrale Dienst voor sociale en culturele actie van het Ministerie van Landsverdediging, dat op 8 december 2023 door het beheerscomité werd goedgekeurd;Overwegende dat voldaan werd aan de bepalingen van artikel 54, tweede lid, van de voornoemde wetten op het gebruik van talen in bestuurszaken;Gelet op het advies nr. 56.316 van de Vaste Commissie voor Taaltoezicht, gegeven op 20 september 2024;Overwegende dat de Centrale Dienst voor sociale en culturele actie van het Ministerie van Landsverdediging over taalkaders dient te beschikken, teneinde de in het personeelsplan opgenomen actieplannen te kunnen uitvoeren;Op voordracht van onze Minister van Defensie,Hebben Wij besloten en besluiten Wij :Artikel 1. De betrekkingen in de centrale diensten van de Centrale Dienst voor sociale en culturele actie van het Ministerie van Landsverdediging, die beantwoorden aan artikel 43, § 3, eerste lid, aan artikel 44 of aan artikel 46, § 1, van de wetten op het gebruik van de talen in bestuurszaken, gecoördineerd op 18 juli 1966, worden ingedeeld in taalkaders zoals in de tabel hierna wordt opgegeven:  </t>
         </is>
       </c>
     </row>
@@ -716,28 +715,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025003755</t>
+          <t>2025003993</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>28 mei 2025</t>
+          <t>23 mei 2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5 mei 2025. - Koninklijk besluit houdende ontslag en benoeming van een regeringscommissaris en ontslag van een plaatsvervangend regeringscommissaris bij het Bureau voor Normalisatie</t>
+          <t>15 mei 2025. - Koninklijk besluit houdende ontslag van een lid van de nationale raad van de Orde van architecten</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-28&amp;numac_search=2025003755&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003755=8&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-23&amp;numac_search=2025003993&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003993=8&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 16 maart 1954 betreffende de controle op sommige instellingen van openbaar nut, artikel 9, § 1, tweede lid;Overwegende het Wetboek van economisch recht, artikel VIII.3;Overwegende het koninklijk besluit van 10 augustus 2009 houdende ontslag en benoeming van een regeringscommissaris en van een plaatsvervangende regeringscommissaris bij het Bureau voor normalisatie;Overwegende het koninklijk besluit van 24 december 2020 houdende ontslag en benoeming van een plaatsvervangend regeringscommissaris bij het Bureau voor Normalisatie;Op de voordracht van de Minister van Economie,Hebben Wij besloten en besluiten Wij :Artikel 1. Aan dhr. Renaud Collette, adviseur, wordt eervol ontslag verleend als regeringscommissaris bij het Bureau voor Normalisatie.Art. 2. Dhr. Herman Van den Langenbergh, adviseur-generaal, wordt benoemd tot regeringscommissaris bij het Bureau voor Normalisatie.Art. 3. Aan dhr. Chris Van der Cruyssen, adviseur-generaal, wordt eervol ontslag verleend als plaatsvervangend regeringscommissaris bij het Bureau voor Normalisatie.Art. 4. De regeringscommissaris bij het Bureau voor Normalisatie oefent zijn bevoegdheden uit overeenkomstig de bepalingen van de wet van 16 maart 1954 betreffende de controle op sommige instellingen van openbaar nut. Hij brengt verslag uit aan de minister bevoegd voor Economie, in het bijzonder aangaande alle beslissingen van de Raad van Bestuur van het Bureau voor Normalisatie.Art. 5. De minister bevoegd voor Economie is belast met de uitvoering van dit besluit.Gegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister van Economie,D. CLARINVAL 
+Bij koninklijk besluit van 15 mei 2025 wordt aan dhr. Joseph Meers eervol ontslag verleend uit zijn functie van lid van de nationale raad van de Orde van architecten, in de hoedanigheid van architect, lid van het onderwijzend personeel van de gesubsidieerde officiële scholen voor bouwkunde.Dit besluit treedt in werking de dag volgend op de bekendmaking ervan bij uittreksel in het Belgisch Staatsblad. 
 </t>
         </is>
       </c>
@@ -748,28 +747,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025003802</t>
+          <t>2025004131</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21 mei 2025</t>
+          <t>30 mei 2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29 april 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat wat betreft de concessie</t>
+          <t>15 mei 2025. - Koninklijk besluit tot uitvoering van artikel 4 § 3 van de wet van 16 mei 2024 betreffende de bevoegdheden op het nationale grondgebied van de leden van de Europese grens- en kustwacht</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-21&amp;numac_search=2025003802&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003802=9&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-30&amp;numac_search=2025004131&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025004131=9&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
           <t xml:space="preserve">
-VERSLAG AAN DE KONINGSire, Het voorgestelde besluit beoogt de concessieprocedure, zoals bepaald in het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat, aan te passen rekening houdend met de wijzigingen aangebracht aan de milieuvergunningsprocedure. Deze laatste werd recent gewijzigd bij het koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden. De wet van 13 juni 1969 inzake de exploratie en de exploitatie van de niet-levende rijkdommen van de territoriale zee en het continentaal plat, schrijft immers dat er voor de exploratie en/of de exploitatie van minerale en andere niet-levende rijkdommen van de zeebodem zowel een milieuvergunning als een concessie vereist is. Deze kunnen dus afzonderlijk worden toegekend, maar beiden zijn noodzakelijk om te kunnen overgaan tot exploratie en/of exploitatie. Om de verschillende procedures betreffende milieuvergunning en concessie beter op elkaar te laten aansluiten, werden er een aantal specifieke wijzigingen aangebracht. De Raad van State adviseert in haar advies 77.319/1 van 14 januari 2025 om de samenhang tussen enkele van deze wijzigingen te verduidelijken. Hierbij refereert hij naar het ontworpen artikel 20, tweede lid, het nieuw artikel 22/1 en het artikel 26, eerste lid.In het oorspronkelijke artikel 20 werd er voorzien dat elke verlengingsaanvraag moest worden ingediend ten minste één jaar voor het verstrijken van de geldigheidsduur van de concessievergunning. In het verleden was deze termijn ingesteld om ervoor te zorgen dat de concessie werd verlengd voordat deze zou aflopen. Deze aansluiting is belangrijk omdat enkel een verlenging van concessie toelaat om rekening te blijven houden met de ontgonnen volumes van de laatste vijf jaar bij het bepalen van het jaarlijkse maximale exploitatievolume per concessiehouder overeenkomstig artikel 26, eerste lid. Indien er een onderbreking is tussen de aflopende concessievergunning en de vernieuwing ervan, moest de concessievernieuwing beschouwd worden als een `nieuwe' concessieaanvraag, waarbij er aan de concessiehouder slechts het minimale volume van 30.000 m3 kan worden toegekend, overeenkomstig artikel 26, tweede lid.Het koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden koppelt de procedure tot het bekomen van een milieuvergunning in het kader van de exploratie en/of exploitatie van de zeebodem los van de procedure tot het bekomen van een concessie. Dit betekent enerzijds dat moet worden voorzien in maatregelen die een verval van concessie voorzien indien de milieuvergunning wordt opgeheven of vervallen wordt verklaard, en anderzijds dat moet worden voorzien in maatregelen om de mogelijkheid op te vangen dat een verlenging van de milieuvergunning wordt aangevraagd en toegekend maar dat de verlenging van de concessievergunning niet bekomen kan worden voordat deze afloopt. In het ontworpen artikel 22/1 worden dus de gevolgen voor de concessie vastgelegd indien de milieuvergunning wordt opgeheven of vervallen worden verklaard.Artikel 20, tweede lid, heeft als doel om de concessiehouder te behoeden voor verlies van zijn ontginningsvolume omwille van procedurele redenen. Het koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden legt geen periode vast waarbinnen de milieuvergunning dient te worden aangevraagd. Het gevaar bestaat dus dat een verlenging van de milieuvergunning wordt aangevraagd en toegekend maar dat de verlenging van de concessievergunning niet bekomen kan worden vóór het verstrijken van de concessie. Het tweede lid van artikel 20 laat dan ook toe dat de concessiehouder die de milieuvergunningsprocedure succesvol heeft doorlopen en dus een milieuvergunning heeft verkregen en die een verlengingsaanvraag voor de concessie heeft ingediend voordat deze verstrijkt, de zekerheid heeft dat eens de concessieprocedure positief is beëindigd, de volumes die de laatste vijf jaar zijn ontgonnen onder zijn concessie in aanmerking worden genomen om het maximale jaarlijkse exploitatievolume te bepalen. Uiteraard zal er geen rekening gehouden kunnen worden met de ontgonnen hoeveelheden van de laatste vijf jaar indien de concessiehouder een verlening van concessie aanvraagt na het verstrijken van de geldigheidstermijn van deze of indien de verlengingsaanvraag van de concessie wordt afgewezen.Deze aansluiting van concessies is ook belangrijk voor de schatting van het beschikbare volume voor de andere concessiehouders. De volumes voor het volgende jaar worden overeenkomstig artikel 26, eerste lid, berekend en medegedeeld aan de concessiehouders vóór 01/08/X-1. Indien het tweede lid niet zou zijn voorzien, zouden de volumes meegedeeld aan de concessiehouders, onzeker zijn. De volumes zouden immers nog kunnen dalen of stijgen naargelang de procedure van een verlenging al dan niet op tijd zou afgerond geraken. Dergelijke onzekerheid zou niet getuigen van goed beheer vanwege de Belgische Staat.Een ander gevolg van het opsplitsen van de procedure in een milieuvergunningsprocedure en een concessieprocedure, is dat de bepalingen van de milieuvergunning in werking zijn getreden op 31 december 2024. De Raad van State raadde in zijn advies nr. 77.319/1 van 14 januari 2025 aan om te voorzien in overgangsmaatregelen om redenen van noodzaak voor de continuïteit en de goede werking van het bestuur. Artikel 26 van het wijzigingsbesluit voorziet dan ook in een overgangsbepaling voor de concessieaanvraag. Indien een aanvraag werd ingediend voor de inwerkingtreding van dit besluit, blijven de oude regels van kracht en wordt de vergunning verleend, verlengd, gewijzigd, uitgebreid, overgedragen of ingetrokken met toepassing van de oude regels. Zo dienen er niet halverwege een procedure nieuwe bepalingen te worden toegepast. Dit zou voor onnodige verwarring en rechtsonzekerheid zorgen. Dit betekent voor wat het luik milieueffectenbeoordeling betreft, dat de aanvragen die ingediend zijn vóór 31 december 2024 beoordeeld zullen worden op grond van het koninklijk besluit van 21 oktober 2018 houdende de regels betreffende de milieueffectenbeoordeling in toepassing van de wet van 13 juni 1969 inzake de exploratie en exploitatie van niet-levende rijkdommen van de territoriale zee en het continentaal plat. Indien dus deze aanvragen aanleiding geven tot een concessie, dan zullen deze toekenningen van concessie geen milieuvergunning inhouden, maar wel een beoordeling van de milieueffecten, zoals het geval was voor de inwerkingtreding van titel 5, hoofdstuk II, van het koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelatingen en Natura 2000-goedkeuringen en tot milieuvergunning in de Belgische zeegebieden. De aanvragen die ingediend worden na 31 december 2024 zullen dus wel moeten beschikken over een milieuvergunning, zoals bepaald in het hierboven vermelde koninklijk besluit van 26 april 2024.Deze aanvragen zullen voor wat het luik concessie wel nog beoordeeld worden op grond van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat, zoals deze gold voor de inwerkingtreding van het ontworpen besluit. Hierdoor wordt de continuïteit en de goede werking van het bestuur verzekerd.Ik heb de eer te zijn,Sire,Van Uwe Majesteit,de zeer eerbiedige en zeer getrouwe dienaar,De Minister van Economie,D. CLARINVALRAAD VAN STATEAfdeling WetgevingAdvies 77.319/1 van 14 januari 2025 over een ontwerp van koninklijk besluit `tot wijziging van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet levende rijkdommen in de territoriale zee en op het continentaal plat wat betreft de concessie'Op 18 december 2024 is de Raad van State, afdeling Wetgeving, Minister van Economie verzocht binnen een termijn van dertig dagen een advies te verstrekken over een ontwerp van koninklijk besluit `tot wijziging van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat wat betreft de concessie'.Het ontwerp is door de eerste kamer onderzocht op 7 januari 2025. De kamer was samengesteld uit Pierre LEFRANC, wnd. kamervoorzitter, Brecht STEEN en Tim CORTHAUT, staatsraden, Michel TISON, assessor, en Eline YOSHIMI, griffier.Het verslag is uitgebracht door Katrien DIDDEN, auditeur.De overeenstemming tussen de Franse en de Nederlandse tekst van het advies is nagezien onder toezicht van Tim CORTHAUT, staatsraad.Het advies, waarvan de tekst hierna volgt, is gegeven op 14 januari 2025.1. Met toepassing van artikel 84, § 3, eerste lid, van de wetten op de Raad van State, gecoördineerd op 12 januari 1973, heeft de afdeling Wetgeving zich toegespitst op het onderzoek van de bevoegdheid van de steller van de handeling, van de rechtsgrond, alsmede van de vraag of aan de te vervullen vormvereisten is voldaan.VOORAFGAANDE OPMERKING2. Rekening houdend met het ogenblik waarop dit advies wordt gegeven, vestigt de Raad van State de aandacht van de adviesaanvrager erop dat de ontbinding van de Wetgevende Kamers tot gevolg heeft dat de regering sedert die datum en totdat, na de verkiezing van de Kamer van volksvertegenwoordigers, een nieuwe regering is benoemd door de Koning, niet meer over de volheid van haar bevoegdheid beschikt. Dit advies wordt evenwel gegeven zonder dat wordt nagegaan of dit ontwerp in die beperkte bevoegdheid kan worden ingepast, aangezien de afdeling Wetgeving geen kennis heeft van het geheel van de feitelijke gegevens die de regering in aanmerking kan nemen als ze te oordelen heeft of het vaststellen of het wijzigen van verordeningen noodzakelijk is.STREKKING VAN HET ONTWERP3. Overeenkomstig artikel 3, § 1, van de wet van 13 juni 1969 `inzake de exploratie en de exploitatie van niet-levende rijkdommen van de territoriale zee en het continentaal plat' is voor de exploratie en/of de exploitatie van de minerale en andere niet-levende rijkdommen van de zeebodem en van de ondergrond zowel een concessie als een milieuvergunning vereist. Een dergelijke concessie kan slechts worden toegestaan mits een milieuvergunning wordt toegekend1.De milieuvergunningsprocedure werd recent gewijzigd bij het koninklijk besluit van 26 april 2024 `betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden' (hierna: milieuvergunningsbesluit).Het om advies voorgelegde ontwerp strekt er in hoofdzaak toe de concessieprocedure, zoals bepaald in het koninklijk besluit van 1 september 2004 `betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat' aan te passen in het licht van de wijzigingen in de milieuvergunningsprocedure.RECHTSGROND4. De ontworpen regeling vindt rechtsgrond in het in de aanhef vermelde artikel 3, § 2, van de wet van 13 juni 1969, dat de Koning machtigt om, op voordracht van de minister bevoegd voor Economie, de voorwaarden en nadere regels tot toekenning van de concessie voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen van de zeebodem vast te stellen.In de mate dat de ontworpen bepalingen bovendien verband houden met de nieuwe regeling voor de milieuvergunning, kan bijkomend rechtsgrond worden gevonden in artikel 3, § 3, van de wet van 13 juni 1969. ONDERZOEK VAN DE TEKSTAanhef5. Het eerste lid van de aanhef dient als volgt te worden geformuleerd:"Gelet op de wet van 13 juni 1969 inzake de exploratie en de exploitatie van de niet levende rijkdommen van de territoriale zee en het continentaal plat, artikel 3, §§ 2 en 3, vervangen bij de wet van 11 december 2022".Artikel 46.1. De invoering van het enkelvoud in het ontworpen artikel 8, § 1, eerste lid, van het koninklijk besluit van 1 september 2004 kan fout worden begrepen. Door te spreken van "de concessieaanvraag voor de exploratie en de exploitatie van de niet-levende rijkdommen van de territoriale zee en het continentaal plat" kan de indruk worden gewekt dat er voortaan maar één concessieaanvraag mogelijk is, en dat die bovendien op zowel de exploratie als de exploitatie betrekking moet hebben, terwijl meerdere concessies kunnen worden verleend en dit voor zowel exploratie, exploitatie als de combinatie van beide. De redactie van het ontworpen artikel 8 van het koninklijk besluit van 1 september 2004 moet worden heroverwogen teneinde op ondubbelzinnige en consistente wijze de bedoelde draagwijdte ervan tot uiting te brengen.6.2. In artikel 4, 4°,  van het ontwerp moet de te vervangen Nederlandse tekst als volgt luiden: "in het geval van een exploratie- en/of exploitatieaanvraag in de controlezones".6.3.De tekst van artikel 4, 5°,  van het ontwerp wordt beter als volgt verwoord: "paragraaf 2, eerste lid, 5°,  gewijzigd bij het koninklijk besluit van 19 april 2014, wordt opgeheven;"Artikel 77. Het ontworpen artikel 11, § 1, tweede lid, laatste zin, van het koninklijk besluit van 1 september 2004 stelt dat het besluit tot verlening van de milieuvergunning aan de commissie wordt bezorgd binnen de veertien dagen na ontvangst van het besluit zoals voorzien in artikel 103, § 6, van het milieuvergunningsbesluit2. Op de vraag wat precies moet worden verstaan onder de ontvangst "zoals voorzien in artikel 103, § 6, van het milieuvergunningsbesluit", nu dit artikel de betekening aan de dienst Continentaal plat regelt, antwoordde de gemachtigde:"De dienst Marien Milieu bezorgt het besluit van de minister wat betreft de milieuvergunning digitaal aan de leden van de Raadgevende Commissie overeenkomstig artikel 83, § 3, juncto artikel 102 van het koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden. Het besluit wordt eveneens aan de dienst Continentaal Plat verstuurd overeenkomstig artikel 78, § 2, juncto artikel 103, § 6 van hetzelfde koninklijk besluit van 26 april 2024. De dienst kan er dan ook over waken dat de beslissing wordt bezorgd aan de Raadgevende Commissie binnen de periode voorzien in het nieuwe artikel 11, § 1, tweede lid."Ter wille van de rechtszekerheid dient in de tekst te worden verduidelijkt door wie het besluit tot verlening van de milieuvergunning aan de commissie wordt bezorgd en op welk ogenblik de bedoelde termijn van veertien dagen ingaat.Artikel 128. In de inleidende zin van artikel 12 moet de verwijzing naar het koninklijk besluit van 21 oktober 2018 worden weggelaten.Meer algemeen verdient het aanbeveling om de nog relevante wetsgeschiedenis van de verschillende bepalingen die door het ontwerp worden gewijzigd te verifiëren.Artikel 149. Het ontworpen artikel 20, tweede lid, van het koninklijk besluit van 1 september 2004 luidt als volgt:"Indien het besluit tot verlening van milieuvergunning werd toegekend vóór het verstrijken van de geldigheidsduur van de exploratie- of exploitatieconcessie, wordt er bij het bepalen van de maximale toegestane jaarlijkse exploitatievolumes rekening gehouden met de ontgonnen hoeveelheden gedurende de vorige 5 jaar, overeenkomstig artikel 26, eerste lid."De noodzaak van het ontworpen artikel 20, tweede lid, van het koninklijk besluit van 1 september 2004 is niet evident, nu het ontworpen artikel 26, eerste lid, van dat koninklijk besluit erin voorziet dat de minister in elk geval jaarlijks het maximaal exploitatievolume per concessiehouder vaststelt, waarbij eveneens rekening moet worden gehouden met de ontgonnen hoeveelheden van de vorige vijf jaar en waarnaar in de ontworpen bepaling ook wordt verwezen. Daarbij lijkt het ook irrelevant wanneer de milieuvergunning werd verleend3. Bijgevolg worden de stellers van het ontwerp uitgenodigd om de samenhang tussen de ontworpen artikelen 20, tweede lid, 22/1 en 26, eerste lid, van het koninklijk besluit van 1 september 2004 beter tot uiting te brengen in het te nemen besluit.Artikelen 15 en 1610. De ontworpen artikelen 22 en 22/1 van het koninklijk besluit van 1 september 2004, voorzien in een "intrekking voor verval van de concessie", bij het niet naleven van de voorwaarden van de concessie, of indien de milieuvergunning is opgeheven of vervallen. Hoewel daarbij wordt aangesloten bij de bestaande terminologie van het koninklijk besluit van 1 september 2004,4 moet worden vastgesteld dat die term niet ondubbelzinnig is en tot rechtsonzekerheid aanleiding kan geven.Vooreerst moet worden opgemerkt dat de Nederlandse woordgroep "intrekking voor verval van de concessie" een slechte vertaling is van de Franse tekst, en er veeleer bedoeld wordt "intrekking wegens het verval van de concessie".Daarnaast moet worden vastgesteld dat met "de intrekking" ("le retrait") in kwestie eigenlijk iets anders wordt bedoeld dan wat in het administratief recht gebruikelijk onder de intrekking van een administratieve rechtshandeling wordt verstaan, met name het met terugwerkende kracht verwijderen van die handeling uit het rechtsverkeer zodat ze wordt geacht nooit uitwerking te hebben gehad5. In casu wordt de concessie immers niet met terugwerkende kracht ongedaan gemaakt, maar wordt ze slechts beëindigd voor de toekomst nadat de minister heeft vastgesteld dat daartoe aanleiding is wegens het niet naleven van de voorwaarden van de concessie (ontworpen artikel 22) of wegens de opheffing of het verval van de milieuvergunning (ontworpen artikel 22/1). In die zin is de "intrekking" te beschouwen als een opheffing.Het is bovendien dubbelop om te spreken van een intrekking (lees: opheffing) voor (lees: wegens) het verval van de concessie, aangezien het verval taalkundig zelf al het einde van de concessie impliceert, zodat een "opheffing wegens het verval van de concessie" beëindigt wat al beëindigd is.Correcter zou zijn om consistent de term "vervallenverklaring van de concessie" ("déclaration de déchéance de la concession") te gebruiken. Op die manier wordt beter tot uiting gebracht dat de beslissing van de minister leidt tot de beëindiging van de concessie.De ontworpen artikelen 22 en 22/1 van het koninklijk besluit van 1 september 2004 moeten in het licht daarvan worden aangepast. Dezelfde terminologische aanpassing moet dan ook worden doorgevoerd in het opschrift van hoofdstuk VII van dat besluit, evenals in artikel 21 van dat besluit.Artikel 2411. Artikel 24 van het ontwerp voorziet in de inwerkingtreding van onder meer titel 5, hoofdstuk II (artikel 24, 1° ) en artikel 111, 4°,  (artikel 24, 2° ) van het milieuvergunningsbesluit op de tiende dag na de bekendmaking ervan in het Belgisch Staatsblad.Overeenkomstig artikel 114 van het milieuvergunningsbesluit treden titel 5, hoofdstuk II en artikel 111, 4°,  van dit besluit in werking "op een door Ons vast te stellen datum en uiterlijk op 31 december 2024". Bij gebrek aan andere regeling zijn de in artikel 24, 1°  en 2°  vermelde bepalingen bijgevolg al in werking getreden op 31 december 2024, zodat de inwerkingtredingsbepaling in artikel 24, 1°  en 2°,  van het ontwerp geen doel meer kan treffen. Artikel 24, 3°,  van het ontwerp, dat de inwerkingtreding van het te nemen besluit bepaalt op de tiende dag na bekendmaking ervan in het Belgisch Staatsblad, bevestigt dan nog enkel de basisregel,6 en is dan verder overbodig.Hierop gewezen, verklaarde de gemachtigde het volgende:"Het dossier heeft helaas een langere doorlooptijd gekend alvorens het ingediend werd bij de Raad van State. Hierdoor is de oorspronkelijke doelstelling, namelijk een publicatie in het Belgisch Staatsblad alvorens de datum van 31 december 2024, helaas niet gehaald. We stellen dan ook voor om de inwerkingtreding van het betrokken besluit inderdaad te voorzien voor 31 december 2024, zodoende dat er geen vacuüm en rechtsonzekerheid ontstaat wat de procedures betreft en dus om artikel 24, 1°  en 2°  van het ontwerp te laten vallen. Artikel 24 van het ontwerp zou dan luiden: `Dit besluit heeft uitwerking met ingang van 31 december 2024.' (`Le présent arrêté produit ses effets le 31 décembre 2024.')."11.1. Met de weglating van artikel 24, 1°  en 2°,  van het ontwerp kan worden ingestemd.11.2. De suggestie van de gemachtigde om het besluit zelf uitwerking te geven met ingang van 31 december 2024 zou echter tot gevolg hebben dat aan het te nemen besluit terugwerkende kracht wordt verleend.Het verlenen van terugwerkende kracht aan besluiten kan slechts onder bepaalde voorwaarden toelaatbaar worden geacht, namelijk wanneer ofwel voor de retroactiviteit een wettelijke grondslag bestaat, ofwel de retroactiviteit betrekking heeft op een regeling waarbij, met inachtneming van het gelijkheidsbeginsel, voordelen worden toegekend ofwel de retroactiviteit noodzakelijk is voor de continuïteit of de goede werking van het bestuur en daardoor, in beginsel, geen verkregen situaties worden aangetast. Enkel indien de retroactiviteit van de ontworpen regeling in één van de opgesomde gevallen valt in te passen, kan deze worden gebillijkt.Volgens de gemachtigde is de terugwerkende kracht nodig om te vermijden dat er een vacuüm en rechtsonzekerheid zou ontstaan wat de procedures betreft. Aldus lijkt de gemachtigde te refereren aan de noodzaak voor de continuïteit of de goede werking van het bestuur.11.3. Niettemin moet worden vastgesteld dat verschillende bepalingen van het ontwerp betrekking hebben op procedurele voorschriften, die uit de aard ervan niet met terugwerkende kracht uitwerking kunnen hebben. Wat de materiële bepalingen betreft kan de terugwerkende kracht slechts worden aanvaard voor zover die in te passen is in de in opmerking 11.2 vermelde gevallen.11.4. Het komt de Raad van State echter voor dat de doelstelling van de gemachtigde ook bereikt kan worden zonder een beroep te doen op de terugwerkende kracht. Het lijkt feitelijk te volstaan om de bekendmaking en inwerkingtreding van het te nemen besluit te bespoedigen - bijvoorbeeld op de dag van die bekendmaking - en de inwerkingtredingsbepaling aan te vullen met een overgangsbepaling7 die stipuleert dat op de dag van inwerkingtreding van het te nemen besluit nog hangende aanvragen die werden ingediend voor de datum van inwerkingtreding van het te nemen besluit geacht worden te zijn ingediend onder het koninklijk besluit van 1 september 2004, zoals gewijzigd door het te nemen besluit, en in overeenstemming daarmee zullen worden beoordeeld.8De Griffier,   De Voorzitter,E. Yoshimi   P. Lefranc_______Nota's1 Artikel 3, § 2, tweede lid, van de wet van 13 juni 1969.Artikel 103, § 6, van het milieuvergunningsbesluit luidt als volgt:2 " § 6. De minister betekent het besluit waarvan sprake in artikel 78, § 2 en in artikel 91, § 4, eveneens aan de dienst Continentaal plat".3 Gelet op het ontworpen artikel 22/1 van het koninklijk besluit van 1 september 2004 is het immers niet evident dat er een verlenging van een concessie zou kunnen worden verleend zonder nog lopende (en dus per definitie vooraf toegekende) milieuvergunning, nu de opheffingof het verval van de milieuvergunning volgens die bepaling resulteert in de beëindiging van de concessie. 4 Naar aanleiding van eerdere opmerkingen van de Raad van State werd al het onderscheid tussen de verschillende gevallen van beëindiging van de concessie, namelijk het verstrijken van de concessie, het "intrekken" door de minister en de verzaking door de houder van de concessie, verduidelijkt, zie adv.RvS 75.402/1 van 20 februari 2024 over een ontwerp dat heeft geleid tot het koninklijk besluit van 4 juli 2024 `tot wijziging van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat wat betreft het registreersysteem', opmerking 7. 5 Daar komt bij dat volgens de leer van de intrekking een individuele administratieve rechtshandeling die rechten heeft verleend (zoals het geval is bij een concessie) slechts kan worden ingetrokken wanneer of omdat die onwettig of onregelmatig is; omgekeerd kan een bestuurshandeling die wettig is niet worden ingetrokken, zie bv. RvS nr. 260.429 van 12 juli 2024, T.P. e.a. /Vlaams Gewest en OVAM, punt 8.19. 6 Artikel 6 van de wet van 31 mei 1961 `betreffende het gebruik der talen in wetgevingszaken, het opmaken, bekendmaken en inwerkingtreden van wetten en verordeningen'.7 Voor een gelijkaardige overgangsregeling in deze materie, zie artikel 30 van het koninklijk besluit van 21 oktober 2018 `houdende de regels betreffende de milieueffectenbeoordeling in toepassing van de wet van 13 juni 1969 inzake de exploratie en exploitatie van niet-levende rijkdommen van de territoriale zee en het continentaal plat'.8 De afdeling Wetgeving heeft geen aanwijzingen dat er sinds 31 december 2024 al concessies zouden zijn verleend op basis van de nog aan te nemen regels. Mocht dat toch het geval zijn, zouden die beslissingen uitdrukkelijk moeten worden bevestigd in een bijkomende overgangsbepaling.29 APRIL 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat wat betreft de concessieFILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 13 juni 1969 inzake de exploratie en de exploitatie van de niet-levende rijkdommen van de territoriale zee en het continentaal plat, artikel 3, §§ 2 en 3, vervangen bij de wet van 11 december 2022;Gelet op het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat;Gelet op het advies van de inspecteur van Financiën, gegeven op 2 september 2024;Gelet op advies 77.319/1 van de Raad van State, gegeven op 14 januari 2025, met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Overwegende het koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden;Overwegende het advies van de raadgevende Commissie belast met de coördinatie tussen de administraties die betrokken zijn bij het beheer van de exploratie en de exploitatie van het continentaal plat en de territoriale zee, gegeven op 26 maart 2024;Op de voordracht van de Minister van Economie,Hebben Wij besloten en besluiten Wij :Artikel 1. In artikel 1 van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat, worden de volgende wijzigingen aangebracht:a) de bepaling onder 2°  wordt opgeheven;a) de bepaling onder 7°  wordt opgeheven;b) de bepaling onder 8°,  gewijzigd bij het koninklijk besluit van 21 oktober 2018, wordt vervangen als volgt:"8°  "milieuvergunningsbesluit": koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden;";c) de bepaling onder 8° /1 wordt ingevoegd, luidende:"8° /1 "milieuvergunning": milieuvergunning voor de exploratie en exploitatie van de minerale en andere niet-levende rijkdommen van de zeebodem en van de ondergrond toegekend krachtens titel 5, hoofdstuk II, van het milieuvergunningsbesluit;";d) in de bepaling onder 12°,  vervangen bij het koninklijk besluit van 19 april 2014, worden de woorden "de Beheerseenheid van het Mathematisch Model van de Noordzee en het Schelde-estuarium, zoals bedoeld in het koninklijk besluit van 29 september 1997 houdende de overdracht van de Beheerseenheid van het Mathematisch Model van de Noordzee en het Schelde-estuarium naar" vervangen door de woorden "de wetenschappelijke dienst Beheerseenheid Mathematisch model van de Noordzee van de Operationele Directie Natuurlijk Milieu van";f) in de bepaling onder 18°  wordt het woord "exploitatie" vervangen door de woorden "uitzonderlijke en onvoorzienbare exploitatie";g) de bepaling onder 29°,  vervangen bij het koninklijk besluit van 21 oktober 2018, wordt opgeheven;h) de bepaling onder 30°  wordt opgeheven;i) in de Nederlandstalige tekst van de bepaling onder 31°,  ingevoegd bij het koninklijk besluit van 19 april 2014, worden de woorden "behorende tot" vervangen door het woord "van";j) de bepaling onder 37°,  ingevoegd bij het koninklijk besluit van 21 oktober 2018, wordt opgeheven.Art. 2. In artikel 4 van hetzelfde besluit, vervangen bij het koninklijk besluit van 19 april 2014 en gewijzigd bij het koninklijk besluit van 12 juni 2024, worden de volgende wijzigingen aangebracht:1°  in het eerste lid worden de woorden ", met uitzondering van sectoren 3a en 3b" opgeheven;2°  het tweede lid wordt opgeheven.Art. 3. Artikel 6 van hetzelfde besluit, gewijzigd bij de koninklijke besluiten van 20 maart 2014 en van 12 juli 2022, wordt opgeheven.Art. 4. In artikel 8 van hetzelfde besluit, worden de volgende wijzigingen aangebracht:1°  in paragraaf 1, eerste lid, worden de woorden "worden aan de afgevaardigde van de minister betekend" vervangen door de woorden "worden ingediend bij de afgevaardigde van de minister";2°  in paragraaf 1, tweede lid, vervangen bij het koninklijk besluit van 19 april 2014 en gewijzigd bij het koninklijk besluit van 21 oktober 2018, wordt de zin "De aanvrager betekent het ingevulde formulier met zijn bijlagen, evenals het milieueffectbeoordelingsrapport, zoals beschreven in hoofdstuk 2 van het MEB-besluit, in één van de landstalen in één papieren en één elektronisch exemplaar aan de afgevaardigde van de minister." vervangen als volgt:"Het ingevulde formulier met eventuele bijlagen, wordt in één van de landstalen door de aanvrager betekend of digitaal verstuurd aan de afgevaardigde van de minister.";3°  in paragraaf 2, eerste lid, 4°  worden de woorden "in het geval van een exploratie- en of exploitatie-aanvraag in de controlezones," opgeheven;4°  paragraaf 2, eerste lid, 5°,  gewijzigd bij het koninklijk besluit van 19 april 2014, wordt opgeheven;5°  paragraaf 3, vervangen bij het koninklijk besluit van 19 april 2014, wordt vervangen als volgt:" § 3. De aanvrager kan de aanvraag ten vroegste indienen na ontvangst van het attest ter bevestiging van de volledigheid en ontvankelijkheid zoals bepaald in artikel 101, § 1, van het milieuvergunningsbesluit en moet deze ten laatste één maand na het verkrijgen van de milieuvergunning voor de gevraagde activiteit hebben ingediend.".Art. 5. In artikel 9 van hetzelfde besluit worden de volgende wijzigingen aangebracht:1°  in paragraaf 1 worden de woorden "van het dossier" vervangen door de woorden "van het betekend of ontvangen dossier";2°  in paragraaf 3, eerste lid, worden de woorden "na vaststelling van de volledigheid van het dossier" ingevoegd tussen de woorden "binnen de tien dagen" en de woorden "in een register van concessieaanvragen";3°  in paragraaf 3, derde lid, vervangen bij het koninklijk besluit van 19 april 2014, worden de woorden "en informeert de bevoegde minister en de BMM van deze inschrijving" opgeheven.Art. 6. In hetzelfde besluit worden de volgende artikelen opgeheven:1°  artikel 9/1, ingevoegd bij het koninklijk </t>
+VERSLAG AAN DE KONINGSire,Het koninklijk besluit waarvan ik de eer heb het aan uwe Majesteit ter ondertekening voor te leggen, heeft als doel, in uitvoering van artikel 4 § 3 van de wet van 16 mei 2024 betreffende de bevoegdheden op het nationaal grondgebied van de leden van de Europese grens- en kustwacht, de geografische zones van het nationale grondgebied af te bakenen waarbinnen zij deze bevoegdheden mogen uitoefenen.De bevoegdheden zelf zijn gelinkt aan de toegekende, eveneens bij deze wet bepaald en duidelijk afgebakende taken in het kader van het Europese grensbeheer. Het gaat hierbij meer in het bijzonder om uitoefenen van grenscontrole, grensbewaking en grenstoezicht enerzijds en de terugkeer van onderdanen van derde landen voor wie een door een Europese lidstaat uitgevaardigd terugkeerbesluit werd uitgevaardigd, anderzijds.Daarbij mogen deze functionarissen deze opdrachten enkel uitvoeren onder het gezag van de bevoegde nationale autoriteiten en de politieambtenaar van de Geïntegreerde Politie aan wie de operationele coördinatie en leiding is toevertrouwd. Met andere woorden treden zij nooit autonoom op op ons grondgebied.Artikel 1 heeft betrekking op de grenscontroletaken bedoeld in artikel 4, § 1, tweede lid, 1°  en 2°  van de wet van 16 mei 2024 en definieert in dit opzicht de geografische gebieden waarbinnen deze functionarissen kunnen worden ingezet voor grenscontroles, grensbewaking en grenstoezicht. Hun modaliteiten en locaties zijn bepaald in de Schengen Grenscode.. De binnen dit artikel weerhouden geografische zones zijn de grensdoorlaatposten opgenomen in bijlage 4 aan het gemeenschappelijke praktisch handboek voor grenswachters (Schengenhandboek), die samen de buitengrenzen van het Schengengebied in België uitmaken.De lijst van geografische zones is de volgende :A) De infrastructuur van de luchthavens van :- Brussel-Nationaal (Zaventem) ;- Oostende ;- Deurne ;- Bierset ;- Gosselies ;- Wevelgem.B) De infrastructuur van de haven van :- Antwerpen ;- Oostende ;- Zeebrugge ;- Nieuwpoort ;- Gent ;- Blankenberge.C) De volgende spoorweginfrastructuur :- De internationale treinverbinding tussen het Verenigd Koninkrijk en het Belgisch grondgebied ;- Het station van Brussel-Zuid.Onder infrastructuur verstaan we de ruimtes die toegankelijk moeten zijn voor de leden van het permanent korps om hun taken uit te voeren. Het gaat hier bijvoorbeeld om de grenscontroleboxen, de gebouwen, gevoelige zones zoals de landingsbanen en tarmacs van luchthavens, de transithallen, de spoorweg- en havenperrons, evenals elke andere locatie die nodig is voor de uitvoering van hun taken.Artikel 2 legt het kader vast voor de betrokkenheid van deze Frontex-functionarissen bij gedwongen terugkeeroperaties, onder verstaan de terugkeer van onderdanen van derde landen ten aanzien van wie een Europese lidstaat een terugkeerbesluit heeft genomen.Om de rechtszekerheid, duidelijkheid en samenhang van gedwongen terugkeeroperaties te garanderen, zijn de plaatsen die essentieel zijn voor het uitvoeren van de taak gedefinieerd op basis van hun specifieke rol bij het uitvoeren van deze operaties, zonder een uitputtende lijst op te stellen.Om dit te kunnen doen, moeten de functionarissen namelijk het hele traject kunnen afleggen, van de plaats waar de uit te zetten personen zich bevinden, zoals gesloten centra of penitentiaire instellingen, tot de plaats van verwijdering.In functie van de modaliteiten van de gedwongen repatriëring, kan die plaats van verwijdering een buitengrens zijn zoals gedefinieerd in artikel 1. In dit geval is de gekozen benadering natuurlijk niet beperkt tot repatriëring per vliegtuig, maar geldt deze voor alle vormen van terugkeer waarin dit artikel voorziet, inclusief bijvoorbeeld terugkeer per trein. Het kan ook gaan om een grenszone met de buurlanden, waar de overgave en overname van de betrokken persoon zich voltrekken in overeenstemming met de bepalingen van de toepasselijke bilaterale of multilaterale verdragen. Om de verdeling van de bevoegdheden te respecteren en elke dubbelzinnigheid over de territoriale gelding van het besluit te vermijden, vallen plaatsen buiten het Belgische grondgebied, zoals luchthavens van andere lidstaten van het Schengengebied, niet onder het besluit. Grensoverschrijdende operaties blijven echter mogelijk, op voorwaarde dat ze binnen het kader vallen van de geldende bilaterale of multilaterale instrumenten, die met name de modaliteiten voor overgave en overname aan de grens regelen.Als voorbeeld van toepasselijke bilaterale en multilaterale verdragen is er het Benelux-verdrag, en meer specifiek diens artikel 25 betreffende het "Grensoverschrijdend vervoer en begeleiding van personen en goederen", dat van toepassing is op gedwongen terugkeerprocedures tussen België, Nederland en Luxemburg.Daarnaast is, artikel 13 van het Akkoord van Doornik II (Akkoord tussen de regering van het Koninkrijk België en de regering van de Franse Republiek betreffende grensoverschrijdende samenwerking op het gebied van politie en douane) van toepassing op verwijderingsoperaties van betrokken personen tussen België en Frankrijk.In de context van gedwongen terugkeer is samenwerking tussen EU-lidstaten essentieel om naleving van de Europese normen te waarborgen en tegelijkertijd de rechten van de betrokken personen te beschermen.De Richtlijn 2008/115/EG (de terugkeerrichtlijn) gemeenschappelijke normen en procedures vastgesteld voor de terugkeer van onderdanen van derde landen die onrechtmatig in de EU-lidstaten verblijven. In deze richtlijn worden de voorwaarden vastgesteld waaronder een gedwongen terugkeer kan worden uitgevoerd, waarbij procedurele waarborgen worden geboden om de rechten van de betrokken personen te beschermen en wordt gezorgd voor een soepele samenwerking tussen de lidstaten.Brussel, 15 mei 2025.Ik heb de eer te zijn,Sire,Van Uwe Majesteit,de zeer eerbiedige en zeer getrouwe dienaar,De Minister van Binnenlandse Zaken,B. QUINTINDe Minister van Justitie,A. VERLINDEN15 MEI 2025. - Koninklijk besluit tot uitvoering van artikel 4 § 3 van de wet van 16 mei 2024 betreffende de bevoegdheden op het nationale grondgebied van de leden van de Europese grens- en kustwachtFILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 16 mei 2024 betreffende de bevoegdheden op het nationale grondgebied van de leden van de Europese grens- en kustwacht, artikel 4, § 3;Gelet op het advies van de Inspecteur-generaal van Financiën, gegeven op 12 maart 2024;Gelet op de akkoordbevinding van de Staatssecretaris van Begroting, gegeven op 14 maart 2024;Gelet op advies 76.399/2 van de Raad van State, gegeven op 17 juni 2024 met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Op de voordracht van de Minister van Binnenlandse Zaken en van de Minister van Justitie en op het advies van de in Raad vergaderde Ministers,Hebben Wij besloten en besluiten Wij :Artikel 1. De geografische zones van het nationale grondgebied waar de leden van het permanent korps de opdrachten bedoeld in artikel 4, §  1, lid 2, 1°  en 2 van de wet van 16 mei 2024 over de bevoegdheden van de leden van de Europese grenswacht en de kustwacht op het nationale grondgebied, mogen uitoefenen, zijn onze buitengrenzen van het Schengengebied en meer bepaald de infrastructuren waarin onze officieel door de Europese Unie erkende grensdoorlaatposten zich bevinden, namelijk :a) de infrastructuur van de luchthavens van:- Brussel-Nationaal (Zaventem);- Oostende;- Deurne;- Bierset;- Gosselies;- Wevelgem.b) de infrastructuur van de havens van :- Antwerpen;- Oostende;- Zeebrugge;- Nieuwpoort;- Gent;- Blankenberge.c) de volgende spoorweginfrastructuur :- de internationale treinverbinding tussen het Verenigd Koninkrijk en het Belgisch grondgebied ;- het station van Brussel-Zuid.Art. 2. Voor de uitvoering van de opdracht bedoeld in artikel 4, § 1, lid 2, 3°,  mogen de leden van het permanent korps hun bevoegdheden uitoefenen op elke locatie die nodig is voor de operationele uitvoering van gedwongen terugkeeroperaties, namelijk:a) de locaties waar onderdanen van derde landen die zich onregelmatig op het grondgebied bevinden, worden vastgehouden of in hechtenis genomen in afwachting van hun verwijdering;b) de routes die worden gevolgd ter uitvoering van deze maatregel, vanaf de in punt a) bedoelde locatie tot de plaats van verwijdering, zijnde:- een locatie vermeld in artikel 1; of- een grenszone met een buurland, waar de overdracht en overname van de in punt a) bedoelde persoon plaatsvinden overeenkomstig de bepalingen van de toepasselijke bilaterale of multilaterale verdragen.Art. 3. Dit besluit treedt in werking op de eerste dag van de maand na die waarin ze is bekendgemaakt in het Belgisch Staatsblad.Art. 4. De ministers bevoegd voor Binnenlandse Zaken en Justitie zijn belast met de uitvoering van dit besluit.Gegeven te Brussel, 15 mei 2025.FILIPVan Koningswege :De Minister van Binnenlandse Zaken,B. QUINTINDe Minister van Justitie,A. VERLINDEN 
+</t>
         </is>
       </c>
     </row>
@@ -779,28 +779,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025003467</t>
+          <t>2025201055</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12 mei 2025</t>
+          <t>23 mei 2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28 april 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 12 december 2018 tot vaststelling van de tegemoetkoming van de verplichte verzekering in de verpleegdagprijs in geval van opneming in een ziekenhuis in het buitenland</t>
+          <t>13 mei 2025. - Koninklijk besluit houdende benoeming van raadsheren en rechters in sociale zaken (1)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-12&amp;numac_search=2025003467&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003467=10&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-23&amp;numac_search=2025201055&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201055=10&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, artikel 37, § 7;Gelet op het koninklijk besluit van 12 december 2018 tot vaststelling van de tegemoetkoming van de verplichte verzekering in de verpleegdagprijs in geval van opneming in een ziekenhuis in het buitenland;Gelet op het advies van de Commissie voor begrotingscontrole, gegeven op 8 januari 2025, met toepassing van artikel 2, eerste lid, van het koninklijk besluit nr. 20 van 13 mei 2020 houdende tijdelijke maatregelen in de strijd tegen de COVID-19 pandemie en ter verzekering van de continuïteit van zorg in de verplichte verzekering voor geneeskundige verzorging;Gelet op het advies van het Comité van de verzekering voor geneeskundige verzorging, gegeven op 13 januari 2025, met toepassing van artikel 2, eerste lid, van het koninklijk besluit nr. 20 van 13 mei 2020 houdende tijdelijke maatregelen in de strijd tegen de COVID-19 pandemie en ter verzekering van de continuïteit van zorg in de verplichte verzekering voor geneeskundige verzorging;Gelet op het advies van de inspecteur van Financiën, gegeven op 31 januari 2025;Gelet op de akkoordbevinding van de minister voor Begroting, gegeven op 27 februari 2025;Gelet op het advies 77.573/2 van de Raad van State, gegeven op 8 april 2025, met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Op de voordracht van de Minister van Sociale Zaken;Hebben Wij besloten en besluiten Wij :Artikel 1. Artikel 1, § 3 van het koninklijk besluit van 12 december 2018 tot vaststelling van de tegemoetkoming van de verplichte verzekering in de verpleegdagprijs in geval van opneming in een ziekenhuis in het buitenland wordt vervangen als volgt:"Voor het tijdvak van 1 januari 2025 tot en met 31 december 2025 is de in § 1 bedoelde verpleegdagprijs vastgesteld op 820,57 euro.".Art. 2. Dit besluit treedt in werking op 1 januari 2025.Art. 3. De minister bevoegd voor Sociale zaken is belast met de uitvoering van dit besluit.Gegeven te Brussel, 28 april 2025.FILIPVan Koningswege :De Minister van Sociale Zaken,F. VANDENBROUCKE 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op het Gerechtelijk Wetboek inzonderheid op de artikelen 198 tot 201, 202, gewijzigd bij de wet van 6 mei 1982, 206, gewijzigd bij de wet van 15 mei 1987, en 216; Gelet op het koninklijk besluit van 7 april 1970 tot vaststelling van het aantal rechters en raadsheren in sociale zaken en van de wijze van voordracht van de kandidaten, gewijzigd bij de koninklijke besluiten van 16 juni 2006 en 25 maart 2014; Gelet op de kandidatenlijsten voorgedragen door de representatieve werkgevers- en werknemersorganisaties; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Tot werkend raadsheer in sociale zaken, als werknemer-arbeider bij het Arbeidshof van Brussel wordt benoemd: - behorend tot het Franse taalstelsel: de heer RENARD Olivier, te ELSENE. Art. 2. Tot werkend raadsheer in sociale zaken, als werknemer-bediende bij het Arbeidshof van Brussel wordt benoemd: - behorend tot het Franse taalstelsel: de heer GUILLOTTE Jean-François, te RAMILLIES. Art. 3. Tot werkend rechter in sociale zaken, als werknemer-arbeider bij de Arbeidsrechtbank van Luik arrondissement Luik worden benoemd: de heer COCX Jean, te BITSINGEN; de heer LEONARD Jean, te VERVIERS; de heer VICARI Roberto, te LUIK. Art. 4. Tot werkend rechter in sociale zaken, als werkgever bij de Arbeidsrechtbank van Luik arrondissement Namen wordt benoemd: de heer RADERMECKER Christian, te HANNUIT. Art. 5. Dit besluit heeft uitwerking met ingang van 1 november 2024. Art. 6. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzingen naar het Belgisch Staatsblad: Koninklijk besluit van 7 april 1970, Belgisch Staatsblad van 24 april 1970. Koninklijk besluit van 16 juni 2006, Belgisch Staatsblad van 28 juni 2006, Koninklijk besluit van 25 maart 2014, Belgisch Staatsblad van 28 maart 2014.
 </t>
         </is>
       </c>
@@ -811,28 +811,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025003470</t>
+          <t>2025200931</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>28 april 2025. - Koninklijk besluit tot wijziging van artikel 25, § 3bis, van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen</t>
+          <t>13 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 11 december 2023, gesloten in het Paritair Comité voor gezondheidsinrichtingen en -diensten, betreffende de toekenning van een uitzonderlijk bedrag in 2023 bovenop de eindejaarstoelage voor de ambulante sectoren van Brussel (1)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-13&amp;numac_search=2025003470&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003470=11&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025200931&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200931=11&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, artikel 35, § 1, vijfde lid, en § 2, eerste lid, 1°,  gewijzigd bij het koninklijk besluit van 25 april 1997, bekrachtigd bij de wet van 12 december 1997;Gelet op het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen;Gelet op het voorstel van de Technische geneeskundige raad, gedaan tijdens zijn vergadering van 25 oktober 2022 ;Gelet op het advies van de Dienst voor geneeskundige evaluatie en controle van het Rijksinstituut voor ziekte- en invaliditeitsverzekering, gegeven op 25 oktober 2022;Gelet op de beslissing van de Nationale commissie artsen-ziekenfondsen van 12 december 2022;Gelet op het advies van de Commissie voor begrotingscontrole, gegeven op 1 maart 2023;Gelet op de beslissing van het Comité van de verzekering voor geneeskundige verzorging van het Rijksinstituut voor ziekte- en invaliditeitsverzekering van 27 maart 2023;Gelet op het advies van de Inspecteur van Financiën, gegeven op 17 februari 2025;Gelet op de akkoordbevinding van de Minister van Begroting van 27 februari 2025;Gelet op advies 77.601/2 van de Raad van State, gegeven op 14 april 2025, met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Op de voordracht van de Minister van Sociale Zaken,Hebben Wij besloten en besluiten Wij :Artikel 1. In artikel 25, § 3bis, van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen, laatstelijk gewijzigd bij het koninklijk besluit van 19 juli 2024, wordt in de vijfde toepassingsregel na de verstrekking 590450 het tweede lid van de bepaling onder 5°  vervangen als volgt:"Het verslag maakt deel uit van het medisch dossier van de patiënt en wordt overgemaakt aan de huisarts die het globaal medisch dossier beheert, en de verwijzende arts.".Art. 2. Dit besluit treedt in werking op de eerste dag van de tweede maand na die waarin het is bekendgemaakt in het Belgisch Staatsblad.Art. 3. De minister bevoegd voor Sociale Zaken is belast met de uitvoering van dit besluit.Gegeven te Brussel, 28 april 2025.FILIPVan Koningswege :De Minister van Sociale Zaken en Volksgezondheid,F. VANDENBROUCKE . 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor gezondheidsinrichtingen en -diensten; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 11 december 2023, gesloten in het Paritair Comité voor gezondheidsinrichtingen en -diensten, betreffende de toekenning van een uitzonderlijk bedrag in 2023 bovenop de eindejaarstoelage voor de ambulante sectoren van Brussel. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor gezondheidsinrichtingen en -diensten Collectieve arbeidsovereenkomst van 11 december 2023 Toekenning van een uitzonderlijk bedrag in 2023 bovenop de eindejaarstoelage voor de ambulante sectoren van Brussel (Overeenkomst geregistreerd op 25 januari 2024 onder het nummer 185580/CO/330) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en werknemers van de sociale diensten, de diensten voor geestelijke gezondheid, van de hulp aan rechtzoekenden en andere ambulante diensten - met uitzondering van de wijkgezondheidscentra - die ressorteren onder het Paritair Comité voor de gezondheidsinrichtingen en -diensten en die erkend en gesubsidieerd zijn door de Gemeenschappelijke Gemeenschapscommissie of door de Franse Gemeenschapscommissie van het Brusselse Hoofdstedelijk Gewest. Onder "werknemers" wordt verstaan : het mannelijk en vrouwelijk werklieden- en bediendepersoneel. Art. 2. Deze collectieve arbeidsovereenkomst voorziet in de toekenning van een uitzonderlijk bedrag in 2023 bovenop de eindejaarstoelage betreffende het jaar 2023 voor de ambulante sectoren van Brussel zoals bepaald door de collectieve arbeidsovereenkomst van 12 december 2022. Dit uitzonderlijk bedrag is : - 1 415,52 EUR voor de ambulante sectoren erkend en gesubsidieerd door de GGC; - 961,6073 EUR voor de ambulante sectoren erkend en gesubsidieerd door de FGC. Art. 3. Dit uitzonderlijk bedrag dat wordt toegevoegd aan de eindejaarstoelage wordt berekend en vereffend volgens dezelfde modaliteiten als die waarin voorzien is door de collectieve arbeidsovereenkomst van 12 december 2022 betreffende de eindejaarstoelage voor de ambulante sectoren van Brussel. Art. 4. De voorwaarde voor de toepassing van deze overeenkomst is : - dat de Franse Gemeenschapscommissie haar financieringsverbintenissen moet uitvoeren, zoals gespecificeerd in de omzendbrief van de Franse Gemeenschapscommissie van 28 november 2023 aan de centra, diensten en tehuizen gesubsidieerd in het kader van het "non-profit-decreet" van 18 oktober 2001, getiteld "eindejaarspremie 2023"; - dat de Gemeenschappelijke Gemeenschapscommissie haar financieringsverbintenissen moet uitvoeren zoals gespecificeerd in de circulaire van de Gemeenschappelijke Gemeenschapscommissie van 6 december 2023 voor de sectoren binnen de non-profit perimeter van de GGC die niet op IFIC zijn overgeschakeld. Art. 5.  Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2023. Zij wordt gesloten voor een bepaalde duur van 1 januari 2023 tot 31 december 2023. Gezien om te worden gevoegd bij het koninklijk besluit van 13 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -843,29 +843,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025201342</t>
+          <t>2025000801</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>02 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit tot hernieuwing van de mandaten van de Wetenschappelijke Raad, ingesteld bij het Federaal agentschap voor beroepsrisico's</t>
+          <t>13 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 29 juni 2023, gesloten in het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap, tot wijziging van de collectieve arbeidsovereenkomst van 28 november 2019 betreffende het geldelijk statuut van het personeel AAJ - SASPE (Overeenkomst geregistreerd op 4 februari 2020 onder het nummer 156747/CO/319.02) (1)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-02&amp;numac_search=2025201342&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025201342=12&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025000801&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025000801=12&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wetten betreffende de preventie van beroepsziekten en de vergoeding van de schade die uit die ziekten voortvloeit, gecoördineerd op 3 juni 1970, artikel 6bis, gewijzigd bij de wet van 13 juli 2006; Gelet op het koninklijk besluit van 25 februari 2007 tot vaststelling van de samenstelling van de Wetenschappelijke Raad en de oprichting van Medische Commissies bij Fedris en tot bepaling van het bedrag van de vergoedingen en presentiegelden toegekend aan de voorzitter en de leden van deze verschillende organen; gewijzigd bij koninklijk besluit van 19 juli 2013; Gelet op het advies van het beheerscomité van het Federaal agentschap voor beroepsrisico's, gegeven op 12 maart 2025; Op de voordracht van de Minister van Sociale Zaken, Hebben Wij besloten en besluiten Wij :Artikel 1. : Worden benoemd, voor een termijn van zes jaar, ingaande op 1 mei 2025, in hoedanigheid van leden van de Wetenschappelijke Raad, ingesteld bij het Federaal agentschap voor beroepsrisico's: 1° In de hoedanigheid van artsen, gespecialiseerd inzake arbeidsgeneeskunde en/of beroepsziekten voorgedragen door de Faculteit geneeskunde van elk van de universiteiten die een specialisatie in de arbeidsgeneeskunde inricht: Université Catholique de Louvain Effectief lid: Mevr. Dahlqvist Caroline Plaatsvervangend lid: Mevr. Gohy SophieKatholieke Universiteit Leuven Effectief lid: Dhr. Godderis Lode Plaatsvervangend lid: Mevr. Lambreghts CharlotteUniversité libre de Bruxelles Effectief lid: Mevr. Haccuria Amaryllis Plaatsvervangend lid: Dhr. Leduc DimitriUniversité de Liège Effectief lid: Mevr. Rusu Donna Plaatsvervangend lid: Dhr. Borguet MarcVrije Universiteit Brussel Effectief lid: Dhr. Versée Mathieu Plaatsvervangend lid: Mevr. Hanon Shane Universiteit Gent Effectief lid: Mevr. Braeckman Lutgart Plaatsvervangend lid: Mevr. Schepens VeerleUniversiteit Antwerpen Effectief lid: Mevr. Acke Sofie Plaatsvervangend lid: Mevr. Claesen Bieke 2° In de hoedanigheid van ingenieurs gespecialiseerd inzake voorkoming van beroepsziekten: Effectieve leden: Dhr. Boogaerts Geert Dhr. Jaupart Samuel Plaatsvervangende leden: Dhr. Van Bouwel Jan 3° In de hoedanigheid van deskundigen in het domein van de scheikunde en twee plaatsvervangers, bijzonder bekwaam inzake industriële toxicologie: Effectieve leden: Dhr. Sanchez Diez Ernesto 4° In de hoedanigheid van artsen gespecialiseerd inzake beroepsziekten, verbonden aan de Algemene Directie Toezicht op het Welzijn op het Werk van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg: Effectieve leden: Dhr. Reyntjes Paulo Dhr. Gahide Désiré Plaatsvervangende leden Dhr. D'Hondt Cynthia Mevr. Lysens Katrien 5° In de hoedanigheid van artsen van het Federaal agentschap voor beroepsrisico's: Effectieve leden: Mevr. Phillips Chantal Dhr. Henriquez Carlos Plaatsvervangende leden: Dhr. Poot Olivier Mevr Van Raemdonck Anuschka 6° In de hoedanigheid van preventieadviseurs-arbeidsartsen, waarvan de ene verbonden is aan een interne dienst voor preventie en bescherming op het werk en de andere aan een externe dienst voor preventie en bescherming op het werk, voorgedragen door de meest representatieve organisaties van preventieadviseurs-arbeidsartsen: Effectief lid: Mevr. Nana Nanjouo Carine Laure Plaatsvervangend lid: Dhr. Rotsaert Paul 7° In de hoedanigheid van deskundigen aangeduid door de representatieve organisaties die zetelen in het Beheerscomité van het Federaal agentschap voor beroepsrisico's: Effectieve leden: Dhr. De Meester Kris Dhr. Van Eyck Kris Plaatsvervangende leden: Mevr. Verdoot Caroline Art. 2. Wordt benoemd voor een termijn van zes jaar, ingaande op 1 mei 2025, in hoedanigheid van voorzitter van de Wetenschappelijke Raad, ingesteld bij het Federaal agentschap voor beroepsrisico's: Dhr. Godderis Lode Art. 3. Dit besluit treedt in werking op 1 mei 2025. Art. 4. De minister bevoegd voor Sociale Zaken is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege : De Minister van Sociale Zaken, F. VANDENBROUCKE 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 29 juni 2023, gesloten in het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap, tot wijziging van de collectieve arbeidsovereenkomst van 28 november 2019 betreffende het geldelijk statuut van het personeel AAJ - SASPE (Overeenkomst geregistreerd op 4 februari 2020 onder het nummer 156747/CO/319.02).Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 13 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige GemeenschapCollectieve arbeidsovereenkomst van 29 juni 2023Wijziging van de collectieve arbeidsovereenkomst van 28 november 2019 betreffende het geldelijk statuut van het personeel AAJ - SASPE (Overeenkomst geregistreerd op 4 februari 2020 onder het nummer 156747/CO/319.02) (Overeenkomst geregistreerd op 27 juli 2023 onder het nummer 181180/CO/319.02)HOOFDSTUK I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is uitsluitend van toepassing op de werknemers en de werkgevers van de inrichtingen en diensten van de "Aide à la Jeunesse" en van de "Services d'Accueil Spécialisés de la Petite Enfance" die ressorteren onder het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap.Art. 2. Onder "werknemers" wordt verstaan :- de mannelijke en vrouwelijke bedienden;- de werklieden en werksters.HOOFDSTUK II. - WijzigingArt. 3. Met toepassing van het "Raamakkoord voor de non-profitsector van de Federatie Wallonië-Brussel 2022-2025" van 28 april 2023, op basis van de middelen toegewezen in 2023 en 2024, komen de partijen het volgende overeen :"Vanaf 1 juli 2023 worden de loonbarema's die van toepassing zijn op de werknemers bedoeld in de artikelen 1 en 2, opgenomen in bijlage van deze overeenkomst. Deze bijlage vervangt de bijlage V van de collectieve arbeidsovereenkomst van 28 november 2019 betreffende het geldelijk statuut van het personeel AAJ - SASPE.".HOOFDSTUK III. - EindbepalingenArt. 4. Deze collectieve arbeidsovereenkomst treedt in werking op 1 juli 2023 en wordt gesloten voor onbepaalde duur.Mits inachtneming van een opzeggingstermijn van zes maanden kan ze door één van de ondertekenende partijen worden opgezegd via een aangetekend schrijven dat gericht is aan de voorzitter van het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap.Gezien om te worden gevoegd bij het koninklijk besluit van 13 mei 2025.De Minister van Werk,D. CLARINVAL Bijlage aan de collectieve arbeidsovereenkomst van 29 juni 2023, gesloten in het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap, tot wijziging van de collectieve arbeidsovereenkomst van 28 november 2019 betreffende het geldelijk statuut van het personeel AAJ - SASPE (Overeenkomst geregistreerd op 4 februari 2020 onder het nummer 156747/CO/319.02) Jaarlijkse barema's die van toepassing zijn op 1 juli 2023/(index 117,17)   </t>
         </is>
       </c>
     </row>
@@ -875,28 +874,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025201150</t>
+          <t>2025200934</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>06 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit tot benoeming van de werkende en plaatsvervangende leden van het Comité overheidsbedrijven, bedoeld in artikel 31, § 6, derde en vierde lid, van de wet van 21 maart 1991 tot hervorming van sommige economische overheidsbedrijven</t>
+          <t>13 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 29 november 2023, gesloten in het Paritair Comité voor de schoonmaak, tot wijziging van de collectieve arbeidsovereenkomst van 12 mei 2003 betreffende de personeelsovername ten gevolge van hergunning van een onderhoudscontract (1)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-06&amp;numac_search=2025201150&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025201150=13&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025200934&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200934=13&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 21 maart 1991 tot hervorming van sommige economische overheidsbedrijven, artikel 31, § 6, derde en vierde lid; Gelet op het koninklijk besluit van 13 januari 1997 betreffende de werking en de samenstelling van het Comité overheidsbedrijven, artikelen 1 en 2; Gelet op het koninklijk besluit van 22 mei 2014 houdende benoeming van de werkende en plaatsvervangende leden van het Comité overheidsbedrijven, bedoeld in artikel 31, § 6, derde en vierde lid, van de wet van 21 maart 1991 tot hervorming van sommige economische overheidsbedrijven;Gelet op het voorstel van de raad van bestuur van bpost van 8 mei 2024; Gelet op de voorstellen van de raad van bestuur van Proximus van 19 september 2024; Gelet op het voorstel van de raad van bestuur van HR Rail van 21 oktober 2024; Gelet op het voorstel van de raad van bestuur van skeyes van 28 november 2024; Gelet op het voorstel van de raad van bestuur van de Nationale Maatschappij voor Belgische Spoorwegen van 13 december 2024; Gelet op het voorstel van de raad van bestuur van Infrabel van 21 januari 2025; Gelet op het advies van de Inspecteur van Financiën, gegeven op 1 april 2025; Op de voordracht van de Eerste Minister en op advies van de in Raad vergaderde Ministers, Hebben Wij besloten en besluiten Wij : Artikel 1. Worden voor een termijn van zes jaar benoemd tot werkende leden van het Comité overheidsbedrijven: a) op voorstel van bpost: - Mevr. An Matthynssens - Mevr. Inge Wevers - De heer Arnaud Parent b) op voorstel van Proximus: - Mevr. Olivia Rolin - De heer Karel Meeusen c) op voorstel van skeyes: - De heer Geert Malfliet - De heer Réginald de Borman d) op voorstel van de Nationale Maatschappij voor Belgische Spoorwegen: - Mevr. Sofia Kolibos e) op voorstel van Infrabel: - De heer Lander Decorte f) op voorstel van HR Rail: - Mevr. Sarah Blancke Art. 2. Worden voor een termijn van zes jaar benoemd tot plaatsvervangende leden van het Comité overheidsbedrijven: a) op voorstel van bpost: - De heer Peter Claes - De heer Dominique Piret - Mevr. Céline Moreau b) op voorstel van Proximus: - Mevr. Kristel Jans - Mevr. Valérie Vermeire c) op voorstel van skeyes: - De heer Egon Michiels - Mevr. Audrey Dorigo d) op voorstel van de Nationale Maatschappij voor Belgische Spoorwegen: - De heer Erwin Deyaert e) op voorstel van Infrabel: - Mevr. Maud Storme f) op voorstel van HR Rail: - Mevr. Leen De Ridder Art. 3. Het koninklijk besluit van 22 mei 2014 houdende benoeming van de werkende en plaatsvervangende leden van het Comité overheidsbedrijven, bedoeld in artikel 31, § 6, derde en vierde lid, van de wet van 21 maart 1991 tot hervorming van sommige economische overheidsbedrijven, wordt opgeheven. Art. 4. Dit besluit treedt heden in werking. Art. 5. De Eerste Minister is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege : De Eerste Minister, B. DE WEVER 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de schoonmaak; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 29 november 2023, gesloten in het Paritair Comité voor de schoonmaak, tot wijziging van de collectieve arbeidsovereenkomst van 12 mei 2003 betreffende de personeelsovername ten gevolge van hergunning van een onderhoudscontract. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de schoonmaak Collectieve arbeidsovereenkomst van 29 november 2023 Wijziging van de collectieve arbeidsovereenkomst van 12 mei 2003 betreffende de personeelsovername ten gevolge van hergunning van een onderhoudscontract (Overeenkomst geregistreerd op 18 december 2023 onder het nummer 184686/CO/121) Toepassingsgebied Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de werklieden en werksters uit de ondernemingen welke onder het Paritair Comité voor de schoonmaak ressorteren, kleine en middelgrote ondernemingen en anderen. Deze collectieve arbeidsovereenkomst zal eveneens van toepassing zijn op elke arbeider of werkster in loondienst, met contract voor onbepaalde of voor bepaalde duur, voor werkzaamheden die in België worden uitgevoerd, welke ook het vestigingsland van de werkgever weze. Artikel 1. In alinea 1 van artikel 3 van de collectieve arbeidsovereenkomst van 12 mei 2003 betreffende de personeelsovername ten gevolge van hergunning van een onderhoudscontract, algemeen verbindend verklaard bij koninklijk besluit vaan 19 juli 2006, gepubliceerd in het Belgisch Staatsblad van 1 september 2006 (67603/CO/121) worden de woorden "waarbij minstens 3 arbeiders betrokken zijn" geschrapt. Alinea 2 van hetzelfde artikel 3 wordt geschrapt. Art. 2.  In artikel 6 van dezelfde collectieve arbeidsovereenkomst, wordt de zin "Deze periode wordt echter op 3 maanden gebracht voor de wisseling van onderhoudscontracten waarbij minder dan 3 arbeiders betrokken zijn" geschrapt.Art. 3. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2024 en heeft dezelfde geldigheidsduur, dezelfde opzeggingsmodaliteiten en -termijnen als de arbeidsovereenkomst welke zij wijzigt. Gezien om te worden gevoegd bij het koninklijk besluit van 13 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -907,29 +906,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025201385</t>
+          <t>2025000767</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>07 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit tot verlenging van de taalkaders voor het personeel van het Grondwettelijk Hof</t>
+          <t>13 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 13 juni 2024, gesloten in het Aanvullend Paritair Comité voor de bedienden, betreffende de invoering van een sectoraal aanvullend pensioenstelsel voor de Bedienden Ondernemingsactiviteit Terugwinning van Metalen (SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen) (1)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-07&amp;numac_search=2025201385&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025201385=14&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025000767&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025000767=14&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de bijzondere wet van 6 januari 1989 op het Grondwettelijk Hof, de artikelen 42 en 66; Gelet op de wetten op het gebruik van de talen in bestuurszaken, gecoördineerd op 18 juli 1966, artikel 43, § 3; Gelet op het koninklijk besluit van 25 februari 2007 tot vaststelling, met het oog op de toepassing van artikel 43 van de wetten op het gebruik van de talen in bestuurszaken, gecoördineerd op 18 juli 1966, van de betrekkingen van het personeel van het Grondwettelijk Hof die eenzelfde trap van de hiërarchie vormen en tot goedkeuring van de taalkaders voor het personeel van het Grondwettelijk Hof, gewijzigd bij het koninklijk besluit van 19 december 2014; Gelet op het koninklijk besluit van 28 juni 2019 tot verlenging van de taalkaders voor het personeel van het Grondwettelijk Hof; Gelet op de beschikking van het Grondwettelijk Hof van 18 december 2024 tot vaststelling van de taalkaders voor het personeel van het Grondwettelijk Hof; Overwegende dat voldaan werd aan de voorschriften van artikel 54, tweede lid, van de voormelde wetten op het gebruik van de talen in bestuurszaken; Gelet op het advies nr. 57.023 van de Vaste Commissie voor Taaltoezicht, gegeven op 28 februari 2025; Gelet op het advies van de Inspecteur van Financiën, gegeven op 4 april 2025; Gelet op het artikel 8, § 1, 3°, van de wet van 15 december 2013 houdende diverse bepalingen inzake administratieve vereenvoudiging, houdende de vrijstelling van een regelgevingsimpactanalyse omdat het een formele beslissing betreft; Op de voordracht van de Eerste Minister en op het advies van de in Raad vergaderde Ministers, Hebben Wij besloten en besluiten Wij : Artikel 1. De taalkaders voor het personeel van het Grondwettelijk Hof, vastgesteld bij artikel 2 van het koninklijk besluit van 25 februari 2007 tot vaststelling, met het oog op de toepassing van artikel 43 van de wetten op het gebruik van de talen in bestuurszaken, gecoördineerd op 18 juli 1966, van de betrekkingen van het personeel van het Grondwettelijk Hof die eenzelfde trap van de hiërarchie vormen en tot goedkeuring van de taalkaders voor het personeel van het Grondwettelijk Hof, en laatst verlengd bij koninklijk besluit van 28 juni 2019, worden verlengd. Art. 2. Dit besluit heeft uitwerking met ingang van 1 maart 2025. Art. 3. De Eerste Minister is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Eerste Minister, B. DE WEVER 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Aanvullend Paritair Comité voor de bedienden;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 13 juni 2024, gesloten in het Aanvullend Paritair Comité voor de bedienden, betreffende de invoering van een sectoraal aanvullend pensioenstelsel voor de Bedienden Ondernemingsactiviteit Terugwinning van Metalen (SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen).Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 13 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageAanvullend Paritair Comité voor de bediendenCollectieve arbeidsovereenkomst van 13 juni 2024Invoering van een sectoraal aanvullend pensioenstelsel voor de Bedienden Ondernemingsactiviteit Terugwinning van Metalen (SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen) (Overeenkomst geregistreerd op 2 september 2024 onder het nummer 189430/CO/200)HOOFDSTUK I. - BegripsomschrijvingenArtikel 1. Voor de toepassing van deze collectieve arbeidsovereenkomst en haar bijlagen, moeten de hierna vermelde begrippen als volgt worden begrepen :- Arbeiders Ondernemingsactiviteit Terugwinning van Metalen : de arbeiders die ressorteren onder PSC 142.01;- Bedienden Ondernemingsactiviteit Terugwinning van Metalen : de bedienden die ressorteren onder PC 200 en werkzaam zijn in de Ondernemingsactiviteit Terugwinning van Metalen en zich in een vergelijkbare situatie bevinden als de Arbeiders Ondernemingsactiviteit Terugwinning van Metalen met wie zij voor doeldoeleinden van het aanvullend pensioen "spiegelen" in de zin van artikel 14 van de WAP. Zij worden overeenkomstig de regels van deze collectieve arbeidsovereenkomst toegewezen aan deze specifieke subcategorie;- Cao van PC 200 van 1 juli 2019 : de collectieve arbeidsovereenkomst van 1 juli 2019 gesloten in PC 200 betreffende de koopkracht in het kader van het koninklijk besluit van 19 april 2019 tot uitvoering van artikel 7, §  1 van de wet van 26 juli 1996 tot bevordering van de werkgelegenheid en tot preventieve vrijwaring van het concurrentievermogen met registratienummer 152849/CO/200, zoals gewijzigd inzake de termijnen door de collectieve arbeidsovereenkomst van 18 november 2021 gesloten in het PC 200 met registratienummer 168827/CO/200;- Harmonisatieverplichting : de wettelijke verplichting tot harmonisering van de aanvullende pensioenen voor arbeiders en bedienden in de zin van de WAP;- Hoofdzakelijkheidscriterium : in situaties waar Werkgevers ressorteren onder meerdere paritaire (sub)comités voor hun arbeiders houdt het hoofdzakelijkheidscriterium in dat de PC 200 Bedienden moeten vergeleken worden met hun collega arbeiders die werken in de hoofdactiviteit van de Werkgever. De hoofdactiviteit wordt voor doeleinden van artikel 14 van de WAP bepaald als de Ondernemingsactiviteit waar de Werkgever het grootst aantal arbeiders tewerkstelt, uitgedrukt in voltijds equivalente arbeiders. De hoofdactiviteit wordt bepaald aan de hand van de officiële sociale documenten waarbij gebruik gemaakt wordt van de kerngetallen en RSZ-identificatienummers;- Inrichter : de multi-sectorale inrichter, "Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Terugwinning van Metalen" (FBZ SAP Ondernemingsactiviteit Terugwinning van Metalen), met zetel te Bluepoint Brussels, 1030 Brussel, Auguste Reyerslaan 80, die optreedt als inrichter van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen en als inrichter van het SAP PSC 142.01 Arbeiders Ondernemingsactiviteit Terugwinning van Metalen voor de arbeiders waarmee de Bedienden Ondernemingsactiviteit Terugwinning van Metalen "spiegelen" in de zin van artikel 14 van de WAP;- Ondernemingsactiviteit (OA) : de beroepscategorieën en ondernemingsactiviteiten zoals bedoeld in artikel 14/4, § 1, eerste lid van de WAP;- Ondernemingsactiviteit Terugwinning van Metalen : de ondernemingsactiviteiten waarvoor het PSC 142.01 bevoegd is en die vallen onder het bevoegdheidsgebied van PSC 142.01 zoals vastgesteld in het koninklijk besluit van 5 september 1974 tot oprichting en tot vaststelling van de benaming en van de bevoegdheid van paritaire subcomités voor de ondernemingen waar teruggewonnen grondstoffen opnieuw ter waarde worden gebracht en tot vaststelling van het aantal leden ervan, zoals laatst gewijzigd door het koninklijk besluit van 5 november 2002;- PSC 142.01 : het Paritair Subcomité voor de terugwinning van metalen;- PC 200 : het Aanvullend Paritair Comité voor de bedienden;- PC 200 Bedienden : de bedienden die vallen onder de bevoegdheid van PC 200;- SAP PSC 142.01 Arbeiders Ondernemingsactiviteit Terugwinning van Metalen : het sectoraal aanvullend pensioenstelsel, per 1 januari 2006 ingevoerd door PSC 142.01 voor de arbeiders werkzaam in PSC 142.01, zijnde de Arbeiders Ondernemingsactiviteit Terugwinning van Metalen;- SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen : het sectoraal aanvullend pensioenstelsel, dat door PC 200 wordt ingevoerd - in overeenstemming met de collectieve arbeidsovereenkomst van 1 juli 2019, voor de Bedienden Ondernemingsactiviteit Terugwinning van Metalen en dat in het kader van de Harmonisatieverplichting de gelijke behandeling beoogt inzake aanvullende pensioenen op sectorniveau tussen de Bedienden Ondernemingsactiviteit Terugwinning van Metalen en de Arbeiders Ondernemingsactiviteit Terugwinning van Metalen met wie zij "spiegelen" in de zin van artikel 14 van de WAP;- Technische bedrijfseenheid : de technische bedrijfseenheid zoals omschreven in artikel 14 van de wet van 20 september 1948 houdende organisatie van het bedrijfsleven;- Vestigingseenheid : een plaats die men, geografisch gezien, kan identificeren door een adres waar ten minste één activiteit van de in de Kruispuntbank van Ondernemingen geregistreerde juridische entiteit wordt uitgeoefend of van waaruit de activiteit wordt uitgeoefend in de zin van artikel I.2., 16°  van boek I van het Wetboek van Economisch recht. Dit komt neer op elke geografisch afgescheiden exploitatiezetel, afdeling of onderafdeling (atelier, fabriek, magazijn, bureau,...) van de betrokken juridische entiteit (op basis van het ondernemingsnummer), gesitueerd op een geografisch welbepaalde locatie en identificeerbaar met een adres en met een vestigingseenheidsnummer;- WAP : de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid, waarin het wettelijk kader inzake de harmonisatie van de aanvullende pensioenen voor arbeiders en bedienden werd ingeschreven door de wet van 5 mei 2014 tot wijziging van het rustpensioen en het overlevingspensioen en tot invoering van de overgangsuitkering in de pensioenregeling voor werknemers en houdende geleidelijke opheffing van de verschillen in behandeling die berusten op het onderscheid tussen werklieden en bedienden inzake aanvullende pensioenen en werd gewijzigd door de wet van 12 december 2021 tot uitvoering van het sociaal akkoord in het kader van de interprofessionele onderhandelingen voor de periode 2021-2022;- WIBP : de wet van 27 oktober 2006 betreffende het toezicht op de instellingen bedrijfspensioenvoorziening;- Werkgever : de juridische entiteit (op basis van het ondernemingsnummer), of desgevallend de Vestigingseenheden (op basis van het vestigingseenheidsnummer) indien de juridische entiteit over meerdere Vestigingseenheden beschikt.HOOFDSTUK II. - ToepassingsgebiedArt. 2. § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de Werkgevers die ressorteren onder PC 200, alsook de PC 200 Bedienden die deze Werkgevers tewerkstellen, op voorwaarde dat :- de betrokken Werkgever voor alle of een deel van de arbeiders die hij tewerkstelt, valt onder de bevoegdheid van PSC 142.01;- de PC 200 Bedienden volledig of deels tewerkgesteld zijn in de Ondernemingsactiviteit Terugwinning van Metalen; en- de PC 200 Bedienden door de betrokken Werkgever tewerkgesteld worden in een Technische Bedrijfseenheid waarin deze Werkgever ook arbeiders tewerkstelt waarvoor hij valt onder de bevoegdheid van PSC 142.01. § 2. De vaststelling of, en welk deel van, de PC 200 Bedienden moeten beschouwd worden als Bedienden Ondernemingsactiviteit Terugwinning van Metalen gebeurt op basis van de regels bepaald in artikel 2, § 3 en § 4 van deze collectieve arbeidsovereenkomst.De Bedienden Ondernemingsactiviteit Terugwinning van Metalen worden vanaf 1 juli 2025 door de betrokken Werkgever of zijn sociaal secretariaat aangegeven in de DmfA onder het RSZ-werkgeverskengetal 079. § 3. Indien de Werkgever voor al zijn arbeiders ressorteert onder PSC 142.01, dan worden de PC 200 Bedienden die de Werkgever tewerkstelt in de Ondernemingsactiviteit Terugwinning van Metalen beschouwd als Bedienden Ondernemingsactiviteit Terugwinning van Metalen. § 4. Indien de Werkgever :- voor een deel van de arbeiders die hij tewerkstelt in de betrokken Technische Bedrijfseenheid, ressorteert onder PSC 142.01 én voor andere arbeiders ressorteert onder de bevoegdheid van één of meerdere andere paritaire (sub)comités voor arbeiders; en- de PC 200 Bedienden die hij tewerkstelt in de betrokken Technische Bedrijfseenheid op basis van de feitelijke omstandigheden niet kan toewijzen aan een van de specifieke Ondernemingsactiviteiten waarvoor één van de betrokken paritaire (sub)comités voor arbeiders bevoegd is, aangezien deze PC 200 Bedienden ondersteunende of overkoepelende taken uitvoeren ten aanzien van meerdere Ondernemingsactiviteiten en/of niet-occasioneel en niet-uitzonderlijk werkzaam zijn in meerdere Ondernemingsactiviteiten van de Werkgever;gelden de volgende regels om te bepalen welke PC 200 Bedienden moeten worden beschouwd als Bedienden Ondernemingsactiviteit Terugwinning van Metalen :(a) De Werkgever moet vaststellen of de PC 200 Bedienden in de betrokken Technische Bedrijfseenheid toegewezen worden aan de Ondernemingsactiviteit Terugwinning van Metalen of aan de Ondernemingsactiviteit(en) die behoren tot het bevoegdheidsgebied van één van de andere paritaire (sub)comités voor arbeiders (overeenkomstig het toepasselijk koninklijk besluit dat de bevoegdheid van dit paritair comité heeft vastgesteld), waaronder de Werkgever voor een deel van zijn arbeiders ressorteert.De Werkgever doet deze vaststelling eenmalig ("foto") volgens de modaliteiten vastgelegd in deze collectieve arbeidsovereenkomst, hetzij (i) naar aanleiding van de inwerkingtreding van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen op 1 juli 2025 (op basis van de DmfA gegevens van het eerste kwartaal van 2022, zoals beschikbaar op 30 juni 2022), hetzij (ii) nadien op het moment dat de Werkgever voor het eerst ook ressorteert onder PSC 142.01 voor een deel van zijn arbeiders (op basis van de DmfA gegevens op het einde van het eerste kwartaal dat de Werkgever ook onder PSC 142.01 ressorteert voor een deel van zijn arbeiders), hetzij (iii) nadien op het moment dat de Werkgever voor een deel van zijn arbeiders naast PSC 142.01 ook ressorteert onder een ander paritair (sub)comité dan PSC 142.01 (op basis van de DmfA gegevens op het einde van het eerste kwartaal dat de Werkgever ook onder een ander paritair (sub)comité dan PSC 142.01 ressorteert voor een deel van zijn arbeiders) en wijzigt niet meer nadien behoudens in de uitzonderlijke situatie zoals vastgelegd hierna in (c);(b) Deze vaststelling gebeurt op basis van het Hoofdzakelijkheidscriterium, in dit kader uitgedrukt op basis van het aantal arbeiders in voltijdsequivalent of FTE, dat de Werkgever tewerkstelt in de betrokken Technische Bedrijfseenheid ("foto" vastgesteld op basis van de DmfA gegevens van het eerste kwartaal van 2022, zoals beschikbaar op 30 juni 2022, op het einde van het eerste kwartaal dat de Werkgever ook onder PSC 142.01 ressorteert voor een deel van zijn arbeiders of op het einde van het eerste kwartaal dat de Werkgever ook onder een ander paritair (sub)comité dan PSC 142.01 ressorteert voor een deel van zijn arbeiders) :- Indien de Werkgever arbeiders tewerkstelt die ressorteren onder meerdere paritaire (sub)comités voor arbeiders, dan worden de PC 200 Bedienden in de betrokken Technische Bedrijfseenheid, die ondersteunende of overkoepelende taken uitvoeren ten aanzien van meerdere Ondernemingsactiviteiten en/of niet-occasioneel en niet-uitzonderlijk werkzaam zijn in meerdere Ondernemingsactiviteiten van de Werkgever, beschouwd als Bedienden Ondernemingsactiviteit Terugwinning van Metalen indien het hoogste aantal arbeiders van de Werkgever ressorteren onder PSC 142.01;- Indien de Werkgever op de in punt (a) en (b) vastgestelde datum een gelijk aantal arbeiders tewerkstelt in de verschillende paritaire (sub)comités voor arbeiders waaronder hij ressorteert en het Hoofdzakelijkheidscriterium geen antwoord biedt, dan worden de PC 200 Bedienden in de betrokken Technische Bedrijfseenheid die ondersteunende of overkoepelende taken uitvoeren ten aanzien van meerdere Ondernemingsactiviteiten en/of niet-occasioneel en niet-uitzonderlijk werkzaam zijn in meerdere Ondernemingsactiviteiten van de Werkgever, beschouwd als Bedienden Ondernemingsactiviteit Terugwinning van Metalen wanneer gemiddeld gedurende acht RSZ kwartalen (dit is gedurende het eerste kwartaal van 2022 en de zeven daaraan voorafgaande RSZ kwartalen) (= de referentieperiode of "film") het hoogste aantal arbeiders (uitgedrukt in voltijdsequivalent of FTE) van de Werkgever ressorteert onder PSC 142.01. Indien er geen acht RSZ kwartalen zijn, wordt het lager aantal beschikbare RSZ kwartalen (dit is het eerste kwartaal van 2022 en het lager aantal daaraan voorafgaande RSZ kwartalen) als referentieperiode of film genomen;- Indien de Werkgever ook gedurende deze voormelde referentieperiode of film een gelijk aantal arbeiders tewerkstelt in de verschillende paritaire (sub)comités voor arbeiders waaronder hij ressorteert, dan worden de PC 200 Bedienden in de betrokken Technische Bedrijfseenheid die ondersteunende of overkoepelende taken uitvoeren ten aanzien van meerdere Ondernemingsactiviteiten en/of niet-occasioneel en niet-uitzonderlijk werkzaam zijn in meerdere Ondernemingsactiviteiten van de Werkgever, beschouwd als Bedienden Ondernemingsactiviteit Terugwinning van Metalen wanneer de Ondernemingsactiviteit Terugwinning van Metalen kan beschouwd worden als de hoofdactiviteit van de Werkgever op basis van de rangorde die gebruikt werd in de activiteiten die opgesomd worden in het maatschappelijk voorwerp, zoals vermeld in de statuten van de Werkgever.(c) Indien de PC 200 Bedienden op basis van de regels in (b) beschouwd worden als Bedienden Ondernemingsactiviteit Terugwinning van Metalen, maar de verhouding tussen de respectievelijke aantallen van arbeiders in de verschillende Ondernemingsactiviteiten nadien op een duurzame en significante wijze wijzigt, kan de Werkgever via een schriftelijks : gemotiveerd verzoek aan de Inrichter vragen dat zijn PC 200 Bedienden in de betrokken Technische Bedrijfseenheid niet langer beschouwd worden als Bedienden Ondernemingsactiviteit Terugwinning van Metalen. De Werkgever brengt hiervan de ondernemingsraad, of bij ontstentenis hiervan, het comité voor preventie en bescherming op het werk, of bij ontstentenis hiervan, de vakbondsafvaardiging op de hoogte.Hiertoe moet de Werkgever in zijn schriftelijk en gemotiveerd verzoek minstens de volgende gegevens opnemen :(i) de aantallen van arbeiders bepaald op het moment voorzien onder (b);(ii) de evolutie op kwartaalbasis van de aantallen van arbeiders bedoeld onder (b) sinds het moment voorzien onder (b), waaruit de duurzame en significante aard van de wijziging blijkt;(iii) aantonen op basis van de activiteiten van de Werkgever waarom deze wijziging zich ook in de toekomst verder zal bestendigen.Mits een voorafgaande discussie met de Werkgever, kan een gelijkaardig schriftelijk en gemotiveerd verzoek worden ingediend door de vertegenwoordigers van de werknemers in de ondernemingsraad, of bij ontstentenis hiervan, de vertegenwoordigers van de werknemers in het comité voor preventie en bescherming op het werk, of bij ontstentenis hiervan, de vakbondsafvaardiging. Dat verzoek moet dezelfde gegevens opnemen dan hierboven vermeld. De betrokken partij brengt de Werkgever hier onverwijld van op de hoogte.De Inrichter van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen beslist over dit verzoek binnen de twee maanden na ontvangst van alle hiervoor vermelde, benodigde gegevens. In geval van een positieve beslissing, zullen de PC 200 Bedienden van de betrokken Werkgever in de betrokken Technische Bedrijfseenheid vanaf het eerstvolgende kwartaal na deze positieve beslissing, niet langer beschouwd worden als Bedienden Ondernemingsactiviteit Terugwinning van Metalen (wat aanleiding geeft tot een uittreding uit het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen). De Werkgever zal de betrokken PC 200 Bedienden hierover inlichten. De Inrichter zal aan PC 200 één keer per jaar een overzicht overmaken van de Werkgevers die toepassing van dit artikel hebben gemaakt.Omgekeerd, indien de PC 200 Bedienden op basis van de regels in (b) niet beschouwd worden als Bedienden Ondernemingsactiviteit Terugwinning van Metalen, maar de verhouding tussen de respectievelijke aantallen van arbeiders in de verschillende Ondernemingsactiviteiten nadien op een duurzame en significante wijze wijzigt, kan de Werkgever zich wenden tot de inrichter van het sectoraal aanvullend pensioenstelsel van de andere (sub)sector waarbij zijn PC 200 Bedienden zijn aangesloten, om te vragen dat zijn PC 200 Bedienden in de betrokken Technische Bedrijfseenheid voortaan kunnen beschouwd worden als Bedienden Ondernemingsactiviteit Terugwinning van Metalen, waarna ze aangesloten worden aan het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen.HOOFDSTUK III. - Voorwerp - Invoering SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van MetalenArt. 3. § 1. De representatieve organisaties in het PC 200 hebben deze collectieve arbeidsovereenkomst gesloten ter uitvoering van de Harmonisatieverplichting en artikel 7, 1°  (i) van de cao van 1 juli 2019.Deze collectieve arbeidsovereenkomst heeft als enige voorwerp de invoering met ingang van 1 juli 2025 van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen.Voor de Bedienden Ondernemingsactiviteit Terugwinning van Metalen die vanaf 1 juli 2025 aangesloten worden bij het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen, stopt vanaf 1 juli 2025 de betaling van de tijdelijke jaarpremie bepaald in artikel 5 van de cao van PC 200 van 1 juli 2019 aangezien het volledige budget van de tijdelijke jaarpremie wordt aangewend voor het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen. Voor 2025 zal nog het gedeelte van de tijdelijke jaarpremie voor de maanden januari tot en met juni uitbetaald worden, volgens de berekenings- en uitbetalingsregels vastgelegd in de cao van PC 200 van 1 juli 2019. § 2. Vanaf 1 januari 2030 en op basis van de schadestatistieken zal het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen worden omgevormd tot een sociaal sectoraal pensioenstelsel waarbij 95,5 pct. van de nettobijdrage zal worden aangewend voor de financiering van de pensioentoezegging en 4,5 pct. voor de financiering van de solidariteitstoezegging.HOOFSTUK IV. - Aansluiting aan het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van MetalenArt. 4. § 1. Alle Bedienden Ondernemingsactiviteit Terugwinning van Metalen die op of na 1 juli 2025 verbonden zijn via een arbeidsovereenkomst met een Werkgever en die niet uitgesloten zijn uit het toepassingsgebied van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen overeenkomstig artikel 10 van deze collectieve arbeidsovereenkomst, worden aangesloten bij het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen. § 2. De hiervoor vermelde Bedienden Ondernemingsactiviteit Terugwinning van Metalen blijven aangesloten aan het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen tot aan hun uittreding, pensionering of overlijden.Bedienden Ondernemingsactiviteit Terugwinning van Metalen, die hun wettelijk (vervroegd) pensioen hebben opgenomen, maar verder of opnieuw tewerkgesteld worden met een arbeidsovereenkomst gesloten met een Werkgever, zoals bedoeld in artikel 4, § 1 in het kader van "toegelaten arbeid voor gepensioneerden", blijven niet aangesloten of worden niet aangesloten bij het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen, overeenkomstig artikel 13 van de WAP. § 3. Een uitzondering geldt voor de Bedienden Ondernemingsactiviteit Terugwinning van Metalen die gebruik hebben gemaakt, voorafgaand aan de invoering van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen van hun wettelijk weigeringsrecht overeenkomstig artikel 16, § 3 van de WAP, op, voorwaarde dat het bestaand pensioenstelsel van de Werkgever zoals van toepassing onmiddellijk voorafgaand aan de invoering van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen en van toepassing op de Bedienden Ondernemingsactiviteit Terugwinning van Metalen, per 1 juli 2025 wordt vervangen door het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen in het kader van de Harmonisatieverplichting. De Bedienden Ondernemingsactiviteit Terugwinning van Metalen die in dit kader gebruik hebben gemaakt van dit weigeringsrecht worden niet aangesloten bij het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen, en dit zolang dit weigeringsrecht verdere toepassing heeft.De betrokken Werkgever moet hiertoe de procedure volgen zoals voorzien in artikel 6, § 2 van de Bijlage 2 bij deze collectieve arbeidsovereenkomst, ten gevolge waarvan de RSZ voor deze Bedienden Ondernemingsactiviteit Terugwinning van Metalen die gebruik hebben gemaakt van dit wettelijk weigeringsrecht, geen patronale bijdragen voor het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen innen, zolang dit weigeringsrecht verder van toepassing is. Vanaf het moment dat dit niet langer het geval is, wordt de betrokken Bediende Ondernemingsactiviteit Terugwinning van Metalen aangesloten bij het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen.HOOFDSTUK V. - Aanduiding van de InrichterArt. 5. § 1. Het "Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Terugwinning van Metalen" (FBZ SAP Ondernemingsactiviteit Terugwinning van Metalen) waarvan de statuten zijn vastgelegd in de collectieve arbeidsovereenkomst van 13 juni 2024 tot oprichting van het "Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Terugwinning van Metalen" (FBZ SAP Ondernemingsactiviteit Terugwinning van Metalen) dat optreedt als multi-sectorale inrichter van het sectoraal aanvullend pensioenstelsel voor de arbeiders en voor de bedienden in de Ondernemingsactiviteit Terugwinning van Metalen en tot vaststelling van de statuten van de multi-sectorale inrichter, wordt aangeduid als de Inrichter van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen (hierna : "Inrichter" of "FBZ SAP Ondernemingsactiviteit Terugwinning van Metalen"). § 2. Voor zover gewenst, kunnen de sociale partners van PC 200 Ondernemingsactiviteit Terugwinning van Metalen gezamenlijk met de sociale partners van PSC 142.01 de leden van de raad van bestuur van de Sectorale Inrichter aanduiden, overeenkomstig de modaliteiten bepaald in de statuten van de Sectorale Inrichter.HOOFDSTUK VI. - Pensioentoezegging - aanduidingvan de pensioeninstellingArt. 6. § 1. Het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen dat per 1 juli 2025 wordt ingevoerd is een gewoon sectoraal aanvullend pensioenstelsel, dat bestaat uit een pensioentoezegging die is vastgelegd in het pensioenreglement (opgenomen in Bijlage 1 bij deze collectieve arbeidsovereenkomst). § 2. De pensioentoezegging is een pensioenstelsel van het type vaste bijdragen die voorziet :- in de opbouw van een aanvullend pensioen dat overeenkomstig de regels en modaliteiten van het pensioenreglement, zoals vastgelegd in Bijlage 1 bij deze cao, wordt uitbetaald aan de aangesloten Bediende Ondernemingsactiviteit Terugwinning van Metalen op het moment van pensionering (in zoverre de betrokken bediende bij uittreden uit de sector zijn verworven pensioenreserves niet heeft overgedragen naar een andere pensioeninstelling);- in een overlijdenskapitaal in geval van overlijden van de aangesloten Bediende Ondernemingsactiviteit Terugwinning van Metalen voor pensionering, dat gelijk is aan de verworven reserves die de aangesloten bediende heeft opgebouwd in het sectoraal aanvullend pensioenstelsel tot op het moment van zijn overlijden en dat wordt uitbetaald aan de begunstigden van de overleden, aangesloten bediende overeenkomstig de regels en modaliteiten van het pensioenreglement (zoals vastgelegd in Bijlage 1 bij deze collectieve arbeidsovereenkomst). § 3. Het beheer en de uitvoering van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen wordt toevertrouwd aan Sefoplus OFP. Sefoplus OFP is een multi-sectorale instelling voor bedrijfspensioenvoorziening, vergund op 19 november 2018, met ondernemingsnummer 0715.441.019, FSMAidentificatienummer 50.624 en maatschappelijke zetel te Marlylaan 15/8, 1120 Brussel. Sefoplus OFP is met andere woorden aangeduid als pensioeninstelling.De pensioenverplichtingen en de activa verbonden aan het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen worden binnen Sefoplus OFP beheerd in een afgezonderd vermogen opgezet voor het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen ("Afzonderlijk Vermogen PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen") in de zin van artikel 2, 15°  van de WIBP. De beheers- en werkingsregels die worden afgesproken tussen de Inrichter en Sefoplus OFP als pensioeninstelling worden vastgelegd in de beheersovereenkomst en de toetredingsakte daartoe, alsook in een algemeen en specifiek luik bij de verklaring inzake de beleggingsbeginselen (SIP) en het financieringsplan van Sefoplus OFP. § 4. De regels en modaliteiten betreffende de pensioentoezegging worden verder vastgelegd in het pensioenreglement dat wordt opgenomen in Bijlage 1 bij deze collectieve arbeidsovereenkomst, die er integraal deel vanuit maakt.HOOFDSTUK VII. - Financiering, bijdragen en inningsmodaliteitenArt. 7. § 1. De financiering van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen gebeurt via een patronale bijdrage. De totale jaarlijkse brutobijdrage is per actieve aangeslotene bij het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen gelijk aan 1,10 pct. van het brutojaarloon waarop inhoudingen door de RSZ worden verricht. § 2. De totale jaarlijkse brutobijdrage per actieve aangeslotene bij het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen wordt verminderd met 4,5 pct. beheerskosten, aangerekend door de Inrichter, wat resulteert in een totale jaarlijkse nettopensioenbijdrage per actieve aangeslotene van 1,05 pct. van het brutojaarloon waarop inhoudingen door de RSZ worden verricht. § 3. Dit resulteert, na vermeerdering van de nettopensioenbijdrage met 0,09 pct. ter dekking van de verschuldigde, bijzondere RSZ-bijdrage van 8,86 pct., in een globale jaarlijkse brutobijdrage van 1,19 pct. voor elke actieve aangeslotene bij het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen. De bijzondere RSZ-bijdrage van 8,86 pct. wordt door de RSZ afgehouden aan de bron. De Werkgevers, die onder het toepassingsgebied vallen van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen, moeten deze niet apart berekenen en aangeven. § 4. De inning en de invordering van deze patronale bijdrage gebeurt door de Rijksdienst voor Sociale Zekerheid (RSZ) via een gedifferentieerde inning, overeenkomstig de daartoe afgesloten beheersovereenkomst met de RSZ. § 5. Elke Werkgever die onder het toepassingsgebied van SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen valt, is gehouden tot de betaling van deze bijdrage.De Rijksdienst voor Sociale Zekerheid maakt de patronale bijdragen voor het sectoraal pensioenstelsel over aan de Inrichter. Vervolgens maakt de Inrichter de ontvangen patronale bijdragen over aan de pensioeninstelling waar deze worden ondergebracht in het Afzonderlijk Vermogen PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen.HOOFSTUK VIII. - Uitbetaling van de voordelenArt. 8. De procedure, de modaliteiten en de vorm van de uitbetaling van de voordelen krachtens het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen worden beschreven in het bijgevoegde pensioenreglement (opgenomen als Bijlage 1 van deze collectieve arbeidsovereenkomst).HOOFDSTUK IX. - UittredingArt. 9. De procedure van uittreding uit het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen wordt geregeld overeenkomstig de bepalingen vermeld in het bijgevoegde pensioenreglement (opgenomen als Bijlage 1 bij deze collectieve arbeidsovereenkomst).HOOFDSTUK X. - Uitsluiting uit het toepassingsgebied van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen ("buiten toepassingsgebied") - geen mogelijkheid tot opting outArt. 10. § 1. De Werkgevers die voor al hun Bedienden Ondernemingsactiviteit Terugwinning van Metalen in de betrokken Technische Bedrijfseenheid op 1 juli 2025 reeds voorzien in één of meerdere aanvullende pensioenstelsels op ondernemingsniveau die minstens gelijkwaardig zijn aan het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen, worden uitgesloten uit het toepassingsgebied van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen, overeenkomstig de regels zoals vastgelegd in Bijlage 2 bij deze collectieve arbeidsovereenkomst.Daarnaast kunnen Werkgevers, die op of na 1 juli 2025 worden opgericht of pas vanaf of na 1 juli 2025 ten gevolge van gewijzigde omstandigheden (zoals onder meer een fusie, een splitsing, een overname of een andere transactie, een wijziging van paritair comité, een wijziging van activiteiten,...) hetzij (i) voor het eerst ressorteren onder PC 200 voor hun Bedienden Ondernemingsactiviteit Terugwinning van Metalen, hetzij (ii) voor het eerst Bedienden Ondernemingsactiviteit Terugwinning van Metalen tewerkstellen, hetzij (iii) voor het eerst ressorteren onder PSC 142.01 voor (een deel van) hun arbeiders, ook worden uitgesloten uit het toepassingsgebied van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen, op voorwaarde dat zij aantonen dat zij op dat moment voor al hun Bedienden Ondernemingsactiviteit Terugwinning van Metalen in de betrokken Technische Bedrijfseenheid voorzien in één of meerdere aanvullende pensioenstelsels op ondernemingsniveau die minstens gelijkwaardig zijn aan het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen.De voorwaarden en modaliteiten om uitgesloten te worden uit het toepassingsgebied van het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen ("buiten toepassingsgebied") worden verder vastgelegd in Bijlage 2 bij deze collectieve arbeidsovereenkomst, die integraal deel uitmaakt van deze collectieve arbeidsovereenkomst.Deze Werkgevers en de Bedienden Ondernemingsactiviteit Terugwinning van Metalen in de betrokken Technische Bedrijfseenheid die zij tewerkstellen nemen bijgevolg niet deel aan het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen, in zoverre en voor zolang de ondernemingspensioenstelsels van de betrokken Werkgevers te allen tijde gelijkwaardig zijn aan het SAP PC 200 Bedienden Ondernemingsactiviteit Terugwinning van Metalen en de betrokken Werkgevers (blijven) voldoen aan de voorwaarden van "buiten toepassingsgebied", zoals vastgelegd in Bijlage 2 bij deze collectieve arbeidsovereenkomst. § 2. De Werkgevers die op basis van artikel 10, § 1 uit</t>
         </is>
       </c>
     </row>
@@ -939,28 +937,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025003537</t>
+          <t>2025003909</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>07 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit tot goedkeuring van het huishoudelijk reglement van de proefbank voor vuurwapens</t>
+          <t>13 mei 2025. - Koninklijk besluit tot goedkeuring van het reglement van de Autoriteit voor Financiële Diensten en Markten betreffende de gestandaardiseerde presentatiewijze van bepaalde informatieverplichtingen inzake aanvullende pensioenen</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-07&amp;numac_search=2025003537&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003537=15&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025003909&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003909=15&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 8 juli 2018 houdende bepalingen inzake de proefbank voor vuurwapens, artikel 5, derde lid;Overwegende dat de organen van de proefbank voor vuurwapens op 13 juni 2024 in overleg hun huishoudelijk reglement hebben opgesteld;Op de voordracht van de Minister van Economie en de Minister van Justitie,Hebben Wij besloten en besluiten Wij :Artikel 1. Het bij dit besluit gevoegde huishoudelijk reglement van de proefbank voor vuurwapens wordt goedgekeurd.Art. 2. Dit besluit treedt in werking de dag waarop het in het Belgisch Staatsblad wordt bekendgemaakt.Art. 3. De minister bevoegd voor Economie en de minister bevoegd voor Justitie zijn, ieder wat hem betreft, belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Economie,D. CLARINVALDe Minister van Justitie,A. VERLINDENBijlageHuishoudelijk reglement van de proefbank voor vuurwapensDe wettelijke bepalingen (wetten en uitvoeringsbesluiten) die van toepassing zijn op de proefbank voor vuurwapens worden beschouwd als een integraal onderdeel van het huishoudelijk reglement. In geval van afwijking of tegenstrijdigheid tussen dit huishoudelijk reglement en de wettelijke bepalingen, hebben deze laatste voorrang.TITEL I. - Identificatie en lokalisatieArtikel 1. De zetel van de proefbank voor vuurwapens (hierna « PB  ») is gevestigd te 4000 Liège, rue Fond des Tawes, 45. Hij is ingeschreven bij de btw onder het nr. BE0206.607.129.Art. 2. De PB gebruikt voor zijn communicatie de Franse en Nederlandse benaming gezamenlijk: « Proefbank voor vuurwapens - Banc d'épreuves des armes à feu ».TITEL II. - Vergaderingen van de Raad van BestuurHOOFDSTUK I. - UitnodigingArt. 3. De Raad van Bestuur wordt bijeengeroepen door de voorzitter van de Raad van Bestuur (per e-mail) met verzoek om ontvangstbevestiging.Behoudens dringende en onvoorziene gevallen, gebeurt de bijeenroeping minimum tien kalenderdagen vóór de vastgestelde datum van de vergadering.De uitnodiging vermeldt de datum, het uur en de plaats van de vergadering, alsmede de agenda. Ze wordt verzonden met de werkdocumenten die verband houden met de punten van de agenda van de vergadering, waaronder de samenvatting van de dossiers betreffende deze punten, en die zich op de zetel van de PB bevinden.De Raad van Bestuur vergadert minstens om de twee maanden. Hij moet worden bijeengeroepen telkens wanneer minstens drie van zijn leden er schriftelijk om verzoeken. De voorzitter is ertoe gehouden de Raad van Bestuur bijeen te roepen binnen eenentwintig kalenderdagen volgend op de ontvangst van het verzoekschrift. In voorkomend geval zijn de leden, die een punt op de agenda wensen te plaatsen, ertoe gehouden, samen met hun aanvraag, een toelichtingsnota betreffende dit punt te overhandigen aan de voorzitter.De uitnodigingen, agenda en werkdocumenten met betrekking tot iedere vergadering worden per e-mail gestuurd naar het mailadres dat door ieder van de leden daartoe meegedeeld is aan de secretaris van de Raad van Bestuur. Iedere adreswijziging wordt ter kennis gebracht van de secretaris.HOOFDSTUK II. - DagordeArt. 4. De voorzitter van de Raad van Bestuur stelt na overleg met de directeur de dagorde van de vergaderingen vast.Art. 5. In geval van dringende noodzaak kunnen hetzij de voorzitter van de Raad van Bestuur, hetzij de directeur, hetzij minstens drie leden een bijkomend punt op de dagorde van de vergadering plaatsen.De dringende noodzaak, vereist om ter zitting bijkomende punten op de dagorde te plaatsen, kan alleen worden aangenomen wanneer dit wordt gevraagd ten laatste twee werkdagen voor de vergaderdatum en wanneer daartoe beslist wordt door de meerderheid van de aanwezige leden. De notulen dienen in dat geval deze beslissing uitdrukkelijk te vermelden, alsmede de volgorde van de punten van de dagorde die wordt vastgesteld volgens de bepalingen van artikel 9.HOOFDSTUK III. - Manier van vergaderen, beraadslagen en beslissenArt. 6. Enkel de bestuurders zetelen in de Raad van Bestuur. De directeur en de regeringscommissarissen wonen de Raad van Bestuur bij. Laatstgenoemden beschikken uitsluitend over een raadgevende stem, in overeenstemming met artikel 41.Art. 7. De Raad van Bestuur vergadert onder het voorzitterschap van zijn voorzitter of, bij zijn ontstentenis, van een onafhankelijke bestuurder aangewezen door de voorzitter of, bij afwezigheid, van een onafhankelijke bestuurder aangesteld door de andere aanwezige bestuurders. Hij is dan de voorzitter van de zitting in kwestie.De vergaderingen van de Raad van Bestuur worden voor geopend en voor gesloten verklaard door de voorzitter van de zitting.Art. 8. De Raad van Bestuur beraadslaagt geldig wanneer minstens de helft plus een van zijn leden aanwezig zijn of door een bijzondere schriftelijke en gedetailleerde volmacht over de agendapunten vertegenwoordigd zijn. De leden kunnen slechts deelnemen aan een vergadering van de Raad van Bestuur nadat hun benoeming in het Belgisch Staatsblad is verschenen.Indien dit quorum niet bereikt wordt, roept de voorzitter binnen de vijftien kalenderdagen een nieuwe vergadering van de Raad van Bestuur met dezelfde agenda bijeen. Tijdens deze vergadering kan de Raad van Bestuur beraadslagen ongeacht het aantal aanwezige leden.Behoudens andere wettelijke, reglementaire of statutaire beschikkingen, worden de beslissingen genomen bij eenvoudige meerderheid van de stemmen van de aanwezige of bij volmacht vertegenwoordigde leden. Bij gelijkheid van stemmen heeft de voorzitter een beslissende stem. Bij de bepaling van het resultaat van de stemming wordt geen rekening gehouden met de onthoudingen.De Raad van Bestuur kan besluiten om bepaalde punten met gesloten deuren te behandelen. In dat geval worden alleen de genomen beslissingen opgenomen in de notulen, die duidelijk moeten aangeven dat de bespreking met gesloten deuren plaatsvond.Art. 9. De punten vermeld in de agenda worden, voor zover de Raad van Bestuur er niet anders over beslist, besproken in de volgorde die vooraf door de voorzitter werd bepaald.Indien een punt bij dringende noodzaak, volgens de procedure van artikel 5, op de agenda wordt gebracht, bepaalt de Raad van Bestuur op voorstel van de voorzitter de nieuwe volgorde waarin de punten worden besproken.Art. 10. De voorzitter van de zitting licht ieder punt toe dat ter bespreking wordt voorgelegd. Hij kan eventueel de directeur met deze toelichting belasten, alsook ieder ander lid van de Raad van Bestuur, hetzij omdat het gegeven punt rechtstreeks verband houdt met de werkzaamheden van dit lid binnen de PB, hetzij omdat dit punt op aanvraag van dit lid, volgens de voorgeschreven procedure, op de agenda werd geplaatst.Art. 11. De voorzitter van de zitting verklaart de bespreking van de punten en de tussenkomsten voor geopend of gesloten.Art. 12. De voorzitter van de zitting neemt deel aan de besprekingen zonder afstand te doen van zijn voorzitterschap.Art. 13. Behoudens andersluidende wettelijke of reglementaire beschikkingen, geschiedt de stemming bij handopsteking. Een lid kan wel om een geheime stemming vragen; de Raad van Bestuur beslist of dit toegestaan wordt.Art. 14. Wanneer de Raad van Bestuur gevraagd wordt door middel van een stemming te kiezen tussen meer dan twee voorstellen zal hij zo nodig overgaan tot één of meerdere voorafgaande stemmingen, zodat de uiteindelijke stemming slaat op de twee voorstellen die het meeste aantal stemmen hebben gekregen tijdens de voorafgaande stembeurt(en). De Raad van Bestuur stelt vooraf de wijze vast waarop de bewuste stemmingen zullen plaatsvinden.Art. 15. Onmiddellijk na de stemming maakt de voorzitter van de zitting de uitslag ervan bekend; de uitslag wordt opgenomen in de notulen.HOOFDSTUK IV. - Secretariaat, opmaken en bijhouden van de notulenArt. 16. Het secretariaat van de Raad van Bestuur wordt, onder de verantwoordelijkheid van de voorzitter van de Raad van Bestuur, waargenomen door een door de voorzitter voorgedragen en door de Raad van Bestuur aangestelde persoon.In zijn hoedanigheid van secretaris staat betrokkene in voor de eindredactie, de vertaling (Frans/Nederlands) en de verzending van de documenten die bestemd zijn voor de Raad van Bestuur, het behartigen van de administratieve relaties met de leden van de Raad van Bestuur en de coördinatie van het beantwoorden van de vragen van de leden van de Raad van Bestuur.In de uitoefening van zijn functie legt de secretaris verantwoording af aan de voorzitter van de Raad van Bestuur voor de acties die hij onder zijn verantwoordelijkheid en in zijn opdracht uitvoert.Art. 17. In beginsel worden in de notulen, per punt van de agenda, de belangrijkste aspecten van de besprekingen en de volledige weergave van de beslissingen opgenomen.Art. 18. Het ontwerp van de notulen wordt binnen de veertien kalenderdagen na de desbetreffende vergadering voorgelegd aan de bestuurders.Ten laatste bij de eerstvolgende vergadering en op uitnodiging van de voorzitter laten de leden hun opmerkingen kennen; de Raad van Bestuur beslist over de gegrondheid van de gemaakte opmerkingen, na de secretaris gehoord te hebben.Wanneer het opmerkingen betreft over tussenkomsten van de leden worden deze bij voorkeur schriftelijk ter zitting aan de secretaris overhandigd.De notulen worden slechts definitief bij goedkeuring op de eerstvolgende vergadering van de Raad van Bestuur. Bij hoogdringendheid kan de voorzitter aan de toen aanwezige bestuurders goedkeuring per e-mail vragen binnen een termijn van minstens vijf werkdagen.Art. 19. Ieder lid mag ter zitting of bij het goedkeuren van de notulen van de vorige zitting vragen de door hem afgelegde verklaringen op te nemen.In dat geval overhandigt het lid bij voorkeur de geschreven tekst van zijn verklaringen tijdens de zitting aan de secretaris.Art. 20. Een exemplaar van de notulen wordt na goedkeuring door de Raad van Bestuur ondertekend en geparafeerd door de voorzitter van de zitting en de secretaris. Deze handtekening mag elektronisch zijn.Het exemplaar wordt bij de PB door de directeur bewaard, met inachtneming van de vertrouwelijkheid.De notulen worden per jaar gebundeld.Art. 21. De leden van de Raad van Bestuur hebben het recht de notulen van de voorbije jaren en van het lopende jaar te raadplegen op de plaats waar deze worden bewaard.Art. 22. De secretaris houdt een register bij van de na elke vergadering naar behoren opgemaakte notulen. Alle leden van de Raad van Bestuur en de regeringscommissarissen ontvangen een kopie van de definitieve notulen. De directeur ontvangt een kopie van de notulen.De kopieën van, of de uittreksels uit de registers van de goedgekeurde notulen worden door de directeur afgeleverd wanneer die:- in rechte of elders moeten worden voorgelegd;- worden gevraagd door een lid;- kunnen door derden worden geraadpleegd overeenkomstig de wet van 11 april 1994 betreffende de openbaarheid van bestuur (BS 30 juni 1994).HOOFDSTUK V. - Rechten en plichten van de ledenArt. 23. De bestuurder die bij een ter goedkeuring aan de Raad van Bestuur voorgelegde zaak een persoonlijk belang heeft dat kan indruisen tegen dat van de PB, is ertoe gehouden de Raad van Bestuur ervan op de hoogte te brengen en deze verklaring in de notulen van de vergadering te doen opnemen. Hij mag niet deelnemen aan de stemming over deze zaak.Art. 24. Wanneer tijdens de zitting een geval behandeld wordt dat het persoonlijk belang van een lid van de Raad van Bestuur raakt, omdat het hetzij hemzelf, hetzij zijn verwanten tot en met de tweede graad betreft, verlaat het betrokken lid de vergadering op het ogenblik dat de kwestie wordt aangesneden.Over gevallen die niet bepaald zijn in de vorige alinea van dit artikel, beslist de Raad van Bestuur bij gewone meerderheid van de stemmen of de persoonlijke belangen van een lid van de Raad van Bestuur al dan niet betrokken zijn.Art. 25. De besprekingen in de Raad van Bestuur zijn vertrouwelijk en mogen niet aan derden meegedeeld worden. De vertrouwelijkheid slaat echter niet op de weergave van de beslissingen die opgenomen zijn in de notulen overeenkomstig artikel 22.Art. 26. De leden van de Raad van Bestuur moeten in alle omstandigheden de hogere belangen van de PB in aanmerking nemen.Art. 27. Elke bestuurder heeft het recht te allen tijde kennis te nemen van de dossiers van de PB met uitzondering van die welke betrekking hebben op de activiteit als officier van gerechtelijke politie van de directeur en de betrokken personeelsleden, en voor zover dit strikt noodzakelijk is voor zijn rol als bestuurder, mits hij de voorzitter van de Raad van Bestuur hiervan van tevoren in kennis stelt. De bestuurder stelt ook de directeur op de hoogte, zodat hij indien nodig over het dossier of de relevante documenten kan beschikken.HOOFDSTUK VI. - Aanwezigheid van derdenArt. 28. De voorzitter van de Raad van Bestuur kan om het even welke persoon, die hij meent te moeten horen, op de vergadering uitnodigen, op voorwaarde dat hij de leden van de Raad van Bestuur hierover minstens twee werkdagen voor de vergadering inlicht en voor zover dit door de meerderheid van de aanwezige leden is aanvaard.Derden verlaten de vergadering wanneer de discussie over het punt dat hen aangaat is afgerond, en in ieder geval wanneer de stemming wordt gehouden.TITEL III. - Bevoegdheden van de Raad van BestuurHOOFDSTUK I. - De Raad van BestuurArt. 29. De Raad van Bestuur beraadslaagt over alle bestuursdaden en schikkingen die de toekomst van de PB aangaan en in het bijzonder over de strategie, de activiteiten, het budget en de jaarrekeningen die hij goedkeurt.Overeenkomstig de bepalingen van artikel 10 van de wet van 8 juli 2018 houdende bepalingen inzake de proefbank voor vuurwapens, worden de tarieven voor het vervullen van de opdrachten van de PB bepaald door de Raad van Bestuur.Art. 30. De Raad van Bestuur bepaalt de wijze waarop de directeur verslag dient uit te brengen over de vervulling van zijn opdracht.HOOFDSTUK II. - De voorzitter van de Raad van BestuurArt. 31. Buiten de bevoegdheden die worden verleend aan de directeur, oefent de voorzitter het algemeen toezicht uit op het beheer van de PB in het kader van de richtlijnen en beslissingen genomen door de Raad van Bestuur.Hij formuleert vanuit de beslissingen van de Raad van Bestuur de nodige adviezen en aanbevelingen aan de directeur in verband met:a) de verwezenlijking van zijn opdrachten;b) de krachtlijnen van het algemeen beleid van de PB;c) het financieel beleid van de PB;d) de voorstellen die aan de Raad van Bestuur dienen te worden gedaan;e) de belangrijke wijzigingen in de organisatie.Art. 32. De voorzitter heeft het recht, binnen het kader van zijn bevoegdheden, alle nuttige voorstellen te doen. Hij heeft ook het recht om, samen met een andere bestuurder, in rechte op te treden in naam van de PB.Art. 33. Hij heeft toegang tot alle inlichtingen of dossiers waarover hij meent te moeten beschikken om zijn taken uit te voeren. Hij beschikt over de voor zijn taken noodzakelijke administratieve en materiële middelen.Art. 34. In geval van een tijdelijke vacature van de functie van voorzitter, benoemt de Raad van Bestuur onder zijn onafhankelijke leden een waarnemend voorzitter, die zijn functies uitoefent tot de aanwijzing van een nieuwe voorzitter.HOOFDSTUK III. - De operationele afdelingenArt. 35. Overeenkomstig artikel 1 van het koninklijk besluit van 10 maart 2022 betreffende het personeel van de proefbank voor vuurwapens, beslist de Raad van Bestuur over de onderverdeling van de PB in operationele afdelingen om de opdrachten zoals bepaald in artikel 3 van de wet van 8 juli 2018 houdende bepalingen inzake de proefbank voor vuurwapens, uit te voeren.Art. 36. Het aantal, de samenstelling, de bevoegdheden en de werkingsregels van deze operationele afdelingen maken het voorwerp uit van een reglement dat door de Raad van Bestuur moet worden goedgekeurd.TITEL IV. - Bevoegdheden van de directeurArt. 37. Ingevolge de wettelijke bepalingen is de directeur belast met de volgende taken:- de directeur bereidt, op voorstel van de voorzitter, de vergaderingen van de Raad van Bestuur voor. Hij stelt de agenda op, houdt toezicht op de voorbereiding van alle documenten en formuleert voorstellen in verband met de in te winnen adviezen;- de directeur keurt, overeenkomstig de wetgeving op de overheidsopdrachten, alle overeenkomsten van financiële, zakelijke of technische aard goed die passen in het kader van de door de Raad van Bestuur goedgekeurde activiteiten en binnen de grenzen van de budgetten, voor zover deze overeenkomsten het bedrag van 25.000 euro niet overschrijden;- de directeur is verantwoordelijk voor het volledige beheer van het personeel van de PB overeenkomstig artikel 3 van het koninklijk besluit van 10 maart 2022 betreffende het personeel van de proefbank voor vuurwapens;- de directeur houdt toezicht op de realisatie van de door de Raad van Bestuur goedgekeurde investeringsprojecten binnen de door de Raad van Bestuur goedgekeurde budgettaire grenzen.Art. 38. De directeur brengt op elke vergadering van de Raad van Bestuur verslag uit over de beslissingen genomen in overeenstemming met de voornoemde delegaties.Art. 39. Ingevolge artikel 9 van de wet van 8 juli 2018 houdende bepalingen inzake de proefbank voor vuurwapens is de directeur verantwoordelijk voor het dagelijkse beheer van de PB.In deze hoedanigheid stelt de directeur alle handelingen die nodig of dienstig zijn voor de uitvoering van zijn opdrachten.Deze opdrachten worden nader bepaald door de Raad van Bestuur.Art. 40. Krachtens artikel 17 van de voornoemde wet van 8 juli 2018 oefenen de directeur en de personeelsleden die zijn aangewezen in de hoedanigheid van officier van gerechtelijke politie hun functie uit onder het gezag van de procureur des Konings. De Raad van Bestuur is niet betrokken bij deze functies.TITEL V. - ToezichtHOOFDSTUK I. - De regeringscommissarissenArt. 41. De regeringscommissarissen wonen de vergaderingen van de Raad van Bestuur bij met raadgevende stem. Zij hebben de ruimste bevoegdheden voor het volbrengen van hun taak overeenkomstig de artikelen 9 en 10 van de wet van 16 maart 1954 betreffende de controle op sommige instellingen van openbaar nut.Art. 42. Overeenkomstig de bepalingen van de bovengenoemde wet beschikt elke regeringscommissaris over een termijn van vier vrije dagen om beroep aan te tekenen tegen de uitvoering van elke beslissing genomen door de Raad van Bestuur, handelend ter uitvoering van de bevoegdheden hem toegewezen krachtens titel III van dit huishoudelijk reglement, en die de regeringscommissaris strijdig acht met de wet, de statuten of het algemeen belang. Het beroep is opschortend.Deze termijn van vier vrije dagen gaat in op de dag van de vergadering waarop de beslissing werd genomen voor zover de regeringscommissaris daarop op regelmatige wijze werd uitgenodigd, of, in het tegenovergestelde geval, de dag waarop hij kennis ervan heeft gekregen.Art. 43. Elke regeringscommissaris tekent beroep aan bij de Minister die hij vertegenwoordigt.De Minister geeft kennis van zijn beslissing binnen een termijn van acht vrije dagen, die ingaat op dezelfde dag als de eerste termijn. De kennisgeving gebeurt per aangetekende zending.Bij een door de Minister aan de voorzitter van de Raad van Bestuur betekende beslissing kan de in de vorige alinea bepaalde termijn met tien vrije dagen worden verlengd.Indien de Minister zijn beslissing niet binnen de hem toegewezen termijn heeft bekendgemaakt, wordt het beroep als verworpen beschouwd en wordt de beslissing definitief.HOOFDSTUK II. - De commissaris-revisorArt. 44. Het toezicht op de verrichtingen van de PB wordt uitgeoefend door een commissaris-revisor, benoemd door de Raad van Bestuur. De directeur organiseert daartoe een openbare aanbesteding.Art. 45. De commissaris-revisor heeft een onbeperkt recht van toezicht en controle over al de boekhoudkundige en financiële verrichtingen van de PB. Hij is ertoe gerechtigd om zonder verplaatsing kennis te nemen van de boeken, de briefwisseling, de notulen en in het algemeen van alle geschriften van de PB.Art. 46. De commissaris-revisor legt aan de Raad van Bestuur de uitslag van zijn opdracht voor, met de voorstellen die hij geschikt acht, en deelt hem de wijze mee waarop hij de inventarissen nagegaan heeft. Om het toezicht op de boeken en rekeningen uit te oefenen, mag de commissaris-revisor zich, op kosten van de PB, overeenkomstig de wettelijke bepalingen, door een deskundige laten bijstaan.TITEL VI. - Vorderingen en beroepen tegen beslissingen van de PB (artikel 12 voornoemde wet 8 juli 2018)Art. 47. Elke persoon die beroep wenst in te stellen tegen een beslissing van de PB moet dit per aangetekende brief richten aan de directeur.Deze brengt onmiddellijk (binnen vijf werkdagen) de voorzitter van de Raad van Bestuur en de secretaris op de hoogte. Hij zendt hun ook het dossier, evenals zijn opmerkingen met betrekking de grondslag van het beroep en elk element dat de Raad van Bestuur in staat kan stellen om een beslissing te nemen.De Raad van Bestuur hoort desgewenst de persoon die beroep heeft ingesteld en/of zijn raadsman binnen de dertig dagen na de indiening ervan.De beslissing van de Raad van Bestuur wordt per aangetekend schrijven meegedeeld aan de persoon die het beroep heeft ingesteld en/of aan zijn raadsman binnen dertig dagen nadat hij is gehoord.Tegen de beslissing in beroep kan hoger beroep worden ingesteld bij de Raad van State onder de voorwaarden van het gemene recht voor beroepen tot schorsing en/of vernietiging bij de Belgische Raad van State.Tegen de beslissingen van de officieren van gerechtelijke politie van de PB kan geen hoger beroep worden ingesteld; ze vallen onder de hiërarchische autoriteit van de procureur des Konings van Luik.TITEL VII. - Inwerkingtreding - Wijziging van het huishoudelijk reglementArt. 48. Het huishoudelijk reglement en de toekomstige wijzigingen ervan treden pas in werking na publicatie in het Belgisch Staatsblad.Na goedkeuring zal het worden gepubliceerd op de website van de PB en ter kennis worden gebracht van alle belanghebbenden.Gezien om te worden gevoegd bij ons besluit van 27 april 2025 tot goedkeuring van het huishoudelijk reglement van de proefbank voor vuurwapens.FILIPVan Koningswege :De Minister van Economie,D. CLARINVALDe Minister van Justitie,A. VERLINDEN 
+VERSLAG AAN DE KONINGSire,Het besluit waarvan we de eer hebben aan uwe Majesteit ter ondertekening voor te leggen, heeft als doel het reglement van 10 december 2024 van de Autoriteit voor Financiële Diensten en Markten betreffende de gestandaardiseerde presentatiewijze van bepaalde informatieverplichtingen inzake aanvullende pensioenen formeel goed te keuren.I. SitueringDe wet van 26 december 2022 tot wijziging van verscheidene bepalingen ter versterking van de transparantie in het kader van de tweede pensioenpijler, zoals gewijzigd door de wet van 11 december 2023 houdende diverse bepalingen inzake pensioenen (hierna de "Transparantiewet") wijzigt een groot aantal bepalingen met betrekking tot informatievoorschriften aan aangeslotenen, begunstigden en rentegenieters in de volgende sociale wetten inzake aanvullende pensioenen:- de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid (hierna "WAP");- de programmawet (I) van 24 december 2002: wet op de aanvullende pensioenen voor zelfstandigen (hierna "WAPZ");- de wet van 15 mei 2014 houdende diverse bepalingen: wet op de aanvullende pensioenen voor zelfstandige bedrijfsleiders (hierna "WAPBL");- de wet van 18 februari 2018 houdende diverse bepalingen inzake aanvullende pensioenen en tot instelling van een aanvullend pensioen voor de zelfstandigen actief als natuurlijk persoon, voor de meewerkende echtgenoten en voor de zelfstandige helpers (hierna "WAPZNP");- de wet van 6 december 2018 tot instelling van een vrij aanvullend pensioen voor de werknemers en houdende diverse bepalingen inzake aanvullende pensioenen (hierna "WAPW").Zo voorziet de Transparantiewet onder meer in een informatieverplichting vóór of bij de aansluiting. Daarbij moeten nieuwe of potentiële aangeslotenen worden geïnformeerd over de belangrijkste kenmerken van de pensioentoezegging of het bilateraal tweede pijlerproduct, zoals voorgeschreven in artikel 41quater van de WAP, artikel 13/2 van de WAPW, artikel 52quater van de WAPZ, artikel 9/2 van de WAPZNP en artikel 41/2 van de WAPBL.In het kader van het vrij aanvullend pensioen voor zelfstandigen moet ook de precontractuele informatie, voorgeschreven door artikel 5 van het Koninklijk besluit van 12 januari 2007 betreffende de aanvullende pensioenovereenkomsten voor zelfstandigen (KB WAPZ), in aanmerking worden genomen.De Transparantiewet gaat daarbij uit van een "principle-based" wettelijk kader waarin de kwalitatieve standaarden worden geformuleerd waaraan de informatie moet voldoen, maar zonder in detail te regelen welke vorm de informatieverstrekking moet aannemen.De FSMA kan bij reglement een gestandaardiseerde presentatiewijze vaststellen van de te verstrekken informatie. Ze kan de vormgeving, waaronder de structuur, de lengte, de inhoud en de volgorde van de rubrieken, de bewoordingen en de layout op een uniforme wijze vaststellen.De wet van 11 december 2023 houdende diverse bepalingen inzake pensioenen gaf de FSMA de opdracht om een gestandaardiseerde presentatiewijze te bepalen voor de informatie aan nieuwe of potentiële aangeslotenen tegen uiterlijk 30 juni 2024. Op 18 juni 2024 heeft de FSMA een eerste versie van het reglement betreffende de gestandaardiseerde presentatiewijze van bepaalde informatieverplichtingen inzake aanvullende pensioenen overgemaakt aan de ministers bevoegd voor aanvullende pensioenen met het oog op de goedkeuring ervan bij Koninklijk besluit.De bevoegde ministers hebben hun ontwerp van Koninklijk besluit tot goedkeuring van het reglement van de FSMA ter advies voorgelegd aan de Commissie voor Aanvullende Pensioenen en de Commissie voor de Aanvullende Pensioenen voor Zelfstandigen. De Commissies hebben hun advies verstrekt op 13 september 2024.Op uitnodiging van de ministers bevoegd voor aanvullende pensioenen heeft de FSMA een aantal verduidelijkingen aangebracht in de toelichting bij het reglement, evenals in de annexen, teneinde tegemoet te komen aan een aantal overwegingen die werden geformuleerd in de adviezen van de commissies.II. "Informatiedocument aanvullend pensioen"De doelstelling is te komen tot een beknopt document waarin de kernelementen van de pensioentoezegging of het bilateraal tweede pijlerproduct worden samengevat. De bedoeling is de (potentiële) aangeslotenen in een begrijpelijke taal en laagdrempelig te informeren over de belangrijkste kenmerken van het aanvullend pensioenplan.Het was de bedoeling van de wetgever dat deze informatie op vormelijk vlak zo veel mogelijk zou aansluiten bij het nieuwe pensioenoverzicht, om een maximale herkenbaarheid van de tweede pensioenpijler te bekomen (Kamer, DOC 55, 3604/002, p. 64).Het spreekt voor zich dat, zou de opmaak van het pensioenoverzicht in de toekomst belangrijke wijzigingen ondergaan, de pensioeninstellingen over de nodige tijd beschikken om het "Informatiedocument aanvullend pensioen" daarmee in overeenstemming te brengen. De gestandaardiseerde presentatiewijze van de informatie vóór of bij aansluiting zal de naam `Informatiedocument aanvullend pensioen' dragen.De precieze inhoud van het `Informatiedocument aanvullend pensioen' wordt toegelicht in vier annexen die bij dit reglement zijn gevoegd. Er zijn verschillende annexen uitgewerkt voor:- pensioentoezeggingen in de zin van de WAP en de WAPBL, die worden gekenmerkt door een driepartijenrelatie, met dien verstande dat de annexen 1.A. en 2.A. ook van toepassing zijn op de onthaalstructuren;- bilaterale tweede pijlerproducten, waarbij twee partijen betrokken zijn.De indeling van de annexen tussen pensioentoezeggingen, enerzijds, en bilaterale tweede pijlerproducten, anderzijds, doet geen uitspraak over het tijdstip waarop de pensioeninstelling het "Informatiedocument aanvullend pensioen" moet meedelen of ter beschikking stellen van de (potentiële) aangeslotenen. Hiervoor gelden de bepalingen van de wetgeving.III. Gebruik in het kader van andere informatieverplichtingenEr moet worden vermeden dat pensioeninstellingen teveel afzonderlijke informatiedocumenten moeten opstellen op grond van de informatieverplichtingen voorzien in de sociale wetgeving inzake aanvullende pensioenen of in andere wetgeving. Een veelheid aan documenten, waarbij dezelfde informatie telkens op een verschillende wijze wordt toegelicht, komt immers verwarrend over voor de (potentiële) aangeslotenen.Om deze reden wordt voorzien dat pensioeninstellingen ervoor kunnen kiezen om het "Informatiedocument aanvullend pensioen" aan te vullen met informatieverplichtingen die worden opgelegd door andere bepalingen.Het betreft bijvoorbeeld:a) Beschrijvende informatie aan aangeslotenen en rentegenietersNaast een informatieverplichting aan nieuwe of potentiële aangeslotenen, voorziet de transparantiewet dat aangeslotenen en rentegenieters ook tijdens de aansluiting recht hebben op begrijpbare informatie over hun aanvullend pensioenplan. Het betreft de beschrijvende informatie, zoals bedoeld in artikel 41quinquies WAP, artikel 13/3 WAPW, artikel 52quinquies WAPZ, artikel 9/3 WAPZNP, en artikel 41/3 WAPBL.Pensioeninstellingen kunnen ervoor kiezen om het "Informatiedocument aanvullend pensioen" ook te gebruiken voor het voldoen van deze informatieverplichtingen aan aangeslotenen en rentegenieters (tijdens de aansluiting) (DOC 55 2942/001, p. 50-51). Inhoudelijk is de informatie aan aangeslotenen en rentegenieters grotendeels dezelfde als deze die moet worden meegedeeld aan potentiële of nieuwe aangeslotenen.Het spreekt voor zich dat dit maar het geval is voor wat de informatie betreft die in het "Informatiedocument aanvullend pensioen" wordt opgenomen en voor zover de andere bepalingen van de betrokken wetgeving (o.a. inzake de modaliteiten van de informatieverstrekking) worden gerespecteerd.Om geen afbreuk te doen aan de gestandaardiseerde presentatiewijze van het "Informatiedocument aanvullend pensioen", bepalen de annexen 2.A. en 2.B de plaats waar in dit kader de eventuele bijkomende vermeldingen kunnen worden opgenomen.Wanneer zij het "Informatiedocument aanvullend pensioen" daarvoor gebruiken, moeten pensioeninstellingen zich er van vergewissen dat de informatie in het "Informatiedocument aanvullend pensioen" dat zij ter beschikking stellen aan aangeslotenen en rentegenieters (bijvoorbeeld via www.mypension.be) up-to-date is.b) Bepaalde informatie te verstrekken door de instellingen voor bedrijfspensioenvoorzieningDe instellingen voor bedrijfspensioenvoorziening kunnen via het "Informatiedocument aanvullend pensioen" tegemoetkomen aan de voorschriften van artikel 96/3 van de wet van 27 oktober 2006 betreffende het toezicht op de instellingen voor bedrijfspensioenvoorziening (WIBP). Het spreekt voor zich dat dit maar het geval is voor wat de informatie betreft die in het "Informatiedocument aanvullend pensioen" wordt opgenomen en voor zover de bepalingen van de betrokken wetgeving (o.a. inzake de modaliteiten van de informatieverstrekking) worden gerespecteerd.Op grond van de Verordening 2019/2088 (SFDR), haar Gedelegeerde Verordeningen en de artikelen 5, 6 en 7 van de Verordening 2020/852 (Taxonomie), moet voor de IBP's bepaalde informatie worden gepubliceerd in "de informatieverschaffing bedoeld in artikel 41 van Richtlijn (EU) 2016/2341" (verwijzing naar artikel 6, lid 3 van de Verordening 2019/2088). Artikel 41 van de Richtlijn 2016/2341 werd omgezet in artikel 96/3 van de WIBP en werd, via de Transparantiewet, geïntegreerd in de sociale wetgeving (in de artikelen 41quater van de WAP, 52quater van de WAPZ, 41/2 van de WAPBL, 13/2 van de WAPW en 9/2 van de WAPZNP - pp.7, 46, 55, 80, 87 en 88 DOC 55 2942/001).De instellingen voor bedrijfspensioenvoorziening kunnen bijgevolg het "Informatiedocument aanvullend pensioen" ook gebruiken om te voldoen aan de precontractuele informatieverplichtingen waarvoor de voormelde Europese regelgeving verwijst naar artikel 6, lid 3 van de Verordening 2019/2088 (SFDR).Het spreekt voor zich dat dit maar het geval is voor wat de informatie betreft die in het "Informatiedocument aanvullend pensioen" wordt opgenomen en voor zover de bepalingen van de betrokken wetgeving (o.a. inzake de modaliteiten van de informatieverstrekking) worden gerespecteerd.Om geen afbreuk te doen aan de gestandaardiseerde presentatiewijze van het "Informatiedocument aanvullend pensioen", bepalen de annexen 2.A. en 2.B. de plaats waar in dit kader de eventuele bijkomende vermeldingen kunnen worden opgenomen.c) Bepaalde informatie te verstrekken door de verzekeringsondernemingenOp dezelfde manier zouden verzekeringsondernemingen ervoor kunnen kiezen om via het "Informatiedocument aanvullend pensioen" ook tegemoet te komen aan hun verplichting tot mededeling van bepaalde precontractuele informatie op grond van de verzekeringswetgeving. Het spreekt voor zich dat dit maar het geval is voor wat de informatie betreft die in het `Informatiedocument aanvullend pensioen' wordt opgenomen en voor zover de bepalingen van de betrokken wetgeving (o.a. inzake de modaliteiten van de informatieverstrekking) worden gerespecteerd.Wij hebben de eer te zijn,Sire,Van Uwe Majesteit,de zeer eerbiedige en zeer getrouwe dienaars,De Minister van Financiën en Pensioenen,J. JAMBONDe Minister van Zelfstandigen,E. SIMONET13 MEI 2025. - Koninklijk besluit tot goedkeuring van het reglement van de Autoriteit voor Financiële Diensten en Markten betreffende de gestandaardiseerde presentatiewijze van bepaalde informatieverplichtingen inzake aanvullende pensioenenFILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de grondwet, artikel 108;Gelet op de wet van 2 augustus 2002 betreffende het toezicht op de financiële sector en de financiële diensten, artikel 64;Gelet op de programmawet (I) van 24 december 2002, artikel 52ter, § 3, tweede lid, ingevoegd bij wet van 26 december 2022, en derde lid, ingevoegd bij wet van 11 december 2023;Gelet op de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid, artikel 41ter, § 3, tweede lid, ingevoegd bij wet van 26 december 2022, en derde lid, ingevoegd bij wet van 11 december 2023;Gelet op de wet van 15 mei 2014 houdende diverse bepalingen, artikel 41/1, § 3, tweede lid, ingevoegd bij wet van 26 december 2022, en derde lid, ingevoegd bij wet van 11 december 2023;Gelet op de wet van 18 februari 2018 houdende diverse bepalingen inzake aanvullende pensioenen en tot instelling van een aanvullend pensioen voor de zelfstandigen actief als natuurlijk persoon, voor de meewerkende echtgenoten en voor de zelfstandige helpers, artikel 4, vierde lid, ingevoegd bij wet van 26 december 2022, en vijfde lid, ingevoegd bij wet van 11 december 2023;Gelet op de wet van 6 december 2018 tot instelling van een vrij aanvullend pensioen voor de werknemers en houdende diverse bepalingen inzake aanvullende pensioenen, artikel 6, vierde lid, ingevoegd bij wet van 26 december 2022, en vijfde lid, ingevoegd bij wet van 11 december 2023;Gelet op het advies van de Raad van toezicht van de Autoriteit voor Financiële Diensten en Markten, gegeven op 5 juni 2024 en op 29 november 2024;Gelet op het advies nr. 44 van de Commissie voor Aanvullende Pensioenen, gegeven op 13 september 2024;Gelet op het advies nr. 19 van de Commissie voor de Aanvullende Pensioenen voor Zelfstandigen, gegeven op 13 september 2024;Op de voordracht van de Minister van Financiën en Pensioenen en de Minister van Zelfstandigen,Hebben Wij besloten en besluiten Wij :Artikel 1. Het bij dit besluit gevoegde reglement van 10 december 2024 van de Autoriteit voor Financiële Diensten en Markten betreffende de gestandaardiseerde presentatiewijze van bepaalde informatieverplichtingen inzake aanvullende pensioenen, wordt goedgekeurd.Art. 2. De minister bevoegd voor Financiën, de minister bevoegd voor Pensioenen en de minister bevoegd voor Zelfstandigen zijn, ieder wat hem betreft, belast met de uitvoering van dit besluit.Gegeven te Brussel, 13 mei 2025.FILIPVan Koningswege :De Minister van Financiën en Pensioenen,J. JAMBONDe Minister van Zelfstandigen,E. SIMONETBIJLAGE BIJ HET KONINKLIJK BESLUIT TOT GOEDKEURING VAN HET REGLEMENT VAN DE AUTORITEIT VOOR FINANCIELE DIENSTEN EN MARKTEN VAN 10 DECEMBER 2024 BETREFFENDE DE GESTANDAARDISEERDE PRESENTATIEWIJZE VAN BEPAALDE INFORMATIEVERPLICHTINGEN INZAKE AANVULLENDE PENSIOENENREGLEMENT VAN DE AUTORITEIT VOOR FINANCIELE DIENSTEN EN MARKTEN VAN 10 DECEMBER 2024 BETREFFENDE DE GESTANDAARDISEERDE PRESENTATIEWIJZE VAN BEPAALDE INFORMATIEVERPLICHTINGEN INZAKE AANVULLENDE PENSIOENENDe Autoriteit voor Financiële Diensten en Markten,Gelet op de wet van 2 augustus 2002 betreffende het toezicht op de financiële sector en de financiële diensten, artikel 64;Gelet op de programmawet (I) van 24 december 2002, artikel 52ter, § 3, tweede lid, ingevoegd bij wet van 26 december 2022 en derde lid, ingevoegd bij wet van 11 december 2023;Gelet op de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid, artikel 41ter, § 3, tweede lid, ingevoegd bij wet van 26 december 2022 en derde lid, ingevoegd bij wet van 11 december 2023;Gelet op de wet van 15 mei 2014 houdende diverse bepalingen, artikel 41/1, § 3, tweede lid, ingevoegd bij wet van 26 december 2022 en derde lid, ingevoegd bij wet van 11 december 2023;Gelet op de wet van 18 februari 2018 houdende diverse bepalingen inzake aanvullende pensioenen en tot instelling van een aanvullend pensioen voor de zelfstandigen actief als natuurlijk persoon, voor de meewerkende echtgenoten en voor de zelfstandige helpers, artikel 4, vierde lid, ingevoegd bij wet van 26 december 2022 en vijfde lid, ingevoegd bij wet van 11 december 2023;Gelet op de wet van 6 december 2018 tot instelling van een vrij aanvullend pensioen voor de werknemers en houdende diverse bepalingen inzake aanvullende pensioenen, artikel 6, vierde lid ingevoegd bij wet van 26 december 2022 en vijfde lid, ingevoegd bij wet van 11 december 2023 ;Gelet op het advies van de Raad van Toezicht, gegeven op 5 juni 2024 en op 29 november 2024;Gelet op het advies nr. 44 van de Commissie voor Aanvullende Pensioenen, gegeven op 13 september 2024;Gelet op het advies nr. 19 van de Commissie voor de Aanvullende Pensioenen voor Zelfstandigen, gegeven op 13 september 2024;Besluit :Artikel 1. - DefinitiesVoor de toepassing van dit reglement wordt verstaan onder:1°  WAP: de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid;2°  WAPZ: de programmawet (I) van 24 december 2002;3°  WAPBL: de wet van 15 mei 2014 houdende diverse bepalingen;4°  WAPZNP: de wet van 18 februari 2018 houdende diverse bepalingen inzake aanvullende pensioenen en tot instelling van een aanvullend pensioen voor de zelfstandigen actief als natuurlijk persoon, voor de meewerkende echtgenoten en voor de zelfstandige helpers;5°  WAPW: de wet van 6 december 2018 tot instelling van een vrij aanvullend pensioen voor de werknemers en houdende diverse bepalingen inzake aanvullende pensioenen;6°  transparantieverslag: het verslag zoals bedoeld in:- artikel 42, § 1, van de WAP;- artikel 14, § 1, van de WAPW;- artikel 53, § 1, van de WAPZ;- artikel 10, § 1, van de WAPZNP;- artikel 42, § 1, van de WAPBL;7°  bilateraal tweede pijlerproduct: het geheel van pensioenovereenkomsten met betrekking tot bovenwettelijke voordelen inzake pensioen en overlijden:- voor de zelfstandigen, de meewerkende echtgenoten of de helpers zoals bedoeld in Titel II, Hoofdstuk 1, Afdeling 4 van de WAPZ;- voor de zelfstandigen zoals bedoeld in Titel II van de WAPZNP;- voor de zorgverleners zoals bedoeld in artikel 54 van de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994;- voor de werknemers zoals bedoeld in Titel 2 van de WAPW;- voor de werknemers zoals bedoeld in artikel 32, § 1, eerste lid, 2°,  van de WAP;die, wat betreft de invulling van de elementen bedoeld in het transparantieverslag, gelijkaardig zijn;8°  pensioentoezegging: de toezegging van een aanvullend pensioen door een inrichter, zoals bedoeld in artikel 3, § 1, 2°  van de WAP en artikel 35, 2°  van de WAPBL. Voor de toepassing van dit reglement wordt de onthaalstructuur, zoals bedoeld in artikel 32, § 2 van de WAP ook als een pensioentoezegging beschouwd.Art. 2 - ToepassingsgebiedDit reglement stelt de gestandaardiseerde presentatiewijze vast van de informatie vóór of bij de aansluiting, zoals bedoeld in:- artikel 41quater van de WAP;- artikel 41/2 van de WAPBL;en de informatie vóór de aansluiting, zoals bedoeld in:- artikel 52quater van de WAPZ;- artikel 9/2 van de WAPZNP;- artikel 13/2 van de WAPW;en artikel 5, eerste lid, 1°  tot en met 4°,  6°  tot en met 12°,  14°  en 15°  van het Koninklijk besluit van 12 januari 2007 betreffende de aanvullende pensioenovereenkomsten voor zelfstandigen.Art. 3 - Informatiedocument aanvullend pensioen § 1. De informatie zoals bedoeld in artikel 2 wordt opgenomen in een op zichzelf staand document met als titel "Informatiedocument aanvullend pensioen". § 2. Het "Informatiedocument aanvullend pensioen" wordt opgesteld voor elke pensioentoezegging of elk bilateraal tweede pijlerproduct afzonderlijk. § 3. Het "Informatiedocument aanvullend pensioen" bevat geen geïndividualiseerde informatie. § 4. De informatie in het "Informatiedocument aanvullend pensioen" wordt concreet en kernachtig verwoord. Voor verdere informatie kan worden doorverwezen naar andere documenten. De doorverwijzing gebeurt zo gedetailleerd mogelijk. Het "Informatiedocument aanvullend pensioen" en de documenten waarnaar wordt verwezen zijn inhoudelijk coherent. Er wordt over gewaakt dat de (potentiële) aangeslotenen effectief toegang hebben tot de documenten waarnaar wordt verwezen. Indien wordt gewerkt met een link, wordt deze tijdig geactualiseerd. § 5. Het "nformatiedocument aanvullend pensioen" voldoet aan de bepalingen van artikel 41ter, § 1, van de WAP, artikel 13/1, § 1, van de WAPW, artikel 52ter, § 1, van de WAPZ, artikel 9/1, § 1, van de WAPZNP en artikel 41/1, § 1, van de WAPBL.Art. 4 - Gestandaardiseerde presentatiewijze § 1. De gestandaardiseerde presentatiewijze van het "Informatiedocument aanvullend pensioen" is vastgelegd in:- annex 1.A. voor wat betreft de pensioentoezeggingen, zoals bedoeld in artikel 1, 8° ;- annex 1.B. voor wat betreft de bilaterale tweede pijlerproducten, zoals bedoeld in artikel 1, 7°. Rekening houdend met het toepassingsgebied ervan, volgt het "Informatiedocument aanvullend pensioen" de structuur en de volgorde van de rubrieken zoals weergegeven in de annexen 1.A. of 1.B. § 2. Het lettertype, de lettergrootte, de visuele elementen en het gebruik van kleuren wordt zo veel mogelijk afgestemd op het pensioenoverzicht, zoals bedoeld in artikel 26 § 1 van de WAP, artikel 10, § 1 van de WAPW, artikel 48, § 1 van de WAPZ, artikel 6, § 1 van de WAPZNP en artikel 39, § 1 van de WAPBL.De informatie wordt helder en goed leesbaar gepresenteerd. Het kleurgebruik mag geen afbreuk doen aan de begrijpelijkheid van de informatie als het "Informatiedocument aanvullend pensioen" in zwart-wit wordt afgedrukt. § 3. Het "Informatiedocument aanvullend pensioen" mag niet langer zijn dan 4 bladzijden van het formaat A4.Art. 5 - Inhoud § 1. Een nadere omschrijving van het toepassingsgebied en de inhoud van de verschillende rubrieken, alsook de te gebruiken bewoordingen, zijn opgenomen in:- annex 2.A. voor wat betreft de pensioentoezeggingen, zoals bedoeld in artikel 1, 8° ;- annex 2.B. voor wat betreft de bilaterale tweede pijlerproducten, zoals bedoeld in artikel 1, 7°.  § 2. Voor zover van toepassing, maken de pensioeninstellingen gebruik van de in de annexen 2.A. of 2.B. opgenomen standaardteksten die de te gebruiken bewoordingen op een uniforme wijze vaststellen.Van de standaardteksten kan enkel worden afgeweken wanneer de toepassing ervan aanleiding zou geven tot verkeerde informatie rekening houdend met de specifieke kenmerken van de pensioentoezegging of het bilaterale tweede pijlerproduct, of eventuele toekomstige wetswijzigingen.De pensioeninstellingen vullen de rubrieken verder aan met de specifieke kenmerken van de pensioentoezegging of het bilaterale tweede pijlerproduct. § 3. Wanneer er meerdere beleggingsopties zijn, wordt de informatie die specifiek betrekking heeft op de beleggingsopties, zoals toegelicht in de annexen 2.A. of 2.B., per beleggingsoptie afzonderlijk in bijlage bij het "Informatiedocument aanvullend pensioen" weergegeven.De pensioeninstellingen kunnen informatie waarvan de mededeling verplicht is op grond van andere regelgeving, opnemen in bijlage bij het "Informatiedocument aanvullend pensioen".De bijlagen worden genummerd en volgen de volgorde voorgeschreven in de annexen 2.A. of 2.B. De bijlagen mogen het maximaal aantal bladzijden, bedoeld in artikel 4, § 3, overschrijden.Art. 6 - InwerkingtredingDit reglement treedt in werking op de datum voorzien in artikel 92, vierde lid, van de wet van 26 december 2022 tot wijziging van verscheidene bepalingen ter versterking van de transparantie in het kader van de tweede pensioenpijler.Brussel, 10 december 2024.De Voorzitter van de Autoriteit voor Financiële Diensten en Markten,J.-P. SERVAISGezien om te worden gevoegd bij Ons besluit tot goedkeuring van het reglement van 10 december 2024 van de Autoriteit voor Financiële Diensten en Markten betreffende de gestandaardiseerde presentatiewijze van bepaalde informatieverplichtingen inzake aanvullende pensioenen.Brussel, 13 mei 2025.FILIPVan Koningswege :De Minister van Financiën en Pensioenen,J. JAMBONDe Minister van Zelfstandigen,E. SIMONET Voor de raadpleging van de tabel, zie beeld  
 </t>
         </is>
       </c>
@@ -971,28 +969,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025003529</t>
+          <t>2025200245</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>07 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit houdende ontslag en benoeming van zes leden van de bijzondere raadgevende commissie Onrechtmatige bedingen</t>
+          <t>13 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 24 oktober 2024, gesloten in het Paritair Comité voor de begrafenisondernemingen, betreffende de vaststelling van de modaliteiten, het bedrag en de wijze van toekenning en uitkering van een tussenkomst in de opleidingskosten aan werknemers en ondernemingen (1)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-07&amp;numac_search=2025003529&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003529=16&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025200245&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200245=16&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op het Wetboek van economisch recht, artikel XIII.7, eerste lid, ingevoegd bij de wet van 15 december 2013;Gelet op het advies van de Centrale Raad voor het Bedrijfsleven, gegeven op 19 februari 2025;Overwegende dat dubbele lijsten van kandidaten aan de Minister van Economie werden voorgelegd;Overwegende de wet van 20 juli 1990 ter bevordering van de evenwichtige aanwezigheid van mannen en vrouwen in organen met adviserende bevoegdheid, de artikelen 2, gewijzigd bij de wet van 17 juli 1997, en 2bis, ingevoegd bij de wet van 17 juli 1997 en gewijzigd bij de wet van 3 mei 2003;Overwegende het koninklijk besluit van 13 december 2017 houdende oprichting van de bijzondere raadgevende commissie "Onrechtmatige bedingen" binnen de Centrale Raad voor het Bedrijfsleven, artikel 2, § 1;Overwegende het koninklijk besluit van 12 mei 2024 tot benoeming van de voorzitter, de ondervoorzitters en de leden van de bijzondere raadgevende commissie "Onrechtmatige bedingen";Op de voordracht van de Minister van Economie en de Minister voor Consumentenbescherming,Hebben Wij besloten en besluiten Wij :Artikel 1. Eervol ontslag wordt verleend aan de heer Sébastien Denoiseux uit zijn mandaat van effectief lid van de bijzondere raadgevende commissie Onrechtmatige bedingen als vertegenwoordiger van de organisaties van de productie.Art. 2. Eervol ontslag wordt verleend aan de heer Maarten Boghaert uit zijn mandaat als effectief lid van de bijzondere raadgevende commissie Onrechtmatige bedingen als vertegenwoordiger van de consumentenorganisaties.Art. 3. Eervol ontslag wordt verleend aan mevrouw Virginie Van Overbeke uit haar mandaat als effectief lid van de bijzondere raadgevende commissie Onrechtmatige bedingen als vertegenwoordigster van de consumentenorganisaties.Art. 4. Eervol ontslag wordt verleend aan de heer Arie Van Hoe uit zijn mandaat van plaatsvervangend lid van de bijzondere raadgevende commissie Onrechtmatige bedingen als vertegenwoordiger van de organisaties van de productie.Art. 5. Eervol ontslag wordt verleend aan mevrouw Elke Van Overwaele uit haar mandaat van plaatsvervangend lid van de bijzondere raadgevende commissie Onrechtmatige bedingen als vertegenwoordigster van de organisaties van de productie.Art. 6. Eervol ontslag wordt verleend aan mevrouw Patricia De Marchi uit haar mandaat van plaatsvervangend lid van de bijzondere raadgevende commissie Onrechtmatige bedingen als vertegenwoordigster van de consumentenorganisaties.Art. 7. Mevrouw Margo Osier wordt benoemd als effectief lid van de bijzondere raadgevende commissie Onrechtmatige bedingen als vertegenwoordigster van de organisaties van de productie. Ze voltooit het mandaat van haar voorganger bedoeld in artikel 1.Art. 8. De heer Joris Verschueren wordt benoemd als effectief lid van de bijzondere raadgevende commissie Onrechtmatige bedingen als vertegenwoordiger van de consumentenorganisaties. Hij voltooit het mandaat van zijn voorganger bedoeld in artikel 2.Art. 9. De heer Hugo Sonck wordt benoemd als effectief lid van de bijzondere raadgevende commissie Onrechtmatige bedingen als vertegenwoordiger van de consumentenorganisaties. Hij voltooit het mandaat van zijn voorgangster bedoeld in artikel 3.Art. 10. Mevrouw Elke Van Overwaele wordt benoemd als plaatsvervangend lid van de bijzondere raadgevende commissie Onrechtmatige bedingen als vertegenwoordigster van de organisaties van de productie. Ze voltooit het mandaat van haar voorganger bedoeld in artikel 4.Art. 11. De heer Thijs Eeckhaut wordt benoemd als plaatsvervangend lid van de bijzondere raadgevende commissie Onrechtmatige bedingen als vertegenwoordiger van de organisaties van de productie. Hij voltooit het mandaat van zijn voorgangster bedoeld in artikel 5.Art. 12. De heer Maarten Boghaert wordt benoemd als plaatsvervangend lid van de bijzondere raadgevende commissie Onrechtmatige bedingen als vertegenwoordiger van de consumentenorganisaties. Hij voltooit het mandaat van zijn voorgangster bedoeld in artikel 6.Art. 13. Dit besluit treedt in werking de dag waarop het in het Belgisch Staatsblad wordt bekendgemaakt.Art. 14. De minister bevoegd voor Economie en de minister bevoegd voor Consumentenbescherming zijn, ieder wat hem betreft, belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Economie,D. CLARINVALDe Minister van Consumentenbescherming,R. BEENDERS 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de begrafenisondernemingen; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 24 oktober 2024, gesloten in het Paritair Comité voor de begrafenisondernemingen, betreffende de vaststelling van de modaliteiten, het bedrag en de wijze van toekenning en uitkering van een tussenkomst in de opleidingskosten aan werknemers en ondernemingen. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de begrafenisondernemingen Collectieve arbeidsovereenkomst van 24 oktober 2024 Vaststelling van de modaliteiten, het bedrag en de wijze van toekenning en uitkering van een tussenkomst in de opleidingskosten aan werknemers en ondernemingen (Overeenkomst geregistreerd op 22 november 2024 onder het nummer 190707/CO/320) HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de arbeiders/arbeidsters en bedienden, hierna werknemers genoemd, van de ondernemingen welke ressorteren onder het Paritair Comité voor de begrafenisondernemingen. HOOFDSTUK II. - Toekenning van een opleidingspremie Art. 2.  § 1. In uitvoering van de bepalingen van artikel 5 en 6 van de statuten, vastgesteld bij de collectieve arbeidsovereenkomst van 9 juni 2020 (159645/CO/320), gesloten in het Paritair Comité voor de begrafenisondernemingen, tot oprichting van een waarborg- en sociaal fonds "Fonds 320" en tot vaststelling van de statuten, wordt aan de werknemers, bedoeld in artikel 1 jaarlijks een opleidingspremie toegekend ten laste van het waarborg- en sociaal fonds, waarvan het bedrag en de wijze van toekenning en uitkering hierna zijn vastgesteld.  § 2. Opleidingsinstellingen die de opleiding tot funerair medewerker/begrafenisondernemer organiseren kunnen de bijbehorende syllabus voor de cursisten gratis ontvangen via het waarborg- en sociaal fonds.HOOFDSTUK III. - Bedrag van de opleidingspremie en tussenkomst kosten rijbewijs Art. 3.  § 1. Vanaf 1 september 2012 is het bedrag van de opleidingspremie gelijk aan maximaal 50 EUR op jaarbasis, per kalenderjaar en per werknemer.  § 2. Voor werknemers die behoren tot de risicogroepen zoals bepaald bij de collectieve arbeidsovereenkomst van 13 november 2019 (156944/CO/320) betreffende maatregelen ten voordele van de werkgelegenheid en de vorming van risicogroepen gesloten in het Paritair Comité van de begrafenisondernemingen, en vanaf 1 januari 2022 een door het Fonds 320 erkende opleidingen gerelateerd aan de begrafenissector bedraagt de opleidingspremie aan de werknemer maximaal 500 EUR op jaarbasis.  § 3. Voor werknemers die behoren tot de risicogroepen zoals bepaald bij de collectieve arbeidsovereenkomst van 7 december 2015 betreffende maatregelen ten voordele van de werkgelegenheid en de vorming van risicogroepen gesloten in het Paritair Comité van de begrafenisondernemingen en die een rijbewijs B behalen na een opleiding in een erkende rijschool, wordt een opleidingspremie toegekend van maximaal 300 EUR. Theoretische en praktische opleidingen voor het behalen van rijbewijs B in erkende rijscholen komen hiervoor in aanmerking. HOOFDSTUK IV. - Toekenningsvoorwaarden Art. 4. Voor elke aanvraag dient er een apart aanvraagformulier bezorgd te worden. De premie kan betrekking hebben op de inschrijvingskost van de opleiding alsook het materiaal (cursussen, handboeken, werkinstrumenten). Bij twijfel worden de dossiers voorgelegd aan de raad van beheer van het waarborg- en sociaal fonds. Van zodra de informatie in het aanvraagdossier volledig is, betaalt het Fonds 320 uit binnen het kwartaal na goedkeuring. De terugbetaling van de opleidingskosten wordt door de werknemer gevraagd op basis van een inschrijvingsformulier dat overgemaakt wordt aan het waarborg- en sociaal fonds, Anspachlaan 111 B13, 1000 Brussel. Op het inschrijvingsformulier dienen de gegevens te komen van de werknemer en een verklaring van de opleidingsinstelling (stempel, handtekening en gegevens van de opleidingsinstelling). De premie kan aangevraagd worden bij aanvang van de opleiding en ten laatste tot 3 maanden na het beëindigen van de opleiding. De opleidingspremie voor het behalen van het rijbewijs B kan aangevraagd worden tot 3 maanden na het behalen van het rijbewijs. Opleidingen die in aanmerking komen, moeten een meerwaarde bieden op professioneel vlak en aansluiten bij de kwaliteitsvereisten van de Belgische arbeidsmarkt. Dit zijn : - de opleidingen erkend in het kader van Betaald Educatief Verlof of Vlaams Opleidingsverlof; - de opleidingen die erkend zijn bij Onderwijs (inclusief CVO-opleidingen en opleidingen sociale promotie), Syntra en de opleidingen erkend door de VDAB in het kader van de opleidingscheques; - opleidingen bij alle organisaties die erkend zijn in het kader van de KMO-Portefeuille of een ESF kwaliteitslabel hebben. De tussenkomst in de kosten van het rijbewijs gaat over werknemers die een rijbewijs B behalen na een opleiding in een erkende rijschool "Theoretische en praktische opleidingen voor het behalen van rijbewijs B in erkende rijscholen komen hiervoor in aanmerking. Voor aanvragen van individuele werknemers voor opleidingen die niet automatisch erkend zijn, kan er enkel een premie worden toegestaan indien de raad van beheer van het waarborg- en sociaal fonds daartoe beslist.HOOFDSTUK V. - Uitvoeringsmodaliteiten Art. 5. De raad van beheer van het waarborg- en sociaal fonds neemt alle vereiste administratieve maatregelen opdat de nodige sommen voor de betaling van de premie aan de rechthebbenden, beschikbaar zouden zijn. HOOFDSTUK VI. - Motivatiepremie en aanwervingspremie Art. 6. Vanaf 1 januari 2022 kan aan de werkgever en aan de werknemer een motivatiepremie toegekend worden bij stage- en leercontracten. Art. 7.  Motivatiepremie Teneinde de tewerkstelling aan te moedigen van personen die behoren tot de "risicogroepen" kan aan de betrokken werknemers een forfaitaire financiële tussenkomst toegekend worden van maximum 200,00 EUR per kwartaal tewerkstelling voor een maximale periode van 1 jaar (dus maximum van 800,00 EUR). Deze personen moeten worden aangeworven met een voltijds contract van onbepaalde duur. Art. 8.  Aanwervingspremie Aan de werkgever die een werknemer uit de risicogroepen, zoals bepaald bij de collectieve arbeidsovereenkomst van 7 december 2015 betreffende maatregelen ten voordele van de werkgelegenheid en de vorming van risicogroepen gesloten in het Paritair Comité van de begrafenisondernemingen in dienst neemt met een arbeidsovereenkomst van onbepaalde duur, kan een aanwervingspremie toegekend worden. Deze premie kan slechts toegekend worden voor de eerste 100 aanwervingen in de sector. Het "Waarborg en Sociaal Fonds voor de begrafenisondernemingen" komt tussen in de loonkosten, met een maximum van 200,00 EUR per kwartaal met een maximum van 1 jaar (dus maximum 800,00 EUR) bij een nieuw voltijds contract van onbepaalde duur. Art. 9.  Toekenningsvoorwaarden Voor elke aanvraag dient er een apart aanvraagformulier bezorgd te worden. Van zodra de informatie in het aanvraagdossier volledig is, betaalt het Fonds 320 uit binnen het kwartaal na het vierde kwartaal na aanwerving en na goedkeuring. De documenten staan op de website van het Fonds 320 : www.fonds320.be. HOOFDSTUK VII. - Algemene bepalingen Art. 10. Alle onvoorziene en/of betwiste gevallen met betrekking tot de uitbetaling van de premie en tot de erkenning van rechthebbende, worden door de raad van beheer van het waarborg- en sociaal fonds beslecht. HOOFDSTUK VIII. - Geldigheidsduur Art. 11. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2023 en is gesloten voor onbepaalde duur. Elk van de partijen kan ze opzeggen met een opzeggingstermijn van drie maanden te betekenen bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Comité voor de begrafenisondernemingen. Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst van 6 juli 2023 (187229/CO/320). Gezien om te worden gevoegd bij het koninklijk besluit van 13 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -1003,29 +1001,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025003530</t>
+          <t>2025201189</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>07 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit houdende hernieuwing van het mandaat van de voorzitter en houdende ontslag en benoeming van een ondervoorzitter en leden van de bijzondere raadgevende commissie Verbruik</t>
+          <t>13 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 24 oktober 2024, gesloten in het Paritair Comité voor de zeevisserij, betreffende de wijziging van de bijlage (pensioenreglement) aan de collectieve arbeidsovereenkomst van 23 december 2008 (registratienr. 90450/CO/143), zoals laatst gewijzigd door de collectieve arbeidsovereenkomst van 23 februari 2023 (registratienr. 178887/CO/143) (1)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-07&amp;numac_search=2025003530&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003530=17&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025201189&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201189=17&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op het Wetboek van economisch recht, de artikel XIII.7, eerste lid, ingevoegd bij de wet van 15 december 2013;Gelet op het advies van de Centrale Raad voor het Bedrijfsleven, gegeven op 19 februari 2025 ;Overwegende dat dubbele lijsten van kandidaten aan de Minister van Economie werden voorgelegd;Overwegende de wet van 20 juli 1990 ter bevordering van de evenwichtige aanwezigheid van mannen en vrouwen in organen met adviserende bevoegdheid, de artikelen 2, gewijzigd bij de wet van 17 juli 1997, en 2bis, ingevoegd bij de wet van 17 juli 1997 en gewijzigd bij de wet van 3 mei 2003;Overwegende het koninklijk besluit van 13 december 2017 houdende oprichting van de bijzondere raadgevende commissie "Verbruik" binnen de Centrale Raad voor het Bedrijfsleven en tot opheffing van de Commissie voor Milieu-etikettering en milieureclame, artikel 3;Overwegende het koninklijk besluit van 30 oktober 2018 tot benoeming van de voorzitter, de ondervoorzitters en de leden van de bijzondere raadgevende commissie "Verbruik";Overwegende het koninklijk besluit van 16 juli 2023 tot benoeming van de ondervoorzitters en de leden van de bijzondere raadgevende commissie "Verbruik";Op de voordracht van de Minister van Economie en de Minister van Consumentenbescherming,Hebben Wij besloten en besluiten Wij :Artikel 1. Het mandaat van voorzitter van de bijzondere raadgevende commissie Verbruik van dhr. Reinhard Steennot wordt hernieuwd voor een termijn van zes jaar.Art. 2. Eervol ontslag wordt verleend aan de heer Arie Van Hoe uit zijn mandaat van ondervoorzitter en effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordiger van de organisaties van de productie.Art. 3. Eervol ontslag wordt verleend aan mevrouw Elke Van Overwaele uit haar mandaat als effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordigster van de organisaties van de productie.Art. 4. Eervol ontslag wordt verleend aan mevrouw Ilse Meyers uit haar mandaat als effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordigster van de organisaties van de distributie.Art. 5. Eervol ontslag wordt verleend aan mevrouw Lynn Jonckheere uit haar mandaat van effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordigster van de organisaties van de middenstand.Art. 6. Eervol ontslag wordt verleend aan de heer Maarten Boghaert uit zijn mandaat van effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordiger van de consumentenorganisaties.Art. 7. Eervol ontslag wordt verleend aan mevrouw Marie-Christine Calmant uit haar mandaat van effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordigster van de consumentenorganisaties.Art. 8. Eervol ontslag wordt verleend aan mevrouw Laura De Brandt uit haar mandaat van effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordigster van de consumentenorganisaties.Art. 9. Eervol ontslag wordt verleend aan de heer Thomas Greuse uit zijn mandaat van effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordiger van de consumentenorganisaties.Art. 10. Eervol ontslag wordt verleend aan mevrouw Tine Debaes uit haar mandaat van plaatsvervangend lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordigster van de organisaties van de productie.Art. 11. Eervol ontslag wordt verleend aan de heer William Donck uit zijn mandaat van plaatsvervangend lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordiger van de organisaties van de distributie.Art. 12. Eervol ontslag wordt verleend aan mevrouw Sophie Heuskin uit haar mandaat van plaatsvervangend lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordigster van de organisaties van de middenstand.Art. 13. Eervol ontslag wordt verleend aan de heer Mario Coppens uit zijn mandaat van plaatsvervangend lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordiger van de consumentenorganisaties.Art. 14. Eervol ontslag wordt verleend aan de heer Bernd Lorch uit zijn mandaat van plaatsvervangend lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordiger van de consumentenorganisaties.Art. 15. Mevrouw Elke Van Overwaele wordt benoemd als ondervoorzitter en effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordigster van de organisaties van de productie. Ze voltooit het mandaat van haar voorganger bedoeld in artikel 2.Art. 16. De heer Thijs Eeckhaut wordt benoemd als effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordiger van de organisaties van de productie. Hij voltooit het mandaat van zijn voorgangster bedoeld ik artikel 3.Art. 17. Mevrouw Ann-Sophie De Graeve wordt benoemd als effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordigster van de organisaties van de distributie. Ze voltooit het mandaat van haar voorgangster bedoeld in artikel 4.Art. 18. Mevrouw Elise Detavernier wordt benoemd als effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordigster van de organisaties van de middenstand. Ze voltooit het mandaat van haar voorgangster bedoeld in artikel 5.Art. 19. De heer Joris Verschueren wordt benoemd als effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordiger van de consumentenorganisaties. Hij voltooit het mandaat van zijn voorganger bedoeld in artikel 6.Art. 20. De heer Bernd Lorch wordt benoemd als effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordiger van de consumentenorganisaties. Hij voltooit het mandaat van zijn voorgangster bedoeld in artikel 7.Art. 21. Mevrouw Cassandra Van Boterdael wordt benoemd als effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordigster van de consumentenorganisaties. Ze voltooit het mandaat van haar voorgangster bedoeld in artikel 8.Art. 22. De heer François Sana wordt benoemd als effectief lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordiger van de consumentenorganisaties. Hij voltooit het mandaat van zijn voorganger bedoeld in artikel 9.Art. 23. Mevrouw Margo Osier wordt benoemd als plaatsvervangend lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordigster van de organisaties van de productie. Ze voltooit het mandaat van haar voorgangster bedoeld in artikel 10.Art. 24. De heer Lucas Devogel wordt benoemd als plaatsvervangend lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordiger van de organisaties van de distributie. Hij voltooit het mandaat van zijn voorganger bedoeld in artikel 11.Art. 25. De heer Olivier Vandenabeele wordt benoemd als plaatsvervangend lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordiger van de organisaties van de middenstand. Hij voltooit het mandaat van zijn voorgangster bedoeld in artikel 12.Art. 26. De heer Maarten Boghaert wordt benoemd als plaatsvervangend lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordiger van de consumentenorganisaties. Hij voltooit het mandaat van zijn voorganger bedoeld in artikel 13.Art. 27. Mevrouw Anne Fily wordt benoemd als plaatsvervangend lid van de bijzondere raadgevende commissie Verbruik als vertegenwoordigster van de consumentenorganisaties. Ze voltooit het mandaat van haar voorganger bedoeld in artikel 14.Art. 28. Dit besluit treedt in werking de dag waarop het in het Belgisch Staatsblad wordt bekendgemaakt.Art. 29. De minister bevoegd voor Economie en de minister bevoegd voor Consumentenbescherming zijn, ieder wat hem betreft, belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Economie,D. CLARINVALDe Minister van Consumentenbescherming,R. BEENDERS 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de zeevisserij; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 24 oktober 2024, gesloten in het Paritair Comité voor de zeevisserij, betreffende de wijziging van de bijlage (pensioenreglement) aan de collectieve arbeidsovereenkomst van 23 december 2008 (registratienr. 90450/CO/143), zoals laatst gewijzigd door de collectieve arbeidsovereenkomst van 23 februari 2023 (registratienr. 178887/CO/143). Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de zeevisserij Collectieve arbeidsovereenkomst van 24 oktober 2024 Wijziging van de bijlage (pensioenreglement) aan de collectieve arbeidsovereenkomst van 23 december 2008 (registratienr. 90450/CO/143), zoals laatst gewijzigd door de collectieve arbeidsovereenkomst van 23 februari 2023 (registratienr. 178887/CO/143) (Overeenkomst geregistreerd op 5 december 2024 onder het nummer 190898/CO/143) HOOFDSTUK I. - Toepassingsgebied Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de reders en de werknemers die ressorteren onder het Paritair Comité (PC 143) voor de zeevisserij en die onder het toepassingsgebied vallen van het koninklijk besluit van 17 februari 2005 tot uitvoering van de bepalingen van de wet van 3 mei 2003 tot regeling van de arbeidsovereenkomst wegens scheepsdienst voor de zeevisserij en tot verbetering van het sociaal statuut van de zeevisserij.  § 2. Voor de toepassing van onderhavige collectieve arbeidsovereenkomst moet worden verstaan onder "werknemers": arbeiders, zowel vrouwen als mannen. HOOFDSTUK II. - Wijziging van het pensioenreglement Art. 2. Het gecoördineerde pensioenreglement in bijlage aan deze collectieve arbeidsovereenkomst wijzigt en vervangt de bijlage aan de collectieve arbeidsovereenkomst van 23 december 2008 (registratienr. 90450/CO/143), zoals laatst gewijzigd door de collectieve arbeidsovereenkomst van 23 februari 2023 (registratienr. 178887/CO/143).HOOFDSTUK III. - Duur en opzeggingsmodaliteiten Art. 3. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van 1 januari 2025 en is gesloten voor onbepaalde tijd en heeft dezelfde opzeggingsmodaliteiten als de collectieve arbeidsovereenkomst van 23 december 2008, zoals laatst gewijzigd door de collectieve arbeidsovereenkomst van 23 februari 2023. Gezien om te worden gevoegd bij het koninklijk besluit van 13 mei 2025. De Minister van Werk, D. CLARINVALBijlage aan de collectieve arbeidsovereenkomst van 24 oktober 2024, gesloten in het Paritair Comité voor de zeevisserij, betreffende de wijziging van de bijlage (pensioenreglement) aan de collectieve arbeidsovereenkomst van 23 december 2008 (registratienr. 90450/CO/143), zoals laatst gewijzigd door de collectieve arbeidsovereenkomst van 23 februari 2023 (registratienr. 178887/CO/143) Zeevissersfonds Pensioenreglement Algemeen De pensioentoezegging treedt in werking op 1 januari 2009 volgens de modaliteiten van de collectieve arbeidsovereenkomst van 23 december 2008 gesloten in het Paritair Comité van de zeevisserij (PC 143), die de collectieve arbeidsovereenkomst van 19 januari 2006 gesloten in het Paritair Comité van de zeevisserij (PC 143) houdende de invoering van een sectoraal pensioenstelsel ten behoeve van de erkende zeevissers wijzigt en vervangt. De Pensioentoezegging wordt beheerd door het pensioenreglement. Het onderhavige pensioenreglement betreft een gecoördineerde versie waarbij de laatste wijzigingen in werking zijn getreden op 1 januari 2025. Artikel 1. Definities Voor de toepassing van dit reglement wordt verstaan onder: Aangeslotene Alle werknemers tewerkgesteld met een arbeidsovereenkomst wegens scheepsdienst voor de zeevisserij (artikel 4 van de wet van 3 mei 2003), die een erkenning hebben verkregen als zeevisser. Arbeidsongeval Een arbeidsongeval dat zich tijdens en door het feit van de uitvoering van een arbeidsovereenkomst wegens scheepsdienst voor de zeevisserij heeft voorgedaan. Bijdrage De bijdragen die door de inrichter gestort worden als tegenwaarde van de verbintenissen van de pensioeninstelling en van de verzekeringsinstelling. FSMA Financiële Autoriteit voor Markten en Diensten ("Financial Services and Markets Authority"). Datum van inwerkingtreding 1 januari 2009. Erkend zeevisser De werknemer die erkend wordt als zeevisser overeenkomstig de bepalingen van het koninklijk besluit van 17 februari 2005 tot uitvoering van de bepalingen van de wet van 3 mei 2003 tot regeling van de arbeidsovereenkomst wegens scheepsdienst voor de zeevisserij en tot verbetering van het sociaal statuut van de zeevisser. Financieringsfonds Stelsel van collectieve reserve, dat beheerd wordt overeenkomstig de in het huidig pensioenreglement gedefinieerde doelstellingen en bepalingen. Gepresteerde RSZ-dagen Al de dagen die deel uitmaken van een arbeidsovereenkomst wegens scheepsdienst voor de zeevisserij, zoals omschreven bij de artikel 8, leden 1 en 2 van de wet van 3 mei 2003 tot regeling van de arbeidsovereenkomst wegens scheepsdienst voor de zeevisserij en tot verbetering van het sociaal statuut van de zeevisser.Inrichter Het fonds voor bestaanszekerheid, "Zeevissersfonds" genaamd dat werd opgericht bij collectieve arbeidsovereenkomst van 29 augustus 1986 gesloten in het Paritair Comité van de zeevisserij. Jaarlijkse aanpassing De datum waarop de aanpassing van de lopende contracten plaatsvindt, met name bij het begin van elk verzekeringsjaar. Pensioenleeftijd De eerste dag van de maand die volgt op de 60ste verjaardag van de aangeslotene. Voor werknemers tewerkgesteld als erkend zeevisser met een arbeidsovereenkomst wegens scheepsdienst voor zeevisserij vanaf 1 januari 2019 is de pensioenleeftijd bepaald op de eerste dag van de maand die volgt op de maand waarin hij de leeftijd van 65 jaar bereikt. Voor werknemers tewerkgesteld als erkend zeevisser met een arbeidsovereenkomst wegens scheepsdienst voor zeevisserij vanaf 1 februari 2025 wordt de pensioenleeftijd bepaald op de eerste dag van de maand die volgt op de maand waarin hij de leeftijd van 66 jaar bereikt. Voor werknemers tewerkgesteld met een arbeidsovereenkomst wegens scheepsdienst voor zeevisserij als erkend zeevisser vanaf 1 februari 2030 is de pensioenleeftijd bepaald op de eerste dag van de maand die volgt op de maand waarin hij de leeftijd van 67 jaar bereikt. Pensioeninstelling AG Insurance n.v., E. Jacqmainlaan 53, 100 Brussel - R.P.R. Brussel, BTW BE 0404.494.849, Belgische verzekeringsonderneming toegelaten onder code 0079, onder het toezicht van de Nationale Bank van België, de Berlaimontlaan 14, 1000 Brussel die wordt belast met het verzekeren van de waarborg leven zoals gedefinieerd in artikel 7 alsook van de waarborg overlijden zoals gedefinieerd in artikel 8.1. Pensioentoezegging De toezegging van een aanvullend pensioen conform onderhavig pensioenreglement door de inrichter aan de aangeslotenen en/of hun rechthebbenden. Pensionering De effectieve ingang van het rustpensioen, al dan niet vervroegd, in het wettelijk pensioenstelsels voor werknemers. Pensioentoezegging van het type "vaste bijdragen" De verbintenis van de inrichter tot het betalen aan de pensioeninstelling van voorafgestelde premies tot financiering van de pensioentoezegging. Uittreding - Hetzij de intrekking van de erkenning als zeevisser anders dan door overlijden of pensionering; - Hetzij het einde van de aansluiting vanwege het feit dat de werknemer de aansluitingsvoorwaarden van artikel 3.1. niet langer vervult, zonder dat dit gepaard gaat met de intrekking van de erkenning als zeevisser of de beëindiging van de arbeidsovereenkomst, anders dan door overlijden of pensionering; - Hetzij het einde van de aansluiting omwille van het feit dat de reder, of in geval van overgang van de arbeidsovereenkomst, de nieuwe reder niet langer valt onder het toepassingsgebied van de collectieve arbeidsovereenkomst van 23 december 2008 betreffende het sectoraal pensioenstelsel ten behoeve van de erkende zeevissers. Verworven reserves De reserves waarop de aangeslotene op een bepaald ogenblik recht heeft overeenkomstig dit pensioenreglement. Verzekeringsinstelling AG Insurance n.v., E. Jacqmainlaan 53, 100 Brussel - R.P.R. Brussel, BTW BE 0404.494.849, Belgische verzekeringsonderneming toegelaten onder code 0079, onder het toezicht van de Nationale Bank van België, de Berlaimontlaan 14, 1000 Brussel die wordt belast met het verzekeren van de waarborgen overlijden ten gevolge van een arbeidsongeval en arbeidsongeschiktheid ten gevolge van een arbeidsongeval, zoals gedefinieerd in artikelen 8.2. en 9. Verzekeringsjaar Het jaar dat aanvangt op 1 januari en eindigt op 31 december daaropvolgend. Wet betreffende de aanvullende pensioenen of WAP De wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid.Art. 2. Voorwerp De inrichter sluit onderhavig pensioenreglement af met het oog op het financieren van een sectoraal pensioenstelsel ten gunste van de werknemers die ressorteren onder de collectieve arbeidsovereenkomst van 23 december 2008 gesloten in het Paritair Comité van de zeevisserij (PC 143), die de collectieve arbeidsovereenkomst van 19 januari 2006 gesloten in het Paritair Comité van de zeevisserij (PC 143) houdende de invoering van een sectoraal pensioenstelsel ten behoeve van de erkende zeevissers wijzigt en vervangt, alsook de latere wijzigingen van deze collectieve arbeidsovereenkomsten. De pensioentoezegging betreft een pensioentoezegging van het type vaste bijdragen zonder gewaarborgd rendement lastens de inrichter, onverminderd de toepassing van de minimumgarantie overeenkomstig de wetgeving en reglementering van toepassing op de aanvullende pensioenen. Het doel van het sectoraal pensioenstelsel is het garanderen, buiten de wettelijke verplichtingen inzake pensioenen en ter verhoging ervan: - aan de aangeslotene, van een kapitaal of een levenslange lijfrente op het ogenblik van zijn pensionering; - aan de begunstigde, bij overlijden van de aangeslotene vóór zijn pensionering, van een kapitaal of een levenslange rente op basis van de verworven reserves op het ogenblik van het overlijden. In geval van arbeidsongeval wordt voorzien in volgende forfaitaire dekkingen: - Ten voordele van de begunstigde, een kapitaal bedoeld in artikel 8.2. in geval van overlijden van de aangeslotene ten gevolge van een arbeidsongeval; - ten voordele van de aangeslotene, een kapitaal in geval van permanente arbeidsongeschiktheid van meer dan 66 pct. ten gevolge van een arbeidsongeval bedoeld in artikel 9. Het pensioenreglement en zijn bijlagen vormen een pensioenstelsel dat het voorwerp uitmaakt van een verklaring aan de gegevensbank inzake "tweede pijler". Art. 3. Aansluiting 1. Alle erkende zeevissers worden verplicht aangesloten bij de pensioentoezegging en de waarborgen permanente arbeidsongeschiktheid en overlijden ten gevolge van arbeidsongeval vanaf de eerste dag van de maand volgend op of samenvallend met de maand waarin de werknemer zijn erkenning als zeevisser heeft verkregen. 2. De aansluiting bij de onderhavige pensioentoezegging en de waarborgen permanente arbeidsongeschiktheid en overlijden ten gevolge arbeidsongeval geschiedt echter ten vroegste op de datum van inwerkingtreding zonder afbreuk te doen aan de reeds in toepassing van collectieve arbeidsovereenkomst van 19 januari 2006 gesloten in het Paritair Comité van de zeevisserij (PC 143) houdende de invoering van een sectoraal pensioenstelsel ten behoeve van de erkende zeevissers bestaande aansluitingen aan huidige sectoraal pensioenstelsel. 3. De aansluiting bij de waarborg leven bedoeld in artikel 7 en de waarborg overlijden bedoeld in artikel 8.1. eindigt: a. bij pensionering van de aangeslotene; b. bij overlijden van de aangeslotene vóór de pensionering. De aansluiting bij de waarborg overlijden ten gevolge van een arbeidsongeval bedoeld in artikel 8.2. en de waarborg permanente arbeidsongeschiktheid bedoeld in artikel 9 eindigt: a. op de eerste dag van de maand volgend op of samenvallend met de maand waarin de erkenning als zeevisser wordt ingetrokken; b. op de pensioenleeftijd of, in geval van verdaging, de leeftijd bedoeld in artikel 6.2.; c. bij overlijden van de aangeslotene vóór de leeftijd bedoeld in b. 4. De aangeslotene blijft pensioenrechten opbouwen zolang hij in dienst is van een reder vallende onder het toepassingsgebied van het sectoraal pensioenstelsel van de inrichter. 5. De erkende zeevissers die op het ogenblik van hun indiensttreding gepensioneerd zijn, worden niet aangesloten bij de pensioentoezegging, met uitzondering van de gepensioneerden die op 1 januari 2016 reeds aangesloten waren.Art. 4. Bijdragen 1. De waarborgen leven, overlijden en permanente arbeidsongeschiktheid ten gevolge van een arbeidsongeval zoals ze worden gedefinieerd in artikelen 7, 8 en 9, worden voor elke aangeslotene gefinancierd door een brutobijdrage. De bijdragen voor de waarborg leven die eveneens de waarborg overlijden bedoeld in artikel 8.1. omvat, worden door de inrichter gestort in het financieringsfonds ingericht bij de pensioeninstelling. De pensioeninstelling put uit dit financieringsfonds de bijdragen voor de waarborg leven, die eveneens de waarborg overlijden bedoeld in artikel 8.1. omvat, om deze op de individuele rekening van de aangeslotene te storten. De bijdragen voor de waarborg overlijden ten gevolge van een arbeidsongeval bedoeld in artikel 8.2. en de waarborg permanente arbeidsongeschiktheid ten gevolge van een arbeidsongeval bedoeld in artikel 9 worden aan de verzekeringsinstelling betaald. 2. De jaarlijkse bijdrage voor de waarborg leven die eveneens de waarborg overlijden bedoeld in artikel 8.1. omvat, wordt vastgesteld op 600 EUR vanaf 1 januari 2017 (425 EUR vanaf 1 januari 2009) per 200 gepresteerde RSZ-dagen per verzekeringsjaar tewerkstelling als erkend zeevisser. Als er minder dan 200 gepresteerde RSZ-dagen als erkend zeevisser kunnen worden bewezen per verzekeringsjaar, wordt de jaarlijkse bijdrage pro rata berekend rekening houdend met de werkelijk gepresteerde RSZ-dagen. Deze jaarlijkse bijdrage is te vermeerderen met de verschuldigde premietaksen en kosten. Voor de berekening van de eindbijdrage: Voor de actieve erkende zeevissers, zal de berekening van de pensioenbijdrage voor het kwartaal van pensionering of overlijden en de 2 daaraan voorafgaande kwartalen die nog niet berekend zijn, gebeuren op basis van de laatste jaarpremie gekend op het ogenblik van pensionering of overlijden. Onder "actieve vissers" wordt verstaan: de vissers die in de 2 kwartalen voorafgaand aan het pensioen of overlijden hebben gevaren. De bijdrage voor de te berekenen kwartalen voorafgaand aan het kwartaal van pensionering of overlijden zal voor elk van deze kwartalen gelijk zijn aan de laatst gekende jaarpremie/4. De bijdrage voor het kwartaal van pensionering of overlijden zal gelijk zijn aan X/12 van de laatst gekende jaarpremie, waarbij X overeenstemt met het aantal begonnen maanden in het kwartaal van pensionering of overlijden. De jaarlijkse bijdrage overeenkomstig de collectieve arbeidsovereenkomst van 24 oktober 2024 gesloten in het Paritair Comité van de zeevisserij (PC 143) tot invulling van de loonnorm wordt vanaf 1 januari 2025 een bijkomende premie aanvullend pensioen gestort voor elke aangeslotene die in het voorafgaande kalenderjaar heeft gevaren en die als volgt wordt berekend: loonmassa voorgaand kalenderjaar x 1,1 pct. Voor de berekening van de eindpremie bij pensionering of overlijden: Voor de actieve erkende zeevissers, zal de berekening van de pensioenbijdrage voor het jaar van pensionering of overlijden en het voorafgaande jaar, gebeuren op basis van de laatst betaalde premie. Onder "actieve vissers" wordt verstaan: de vissers die in het jaar van pensionering of overlijden en/of het voorafgaande jaar hebben gevaren. De bijdrage voor het jaar van pensionering of overlijden zal gelijk zijn aan X/12 van de laatst betaalde premie, waarbij X overeenstemt met het aantal begonnen maanden in het jaar van pensionering of overlijden. De bijdrage voor het jaar voorafgaand aan het jaar van pensionering of overlijden zal gelijk zijn aan de laatst betaalde premie. De berekening is definitief en kan dus niet worden herzien in functie van gegevens die later alsnog beschikbaar zouden worden. De jaarlijkse bijdrage voor de waarborg overlijden ten gevolge van een arbeidsongeval bedoeld in artikel 8.2. en de waarborg permanente arbeidsongeschiktheid ten gevolge van arbeidsongeval bedoeld in artikel 9 wordt vastgesteld op 75,00 EUR per erkende zeevisser per verzekeringsjaar. Deze jaarlijkse bijdrage is te vermeerderen met de verschuldigde premietaksen en kosten.3. De bijdrage voor de waarborg leven wordt bij de aanvang van ieder verzekeringsjaar geïndexeerd op basis van de evolutie van de gezondheidsindex met als basis het laatst gekende indexcijfer op 1 januari 2006. De bijdrage voor de waarborg overlijden ten gevolge van een arbeidsongeval en de waarborg permanente arbeidsongeschiktheid ten gevolge van een arbeidsongeval wordt jaarlijks aangepast op 1 januari volgens dezelfde evolutie als het wettelijk maximum zoals bepaald door de wetgeving inzake arbeidsongevallen met als basis het laatst gekende indexcijfer op 1 januari 2006. 4. De bijdragen verschuldigd voor de waarborg overlijden ten gevolge van een arbeidsongeval en de waarborg permanente arbeidsongeschiktheid ten gevolge van een arbeidsongeval worden bij de aanvang van ieder verzekeringsjaar door de inrichter aan de verzekeringsinstelling betaald. 5. De bijdrage voor de waarborg leven, die eveneens de waarborg overlijden bedoeld in artikel 8.1. omvat, wordt trimestrieel berekend en betaald op basis van het aantal gepresteerde RSZ-dagen van de aangeslotene in het afgelopen trimester. Deze bijdrage voor de waarborg leven wordt door de inrichter berekend en meegedeeld aan de pensioeninstelling. 6. De pensioeninstelling en de verzekeringsinstelling dekken de aangeslotene op basis van de gegevens, zoals die door de inrichter worden overgemaakt en waarbij de inrichter instaat voor de nauwkeurigheid van de inlichtingen. 7. De bijdragen zijn verschuldigd vanaf het ogenblik van aansluiting van de erkende zeevisser. 8. De inrichter neemt de bijdragen en daarop verschuldigde taksen, socialezekerheidsbijdragen en andere kosten ten hare laste. 9. COVID-19-pandemie: De aangeslotenen bleven en blijven gedurende de gehele periode van opschorting van hun arbeidsovereenkomst omwille van tijdelijke werkloosheid wegens overmacht of wegens economische redenen in het kader van de crisis van het coronavirus COVID-19 genieten van de pensioenopbouw. De premies die verschuldigd waren voor deze periode worden berekend overeenkomstig het pensioenreglement alsof de arbeidsovereenkomst niet werd opgeschort. De betrokken aangeslotenen werden ingelicht over het behoud van de pensioenopbouw. 10. Tijdelijke werkloosheid energie: De aangeslotenen blijven gedurende de gehele periode van opschorting van hun arbeidsovereenkomst omwille van tijdelijke werkloosheid wegens overmacht of wegens economische redenen in het kader van de energiecrisis genieten van de pensioenopbouw. De premies die verschuldigd zijn voor deze periode worden berekend overeenkomstig het pensioenreglement alsof de arbeidsovereenkomst niet werd opgeschort. De betrokken aangeslotenen worden ingelicht over het behoud van de pensioenopbouw. Art. 5. Verzekeringstechniek 1. De bijdrage voor de waarborg leven die de waarborg overlijden bedoeld in artikel 8.1. omvat, wordt aangewend als een koopsom op de individuele rekening van elk der aangeslotenen. 2. De verzekeringstechniek die aangewend wordt om de waarborg leven te financieren is deze van "Uitgesteld Kapitaal Met Terugbetaling van de Reserve bij vroegtijdig overlijden" (U.K.M.T.R.). 3. De pensioeninstelling gaat een resultaatsverbintenis aan voor de kapitalisatie van de gestorte bijdragen voor de waarborg leven op basis van het tarief neergelegd bij de bevoegde toezichthouder en volgens de eventuele bijkomende modaliteiten voorzien in het pensioenreglement. Art. 6. Verdaging van de pensioenleeftijd Zolang de aangeslotene als erkend zeevisser tewerkgesteld blijft bij een reder na de pensioenleeftijd wordt de pensioenleeftijd verdaagd als volgt: 1. Voor de waarborg leven, met inbegrip van de waarborg overlijden bedoeld in artikel 8.1.: de aanwezige reserve op 60 jaar wordt aangewend als koopsom voor een verzekeringstechniek met als einddatum de eerste van de maand volgend op de eerstvolgende verjaardag van de aangeslotene. Deze verzekeringstechniek gebeurt in het tarief "Uitgesteld Kapitaal Met Terugbetaling van de Reserve bij vroegtijdig overlijden" (U.K.M.T.R.) zoals omschreven in artikel 5.2. van onderhavig pensioenreglement, en wordt ieder jaar herhaald met als nieuwe einddatum telkens één jaar later; 2. De waarborgen overlijden ten gevolge van een arbeidsongeval en permanente arbeidsongeschiktheid ten gevolge van arbeidsongeval, zoals beschreven in artikelen 8.2. en 9, worden behouden tot uiterlijk de eerste van de maand volgend op de 70ste verjaardag van de aangeslotene.Art. 7. Waarborg leven 1. Onverminderd de bepalingen in verband met de minimumgarantie voorzien door de wetgeving en reglementering van toepassing op de aanvullende pensioenen, waarborgt de inrichter geen rendement. 2. Het rendement met betrekking tot de waarborg leven is gelijk aan de som van de intrestvoet gewaarborgd door de pensioeninstelling en van de eventuele winstdeelname toegekend door de pensioeninstelling aan de individuele rekeningen. 3. De aangeslotene heeft onmiddellijk aanspraak op zijn verworven reserves. 4. De verworven reserves zijn minimaal gelijk aan de reserves die krachtens de WAP en haar uitvoeringsbesluiten moeten worden opgebouwd. 5. Zolang de aangeslotene tewerkgesteld is als erkend zeevisser kan hij geen uitbetaling van de verworven reserves krijgen. 6. Afkoop der verworven reserves vóór de pensionering, voorschotten op de contracten en inpandgevingen zijn niet toegelaten, zonder evenwel afbreuk te doen aan artikel 13.1., a., b. en c. 7. De aangeslotene heeft bij zijn uittreding, bij pensionering, of bij opheffing van de pensioentoezegging minstens recht op de verworven reserves desgevallend aangevuld tot de bedragen gewaarborgd in toepassing van artikel 24 van de WAP. 8. Indien bij de overdracht van de verworven reserves bij uittreding, op het ogenblik van de pensionering of de opheffing van de pensioentoezegging, het bedrag van de verworven reserves lager zou zijn dan het bedrag van de minimum garantie overeenkomstig de wetgeving en reglementering van toepassing op de aanvullende pensioenen, wordt het bedrag dat nodig is om het tekort aan te zuiveren uit het financieringsfonds geput. Indien de middelen van het financieringsfonds ontoereikend zouden zijn om het tekort aan te zuiveren, stort de inrichter aan de pensioeninstelling een bijkomende eenmalige bijdrage om het tekort aan te zuiveren. 9. De individuele rekening wordt gesloten wanneer een aangeslotene overlijdt, wanneer hij bij uittreding kiest om zijn verworven reserves te transfereren conform artikel 13.1., a. en b. of bij zijn pensionering. 10. De prestatie van de waarborg leven wordt vereffend op het ogenblik van pensionering van de aangeslotene. Zij wordt berekend op de datum van pensionering en wordt uitbetaald binnen de 30 dagen die volgen op de mededeling door de aangeslotene aan de pensioeninstelling van de gegevens die voor de uitbetaling noodzakelijk zijn. Art. 8. Waarborg overlijden 1. In geval van overlijden van de aangeslotene vóór de pensionering worden de verworven reserves uitgekeerd aan de begunstigde(n) bedoeld in artikel 8.3. 2. In geval van overlijden van de aangeslotene ten gevolge van een arbeidsongeval vóór de pensioenleeftijd, of desgevallend vóór de verdaagde pensioenleeftijd, wordt een bijkomend kapitaal overlijden voorzien ten behoeve van de begunstigde(n) bedoeld in artikel 8.3. Dit kapitaal overlijden is gelijk aan: 25 000 EUR. Dit kapitaal overlijden wordt jaarlijks aangepast op 1 januari aan de evolutie van de index overeenkomstig artikel 39 van de arbeidsongevallenwet van 10 april 1971 met als basis het gekende indexcijfer op 1 januari 2006. 3. In geval van overlijden van de aangeslotene vanaf 5 maart 2014 zijn de begunstigden bij voorrang: a. De echtgeno(o)t(e) van de aangeslotene, behalve indien hij uit de echt of gerechtelijk van tafel en bed gescheiden is, of de wettelijk samenwonende partner van de aangeslotene, behalve indien aan de wettelijke samenwoning een einde is gemaakt volgens de wettelijke procedure. Onder "wettelijke samenwoning" wordt verstaan: de toestand van samenleven van twee personen die een verklaring van wettelijke samenwoning hebben afgelegd door middel van een geschrift dat tegen ontvangstbewijs werd overhandigd aan de ambtenaar van de burgerlijke stand van de gemeenschappelijke woonplaats; b. De ontstentenis, de kinderen van de aangeslotene, in gelijke delen. Indien één van de kinderen van de aangeslotene voor overleden is, komt het aandeel van dit kind, in gelijke delen, toe aan zijn kinderen; bij ontstentenis, in gelijke delen aan de andere kinderen van de aangeslotene; c. Bij ontstentenis, iedere persoon aangewezen in een door de aangeslotene ondertekend document; d. Bij ontstentenis, de vader en moeder van de aangeslotene;e. Bij ontstentenis, de broers en zusters van de aangeslotene. De halfbroers of halfzusters worden in deze rang slechts in aanmerking genomen indien ze nominatief aangeduid zijn in een document ondertekend door de aangeslotene. Onder "halfbroers" of "halfzusters" wordt verstaan: de broers of zusters die één gemeenschappelijke ouder hebben met de aangeslotene; f. Bij ontstentenis, de nalatenschap met uitsluiting van de Staat; g. Bij ontstentenis, het financieringsfonds. De aangeslotene kan hiervan altijd afwijken om de bovengenoemde rangorde te wijzigen en/of zelf een begunstigde aan te duiden. Deze afwijking wordt vermeld in een door de aangeslotene ondertekende gedateerde verklaring gericht aan de inrichter waarbij de laatste verklaring doorslaggevend zal zijn. 4. Indien er meerdere begunstigden zijn, wordt de waarborg overlijden in gelijke delen onder hen verdeeld. 5. De uitkeringen worden rechtstreeks aan de begunstigde(n) gedaan. De inrichter behoudt zich het recht voor bij de uitkeringen een levensbewijs te vragen van de begunstigde(n) of ieder bijkomend document om de identiteit van de begunstigde(n) te verifiëren. 6. De belastingen, voorheffingen, rechten, taksen of belastingen op kapitalen, afkoopwaarden en renten zijn ten laste van de begunstigde(n). Art. 9. Waarborg arbeidsongeschiktheid 1. In geval van een permanente arbeidsongeschiktheid van meer dan 66 pct. van de aangeslotene ten gevolge van een arbeidsongeval wordt een kapitaal arbeidsongeschiktheid voorzien ten behoeve van de aangeslotene. Dit kapitaal arbeidsongeschiktheid is gelijk aan: 25 000 EUR. Dit kapitaal arbeidsongeschiktheid wordt jaarlijks aangepast op 1 januari aan de evolutie van de index overeenkomstig artikel 39 van de arbeidsongevallenwet van 10 april 1971 met als basis het laatst gekende indexcijfer op 1 januari 2006. 2. De belastingen, voorheffingen, rechten, taksen of belastingen op kapitalen, afkoopwaarden en renten zijn ten laste van de aangeslotene. Art. 10. Transparantie 1. De inrichter overhandigt op eenvoudig verzoek van de aangeslotene de tekst van dit voorliggend reglement en alle latere wijzigingen hiervan. 2. De pensioeninstelling zal jaarlijks een verslag over het beheer van de pensioentoezegging opstellen en ter beschikking stellen van de inrichter. Op eenvoudig verzoek van de aangeslotene, deelt de inrichter dit verslag mee aan de aangeslotene. Het verslag wordt opgesteld volgens de modaliteiten bepaald in artikel 42 van de WAP. 3. De pensioeninstelling stelt een schriftelijke verklaring op met de principes van haar beleggingsbeleid. Deze verklaring wordt ter beschikking gesteld van de inrichter die ze op eenvoudig verzoek aan de aangeslotene bezorgt. De verklaring wordt ten minste om de drie jaar herzien en onmiddellijk na elke belangrijke wijziging van het beleggingsbeleid. 4. De pensioeninstelling zal jaarlijks aan alle aangeslotenen die niet zijn uitgetreden een pensioenfiche bezorgen, met gedetailleerde gegevens over de verworven reserves van de aangeslotene. De pensioenfiche wordt opgesteld volgens de modaliteiten bepaald in artikel 26 van de WAP. 5. De inrichter overhandigt op eenvoudig verzoek van de aangeslotene een historisch overzicht van de verworven reserves volgens de modaliteiten bepaald in artikel 26, § 2 van de WAP. 6. De inrichter informeert de aangeslotene aangaande het recht tot omvorming van het kapitaal leven in rente, en dit twee maanden vóór de pensionering op de wettelijke pensioenleeftijd of, in geval van vervroegde pensionering, binnen de 2 weken nadat hij van de vervroegde pensionering in kennis werd gesteld. In geval van overlijden van de aangeslotene, zal de inrichter de begunstigde(n) van de aangeslotene informeren over dit recht op omzetting met betrekking tot de waarborg overlijden bedoeld in artikel 8.1., en dit binnen de twee weken nadat de inrichter op de hoogte werd gebracht van het overlijden van de aangeslotene.Art. 11. Voorwaarden tot fiscale aftrek Overeenkomstig de beschikkingen van het Wetboek der Inkomstenbelastingen, zijn de aftrek van de werkgeversbijdragen voor de waarborg leven slechts toegestaan in de mate waarin de toekenningen naar aanleiding van pensionering, zowel de wettelijke als de extra-wettelijke, uitgedrukt in jaarlijkse renten, met uitzondering van de toekenningen uit hoofde van persoonlijk onderschreven individuele levensverzekeringen, niet meer bedragen dan 80 pct. van de laatste normale brutojaarbezoldiging. Hierbij wordt rekening gehouden met de normale duur van de beroepswerkzaamheid, de overdraagbaarheid ten gunste van de overlevende echtgeno(o)t(e) of we wettelijk samenwonende partner (met een maximum van 80 pct.) en de voorziene indexatie van de rente (met een maximum van 2 pct.). Art. 12. Vereffening 1. Bij vereffening kan de aangeslotene met betrekking tot de waarborg leven of de begunstigde(n) met betrekking tot de waarborg overlijden bedoeld in artikel 8.1. kiezen tussen hetzij de eenmalige uitbetaling in kapitaal, hetzij een omzetting in een levenslange rente. 2. Naar keuze van de aangeslotene of de begunstigde(n) kan het gaan om een lijfrente die enkel aan hem betaald wordt of om een lijfrente die in geval van later overlijden van de begunstigde voor maximaal 80 pct. overdraagbaar is op de overlevende echtgeno(o)t(e) of wettelijke samenwonende partner van de begunstigde. De begunstigde kan kiezen voor een jaarlijkse vaste indexatie van de lijfrente met ten hoogste 2 pct. 3. De berekening van de omzetting van kapitaal in rente zal gebeuren in overeenstemming met artikel 19, § 1 van het koninklijk besluit van 14 november 2003 tot uitvoering van de WAP. 4. Wanneer het jaarlijks bedrag van de rente bij de aanvang ervan lager is dan of gelijk aan 500 EUR, wordt de prestatie in de vorm van een kapitaal uitbetaald. Het minimumbedrag van 500 EUR wordt geïndexeerd volgens de bepalingen van de wetgeving en reglementering van toepassing op de aanvullende pensioenen (spilindex basis 1996: op 1 januari 2004 = 111,64; op 1 januari 2007 = 118,47). Art. 13. Uittreding 1. Onverminderd artikel 13.2. beschikt de aangeslotene bij uittreding over de volgende keuzemogelijkheden met betrekking tot de bestemming van zijn verworven reserves: a. De verworven reserves overdragen naar de pensioeninstelling van ofwel de nieuwe werkgever met wie hij een arbeidsovereenkomst heeft gesloten, indien hij wordt aangesloten bij de pensioentoezegging van die werkgever, ofwel de nieuwe rechtspersoon - paritair samengesteld - waaronder de werkgever ressorteert met wie hij een arbeidsovereenkomst heeft gesloten, indien hij wordt aangesloten bij de pensioentoezegging van die rechtspersoon; b. De verworven reserves overdragen naar een pensioen</t>
         </is>
       </c>
     </row>
@@ -1035,28 +1032,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025003466</t>
+          <t>2025200930</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>08 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 8 mei 2007 houdende omzetting van Richtlijn 2006/22/EG van het Europees Parlement en de Raad van 15 maart 2006 inzake minimumvoorwaarden voor de uitvoering van de Verordeningen (EEG) nr. 3820/85 en (EEG) nr. 3821/85 van de Raad betreffende voorschriften van sociale aard voor het wegvervoer en tot intrekking van Richtlijn 88/599/EEG van de Raad</t>
+          <t>13 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 20 november 2024, gesloten in het Paritair Comité voor het tuinbouwbedrijf, tot vaststelling van de werkgeversbijdrage aan het "Sociaal Fonds voor de inplanting en het onderhoud van parken en tuinen" (1)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-08&amp;numac_search=2025003466&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003466=18&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025200930&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200930=18&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 18 februari 1969 betreffende de maatregelen ter uitvoering van de internationale verdragen en akten inzake vervoer over zee, over de weg, de spoorweg of de waterweg, artikel 1;Gelet op het koninklijk besluit van 8 mei 2007 houdende omzetting van Richtlijn 2006/22/EG van het Europees Parlement en de Raad van 15 maart 2006 inzake minimumvoorwaarden voor de uitvoering van de Verordeningen (EEG) nr. 3820/85 en (EEG) nr. 3821/85 van de Raad betreffende voorschriften van sociale aard voor het wegvervoer en tot intrekking van Richtlijn 88/599/EEG van de Raad;Gelet op de betrokkenheid van de Gewestregeringen;Overwegende dat de bijlage III van de Richtlijn 2006/22/EG werd aangepast door de gedelegeerde Richtlijn (EU) 2024/846 van de Commissie van 14 maart 2024 en het daarom noodzakelijk is om in het omzettingsbesluit van de Richtlijn 2006/22/EG een formele verwijzing (koppelingsclausule) naar die gedelegeerde Richtlijn op te nemen,Op de voordracht van de Minister van Mobiliteit,Hebben Wij besloten en besluiten Wij :Artikel 1. Artikel 1 van het koninklijk besluit van 8 mei 2007 houdende omzetting van Richtlijn 2006/22/EG van het Europees Parlement en de Raad van 15 maart 2006 inzake minimumvoorwaarden voor de uitvoering van de Verordeningen (EEG) nr. 3820/85 en (EEG) nr. 3821/85 van de Raad betreffende voorschriften van sociale aard voor het wegvervoer en tot intrekking van Richtlijn 88/599/EEG van de Raad, gewijzigd bij het koninklijk besluit van 3 november 2024, wordt vervangen als volgt:"Dit besluit voorziet in de gedeeltelijke omzetting van:1°  de Richtlijn 2006/22/EG van het Europees Parlement en de Raad van 15 maart 2006 inzake minimumvoorwaarden voor de uitvoering van de Verordeningen (EG) nr. 561/2006 en (EU) nr. 165/2014 en van Richtlijn 2002/15/EG betreffende voorschriften van sociale aard voor het wegvervoer en tot intrekking van Richtlijn 88/599/EEG van de Raad;2°  de Richtlijn (EU) 2020/1057 van het Europees Parlement en de Raad van 15 juli 2020 tot vaststelling van specifieke regels met betrekking tot Richtlijn 96/71/EG en Richtlijn 2014/67/EU wat betreft de detachering van bestuurders in de wegvervoersector en tot wijziging van Richtlijn 2006/22/EG wat betreft de handhavingsvoorschriften en Verordening (EU) nr. 1024/2012;3°  de gedelegeerde Richtlijn (EU) 2024/846 van de Commissie van 14 maart 2024 tot wijziging van Richtlijn 2006/22/EG van het Europees Parlement en de Raad inzake minimumvoorwaarden voor de uitvoering van de Verordeningen (EG) nr. 561/2006 en (EU) nr. 165/2014 en van Richtlijn 2002/15/EG betreffende voorschriften van sociale aard voor het wegvervoer.".Art. 2.  De minister bevoegd voor het wegvervoer is belast met de uitvoering van dit besluit.Gegeven te Brussel op 27 april 2025.FILIPVan Koningswege :De Minister van Mobiliteit,Klimaat en Ecologische Transitie,J.-L. CRUCKE 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het tuinbouwbedrijf; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 20 november 2024, gesloten in het Paritair Comité voor het tuinbouwbedrijf, tot vaststelling van de werkgeversbijdrage aan het "Sociaal Fonds voor de inplanting en het onderhoud van parken en tuinen". Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het tuinbouwbedrijf Collectieve arbeidsovereenkomst van 20 november 2024 Vaststelling van de werkgeversbijdrage aan het "Sociaal Fonds voor de inplanting en het onderhoud van parken en tuinen" (Overeenkomst geregistreerd op 20 december 2024 onder het nummer 191193/CO/145) HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op hun arbeiders en bedienden zonder onderscheid naar gender, hierna "werknemers" genoemd, van de ondernemingen die onder het Paritair Comité voor het tuinbouwbedrijf ressorteren en waarvan de hoofdactiviteit bestaat uit het aanleggen en onderhouden van parken en tuinen. Onder "arbeiders en bedienden" worden ook de flexi-jobbers verstaan. HOOFDSTUK II. - Werkgeversbijdragen Art. 2.  § 1. In toepassing van artikel 9 van de collectieve arbeidsovereenkomst van 23 juni 1976, gesloten in het Paritair Comité voor het tuinbouwbedrijf, tot oprichting van een fonds voor bestaanszekerheid, algemeen verbindend verklaard bij koninklijk besluit van 7 oktober 1976 (Belgisch Staatsblad van 22 oktober 1976), wordt de werkgeversbijdrage aan het" Sociaal Fonds voor de inplanting en het onderhoud van parken en tuinen" vanaf 1 januari 2023 : - voor de arbeiders vastgesteld op 11,40 pct. van de loonmassa, met inbegrip van de 0,10 pct. voor de risicogroepen, de 0,20 pct. voor de conventionele inspanning en de 9,15 pct. voor de eindejaarspremie; - voor de bedienden vastgesteld op 1,95 pct. van de loonmassa, met inbegrip van de 0,10 pct. voor de risicogroepen en de 0,20 pct. voor de conventionele inspanning.  § 2. In toepassing van artikel 11 van dezelfde collectieve arbeidsovereenkomst, wordt de bij artikel 2, § 1 vastgestelde werkgeversbijdrage geïnd en ingevorderd door de Rijksdienst voor Sociale Zekerheid. HOOFDSTUK III. - Geldigheid Art. 3. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van 1 januari 2025 en is gesloten voor een onbepaalde duur. Zij vervangt de collectieve arbeidsovereenkomst van 19 januari 2023 betreffende de vaststelling van de werkgeversbijdrage aan het "Sociaal Fonds voor de inplanting en het onderhoud van parken en tuinen", geregistreerd onder het nr. 178077/CO/145. Zij kan door elk van de ondertekenende partijen worden opgezegd met een opzegging van ten minste drie maanden, betekend bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Comité voor het tuinbouwbedrijf. Gezien om te worden gevoegd bij het koninklijk besluit van 13 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -1067,28 +1064,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025002520</t>
+          <t>2025200932</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>09 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 10 november 2023, gesloten in het Paritair Comité voor het glasbedrijf, betreffende de arbeids- en verloningsvoorwaarden en andere arbeidsmodaliteiten in de aanvullende subsector van de glasindustrie in 2023 en 2024 (1)</t>
+          <t>13 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 9 december 2024, gesloten in het Paritair Comité voor de bedienden der metaalfabrikatennijverheid, betreffende de gewaarborgde minimum maandwedde vanaf 1 januari 2025 (1)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-09&amp;numac_search=2025002520&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025002520=19&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025200932&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200932=19&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor het glasbedrijf;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 10 november 2023, gesloten in het Paritair Comité voor het glasbedrijf, betreffende de arbeids- en verloningsvoorwaarden en andere arbeidsmodaliteiten in de aanvullende subsector van de glasindustrie in 2023 en 2024.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het glasbedrijfCollectieve arbeidsovereenkomst van 10 november 2023Arbeids- en verloningsvoorwaarden en andere arbeidsmodaliteiten in de aanvullende subsector van de glasindustrie in 2023 en 2024 (Overeenkomst geregistreerd op 30 november 2023 onder het nummer 184282/CO/115)VoorwoordDe sociale partners zijn van oordeel dat het opportuun is de arbeidsvoorwaarden en de basisverloning te bepalen voor de arbeiders van de aanvullende subsector van de glasindustrie die niet gedekt zijn door een collectieve ondernemingsovereenkomst.Het gaat over een suppletief systeem, van toepassing bij afwezigheid van conventionele bepalingen overeengekomen op bedrijfsniveau.TITEL I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de werklieden van de ondernemingen van volgende bedrijfssectoren, het door hen verrichte monteren en plaatsen inbegrepen :1°  glas voor industriële of huishoudelijke toepassingen (zoals pannen, kranen, tegels, stelen in glas en vitro ceramische platen);2°  buizen, staven en staafjes in glas (namelijk voor de chemische, farmaceutische en elektrotechnische nijverheden);3°  verlichting en seininrichting (zoals glasballons en elektrische buizen, lichtreclames);4°  glasvezels, glaswol en cellulair glas;5°  voorwerpen in glas voor elk technisch, wetenschappelijk en industrieel gebruik (zoals leidingen, microkogels en -parels);6°  verwerkt en/of bewerkt holglas, zoals glasballons, flacons, kolven en laboratoriumtoestellen (laboratoriumglas), isolerende flessen;7°  ver- en bewerking van borosilicaat en ceramisch vlakglas, glasblazen (voor wetenschappelijke en industriële apparaten);8°  optiekglas, alsmede het slijpen en het versieren van deze glazen (glazen voor brillenfabricage).Deze ondernemingen behoren tot de aanvullende bedrijfssector glas voor zover één van de voormelde activiteiten in hoofdzaak wordt uitgeoefend en niet als bijkomstige activiteit van een andere sector van de glasindustrie.Onder "arbeiders" verstaat men : zowel arbeiders als arbeidsters.TITEL II. - OnderhandelingskaderArt. 2. De ondertekenende partijen en hun leden zijn akkoord om volgend punt na te leven gedurende eventuele onderhandelingen voor de periode 2023-2024 : er zullen geen eisen ingediend of besproken worden in de sector, de subsectoren en de ondernemingen uit de glasindustrie die in tegenspraak of conflict zijn met het wettelijk kader voorzien door de wet van 26 juli 1996 tot de bevordering van de werkgelegenheid en tot preventieve vrijwaring van het concurrentievermogen gewijzigd door de wet van 19 maart 2017 en door het koninklijk besluit van 13 mei 2023 tot uitvoering van artikel 7, § 1 van de wet van 26 juli 1996 tot bevordering van de werkgelegenheid en tot preventieve vrijwaring van het concurrentievermogen (Belgisch Staatsblad van 26 mei 2023) tot vaststelling van de maximale marge voor loonkostontwikkeling voor de periode 2023-2024 en het koninklijk besluit van 23 april 2023 betreffende de koopkrachtpremie (Belgisch Staatsblad van 28 april 2023).TITEL III. - ArbeidsvoorwaardenHOOFDSTUK I. - Wekelijkse arbeidsduur en anciënniteitsverlofArt. 3. De conventionele wekelijkse arbeidsduur bedraagt maximum 37 uur en 50 minuten volgens de toepassingsmodaliteiten die paritair op ondernemingsvlak en rekening houdend met de imperatieven van de arbeidsorganisatie en de productie en met het oog op het behoud van de werkgelegenheid, werden afgesproken.Bovendien, gebeurt de overgang van 38 uur naar 37 uur en 50 minuten in de vorm van een betaalde dag inhaalrust.Art. 4. Na 25 jaar dienst in de onderneming wordt er aan de arbeiders een eerste verlofdag toegekend. Vanaf 1 januari 2024 wordt de anciënniteit van 25 jaar die in het bedrijf moet worden behaald, vervangen door een anciënniteit die in de sector moet worden verworven.De arbeider moet een bewijs van anciënniteit in de sector bij zich dragen.De dag wordt toegekend zodra de anciënniteit is bereikt.De verlofdag wordt vastgesteld in overleg met de werkgever, rekening houdend met de arbeidsorganisatie.Deze verlofdag is niet cumuleerbaar met een anciënniteitsdag toegekend door een vóór 31 maart 2006 afgesloten collectieve arbeidsovereenkomst op ondernemingsvlak.Deze verlofdag geldt niet wanneer op 31 maart 2006 gelijkaardige of voordeligere voorwaarden van kracht zijn in de vorm van een dag- en/of anciënniteitspremie via een ondernemings-collectieve arbeidsovereenkomst. In dit geval, blijven enkel de voorwaarden voorzien in de ondernemings-collectieve arbeidsovereenkomst van toepassing.HOOFDSTUK II. - FunctieclassificatieArt. 5. Behalve bijzondere bepalingen gesloten op het vlak van de onderneming, worden de functies van de in artikel 1 bedoelde arbeiders ingedeeld in zeven categorieën volgens de hierna vermelde algemene criteria :Categorie 1 :Functie die geen enkele beroepsopleiding vergt of waarvoor enkel een opleiding van zeer korte duur noodzakelijk is om de eenvoudige taken waaruit zij in hoofdzaak bestaat te kunnen uitvoeren.Categorie 2 :Functie die geen enkele beroepsopleiding vergt, maar waarvoor een in de onderneming verstrekte bijzondere opleiding noodzakelijk is.Categorie 3 :Functie die geen enkele beroepsopleiding vergt, enkel maar een opleiding van enkele dagen in de onderneming.Categorie 4 :Functie die een beroepsopleiding van langere duur vergt (van drie tot zes maanden).Categorie 5 :Veelzijdige functie betreffende meerdere uiteenlopende taken in eenzelfde afdeling of in verschillende afdelingen.Categorie 6A en 6B :Geschoolde arbeiders.HOOFDSTUK III. - LoonvoorwaardenArt. 6. De koopkrachtpremieDe sociale partners hebben de mogelijkheid om op ondernemingsvlak een akkoord te onderhandelen over de koopkrachtpremie tot 15 december 2023, dat in overeenstemming is met het koninklijk besluit van 23 april 2023 betreffende de koopkrachtpremie. Als uiterlijk op 15 december 2023 geen akkoord wordt bereikt op ondernemingsniveau, zal een koopkrachtpremie worden toegekend aan de arbeiders door bedrijven die een hoge of uitzonderlijk hoge winst hebben gerealiseerd in 2022."Winst in 2022" wordt voor de toepassing van deze collectieve arbeidsovereenkomst gedefinieerd als de som van de volgende codes van de jaarrekening voor het boekjaar 2022 :- Code 9901 (bedrijfswinst/verlies);- Code 630 (afschrijvingen en waardeverminderingen op oprichtingskosten, op immateriële en materiële vaste activa);- Code 631/4 (waardeverminderingen op voorraden, op bestellingen in uitvoering en op handelsvorderingen : toevoegingen (terugnemingen)).Een bedrijf heeft een "hoge winst in 2022" gerealiseerd als zijn "winst in 2022" positief is.Een bedrijf heeft een "uitzonderlijk hoge winst in 2022" gerealiseerd als zijn "winst in 2022" minstens 1,15 x hoger is dan de gemiddelde winst in de 3 voorafgaande afgesloten boekjaren. Voor de berekening van dit gemiddelde worden enkel de boekjaren met een positieve "winst" meegeteld.Het bedrag van de koopkrachtpremie :In de ondernemingen die op 15 december 2023 geen bedrijfsakkoord hebben afgesloten en die een hoge winst hebben gerealiseerd in 2022, zoals hierboven gedefinieerd, wordt een koopkrachtpremie van 250 EUR toegekend.In de ondernemingen die op 15 december 2023 geen bedrijfsakkoord hebben afgesloten en die een uitzonderlijk hoge winst hebben gerealiseerd in 2022, zoals hierboven gedefinieerd, wordt een koopkrachtpremie van 350 EUR toegekend.Modaliteiten van toekenning :De koopkrachtpremie wordt toegekend in de loop van de maand december 2023 aan de arbeiders die in dienst zijn op 15 december 2023 :- pro rata van de arbeidsprestaties tijdens de periode die loopt van 1 januari 2022 tot en met 31 december 2022, met gelijkstellingen zoals overeengekomen in de collectieve arbeidsovereenkomst betreffende de eindejaarspremie;- pro rata van het arbeidsregime van de werknemer op 31 december 2022.Voor bedrijven wiens boekjaar niet overeenstemt met een kalenderjaar zal voor het bepalen van de winst/hoge winst/uitzonderlijk hoge winst het boekjaar genomen wordt dat eindigt in 2022.In overeenstemming met het koninklijk besluit van 23 april 2023 wordt de koopkrachtpremie op een papieren drager (cheques) of in elektronische vorm toegekend.Art. 7. MinimumuurlonenDe minimumuurlonen van de arbeiders die een in artikel 5 bepaalde functie uitoefenen worden als volgt vastgesteld in een wekelijkse arbeidsregeling van 37 uur 50 minuten :- Vanaf 1 januari 2023 :  </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de bedienden der metaalfabrikatennijverheid;Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 9 december 2024, gesloten in het Paritair Comité voor de bedienden der metaalfabrikatennijverheid, betreffende de gewaarborgde minimum maandwedde vanaf 1 januari 2025. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de bedienden der metaalfabrikatennijverheid Collectieve arbeidsovereenkomst van 9 december 2024 Gewaarborgde minimum maandwedde vanaf 1 januari 2025 (Overeenkomst geregistreerd op 20 december 2024 onder het nummer 191196/CO/209) Artikel 1. Toepassingsgebied Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en hun werknemers met een arbeidsovereenkomst voor bedienden die behoren tot het Paritair Comité voor de bedienden der metaalfabrikatennijverheid. Onder "bedienden" wordt verstaan : de gebaremiseerde en baremiseerbare bedienden. Art. 2. Gewaarborgde minimum maandwedde Vanaf 1 januari 2025 wordt aan elke bediende (in een voltijds arbeidsregime) een minimum maandwedde van 2 508,01 EUR gewaarborgd. Voor deeltijdse bedienden wordt deze gewaarborgde minimum maandwedde pro rata hun tewerkstellingsbreuk toegepast. Deze gewaarborgde minimum maandwedde wordt jaarlijks geïndexeerd op 1 juli. Daartoe wordt het 4-maandelijks gemiddelde van het indexcijfer van de maand juni van het lopende jaar geplaatst tegenover het 4-maandelijks gemiddelde van het indexcijfer van de maand juni van het vorige jaar. De toepassing van deze gewaarborgde minimum wedde doet geen afbreuk aan de toepassing van de sectorale minimumlonen, zoals opgenomen in de collectieve arbeidsovereenkomst van 9 december 2024 inzake de sectorale minimumlonen vanaf 1 januari 2025 (registratieprocedure lopende). Art. 3. Duur en vervanging Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025 en wordt gesloten voor onbepaalde duur. Zij vervangt de collectieve arbeidsovereenkomst van 8 juli 2024 betreffende de gewaarborgde minimum maandwedde met registratienummer 189034/CO/209. Zij kan door één van de partijen worden opgezegd met een opzegging van 3 maanden betekend bij een ter post aangetekende brief gericht aan de voorzitter van het paritair comité en aan elk van de ondertekenende organisaties. Gezien om te worden gevoegd bij het koninklijk besluit van 13 mei 2025. De Minister van Werk, D. CLARINVAL 
+</t>
         </is>
       </c>
     </row>
@@ -1098,28 +1096,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025200971</t>
+          <t>2025200276</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>09 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 30 november 2023, gesloten in het Paritair Comité voor de zelfstandige kleinhandel, betreffende het sectorakkoord 2023-2024 (1)</t>
+          <t>13 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 18 november 2024, gesloten in het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap, betreffende flexibiliteit en variabele tewerkstelling (1)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-09&amp;numac_search=2025200971&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200971=20&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025200276&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200276=20&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de zelfstandige kleinhandel; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 30 november 2023, gesloten in het Paritair Comité voor de zelfstandige kleinhandel, betreffende het sectorakkoord 2023-2024. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de zelfstandige kleinhandel Collectieve arbeidsovereenkomst van 30 november 2023 Sectorakkoord 2023-2024 (Overeenkomst geregistreerd op 18 december 2023 onder het nummer 184682/CO/201) Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de bedienden van de ondernemingen welke ressorteren onder het Paritair Comité voor de zelfstandige kleinhandel.1. Woon-werkverkeer - eigen vervoer Vanaf 2024 is een werkgeversbijdrage verplicht wanneer een werknemer uitsluitend met eigen vervoer naar het werk reist. Deze bijdrage is vastgesteld op 50 pct. van de prijs van de maandelijkse treinkaart in de 2de klas, en voor een gelijkwaardige afstand. De vergoeding wordt betaald vanaf de eerste kilometer en is beperkt tot het bedrag dat overeenkomt met een reis van 10 km (heen). De vergoeding wordt evenredig verdeeld op basis van het aantal gewerkte dagen. 2. Fietsvergoeding Vanaf 1 januari 2024 wordt het bedrag van de vergoeding verhoogd tot 0,27 EUR/km. 3. Koopkrachtpremie Het gunningscriterium is de stijging van het bedrijfsresultaat (code 9901) 2022 in vergelijking met het gemiddelde van de vorige boekjaren (2019-2020-2021) : - + 5 pct. : - Non-food en food speciaalzaken : 75 EUR; - Supermarkten : 150 EUR. - + 25 pct. : - Non-food en food speciaalzaken : 150 EUR; - Supermarkten : 250 EUR. Met 2022, wordt verwezen naar het boekjaar waarvan de meeste maanden zich in 2022 bevinden. Wanneer het boekjaar afsluit op 30 juni, wordt verwezen naar het boekjaar dat afsluit in 2022. Bedrijven die niet bestonden gedurende de hele periode 2019-2021 zullen het gemiddelde berekenen over de boekjaren waarin ze wel bestonden. Toekenningsvoorwaarden De premie wordt toegekend aan werknemers die : - op 31 oktober 2023 en op het moment van uitbetaling van de premie een arbeidsovereenkomst hebben; - naar rato van de effectieve of gelijkgestelde arbeidsprestaties tussen 1 november 2022 en 31 oktober 2023 (overeenkomstig het koninklijk besluit van 30 maart 1967 betreffende de jaarlijkse vakantie); - aan de deeltijdse werknemers naar rato van hun effectieve gepresteerde en gelijkgestelde uren tussen 1 november 2022 en 31 oktober 2023. Deze eenmalige premie wordt tegelijk met de eindejaarspremie uitbetaald, maar wordt niet meegeteld bij de berekening ervan. De werkgevers zullen de koopkrachtpremie in elektronische of papieren vorm toekennen volgens de concrete modaliteiten voorzien in deze overeenkomst. De sociale partners zijn het erover eens dat het paritair comité een mededeling kan organiseren over de toekenning van de koopkrachttegemoetkoming. 4. Eindejaarspremie Vanaf 2024, het artikel 5 van de collectieve arbeidsovereenkomst van 20 januari 2022 (172548/CO/201) betreffende de eindejaarspremie wordt vervangen door de volgende tekst : "Art. 5. Het bedrag van de eindejaarspremie mag niet worden verminderd voor afwezigheden wegens het opnemen van vakantieverlof, wettelijke feestdagen, in de collectieve arbeidsovereenkomst bepaalde dagen van inactiviteit, klein verlet, verlof om dwingende redenen, beroepsziekte of arbeidsongeval. Voor een maximum van 60 dagen per jaar afwezigheid wegens ziekte of ongeval, bevallingsverlof of vaderschapsverlof voor een werknemer wiens vrouw geen bevallingsverlof kan opnemen, wordt het bedrag van de eindejaarspremie evenmin verlaagd.". 5. Opleiding Binnen de het paritair comité wordt een stuurgroep "opleiding" opgericht om de opleiding in de sector te volgen. De sociale partners bevelen aan om de verhouding tussen "formele" en "informele" opleidingen in evenwicht te houden, en de voorkeur te geven aan opleidingen die leiden tot een certificaat (certificering kan intern in het bedrijf zijn). Als de werkgever niet voldoende opleidingsdagen over het jaar aanbiedt (ten opzichte van het groeipad), wordt het ontbrekende aantal dagen overgedragen naar het volgende jaar.6. Tijdskrediet, landingsbanen en SWT Bestaande collectieve arbeidsovereenkomsten worden verlengd voor de duur van de overeenkomst. 7. Tweede pensioenpijler De sociale partners verbinden er zich toe de toekomstige evoluties van de regelgeving met betrekking tot de harmonisatie van de aanvullende pensioenen voor arbeiders en bedienden op te volgen en indien nodig op gepaste wijze tussen te komen. Indien nodig zullen experts bij de besprekingen betrokken worden. 8. Agressiviteit op de werkvloer De sociale partners zijn zich bewust van het belang van een doeltreffend veiligheidsbeleid in de winkels, zodat de bedienden hun werk in een rustig klimaat kunnen verrichten. Vanuit het sociaal fonds verbinden zij zich ertoe samen te overleggen en na te denken over een positieve sensibiliseringscampagne naar de klanten. Sociale vrede De werknemers en werkgevers verbinden zich ertoe de sociale vrede in de bedrijven te bewaren tijdens de duur van dit akkoord. De partijen zullen tijdens de looptijd van dit akkoord geen nieuwe eisen stellen met betrekking tot de inhoud van het akkoord op sectoraal of bedrijfsniveau. Duur van de overeenkomst Deze overeenkomst treedt in werking op 1 juli 2023 en houdt op van kracht te zijn op 30 juni 2025, tenzij anders vermeld. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 18 november 2024, gesloten in het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap, betreffende flexibiliteit en variabele tewerkstelling. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap Collectieve arbeidsovereenkomst van 18 november 2024 Flexibiliteit en variabele tewerkstelling (Overeenkomst geregistreerd op 7 januari 2025 onder het nummer 191321/CO/318.02) I. Algemene bepalingen Artikel 1. Toepassingsgebied Deze collectieve arbeidsovereenkomst is van toepassing op de werknemers en de werkgevers van de diensten voor gezinszorg (gezins- en bejaardenhulp) van de Vlaamse Gemeenschap. Onder "werknemers" wordt verstaan : de werknemers die worden tewerkgesteld als verzorgende, oppasser, poetshulp/huishoudhulp in de gezinszorg, ongeacht hun arbeidsritme (vast of variabel) en ongeacht hun uurrooster (vast of variabel), inbegrepen de werknemers betaald uit de middelen Sociale Maribel en de werknemers tewerkgesteld in een GESCO-statuut. Art. 2.  Doelstelling Deze collectieve arbeidsovereenkomst heeft tot doel een flexibele werkregeling te organiseren. Door flexibel werk kunnen werknemers beter regelen wanneer ze meer en wanneer ze minder willen werken. Wendbaar werk en een werkbare combinatie van het werk- en privéleven dragen bovendien bij tot de aantrekkelijkheid van het beroep. Van werkgeverszijde ervaart men een noodzaak om te kunnen beantwoorden aan de specifieke zorgbehoeften van cliënten en te kunnen inspelen op actuele zorgvragen. Op deze manier wordt de zorgverlening gebaseerd op de zorgnood van de cliënt op momenten dat cliënten deze zorg nodig hebben en kan worden afgestapt van het standaard zorgaanbod.Ook vanuit organisatorische redenen dringt een flexibele arbeidsregeling zich op. De collectieve arbeidsovereenkomst van 18 november 2021 betreffende de continue dienstverlening blijft onverminderd van toepassing. Art. 3.  Vrijwilligheid  § 1. Alle werknemers - zowel bestaande werknemers als werknemers die nieuw in dienst treden - hebben de keuze tussen enerzijds de flexibele werkregeling en anderzijds de werkregeling die binnen het algemeen wettelijk kader kan worden toegepast.  § 2. De werknemer die in het flexibel werksysteem wil stappen, geeft dit te kennen : - bij de indiensttreding, door het ondertekenen van een addendum als bijlage bij de nieuwe arbeidsovereenkomst; - indien de werknemer reeds in dienst is, door het ondertekenen van een addendum aan de lopende arbeidsovereenkomst.  § 3. De vrijwilligheid wordt gegarandeerd door de mogelijkheid voor de werknemers om uit het flexibele werksysteem te stappen conform het deel IV - Terugkeermogelijkheid van deze regeling. II. Verzorgenden en oppassers HOOFDSTUK I. - Principes van flexibel werken Art. 4.  Uurroosters en uurroosterverstoring  § 1. De werknemers worden tewerkgesteld door middel van een variabel uurrooster met een variabel arbeidsritme met annualisering.  § 2. Om de voorspelbaarheid van dit werkregime te verhogen, wordt dit flexibel werkregime gebaseerd op een referentie uurrooster dat in onderling overleg wordt overeengekomen en door de dienst dient nageleefd te worden.  § 3. De gemiddelde wekelijkse arbeidsduur wordt in de individuele arbeidsovereenkomst vastgelegd.  § 4. De grenzen van de arbeidsduur in de artikelen 19, 20, 20bis en 27 van de Arbeidswet mogen overschreden worden op voorwaarde dat : - de dagelijkse arbeidstijd 9 uren niet overschrijdt; - de wekelijkse arbeidstijd 45 uren niet overschrijdt; - de wekelijkse arbeidsduur over een periode van 1 jaar (52 weken) de grenzen van de in de arbeidsovereenkomst vastgelegde gemiddelde wekelijkse arbeidsduur niet overschrijdt. Over een periode van 1 jaar (52 weken) bedraagt het maximumaantal te presteren arbeidsuren aldus 52 weken x de voltijdse arbeidsduur van toepassing in de onderneming.  § 5. De referteperiode van 1 jaar waarover de gemiddelde wekelijkse arbeidsduur gemiddeld moet nageleefd worden, wordt vastgelegd van 1 oktober tot 30 september, tenzij hiervan op ondernemingsniveau wordt afgeweken. Afhankelijk van de effectieve ingangsdatum van de collectieve arbeidsovereenkomst, wordt een beginreferteperiode vastgelegd die eveneens kan afwijken van de algemene referteperiode van 1 oktober tot en met 30 september.  § 6. Uren die meer gepresteerd worden dan de gemiddelde wekelijkse arbeidsduur zijn plusuren. Uren die minder gepresteerd worden dan de gemiddelde wekelijkse arbeidsduur zijn minuren.  § 7. Werknemers in het flexibel werksysteem kunnen de ene week meer uren (opbouw plusuren of afbouw minuren) en een andere week minder uren (afbouw plusuren of opbouw minuren) presteren dan de in hun arbeidsovereenkomst opgenomen gemiddelde wekelijkse arbeidsduur, voor zover de gemiddelde wekelijkse arbeidsduur over de referteperiode wordt gerespecteerd.  § 8. Indien een werknemer na het overschrijden van de jaargrens getroffen wordt door een gerechtvaardigde afwezigheid tot het einde van de referteperiode blijven de gepresteerde plusuren verworven en worden zij vergoed a rato van 100 pct.  § 9. Wanneer de werkgever de nieuwe arbeidsregeling invoert, moet hij voorafgaandelijk aan de werknemers schriftelijk informatie verstrekken omtrent het soort van arbeidssysteem en omtrent de factoren die de invoering ervan rechtvaardigen. De ondernemingsraad ontvangt deze informatie, bij ontstentenis het CPBW, bij ontstentenis de vakbondsafvaardiging. Bij ontstentenis van vakbondsafvaardiging wordt de informatie aan elke werknemer individueel verstrekt.  § 10. Overeenkomstig artikel 5 van de wet van 17 maart 1987 wordt het arbeidsreglement automatisch in overeenstemming gebracht met de nieuwe arbeidsregeling.HOOFDSTUK II. - Schommelingen in de arbeidstijd Art. 5.  § 1. De ondernemingen stellen een nieuw arbeidsregime in met een arbeidsduur van maximum 9 uur per dag en 45 uur per week.  § 2. Per werknemer zijn het aantal minuren en het aantal plusuren begrensd, waarbij de opvolging van de grenzen op een administratief eenvoudige manier wordt geregeld. Voor werknemers die meer dan halftijds werken wordt de grens vastgelegd op 16 minuren en 48 plusuren. Voor werknemers die halftijds of minder werken wordt de grens vastgelegd op 8 minuren en 24 plusuren.  § 3. Wanneer deze grens bereikt wordt, moeten de min- of plusuren eerst worden weggewerkt vooraleer bijkomende min- of plusuren op de teller kunnen worden opgenomen. HOOFDSTUK III. - Referentie-uurrooster Art. 6.  § 1. Elke werknemer heeft een referentie-uurrooster dat als uitgangspunt dient voor zijn/haar werkregeling. De flexibiliteit zorgt ervoor dat er wekelijks wijzigingen kunnen zijn ten opzichte van het referentie-uurrooster.  § 2. Bij werknemers met een voltijds arbeidsritme in dit flexibel werksysteem zal het referentie-uurrooster verspreid worden over 5 werkdagen.  § 3. Werknemers in dit flexibel werksysteem hebben de mogelijkheid om een vast vrij dagdeel (voormiddag, namiddag, avond, volledige nacht) aan te duiden waarop zij niet tewerkgesteld willen worden. Dit vast vrij dagdeel wordt vermeld in de individuele arbeidsovereenkomst. Het referentie-uurrooster zal over de overige dagdelen verspreid worden.  § 4. In overleg met en na goedkeuring van de directe leidinggevende zal de werknemer in het flexibel werksysteem bij zijn/haar aanvraag tot tijdskrediet of thematisch verlof (ouderschapsverlof, medische bijstand, palliatief verlof) zijn/haar vrije dag(en) in het kader van tijdskrediet of thematisch verlof kunnen vastleggen. Het referentie-uurrooster zal over de overige werkdagen verspreid worden. HOOFDSTUK IV. - Loon, bijkomende prestaties voor deeltijdse werknemers, overwerk, overloon en inhaalrust Art. 7. Loon  § 1. De werknemers krijgen op het einde van de maand een loon uitbetaald volgens de gemiddelde wekelijkse arbeidsduur.  § 2. Indien een werknemer meer of minder werkt ten opzichte van het referentie-uurrooster, heeft dit geen invloed op het maandelijks loon. Ook afwezigheden waarvoor gewaarborgd loon verschuldigd is, hebben geen invloed op het maandelijks loon.  § 3. Als een werknemer afwezig is, worden de uren tijdens sommige periodes van afwezigheid wel als gepresteerd in aanmerking genomen voor de opbouw of afbouw van het aantal plusuren of minuren : - Klein verlet : de uren afwezigheid tijdens een volledige dag onvoorzien klein verlet worden als gepresteerd beschouwd ten belope van het bekendgemaakt uurrooster en tijdens voorzienbaar klein verlet ten belope van het referentie-uurrooster. - Feestdag : de uren afwezigheid tijdens een feestdag worden als gepresteerd beschouwd ten belope van het bekendgemaakt uurrooster met een minimum van 1/5de van de gemiddelde wekelijkse arbeidsduur. - Arbeidsongeschiktheid : de uren afwezigheid tijdens een dag arbeidsongeschiktheid worden als gepresteerd beschouwd ten belope van het bekendgemaakt uurrooster. Indien de ziekteperiode langer loopt dan het bekendgemaakt uurrooster, worden de uren afwezigheid :  - voor voltijdse werknemers als gepresteerd beschouwd ten belope van 1/5de van de gemiddelde wekelijkse arbeidsduur per volledige dag ziekte;  - voor deeltijdse werknemers als gepresteerd beschouwd ten belope van het referentie-uurrooster. Art. 8.  Bijkomende prestaties voor deeltijdse werknemers  § 1. Bijkomende prestaties zijn uren die de contractuele arbeidsduur van de deeltijdse werknemer overschrijden zonder de normale arbeidsduur van de voltijdse werknemers te overschrijden. Bij een variabel arbeidsritme en variabel uurrooster is er sprake van bijkomende prestaties wanneer : - de werknemer werkt buiten het bekendgemaakte uurrooster; - de werknemer heeft gewerkt bovenop de contractuele arbeidsduur. § 2. Het urenkrediet voor bijkomende prestaties waarvoor de werkgevers geen toeslag voor overloon verschuldigd zijn, wordt voor deeltijdse werknemers met een variabel uurrooster vastgesteld op 4 uren x het aantal weken begrepen in de referteperiode (met een maximum van 208 uren).  § 3. De omwisseling van uurroosters tussen werknemers onderling of de verschuiving van uurroosters op verzoek van de werknemer, blijven uit het krediet van bijkomende prestaties. Op het niveau van de organisatie wordt aantoonbaar gemaakt van wie de vraag tot omwisseling of verschuiving van uurroosters afkomstig is. Art. 9.  Overwerk, overloon en inhaalrust  § 1. Er is sprake van overwerk : - wanneer men meer werkt dan 9 uur per dag of 45 uur per week; - wanneer men de contractuele arbeidsduur na afloop van de referteperiode overschrijdt, met uitzondering van het eventuele over te dragen urenkrediet zoals vermeld in artikel 9, § 4; - wanneer men de interne grens van plusuren zoals vermeld in artikel 5 overschrijdt; - wanneer het urenkrediet bijkomende prestaties zoals vermeld in artikel 8, § 2 overschreden wordt.  § 2. Werknemers in het flexibel werksysteem hebben de keuze om het overwerk te compenseren door : - opname in 100 pct. inhaalrust en 50 pct. toeslag in geld; - 150 pct. inhaalrust.  § 3. Bij de instap in het flexibel werksysteem maakt de werknemer zijn/haar keuze schriftelijk kenbaar. Deze keuze kan nadien 3 maanden vóór het einde van de jaarlijkse referteperiode gewijzigd worden op eenvoudig schriftelijk verzoek.  § 4. Werknemers die meer dan halftijds werken, kunnen een krediet van 24 uren overdragen op het einde van de referteperiode naar een volgende referteperiode zonder dat hier enige toeslag voor verschuldigd is. Werknemers die halftijds of minder werken kunnen een krediet van 16 uren overdragen op het einde van de referteperiode naar een volgende referteperiode zonder dat hier enige toeslag voor verschuldigd is. Minuren op het einde van de referteperiode zijn verworven voor de medewerker. Dit saldo wordt niet overgedragen naar een volgende referteperiode. HOOFDSTUK V. - Opname plus- en minuren Art. 10.  § 1. De werknemer in het flexibel werksysteem heeft de mogelijkheid om wekelijks op donderdag van week X aan de leidinggevende te laten weten op welk tijdstip zij/hij in de tweede daaropvolgende week (week X+2) plusuren wenst te recupereren of bij gebrek aan plusuren toch minder wil werken dan de gemiddelde wekelijkse arbeidsduur en zo minuren wenst te realiseren. De leidinggevende zal bij de opmaak van de uurroosters van de daaropvolgende week met deze aanvraag rekening houden en kan enkel omwille van de continuïteit van de dienstverlening deze aanvraag weigeren. In geval van dringende noodzakelijkheid zal door de leidinggevende de nodige welwillendheid aan de dag gelegd worden in verband met het respecteren van de termijn voor het indienen van de aanvragen zoals hierboven uiteengezet wordt.  § 2. Compensatie van plusuren of het realiseren van minuren die na overleg minimum 6 weken op voorhand worden aangevraagd en goedgekeurd door de leidinggevende, kunnen vastgeklikt worden. De werknemer kan zeker zijn - behoudens overmacht - dat hij/zij tijdens de vastgeklikte periode ook effectief inhaalrust (recuperatie plusuren) of realisatie van minuren heeft. Het vastklikken van plus- of minuren kan de referteperiode zoals bepaald in huidige collectieve arbeidsovereenkomst niet overschrijden.  § 3. De werknemer krijgt een overzicht van de min- en plusuren via zijn loonfiche of via een ander volwaardig alternatief (bijvoorbeeld online-toepassing).  § 4. De regeling van de realisatie en opname van plusuren en het realiseren van minuren is het voorwerp van een voortdurende dialoog tussen leidinggevende en werknemer.III. Schoonmaakhulpen HOOFDSTUK I. - Principes van flexibel werken Art. 11. De schoonmaakhulpen die onder het toepassingsgebied van deze regeling vallen worden tewerkgesteld door middel van een vast arbeidsritme met een variabel uurrooster. Deze regeling is enkel mogelijk voor deeltijdse schoonmaakhulpen. Voor voltijdse schoonmaakhulpen wordt geen flexibele werkregeling voorzien in onderhavige tekst. HOOFDSTUK II. - Bijkomende prestaties Art. 12.  § 1. Het urenkrediet voor bijkomende prestaties waarvoor de werkgevers geen toeslag voor overloon verschuldigd zijn, wordt voor deeltijdse werknemers met een variabel uurrooster vastgesteld op 4 uren x het aantal weken begrepen in de referteperiode (met een maximum van 208 uren).  § 2. De omwisseling van uurroosters tussen werknemers onderling of de verschuiving van uurrooster op verzoek van de werknemer, blijven uit het krediet van bijkomende prestaties.  § 3. Werknemers in dit flexibel werksysteem hebben de mogelijkheid om een vast vrij dagdeel (voormiddag, namiddag, avond) aan te duiden waarop zij niet tewerkgesteld willen worden. Dit vast vrij dagdeel wordt vermeld in de individuele arbeidsovereenkomst. Het referentie-uurrooster zal over de overige dagdelen verspreid worden. IV. Terugkeermogelijkheid HOOFDSTUK I. - Voor onbepaalde tijd Art. 13.  § 1. Indien de werknemer niet langer wenst tewerkgesteld te worden in het flexibel werksysteem, kan hij/zij mits een opzeggingsperiode van 3 maanden een aanvraag richten om over te schakelen naar het systeem waarin hij/zij werkte vóór de overstap naar het flexibel systeem of voor nieuwe werknemers om over te schakelen naar een overeen te komen vast arbeidsritme. Deze aanvraag dient schriftelijk te gebeuren.  § 2. De werkgever zal zo snel als mogelijk deze aanvraag beantwoorden en uiterlijk binnen de maand na de verzending van de aanvraag. In geval van weigering, dient de werkgever op de vraag van de werknemer in te gaan binnen de 6 maanden na diens aanvraag. HOOFDSTUK II. - Voor bepaalde tijd Art. 14.  § 1. Een tijdelijke terugkeer naar het basisuurrooster is eveneens voor alle werknemers mogelijk omwille van dwingende familiale en persoonlijke redenen.  § 2. Deze aanvraag dient schriftelijk te gebeuren.  § 3. De werkgever zal zo snel als mogelijk antwoord geven aan deze aanvraag en uiterlijk binnen de 2 weken na de verzending van de aanvraag. De werkgever kan enkel weigeren bij manifeste ongegrondheid van de aangehaalde redenen.  § 4. De werknemer kan bij positief antwoord van de werkgever gedurende 6 maanden volgens het basisuurrooster werken. Indien de onverwachte familiale of persoonlijke redenen dan nog bestaan, kan die periode met maximaal 6 maanden verlengd worden. Daarna werkt de werknemer terug volgens de flexibele werkregeling. V. Mogelijkheid om een deeltijdse arbeidsovereenkomst om te zetten in een voltijdse arbeidsovereenkomst Art. 15.  § 1. De flexibele arbeidsregeling heeft geenszins het opzet om het aantal deeltijds tewerkgestelde werknemers te verhogen.  § 2. Een deeltijdse werknemer die voltijds wenst te werken, krijgt conform artikel 4 van de collectieve arbeidsovereenkomst nr. 35 van 27 februari 1981 betreffende sommige bepalingen van het arbeidsrecht ten aanzien van de deeltijdse arbeid, gewijzigd door de collectieve arbeidsovereenkomst nr. 35bis van 9 februari 2000, voorrang op een voltijdse vacature. VI. Bevoegdheid van de sociale overlegorganen Art. 16. De werknemersdelegatie krijgt in de diverse sociale overlegorganen het recht om informatie in te winnen over flexibele contracten en het ziektecijfer. Een overzicht van het aantal werknemers die werken volgens deze flexibele werkregeling en een overzicht van de min- en plusuren wordt standaard aangeboden.VII. Inwerkingtreding Art. 17.  § 1. Deze collectieve arbeidsovereenkomst wordt gesloten in uitvoering van de sectorale maatregelen kwaliteit en uitbreidingsbeleid, zoals afgesproken in het 6de Vlaams Intersectoraal Akkoord.  § 2. De hierboven vermelde bepalingen kunnen enkel toegepast worden onder voorbehoud dat de financiering is opgenomen in de betoelagingsreglementering van de subsidiërende overheid. Art. 18.  § 1. Deze collectieve arbeidsovereenkomst wordt gesloten voor onbepaalde duur. Zij treedt in werking op 1 november 2024.  § 2. Deze collectieve arbeidsovereenkomst kan opgezegd worden door elk der partijen, mits een opzegging van drie maanden, betekend door middel van een aangetekend schrijven gericht aan de voorzitter van het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap. Gezien om te worden gevoegd bij het koninklijk besluit van 13 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -1130,28 +1128,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025002625</t>
+          <t>2025200296</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>09 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 10 december 2024, gesloten in het Paritair Comité voor de voedingsnijverheid, betreffende de toekenning van een syndicale premie aan de gesyndiceerde arbeiders (bakkerij) (1)</t>
+          <t>13 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 9 december 2024, gesloten in het Paritair Subcomité voor de terugwinning van allerlei producten, betreffende de buitengewone bijdrage aan het sociaal fonds (1)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-09&amp;numac_search=2025002625&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025002625=21&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025200296&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200296=21&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de voedingsnijverheid;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 10 december 2024, gesloten in het Paritair Comité voor de voedingsnijverheid, betreffende de toekenning van een syndicale premie aan de gesyndiceerde arbeiders (bakkerij).Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de voedingsnijverheidCollectieve arbeidsovereenkomst van 10 december 2024Toekenning van een syndicale premie aan de gesyndiceerde arbeiders (bakkerij) (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191523/CO/118)Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de arbeiders van de ondernemingen die onder de bevoegdheid vallen van het Paritair Comité voor de voedingsnijverheid, sector van de bakkerijen, de banketbakkerijen die "verse" producten vervaardigen voor onmiddellijke consumptie met zeer beperkte houdbaarheid en de verbruikszalen bij een banketbakkerij. § 2. Onder "werknemers" wordt verstaan : de arbeiders zonder onderscheid naar gender.Art. 2. Bij toepassing van artikel 3, 2°  van de statuten van het "Waarborg- en Sociaal Fonds voor de bakkerij, banketbakkerij en verbruikszalen bij een banketbakkerij", vastgesteld bij collectieve arbeidsovereenkomst van 17 januari 2002 gesloten in het Paritair Comité voor de voedingsnijverheid (registratienr. 62140/CO/118), algemeen verbindend verklaard bij koninklijk besluit van 11 september 2003 (Belgisch Staatsblad van 17 oktober 2003), wordt ten laste van het fonds een syndicale premie toegekend.HOOFDSTUK I. - Actieve werknemersArt. 3.  § 1. Er wordt jaarlijks een syndicale premie toegekend. Het globaal jaarlijks bedrag ervan wordt toegekend aan de werknemers die in de referteperiode, lopend van 1 juli van jaar X tot 30 juni van jaar X + 1, terzelfder tijd :a) lid zijn van één van de representatieve interprofessionele werknemersorganisaties, vertegenwoordigd in het Paritair Comité van de voedingsnijverheid;b) krachtens een arbeidsovereenkomst verbonden zijn aan een in artikel 1 bedoelde onderneming. § 2. Het bedrag van de syndicale premie wordt berekend op basis van het aantal gewerkte en gelijkgestelde dagen in de referteperiode en bedraagt 1/12de per maand lidmaatschap van een representatieve interprofessionele werknemersorganisatie tijdens de referteperiode vermeld in § 1.   </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Subcomité voor de terugwinning van allerlei producten; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 9 december 2024, gesloten in het Paritair Subcomité voor de terugwinning van allerlei producten, betreffende de buitengewone bijdrage aan het sociaal fonds. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Subcomité voor de terugwinning van allerlei producten Collectieve arbeidsovereenkomst van 9 december 2024 Buitengewone bijdrage aan het sociaal fonds (Overeenkomst geregistreerd op 7 januari 2025 onder het nummer 191331/CO/142.04) In uitvoering van artikel 13, lid 4 van de collectieve arbeidsovereenkomst van 15 december 2023 inzake wijziging en coördinatie van de collectieve arbeidsovereenkomst betreffende de instelling van een sociaal fonds. HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en arbeiders van de ondernemingen welke ressorteren onder het Paritair Subcomité voor de terugwinning van allerlei producten. Voor de toepassing van deze collectieve arbeidsovereenkomst wordt onder "arbeiders" verstaan : de mannelijke en vrouwelijke werklieden. HOOFDSTUK II. - Buitengewone bijdrage Art. 2. Overeenkomstig het artikel 13, lid 4 van de statuten van het "Sociaal Fonds voor de ondernemingen voor de terugwinning van allerlei producten", gecoördineerd bij collectieve arbeidsovereenkomst van 15 december 2023, wordt een buitengewone bijdrage bepaald. Deze buitengewone bijdrage voor het sociaal fonds wordt vastgelegd op 1 pct. van de niet-geplafonneerde brutolonen van de arbeiders vanaf 1 april 2025 tot en met 30 juni 2025. Deze buitengewone bijdrage voor het sociaal fonds wordt vastgelegd op 0,5 pct. van de niet-geplafonneerde brutolonen van de arbeiders vanaf 1 juli 2025 tot en met 31 maart 2026. Deze heeft tot doel de financiële situatie van het sociaal fonds gezond te maken. Art. 3. Deze bijzondere bijdrage wordt geïnd voor de financiering van de in artikel 6 bedoelde voordelen van de statuten van het "Sociaal Fonds voor de ondernemingen voor de terugwinning van allerlei producten", gecoördineerd bij de collectieve arbeidsovereenkomst van 15 december 2023. Art. 4. Partijen engageren zich ertoe de financiële situatie van het sociaal fonds van nabij te volgen en, desgevallend, de nodige maatregelen te nemen. HOOFDSTUK III. - Inning en invordering Art. 5. De inning en de invordering van de bijdragen worden door de Rijksdienst voor Sociale Zekerheid verzekerd in toepassing van artikel 7 van de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid. HOOFDSTUK IV. - Slotbepalingen Art. 6. Deze collectieve arbeidsovereenkomst treedt in werking op 1 april 2025 en treedt buiten werking op 31 maart 2026. Gezien om te worden gevoegd bij het koninklijk besluit van 13 mei 2025. De Minister van Werk, D. CLARINVAL 
+</t>
         </is>
       </c>
     </row>
@@ -1161,28 +1160,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025003613</t>
+          <t>2025201312</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>09 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit tot aanvaarding van het ontslag en tot benoeming van een vertegenwoordiger en plaatsvervanger bij het Comité voor schadeafwikkeling bij terrorisme</t>
+          <t>13 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 20 februari 2025, gesloten in het Paritair Comité voor het vervoer en de logistiek, betreffende het tijdskrediet in de afhandeling op de luchthavens (1)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-09&amp;numac_search=2025003613&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003613=22&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025201312&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201312=22&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 3 mei 2024 betreffende de schadeloosstelling van slachtoffers van een daad van terrorisme en betreffende de verzekering tegen schade veroorzaakt door terrorisme, artikel 13, § 1, eerste lid;Op de voordracht van de minister van Begroting,Hebben Wij besloten en besluiten Wij :Artikel 1. Uit zijn functie van vertegenwoordiger van de minister bevoegd voor Begroting het Comité voor schadeafwikkeling bij terrorisme, wordt eervol ontslag verleend aan dhr. Marc Cools.Art. 2. Wordt benoemd tot vertegenwoordiger van de ministerbevoegd voor Begroting bij het Comité voor schadeafwikkeling bij terrorisme, mevr. Séni Van Hauwaert, die het mandaat van dhr. Marc Cools beëindigt.Art. 3. Wordt benoemd tot plaatsvervangend lid bij het Comité voor schadeafwikkeling bij terrorisme, Mevr. Caroline Lietart.Art. 4. Dit besluit treedt in werking op de dag van de bekendmaking in het Belgisch Staatsblad.Art. 5. De minister bevoegd voor Begroting is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De minister van Begroting,V. VAN PETEGHEM 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het vervoer en de logistiek;Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 20 februari 2025, gesloten in het Paritair Comité voor het vervoer en de logistiek, betreffende het tijdskrediet in de afhandeling op de luchthavens. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 mei 2025. FILIPVan Koningswege :De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het vervoer en de logistiek Collectieve arbeidsovereenkomst van 20 februari 2025 Tijdskrediet in de afhandeling op de luchthavens (Overeenkomst geregistreerd op 20 maart 2025 onder het nummer 192665/CO/140) HOOFDSTUK I. - Toepassingsgebied Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en hun werknemers die ressorteren onder het Paritair Subcomité voor de grondafhandeling op luchthavens.  § 2. Onder "grondafhandeling" wordt begrepen : platform-, passagiers-, bagage-, grondtransport- en vracht- en postafhandeling en bijstand aan bemanning. Onder "luchthavens" wordt begrepen : elk bepaald grond of wateroppervlak (met gebouwen, installaties en materiaal) in hoofdzaak bestemd om, geheel of gedeeltelijk, door derden te worden gebruikt voor de aankomst, het vertrek en de bewegingen van vliegtuigen op het oppervlak. Het Paritair Subcomité voor de grondafhandeling op luchthavens is niet bevoegd voor ondernemingen voor grondafhandeling op luchthavens die vallen onder de bevoegdheid van het Paritair Comité voor de petroleumnijverheid en -handel, het Paritair Comité voor de schoonmaak, het Paritair Comité voor de handel in brandstoffen, het Paritair Comité voor het hotelbedrijf of het Paritair Comité voor de handelsluchtvaart, uitgezonderd de ondernemingen die luchthavens beheren. Het Paritair Comité voor het vervoer en de logistiek is niet bevoegd voor ondernemingen voor grondafhandeling op luchthavens die vallen onder de bevoegdheid van het Paritair Comité voor de petroleumnijverheid en -handel, het Paritair Comité voor de schoonmaak, het Paritair Comité voor de handel in brandstoffen, het Paritair Comité voor het hotelbedrijf of het Paritair Comité voor de handelsluchtvaart, uitgezonderd de ondernemingen die luchthavens beheren.  § 3. Onder "werknemers" wordt begrepen : de arbeiders en arbeidsters van de werkgevers bedoeld in § 1 aangegeven in de RSZ-categorie 283 met werknemerskengetal 015 of 027. Deze collectieve arbeidsovereenkomst is evenwel niet van toepassing op : a) de leerlingen aangegeven in de RSZ- categorie 283 met werknemerskengetal 035; b) de leerlingen die vanaf 1 januari van het jaar waarin ze 19 jaar worden, aangegeven worden met werknemerskengetal 015, maar werken onder leercontract zoals aangegeven aan de RSZ met vermelding type leerling in de zone "type leercontract". HOOFDSTUK II. - Definities Art. 2. Voor de toepassing van deze collectieve arbeidsovereenkomst wordt verstaan onder : - "CAO 103", afgesloten in de Nationale Arbeidsraad : de collectieve arbeidsovereenkomst nr. 103 tot invoering van een stelsel van tijdskrediet, loopbaanvermindering en landingsbanen, gesloten in de Nationale Arbeidsraad op 27 juni 2012, gewijzigd door de collectieve arbeidsovereenkomsten nr. 103bis van 27 april 2015, nr. 103ter van 20 december 2016, nr. 103/4 van 29 januari 2018 en nr. 103/5 van 7 oktober 2020. Art. 3. Voor de toepassing van de CAO 103 wordt rekening gehouden met de bijzondere toepassingsmodaliteiten vervat in artikel 4 hierna. HOOFDSTUK III. - Tijdskrediet met motief Art. 4.  § 1. De werknemers hebben recht op een voltijds tijdskrediet, halftijdse of 1/5de loopbaanvermindering tot maximaal 36 maanden voor het verlenen van zorgen, zoals voorzien in artikel 4, § 1, a), b) en c) van de CAO 103. Dit recht wordt uitgebreid naar maximaal 51 maanden voor alle aanvragen en verlengingsaanvragen die na 1 april 2017 aan de werkgever ter kennis werden gegeven.  § 2. De werknemers hebben recht op een voltijds tijdskrediet, halftijdse of 1/5de loopbaanvermindering tot maximum 36 maanden voor het volgen van een opleiding, zoals voorzien in artikel 4, § 2 van de CAO 103.  § 3. De periodes bedoeld in § 1 en § 2 mogen samen niet meer dan 51 maanden bedragen. HOOFDSTUK IV. - Tegemoetkoming Art. 5. Vanaf 1 januari 2025 worden de volgende aanvullende premies betaald aan de werknemers in tijdskrediet van minstens 55 jaar : - 100 EUR bruto bij 1/5de tijdskrediet; - 200 EUR bruto bij 1/2de tijdskrediet. Voor de werknemers, bedoeld in artikel 1, § 3, kan de werkgever terugbetaling bekomen van de aanvullende premies uitbetaald bij tijdskrediet, door tussenkomst van het "Sociaal Fonds voor de afhandeling op luchthavens" mits hij behoort tot de RSZ-categorie 283 gedurende de periodes waarvoor hij deze aanvullende premies terugvordert van het sociaal fonds. De raad van beheer van het "Sociaal Fonds voor de afhandeling op luchthavens" is belast met het vaststellen van de procedure tot indiening van de terugbetalingsaanvragen en de modaliteiten voor de terugbetaling van deze aanvullende premies. HOOFDSTUK V. - Geldigheidsduur en overgangsmaatregelen Art. 6. Deze collectieve arbeidsovereenkomst van bepaalde duur start op 1 januari 2025 om buiten werking te treden op 31 december 2026. Gezien om te worden gevoegd bij het koninklijk besluit van 13 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -1193,29 +1192,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025003571</t>
+          <t>2025200936</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12 mei 2025</t>
+          <t>30 mei 2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 24 oktober 2001 houdende de benaming van de politiezones</t>
+          <t>13 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 18 november 2024, gesloten in het Paritair Comité voor de bedienden uit de voedingsnijverheid, tot wijziging van de collectieve arbeidsovereenkomst van 16 april 2012 betreffende de invoering van een sociaal sectoraal aanvullend pensioenstelsel (registratienummer 109446/CO/220) (1)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-12&amp;numac_search=2025003571&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003571=23&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-30&amp;numac_search=2025200936&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200936=23&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 7 december 1998 tot organisatie van een geïntegreerde politiedienst, gestructureerd op twee niveaus, artikel 141;Gelet op het koninklijk besluit van 24 oktober 2001 houdende de benaming van de politiezones;Gelet op het koninklijk besluit van 5 maart 2025 tot instelling van de lokale politie van de politiezone Beveren-Kruibeke-Zwijndrecht/Sint-Gillis-Waas/Stekene/Temse (PZ SCHELDEWAAS);Overwegende dat de instelling van de lokale politie Beveren-Kruibeke-Zwijndrecht/Sint-Gillis-Waas/Stekene/Temse vereist dat er een code van vier cijfers wordt toegekend aan de nieuwe politiezone, welke haar officiële identificatie vormt;Op de voordracht van de Minister van Veiligheid en Binnenlandse Zaken,Hebben Wij besloten en besluiten Wij :Artikel 1. In de bijlage van het koninklijk besluit van 24 oktober 2001 houdende de benaming van de politiezones, wordt de lijst aangevuld met de woorden "5964 PZ Beveren-Kruibeke-Zwijndrecht/Sint-Gillis-Waas/Stekene/Temse". Art. 2. In dezelfde bijlage worden de woorden "5346 PZ Zwijndrecht" en "5904 PZ Beveren/Sint-Gillis-Waas/Stekene" en "5433 PZ Kruibeke/Temse" opgeheven.Art. 3. De minister bevoegd voor Binnenlandse Zaken is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Veiligheid en Binnenlandse Zaken,B. QUINTIN 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de bedienden uit de voedingsnijverheid; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 18 november 2024, gesloten in het Paritair Comité voor de bedienden uit de voedingsnijverheid, tot wijziging van de collectieve arbeidsovereenkomst van 16 april 2012 betreffende de invoering van een sociaal sectoraal aanvullend pensioenstelsel (registratienummer 109446/CO/220). Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de bedienden uit de voedingsnijverheid Collectieve arbeidsovereenkomst van 18 november 2024 Wijziging van de collectieve arbeidsovereenkomst van 16 april 2012 betreffende de invoering van een sociaal sectoraal aanvullend pensioenstelsel (registratienummer 109446/CO/220) (Overeenkomst geregistreerd op 20 december 2024 onder het nummer 191183/CO/220) Voorwoord Ingevolge de wet van 26 december 2022 tot wijziging van verscheidene bepalingen ter versterking van de transparantie in het kader van de tweede pensioenpijler ("Transparantiewet"), is vanaf 1 januari 2025, overeenkomstig de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid, bij niet naleving door de pensioeninstelling van de betalingstermijn voor de in het pensioenreglement bedoelde prestaties, de wettelijke intrestvoet zoals bepaald in artikel 2, § 1 van de wet van 5 mei 1865 betreffende de lening tegen intrest, verschuldigd op de uit te keren prestaties. Teneinde laattijdige betaling van deze prestaties te voorkomen, dringen zich een aantal wijzigingen op aan het pensioen- en solidariteitsreglement. Verder dient, ingevolge de verhoging van de wettelijke pensioenleeftijd vanaf 2025, de einddatum van de pensioentoezegging aangepast te worden. HOOFDSTUK I. - Toepassingsgebied Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en hun bedienden die ressorteren onder het Paritair Comité 220 voor de bedienden uit de voedingsnijverheid en die, in uitvoering van de collectieve arbeidsovereenkomst van 16 april 2012 (registratienummer 109446) niet zijn uitgesloten van het toepassingsgebied van het sociaal sectoraal aanvullend pensioenstelsel.  § 2. Met "bedienden" worden alle bedienden bedoeld zonder onderscheid naar gender. HOOFDSTUK II. - Pensioenreglement Art. 2. Het pensioenreglement, zoals laatste gewijzigd bij collectieve arbeidsovereenkomst van 16 december 2019 (registratienummer 156937/CO/220) en opgenomen in bijlage bij de collectieve arbeidsovereenkomst van 16 april 2012 tot invoering van een sociaal sectoraal aanvullend pensioenstelsel (registratienummer 109446/CO/220) wordt vervangen door het pensioenreglement opgenomen in bijlage 1 van onderhavige collectieve arbeidsovereenkomst. HOOFDSTUK III. - Solidariteitsreglement Art. 3. Het solidariteitsreglement, zoals laatst gewijzigd door de collectieve arbeidsovereenkomst van 18 januari 2021 (registratienummer 165171/CO/220), en opgenomen in bijlage bij de collectieve arbeidsovereenkomst van 16 april 2012 tot invoering van een sociaal sectoraal aanvullend pensioenstelsel (registratienummer 109446/CO/220), wordt vervangen door het solidariteitsreglement opgenomen in bijlage 2 van onderhavige collectieve arbeidsovereenkomst. HOOFDSTUK IV. - Eindleeftijd Art. 4. De definities onder 3.1.12, 3.1.13 en 3.1.14 van de collectieve arbeidsovereenkomst van 16 april 2012 tot invoering van een sociaal sectoraal aanvullend pensioenstelsel (registratienummer 109446/CO/220), toegevoegd ingevolge de collectieve arbeidsovereenkomst van 16 december 2019, worden als volgt vervangen met ingang vanaf 1 januari 2025 : "3.1.12. Pensioenleeftijd (= eindleeftijd) : dit is de wettelijke pensioenleeftijd. 3.1.13. Einddatum : de eerste dag van de maand volgende op de wettelijke pensioenleeftijd. 3.1.14. Eindleeftijd (= pensioenleeftijd) : dit is de wettelijke pensioenleeftijd.". HOOFDSTUK V. - Geldigheidsduur Art. 5.  § 1. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025 en wordt gesloten voor onbepaalde duur.  § 2. Overeenkomstig artikel 14 van de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités worden, voor wat betreft de ondertekening van deze collectieve arbeidsovereenkomst, de handtekeningen van de personen die deze aangaan namens de werknemersorganisaties enerzijds en namens de werkgeversorganisaties, anderzijds, vervangen door de door de voorzitter en de secretaris ondertekende en door de leden goedgekeurde notulen van de vergadering.  § 3. Zij kan door één der partijen worden opgezegd mits een opzegging van zes maanden, bij een ter post aangetekende brief, gericht aan de voorzitter van het Paritair Comité voor de bedienden uit de voedingsnijverheid en aan de erin vertegenwoordigde organisaties. De opzegging is alleen geldig voor zover artikel 10, § 1, 3° van de WAP is nageleefd. Gezien om te worden gevoegd bij het koninklijk besluit van 13 mei 2025. De Minister van Werk, D. CLARINVALBijlage 1 aan de collectieve arbeidsovereenkomst van 18 november 2024, gesloten in het Paritair Comité voor de bedienden uit de voedingsnijverheid, tot wijziging van de collectieve arbeidsovereenkomst van 16 april 2012 betreffende de invoering van een sociaal sectoraal aanvullend pensioenstelsel (registratienummer 109446/CO/220) Pensioenreglement 1. Voorwerp De pensioentoezegging heeft tot doel om een kapitaal samen te stellen dat aan de aangeslotene uitgekeerd wordt, of aan zijn rechthebbende(n) ingeval de aangeslotene overlijdt vóór de voorziene einddatum.Het kapitaal kan op vraag van de aangeslotene of de rechthebbende(n) omgezet worden in een lijfrente. Dit pensioenreglement bepaalt de rechten en verplichtingen van de inrichter, de pensioeninstelling, de werkgevers, de aangeslotenen en hun rechthebbende(n), en de voorwaarden waaronder deze rechten uitgeoefend kunnen worden. Het pensioenreglement dient in samenhang met het solidariteitsreglement en het financieringsreglement te worden gelezen. 2. Werking in de tijd Het onderhavig pensioenreglement neemt aanvang op 1 januari 2013. 3. Aansluiting De aansluiting is verplicht voor alle bedienden die zijn tewerkgesteld met een arbeidsovereenkomst bij een werkgever waarop het sociaal sectoraal pensioenstelsel voor bedienden uit de voedingsnijverheid van toepassing is. De gepensioneerde bediende tewerkgesteld met een arbeidsovereenkomst bij een werkgever waarop het pensioenreglement van toepassing is, is niet aangesloten bij de pensioentoezegging, tenzij de bediende als gepensioneerde op 31 december 2015 krachtens de bepalingen van het pensioenreglement al aangesloten was bij onderhavige pensioentoezegging. Vóór 1 januari 2019 heeft de aansluiting plaats op de datum waarop de bediende aan de aansluitingsvoorwaarden voldoet, en ten vroegste op 1 januari 2013. Vanaf 1 januari 2019 zijn alle bedienden die onder het sociaal sectoraal pensioenstelsel vallen onmiddellijk aangesloten bij de pensioentoezegging. 4. Verworven rechten van de aangeslotene op de reserves Tot en met 31 december 2018 zijn de reserves op de individuele rekeningen verworven door de aangeslotene indien gedurende minstens 132, niet noodzakelijk opeenvolgende, RSZ-dagen bijdragen betaald werden aan het sectoraal pensioenstelsel, over een periode van 12 opeenvolgende kwartalen. Is deze minimale aansluitingstermijn niet voldaan op het einde van die periode, dan wordt in voorkomend geval het aantal RSZ-dagen waarvoor bijdragen betaald werden aan het sectoraal pensioenstelsel voor bedienden in de voedingsnijverheid in betreffende periode meegeteld teneinde na te gaan of de minimale aansluitingstermijn is voldaan. Vanaf 1 januari 2019 vervalt de voorwaarde van de 132 RSZ-dagen bijdragebetaling aan het sectoraal pensioenstelsel voor bedienden over een periode van 12 opeenvolgende kwartalen. Dit heeft tot gevolg dat : - reserves opgebouwd vanaf 1 januari 2019 onmiddellijk verworven zijn; - reserves opgebouwd vóór 1 januari 2019 verworven zijn door de aangeslotene indien vóór 1 januari 2019 gedurende minstens 132 RSZ-dagen over een periode van 12 opeenvolgende kwartalen bijdragen werden betaald aan het sectoraal pensioenstelsel. Voor aangeslotenen in dienst van een werkgever onderworpen aan onderhavig pensioenreglement in de loop van het vierde kwartaal 2018 wordt deze voorwaarde tevens als vervuld beschouwd en de reserves als verworven indien zij in de loop van het eerste kwartaal van 2019 nog steeds in dienst zijn van een werkgever onderworpen aan onderhavig pensioenreglement. Een aangeslotene die de vereffening van zijn verzekerde bedragen heeft verkregen en die nadien opnieuw wordt aangesloten, wordt als een nieuwe aangeslotene beschouwd. Een aangeslotene die ervoor gekozen heeft zijn verworven reserves over te dragen naar een andere pensioeninstelling en die nadien opnieuw wordt aangesloten, wordt eveneens als een nieuwe aangeslotene beschouwd. Afkoop der verworven rechten vóór de einddatum, vervroeging, voorschotten op de contracten en inpandgevingen zijn niet toegelaten, behoudens anders vermeld in dit reglement. Indien de aangeslotene of zijn rechthebbende(n) geen recht heeft (hebben) op de reserves die opgebouwd zijn op de individuele rekeningen, worden deze bedragen in het financieringsfonds gestort. 5. De pensioeninstelling en haar aanduiding Het beheer van de pensioentoezegging wordt toevertrouwd aan een pensioeninstelling. De aanduiding van de pensioeninstelling gebeurt bij collectieve arbeidsovereenkomst.6. De bijdrage ter financiering van de pensioentoezegging 6.1. Financiering van de pensioentoezegging De uitkeringen bij pensionering en in geval van vroegtijdig overlijden vóór de einddatum, worden gefinancierd door trimestriële bijdragen van de werkgever. De RSZ wordt belast met de trimestriële inning van deze bijdragen (hierna "pensioentoelagen"). De pensioentoelagen worden na ontvangst van de RSZ, door de pensioeninrichter aan de pensioeninstelling gestort. De regels en de modaliteiten inzake de financiering van het sociaal sectoraal pensioenstelsel worden vastgelegd in een financieringsreglement. Dit financieringsreglement wordt als bijlage van een collectieve arbeidsovereenkomst ingevoerd. 6.2. De berekening en aanwending van de pensioentoelage  § 1. De pensioentoelage wordt, na afhouding van alle toepasselijke kosten en fiscale en parafiscale lasten, voor iedere aangeslotene op een individuele pensioenrekening gestort voor een verzekering van een "uitgesteld kapitaal met terugbetaling van de reserve in het geval van overlijden" (UKMTR).  § 2. Voor pensioneringen vanaf 1 januari 2025 wijkt voor het kwartaal van pensionering en de twee daaraan voorafgaande kwartalen de pensioentoelage die, na afhouding van alle toepasselijke kosten en fiscale en parafiscale lasten, op de individuele rekening wordt gestort af van de pensioentoelage berekend conform het financieringsreglement. Voor deze kwartalen wordt de pensioentoelage berekend zoals hierna beschreven. De pensioentoelage voor het kwartaal van pensionering wordt berekend op het gemiddelde over de refertekwartalen van het referteloon per kwartaal, pro rata het aantal verlopen maanden in het kwartaal van pensionering vóór de datum van pensionering. De pensioentoelagen voor de twee kwartalen voorafgaand aan het kwartaal van pensionering worden eveneens berekend op het gemiddelde over de refertekwartalen van het referteloon per kwartaal. Het referteloon van de refertekwartalen die zich bevinden in het jaar/de jaren voor het jaar van pensionering zal voor de berekening van de pensioentoelage voor het kwartaal van pensionering en de twee daaraan voorafgaande kwartalen, aangepast worden aan de indexering en de sectoraal afgesproken baremaverhogingen van de lonen. Voor de pensioentoelagen met betrekking tot het kwartaal van pensionering en de twee daaraan voorafgaande kwartalen wordt rendement toegekend vanaf de eerste dag van de maand van pensionering.  § 3. Voor overlijdens vanaf 1 januari 2025 wijkt voor het kwartaal van overlijden en de twee daaraan voorafgaande kwartalen de pensioentoelage die op de individuele rekening wordt gestort af van de bijdrage berekend conform het financieringsreglement. Voor deze kwartalen wordt de pensioentoelage die op de individuele rekening wordt gestort berekend op dezelfde wijze als de pensioentoelagen voor het kwartaal van pensionering en de twee daaraan voorafgaande kwartalen, zoals beschreven in § 2. Voor de pensioentoelagen met betrekking tot het kwartaal van overlijden en de twee daaraan voorafgaande kwartalen wordt rendement toegekend vanaf de eerste dag van de maand van overlijden.  § 4. De refertekwartalen betreffen "de 4 aaneensluitende kwartalen onmiddellijk voorafgaand aan de 2 kwartalen voorafgaand aan het kwartaal van pensionering of van overlijden. Deze kwartalen vormen samen een vaste periode: indien voor een kwartaal geen bijdrage werd gestort, blijven de refertekwartalen ongewijzigd.".  § 5. De hiervoor beschreven berekening van de pensioentoelage is definitief. Voor zover als nodig worden alle aan onderhavig pensioenreglement verwante documenten naar analogie aangepast voor de berekening van de pensioentoelage van het kwartaal van pensionering en de twee daaraan voorafgaande kwartalen, en voor de berekening van de pensioentoelage voor het kwartaal van overlijden en de twee daaraan voorafgaande kwartalen.  § 6. De oprenting gebeurt: - vanaf de 1ste dag van het 2de trimester volgend op het einde van het trimester waarop de pensioentoelagen betrekking hebben; - tot op de dag waarop de uitbetaling van het aanvullend pensioen gebeurt. Voor de pensioentoelagen met betrekking tot het kwartaal van pensionering en de twee daaraan voorafgaande kwartalen gebeurt de oprenting vanaf de 1ste dag van de maand van pensionering.Voor de pensioentoelagen met betrekking tot het kwartaal van overlijden en de twee daaraan voorafgaande kwartalen gebeurt de oprenting vanaf de 1ste dag van de maand van overlijden. 6.3. Het rendement De pensioenrekening ontvangt een door de pensioeninstelling gewaarborgd rendement. Bij uittreding, pensionering of wanneer prestaties verschuldigd zijn overeenkomstig artikel 27, § 1, 6de lid of de artikelen 63/2 en 63/3 van de WAP of bij opheffing van de pensioentoezegging worden indien nodig de reserves aangevuld om het rendement dat vereist is in uitvoering van artikel 24 van de WAP te bereiken. De financiering van dit bedrag is ten laste van het financieringsfonds of de inrichter indien de middelen van het financieringsfonds ontoereikend zouden zijn. 6.4. Winstdeelname De pensioeninstelling kan overgaan tot het toekennen van een winstdeelname. Deze winstdeelname zal op de individuele pensioenrekening gestort worden voor wat betreft de reserve die op de individuele rekening aanwezig is, en in het financieringsfonds voor wat betreft de daar aanwezige sommen. 6.5. Tarieven De toegepaste tarieven zijn de door de pensioeninstelling bij de toezichthoudende overheid neergelegde tarieven. Bij wijziging van de tarieven zal elke nieuwe premie en elke omzetting in renten berekend worden met behulp van het nieuwe tarief. 6.6. Uitbetaling De pensioeninstelling zal de voorziene bedragen, na ontvangst van alle noodzakelijke gegevens, binnen de wettelijk voorziene termijn uitbetalen. 7. Uitkering 7.1. Uitkering op de einddatum Behoudens toepassing van punt 7.2. of 7.3. van dit reglement, wordt de einddatum waarop het bedrag, dat op de individuele pensioenrekening werd opgebouwd, opeisbaar is en kan omgezet worden in een rente, vastgesteld op de eerste dag van de maand volgend op de pensioenleeftijd. De pensioenleeftijd is 65 jaar tot 31 december 2024. Met ingang van 1 januari 2025 wordt de einddatum vastgesteld op de eerste dag van de maand volgend op het bereiken van de wettelijke pensioenleeftijd door de aangeslotene. Indien de pensionering later is dan de datum waarop de aangeslotene de wettelijke pensioenleeftijd bereikt, mag het verzekerd bedrag bij leven op verzoek van de aangeslotene betaald worden, voor zover dit wettelijk mogelijk is. 7.2. Uitkering na de einddatum Voor de actieve aangeslotene die na de einddatum in dienst blijft van een werkgever waarop het sociaal sectoraal pensioenstelsel van toepassing is, blijft de pensioentoelage verschuldigd en dit zo lang hij in dienst blijft en niet met pensioen gaat. De aangeslotene zal dan de uitkering van de op zijn individuele pensioenrekening opgebouwde pensioenrechten bekomen bij de vroegste van de volgende gebeurtenissen : - Wanneer de aangeslotene zijn pensioen opneemt; - Wanneer de aangeslotene de uitkering van zijn pensioenrechten vraagt. De bediende die als gepensioneerde krachtens de bepalingen van onderhavig pensioenreglement actieve aangeslotene was op 31 december 2015, blijft actieve aangeslotene bij het sociaal sectoraal pensioenstelsel zo lang hij in dienst blijft. Voor de aangeslotene die uitgetreden is voor de einddatum en zijn verworven reserve bij de pensioeninstelling gelaten heeft (de slaper), gebeurt de uitkering, behoudens toepassing van punt 7.3. hierna, op de einddatum, onafhankelijk van het feit of hij al dan niet is blijven werken na die datum. 7.3. Uitkering vóór de einddatum (vervroeging) Wanneer de aangeslotene (actieve of slaper) met pensioen gaat vóór de einddatum, worden de op de individuele rekening opgebouwde pensioenrechten, uitgekeerd. De aangeslotene die niet meer in dienst is bij een werkgever waarop het sociaal sectoraal pensioenstelsel van toepassing is (slaper), kan op zijn verzoek de uitkering van de pensioenrechten vóór de einddatum bekomen wanneer hij voldoet aan de voorwaarden van de overgangsmaatregelen opgenomen in artikel 63/2 van de WAP. De actieve aangeslotene beschikt niet over deze mogelijkheid.De uitkering van de op de individuele rekening opgebouwde pensioenrechten is in geen geval mogelijk vóór de leeftijd van 60 jaar. De vervroegde uitkering brengt het verval van het recht op een uitkering bij overlijden vóór de einddatum mee. 8. Uitkering in geval van overlijden vóór de einddatum Wanneer een aangeslotene overlijdt, heeft (hebben) de rechthebbende(n) recht op de op het ogenblik van het overlijden opgebouwde waarde op de individuele pensioenrekening. 9. De aangeslotene verlaat de sector vóór de einddatum 9.1. Uittreding Wordt als uittreding beschouwd: 1. Hetzij de beëindiging van de arbeidsovereenkomst met een werkgever op wie dit pensioenreglement van toepassing is, anders dan door overlijden of pensionering. Wordt evenwel niet als een uittreding beschouwd, de beëindiging van de arbeidsovereenkomst, anders dan door overlijden of pensionering, die wordt gevolgd door het sluiten van een arbeidsovereenkomst binnen de twee trimesters met een andere werkgever die onder het toepassingsgebied van onderhavig pensioenreglement valt; 2. Hetzij het einde van de aansluiting vanwege het feit dat de bediende niet langer de aansluitingsvoorwaarden van het pensioenstelsel vervult, zonder dat dit samenvalt met de beëindiging van de arbeidsovereenkomst, anders dan door overlijden of pensionering; 3. Hetzij het einde van de aansluiting vanwege het feit dat de werkgever of, in geval van de overgang van de arbeidsovereenkomst, de nieuwe werkgever niet langer valt onder het toepassingsgebied van de collectieve arbeidsovereenkomst die het pensioenstelsel heeft ingevoerd. 9.2. Keuzemogelijkheden Wanneer de arbeidsovereenkomst van de aangeslotene beëindigd wordt om een andere reden dan het overlijden of pensionering, en de aangeslotene niet binnen de twee trimesters het werk hervat bij een werkgever waarop dit pensioenreglement van toepassing is, heeft de aangeslotene de keuze tussen de volgende mogelijkheden : a. Hetzij de verworven reserve zonder wijziging van de pensioenbelofte laten bij de pensioeninstelling en op de einddatum of bij overlijden een kapitaal ontvangen; b. Hetzij de verworven reserve overdragen naar de pensioeninstelling van : - ofwel de nieuwe werkgever met wie hij een arbeidsovereenkomst heeft gesloten, indien hij wordt aangesloten bij de pensioentoezegging van die werkgever;  - ofwel de nieuwe rechtspersoon, bedoeld in artikel 3, § 1, 5°, a) van de WAP, waaronder de werkgever ressorteert met wie hij een arbeidsovereenkomst heeft gesloten, indien hij wordt aangesloten bij de pensioentoezegging van die rechtspersoon; c. Hetzij de verworven reserve overdragen naar een andere pensioeninstelling die de totaliteit van haar winsten proportioneel met de reserves verdeelt onder de aangeslotenen, en die de kosten beperkt als gevolg van de regels bepaald door het koninklijk besluit van 14 november 2003 betreffende de toekenning van buitenwettelijke voordelen aan werknemers en aan bedrijfsleiders. Indien de aangeslotene geen expliciete keuze maakt binnen de dertig dagen, te rekenen vanaf de kennisgeving van de hierboven vermelde keuzemogelijkheden door de pensioeninstelling, wordt hij verondersteld gekozen te hebben voor het behoud van zijn reserves bij de pensioeninstelling zonder wijziging van de pensioenbelofte (punt a. hiervoor). Na het verstrijken van de termijn van 30 dagen kan de aangeslotene te allen tijde vragen om zijn reserves over te dragen naar een andere pensioeninstelling. In afwijking van het voorgaande blijft het bedrag van de verworven reserves op de datum van uittreding bij de pensioeninstelling, zonder wijziging van de pensioentoezegging, wanneer dit bedrag lager is dan of gelijk aan 150 EUR. Dit bedrag van 150 EUR wordt geïndexeerd overeenkomstig artikel 32, § 1, laatste lid van de WAP. 10. De manier van uitkeren De aangeslotene of de rechthebbende(n) worden verondersteld te kiezen voor de uitkering van de verzekerde voordelen in de vorm van een kapitaal. De aangeslotene of de rechthebbende(n) kan (kunnen) vragen om het kapitaal dat aan hem (hen) toekomt, om te vormen in een lijfrente. De hoogte van de lijfrente wordt bepaald op basis van de op het moment van de omzetting door de pensioeninstelling gehanteerde tarieven. Een keuze voor een vereffening als lijfrente moet uiterlijk één maand vóór de datum waarop de uitkering aanvangt schriftelijk door de aangeslotene of de rechthebbende(n) aan de pensioeninstelling meegedeeld worden. Het kan volgens de keuze van de aangeslotene of de rechthebbende(n) gaan om een lijfrente die enkel aan hem betaald wordt, of om een lijfrente die in geval van overlijden van de aangeslotene of de rechthebbende(n) voor maximaal 80 pct. overdraagbaar is op de overlevende echtgeno(o)t(e) of op de partner waarmee hij wettelijk samenwoont. De aangeslotene of de rechthebbende(n) kan (kunnen) kiezen voor een jaarlijkse vaste indexatie van de lijfrente met ten hoogste 2 pct. De renten worden in maandelijkse delen betaald op de laatste dag van elke maand, tot en met de laatste vervaldag die voorafgaat aan het overlijden van de aangeslotene of de rechthebbende(n). Wanneer de lijfrente lager is dan 500 EUR per jaar, wordt het pensioenkapitaal uitgekeerd en heeft de aangeslotene of de rechthebbende geen optie tot omzetting in lijfrente. Wanneer het jaarbedrag van de rente gelegen is tussen 500 en 800,01 EUR, dan wordt ze niet maandelijks betaald, maar in vier gelijke delen op het einde van ieder trimester. De in voorgaande leden vermelde drempels worden geïndexeerd volgens de bepalingen van de wet van 2 augustus 1971 houdende inrichting van een stelsel waarbij de wedden, lonen, pensioenen, toelagen en tegemoetkomingen ten laste van de openbare schatkist geïndexeerd worden. 11. Begunstigde 11.1. De begunstigde van de uitkering op de einddatum Indien de aangeslotene in leven is op de einddatum, wordt het kapitaal uitgekeerd aan de aangeslotene zelf. Indien de voordelen bij leven na het bereiken van de einddatum door de aangeslotene niet worden opgevraagd binnen een periode van 5 jaar vanaf de dag volgend op die waarop de aangeslotene kennis heeft gekregen of redelijkerwijze kennis had moeten krijgen van het voorval dat het vorderingsrecht doet ontstaan, worden, behoudens overmacht in hoofde van de aangeslotene, deze voordelen in het financieringsfonds gestort. 11.2. De begunstigde van de uitkering bij overlijden Indien de aangeslotene overlijdt vóór de einddatum, wordt de voorziene uitkering bij overlijden uitgekeerd aan de rechthebbende(n) op basis van de volgende voorrangsorde : - De echtgeno(o)t(e) van de aangeslotene, voor zover die niet gerechtelijk van tafel en bed of feitelijk gescheiden is, of die zich niet in aanleg tot scheiding van tafel en bed of echtscheiding bevindt. De echtgenoten worden geacht feitelijk gescheiden te zijn wanneer uit de bevolkingsregisters blijkt dat zij een verschillende woonplaats hebben; - Bij ontstentenis, de persoon die wettelijk samenwoont met de aangeslotene in de zin van artikelen 1475 tot 1479 van het Burgerlijk Wetboek, uitgezonderd indien deze een bloedverwant van de aangeslotene is of indien de wettelijke samenwoning officieel beëindigd werd of indien zulke procedure lopende is; - Bij ontstentenis, de kinderen van de aangeslotene, waarvan de afstamming vaststaat of zijn adoptieve kinderen, of, bij plaatsvervulling, hun nakomelingen, voor het gedeelte dat zou toegekomen zijn aan de begunstigde in wiens plaats ze treden; - Bij ontstentenis, de ouders van de aangeslotene, elk voor de helft. Bij overlijden van één van hen komt het kapitaal toe aan de langstlevende; - Bij ontstentenis, het financieringsfonds. Indien er meerdere rechthebbenden zijn, wordt het voorziene kapitaal in gelijke delen onder hen verdeeld. Ingeval de aangeslotene en de rechthebbende overlijden zonder dat de volgorde van overlijden kan bepaald worden, wordt het kapitaaloverlijden uitgekeerd aan de plaatsvervanger(s) van de rechthebbende(n). Indien het overlijden van de aangeslotene het gevolg is van een opzettelijke daad te wijten aan of aangezet door één van de begunstigde(n), wordt deze automatisch als begunstigde geschrapt. Indien de voordelen bij overlijden niet worden opgevraagd door de rechthebbende(n) binnen de 5 jaar volgend op de dag waarop de begunstigde kennis heeft gekregen of redelijkerwijze kennis had moeten krijgen van het bestaan van het aanvullend pensioen, van zijn hoedanigheid van begunstigde en van het overlijden van de aangeslotene, worden deze voordelen, behoudens overmacht in hoofde van de rechthebbende(n), in het financieringsfonds gestort.11.3. Aanduiding van de begunstigde Met respect voor de wettelijke bepalingen en zonder dat de inrichter of de pensioeninstelling aansprakelijk kan worden gesteld voor een eventuele betwisting, kan de aangeslotene altijd afwijken van deze rangorde of zelf een begunstigde aanduiden. De aangeslotene dient deze afwijking schriftelijk per aangetekende brief aan de inrichter mee te delen, waarbij de laatst bij de inrichter aangekomen betekende brief doorslaggevend zal zijn. Bij gebrek aan verdeling van de prestaties, zullen deze in gelijke delen verdeeld worden. De schriftelijke aanvaarding van de begunstiging door de betrokken persoon maakt de begunstiging onherroepbaar zonder diens akkoord. Indien er geen schriftelijke aanvaarding van de begunstiging is, kan de aanduiding van de begunstigde vrij herroepen worden. Elke herroeping moet volgens dezelfde procedure gebeuren als hierboven. 12. Verplichtingen van de inrichter De inrichter gaat tegenover alle werkgevers en aangeslotenen de verbintenis aan alles te doen wat nodig is voor de goede uitvoering van dit pensioenstelsel. Hij zal de bij de werkgever geïnde pensioentoelagen zo spoedig mogelijk aan de pensioeninstelling overmaken. Bovendien zal hij alle voor het beheer van het pensioenstelsel benodigde gegevens overmaken. De inrichter maakt hiervoor gebruik van de persoonsgegevens zoals meegedeeld uit het netwerk van de sociale zekerheid door de Kruispuntbank van de Sociale Zekerheid aan de inrichter, alsook de wijzigingen dewelke tijdens de duur van de aansluiting in voormelde gegevens voorkomen. 13. Verplichtingen van de aangeslotene en de rechthebbende De aangeslotene of de rechthebbende zal alle ontbrekende inlichtingen en bewijsstukken die nodig zijn opdat de pensioeninstelling zijn verplichtingen tegenover de aangeslotene of zijn rechthebbenden kan uitvoeren, op eenvoudige vraag overmaken. Zolang de aangeslotene deze inlichtingen of bewijsstukken niet overmaakt, zullen de inrichter en de pensioeninstelling hun verplichtingen tegenover de aangeslotene met betrekking tot het aanvullend pensioen dat in dit reglement wordt beschreven, niet kunnen uitvoeren. Er kan in dat geval geen sprake zijn van enige vorm van vergoeding of verwijlinterest voor een gebeurlijke late uitbetaling van rechten. Indien de aangeslotene of de rechthebbende(n) zich niet spontaan en binnen een redelijke termijn aanmelden zullen de inrichter en de pensioeninstelling zich van al hun wettelijke verplichtingen tot opzoeking van de aangeslotene en de rechthebbende(n) kwijten. De pensioeninstelling noch de inrichter kunnen aansprakelijk gesteld worden indien deze opzoekingen zonder resultaat blijven. De aangeslotene en de rechthebbende blijven verantwoordelijk voor de inlichtingen die ze overmaken. De inrichter en de pensioeninstelling kunnen niet aansprakelijk gesteld worden voor de gevolgen van laattijdige of foutieve informatie. 14. Gevolgen van het niet-betalen van de pensioentoelagen De RSZ zal de verschuldigde pensioentoelagen via de inrichter aan de pensioeninstelling overmaken. De pensioeninstelling zal iedere aangeslotene uiterlijk binnen de 3 maanden volgend op de datum waarop zij kennis kreeg van een betalingsachterstand, doormiddel van een op zijn persoonlijk adres gestuurde brief op de hoogte brengen. 15. Fiscale bepalingen 15.1. Algemeen De informatie opgenomen in dit artikel wordt verstrekt strikt ten indicatieve titel en onder voorbehoud van eventuele wijzigingen of interpretatie in de fiscale wetgeving of regelgeving. 15.2. Toepasselijke fiscale wetgeving Wanneer de aangeslotene en de rechthebbende hun woon- en/of werkplaats in België hebben, en de werkgever in België is gevestigd, is de Belgische fiscale wetgeving van toepassing op zowel de pensioentoelagen als op de uitkeringen. Is dit niet het geval, dan zouden de fiscale en/of sociale lasten kunnen verschuldigd zijn op basis van een buitenlandse wetgeving, in uitvoering van de internationale verdragen die in dat verband gelden. 15.3. Belastingstatuut van de bijdrage ter financiering van de pensioentoezegging Op basis van de Belgische fiscale wetgeving van kracht op de ingangsdatum van dit pensioenreglement, vormen de werkgeversbijdragen ter financiering van de pensioentoezegging in principe aftrekbare beroepskosten in de vennootschapsbelasting en geven geen aanleiding tot bijkomende heffing in de rechtspersonenbelasting, noch tot een dadelijk belastbaar voordeel voor de aangeslotene.Behoudens andersluidende wettelijke bepalingen, mag het bedrag, uitgedrukt in jaarlijkse : - van de voorziene uitkeringen naar aanleiding van pensionering in uitvoering van dit pensioenreglement, en; - van het wettelijk pensioen; en - van andere aanvullende pensioenuitkeringen waarop de aangeslotene recht heeft, evenwel 80 pct. van het laatste normale brutojaarloon niet overschrijden, rekening houdend met de normale duur van een beroepswerkzaamheid en met een overdraagbaarheid van de rente ten gunste van de overlevende echtgeno(o)t(e) van 80 pct., en met een indexatie van de rente. De normale duur van beroepsactiviteit is vastgelegd op 40 jaar. Het laatste normale brutojaarloon is het brutojaarloon dat gezien de vorige lonen van de aangeslotene, als normaal kan worden beschouwd en dat hem wordt betaald of toegekend tijdens het laatste jaar dat aan zijn pensionering voorafgaat tijdens hetwelk hij een normale beroepsactiviteit heeft uitgeoefend. Indien een werkgever voor een aangeslotene nog andere aanvullende pensioenvoordelen zou voorzien dan diegene die voortkomen uit dit pensioenreglement, zal een gebeurlijke overschrijding van de fiscaal toegelaten grens aangerekend worden op de financiering van die andere pensioenvoordelen. 15.4. Taxatie van de verzekerde prestaties De taxatie van de </t>
         </is>
       </c>
     </row>
@@ -1225,28 +1223,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025003572</t>
+          <t>2025003413</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>12 mei 2025</t>
+          <t>16 mei 2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 8 februari 2001 tot uitvoering van de wet van 24 maart 1999 tot regeling van de betrekkingen tussen de overheid en de vakverenigingen van het personeel van de politiediensten</t>
+          <t>12 mei 2025. - Koninklijk besluit tot verlenging van bepaalde maatregelen voorzien in de wet van 20 november 2022 houdende maatregelen aangaande de personeelsschaarste in de zorgsector</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-12&amp;numac_search=2025003572&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003572=24&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-16&amp;numac_search=2025003413&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003413=24&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 24 maart 1999 tot regeling van de betrekkingen tussen de overheid en de vakverenigingen van het personeel van de politiediensten;Gelet op het koninklijk besluit van 8 februari 2001 tot uitvoering van de wet van 24 maart 1999 tot regeling van de betrekkingen tussen de overheid en de vakverenigingen van het personeel van de politiediensten;Gelet op het koninklijk besluit van 5 maart 2025 tot instelling van de lokale politie van de politiezone Beveren-Kruibeke-Zwijndrecht/Sint-Gillis-Waas/Stekene/Temse (PZ SCHELDEWAAS);Overwegende dat iedere politiezone is voorzien van een basisoverlegcomité dat wordt geïdentificeerd met een eigen nummering;Overwegende dat de instelling van de lokale politie van de nieuwe politiezone Beveren-Kruibeke-Zwijndrecht/Sint-Gillis-Waas/Stekene/ Temse bijgevolg vereist dat er een nummer wordt toegekend aan haar basisoverlegcomité;Op de voordracht van de Minister van Veiligheid en Binnenlandse Zaken,Hebben Wij besloten en besluiten Wij :Artikel 1. In de bijlage van het koninklijk besluit van 8 februari 2001 tot uitvoering van de wet van 24 maart 1999 tot regeling van de betrekkingen tussen de overheid en de vakverenigingen van het personeel van de politiediensten, worden de volgende wijzigingen aangebracht:1°  de woorden "Beveren-Sint-Gillis-Waas/Stekene 104" worden vervangen door de woorden "Beveren-Kruibeke-Zwijndrecht/Sint-Gillis-Waas/ Stekene/Temse 104";2°  de woorden "Zwijndrecht 45" en "Kruibeke/ Temse 106" worden opgeheven.Art. 2. De minister bevoegd voor Binnenlandse Zaken is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Veiligheid en Binnenlandse Zaken,B. QUINTIN 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 20 november 2022 houdende maatregelen aangaande de personeelsschaarste in de zorgsector, artikel 21, vervangen bij de wet van 15 december 2024 en gewijzigd bij het koninklijk besluit van 12 januari 2025;Gelet op de adviezen van de Inspecteurs van Financiën, gegeven op 13 maart 2025 en 26 maart 2025;Gelet op de akkoordbevinding van de Minister van Begroting, d.d. 10 april 2025;Gelet op de wet van 25 april 1963 betreffende het beheer van de instellingen van openbaar nut voor sociale zekerheid en sociale voorzorg, artikel 15, eerste lid;Gelet op de dringende noodzakelijkheid;Gelet op de uitzondering inzake het verrichten van de regelgevingsimpactanalyse, bedoeld in artikel 8, § 2, 2°,  van de wet van 15 december 2013 houdende diverse bepalingen inzake administratieve vereenvoudiging;Gelet op de hoogdringendheid gemotiveerd door het feit dat de maatregel die momenteel van toepassing is en die het voorwerp uitmaakt van de verlenging waarnaar in dit besluit wordt verwezen, op 31 maart 2025 afloopt;Dat gezien de context van de recente vorming van de nieuwe regering, er nog geen structurele maatregelen konden worden genomen om het personeelstekort in de zorgsector op te vangen;Het is gebleken dat het tekort in de zorgsector nog steeds een realiteit is en dat de vrijstellingsmaatregel het mogelijk maakt om er iets aan te doen, al is het maar gedeeltelijk;Dat het om die reden belangrijk is om deze vrijstellingsmaatregel zo snel mogelijk te verlengen voor een periode van drie maanden;Gelet op het advies nr. 77.653/16 van de Raad van State, gegeven op 18 april 2025 in toepassing van artikel 84, § 1, eerste lid, 3°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Op de voordracht van de Minister van Werk en van de Minister van Sociale Zaken en op het advies van de in Raad vergaderde ministers,Hebben Wij besloten en besluiten Wij :Artikel 1. In artikel 21 van de wet van 20 november 2022 houdende maatregelen aangaande de personeelsschaarste in de zorgsector, vervangen bij de wet van 15 december 2024 en gewijzigd bij het koninklijk besluit van 12 januari 2025, worden de volgende wijzigingen aangebracht:1°  in het derde lid worden de woorden "op 31 maart 2025" vervangen door de woorden "op 30 juni 2025";2°  in het vijfde lid worden de woorden "op 31 maart 2025" vervangen door de woorden "op 30 juni 2025".Art. 2.  Dit besluit heeft uitwerking met ingang van 31 maart 2025.Art. 3.  De minister bevoegd voor Werk en de minister bevoegd voor Sociale Zaken, zijn, ieder wat hem betreft, belast met de uitvoering van dit besluit.Gegeven te Brussel, 12 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVALDe Minister van Sociale Zaken,F. VANDENBROUCKE 
 </t>
         </is>
       </c>
@@ -1257,28 +1255,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025000763</t>
+          <t>2025003891</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>12 mei 2025</t>
+          <t>22 mei 2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 6 december 2023, gesloten in het Paritair Subcomité voor het bedrijf der kalksteengroeven, cementfabrieken en kalkovens van het administratief arrondissement Doornik, betreffende het protocolakkoord (1)</t>
+          <t>12 mei 2025. - Koninklijk besluit ter wijziging van het koninklijk besluit van 20 mei 2021 tot benoeming van sommige leden van de raad van bestuur van het Federaal Kenniscentrum voor de Gezondheidszorg</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-12&amp;numac_search=2025000763&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025000763=25&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-22&amp;numac_search=2025003891&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003891=25&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Subcomité voor het bedrijf der kalksteengroeven, cementfabrieken en kalkovens van het administratief arrondissement Doornik;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 6 december 2023, gesloten in het Paritair Subcomité voor het bedrijf der kalksteengroeven, cementfabrieken en kalkovens van het administratief arrondissement Doornik, betreffende het protocolakkoord.Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad:Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Subcomité voor het bedrijf der kalksteengroeven, cementfabrieken en kalkovens van het administratief arrondissement DoornikCollectieve arbeidsovereenkomst van 6 december 2023Protocolakkoord (Overeenkomst geregistreerd op 21 december 2023 onder het nummer 184802/CO/102.07)HOOFDSTUK I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de werknemers van de ondernemingen die ressorteren onder het Paritair Subcomité voor het bedrijf der kalksteengroeven, cementfabrieken en kalkovens van het administratief arrondissement Doornik (PSC 102.07).Onder "werknemers" wordt verstaan : de arbeiders en de arbeidsters.HOOFDSTUK II. - Protocolakkoord en bijlage van 25 oktober 2023Art. 2. Verlenging van alle vorige akkoordenArt. 3. Geldigheidsduur : 1 januari 2023 tot 31 december 2024 (behalve voor de verlengbare SWT tot 30 juni 2025 + beschikbaarheden)Art. 4. ArbeidsvolumeDe werkgevers verbinden zich ertoe alles in het werk te stellen tijdens de duur van de collectieve arbeidsovereenkomst om geen toevlucht te nemen tot ontslagen om conjuncturele redenen. Als er zich ter zake moeilijkheden voordoen, zal de voorkeur worden gegeven aan het stelsel van deeltijdse werkloosheid. Wanneer het absoluut noodzakelijk is, zal pas na overleg met de vakbondsafvaardigingen, met inbegrip van de vakbondsvrijgestelden, deeltijdse werkloosheid worden ingevoerd.Dit overleg zal tot doel hebben de rotatie en de frequentie van de werkloosheid te bepalen, zodat de nadelige individuele impact ervan zo klein mogelijk is voor de werknemers. Over alle problemen betreffende het behoud van het tewerkstellingsniveau in de ondernemingen zal permanent paritair overleg worden gepleegd binnen de ondernemingsraden of met de vakbondsafvaardigingen, met inbegrip van de vakbondsvrijgestelden. Voor het geval er toch ontslagen zouden worden overwogen om economische en conjuncturele redenen, zullen de ondernemingsraad, bij gebreke hiervan het comité voor preventie en bescherming op het werk of bij gebreke hiervan de vakbondsafvaardiging of bij gebreke hiervan de vakbondsvrijgestelden hiervan vooraf op de hoogte worden gebracht.De partijen zullen in dit verband de voorkeur geven aan de maatregelen die zouden kunnen worden genomen om de ongemakken van deze ontslagen voor de arbeiders te beperken, bijvoorbeeld en in functie van de omstandigheden en mogelijkheden : inhaalrust, verdeling van het werk, tijdskrediet, afschaffing van overuren,... De reglementaire vervanging van een arbeider die vertrokken is binnen het stelsel van werkloosheid met bedrijfstoeslag zal gebeuren door een andere arbeider.Art. 5. Koopkrachta. ConsumptiepremieBedrag van 750 EUR voor de werknemers die ten minste 1 dag effectieve prestaties hebben in 2022.Voor de werknemers die zijn in dienst getreden tijdens de periode van 1 januari 2023 tot 31 oktober 2023 zal een bedrag van 34 EUR worden toegekend per gepresteerde maand.In de 2 gevallen zal de betaling gebeuren aan het personeel op de payroll op datum van 25 oktober 2023.b. De ecocheques worden op 250 EUR gebracht vanaf 2023.c. Vanaf 2023, toekenning van een jaarlijkse cadeaucheque van 40,00 EUR indien 1 effectieve arbeidsdag in het jaar van de betaling en aanwezigheid op de payroll van de onderneming op het ogenblik van de betaling.d. Herwaardering van de kledijvergoeding tot het wettelijk maximum (1,02 EUR).e. Toekenning van een pensioenbonus berekend als volgt : 40,00 EUR per aangevat dienstjaar, met een maximum van 1 000,00 EUR.Art. 6. Verlenging van de tijdskredietstelsels, op basis van de wettelijke bepalingenBovendien, betaling van een toeslag van 100 EUR bruto in de vorm van bestaanszekerheid voor de personen die halftijds tijdskrediet nemen op het einde van de loopbaan en betaling van een toeslag van 50 EUR bruto in de vorm van bestaanszekerheid voor de personen die op het einde van de loopbaan 1/5de tijdskrediet nemen.Deze bedragen worden toegekend op voorwaarde dat de werknemer een vergoeding van de RVA geniet in het kader van deze tijdskredieten.Deze 2 bedragen zijn onderworpen aan indexering.Art. 7. Verlenging van de bestaande SWT-stelsels en afwijking per stelsel wat de beschikbaarheid ten aanzien van de wettelijke bepalingen betreft.Art. 8. Hospitalisatieverzekering : Terugbetaling van de franchise ten belope van maximaal 75 EUR voor de actieve werknemers en de gezinsleden die recht hebben op de hospitalisatieverzekering.Art. 9. Opleidingen"Een individueel recht op opleiding wordt ingevoerd volgens het volgende groeitraject :- vanaf 1 januari 2023 : 2 dagen per jaar;- vanaf 1 januari 2025 : 3 dagen per jaar;- vanaf 1 januari 2027 : 4 dagen per jaar;- vanaf 1 januari 2029 : 5 dagen per jaar.De opleidingsinspanning van gemiddeld 4 dagen per werknemer en per jaar zal worden voortgezet tijdens dit groeitraject.Voor het individueel recht op opleiding en voor de collectieve opleidingsinspanning, wordt onder "opleiding" verstaan : elke formele of informele opleiding, met inbegrip van de opleidingen over de materies betreffende het welzijn, die aan bod komen in de Jobsdeal.".Art. 10. Collectieve arbeidsovereenkomst nr. 104 : 1 dag "verlof" per jaar wordt toegekend vanaf 45 jaar.Art. 11. Sociale vredeDe sociale vrede zal worden gewaarborgd tijdens de duur van deze collectieve arbeidsovereenkomst, namelijk tot 31 december 2024. Bijgevolg zal geen enkele complementaire of aanvullende eis, van algemene of collectieve aard, die de verbintenissen van de ondernemingen waarin voorzien is door deze collectieve arbeidsovereenkomst zou uitbreiden of wijzigen op welk niveau dan ook worden ingediend of ondersteund.Bij schending van de sociale vrede zullen de vakbondsvrijgestelden en -afgevaardigden interveniëren en zo nodig een verzoeningsbureau inschakelen.Art. 12. Duur § 1. Deze overeenkomst treedt in werking op 1 januari 2023 en is van toepassing tot 31 december 2024. § 2. In afwijking van § 1 is artikel 1 van toepassing van 1 januari 2023 tot 30 juni 2025, en artikel 7 is van toepassing van 1 juli 2023 tot 30 juni 2025.Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk,D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de programmawet (I) van 24 december 2002, artikel 270, § 1 vervangen bij artikel 66 van de wet van 23 december 2005, gewijzigd bij artikel 34 van de wet van 13 december 2006, bij artikel 75 van de wet van 6 mei 2009, bij artikel 39 van de wet van 23 december 2009 en bij artikel 102 van de wet van 17 juli 2015;Gelet op het koninklijk besluit van 20 mei 2021 tot benoeming van sommige leden van de raad van bestuur van het Federaal Kenniscentrum voor de Gezondheidszorg zoals laatst gewijzigd door het koninklijk besluit van 29 mars 2025;Gelet op het voorstel van 1 april 2025 van het Intermutualistisch Agentschap om de heer Patrick Verertbruggen te laten vervangen door de heer Pieter Vandenbroucke als effectief lid binnen de raad van bestuur van het Federaal Kenniscentrum voor de Gezondheidszorg;Gelet op artikel 8 van de wet van 15 december 2013 houdende diverse bepalingen inzake administratieve vereenvoudiging, is dit besluit vrijgesteld van een regelgevingsimpactanalyse omdat het een formele beslissing betreft;Op de voordracht van de Minister van Sociale Zaken en Volksgezondheid;Hebben Wij besloten en besluiten Wij :Artikel 1. Wordt benoemd tot effectief lid binnen de raad van bestuur van het Federaal Kenniscentrum voor de Gezondheidszorg, op voordracht van het Intermutualistisch Agentschap en ter vervanging van de heer Patrick Verertbruggen waarvan hij het mandaat zal beëindigen:- De heer Vandenbroucke, Pieter, wonende te Wilsele.Art. 2. In artikel 1 van het koninklijk besluit van 20 mei 2021 tot benoeming van sommige leden van de raad van bestuur van het Federaal Kenniscentrum voor de Gezondheidszorg zoals laatst gewijzigd door het koninklijk besluit van 29 maart 2025 worden de woorden :« De heer Verertbruggen, Patrick, wonende te Ternat » vervangen door de woorden « De heer Vandenbroucke, Pieter, wonende te Wilsele »;Art. 3. In artikel 2 van het koninklijk besluit van 20 mei 2021 tot benoeming van sommige leden van de raad van bestuur van het Federaal Kenniscentrum voor de Gezondheidszorg zoals laatst gewijzigd door het koninklijk besluit van 29 maart 2025 worden de woorden:« Patrick Verertbruggen » vervangen door de woorden « Pieter Vandenbroucke »;Art. 4. Dit besluit treedt in werking op 22 april 2025.Art. 5. De minister bevoegd voor Sociale Zaken en Volksgezondheid is belast met de uitvoering van dit besluitGegeven te Brussel, 12 mei 2025.FILIPVan Koningswege :De Minister van Sociale Zaken en Volksgezondheid,F. VANDENBROUCKE 
 </t>
         </is>
       </c>
@@ -1289,28 +1287,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025002528</t>
+          <t>2025003972</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>12 mei 2025</t>
+          <t>26 mei 2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 15 december 2023, gesloten in het Paritair Comité voor het tuinbouwbedrijf, betreffende de vaststelling van de sectorale minimumloonschalen voor de bedienden op basis van beroepservaring (1)</t>
+          <t>12 mei 2025. - Koninklijk besluit houdende goedkeuring van de wijzigingen van het reglement betreffende de organisatie van en het toezicht op de boekhouding van de notarissen goedgekeurd bij koninklijk besluit van 3 juni 2022</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-12&amp;numac_search=2025002528&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025002528=26&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-26&amp;numac_search=2025003972&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003972=26&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor het tuinbouwbedrijf;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 15 december 2023, gesloten in het Paritair Comité voor het tuinbouwbedrijf, betreffende de vaststelling van de sectorale minimumloonschalen voor de bedienden op basis van beroepservaring.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het tuinbouwbedrijfCollectieve arbeidsovereenkomst van 15 december 2023Vaststelling van de sectorale minimumloonschalen voor de bedienden op basis van beroepservaring (Overeenkomst geregistreerd op 25 januari 2024 onder het nummer 185558/CO/145)PreambuleBetreft de aanpassing van de lonen en de premies aan de indexering met 1,83 pct. vanaf 1 januari 2024.Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de bedienden van de ondernemingen die ressorteren onder het Paritair Comité voor het tuinbouwbedrijf. § 2. Onder "bedienden" wordt verstaan : de bedienden zonder onderscheid naar gender.Art. 2.  § 1. De minimummaandlonen per klasse van de voltijds tewerkgestelde bedienden, zoals bepaald in artikel 2 van de collectieve arbeidsovereenkomst van 24 mei 2023 betreffende de beroeps indeling, wordt vastgesteld op basis van het aantal jaren beroepservaring :- volgens schaal I, opgenomen in bijlage 1 a van deze collectieve arbeidsovereenkomst vanaf het eerste jaar van de indiensttreding;- volgens schaal II, opgenomen in bijlage 1 b van deze collectieve arbeidsovereenkomst voor de bedienden die minstens 1 jaar werkzaam zijn in dezelfde onderneming.De bedragen vermeld in de minimumloonschalen I en II opgenomen in bijlagen l a, 1 b, 1 c en 1 d van deze collectieve arbeidsovereenkomst worden geïndexeerd volgens de modaliteiten voorzien in de collectieve arbeidsovereenkomst van 15 december 2023 betreffende de indexering van de lonen, gesloten in het Paritair Comité voor het tuinbouwbedrijf.De aanvangslonen die in de minimumloonschaal I voor alle functieklassen worden vastgelegd stemmen overeen met 0 jaar beroepservaring.De overgang van de ene loonschaal naar de andere gebeurt in de maand die volgt op die waarin de bediende aan de toekenningsvoorwaarde voldoet.De toepassing van de loonschalen heeft alleen betrekking op de minimumlonen van de bedienden die ook aan de toekenningsvoorwaarden voldoen; ze kan geen invloed hebben op de lonen van de bedienden die boven deze minima worden betaald. § 2. De deeltijdse bedienden moeten voor een gelijk werk of voor een werk van gelijke waarde, in verhouding, hetzelfde loon ontvangen als een voltijdse bediende.Art. 3.  § 1. Onder "beroepservaring" wordt verstaan : de periode van effectieve en gelijkgestelde beroepsprestaties bij de werkgever waar de bediende in dienst is, evenals de periodes van effectieve en gelijkgestelde beroepsprestaties die de bediende vóór de indiensttreding verworven heeft als werknemer, zelfstandige of als statutair ambtenaar. § 2. Voor de bepaling van de periode van beroepservaring worden deeltijdse prestaties gelijkgesteld met voltijdse prestaties. § 3. De hierna bepaalde periodes van volledige schorsing van de uitvoering van de arbeidsovereenkomst worden met effectieve beroepsprestaties gelijkgesteld :- de periodes van arbeidsongeschiktheid wegens arbeidsongeval of beroepsziekte;- de periodes van arbeidsongeschiktheid wegens ziekte of ongeval, anders dan arbeidsongeval, met een maximum van 3 jaar;- de periodes van voltijds tijdskrediet om thematische redenen, zoals voorzien in artikel 4 van de collectieve arbeidsovereenkomst nr. 103 en voor zover RVA-uitkeringen worden toegekend en thematisch verlof (ouderschapsverlof, bijstand en verzorging van een zwaar ziek gezins- of familielid, palliatieve zorgen), met een maximum van 3 jaar;- de periodes van voltijds tijdskrediet zonder thematische redenen voor zover RVA-uitkeringen worden toegekend, met een maximum van 1 jaar;- de periodes van zwangerschapsverlof;- de periodes van profylactisch verlof;- de periodes van vaderschapsverlof;- de periodes in toepassing van de crisismaatregelen zoals voorzien door de wet van 19 juli 2009;- de overige periodes van volledige schorsing van de arbeidsovereenkomst zoals voorzien in de wet van 3 juli 1978, welke gepaard gaan met behoud van loon.Volgende periodes buiten schorsing van de arbeidsovereenkomst worden gelijkgesteld met effectieve beroepsprestaties :- de periodes van uitkeringsgerechtigde werkloosheid met een maximum van 1 jaar indien de uitkeringsgerechtigde werkzoekende een beroepservaring heeft van minder dan 15 jaar en een maximum van 2 jaar indien de uitkeringsgerechtigde werkloze een beroepservaring heeft van meer dan 15 jaar. § 4. De beroepservaring en anciënniteit vóór 18 jaar, waarvoor het jongerenbarema geldt zoals bepaald in artikel 6, wordt meegeteld bij de start van het ervaringsbarema zoals bepaald in 2.Commentaar :Voor de aanrekening van de beroepservaring mag geen enkele gelijkstellingsperiode gecumuleerd worden met een periode van beroepsactiviteit of met een andere gelijkstellingsperiode.Art. 4. Bedienden die op 31 december 2022 in dienst waren van een werkgever die ressorteerde onder Aanvullend Paritair Comité de bedienden en op 1 januari 2023 in dienst zijn bij een werkgever die ressorteert onder Paritair Comité voor het tuinbouwbedrijf, nemen hun aantal beroepservaring mee.Art. 5.  § 1. Op het ogenblik van de indiensttreding wordt het baremaloon van de bediende vastgesteld in overeenstemming met het beroepservaringsbarema van de klasse waartoe zijn functie behoort en op basis van de beroepservaring zoals bepaald in artikelen 2, 3 en 4 hiervoor.De som van de beroepservaringsperioden en gelijkgestelde perioden wordt uitgedrukt in jaren en maanden.De eerste baremieke verhoging na de indiensttreding zal gebeuren op de eerste dag van de maand nadat de bediende het eerstvolgende jaar beroepservaring heeft bereikt. § 2. Wanneer de periode van beroepservaring met 12 maanden is toegenomen sinds de laatste baremieke verhoging, stijgt het baremaloon van de bediende met een beroepservaringsjaar volgens de loonbaremaschaal op de eerste dag van de daaropvolgende maand. § 3. Bij een nieuwe aanwerving zal de kandidaat aan de werkgever alle noodzakelijke informatie overmaken zodat deze het loon kan bepalen dat overeenkomt met de bepalingen van deze collectieve arbeidsovereenkomst.Art. 6.  § 1. Teneinde de inschakeling van jongeren in het arbeidsproces te bevorderen, wordt een specifiek jongerenbarema voorzien voor de volgende bedienden :- 80 pct. van het loon aan 0 jaar ervaring voor de jongere bedienden van 17 jaar;- 75 pct. van het loon aan 0 jaar ervaring voor de jongere bedienden van 16 jaar. § 2. Voor bedienden met een studentenovereenkomst zoals bepaald in titel VII van de wet van 3 juli 1978 betreffende de arbeidsovereenkomsten wordt het volgende barema voorzien (bedragen van toepassing vanaf 1 januari 2024) :Klassen A en B voor de leeftijd van 16 en 17 jaar :- Klasse A :- 16 jaar : 1 346,86 EUR;- 17 jaar : 1 522,72 EUR.- Klasse B :- 16 jaar : 1 400,37 EUR;- 17 jaar : 1 584,20 EUR.Art. 7.  § 1. Geranten en aan-huis-verkopersTwee gevallen kunnen zich voordoen :- Zij genieten van een vast loon;- Hun loon omvat commissielonen welke zijn vastgesteld overeenkomstig het bedrag van de handelsomzet of volgens andere maatstaven.In beide gevallen, en voor zover zij fulltime werkzaam zijn, moet hun loon ten minste gelijk zijn aan het loon voor een bediende met niveau "0" beroepservaring volgens de schaal voor klasse C. § 2. HandelsvertegenwoordigersVoor de handelsvertegenwoordigers met minder dan 4 jaren beroepservaring, is het loon ten minste gelijk aan de schaalminima volgens beroepservaring van klasse C.Voor de handelsvertegenwoordigers met 4 of meer jaren beroepservaring, is het loon ten minste gelijk aan de schaalminima volgens beroepservaring van klasse D.Gedurende de eerste 6 maanden vanaf de aanvang van de arbeidsovereenkomst echter is het maandelijks minimumloon, ingevolge voorgaande alinea's, ten minste gelijk aan het loon vastgesteld voor een bediende met beroepservaring niveau "0" in klasse A.Dit minimumloon wordt maandelijks als voorschot op het commissieloon betaald en de eindrekening wordt jaarlijks vastgesteld op basis van de lonen berekend op een gemiddelde van 12 maanden.Art. 8. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van 1 januari 2024 en wordt gesloten voor een onbepaalde tijd. Zij vervangt de collectieve arbeidsovereenkomst van 24 mei 2023, geregistreerd onder het nr. 180775/CO/145.Elk van de contracterende partijen kan ze opzeggen mits een opzeggingstermijn van drie maanden, te betekenen bij een ter post aangetekende brief aan de voorzitter van het Paritair Comité voor het tuinbouwbedrijf.Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025.De Minister van Werk,D. CLARINVALBijlage 1 aan de collectieve arbeidsovereenkomst van 15 december 2023, gesloten in het Paritair Comité voor het tuinbouwbedrijf, betreffende de vaststelling van de sectorale minimumloonschalen voor de bedienden op basis van beroepservaringBijlage 1 a. Barema's gebaseerd op beroepservaringDit barema is van toepassing vanaf 1 januari 2024.  </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 16 maart 1803 op het notarisambt, artikel 91, tweede lid, ingevoegd bij de wet van 4 mei 1999 en gewijzigd en vernummerd bij de wet van 22 november 2022;Overwegende de wet van 16 maart 1803 op het notarisambt, artikel 91, eerste lid, 5°,  tweede streepje, ingevoegd bij de wet van 4 mei 1999 en gewijzigd bij de wet van 6 juli 2017;Overwegende het koninklijk besluit van 3 juni 2022 houdende goedkeuring van het reglement betreffende de organisatie van en het toezicht op de boekhouding van de notarissen vastgesteld door de Nationale Kamer van notarissen;Overwegende het koninklijk besluit van 21 april 2024 houdende goedkeuring van de wijziging van het reglement betreffende de organisatie van en het toezicht op de boekhouding van de notarissen goedgekeurd bij koninklijk besluit van 3 juni 2022;Op de voordracht van de Minister van Justitie,Hebben Wij besloten en besluiten Wij :Artikel 1. De volgende wijzigingen van het bij koninklijk besluit van 3 juni 2022 goedgekeurde reglement betreffende de organisatie van en het toezicht op de boekhouding van de notarissen vastgesteld door de Nationale Kamer van notarissen, dat werd aangenomen op 24 oktober 2024 door de Nationale Kamer van notarissen, worden goedgekeurd en hebben bindende kracht:1°  in artikel 3, 21°,  worden de woorden "die beschikken over een opeisbare schuldvordering" opgeheven;2°  in artikel 22, worden de woorden "die beschikken over een opeisbare schuldvordering" opgeheven en worden de woorden "en de aan de cliënten en bovenvermelde schuldeisers verschuldigde sommen" vervangen door de woorden ", de aan de cliënten en de schuldeisers verschuldigde sommen en de boekhoudkundig verantwoord aan te leggen provisies".Art. 2. De minister bevoegd voor Justitie is belast met de uitvoering van dit besluit.Gegeven te Brussel, 12 mei 2025.FILIPVan Koningswege :De Minister van Justitie,A. VERLINDEN 
+</t>
         </is>
       </c>
     </row>
@@ -1320,28 +1319,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025000797</t>
+          <t>2025200868</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12 mei 2025</t>
+          <t>15 mei 2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 18 juni 2024, gesloten in het Paritair Subcomité voor de edele metalen, betreffende de wijziging en coördinatie van het sociaal sectoraal pensioenstelsel (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit tot vaststelling, voor het jaar 2025, van de dotaties bedoeld in Titel IV en in Titel VII van het koninklijk besluit van 18 juli 2002 houdende maatregelen met het oog op de bevordering van de tewerkstelling in de non-profit sector</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-12&amp;numac_search=2025000797&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025000797=27&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-15&amp;numac_search=2025200868&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200868=27&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Subcomité voor de edele metalen;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 18 juni 2024, gesloten in het Paritair Subcomité voor de edele metalen, betreffende de wijziging en coördinatie van het sociaal sectoraal pensioenstelsel.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Subcomité voor de edele metalenCollectieve arbeidsovereenkomst van 18 juni 2024Wijziging en coördinatie van het sociaal sectoraal pensioenstelsel (Overeenkomst geregistreerd op 25 juli 2024 onder het nummer 189019/CO/149.03)HOOFDSTUK I. - ToepassingsgebiedArtikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en arbeiders van de ondernemingen welke ressorteren onder het Paritair Subcomité 149.03 voor de edele metalen. § 2. Worden uitgesloten van het toepassingsgebied van deze overeenkomst, de buiten België gevestigde werkgevers waarvan de werknemers in België gedetacheerd worden in de zin van de bepalingen van de verordening (EEG) nr. 1408/71 van de Raad of de verordening (EG) nr. 883/2004 van het Europees Parlement en de Raad. § 3. Onder "arbeiders" wordt verstaan : de mannelijke en vrouwelijke arbeiders.HOOFDSTUK II. - VoorwerpArt. 2.  § 1. Deze collectieve arbeidsovereenkomst heeft tot doel om vanaf 1 januari 2025 de collectieve arbeidsovereenkomst van 20 december 2023 tot wijziging en coördinatie van het sociaal sectoraal pensioenstelsel en overgang van solidariteitsinstelling met overdracht van het solidariteitsfonds, geregistreerd onder het nummer 185556/CO/149.03, te vervangen. § 2. De begrippen die in het vervolg van deze collectieve arbeidsovereenkomst opgenomen zijn, moeten worden opgevat in hun betekenis zoals bepaald in de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid (Belgisch Staatsblad van 15 mei 2003, ed. 2, p. 26407, erratum Belgisch Staatsblad van 26 mei 2003) en haar uitvoeringsbesluiten. Deze wet zal in het vervolg van deze overeenkomst "W.A.P." worden genoemd.HOOFDSTUK III. - Aanduiding van de InrichterArt. 3.  § 1. Overeenkomstig artikel 3, § 1, 5°  van de W.A.P. werd het fonds voor bestaanszekerheid, genaamd "Fonds voor bestaanszekerheid - Edele Metalen" via de collectieve arbeidsovereenkomst van 22 mei 2014 (122030/CO/149.03) door de representatieve organisaties van het voormelde Paritair Subcomité aangeduid als Inrichter van dit sociaal sectoraal pensioenstelsel. § 2. Deze aanduiding blijft uiteraard gelden in het kader van deze collectieve arbeidsovereenkomst van 18 juni 2024 tot wijziging en coördinatie van het sociaal sectoraal pensioenstelsel. § 3. Indien de representatieve organisaties vertegenwoordigd in het paritair subcomité 149.03 zouden beslissen dat het "Fonds voor bestaanszekerheid - Edele Metalen" niet langer zal optreden als de Inrichter van dit sociaal sectoraal pensioenstelsel dan duiden zij een andere inrichter aan die alle rechten en verplichtingen overneemt van het "Fonds voor bestaanszekerheid - Edele Metalen" die betrekking hebben op de inrichting van dit sociaal sectoraal pensioenstelsel.HOOFDSTUK IV. - AansluitingsvoorwaardenArt. 4.  § 1. Alle arbeiders die op of na 1 januari 2015 met de werkgevers zoals bedoeld in artikel 1, § 1 van deze overeenkomst verbonden zijn of waren via een arbeidsovereenkomst (ongeacht de aard van arbeidsovereenkomst), worden ambtshalve aangesloten bij dit sociaal sectoraal pensioenplan. In de praktijk gaat het om de werklieden aangegeven onder de werknemerskengetallen 015, 024 en 027. § 2. Worden echter niet aangesloten bij dit pensioenplan :-de personen tewerkgesteld via een overeenkomst van studentenarbeid;- de personen tewerkgesteld via een overeenkomst voor uitzendarbeid, zoals geregeld door hoofdstuk II van de wet van 24 juli 1987 betreffende de tijdelijke arbeid, de uitzendarbeid en het ter beschikking stellen van de werknemers ten behoeve van gebruikers;- de leerlingen;- de personen tewerkgesteld met een arbeidsovereenkomst gesloten in het kader van een speciaal met steun van de overheid gevoerd opleidings-, arbeidsinspannings- en omscholingsprogramma;- de personen die effectief hun wettelijk (vervroegd) pensioen hebben opgenomen vanaf 1 januari 2016, maar vervolgens als gepensioneerde verder of opnieuw tewerkgesteld worden met een arbeidsovereenkomst afgesloten met hun werkgevers zoals bedoeld in artikel 1, § 1 van deze overeenkomst.HOOFDSTUK V. - Bijdrage vanaf 1 januari 2025 tot en met 30 juni 2025Art. 5.  § 1. In het voordeel van de in artikel 4 bedoelde personen zullen er maandelijks door de Inrichter één of meerdere bijdragen gestort worden ter financiering van het sociaal sectoraal pensioenstelsel ter aanvulling van de wettelijke pensioenregeling. § 2. De totale jaarlijkse brutobijdrage per aangeslotene bij het sociaal sectoraal pensioenstelsel bedraagt vanaf 1 januari 2025 en tot en met 30 juni 2025 1,15 pct. van diens jaarlijks brutoloon waarop R.S.Z.-inhoudingen worden gedaan. § 3. De totale jaarlijkse brutobijdrage per aangeslotene bij het sociaal sectoraal pensioenstelsel wordt verminderd met 4,5 pct. beheerskosten, aangerekend door de Inrichter, wat resulteert in een totale jaarlijkse nettobijdrage per aangeslotene van 1,10 pct. van diens jaarlijks brutoloon waarop R.S.Z.-inhoudingen worden gedaan. § 4. Deze nettobijdrage wordt als volgt verdeeld : 1,05 pct. wordt aangewend ter financiering van individuele pensioenrechten in hoofde van de bij het sociaal sectoraal stelsel aangeslotenen en de overige 0,05 pct. wordt gebruikt ter financiering van een solidariteitstoezegging zoals bedoeld in titel II, hoofdstuk 9 van de W.A.P. § 5. Dit resulteert, na vermeerdering van de nettobijdrage met 0,09 pct. ter dekking van de verschuldigde, bijzondere bijdrage van 8,86 pct., in een globale bijdrage van 1,24 pct. § 6. Voor bepaalde aangeslotenen bij het sociaal sectoraal pensioenstelsel, stort de Inrichter tijdens het derde kwartaal van 2019 vanuit haar reserves opgebouwd door bijdragen die in het verleden werden geïnd in het kader van de aanvullende sociale voordelen die door de Inrichter worden toegekend, een forfaitair bedrag van 300 EUR voor elke arbeider die actief was tijdens het eerste kwartaal van 2019 overeenkomstig artikel 2.23 van het pensioenreglement, én die op 1 oktober 2019 verworven reserves heeft op zijn individuele rekening bij de pensioeninstelling. Dit forfaitair bedrag wordt op datum van 1 oktober 2019 ingeschreven op de individuele rekening van de in aanmerking komende arbeider. § 7. De Inrichter stort, vanaf 2022, een jaarlijkse, bijkomende bijdrage uit zijn reserves aan SEFOPLUS OFP in het Afzonderlijk Vermogen Solidariteit SEFOCAM-sectoren om mogelijke tekorten te dekken in de financiering van de solidariteitsprestaties op basis van de hoger in § 4 vermelde 0,04 pct. van de nettobijdrage. De hoogte van deze jaarlijkse bijkomende bijdrage wordt berekend door SEFOPLUS OFP op basis van inschattingen die enerzijds rekening houden met de effectieve solidariteitsprestaties van de voorgaande jaren (statistieken) en anderzijds met mogelijke toekomstige evoluties en/of fluctuaties. § 8. De beheerskosten van 4,5 pct. evenals de bijzondere R.S.Z-bijdrage van 8,86 pct., verschuldigd door de Inrichter ingevolge de toepassing van artikel 5, § 6 en § 7, zullen door de Inrichter worden voldaan ten aanzien van respectievelijk de pensioeninstelling en de Rijksdienst voor de Sociale Zekerheid.HOOFDSTUK VI. - Bijdrage vanaf 1 juli 2025Art. 6.  § 1. In het voordeel van de in artikel 4 bedoelde personen zullen er maandelijks door de Inrichter één of meerdere bijdragen gestort worden ter financiering van het sociaal sectoraal pensioenstelsel ter aanvulling van de wettelijke pensioenregeling. § 2. De totale jaarlijkse brutobijdrage per aangeslotene bij het sociaal sectoraal pensioenstelsel bedraagt vanaf 1 juli 2025 en voor onbepaalde duur 1,05 pct. van diens jaarlijks brutoloon waarop R.S.Z.-inhoudingen worden gedaan. § 3. De totale jaarlijkse brutobijdrage per aangeslotene bij het sociaal sectoraal pensioenstelsel wordt verminderd met 4,5 pct. beheerskosten, aangerekend door de Inrichter, wat resulteert in een totale jaarlijkse nettobijdrage per aangeslotene van 1,00 pct. van diens jaarlijks brutoloon waarop R.S.Z.-inhoudingen worden gedaan. § 4. Deze nettobijdrage wordt als volgt verdeeld : 0,96 pct. wordt aangewend ter financiering van individuele pensioenrechten in hoofde van de bij het sociaal sectoraal stelsel aangeslotenen en de overige 0,04 pct. wordt gebruikt ter financiering van een solidariteitstoezegging zoals bedoeld in titel II, hoofdstuk 9 van de W.A.P. § 5. Dit resulteert, na vermeerdering van de nettobijdrage met 0,09 pct. ter dekking van de verschuldigde, bijzondere bijdrage van 8,86 pct., in een globale bijdrage van 1,14 pct. § 6. Voor bepaalde aangeslotenen bij het sociaal sectoraal pensioenstelsel, stort de Inrichter tijdens het derde kwartaal van 2019 vanuit haar reserves opgebouwd door bijdragen die in het verleden werden geïnd in het kader van de aanvullende sociale voordelen die door de Inrichter worden toegekend, een forfaitair bedrag van 300 EUR voor elke arbeider die actief was tijdens het eerste kwartaal van 2019 overeenkomstig artikel 2.23 van het pensioenreglement, én die op 1 oktober 2019 verworven reserves heeft op zijn individuele rekening bij de pensioeninstelling. Dit forfaitair bedrag wordt op datum van 1 oktober 2019 ingeschreven op de individuele rekening van de in aanmerking komende arbeider. § 7. De Inrichter stort, vanaf 2022, een jaarlijkse, bijkomende bijdrage uit zijn reserves aan SEFOPLUS OFP in het Afzonderlijk Vermogen Solidariteit SEFOCAM-sectoren om mogelijke tekorten te dekken in de financiering van de solidariteitsprestaties op basis van de hoger in § 4 vermelde 0,04 pct. van de nettobijdrage. De hoogte van deze jaarlijkse bijkomende bijdrage wordt berekend door SEFOPLUS OFP op basis van inschattingen die enerzijds rekening houden met de effectieve solidariteitsprestaties van de voorgaande jaren (statistieken) en anderzijds met mogelijke toekomstige evoluties en/of fluctuaties. § 8. De beheerskosten van 4,5 pct. evenals de bijzondere R.S.Z-bijdrage van 8,86 pct., verschuldigd door de Inrichter ingevolge de toepassing van artikel 5, § 6 en § 7, zullen door de Inrichter worden voldaan ten aanzien van respectievelijk de pensioeninstelling en de Rijksdienst voor de Sociale Zekerheid.HOOFDSTUK VII. - Pensioentoezegging : overgang van pensioeninstelling met collectieve overdracht van verworven reservesArt. 7.  § 1. Tot 31 december 2018 werd het financieel, boekhoudkundig, actuarieel en administratief beheer van de Pensioentoezegging door de Inrichter toevertrouwd aan Belfius Verzekeringen n.v., erkend door de Nationale Bank van België onder nummer 37, met maatschappelijke zetel te 1210 Brussel, Karel Rogierplein 11, die 50 pct. van haar risico herverzekerde via KBC Verzekeringen n.v., erkend door de Nationale Bank van België onder nummer 14, met maatschappelijke zetel te 3000 Leuven, Professor Roger Van Overstraetenplein 2.Met ingang van 1 januari 2019 werd het financieel, boekhoudkundige, actuarieel en administratief beheer overgedragen aan SEFOPLUS OFP, de multi-sectorale instelling voor bedrijfspensioenvoorziening (IBP), toegelaten door de FSMA op 19 november 2018 met identificatienummer 50.624, met maatschappelijke zetel te 1120 Brussel, Marlylaan 15, bus 8.De raad van bestuur van SEFOPLUS OFP is in overeenstemming met artikel 41, § 1, 1°  van de W.A.P. paritair samengesteld. § 2. De overgang van pensioeninstelling van Belfius Verzekeringen n.v. naar SEFOPLUS OFP ging gepaard met een collectieve overdracht van de reserves in de zin van artikel 34 van de W.A.P. Deze collectieve overdracht werd geregeld in de overdrachtsovereenkomst tussen de deelnemende sectorale inrichters, SEFOPLUS OFP en Belfius Verzekeringen n.v. In het kader van deze collectieve overdracht werd geen enkele vergoeding of verlies van winstdelingen ten laste gelegd van de aangeslotenen, of van de op het ogenblik van de overdracht verworven reserves afgetrokken. § 3. De regels van de pensioentoezegging zijn vastgelegd in een pensioenreglement dat wordt opgenomen als bijlage bij deze collectieve arbeidsovereenkomst waarvan het integraal deel uitmaakt. Het pensioenreglement zal door SEFOPLUS OFP, via de v.z.w. SEFOCAM, aan de aangeslotenen ter beschikking worden gesteld op hun eenvoudig verzoek. § 4. Onder de naam "transparantieverslag" stelt SEFOPLUS OFP jaarlijks een verslag op over het door haar gevoerde beheer van de pensioentoezegging.HOOFDSTUK VIII. - Uitbetaling van de voordelenArt. 8. De procedure, de modaliteiten en de vorm van de uitbetaling van de voordelen worden beschreven in artikel 7 tot en met artikel 14 van het bijgevoegde pensioenreglement.HOOFDSTUK IX. - Solidariteitstoezegging - Overgang van solidariteitsinstelling met overdracht van solidariteitsfondsArt. 9.  § 1. Vanaf 1 januari 2015 wordt een gedeelte van de globale nettobijdrage, zoals vastgelegd in artikel 5 en 6 van deze overeenkomst (in overeenstemming met artikel 43 van de W.A.P.) aangewend ter financiering van de solidariteitstoezegging die deel uitmaakt van het sociaal sectoraal pensioenstelsel. § 2. Deze bijdrage wordt aangewend ter financiering van de solidariteitsprestaties, waaronder in het bijzonder de financiering van de opbouw van de pensioentoezegging gedurende bepaalde periodes van inactiviteit en de vergoeding van inkomstenverlies in bepaalde gevallen. De exacte inhoud van deze solidariteitstoezegging alsook de financieringswijze ervan, werd uitgewerkt in een solidariteitsreglement (zie hierna in artikel 9). § 3. Het beheer van de solidariteitstoezegging werd door de Inrichter tot en met 31 december 2021 toevertrouwd aan Belfius Verzekeringen n.v., afgekort "Belins n.v.", erkend door de Nationale Bank van België onder nummer 37, met maatschappelijke zetel te 1210 Brussel, Karel Rogierplein 11.Met ingang van 1 januari 2022 werd het beheer van de solidariteitstoezegging door de Inrichter toevertrouwd aan SEFOPLUS OFP, de multi-sectorale instelling voor bedrijfspensioenvoorziening (IBP), toegelaten door de FSMA op 19 november 2018 met identificatienummer 50.624, met maatschappelijke zetel te 1120 Brussel, Marlylaan 15, bus 8, die reeds sinds 1 januari 2019 optreedt als pensioeninstelling. § 4. De overgang van solidariteitsinstelling van Belfius Verzekeringen n.v. naar SEFOPLUS OFP ging gepaard met de overdracht van het Sefocam solidariteitsfonds (collectieve solidariteits-reserves) van Belfius Verzekeringen n.v. naar SEFOPLUS OFP. Deze overdracht van het Sefocam solidariteitsfonds werd geregeld in de overdrachtsovereenkomst tussen de deelnemende sectorale inrichters, SEFOPLUS OFP, v.z.w. SEFOCAM en Belfius Verzekeringen n.v. § 5. SEFOPLUS OFP zal een "transparantieverslag" opstellen en zal dit op haar website ter beschikking stellen. Het verslag betreft de elementen zoals beschreven in de W.A.P.HOOFDSTUK X. - SolidariteitsreglementArt. 10.  § 1. Het solidariteitsreglement expliciteert de modaliteiten van de solidariteitstoezegging en werd als bijlage opgenomen bij deze collectieve arbeidsovereenkomst waarvan het integraal deel uitmaakt. § 2. Het solidariteitsreglement zal door de Inrichter, via de v.z.w. SEFOCAM, op hun eenvoudig verzoek ter beschikking worden gesteld aan de bij dit pensioenstelsel aangesloten werknemers.HOOFDSTUK XI. - Procedure in geval van uittreding van een arbeiderArt. 11. De procedure van uittreding uit het sectoraal pensioenstelsel wordt geregeld door artikel 18 van het hierna bijgevoegde pensioenreglement.HOOFDSTUK XII. - InningsmodaliteitenArt. 12.  § 1. Teneinde de bijdrage zoals voorzien in artikel 5, § 2 en 6, § 2 van deze overeenkomst in te vorderen zal door de Rijksdienst voor Sociale Zekerheid, overeenkomstig artikel 7 van de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid een voorlopige bijdrage worden geïnd. Deze voorlopige bijdrage zal na de terbeschikkingstelling ervan aan de Inrichter door laatstgenoemde worden doorgestort aan :- de pensioeninstelling : het gedeelte van de nettobijdrage die wordt aangewend ter financiering van de individuele pensioenrechten, alsook een gedeelte van de ingehouden beheerskosten overeenkomstig artikelen 5 en 6 van deze overeenkomst, en- de solidariteitsinstelling : het gedeelte van de nettobijdrage die wordt aangewend ter financiering van de solidariteitstoezegging, alsook een gedeelte van de ingehouden beheerskosten overeenkomstig artikelen 5 en 6 van deze overeenkomst § 2. Van zodra de Inrichter, via de v.z.w. SEFOCAM, over definitieve loongegevens beschikt, zal de voorlopige bijdrage worden vergeleken met de effectief verschuldigde bijdrage. Jaarlijks wordt een vergelijking gemaakt van de voorlopige bijdragen en de definitieve bijdragen voor alle voorafgaande jaren. Indien het totaal van de voorlopige bijdragen groter is dan het totaal van de effectief verschuldigde, definitieve bijdragen, wordt dit verschil op het eind van het jaar overgemaakt aan de Inrichter. In het omgekeerde geval, stort de Inrichter het bijdragetekort aan SEFOPLUS OFP. § 3. Vanaf 1 januari 2016 wordt er gebruik gemaakt van de gedifferentieerde R.S.Z.-inningstechniek waardoor de bijdrage voor het sociaal sectoraal aanvullend pensioenstelsel wordt afgescheiden van de basisbijdrage bestemd voor het fonds voor bestaanszekerheid. De bijzondere R.S.Z.-bijdrage van 8,86 pct. verschuldigd op de nettobijdrage zoals weergegeven in artikelen 5, § 4 en 6, § 4, wordt voldaan ten aanzien van de Rijksdienst voor de Sociale Zekerheid bij wijze van verhoging van deze nettobijdrage voor de pensioentoezegging zoals weergegeven in artikelen 5, § 4 en 6, § 4 en wordt door de R.S.Z. afgehouden aan de bron. Bijgevolg dient de bijzondere bijdrage van 8,86 pct. niet apart te worden aangegeven daar de globale bijdrage zoals weergegeven in artikelen 5, § 5 en 6, § 5 aangegeven moet worden onder bijdragecode 825 type "0". § 4. Het forfaitair bedrag in uitvoering van artikelen 5, § 6 en 6, § 6, evenals de beheerskosten vermeld onder artikelen 5, § 7 en 6, § 7, zal door de Inrichter rechtstreeks overgemaakt worden aan de pensioeninstelling zonder een beroep te doen op enig inningsmechanisme. Deze doorstorting geschiedt met valutadatum 1 oktober 2019. De bijzondere R.S.Z.-bijdrage van 8,86 pct. verschuldigd door de Inrichter ingevolge de toepassing van artikelen 5, § 7 en 6, § 7 zal door de Inrichter rechtstreeks worden voldaan ten aanzien van de Rijksdienst voor Sociale Zekerheid.HOOFDSTUK XIII. - Tijdelijke werkloosheid coronaArt. 13.  § 1. In het kader van de COVID-19 pandemie werd de wet van 7 mei 2020 houdende uitzonderlijke maatregelen in het kader van de COVID-19 pandemie inzake pensioenen, aanvullende pensioenen en andere voordelen inzake sociale zekerheid, ingevoerd (hierna "de wet van 7 mei 2020").Deze wet voorziet dat de pensioenopbouw en de overlijdensdekking van werknemers in een situatie van tijdelijke werkloosheid wegens overmacht of wegens economische redenen in het kader van de crisis van het coronavirus COVID-19 (hierna kortweg "tijdelijke werkloosheid corona") automatisch voortgezet worden gedurende de hele periode van tijdelijke werkloosheid corona, behoudens wanneer er wordt gekozen voor de opt-out mogelijkheid. § 2. Zoals voorzien in artikel 9, § 4 en § 5 van de wet van 7 mei 2020 heeft de Inrichter gekozen voor deze opt-out mogelijkheid. Hierdoor bouwen de aangeslotenen in tijdelijke werkloosheid corona geen pensioenrechten op onder dit sociaal sectoraal pensioenstelsel voor deze periode van tijdelijke werkloosheid corona, maar genieten zij tijdens deze periode wel verder van de overlijdensdekking. § 3. Overeenkomstig de wet van 7 mei 2020 wordt artikel 7 van het solidariteitsreglement (bijlage 2 van deze collectieve arbeidsovereenkomst) overeenkomstig aangepast.HOOFDSTUK XIV. - Tijdelijke werkloosheid energieArt. 14.  § 1. In het kader van de energiecrisis werd de wet van 30 oktober 2022 houdende tijdelijke ondersteuningsmaatregelen ten gevolge van de energiecrisis ingevoerd (hierna "de wet van 30 oktober 2022").Deze wet voorziet dat de pensioenopbouw en de overlijdensdekking van werknemers in een situatie van tijdelijke economische werkloosheid voor energie-intensieve bedrijven die operationele verliezen lijden wegens de stijging van aardgas- en elektriciteitskosten ten gevolge van de Russische militaire agressie tegen Oekraïne (hierna kortweg "tijdelijke werkloosheid energie") automatisch voortgezet worden gedurende de hele periode van tijdelijke werkloosheid energie, behoudens wanneer er wordt gekozen voor de opt-out mogelijkheid. § 2. Zoals voorzien in artikel 27, § 5 van de wet van 30 oktober 2022 heeft de Inrichter gekozen voor deze opt-out mogelijkheid. Concreet betekent dit dat de aanvullende pensioenopbouw zoals voorzien in het pensioenreglement wordt geschorst tijdens de volledige periode(s) van tijdelijke werkloosheid energie, maar genieten de aangeslotenen tijdens deze periode wel verder van de overlijdensdekking. Eveneens blijven de aangeslotenen genieten van de solidariteitstoezegging "pensioenopbouw gedurende periodes van economische werkloosheid", zoals opgenomen in artikel 7 van het solidariteitsreglement (bijlage 2 van deze collectieve arbeidsovereenkomst). § 3. Overeenkomstig de wet van 30 oktober 2022 wordt artikel 7 van het solidariteitsreglement (bijlage 2 van deze collectieve arbeidsovereenkomst) overeenkomstig aangepast.HOOFDSTUK XV. - Inwerkingtreding en opzeggingsmogelijkhedenArt. 15.  § 1. De collectieve arbeidsovereenkomst van 20 december 2023 tot wijziging en coördinatie van het sociaal sectoraal pensioenstelsel en overgang van solidariteitsinstelling met overdracht van solidariteitsfonds, geregistreerd onder het nummer 185556/CO/149.03, wordt vervangen vanaf 1 januari 2025. § 2. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van 1 januari 2025 en wordt gesloten voor onbepaalde duur. § 3. Zij kan worden beëindigd mits opzegging van zes maanden en wordt betekend per ter post aangetekend schrijven, gericht aan de voorzitter van het voormelde paritair subcomité. Voorafgaandelijk aan de opzegging van de collectieve arbeidsovereenkomst moet het paritair subcomité de beslissing nemen om het sectoraal pensioenstelsel op te heffen. Deze beslissing tot opheffing is enkel geldig wanneer zij wordt genomen in overeenstemming met de bepalingen in artikel 10, § 1, 3°  van de W.A.P.Art. 16. Ondertekenende partijen vragen dat deze collectieve arbeidsovereenkomst, inclusief de bijlagen, zo vlug mogelijk bij koninklijk besluit algemeen verbindend wordt verklaard.Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025.De Minister van Werk,D. CLARINVALBijlage 1 aan de collectieve arbeidsovereenkomst van 18 juni 2024, gesloten in het Paritair Subcomité voor de edele metalen, betreffende de wijziging en coördinatie van het sociaal sectoraal pensioenstelselAanvullend pensioenplan ten gunste van de arbeiders van het Paritair Subcomité voor de edele metalenSectoraal pensioenreglement afgesloten in uitvoering van artikel 7 van de collectieve arbeidsovereenkomst van 18 juni 2024HOOFDSTUK I. - VoorwerpArtikel 1.  § 1. Dit sectoraal pensioenreglement wordt opgemaakt in uitvoering van artikel 7 van de collectieve arbeidsovereenkomst van 18 juni 2024 tot wijziging en coördinatie van het sociaal sectoraal pensioenstelsel. § 2. Dit pensioenreglement beoogt het pensioenreglement dat als bijlage opgenomen was bij de collectieve arbeidsovereenkomst van 20 december 2023 aan te passen. § 3. Dit pensioenreglement bepaalt de rechten en de plichten van de Inrichter, de pensioensinstelling, de werkgevers die behoren tot het ressort van het voormelde paritair subcomité, de aangeslotenen en hun begunstigde(n). Tevens worden de aansluitingsvoorwaarden alsook de regels betreffende de uitvoering van de pensioentoezegging erin vastgelegd. De rechten van de aangeslotenen die gewezen werknemers zijn die na hun uittreding nog steeds actuele of uitgestelde rechten genieten, worden in de regel bepaald door het pensioenreglement zoals van toepassing op het ogenblik van hun uittreding, behoudens in geval van andersluidende wettelijke bepalingen. § 4. Dit pensioenreglement is gepubliceerd op de website van SEFOPLUS OFP (www.sefoplus.be) en is daar publiek raadpleegbaar. De aangeslotenen kunnen het pensioenreglement eveneens raadplegen via www.mypension.be. Bovendien zal de tekst van dit pensioenreglement door SEFOPLUS OFP, eventueel via de v.z.w. SEFOCAM ter beschikking worden gesteld aan de aangeslotene op diens eenvoudig verzoek.HOOFDSTUK II. - BegripsomschrijvingenArt. 2. 1. Het aanvullend pensioenDe kapitaalswaarde van het rust- en/of overlevingspensioen bij overlijden van de aangeslotene (vóór of na de pensionering), of de omzetting van deze in een levenslange lijfrente, toegekend op basis van de in dit pensioenreglement bepaalde verplichte stortingen, ter aanvulling van een krachtens een wettelijke socialezekerheidsregeling vastgesteld pensioen. Deze zal niet lager zijn dan de verworven reserves per 31 december 2018, op het moment van overgang van pensioeninstelling.2. De pensioentoezeggingDe toezegging van een aanvullend pensioen gedaan door de Inrichter aan de aangeslotenen en/of hun begunstigde(n) in uitvoering van de collectieve arbeidsovereenkomst van 22 mei 2014, alsook van de collectieve arbeidsovereenkomsten tot wijziging en coördinatie van het sociaal sectoraal pensioenstelsel.De toezegging die de Inrichter hier doet betreft een pensioentoezegging van het type vaste bijdragen zonder gewaarborgd rendement. De Inrichter garandeert dus enkel de betaling van de vaste bijdrage maar doet geen enkele belofte op het gebied van de kapitalisatie van de bijdragen. De Inrichter zal weliswaar voldoen aan de verplichtingen inzake de minimum rendementsgarantie conform de bepalingen van artikel 24 van de W.A.P.SEFOPLUS OFP gaat op haar beurt, als pensioeninstelling, een middelenverbintenis aan. Dit houdt in dat SEFOPLUS OFP er zich toe verbindt om de vaste bijdragen die door de Inrichter worden gestort zo goed en zo zorgvuldig mogelijk te beheren (als een goede huisvader) met het oog op de verwezenlijking van haar doel, zonder dat zij zich verbindt tot een resultaat. De bijdragen gestort door de Inrichter zullen worden gekapitaliseerd aan het netto financieel rendement zoals gedefinieerd in artikel 2.4 van dit pensioenreglement.3. Het pensioenstelselEen collectieve pensioentoezegging.4. Het netto financieel rendement (NFR)Het netto financieel rendement (afgekort als "NFR") van het Afzonderlijk Vermogen Pensioen PSC 149.03 wordt voor het afgelopen boekjaar berekend per 31 december van het boekjaar. Hiertoe worden de investeringskosten in mindering gebracht van het financieel rendement van het Afzonderlijk Vermogen Pensioen PSC 149.03.Vervolgens wordt voor de vaststelling van het netto financieel rendement dat wordt ingeschreven op de individuele rekeningen van de aangeslotenen rekening gehouden met de beschikbare vrije reserve van het Afzonderlijk Vermogen Pensioen PSC 149.03 die dient als buffer. Deze vrije reserve of buffer is gelijk aan het bedrag van de activa van het Afzonderlijk Vermogen Pensioen PSC 149.03 die volgend bedrag overstijgen :- de reserves ingeschreven op de individuele rekeningen van de aangeslotenen, in overeenstemming met dit pensioenreglement; hierbij wordt voor de berekening van deze reserves voor de periode gelegen tussen 1 januari en 31 december van het berekeningsjaar uitgegaan van een netto financieel rendement dat gelijk is aan de rentevoet van toepassing voor de berekening van de minimum rendementsgarantie conform artikel 24 van de W.A.P.;- desgevallend verhoogd met de minimum rendementsgarantie conform artikel 24 van de W.A.P.Bij de toekenning van het netto financieel rendement geldt als basisprincipe dat de Inrichter ernaar streeft, vanuit de doelstelling van een veilig en prudent beheer van het sociaal sectoraal pensioenstelsel, om steeds een buffer te hebben die gelijk is aan 10 pct. teneinde eventuele, toekomstige negatieve schommelingen in de beleggingen te kunnen opvangen. Echter, zelfs indien de buffer lager is dan 10 pct. en er een positief netto financieel rendement is, dan zal dit tot aan de minimum rendementsgarantie conform artikel 24 van de W.A.P. toch worden toegekend, zoals hierna bepaald.Indien deze vrije reserve of buffer van het Afzonderlijk Vermogen Pensioen PSC 149.03 hoger is dan of gelijk aan 10 pct. :- in geval van een positief netto financieel rendement wordt dit volledig netto financieel rendement, evenwel verminderd met het bedrag nodig om ervoor te zorgen dat ook na de toekenning van het netto financieel rendement de vrije reserve of buffer van het Afzonderlijk Vermogen Pensioen PSC 149.03 gelijk is aan 10 pct., ingeschreven op de individuele rekeningen van de aangeslotenen;- in geval van een negatief netto financieel rendement wordt dit volledig netto financieel rendement ingeschreven op de individuele rekeningen van de aangeslotenen.Indien deze vrije reserve of buffer van het Afzonderlijk Vermogen Pensioen PSC 149.03 lager is dan 10 pct. dan wordt het volledig negatief netto financieel rendement ingeschreven op de individuele rekeningen van de aangeslotenen. Het positief netto financieel rendement dat wordt ingeschreven op de individuele rekeningen van de aangeslotenen wordt dan beperkt tot de rentevoet van toepassing voor de berekening van de minimum rendementsgarantie conform artikel 24 van de W.A.P. (per 30 januari 2024 gelijk aan 1,75 pct.). Het overstijgend gedeelte wordt toegekend aan de vrije reserve van het Afzonderlijk Vermogen Pensioen PSC 149.03 ter verhoging van de buffer. Schematisch kan dit als volgt worden voorgesteld :  </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 29 juni 1981 houdende de algemene beginselen van de sociale zekerheid voor werknemers, artikel 35, § 5, vervangen bij de programmawet van 22 december 2003 en laatst gewijzigd bij de wet van 20 maart 2023; Gelet op het bijzondere-machtenbesluit nr. 37 van 24 juni 2020 tot uitvoering van artikelen 2 en 5 van de wet van 27 maart 2020 die machtiging verleent aan de Koning om maatregelen te nemen in de strijd tegen de verspreiding van het coronavirus COVID-19 (II) tot ondersteuning van de werknemers, artikelen 5 en 6; Gelet op het koninklijk besluit van 18 juli 2002 houdende maatregelen met het oog op de bevordering van de tewerkstelling in de non-profit sector, de artikelen 2, laatst gewijzigd bij het koninklijk besluit van 23 maart 2022, 2bis, laatst gewijzigd bij het koninklijk besluit van 1 mei 2022, 3, gewijzigd bij het koninklijk besluit van 1 september 2006, 4, ingevoegd bij het koninklijk besluit van 1 september 2006 en gewijzigd bij het koninklijk besluit van 15 maart 2017, 6, laatst gewijzigd bij het koninklijk besluit van 31 mei 2023, 6bis, ingevoegd bij het koninklijk besluit van 13 juni 2010 en gewijzigd bij het koninklijk besluit van 29 juni 2014; Gelet op het advies van de inspecteur van Financiën, gegeven op 10 december 2024; Gelet op de akkoordbevinding van de Staatssecretaris voor Begroting, gegeven op 23 januari 2025; Op de voordracht van de Minister van Werk en de Minister van Sociale Zaken; Hebben Wij besloten en besluiten Wij : Artikel 1. Voor het jaar 2025, worden de bedragen van de opbrengst van de patronale bijdrageverminderingen bedoeld in artikel 35, § 5, van de wet van 29 juni 1981 houdende de algemene beginselen van de sociale zekerheid voor werknemers vastgesteld als volgt: - Fonds sectoriel Maribel RW-RB-CG, opgericht door het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap (PSC 318.01): 13.396.731,99 euro; - Fonds Sociale Maribel voor de diensten gezinszorg van de Vlaamse Gemeenschap, opgericht door het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap (PSC 318.02): 35.026.006,51 euro; - Fonds Sociale Maribel voor de instellingen en diensten die behoren tot het bevoegdheidsgebied van het Paritair Comité voor de opvoedings- en huisvestingsinrichtingen en -diensten (PC 319): 6.814.905,12 euro; - Sectoraal Fonds Sociale Maribel voor de opvoedings- en huisvestingsinrichtingen van de Vlaamse Gemeenschap, opgericht door het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Vlaamse Gemeenschap (PSC 319.01): 78.712.529,03 euro; - Fonds Mirabel, opgericht door het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap (PSC 319.02): 51.123.533,95 euro; - Vlaams Sociaal Fonds voor de bevordering van de tewerkstelling in de maatwerkbedrijven, opgericht door het Paritair Subcomité voor de Vlaamse sector van de beschutte werkplaatsen, de sociale werkplaatsen en de maatwerkbedrijven (PSC 327.01): 57.805.937,72 euro; - Fonds Maribel social pour les entreprises de travail adapté subsidiées par la Commission communautaire française, opgericht door het Paritair Subcomité voor de beschutte werkplaatsen gesubsidieerd door de Franse Gemeenschapscommissie (PSC 327.02): 3.429.147,62 euro, verminderd met 63.488,19 euro aan niet-recurrente middelen; - Sociaal Fonds voor de bevordering van de tewerkstelling in de beschutte werkplaatsen, opgericht door het Paritair Subcomité voor de beschutte werkplaatsen van het Waalse Gewest en van de Duitstalige Gemeenschap (PSC 327.03): 16.952.697,73 euro; - Fonds Sociale Maribel van de socio-culturele sector voor federale en bicommunautaire organisaties, opgericht door het Paritair Subcomité voor de federale en bicommunautaire socio-culturele organisaties (PSC 329.03): 7.992.456,75 euro; - Sociaal Fonds Sociale Maribel voor de socioculturele sector van de Vlaamse Gemeenschap, opgericht door het Paritair Comité voor de socioculturele sector (PSC 329.01): 34.049.535,13 euro; - Fonds social Maribel social du secteur socioculturel des communautés française et germanophone, opgericht door het Paritair Comité voor de socioculturele sector (PSC 329.02): 41.898.046,69 euro; - Fonds sociale Maribel, opgericht door het Paritair Comité voor de gezondheidsinrichtingen en diensten (PC 330): 482.932.054,65 euro, te vermeerderen met 7.351.267,45 euro; - Sectoraal Fonds Sociale Maribel voor de Vlaamse welzijns- en gezondheidssector, opgericht door het Paritair Comité voor de Vlaamse welzijns- en gezondheidssector (PC 331): 26.902.256,56 euro; - Sociale Maribel Fonds, opgericht door het Paritair Comité van de Franstalige en Duitstalige welzijns- en gezondheidssector (PC 332): 21.381.358,73 euro; - Fonds sociale Maribel bedoeld in artikel 35, § 5, C, van de wet van 29 juni 1981 houdende de algemene beginselen van de sociale zekerheid voor werknemers: 409.902.711,57 euro, te vermeerderen met 38.720.000,00 euro. Art. 2.  Dit besluit heeft uitwerking met ingang van 1 januari 2025. Art. 3.  De minister bevoegd voor Werk en de minister bevoegd voor Sociale Zaken zijn, ieder wat hem betreft, belast met de uitvoering van dit besluit. Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL De Minister van Sociale Zaken, F. VANDENBROUCKE _______Nota(1) Verwijzingen naar het Belgisch Staatsblad: Wet van 29 juni 1981, Belgisch Staatsblad van 2 juli 1981. Programmawet van 22 december 2003, Belgisch Staatsblad van 31 december 2003. Wet van 20 maart 2023, Belgisch Staatsblad van 6 april 2023. Bijzondere-machtenbesluit nr. 37 van 24 juni 2020, Belgisch Staatsblad van 3 juli 2020. Koninklijk besluit van 18 juli 2002, Belgisch Staatsblad van 22 augustus 2002. Koninklijk besluit van 1 september 2006, Belgisch Staatsblad van 11 september 2006. Koninklijk besluit van 13 juni 2010, Belgisch Staatsblad van 25 juni 2010. Koninklijk besluit van 29 juni 2014, Belgisch Staatsblad van 11 juli 2014. Koninklijk besluit van 15 maart 2017, Belgisch Staatsblad van 27 maart 2017. Koninklijk besluit van 23 maart 2022, Belgisch Staatsblad van 4 april 2022. Koninklijk besluit van 1 mei 2022, Belgisch Staatsblad van 16 mei 2022. Koninklijk besluit van 31 mei 2023, Belgisch Staatsblad van 8 juni 2023. 
+</t>
         </is>
       </c>
     </row>
@@ -1351,28 +1351,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025200237</t>
+          <t>2025003788</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13 mei 2025</t>
+          <t>16 mei 2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 26 november 2024, gesloten in het Paritair Subcomité voor de metaalhandel, betreffende de oprichting van het "Fonds voor Bestaanszekerheid SAP Ondernemingsactiviteit Metaalhandel" dat optreedt als multi-sectorale inrichter van het sectoraal aanvullend pensioenstelsel voor de arbeiders en voor de bedienden in de Ondernemingsactiviteit Metaalhandel en tot vaststelling van de statuten van de multi-sectorale inrichter (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit tot vaststelling van de taalkaders van de Nationale Bank van België</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-13&amp;numac_search=2025200237&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200237=28&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-16&amp;numac_search=2025003788&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003788=28&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Subcomité voor de metaalhandel; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 26 november 2024, gesloten in het Paritair Subcomité voor de metaalhandel, betreffende de oprichting van het "Fonds voor Bestaanszekerheid SAP Ondernemingsactiviteit Metaalhandel" dat optreedt als multi-sectorale inrichter van het sectoraal aanvullend pensioenstelsel voor de arbeiders en voor de bedienden in de Ondernemingsactiviteit Metaalhandel en tot vaststelling van de statuten van de multi-sectorale inrichter. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Subcomité voor de metaalhandel Collectieve arbeidsovereenkomst van 26 november 2024 Oprichting van het "Fonds voor Bestaanszekerheid SAP Ondernemingsactiviteit Metaalhandel" dat optreedt als multi-sectorale inrichter van het sectoraal aanvullend pensioenstelsel voor de arbeiders en voor de bedienden in de Ondernemingsactiviteit Metaalhandel en vaststelling van de statuten van de multi-sectorale inrichter (Overeenkomst geregistreerd op 20 december 2024 onder het nummer 191186/CO/149.04) Gelet op de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid (hierna "FBZ-wet"); Gelet op de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid (hierna "WAP"); Gelet op de beslissing van de sociale partners van het Paritair Subcomité voor de metaalhandel (PSC 149.04) tot wijziging van het sociaal sectoraal pensioenstelsel en het desbetreffende pensioenreglement (SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel) en de beslissing van de sociale partners van het Aanvullend Paritair Comité voor de bedienden (PC 200) tot invoering van een sectoraal aanvullend pensioenstelsel voor de Bedienden in de Ondernemingsactiviteit Metaalhandel ("SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel"), in lijn met de wettelijke verplichting tot harmonisering van de aanvullende pensioenen voor arbeiders en bedienden in de zin van artikel 14 en volgende van de WAP;Gelet op de beslissing van de sociale partners van het het Paritair Subcomité voor de metaalhandel (PSC 149.04) en de sociale partners van het Aanvullend Paritair Comité voor de bedienden (PC 200) Ondernemingsactiviteit Metaalhandel om gebruik te maken van dezelfde multi-sectorale inrichter en daartoe het "Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Metaalhandel" (FBZ SAP Ondernemingsactiviteit Metaalhandel) op te richten en aan te duiden als de multi-sectorale inrichter van zowel het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel als het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel; Gelet op artikel 3, § 1, 5°, a), 1 van de WAP, moet de inrichter die optreedt voor meerdere paritaire (sub)comités de opbouw van aanvullende pensioenen als uitsluitend doel hebben. Het fonds voor bestaanszekerheid, genaamd "Sociaal Fonds voor de metaalhandel", werd via de collectieve arbeidsovereenkomst van 5 juli 2002 (63600/CO/149.04) door de representatieve organisaties van het Paritair Subcomité voor de metaalhandel (PSC 149.04) aangeduid als de inrichter van het sociaal sectoraal pensioenstelsel voor de arbeiders van het PSC 149.04 (SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel). Aangezien het "Sociaal Fonds voor de metaalhandel" ook andere taken heeft dan de opbouw van aanvullende pensioenen, kan het niet optreden als multi-sectorale inrichter van zowel het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel als het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel. Bijgevolg hebben de sociale partners van het Paritair Subcomité voor de metaalhandel (PSC 149.04) beslist dat, vanaf 1 juli 2025, het "Sociaal Fonds voor de metaalhandel" niet langer zal optreden als de inrichter van het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel en hebben zij samen met de sociale partners van het Aanvullend Paritair Comité voor de bedienden (PC 200) Ondernemingsactiviteit Metaalhandel beslist om het "Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Metaalhandel" (FBZ SAP Ondernemingsactiviteit Metaalhandel) op te richten en aan te duiden als de multi-sectorale inrichter van zowel het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel als het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel. FBZ SAP Ondernemingsactiviteit Metaalhandel neemt vanaf 1 juli 2025 alle rechten en verplichtingen over van het "Sociaal Fonds voor de metaalhandel" die betrekking hebben op de inrichting van het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel; Gelet op artikel 7/2 van de WAP, dat bepaalt dat de inhoud van de statuten van de inrichter of de oprichtingsakte van de inrichter in identieke bewoordingen moet worden opgenomen in alle collectieve arbeidsovereenkomsten die de tussenkomst van de inrichter voor verschillende paritaire comités en/of paritaire subcomités regelen. Artikel 1. Toepassingsgebied  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers die ressorteren onder het Paritair Subcomité voor de metaalhandel en die aangesloten zijn bij het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel, alsook op de arbeiders in de Ondernemingsactiviteit Metaalhandel die zij tewerkstellen.  § 2. Worden uitgesloten van het toepassingsgebied van deze overeenkomst, de buiten België gevestigde werkgevers waarvan de werknemers in België gedetacheerd worden in de zin van de bepalingen van de verordening (EEG) nr. 1408/71 van de Raad of de verordening (EG) nr. 883/2004 van het Europees Parlement en de Raad. Art. 2. Begripsomschrijvingen Voor de toepassing van deze collectieve arbeidsovereenkomst en de statuten in bijlage bij deze collectieve arbeidsovereenkomst, moeten de hierna vermelde begrippen als volgt worden begrepen : - Bedienden Ondernemingsactiviteit Metaalhandel : de bedienden die ressorteren onder het Aanvullend Paritair Comité voor de bedienden (PC 200) en werkzaam zijn in de Ondernemingsactiviteit Metaalhandel, die zich in een vergelijkbare situatie bevinden als de arbeiders die werkzaam zijn in de Ondernemingsactiviteit Metaalhandel (dit zijn de arbeiders die onder het PSC 149.04 ressorteren) met wie zij voor doeleinden van het aanvullend pensioen "spiegelen" in de zin van artikel 14 van de WAP. Zij worden overeenkomstig de regels van de collectieve arbeidsovereenkomst gesloten binnen het PC 200 van 13 juni 2024 tot invoering van een sectoraal aanvullend pensioenstelsel voor de Bedienden Ondernemingsactiviteit Metaalhandel ("SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel") toegewezen aan deze specifieke subcategorie;- Cao van 1 juli 2019 : de collectieve arbeidsovereenkomst van 1 juli 2019 gesloten in het PC 200 betreffende de koopkracht in het kader van het koninklijk besluit van 19 april 2019 tot uitvoering van artikel 7, § 1 van de wet van 26 juli 1996 tot bevordering van de werkgelegenheid en tot preventieve vrijwaring van het concurrentievermogen met registratienummer 152849/CO/200, zoals gewijzigd inzake de termijnen door de collectieve arbeidsovereenkomst van 18 november 2021 gesloten in het PC 200 met registratienummer 168827/CO/200; - Harmonisatieverplichting : de wettelijke verplichting tot harmonisering van de aanvullende pensioenen voor arbeiders en bedienden in de zin van de WAP; - Ondernemingsactiviteit (OA) : de beroepscategorieën en ondernemingsactiviteiten zoals bedoeld in artikel 14/4, § 1, eerste lid van de WAP; - Ondernemingsactiviteit Metaalhandel : de ondernemingsactiviteiten waarvoor het PSC 149.04 bevoegd is en die vallen onder het bevoegdheidsgebied van het PSC 149.04 zoals vastgesteld in het koninklijk besluit van 13 maart 1985 tot oprichting en tot vaststelling van de benaming en van de bevoegdheid van paritaire subcomités voor de sectoren die aan de metaal-, machine- en elektrische bouw verwant zijn en tot vaststelling van het aantal leden ervan, zoals laatst gewijzigd door het koninklijk besluit van 24 oktober 2012; - PC 200 : het Aanvullend Paritair Comité voor de bedienden; - PSC 149.04 : het Paritair Subcomité voor de metaalhandel; - SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel : het sectoraal aanvullend pensioenstelsel per 1 januari 2002 ingevoerd door het PSC 149.04 voor de arbeiders werkzaam in het PSC 149.04, zijnde de Arbeiders Ondernemingsactiviteit Metaalhandel; - SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel : het sectoraal aanvullend pensioenstelsel, dat door het PC 200 wordt ingevoerd - in overeenstemming met de cao van 1 juli 2019 - voor de bedienden Ondernemingsactiviteit Metaalhandel en dat in het kader van de Harmonisatieverplichting de gelijke behandeling beoogt inzake aanvullende pensioenen op sectorniveau tussen de Bedienden Ondernemingsactiviteit Metaalhandel en de arbeiders in de Ondernemingsactiviteit Metaalhandel met wie zij "spiegelen" in de zin van artikel 14 van de WAP; - Vestigingseenheid : een plaats die men, geografisch gezien, kan identificeren door een adres waar ten minste één activiteit van de in de Kruispuntbank van Ondernemingen geregistreerde juridische entiteit wordt uitgeoefend of van waaruit de activiteit wordt uitgeoefend in de zin van artikel I.2., 16° van boek I van het Wetboek van economisch recht. Dit komt neer op elke geografisch afgescheiden exploitatiezetel, afdeling of onderafdeling (atelier, fabriek, magazijn, bureau,...) van de betrokken juridische entiteit (op basis van het ondernemingsnummer), gesitueerd op een geografisch welbepaalde locatie en identificeerbaar met een adres en met een vestigingseenheidsnummer; - WAP : de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid, waarin het wettelijk kader inzake de harmonisatie van de aanvullende pensioenen voor arbeiders en bedienden werd ingeschreven door de wet van 5 mei 2014 tot wijziging van het rustpensioen en het overlevingspensioen en tot invoering van de overgangsuitkering in de pensioenregeling voor werknemers en houdende geleidelijke opheffing van de verschillen in behandeling die berusten op het onderscheid tussen werklieden en bedienden inzake aanvullende pensioenen en werd gewijzigd door de wet van 12 december 2021 tot uitvoering van het sociaal akkoord in het kader van de interprofessionele onderhandelingen voor de periode 2021-2022; - Werkgever : de juridische entiteit (op basis van het ondernemingsnummer), of desgevallend de Vestigingseenheden (op basis van het vestigingseenheidsnummer) indien de juridische entiteit over meerdere Vestigingseenheden beschikt. Art. 3. Multi-sectorale inrichter  § 1. Met ingang van 1 juli 2025 wordt het "Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Metaalhandel" ("FBZ SAP Ondernemingsactiviteit Metaalhandel") opgericht.  § 2. FBZ SAP Ondernemingsactiviteit Metaalhandel is een multi-sectorale inrichter, in de zin van artikel 3, 5°, a) van de WAP, die met ingang van 1 juli 2025 door de sociale partners van het PSC 149.04 wordt aangeduid als inrichter van het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel en door de sociale partners van het PC 200 als inrichter van het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel. § 3. De statuten van het FBZ SAP Ondernemingsactiviteit Metaalhandel die als bijlage bij deze collectieve arbeidsovereenkomst worden gevoegd, maken integraal deel uit van deze collectieve arbeidsovereenkomst. Art. 4. Geldigheidsduur  § 1. Deze collectieve arbeidsovereenkomst treedt in werking op 1 juli 2025. Zij wordt gesloten voor onbepaalde duur.  § 2. Zij kan worden opgezegd door één van de ondertekenende partijen mits een opzegging van 6 maanden, betekend bij een ter post aangetekende brief, gericht aan de voorzitter van PSC 149.04, die een kopie van de opzegging aan ieder van de ondertekenende partijen overmaakt. Art. 5. Algemeen verbindend verklaring Deze collectieve arbeidsovereenkomst wordt neergelegd ter Griffie van de Algemene Directie Collectieve Arbeidsbetrekkingen van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg en de algemeen verbindende kracht bij koninklijk besluit wordt gevraagd. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL BijlageBijlage aan de collectieve arbeidsovereenkomst van 26 november 2024, gesloten in het Paritair Subcomité voor de metaalhandel, betreffende de oprichting van het "Fonds voor Bestaanszekerheid SAP Ondernemingsactiviteit Metaalhandel" dat optreedt als multi-sectorale inrichter van het sectoraal aanvullend pensioenstelsel voor de arbeiders en voor de bedienden in de Ondernemingsactiviteit Metaalhandel en tot vaststelling van de statuten van de multi-sectorale inrichter Statuten FBZ SAP Ondernemingsactiviteit Metaalhandel HOOFDSTUK I. - Benaming, zetel, doel en duur Artikel 1. Benaming Er wordt op 1 juli 2025 een fonds voor bestaanszekerheid opgericht door het Paritair Subcomité voor de metaalhandel (PSC 149.04) en het Aanvullend Paritair Comité voor de bedienden (PC 200), genaamd "Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Metaalhandel" (afgekort : FBZ SAP Ondernemingsactiviteit Metaalhandel), verder ook het "fonds" genoemd. Art. 2. Zetel De maatschappelijke zetel en het secretariaat van het fonds is gevestigd te Marlylaan 15/8, 1120 Brussel. De zetel mag naar elk ander adres in België worden overgebracht mits statutenwijziging. Art. 3. Opdrachten - doel  § 1. Het fonds is een multi-sectorale inrichter in de zin van artikel 3, § 1, 5°, a), 1 van de WAP. Het fonds is : - met ingang van 1 juli 2025, aangeduid als inrichter van het sociaal sectoraal aanvullend pensioenstelsel ingevoerd door het Paritair Subcomité voor de metaalhandel (PSC 149.04) voor de arbeiders van de ondernemingen die onder de bevoegdheid vallen van het PSC 149.04 (hierna "SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel"), als opvolger van het sociaal fonds van het Paritair Subcomité voor de metaalhandel dat tot en met 30 juni 2025 de (mono-sectorale) inrichter was; - met ingang van 13 juni 2024, aangeduid als inrichter van het sectoraal aanvullend pensioenstelsel dat door het Aanvullend Paritair Comité voor de bedienden (PC 200) op die datum wordt ingevoerd voor de bedienden in de Ondernemingsactiviteit Metaalhandel (hierna "SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel").  § 2. Het fonds heeft, overeenkomstig artikel 3, § 1, 5°, a), 1 van de WAP als uitsluitend doel de opbouw van aanvullende pensioenen. Het fonds heeft met name als bevoegdheden : (1) De wijziging of opheffing van het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel en het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel; (2) De financiering van het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel en het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel door het laten innen, in zijn naam en voor zijn rekening, door de Rijksdienst voor Sociale Zekerheid van de bijdragen overeenkomstig de toepasselijke sectorale collectieve arbeidsovereenkomsten gesloten in het PSC 149.04 en in het PC 200 voor de bedienden in de Ondernemingsactiviteit Metaalhandel; (3) Het aanzuiveren van tekorten van de verworven reserves van de aangeslotenen, de tekorten ten opzichte van de WAP-rendementsgarantie, alsook de tekorten inzake de werkings- en beheerskosten van de pensioeninstelling : (i) via de eigen middelen in het Compartiment SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel of via een bijkomende bijdrage geïnd bij de werkgevers die ressorteren onder het PSC 149.04 en die deelnemen aan het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel, voor de voormelde tekorten met betrekking tot het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel; (ii) via de eigen middelen in het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel of via een bijkomende bijdrage geïnd bij de werkgevers die ressorteren onder het PC 200 en aangesloten zijn aan het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel voor de tekorten met betrekking tot het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel; (4) Het uitvoeren of in zijn naam en voor zijn rekening laten uitvoeren van alle noodzakelijke mededelingen aan de pensioeninstelling, de werkgevers, de aangeslotenen van het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel en het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel, hun begunstigden of rechthebbenden, de FSMA en andere belanghebbende partijen of overheidsinstellingen; (5) Het instellen en behandelen of het in zijn naam en voor zijn rekening laten instellen en behandelen van vorderingen in en buiten rechte wegens de niet-betaling van de bijdragen ter financiering van het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel en het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel en/of andere wettelijke en/of contractuele tekortkomingen die verband houden met (het beheer en de uitvoering van) het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel en het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel; (6) Het uitvoeren of in zijn naam en voor zijn rekening laten uitvoeren van elke verplichting opgelegd door de wetgeving van toepassing op aanvullende pensioenen en instellingen voor bedrijfspensioenvoorziening, en de uitvoeringsbesluiten.  § 3. Het fonds kan alle daden stellen die rechtstreeks of onrechtstreeks, geheel of gedeeltelijk, verband houden met zijn doel en kan ervoor opteren om één of meerdere aspecten hiervan aan derden uit te besteden.  § 4. In het kader van de verplichte externalisatie opgelegd door de WAP wordt het beheer en de uitvoering van het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel en het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel in ieder geval toevertrouwd aan een pensioeninstelling en zal het fonds hier niet zelf voor instaan. Art. 4. Duur Het fonds wordt voor onbepaalde duur opgericht. HOOFDSTUK II. - Toepassingsgebied Art. 5. De bepalingen van deze statuten gelden voor : (1) het fonds; (2) de werkgevers die ressorteren onder het PSC 149.04 en die deelnemen aan het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel en de arbeiders die zij tewerkstellen zoals bepaald in de toepasselijke sectorale collectieve arbeidsovereenkomsten gesloten in het PSC 149.04; (3) de werkgevers die ressorteren onder het PC 200 en die voor de bedienden in de Ondernemingsactiviteit Metaalhandel deelnemen aan het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel en de Bedienden Ondernemingsactiviteit Metaalhandel die zij tewerkstellen, zoals bepaald in de toepasselijke sectorale collectieve arbeidsovereenkomsten gesloten in het PC 200. HOOFDSTUK III. - Voordelen Art. 6. De voordelen toegekend door het fonds zijn : - De pensioen- en solidariteitstoezegging voorzien in het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel, die het voorwerp uitmaakt van één of meerdere bij koninklijk besluit algemeen verbindend verklaarde collectieve arbeidsovereenkomsten gesloten in het PSC 149.04, waarin de personen staan vermeld die ervan kunnen genieten (aangeslotenen, begunstigden en/of pensioengerechtigden) en ook de aard en de toekennings- en uitbetalingsmodaliteiten van de toegekende voordelen worden vastgesteld; - De pensioentoezegging voorzien in het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel, die het voorwerp uitmaakt van één of meerdere bij koninklijk besluit algemeen verbindend verklaarde collectieve arbeidsovereenkomsten gesloten in het PC 200, waarin de personen staan vermeld die ervan kunnen genieten (aangeslotenen, begunstigden en/of pensioengerechtigden) en ook de aard en de toekennings- en uitbetalingsmodaliteiten van de toegekende voordelen worden vastgesteld. HOOFDSTUK IV. - Beheer van het fonds Art. 7. Het fonds wordt beheerd door een paritair samengestelde raad van bestuur die gezamenlijk door het PSC 149.04 en het PC 200 worden aangeduid. De raad van bestuur bestaat uit zestien leden, zijnde : - acht vertegenwoordigers voorgedragen door de meest representatieve werkgeversorganisaties vertegenwoordigd in het PSC 149.04; - acht vertegenwoordigers voorgedragen door de meest representatieve werknemersorganisaties vertegenwoordigd in het PSC 149.04. Elke organisatie heeft de bevoegdheid om op elk moment in de vervanging van zijn vertegenwoordigers te voorzien in overleg met het PC 200. Art. 8. Het voorzitterschap wordt door de werkgeversafvaardiging waargenomen. De voorzitter wordt jaarlijks aangeduid door de raad van bestuur. De eerste en de derde ondervoorzitter behoren tot de werknemersgroep en worden jaarlijks aangeduid door de raad van bestuur. De tweede ondervoorzitter behoort tot de werkgeversgroep en wordt jaarlijks door de raad van bestuur aangeduid. Art. 9.  § 1. De raad van bestuur wordt door zijn voorzitter bijeengeroepen. De voorzitter is ertoe gehouden de raad van bestuur ten minste eenmaal per semester bijeen te roepen en telkens wanneer ten minste twee leden van de raad van bestuur erom verzoeken.  § 2. De uitnodiging vermeldt de agenda.  § 3. De notulen worden door de, door de raad van bestuur aangeduide secretaris opgesteld. De uittreksels uit deze notulen worden door de voorzitter of twee bestuurders ondertekend. Deze notulen worden ter beschikking gesteld van de representatieve werkgeversorganisatie(s) en werknemersorganisaties vertegenwoordigd in het Aanvullend Paritair Comité voor de bedienden (PC 200), alsook de gerelateerde relevante documenten die betrekking hebben op het beheer van het (Compartiment) SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel.  § 4. Wanneer tot de stemming moet worden overgegaan, dient een gelijk aantal leden van elke afvaardiging aan de stemming deel te nemen. Is het aantal ongelijk, dan onthoudt (onthouden) zich het jongste lid (de jongste leden).  § 5. De raad van bestuur kan slechts geldig beslissen over de op de agenda gestelde kwesties en in aanwezigheid van ten minste de helft van de leden die tot de werknemersafvaardiging en ten minste de helft van de leden die tot de werkgeversafvaardiging behoren. De beslissingen worden met een meerderheid van twee derden van de stemgerechtigden genomen. Art. 10.  § 1. De raad van bestuur heeft tot taak het fonds te beheren en alle maatregelen te treffen die voor zijn goede werking zijn vereist. Hij beschikt over de meest uitgebreide bevoegdheid inzake het beheer en de leiding van het fonds.  § 2. De raad van bestuur keurt de rekeningen en de begroting goed en treedt in rechte op in naam van het fonds, op vervolging en op verzoek van de voorzitter of van een tot dat doel afgevaardigde bestuurder.  § 3. De raad van bestuur kan bijzondere bevoegdheden overdragen aan één of meer van zijn leden of zelfs aan derden. Voor al de andere handelingen dan deze waarvoor de raad van bestuur speciale volmachten heeft verleend, volstaan de gezamenlijke handtekeningen van twee bestuurders (één van werknemerszijde en één van werkgeverszijde).  § 4. De verantwoordelijkheid van de bestuurders beperkt zich tot de uitvoering van hun mandaat en zij gaan geen enkele persoonlijke verbintenis aan betreffende hun beheer ten opzichte van de verplichtingen van het fonds. § 5. Het lid dat voor de vergadering van de raad van bestuur belet is, kan schriftelijk of per e-mail volmacht verlenen aan één van zijn collega's behorende tot dezelfde groep (werknemers- of werkgeversgroep) om hem te vervangen. Nochtans mag geen enkel lid meer dan één andere bestuurder vertegenwoordigen. HOOFDSTUK V. Financiering van het fonds Art. 11.  § 1. De bijdragen ter financiering van het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel, alsook voor de financiering van de beheers- en werkingskosten en het aanleggen van een (eventuele) buffer en/of voor de aanzuivering van tekorten, worden uitsluitend vastgelegd in een bij koninklijk besluit algemeen verbindend verklaarde collectieve arbeidsovereenkomst gesloten in het PSC 149.04. De inning en de invordering van deze bijdrage gebeurt door de Rijksdienst voor Sociale Zekerheid (RSZ) bij toepassing van artikel 7 van de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid en overeenkomstig de daartoe met de RSZ afgesloten beheersovereenkomst.  § 2. De bijdragen ter financiering van het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel, alsook voor de financiering van de beheers- en werkingskosten en het aanleggen van een (eventuele) buffer en/of voor de aanzuivering van tekorten, worden uitsluitend vastgelegd in een bij koninklijk besluit algemeen verbindend verklaarde collectieve arbeidsovereenkomst gesloten in het PC 200. De inning en de invordering van deze bijdragen gebeurt door de RSZ bij toepassing van artikel 7 van de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid en overeenkomstig de daartoe met de RSZ afgesloten beheersovereenkomst. Art. 12. Afgezonderd beheer Binnen het fonds wordt er gewerkt met afgezonderd beheer. Dit houdt in dat de bijdragen ter financiering van het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel en de daaraan gerelateerde werkingskosten enerzijds en de bijdragen ter financiering van het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel en de daaraan gerelateerde werkingskosten anderzijds, worden beheerd in twee afgescheiden compartimenten binnen het fonds : (1) Het Compartiment SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel, waarin alle bijdragen en middelen (en de eventuele opbrengsten ervan) worden ondergebracht die het fonds vanaf 1 juli 2025 ontvangt van de RSZ of desgevallend van het sociaal fonds van het paritair subcomité voor de metaalhandel voor de financiering van het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel (alsook van de beheers- en werkingskosten, de (eventuele) buffer en/of de aanzuivering van tekorten); (2) Het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel, waarin alle bijdragen en middelen (en de eventuele opbrengsten ervan) worden ondergebracht die het fonds vanaf 1 juli 2025 ontvangt van de RSZ voor de financiering van het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel (alsook van de beheers- en werkingskosten, de (eventuele) buffer en/of de aanzuivering van tekorten). Art. 13. Geen solidariteit  § 1. Er bestaat geen solidariteit tussen het Compartiment SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel en het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel, niet voor de financiering van de respectievelijke sectorale aanvullende pensioenstelsels (met inbegrip van de aanleg van een eventuele buffer en de aanzuivering van tekorten in de verworven reserves van de aangeslotenen in het kader van de WAP-rendementsgarantie), noch voor de daaraan gerelateerde beheer- en werkingskosten (van het fonds en van de pensioeninstelling). Dit betekent concreet dat de bijdragen en de middelen toegewezen aan het Compartiment SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel enkel kunnen gebruikt worden voor de hiervoor vermelde posten inzake de financiering van het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel. Indien de middelen van het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel ontoereikend zouden zijn, kan het fonds de middelen (het surplus) in het Compartiment SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel in geen geval aanwenden ter dekking van het tekort in het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel. Analoog, kunnen de bijdragen en de middelen toegewezen aan het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel enkel gebruikt worden voor de hiervoor vermelde posten inzake de financiering van het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel. Indien de middelen van het Compartiment SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel ontoereikend zouden zijn, kan het fonds de middelen (het surplus) in het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel in geen geval aanwenden ter dekking van het tekort in het Compartiment SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel.  § 2. Inzake de betaling van de bijdragen ter financiering van de respectievelijke sectorale aanvullende pensioenstelsels (met inbegrip van de aanleg van een eventuele buffer en de aanzuivering van tekorten in de verworven reserves van de aangeslotenen in het kader van de WAP-rendementsgarantie) en de daaraan gerelateerde beheer- en werkingskosten bestaat er geen solidariteit tussen de werkgevers die vallen onder het toepassingsgebied zoals bepaald in artikel 5 van deze statuten. Art. 14. Tekorten  § 1. Tekorten binnen het Compartiment SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel of met betrekking tot het SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel in het algemeen, worden aangezuiverd via een bijkomende storting vanuit het sociaal fonds van het Paritair Subcomité voor de metaalhandel, dan wel een bijkomende/verhoogde bijdrage geïnd door de RSZ bij de werkgevers bedoeld in artikel 5 (2) van deze statuten.  § 2. Tekorten binnen het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel of met betrekking tot het SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel in het algemeen, worden aangezuiverd via een bijkomende/verhoogde bijdrage geïnd door de RSZ bij de werkgevers bedoeld in artikel 5 (3) van deze statuten. HOOFDSTUK VI. - Begroting en jaarrekeningen Art. 15. Begroting, jaarrekeningen  § 1. Het boekjaar neemt een aanvang op 1 januari van elk jaar en sluit op 31 december van hetzelfde jaar.  § 2. Op 31 december worden de rekeningen van het verlopen jaar afgesloten. De afsluiting en de balans moeten op boekhoudkundig gebied voldoende gespecificeerd worden.  § 3. De raad van bestuur, alsmede de bij toepassing van artikel 12 van de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid aangewezen revisor, brengen jaarlijks ieder een schriftelijk verslag uit over het vervullen van hun opdracht tijdens het verlopen jaar.  § 4. De jaarrekeningen, samen met voornoemde schriftelijke verslagen, moeten uiterlijk in de maand juli ter goedkeuring aan het Paritair Subcomité voor de metaalhandel (PSC 149.04) worden voorgelegd. Voorafgaand aan deze goedkeuring, worden deze documenten ter informatie ook overgemaakt aan het Aanvullend Paritair Comité voor de bedienden (PC 200). HOOFDSTUK VII. - Ontbinding en vereffening Art. 16. Het fonds kan enkel ontbonden worden bij een eenparige beslissing van het PSC 149.04 en het PC 200. Art. 17.  § 1. In geval van vrijwillige ontbinding van het fonds, waarbij er gelden of middelen beschikbaar blijven, zullen het PSC 149.04 en het PC 200 die gezamenlijk tot deze ontbinding beslist hebben, gezamenlijk de vereffenaars benoemen, hun bevoegdheden en hun eventuele bezoldiging vaststellen.  § 2. Aan het overblijvend vermogen van het fonds, na vereffening van de schulden, zullen de sociale partners van het PSC 149.04 en de sociale partners van het PC 200 een bestemming geven welke zoveel mogelijk het doel benadert met het oog waarop het fonds voor bestaanszekerheid werd opgericht, met name aanvullende pensioenopbouw. Hierbij zal rekening worden gehouden met het afgezonderd beheer zoals bepaald in deze statuten. Concreet betekent dit dat het overblijvend vermogen behorende tot het Compartiment SAP PSC 149.04 Arbeiders Ondernemingsactiviteit Metaalhandel zal worden overdragen naar de pensioeninstelling gekozen door de sociale partners van het PSC 149.04 en dat het overblijvend vermogen behorende tot het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Metaalhandel zal worden overgedragen naar de pensioeninstelling gekozen door de sociale partners van het PC 200. HOOFDSTUK VIII</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wetten op het gebruik van de talen in bestuurszaken, gecoördineerd op 18 juli 1966, artikel 43, laatst gewijzigd bij wet van 4 april 2006;Gelet op de wet van 22 februari 1998 tot vaststelling van het organiek statuut van de Nationale Bank van België, artikel 34;Gelet op het koninklijk besluit van 2 februari 2025 tot vaststelling van de trappen van de hiërarchie van het personeel van de Nationale Bank van België;Gelet op het koninklijk besluit van 24 juin 2018 tot vaststelling van de taalkaders van de Nationale Bank van België;Gelet op het personeelsplan van de Nationale Bank van België voor 2024, zoals vastgelegd door het Directiecomité in december 2023;Overwegende dat artikel 43, § 3, van voormelde wetten op het gebruik van de talen in bestuurszaken bepaalt dat de Koning voor iedere centrale dienst en voor een duur van ten hoogste zes jaar, het percentage betrekkingen bepaalt dat aan het Nederlands en aan het Frans kader dient toegewezen te worden;Overwegende dat de taalkaders vastgesteld door voormeld koninklijk besluit van 24 juni 2018, dat met ingang van 19 juni 2018 uitwerking heeft gehad, bijgevolg niet langer van toepassing zijn vanaf 19 juni 2024;Overwegende dat het dan ook passend is om de geactualiseerde taalkaders van de Nationale Bank van België vast te stellen;Overwegende dat voldaan is aan de voorschriften van artikel 54, tweede lid, van voornoemde wetten op het gebruik van de talen in bestuurszaken;Gelet op het advies nr. 57.045 van de Vaste Commissie voor taaltoezicht, gegeven op 18 april 2025;Op de voordracht van de minister bevoegd voor Financiën.Hebben Wij besloten en besluiten Wij :Artikel 1. De betrekkingen van de Nationale Bank van België worden over de taalrollen verdeeld als volgt:  </t>
         </is>
       </c>
     </row>
@@ -1382,28 +1382,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025002626</t>
+          <t>2025003790</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 19 december 2024, gesloten in het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap, tot wijziging van de collectieve arbeidsovereenkomst van 26 juni 2008 betreffende de vakbondspremie in het Waalse Gewest (overeenkomst die werd geregistreerd op 18 augustus 2008 onder het nummer 89035/CO/319.02) (1)</t>
+          <t>11 mei 2025. - Koninklijk Besluit tot aanwijzing van een bevoegde autoriteit voor luchtvaartuigexploitanten en Unieluchthavenbeheerders zoals bedoeld in de verordening (EU) 2023/2405 van het Europees Parlement en de Raad van 18 oktober 2023 inzake het waarborgen van een gelijk speelveld voor duurzaam luchtvervoer</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-13&amp;numac_search=2025002626&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025002626=29&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025003790&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003790=29&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt ver-klaard de als bijlage overgenomen collectieve ar-beidsovereenkomst van 19 december 2024, geslo-ten in het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap, tot wijziging van de collectieve arbeidsovereenkomst van 26 juni 2008 betreffende de vakbondspremie in het Waalse Gewest (overeenkomst die werd geregistreerd op 18 augustus 2008 onder het nummer 89035/CO/319.02).Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige GemeenschapCollectieve arbeidsovereenkomst van 19 december 2024Wijziging van de collectieve arbeidsovereenkomst van 26 juni 2008 betreffende de vakbondspremie in het Waalse Gewest (overeenkomst die werd geregistreerd op 18 augustus 2008 onder het nummer 89035/CO/319.02) (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191540/CO/319.02)Artikel 1. Deze collectieve arbeidsovereenkomst is uitsluitend van toepassing op de werknemers en werkgevers van de opvoedings- en huisvestings-richtingen en -diensten die erkend en/of gesubsidieerd zijn door het Waalse Gewest en op de werknemers en werkgevers van de inrichtingen en diensten die dezelfde activiteiten uitvoeren en die noch erkend zijn noch gesubsidieerd worden en wier hoofdactiviteit zich in het Waalse Gewest bevindt, die onder de bevoegdheid vallen van het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap.Art. 2. De bijlage bij de voornoemde collectieve arbeidsovereenkomst van 26 juni 2008, gewijzigd door de collectieve arbeidsovereenkomst van 22 november 2018, wordt vervangen door de bijlage van deze overeenkomst.Art. 3. Deze collectieve arbeidsovereenkomst wijzigt de collectieve arbeidsovereenkomst van 26 juni 2008 betreffende de vakbondspremie in het Waalse Gewest (overeenkomst die werd geregistreerd op 18 augustus 2008 onder het nummer 89035/CO/319.02).Zij treedt in werking met ingang van 1 januari 2025. Ze wordt gesloten voor onbepaalde duur. Deze collectieve arbeidsovereenkomst kan worden opgezegd door een vooropzegging van één jaar die per aangetekend schrijven wordt betekend aan de voorzitter van het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap, die de andere partijen hiervan op de hoogte brengt.Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025.De Minister van Werk,D. CLARINVALBijlage bij de collectieve arbeidsovereenkomst van 19 december 2024, gesloten in het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap, tot wijziging van de collectieve arbeidsovereenkomst van 26 juni 2008 betreffende de vakbondspremie in het Waalse Gewest (overeenkomst die werd geregistreerd op 18 augustus 2008 onder het nummer 89035/CO/319.02)Intersyndicaal Fonds van de sectoren van het Waalse GewestAanvraag vakbondspremie : Dienstjaar 20 . . - Betaalbaar in 20 . . (1)De premie kan alleen worden betaald aan de volgende voorwaarden :- de aanvraag moet door de werknemer worden ingediend per post of elektronisch medium bij zijn vakorganisatie vóór 31 maart van het jaar dat volgt op het dienstjaar dat wordt gedekt door de premie;- het tewerkstellingsattest (verso) moet voorafgaand ingevuld worden door de werkgever.Identificatie van de werknemer (2)(in te vullen door de vakorganisatie en/of de werknemer)Naam : . . . . . Voornaam : . . . . . Nr. rijksregister : . . . . . Adres : . . . . . Vakorganisatie . . . . . Lidnummer : . . . . . Datum aansluiting . . . . . Rekeningnr. (voor terugbetaling) : BE . . . . . Bijdrage : o voltijds o deeltijdsIk verklaar voor het jaar 20.. (1) slechts één aanvraagformulier per arbeidsperiode te hebben ingediend. Ik bevestig dat de medegedeelde informatie oprecht en volledig is.Datum : . . . . . Handtekening : . . . . . (1) Invullen.(2) Om het privéleven te beschermen, worden de nieuwe Europese regels betreffende de algemene verordening betreffende de bescherming van de gegevens (AVG - Verordening (EU) 2016/679 van het Europees Parlement) nageleefd. De informatie op dit formulier mag alleen gebruikt worden in het kader van de behandeling van de vakbondspremie zoals bepaald door de collectieve arbeidsovereenkomst van 26 juni 2008, gewijzigd door de collectieve arbeidsovereenkomst van 22 november 2018. Ondergetekende geeft zijn formele toestemming voor het gebruik ervan.Tewerkstellingsattest : in te vullen door de werkgeverMoet jaarlijks verplicht door de werkgever worden ingevuld en, volgens de modaliteiten bepaald door de collectieve arbeidsovereenkomst van 26 juni 2008 aan alle werknemers die behoren tot Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap en die in de loop van het jaar tewerkgesteld zijn in een inrichting die wordt erkend en/of gesubsidieerd door het Waalse Gewest of in een inrichting die dezelfde activiteiten uitvoert en die noch erkend noch gesubsidieerd wordt en waarvan de hoofdactiviteit zich in het Waalse Gewest bevindt.Ik, ondergetekende, vertegenwoordiger van de dienst : . . . . . Naam : . . . . . Adres : . . . . . Identificatienr. : . . . . . RSZ-nr. : . . . . . Sector (1)o Erkend en gesubsidieerd AViQo Erkend en niet gesubsidieerd AViQ (3)o SAFAE (3)o Noch erkend noch gesubsidieerd AViQ (3)o Opvangtehuizen, gemeenschapshuizen, nachtasielen en opvangtehuizen van het gezinstypeo Sociale Immobiliënkantoren (SIK) (3) o Associations de promotion du logement (APL) (3)De diensten die onder een erkenning die worden verstrekt door het AViQ zijn verplicht in onderstaand vakje hun "AViQ-identificatienummer"   </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de verordening (EU) 2023/2405 van het Europees Parlement en de Raad van 18 oktober 2023 inzake het waarborgen van een gelijk speelveld voor duurzaam luchtvervoer (ReFuelEU Luchtvaart);Gelet op de wet van 27 juni 1937 houdende herziening van de wet van 16 November 1919, betreffende de regeling der Luchtvaart, artikel 5, § 1, gewijzigd bij de wet van 2 januari 2001 houdende sociale, budgettaire en andere bepalingen, artikel 18;Gelet op de betrokkenheid van de gewestregeringen;Gelet op het advies van de inspecteur van Financiën, gegeven op 20 januari 2025;Overwegende dat dit besluit niet van regelgevende aard is in de zin van artikel 3, § 1, van de wetten op de Raad van State, gecoördineerd op 12 januari 1973; dat de afdeling Wetgeving van de Raad van State derhalve niet bevoegd is om over dit ontwerp een advies te verlenen;Overwegende dat de verordening (EU) 2023/2405 van het Europees Parlement en de Raad van 18 oktober 2023 inzake het waarborgen van een gelijk speelveld voor duurzaam luchtvervoer ("ReFuelEU Luchtvaart"), van toepassing is vanaf 1 januari 2024; dat de artikelen 4, 5, 6, 8 en 10 evenwel pas van toepassing zijn met ingang van 1 januari 2025;Overwegende dat luidens artikel 288, tweede lid, VWEU een verordening een algemene strekking heeft en verbindend is in al haar onderdelen en rechtstreeks toepasselijk is in elke lidstaat;Overwegende dat luidens artikel 11, eerste lid, van de ReFuelEU Luchtvaart-verordening, de lidstaten de bevoegde autoriteiten aanwijzen die verantwoordelijk zijn voor de handhaving van deze verordening en voor het opleggen van boeten aan luchtvaartuigexploitanten, aan Unieluchthavenbeheerders en aan luchtvaartbrandstofleveranciers; dat het boetesysteem nog in een ander rechtsinstrument kan worden uitgevoerd; dat het echter reeds noodzakelijk is om een bevoegde autoriteit aan te wijzen voor de werking van de artikelen vijf tot en met acht ervan;Overwegende dat de rechtsgrond om een dergelijke bevoegde autoriteit voor enerzijds de Unieluchthavenbeheerders en anderzijds de luchtvaartuigexploitanten aan te wijzen te vinden is in artikel 5, § 1, van de wet van 27 juni 1937 betreffende de regeling der Luchtvaart; dat het aanwijzen van een dergelijke bevoegde autoriteit voor luchtvaartbrandstofleveranciers in een aparte regeling zal worden getroffen;Overwegende dat volgens het tweede lid van artikel 11 van dezelfde verordening de lidstaten ervoor zorgen dat hun bevoegde autoriteiten hun toezichts- en handhavingstaken op onpartijdige en transparante wijze uitoefenen, op een wijze die onafhankelijk is van luchtvaartuigexploitanten, luchtvaartbrandstofleveranciers en Unieluchthaven-beheerders; dat de lidstaten er ook op toezien dat hun bevoegde autoriteiten over de nodige middelen en capaciteit beschikken om de hun bij deze verordening toevertrouwde taken doelmatig en tijdig uit te voeren; dat het directoraat-generaal Luchtvaart (DGLV) van de FOD Mobiliteit en Vervoer beantwoordt aan deze vereisten;Overwegende dat luchtvaartuigexploitanten aan het DGLV in toepassing van artikel 5 van de bovenvermelde verordening, enerzijds de verantwoording moeten indienen waarom ze voor de naleving van de toepasselijke brandstofveiligheidsvoorschriften minder dan 90 procent van de jaarlijks vereiste luchtvaartbrandstof hebben getankt, en anderzijds een verzoek kunnen indienen om een tijdelijke vrijstelling van deze tankverplichting te bekomen;Overwegende dat in toepassing van artikel 6 van dezelfde verordening de luchtvaartuigexploitanten bij het DGLV een melding kunnen indienen bij moeilijkheden bij de toegang tot luchtvaartbrandstoffen met een minimaal percentage duurzame luchtvaartbrandstoffen op Unieluchthavens; dat in de huidige stand de volgende Belgische luchthavens "Unieluchthavens" zijn in de zin van de verordening: Brussel-Nationaal, Charleroi en Luik;Overwegende dat de Unieluchthavenbeheerders in toepassing van artikel 7, derde lid, onder meer aan het DGLV, de voortgang van bestaande projecten rapporteren;Overwegende dat luchtvaartexploitanten de DGLV de in artikel 8 van dezelfde verordening gespecificeerde informatie moeten verstrekken;Op de voordracht van de Minister van Mobiliteit,Hebben Wij besloten en besluiten Wij :Artikel 1. Voor de toepassing van dit Koninklijk Besluit wordt verstaan onder:1°  FOD Mobiliteit en Vervoer: de Federale Overheidsdienst Mobiliteit en Vervoer;2°  DGLV: het directoraat-generaal Luchtvaart van de FOD Mobiliteit en Vervoer;3°  directeur-generaal: de directeur-generaal van het DGLV;4°  ReFuelEU Luchtvaart-verordening: de verordening (EU) 2023/2405 van het Europees Parlement en de Raad van 18 oktober 2023 inzake het waarborgen van een gelijk speelveld voor duurzaam luchtvervoer;5°  Unieluchthavenbeheerder: de in artikel 3, tweede lid, van de ReFuelEU Luchtvaart-verordening bedoelde luchthavenbeheerder of instantie, of zoals later gewijzigd, waarvoor België in toepassing van art. 11, zesde lid, verantwoordelijke lidstaat is;6°  luchtvaartuigexploitant: de in artikel 3, derde lid, van de ReFuelEU Luchtvaartverordening bedoelde persoon of eigenaar, of zoals later gewijzigd, waarvoor België in toepassing van art. 11, vijfde lid, verantwoordelijke lidstaat is.Art. 2. Het DGLV is de bevoegde autoriteit zoals bedoeld in de ReFuelEU Luchtvaartverordening voor wat betreft de luchtvaartuigexploitanten en de Unieluchthavenbeheerder.Art. 3. De directeur-generaal of zijn gemachtigde verleent de in artikel 5 van de RefuelEU Luchtvaartverordening bedoelde tijdelijke vrijstelling.Art. 4. De minister bevoegd voor luchtvaart is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Mobiliteit,J.-L. CRUCKE 
+</t>
         </is>
       </c>
     </row>
@@ -1413,28 +1414,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025200281</t>
+          <t>2025003888</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>14 mei 2025</t>
+          <t>21 mei 2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 20 november 2024, gesloten in het Paritair Comité voor het tuinbouwbedrijf, betreffende de getrouwheidspremie (parken en tuinen) (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit houdende ontslag van de leden van de Federale Raad van landmeters-experten en van de Federale Raad van Beroep van landmeters-experten</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-14&amp;numac_search=2025200281&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200281=30&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-21&amp;numac_search=2025003888&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003888=30&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor het tuinbouwbedrijf; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 20 november 2024, gesloten in het Paritair Comité voor het tuinbouwbedrijf, betreffende de getrouwheidspremie (parken en tuinen). Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor het tuinbouwbedrijf Collectieve arbeidsovereenkomst van 20 november 2024 Getrouwheidspremie (parken en tuinen) (Overeenkomst geregistreerd op 20 december 2024 onder het nummer 191194/CO/145) Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de arbeiders van de ondernemingen die ressorteren onder het Paritair Comité voor het tuinbouwbedrijf en waarvan de hoofdactiviteit bestaat in het inplanten en onderhouden van parken en tuinen. Deze collectieve arbeidsovereenkomst is niet van toepassing op de bedienden.  § 2. Met "arbeiders" worden de arbeiders zonder onderscheid naar gender bedoeld. Art. 2. Een getrouwheidspremie wordt toegekend aan de arbeiders die tijdens het refertejaar tewerkgesteld zijn in de ondernemingen voor het inplanten en onderhouden van parken en tuinen die ressorteren onder het Paritair Comité voor het tuinbouwbedrijf. Met "refertejaar" wordt bedoeld : de periode van 1 juli van het vorig jaar tot 30 juni van het jaar waarin de premie uitbetaald wordt. Alleen arbeiders met een anciënniteit van ten minste 6 maanden in de sector komen in aanmerking voor de toekenning van een getrouwheidspremie. De anciënniteitsvoorwaarde wordt jaarlijks beoordeeld bij het einde van de referteperiode. Dit wil zeggen op 1 juli van elk kalenderjaar. De arbeiders die na afloop van de referteperiode in dienst blijven en die op een later tijdstip dan 1 juli de 6 maanden anciënniteit in de sector bereiken, verwerven alsnog het recht op de getrouwheidspremie. Wanneer een getrouwheidspremie niet wordt uitgekeerd, blijven de door de werkgevers gestorte bijdragen evenwel verworven voor het sociaal fonds. Art. 3. De getrouwheidspremie wordt als volgt vastgesteld : - van 0 tot 5 opeenvolgende jaren dienst in de sector : 6,00 pct.; - van 5 tot 15 opeenvolgende jaren dienst in de sector : 7,00 pct.; - meer dan 15 opeenvolgende jaren dienst in de sector : 8,50 pct., en dit van het brutoloon verdiend voor de gewerkte dagen in de sector tijdens het refertejaar. De getrouwheidspremie wordt berekend voor de effectief gepresteerde dagen en voor de daarmee gelijkgestelde dagen, overeenkomstig de bepalingen voorzien in de wetgeving betreffende de jaarlijkse vakantie van de arbeiders.Met ingang van de referteperiode die een aanvang neemt op 1 juli 2005, worden de dagen economische werkloosheid evenwel niet meer gelijkgesteld met het oog op de berekening van de getrouwheidspremie. Art. 4.  Uiterlijk in de loop van de maand juni van het refertejaar waarop de getrouwheidspremie betrekking heeft, bepaalt de raad van beheer van het "Sociaal Fonds voor de inplanting en het onderhoud van parken en tuinen" het tijdstip vanaf wanneer aan alle rechthebbenden de getrouwheidspremie kan worden betaald. Art. 5.  Genieten eveneens de getrouwheidspremie volgens de modaliteiten van artikel 3 : - de arbeiders die in de loop van het refertejaar worden gepensioneerd of met SWT worden gesteld; - de rechtverkrijgenden van de arbeiders die in de loop van het refertejaar zijn overleden; - de arbeiders waarvan de arbeidsovereenkomst in de loop van het refertejaar wordt beëindigd door de werkgever (middels gewone opzeg of vergoeding), in onderling overleg of ingevolge overmacht; - de arbeiders verbonden met een arbeidsovereenkomst voor bepaalde duur of voor een welomschreven werk die een einde neemt in de loop van het refertejaar; - de arbeiders die in de loop van het refertejaar zelf ontslag nemen. Art. 6.  Genieten bijgevolg niet de getrouwheidspremie, de arbeiders : - die ontslagen worden om dringende reden in de loop van het refertejaar; - die geen 6 maanden anciënniteit bereiken op 1 juli, rekening houdende met de voorwaarden bepaald in artikel 3. Art. 7.  Onverminderd de bepalingen van deze collectieve arbeidsovereenkomst, blijven de bijkomende voordelen voorzien bij particuliere akkoorden gesloten op het vlak van de onderneming, behouden. Art. 8. Deze collectieve arbeidsovereenkomst treedt in werking op 20 november 2024 en is gesloten voor een onbepaalde tijd. Zij vervangt de collectieve arbeidsovereenkomst betreffende de getrouwheidspremie van 15 december 2023, geregistreerd onder het nr. 185559. Elk van de contracterende partijen kan ze opzeggen mits een opzeggingstermijn van drie maanden, te betekenen bij een ter post aangetekende brief aan de voorzitter van het Paritair Comité voor het tuinbouwbedrijf. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 27 maart 2023 tot bescherming van het beroep en de titel van landmeter-expert en tot oprichting van een Orde van landmeters-experten, artikel 61;Gelet op het koninklijk besluit van 25 april 2024 tot bepaling van de datum van inwerkingtreding van de wet van 27 maart 2023 tot bescherming van het beroep en de titel van landmeter-expert en tot oprichting van een Orde van landmeters-experten en tot opheffing van de wet van 11 mei 2003 tot bescherming van de titel en van het beroep van landmeter-expert en van de wet van 11 mei 2003 tot oprichting van federale raden van landmeters-experten, artikel 2, tweede lid;Overwegende de koninklijke besluiten van 7 mei 2019 houdende benoeming van de voorzitter van de Franstalige Kamer van de Federale Raad van beroep van landmeters-experten en houdende benoeming van de voorzitter van de Franstalige Kamer van de Federale Raad van landmeters-experten;Overwegende het koninklijk besluit van 5 maart 2021 houdende benoeming van de plaatsvervangend voorzitter van de Nederlandstalige Kamer van de Federale Raad van landmeters-experten;Overwegende het koninklijk besluit van 21 maart 2021 houdende benoeming van de plaatsvervangend voorzitter van de Franstalige Kamer van de Federale Raad van landmeters-experten;Overwegende het koninklijk besluit van 27 juni 2021 houdende benoeming van de plaatsvervangend voorzitter van de Nederlandstalige Kamer van de Federale Raad van beroep van landmeters-experten;Overwegende dat, hoewel de wet van 11 mei 2003 tot oprichting van federale raden van landmeters-experten sinds 1 januari 2025 is opgeheven door artikel 2, tweede lid, van het bovengemelde koninklijk besluit van 25 april 2024, het noodzakelijk is, omwille van de rechtszekerheid, een einde te maken aan de theoretisch nog lopende mandaten bij de Federale Raad van landmeters-experten en de Federale Raad van Beroep van landmeters-experten;Op de voordracht van de Minister van Middenstand,Hebben Wij besloten en besluiten Wij :Artikel 1. Aan de heer Philippe ARNOULD wordt eervol ontslag verleend uit zijn functie van voorzitter van de Franstalige Kamer van de Federale Raad van landmeters-experten.Art. 2. Aan de heer Bernard DENAMUR wordt eervol ontslag verleend uit zijn functie van plaatsvervangend voorzitter van de Franstalige Kamer van de Federale Raad van landmeters-experten.Art. 3. Aan mevrouw Nicole D'HONT wordt eervol ontslag verleend uit haar functie van plaatsvervangend voorzitter van de Nederlandstalige Kamer van de Federale Raad van landmeters-experten.Art. 4. Aan de heer Philippe AOUST wordt eervol ontslag verleend uit zijn functie van voorzitter van de Franstalige Kamer van de Federale Raad van Beroep van landmeters-experten.Art. 5. Aan de heer Stefaan DESMET wordt eervol ontslag verleend uit zijn functie van plaatsvervangend voorzitter van de Nederlandstalige Kamer van de Federale Raad van Beroep van landmeters-experten.Art. 6. Dit besluit treedt in werking de dag waarop het in het Belgisch Staatsblad wordt bekendgemaakt.Art. 7. De minister bevoegd voor Middenstand is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Middenstand,E. SIMONET 
 </t>
         </is>
       </c>
@@ -1445,28 +1446,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025200960</t>
+          <t>2025003896</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15 mei 2025</t>
+          <t>23 mei 2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 31 januari 2024, gesloten in het Paritair Comité voor de bedienden van de textielnijverheid, betreffende de invoering en organisatie van overbruggingsploegen voor de bedienden in de textielsector (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit tot bepaling van de datum van inwerkingtreding van de artikelen 79 en 81 tot 88 van de wet van 3 mei 2024 houdende diverse bepalingen inzake economie (I)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-15&amp;numac_search=2025200960&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200960=31&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-23&amp;numac_search=2025003896&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003896=31&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de bedienden van de textielnijverheid; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 31 januari 2024, gesloten in het Paritair Comité voor de bedienden van de textielnijverheid, betreffende de invoering en organisatie van overbruggingsploegen voor de bedienden in de textielsector. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de bedienden van de textielnijverheid Collectieve arbeidsovereenkomst van 31 januari 2024 Invoering en organisatie van overbruggingsploegen voor de bedienden in de textielsector (Overeenkomst geregistreerd op 27 februari 2024 onder het nummer 186294/CO/214) HOOFDSTUK I. - Algemene bepalingen Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op alle werkgevers die onder de bevoegdheid vallen van het Paritair Comité voor de bedienden van de textielnijverheid (PC 214) en op de bedienden die ze tewerkstellen.  § 2. Met "bedienden" worden de mannelijke en vrouwelijke bedienden bedoeld. Art. 2. Het stelsel van de overbruggingsploegen biedt aan de in artikel 1 bedoelde ondernemingen de mogelijkheid om, hetzij voor heel de onderneming, hetzij voor één of meerdere afdelingen ervan, een aantal bijkomende machine-uren per jaar te realiseren.Art. 3. De ondernemingen die van de mogelijkheden van deze collectieve arbeidsovereenkomst gebruik wensen te maken, dienen zich in een ondernemingsovereenkomst, gesloten overeenkomstig de bepalingen van hiernavolgend artikel 5, te verbinden tot een verhoging van het aantal arbeidsplaatsen in de afdeling(en) waar het stelsel van de overbruggingsploegen wordt ingevoerd. De invoering van de overbruggingsploegen dient in elk geval een verhoging van het totaal aantal effectief tewerkgestelde werknemers in de onderneming tot gevolg te hebben. De invoering van de overbruggingsploegen in één of meerdere afdelingen mag geen aanleiding geven tot afdankingen in andere afdelingen, tenzij in geval van sluiting van bepaalde afdelingen van de betrokken onderneming. In geval van invoering van productievere technologieën kan afgeweken worden van de verplichting tot verhoging van de tewerkstelling mits ter zake en voorafgaand aan de invoering ervan, een ondernemingsovereenkomst gesloten wordt tussen de betrokken werkgever, de vertegenwoordigers van de bedienden in de onderneming, Fedustria en de werknemersorganisaties. Art. 4. De ondernemingen die overbruggingsploegen hebben ingevoerd, dienen bij eventuele tijdelijke werkloosheid om economische redenen deze gelijkwaardig te verdelen over alle werkstelsels van de betrokken afdeling(en). Art. 5. Elke onderneming, bedoeld in artikel 1, kan overgaan tot de invoering van overbruggingsploegen op voorwaarde dat zulks het voorwerp uitmaakt van een overeenkomst gesloten op het vlak van de onderneming tussen de werkgever, de vertegenwoordigers van de bedienden, Fedustria en de werknemersorganisaties. Fedustria en de werknemersorganisaties zullen met elkaar contact opnemen vooraleer zij, in toepassing van deze kaderovereenkomst, een ondernemingsakkoord sluiten en/of concrete werkvoorwaarden bepalen. Ter gelegenheid van dit contact zal nagegaan worden of de verhoging of bevordering van de tewerkstelling in de onderneming de optimale benutting van het productieapparaat vergt. Art. 6. De in artikel 5 bedoelde ondernemingsovereenkomsten dienen in elk geval de regels en principes te eerbiedigen welke in deze collectieve arbeidsovereenkomst worden vastgelegd. De in artikel 5 bedoelde ondernemingsovereenkomsten die van toepassing zijn op de datum van inwerkingtreding van onderhavige collectieve arbeidsovereenkomst, worden geacht te zijn gesloten in uitvoering van onderhavige collectieve arbeidsovereenkomst. HOOFDSTUK II. - Arbeidsduur en bezoldiging Art. 7. De overbruggingsploegen verzekeren de continuïteit van de bedrijfsactiviteiten in de afdeling(en) waar ze worden ingevoerd en dit op de zaterdagen, zondagen, wettelijke feestdagen en op de vervangingsdagen voor de wettelijke feestdagen en op andere dagen waarop door de traditionele ploegen niet gewerkt wordt. Per ploeg zal de bediende 12 uur aanwezig zijn waarvan 11 u 30 prestaties en een 1/2 uur bezoldigde rust. Zij zullen evenwel geen prestaties leveren op drie zaterdagen en drie zondagen per jaar, dit in de periode van de jaarlijkse collectieve vakantie. Art. 8. Voor de in artikel 7 bedoelde arbeidsprestaties en betaalde rust dient de globale jaarbezoldiging, die aan de bediende zou betaald worden indien hij normaal tijdens de weekdagen zou tewerkgesteld worden, gewaarborgd te worden. Art. 9. Elke andere prestatie dan deze bedoeld in artikel 7, moet als een buitengewone prestatie beschouwd worden en dient vergoed te worden aan hetzelfde loon als voor de gewone prestaties in de overbruggingsploegen. De werknemers in de overbruggingsploegen kunnen echter niet opgeroepen worden op dagen tijdens de periode van de jaarlijkse collectieve vakantie. Art. 10. De tijd gedurende dewelke de in dit stelsel tewerkgestelde bediende op vraag van de werkgever opleiding volgt tijdens de weekdagen (maandag tot en met vrijdag) zal betaald worden aan het loon die aan de bediende zou betaald worden indien hij normaal tijdens de weekdagen zou tewerkgesteld worden.Eventueel gunstigere regelingen, die op het vlak van de onderneming bestaan, blijven verder van toepassing. Art. 11. De tijd gedurende dewelke de in dit stelsel tewerkgestelde bediende tijdens de weekdagen (maandag tot en met vrijdag) deelneemt aan de vergadering van de ondernemingsraad en/of het comité voor preventie en bescherming op het werk, zal betaald worden aan het loon die aan de bediende zou betaald worden indien hij normaal tijdens de weekdagen zou tewerkgesteld worden. Eventueel gunstigere regelingen, die op het vlak van de onderneming bestaan, blijven verder van toepassing. HOOFDSTUK III. - Toetreding Art. 12. De toetreding tot het stelsel van de overbruggingsploegen is vrij. Voor de bedienden betekent dit dat zij niet kunnen verplicht worden om in bedoeld stelsel te werken. Bovendien wordt uitdrukkelijk overeengekomen dat de ondernemingen die de overbruggingsploegen willen invoeren, voor de samenstelling van deze ploegen uitsluitend mogen rekruteren uit volledig en uitkeringsgerechtigde werklozen, behoudens het op vrijwillige basis inschakelen in deze ploegen van bij de onderneming in dienst zijnde werknemers op voorwaarde dat elk van deze bedienden op zijn oorspronkelijke werkpost vervangen wordt onverminderd de toepassing van de beschikkingen van de laatste alinea van artikel 3. HOOFDSTUK IV. - Waarborgen Art. 13.  De ondernemingen die overbruggingsploegen invoeren, dienen voor de in dit stelsel tewerkgestelde bedienden alle rechten en voordelen te waarborgen die voortvloeien uit de uitvoering van een arbeidsovereenkomst voor onbepaalde duur in de traditionele werkstelsels. Art. 14. Elke onderneming die een stelsel van overbruggingsploegen invoert dient er voor te zorgen dat de in het stelsel tewerkgestelde bedienden geen enkel financieel nadeel inzake socialezekerheidsvergoedingen ondervinden tijdens de uitvoering van de arbeidsovereenkomst en na de beëindiging van de arbeidsovereenkomst. HOOFDSTUK V. - Evaluatie Art. 15. Het Paritair Comité voor de bedienden van de textielnijverheid zal tweejaarlijks, in de loop van de maand december, een rapport opmaken inzake de naleving van deze collectieve arbeidsovereenkomst en de tewerkstellingsresultaten die de toepassing van overbruggingsploegen oplevert. Art. 16.  Teneinde het paritair comité in de mogelijkheid te stellen het in artikel 15 bedoelde rapport op te stellen, is elke onderneming die de overbruggingsploegen invoert, ertoe gehouden, binnen de maand volgend op het sluiten van de desbetreffende ondernemingsovereenkomst, een exemplaar van de overeenkomst over te maken aan de voorzitter van het Paritair Comité voor de bedienden van de textielnijverheid. Bovendien dient Fedustria alle gegevens te verzamelen betreffende de tweejaarlijkse evolutie van de tewerkstelling in de ondernemingen waar het stelsel van overbruggingsploegen werd ingevoerd. Meer in het bijzonder dient voor elk van deze ondernemingen een overzicht opgemaakt te worden betreffende de evolutie van het aantal arbeidsplaatsen in de afdeling(en) waar dergelijk stelsel werd ingevoerd en tevens van de evolutie van het aantal arbeidsplaatsen voor de totaliteit van de onderneming. Deze gegevens dienen vervat te worden in een verslag dat per onderneming het beoogde overzicht weergeeft. Bedoeld verslag dient door Fedustria aan de voorzitter van het Paritair Comité voor de bedienden van de textielnijverheid te worden overgemaakt. HOOFDSTUK VI. - Eindbepalingen Art. 17. Er kan een einde worden gesteld aan een stelsel van overbruggingsploegen in een onderneming of in een ondernemingsafdeling, mits het in acht nemen van een opzeg van drie maanden, schriftelijk betekend aan de ondertekenende partijen van de ondernemingsovereenkomst. Art. 18. Elk interpretatiegeschil betreffende deze kaderovereenkomst zal aan het Paritair Comité voor de bedienden van de textielnijverheid voorgelegd worden en door deze beslecht worden. Art. 19. Deze collectieve overeenkomst heeft uitwerking vanaf 1 januari 2024. Zij wordt gesloten voor onbepaalde duur en kan slechts opgezegd worden mits een opzeg van één jaar, schriftelijk aan de ondertekenende partijen betekend.Art. 20. De nationale kaderovereenkomst van 12 januari 2023 betreffende de invoering en organisatie van overbruggingsploegen voor de bedienden in de textielsector (registratienummer 177861/CO/214), wordt opgeheven met ingang van de datum van inwerkingtreding van onderhavige collectieve arbeidsovereenkomst. Art. 21. De ondertekenende partijen vragen dat deze collectieve arbeidsovereenkomst algemeen verbindend zou verklaard worden per koninklijk besluit. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 3 mei 2024 houdende diverse bepalingen inzake economie (I), artikel 101;Gelet op het advies van de Inspecteur van Financiën, gegeven op 28 januari 2025;Gelet op advies 77.551/1 van de Raad van State, gegeven op 3 april 2025, met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Overwegende dat alle bepalingen van de wet van 27 maart 2023 tot bescherming van het beroep en de titel van landmeter-expert en tot oprichting van een Orde van landmeters-experten in werking zijn getreden op 1 januari 2025, en dit krachtens artikel 1 van het koninklijk besluit van 25 april 2024 tot bepaling van de datum van inwerkingtreding van de wet van 27 maart 2023 tot bescherming van het beroep en de titel van landmeter-expert en tot oprichting van een Orde van landmeters-experten en tot opheffing van de wet van 11 mei 2003 tot bescherming van de titel en van het beroep van landmeter-expert en van de wet van 11 mei 2003 tot oprichting van federale raden van landmeters-experten;Overwegende dat artikel 79 van de wet van 3 mei 2024 houdende diverse bepalingen inzake economie (I) de omschrijving van één van de Belgische diploma's erkend door de Franse Gemeenschap dat toegang geeft tot het beroep van landmeter-expert wijzigt, omdat de titel die wordt uitgereikt door het hoger onderwijs in de Franse Gemeenschap "master en sciences de l'ingénieur industriel, orientation géomètre" is, en niet "master en sciences de l'ingénieur industriel, finalité géomètre";Overwegende dat deze bepaling op dezelfde datum in werking moet treden als de andere bepalingen van de voornoemde wet van 27 maart 2023, aangezien zij ertoe strekt een feitelijke toestand te regulariseren;Overwegende dat de artikelen 81 tot 88 van de wet van 3 mei 2024 houdende diverse bepalingen inzake economie (I) wijzigingen aanbrengen aan diezelfde wet van 27 maart 2023 met verwijzingen naar de bevoegdheden, procedures en mogelijkheden tot vervolging voorzien in het Wetboek van economisch recht;Overwegende het voornoemde advies van de Raad van State, onder randnummer 4.2.;Overwegende dat de voornoemde artikelen 81 tot en met 88 niet op dezelfde datum, namelijk op 1 januari 2025, in werking mogen treden, aangezien de geldboeten waarin deze bepalingen voorzien, strafrechtelijk van aard zijn en geen terugwerkende kracht mogen hebben;Op de voordracht van de Minister van Middenstand,Hebben Wij besloten en besluiten Wij :Artikel 1. Artikel 79 van de wet van 3 mei 2024 houdende diverse bepalingen inzake economie (I) heeft uitwerking met ingang van 1 januari 2025.De artikelen 81 tot 88 van dezelfde wet treden in werking op de eerste dag van de maand na afloop van een termijn van tien dagen te rekenen van de dag volgend op de bekendmaking van dit besluit in het Belgisch Staatsblad.Art. 2. De minister bevoegd voor Middenstand is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Middenstand,E. SIMONET 
 </t>
         </is>
       </c>
@@ -1477,28 +1478,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025200286</t>
+          <t>2025003814</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>15 mei 2025</t>
+          <t>26 mei 2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 14 november 2024, gesloten in het Paritair Comité voor het bouwbedrijf, betreffende de wijziging van de collectieve arbeidsovereenkomst van 16 november 2006 tot invoering van een overgangsregeling inzake pensioen ten voordele van de arbeiders van de bouwnijverheid (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit tot wijziging van de artikelen 11, §§ 4 en 5, 14, e), 20, §§  1 en 2, 25, § 4, en 34, § 1, van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-15&amp;numac_search=2025200286&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200286=32&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-26&amp;numac_search=2025003814&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003814=32&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het bouwbedrijf; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 14 november 2024, gesloten in het Paritair Comité voor het bouwbedrijf, betreffende de wijziging van de collectieve arbeidsovereenkomst van 16 november 2006 tot invoering van een overgangsregeling inzake pensioen ten voordele van de arbeiders van de bouwnijverheid. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor het bouwbedrijf Collectieve arbeidsovereenkomst van 14 november 2024 Wijziging van de collectieve arbeidsovereenkomst van 16 november 2006 tot invoering van een overgangsregeling inzake pensioen ten voordele van de arbeiders van de bouwnijverheid (Overeenkomst geregistreerd op 5 december 2024 onder het nummer 190882/CO/124) HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers van de ondernemingen die onder het Paritair Comité voor het bouwbedrijf ressorteren en op de arbeiders die tewerkgesteld zijn of werden door één of meerdere ondernemingen die ressorteren onder dit paritair comité en die behoren tot één van de categorieën die vastgesteld worden in de artikelen 1 en 2 van de collectieve arbeidsovereenkomst van 16 november 2006 tot invoering van een overgangsregeling inzake pensioen ten voordele van de arbeiders van de bouwnijverheid (registratienummer : 81511/CO/124). Onder "arbeiders" wordt verstaan : de arbeiders en de arbeidsters. Art. 2. Deze collectieve arbeidsovereenkomst heeft tot doel de voormelde collectieve arbeidsovereenkomst van 16 november 2006 tot invoering van een overgangsregeling inzake pensioen ten voordele van de arbeiders van de bouwnijverheid te wijzigen. HOOFDSTUK II. - Wijzigende bepaling Art. 3. Artikel 4, § 2 van de in artikel 2 bedoelde collectieve arbeidsovereenkomst van 16 november 2006 wordt vervangen door de volgende bepaling : " § 2. Voor deze arbeiders geldt eveneens dat : 1° Indien P1 + C &gt; 2 000 EUR dan wordt P1 = max (0,2 000-C); 2° Indien P1 + C &lt; R, Constructiv in plaats van een pensioen P1, een pensioen P2 zal toekennen dat gelijk is aan : (n'+30)/45 * R Indien P2 + C groter is dan R, wordt P2 = max (0, R - C) Waarbij : n' (beperkt tot 15) gelijk is aan het aantal legitimatiekaarten "Rechthebbende" met betrekking tot prestaties vóór 2007; C = de rente die wordt bekomen door de kapitaalswaarde waarop de arbeider op datum van pensionering recht heeft binnen de toekomstige pensioentoezegging opgericht in het kader van de wet van 28 april 2003 betreffende de aanvullende pensioenen, om te zetten in een jaarlijkse, achteraf betaalbare, levenslange rente. Deze omzetting gebeurt op basis van de sterftetabel MR met een leeftijdscorrectie van -5 jaar en een technische rentevoet die overeenkomt met het wettelijke minimumrendement uit de wet van 28 april 2003 betreffende de aanvullende pensioenen (WAP) + 0,25 pct.". HOOFDSTUK III. - Geldigheidsduur Art. 4. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025. Zij heeft dezelfde geldigheidsduur en opzegmodaliteiten als de voormelde collectieve arbeidsovereenkomst van 16 november 2006 tot invoering van een overgangsregeling inzake pensioen ten voordele van de arbeiders van de bouwnijverheid, die zij wijzigt. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, artikel 35, § 1, vijfde lid, en § 2, eerste lid, 1°,  gewijzigd bij het koninklijk besluit van 25 april 1997, bekrachtigd bij de wet van 12 december 1997;Gelet op het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen;Gelet op het voorstel van de Technische geneeskundige raad, gedaan tijdens zijn vergadering van 18 juni 2024;Gelet op het advies van de Dienst voor geneeskundige evaluatie en controle van het Rijksinstituut voor ziekte- en invaliditeitsverzekering, gegeven op 18 juni 2024;Gelet op de beslissing van de Nationale commissie artsen-ziekenfondsen van 27 september 2024;Gelet op het advies van de Commissie voor begrotingscontrole, gegeven op 23 oktober 2024;Gelet op de beslissing van het Comité van de verzekering voor geneeskundige verzorging van het Rijksinstituut voor ziekte- en invaliditeitsverzekering van 28 oktober 2024;Gelet op het advies van de Inspecteur van Financiën, gegeven op 19 december 2024;Gelet op de akkoordbevinding van de Minister van Begroting van 14 maart 2025;Gelet op advies 77.632/2 van de Raad van State, gegeven op 25 april 2025, met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Op de voordracht van de Minister van Sociale Zaken,Hebben Wij besloten en besluiten Wij :Artikel 1. In artikel 11 van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen, laatstelijk gewijzigd bij het koninklijk besluit van 28 maart 2024, worden de volgende wijzigingen aangebracht:1°  in paragraaf 4,a) wordt de omschrijving van de verstrekking 355434-355445 vervangen als volgt:"° *Peritoneale punctie van vrij vocht . . . . . K 10,5";b) wordt de omschrijving van de verstrekking 355456-355460 vervangen als volgt:"° *Peritoneale drainage van vrij vocht, inclusief de eventuele inspuitingen en spoelingen . . . . . K 19";c) wordt de omschrijving van de verstrekking 355471-355482 vervangen als volgt:"° *Pericardpunctie of pericarddrainage (inclusief de eventuele inspuitingen en spoelingen) . . . . . K 70";d) worden na de verstrekking 355471-355482 de volgende verstrekkingen en toepassingsregels ingevoegd:"355994-356005° * Diagnostische, unilaterale pleurapunctie, één of meerdere . . . . .  . . . . . K 25 356016-356020° * Therapeutische, unilaterale pleurapunctie (evacuatie van vocht of lucht), één of meerdere, inclusief eventuele inspuitingen . . . . . K 32356031-356042°  Plaatsen van één of meerdere, unilaterale pleuradrains voor pneumothorax, pleuravocht of hemothorax, al dan niet gevolgd door continue aspiratie, buiten heelkundige en percutane interventionele verstrekkingen . . . . . K 56356053-356064° * Unilaterale pleurodese via één of meerdere pleuradrains . . . . . K 35Bij het aanrekenen van de verstrekkingen 355994-356005, 356016-356020 en 356031-356042 dient de lateraliteit (links of rechts) vermeld te worden en dit ongeacht de wijze van aanrekenen.De verstrekkingen 355994-356005, 356016-356020 en 356031-356042 kunnen niet op dezelfde dag met elkaar worden gecumuleerd, als ze aan dezelfde kant worden uitgevoerd.Indien puncties en/of pleurale drainages bilateraal worden uitgevoerd, mag voor elke zijde een van de verstrekkingen 355994-356005, 356016-356020 en 356031-356042 aan 100% aangerekend worden.De verstrekking 356053-356064 mag niet op dezelfde dag gecumuleerd worden met de verstrekking 356031-356042.";2°  in paragraaf 5,a) wordt het eerste lid vervangen als volgt:" § 5. Voor de verstrekkingen 350033-350044, 350055-350066, 351035-351046, 353172-353183, 353231-353242, 353275-353286, 354056-354060, 354196-354200, 354325, 355132-355143, 355316-355320, 355375-355386, 355412-355423, 355434-355445, 355456-355460, 355471-355482, 355493-355504, 355552-355563, 355530-355541, 355574-355585, 355596-355600, 355611-355622, 355633-355644, 355655-355666, 355670-355681, 355692-355703, 355714-355725, 355736-355740, 355751-355762, 355795-355806, 355810-355821, 355854-355865, 355876-355880, 355891-355902, 355913-355924, 355935-355946, 355950-355961, 355972-355983, 355994-356005, 356016-356020, 356031-356042, 356053-356064 en 475075-475086, verricht bij kinderen jonger dan 7 jaar wordt de betrekkelijke waarde verhoogd met 13 %.";b) wordt de omschrijving van de verstrekking 355913-355924 vervangen als volgt:"Bijkomend honorarium bij de verstrekkingen 355353-355364, 355375-355386, 355434-355445, 355456-355460, 355471-355482, 355552-355563, 355596-355600, 355611-355622, 355633-355644, 355670-355681, 355714-355725, 355751-355762, 355994-356005, 356016-356020, 356031-356042, 475930-475941, 475952-475963, 475974-475985 en 475996-476000, wanneer zij uitgevoerd worden onder echografische of radiologische controle . . . . . K 20".Art. 2. In artikel 14, e), van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen, laatstelijk gewijzigd bij het koninklijk besluit van 3 oktober 2018, wordt de verstrekking 227496-227500 geschrapt.Art. 3. In artikel 20 van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen, laatstelijk gewijzigd bij het koninklijk besluit van 29 februari 2024, worden de volgende wijzigingen aangebracht:1°  in paragraaf 1,a) worden in de bepalingen onder b),(i) de verstrekkingen 471516-471520, 471531-471542 en 471553-471564 geschrapt;(ii) in de tweede toepassingsregel na de verstrekking 471855-471866 worden de woorden "471516 - 471520, 471531 - 471542, 471553 - 471564, " geschrapt;b) wordt in de bepalingen onder c) de vierde toepassingsregel na de verstrekking 473970-473981 vervangen als volgt:"De verstrekking wordt niet gecumuleerd met een verstrekking voor een handeling ter aanvulling van een digestieve endoscopie (474736 - 474740, 473874 - 473885, 472393 - 472404, 473211 - 473222, 473270 - 473281, 473292 - 473303, 474773 - 474784, 473675 - 473686, 474891 - 474902, 473815 - 473826, 473911 - 473922, 473955 - 473966, 474795 - 474806), met uitzondering van de behandeling van een fistel of perforatie van het spijsverteringskanaal.";c) worden in de bepalingen onder d) de verstrekkingen 474036-474040, 474132-474143, 474154-474165 en 474213-474224 geschrapt;2°  in paragraaf 2,a) worden in de bepalingen onder A., 4., de woorden "471516-471520, 471531-471542, 471553-471564, " geschrapt;b) worden in de bepaling onder B., 3., de woorden "471516-471520, 471531-471542, 471553-471564, ", de woorden "474036-474040, " en de woorden "474213-474224, " geschrapt;c) in de bepalingen onder C.,(i) worden in de bepaling onder 5. de woorden "471516-471520, ", de woorden "474036-474040, " en de woorden ", 474213-474224" geschrapt;(ii) worden in de bepaling onder 6. de woorden "471516-471520, ", de woorden "474036-474040, " en de woorden ", 474213-474224" geschrapt.Art. 4. In artikel 25, § 4, van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen, laatstelijk gewijzigd bij het koninklijk besluit van 7 mei 2023, worden de woorden "471553 - 471564, ", de woorden "474036 - 474040, ", de woorden "474132 - 474143, 474154 - 474165, " en de woorden "474213 - 474224, " geschrapt.Art. 5. In artikel 34, § 1, b), van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen, laatstelijk gewijzigd bij het koninklijk besluit van 19 januari 2023, worden de volgende wijzigingen aangebracht:1°  de omschrijving van de verstrekking 589234-589245 wordt vervangen als volgt:"Percutane drainage van een vochtcollectie in een streek of in een diepliggend orgaan van de thorax, van het abdomen of van het bekken onder controle van medische beeldvorming, inclusief de manipulaties en controles tijdens de behandeling en de gebruikte katheters, exclusief de farmaca, de contrastmiddelen en de tweewegdraineersonden . . . . . I 329";2°  na de verstrekking 589234-589245 wordt de volgende toepassingsregel ingevoegd:"De verstrekking 589234-589245 kan niet worden aangerekend voor een punctie of drainage van de pleura of het pericard of van vrij intraperitoneaal vocht.".Art. 6. Dit besluit treedt in werking op de eerste dag van de tweede maand na die waarin het is bekendgemaakt in het Belgisch Staatsblad.Art. 7. De minister bevoegd voor Sociale Zaken is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Sociale Zaken en Volksgezondheid,F. VANDENBROUCKE 
 </t>
         </is>
       </c>
@@ -1509,28 +1510,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025200238</t>
+          <t>2025003815</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15 mei 2025</t>
+          <t>26 mei 2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 18 november 2024, gesloten in het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap, betreffende de minimumduur van de werkperiode, de grens bijkomende prestaties voor deeltijdse werknemers en uurroosterverstoring (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit tot wijziging van artikel 37bis, § 1, E., van de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-15&amp;numac_search=2025200238&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200238=33&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-26&amp;numac_search=2025003815&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003815=33&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 18 november 2024, gesloten in het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap, betreffende de minimumduur van de werkperiode, de grens bijkomende prestaties voor deeltijdse werknemers en uurroosterverstoring. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap Collectieve arbeidsovereenkomst van 18 november 2024 Minimumduur van de werkperiode, grens bijkomende prestaties voor deeltijdse werknemers en uurroosterverstoring (Overeenkomst geregistreerd op 20 december 2024 onder het nummer 191192/CO/318.02) Artikel 1. Toepassingsgebied Deze collectieve arbeidsovereenkomst is van toepassing op de werknemers en de werkgevers van de diensten voor gezinszorg (gezins- en bejaardenhulp) van de Vlaamse Gemeenschap. Onder "werknemers" wordt verstaan : de werknemers die worden tewerkgesteld als verzorgende, oppasser, poetshulp/huishoudhulp in de gezinszorg, ongeacht hun arbeidsritme (vast of variabel) en ongeacht hun uurrooster (vast of variabel), inbegrepen de werknemers betaald uit de middelen Sociale Maribel en de werknemers tewerkgesteld in een GESCO-statuut, uitgezonderd medewerkers tewerkgesteld in het kader van "Opvang ziek kind". Art. 2. Minimumduur van de werkperiode In toepassing van het artikel 21 van de arbeidswet van 16 maart 1971 wordt de duur van de werkperiode bepaald op twee uren voor vooraf bepaalde situaties. Dit is het geval voor cliëntenoverleg, wijkwerking, medisch onderzoek en voor cliëntgerichte vormingen die op de werkvloer dienen georganiseerd te worden. Art. 3.  Verhoging van de grens bijkomende prestaties voor deeltijdse werknemers  § 1. Voor de toepassing van deze collectieve arbeidsovereenkomst wordt verstaan onder bijkomende prestaties : - Wanneer er een vast arbeidsritme wordt toegepast : elke prestatie die buiten het uurrooster wordt verricht; - Wanneer een variabel arbeidsritme wordt toegepast : elke prestatie die verricht wordt : - buiten het bekendgemaakt uurrooster; - bovenop de contractuele arbeidsduur.  § 2. Het urenkrediet voor bijkomende prestaties waarvoor de werkgevers geen toeslag voor overloon verschuldigd zijn, wordt voor werknemers met een vast arbeidsritme vastgesteld op 30 uur per maand. Werknemers verrichten deze bijkomende prestaties op vrijwillige basis en in het kader van cliëntgebonden behoeften en vragen.  § 3. Het urenkrediet voor bijkomende prestaties waarvoor de werkgevers geen toeslag voor overloon verschuldigd zijn, wordt voor werknemers met een variabel arbeidsritme vastgesteld op 4 uren x het aantal weken begrepen in de referteperiode (met een maximum van 208 uren).  § 4. De omwisseling van uurroosters tussen werknemers onderling of de verschuiving van uurroosters op verzoek van de werknemer, blijven uit het krediet van bijkomende prestaties. Op het niveau van de organisatie wordt aantoonbaar gemaakt van wie de vraag tot omwisseling of verschuiving van uurroosters afkomstig is.Art. 4.  Uurroosters en uurroosterverstoring  § 1. Voor werknemers met een vast uurrooster ligt het uurrooster vast in de individuele arbeidsovereenkomst. Dit uurrooster wordt in de regel gevolgd. Het vaste uurrooster moet wettelijk gezien niet bekend gemaakt worden.  § 2. Voor werknemers die variabel werken (cfr. collectieve arbeidsovereenkomst van 18 november 2024 betreffende flexibiliteit en variabele tewerkstelling) is het werkregime gebaseerd op een referentie-uurrooster (cfr. artikel 4, § 2). Tot uiterlijk 7 werkdagen op voorhand kunnen wijzigingen aangebracht worden aan het referentie-uurrooster, conform artikel 6, § 1, 1°, d) van de wet van 8 april 1965 tot instelling van de arbeidsreglementen, zoals gewijzigd door artikel 2, 1° van de wet van 3 oktober 2022 houdende de diverse arbeidsbepalingen. Dit aldus bekendgemaakt uurrooster wordt gevolgd, tenzij in de uitzonderingen voorzien in artikel 4, § 5.  § 3. De kennisgeving van de uurroosters/werktijden gebeurt door middel van een aantoonbare communicatie. Op ondernemingsniveau worden de gebruikte communicatiemiddelen en de modaliteiten van het gebruik ervan vastgelegd in overleg met de ondernemingsraad of, bij ontstentenis, het CPBW of, bij ontstentenis, de syndicale delegatie.  § 4. De werkgevers verbinden zich ertoe alles in het werk te stellen om de uurroosters/werktijden van de werknemers te respecteren. Indien er in de dienst voor gezinszorg een mobiele equipe/vervangequipe/vlinderteam is, wordt in de eerste plaats dit team ingeschakeld voor dringende hulpvragen.  § 5. Teneinde de continuïteit van de zorg te waarborgen en teneinde tegemoet te komen aan dringende hulpvragen kunnen de werkgevers vragen aan zowel de werknemers met een vast uurrooster als deze met een variabel uurrooster om af te wijken van het uurrooster na de bekendmaking ervan 7 werkdagen op voorhand. Dit wordt een uurroosterverstoring genoemd. Een dringende hulpvraag is een vraag waarbij de zorgverlening omwille van de eigenschappen van de hulpvraag niet kan worden uitgesteld. Zowel het moment waarop de zorgverlening dient te gebeuren als de betrokkenheid op de persoon van de cliënt als de aard van de opdracht zijn elementen die de dringendheid van de hulpvraag bepalen. De uurroosterverstoring kan enkel plaatsvinden met toestemming van de werknemer. Deze toestemming kan zowel mondeling als schriftelijk (sms, e-mail, overeenkomst, enz.) zijn. De werkgevers voorzien nadien in een schriftelijk spoor van de toestemming. De werknemer behoudt dan ook het recht om de vraag tot uurroosterverstoring te kunnen weigeren.  § 6. Afwijkingen van het uurrooster op vraag van de werknemer zelf en wissels tussen werknemers onderling worden in geen geval beschouwd als een uurroosterverstoring. Art. 5.  Vergoeding voor uurroosterverstoring  § 1. Indien er zich een uurroosterverstoring voordoet, waarbij op vraag van de werkgever de werknemer akkoord is gegaan om te werken op een moment dat niet voorzien werd in het uurrooster dat of de werkplanning die 7 werkdagen op voorhand werd meegedeeld, ontvangt de werknemer een : - vergoeding van 7 EUR indien de wijziging wordt overeengekomen op de 4de, 3de of 2de werkdag vóór de prestatie; - vergoeding van 13 EUR indien de wijziging wordt overeengekomen op de werkdag vóór de dag van de prestatie; - vergoeding van 16 EUR indien de wijziging wordt overeengekomen op de dag van de prestatie zelf. De hierboven vermelde vergoedingen zijn van toepassing op 1 november 2021 en zijn gekoppeld aan spilindex 109,34. Zij worden geïndexeerd volgens dezelfde regels als de lonen van de werknemers aan wie de vergoedingen worden uitbetaald. De geïndexeerde bedragen worden afgerond tot 2 decimalen. De effectief uitbetaalde vergoedingen worden per dag volgens de wiskundige regels afgerond tot de halve EUR, zonder dat het onderliggende bedrag verder wordt afgerond. Bij meerdere wijzigingen van de planning is het enkel de hoogste vergoeding die wordt voorzien. Indien een overeengekomen roosterwijziging op een later moment in onderling akkoord ongedaan gemaakt wordt, geldt dit niet als een nieuwe roosterverstoring. In dit geval blijft de vergoeding van de eerste roosterwijziging van toepassing.  § 2. De vergoeding is evenwel niet van toepassing : - bij een uurroosterverstoring die bestaat uit het wijzigen of verschuiven van het voorziene rooster met minder dan 1 uur;- bij het inschakelen van een medewerker die gedurende die periode van wacht is en die hiervoor een wachtvergoeding ontvangt. Art. 6. Cumul met andere toeslagen  § 1. De collectieve arbeidsovereenkomst van 18 november 2021 (registratienummer : 168821/CO/318.02) betreffende de continue dienstverlening blijft onverminderd van toepassing.  § 2. Er is geen cumul mogelijk tussen de vergoeding voor uurroosterverstoringen en overloon. Indien er samenloop is van beide toeslagen, zal de hoogste toeslag toegekend worden, namelijk het overloon. Art. 7. Bijstand en opvolging inzake uurroosterverstoring  § 1. De syndicale delegatie krijgt het recht om werknemers bij te staan aangaande roosterverstoringen.  § 2. De ondernemingsraad ontvangt jaarlijks een rapportering over de omvang en de kostprijs van de toeslagen ingevolge de roosterverstoringen. Art. 8. Toekenning  § 1. Wanneer de werknemer overeenkomstig de toepassing van deze collectieve arbeidsovereenkomst recht heeft op een vergoeding voor de uurroosterverstoring wordt dit voor de werknemer automatisch gegarandeerd. Concrete afspraken hierover worden op ondernemingsvlak gemaakt.  § 2. Deze collectieve arbeidsovereenkomst voorziet in de uitvoering van de sectorale maatregelen kwaliteit en uitbreidingsbeleid, zoals afgesproken in het 6de Vlaams Intersectoraal Akkoord.  § 3. De hierboven vermelde bepalingen kunnen enkel toegepast worden onder voorbehoud dat de financiering ervan is opgenomen in de betoelagingsreglementering van de subsidiërende overheid. Art. 9. Inwerkingtreding  § 1. Deze collectieve arbeidsovereenkomst treedt in werking op 1 november 2024 en wordt gesloten voor onbepaalde duur.  § 2. Deze collectieve arbeidsovereenkomst kan opgezegd worden door elk der partijen, mits een opzegging van drie maanden, betekend door middel van een aangetekend schrijven gericht aan de voorzitter van het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, artikel 37ter, tweede lid, ingevoegd bij de wet van 21 december 1994;Gelet op de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994;Gelet op het advies van het Comité van de verzekering voor geneeskundige verzorging van het Rijksinstituut voor ziekte- en invaliditeitsverzekering van 28 oktober 2024;Gelet op het advies van de Inspecteur van Financiën, gegeven op 19 december 2024;Gelet op de akkoordbevinding van de Minister van Begroting van 14 maart 2025;Gelet op de impactanalyse van de regelgeving, uitgevoerd overeenkomstig artikelen 6 en 7 van de wet van 15 december 2013 houdende diverse bepalingen inzake administratieve vereenvoudiging;Gelet op advies 77.633/2 van de Raad van State, gegeven op 25 april 2025, met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Overwegende het advies van de Commissie voor begrotingscontrole, gegeven op 23 oktober 2024;Op de voordracht van de Minister van Sociale Zaken en Volksgezondheid, en op het advies van de in Raad vergaderde Ministers,Hebben Wij besloten en besluiten Wij :Artikel 1. In artikel 37bis, § 1, E, van de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, laatstelijk gewijzigd bij het koninklijk besluit van 12 augustus 2024, worden de volgende wijzigingen aangebracht:1) in de bepaling onder 1°  wordt het rangnummer "355994" ingevoegd tussen het rangnummer "355972" en het rangnummer "472511";2) in de bepaling onder 5°  worden de rangnummers "471516", "474132" en "474154" geschrapt.3) in de bepaling onder 7°  worden in het tweede lid de woorden "en 553630" vervangen door de woorden ", 553630 en 557314".Art. 2. Dit besluit treedt in werking op de eerste dag van de tweede maand na die waarin het is bekendgemaakt in het Belgisch Staatsblad, met uitzondering van de bepaling onder 3) van artikel 1 dat uitwerking heeft met ingang van 1 januari 2025.Art. 3. De minister bevoegd voor Sociale Zaken is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Sociale Zaken en Volksgezondheid,F. VANDENBROUCKE 
 </t>
         </is>
       </c>
@@ -1541,29 +1542,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025200959</t>
+          <t>2025200283</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>15 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 16 december 2024, gesloten in het Aanvullend Paritair Comité voor de non-profitsector, betreffende de besteding van de middelen geïnd via de responsabiliseringsbijdrage voor langdurig zieken (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 10 november 2023, gesloten in het Paritair Comité voor het glasbedrijf, betreffende de arbeids- en loonvoorwaarden in 2023 en 2024 (1)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-15&amp;numac_search=2025200959&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200959=34&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025200283&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200283=34&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Aanvullend Paritair Comité voor de non-profitsector; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 16 december 2024, gesloten in het Aanvullend Paritair Comité voor de non-profitsector, betreffende de besteding van de middelen geïnd via de responsabiliseringsbijdrage voor langdurig zieken.Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Aanvullend Paritair Comité voor de non-profitsector Collectieve arbeidsovereenkomst van 16 december 2024 Besteding van de middelen geïnd via de responsabiliseringsbijdrage voor langdurig zieken (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191519/CO/337) Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en werknemers van de ondernemingen die tot de bevoegdheid van het Aanvullend Paritair Comité voor de non-profitsector (PC 337) behoren. Art. 2. In afwijking van het eerste artikel is deze collectieve arbeidsovereenkomst niet van toepassing op de assistenten aangeworven in het kader van een persoonlijk assistentie-budget (PAB'ers). Juridisch kader Art. 3. Deze collectieve arbeidsovereenkomst wordt gesloten in uitvoering van : - de programmawet van 27 december 2021, artikel 147, § 2; - het koninklijk besluit van 1 oktober 2023 houdende de uitvoering van artikel 147, § 4 en § 5 van de programmawet van 27 december 2021. Bevoegd fonds Art. 4. De door de Rijksdienst voor Sociale Zekerheid geïnde middelen in het kader van de responsabiliseringsbijdrage worden toegewezen aan het "Aanvullend Sociaal Fonds van de non-profit", opgericht bij de collectieve arbeidsovereenkomst van 7 november 2017, gesloten in het Aanvullend Paritair Comité voor de non-profitsector. Art. 5. Het "Aanvullend Sociaal Fonds van de non-profit" (hierna "het fonds") wordt belast met de besteding en het gebruik van de opbrengst van de responsabiliseringsbijdrage bestemd voor preventieve maatregelen inzake gezondheid en veiligheid op het werk en/of maatregelen inzake duurzame herinschakeling van langdurig zieken. Het fonds beschikt over een termijn van drie jaar om het geïnde bedrag van de responsabiliseringsbijdrage op te vragen bij de Rijksdienst voor Sociale Zekerheid, en over drie jaar vanaf de datum van storting van de beschikbare opbrengst aan het fonds om het te besteden aan de uitvoering van de maatregelen die in deze collectieve arbeidsovereenkomst zijn vastgelegd. Art. 6. Het fonds zal de inkomsten van de responsabiliseringbijdrage gebruiken onder meer voor de volgende acties, rekening houdend met de beschikbare middelen : - Preventieve maatregelen voor gezondheid en veiligheid op de werkplek : - individuele en groepsrisicoanalyses, algemeen of specifiek met betrekking tot een domein van welzijn op het werk (gezondheid, veiligheid, psychosociale aspecten, hygiëne, ergonomie, verfraaiing van de werkplek en de werkomgeving); - het onderzoeken en/of oprichten van discussiegroepen om actievoorstellen uit te werken rond thema's die verband houden met gezondheid en veiligheid op het werk; - ontwikkeling van hulpmiddelen om het bewustzijn te vergroten en psychosociale risico's te voorkomen, die worden verspreid onder de werknemers en de leidinggevenden van de organisatie (checklists, brochures, vragenlijsten, video's met uitleg, enz.); - individuele begeleiding van werknemers (coaching, psychologische follow-up, enz.);- ergonomisch materiaal verbeteren en/of aanpassen aan de handicap; - aanpassing van de werkplek (uitgevoerde taken, werktijden, werkmethoden, enz.); - Maatregelen voor de duurzame re-integratie van langdurig zieken : - het opzetten van specifieke opleidingen; - het opzetten van vaardigheidstests, persoonlijkheidstests en motivatie-uitwisselingen tussen werknemers; - terbeschikkingstelling van middelen om waar mogelijk specifieke afdelingen op te richten die verantwoordelijk zijn voor de re-integratie van langdurig zieke werknemers (opleiding, counseling, enz.); - informeren over de procedures en mensen die verantwoordelijk zijn voor het opzetten van aangepaste werkvormen binnen de organisatie (aanpassen van werkplekken, kortere werktijden, andere functies, enz.); - koppelingen met bestaande structuren vergemakkelijken; - oprichting van een "peterschap" tussen de werknemer die terugkeert na een lange afwezigheid en een medewerker van het team, om het gewicht van de mentale belasting als gevolg van de terugkeer te verminderen; - het opzetten, voor zowel het team als de werknemer die terugkeert na een lange afwezigheid, van een coachingsaanbod met een (bedrijfs)psycholoog om enerzijds de terugkeer van de collega voor te bereiden en anderzijds te begeleiden bij de hervatting van het werk; - het opzetten voor de werkgever, de werknemer en/of de sociale partners van begeleiding/coachingsaanbod om in geval van terugkerende uitval van werknemers een concreet en aangepast preventiebeleid in de organisatie te kunnen ontwikkelen. Dit budget mag niet worden gebruikt voor maatregelen om te voldoen aan een wettelijke verplichting die voortvloeit uit de toepassing van de Codex rond welzijn op het werk. Slotbepalingen en inwerkingtreding Art. 7.  § 1. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2023 en wordt aangegaan voor onbepaalde duur.  § 2. Deze collectieve arbeidsovereenkomst kan door elk van de partijen worden opgezegd met inachtneming van een opzeggingstermijn van zes maanden. De opzegging wordt bij een ter post aangetekende brief gericht aan de voorzitter van het Aanvullend Paritair Comité voor de non-profitsector. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het glasbedrijf; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 10 november 2023, gesloten in het Paritair Comité voor het glasbedrijf, betreffende de arbeids- en loonvoorwaarden in 2023 en 2024. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 11 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor het glasbedrijf Collectieve arbeidsovereenkomst van 10 november 2023 Arbeids- en loonvoorwaarden in 2023 en 2024 (Overeenkomst geregistreerd op 30 november 2023 onder het nummer 184270/CO/115) TITEL I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en arbeiders van de ondernemingen die ressorteren onder het Paritair Comité voor het glasbedrijf. De titel IV "Loonvoorwaarden" van deze collectieve arbeidsovereenkomst is echter niet van toepassing op de werkgevers en arbeiders van de ondernemingen die ressorteren onder de subsector van de spiegelmakerij waarvoor een specifieke collectieve arbeidsovereenkomst is gesloten. Onder "arbeiders" verstaat men : zowel arbeiders als arbeidsters. TITEL II. - Onderhandelingskader Art. 2. De ondertekenende partijen en hun leden zijn akkoord om volgend punt na te leven gedurende eventuele onderhandelingen voor de periode 2023-2024 : er zullen geen eisen ingediend of besproken worden in de sector, de subsectoren en de ondernemingen uit de glasindustrie die in tegenspraak of conflict zijn met het wettelijk kader voorzien door de wet van 26 juli 1996 tot de bevordering van de werkgelegenheid en tot preventieve vrijwaring van het concurrentievermogen, gewijzigd door de wet van 19 maart 2017 en het koninklijk besluit van 13 mei 2023 tot uitvoering van artikel 7, § 1 van de wet van 26 juli 1996 tot bevordering van de werkgelegenheid en tot preventieve vrijwaring van het concurrentievermogen (Belgisch Staatsblad van 26 mei 2023) tot vaststelling van de maximale marge voor loonkostontwikkeling voor de periode 2023-2024 en het koninklijk besluit van 23 april 2023 betreffende de koopkrachtpremie (Belgisch Staatsblad van 28 april 2023).TITEL III. - Arbeidsvoorwaarden HOOFDSTUK I. - Arbeidsduur Art. 3. De overeengekomen wekelijkse arbeidsduur mag op jaarbasis gemiddeld de 38 uur per week niet overschrijden. HOOFDSTUK II. - Opeenvolgende arbeidsovereenkomsten Art. 4. In geval van opeenvolgende arbeidsovereenkomsten van bepaalde duur of vervangingsovereenkomsten, zal de gedekte periode door de bedoelde arbeidsovereenkomsten in aanmerking worden genomen voor de berekening van de anciënniteit in geval van definitieve aanwerving, voor zover er geen onderbreking plaats heeft gehad in de opeenvolging van deze contracten van meer dan vier weken. HOOFDSTUK III. - Arbeidsovereenkomsten van bepaalde duur en uitzendwerk Art. 5. De vakbondsorganisaties engageren zich om het gebruik van uitzendkrachten toe te staan daar waar het wettelijk mogelijk is. Anderzijds verbinden de werkgevers er zich toe het gebruik van uitzendarbeid te beperken tot die gevallen voorzien in de wetgeving. In dit kader, in geval van definitieve aanwerving in het vooruitzicht, zal er, in geval van gelijke competentie, voorrang verleend worden aan werknemers die verbonden waren door een arbeidsovereenkomst van bepaalde duur en aan werknemers die reeds een interimopdracht hebben uitgevoerd in de onderneming, voor zover er geen onderbreking van meer dan 18 maanden is geweest sinds hun laatste contract of missie. Er zal rekening gehouden worden met hun vorige periode(s) van ononderbroken tewerkstelling in de onderneming om hun anciënniteit te bepalen in de onderneming. Die anciënniteit zal enkel dienen voor wat betreft het basisloon en de duur van de opzeggingstermijn. HOOFDSTUK IV. - Arbeidsongevallen, andersvaliden en reintegratietraject Art. 6. Slachtoffers van een arbeidsongeval en gehandicapten De werkgevers verbinden er zich toe, in functie van de mogelijkheden, om werknemers met fysisch verminderde capaciteiten al dan niet veroorzaakt door ongeval (arbeidsongeval of privé-ongeval) of door ziekte (beroepsziekte of gewone ziekte) aan te werven of aan het werk te houden. In geval van gedeeltelijke ongeschiktheid en om maximaal ontslagen wegens overmacht te beperken, zullen de ondertekenende partijen van deze collectieve arbeidsovereenkomst alles in het werk stellen om betrokken arbeiders aan het werk te houden, in overleg met de preventieadviseur, het comité voor preventie en bescherming op het werk (of, bij ontstentenis, de vakbondsafvaardiging), de geneesheer van de externe dienst, de AWIPH en VOP met het oog op de promotie van tewerkstelling van gehandicapten, waar dit mogelijk blijkt. De ondertekenende partijen van deze collectieve arbeidsovereenkomst doen eveneens de aanbeveling om bij aanwerving van personen met een handicap gebruik te maken van de regionale subsidies (AWIPH en VOP) met het oog op de promotie van tewerkstelling van gehandicapten daar waar dit mogelijk blijkt. Art. 7. Re-integratietraject In het kader van de procedures van reintegratieprojecten, waken de werkgevers van de sector er in het bijzonder over de betrokken werknemers, met respect voor het privéleven, eraan te herinneren dat zij zich kunnen laten bijstaan door een werknemersvertegenwoordiger van het comité voor preventie en bescherming op het werk of door een syndicaal afgevaardigde van hun keuze gedurende het hele re-integratietraject (artikel 1.4-77 van de Code voor welzijn op het werk). In dit kader wordt het belang van samenwerking erkent tussen werkgevers en werknemers om het reintegratietraject goed te laten verlopen (artikel 1.4-78) en om regelmatig het comité voor preventie en bescherming op het werk te consulteren betreffende collectieve aspecten van de re-integratie en de reintegratiepolitiek in het algemeen (artikelen 1.4-78 en 1.4-79). HOOFDSTUK V. - Onderaanneming Art. 8. Indien het nodig blijkt een beroep te moeten doen op onderaannemingsbedrijven, verbindt de werkgever er zich toe de vakbondsafvaardiging of de ondernemingsraad op de hoogte te brengen van de gekende en geplande onderaannemingsactiviteiten. De informatie zal betrekking hebben op de aard van de werken, hun duur en de kwalificatie van de werknemers die deze werken zullen uitvoeren.De werkgever verbindt er zich toe een beroep te doen op onderaannemingsbedrijven die de wettelijke bepalingen inzake personeelsbezetting, de wetten en Belgische reglementen betreffende veiligheid en gezondheid van de werknemers, naleven. De opvolging van de wettelijke bepalingen inzake veiligheid en gezondheid zal gebeuren in overleg met het comité voor preventie en bescherming op het werk. HOOFDSTUK VI. - Klein verlet Art. 8bis. Vanaf 1 oktober 2023 wordt wettelijk samenwonen gelijkgesteld met huwelijk voor klein verlet huwelijk (zonder cumulatie met huwelijk). Dit betekent dat als de werknemer ervoor kiest om de 3 dagen kleine verlet (die bij een huwelijk worden toegekend) op te nemen voor het sluiten van een wettelijk samenlevingscontract, hij/zij deze niet kan terugnemen voor zijn/haar huwelijk. TITEL IV. - Loonvoorwaarden HOOFDSTUK I. - De koopkrachtpremie Art. 9. De sociale partners hebben de mogelijkheid om op ondernemingsvlak een akkoord te onderhandelen over de koopkrachtpremie tot 15 december 2023, dat in overeenstemming is met het koninklijk besluit van 23 april 2023 betreffende de koopkrachtpremie. Als uiterlijk op 15 december 2023 geen akkoord wordt bereikt op ondernemingsniveau, zal een koopkrachtpremie worden toegekend aan de arbeiders door bedrijven die een hoge of uitzonderlijk hoge winst hebben gerealiseerd in 2022. "Winst in 2022" wordt voor de toepassing van deze collectieve arbeidsovereenkomst gedefinieerd als de som van de volgende codes van de jaarrekening voor het boekjaar 2022 : - Code 9901 (bedrijfswinst/verlies); - Code 630 (afschrijvingen en waardeverminderingen op oprichtingskosten, op immateriële en materiële vaste activa); - Code 631/4 (waardeverminderingen op voorraden, op bestellingen in uitvoering en op handelsvorderingen : toevoegingen (terugnemingen)). Een bedrijf heeft een "hoge winst in 2022" gerealiseerd als zijn "winst in 2022" positief is. Een bedrijf heeft een "uitzonderlijk hoge winst in 2022" gerealiseerd als zijn "winst in 2022" minstens 1,15 x hoger is dan de gemiddelde winst in de 3 voorafgaande afgesloten boekjaren. Voor de berekening van dit gemiddelde worden enkel de boekjaren met een positieve "winst" meegeteld. Het bedrag van de koopkrachtpremie : In de ondernemingen die op 15 december 2023 geen bedrijfsakkoord hebben afgesloten en die een hoge winst hebben gerealiseerd in 2022, zoals hierboven gedefinieerd, wordt een koopkrachtpremie van 250 EUR toegekend. In de ondernemingen die op 15 december 2023 geen bedrijfsakkoord hebben afgesloten en die een uitzonderlijk hoge winst hebben gerealiseerd in 2022, zoals hierboven gedefinieerd, wordt een koopkrachtpremie van 350 EUR toegekend. Modaliteiten van toekenning : De koopkrachtpremie wordt toegekend in de loop van de maand december 2023 aan de arbeiders die in dienst zijn op 15 december 2023 : - pro rata van de arbeidsprestaties tijdens de periode die loopt van 1 januari 2022 tot en met 31 december 2022, met gelijkstellingen zoals overeengekomen in de collectieve arbeidsovereenkomst betreffende de eindejaarspremie; - pro rata van het arbeidsregime van de werknemer op 31 december 2022. Voor bedrijven wiens boekjaar niet overeenstemt met een kalenderjaar zal voor het bepalen van de winst/hoge winst/uitzonderlijk hoge winst het boekjaar genomen wordt dat eindigt in 2022. In overeenstemming met het koninklijk besluit van 23 april 2023 wordt de koopkrachtpremie op een papieren drager (cheques) of in elektronische vorm toegekend. HOOFDSTUK II. - Minimum aanwervingsloon Art. 10.  § 1. Vanaf 1 januari 2023 wordt het minimum aanwervingsloon vastgesteld op 13,5076 EUR/uur. De bovenvermelde bedragen moeten worden gesteld tegenover het spilindexcijfer 122,95 (basis 2013 = 100).Vanaf 1 november 2023 wordt het minimum aanwervingsloon vastgesteld op 13,7778 EUR/uur. De bovenvermelde bedragen moeten worden gesteld tegenover het spilindexcijfer 125,41 (basis 2013 = 100).  § 2. De mogelijkheid om een minimum aanwervingsloon betalen gelijk aan 95 pct. van het minimumloon gedurende maximum 4 weken effectieve arbeid wordt afgeschaft vanaf 1 oktober 2023. HOOFDSTUK III. - Minimale ploegenpremies Art. 11. Wanneer het werk in twee of in drie "draaiende" ploegen is ingericht, worden aan de arbeiders, zonder onderscheid van leeftijd, de ploegenpremies toegekend voor een arbeidsregeling van 38 uren per week :   </t>
         </is>
       </c>
     </row>
@@ -1573,28 +1573,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025003732</t>
+          <t>2025200278</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>15 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit tot toekenning van een subsidie van 944.000 euro voor de werking van de Centrale Raad der Niet-Confessionele Levensbeschouwelijke Gemeenschappen van België</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 19 december 2023, gesloten in het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Franse Gemeenschap en de Duitstalige Gemeenschap, betreffende de vrijstelling van de verplichting inzake aangepaste beschikbaarheid - uitzonderingsregeling in toepassing van de collectieve arbeidsovereenkomst nr. 168 gesloten in de Nationale Arbeidsraad (1)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-15&amp;numac_search=2025003732&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003732=35&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025200278&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200278=35&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de Grondwet, artikel 181, § 2;Gelet op de wet van 21 juni 2002 betreffende de Centrale Raad der Niet-Confessionele Levensbeschouwelijke Gemeenschappen van België, de afgevaardigden en de instellingen belast met het beheer van de materiële en financiële belangen van de erkende niet-confessionele levensbeschouwelijke gemeenschappen, de artikelen 48 tot 51;Gelet op de wet van 22 mei 2003 houdende organisatie van de begroting en van comptabiliteit van de federale Staat, de artikelen 121 tot 124;Gelet op de financiewet van 20 december 2024 voor het begrotingsjaar 2025, de justitiebegroting programma 59/1;Gelet op de begroting van de Centrale Raad der Niet-Confessionele Levensbeschouwelijke Gemeenschappen van België voor het dienstjaar 2025;Gelet op het advies van de Inspectie van Financiën van 20 januari 2025;Gelet op de akkoordbevinding van de Minister van Begroting van 4 april 2025;Op de voordracht van de minister van Justitie,Hebben Wij besloten en besluiten Wij :Artikel 1. Een som van 944.000 euro, ingeschreven op artikel 11.33-16 van de Afdeling 59 - Erediensten en Laïciteit - van de begroting van de FOD Justitie wordt toegekend aan de Centrale Raad der Niet-Confessionele Levensbeschouwelijke Gemeenschappen van België voor het dienstjaar 2025. Deze som is toegewezen volgens de volgende schijven:Eerste schijf   849.600 euroTweede schijf   94.400 euroArt. 2. Deze som is volgens de volgende modaliteiten toegewezen:- Personeel   169.200 euro- Werking - algemene kosten   393.200 euro- Coördinatie verenigingen, media   310.905 euro- Afschrijvingen   57.870 euro- Belastingen en bankkosten   12.825 euroArt. 3. De schijf van 10% van het subsidiebedrag wordt uitbetaald nadat de bewijsstukken betreffende de uitgaven van het jaar 2025 en het verslag van een door het Instituut van de Bedrijfsrevisoren erkende bedrijfsrevisor voor 1 mei 2026 aan de minister van Justitie zijn voorgelegd en na controle en goedkeuring van deze stukken door de FOD Justitie.Alle stukken dienen te zijn ondertekend door alle daartoe statutair toegelaten personen.Indien de sociale bijdragen en de belastingen niet zouden worden betaald, is deze subsidie onmiddellijk terugvorderbaar.De Centrale Vrijzinnige Raad wordt hoofdzakelijk gesubsidieerd door de FOD Justitie en is ertoe verplicht de wetgeving inzake overheidsopdrachten na te leven.Elke niet-verantwoorde subsidie moet worden terugbetaald.Art. 4. Dit besluit treedt in werking op 1 januari 2025.Art. 5. De minister bevoegd voor Justitie is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Justitie,A. VERLINDEN 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Franse Gemeenschap en de Duitstalige Gemeenschap; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 19 december 2023, gesloten in het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Franse Gemeenschap en de Duitstalige Gemeenschap, betreffende de vrijstelling van de verplichting inzake aangepaste beschikbaarheid - uitzonderingsregeling in toepassing van de collectieve arbeidsovereenkomst nr. 168 gesloten in de Nationale Arbeidsraad. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 11 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Franse Gemeenschap en de Duitstalige Gemeenschap Collectieve arbeidsovereenkomst van 19 december 2023 Vrijstelling van de verplichting inzake aangepaste beschikbaarheid - uitzonderingsregeling in toepassing van de collectieve arbeidsovereenkomst nr. 168 gesloten in de Nationale Arbeidsraad (Overeenkomst geregistreerd op 25 januari 2024 onder het nummer 185594/CO/152.02) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de werknemers van de onderwijsinstellingen en de internaten van het vrij onderwijs van de Franse Gemeenschap en de Duitstalige Gemeenschap, waarvan de maatschappelijke zetel gevestigd is in het Waalse Gewest en in het Brusselse Hoofdstedelijk Gewest en die zijn ingeschreven bij de Rijksdienst voor Sociale Zekerheid op de Franse taalrol. Onder "werknemers" wordt verstaan : de arbeiders en arbeidsters. Art. 2. Deze collectieve arbeidsovereenkomst wordt gesloten tot uitvoering van de collectieve arbeidsovereenkomst nr. 168 van 30 mei 2023 tot vaststelling, voor de periode van 1 juli 2023 tot 31 december 2024, van de toekenningsvoorwaarden van de vrijstelling van de verplichting inzake aangepaste beschikbaarheid voor de oudere werknemers met een lange loopbaan die vóór 1 januari 2025 ontslagen worden in het kader van een stelsel van werkloosheid met bedrijfstoeslag. Art. 3.  Tijdens de periode van 1 juli 2023 tot 31 december 2024 kunnen de werknemers bedoeld in artikel 1 vragen om vrijgesteld te worden van de verplichting inzake aangepaste beschikbaarheid voor de arbeidsmarkt, wanneer zij op het moment van hun aanvraag : - hetzij de leeftijd van 62 jaar bereikt hebben; - hetzij een beroepsverleden bewijzen van 42 jaar. Art. 4.  Tijdens de periode van 1 juli 2023 tot 31 december 2024 kunnen de werknemers die voldoen aan de voorwaarden bedoeld in de collectieve arbeidsovereenkomst nr. 167 van 30 mei 2023 tot invoering, voor de periode van 1 juli 2023 tot 30 juni 2025, van een stelsel van bedrijfstoeslag voor sommige oudere werknemers met een lange loopbaan die worden ontslagen, vragen om vrijgesteld te worden van de verplichting inzake aangepaste beschikbaarheid voor de arbeidsmarkt, op voorwaarde : - dat zij uiterlijk ontslagen worden op 31 december 2024 en tijdens de geldigheidsduur van deze overeenkomst; en - de leeftijd van 60 jaar of ouder bereikt hebben uiterlijk op 31 december 2024 en op het ogenblik van de beëindiging van de arbeidsovereenkomst. Art. 5. Voor alles waarin niet uitdrukkelijk in deze collectieve arbeidsovereenkomst is voorzien, gelden de bepalingen van de collectieve arbeidsovereenkomst nr. 168 van 30 mei 2023.Art. 6. Deze collectieve arbeidsovereenkomst wordt gesloten voor een bepaalde duur. Zij treedt in werking op 1 juli 2023 en treedt buiten werking op 31 december 2024. Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -1605,29 +1605,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025200933</t>
+          <t>2025002525</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>16 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 22 oktober 2024, gesloten in het Paritair Comité voor het kleding- en confectiebedrijf, betreffende de wijziging en coördinatie van de statuten van het "Sociaal Waarborgfonds voor de kleding- en confectienijverheid" (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 15 februari 2024, gesloten in het Paritair Comité voor het vervoer en de logistiek, tot invoering van een sectoraal aanvullend pensioenstelsel voor de arbeiders tewerkgesteld bij een onderneming die een taxionderneming of diensten voor het verhuren van voertuigen met bestuurder uitbaat en ressorteert onder het Paritair Comité voor het vervoer en de logistiek ("SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB") (1)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-16&amp;numac_search=2025200933&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200933=36&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025002525&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025002525=36&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het kleding- en confectiebedrijf; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 22 oktober 2024, gesloten in het Paritair Comité voor het kleding- en confectiebedrijf, betreffende de wijziging en coördinatie van de statuten van het "Sociaal Waarborgfonds voor de kleding- en confectienijverheid". Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor het kleding- en confectiebedrijf Collectieve arbeidsovereenkomst van 22 oktober 2024 Wijziging en coördinatie van de statuten van het "Sociaal Waarborgfonds voor de kleding- en confectienijverheid" (Overeenkomst geregistreerd op 22 november 2024 onder het nummer 190717/CO/109) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de arbeiders en arbeidsters, hierna "werknemers" genoemd, die onder het Paritair Comité voor het kleding- en confectiebedrijf ressorteren. Art. 2. De statuten van het "Sociaal Waarborgfonds voor de kleding- en confectienijverheid" zoals zij werden vastgesteld bij de collectieve arbeidsovereenkomst van 23 april 1979, gesloten in het Paritair Comité voor het kleding- en confectiebedrijf, en haar latere wijzigingen, worden gecoördineerd overeenkomstig de hierna opgestelde tekst. Art. 3. Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst houdende de statuten van het "Sociaal Waarborgfonds voor de kleding- en confectienijverheid" van 8 november 2023 (registratienummer 185722/CO/109). Art. 4. Deze collectieve arbeidsovereenkomst treedt in werking op 22 oktober 2024 en is gesloten voor een onbepaalde tijd. Zij kan worden opgezegd door één van de partij en, mits een opzegging van zes maanden, betekend bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Comité voor het kleding- en confectiebedrijf en aan de organisaties vertegenwoordigd in dat paritair comité. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL Bijlage aan de collectieve arbeidsovereenkomst van 22 oktober 2024, gesloten in het Paritair Comité voor het kleding- en confectiebedrijf, betreffende de wijziging en coördinatie van de statuten van het "Sociaal Waarborgfonds voor de kleding- en confectienijverheid" Tekst van de gewijzigde en gecoördineerde statuten HOOFDSTUK I. - Benaming, zetel, doel en duur Artikel 1. Er wordt een fonds voor bestaanszekerheid opgericht onder de benaming "Sociaal Waarborgfonds voor de kleding- en confectienijverheid'', hierna het "fonds" genoemd. Art. 2. De maatschappelijke zetel van het fonds is gevestigd te Zellik, Leliegaarde 22. Hij kan, bij beslissing van het Paritair Comité voor het kleding- en confectiebedrijf, naar elke andere plaats in België worden overgebracht. Art. 3. Het fonds heeft tot doel : 1° aan de bij artikel 6 bedoelde werknemers een syndicale premie toe te kennen en uit te keren; 2° het financieren en de terugbetaling aan de werkgevers van de initiatieven te nemen door de in het paritair comité vertegenwoordigde organisaties, met het oog op de sociale en beroepsopleiding zoals zij door de raad van beheer van het fonds worden omschreven; 3° het verrichten van de betaling van de bedrijfstoeslag in het kader van de wettelijke stelsels van werkloosheid met bedrijfstoeslag voorzien in een door de Koning algemeen verbindend verklaarde sectorale collectieve arbeidsovereenkomst over dit onderwerp, evenals van de bijzondere werkgeversbijdragen, bedoeld in hoofdstuk VI van titel XI van de wet van 27 december 2006 houdende diverse bepalingen (1), laatst gewijzigd door de programmawet (I) van 29 maart 2012, die zijn verschuldigd op de bedrijfstoeslag betaald door het fonds, evenwel rekening houdend met de bepalingen terzake in voornoemde sectorale collectieve arbeidsovereenkomst; 4° het innen van de bijdragen nodig voor de werking van het fonds; 5° de financiering van het Instituut voor Vorming en Onderzoek in de Confectie zoals voorzien in deze statuten en ter uitvoering van de sectorale collectieve arbeidsovereenkomsten betreffende de vorming en tewerkstelling; 6° het innen van een bijdrage voor een sectorale hospitalisatieverzekering en het financieren en beheren daarvan; 7° de uitkering van een toeslag bij tijdelijke werkloosheid zoals bedoeld in artikel 9 van de wet van 12 april 2011 houdende aanpassing van de wet van 1 februari 2011 houdende verlenging van de crisismaatregelen en uitvoering van het interprofessioneel akkoord, en tot uitvoering van het compromis van de regering met betrekking tot het interprofessioneel akkoord, overeenkomstig een door de Koning algemeen verbindend te verklaren sectorale collectieve arbeidsovereenkomst over dit onderwerp; 8° het financieren en administratief verwerken van de terugbetaling aan de werkgevers van het loon, evenals de socialezekerheidsbijdragen, voor de dagen anciënniteitsverlof vanaf 10, 15 en 20 jaar dienst in de sector, zoals voorzien in de sectorale collectieve arbeidsovereenkomst betreffende het anciënniteitsverlof; 9° het uitkeren van een sectoraal supplement ter ondersteuning van ouders met jonge kinderen, zoals bepaald in artikel 10 van de collectieve arbeidsovereenkomst van 8 november 2023 houdende akkoord van sociale vrede 2023-2024; 10° het financieren van de terugbetaling aan de werkgevers van de gelijkstelling van de moederschapsrust voor de berekening van de aanvullende vergoeding bij het dubbel vakantiegeld, zoals bepaald in artikel 8 van de collectieve arbeidsovereenkomst van 8 november 2023 houdende akkoord van sociale vrede 2023-2024. Art. 4. Het fonds is voor de duur van één jaar opgericht met ingang van 1 januari 1964. De duur ervan wordt telkens met één jaar verlengd, indien niet vóór 30 juni van het voorafgaande jaar een opzegging wordt betekend door ten minste zes stemgerechtigde leden van het Paritair Comité voor het kleding- en confectiebedrijf. HOOFDSTUK II. - Toepassingsgebied Art. 5. De bepalingen van deze statuten zijn van toepassing op de werkgevers en de werknemers die ressorteren onder het Paritair Comité voor het kleding- en confectiebedrijf.HOOFDSTUK III. - Syndicale premie Art. 6.  § 1. De in artikel 5 bedoelde werknemers die lid zijn van één van de representatieve werknemersorganisaties welke op nationaal niveau zijn vertegenwoordigd, hebben recht op de bij artikel 7 voorziene syndicale premie, voor zover zij op cumulatieve wijze de hierna opgesomde voorwaarden vervullen : a) in de onderneming zijn tewerkgesteld op de vrijdag welke 31 maart van het jaar waarop de syndicale premie betrekking heeft voorafgaat, of welke gebeurlijk met laatstgenoemde datum samenvalt; b) van dit recht niet uitgesloten zijn ingevolge de verstoring van de sociale vrede. Deze uitsluiting wordt eventueel door het paritair comité vastgesteld. Voor de omschrijving van de "verstoring van de sociale vrede" wordt naar het huishoudelijk reglement van bedoeld comité verwezen.  § 2. Hebben eveneens recht op de syndicale premie, de werknemers, lid van één van de representatieve interprofessionele werknemersorganisaties welke op nationaal niveau zijn vertegenwoordigd, die in één of meer kleding- en confectiebedrijven tewerkgesteld zijn geweest na de vrijdag welke 31 maart van het voorgaande jaar voorafgaat, of gebeurlijk met laatstgenoemde datum samenvalt, en die volledig en ononderbroken werkloos zijn gebleven tot op de referentiedatum, zijnde de vrijdag welke voorafgaat aan of gebeurlijk samenvalt met 31 maart van het jaar waarop de syndicale premie betrekking heeft.  § 3. De uitkering van de syndicale premie aan de in § 2 bedoelde rechthebbenden kan tijdens een ononderbroken werkloosheidsperiode slechts eenmaal worden opgevorderd.  § 4. De in § 2 bedoelde rechthebbenden moeten, op het ogenblik van het indienen van de aanvraag tot uitkering van deze syndicale premie, bij het uitbetalend organisme van hun keuze : a) een attest inleveren uitgaande van de werkgever uit het kleding- en confectiebedrijf die hen het laatst tewerkstelde, waaruit de datum van ontslag blijkt; b) een bewijs van ononderbroken werkloosheid inleveren uitgaande van een betaalorganisme van de wettelijke werkloosheidsvergoedingen.  § 5. Hebben eveneens recht op de syndicale premie, de werknemers, lid van één van de representatieve interprofessionele werknemersorganisaties welke op nationaal niveau zijn vertegenwoordigd, die in één of meer kleding- en confectiebedrijven tewerkgesteld zijn geweest na de vrijdag welke 31 maart van het voorgaande jaar voorafgaat, of welke gebeurlijk met laatstgenoemde datum samenvalt, en die met pensioen zijn gegaan vóór de vrijdag welke voorafgaat aan of gebeurlijk samenvalt met 31 maart van het jaar waarop de syndicale premie betrekking heeft.  § 6. Hebben eveneens recht op de syndicale premie, de werknemers, leden van één van de representatieve interprofessionele werknemersorganisaties welke op nationaal niveau zijn vertegenwoordigd, in de schoot van het Paritair Comité voor het kleding- en confectiebedrijf en die, tot op de tweede referentiedatum die volgt op de datum van de afdanking, volledig en ononderbroken onvrijwillig werkloos gebleven zijn.  § 7. Hebben eveneens recht op de syndicale premie, de werknemers, leden van één van de representatieve interprofessionele werknemersorganisaties welke op nationaal niveau zijn vertegenwoordigd in de schoot van het Paritair Comité voor het kleding- en confectiebedrijf en die, tot op de derde referentiedatum die volgt op de datum van afdanking, volledig en ononderbroken onvrijwillig werkloos gebleven zijn.  § 8. Hebben eveneens recht op de syndicale premie, de werknemers, leden van één van de representatieve interprofessionele werknemersorganisaties welke op nationaal niveau zijn vertegenwoordigd in de schoot van het Paritair Comité voor het kleding- en confectiebedrijf en op wie op de eerste referentiedatum die volgt op de datum van afdanking de volgende situatie van toepassing is : in de loop van de referteperiode de werkloosheid hebben onderbroken door een tewerkstelling in een onderneming die niet ressorteert onder het Paritair Comité voor het kleding- en confectiebedrijf, wanneer de duur van deze tewerkstelling niet langer was dan de helft van het nog te lopen gedeelte van de referteperiode, te rekenen vanaf het begin van de hiervoor bedoelde tewerkstelling, en wanneer de betrokkene opnieuw volledig en onvrijwillig werkloos is op de beschouwde refertedatum. Art. 7. Het bedrag van de syndicale premie, welke elk dienstjaar aan de rechthebbenden dient toegekend, wordt vastgesteld bij collectieve arbeidsovereenkomst, gesloten in het Paritair Comité voor het kleding- en confectiebedrijf en algemeen verbindend verklaard bij koninklijk besluit.De syndicale premie wordt door het fonds aan de rechthebbenden uitbetaald. Daartoe stuurt het fonds aan de mogelijk belanghebbenden een persoonlijke titel. Deze titel wordt vervolgens door de werknemersorganisatie waarbij zij zijn aangesloten nagezien en gevalideerd. De werknemersorganisatie bezorgt daarna de gevalideerde titels voor uitbetaling aan het fonds. De raad van beheer van het fonds stelt alle andere modaliteiten vast met betrekking tot het uitreiken van en het toezicht over de titels. Art. 8. De raad van beheer van het fonds bepaalt de modaliteiten van toekenning en uitkering van een administratieve vergoeding aan elk van de meest representatieve werknemersorganisaties. Art. 9. Op het einde van elk dienstjaar, en op verplichtende wijze in de loop van de maand december, roept de voorzitter de raad van beheer van het fonds samen om vast te stellen of de sociale vrede al dan niet werd geëerbiedigd, zowel op het vlak van de bedrijfssector als op dat van de ondernemingen. De raad van beheer stelt vervolgens de bedragen vast welke aangewend moeten worden door het fonds ter uitbetaling van de syndicale premies. HOOFDSTUK IV. - Anciënniteitsverlof Art. 10. Het fonds neemt de volgende taken op zich inzake de terugbetaling aan de werkgevers van het loon, evenals de werkgeversbijdragen voor de sociale zekerheid, voor de dagen anciënniteitsverlof toegekend vanaf 10, 15 en 20 jaar anciënniteit in de sector zoals voorzien in de sectorale collectieve arbeidsovereenkomst betreffende het anciënniteitsverlof : - vaststellen of een werknemer de anciënniteitsvoorwaarde vervult; - informeren van de werkgevers over de werknemers die de anciënniteitsvoorwaarde vervullen; - opmaken en bekendmaken van een procedure die de werkgever moet volgen om aanspraak te maken op de terugbetaling; - de aanvragen van de werkgevers controleren; - de terugbetaling uitvoeren. De raad van beheer van het fonds bepaalt de modaliteiten van deze verplichtingen. Ze worden op eenvoudig verzoek van de betrokkenen meegedeeld door het fonds alsook op permanente wijze toegelicht op de website http://www.swfkleding.be. HOOFDSTUK V. - Beheer Art. 11.  § 1. Het fonds wordt door een paritaire raad van beheer beheerd. Deze raad is samengesteld uit vijf leden, vertegenwoordigers van de werknemers, en uit vijf leden, vertegenwoordigers van de werkgevers, die door het Paritair Comité voor het kleding- en confectiebedrijf in zijn schoot worden aangeduid. Ze hebben de hoedanigheid van effectieve leden. De hoedanigheid van lid van de raad van beheer gaat verloren gelijktijdig met het verlies van de hoedanigheid van effectief of plaatsvervangend lid van het paritair comité.  § 2. In afwijking van de beschikkingen welke het voorwerp uitmaken van § 1 van dit artikel, kan het Paritair Comité voor het kleding- en confectiebedrijf een gewezen lid van dit laatste aanduiden in de hoedanigheid van lid van de raad van beheer van het fonds. Die aanduiding mag niet leiden tot een verhoging van het aantal beheerders zoals het is vastgesteld bij § 1 van dit artikel. Art. 12. Elk jaar stelt de raad van beheer in zijn schoot een voorzitter en een ondervoorzitter aan. Voor het voorzitterschap en het onder voorzitterschap wordt een beurtregeling toegepast onder de vertegenwoordigers van de werkgevers en deze van de werknemers. Art. 13. De raad van beheer vergadert op uitnodiging van zijn directeur. De directeur dient de raad minstens eenmaal per kwartaal bijeen te roepen en telkens als ten minste twee leden van de raad er om verzoeken. De uitnodiging vermeldt de bondige agenda. De notulen worden opgesteld door de directeur en ondertekend door de voorzitter van de vergadering. De uittreksels uit de notulen worden door de voorzitter ondertekend.De beslissingen worden genomen met twee derden van de stemmen van de aanwezige leden. De stemming is geldig wanneer ten minste drie leden van elke paritaire groep aan de stemming hebben deelgenomen en op voorwaarde dat het ter stemming gelegde punt duidelijk staat vermeld op de agenda van de vergadering. Art. 14. De raad van beheer heeft tot taak het fonds te beheren en alle voor zijn goede werking vereiste maatregelen te treffen. Het beschikt over de ruimste machten voor het beheer en de leiding van het fonds. De raad van beheer verschijnt in rechte in naam van het fonds. De raad van beheer kan aan één of meer van zijn leden, of zelfs aan derden, bijzondere machten overdragen. Voor alle handelingen, andere dan deze waarvoor de raad bijzondere volmachten verleent, volstaat de gemeenschappelijke handtekening van twee beheerders, één van elke paritaire groep. De verantwoordelijkheid van de beheerders is beperkt tot de uitvoering van hun mandaat en hun beheer en behelst geen enkele persoonlijke verplichting ten aanzien van de verbintenissen van het fonds. HOOFDSTUK VI. - Financiering Art. 15.  § 1. Het fonds beschikt over de door de werkgevers verschuldigde bijdragen, bedoeld in artikel 16 van deze statuten.  § 2. Ter uitvoering van artikel 3, 5° van deze statuten maakt het fonds, onmiddellijk na ontvangst van de in § 1 van dit artikel bedoelde bijdragen, aan het Instituut voor Vorming en Onderzoek in de Confectie (IVOC) een als volgt vastgesteld bedrag over : - van 1 januari 2002 tot 31 december 2014 : 8,82 pct. van de in § 1 van dit artikel bedoelde bijdragen; - van 1 januari 2015 tot 31 december 2025 : 10,00 pct. van de in § 1 van dit artikel bedoelde bijdragen. Art. 16. Van 1 januari 2002 tot 31 december 2014 worden de werkgeversbijdragen bepaald op 3,40 pct. van de brutolonen van de werknemers. Van 1 januari 2015 tot 31 december 2025 worden de werkgeversbijdragen bepaald op 3,00 pct. van de brutolonen van de werknemers. Art. 17. De bijdragen worden geïnd en ingevorderd door de Rijksdienst voor Sociale Zekerheid, overeenkomstig artikel 7 van de wet van 7 januari 1958, betreffende de fondsen voor bestaanszekerheid. Van de door de Rijksdienst voor Sociale Zekerheid aan het fonds gestorte bijdragen worden vooraf de door de raad van beheer van het bedoeld fonds vastgestelde beheers- en werkingskosten afgetrokken. HOOFDSTUK VII. - Begroting, rekeningen Art. 18. Het dienstjaar vangt aan op 1 januari en eindigt op 31 december. Op laatstgenoemde datum worden de rekeningen afgesloten en onderzocht door de raad van beheer, vervolgens door een door het Paritair Comité voor het kleding- en confectiebedrijf aangeduide bedrijfsrevisor, welke ermee wordt belast ze te controleren. Vóór 1 mei worden de jaarrekeningen, het jaarverslag met betrekking tot het fonds en het verslag van de bedrijfsrevisor overgemaakt aan de voorzitter van het Paritair Comité voor het kleding- en confectiebedrijf. Art. 19. Bij de aanvang van elk dienstjaar, en vóór 1 mei, maakt de raad van beheer van het fonds een begroting voor het dienstjaar op. Deze begroting moet behelzen : - het bedrag van de onder de werknemers te verdelen sommen, indien de in artikel 9 voorziene voorwaarden zijn vervuld; - het bedrag van de sommen welke toekomen aan de werknemersorganisaties in verband met de voornoemde syndicale premie; - het voor de beheers- en werkingskosten voorbehouden bedrag; - de gekende of in te schatten bedragen betreffende de doelen zoals beschreven in artikel 3; - het ereloon van de bedrijfsrevisor die met het nazicht van de rekeningen is belast.HOOFDSTUK VIII. - Ontbinding, vereffening Art. 20. Het fonds kan worden ontbonden op elk ogenblik door opzegging overeenkomstig artikel 4 van deze statuten. Het Paritair Comité voor het kleding- en confectiebedrijf stelt de vereffenaars aan en bepaalt de vereffeningsmodaliteiten. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor het vervoer en de logistiek;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 15 februari 2024, gesloten in het Paritair Comité voor het vervoer en de logistiek, tot invoering van een sectoraal aanvullend pensioenstelsel voor de arbeiders tewerkgesteld bij een onderneming die een taxionderneming of diensten voor het verhuren van voertuigen met bestuurder uitbaat en ressorteert onder het Paritair Comité voor het vervoer en de logistiek ("SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB").Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het vervoer en de logistiekCollectieve arbeidsovereenkomst van 15 februari 2024Invoering van een sectoraal aanvullend pensioenstelsel voor de arbeiders tewerkgesteld bij een onderneming die een taxionderneming of diensten voor het verhuren van voertuigen met bestuurder uitbaat en ressorteert onder het Paritair Comité voor het vervoer en de logistiek ("SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB") (Overeenkomst geregistreerd op 30 mei 2024 onder het nummer 187889/CO/140)Artikel 1. BegripsomschrijvingenVoor de toepassing van deze collectieve arbeidsovereenkomst en haar bijlage, moeten de hierna vermelde begrippen als volgt worden begrepen :- "Arbeiders Ondernemingsactiviteit Taxi en VVB" : de arbeiders die ressorteren onder het Paritair Comité voor het vervoer en de logistiek, tewerkgesteld worden in de Ondernemingsactiviteit Taxi en VVB en in DmfA worden aangegeven onder het RSZ-werkgeverskengetal 068;- "Bedienden ondernemingsactiviteit Taxi en VVB" : de bedienden die door de werkgever worden tewerkgesteld, die ressorteren onder het Aanvullend Paritair Comité voor de bedienden en werkzaam zijn in de Ondernemingsactiviteit Taxi en VVB en die zich in een vergelijkbare situatie bevinden als de Arbeiders Ondernemingsactiviteit Taxi en VVB die door de werkgever worden tewerkgesteld, en met wie zij voor doeldoeleinden van het aanvullend pensioen "spiegelen" in de zin van artikel 14 van de WAP. Zij worden overeenkomstig de regels voorzien in de toepasselijke collectieve arbeidsovereenkomst van het Aanvullend Paritair Comité voor de bedienden tot invoering van een sectoraal aanvullend pensioenstelsel voor de bedienden Ondernemingsactiviteit Taxi en VVB ("SAP PC 200 bedienden ondernemingsactiviteit Taxi en VVB") toegewezen aan deze specifieke subcategorie;- "Cao van PC 200 van 1 juli 2019" : de collectieve arbeidsovereenkomst van 1 juli 2019 gesloten in het Aanvullend Paritair Comité voor de bedienden betreffende de koopkracht in het kader van het koninklijk besluit van 19 april 2019 tot uitvoering van artikel 7, § 1 van de wet van 26 juli 1996 tot bevordering van de werkgelegenheid en tot preventieve vrijwaring van het concurrentievermogen met registratienummer 152849/CO/200, zoals gewijzigd inzake de termijnen door de collectieve arbeidsovereenkomst van 18 november 2021 gesloten in het Aanvullend Paritair Comité voor de bedienden met registratienummer 168827/CO/200;- "Harmonisatieverplichting" : de wettelijke verplichting tot harmonisering van de aanvullende pensioenen voor arbeiders en bedienden in de zin van de WAP;- "Hoofdzakelijkheidscriterium" : in situaties waar werkgevers ressorteren onder meerdere paritaire (sub)comités voor hun arbeiders houdt het hoofdzakelijkheidscriterium in dat de bedienden PC 200 moeten vergeleken worden met hun collega arbeiders die werken in de hoofdactiviteit van de werkgever. De hoofdactiviteit wordt voor doeleinden van artikel 14 van de WAP bepaald als de ondernemingsactiviteit waar de werkgever het grootst aantal arbeiders tewerkstelt, uitgedrukt in voltijds equivalente arbeiders. De hoofdactiviteit wordt bepaald aan de hand van de officiële sociale documenten waarbij gebruik gemaakt wordt van de kengetallen en RSZ-identificatienummers;- "Inrichter" : de multi-sectorale inrichter, Fonds voor bestaanszekerheid "Fonds tweede pijler Taxi+ (FBZ P2P Taxi+)", met zetel te Metrologielaan 8, 1130 Brussel en met ondernemingsnummer 0696.700.619, die optreedt als inrichter van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB inricht en als inrichter van het SAP PC 200 Bedienden Ondernemingsactiviteit Taxi en VVB voor de Bedienden Ondernemingsactiviteit Taxi en VVB waarmee de Arbeiders Ondernemingsactiviteit Taxi en VVB "spiegelen" in de zin van artikel 14 van de WAP;- "Ondernemingsactiviteit (OA)" : de beroepscategorieën en ondernemingsactiviteiten zoals bedoeld in artikel 14/4, § 1, eerste lid van de WAP;- "Ondernemingsactiviteit Taxi en VVB" : de ondernemingsactiviteit van ondernemingen die een taxionderneming of die diensten voor het verhuren van voertuigen met bestuurder (VVB) uitbaten. Met "VVB" wordt bedoeld : het vervoer zoals omschreven in artikel 2, §  2 van deze collectieve arbeidsovereenkomst. De ondernemingen met Ondernemingsactiviteit Taxi en VVB ressorteren voor hun arbeiders onder het Paritair Comité voor het vervoer en de logistiek en voor hun Bedienden Ondernemingsactiviteit Taxi en VVB onder het Aanvullend Paritair Comité voor de bedienden. Deze Arbeiders Ondernemingsactiviteit Taxi en VVB en Bedienden Ondernemingsactiviteit Taxi en VVB die door de werkgever worden tewerkgesteld, worden in de DmfA aangegeven onder werkgeverskengetal 068. Voor de volledigheid wordt hierbij vermeld dat de PC 200 bedienden van de ondernemingen die een taxionderneming of die diensten voor het verhuren van voertuigen met bestuurder (VVB) uitbaten, maar binnen dezelfde technische bedrijfseenheid waar ze deze PC 200 bedienden tewerkstellen geen Arbeiders Ondernemingsactiviteit Taxi en VVB tewerkstellen, in DmfA niet mogen worden aangegeven onder het RSZ-werkgeverskengetal 068. Overeenkomstig artikel 2, § 1 van de collectieve arbeidsovereenkomst van 15 februari 2024 tot invoering van een sectoraal aanvullend pensioenstelsel voor de Bedienden Ondernemingsactiviteit Taxi en VVB ("SAP PC 200 Bedienden Ondernemingsactiviteit Taxi en VVB") gesloten binnen het Aanvullend Paritair Comité voor de bedienden, zijn deze PC 200 bedienden immers geen Bedienden Ondernemingsactiviteit Taxi en VVB. Enkel deze subcategorie van PC 200 bedienden (namelijk Bedienden ondernemingsactiviteit Taxi en VVB) mogen in DmfA onder het RSZ-werkgeverskengetal 068 worden aangegeven, naast de Arbeiders Ondernemingsactiviteit Taxi en VVB;- "PC 200" : het Aanvullend Paritair Comité voor de bedienden;- "PC 140" : het Paritair Comité voor het vervoer en de logistiek;- "SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB" : het sectoraal aanvullend pensioenstelsel ingevoerd door het CP 140 voor de Arbeiders Ondernemingsactiviteit Taxi en VVB overeenkomstig deze collectieve arbeidsovereenkomst;- "SAP PC 200 Bedienden Ondernemingsactiviteit - Taxi en VVB" : het sectoraal aanvullend pensioenstelsel dat door het PC 200 wordt ingevoerd in overeenstemming met de cao van het PC 200 van 1 juli 2019 - voor de Bedienden Ondernemingsactiviteit Taxi en VVB dat in het kader van de harmonisatieverplichting de gelijke behandeling beoogt inzake aanvullende pensioenen op sectorniveau tussen de Bedienden Ondernemingsactiviteit Taxi en VVB en de Arbeiders Ondernemingsactiviteit Taxi en VVB met wie zij "spiegelen" in de zin van artikel 14 van de WAP;- "Technische bedrijfseenheid" : de technische bedrijfseenheid zoals omschreven in artikel 14 van de wet van 20 september 1948 houdende organisatie van het bedrijfsleven;- "Vestigingseenheid" : een plaats die men, geografisch gezien, kan identificeren door een adres waar ten minste één activiteit van de in de Kruispuntbank van Ondernemingen geregistreerde juridische entiteit wordt uitgeoefend of van waaruit de activiteit wordt uitgeoefend in de zin van artikel I.2., 16°  van boek I van het Wetboek van Economisch recht. Dit komt neer op elke geografisch afgescheiden exploitatiezetel, afdeling of onderafdeling (atelier, fabriek, magazijn, bureau,...) van de betrokken juridische entiteit (op basis van het ondernemingsnummer), gesitueerd op een geografisch welbepaalde locatie en identificeerbaar met een adres en met een vestigingseenheidsnummer;- "WAP" : de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid, waarin het wettelijk kader inzake de harmonisatie van de aanvullende pensioenen voor arbeiders en bedienden werd ingeschreven door de wet van 5 mei 2014 tot wijziging van het rustpensioen en het overlevingspensioen en tot invoering van de overgangsuitkering in de pensioenregeling voor werknemers en houdende geleidelijke opheffing van de verschillen in behandeling die berusten op het onderscheid tussen werklieden en bedienden inzake aanvullende pensioenen en werd gewijzigd door de wet van 12 december 2021 tot uitvoering van het sociaal akkoord in het kader van de interprofessionele onderhandelingen voor de periode 2021-2022;- "Werkgever" : de juridische entiteit (op basis van het ondernemingsnummer), of desgevallend de vestigingseenheden (op basis van het vestigingseenheidsnummer) indien de juridische entiteit over meerdere vestigingseenheden beschikt;- "WIBP" : de wet van 27 oktober 2006 betreffende het toezicht op de instellingen voor bedrijfspensioenvoorziening.Art. 2. Toepassingsgebied § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de Werkgevers die een taxionderneming uitbaten of die diensten voor het verhuren van voertuigen met bestuurder (VVB) uitbaten en die ressorteren onder het Paritair Comité voor het vervoer en de logistiek alsook op hun arbeiders die worden aangegeven in de DmfA onder het RSZ-werkgeverskengetal 068, zijnde de Arbeiders Ondernemingsactiviteit Taxi en VVB. § 2 Met "vervoer verricht met huurauto's met bestuurder (VVB)" wordt bedoeld : ieder bezoldigd personenvervoer met voertuigen met een capaciteit van maximum 9 plaatsen (de bestuurder inbegrepen) met uitzondering van het taxivervoer en het geregeld vervoer. Met "geregeld vervoer" wordt bedoeld : het personenvervoer verricht voor rekening van de VVM en de SRWT-TEC, ongeacht de capaciteit van het voertuig en ongeacht het soort aandrijving van de gebruikte vervoermiddelen. Dit vervoer wordt verricht volgens de volgende criteria : een welbepaald traject en een welbepaald, geregeld uurrooster. De passagiers worden opgehaald en afgezet aan vooraf vastgelegde halten. Dit vervoer is toegankelijk voor iedereen, zelfs indien, in voorkomend geval, het verplicht is de reis vooraf te reserveren.Art. 3. Voorwerp - Invoering SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVBDeze collectieve arbeidsovereenkomst heeft als enige voorwerp de invoering met ingang van 1 januari 2025 van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB.Art. 4. Aansluiting bij SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB § 1. Alle Arbeiders Ondernemingsactiviteit Taxi en VVB die op of na 1 januari 2025 verbonden zijn via een arbeidsovereenkomst met een aangesloten bij het SAP Werkgever worden PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB. § 2. De hiervoor vermelde Arbeiders Ondernemingsactiviteit Taxi en VVB blijven aangesloten aan het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB tot aan hun uittreding, pensionering of overlijden.Arbeiders Ondernemingsactiviteit Taxi en VVB, die hun wettelijk (vervroegd) pensioen hebben opgenomen, maar verder of opnieuw tewerkgesteld worden met een arbeidsovereenkomst gesloten met een werkgever, zoals bedoeld in artikel 4, § 1 in het kader van "toegelaten arbeid voor gepensioneerden", blijven of worden niet aangesloten bij het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB, overeenkomstig artikel 13 van de WAP. § 3. Een uitzondering geldt voor de Arbeiders Ondernemingsactiviteit Taxi en VVB die gebruik hebben gemaakt, voorafgaand aan de invoering van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB, van hun wettelijk weigeringsrecht overeenkomstig artikel 16, § 3 van de WAP, op voorwaarde dat het bestaand pensioenstelsel van de Werkgever zoals van toepassing onmiddellijk voorafgaand aan de invoering van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB en van toepassing op de Arbeiders Ondernemingsactiviteit Taxi en VVB, per 1 januari 2025 wordt vervangen door het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB in het kader van de harmonisatieverplichting. De Arbeiders Ondernemingsactiviteit Taxi en VVB die in dit kader gebruik hebben gemaakt van dit weigeringsrecht worden niet aangesloten bij het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB, en dit zolang dit wettelijk weigeringsrecht verdere toepassing heeft.De betrokken Werkgever moet uiterlijk tegen 30 november 2024 aan de Inrichter de lijst van de Arbeiders Ondernemingsactiviteit Taxi en VVB meedelen die van hun wettelijk weigeringsrecht hebben gebruik gemaakt. Ook eventuele latere wijzingen aan deze lijst van de Arbeiders Ondernemingsactiviteit Taxi en VVB die van hun wettelijk weigeringsrecht hebben gebruik gemaakt, moeten door de betrokken Werkgever onverwijld aan de Inrichter meegedeeld worden. De Inrichter zal de naam en het KBO-nummer van de betrokken werkgevers meedelen aan de RSZ, zodat deze werkgevers in de DmfA de mogelijkheid hebben om aan te duiden dat er voor bepaalde Arbeiders Ondernemingsactiviteit Taxi en VVB geen patronale bijdragen voor het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB moeten worden geïnd.Art. 5. Aanduiding van de InrichterHet fonds voor bestaanszekerheid "Fonds tweede pijler Taxi+" hierna "FBZ P2P Taxi+", de multi-sectorale Inrichter waarvan de statuten zijn vastgelegd in de collectieve arbeidsovereenkomst van 15 februari 2024 ter vervanging van de collectieve arbeidsovereenkomst van 21 december 2017 betreffende de oprichting van een fonds voor bestaanszekerheid genaamd "Fonds tweede pijler Taxi+ (FBZ P2P Taxi+)" en tot vaststelling van zijn statuten en tot omvorming van het fonds voor bestaanszekerheid "Fonds tweede pijler Taxi+ (FBZ P2P Taxi+)" tot multi-sectorale Inrichter van de sectorale aanvullende pensioenstelsels voor de arbeiders en voor de bedienden in de Ondernemingsactiviteit Taxi en VVB en tot vaststelling van de statuten van de multi-sectorale Inrichter, wordt aangeduid als de inrichter van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB (hierna : "Inrichter" of "FBZ P2P Taxi+").Art. 6. Pensioentoezegging - aanduiding van de pensioeninstelling § 1. Het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB dat per 1 januari 2025 wordt ingevoerd, is een sectoraal aanvullend pensioenstelsel dat voorziet in een pensioentoezegging die is vastgelegd in het pensioenreglement (opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst). § 2. Deze pensioentoezegging is een pensioenstelsel van het type vaste bijdragen die voorziet :- in de opbouw van een aanvullend pensioen dat overeenkomstig de regels en modaliteiten van het pensioenreglement, zoals vastgelegd in bijlage 1 bij deze collectieve arbeidsovereenkomst, wordt uitbetaald aan de aangesloten Arbeiders Ondernemingsactiviteit Taxi en VVB op het moment van pensionering (in zoverre de betrokken Arbeider Ondernemingsactiviteit Taxi en VVB bij uittreding uit de sector zijn verworven pensioenreserves niet heeft overgedragen naar een andere pensioeninstelling);- in een overlijdenskapitaal in geval van overlijden van de aangesloten Arbeider Ondernemingsactiviteit taxi en VVB vóór pensionering, dat gelijk is aan de verworven reserves die de aangesloten Arbeider Ondernemingsactiviteit Taxi en VVB heeft opgebouwd onder het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB tot op het moment van zijn overlijden en dat wordt uitbetaald aan de begunstigden van de overleden aangesloten Arbeider Ondernemingsactiviteit Taxi en VVB overeenkomstig de regels en modaliteiten van het pensioenreglement (zoals vastgelegd in bijlage 1 bij deze collectieve arbeidsovereenkomst). § 3. Het beheer en de uitvoering van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB wordt toevertrouwd aan Sefoplus OFP. Sefoplus OFP is een multi-sectorale instelling voor bedrijfspensioenvoorziening, vergund op 19 november 2018 met ondernemingsnummer 0715.441.019, FSMA-identificatienummer 50.624 en maatschappelijke zetel te Marlylaan 15/8, 1120 Brussel. Sefoplus OFP is met andere woorden aangeduid als pensioeninstelling.De pensioenverplichtingen en de activa verbonden aan het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB worden binnen Sefoplus OFP beheerd in een afgezonderd compartiment ("Compartiment SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB") binnen een afzonderlijk vermogen opgezet voor het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB en het SAP PC 200 Bedienden Ondernemingsactiviteit Taxi en VVB ("Afzonderlijk Vermogen Ondernemingsactiviteit Taxi en VVB") in de zin van artikel 2, 15°  van de WIBP. De beheers- en werkingsregels die worden afgesproken tussen het FBZ P2P Taxi+ als Inrichter en Sefoplus OFP als pensioeninstelling worden vastgelegd in de beheersovereenkomst en de toetredingsakte daartoe, alsook in een algemeen en specifiek luik bij de verklaring inzake de beleggingsbeginselen (SIP) en het financieringsplan van Sefoplus OFP. § 4. De regels en modaliteiten betreffende de pensioentoezegging worden verder vastgelegd in het pensioenreglement dat wordt opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst, die er integraal deel vanuit maakt.Art. 7. Financiering, bijdragen en inningsmodaliteiten § 1. De financiering van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB gebeurt via een patronale bijdrage. De totale jaarlijkse brutobijdrage voor elke aangeslotene bij het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB is gelijk aan 1 pct. van de pensioengrondslag. De pensioengrondslag is gelijk is aan het brutoloon van de aangeslotene onderworpen aan RSZ-bijdragen, vermenigvuldigd met 108 pct.Deze totale jaarlijkse brutobijdrage is op de volgende wijze samengesteld :(i) een nettopensioenbijdrage van 0,88 pct.;(ii) de bijzondere RSZ-bijdrage van 8,86 pct. verschuldigd op de nettopensioenbijdrage zoals vermeld onder punt (i), gelijk is aan 0,08 pct.;(iii) de beheers- en werkingskosten van de Inrichter en van de pensioeninstelling gelijk aan 5 pct. van de nettopensioenbijdrage zoals vermeld onder (i) en verminderd met de bijzondere RSZ-bijdrage van 8,86 pct. daarop zoals vermeld onder (ii), die gelijk zijn aan 0,04 pct. § 2. De inning en de invordering van deze patronale bijdrage, zoals vastgelegd in § 1, gebeurt door de Rijksdienst voor Sociale Zekerheid (RSZ) via een gedifferentieerde inning, overeenkomstig de daartoe afgesloten beheersovereenkomst met de RSZ.Elke Werkgever die onder het toepassingsgebied van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB valt, is gehouden tot de betaling van deze bijdragen.De bijzondere RSZ-bijdrage van 8,86 pct., verschuldigd op de netto pensioenbijdrage zoals bepaald in § 1, onder punt (ii), wordt door de RSZ afgehouden aan de bron. Bijgevolg moeten de Werkgevers die onder het toepassingsgebied vallen van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB, de bijzondere RSZ-bijdrage van 8,86 pct. niet apart berekenen en aangeven. § 3. Op 1 januari 2025 zal een inhaalbijdrage worden ingeschreven op de individuele rekening van de per 1 januari 2025 aangesloten Arbeiders Ondernemingsactiviteit Taxi en VVB die :- in de periode van 1 april 2018 tot 1 januari 2025 tewerkgesteld waren door een werkgever die voldoet aan de toepassingsvoorwaarden van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB; en- op 1 januari 2025 nog steeds in dienst zijn van een werkgever die voldoet aan de toepassingsvoorwaarden van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB.Deze inhaalbijdrage is gelijk aan :- voor de maanden van ononderbroken tewerkstelling in de Ondernemingsactiviteit Taxi en VVB tussen 1 april 2018 en 1 april 2019 : 1,5 pct. van de pensioengrondslag van de aangesloten Arbeider Ondernemingsactiviteit Taxi en VVB, gekapitaliseerd voor de betrokken periode op basis van de toepasselijke intrestvoet gebruikt voor de berekening van de WAP-rendementsgarantie overeenkomstig artikel 24 van de WAP. De pensioengrondslag is gelijk is aan het brutoloon onderworpen aan RSZ-bijdragen, vermenigvuldigd met x 108 pct.;- Voor de maanden van de onmiddellijk daarop volgende ononderbroken tewerkstelling in de Ondernemingsactiviteit Taxi en VVB tussen 1 april 2019 en 1 januari 2025 : 1 pct. van de pensioengrondslag, gekapitaliseerd voor de betrokken periode op basis van de toepasselijke intrestvoet gebruikt voor de berekening van de WAP rendementsgarantie overeenkomstig artikel 24 van de WAP. De pensioengrondslag is gelijk is aan het brutoloon onderworpen aan RSZ-bijdragen, vermenigvuldigd met 108 pct.Deze inhaalbijdrage wordt door de Inrichter uiterlijk op 1 januari 2025 aan de pensioeninstelling Sefoplus OFP gestort. Deze inhaalbijdrage wordt gefinancierd vanuit de middelen van de Inrichter en wordt dus niet geïnd (niet door de RSZ, noch door de Inrichter) bij de Werkgevers die onder het toepassingsgebied van SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB vallen.Art. 8. Geen mogelijkheid tot uitsluiting uit het toepassingsgebied, noch een mogelijkheid tot opting-outHet SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB is van toepassing op alle Arbeiders Ondernemingsactiviteit Taxi en VVB. Werkgevers kunnen niet uitgesloten worden uit het toepassingsgebied van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB.Er wordt ook geen gebruik gemaakt van de mogelijkheid tot opting-out, zoals voorzien in artikel 9 van de WAP.Art. 9. Geldigheidsduur § 1. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025. Zij wordt gesloten voor onbepaalde duur.Deze collectieve arbeidsovereenkomst vervangt vanaf 1 januari 2025 de collectieve arbeidsovereenkomst van 18 januari 2018 betreffende de financiering van het "Fonds voor bestaanszekerheid P2P Taxi+" in de sector van de taxiondernemingen en de diensten voor het verhuur van voertuigen met chauffeur, geregistreerd onder het nummer 145044/CO/140. § 2. Deze collectieve arbeidsovereenkomst kan worden opgezegd door één van de ondertekenende partijen mits een opzegging van 6 maanden, betekend bij een ter post aangetekende brief, gericht aan de voorzitter van het Paritair Comité voor het vervoer en de logistiek (PC 140), die een kopie van de opzegging aan ieder van de ondertekenende partijen overmaakt. § 3. Voorafgaand aan de opzegging van deze collectieve arbeidsovereenkomst moeten de sociale partners van het Paritair Comité voor het vervoer en de logistiek de beslissing nemen om het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB op te heffen, waarbij rekening moet worden gehouden met de regels van de WAP inzake de Harmonisatieverplichting.Art. 10. Algemeen verbindend verklaringDeze collectieve arbeidsovereenkomst wordt neergelegd ter Griffie van de Algemene Directie Collectieve Arbeidsbetrekkingen van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg en de algemeen verbindende kracht bij koninklijk besluit wordt gevraagd.Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025.De Minister van Werk,D. CLARINVALBijlage aan de collectieve arbeidsovereenkomst van 15 februari 2024, gesloten in het Paritair Comité voor het vervoer en de logistiek, tot invoering van een sectoraal aanvullend pensioenstelsel voor de arbeiders tewerkgesteld bij een onderneming die een taxionderneming of diensten voor het verhuren van voertuigen met bestuurder uitbaat en ressorteert onder het Paritair Comité voor het vervoer en de logistiek ("SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB")HOOFDSTUK I. - VoorwerpArtikel 1.  § 1. Dit sectoraal pensioenreglement is opgemaakt in uitvoering van artikel 6, § 4 van de collectieve arbeidsovereenkomst van 15 februari 2024 tot invoering van een sectoraal aanvullend pensioenstelsel voor de arbeiders tewerkgesteld bij een onderneming die een taxionderneming of diensten voor het verhuren van voertuigen met bestuurder uitbaat en ressorteert onder het Paritair Comité voor het vervoer en de logistiek ("SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB"). § 2. Dit pensioenreglement legt de sectorale pensioentoezegging van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB vast. Het bepaalt de rechten en de plichten van de Inrichter, de Pensioeninstelling, de Aangeslotenen, de Begunstigden en de Werkgevers die onder het toepassingsgebied vallen van de collectieve arbeidsovereenkomst van 15 februari 2024 tot invoering van een sectoraal aanvullend pensioenstelsel voor de arbeiders tewerkgesteld bij een onderneming die een taxionderneming of diensten voor het verhuren van voertuigen met bestuurder uitbaat en ressorteert onder het Paritair Comité voor het vervoer en de logistiek ("SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB").Dit pensioenreglement bepaalt eveneens de aansluitingsvoorwaarden, alsook de regels betreffende de uitvoering van de Sectorale Pensioentoezegging. § 3. De rechten van de gewezen Aangeslotenen worden in de regel bepaald door het pensioenreglement zoals van toepassing op het ogenblik van hun Uittreding, behoudens in geval van andersluidende wettelijke bepalingen.HOOFDSTUK II. - DefinitiesArt. 2. 1. AangeslotenenDe Aangeslotenen worden opgedeeld in twee categorieën :1. Actieve aangeslotenen : de Arbeiders Taxi en VVB die 1 voldoen aan de aansluitingsvoorwaarden, zoals vermeld in artikel 3 van dit pensioenreglement;2. Passieve Aangeslotenen : de gewezen Actieve Aangeslotenen die na de Uittreding hun Verworven Reserves overeenkomstig artikel 16 van dit pensioenreglement bij de pensioeninstelling hebben gelaten.2. Aanvullend PensioenHet kapitaal of de hiermee overeenstemmende rente waarop een Aangeslotene recht heeft op basis van de door de Inrichter gestorte bijdragen in overeenstemming met dit pensioenreglement, en het rendement. Het Aanvullend Pensioen vormt een aanvulling op het wettelijk pensioen.3. Afzonderlijk vermogen Ondernemingsactiviteit Taxi en VVBBinnen Sefoplus OFP worden afzonderlijke vermogens ingericht in de zin van de WIBP voor het beheer van de sectorale pensioentoezeggingen enerzijds en voor het afzonderlijk beheer van de sectorale solidariteitstoezeggingen anderzijds, in lijn met de toepasselijke regelgeving.De sectorale pensioentoezegging wordt beheerd in het afzonderlijk vermogen ondernemingsactiviteit taxi en VVB, dat specifiek werd opgericht voor het beheer van deze sectorale pensioentoezegging en het SAP PC 200 Arbeiders Ondernemingsactiviteit Taxi en VVB. Concreet betekent dit dat de reserves en activa die verbonden zijn aan het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB en aan het SAP PC 200 Bedienden Ondernemingsactiviteit Taxi en VVB afgescheiden zijn van de overige activa en de overige afzonderlijke vermogens binnen Sefoplus OFP, en dus niet kunnen aangewend worden in het kader van andere sectorale pensioentoezeggingen ingericht door andere sectorale inrichters, die beheerd worden door Sefoplus OFP, noch in het kader van de solidariteitstoezeggingen beheerd door Sefoplus OFP.In het Afzonderlijk vermogen Ondernemingsactiviteit Taxi en VVB zijn twee afzonderlijke compartimenten opgezet :- de pensioenverplichtingen en de activa die verband houden met het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB worden afgezonderd beheerd in een specifiek daartoe gecreëerd compartiment, Compartiment SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB genaamd;- de pensioenverplichtingen en de activa die verband houden met het SAP PC 200 Bedienden Ondernemingsactiviteit Taxi en VVB worden afgezonderd beheerd in een specifiek daartoe gecreëerd compartiment, Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Taxi en VVB genaamd.4. Arbeiders Ondernemingsactiviteit Taxi en VVBDe arbeiders die ressorteren onder het PC 140, tewerkgesteld worden in de ondernemingsactiviteit Taxi en VVB en in de DmfA worden aangegeven onder het RSZ-werkgeverskengetal 068.5. Begunstigde(n)De persoon of personen die overeenkomstig artikel 10 van dit pensioenreglement aanspraak maken op een overlijdensprestatie in geval van overlijden van de Aangeslotene vóór Pensionering of alvorens het Aanvullend Pensioen naar aanleiding van de pensionering (volledig) is uitbetaald aan de Aangeslotene.6. HerberekeningsdatumDe Herberekeningsdatum voor dit pensioenreglement wordt vastgesteld op 1 januari.7. InrichterConform artikel 3, § 1, 5°  van de WAP hebben de representatieve organisaties vertegenwoordigd in het Paritair Comité voor het vervoer en de logistiek (PC 140), het fonds voor bestaanszekerheid - "Fonds tweede pijler Taxi+" afgekort "FBZ P2P Taxi+", aangeduid als Inrichter van het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB.Het gaat hier om een multi-sectorale Inrichter, die als gemeenschappelijke inrichter optreedt voor het SAP PC 140 Arbeiders Ondernemingsactiviteit Taxi en VVB en het SAP PC 200 Bedienden Ondernemingsactiviteit Taxi en VVB.Aangezien FBZ P2P Taxi+ optreedt voor meerdere paritaire comités zal het, in overeenstemming met de WAP, als uitsluitend doel de opbouw van aanvullende pensioenen hebben.8. KB WAPKoninklijk besluit van 14 november 2003 tot uitvoering van de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid.9. KB WIBPKoninklijk besluit van 12 januari 2007 betreffende het prudentiële toezicht op de instellingen voor bedrijfspensioenvoorziening.10. KindElk wettig geboren of verwekt kind van de Aangeslotene alsook elk erkend natuurlijk kind of elk geadopteerd kind van de Aangeslotene.11. Netto Financieel RendementHet Netto Financieel Rendement (afgekort als "NFR") van het Afzonderlijk Vermogen Ondernemingsactiviteit Taxi en VVB wordt voor het afgelopen boekjaar berekend per 31 december van het boekjaar. Hiertoe worden de investeringskosten in mindering gebracht van het financieel rendement van het Afzonderlijk Vermogen Ondernemingsactiviteit Taxi en VVB.Vervolgens wordt voor de vaststelling van het Netto Financieel Rendement dat wordt ingeschreven op de individuele rekeningen van de Aangeslotenen rekening gehouden met de beschikbare Vrije Reserve die dient als buffer. Deze Vrije Reserve of buffer is gelijk aan het bedrag van de activa van het Afzonderlijk Vermogen Ondernemingsactiviteit Taxi en VVB die volgend bedrag overstijgen :1. de reserves ingeschreven op de individuele rekeningen van de Aangeslotenen, in overeenstemming met dit pensioenreglement; hierbij wordt voor de berekening van deze reserves voor de periode gelegen tussen 1 januari en 31 december van het berekeningsjaar uitgegaan van een Netto Financieel Rendement dat gelijk is aan de rentevoet die wordt gebruikt voor de vaststelling van de WAP-Rendementsgarantie;2. desgevallend verhoogd met de WAP-Rendementsgarantie.Bij de toekenning van het Netto Financieel Rendement geldt als basisprincipe dat de Inrichter ernaar streeft, vanuit de doelstelling van een veilig en prudent Beheer van het Sectoraal Pensioenstelsel, om een buffer op te bouwen die gelijk is aan 10 pct. om eventuele, toekomstige negatieve schommelingen in de beleggingen te kunnen opvangen. Echter, zelfs indien de Vrije Reserve (buffer) lager is dan 10 pct. en er een positief Netto Financieel Rendement is, dan zal dit tot aan de WAP-Rendementsgarantie toch worden toegekend, zoals hierna bepaald :- Indien deze Vrije Reserve of buffer van het Afzonderlijk Vermogen Ondernemingsactiviteit Taxi en VVB hoger is dan of gelijk aan 10 pct. :- in geval van een positief Netto Financieel Rendement wordt dit volledig Netto Financieel Rendement, evenwel verminderd met het bedrag nodig om ervoor te zorgen dat ook na de toekenning van het Netto Financieel Rendement de Vrije Reserve of buffer van het Afzonderlijk Vermogen Ondernemingsactiviteit Taxi en VVB gelijk is aan 10 pct., ingeschreven op de individuele rekening</t>
         </is>
       </c>
     </row>
@@ -1637,28 +1636,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2025200234</t>
+          <t>2025201162</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>16 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 26 november 2024, gesloten in het Paritair Comité voor het garagebedrijf, tot oprichting van het "Fonds voor Bestaanszekerheid SAP Ondernemingsactiviteit Garagebedrijf" dat optreedt als multi-sectorale inrichter van het sectoraal aanvullend pensioenstelsel voor de arbeiders en voor de bedienden in de Ondernemingsactiviteit Garagebedrijf en tot vaststelling van de statuten van de multi-sectorale inrichter (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 20 november 2024, gesloten in het Paritair Comité voor de ondernemingen van technische land- en tuinbouwwerken, betreffende de vaststelling van de werkgeversbijdrage aan het "Waarborg- en Sociaal Fonds voor de ondernemingen van technische land- en tuinbouwwerken" (1)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-16&amp;numac_search=2025200234&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200234=37&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025201162&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201162=37&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het garagebedrijf; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 26 november 2024, gesloten in het Paritair Comité voor het garagebedrijf, tot oprichting van het "Fonds voor Bestaanszekerheid SAP Ondernemingsactiviteit Garagebedrijf" dat optreedt als multi-sectorale inrichter van het sectoraal aanvullend pensioenstelsel voor de arbeiders en voor de bedienden in de Ondernemingsactiviteit Garagebedrijf en tot vaststelling van de statuten van de multi-sectorale inrichter. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor het garagebedrijf Collectieve arbeidsovereenkomst van 26 november 2024 Oprichting van het "Fonds voor Bestaanszekerheid SAP Ondernemingsactiviteit Garagebedrijf" dat optreedt als multi-sectorale inrichter van het sectoraal aanvullend pensioenstelsel voor de arbeiders en voor de bedienden in de Ondernemingsactiviteit Garagebedrijf en vaststelling van de statuten van de multi-sectorale inrichter (Overeenkomst geregistreerd op 20 december 2024 onder het nummer 191180/CO/112) Gelet op de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid (hierna "FBZ-wet");Gelet op de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid (hierna "WAP"); Gelet op de beslissing van de sociale partners van het Paritair Comité voor het garagebedrijf (PC 112) tot wijziging van het sociaal sectoraal pensioenstelsel en het desbetreffende pensioenreglement (SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf) en de beslissing van de sociale partners van het Aanvullend Paritair Comité voor de bedienden (PC 200) tot invoering van een sectoraal aanvullend pensioenstelsel voor de Bedienden in de Ondernemingsactiviteit Garagebedrijf ("SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf") in lijn met de wettelijke verplichting tot harmonisering van de aanvullende pensioenen voor arbeiders en bedienden in de zin van artikel 14 en volgende van de WAP; Gelet op de beslissing van de sociale partners van het Paritair Comité voor het garagebedrijf (PC 112) en de sociale partners van het Aanvullend Paritair Comité voor de Bedienden (PC 200) Ondernemingsactiviteit Garagebedrijf om gebruik te maken van dezelfde multi-sectorale inrichter en daartoe het "Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Garagebedrijf" (FBZ SAP Ondernemingsactiviteit Garagebedrijf) op te richten en aan te duiden als de multi-sectorale inrichter van zowel het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf als het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf; Gelet op artikel 3, § 1, 5°, a), 1 van de WAP, moet de inrichter die optreedt voor meerdere paritaire (sub)comités de opbouw van aanvullende pensioenen als uitsluitend doet hebben. Het fonds voor bestaanszekerheid, genaamd "Sociaal Fonds voor het garagebedrijf", werd via de collectieve arbeidsovereenkomst van 5 juli 2002 (63461/CO/112) door de representatieve organisaties van het Paritair Comité voor het garagebedrijf (PC 112) aangeduid als de inrichter van het sociaal sectoraal pensioenstelsel voor de arbeiders van PC 112 (SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf). Aangezien het "Sociaal Fonds voor het garagebedrijf" ook andere taken heeft dan de opbouw van aanvullende pensioenen, kan het niet optreden als multi-sectorale inrichter van zowel het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf als het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf. Bijgevolg hebben de sociale partners van het Paritair Comité voor het garagebedrijf (PC 112) beslist dat, vanaf 1 juli 2025, het "Sociaal Fonds voor het garagebedrijf" niet langer zal optreden als de Inrichter van het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf en hebben zij samen met de sociale partners van het Aanvullend Paritair Comité voor de bedienden (PC 200) Ondernemingsactiviteit Garagebedrijf beslist om het "Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Garagebedrijf" (FBZ SAP Ondernemingsactiviteit Garagebedrijf) op te richten en aan te duiden als de multi-sectorale inrichter van zowel het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf als het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf. FBZ SAP Ondernemingsactiviteit Garagebedrijf neemt vanaf 1 juli 2025 alle rechten en verplichtingen over van het "Sociaal Fonds voor het garagebedrijf" die betrekking hebben op de inrichting van het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf; Gelet op artikel 7/2 van de WAP, dat bepaalt dat de inhoud van de statuten van de inrichter of de oprichtingsakte van de inrichter in identieke bewoordingen moet worden opgenomen in alle collectieve arbeidsovereenkomsten die de tussenkomst van de inrichter voor verschillende paritaire comités en/of paritaire subcomités regelen. Artikel 1. Toepassingsgebied  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers die ressorteren onder het Paritair Comité voor het garagebedrijf (PC 112) en die aangesloten zijn bij het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf, alsook op de arbeiders in de Ondernemingsactiviteit Garagebedrijf die zij tewerkstellen.  § 2. Worden uitgesloten van het toepassingsgebied van deze overeenkomst, de buiten België gevestigde werkgevers waarvan de werknemers in België gedetacheerd worden in de zin van de bepalingen van de verordening (EEG) nr. 1408/71 van de Raad of de verordening (EG) nr. 883/2004 van het Europees Parlement en de Raad. Art. 2. Begripsomschrijvingen Voor de toepassing van deze collectieve arbeidsovereenkomst en de statuten in bijlage bij deze collectieve arbeidsovereenkomst, moeten de hierna vermelde begrippen als volgt worden begrepen : - Bedienden Ondernemingsactiviteit Garagebedrijf : de bedienden die ressorteren onder het Aanvullend Paritair Comité voor de bedienden (PC 200) en werkzaam zijn in de Ondernemingsactiviteit Garagebedrijf,die zich in een vergelijkbare situatie bevinden als de arbeiders die werkzaam zijn in de Ondernemingsactiviteit Garagebedrijf (dit zijn de arbeiders die onder het PC 112 ressorteren) met wie zij voor doeleinden van het aanvullend pensioen "spiegelen" in de zin van artikel 14 van de WAP. Zij worden overeenkomstig de regels van de collectieve arbeidsovereenkomst gesloten binnen het PC 200 van 13 juni 2024 tot invoering van een sectoraal aanvullend pensioenstelsel voor de Bedienden Ondernemingsactiviteit Garagebedrijf ("SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf") toegewezen aan deze specifieke subcategorie; - Cao van 1 juli 2019 : de collectieve arbeidsovereenkomst van 1 juli 2019 gesloten in het PC 200 betreffende de koopkracht in het kader van het koninklijk besluit van 19 april 2019 tot uitvoering van artikel 7, § 1 van de wet van 26 juli 1996 tot bevordering van de werkgelegenheid en tot preventieve vrijwaring van het concurrentievermogen met registratienummer 152849/CO/200, zoals gewijzigd inzake de termijnen door de collectieve arbeidsovereenkomst van 18 november 2021 gesloten in het PC 200 met registratienummer 168827/CO/200; - Harmonisatieverplichting : de wettelijke verplichting tot harmonisering van de aanvullende pensioenen voor arbeiders en bedienden in de zin van de WAP; - Ondernemingsactiviteit (OA) : de beroepscategorieën en ondernemingsactiviteiten zoals bedoeld in artikel 14/4, § 1, eerste lid van de WAP; - Ondernemingsactiviteit Garagebedrijf : de ondernemingsactiviteiten waarvoor het PC 112 bevoegd is en die vallen onder het bevoegdheidsgebied van het PC 112 zoals vastgesteld in het koninklijk besluit van 1 juli 1974 tot oprichting en tot vaststelling van de benaming en van de bevoegdheid van het Paritair Comité voor het garagebedrijf, zoals laatst gewijzigd door het koninklijk besluit van 7 mei 2007; - PC 200 : het Aanvullend Paritair Comité voor de bedienden; - PC 112 : het Paritair Comité voor het garagebedrijf; - SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf : het sectoraal aanvullend pensioenstelsel per 1 januari 2002 ingevoerd door het PC 112 voor de arbeiders werkzaam in het PC 112; - SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf : het sectoraal aanvullend pensioenstelsel, dat door het PC 200 wordt ingevoerd - in overeenstemming met de cao van 1 juli 2019 - voor de Bedienden Ondernemingsactiviteit Garagebedrijf en dat in het kader van de Harmonisatieverplichting de gelijke behandeling beoogt inzake aanvullende pensioenen op sectorniveau tussen de Bedienden Ondernemingsactiviteit Garagebedrijf en de arbeiders in de Ondernemingsactiviteit Garagebedrijf met wie zij "spiegelen" in de zin van artikel 14 van de WAP; - Vestigingseenheid : een plaats die men, geografisch gezien, kan identificeren door een adres waar ten minste één activiteit van de in de Kruispuntbank van Ondernemingen geregistreerde juridische entiteit wordt uitgeoefend of van waaruit de activiteit wordt uitgeoefend in de zin van artikel I.2., 16° van boek I van het Wetboek van economisch recht. Dit komt neer op elke geografisch afgescheiden exploitatiezetel, afdeling of onderafdeling (atelier, fabriek, magazijn, bureau,...) van de betrokken juridische entiteit (op basis van het ondernemingsnummer), gesitueerd op een geografisch welbepaalde locatie en identificeerbaar met een adres en met een vestigingseenheidsnummer; - WAP : de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid, waarin het wettelijk kader inzake de harmonisatie van de aanvullende pensioenen voor arbeiders en bedienden werd ingeschreven door de wet van 5 mei 2014 tot wijziging van het rustpensioen en het overlevingspensioen en tot invoering van de overgangsuitkering in de pensioenregeling voor werknemers en houdende geleidelijke opheffing van de verschillen in behandeling die berusten op het onderscheid tussen werklieden en bedienden inzake aanvullende pensioenen en werd gewijzigd door de wet van 12 december 2021 tot uitvoering van het sociaal akkoord in het kader van de interprofessionele onderhandelingen voor de periode 2021-2022; - Werkgever : de juridische entiteit (op basis van het ondernemingsnummer), of desgevallend de Vestigingseenheden (op basis van het vestigingseenheidsnummer) indien de juridische entiteit over meerdere Vestigingseenheden beschikt. Art. 3. Multi-sectorale inrichter  § 1. Met ingang van 1 juli 2025 wordt het "Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Garagebedrijf" ("FBZ SAP Ondernemingsactiviteit Garagebedrijf") opgericht. § 2. FBZ SAP Ondernemingsactiviteit Garagebedrijf is een multi-sectorale inrichter, in de zin van artikel 3, 5° a) van de WAP, die met ingang van 1 juli 2025 door de sociale partners van het PC 112 wordt aangeduid als inrichter van het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf en door de sociale partners van het PC 200 als inrichter van het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf.  § 3. De statuten van het FBZ SAP Ondernemingsactiviteit Garagebedrijf die als bijlage bij deze collectieve arbeidsovereenkomst worden gevoegd, maken integraal deel uit van deze collectieve arbeidsovereenkomst. Art. 4. Geldigheidsduur  § 1. Deze collectieve arbeidsovereenkomst treedt in werking op 1 juli 2025. Zij wordt gesloten voor onbepaalde duur.  § 2. Zij kan worden opgezegd door één van de ondertekenende partijen mits een opzegging van 6 maanden, betekend bij een ter post aangetekende brief, gericht aan de voorzitter van Paritair Comité voor het garagebedrijf, die een kopie van de opzegging aan ieder van de ondertekenende partijen overmaakt. Art. 5.  Algemeen verbindend verklaring Deze collectieve arbeidsovereenkomst wordt neergelegd ter Griffie van de Algemene Directie Collectieve Arbeidsbetrekkingen van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg en de algemeen verbindende kracht bij koninklijk besluit wordt gevraagd. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL BijlageBijlage bij de collectieve arbeidsovereenkomst van 26 november 2024, gesloten in het Paritair Comité voor het garagebedrijf, tot oprichting van het "Fonds voor Bestaanszekerheid SAP Ondernemingsactiviteit Garagebedrijf" dat optreedt als multi-sectorale inrichter van het sectoraal aanvullend pensioenstelsel voor de arbeiders en voor de bedienden in de Ondernemingsactiviteit Garagebedrijf en tot vaststelling van de statuten van de multi-sectorale inrichter Statuten FBZ SAP Ondernemingsactiviteit Garagebedrijf HOOFDSTUK I. - Benaming, zetel, doel en duur Artikel 1. Benaming Er wordt op 1 juli 2025 een fonds voor bestaanszekerheid opgericht door het Paritair Comité voor het garagebedrijf (PC 112) en het Aanvullend Paritair Comité voor de bedienden (PC 200), genaamd "Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Garagebedrijf" (afgekort : FBZ SAP Ondernemingsactiviteit Garagebedrijf), verder ook het "fonds" genoemd. Art. 2. Zetel De maatschappelijke zetel en het secretariaat van het fonds is gevestigd te Marlylaan 15/8, 1120 Brussel. De zetel mag naar elk ander adres in België worden overgebracht mits statutenwijziging. Art. 3. Opdrachten - doel  § 1. Het fonds is een multi-sectorale inrichter in de zin van artikel 3, § 1, 5°, a), 1 van de WAP. Het fonds is : - met ingang van 1 juli 2025, aangeduid als inrichter van het sociaal sectoraal aanvullend pensioenstelsel ingevoerd door Paritair Comité voor het garagebedrijf (PC 112) voor de arbeiders van de ondernemingen die onder de bevoegdheid vallen van het PC 112 (hierna "SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf"), als opvolger van het "Sociaal Fonds voor het garagebedrijf" dat tot en met 30 juni 2025 de (mono-sectorale) inrichter was; - met ingang van 13 juni 2024, aangeduid als inrichter van het sectoraal aanvullend pensioenstelsel dat door het Aanvullend Paritair Comité voor de bedienden (PC 200) op die datum wordt ingevoerd voor de bedienden in de Ondernemingsactiviteit Garagebedrijf (hierna "SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf"). § 2. Het fonds heeft, overeenkomstig artikel 3, § 1, 5°, a), 1 van de WAP als uitsluitend doel de opbouw van aanvullende pensioenen. Het fonds heeft met name als bevoegdheden : (1) De wijziging of opheffing van het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf en het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf; (2) De financiering van het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf en het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf door het laten innen, in zijn naam en voor zijn rekening, door de Rijksdienst voor Sociale Zekerheid van de bijdragen overeenkomstig de toepasselijke sectorale collectieve arbeidsovereenkomsten gesloten in het PC 112 en in het PC 200 voor de bedienden in de Ondernemingsactiviteit Garagebedrijf; (3) Het aanzuiveren van tekorten van de verworven reserves van de aangeslotenen, de tekorten ten opzichte van de WAP-rendementsgarantie, alsook de tekorten inzake de werkings- en beheerskosten van de pensioeninstelling : (i) via de eigen middelen in het Compartiment SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf of via een bijkomende bijdrage geïnd bij de werkgevers die ressorteren onder het PC 112 en die deelnemen aan het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf, voor de voormelde tekorten met betrekking tot het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf; (ii) via de eigen middelen in het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf of via een bijkomende bijdrage geïnd bij de werkgevers die ressorteren onder het PC 200 en aangesloten zijn aan het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf voor de tekorten met betrekking tot het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf; (4) Het uitvoeren of in zijn naam en voor zijn rekening laten uitvoeren van alle noodzakelijke mededelingen aan de pensioeninstelling, de werkgevers, de aangeslotenen van het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf en het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf, hun begunstigden of rechthebbenden, de FSMA en andere belanghebbende partijen of overheidsinstellingen; (5) Het instellen en behandelen of het in zijn naam en voor zijn rekening laten instellen en behandelen van vorderingen in en buiten rechte wegens de niet-betaling van de bijdragen ter financiering van het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf en het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf en/of andere wettelijke en/of contractuele tekortkomingen die verband houden met (het beheer en de uitvoering van) het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf en het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf; (6) Het uitvoeren of in zijn naam en voor zijn rekening laten uitvoeren van elke verplichting opgelegd door de wetgeving van toepassing op aanvullende pensioenen en instellingen voor bedrijfspensioenvoorziening en de uitvoeringsbesluiten.  § 3. Het fonds kan alle daden stellen die rechtstreeks of onrechtstreeks, geheel of gedeeltelijk, verband houden met zijn doel en kan ervoor opteren om één of meerdere aspecten hiervan aan derden uit te besteden.  § 4. In het kader van de verplichte externalisatie opgelegd door de WAP wordt het beheer en de uitvoering van het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf en het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf in ieder geval toevertrouwd aan een pensioeninstelling en zal het fonds hier niet zelf voor instaan. Art. 4.  Duur Het fonds wordt voor onbepaalde duur opgericht. HOOFDSTUK II. - Toepassingsgebied Art. 5. De bepalingen van deze statuten gelden voor : (1) het fonds; (2) de werkgevers die ressorteren onder het PC 112 en die deelnemen aan het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf en de arbeiders die zij tewerkstellen zoals bepaald in de toepasselijke sectorale collectieve arbeidsovereenkomsten gesloten in het PC 112;(3) de werkgevers die ressorteren onder het PC 200 en die voor de bedienden in de Ondernemingsactiviteit Garagebedrijf deelnemen aan het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf en de Bedienden Ondernemingsactiviteit Garagebedrijf die zij tewerkstellen, zoals bepaald in de toepasselijke sectorale collectieve arbeidsovereenkomsten gesloten in het PC 200. HOOFDSTUK III. - Voordelen Art. 6. De voordelen toegekend door het fonds zijn : - De pensioen- en solidariteitstoezegging voorzien in het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf, die het voorwerp uitmaakt van één of meerdere bij koninklijk besluit algemeen verbindend verklaarde collectieve arbeidsovereenkomsten gesloten in het PC 112, waarin de personen staan vermeld die ervan kunnen genieten (aangeslotenen, begunstigden en/of pensioengerechtigden) en ook de aard en de toekennings- en uitbetalingsmodaliteiten van de toegekende voordelen worden vastgesteld; - De pensioentoezegging voorzien in het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf, die het voorwerp uitmaakt van één of meerdere bij koninklijk besluit algemeen verbindend verklaarde collectieve arbeidsovereenkomsten gesloten in het PC 200, waarin de personen staan vermeld die ervan kunnen genieten (aangeslotenen, begunstigden en/of pensioengerechtigden) en ook de aard en de toekennings- en uitbetalingsmodaliteiten van de toegekende voordelen worden vastgesteld. HOOFDSTUK IV. - Beheer van het fonds Art. 7. Het fonds wordt beheerd door een paritair samengestelde raad van bestuur die gezamenlijk door het PC 112 en het PC 200 worden aangeduid. De raad van bestuur bestaat uit zestien leden, zijnde : - acht vertegenwoordigers voorgedragen door de meest representatieve werkgeversorganisaties vertegenwoordigd in het PC 112; - acht vertegenwoordigers voorgedragen door de meest representatieve werknemersorganisaties vertegenwoordigd in het PC 112. Elke organisatie heeft de bevoegdheid om op elk moment in de vervanging van zijn vertegenwoordigers te voorzien in overleg met het PC 200. Art. 8. Het voorzitterschap wordt door de werkgeversafvaardiging waargenomen. De voorzitter wordt jaarlijks aangeduid door de raad van bestuur. De eerste en de derde ondervoorzitter behoren tot de werknemersgroep en worden jaarlijks aangeduid door de raad van bestuur. De tweede ondervoorzitter behoort tot de werkgeversgroep en wordt jaarlijks door de raad van bestuur aangeduid. Art. 9.  § 1. De raad van bestuur wordt door zijn voorzitter bijeengeroepen. De voorzitter is ertoe gehouden de raad van bestuur ten minste eenmaal per semester bijeen te roepen en telkens wanneer ten minste twee leden van de raad van bestuur erom verzoeken.  § 2. De uitnodiging vermeldt de agenda.  § 3. De notulen worden door de, door de raad van bestuur aangeduide secretaris opgesteld. De uittreksels uit deze notulen worden door de voorzitter of twee bestuurders ondertekend. Deze notulen worden ter beschikking gesteld van de representatieve werkgeversorganisatie(s) en werknemersorganisaties vertegenwoordigd in het Aanvullend Paritair Comité voor de bedienden (PC 200), alsook de gerelateerde documenten die betrekking hebben op het beheer van het (Compartiment) SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf.  § 4. Wanneer tot de stemming moet worden overgegaan, dient een gelijk aantal leden van elke afvaardiging aan de stemming deel te nemen. Is het aantal ongelijk, dan onthoudt (onthouden) zich het jongste lid (de jongste leden).  § 5. De raad van bestuur kan slechts geldig beslissen over de op de agenda gestelde kwesties en in aanwezigheid van ten minste de helft van de leden die tot de werknemersafvaardiging en ten minste de helft van de leden die tot de werkgeversafvaardiging behoren. De beslissingen worden met een meerderheid van twee derden van de stemgerechtigden genomen.  § 6. Elke organisatie die vertegenwoordigd is in de raad van bestuur, mag maximum 2 experten uitnodigen om als waarnemer zonder stemrecht deel te nemen aan de vergadering. De namen van deze bijkomende personen dienen dan mee op de aanwezigheidslijst geregistreerd te worden.Art. 10.  § 1. De raad van bestuur heeft tot taak het fonds te beheren en alle maatregelen te treffen die voor zijn goede werking zijn vereist. Hij beschikt over de meest uitgebreide bevoegdheid inzake het beheer en de leiding van het fonds.  § 2. De raad van bestuur keurt de rekeningen en de begroting goed en treedt in rechte op in naam van het fonds, op vervolging en op verzoek van de voorzitter of van een tot dat doel afgevaardigde bestuurder.  § 3. De raad van bestuur kan bijzondere bevoegdheden overdragen aan één of meer van zijn leden of zelfs aan derden. Voor al de andere handelingen dan deze waarvoor de raad van bestuur speciale volmachten heeft verleend, volstaan de gezamenlijke handtekeningen van twee bestuurders (één van werknemerszijde en één van werkgeverszijde).  § 4. De verantwoordelijkheid van de bestuurders beperkt zich tot de uitvoering van hun mandaat en zij gaan geen enkele persoonlijke verbintenis aan betreffende hun beheer ten opzichte van de verplichtingen van het fonds.  § 5. Het lid dat voor de vergadering van de raad van bestuur belet is, kan schriftelijk of per e-mail volmacht verlenen aan één van zijn collega's behorende tot dezelfde groep (werknemers- of werkgeversgroep) om hem te vervangen. Nochtans mag geen enkel lid meer dan één andere bestuurder vertegenwoordigen. HOOFDSTUK V. - Financiering van het fonds Art. 11.  § 1. De bijdragen ter financiering van het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf, alsook voor de financiering van de beheers- en werkingskosten en het aanleggen van een (eventuele) buffer en/of voor de aanzuivering van tekorten, worden uitsluitend vastgelegd in een bij koninklijk besluit algemeen verbindend verklaarde collectieve arbeidsovereenkomst gesloten in het PC 112. De inning en de invordering van deze bijdrage gebeurt door de Rijksdienst voor Sociale Zekerheid (RSZ) bij toepassing van artikel 7 van de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid en overeenkomstig de daartoe met de RSZ afgesloten beheersovereenkomst.  § 2. De bijdragen ter financiering van het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf, alsook voor de financiering van de beheers- en werkingskosten en het aanleggen van een (eventuele) buffer en/of voor de aanzuivering van tekorten, worden uitsluitend vastgelegd in een bij koninklijk besluit algemeen verbindend verklaarde collectieve arbeidsovereenkomst gesloten in het PC 200. De inning en de invordering van deze bijdragen gebeurt door de RSZ bij toepassing van artikel 7 van de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid en overeenkomstig de daartoe met de RSZ afgesloten beheersovereenkomst. Art. 12. Afgezonderd beheer Binnen het fonds wordt er gewerkt met afgezonderd beheer. Dit houdt in dat de bijdragen ter financiering van het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf en de daaraan gerelateerde werkingskosten enerzijds en de bijdragen ter financiering van het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf en de daaraan gerelateerde werkingskosten anderzijds, worden beheerd in twee afgescheiden compartimenten binnen het fonds : (1) Het Compartiment SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf, waarin alle bijdragen en middelen (en de eventuele opbrengsten ervan) worden ondergebracht die het fonds vanaf 1 juli 2025 ontvangt van de RSZ of desgevallend van het "Sociaal Fonds voor het garagebedrijf", voor de financiering van het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf (alsook van de beheers- en werkingskosten, de (eventuele) buffer en/of de aanzuivering van tekorten); (2) Het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf, waarin alle bijdragen en middelen (en de eventuele opbrengsten ervan) worden ondergebracht die het fonds vanaf 1 juli 2025 ontvangt van de RSZ voor de financiering van het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf (alsook van de beheers- en werkingskosten, de (eventuele) buffer en/of de aanzuivering van tekorten).Art. 13. Geen solidariteit  § 1. Er bestaat geen solidariteit tussen het Compartiment SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf en het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf, niet voor de financiering van de respectievelijke sectorale aanvullende pensioenstelsels (met inbegrip van de aanleg van een eventuele buffer en de aanzuivering van tekorten in de verworven reserves van de aangeslotenen in het kader van de WAP-rendementsgarantie), noch voor de daaraan gerelateerde beheer- en werkingskosten (van het fonds en van de pensioeninstelling). Dit betekent concreet dat de bijdragen en de middelen toegewezen aan het Compartiment SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf enkel kunnen gebruik worden voor de hiervoor vermelde posten inzake de financiering van het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf. Indien de middelen van het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf ontoereikend zouden zijn, kan het fonds de middelen (het surplus) in het Compartiment SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf in geen geval aanwenden ter dekking van het tekort in het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf. Analoog, kunnen de bijdragen en de middelen toegewezen aan het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf enkel gebruikt worden voor de hiervoor vermelde posten inzake de financiering van het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf. Indien de middelen van het Compartiment SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf ontoereikend zouden zijn, kan het fonds de middelen (het surplus) in het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf in geen geval aanwenden ter dekking van het tekort in het Compartiment SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf.  § 2. Inzake de betaling van de bijdragen ter financiering van de respectievelijke sectorale aanvullende pensioenstelsels (met inbegrip van de aanleg van een eventuele buffer en de aanzuivering van tekorten in de verworven reserves van de aangeslotenen in het kader van de WAP-rendementsgarantie) en de daaraan gerelateerde beheer- en werkingskosten bestaat er geen solidariteit tussen de werkgevers die vallen onder het toepassingsgebied zoals bepaald in artikel 5 van deze statuten. Art. 14. Tekorten  § 1. Tekorten binnen het Compartiment SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf of met betrekking tot het SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf in het algemeen, worden aangezuiverd via een bijkomende storting vanuit het "Sociaal Fonds voor het garagebedrijf", dan wel een bijkomende/verhoogde bijdrage geïnd door de RSZ bij de werkgevers bedoeld in artikel 5 (2) van deze statuten.  § 2. Tekorten binnen het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf of met betrekking tot het SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf in het algemeen, worden aangezuiverd via een bijkomende/verhoogde bijdrage geïnd door de RSZ bij de werkgevers bedoeld in artikel 5 (3) van deze statuten. HOOFDSTUK VI. - Begroting en jaarrekeningen Art. 15. Begroting, jaarrekeningen  § 1. Het boekjaar neemt een aanvang op 1 januari van elk jaar en sluit op 31 december van hetzelfde jaar.  § 2. Op 31 december worden de rekeningen van het verlopen jaar afgesloten. De afsluiting en de balans moeten op boekhoudkundig gebied voldoende gespecificeerd worden.  § 3. De raad van bestuur, alsmede de bij toepassing van artikel 12 van de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid aangewezen revisor, brengen jaarlijks ieder een schriftelijk verslag uit over het vervullen van hun opdracht tijdens het verlopen jaar.  § 4. De jaarrekeningen, samen met voornoemde schriftelijke verslagen, moeten uiterlijk in de loop van het tweede kwartaal van het volgende jaar ter goedkeuring aan het Paritair Comité voor het garagebedrijf (PC 112) worden voorgelegd. Voorafgaand aan deze goedkeuring, worden deze documenten ter informatie ook overgemaakt aan het Aanvullend Paritair Comité voor de bedienden (PC 200).HOOFDSTUK VII. - Ontbinding en vereffening Art. 16. Het fonds kan enkel ontbonden worden bij een eenparige beslissing van het PC 112 en het PC 200. Art. 17.  § 1. In geval van vrijwillige ontbinding van het fonds, waarbij er gelden of middelen beschikbaar blijven, zullen het PC 112 en het PC 200 die gezamenlijk tot deze ontbinding beslist hebben, gezamenlijk de vereffenaars benoemen, hun bevoegdheden en hun eventuele bezoldiging vaststellen.  § 2. Aan het overblijvend vermogen van het fonds, na vereffening van de schulden, zullen de sociale partners van het PC 112 en de sociale partners van het PC 200 een bestemming geven welke zoveel mogelijk het doel benadert met het oog waarop het fonds voor bestaanszekerheid werd opgericht, met name aanvullende pensioenopbouw. Hierbij zal rekening worden gehouden met het afgezonderd beheer zoals bepaald in deze statuten. Concreet betekent dit dat het overblijvend vermogen behorende tot het Compartiment SAP PC 112 Arbeiders Ondernemingsactiviteit Garagebedrijf zal worden overdragen naar de pensioeninstelling gekozen door de sociale partners van het PC 112 en dat het overblijvend vermogen behorende tot het Compartiment SAP PC 200 Bedienden Ondernemingsactiviteit Garagebedrijf zal worden overgedragen naar de pensioeninstelling gekozen door de sociale partners van het PC 200. HOOFDSTUK VIII. - Het fonds treedt niet langer op voor één van de paritaire comités Art. 18.  § 1. Het PC 112 </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de ondernemingen van technische land- en tuinbouwwerken; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 20 november 2024, gesloten in het Paritair Comité voor de ondernemingen van technische land- en tuinbouwwerken, betreffende de vaststelling van de werkgeversbijdrage aan het "Waarborg- en Sociaal Fonds voor de ondernemingen van technische land- en tuinbouwwerken". Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 11 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de ondernemingen van technische land- en tuinbouwwerken Collectieve arbeidsovereenkomst van 20 november 2024 Vaststelling van de werkgeversbijdrage aan het "Waarborg- en Sociaal Fonds voor de ondernemingen van technische land- en tuinbouwwerken" (Overeenkomst geregistreerd op 20 december 2024 onder het nummer 191188/CO/132) HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de arbeiders en op de bedienden zonder onderscheid naar gender, hierna "werknemers" genoemd, van de ondernemingen die onder het Paritair Comité voor de ondernemingen van technische land- en tuinbouwwerken ressorteren en op hun werkgevers. Onder arbeiders en bedienden worden ook de flexi-jobbers verstaan. HOOFDSTUK II. - Werkgeversbijdragen Art. 2.  § 1. In toepassing van artikel 6 van de statuten van het "Waarborg- en Sociaal Fonds voor de ondernemingen van technische land- en tuinbouwwerken", gevoegd bij de collectieve arbeidsovereenkomst van 25 mei 1976, wordt de werkgeversbijdrage aan het waarborg- en sociaal fonds vanaf 1 januari 2025 : - voor de arbeiders vastgesteld op 12,40 pct. van de loonmassa, met inbegrip van de 0,30 pct. voor de vakopleiding en van 0,10 pct. voor maatregelen ten voordele van jonge en oude werknemers ("penibiliteitsfonds"); - voor de bedienden vastgesteld op 2,00 pct. van de loonmassa, met inbegrip van de 0,30 pct. voor de vakopleiding en van 0,10 pct. voor maatregelen ten voordele van jonge en oude werknemers ("penibiliteitsfonds"). § 2. In toepassing van artikel 11 van bovenvermelde statuten, wordt de bij artikel 2, § 1 vastgestelde werkgeversbijdrage geïnd en ingevorderd door de Rijksdienst voor Sociale zekerheid. HOOFDSTUK III. - Geldigheid Art. 3. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van 1 januari 2025 en is gesloten voor een onbepaalde duur. Zij vervangt de collectieve arbeidsovereenkomst van 17 november 2023, geregistreerd onder het nr. 184244/CO/132. Zij kan door elk van de ondertekenende partijen worden opgezegd met een opzegging van ten minste drie maanden, betekend bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Comité voor de ondernemingen van technische land- en tuinbouwwerken. Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025. De Minister van Werk, D. CLARINVAL 
+</t>
         </is>
       </c>
     </row>
@@ -1668,28 +1668,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025002623</t>
+          <t>2025002519</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>16 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 16 december 2024, gesloten in het Paritair Comité voor de bedienden uit de voedingsnijverheid, betreffende de toekenning van een syndicale premie aan de gesyndiceerde bedienden (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 9 december 2024, gesloten in het Paritair Comité voor de bedienden der metaalfabrikatennijverheid, betreffende de sectorale minimumlonen vanaf 1 januari 2025 (1)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-16&amp;numac_search=2025002623&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025002623=38&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025002519&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025002519=38&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de bedienden uit de voedingsnijverheid;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 16 december 2024, gesloten in het Paritair Comité voor de bedienden uit de voedingsnijverheid, betreffende de toekenning van een syndicale premie aan de gesyndiceerde bedienden.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de bedienden uit de voedingsnijverheidCollectieve arbeidsovereenkomst van 16 december 2024Toekenning van een syndicale premie aan de gesyndiceerde bedienden (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191524/CO/220)Artikel 1.  § 1 Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de bedienden van de ondernemingen die onder de bevoegdheid vallen van het Paritair Comité voor de bedienden uit de voedingsnijverheid. § 2. Onder "bedienden" wordt verstaan : de bedienden zonder onderscheid naar gender.Art. 2. Bij toepassing van artikel 3, 2°  van de statuten van het "Waarborg- en Sociaal Fonds van de bedienden van de voedingsnijverheid", vastgesteld bij collectieve arbeidsovereenkomst van 23 februari 2009, gesloten in het Paritair Comité voor de bedienden uit de voedingsnijverheid (registratienr. 91403/CO/220), algemeen verbindend verklaard bij koninklijk besluit van 2 juni 2010 (Belgisch Staatsblad van 9 augustus 2010), wordt ten laste van het fonds een syndicale premie toegekend.HOOFDSTUK I. - Actieve bediendenArt. 3.  § 1. Er wordt jaarlijks een syndicale premie toegekend. Het globaal jaarlijks bedrag ervan wordt toegekend aan de bedienden die in de referteperiode, lopend van 1 april van jaar X tot 31 maart van jaar X + 1, terzelfder tijd :a) lid zijn van één van de representatieve interprofessionele werknemersorganisaties, vertegenwoordigd in het Paritair Comité voor de bedienden uit de voedingsnijverheid;b) krachtens een arbeidsovereenkomst verbonden zijn aan een in artikel 1 bedoelde onderneming. § 2. Het bedrag van de syndicale premie wordt berekend op basis van het aantal gewerkte en gelijkgestelde dagen in de referteperiode en bedraagt 1/12de per maand lidmaatschap van een representatieve interprofessionele werknemersorganisatie tijdens de referteperiode vermeld in § 1.  </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de bedienden der metaalfabrikatennijverheid;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 9 december 2024, gesloten in het Paritair Comité voor de bedienden der metaalfabrikatennijverheid, betreffende de sectorale minimumlonen vanaf 1 januari 2025.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de bedienden der metaalfabrikatennijverheidCollectieve arbeidsovereenkomst van 9 december 2024Sectorale minimumlonen vanaf 1 januari 2025 (Overeenkomst geregistreerd op 20 december 2024 onder het nummer 191195/CO/209)Artikel 1. ToepassingsgebiedDeze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en hun werknemers met een arbeidsovereenkomst voor bedienden die behoren tot het Paritair Comité voor de bedienden der metaalfabrikatennijverheid.Onder "bedienden" wordt verstaan : de gebaremiseerde en baremiseerbare bedienden.Art. 2. Sectorale minimumlonenDe in bijlage van de collectieve arbeidsovereenkomst van 8 juli 2024 (registratienummer 189035/CO/209) opgenomen sectorale minimumlonen worden vanaf 1 januari 2025 vervangen door de sectorale minimumlonen gevoegd als bijlage aan deze collectieve arbeidsovereenkomst.Art. 3. DuurDeze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025 en wordt gesloten voor onbepaalde duur.Zij kan door één van de partijen worden opgezegd met een opzegging van 3 maanden betekend bij een ter post aangetekende brief gericht aan de voorzitter van het paritair comité en aan elk van de ondertekenende organisaties.Zij wordt alleszins opgeheven op de datum van inwerkingtreding van een nog te sluiten collectieve arbeidsovereenkomst die een nieuw sectoraal minimumbarema invoert op basis van de classificatie beschreven in de collectieve arbeidsovereenkomst van 31 maart 2014 met betrekking tot een sectorale functieclassificatie met het oog op de toepassing van het sectorale minimumbarema (met registratienummer 122085/CO/209).Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025.De Minister van Werk,D. CLARINVALBijlage aan de collectieve arbeidsovereenkomst van 9 december 2024, gesloten in het Paritair Comité voor de bedienden der metaalfabrikatennijverheid, betreffende de sectorale minimumlonen vanaf 1 januari 2025Sectorale minimumlonen op 1 januari 2025  </t>
         </is>
       </c>
     </row>
@@ -1699,28 +1699,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2025200970</t>
+          <t>2025000880</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>16 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 9 december 2024, gesloten in het Paritair Comité voor de socio-culturele sector, betreffende de opheffing van de collectieve arbeidsovereenkomst van 13 december 2002 betreffende de oprichting van een fonds voor bestaanszekerheid genaamd "Sociaal Fonds Sociale Maribel voor de socio-culturele sector" en tot vaststelling van de statuten ervan (overeenkomst geregistreerd op 20 februari 2003 onder het nummer 65534/CO/329) (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 11 december 2024, gesloten in het Paritair Subcomité voor de bedienden van de inrichtingen van het gesubsidieerd vrij onderwijs van de Franse Gemeenschap en de Duitstalige Gemeenschap, betreffende de verplichte verbinding en het recht op deconnectie in de professionele betrekkingen (1)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-16&amp;numac_search=2025200970&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200970=39&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025000880&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025000880=39&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de socio-culturele sector; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 9 december 2024, gesloten in het Paritair Comité voor de socio-culturele sector, betreffende de opheffing van de collectieve arbeidsovereenkomst van 13 december 2002 betreffende de oprichting van een fonds voor bestaanszekerheid genaamd "Sociaal Fonds Sociale Maribel voor de socio-culturele sector" en tot vaststelling van de statuten ervan (overeenkomst geregistreerd op 20 februari 2003 onder het nummer 65534/CO/329).Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de socio-culturele sector Collectieve arbeidsovereenkomst van 9 december 2024 Opheffing van de collectieve arbeidsovereenkomst van 13 december 2002 betreffende de oprichting van een fonds voor bestaanszekerheid genaamd "Sociaal Fonds Sociale Maribel voor de socio-culturele sector" en tot vaststelling van de statuten ervan (overeenkomst geregistreerd op 20 februari 2003 onder het nummer 65534/CO/329) (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191534/CO/329) HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers die ressorteren onder het Paritair Subcomité voor de federale en bicommunautaire socio-culturele organisaties en op hun werknemers. HOOFDSTUK II. - Opheffingsbepalingen Art. 2. De collectieve arbeidsovereenkomst van 13 december 2002 betreffende de oprichting van een fonds voor bestaanszekerheid genaamd "Sociaal Fonds Sociale Maribel voor de socio-culturele sector" en tot vaststelling van de statuten ervan (overeenkomst geregistreerd op 20 februari 2003 onder het nummer 65534/CO/329) wordt opgeheven vanaf 20 november 2023 om middernacht. Toelichting Voor de continuïteit van de uitvoering van de opgeheven overeenkomst wordt gezorgd door de ondertekening van een overeenkomst van dezelfde aard in het Paritair Subcomité voor de federale en bicommunautaire socioculturele organisaties (PSC 329.03) met inwerkingtreding op 21 november 2023. Art. 3.  Deze collectieve arbeidsovereenkomst vervangt integraal de collectieve arbeidsovereenkomst van 20 november 2023 gesloten in het Paritair Comité voor de socio-culturele sector betreffende de opheffing van de collectieve arbeidsovereenkomst van 13 december 2002 betreffende de oprichting van een fonds voor bestaanszekerheid genaamd "Sociaal Fonds Sociale Maribel voor de socio-culturele sector" en tot vaststelling van de statuten ervan (registratienummer 185726/CO/329). Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van 20 november 2023 om middernacht en is gesloten voor onbepaalde tijd. Zij kan door elk van de partijen worden opgezegd mits een opzeggingstermijn van zes maanden betekend bij een ter post aangetekende brief, gericht aan de voorzitter van het Paritair Comité voor de socio-culturele sector. Overeenkomstig artikel 14 van de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, worden voor wat betreft de ondertekening van deze collectieve arbeidsovereenkomst, de handtekeningen van de personen die deze aangaan namens de werknemersorganisaties enerzijds, en namens de werkgeversorganisaties anderzijds, vervangen door de, door de voorzitter en de secretaris ondertekende en door de leden goedgekeurde notulen van de vergadering. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Subcomité voor de bedienden van de inrichtingen van het gesubsidieerd vrij onderwijs van de Franse gemeenschap en de Duitstalige gemeenschap;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 11 december 2024, gesloten in het Paritair Subcomité voor de bedienden van de inrichtingen van het gesubsidieerd vrij onderwijs van de Franse Gemeenschap en de Duitstalige Gemeenschap, betreffende de verplichte verbinding en het recht op deconnectie in de professionele betrekkingen.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Subcomité voor de bedienden van de inrichtingen van het gesubsidieerd vrij onderwijs van de Franse Gemeenschap en de Duitstalige GemeenschapCollectieve arbeidsovereenkomst van 11 december 2024Verplichte verbinding en recht op deconnectie in de professionele betrekkingen (Overeenkomst geregistreerd op 7 januari 2025 onder het nummer 191323/CO/225.02)Artikel 1. ToepassingsgebiedDeze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de werknemers van de onderwijsinstellingen en de internaten van het vrij onderwijs van de Franse Gemeenschap en de Duitstalige Gemeenschap, waarvan de maatschappelijke zetel gevestigd is in het Waalse Gewest en in het Brusselse Hoofdstedelijk Gewest en die zijn ingeschreven bij de Rijksdienst voor Sociale Zekerheid op de Franse taalrol.Art. 2. DefinitieHet recht op deconnectie is het recht van de werknemer om niet ingelogd te zijn op zijn professionele digitale tools buiten de overeengekomen werkuren. De bedoelde digitale tools omvatten de digitale tools die ter beschikking zijn gesteld door de werkgever (platform, mailadressen, enz.). De persoonlijke digitale tools (gsm, smartphone, enz.) zijn persoonlijke communicatiemiddelen die dus buiten de verplichte verbinding vallen in het kader van de professionele relaties.De doelstelling van deze tekst is het omkaderen van de verbindingen en het vaststellen van deconnectiemomenten om, enerzijds, de overconnectie van de werknemers te voorkomen en, anderzijds, om de rust- en vakantietijden na te leven, alsook het noodzakelijke evenwicht tussen het beroepsleven en het privéleven, en tegelijk te zorgen voor een kwaliteitsvolle dienstverlening.Art. 3. Verplichte verbindingOnder voorbehoud van de terbeschikkingstelling van het nodige materiaal en van de mogelijkheid tot toegang tot het netwerk, als de werknemer zijn mails moet raadplegen, werken op een platform of al het andere werk in verband met het digitale uitvoeren, gebeurt dit in het kader van de arbeidstijd van de werknemer. Onder deze voorwaarden zal de werknemer die voltijds werkt erop toezien dat hij de verschillende digitale tools ten minste één keer per dag raadpleegt. Voor de werknemers die deeltijds werken, zij hebben slechts in verhouding tot de gepresteerde opdrachtbreuk de verplichting om verbonden te zijn.Tijdens de verloven, de jaarlijkse vakanties alsook gedurende de periodes van schorsing van de arbeidsovereenkomst is de werknemer niet verplicht om verbonden te zijn en, bijvoorbeeld, om zijn professionele berichten te raadplegen.Art. 4. Recht op deconnectieOm een te grote inmenging van de beroepssfeer in de privésfeer te voorkomen, moeten de volgende principes worden nageleefd :- De verzending van de dienstmededelingen van de directie of van de inrichtende macht naar de werknemers moet in principe gebeuren :- via het professioneel e-mailadres als het wordt verstrekt door de werkgever of bij gebreke daarvan het adres dat werd medegedeeld door de werknemer;- gedurende de openingsuren van de instelling.Als de directie ertoe wordt gebracht om mededelingen te doen buiten deze periodes, en dit in geval van noodzaak voor de dienst, zal zij erop toezien dat zij enkel de noodzakelijke informatie mededeelt en zal zij het meest directe en het minst invasieve communicatiemiddel voor de werknemer gebruiken (1).- De professionele mededelingen die uitgaan van de werknemers onderling of ten aanzien van de directie of van de inrichtende macht moeten in principe gebeuren :- via het professioneel e-mailadres als het wordt verstrekt door de werkgever of bij gebreke daarvan het adres dat werd medegedeeld door de werknemer;- gedurende de openingsuren van de instelling.Als de werknemer ertoe wordt gebracht om mededelingen te doen buiten deze periodes, aan zijn collega's of aan de directie of aan de inrichtende macht, en dit in geval van noodzaak voor de dienst, zal hij erop toezien om enkel de noodzakelijke informatie mede te delen en zal hij het meest directe en het minst invasieve communicatiemiddel voor de bestemmeling gebruiken (2).Als het elektronisch bericht een antwoord vraagt (mondeling, schriftelijk of in de vorm van een actie), moet in een redelijke termijn hiervoor worden voorzien. Het redelijk karakter van de termijn moet worden vermeld in het bericht en zal rekening houden met de soort verzoek, de dringendheid ervan en de arbeidstijd van de betrokken werknemer.Voor wat de organisatie en het houden van culturele of pedagogische activiteiten buiten de openingsuren van de instelling betreft, zal in een beperkte soepelheid in de tijd kunnen worden voorzien die binnen een redelijke termijn wordt medegedeeld aan alle betrokken werknemers.Art. 5. Preventiebeleid en risicoanalyseElke werkgever zal een communicatiebeleid volgen dat wordt bepaald in overleg met het lokaal sociaaloverlegorgaan dat bevoegd is inzake risicopreventiebeleid. Dit beleid zal de risicoanalyse in verband met overconnectie in rekening nemen.Op basis van deze analyse zal het intern beleid voorzien in momenten en modaliteiten voor informatie en sensibilisering voor de doordachte en zorgzame communicatie. Het beleid zal regelmatig opnieuw worden geëvalueerd door het lokaal sociaal overlegorgaan dat bevoegd is inzake risicopreventiebeleid om te evolueren met de behoeften en de risico's die werden aangepakt bij inrichtende macht.Als het intranet (of een ander digitaal platform) ingevoerd door de inrichtende macht de communicatie met de studenten/de leerlingen/de ouders mogelijk maakt, zal het communicatiebeleid vastgesteld door de inrichtende macht in overleg met het lokaal sociaal overlegorgaan dat bevoegd is inzake risicopreventiebeleid de gebruiksmodaliteiten ervan aangeven in de geest van deze bepalingen.Voorafgaandelijk aan de keuze van een digitaal platform zal de inrichtende macht het lokaal sociaal overlegorgaan dat bevoegd is inzake risicopreventiebeleid raadplegen over de behoeften waaraan moet worden voldaan en over de gewenste werkingsmodaliteiten van de tool.De werkgever zal voor de werknemers de toegang waarborgen tot de opleidingen/informatie voor het gebruik van de digitale middelen die ter beschikking worden gesteld van de werknemer binnen zijn instelling(en).Art. 6. Inwerkingtreding en geldigheidDeze collectieve arbeidsovereenkomst treedt in werking op 1 februari 2025 en wordt gesloten voor onbepaalde duur.De sociale partners vragen de algemeen verbindend verklaring.Ze kan door elk van de partijen worden opgezegd door middel van een opzeggingstermijn van zes maanden die wordt betekend bij een ter post aangetekend schrijven, gericht aan de voorzitter van het Paritair Subcomité voor de bedienden van de inrichtingen van het gesubsidieerde vrij onderwijs van de Franse Gemeenschap en de Duitstalige Gemeenschap.Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025.De Minister van Werk,D. CLARINVAL_______Nota(1) Dit is van toepassing met naleving van het 2de lid van artikel 3 - Verplichte verbinding.(2) Dit is van toepassing met naleving van het 2de lid van artikel 3 - Verplichte verbinding. 
 </t>
         </is>
       </c>
@@ -1731,29 +1731,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025200961</t>
+          <t>2025002979</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>16 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 16 december 2024, gesloten in het Paritair Comité voor de apotheken en tarificatiediensten, betreffende de vorming (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 12 december 2024, gesloten in het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap, betreffende de samenstelling van het "Fonds tweede pijler PSC 152.01" (1)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-16&amp;numac_search=2025200961&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200961=40&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025002979&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025002979=40&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de apotheken en tarificatiediensten; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 16 december 2024, gesloten in het Paritair Comité voor de apotheken en tarificatiediensten, betreffende de vorming. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de apotheken en tarificatiediensten Collectieve arbeidsovereenkomst van 16 december 2024 Vorming (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191544/CO/313) Artikel 1. Voor de toepassing van deze collectieve arbeidsovereenkomst, wordt verstaan onder "werknemers" : de mannelijke en vrouwelijke werknemers. HOOFDSTUK I. - De werkgevers die minder dan tien werknemers tewerkstellen Afdeling I. - Toepassingsgebied Art. 2. Dit hoofdstuk is van toepassing op de werkgevers die minder dan tien werknemers tewerkstellen en de werknemers die onder de bevoegdheid vallen van het Paritair Comité voor de apotheken en tarificatiediensten, werknemers die, ofwel onder arbeidscontract gesloten voor onbepaalde duur, ofwel onder arbeidscontract van bepaalde duur van een jaar of langer tewerkgesteld zijn. Afdeling II. - Algemene beschikkingen Art. 3. De farmaceutisch-technische assistenten die voltijds tewerkgesteld zijn hebben recht op drie dagen vorming per jaar. Voor de farmaceutisch-technische assistenten die tewerkgesteld zijn in een deeltijds stelsel gelijk aan minstens 50 pct. van de in de onderneming geldende voltijdse arbeidsduur worden de drie dagen bedoeld in vorige alinea beperkt tot 1 1/2 dag. De vormingen die binnen het bedrijf of door meerdere bedrijven samen worden georganiseerd komen in aanmerking als vormingsdagen zoals bepaald in dit artikel. Art. 4. De vormingen bedoeld in artikel 3 komen ten laste van de werkgever wanneer zij binnen het bedrijf of door meerdere bedrijven samen georganiseerd worden of, voor de andere vormingen, wanneer zij erkend zijn door het paritair fonds opgericht door de sectorale collectieve arbeidsovereenkomst van 9 juni 1997 (koninklijk besluit van 22 januari 2002; Belgisch Staatsblad van 4 april 2002). Art. 5. De andere werknemers, die noch farmaceutisch-technische assistenten noch apothekers zijn, hebben recht op drie dagen vorming per jaar voor zover de gekozen vormingen van aard zijn hun beroepskwalificatie in de uitgeoefende functie te verbeteren of een gunstige evolutie van hun beroepsloopbaan te bevorderen. Voor de werknemers voorzien onder alinea 1 die tewerkgesteld zijn in een deeltijds stelsel gelijk aan minstens 50 pct. van de in de onderneming geldende voltijdse arbeidsduur worden de drie dagen bedoeld in vorige alinea beperkt tot 1 1/2 dag. Art. 6. De werkgevers die deze vormingsdagen, zoals bepaald in artikelen 3, 4 en 5, weigeren zijn verplicht als compensatie bezoldigde afwezigheden toe te kennen. De bezoldigde afwezigheden worden toegekend tijdens het vierde kwartaal van elk kalenderjaar, naar keuze van de werknemer a rato van ofwel volledige opeenvolgende dagen, ofwel halve dagen. Art. 7. De werkgever betaalt aan de werknemer die om een andere reden dan om een dwingende reden werd ontslagen, de bezoldiging verbonden met de in het lopende kalenderjaar nog niet gebruikte vormingsdagen. In dat geval heeft de werknemer geen recht meer op die vormingsdagen bij een nieuwe door deze collectieve arbeidsovereenkomst gebonden werkgever. Art. 8. De adjunct-apothekers en de apothekerstitularissen die geen eigenaar zijn van een apotheek hebben, recht op een forfaitaire vergoeding vastgesteld op 50 EUR per kalenderjaar, ten laste van hun werkgever en betaald na voorlegging van een bewijs van aanwezigheid op enige vorming die kan bijdragen tot de verbetering van hun beroepskwalificatie en op voorwaarde dat de opleidingen niet door de werkgever worden ten laste genomen. HOOFDSTUK II. - De werkgevers die minstens tien en minder dan twintig werknemers tewerkstellen Dit hoofdstuk is vastgesteld ter uitvoering van hoofdstuk XII van de wet van 3 oktober 2022 houdende diverse arbeidsbepalingen. Afdeling I. - Toepassingsgebied Art. 9. Dit hoofdstuk is van toepassing op werkgevers die minstens tien en minder dan twintig werknemers tewerkstellen, en de werknemers die ressorteren onder de bevoegdheid van het Paritair Comité voor de apotheken en tarificatiediensten. Art. 10. Dit hoofdstuk wordt gesloten in uitvoering van artikel 58 van de wet van 3 oktober 2022 houdende diverse arbeidsbepalingen. Afdeling II. - Algemene beschikkingen Art. 11. De werkgevers die ressorteren onder de bevoegdheid van het Paritair Comité voor de apotheken en tarificatiediensten engageren zich om de interprofessionele collectieve doelstelling van 5 opleidingsdagen voor alle werknemers per jaar per voltijds equivalent te bereiken met als traject : - 2 dagen in 2022 inclusief één dag individuele opleiding; - 3 dagen in 2024 inclusief één dag individuele opleiding; - 4 dagen in 2026 inclusief één dag individuele opleiding; - 5 dagen in 2028 inclusief één dag individuele opleiding. Voor de werknemers die tewerkgesteld zijn in een deeltijds stelsel gelijk aan minstens 50 pct. van de in de onderneming geldende voltijdse arbeidsduur worden de dagen bedoeld in vorige alinea beperkt tot de helft van de opleidingsdagen per jaar. Art. 12. De vormingen, bedoeld in artikel 10, komen ten laste van de werkgever wanneer zij binnen het bedrijf of door meerdere bedrijven samen georganiseerd worden of voor de andere vormingen, wanneer zij erkend zijn door het Fonds 313 opgericht door de sectorale collectieve arbeidsovereenkomst van 9 juni 1997 (45742/CO/313, koninklijk besluit van 22 januari 2002; Belgisch Staatsblad van 4 april 2022). HOOFDSTUK III. - De werkgevers die minstens twintig werknemers tewerkstellen Dit hoofdstuk is vastgesteld ter uitvoering van hoofdstuk XII van de wet van 3 oktober 2022 houdende diverse arbeidsbepalingen.Afdeling I. - Toepassingsgebied Art. 13. Dit hoofdstuk is van toepassing op de werkgevers die minstens twintig werknemers tewerkstellen, en de werknemers die ressorteren onder de bevoegdheid van het Paritair Comité voor de apotheken en tarificatiediensten. Dit hoofdstuk wordt uitdrukkelijk gesloten in uitvoering van de wet van 3 oktober 2022 houdende diverse arbeidsbepalingen - hoofdstuk XII : "Investeren in opleiding" en meer bepaald artikelen 52 en volgende over "Principes inzake het individueel opleidingsrecht en invoeringsvoorwaarden en -modaliteiten ervan" en betreft uitsluitend de werkgevers zoals vermeld in artikel 51 van deze wet. Afdeling II. - Algemene beschikkingen Art. 14. De werkgevers die ressorteren onder de bevoegdheid van het Paritair Comité voor de apotheken en tarificatiediensten die ten minste twintig werknemers tewerkstellen engageren zich om vanaf 2024 het individuele recht op opleiding van 5 opleidingsdagen voor alle werknemers per jaar per voltijds equivalent te bereiken. Voor de werknemers die tewerkgesteld zijn in een deeltijds stelsel gelijk aan minstens 50 pct. van de in de onderneming geldende voltijdse arbeidsduur worden de dagen bedoeld in vorige alinea beperkt tot de helft van de opleidingsdagen per jaar. Art. 15. De opleidingen die in aanmerking worden genomen om het aantal individuele opleidingsdagen te bepalen zijn ten minste : - de "formele opleiding" en "informele opleiding" gedefinieerd overeenkomstig artikel 50, § 1, a) en b) van de bovenvermelde wet van 3 oktober 2022; - de opleidingen die betrekking hebben op de materies inzake het welzijnsbeleid bedoeld in de wet van 4 augustus 1996 betreffende het welzijn van de werknemers bij de uitvoering van hun werk. HOOFDSTUK IV. - Werktijden Art. 16.  Overeenkomstig artikel 59 van de wet van 3 oktober 2022 houdende diverse arbeidsbepalingen, de opleiding kan door de werknemer worden gevolgd, hetzij binnen zijn gewone werktijden, hetzij buiten zijn gewone werktijden. Wanneer de opleiding buiten de gewone werktijden wordt gevolgd, geven de uren die daarmee overeenkomen recht op de betaling van het normale loon, zonder evenwel aanleiding te geven tot de betaling van een eventueel overloon. HOOFDSTUK V. - Aanvullend karakter Art. 17. Deze collectieve arbeidsovereenkomst doet geen afbreuk aan gunstigere bedrijfscollectieve arbeidsovereenkomsten of individuele overeenkomsten. HOOFDSTUK VI. - Geldigheid Art. 18. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2024 en vervangt de bepalingen van de eerdere collectieve arbeidsovereenkomsten betreffende de opleiding van te weten de collectieve arbeidsovereenkomsten van 16 december 2003 (69886/CO/313), van 27 februari 2008 (88454/CO/313), van 14 april 2011 (103975/CO/313), van 24 oktober 2011 (106884/CO/313), van 17 december 2021 (175922/CO/313), alsook van 22 december 2023 (185589/CO/313), gesloten in het Paritair Comité voor de apotheken en tarificatiediensten. Deze collectieve arbeidsovereenkomst wordt gesloten voor een onbepaalde duur. Elke partij kan deze collectieve arbeidsovereenkomst opzeggen met een opzeggingstermijn van 3 maanden, middels de verzending van een aangetekende brief aan de voorzitter van het Paritair Comité voor de apotheken en tarificatiediensten. Overeenkomstig artikel 14 van de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, worden voor wat betreft de ondertekening van deze collectieve arbeidsovereenkomst, de handtekeningen van de personen die deze aangaan namens de werknemersorganisaties enerzijds, en namens de werkgeversorganisaties anderzijds, vervangen door de, door de voorzitter en de secretaris ondertekende en door de leden goedgekeurde notulen van de vergadering. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 12 december 2024, gesloten in het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap, betreffende de samenstelling van het "Fonds tweede pijler PSC 152.01".Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse GemeenschapCollectieve arbeidsovereenkomst van 12 december 2024Samenstelling van het "Fonds tweede pijler PSC 152.01" (Overeenkomst geregistreerd op 7 januari 2025 onder het nummer 191328/CO/152.01)HOOFDSTUK I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers van de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap en op hun werknemers, met uitzondering van de hogescholen.Onder "werknemers" wordt verstaan : de arbeiders zonder onderscheid naar gender.HOOFDSTUK II. - Samenstelling van de raad van beheerArt. 2. De statuten van het "Fonds tweede pijler PSC152.01", opgericht bij de collectieve arbeidsovereenkomst van 4 april 2019 (registratienummer 151589/CO/152.01), worden aangevuld met een bijlage waarin de leden van de raad van bestuur worden opgesomd.HOOFDSTUK III. - GeldigheidArt. 3. Deze collectieve arbeidsovereenkomst treedt in werking op datum van ondertekenen en is gesloten voor onbepaalde duur.Zij vervangt de collectieve arbeidsovereenkomst van 9 februari 2023, geregistreerd onder het nummer 179362/CO/152.01.Zij kan door elk van de partijen opgezegd worden mits een opzegging van zes maanden, te betekenen bij een ter post aangetekende brief, gericht aan de voorzitter van het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap.Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025.De Minister van Werk,D. CLARINVALBijlage aan de collectieve arbeidsovereenkomst van 12 december 2024, gesloten in het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap, betreffende de samenstelling van het "Fonds tweede pijler PSC 152.01"In toepassing van artikel 16 van de statuten van het "Fonds tweede pijler PSC 152.01" heeft het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap als leden van de raad van bestuur benoemd :  </t>
         </is>
       </c>
     </row>
@@ -1763,28 +1762,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025000771</t>
+          <t>2025002981</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>16 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 30 mei 2024, gesloten in het Paritair Subcomité voor het koetswerk, tot wijziging en coördinatie van het sociaal sectoraal pensioenstelsel (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor de landbouw, tot vaststelling van de sectorale minimumloonschalen voor de bedienden op basis van beroepservaring (1)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-16&amp;numac_search=2025000771&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025000771=41&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025002981&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025002981=41&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Subcomité voor het koetswerk;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 30 mei 2024, gesloten in het Paritair Subcomité voor het koetswerk, tot wijziging en coördinatie van het sociaal sectoraal pensioenstelsel.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Subcomité voor het koetswerkCollectieve arbeidsovereenkomst van 30 mei 2024Wijziging en coördinatie van het sociaal sectoraal pensioenstelsel (Overeenkomst geregistreerd op 2 september 2024 onder het nummer 189427/CO/149.02)HOOFDSTUK I. - ToepassingsgebiedArtikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en arbeiders van de ondernemingen welke ressorteren onder het Paritair Subcomité 149.02 voor het koetswerk. § 2. Worden uitgesloten van het toepassingsgebied van deze overeenkomst, de buiten België gevestigde werkgevers waarvan de werknemers in België gedetacheerd worden in de zin van de bepalingen van de verordening (EEG) nr. 1408/71 van de Raad of de verordening (EG) nr. 883/2004 van het Europees Parlement en de Raad. § 3. Onder "arbeiders" wordt verstaan : de mannelijke en vrouwelijke arbeiders.HOOFDSTUK II. - VoorwerpArt. 2.  § 1. Deze collectieve arbeidsovereenkomst heeft tot doel om vanaf 31 december 2023 de collectieve arbeidsovereenkomst van 2 december 2021 tot wijziging en coördinatie van het sociaal sectoraal pensioenstelsel en overgang van solidariteitsinstelling met overdracht van het solidariteitsfonds, geregistreerd onder het nummer 170156/CO/149.02, te vervangen. § 2. De begrippen die in het vervolg van deze collectieve arbeidsovereenkomst opgenomen zijn, moeten worden opgevat in hun betekenis zoals bepaald in de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid (Belgisch Staatsblad van 15 mei 2003, editie 2, p. 26407, erratum Belgisch Staatsblad van 26 mei 2003) en haar uitvoeringsbesluiten. Deze wet zal in het vervolg van deze collectieve arbeidsovereenkomst "W.A.P." worden genoemd.HOOFDSTUK III. - Aanduiding van de InrichterArt. 3.  § 1. Overeenkomstig artikel 3, § 1, 5°  van de W.A.P. werd het fonds voor bestaanszekerheid, genaamd "Sociaal Fonds voor de koetswerkondernemingen" via de collectieve arbeidsovereenkomst van 5 juli 2002 (63599/CO/149.02) door de representatieve organisaties van het voormelde paritair subcomité aangeduid als Inrichter van dit sociaal sectoraal pensioenstelsel. § 2. Deze aanduiding blijft uiteraard gelden in het kader van deze collectieve arbeidsovereenkomst van 30 mei 2024 tot wijziging en coördinatie van het sociaal sectoraal pensioenstelsel. § 3. Indien de representatieve organisaties vertegenwoordigd in het Paritair Subcomité voor het koetswerk zouden beslissen dat het "Sociaal Fonds voor de koetswerkondernemingen" niet langer zal optreden als de Inrichter van dit sociaal sectoraal pensioenstelsel dan duiden zij een andere inrichter aan die alle rechten en verplichtingen overneemt van het Sociaal fonds voor de koetswerkondernemingen die betrekking hebben op de inrichting van dit sociaal sectoraal pensioenstelsel.HOOFDSTUK IV. - AansluitingsvoorwaardenArt. 4.  § 1. Alle arbeiders die op of na 1 januari 2002 met de werkgevers zoals bedoeld in artikel 1, § 1 van deze overeenkomst verbonden zijn of waren via een arbeidsovereenkomst (ongeacht de aard van arbeidsovereenkomst), worden ambtshalve aangesloten bij dit sociaal sectoraal pensioenplan. In de praktijk gaat het om de werklieden aangegeven onder de werknemerskengetallen 015, 024 en 027. § 2. Worden echter niet aangesloten bij dit pensioenplan :- de personen tewerkgesteld via een overeenkomst van studentenarbeid;- de personen tewerkgesteld via een overeenkomst voor uitzendarbeid, zoals geregeld door hoofdstuk II van de wet van 24 juli 1987 betreffende de tijdelijke arbeid, de uitzendarbeid en het ter beschikking stellen van de werknemers ten behoeve van gebruikers;- de leerlingen;- de personen tewerkgesteld met een arbeidsovereenkomst gesloten in het kader van een speciaal met steun van de overheid gevoerd opleidings-, arbeidsinspannings-, en omscholingsprogramma;- de personen die effectief hun wettelijk (vervroegd) pensioen hebben opgenomen vanaf 1 januari 2016, maar vervolgens als gepensioneerde verder of opnieuw tewerkgesteld worden met een arbeidsovereenkomst afgesloten met hun werkgevers zoals bedoeld in artikel 1, § 1 van deze overeenkomst.HOOFDSTUK V. - BijdrageArt. 5.  § 1. In het voordeel van de in artikel 4 bedoelde personen zullen er maandelijks door de Inrichter één of meerdere bijdragen gestort worden ter financiering van het sociaal sectoraal pensioenstelsel ter aanvulling van de wettelijke pensioenregeling. § 2. De totale jaarlijkse brutobijdrage per aangeslotene bij het sociaal sectoraal pensioenstelsel bedraagt sinds 1 januari 2016 2,20 pct. van diens jaarlijks brutoloon waarop R.S.Z.-inhoudingen worden gedaan. § 3. De totale jaarlijkse brutobijdrage per aangeslotene bij het sociaal sectoraal pensioenstelsel wordt verminderd met 4,5 pct. beheerskosten, aangerekend door de Inrichter, wat resulteert in een totale jaarlijkse nettobijdrage per aangeslotene van 2,10 pct. van diens jaarlijks brutoloon waarop R.S.Z.-inhoudingen worden gedaan. § 4. Deze nettobijdrage wordt als volgt verdeeld : 2,01 pct. wordt aangewend ter financiering van individuele pensioenrechten in hoofde van de bij het sociaal sectoraal stelsel aangeslotenen en de overige 0,09 pct. wordt gebruikt ter financiering van een solidariteitstoezegging zoals bedoeld in titel II, hoofdstuk 9 van de W.A.P. § 5. Dit resulteert, na vermeerdering van de nettobijdrage met 0,18 pct. ter dekking van de verschuldigde, bijzondere bijdrage van 8,86 pct., in een globale bijdrage van 2,38 pct.HOOFDSTUK VI. - Pensioentoezegging : overgang van pensioeninstelling met collectieve overdracht van verworven reservesArt. 6.  § 1. Tot 31 december 2018 werd het financieel, boekhoudkundig, actuarieel en administratief beheer van de pensioentoezegging door de Inrichter toevertrouwd aan Belfius Verzekeringen n.v., erkend door de Nationale Bank van België onder nummer 37, met maatschappelijke zetel te 1210 Brussel, Karel Rogierplein 11, die 50 pct. van haar risico herverzekerde via KBC Verzekeringen nv, erkend door de Nationale Bank van België onder nummer 14, met maatschappelijke zetel te 3000 Leuven, Professor Roger Van Overstraetenplein 2.Met ingang van 1 januari 2019 werd het financieel, boekhoudkundige, actuarieel en administratief beheer overgedragen aan SEFOPLUS OFP, de multi-sectorale instelling voor bedrijfspensioenvoorziening (IBP), toegelaten door de FSMA op 19 november 2018 met identificatienummer 50.624, met maatschappelijke zetel te 1120 Brussel, Marlylaan 15, bus 8.De raad van bestuur van SEFOPLUS OFP is in overeenstemming met artikel 41, § 1, 1°  van de W.A.P. paritair samengesteld. § 2. De overgang van pensioeninstelling van Belfius Verzekeringen n.v. naar SEFOPLUS OFP ging gepaard met een collectieve overdracht van de reserves in de zin van artikel 34 van de W.A.P. Deze collectieve overdracht werd geregeld in de overdrachtsovereenkomst tussen de deelnemende sectorale inrichters, SEFOPLUS OFP en Belfius Verzekeringen n.v. In het kader van deze collectieve overdracht werd geen enkele vergoeding of verlies van winstdelingen ten laste gelegd van de aangeslotenen, of van de op het ogenblik van de overdracht verworven reserves afgetrokken. § 3. De regels van de pensioentoezegging zijn vastgelegd in een pensioenreglement dat wordt opgenomen als bijlage bij deze collectieve arbeidsovereenkomst waarvan het integraal deel uitmaakt. Het pensioenreglement zal door SEFOPLUS OFP, via de v.z.w. SEFOCAM, aan de aangeslotenen ter beschikking worden gesteld op hun eenvoudig verzoek. § 4. Onder de naam "transparantieverslag" stelt SEFOPLUS OFP jaarlijks een verslag op over het door haar gevoerde beheer van de pensioentoezegging.HOOFDSTUK VII. - Uitbetaling van de voordelenArt. 7. De procedure, de modaliteiten en de vorm van de uitbetaling van de voordelen worden beschreven in artikel 7 tot en met artikel 14 van het bijgevoegde pensioenreglement.HOOFDSTUK VIII. - Solidariteitstoezegging - Overgang van solidariteitsinstelling met overdracht van solidariteitsfondsArt. 8.  § 1. Vanaf 1 januari 2004 wordt een gedeelte van de globale nettobijdrage, zoals vastgelegd in artikel 5 van deze overeenkomst (in overeenstemming met artikel 43 van de W.A.P.) aangewend ter financiering van de solidariteitstoezegging die deel uitmaakt van het sociaal sectoraal pensioenstelsel. § 2. Deze bijdrage wordt aangewend ter financiering van de solidariteitsprestaties, waaronder in het bijzonder de financiering van de opbouw van de pensioentoezegging gedurende bepaalde periodes van inactiviteit en de vergoeding van inkomstenverlies in bepaalde gevallen. De exacte inhoud van deze solidariteitstoezegging alsook de financieringswijze ervan, werd uitgewerkt in een solidariteitsreglement (zie hierna in artikel 9). § 3. Het beheer van de solidariteitstoezegging werd door de Inrichter tot en met 31 december 2021 toevertrouwd aan Belfius Verzekeringen n.v., afgekort "Belins n.v.", erkend door de Nationale Bank van België onder nummer 37, met maatschappelijke zetel te 1210 Brussel, Karel Rogierplein 11.Met ingang van 1 januari 2022 werd het beheer van de solidariteitstoezegging door de Inrichter toevertrouwd aan SEFOPLUS OFP, de multi-sectorale instelling voor bedrijfspensioenvoorziening (IBP), toegelaten door de FSMA op 19 november 2018 met identificatienummer 50.624, met maatschappelijke zetel te 1120 Brussel, Marlylaan 15, bus 8, die reeds sinds 1 januari 2019 optreedt als pensioeninstelling. § 4. De overgang van solidariteitsinstelling van Belfius Verzekeringen n.v. naar SEFOPLUS OFP ging gepaard met de overdracht van het Sefocam solidariteitsfonds (collectieve solidariteitsreserves) van Belfius Verzekeringen n.v. naar SEFOPLUS OFP. Deze overdracht van het Sefocam solidariteitsfonds werd geregeld in de overdrachtsovereenkomst tussen de deelnemende sectorale inrichters, SEFOPLUS OFP, v.z.w. SEFOCAM en Belfius Verzekeringen n.v. § 5. SEFOPLUS OFP zal een "transparantieverslag" opstellen, met betrekking tot het door haar gevoerde beheer van de solidariteitstoezegging en zal dit op haar website ter beschikking stellen. Het verslag betreft de elementen zoals beschreven in de W.A.P.HOOFDSTUK IX. - SolidariteitsreglementArt. 9.  § 1. Het solidariteitsreglement expliciteert de modaliteiten van de solidariteitstoezegging en werd als bijlage opgenomen bij deze collectieve arbeidsovereenkomst waarvan het integraal deel uitmaakt. § 2. Het solidariteitsreglement zal door de Inrichter, via de v.z.w. SEFOCAM, op hun eenvoudig verzoek ter beschikking worden gesteld aan de bij dit pensioenstelsel aangesloten werknemers.HOOFDSTUK X. - Procedure in geval van uittreding van een arbeiderArt. 10. De procedure van uittreding uit het sectoraal pensioenstelsel wordt geregeld door artikel 18 van het hierna bijgevoegde pensioenreglement.HOOFDSTUK XI. - InningsmodaliteitenArt. 11.  § 1. Teneinde de bijdrage zoals voorzien in artikel 5, § 2 van deze overeenkomst in te vorderen zal door de Rijksdienst voor Sociale Zekerheid, overeenkomstig artikel 7 van de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid een voorlopige bijdrage worden geïnd. Deze voorlopige bijdrage zal na de terbeschikkingstelling ervan aan de Inrichter door laatstgenoemde worden doorgestort aan :- de pensioeninstelling : het gedeelte van de nettobijdrage die wordt aangewend ter financiering van de individuele pensioenrechten, alsook een gedeelte van de ingehouden beheerskosten overeenkomstig artikel 5 van deze overeenkomst, en;- de solidariteitsinstelling : het gedeelte van de nettobijdrage die wordt aangewend ter financiering van de solidariteitstoezegging, alsook een gedeelte van de ingehouden beheerskosten overeenkomstig artikel 5 van deze overeenkomst. § 2. Van zodra de Inrichter, via de v.z.w. SEFOCAM, over definitieve loongegevens beschikt, zal de voorlopige bijdrage worden vergeleken met de effectief verschuldigde bijdrage. Jaarlijks wordt een vergelijking gemaakt van de voorlopige bijdragen en de definitieve bijdragen voor alle voorafgaande jaren. Indien het totaal van de voorlopige bijdragen groter is dan het totaal van de effectief verschuldigde, definitieve bijdragen, wordt dit verschil op het eind van het jaar overgemaakt aan de Inrichter. In het omgekeerde geval, stort de Inrichter het bijdragetekort aan SEFOPLUS OFP. § 3. Vanaf 1 januari 2016 wordt er gebruik gemaakt van de gedifferentieerde R.S.Z.-inningstechniek waardoor de bijdrage voor het sociaal sectoraal aanvullend pensioenstelsel wordt afgescheiden van de basisbijdrage bestemd voor het fonds voor bestaanszekerheid. De bijzondere R.S.Z.-bijdrage van 8,86 pct. verschuldigd op de nettobijdrage zoals weergegeven in artikel 5, § 4, wordt voldaan ten aanzien van de Rijksdienst voor de Sociale Zekerheid bij wijze van verhoging van deze nettobijdrage voor de pensioentoezegging zoals weergegeven in artikel 5, § 4 en wordt door de R.S.Z. afgehouden aan de bron.Bijgevolg dient de bijzondere bijdrage van 8,86 procent niet apart te worden aangegeven daar de globale bijdrage zoals weergegeven in artikel 5, § 5 aangegeven moet worden onder bijdragecode 825 type "0".HOOFDSTUK XII. - Tijdelijke werkloosheid coronaArt. 12.  § 1. In het kader van de COVID-19 pandemie werd de wet van 7 mei 2020 houdende uitzonderlijke maatregelen in het kader van de COVID-19 pandemie inzake pensioenen, aanvullende pensioenen en andere voordelen inzake sociale zekerheid, ingevoerd (hierna "de wet van 7 mei 2020").Deze wet voorziet dat de pensioenopbouw en de overlijdensdekking van werknemers in een situatie van tijdelijke werkloosheid wegens overmacht of wegens economische redenen in het kader van de crisis van het coronavirus COVID-19 (hierna kortweg "tijdelijke werkloosheid corona") automatisch voortgezet worden gedurende de hele periode van tijdelijke werkloosheid corona, behoudens wanneer er wordt gekozen voor de opt-out mogelijkheid. § 2. Zoals voorzien in artikel 9, § 4 en § 5 van de wet van 7 mei 2020 heeft de Inrichter gekozen voor deze opt-out mogelijkheid. Hierdoor bouwen de aangeslotenen in tijdelijke werkloosheid corona geen pensioenrechten op onder dit sociaal sectoraal pensioenstelsel voor deze periode van tijdelijke werkloosheid corona, maar genieten zij tijdens deze periode wel verder van de overlijdensdekking. § 3. Overeenkomstig de wet van 7 mei 2020 wordt artikel 7 van het solidariteitsreglement (bijlage 2 van deze collectieve arbeidsovereenkomst) overeenkomstig aangepast.HOOFDSTUK XIII. - Tijdelijke werkloosheid energieArt. 13.  § 1. In het kader van de energiecrisis werd de wet van 30 oktober 2022 houdende tijdelijke ondersteuningsmaatregelen ten gevolge van de energiecrisis ingevoerd (hierna "de wet van 30 oktober 2022").Deze wet voorziet dat de pensioenopbouw en de overlijdensdekking van werknemers in een situatie van tijdelijke economische werkloosheid voor energie-intensieve bedrijven die operationele verliezen lijden wegens de stijging van aardgas- en elektriciteitskosten ten gevolge van de Russische militaire agressie tegen Oekraïne (hierna kortweg "tijdelijke werkloosheid energie") automatisch voortgezet worden gedurende de hele periode van tijdelijke werkloosheid energie, behoudens wanneer er wordt gekozen voor de opt-out mogelijkheid. § 2. Zoals voorzien in artikel 27, § 5 van de wet van 30 oktober 2022 heeft de Inrichter gekozen voor deze opt-out mogelijkheid. Concreet betekent dit dat de aanvullende pensioenopbouw zoals voorzien in het pensioenreglement wordt geschorst tijdens de volledige periode(s) van tijdelijke werkloosheid energie, maar genieten de aangeslotenen tijdens deze periode wel verder van de overlijdensdekking. Eveneens blijven de aangeslotenen genieten van de solidariteitstoezegging "pensioenopbouw gedurende periodes van economische werkloosheid", zoals opgenomen in artikel 7 van het solidariteitsreglement (bijlage 2 van deze collectieve arbeidsovereenkomst). § 3. Overeenkomstig de wet van 30 oktober 2022 wordt artikel 7 van het solidariteitsreglement (bijlage 2 van deze collectieve arbeidsovereenkomst) overeenkomstig aangepast.HOOFDSTUK XIV. - Inwerkingtreding en opzeggingsmogelijkhedenArt. 14.  § 1. De collectieve arbeidsovereenkomst van 2 december 2021 tot wijziging en coördinatie van het sociaal sectoraal pensioenstelsel en overgang van solidariteitsinstelling met overdracht van solidariteitsfonds, geregistreerd onder het nummer 170156/CO/149.02, wordt vervangen vanaf 31 december 2023. § 2. Deze collectieve arbeidsovereenkomst heft de collectieve arbeidsovereenkomst van 14 december 2023 betreffende de wijziging en coördinatie van het sociaal sectoraal pensioenstelsel (187445/CO/149.02) op.Door de opheffing van de collectieve arbeidsovereenkomst van 14 december 2023 blijft de collectieve arbeidsovereenkomst van 23 oktober 2023 betreffende de wijziging en coördinatie van de statuten van het sociaal fonds (184482/CO/149.02) volledig van toepassing. § 2. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van 31 december 2023 en wordt gesloten voor onbepaalde duur. § 3. Zij kan worden beëindigd mits opzegging van zes maanden en wordt betekend per ter post aangetekend schrijven, gericht aan de voorzitter van het voormelde paritair subcomité. Voorafgaandelijk aan de opzegging van de collectieve arbeidsovereenkomst moet het paritair subcomité de beslissing nemen om het sectoraal pensioenstelsel op te heffen. Deze beslissing tot opheffing is enkel geldig wanneer zij wordt genomen in overeenstemming met de bepalingen in artikel 10, § 1, 3°  van de W.A.P.Art. 15. Ondertekenende partijen vragen dat deze collectieve arbeidsovereenkomst, inclusief de bijlagen, zo vlug mogelijk bij koninklijk besluit algemeen verbindend wordt verklaard.Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025.De Minister van Werk,D. CLARINVALBijlage 1 aan de collectieve arbeidsovereenkomst van 30 mei 2024, gesloten in het Paritair Subcomité voor het koetswerk, tot wijziging en coördinatie van het sociaal sectoraal pensioenstelselAanvullend pensioenplan ten gunste van de arbeidersvan het Paritair Subcomité voor het koetswerkSectoraal pensioenreglement afgesloten in uitvoering van artikel 6van de collectieve arbeidsovereenkomst van 30 mei 2024HOOFDSTUK I. - VoorwerpArtikel 1.  § 1. Dit sectoraal pensioenreglement wordt opgemaakt in uitvoering van artikel 6 van de collectieve arbeidsovereenkomst van 30 mei 2024 tot wijziging en coördinatie van het sociaal sectoraal pensioenstelsel. § 2. Dit pensioenreglement beoogt het pensioenreglement dat als bijlage opgenomen was bij de collectieve arbeidsovereenkomst van 2 december 2021 aan te passen. § 3. Dit pensioenreglement bepaalt de rechten en de plichten van de Inrichter, de pensioeninstelling, de werkgevers die behoren tot het ressort van het voormelde paritair subcomité, de aangeslotenen en hun begunstigde(n). Tevens worden de aansluitingsvoorwaarden alsook de regels betreffende de uitvoering van de pensioentoezegging erin vastgelegd. De rechten van de aangeslotenen die gewezen werknemers zijn die na hun uittreding nog steeds actuele of uitgestelde rechten genieten, worden in de regel bepaald door het pensioenreglement zoals van toepassing op het ogenblik van hun uittreding, behoudens in geval van andersluidende wettelijke bepalingen. § 4. Dit pensioenreglement is gepubliceerd op de website van SEFOPLUS OFP (www.sefoplus.be) en is daar publiek raadpleegbaar. De aangeslotenen kunnen het pensioenreglement eveneens raadplegen via www.mypension.be. Bovendien zal de tekst van dit pensioenreglement door SEFOPLUS OFP, eventueel via de v.z.w. SEFOCAM ter beschikking worden gesteld aan de aangeslotene op diens eenvoudig verzoek.HOOFDSTUK II. - BegripsomschrijvingenArt. 2. 1. Het aanvullend pensioenDe kapitaalswaarde van het rust- en/of overlevingspensioen bij overlijden van de aangeslotene (vóór of na de pensionering), of de omzetting van deze in een levenslange lijfrente, toegekend op basis van de in dit pensioenreglement bepaalde verplichte stortingen, ter aanvulling van een krachtens een wettelijke socialezekerheidsregeling vastgesteld pensioen. Deze zal niet lager zijn dan de verworven reserves per 31 december 2018, op het moment van overgang van pensioeninstelling.2. De pensioentoezeggingDe toezegging van een aanvullend pensioen gedaan door de Inrichter aan de aangeslotenen en/of hun begunstigde(n) in uitvoering van de collectieve arbeidsovereenkomst van 5 juli 2002, alsook van de collectieve arbeidsovereenkomsten tot wijziging en coördinatie van het sociaal sectoraal pensioenstelsel.De toezegging die de Inrichter hier doet betreft een pensioentoezegging van het type vaste bijdragen zonder gewaarborgd rendement. De Inrichter garandeert dus enkel de betaling van de vaste bijdrage maar doet geen enkele belofte op het gebied van de kapitalisatie van de bijdragen. De Inrichter zal weliswaar voldoen aan de verplichtingen inzake de minimum rendementsgarantie conform de bepalingen van artikel 24 van de W.A.P.SEFOPLUS OFP gaat op haar beurt, als pensioeninstelling, een middelenverbintenis aan. Dit houdt in dat SEFOPLUS OFP er zich toe verbindt om de vaste bijdragen die door de Inrichter worden gestort zo goed en zo zorgvuldig mogelijk te beheren (als een goede huisvader) met het oog op de verwezenlijking van haar doel, zonder dat zij zich verbindt tot een resultaat. De bijdragen gestort door de Inrichter zullen worden gekapitaliseerd aan het netto financieel rendement zoals gedefinieerd in artikel 2.4 van dit pensioenreglement.3. Het pensioenstelselEen collectieve pensioentoezegging.4. Het netto financieel rendement (NFR)Het netto financieel rendement (afgekort als "NFR") van het Afzonderlijk Vermogen Pensioen PSC 149.02 wordt voor het afgelopen boekjaar berekend per 31 december van het boekjaar. Hiertoe worden de investeringskosten in mindering gebracht van het financieel rendement van het Afzonderlijk Vermogen Pensioen PSC 149.02.Vervolgens wordt voor de vaststelling van het netto financieel rendement dat wordt ingeschreven op de individuele rekeningen van de aangeslotenen rekening gehouden met de beschikbare vrije reserve van het Afzonderlijk Vermogen Pensioen PSC 149.02 die dient als buffer. Deze vrije reserve of buffer is gelijk aan het bedrag van de activa van het Afzonderlijk Vermogen Pensioen PSC 149.02 die volgend bedrag overstijgen :- de reserves ingeschreven op de individuele rekeningen van de aangeslotenen, in overeenstemming met dit pensioenreglement; hierbij wordt voor de berekening van deze reserves voor de periode gelegen tussen 1 januari en 31 december van het berekeningsjaar uitgegaan van een netto financieel rendement dat gelijk is aan de rentevoet van toepassing voor de berekening van de minimum rendementsgarantie conform artikel 24 van de W.A.P.;- desgevallend verhoogd met de minimum rendementsgarantie conform artikel 24 van de W.A.P.Bij de toekenning van het netto financieel rendement geldt als basisprincipe dat de inrichter ernaar streeft, vanuit de doelstelling van een veilig en prudent beheer van het sociaal sectoraal pensioenstelsel, om steeds een buffer te hebben die gelijk is aan 10 pct. teneinde eventuele, toekomstige negatieve schommelingen in de beleggingen te kunnen opvangen. Echter, zelfs indien de buffer lager is dan 10 pct. en er een positief netto financieel rendement is, dan zal dit tot aan de minimum rendementsgarantie conform artikel 24 van de W.A.P. toch worden toegekend, zoals hierna bepaald.Indien deze vrije reserve of buffer van het Afzonderlijk Vermogen Pensioen PSC 149.02 hoger is dan of gelijk aan 10 pct. :- in geval van een positief netto financieel rendement wordt dit volledig netto financieel rendement, evenwel verminderd met het bedrag nodig om ervoor te zorgen dat ook na de toekenning van het netto financieel rendement de vrije reserve of buffer van het Afzonderlijk Vermogen Pensioen PSC 149.02 gelijk is aan 10 pct., ingeschreven op de individuele rekeningen van de aangeslotenen;- in geval van een negatief netto financieel rendement wordt dit volledig netto financieel rendement ingeschreven op de individuele rekeningen aangeslotenen.Indien deze vrije reserve of buffer van het Afzonderlijk Vermogen Pensioen PSC 149.02 lager is dan 10 pct. dan wordt het volledig negatief netto financieel rendement ingeschreven op de individuele rekeningen van de aangeslotenen. Het positief netto financieel rendement dat wordt ingeschreven op de individuele rekeningen van de aangeslotenen wordt dan beperkt tot de rentevoet van toepassing voor de berekening van de minimum rendementsgarantie conform artikel 24 van de W.A.P. (per 14 december 2023 gelijk aan 1,75 pct.). Het overstijgend gedeelte wordt toegekend aan de vrije reserve van het Afzonderlijk Vermogen Pensioen PSC 149.02 ter verhoging van de buffer. Schematisch kan dit als volgt worden voorgesteld :  </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de landbouw;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor de landbouw, tot vaststelling van de sectorale minimumloonschalen voor de bedienden op basis van beroepservaring.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de landbouwCollectieve arbeidsovereenkomst van 17 december 2024Vaststelling van de sectorale minimumloonschalen voor de bedienden op basis van beroepservaring (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191511/CO/144) Betreft de aanpassing van de lonen en de premies aan de indexering met 3,57 pct. vanaf 1 januari 2025.Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de bedienden van de ondernemingen die ressorteren onder het Paritair Comité voor de landbouw. § 2. Onder "bedienden" wordt verstaan : de bedienden zonder onderscheid naar gender.Art. 2.  § 1. De minimummaandlonen per klasse van de voltijds tewerkgestelde bedienden, zoals bepaald in artikel 2 van de collectieve arbeidsovereenkomst van 24 mei 2023 betreffende de beroepsindeling, wordt vastgesteld op basis van het aantal jaren beroepservaring :- volgens schaal I, opgenomen in bijlage 1a van deze collectieve arbeidsovereenkomst vanaf het eerste jaar van de indiensttreding;- volgens schaal II opgenomen in bijlage 1b van deze collectieve arbeidsovereenkomst voor de bedienden die minstens 1 jaar werkzaam zijn in dezelfde onderneming.De bedragen vermeld in de minimumloonschalen I en II opgenomen in bijlagen 1a, 1b, 1c en 1d van deze collectieve arbeidsovereenkomst worden geïndexeerd volgens de modaliteiten voorzien in de collectieve arbeidsovereenkomst van 18 april 2024 betreffende de indexering van de lonen (landbouw zonder vlas), geregistreerd onder het nummer 187715/CO/144.De aanvangslonen die in de minimumloonschaal I voor alle functieklassen worden vastgelegd stemmen overeen met 0 jaar beroepservaring.De overgang van de ene loonschaal naar de andere gebeurt in de maand die volgt op die waarin de bediende aan de toekenningsvoorwaarde voldoet.De toepassing van de loonschalen heeft alleen betrekking op de minimumlonen van de bedienden die ook aan de toekenningsvoorwaarden voldoen; ze kan geen invloed hebben op de lonen van de bedienden die boven deze minima worden betaald. § 2. De deeltijdse bedienden moeten voor een gelijk werk of voor een werk van gelijke waarde, in verhouding, hetzelfde loon ontvangen als een voltijdse bediende.Art. 3.  § 1. Onder "beroepservaring" wordt verstaan : de periode van effectieve en gelijkgestelde beroepsprestaties bij de werkgever waar de bediende in dienst is, evenals de periodes van effectieve en gelijkgestelde beroepsprestaties die de bediende vóór de indiensttreding verworven heeft als werknemer, zelfstandige of als statutair ambtenaar. § 2. Voor de bepaling van de periode van beroepservaring worden deeltijdse prestaties gelijkgesteld met voltijdse prestaties. § 3. De hierna bepaalde periodes van volledige schorsing van de uitvoering van de arbeidsovereenkomst worden met effectieve beroepsprestaties gelijkgesteld :- de periodes van arbeidsongeschiktheid wegens arbeidsongeval of beroepsziekte;- de periodes van arbeidsongeschiktheid wegens ziekte of ongeval, anders dan arbeidsongeval, met een maximum van 3 jaar;- de periodes van voltijds tijdskrediet om thematische redenen, zoals voorzien in artikel 4 van collectieve arbeidsovereenkomst nr. 103 en voor zover RVA-uitkeringen worden toegekend, en thematisch verlof (ouderschapsverlof, bij stand en verzorging van een zwaar ziek gezins- of familielid, palliatieve zorgen), met een maximum van 3 jaar;- de periodes van voltijds tijdskrediet zonder thematische redenen voor zover RVA-uitkeringen worden toegekend, met een maximum van 1 jaar;- de periodes van zwangerschapsverlof;- de periodes van profylactisch verlof;- de periodes van vaderschapsverlof;- de periodes in toepassing van de crisismaatregelen zoals voorzien door de wet van 19 juli 2009;- de overige periodes van volledige schorsing van de arbeidsovereenkomst zoals voorzien in de wet van 3 juli 1978, welke gepaard gaan met behoud van loon.Volgende periodes buiten schorsing van de arbeidsovereenkomst worden gelijkgesteld met effectieve beroepsprestaties :- de periodes van uitkeringsgerechtigde werkloosheid met een maximum van 1 jaar indien de uitkeringsgerechtigde werkzoekende een beroepservaring heeft van minder dan 15 jaar en een maximum van 2 jaar indien de uitkeringsgerechtigde werkloze een beroepservaring heeft van meer dan 15 jaar. § 4. De beroepservaring en anciënniteit vóór 18 jaar, waarvoor het jongerenbarema geldt zoals bepaald in artikel 6, wordt meegeteld bij de start van het ervaringsbarema zoals bepaald in artikel 2.Commentaar :Voor de aanrekening van de beroepservaring mag geen enkele gelijkstellingsperiode gecumuleerd worden met een periode van beroepsactiviteit of met een andere gelijkstellingsperiode.Art. 4. Bedienden die op 31 december 2022 in dienst waren van een werkgever die ressorteerde onder Aanvullend Paritair Comité voor de bedienden en op 1 januari 2023 in dienst zijn bij een werkgever die ressorteert onder Paritair Comité voor de landbouw nemen hun aantal jaren beroepservaring die ze hadden in Aanvullend Paritair Comité voor de bedienden mee.Art. 5.  § 1. Op het ogenblik van de indiensttreding wordt het baremaloon van de bediende vastgesteld in overeenstemming met het beroepservaringsbarema van de klasse waartoe zijn functie behoort en op basis van de beroepservaring zoals bepaald in artikels 2, 3 en 4 hiervoor.De som van de beroepservaringsperioden en gelijkgesteldeperioden wordt uitgedrukt in jaren en maanden.De eerste baremieke verhoging na de indiensttreding zal gebeuren op de eerste dag van de maand nadat de bediende het eerstvolgende jaar beroepservaring heeft bereikt. § 2. Wanneer de periode van beroepservaring met 12 maanden is toegenomen sinds de laatste baremieke verhoging, stijgt het baremaloon van de bediende met een beroepservaringsjaar volgens de loonbaremaschaal op de eerste dag van de daaropvolgende maand. § 3. Bij een nieuwe aanwerving zal de kandidaat aan de werkgever alle noodzakelijke informatie overmaken zodat deze het loon kan bepalen dat overeenkomt met de bepalingen van deze collectieve arbeidsovereenkomst.Art. 6.  § 1. Teneinde de inschakeling van jongeren in het arbeidsproces te bevorderen, wordt een specifiek jongerenbarema voorzien voor de volgende bedienden :- 80 pct. van het loon aan 0 jaar ervaring voor de jongere bedienden van 17 jaar;- 75 pct. van het loon aan 0 jaar ervaring voor de jongere bedienden van 16 jaar. § 2. Voor bedienden met een studentenovereenkomst zoals bepaald in titel VII van de wet van 3 juli 1978 betreffende de arbeidsovereenkomsten wordt het volgende barema voorzien 1:   </t>
         </is>
       </c>
     </row>
@@ -1794,29 +1793,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2025200285</t>
+          <t>2025002982</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>16 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 17 oktober 2024, gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, tot wijziging van de collectieve arbeidsovereenkomst van 25 september 2002 betreffende de eindejaarstoelage (geregistreerd onder nummer : 64174/CO/305, algemeen verbindend verklaard door koninklijk besluit van 23 oktober 2002, Belgisch Staatsblad van 5 november 2002) (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 19 december 2024, gesloten in het Paritair Subcomité voor het wegvervoer en de logistiek voor rekening van derden, betreffende de toepassing van de koppeling van de lonen en vergoedingen aan de index op 1 januari 2025 (1)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-16&amp;numac_search=2025200285&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200285=42&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025002982&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025002982=42&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de gezondheidsinrichtingen en -diensten; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 17 oktober 2024, gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, tot wijziging van de collectieve arbeidsovereenkomst van 25 september 2002 betreffende de eindejaarstoelage (geregistreerd onder nummer : 64174/CO/305, algemeen verbindend verklaard door koninklijk besluit van 23 oktober 2002, Belgisch Staatsblad van 5 november 2002). Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de gezondheidsinrichtingen en -diensten Collectieve arbeidsovereenkomst van 17 oktober 2024 Wijziging van de collectieve arbeidsovereenkomst van 25 september 2002 betreffende de eindejaarstoelage (geregistreerd onder nummer : 64174/CO/305, algemeen verbindend verklaard door koninklijk besluit van 23 oktober 2002, Belgisch Staatsblad van 5 november 2002) (Overeenkomst geregistreerd op 22 november 2024 onder het nummer 190701/CO/330) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op werkgevers en werknemers : - van psychiatrische verzorgingstehuizen; - van samenwerkingsverbanden voor de oprichting en het beheer van initiatieven van beschut wonen; - van rusthuizen; - van rust- en verzorgingstehuizen; - van serviceflats en dienstencentra die zorg verlenen aan ouderen; - van revalidatiecentra. Onder "werknemers" wordt verstaan : elke persoon, ongeacht het geslacht, die in dienst is op basis van een arbeidsovereenkomst in de zin van de wet van 3 juli 1978. Art. 2. Deze collectieve arbeidsovereenkomst wordt gesloten in het kader van de collectieve arbeidsovereenkomst van 17 oktober 2024 ter bevordering van de fietsmobiliteit en wijzigt de collectieve arbeidsovereenkomst van 25 september 2002 betreffende de eindejaarstoelage (geregistreerd onder nummer 64174/CO/305, algemeen verbindend verklaard door koninklijk besluit van 23 oktober 2002, Belgisch Staatsblad van 5 november 2002), overgenomen door het Paritair Comité voor de gezondheidsinrichtingen en -diensten bij bijzondere collectieve arbeidsovereenkomst van 10 september 2007 (registratienummer 85666/CO/330, algemeen verbindend verklaard bij koninklijk besluit van 30 juli 2008, Belgisch Staatsblad van 3 september 2008). Art. 3. In de collectieve arbeidsovereenkomst van 25 september 2002, zoals gewijzigd door de collectieve arbeidsovereenkomst van 12 februari 2007, wordt het volgende lid 2 toegevoegd aan artikel 6 : "De eindejaarstoelage kan worden omgezet in één enkel alternatief voordeel, zoals vastgelegd in artikel 6. Enkel een omzetting van de bruto-eindejaarspremie met inbegrip van de patronale RSZ-bijdrage tot invoering op bedrijfsvlak van een fietsleasing is mogelijk conform de bepalingen van de collectieve arbeidsovereenkomst van 17 oktober 2024 ter ondersteuning van de fietsmobiliteit waarin ook de modaliteiten met betrekking tot de invoering van een fietsleasing zijn opgenomen.".Art. 4. In dezelfde collectieve arbeidsovereenkomst van 25 september 2002, zoals gewijzigd door de collectieve arbeidsovereenkomst van 12 februari 2007, wordt het volgende lid 3 toegevoegd aan artikel 6 : "Het deel van het jaarlijks bedrag van de eindejaarstoelage dat maximaal mag worden gebruikt als alternatief voordeel voor het leasen van een fiets, wordt geplafonneerd. Dit grensbedrag/plafond wordt vastgelegd op het bedrag dat vereist is voor de totale kost voor de fietsleasing van maximum 12 000 EUR voor de leaseperiode van 3 jaar. Dit bedrag van 12 000 EUR wordt geproratiseerd in geval van een kortere duurtijd en wordt geïndexeerd door toepassing van een percentage dat afhangt van de evolutie van het indexcijfer van de consumptieprijzen. Dit percentage wordt bekomen door het indexcijfer dat van kracht is in oktober van het betrokken kalenderjaar van uitbetaling te delen door het indexcijfer dat van kracht was in oktober van het voorgaande kalenderjaar. Het percentage wordt berekend tot op vier decimalen en afgerond volgens de wiskundige regels.". Art. 5. Artikel 8 van dezelfde collectieve arbeidsovereenkomst van 25 september 2002 wordt aangevuld met een tweede alinea, als volgt geformuleerd : "Alternatieve regelingen via de omzetting van een geheel of een gedeelte van de bruto-eindejaarstoelage kunnen worden overeengekomen bij sectorale collectieve arbeidsovereenkomst ter ondersteuning van de fietsmobiliteit.". Art. 6. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang vanaf 1 januari 2024. Zij is gesloten voor onbepaalde tijd en kan worden opgezegd door elk van de partijen, mits een opzeggingstermijn van zes maanden, bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Comité voor de gezondheidsinrichtingen en -diensten die alle ondertekenende organisaties hiervan in kennis stelt. De opzeggingstermijn begint te lopen vanaf de eerste dag van de maand die volgt op de datum waarop de voorzitter van het Paritair Comité voor de gezondheidsinrichtingen en -diensten de betrokken organisaties in kennis heeft gesteld van de opzegging. Art. 7. Overeenkomstig artikel 14 van de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, worden voor wat betreft de ondertekening van deze collectieve arbeidsovereenkomst, de handtekeningen van de personen die deze aangaan namens de werknemersorganisaties enerzijds, en namens de werkgeversorganisaties anderzijds, vervangen door de voorzitter en de secretaris ondertekende en door de leden goedgekeurde notulen van de vergadering. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Subcomité voor het wegvervoer en de logistiek voor rekening van derden;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 19 december 2024, gesloten in het Paritair Subcomité voor het wegvervoer en de logistiek voor rekening van derden, betreffende de toepassing van de koppeling van de lonen en vergoedingen aan de index op 1 januari 2025.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Subcomité voor het wegvervoeren de logistiek voor rekening van derdenCollectieve arbeidsovereenkomst van 19 december 2024Toepassing van de koppeling van de lonen en vergoedingen aan de index op 1 januari 2025 (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191533/CO/140.03)HOOFDSTUK I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en hun werknemers die vallen onder het ressort van het Paritair Subcomité 140.03 voor het wegvervoer en de logistiek voor rekening van derden.Met "werknemers" wordt bedoeld : de arbeiders en arbeidsters, aangegeven in de RSZ-categorie 083.HOOFDSTUK II. - Juridisch kaderArt. 2. Deze collectieve arbeidsovereenkomst wordt gesloten in uitvoering van de collectieve arbeidsovereenkomst van 19 oktober 2017 betreffende het indexmechanisme en de koppeling van de lonen en vergoedingen aan de index in het Paritair Subcomité voor het wegvervoer en de logistiek voor rekening van derden.HOOFDSTUK III. - Koppeling van de lonen en vergoedingen aan de index voor zowel het rijdend personeel als het niet-rijdend personeel, met inbegrip van het garagepersoneel, mailhousing en studentenArt. 3. In uitvoering van de in artikel 2 vernoemde collectieve arbeidsovereenkomst worden de bedragen van de in die collectieve arbeidsovereenkomst opgesomde lonen en vergoedingen vanaf 1 januari 2025 vastgelegd zoals opgenomen in bijlage bij onderhavige collectieve arbeidsovereenkomst.HOOFDSTUK IV. - GeldigheidsduurArt. 4.  § 1. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025. § 2. Zij is gesloten voor onbepaalde tijd. § 3. Zij kan door elk van de contracterende partijen worden opgezegd. Deze opzegging moet minstens drie maanden op voorhand geschieden bij een ter post aangetekende brief, gericht aan de voorzitter van het Paritair Subcomité voor het wegvervoer en de logistiek voor rekening van derden, die zonder verwijl de betrokken partijen in kennis zal stellen. De termijn van drie maanden begint te lopen vanaf de datum van verzending van bovengenoemde aangetekende brief.Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025.De Minister van Werk,D. CLARINVALBijlage aan de collectieve arbeidsovereenkomst van 19 december 2024, gesloten in het Paritair Subcomité voor het wegvervoer en de logistiek voor rekening van derden, betreffende de toepassing van de koppeling van de lonen en vergoedingen aan de index op 1 januari 2025.Actueel loonoverzicht van toepassing op 1 januari 2025 PSC 140.031. Rijdend personeel1.1.Rijdend personeel lonen   </t>
         </is>
       </c>
     </row>
@@ -1826,28 +1824,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2025000889</t>
+          <t>2025201254</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>16 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 17 oktober 2024, gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, betreffende de ondersteuning van de fietsmobiliteit (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 15 januari 2025, gesloten in het Paritair Comité voor de handel in voedingswaren, betreffende de lonen (slagers) (verhoging met 0,4 pct. vanaf 1 januari 2022) (1)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-16&amp;numac_search=2025000889&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025000889=43&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025201254&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201254=43&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de gezondheidsinrichtingen en -diensten;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 17 oktober 2024, gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, betreffende de ondersteuning van de fietsmobiliteit.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de gezondheidsinrichtingen en -dienstenCollectieve arbeidsovereenkomst van 17 oktober 2024Ondersteuning van de fietsmobiliteit (Overeenkomst geregistreerd op 22 november 2024 onder het nummer 190702/CO/330)HOOFDSTUK I. - DoelArtikel 1. Deze collectieve arbeidsovereenkomst heeft als doel uitvoering te geven aan de bepalingen van de collectieve arbeidsovereenkomsten met betrekking tot de eindejaarspremie en, waar deze nog bestaat de attractiviteitspremie, die een volledige of gedeeltelijke omzetting van de eindejaarspremie en in voorkomend geval de attractiviteitspremie, mogelijk maken voor de financiering van de fietsleasing, volgens de hieronder vastgestelde modaliteiten.Voor de toepassing van huidige collectieve arbeidsovereenkomst, moet men onder "eindejaarspremie" verstaan : het bedrag van de premies zoals gedefinieerd in de opgesomde collectieve arbeidsovereenkomsten voor de verschillende betrokken sectoren, (verhoogd met de attractiviteitspremie voor de sectoren waar deze nog bestaat) zoals opgenomen in bijlage 1 van onderhavige collectieve arbeidsovereenkomst.HOOFDSTUK II. - ToepassingsgebiedArt. 2.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de werknemers die ressorteren onder het Paritair Comité voor de gezondheidsinrichtingen en -diensten en die behoren tot :- de inrichtingen die aan de wet op de ziekenhuizen onderworpen zijn;- de forensisch-psychiatrische centra;- de revalidatiecentra waarvoor het Comité van de verzekering van het RIZIV, op voorstel van het College van geneesheren-directeurs, in toepassing van artikel 22, 6°  van de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, een overeenkomst heeft gesloten en die niet vallen onder de toepassing van artikel 5, § 1, I, 5°  van de bijzondere wet van 8 augustus 1980 tot hervorming der instellingen;- de thuisverpleging;- de diensten voor het bloed van het Rode Kruis van België;- de medisch-pediatrische centra;- de wijkgezondheidscentra;- de categorale ziekenhuizen (dit is elk ziekenhuis dat uitsluitend beschikt over een G-dienst (revalidatie van geriatrische patiënten) en/of een Sp-dienst (gespecialiseerde dienst voor behandeling en revalidatie) als vermeld in artikel 5, § 1, I, eerste lid, 3°  en 4°  van de bijzondere wet van 8 augustus 1980 tot hervorming der instellingen);- de rusthuizen voor bejaarden, de rust- en verzorgingstehuizen, de dagverzorgingscentra, de assistentiewoningen, de centra voor kortverblijf voor bejaarden;- de psychiatrische verzorgingstehuizen;- de initiatieven van beschut wonen;- de revalidatiecentra, met uitsluiting van de instellingen waarmee het Verzekeringscomité van het RIZIV op voorstel van het College van geneesheren-directeurs, in uitvoering van artikel 22, 6°  van de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen gecoördineerd op 14 juli 1994, een overeenkomst heeft gesloten en die niet vallen onder de toepassing van artikel 5, § 1, I, 5°  van de bijzondere wet van 8 augustus 1980 tot hervorming van de instellingen;- de multidisciplinaire begeleidingsequipes en netwerken palliatieve zorgen;- aan de sociale diensten, diensten voor geestelijke gezondheidszorg, diensten voor hulp aan rechtzoekenden en andere ambulante diensten - met uitzondering van de wijkgezondheidscentra - die erkend en gesubsidieerd worden door de Gemeenschappelijke Gemeenschapscommissie. § 2. Onder "werknemers" wordt verstaan : elke persoon, ongeacht geslacht, tewerkgesteld op basis van een arbeidsovereenkomst in de zin van de wet van 3 juli 1978. § 3. In overeenstemming met de collectieve arbeidsovereenkomst van 13 december 2021 betreffende de eindejaarspremie, zijn voor de daarin vermelde federale sectoren, de artsen uitgesloten van het toepassingsgebied, met uitzondering van de loontrekkende artsen van de wijkgezondheidscentra.HOOFDSTUK III. - FietsmobiliteitArt. 3. Algemene principes § 1. Het theoretische budget dat aan fietsleasing kan worden toegewezen, bestaat uit de gehele of gedeeltelijke omzetting van de bruto eindejaarspremie zoals bepaald in de sectorale collectieve arbeidsovereenkomsten die van toepassing zijn op de werknemer.Dit theoretisch budget kan door de werknemer gebruikt worden om een leasingproject aan te gaan, binnen het grensbedrag zoals vastgelegd in de collectieve arbeidsovereenkomsten eindejaarspremie opgenomen in bijlage 1. § 2. De omzetting van een deel of het geheel van de bruto eindejaarspremie in het alternatieve voordeel van een fietslease mag geen kostenbesparing inhouden. § 3. Het artikel 3, § 4, tweede alinea van de collectieve arbeidsovereenkomst van 29 juni 2009 met betrekking tot woon-werkverkeer is niet van toepassing op de fietsleasing in uitvoering van onderhavige collectieve arbeidsovereenkomst. Als gevolg is voor fietsleasing waarbij gebruikt gemaakt wordt van de omzetting van (een deel van) de eindejaarspremie, de fietsvergoeding wel verschuldigd.HOOFDSTUK IV. - ToepassingsmodaliteitenArt. 4. Modaliteiten inzake omzetting van de eindejaarspremie op organisatieniveau § 1. Op organisatieniveau kan via het sluiten van een collectieve arbeidsovereenkomst, de eindejaarspremie omgezet worden in een fietslease, na besprekingen binnen het lokale sociaal overleg in overeenstemming met de artikelen 5 en 6 van deze collectieve arbeidsovereenkomst. § 2. Een model van een lokale collectieve arbeidsovereenkomst in overeenstemming met deze collectieve arbeidsovereenkomst is te vinden in de bijlage van deze collectieve arbeidsovereenkomst (bijlage 2). Dit model is optioneel en kan lokaal worden aangepast.Art. 5. Alternatief collectief aanbodVoorafgaandelijk aan het afsluiten van een fietsleaseplan dienen alternatieven besproken te worden in het lokaal sociaal overleg (OR/CPBW/SD) waar dit aanwezig is. Het betreft onder meer :- het faciliteren door de werkgever van een groepsaankoop fietsen;- aankoop door werkgever van fietsen;- fietsverhuur door de werkgever;- fietslening.Het alternatief collectief aanbod wordt voorgelegd en besproken in het lokaal sociaal overleg.Art. 6. Fietsleasepolicy § 1. Inhoud van de fietsleasepolicyIn het lokaal sociaal overleg (OR/CPBW/SD) van de onderneming moet met oog op het afsluiten van een collectieve arbeidsovereenkomst op voorzieningsniveau een fietsleasepolicy overlegd en overeengekomen worden. De fietsleasepolicy moet minstens bepalingen bevatten over volgende onderwerpen :a) Verplichte bepalingen :- Gebruik van de leasefiets;- Toepassingsgebied : de betrokken werknemers;- Partijen bij de fietslease;- Voorwaarden en modaliteiten van het aanbod;- Gevolgen van de terbeschikkingstelling van een leasefiets zoals omschreven in artikel 7 van deze collectieve arbeidsovereenkomst;- Keuze type leasefiets (elektrisch/speedpedelec/andere) en bestelprocedure;- Jaarlijks onderhoud;- Verzekeringen (onder andere diefstal, schade en fietsbijstandsverzekering);- Looptijd en einde van het leasecontract;- In geval van overname : het exacte percentage van de aankoopprijs dat de overnameprijs bepaalt aan het einde van het leasingcontract;- Vroegtijdige beëindiging van het leasecontract (bij einde arbeidsovereenkomst, overlijden werknemer, diefstal of verlies van de fiets,...);- Inleveren van de fiets;- Voorbeeldberekeningen.b) Facultatieve bepalingen :- Maximum bedrag aankoopwaarde fiets;- Instapperiode (bijvoorbeeld gans jaar mogelijk of slechts X aantal maanden);- Eventuele accessoire op kost van de werkgever (bijvoorbeeld fluo hesje,...). § 2. Modaliteiten voor organisaties die reeds een fietspolicy hebbenIndien de organisatie reeds beschikt over afspraken met betrekking tot een fietsbeleid/fietspolicy kan de fietsleasepolicy hierin geïntegreerd worden in overleg met het lokaal sociaal overleg.Art. 7. Informatieverplichting aan de werknemerVoorafgaand aan de beslissing van de werknemer om in te stappen in de fietslease, moet de werkgever volgende informatie verstrekken aan de werknemer :- berekeningen met betrekking tot de loonomzetting en de kostprijs van de fietslease, bijvoorbeeld jaarlijkse kost van de fietsleasing en de financiële impact op de eindejaarspremie;- informatie over de eventuele gevolgen van de omzetting van de eindejaarspremie op andere loonelementen;- gevolgen van de keuze van een fietslease bij schorsing van de arbeidsovereenkomst;- informatie met betrekking tot de vroegtijdige beëindiging van het leasecontract bij het einde van de arbeidsovereenkomst;- in geval van overname : het exacte percentage van de aankoopprijs dat de overnameprijs bepaalt aan het einde van het leasingcontract;- een fietsleasepolicy waarin alle rechten en verplichtingen van de werknemer worden opgenomen.Art. 8. Bijlage aan de arbeidsovereenkomst voor de werknemer die kiest voor fietsleasing § 1. Om een loonomzetting van de eindejaarspremie mogelijk te maken zal de werknemer een bijlage aan zijn arbeidsovereenkomst ontvangen waarin de modaliteiten van de loonomzetting worden voorzien. § 2. De fietsleasepolicy wordt eveneens ter beschikking gesteld van de werknemer die instapt in het stelsel van fietsleasing. § 3. De fietslease gebeurt op vrijwillige basis. Het personeelslid dat ervoor kiest om de eindejaarspremie volledig of gedeeltelijk om te zetten in een theoretisch budget voor de financiering van een leasefiets, doet voor de periode waarop de fietsleasing betrekking heeft definitief afstand van het recht op de gehele of het desbetreffende gedeelte van de eindejaarspremie.HOOFDSTUK V. - SlotbepalingenArt. 9. OvergangsbepalingFietsleasingregelingen die op het moment van de inwerkingtreding van onderhavige sectorale collectieve arbeidsovereenkomst in de organisatie toepassing vinden, die niet in overeenstemming zijn met de bepalingen van onderhavige collectieve arbeidsovereenkomst, kunnen voorlopig ongewijzigd toepassing blijven vinden tot aan de beëindiging van het lopende contract. Na de inwerkingtreding van onderhavige sectorale collectieve arbeidsovereenkomst engageren de sociale partners in het lokaal sociaal overleg zich ertoe te onderzoeken op welke manier dit alternatief beleid in overeenstemming gebracht kan worden met de bepalingen van onderhavige collectieve arbeidsovereenkomst.Art. 10. DuurtijdDeze collectieve arbeidsovereenkomst heeft uitwerking met ingang vanaf 25 september 2024. Zij is gesloten voor onbepaalde tijd en kan worden opgezegd door elk van de partijen, mits een opzeggingstermijn van zes maanden, bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Comité voor de gezondheidsinrichtingen en -diensten die alle ondertekenende organisaties hiervan in kennis stelt. De opzeggingstermijn begint te lopen vanaf de eerste dag van de maand die volgt op de datum waarop de voorzitter van het Paritair Comité voor de gezondheidsinrichtingen en -diensten de betrokken organisaties in kennis heeft gesteld van de opzegging.Art. 11. Overeenkomstig artikel 14 van de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, worden voor wat betreft de ondertekening van deze collectieve arbeidsovereenkomst, de handtekeningen van de personen die deze aangaan namens de werknemersorganisaties enerzijds, en namens de werkgeversorganisaties anderzijds, vervangen door de, door de voorzitter en de secretaris ondertekende en door de leden goedgekeurde notulen van de vergadering.Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025.De Minister van Werk,D. CLARINVALBijlage 1 aan de collectieve arbeidsovereenkomst van 17 oktober 2024, gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, betreffende de ondersteuning van de fietsmobiliteitLijst van sectorale collectieve arbeidsovereenkomsten (PC 330) met betrekking tot de eindejaarspremie met inbegrip van de wijzigingen aan deze collectieve arbeidsovereenkomsten.Federale sectoren :- Collectieve arbeidsovereenkomst van 13 december 2021 betreffende de eindejaarspremie, gewijzigd door de collectieve arbeidsovereenkomst van 13 juni 2022 betreffende het forfaitair deel van de eindejaarspremie, zoals gewijzigd door de collectieve arbeidsovereenkomst van 17 oktober 2024.Vlaamse sectoren :- Collectieve arbeidsovereenkomst van 12 november 2018 betreffende de eindejaarspremie, zoals gewijzigd door de collectieve arbeidsovereenkomst van 17 oktober 2024.Waalse sectoren :- Collectieve arbeidsovereenkomst van 25 september 2002 betreffende de toekenning van een eindejaarspremie (algemeen verbindend verklaard bij koninklijk besluit van 23 oktober 2002), zoals gewijzigd door de collectieve arbeidsovereenkomst van 17 oktober 2024;- Collectieve arbeidsovereenkomst van 30 juni 2006 betreffende de toekenning van een attractiviteitspremie (algemeen verbindend verklaard bij koninklijk besluit van 1 oktober 2008), zoals gewijzigd door de collectieve arbeidsovereenkomst van 17 oktober 2024;- Collectieve arbeidsovereenkomst van 14 september 2020 betreffende de betaling van een eindejaarspremie aan het personeel van de diensten die ressorteren onder het Paritair Comité voor de gezondheidsinrichtingen en -diensten, erkend en/of gesubsidieerd door het Waalse Gewest tot uitvoering van de tripartiete raamovereenkomst voor de Waalse non-profitsector 2018-2020, zoals gewijzigd door de collectieve arbeidsovereenkomst van 17 oktober 2024.Brusselse sectoren :- Collectieve arbeidsovereenkomst van 12 december 2022, ter vervanging van de collectieve arbeidsovereenkomst van 9 december 2019 tot toekenning van de eindejaarspremie voor de geregionaliseerde sectoren in Brussel, zoals gewijzigd door de collectieve arbeidsovereenkomst van 17 oktober 2024;- Collectieve arbeidsovereenkomst van 30 juni 2006 betreffende de toekenning van een attractiviteitspremie, zoals gewijzigd door de collectieve arbeidsovereenkomst van 17 oktober 2024;- Collectieve arbeidsovereenkomst van 12 december 2022 betreffende de eindejaarstoelage voor de ambulante sectoren van Brussel, zoals gewijzigd door de collectieve arbeidsovereenkomst van 17 oktober 2024.Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025.De Minister van Werk,D. CLARINVALBijlage 2 aan de collectieve arbeidsovereenkomst van 17 oktober 2024, gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, betreffende de ondersteuning van de fietsmobiliteitModel van ondernemings-collectieve arbeidsovereenkomst voor toetreding tot het systeem van fietsleaseCollectieve arbeidsovereenkomst van ................ (datum) tot uitwerking van een stelsel van fietsleaseDeze overeenkomst wordt gesloten op ondernemingsniveau, tussen :Enerzijds de werkgever ........................., met zetel te ....................., KBO-nummer ..............., vertegenwoordigd door .............., in de hoedanigheid van ..................., e-mail ...........................Anderzijds de werknemersorganisatie(s)Benaming ......................., adres ........................, vertegenwoordigd door ........................., in de hoedanigheid van .........................., e-mail ..............................Benaming ......................., adres ........................, vertegenwoordigd door ........................., in de hoedanigheid van .........................., e-mail ..............................Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op (de werkgever) ............ en op de door haar tewerkgestelde werknemers (of : de volgende groep(en) van werknemers, met name ............ (omschrijving betrokken groep(en) werknemers)).Art. 2. De ondertekenende partijen komen overeen dat een werknemer, behorende tot het toepassingsgebied van deze collectieve arbeidsovereenkomst, de eindejaarspremie kan omzetten in een fietslease, in overeenstemming met de modaliteiten zoals bepaald in de collectieve arbeidsovereenkomst van 17 oktober 2024 tot wijziging van de collectieve arbeidsovereenkomst van xx/xx/xxxx (toepasselijke collectieve arbeidsovereenkomst van betrokken sector invoegen) betreffende de eindejaarspremie(1).Art. 3. De modaliteiten van de fietslease zijn uitgewerkt in overeenstemming met de bepalingen van de sectorale collectieve arbeidsovereenkomst van 17 oktober 2024 ter ondersteuning van de fietsmobiliteit.Art. 4. De fietsleasepolicy zoals overeengekomen in de onderneming is als bijlage toegevoegd bij de onderhavige collectieve arbeidsovereenkomst.Art. 5. Voorafgaand aan de beslissing van de werknemer om in te stappen in de fietslease, moet de werkgever de informatie verstrekken aan de werknemer, zoals omschreven in artikel 7 van sectorale collectieve arbeidsovereenkomst van 17 oktober 2024 ter ondersteuning van de fietsmobiliteit.Art. 6. Deze collectieve arbeidsovereenkomst treedt in werking op ..........Zij is gesloten voor onbepaalde duur.Zij kan worden opgezegd door elk der partijen, mits een opzeggingstermijn van drie maanden, gericht bij een ter post aangetekende brief aan elke andere ondertekenende partijen.Aldus opgemaakt en ondertekend te ...............op ............in ................ exemplaren, waarvan één ter registratie door de werkgever wordt bezorgd aan de Griffie van de Algemene Directie Collectieve Arbeidsbetrekkingen van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg.   </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de handel in voedingswaren; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 15 januari 2025, gesloten in het Paritair Comité voor de handel in voedingswaren, betreffende de lonen (slagers) (verhoging met 0,4 pct. vanaf 1 januari 2022). Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 11 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de handel in voedingswaren Collectieve arbeidsovereenkomst van 15 januari 2025 Lonen (slagers) (verhoging met 0,4 pct. vanaf 1 januari 2022) (Overeenkomst geregistreerd op 31 januari 2025 onder het nummer 191693/CO/119) HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing : 1) op de arbeiders die technische slagerij-, spekslagerij en penserijfuncties uitoefenen in de ondernemingen die onder het Paritair Comité voor de handel in voedingswaren ressorteren met uitzondering van de leerlingen wier leerovereenkomst door het Ministerie van Middenstand gehomologeerd is; 2) op de werkgevers die de in 1) bedoelde arbeiders tewerkstellen. Zij is niet van toepassing op de andere arbeiders van deze ondernemingen voor wie de algemene loonsovereenkomsten van dit paritair comité blijven gelden.  § 2. Met "arbeiders" worden de mannelijke en de vrouwelijke arbeiders bedoeld. HOOFDSTUK II. - Loonschalen I Art. 2.  § 1. In ondernemingen waar de ecocheques, toe te kennen op grond van de collectieve arbeidsovereenkomst van 28 mei 2009 betreffende de ecocheques, werden omgezet in een ander voordeel en in ondernemingen waar de ecocheques, op grond van de collectieve arbeidsovereenkomst van 6 oktober 2011 betreffende de omzetting van de ecocheques, werden omgezet in een ander voordeel of in een verhoging van de maaltijdcheque met 1,08 EUR, blijven de gemaakte afspraken onverkort gelden.  § 2. Voor een arbeidstijdregeling van 38 uur per week zijn deze ondernemingen gehouden de lagere loonschalen te betalen : loonschalen I (ecocheques omgezet in een ander voordeel).De werknemers- en werkgeversorganisaties verbinden er zich toe om deze afspraken niet opnieuw in vraag te stellen. HOOFDSTUK III. - Loonschalen II Art. 3. Voor een arbeidstijdregeling van 38 uur per week zijn de volgende ondernemingen gehouden vanaf 1 januari 2016 de verhoogde loonschalen te betalen : loonschalen II (loonschalen I + 0,0875 EUR/uur) : - De ondernemingen waar de ecocheques, toe te kennen op grond van de collectieve arbeidsovereenkomst van 28 mei 2009 betreffende de ecocheques, niet werden omgezet in een ander voordeel en in ondernemingen waar de ecocheques, op grond van de collectieve arbeidsovereenkomst van 6 oktober 2011 betreffende de omzetting van de ecocheques, niet werden omgezet in een ander voordeel of in een verhoging van de maaltijdcheque met 1,08 EUR; - De ondernemingen opgericht vanaf 1 januari 2016; - De reeds vóór 1 januari 2016 bestaande ondernemingen die pas vanaf 1 januari 2016 voor het eerst arbeiders in dienst genomen hebben. HOOFDSTUK IV. - Evolutie in de loonschalen Art. 4. De minimumuurlonen der arbeiders worden volgens hun leeftijd en hun jaren praktijk in het vak vastgesteld. Worden als "jaren praktijk" beschouwd : a) de jaren dienst in een technische slagerij-, spekslagerij- of penserijfunctie, gerealiseerd in één of meerdere ondernemingen; b) de jaren vakopleiding onder een door het Ministerie van Middenstand gehomologeerde overeenkomst; c) de twee derden van de studiejaren in een dagberoepsschool (of centrum voor deeltijds onderwijs, minimum halftijds, door een getuigschrift bevestigd; d) de helft van de studiejaren in een avond- of zondagberoepsschool, door een getuigschrift bevestigd. HOOFDSTUK V. - Jongerenbarema's Art. 5.  § 1. De arbeiders - uitgezonderd de studenten, leerlingen en stagiaires - die minder dan 21 jaar oud zijn, hebben, afhankelijk van hun leeftijd, recht op een bepaald percentage van de minimumuurlonen van de arbeiders van 21 jaar zoals vastgesteld in de loonschalen I : - 20 jaar : 100 pct.; - 19 jaar : 100 pct.; - 18 jaar : 100 pct.; - 17 jaar : 77,5 pct.; - 16 jaar : 70 pct.; - 15 jaar : 70 pct.  § 2. Ingeval de loonschalen II van toepassing zijn, worden de toepasselijke bedragen van loonschaal I vermeerderd met 0,0875 EUR per uur. Art. 6.  § 1. De studenten, leerlingen en stagiaires die minder dan 21 jaar oud zijn, hebben, afhankelijk van hun leeftijd, recht op een bepaald percentage van de minimumuurlonen van de arbeiders van 21 jaar zoals vastgesteld in de loonschalen I : - 20 jaar : 97,5 pct.; - 19 jaar : 92,5 pct.; - 18 jaar : 85 pct.; - 17 jaar : 77,5 pct.; - 16 jaar : 70 pct.; - 15 jaar : 70 pct.  § 2. Ingeval de loonschalen II van toepassing zijn, worden de toepasselijke bedragen van loonschaal I vermeerderd met 0,0875 EUR per uur. HOOFDSTUK VI. - Koppeling van de lonen aan de gezondheidsindex Art. 7. De minimumuurlonen vastgesteld in artikel 2, § 2 worden gekoppeld aan het indexcijfer van de gezondheidsindex overeenkomstig de collectieve arbeidsovereenkomst van 8 juni 2009 betreffende de indexering van de lonen. HOOFDSTUK VII. - Conventionele verhoging in toepassing van het sectorakkoord 2021-2022 Art. 8.  De minimumbarema's en de werkelijk betaalde lonen zijn vanaf 1 januari 2022 verhoogd met 0,4 pct. Een gelijkwaardig voordeel kan ook op bedrijfsniveau worden toegekend.HOOFDSTUK VIII. - Slotbepalingen Art. 9.  Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst van 27 maart 2019, geregistreerd onder het nummer 151750/CO/119, betreffende de lonen. Art. 10.  Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2022. Zij is gesloten voor onbepaalde tijd. Zij kan door elk van de ondertekenende partijen worden opgezegd mits een opzeggingstermijn van drie maanden gegeven bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Comité voor de handel in voedingswaren. Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025. De Minister van Werk, D. CLARINVAL 
+</t>
         </is>
       </c>
     </row>
@@ -1857,28 +1856,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2025003770</t>
+          <t>2025200929</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>19 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit tot ontslag en benoeming van een regeringscommissaris bij de administratieve dienst met boekhoudkundige autonomie genaamd "Belgisch Commissariaat generaal voor de Internationale Tentoonstellingen"</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor de landbouw, betreffende de vaststelling van loon- en arbeidsvoorwaarden (1)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-19&amp;numac_search=2025003770&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003770=44&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025200929&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200929=44&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 18 april 2017 houdende diverse bepalingen inzake economie, artikel 66;Gelet op het koninklijk besluit van 22 juni 2017 betreffende het financieel beheer van de administratieve dienst met boekhoudkundige autonomie, genaamd: "Belgisch Commissariaat-generaal voor de Internationale Tentoonstellingen", artikel 13;Gelet op het koninklijk besluit van 2 juli 2023 tot benoeming van een regeringscommissaris bij de administratieve dienst met boekhoudkundige autonomie genaamd "Belgisch Commissariaat generaal voor de Internationale TentoonstellingenOp de voordracht van de Vice-Eersteminister en Minister van Economie,Hebben Wij besloten en besluiten Wij :Artikel 1. Eervol ontslag uit haar mandaat als regeringscommissaris bij de administratieve dienst met boekhoudkundige autonomie, genaamd "Belgisch Commissariaat-generaal voor de Internationale Tentoonstellingen", wordt verleend aan mevrouw Isabelle Karlshausen.Art. 2. De heer Quentin Maitrejean wordt benoemd tot regeringscommissaris bij de administratieve dienst met boekhoudkundige autonomie, genaamd "Belgisch Commissariaat-generaal voor de Internationale Tentoonstellingen".Art. 3. Het koninklijk besluit van 2 juli 2023 tot benoeming van een regeringscommissaris bij de administratieve dienst met boekhoudkundige autonomie genaamd "Belgisch Commissariaat generaal voor de Internationale Tentoonstellingen" est abrogé. Art. 4. Dit besluit treedt in werking de dag waarop het in het Belgisch Staatsblad wordt bekendgemaakt.Art. 5. De minister bevoegd voor Economie is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Economie,D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de landbouw; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor de landbouw, betreffende de vaststelling van loon- en arbeidsvoorwaarden. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 11 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de landbouw Collectieve arbeidsovereenkomst van 17 december 2024 Vaststelling van loon- en arbeidsvoorwaarden (Overeenkomst geregistreerd op 7 januari 2025 onder het nummer 191333/CO/144) Preambule Betreft de aanpassing van de lonen en de premies aan de indexering met 3,57 pct. vanaf 1 januari 2025. HOOFDSTUK I. - Toepassingsgebied Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de door hen tewerkgestelde werknemers, die ressorteren onder het Paritair Comité voor de landbouw, met uitzondering van : - de werknemers die tewerkgesteld worden in de sector en die bedoeld worden in artikel 8bis van het koninklijk besluit van 28 november 1969, Belgisch Staatsblad van 5 december 1969, inzake sociale zekerheid van de arbeiders; - de werkgevers die als hoofdactiviteit de vlasteelt, de hennepteelt, de eerste verwerking van vlas en/of hennep hebben, en de door hen tewerkgestelde werknemers. Onder "eerste verwerking" wordt verstaan : het scheiden van de verschillende onderdelen van de plant; - de bedienden.  § 2. Met de term "werknemers" worden : de arbeiders bedoeld zonder onderscheid naar gender.HOOFDSTUK II. - Beroepenclassificatie Art. 2. De werknemers worden ingedeeld in 4 categorieën : 1. Meergeschoolden De werknemers die enerzijds al de taken kunnen verrichten van een geschoolde en die, anderzijds, belast zijn met het nemen van beslissingen in verband met het geheel van het bedrijf en verantwoordelijk zijn voor de uitvoering ervan zoals : - het bepalen van de datum en de methode van het bewerken van de grond; - de bemesting van de grond; - het zaaien en het planten; - de oogst; - de phytosanitaire werkzaamheden; - verzorging en voeding van de veestapel; - de fokkerij; - het teeltplan. Deze werknemers hebben hetzij een scholing van A2-niveau doorgemaakt, aangevuld met een cursus bedrijfsleiding in het naschoolse onderwijs of een ervaring als bedrijfsleider, hetzij een voldoende lange ervaring als bedrijfsleider. 2. Geschoolden De werknemers die het geheel van de landbouwwerkzaamheden die hen worden opgedragen en die verband houden met alle activiteiten van het bedrijf of van een bedrijfstak zelfstandig en volledig kunnen verrichten, die alle machines en werktuigen die zij nodig hebben om deze werkzaamheden te verrichten kunnen bedienen, afstellen en onderhouden. Deze kwalificatie kan worden bereikt hetzij door scholing of bijscholing, hetzij door beroepservaring of door beide samen. 3. Geoefenden De werknemers die reeds drie jaar ervaring hebben in dezelfde activiteit of onderneming en die minstens de helft van de taken van een geschoolde kunnen uitvoeren. 4. Ongeschoolden De overige permanente werknemers. HOOFDSTUK III. - Loonvoorwaarden A. Minimum uurlonen Art. 3. De minimum uurlonen en de werkelijk betaalde lonen van de in artikel 1 bedoelde werknemers worden op basis van een wekelijkse arbeidsduur van 38 uren, op 1 januari 2025, na indexering met 3,57 pct., als volgt vastgesteld : - Ongeschoolden : 12,16 EUR; - Geoefenden : 12,82 EUR; - Geschoolden : 13,41 EUR; - Meergeschoolden : loon overeen te komen, met een minimum van 13,41 EUR. B. Anciënniteitstoeslag Art. 4. Op de minimum uurlonen wordt een anciënniteitstoeslag toegekend. Deze toeslag bedraagt 0,5 pct. bij een anciënniteit van 5 jaar in de onderneming, 1 pct. bij een anciënniteit van 10 jaar in de onderneming, 1,5 pct. bij een anciënniteit van 15 jaar in de onderneming, 2 pct. bij een anciënniteit van 20 jaar in de onderneming, 2,5 pct. bij een anciënniteit van 25 jaar in de onderneming, 3 pct. bij een anciënniteit van 30 jaar in de onderneming, 3,5 pct. bij een anciënniteit van 35 jaar in de onderneming en 4 pct. bij een anciënniteit van 40 jaar in de onderneming. Art. 5. De toeslag wordt betaald vanaf de eerste dag van de maand volgend op het bereiken van de anciënniteit van 5, 10, 15, 20, 25, 30, 35 of 40 jaar.C. Forfaitaire premie Art. 6.  § 1. Vanaf het kalenderjaar 2016 betaalt de werkgever elk jaar op 1 juli aan de werknemers die bedoeld worden in het hierboven vermelde artikel 1 een forfaitaire premie. Deze forfaitaire premie wordt enkel toegekend aan de werknemers die tijdens de referteperiode van 1 juli van het voorgaande kalenderjaar tot 30 juni van het lopende kalenderjaar tewerkgesteld zijn geweest in de ondernemingen die ressorteren onder het Paritair Comité voor de landbouw. Onder "tewerkstelling" wordt begrepen : de gewerkte en gelijkgestelde dagen zoals gedefinieerd in artikel 16 van het koninklijk besluit van 30 maart 1967 tot bepaling van de algemene uitvoeringsmodaliteiten van de wetten betreffende de jaarlijkse vakantie van de werknemers (Belgisch Staatsblad van 6 april 1967).  § 2. Voor de voltijds tewerkgestelde werknemers met een volledige referteperiode stemt het bedrag van deze brutopremie overeen met 55,00 EUR. Voor de deeltijdse werknemers zal de brutopremie worden berekend in verhouding tot deze van de voltijdse arbeiders en dit in functie van de deeltijdse arbeidsduur. Voor de werknemers die geen prestaties kunnen bewijzen gedurende een volledig refertejaar, wordt de brutopremie pro rata temporis berekend. Elke begonnen maand telt als 1/12. Bij uitdiensttreding wordt de premie verrekend met de laatste loonafrekening.  § 3. Het bedrag van de premie wordt gekoppeld aan de evolutie van de afgevlakte gezondheidsindex, overeenkomstig de bepalingen van de collectieve arbeidsovereenkomst van 18 april 2024, gesloten in het Paritair Comité voor de landbouw, betreffende de indexering van de lonen (arbeiders en alle bedienden met uitzondering van de arbeiders in de vlassector) en geregistreerd onder het nr. 187715/CO/144. Deze premie bedraagt op 1 januari 2025 72,56 EUR.  § 4. Op ondernemingsvlak kan deze forfaitaire premie worden omgezet in een gelijkwaardig voordeel (bij omzetting in maaltijdcheques verhoogt het werkgeversaandeel met 0,5 EUR per dag) mits het afsluiten van een collectieve arbeidsovereenkomst, neergelegd uiterlijk op 1 mei van het lopende jaar en mits het bezorgen van een kopie van deze ondernemings-collectieve arbeidsovereenkomst aan de voorzitter van het Paritair Comité van de landbouw. Zolang er een verlenging van het basisakkoord bestaat op het niveau van het paritair comité, wordt de omzetting automatisch verlengd. HOOFDSTUK IV. - Koppeling van de lonen Art. 7. De werkelijke uurlonen evenals de in artikel 3 vastgestelde minimum uurlonen worden gekoppeld aan de evolutie van de afgevlakte gezondheidsindex, overeenkomstig de bepalingen van de collectieve arbeidsovereenkomst van 18 april 2024, gesloten in het Paritair Comité voor de landbouw, betreffende de indexering van de lonen (landbouw, exclusief vlas) en geregistreerd onder het nr. 187715/CO/144. HOOFDSTUK V. - Geldigheid Art. 8. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van 1 januari 2025 en wordt gesloten voor een onbepaalde duur. Zij vervangt de collectieve arbeidsovereenkomst betreffende de loon- en arbeidsvoorwaarden van 15 december 2023, gesloten in het Paritair Comité voor de landbouw, geregistreerd onder het nr. 185623/CO/144. Elk van de contracterende partij en kan ze opzeggen mits een opzeggingstermijn van drie maanden, te betekenen bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Comité voor de landbouw. Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -1889,29 +1888,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2025200972</t>
+          <t>2025002974</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>21 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 23 december 2024, gesloten in het Paritair Subcomité voor de erkende ondernemingen die buurtwerken of -diensten leveren, betreffende de rechthebbenden en modaliteiten van toekenning en van uitkering van aanvullende vergoedingen ten laste van het "Sociaal Fonds voor de dienstencheques" (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor het tuinbouwbedrijf, tot vaststelling van de loon en arbeidsvoorwaarden voor gelegenheidswerknemers (1)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-21&amp;numac_search=2025200972&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200972=45&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025002974&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025002974=45&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Subcomité voor de erkende ondernemingen die buurtwerken of -diensten leveren; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 23 december 2024, gesloten in het Paritair Subcomité voor de erkende ondernemingen die buurtwerken of -diensten leveren, betreffende de rechthebbenden en modaliteiten van toekenning en van uitkering van aanvullende vergoedingen ten laste van het "Sociaal Fonds voor de dienstencheques". Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Subcomité voor de erkende ondernemingendie buurtwerken of -diensten leveren Collectieve arbeidsovereenkomst van 23 december 2024 Rechthebbenden en modaliteiten van toekenning en van uitkering van aanvullende vergoedingen ten laste van het "Sociaal Fonds voor de dienstencheques" (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191518/CO/322.01) HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de werknemers van de ondernemingen die ressorteren onder het Paritair Subcomité voor de erkende ondernemingen die buurtwerken of -diensten leveren.Art. 2. In toepassing van de collectieve arbeidsovereenkomst van 9 november 2005 van het Paritair Subcomité voor de erkende ondernemingen die buurtwerken of -diensten leveren, tot oprichting van een fonds voor bestaanszekerheid en tot vaststelling van zijn statuten, worden de volgende aanvullende vergoedingen toegekend ten laste van het "Fonds voor bestaanszekerheid voor de ondernemingen die buurtwerken of -diensten leveren", ook benoemd sinds de collectieve arbeidsovereenkomst van 28 februari 2019 "Sociaal Fonds voor de dienstencheques" : 1° een eindejaarspremie; 2° een syndicale premie. HOOFDSTUK II. - Eindejaarspremie Art. 3.  § 1. Vanaf het jaar 2016 wordt de eindejaarspremie verhoogd tot 4,50 pct. van de brutolonen die op jaarbasis aan de werknemer worden betaald tijdens de referteperiode bepaald in § 3. De periodes van moederschapsverlof worden in aanmerking genomen voor de berekening van de eindejaarspremie. De premie wordt in de loop van de maand december van het lopende kalenderjaar uitbetaald door het "Sociaal Fonds voor de dienstencheques".  § 2. De voorwaarden zijn de volgende : - tijdens het lopende kalenderjaar verbonden zijn door een arbeidsovereenkomst in een bij artikel 1 van de onderhavige collectieve arbeidsovereenkomst bedoelde onderneming; - een anciënniteit hebben van minstens 65 arbeidsdagen (dagen waarvoor inhoudingen voor de sociale zekerheid werden gedaan) in de sector gedurende de referteperiode zoals bepaald in § 3 wat betreft de toekenning van de premie 2021. Vanaf de toekenning van de premie 2022, wordt de vereiste anciënniteit : minstens 30 arbeidsdagen (dagen waarvoor inhoudingen voor de sociale zekerheid werden gedaan) in de sector gedurende de referteperiode zoals bepaald in § 3. Dagen van tijdelijke werkloosheid wegens economische redenen worden gelijkgesteld met de arbeidsdagen vermeld in de vorige alinea, met een maximum van 26 dagen per referteperiode. Dagen van tijdelijke werkloosheid Corona worden gelijkgesteld met arbeidsdagen vermeld in het tweede streepje van deze paragraaf voor het openen van het recht op een eindejaarspremie, maar deze gelijkstelling geldt niet voor het berekenen van het bedrag van de eindejaarspremie.  § 3. De referteperiode vangt aan op 1 juli van het vorige kalenderjaar en eindigt op 30 juni van het lopende kalenderjaar. Deze referteperiode geldt ook voor de loonmassa die dient als basis voor de berekening van de eindejaarspremie. Art. 4. De premie wordt in de loop van de maand december toegekend volgens de door de raad van beheer van het "Sociaal Fonds voor de dienstencheques" vastgestelde modaliteiten. HOOFDSTUK III. - Syndicale premie Art. 5. Een syndicale premie wordt toegekend aan de werknemers die het recht verworven hebben op de eindejaarspremie zoals voorzien in hoofdstuk II, artikel 3, § 2 en § 3 van de onderhavige collectieve arbeidsovereenkomst en die lid zijn van één van de representatieve interprofessionele organisaties van werknemers die op nationaal niveau een federatie vormen, voor zover zij tijdens de referteperiode tewerkgesteld werden in een bij artikel 1 van de onderhavige collectieve arbeidsovereenkomst bedoelde onderneming. Art. 6. De toepassingsmodaliteiten van de syndicale premie worden jaarlijks vastgesteld door een unanieme beslissing van de raad van beheer van het "Sociaal Fonds voor de dienstencheques" en ter goedkeuring voorgelegd aan het paritair comité. Vanaf het jaar 2021 wordt dit bedrag vastgesteld op 145 EUR. Art. 7.  § 1. In de loop van de maand december van elk jaar stuurt het "Sociaal Fonds voor de dienstencheques" aan de werknemers een formulier volgens de modaliteiten bepaald door de raad van beheer van het fonds.  § 2. Bij ontvangst overhandigen de werknemers het formulier aan hun syndicale organisatie. Deze syndicale organisatie stort het bedrag aan de rechthebbende.HOOFDSTUK IV. - Slotbepalingen Art. 8. Deze collectieve arbeidsovereenkomst treedt in werking op 1 juli 2024 en wordt gesloten voor onbepaalde duur. Zij vervangt de bepalingen van : - de collectieve arbeidsovereenkomst van 22 juni 2022 inzake wijzigingen aan de collectieve arbeidsovereenkomst betreffende de rechthebbenden en de modaliteiten van toekenning en van uitkering van aanvullende vergoedingen ten laste van het "Fonds voor bestaanszekerheid voor de ondernemingen die buurtwerken of -diensten leveren", geregistreerd op de Griffie van de Administratie van Collectieve Arbeidsbetrekkingen onder het nummer 174569/CO/322.01. Zij kan worden opgezegd op verzoek van de meest gerede partij, mits een opzegging van zes maanden, gericht bij ter post aangetekende brief aan de voorzitter van het Paritair Subcomité voor de erkende ondernemingen die buurtwerken of -diensten leveren. Gezien om te worden gevoegd bij het koninklijk besluit van 27 april 2025. De Minister van Werk, D. CLARINVAL 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor het tuinbouwbedrijf;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor het tuinbouwbedrijf, tot vaststelling van de loon en arbeidsvoorwaarden voor gelegenheidswerknemers.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het tuinbouwbedrijfCollectieve arbeidsovereenkomst van 17 december 2024Vaststelling van de loon en arbeidsvoorwaarden voor gelegenheidswerknemers (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191510/CO/145)PreambuleBetreft de indexering van de lonen vanaf 1 januari 2025.ToepassingsgebiedArtikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers die ressorteren onder het toepassingsgebied van het Paritair Comité voor het tuinbouwbedrijf, met uitsluiting van de ondernemingen waarvan de hoofdactiviteit bestaat uit het aanleggen en onderhouden van parken en tuinen, en op hun als arbeider of arbeidster tewerkgesteld gelegenheidspersoneel zoals bepaald in artikel 8bis van het koninklijk besluit van 28 november 1969 tot uitvoering van de wet van 27 juni 1969 tot herziening van de besluitwet van 28 december 1944 betreffende de maatschappelijke zekerheid der arbeiders. § 2. Met de term "werknemers" worden de arbeiders bedoeld zonder onderscheid naar gender.LonenArt. 2.  § 1. Het minimumuurloon van de in artikel 1 genoemde gelegenheidswerknemers bedraagt na indexering vanaf 1 januari 2025 :  </t>
         </is>
       </c>
     </row>
@@ -1921,28 +1919,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2025004114</t>
+          <t>2025201173</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>30 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>27 april 2025. - Koninklijk besluit tot vergoeding van de regeringscommissaris en diens vervanger bij de naamloze vennootschap van publiek recht Belgische Investeringsmaatschappij voor Ontwikkelingslanden (BIO NV)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, betreffende de toekenning van een uitzonderlijk bedrag in 2024 bovenop de eindejaarstoelage voor de ambulante sectoren van Brussel (1)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-30&amp;numac_search=2025004114&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025004114=46&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025201173&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201173=46&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 3 november 2001 tot oprichting van de Belgische Investeringsmaatschappij voor Ontwikkelingslanden, artikel 5, § 4;Gelet op het koninklijk besluit van 7 mei 2024 tot vergoeding van de regeringscommissaris bij de naamloze vennootschap van publiek recht "Belgische Investeringsmaatschappij voor Ontwikkelingslanden/BIO NV",Hebben Wij besloten en besluiten Wij :Artikel 1. De regeringscommissaris ontvangt een zitpenning van 0 euro per zitting van de raad van bestuur en van de comités opgericht door de raad van bestuur, zoals het investeringscomité, het auditcomité en het human ressources comité, waaraan die deelneemt.Art. 2. De jaarlijkse vergoeding van de regeringscommissaris bedraagt 0 euro.Art. 3. De plaatsvervanger van de regeringscommissaris ontvangt een zitpenning van 0 euro per zitting van de raad van bestuur en van de comités opgericht door de raad van bestuur, zoals het investeringscomité, het auditcomité en het human ressources comité, waarin die de regeringscommissaris vervangt.De jaarlijkse vergoeding van de plaatsvervanger van de regeringscommissaris bedraagt 0 euro.Art. 4. Het koninklijk besluit van 7 mei 2024 tot vergoeding van de regeringscommissaris bij de naamloze vennootschap van publiek recht "Belgische Investeringsmaatschappij voor Ontwikkelingslanden/BIO NV" wordt opgeheven.Art. 5. Dit besluit heeft uitwerking met ingang van 28 maart 2025.Art. 6. De minister bevoegd voor Ontwikkelingssamenwerking is belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Ontwikkelingssamenwerking,M. PREVOT 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de gezondheidsinrichtingen en -diensten; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, betreffende de toekenning van een uitzonderlijk bedrag in 2024 bovenop de eindejaarstoelage voor de ambulante sectoren van Brussel. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 11 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de gezondheidsinrichtingen en -diensten Collectieve arbeidsovereenkomst van 18 december 2024 Toekenning van een uitzonderlijk bedrag in 2024 bovenop de eindejaarstoelage voor de ambulante sectoren van Brussel (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191542/CO/330) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en werknemers van de sociale diensten, de diensten voor geestelijke gezondheid, van de hulp aan rechtzoekenden en andere ambulante diensten - met uitzondering van de wijkgezondheidscentra - die ressorteren onder het Paritair Comité voor de gezondheidsinrichtingen en -diensten en die erkend en gesubsidieerd zijn door de Gemeenschappelijke Gemeenschapscommissie of door de Franse Gemeenschapscommissie van het Brusselse Hoofdstedelijk Gewest.Onder "werknemers" wordt verstaan: het arbeiders- en bediendepersoneel, zonder onderscheid van geslacht. Art. 2. Deze collectieve arbeidsovereenkomst voorziet in de toekenning van een uitzonderlijk bedrag in 2024 bovenop de eindejaarstoelage betreffende het jaar 2024 voor de ambulante sectoren van Brussel zoals bepaald door de collectieve arbeidsovereenkomst van 12 december 2022. Dit uitzonderlijk bedrag is: - 2 173,62 EUR voor de ambulante sectoren erkend en gesubsidieerd door de GGC; - 1 920,7441 EUR voor de ambulante sectoren erkend en gesubsidieerd door de FGC. Art. 3. Dit uitzonderlijk bedrag dat wordt toegevoegd aan de eindejaarstoelage wordt berekend en vereffend volgens dezelfde modaliteiten als die waarin voorzien is door de collectieve arbeidsovereenkomst van 12 december 2022 betreffende de eindejaarstoelage voor de ambulante sectoren van Brussel. Indien het niet wordt toegevoegd aan de eindejaarstoelage, zal het bedrag worden uitbetaald vóór 31 januari 2025. Art. 4. De voorwaarde voor de toepassing van deze overeenkomst is: - dat de Franse Gemeenschapscommissie haar financieringsverbintenissen moet uitvoeren, zoals gespecificeerd in de omzendbrief van de Franse Gemeenschapscommissie van 26 november 2024 aan de centra, diensten en tehuizen gesubsidieerd in het kader van het "non-profit-decreet" van 18 oktober 2001, getiteld "eindejaarspremie 2024"; - dat de Gemeenschappelijke Gemeenschapscommissie haar financieringsverbintenissen moet uitvoeren. Art. 5. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2024. Zij wordt gesloten voor een bepaalde duur van 1 januari 2024 tot 31 januari 2025. Overeenkomstig artikel 14 van de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités worden, voor wat betreft de ondertekening van deze collectieve arbeidsovereenkomst, de handtekeningen van de personen die deze aangaan namens de werknemersorganisaties enerzijds en namens de werkgeversorganisaties anderzijds, vervangen door de notulen van de vergadering die zijn ondertekend door de voorzitter en de secretaris en goedgekeurd door de leden. Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -1953,28 +1951,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2025000887</t>
+          <t>2025201168</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>06 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>13 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 10 november 2023, gesloten in het Paritair Comité voor het glasbedrijf, betreffende de arbeids- en loonvoorwaarden, akkoorden voor de werkgelegenheid en de vorming en andere arbeidsmodaliteiten in de subsector van de spiegelmakerij en van de fabricage van kunstramen in 2023 en 2024 (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 12 december 2024, gesloten in het Paritair Comité voor de zeevisserij, betreffende de wijziging van de statuten van het "Waarborg- en Sociaal Fonds voor de zeevisserij" (1)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-06&amp;numac_search=2025000887&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025000887=47&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025201168&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201168=47&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor het glasbedrijf;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 10 november 2023, gesloten in het Paritair Comité voor het glasbedrijf, betreffende de arbeids- en loonvoorwaarden, akkoorden voor de werkgelegenheid en de vorming en andere arbeidsmodaliteiten in de subsector van de spiegelmakerij en van de fabricage van kunstramen in 2023 en 2024.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 13 april 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het glasbedrijfCollectieve arbeidsovereenkomst van 10 november 2023Arbeids- en loonvoorwaarden, akkoorden voor de werkgelegenheid en de vorming en andere arbeids-modaliteiten in de subsector van de spiegelmakerij en van de fabricage van kunstramen in 2023 en 2024 (Overeenkomst geregistreerd op 30 november 2023 onder het nummer 184268/CO/115)VoorwoordDe sociale partners willen een suppletief akkoord sluiten betreffende artikel 8 "De koopkrachtpremie" van titel IV "Loonsvoorwaarden" dat enerzijds de wet van 26 juli 1996 betreffende de bevordering van de tewerkstelling en de preventieve vrijwaring van het concurrentievermogen gewijzigd door de wet van 19 maart 2017 en het koninklijk besluit van 13 mei 2023 tot uitvoering van artikel 7, § 1 van de wet van 26 juli 1996 tot bevordering van de werkgelegenheid en tot preventieve vrijwaring van het concurrentievermogen (Belgisch Staatsblad van 26 mei 2023) tot vaststelling van de maximale marge voor loonkostontwikkeling voor de periode 2023-2024 en het koninklijk besluit van 23 april 2023 betreffende de koopkrachtpremie (Belgisch Staatsblad van 28 april 2023) en de collectieve arbeidsovereenkomsten gesloten voor de ganse glassector respecteert, en anderzijds, rekening houdt met de socio-economische realiteit die leeft in de subsector van de verwerking van vlakglas, met andere woorden in de spiegelmakerij.TITEL I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de arbeiders van de fabrieken en ondernemingen van de volgende bedrijfssectoren, het door hen verrichte monteren en plaatsen inbegrepen, met uitzondering van de naamloze vennootschap AGC MIRODAN N.V. te 8501 Heule, Industrielaan 1 :1°  samengevoegd en/of omgevormd en/of bewerkt vlak glas, bijvoorbeeld : isolerende beglazing, spiegelglas, geslepen spiegelglas, met geslepen rand, verzilverd, gegraveerd, versierd, gewelfd, dofgemaakt, fijn glas, kortom de spiegelmakerij, en andere;2°  de fabricage van kunstramen.De bepalingen voorzien in artikelen 23 tot 26 van de huidige collectieve arbeidsovereenkomst gelden echter ook integraal voor de naamloze vennootschap AGC MIRODAN N.V. (Industrielaan 1 - 8501 Heule).Met "arbeiders" worden arbeiders en arbeidsters bedoeld.TITEL II. - OnderhandelingskaderArt. 2. De ondertekenende partijen en hun leden zijn akkoord om volgend punt na te leven gedurende eventuele onderhandelingen voor de periode 2023-2024 : er zullen geen eisen ingediend of besproken worden in de sector, de subsectoren en de ondernemingen uit de glasindustrie die in tegenspraak of conflict zijn met het wettelijk kader voorzien door de wet van 26 juli 1996 tot de bevordering van de werkgelegenheid en tot preventieve vrijwaring van het concurrentievermogen gewijzigd door de wet van 19 maart 2017 en door het koninklijk besluit van 13 mei 2023 tot uitvoering van artikel 7, § 1 van de wet van 26 juli 1996 tot bevordering van de werkgelegenheid en tot preventieve vrijwaring van het concurrentievermogen (Belgisch Staatsblad van 26 mei 2023) tot vaststelling van de maximale marge voor loonkostontwikkeling voor de periode 2023-2024 en het koninklijk besluit van 23 april 2023 betreffende de koopkrachtpremie (Belgisch Staatsblad van 28 april 2023).TITEL III. - ArbeidsvoorwaardenHOOFDSTUK I. - Wekelijkse arbeidsduurArt. 3. De overeengekomen wekelijkse arbeidsduur mag op jaarbasis gemiddeld de 38 uur per week niet overschrijden.HOOFDSTUK II. - AnciënniteitsverlofArt. 4. De arbeiders hebben recht op anciënniteits-verlof conform het hierna bepaalde :- één dag verlof na 5 jaar anciënniteit in de onderneming;- twee dagen verlof na 10 jaar anciënniteit in de onderneming;- drie dagen verlof na 15 jaar anciënniteit in de onderneming.Deze dagen zijn verworven zodra de anciënniteit bereikt is.De verlofdata worden vastgesteld in akkoord met de werkgever, rekening houdend met de werkorganisatie.HOOFDSTUK III. - FunctieclassificatieA. FabricagepersoneelArt. 5. De functies van de arbeiders die tewerkgesteld zijn in de fabricage worden ingedeeld in zes groepen volgens de hierna vermelde algemene criteria :Groep 1Vergt geen enkele schoolse vooropleiding, interne beroepsopleiding van minder dan één (1) week, uitvoeren van eenvoudige repetitieve taken op één werkpost, kunnen lezen en schrijven, voldoende kwaliteit en rendement, aanhoudende aandacht.Groep 2Vergt geen specifieke schoolse vooropleiding, interne beroepsopleiding van maximum één (1) week, uitvoeren van eenvoudige repetitieve taken op meerdere werkposten, kunnen lezen en schrijven, voldoende kwaliteit en rendement, aanhoudende aandacht.Groep 3Interne opleiding van één (1) week tot minder dan één (1) maand, uitvoeren van taken die een langere scholing vereisen op meerdere werkposten, in staat zijn de functies van groepen 1 en 2 uit te oefenen, niveau A3 of gelijkgesteld. Bewakers en huisbewaarders vallen eveneens onder die categorie. Voldoende kwaliteit en rendement.Groep 4Interne beroepsopleiding van één (1) maand tot minder dan drie (3) maanden, uitvoeren van taken die een aanpassingsperiode en een specifieke kennis vereisen op meerdere werkposten, niveau A3 of gelijkgesteld.Groep 5Interne beroepsopleiding van drie (3) tot zes (6) maanden, uitvoeren van taken die een vakkennis (specialisatie) vereisen, bijna zelfstandig kunnen werken (met minimale hiërarchische ondersteuning), niveau A2 of gelijkgesteld.Groep 6Interne beroepsopleiding van zes (6) maanden of meer, uitvoeren van meerdere taken op diverse werkposten die een volledige vakkennis vereisen, volledig zelfstandig kunnen werken, niveau A2 of gelijkgesteld.B. Onderhoudspersoneel en aanvullende dienstenArt. 6. De arbeiders die tewerkgesteld zijn in de onderhouds- en aanvullende diensten worden als volgt ingedeeld :1°  De geoefende hulparbeiders worden ten minste gerangschikt in de in artikel 5 bepaalde groep 5;2°  De geschoolde arbeiders worden als volgt ingedeeld :1) Categorie A : nieuw gediplomeerden A4, A3, B2;2) Categorie B : nieuw gediplomeerden A4, A3, B2 na een proeftijd;3) Categorie C : gediplomeerden A4 of B6, met ten minste twee jaar ervaring;4) Categorie D : gediplomeerden A3, B2 of B1, met ten minste vijf jaar ervaring;5) Brigadiers : gediplomeerden zoals bepaald voor categorie D en met uitoefening van gezag.De toegang tot de hogere categorieën is mogelijk bij uitzonderlijke verdienste of voldoende anciënniteit voor de arbeiders die niet in het bezit zijn van een diploma overeenkomstig artikel 6, 2°. De overgang van een categorie naar een andere vergt echter, zoals de overgang van de ene basisgroep naar de andere, een voldoende rendement en arbeidskwaliteit.Art. 7. De objectieve toepassing van de bij de artikelen 5 en 6 vastgestelde criteria wordt in de onderneming paritair onderzocht.TITEL IV. - LoonvoorwaardenArt. 8. De koopkrachtpremieDe sociale partners hebben de mogelijkheid om op ondernemingsvlak een akkoord te onderhandelen over de koopkrachtpremie tot 15 december 2023, dat in overeenstemming is met het koninklijk besluit van 23 april 2023 betreffende de koopkrachtpremie.Als uiterlijk op 15 december 2023 geen akkoord wordt bereikt op ondernemingsniveau, zal een koop-krachtpremie worden toegekend aan de arbeiders door bedrijven die een hoge of uitzonderlijk hoge winst hebben gerealiseerd in 2022."Winst in 2022" wordt voor de toepassing van deze collectieve arbeidsovereenkomst gedefinieerd als de som van de volgende codes van de jaarrekening voor het boekjaar 2022 :- Code 9901 (bedrijfswinst/verlies);- Code 630 (afschrijvingen en waardeverminderingen op oprichtingskosten, op immateriële en materiële vaste activa);- Code 631/4 (waardeverminderingen op voorraden, op bestellingen in uitvoering en op handelsvorderingen : toevoegingen (terugnemingen)).Een bedrijf heeft een "hoge winst in 2022" gerealiseerd als zijn "winst in 2022" positief is.Een bedrijf heeft een "uitzonderlijk hoge winst in 2022" gerealiseerd als zijn "winst in 2022" minstens 1,15 x hoger is dan de gemiddelde winst in de 3 voorafgaande afgesloten boekjaren. Voor de berekening van dit gemiddelde worden enkel de boekjaren met een positieve "winst" meegeteld.Het bedrag van de koopkrachtpremie :In de ondernemingen die op 15 december 2023 geen bedrijfsakkoord hebben afgesloten en die een hoge winst hebben gerealiseerd in 2022, zoals hierboven gedefinieerd, wordt een koopkrachtpremie van 75 EUR toegekend.In de ondernemingen die op 15 december 2023 geen bedrijfsakkoord hebben afgesloten en die een uitzonderlijk hoge winst hebben gerealiseerd in 2022, zoals hierboven gedefinieerd, wordt een koop-krachtpremie van 76 EUR toegekend.Modaliteiten van toekenning :De koopkrachtpremie wordt toegekend in de loop van de maand december 2023 aan de arbeiders die in dienst zijn op 15 december 2023 :- pro rata van de arbeidsprestaties tijdens de periode die loopt van 1 januari 2022 tot en met 31 december 2022. Worden met arbeidsprestaties gelijkgesteld : jaarlijkse vakantie, wettelijke feestdagen, vaderschapsverlof, betaald educatief verlof, syndicaal verlof, kort verzuim, beroepsziekte, arbeidsongeval en bevallingsrust en 60 dagen ziekte of ongeval, ongeacht of deze hun basis vinden in wettelijke, reglementaire of conventionele bepalingen;- pro rata van het arbeidsregime van de werknemer op 31 december 2022.Voor bedrijven wiens boekjaar niet overeenstemt met een kalenderjaar zal voor het bepalen van de winst/hoge winst/uitzonderlijk hoge winst het boekjaar genomen wordt dat eindigt in 2022.In overeenstemming met het koninklijk besluit van 23 april 2023 wordt de koopkrachtpremie op een papieren drager (cheques) of in elektronische vorm toegekend.Art. 9. Minimum uurlonenA. Personeel aan de fabricageDe minimum uurlonen van de arbeiders die een in artikel 5 bepaalde functie uitoefenen worden als volgt bepaald voor een 38-urige werkweek :  </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet. Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de zeevisserij; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 12 december 2024, gesloten in het Paritair Comité voor de zeevisserij, betreffende de wijziging van de statuten van het "Waarborg- en Sociaal Fonds voor de zeevisserij".Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 11 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de zeevisserij Collectieve arbeidsovereenkomst van 12 december 2024 Wijziging van de statuten van het "Waarborg- en Sociaal Fonds voor de zeevisserij" (Overeenkomst geregistreerd op 10 februari 2025 onder het nummer 191997/CO/143) Artikel 1. Artikel 5 van de statuten opgenomen bij de collectieve arbeidsovereenkomst van 4 oktober 2018 tot wijziging en coördinatie van de statuten van het "Waarborg- en Sociaal Fonds voor de zeevisserij" (registratienummer 153649/CO/143) wordt vervangen door de volgende bepaling : "De statuten zijn van toepassing : a) op de werkgevers van de ondernemingen die onder het Paritair Comité van de zeevisserij ressorteren, met uitzondering van de rederijen; b) op de werklieden en werksters, tewerkgesteld door de onder artikel 5, a) bedoelde werkgevers. Onder werklieden en werksters moet ook worden verstaan de flexi-jobwerknemers.". Art. 2. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025. Zij wordt gesloten voor de periode van één jaar. De duur ervan wordt telkens stilzwijgend met één jaar verlengd, behalve bij opzegging door één der organisaties die vertegenwoordigd zijn in het Paritair Comité voor de zeevisserij, betekend bij aangetekende brief aan de voorzitter van het Paritair Comité voor de zeevisserij, ten laatste zes maanden voor de jaarlijkse vervaldag. Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025. De Minister van Werk, D. CLARINVAL 
+</t>
         </is>
       </c>
     </row>
@@ -1984,28 +1983,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2025002517</t>
+          <t>2025201249</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>07 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>13 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 20 december 2021, gesloten in het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap, betreffende de vaststelling van de arbeids-, loon- en loonindexeringsvoorwaarden voor het personeel van de diensten voor gezins- en bejaardenhulp die gesubsidieerd zijn door het Waalse Gewest (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 3 februari 2025, gesloten in het Paritair Comité voor de Vlaamse welzijns- en gezondheidssector, tot vaststelling van het percentage van de bijdragen voor het jaar 2025 voor het fonds voor bestaanszekerheid genaamd "Sociaal Fonds 331 tot financiering tweede pensioenpijler" en tot bepaling van de datum van aanvraag tot vrijstelling van de bijdragen voor het jaar 2025 (1)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-07&amp;numac_search=2025002517&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025002517=48&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025201249&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201249=48&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 20 december 2021, gesloten in het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap, betreffende de vaststelling van de arbeids-, loon- en loonindexeringsvoorwaarden voor het personeel van de diensten voor gezins- en bejaardenhulp die gesubsidieerd zijn door het Waalse Gewest.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 13 april 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige GemeenschapCollectieve arbeidsovereenkomst van 20 december 2021Vaststelling van de arbeids-, loon- en loonindexeringsvoorwaarden voor het personeel van de diensten voor gezins- en bejaardenhulp die gesubsidieerd zijn door het Waalse Gewest (Overeenkomst geregistreerd op 4 juli 2022 onder het nummer 173808/CO/318.01)HOOFDSTUK I. - ToepassingsgebiedArtikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werknemers en werkgevers van de diensten voor gezins- en bejaardenhulp die erkend en gesubsidieerd zijn door het Waalse Gewest en die vallen onder de bevoegdheid van het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap. § 2. Voor de toepassing van deze collectieve arbeidsovereenkomst wordt onder "werknemer" verstaan : het vrouwelijk en mannelijk arbeiders- en bediendenpersoneel.In deze collectieve arbeidsovereenkomst wordt het mannelijk geslacht gebruikt als soortnaam, enkel om de tekst niet te verzwaren. § 3. Deze collectieve arbeidsovereenkomst geeft uitvoering aan het intersectoraal tripartiete kaderakkoord van de Waalse non-profitsector 2021-2024 van 26 mei 2021.Art. 2. De bepalingen van deze collectieve arbeidsovereenkomst stellen de regels vast die toepasbaar zijn op alle werknemers opgenomen in artikel 1, en stellen enkel de minimumlonen vast, waarbij alle vrijheid aan de partijen wordt gelaten om overeen te komen over gunstigere voorwaarden voor de werknemers. Zij mogen bovendien geen afbreuk doen aan de bepalingen die gunstiger zijn voor de werknemers, daar waar een gelijkaardige situatie bestaat.De juiste toepassing ervan vereist dat alle bijkomende subsidies toegekend ten gunste van de werknemers krachtens de intersectorale tripartiete raamovereenkomst van de Waalse non-profitsector en de toepassingsmodaliteiten ervan hen integraal worden toegewezen. Over de gebruiksmodaliteiten van de subsidie zal lokaal sociaal overleg worden gepleegd in de ondernemingsraad, bij gebreke hiervan in het CPBW, bij gebreke daarvan met de vakbondsafvaardiging of bij gebreke daarvan rechtstreeks met de werknemers.Art. 3. De opsomming van de functies die gerangschikt zijn in de verschillende hierna vastgestelde categorieën, moet als voorbeeld en als niet-beperkend worden beschouwd.Art. 4. Technisch personeel (2 categorieën)Eerste categorie- OnderhoudstechnicusPersoneel waarvan de functie bestaat in het reinigen van de lokalen van de diensten.ProfielBlijk geven van een algemene technische basiskennis betreffende het huishoudelijk onderhoud.StatuutArbeiderTweede categorie- Polyvalent arbeider, chauffeur, sociaal huishoudhulpa) Polyvalent arbeiderWerknemer wiens functie erin bestaat om uitsluitend eenvoudige manuele en technische werkzaamheden uit te voeren, teneinde het levensmilieu van de hulpbehoevenden te verbeteren :1. de lokalen waar de gezinnen, de bejaarden, gehandicapten en/of zieken wonen inrichten en/of aanpassen;2. het personenalarmeringsmateriaal plaatsen, onderhouden;3. het sanitair materiaal vervoeren en onderhouden.De arbeider zal op geen enkel ogenblik een privéonderneming vervangen. De polyvalente arbeider wordt ertoe aangezet om :1. nauw samen te werken met de verantwoordelijke van de dienst en/of de omkaderingspersoon;2. zich in te passen in een interdisciplinaire hulp- en zorgarbeid en zich te wenden tot de verantwoordelijke van de dienst of tot de coördinator voor alle handelingen die buiten zijn bevoegdheid vallen;3. deel te nemen aan de opleidingen die voor hem/haar bestemd zijn.ProfielBij gebreke van een reglementering ter zake, blijk geven van :- een algemene en technische basiskennis en -vaar-digheid;- kwaliteiten inzake openheid en werken in ploegverband;- aanpassingsvermogen om zich in de context van het dagelijks leven van de rechthebbenden te verplaatsen;- interpersoonlijke vaardigheden.StatuutArbeiderb) ChauffeurWerknemer wiens functie erin bestaat om de voertuigen te besturen die bestemd zijn voor het vervoer van personen van hun woonplaats naar een ziekenhuisinstelling of een gezondheidsdienst. De functie wordt gekenmerkt door :1. de ter beschikking gestelde voertuigen te besturen, met naleving van de wegcode en in alle veiligheid, en als een "goede huisvader" toe te zien op het algemeen onderhoud ervan;2. nauw samen te werken met de dienstverantwoordelijke;3. zich in te passen in een interdisciplinaire hulp- en zorgarbeid en zich te wenden tot de verantwoordelijke van de dienst of tot de coördinator voor alle handelingen die buiten zijn bevoegdheid vallen.4. Deel te nemen aan de opleidingen die voor hem/haar bestemd zijn.ProfielBij gebreke van een reglementering ter zake :- in bezit zijn van het diploma van hulpverlener en van het passende rijbewijs;- de medische selectie hebben die noodzakelijk is voor de activiteit;- blijk geven van kwaliteiten inzake openheid en werken in ploegverband;- blijk geven van aanpassingsvermogen om zich in de context van het dagelijks leven van de rechthebbenden te verplaatsen;- blijk geven van interpersoonlijke vaardigheden.StatuutArbeiderc) Sociaal huishoudhulpWerknemer wiens functie erin bestaat om uitsluitend huishoudelijke werkzaamheden uit te voeren. Hij/Zij maakt het voor de hulpbehoevenden mogelijk om thuis te blijven in een verzorgd en net kader. Deze functie wordt gekenmerkt door :1. onderhouden, handhaven en verbeteren van de hygiëne van de woning;2. zich integreren in een ploeg van huishoudhulpen en in nauwe samenwerking werken met de sociaal assistent of de verantwoordelijke die de ploeg van huishoudhulpen omkadert waarvan zij deel uitmaakt;3. zich inpassen in een interdisciplinaire hulp- en zorgarbeid en zich wenden tot de verantwoordelijke van de dienst of tot de coördinator voor alle handelingen die buiten zijn bevoegdheid vallen;4. deelnemen aan de opleidingen die voor hem/haar bestemd zijn.ProfielBij gebreke van een reglementering ter zake, blijk geven van :- vaardigheid op het gebied van huishoudelijke taken;- kwaliteiten inzake openheid en werken in ploegverband;- aanpassingsvermogen om zich in de context van het dagelijks leven van de rechthebbenden te verplaatsen;- interpersoonlijke vaardigheden.StatuutArbeiderArt. 5. Administratief personeel (4 categorieën)Eerste categorie- KlerkBedienden waarvan de functie wordt gekenmerkt door :1. de gelijkstelling ofwel door onderwijs, ofwel in de praktijk, of door kennis die overeenstemt met de 3 jaren van het lager secundair onderwijs;2. het uitvoeren van eenvoudige, weinig gediversifieerde taken waarvan de verantwoordelijkheid beperkt wordt door direct en constant toezicht;3. een beperkte assimilatietijd die het mogelijk maakt om een bekwaamheid te verwerven binnen een bepaalde tijd.Voorbeelden :Administratief- telefonist van de centrale die op eigen initiatief eenvoudige antwoorden moet verstrekken aan de correspondenten of telefonist van een coördinatiecentrum voor thuiszorg en -diensten;- archivist-klasseerder die blijk moet geven van beoordelings- en onderscheidingsvermogen;- ervaren typist die 40 woorden/minuut kan typen, een correcte spelling heeft en zijn werk goed kan opmaken;- bediende belast met eenvoudig redactioneel werk, rekenwerk, invoeren van lijsten, opmaken van staten of andere bijkomstige taken van hetzelfde niveau die enig gezond verstand vereisen en onder rechtstreeks toezicht worden uitgevoerd;- hulpbediende bij de loonadministratie (onder toezicht);- bediende boekhouding (invoeren van boekhoudkundige elementen zonder bepaling van de boeking);- facturatiebediende belast met het opmaken van de lopende facturen en van de statistieken.Informatica- codeerder;- gebruiker van directe registratie.StatuutBediendeTweede categorie- OpstellerBedienden waarvan de functie wordt gekenmerkt door :1. een opleiding die gelijkwaardig is aan de 6 jaar van het hoger secundair onderwijs - of een praktische opleiding verworven door stages of door het uitoefenen van dezelfde of soortgelijke functies;2. een beperkte assimilatietijd;3. autonoom, gevarieerd werk dat van diegene die het uitvoert een bovengemiddelde beroepswaarde, initiatief en verantwoordelijkheidszin vereist;4. de mogelijkheid :- om alle taken lager dan zijn specialiteit uit te voeren;- om alle elementen samen te brengen van de taken die hem worden toevertrouwd, eventueel met de hulp van de bedienden van de vorige categorie.Voorbeelden :Administratief- typiste die eveneens met een secretariaatstaak is belast;- bediende die belast is met de berekening van de lonen en de gangbare toepassing van de sociale wetgeving ter zake; hij/zij voert eveneens de betaling van de lonen uit, de verdeling van de arbeidsuren met het oog op het vaststellen van de kostprijzen en voert af en toe berekeningen uit voor de toepassing van de sociale wetgeving;- hulpboekhouder (algemene, analytische of industriële boekhouding) belast met het opmaken, met behulp van boekhoudkundige aanvangsdocumenten, van een gedeelte van de boekhouding of van de lopende boekingen die echter een homogeen geheel vormen, voorafgaand aan de centralisatie, zoals bijvoorbeeld de lopende rekeningen van klanten en leveranciers, tussentijdse rekeningen. Deze verrichtingen kunnen zowel manueel als machinaal worden uitgevoerd;- bediende belast met het opstellen van niet-repetitieve brieven;- bediende die, niet enkel bij afwezigheid van de sociaal assistenten, de wijzigingen moet ten laste nemen inzake toewijzing van taken van de gezinshelpers, in verband met de afwezigheid van de gezinshelpers en de evolutie van de vragen van de bejaarden;- bediende die regelmatig moet aanwezig zijn op het secretariaat.InformaticaExploitatie- monitor : verdeelt en ziet toe op het werk van de codeerders; bovendien begeleidt hij/zij het nieuwe personeel tijdens de proefperiode.- operator : persoon die belast is met de uitrusting en inwerkingstelling van de randapparatuur van de computer, volgens de uitvoeringsaanwijzingen.StatuutBediendeDerde categorie- Administratief bediende in bezit van een graduaat vereist bij de indienstnemingWerknemer die houder is van een diploma dat uitgereikt is door een school uit het hoger onderwijs en vereist is bij de indienstneming.Voorbeelden :Administratief- boekhouder, dat wil zeggen bediende belast met het omzetten van alle verrichtingen in boekhoudkundige termen, met het bijeenbrengen ervan en het samenstellen teneinde de algemene balans ervan op te maken, voorafgaandelijk aan de vooruitzichten, balansen, resultaten;- bediende belast met het boekhoudkundig inschrijven van alle verrichtingen die verband houden met de productie, deze samen te stellen en bijeen te brengen teneinde de kostprijs te kunnen berekenen;- bediende verantwoordelijk voor de toepassing van elke loon- en sociale bepaling;- secretaris op een directieniveau.InformaticaExploitatie- deskoperator : leidt een grote eonfiguratie van heel het informaticasysteem door middel van het besturingssysteem (software van de machine);- Voorbereider van de dragers en van de planning: staat in voor de planning van de werkzaamheden en de aanvoer van gegevensdragers.Ontwikkeling- programmeur : ontwerpt de gedetailleerde toepassingsprogramma's en werkt ze uit op basis van het analysedossier; hij maakt het toepassingsdossier klaar; hij zorgt voor de opvolging van de tests.StatuutBediendeVierde categorie- Administratief bediende in bezit van een licentie vereist bij de indienstnemingWerknemer houder van een diploma uitgereikt door een school uit het hoger onderwijs van het lange type (universiteit) en voor wie het bezit van deze titel vereist is.Voorbeelden : informaticus analist, jurist.StatuutBediendeArt. 6. Sociaal personeel (4 categorieën)Eerste categorie- Thuisoppas en gezinshulpa) ThuisoppasIn het Waalse Gewest is het statuut van de thuisoppas opgenomen in artikel 323 van het Waalse Wetboek van Sociale Actie en Gezondheid.Heeft de opdracht samen te werken en het mentaal, fysiek en sociaal welzijn te optimaliseren van de rechthebbende van de dienst, die een voortdurende aanwezigheid nodig heeft, in samenwerking met de omgeving van deze laatste :1. instaan voor het actief toezicht tijdens de dag en/of de nacht van een rechthebbende van de dienst, samen met de nabije omgeving;2. ervoor zorgen dat de rechthebbende in optimale omstandigheden op het gebied van veiligheid en hygiëne kan blijven wonen;3. toezien op de correcte inname van de geneesmiddelen volgens het voorschrift van de behandelende geneesheer;4. de gerechtigde helpen en hem leren, in functie van zijn fysieke en mentale capaciteiten, de "tijd" kwalitatief te gebruiken;5. de maaltijden klaarmaken en geven aan de gerechtigde;6. zich inpassen in een interdisciplinaire arbeid en zich wenden tot de verantwoordelijke van de dienst of tot de coördinator voor alle handelingen die buiten zijn bevoegdheid vallen;7. deelnemen aan de opleidingen die worden georganiseerd;8. de hoofdbegeleider ondersteunen.ProfielKennis :- ofwel een opleiding die toegang geeft tot het beroep van gezinshelper of gelijkwaardig geoordeeld wordt;- ofwel geen enkele overeenstemmende maar gelijkgestelde opleiding met toepassing van de besluiten van de Waalse Regering van 29 januari 2004 en 15 april 2005;- ofwel een door het Europees Sociaal Fonds of in het kader van het NOW-project (Onderwijs voor Sociale Promotie) gesubsidieerde kwalificatie-opleiding tot thuisoppas;- ofwel een opleiding van thuisoppas of een gelijkwaardige opleiding die in de toekomst zou worden goedgekeurd door het onderwijs voor sociale promotie en die zou beantwoorden aan het beroepsprofiel dat op 24 mei 1996 werd aangenomen door de Hoge Raad van het Onderwijs voor Sociale Promotie.Capaciteiten :- blijk geven van zin voor openheid en samenwerken in ploegverband, analyse van situaties en terugschakelen naar de diensten;- blijk geven van bekwaamheid om de mogelijkheden van de rechthebbende te evalueren en deze te stimuleren opdat deze laatste actief blijft in de zorg voor zijn dagelijkse leefwereld;- blijk geven van bekwaamheid om mee te werken met de omgeving.StatuutBediendeb) GezinshulpIn het Waalse Gewest, personeel van wie de functie bepaald is in punt A van het statuut dat als bijlage gevoegd is bij het besluit van de Waalse Regering van 16 juli 1998 (Belgisch Staatsblad van 8 september 1998) houdende goedkeuring van het statuut van gezinshelper - en van wie het profiel bepaald is in punt B van hetzelfde besluit - gewijzigd door het besluit van de Waalse Regering van 8 april 2000 (Belgisch Staatsblad van 19 april 2000) - gewijzigd door het besluit van de Waalse Regering van 30 april 2009 (Belgisch Staatsblad van 22 juli 2009).StatuutBediendeTweede categorie- Thuisoppas voor zieke kinderenWerknemer die als taak heeft, door zijn aanwezigheid, mee te werken aan het welzijn en het fysiek en mentaal comfort van het zieke kind, wanneer een voortdurende aanwezigheid vereist is en wiens functie wordt gekenmerkt door :1. omstandigheden van veiligheid en hygiëne bewaren voor het zieke kind en het helpen om de tijd kwalitatief te gebruiken;2. toezien op de correcte inname van de geneesmiddelen;3. de maaltijden klaarmaken en geven aan het zieke kind;4. zich inpassen in een interdisciplinaire taak en zich wenden tot andere beroepskrachten voor alle handelingen die zijn bevoegdheid overschrijden;5. deelnemen aan de opleidingen die voor hem worden georganiseerd.ProfielKennis:- ofwel een diploma van kinderverzorger;- ofwel een opleiding die toegang geeft tot de uitoefening van het beroep van gezinshelper op voorwaarde dat hij/zij een specifieke voortgezette opleiding heeft gevolgd voor de opvang van zieke kinderen.Capaciteiten :- blijk geven van zin voor openheid en samenwerken in ploegverband, analyse van situaties en terugschakelen naar de diensten;- blijk geven van bekwaamheid om een relatie op te bouwen met de zieke kinderen en zich ermee bezig te houden;- blijk geven van een vermogen tot educatieve omkadering;- blijk geven van bekwaamheid om mee te werken met de omgeving.StatuutBediendeDerde categorie- Maatschappelijk assistentWerknemer van wie de functie bestaat in de omkadering en de organisatie van de voortgezette opleiding van de gezins- en bejaardenhelpers en/of andere zorgaanbieders en in de begeleiding van de rechthebbenden.Vereiste diploma's : sociaal assistent, gegradueerd sociaal verpleegkundige.StatuutBediendeVierde categorie- Sociaal personeel houder van een licentie vereist bij de indienstnemingSociaal werknemer houder van een diploma uitgereikt door een school van het hoger onderwijs van het lange type (universiteit) en voor wie het bezit van deze titel vereist is bij de indienstneming.Voorbeelden : psycholoog, socioloog,...StatuutBediendeHOOFDSTUK II. - Loonschalen - omzettingBijlagen : loonschaaltabellen van januari 2022Art. 7.  § 1. Een loonschaalverhoging is van toepassing op 1 januari 2022, overeenkomstig bijlage 1. Deze past in het kader van een traject voor herwaardering van de loonschalen, dat deel uitmaakt van het budgettair traject van de NPA 2021-2024; overeenkomstig het protocolakkoord van de sociale partners dat werd ondertekend op 20 december 2021 (cfr. bijlage 2). § 2. De omzetting naar de referentieloonschalen gebeurt volgens de volgende tabellen :Technisch personeel  </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de Vlaamse welzijns- en gezondheidssector;Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 3 februari 2025, gesloten in het Paritair Comité voor de Vlaamse welzijns- en gezondheidssector, tot vaststelling van het percentage van de bijdragen voor het jaar 2025 voor het fonds voor bestaanszekerheid genaamd "Sociaal Fonds 331 tot financiering tweede pensioenpijler" en tot bepaling van de datum van aanvraag tot vrijstelling van de bijdragen voor het jaar 2025. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 11 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de Vlaamse welzijns- en gezondheidssector Collectieve arbeidsovereenkomst van 3 februari 2025 Vaststelling van het percentage van de bijdragen voor het jaar 2025 voor het fonds voor bestaanszekerheid genaamd "Sociaal Fonds 331 tot financiering tweede pensioenpijler" en bepaling van de datum van aanvraag tot vrijstelling van de bijdragen voor het jaar 2025 (Overeenkomst geregistreerd op 17 februari 2025 onder het nummer 192125/CO/331) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de werknemers die ressorteren onder het Paritair Comité voor de Vlaamse welzijns- en gezondheidssector. Onder "werknemers" wordt verstaan : het vrouwelijk en mannelijk werklieden- en bediendepersoneel. Art. 2. In toepassing van artikel 7 van de collectieve arbeidsovereenkomst van 7 februari 2011 tot wijziging van de statuten en de benaming van het fonds voor bestaanszekerheid genaamd "Sociaal Fonds 331 tot aanvullende financiering tweede pensioenpijler", gesloten in het Paritair Comité voor de Vlaamse welzijns- en gezondheidssector (registratienummer 103527/CO/331, algemeen verbindend verklaard bij koninklijk besluit op 4 oktober 2011, gepubliceerd in het Belgisch Staatsblad op 8 december 2011), wordt het percentage van de bijdragen voor het jaar 2025 op jaarbasis bepaald als volgt : per kwartaal 0,22 pct. van het brutobedrag van de bezoldigingen, vóór inhouding van de persoonlijke socialezekerheidsbijdragen. De inning van deze bijdragen geschiedt voor het jaar 2025 als volgt : - geen inning in het eerste en het tweede kwartaal; - 0,44 pct. van het brutobedrag van de bezoldigingen, vóór inhouding van de persoonlijke sociale zekerheidsbijdragen, tijdens het derde en het vierde kwartaal. Art. 3. Er werd geen bepaling meer voorzien in uitvoering van de opting-out waarvan sprake in artikel 7 van de hogervermelde collectieve arbeidsovereenkomst omdat deze opting-out in voorgaande jaren al zonder voorwerp is geworden. Art. 4. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van de datum van ondertekening en is gesloten voor onbepaalde tijd. Zij kan worden opgezegd door elk van de partijen, mits een opzeggingstermijn van zes maanden, gericht bij een ter post aangetekend schrijven aan de voorzitter van het Paritair Comité voor de Vlaamse welzijns- en gezondheidssector. Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025. De Minister van Werk, D. CLARINVAL 
+</t>
         </is>
       </c>
     </row>
@@ -2015,28 +2015,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2025200284</t>
+          <t>2025003001</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>08 mei 2025</t>
+          <t>28 mei 2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>13 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 29 november 2024, gesloten in het Paritair Comité voor het vermakelijkheidsbedrijf, betreffende de eindejaarspremie (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 3 maart 2025, gesloten in het Paritair Comité voor het verzekeringswezen, betreffende de besteding en het gebruik van de responsabiliseringsbijdrage van de werkgevers inzake invaliditeit (1)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-08&amp;numac_search=2025200284&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200284=49&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025003001&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003001=49&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het vermakelijkheidsbedrijf; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 29 november 2024, gesloten in het Paritair Comité voor het vermakelijkheidsbedrijf, betreffende de eindejaarspremie. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor het vermakelijkheidsbedrijf Collectieve arbeidsovereenkomst van 29 november 2024 Eindejaarspremie (Overeenkomst geregistreerd op 20 december 2024 onder het nummer 191181/CO/304) HOOFDSTUK I. - Voorwerp Artikel 1. Onderstaande collectieve arbeidsovereenkomst vervangt vanaf 1 januari 2024 de collectieve arbeidsovereenkomst van 24 oktober 2023 (registratienummer 184299/CO/304). HOOFDSTUK II. - Toepassingsgebied Art. 2. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de werknemers van de organisaties of instellingen die ressorteren onder het Paritair Comité voor het vermakelijkheidsbedrijf en die aan één van de volgende voorwaarden voldoen : - een rechtspersoon met maatschappelijke zetel in het Vlaamse Gewest; - een rechtspersoon met maatschappelijke zetel in het Brusselse Hoofdstedelijk Gewest en ingeschreven bij de Rijksdienst voor Sociale Zekerheid op de Nederlandse taalrol. Daarnaast moet de werknemer in de referteperiode tewerkgesteld zijn bij een werkgever die gesubsidieerd wordt door de Vlaamse overheid op basis van één van de volgende decreten en/of reglementeringen : - kunstendecreet; - de nominatim in programma H Beleidsdomein CJSM van de begroting van de Vlaamse overheid ingeschreven organisaties; - het circusdecreet; - het decreet vernieuwd jeugd- en kinderrechtenbeleid; - het decreet bovenlokale cultuurwerking; - het decreet bovenlokaal jeugdwerk, jeugdhuizen en jeugdwerk voor bijzondere doelgroepen;- het decreet houdende flankerende en stimulerende maatregelen ter bevordering van de participatie in cultuur, jeugdwerk en sport (participatiedecreet); - het reglement publiekswerking van het Vlaams Audiovisueel Fonds voor organisaties met internationale uitstraling of structurele werkingen; - organisaties die structurele subsidies ontvangen van Literatuur Vlaanderen. Met uitzondering van de subsidies van het Vlaams Audiovisueel Fonds en Literatuur Vlaanderen vallen zowel structurele als projectmatige subsidies onder het toepassingsgebied. Art. 3. Deze collectieve arbeidsovereenkomst wordt gesloten ter uitvoering van het Vlaams Intersectoraal Akkoord voor de kunstensector (VIA 3 van 4 juni 2021) met betrekking tot een eindejaarspremie en dit binnen het financieel kader dat de Vlaamse overheid in het kader van VIA 3 en de voorgaande VIA akkoorden hiervoor voorziet. HOOFDSTUK III. - Doel en budget Art. 4. In het kader van het VIA 3 en voortbouwend op de voorgaande VIA akkoorden wordt door de Vlaamse overheid vanaf 1 januari 2021 een jaarlijks budget ter beschikking gesteld van de kunstensector, in casu van het "Sociaal Fonds voor de podiumkunsten" (SFP), als tegemoetkoming voor de toekenning van een eindejaarspremie. Voor de tewerkstellingsperiodes van minder dan 4 maanden wordt de eindejaarspremie uitbetaald door het "Sociaal Fonds voor de podiumkunsten", met als referteperiode het voorbije seizoen. Voor de tewerkstellingsperiodes van 4 maanden of langer wordt de eindejaarspremie uitbetaald door de werkgever, met als referteperiode het lopende kalenderjaar. De werkgever ontvangt hiervoor een tussenkomst van het "Sociaal Fonds voor de podiumkunsten". Onder "tewerkstellingsperiode korter dan 4 maanden" wordt verstaan : elke aaneengesloten periode van tewerkstelling waarvoor een arbeidsovereenkomst is afgesloten waarvan de duur korter is dan 4 maanden. Opeenvolgende arbeidsovereenkomsten die mekaar zonder onderbreking opvolgen en waarvan de gezamenlijke duur korter is dan 4 maanden, worden eveneens beschouwd als tewerkstellingsperiodes korter dan 4 maanden. Onder "tewerkstellingsperiode van 4 maanden of langer" wordt verstaan : elke aaneengesloten periode van tewerkstelling waarvoor een arbeidsovereenkomst van 4 maanden of langer werd afgesloten. Opeenvolgende arbeidsovereenkomsten waarvan de gezamenlijke duur 4 maanden of meer bedraagt en die mekaar zonder onderbreking opvolgen worden eveneens beschouwd als tewerkstellingsperiodes van 4 maanden of langer. De werkgever verschaft aan het "Sociaal Fonds voor de podiumkunsten", op eenvoudig verzoek, alle informatie nodig voor de uitbetaling van de eindejaarspremies aan de werknemers en/of voor de uitbetaling van de tussenkomst aan de werkgevers. Deze collectieve arbeidsovereenkomst bepaalt welke principes en toekenningsvoorwaarden gelden voor de eindejaarspremie. HOOFDSTUK IV. - Modaliteiten en toekenningsvoorwaarden Art. 5. Er wordt aan de werknemers een eindejaarspremie toegekend. De betaling van de premie gebeurt jaarlijks in de loop van de maand december. Wanneer een werknemer, die 4 maanden of langer is tewerkgesteld, uit dienst treedt, is de verschuldigde eindejaarspremie betaalbaar bij de uitdiensttreding. Wanneer op het einde van het jaar de periode van minstens vier maanden nog niet is verlopen bij arbeidsovereenkomsten van vier maanden of meer, wordt de eindejaarspremie die betrekking heeft op de prestaties in het lopende jaar door de werkgever in december uitbetaald. De eindejaarspremie die betrekking heeft op het daaropvolgende jaar wordt door de werkgever betaald bij het einde van de arbeidsovereenkomst. De eindejaarspremie is niet verplicht voor jobstudenten (werknemerscode 840 en 841) en bij flexi-jobs (werknemerscode 050 en 450). Art. 6.  § 1. Aan de werknemers wordt een eindejaarspremie uitbetaald overeenkomstig de gewerkte dagen in de referteperiode. Voor de tewerkstellingsperiodes van minder dan 4 maanden, loopt de referteperiode van 1 juli van het voorafgaande tot en met 30 juni van het lopende kalenderjaar. Voor de tewerkstellingsperiodes van 4 maanden en meer, loopt de referteperiode van 1 januari tot en met 31 december van het lopende kalenderjaar.Een volledig gewerkte referteperiode komt dus overeen met een volledige eindejaarspremie, een onvolledige referteperiode of deeltijdse arbeid met een onvolledige eindejaarspremie, en dit in verhouding tot de gewerkte dagen in de referteperiode.  § 2. De inactiviteitsperiodes, vastgelegd bij koninklijk besluit van 30 maart 1967 tot bepaling van de algemene uitvoeringsbesluiten van de wetten betreffende de jaarlijkse vakantie der loonarbeiders, worden gelijkgesteld met gewerkte of als dusdanig beschouwde dagen. De dagen tijdelijke werkloosheid wegens overmacht door corona en energie worden eveneens gelijkgesteld met gewerkte of als dusdanig beschouwde dagen. Onbetaald verlof, alle wettelijke vormen van tijdskrediet en thematische verloven worden niet gelijkgesteld met gewerkte periodes voor de toekenning van de eindejaarspremie, behoudens palliatief verlof en verlof voor verzorging van een zwaar ziek gezins- of familielid, die worden gelijkgesteld met gewerkte periodes voor een maximumperiode van drie kalendermaanden. Art. 7. De eindejaarspremie in het kader van het VIA akkoord wordt vanaf 1 januari 2024 vastgesteld, voor elke voltijds tewerkgestelde werknemer, op minimaal 1 682 EUR bruto. Wanneer bij verhoging het bedrag van een volledige dertiende maand wordt overschreden of wanneer reeds een volledige dertiende maand wordt betaald, mag de eindejaarspremie beperkt worden tot het bedrag van de dertiende maand. Bij een onvolledige of deeltijdse tewerkstelling wordt de verschuldigde eindejaarspremie pro rata berekend. HOOFDSTUK V. - Uitvoering van deze collectieve arbeidsovereenkomst Art. 8.  § 1. Het SFP wordt belast met de berekening en de betaling van de eindejaarspremie voor de tewerkstellingsperiodes van minder dan 4 maanden, de werkgever voor de tewerkstellingsperiodes van 4 maanden of meer.  § 2. Het SFP zal bij de verwerking van de gegevens die nodig zijn voor de toepassing van deze collectieve arbeidsovereenkomst alle informatie met betrekking tot individuele werknemers beschermen en op geen enkele manier aan derden of sociale partners meedelen. De medewerkers van het SFP die met deze gegevens in aanraking komen, zullen een verklaring moeten ondertekenen die dit engagement betreffende de privacy bevestigt. Art. 9. Wanneer het SFP of de werkgever geconfronteerd worden met interpretatieve vragen waarvoor deze collectieve arbeidsovereenkomst geen oplossing biedt, moet het advies ingewonnen worden van een paritair samengestelde sectorale commissie bestaande uit 3 vertegenwoordigers van de werknemersafgevaardigden en 3 vertegenwoordigers van de werkgeversafgevaardigden. In geval van onenigheid binnen deze commissie wordt aan de voorzitter van het paritair comité gevraagd om te bemiddelen. Het advies van deze commissie is bindend voor het SFP of de werkgever. HOOFDSTUK VI. - Gelijkwaardig voordeel en rapporiering Art. 10. De werkgever die vóór uitvoering van VIA 1 een eindejaarspremie betaalde en waar sinds de invoering van VIA 1 een gelijkwaardig voordeel werd overeengekomen in de vorm van behoud van koopkracht, verhoging van de koopkracht of behoud van tewerkstelling, kan het gelijkwaardig voordeel enkel afschaffen of aanpassen in overleg met de vakbondsafgevaardigden binnen de onderneming of met de vakbondssecretarissen van de erkende vakbonden indien er geen wettelijk overlegorgaan (Ondernemingsraad, comité voor preventie en bescherming op het werk, vakbondsafvaardiging) voorzien is. Art. 11. Waar een eindejaarspremie wordt toegekend in de vorm van een dertiende maand, licht de werkgever de werknemers toe hoe hij/zij het hem/haar toegekende bedrag vanuit het VIA besteedt aan een hetzij evenredige koopkrachtverhoging en/of ander voordeel, hetzij behoud van koopkracht, hetzij behoud of verhogen van de tewerkstelling. Op de plaatsen waar dit wettelijk voorzien is (conform artikel 30 van het koninklijk besluit van 27 november 1973), gebeurt deze bespreking in de overlegorganen zoals de ondernemingsraad of het comité voor preventie en bescherming op het werk. Art. 12. De werkgevers rapporteren het SFP uiterlijk op 31 januari van het daaropvolgende jaar over de uitbetaalde ondernemingspremies. De werkgever bezorgt het SFP een nominatieve lijst met per werknemer gegevens over het brutobedrag van de eindejaarspremie en de socialezekerheidsbijdragen. HOOFDSTUK VII. - Slotbepalingen Art. 13. Deze collectieve arbeidsovereenkomst bevat sectorale minimumafspraken. Afwijkingen op ondernemingsvlak zijn niet mogelijk tenzij na overleg en akkoord op ondernemingsvlak tussen de werkgever en de representatieve vakbonden. Art. 14. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang op 1 januari 2024 en wordt gesloten voor onbepaalde duur. Ze wordt uitgevoerd op voorwaarde van een effectieve terbeschikkingstelling van de financiële middelen waarin krachtens de VIA-akkoorden is voorzien. Art. 15. Deze collectieve arbeidsovereenkomst kan opgezegd worden door elk van de partijen met een opzeggingstermijn van zes maanden, gericht bij een ter post aangetekend schrijven aan de voorzitter van het Paritair Comité voor het vermakelijkheidsbedrijf. Gezien om te worden gevoegd bij het koninklijk besluit van 13 april 2025. De Minister van Werk, D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor het verzekeringswezen;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 3 maart 2025, gesloten in het Paritair Comité voor het verzekeringswezen, betreffende de besteding en het gebruik van de responsabiliseringsbijdrage van de werkgevers inzake invaliditeit.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het verzekeringswezenCollectieve arbeidsovereenkomst van 3 maart 2025Besteding en het gebruik van de responsabiliseringsbijdrage van de werkgevers inzake invaliditeit (Overeenkomst geregistreerd op 13 maart 2025 onder het nummer 192571/CO/306)Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de werknemers van de ondernemingen die ressorteren onder het Paritair Comité voor het verzekeringswezen.Art. 2. Deze overeenkomst wordt gesloten met toepassing van artikel 147, § 2 van de programmawet van 27 december 2021.Art. 3. FOPAS1 wordt door het paritair comité aangewezen als ontvanger van de opbrengsten die de RSZ stort zoals geregeld door artikel 147 van de programmawet van 27 december 2021 en hoofdstuk 2 van het koninklijk besluit van 1 oktober 2023 tot uitvoering van artikel 147, § 4 en § 5 van de programmawet van 27 december 2021 betreffende de responsabiliseringsbijdrage.Art. 4. FOPAS wordt belast met de toekenning en het gebruik van de gelden bestemd voor preventieve maatregelen inzake gezondheid en veiligheid op het werk en/of maatregelen inzake duurzame herinschakeling van langdurig zieken.Art. 5. De maatregelen van FOPAS inzake preventie en/of herinschakeling zijn :- Sensibiliseringsacties inzake psychosociale risico's;- De financiering van pilootprojecten in verband met herinschakeling;- Preventieve informatieprogramma's;- De verspreiding van preventieprogramma's (bijvoorbeeld : FEDRIS,...),...Art. 6. Deze collectieve arbeidsovereenkomst treedt in werking op de dag van ondertekening en wordt voor onbepaalde duur gesloten.Elke ondertekenende partij kan deze collectieve arbeidsovereenkomst opzeggen met inachtneming van een opzeggingstermijn van drie maanden.Die opzegging moet, aangetekend per post, aan de voorzitter van het Paritair Comité voor het verzekeringswezen worden gericht.Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025.De Minister van Werk,D. CLARINVAL_______Nota(1) Het fonds voor bestaanszekerheid waarin is voorzien door de collectieve arbeidsovereenkomst van 30 juni 2022, geregistreerd onder het nr. 175796, tot vaststelling van de statuten van FOPAS, het "Fonds voor de bevordering van de werkgelegenheid en de opleiding in de verzekeringssector". 
 </t>
         </is>
       </c>
@@ -2047,28 +2047,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2025000770</t>
+          <t>2025000764</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>08 mei 2025</t>
+          <t>30 mei 2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 13 juni 2024, gesloten in het Aanvullend Paritair Comité voor de bedienden, tot invoering van een sectoraal aanvullend pensioenstelsel voor de Bedienden Ondernemingsactiviteit Edele Metalen ("SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen") (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 19 november 2024, gesloten in het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren, betreffende de pensioenpremie voor de uitzendkrachten (1)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-08&amp;numac_search=2025000770&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025000770=50&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-30&amp;numac_search=2025000764&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025000764=50&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Aanvullend Paritair Comité voor de bedienden;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 13 juni 2024, gesloten in het Aanvullend Paritair Comité voor de bedienden, tot invoering van een sectoraal aanvullend pensioenstelsel voor de Bedienden Ondernemingsactiviteit Edele Metalen ("SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen").Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 13 april 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageAanvullend Paritair Comité voor de bediendenCollectieve arbeidsovereenkomst van 13 juni 2024Invoering van een sectoraal aanvullend pensioenstelsel voor de Bedienden Ondernemingsactiviteit Edele Metalen ("SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen") (Overeenkomst geregistreerd op 2 september 2024 onder het nummer 189433/CO/200)HOOFDSTUK I. - BegripsomschrijvingenArtikel 1. Voor de toepassing van deze collectieve arbeidsovereenkomst en haar bijlagen, moeten de hierna vermelde begrippen als volgt worden begrepen :- Arbeiders Ondernemingsactiviteit Edele Metalen : de arbeiders die ressorteren onder PSC 149.03;- Bedienden Ondernemingsactiviteit Edele Metalen : de bedienden die ressorteren onder PC 200 en werkzaam zijn in de Ondernemingsactiviteit Edele Metalen en zich in een vergelijkbare situatie bevinden als de Arbeiders Ondernemingsactiviteit Edele Metalen met wie zij voor doeldoeleinden van het aanvullend pensioen "spiegelen" in de zin van artikel 14 van de WAP. Zij worden overeenkomstig de regels van deze collectieve arbeidsovereenkomst toegewezen aan deze specifieke subcategorie;- Cao van PC 200 van 1 juli 2019 : de collectieve arbeidsovereenkomst van 1 juli 2019 gesloten in PC 200 betreffende de koopkracht in het kader van het koninklijk besluit van 19 april 2019 tot uitvoering van artikel 7, §  1 van de wet van 26 juli 1996 tot bevordering van de werkgelegenheid en tot preventieve vrijwaring van het concurrentievermogen met registratienummer 152849/CO/200, zoals gewijzigd inzake de termijnen door de collectieve arbeidsovereenkomst van 18 november 2021 gesloten in het PC 200 met registratienummer 168827/CO/200;- Harmonisatieverplichting : de wettelijke verplichting tot harmonisering van de aanvullende pensioenen voor arbeiders en bedienden in de zin van de WAP;- Hoofdzakelijkheidscriterium : in situaties waar Werkgevers ressorteren onder meerdere paritaire (sub)comités voor hun arbeiders houdt het hoofdzakelijkheidscriterium in dat de PC 200 Bedienden moeten vergeleken worden met hun collega arbeiders die werken in de hoofdactiviteit van de Werkgever. De hoofdactiviteit wordt voor doeleinden van artikel 14 van de WAP bepaald als de Ondernemingsactiviteit waar de Werkgever het grootst aantal arbeiders tewerkstelt, uitgedrukt in voltijds equivalente arbeiders. De hoofdactiviteit wordt bepaald aan de hand van de officiële sociale documenten waarbij gebruik gemaakt wordt van de kerngetallen en RSZ-identificatienummers;- Inrichter : de multi-sectorale inrichter, Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Edele Metalen (FBZ SAP Ondernemingsactiviteit Edele Metalen), met zetel te 1120 Brussel, Marlylaan 15/8, die optreedt als inrichter van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen en als inrichter van het SAP PSC 149.03 Arbeiders Ondernemingsactiviteit Edele Metalen voor de arbeiders waarmee de Bedienden Ondernemingsactiviteit Edele Metalen "spiegelen" in de zin van artikel 14 van de WAP;- Ondernemingsactiviteit (OA) : de beroepscategorieën en ondernemingsactiviteiten zoals bedoeld in artikel 14/4, § 1, eerste lid van de WAP;- Ondernemingsactiviteit Edele Metalen : de ondernemingsactiviteiten waarvoor het PSC 149.03 bevoegd is en die vallen onder het bevoegdheidsgebied van PSC 149.03 zoals vastgesteld in koninklijk besluit van 13 maart 1985 tot oprichting en tot vaststelling van de benaming en van de bevoegdheid van paritaire subcomités voor de sectoren die aan de metaal-, machine- en elektrische bouw verwant zijn en tot vaststelling van het aantal leden ervan, zoals laatst gewijzigd door het koninklijk besluit van 24 oktober 2012;- PSC 149.03 : het Paritair Subcomité voor de edele metalen;- PC 200 : het Aanvullend Paritair Comité voor de bedienden;- PC 200 Bedienden : de bedienden die vallen onder de bevoegdheid van PC 200;- SAP PSC 149.03 Arbeiders Ondernemingsactiviteit Edele Metalen : het sectoraal aanvullend pensioenstelsel per 1 januari 2015 ingevoerd door PSC 149.03 voor de arbeiders werkzaam in PSC 149.03, zijnde de Arbeiders Ondernemingsactiviteit Edele Metalen;- SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen : het sectoraal aanvullend pensioenstelsel, dat door PC 200 wordt ingevoerd - in overeenstemming met de collectieve arbeidsovereenkomst van 1 juli 2019 - voor de Bedienden Ondernemingsactiviteit Edele Metalen en dat in het kader van de Harmonisatieverplichting de gelijke behandeling beoogt inzake aanvullende pensioenen op sectorniveau tussen de Bedienden Ondernemingsactiviteit Edele Metalen en de Arbeiders Ondernemingsactiviteit Edele Metalen met wie zij "spiegelen" in de zin van artikel 14 van de WAP;- Technische bedrijfseenheid : de technische bedrijfseenheid zoals omschreven in artikel 14 van de wet van 20 september 1948 houdende organisatie van het bedrijfsleven;- Vestigingseenheid : een plaats die men, geografisch gezien, kan identificeren door een adres waar ten minste één activiteit van de in de Kruispuntbank van Ondernemingen geregistreerde juridische entiteit wordt uitgeoefend of van waaruit de activiteit wordt uitgeoefend in de zin van artikel I.2., 16°  van boek I van het Wetboek van Economisch recht. Dit komt neer op elke geografisch afgescheiden exploitatiezetel, afdeling of onderafdeling (atelier, fabriek, magazijn, bureau,...) van de betrokken juridische entiteit (op basis van het ondernemingsnummer), gesitueerd op een geografisch welbepaalde locatie en identificeerbaar met een adres en met een vestigingseenheidsnummer;- WAP : de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid, waarin het wettelijk kader inzake de harmonisatie van de aanvullende pensioenen voor arbeiders en bedienden werd ingeschreven door de wet van 5 mei 2014 tot wijziging van het rustpensioen en het overlevingspensioen en tot invoering van de overgangsuitkering in de pensioenregeling voor werknemers en houdende geleidelijke opheffing van de verschillen in behandeling die berusten op het onderscheid tussen werklieden en bedienden inzake aanvullende pensioenen en werd gewijzigd door de wet van 12 december 2021 tot uitvoering van het sociaal akkoord in het kader van de interprofessionele onderhandelingen voor de periode 2021-2022;- WIBP : de wet van 27 oktober 2006 betreffende het toezicht op de instellingen bedrijfspensioenvoorziening;- Werkgever : de juridische entiteit (op basis van het ondernemingsnummer), of desgevallend de Vestigingseenheden (op basis van het vestigingseenheidsnummer) indien de juridische entiteit over meerdere Vestigingseenheden beschikt.HOOFDSTUK II. - ToepassingsgebiedArt. 2.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de Werkgevers die ressorteren onder PC 200, alsook de PC 200 Bedienden die deze Werkgevers tewerkstellen, op voorwaarde dat :- de betrokken Werkgever voor alle of een deel van de arbeiders die hij tewerkstelt, valt onder de bevoegdheid van PSC 149.03;- de PC 200 Bedienden volledig of deels tewerkgesteld zijn in de Ondernemingsactiviteit Edele Metalen; en- de PC 200 Bedienden door de betrokken Werkgever tewerkgesteld worden in een Technische Bedrijfseenheid waarin deze Werkgever ook arbeiders tewerkstelt waarvoor hij valt onder de bevoegdheid van PSC 149.03. § 2. De vaststelling of, en welk deel van, de PC 200 Bedienden moeten beschouwd worden als Bedienden Ondernemingsactiviteit Edele Metalen gebeurt op basis van de regels bepaald in artikel 2, § 3 en § 4 van deze collectieve arbeidsovereenkomst.De Bedienden Ondernemingsactiviteit Edele Metalen worden vanaf 1 juli 2025 door de betrokken Werkgever of zijn sociaal secretariaat aangegeven in de DmfA onder het RSZ-werkgeverskengetal 078. § 3. Indien de Werkgever voor al zijn arbeiders ressorteert onder PSC 149.03, dan worden de PC 200 Bedienden die de Werkgever tewerkstelt in de Ondernemingsactiviteit Edele Metalen beschouwd als Bedienden Ondernemingsactiviteit Edele Metalen. § 4. Indien de Werkgever :- voor een deel van de arbeiders die hij tewerkstelt in de betrokken Technische Bedrijfseenheid, ressorteert onder PSC 149.03 én voor andere arbeiders ressorteert onder de bevoegdheid van één of meerdere andere paritaire (sub)comités voor arbeiders; en- de PC 200 Bedienden die hij tewerkstelt in de betrokken Technische Bedrijfseenheid op basis van de feitelijke omstandigheden niet kan toewijzen aan een van de specifieke Ondernemingsactiviteiten waarvoor één van de betrokken paritaire (sub)comités voor arbeiders bevoegd is, aangezien deze PC 200 Bedienden ondersteunende of overkoepelende taken uitvoeren ten aanzien van meerdere Ondernemingsactiviteiten en/of niet-occasioneel en niet-uitzonderlijk werkzaam zijn in meerdere Ondernemingsactiviteiten van de Werkgever;gelden de volgende regels om te bepalen welke PC 200 Bedienden moeten worden beschouwd als Bedienden Ondernemingsactiviteit Edele Metalen :(a) De Werkgever moet vaststellen of de PC 200 Bedienden in de betrokken Technische Bedrijfseenheid toegewezen worden aan de Ondernemingsactiviteit Edele Metalen of aan de Ondernemingsactiviteit(en) die behoren tot het bevoegdheidsgebied van één van de andere paritaire (sub)comités voor arbeiders (overeenkomstig het toepasselijk koninklijk besluit dat de bevoegdheid van dit paritair comité heeft vastgesteld), waaronder de Werkgever voor een deel van zijn arbeiders ressorteert.De Werkgever doet deze vaststelling eenmalig ("foto") volgens de modaliteiten vastgelegd in deze collectieve arbeidsovereenkomst, hetzij (i) naar aanleiding van de inwerkingtreding van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen op 1 juli 2025 (op basis van de DmfA-gegevens van het eerste kwartaal van 2022, zoals beschikbaar op 30 juni 2022), hetzij (ii) nadien op het moment dat de Werkgever voor het eerst ook ressorteert onder PSC 149.03 voor een deel van zijn arbeiders (op basis van de DmfA-gegevens op het einde van het eerste kwartaal dat de Werkgever ook onder PSC 149.03 ressorteert voor een deel van zijn arbeiders), hetzij (iii) nadien op het moment dat de Werkgever voor een deel van zijn arbeiders naast PSC 149.03 ook ressorteert onder een ander paritair (sub)comité dan PSC 149.03 (op basis van de DmfA-gegevens op het einde van het eerste kwartaal dat de Werkgever ook onder een ander paritair (sub)comité dan PSC 149.03 ressorteert voor een deel van zijn arbeiders) en wijzigt niet meer nadien behoudens in de uitzonderlijke situatie zoals vastgelegd hierna in (c);(b) Deze vaststelling gebeurt op basis van het Hoofdzakelijkheidscriterium, in dit kader uitgedrukt op basis van het aantal arbeiders in voltijdsequivalent of FTE, dat de Werkgever tewerkstelt in de betrokken Technische Bedrijfseenheid ("foto" vastgesteld op basis van de DmfA-gegevens van het eerste kwartaal van 2022, zoals beschikbaar op 30 juni 2022, op het einde van het eerste kwartaal dat de Werkgever ook onder PSC 149.03 ressorteert voor een deel van zijn arbeiders of op het einde van het eerste kwartaal dat de Werkgever ook onder een ander paritair (sub)comité dan PSC 149.03 ressorteert voor een deel van zijn arbeiders) :- Indien de Werkgever arbeiders tewerkstelt die ressorteren onder meerdere paritaire (sub)comités voor arbeiders, dan worden de PC 200 Bedienden in de betrokken Technische Bedrijfseenheid, die ondersteunende of overkoepelende taken uitvoeren ten aanzien van meerdere Ondernemingsactiviteiten en/of niet-occasioneel en niet-uitzonderlijk werkzaam zijn in meerdere Ondernemingsactiviteiten van de Werkgever, beschouwd als Bedienden Ondernemingsactiviteit Edele Metalen indien het hoogste aantal arbeiders van de Werkgever ressorteren onder PSC 149.03;- Indien de Werkgever op de in punt (a) en (b) vastgestelde datum een gelijk aantal arbeiders tewerkstelt in de verschillende paritaire (sub)comités voor arbeiders waaronder hij ressorteert en het Hoofdzakelijkheidscriterium geen antwoord biedt, dan worden de PC 200 Bedienden in de betrokken Technische Bedrijfseenheid die ondersteunende of overkoepelende taken uitvoeren ten aanzien van meerdere Ondernemingsactiviteiten en/of niet-occasioneel en niet-uitzonderlijk werkzaam zijn in meerdere Ondernemingsactiviteiten van de Werkgever, beschouwd als Bedienden Ondernemingsactiviteit Edele Metalen wanneer gemiddeld gedurende acht RSZ kwartalen (dit is gedurende het eerste kwartaal van 2022 en de zeven daaraan voorafgaande RSZ kwartalen) (= de referentieperiode of "film") het hoogste aantal arbeiders (uitgedrukt in voltijdsequivalent of FTE) van de Werkgever ressorteert onder PSC 149.03. Indien er geen acht RSZ kwartalen zijn, wordt het lager aantal beschikbare RSZ kwartalen (dit is het eerste kwartaal van 2022 en het lager aantal daaraan voorafgaande RSZ kwartalen) als referentieperiode of film genomen.Indien de Werkgever ook gedurende deze voormelde referentieperiode of film een gelijk aantal arbeiders tewerkstelt in de verschillende paritaire (sub)comités voor arbeiders waaronder hij ressorteert, dan worden de PC 200 Bedienden in de betrokken Technische Bedrijfseenheid die ondersteunende of overkoepelende taken uitvoeren ten aanzien van meerdere Ondernemingsactiviteiten en/of niet-occasioneel en niet-uitzonderlijk werkzaam zijn in meerdere Ondernemingsactiviteiten van de Werkgever, beschouwd als Bedienden Ondernemingsactiviteit Edele Metalen wanneer de Ondernemingsactiviteit Edele Metalen kan beschouwd worden als de hoofdactiviteit van de Werkgever op basis van de rangorde die gebruikt werd in de activiteiten die opgesomd worden in het maatschappelijk voorwerp, zoals vermeld in de statuten van de Werkgever;(c) Indien de PC 200 Bedienden op basis van de regels in (b) beschouwd worden als Bedienden Ondernemingsactiviteit Edele Metalen, maar de verhouding tussen de respectievelijke aantallen van arbeiders in de verschillende Ondernemingsactiviteiten nadien op een duurzame en significante wijze wijzigt, kan de Werkgever via een schriftelijk, gemotiveerd verzoek aan de Inrichter vragen dat zijn PC 200 Bedienden in de betrokken Technische Bedrijfseenheid niet langer beschouwd worden als Bedienden Ondernemingsactiviteit Edele Metalen. De Werkgever brengt hiervan de ondernemingsraad, of bij ontstentenis hiervan, het comité voor preventie en bescherming op het werk, of bij ontstentenis hiervan, de vakbondsafvaardiging op de hoogte.Hiertoe moet de Werkgever in zijn schriftelijk en gemotiveerd verzoek minstens de volgende gegevens opnemen :(i) de aantallen van arbeiders bepaald op het moment voorzien onder (b);(ii) de evolutie op kwartaalbasis van de aantallen van arbeiders bedoeld onder (b) sinds het moment voorzien onder (b), waaruit de duurzame en significante aard van de wijziging blijkt;(iii) aantonen op basis van de activiteiten van de Werkgever waarom deze wijziging zich ook in de toekomst verder zal bestendigen.Mits een voorafgaande discussie met de Werkgever, kan een gelijkaardig schriftelijk en gemotiveerd verzoek worden ingediend door de vertegenwoordigers van de werknemers in de ondernemingsraad, of bij ontstentenis hiervan, de vertegenwoordigers van de werknemers in het comité voor preventie en bescherming op het werk, of bij ontstentenis hiervan, de vakbondsafvaardiging. Dat verzoek moet dezelfde gegevens opnemen dan hierboven vermeld. De betrokken partij brengt de Werkgever hier onverwijld van op de hoogte.De Inrichter van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen beslist over dit verzoek binnen de twee maanden na ontvangst van alle hiervoor vermelde, benodigde gegevens. In geval van een positieve beslissing, zullen de PC 200 Bedienden van de betrokken Werkgever in de betrokken Technische Bedrijfseenheid vanaf het eerstvolgende kwartaal na deze positieve beslissing, niet langer beschouwd worden als Bedienden Ondernemingsactiviteit Edele Metalen (wat aanleiding geeft tot een uittreding uit het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen). De Werkgever zal de betrokken PC 200 Bedienden hierover inlichten. De Inrichter zal aan PC 200 één keer per jaar een overzicht overmaken van de Werkgevers die toepassing van dit artikel hebben gemaakt.Omgekeerd, indien de PC 200 Bedienden op basis van de regels in (b) niet beschouwd worden als Bedienden Ondernemingsactiviteit Edele Metalen, maar de verhouding tussen de respectievelijke aantallen van arbeiders in de verschillende Ondernemingsactiviteiten nadien op een duurzame en significante wijze wijzigt, kan de Werkgever zich wenden tot de inrichter van het sectoraal aanvullend pensioenstelsel van de andere (sub)sector waarbij zijn PC 200 Bedienden zijn aangesloten, om te vragen dat zijn PC 200 Bedienden in de betrokken Technische Bedrijfseenheid voortaan kunnen beschouwd worden als Bedienden Ondernemingsactiviteit Edele Metalen, waarna ze aangesloten worden aan het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen.HOOFDSTUK III. - Voorwerp - Invoering SAP PC 200 Bedienden Ondernemingsactiviteit Edele MetalenArt. 3.  § 1. De representatieve organisaties in het PC 200 hebben deze collectieve arbeidsovereenkomst gesloten ter uitvoering van de Harmonisatieverplichting en artikel 7, 1°,  (i) van de collectieve arbeidsovereenkomst van 1 juli 2019.Deze collectieve arbeidsovereenkomst heeft als enige voorwerp de invoering met ingang van 1 juli 2025 van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen.Voor de Bedienden Ondernemingsactiviteit Edele Metalen die vanaf 1 juli 2025 aangesloten worden bij het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen, stopt vanaf 1 juli 2025 de betaling van de tijdelijke jaarpremie bepaald in artikel 5 van de collectieve arbeidsovereenkomst van PC 200 van 1 juli 2019 aangezien het volledige budget van de tijdelijke jaarpremie wordt aangewend voor het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen. Voor 2025 zal nog het gedeelte van de tijdelijke jaarpremie voor de maanden januari tot en met juni uitbetaald worden, volgens de berekenings- en uitbetalingsregels vastgelegd in de cao van PC 200 van 1 juli 2019. § 2. Vanaf 1 januari 2027 zal het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen worden omgevormd tot een sociaal sectoraal pensioenstelsel waarbij 95,5 pct. van de nettobijdrage zal worden aangewend voor de financiering van de pensioentoezegging en 4,5 pct. voor de financiering van de solidariteitstoezegging.HOOFDSTUK IV. - Aansluiting aan het SAP PC 200 Bedienden Ondernemingsactiviteit Edele MetalenArt. 4.  § 1. Alle Bedienden Ondernemingsactiviteit Edele Metalen die op of na 1 juli 2025 verbonden zijn via een arbeidsovereenkomst met een Werkgever en die niet uitgesloten zijn uit het toepassingsgebied van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen overeenkomstig artikel 10 van deze collectieve arbeidsovereenkomst, worden aangesloten bij het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen. § 2. De hiervoor vermelde Bedienden Ondernemingsactiviteit Edele Metalen blijven aangesloten aan het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen tot aan hun uittreding, pensionering of overlijden.Bedienden Ondernemingsactiviteit Edele Metalen, die hun wettelijk (vervroegd) pensioen hebben opgenomen, maar verder of opnieuw tewerkgesteld worden met een arbeidsovereenkomst gesloten met een Werkgever, zoals bedoeld in artikel 4, § 1 in het kader van "toegelaten arbeid voor gepensioneerden", blijven niet aangesloten of worden niet aangesloten bij het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen, overeenkomstig artikel 13 van de WAP. § 3. Een uitzondering geldt voor de Bedienden Ondernemingsactiviteit Edele Metalen die gebruik hebben gemaakt, voorafgaand aan de invoering van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen van hun wettelijk weigeringsrecht overeenkomstig artikel 16, § 3 van de WAP, op voorwaarde dat het bestaand pensioenstelsel van de Werkgever zoals van toepassing onmiddellijk voorafgaand aan de invoering van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen en van toepassing op de Bedienden Ondernemingsactiviteit Edele Metalen, per 1 juli 2025 wordt vervangen door het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen in het kader van de Harmonisatieverplichting. De Bedienden Ondernemingsactiviteit Edele Metalen die in dit kader gebruik hebben gemaakt van dit weigeringsrecht worden niet aangesloten bij het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen, en dit zolang dit weigeringsrecht verdere toepassing heeft.De betrokken Werkgever moet hiertoe de procedure volgen zoals voorzien in artikel 6, § 2 van de Bijlage 2 bij deze collectieve arbeidsovereenkomst, ten gevolge waarvan de RSZ voor deze Bedienden Ondernemingsactiviteit Edele Metalen die gebruik hebben gemaakt van dit wettelijk weigeringsrecht, geen patronale bijdragen voor het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen innen, zolang dit weigeringsrecht verder van toepassing is. Vanaf het moment dat dit niet langer het geval is, wordt de betrokken Bediende Ondernemingsactiviteit Edele Metalen aangesloten bij het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen.HOOFDSTUK V. - Aanduiding van de InrichterArt. 5.  § 1. Het Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Edele Metalen (FBZ SAP Ondernemingsactiviteit Edele Metalen) waarvan de statuten zijn vastgelegd in de collectieve arbeidsovereenkomst van 13 juni 2024 tot oprichting van het Fonds voor Bestaanszekerheid Sectoraal Aanvullend Pensioen Ondernemingsactiviteit Edele Metalen (FBZ SAP Ondernemingsactiviteit Edele Metalen) dat optreedt als multi-sectorale inrichter van het sectoraal aanvullend pensioenstelsel voor de arbeiders en voor de bedienden in de Ondernemingsactiviteit Edele Metalen en tot vaststelling van de statuten van de multi-sectorale inrichter, wordt aangeduid als de Inrichter van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen (hierna : "Inrichter" of "FBZ SAP Ondernemingsactiviteit Edele Metalen"). § 2. Voor zover gewenst, kunnen de sociale partners van PC 200 Ondernemingsactiviteit Edele Metalen gezamenlijk met de sociale partners van PSC 149.03 de leden van de raad van bestuur van de Sectorale Inrichter aanduiden, overeenkomstig de modaliteiten bepaald in de statuten van de Sectorale Inrichter.HOOFDSTUK VI. - Pensioentoezegging - aanduiding van de pensioeninstellingArt. 6.  § 1. Het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen dat per 1 juli 2025 wordt ingevoerd is een gewoon sectoraal aanvullend pensioenstelsel, dat bestaat uit een pensioentoezegging dié is vastgelegd in het pensioenreglement (opgenomen in Bijlage 1 bij deze collectieve arbeidsovereenkomst). § 2. De pensioentoezegging is een pensioenstelsel van het type vaste bijdragen die voorziet :- in de opbouw van een aanvullend pensioen dat overeenkomstig de regels en modaliteiten van het pensioenreglement, zoals vastgelegd in Bijlage 1 bij deze collectieve arbeidsovereenkomst, wordt uitbetaald aan de aangesloten Bediende Ondernemingsactiviteit Edele Metalen op het moment van pensionering (in zoverre de betrokken bediende bij uittreden uit de sector zijn verworven pensioenreserves niet heeft overgedragen naar een andere pensioeninstelling);- in een overlijdenskapitaal in geval van overlijden van de aangesloten Bediende Ondernemingsactiviteit Edele Metalen voor pensionering, dat gelijk is aan de verworven reserves die de aangesloten bediende heeft opgebouwd in het sectoraal aanvullend pensioenstelsel tot op het moment van zijn overlijden en dat wordt uitbetaald aan de begunstigden van de overleden, aangesloten bediende overeenkomstig de regels en modaliteiten van het pensioenreglement (zoals vastgelegd in Bijlage 1 bij deze collectieve arbeidsovereenkomst). § 3. Het beheer en de uitvoering van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen wordt toevertrouwd aan Sefoplus OFP. Sefoplus OFP is een multi-sectorale instelling voor bedrijfspensioenvoorziening, vergund op 19 november 2018, met ondernemingsnummer 0715.441.019, FSMA-identificatienummer 50.624 en maatschappelijke zetel te Marlylaan 15/8, 1120 Brussel. Sefoplus OFP is met andere woorden aangeduid als pensioeninstelling.De pensioenverplichtingen en de activa verbonden aan het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen worden binnen Sefoplus OFP beheerd in een afgezonderd vermogen opgezet voor het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen ("Afzonderlijk Vermogen PC 200 Bedienden Ondernemingsactiviteit Edele Metalen") in de zin van artikel 2, 15°  van de WIBP. De beheers- en werkingsregels die worden afgesproken tussen de Inrichter en Sefoplus OFP als pensioeninstelling worden vastgelegd in de beheersovereenkomst en de toetredingsakte daartoe, alsook in een algemeen en specifiek luik bij de verklaring inzake de beleggingsbeginselen (SIP) en het financieringsplan van Sefoplus OFP.HOOFDSTUK VII. - Financiering, bijdragen en inningsmodaliteitenArt. 7.  § 1. De financiering van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen gebeurt via een patronale bijdrage. De totale jaarlijkse brutobijdrage is voor elke actieve aangeslotene bij het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen gelijk aan 1,10 pct. van het brutojaarloon waarop inhoudingen door de RSZ worden verricht. § 2. De totale jaarlijkse brutobijdrage per actieve aangeslotene bij het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen wordt verminderd met 4,5 pct. beheerskosten, aangerekend door de Inrichter, wat resulteert in een totale jaarlijkse nettopensioenbijdrage per actieve aangeslotene van 1,05 pct. van het brutojaarloon waarop inhoudingen door de RSZ worden verricht. § 3. Dit resulteert, na vermeerdering van de nettopensioenbijdrage met 0,09 pct. ter dekking van de verschuldigde, bijzondere RSZ-bijdrage van 8,86 pct., in een globale jaarlijkse brutobijdrage van 1,19 pct. voor elke actieve aangeslotene bij het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen. De bijzondere RSZ-bijdrage van 8,86 pct. wordt door de RSZ afgehouden aan de bron. De Werkgevers, die onder het toepassingsgebied vallen van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen, moeten deze niet apart berekenen en aangeven. § 4. De inning en de invordering van deze patronale bijdrage gebeurt door de Rijksdienst voor Sociale zekerheid (RSZ) via een gedifferentieerde inning, overeenkomstig de daartoe afgesloten beheersovereenkomst met de RSZ. § 5. Elke Werkgever die onder het toepassingsgebied van SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen valt, is gehouden tot de betaling van deze bijdrage.De Rijksdienst voor Sociale Zekerheid maakt de patronale bijdragen voor het sectoraal pensioenstelsel over aan de Inrichter. Vervolgens maakt de Inrichter de ontvangen patronale bijdragen over aan de pensioeninstelling waar deze worden ondergebracht in het Afzonderlijk Vermogen PC 200 Bedienden Ondernemingsactiviteit Edele Metalen.HOOFDSTUK VIII. - Uitbetaling van de voordelenArt. 8. De procedure, de modaliteiten en de vorm van de uitbetaling van de voordelen krachtens het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen worden beschreven in het bijgevoegde pensioenreglement (opgenomen als Bijlage 1 van deze collectieve arbeidsovereenkomst).HOOFDSTUK IX. - UittredingArt. 9. De procedure van uittreding uit het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen wordt geregeld overeenkomstig de bepalingen vermeld in het bijgevoegde pensioenreglement (opgenomen als Bijlage 1 bij deze collectieve arbeidsovereenkomst).HOOFDSTUK X. - Uitsluiting uit het toepassingsgebied van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen ("buiten toepassingsgebied") - geen mogelijkheid tot opting outArt. 10.  § 1. De Werkgevers die voor al hun Bedienden Ondernemingsactiviteit Edele Metalen in de betrokken Technische Bedrijfseenheid op 1 juli 2025 reeds voorzien in één of meerdere aanvullende pensioenstelsels op ondernemingsniveau die minstens gelijkwaardig zijn aan het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen, worden uitgesloten uit het toepassingsgebied van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen, overeenkomstig de regels zoals vastgelegd in Bijlage 2 bij deze collectieve arbeidsovereenkomst.Daarnaast kunnen Werkgevers, die op of na 1 juli 2025 worden opgericht of pas vanaf of na 1 juli 2025 ten gevolge van gewijzigde omstandigheden (zoals onder meer een fusie, een splitsing, een overname of een andere transactie, een wijziging van paritair comité, een wijziging van activiteiten,...) hetzij (i) voor het eerst ressorteren onder PC 200 voor hun Bedienden Ondernemingsactiviteit Edele Metalen, hetzij (ii) voor het eerst Bedienden Ondernemingsactiviteit Edele Metalen tewerkstellen, hetzij (iii) voor het eerst ressorteren onder PSC 149.03 voor (een deel van) hun arbeiders, ook worden uitgesloten uit het toepassingsgebied van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen, op voorwaarde dat zij aantonen dat zij op dat moment voor al hun Bedienden Ondernemingsactiviteit Edele Metalen in de betrokken Technische Bedrijfseenheid voorzien in een of meerdere aanvullende pensioenstelsels op ondernemingsniveau die minstens gelijkwaardig zijn aan het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen.De voorwaarden en modaliteiten om uitgesloten te worden uit het toepassingsgebied van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen ("buiten toepassingsgebied") worden verder vastgelegd in Bijlage 2 bij deze collectieve arbeidsovereenkomst, die integraal deel uitmaakt van deze collectieve arbeidsovereenkomst.Deze Werkgevers en de Bedienden Ondernemingsactiviteit Edele Metalen in de betrokken Technische Bedrijfseenheid die zij tewerkstellen nemen bijgevolg niet deel aan het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen, in zoverre en voor zolang de ondernemingspensioenstelsels van de betrokken Werkgevers te allen tijde gelijkwaardig zijn aan het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen en de betrokken Werkgevers (blijven) voldoen aan de voorwaarden van "buiten toepassingsgebied", zoals vastgelegd in Bijlage 2 bij deze collectieve arbeidsovereenkomst. § 2. De Werkgevers die op basis van artikel 10, § 1 uitgesloten worden uit het toepassingsgebied van het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen in de betrokken Technische Bedrijfseenheid, kunnen nadien op eender welk moment beslissen om voor de toekomst voor hun Bedienden Ondernemingsactiviteit Edele Metalen toch deel te nemen aan het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen.Zij dienen in dat geval hun wens tot deelname aan het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen te melden aan de Inrichter, volgens de modaliteiten die worden vastgelegd in Bijlage 2 bij deze collectieve arbeidsovereenkomst. De deelname aan het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen zal ingaan vanaf het eerstvolgend kwartaal na de bevestiging van deelname door de Inrichter aan de betrokken Werkgever. § 3. Er wordt geen gebruik gemaakt van de mogelijkheid tot opting-out zoals voorzien in artikel 9 van de WAP.HOOFDSTUK XI. - Duur en algemeen verbindend verklaringArt. 11.  § 1. Deze collectieve arbeidsovereenkomst treedt in werking op 13 juni 2024, met dien verstande dat het SAP PC 200 Bedienden Ondernemingsactiviteit Edele Metalen slechts van toepassing is vanaf 1 juli 2025. Zij wordt gesloten voor een onbepaalde duur. § 2. Deze collectieve arbeidsovereenkomst kan enkel bij eenparig akkoord van de ondertekenende partijen met inachtneming van een opz</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 19 november 2024, gesloten in het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren, betreffende de pensioenpremie voor de uitzendkrachten.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad:Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leverenCollectieve arbeidsovereenkomst van 19 november 2024Pensioenpremie voor de uitzendkrachten (Overeenkomst geregistreerd op 5 december 2024 onder het nummer 190880/CO/322)PreambuleEen groeiend aantal sectoren waar de uitzendkrachten tewerkgesteld zijn, hebben een eigen sectorale pensioenpijler uitgewerkt.Daarbij betalen de bedrijven van deze sectoren een bijdrage aan een sectoraal orgaan ter dekking van de betaling van dit sectoraal pensioen.Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op :1°  de uitzendbureaus, bedoeld bij artikel 7, 1°  van de wet van 24 juli 1987 betreffende de tijdelijke arbeid, de uitzendarbeid en het ter beschikking stellen van werknemers ten behoeve van gebruikers;2°  de uitzendkrachten, bedoeld bij artikel 7, 3°  van genoemde wet van 24 juli 1987, die door de uitzendbureaus worden tewerkgesteld.Zijn uitgesloten uit het toepassingsgebied van onderhavige collectieve arbeidsovereenkomst :- de studenten uitzendkrachten onderworpen aan de solidariteitsbijdrage.Art. 2.  § 1. Partijen komen overeen voor de periode van 1 december 2024 tot 30 juni 2026 de brutolonen van de uitzendkrachten, die tewerkgesteld zijn in sectoren met een sectorale pensioenregeling, te verhogen met een percentage dat overeenkomt met de in deze sectoren betaalde bijdrage, omgezet op basis van een reconversie coëfficiënt. § 2. Deze coëfficiënt houdt rekening met de patronale bijdragen aan de Rijksdienst voor Sociale Zekerheid.Deze reconversiecoëfficiënt bedraagt 0,6943 voor de arbeiders en 0,7158 voor de bedienden. § 3. De in § 1 genoemde percentages die van toepassing zijn voor de periode van 1 december 2024 tot en met 30 juni 2026 zijn de percentages die opgenomen zijn in de bijlage bij deze collectieve arbeidsovereenkomst. § 4. De premie wordt berekend op het loon van de uitzendkracht en wordt toegekend per loonafrekening.De premie wordt afzonderlijk vermeld op de loonfiche van de uitzendkracht onder de uniforme benaming "pensioenpremie".Evenwaardig is de vermelding dat de "pensioenpremie" inbegrepen is in het brutoloon. § 5. Deze regeling maakt toepassing van artikel 12, tweede lid van de wet van 24 juli 1987 en geniet derhalve voorrang op de eventuele sectorale aanvullende pensioenregelingen van de gebruikende ondernemingen. § 6. De partijen komen overeen dat de volgende procedure wordt toegepast :Van zodra de voorzitter van het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren van de uitzendsector ervan verwittigd wordt dat er in een bepaalde sector een regeling inzake een sectorale pensioenpijler is overeengekomen, zal hij aan de voorzitter van het betrokken paritair comité vragen om de modaliteiten van deze regeling over te maken en zal hij deze informatie bezorgen aan de leden van het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren.Het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren sluit vervolgens een collectieve arbeidsovereenkomst af die voorziet in een regeling zoals hierboven overeengekomen.Een dergelijke regeling kan niet ingevoerd worden met terugwerkende kracht.Art. 3. Partijen engageren zich om het onderzoek verder te zetten met het oog op de creatie van een intersectoraal systeem op het niveau van de uitzendsector.Art. 4. Deze collectieve arbeidsovereenkomst treedt in werking op 1 december 2024.Ze vervangt de collectieve arbeidsovereenkomst van 26 juni 2024 betreffende de pensioenpremie voor de uitzendkrachten, geregistreerd onder nummer 188644/CO/322 op 9 juli 2024.Zij wordt gesloten voor een bepaalde duur en verstrijkt op 30 juni 2026.Zij kan, mits een opzeggingstermijn van 3 maanden wordt in acht genomen, door elk van de partijen worden opgezegd met een aangetekend schrijven gericht aan de voorzitter van het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren.Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025.De Minister van Werk,D. CLARINVAL Bijlage bij de collectieve arbeidsovereenkomst van 19 november 2024, gesloten in het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren, betreffende de pensioenpremie voor de uitzendkrachten   </t>
         </is>
       </c>
     </row>
@@ -2078,29 +2078,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2025200939</t>
+          <t>2025002518</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>08 mei 2025</t>
+          <t>30 mei 2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>13 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 18 november 2024, gesloten in het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap, betreffende de bekwame helper in de zorgverlening (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 14 november 2024, gesloten in het Paritair Comité voor het bouwbedrijf, betreffende de vaststelling van het kwartaalbedrag van de forfaitaire bijdrage aan het fonds voor bestaanszekerheid Constructiv (1)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-08&amp;numac_search=2025200939&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200939=51&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-30&amp;numac_search=2025002518&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025002518=51&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 18 november 2024, gesloten in het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap, betreffende de bekwame helper in de zorgverlening.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap Collectieve arbeidsovereenkomst van 18 november 2024 Bekwame helper in de zorgverlening (Overeenkomst geregistreerd op 20 december 2024 onder het nummer 191191/CO/318.02) Artikel 1. Toepassingsgebied Deze collectieve arbeidsovereenkomst is van toepassing op de werknemers en de werkgevers van de diensten voor gezinszorg (gezins- en bejaardenhulp) van de Vlaamse Gemeenschap. Onder "werknemers" wordt verstaan : de werknemers die worden tewerkgesteld als verzorgende, oppasser, poetshulp/huishoudhulp in de gezinszorg, inbegrepen de werknemers betaald uit de middelen Sociale Maribel en de werknemers tewerkgesteld in een GESCOstatuut, maar met uitsluiting van de werknemers die tewerkgesteld zijn in het kader van de dienstencheques. Art. 2. Voorwerp Deze collectieve arbeidsovereenkomst wordt gesloten in uitvoering van artikel 4 van de wet van 18 juni 2023 tot invoering van een overlegprocedure in het kader van de uitoefening van technische verpleegkundige verstrekkingen door bekwame helpers zoals bepaald in de wet van 11 juni 2023 tot wijziging van artikel 124, 1° van de wet betreffende de uitoefening van de gezondheidszorgberoepen, gecoördineerd op 10 mei 2015, teneinde de wetgeving betreffende de uitoefening van technische verpleegkundige verstrekkingen door een mantelzorger of door een bekwame helper, hierin aan te passen. Onverminderd blijven de activiteiten van zorg- en bijstandsverlening zoals bepaald in het decreet betreffende de zorg- en bijstandsverlening van 18 juli 2008 van toepassing. De technische verpleegkundige verstrekkingen die toevertrouwd worden aan een bekwame helper kunnen enkel gelden als een uitbreiding bovenop de reeds toegestane handelingen. Art. 3. Modaliteiten en overlegprocedure Elke dienst voor gezinszorg stelt een afsprakenkader op waarin volgende aspecten worden geconcretiseerd : - de toegelaten technische verpleegkundige verstrekkingen die door de medewerker als bekwame helpers kunnen uitgeoefend worden; - opleidings- en instructiebeleid vereist in kader van de uitoefening van technische verpleegkundige verstrekkingen door bekwame helpers; - communicatie en informatie-uitwisseling tussen de bekwame helper en arts en/of verpleegkundige verantwoordelijk voor algemene zorg en/of een basisverpleegkundige en de teamverantwoordelijke van de dienst. Dit afsprakenkader wordt voorafgaandelijk besproken en goedgekeurd op de Ondernemingsraad, bij ontstentenis het comité voor preventie en bescherming op het werk (CPBW), bij ontstentenis de syndicale afvaardiging binnen de dienst. De toepassing van het stelsel van de bekwame helper wordt minstens jaarlijks besproken en geëvalueerd in de ondernemingsraad, of bij ontstentenis het CPBW, of bij ontstentenis, de vakbondsafvaardiging. De werkgever bezorgt hiervoor een overzicht met minstens volgende gegevens : - het aantal betrokken werknemers; - het aantal betrokkencliënten en aanvragen; - de aard van de technische verpleegkundige verstrekkingen;- de aangeboden en gevolgde opleidingen en/of ontvangen instructies; - de impact op de arbeidsorganisatie. Het paritair subcomité 318.02 zet de bespreking over de toepassing van deze wet binnen de sector minstens eenmaal per jaar op de agenda van het paritair comité. Art. 4. Opleidingsvoorwaarden Wanneer toegelaten technische verpleegkundige verstrekkingen worden uitgeoefend door bekwame helpers, gaat de werkgever voorafgaand na dat de medewerker beschikt over de nodige instructies en/of de nodige opleiding. De opleiding kan zowel intern als extern worden georganiseerd. Art. 5. Vrijwilligheid Onder geen enkel beding kan een medewerker verplicht worden om technisch verpleegkundige verstrekkingen als bekwame helper uit te voeren. De goedkeuring van de medewerker dient voorafgaand, schriftelijk bevestigd te worden aan de hand van het attest dat wordt opgesteld conform de wettelijke bepalingen. Dit attest bevat : - de identiteit van de cliënt; - de identiteit van de medewerker die de toelating heeft gekregen; - de toegelaten technische verpleegkundige verstrekkingen; - de duur van de toelating; - de eventuele bijkomende voorwaarden en waarschuwingscriteria; - modaliteiten van het overleg tussen de bekwame helper en de arts of verpleegkundige die de toelating gegeven heeft; - de toestemming van de cliënt of diens vertegenwoordiger. Het staat de medewerker vrij de toevertrouwde handeling(en) te weigeren, of een eerder gegeven goedkeuring te allen tijde te herzien. Hieruit vloeit geen nadelige behandeling voort op vlak van loon-, arbeids- en tewerkstellingsvoorwaarden. Ook de werkgever dient zijn goedkeuring te geven over de inschakeling van de medewerker als bekwame helper. De werkgever beoordeelt elke aanvraag in functie van dienstnoodwendigheden, de mogelijkheden binnen het team en de individuele competenties. Het staat de organisatie vrij in functie van de continuïteit van zorg en in samenspraak met de arts of verpleegkundige en mits akkoord van de medewerkers, meerdere medewerkers te delegeren als bekwame helper bij eenzelfde cliënt. Art. 6. Verantwoordelijkheid en aansprakelijkheid De arts en/of verpleegkundige verantwoordelijk voor algemene zorg en/of een basisverpleegkundige, die de technisch verpleegkundige verstrekkingen delegeert, is verantwoordelijk voor : - de beoordeling van de vaardigheden van de medewerker; - het verzekeren van de nodige opleiding; - het bezorgen van de instructies aan de bekwame helper; - de (her)evaluatie van de gezondheidstoestand van de patiënt. De medewerker die de technische verpleegkundige verstrekking(en) als bekwame helper aanvaardt, staat in voor de kwaliteitsvolle uitvoering volgens de gegeven instructie en opleiding. De medewerker heeft een signaalfunctie om tijdig problemen of knelpunten met betrekking tot de uit te voeren handelingen, te melden aan de arts en/of verpleegkundige verantwoordelijk voor algemene zorg en/of een basisverpleegkundige. Dit beperkt zich uitsluitend tot een signaalfunctie en tot de uit te voeren handelingen. De medewerker kan op geen enkele manier de gezondheidstoestand van de gebruiker-client beoordelen. De werkgever is verantwoordelijk voor het verzekeren van de medewerker en het aanbieden van de nodige rechtsbijstand. De werkgever informeert tijdig de verzekeringsinstelling over het stellen van de technische verpleegkundige handelingen als bekwame helper zodat de burgerlijke aansprakelijkheid van de bekwame helper in het kader van het stellen van de toegelaten verpleegkundige handelingen verzekerd is. Ook de kosten verbonden aan gebeurlijke dagvaarding van de bekwame helper voor een rechtscollege in een zaak betreffende (gevolgen van) het stellen van de toegelaten technische verpleegkundige verstrekkingen, zijn ten laste van de werkgever of diens verzekeringsinstelling.Art. 7. Slotbepalingen en inwerkingtreding Deze collectieve arbeidsovereenkomst wordt gesloten voor onbepaalde duur en treedt in werking op 1 december 2024. Deze collectieve arbeidsovereenkomst kan opgezegd worden door elk der partijen, mits een opzegging van drie maanden, betekend door middel van een aangetekend schrijven gericht aan de voorzitter van het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Vlaamse Gemeenschap. Gezien om te worden gevoegd bij het koninklijk besluit van 13 april 2025. De Minister van Werk, D. CLARINVAL 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor het bouwbedrijf;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 14 november 2024, gesloten in het Paritair Comité voor het bouwbedrijf, betreffende de vaststelling van het kwartaalbedrag van de forfaitaire bijdrage aan het fonds voor bestaanszekerheid Constructiv.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het bouwbedrijfCollectieve arbeidsovereenkomst van 14 november 2024Vaststelling van het kwartaalbedrag van de forfaitaire bijdrage aan het fonds voor bestaanszekerheid Constructiv (Overeenkomst geregistreerd op 5 december 2024 onder het nummer 190881/CO/124)HOOFDSTUK I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers van de ondernemingen die onder het Paritair Comité voor het bouwbedrijf ressorteren en op de arbeiders die zij tewerkstellen, alsook op de uitzendkantoren voor de arbeiders die zij ter beschikking stellen van de werkgevers die onder het Paritair Comité voor het bouwbedrijf ressorteren.Onder "arbeiders" wordt verstaan : de arbeiders en de arbeidsters.Ze stelt, in uitvoering van artikel 4 van de collectieve arbeidsovereenkomst van 3 juni 2004 tot vaststelling van de forfaitaire bijdrage aan het fonds voor bestaanszekerheid Constructiv (registratienummer : 72150/CO/124), het kwartaalbedrag vast van de forfaitaire bijdrage voor de 4 kwartalen van 2025.HOOFDSTUK II. - Vaststelling bedrag forfaitaire bijdrageArt. 2. Het kwartaalbedrag van de forfaitaire bijdrage is voor de 4 kwartalen van 2025 vastgesteld op :  </t>
         </is>
       </c>
     </row>
@@ -2110,28 +2109,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2025200926</t>
+          <t>2025200927</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>13 mei 2025</t>
+          <t>30 mei 2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>13 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 4 oktober 2023, gesloten in het Paritair Subcomité voor de metaalhandel, betreffende de wijziging en coördinatie van de statuten van het sociaal fonds (1)</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor de landbouw, betreffende de loon- en arbeidsvoorwaarden (vlas) (1)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-13&amp;numac_search=2025200926&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200926=52&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-30&amp;numac_search=2025200927&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200927=52&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Subcomité voor de metaalhandel; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 4 oktober 2023, gesloten in het Paritair Subcomité voor de metaalhandel, betreffende de wijziging en coördinatie van de statuten van het sociaal fonds. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 13 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Subcomité voor de metaalhandel Collectieve arbeidsovereenkomst van 4 oktober 2023 Wijziging en coördinatie van de statuten van het sociaal fonds (Overeenkomst geregistreerd op 5 december 2024 onder het nummer 190899/CO/149.04) In uitvoering van artikel 5 van het nationaal akkoord 2023-2024 van 4 oktober 2023 en vervanging van de collectieve arbeidsovereenkomst : "Wijziging en coördinatie van de statuten van het sociaal fonds" van 2 december 2021. Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de arbeiders van de ondernemingen die ressorteren onder het Paritair Subcomité voor de metaalhandel. Voor de toepassing van deze collectieve arbeidsovereenkomst, wordt onder "arbeiders" verstaan : de mannelijke en vrouwelijke werklieden. Art. 2. De statuten van het "Sociaal Fonds voor de metaalhandel" zijn bijgevoegd in bijlage. Art. 3. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2024 en wordt gesloten voor onbepaalde tijd. De collectieve arbeidsovereenkomst kan worden opgezegd door één van de ondertekenende partijen mits een opzegging van 6 maanden, betekend bij een ter post aangetekend schrijven, gericht aan de voorzitter van het Paritair Subcomité voor de metaalhandel. Deze opzegging kan slechts ingaan ten vroegste vanaf 1 juli 2025.Art. 4. Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst van 2 december 2021 betreffende de wijziging en coördinatie van de statuten van het sociaal fonds, geregistreerd onder het nummer 170278/CO/149.04. Gezien om te worden gevoegd bij het koninklijk besluit van 13 april 2025. De Minister van Werk, D. CLARINVAL BijlageBijlage aan de collectieve arbeidsovereenkomst van 4 oktober 2023, gesloten in het Paritair Subcomité voor de metaalhandel, betreffende de wijziging en coördinatie van de statuten van het sociaal fonds Statuten van het fonds HOOFDSTUK I. - Benaming, zetel, opdrachten en duur 1. Benaming Artikel 1. Er wordt een fonds voor bestaanszekerheid opgericht het : "Sociaal fonds van het Paritair Subcomité voor de metaalhandel" afgekort "Sociaal Fonds voor de metaalhandel", verder in deze statuten het "fonds" genoemd. Dit fonds wordt opgericht bij collectieve arbeidsovereenkomst van 28 mei 1970, algemeen verbindend verklaard bij koninklijk besluit van 11 augustus 1978 (Belgisch Staatsblad van 19 november 1978). Met "fonds" wordt verder in deze statuten bedoeld : "Sociaal Fonds voor de metaalhandel". 2. Zetel Art. 2. De maatschappelijke zetel van het fonds is gevestigd te 1120 Brussel, Marlylaan 15/8. Hij kan, bij beslissing van het Paritair Subcomité voor de metaalhandel, naar elke andere plaats in België worden overgebracht. 3. Opdrachten Art. 3. Het fonds heeft als opdracht : 3.1 de inning en de invordering van de bijdragen ten laste van de in artikel 5 bedoelde werkgevers te regelen en te verzekeren; 3.2. de toekenning en de uitkering van de aanvullende vergoedingen te regelen en te verzekeren; 3.3. de vakbondsvorming van de arbeiders te bevorderen; 3.4. de vorming en informatie van de werkgevers te stimuleren; 3.5. een deel van de werking en sommige initiatieven van de vzw "EDUCAM" te financieren; 3.6. ten laste nemen van bijzondere bijdragen; 3.7. de inning van de bijdrage voorzien voor de financiering en inrichting van een sectoraal pensioenstelsel. 4. Duur Art. 4.  Het fonds wordt opgericht voor onbepaalde tijd. HOOFDSTUK II. - Toepassingsgebied Art. 5.  Onderhavige statuten zijn van toepassing op de werkgevers en de arbeiders van de ondernemingen die ressorteren onder het Paritair Subcomité voor de metaalhandel. Met "arbeiders" wordt bedoeld : de mannelijke en vrouwelijke werklieden. HOOFDSTUK III. - Statutaire opdrachten van het fonds 1. Inning en invordering van de bijdragen Art. 6. Het fonds is gelast de inning en de invordering van de bijdragen ten laste van de in artikel 5 bedoelde werkgevers te regelen en te verzekeren. 2. Toekenning en uitkering van de aanvullende vergoedingen 2.1. Aanvullende vergoeding bij tijdelijke werkloosheid Art. 7.  § 1. De bij artikel 5 bedoelde arbeiders hebben recht, ten laste van het fonds, voor elke werkloosheidsuitkering of halve werkloosheidsuitkering erkend door de Rijksdienst voor Arbeidsvoorziening en voorzien in : - artikel 26, 1° - tijdelijke werkloosheid omwille van overmacht;- artikel 28, § 1 - tijdelijke werkloosheid omwille van sluiting van de onderneming wegens jaarlijks verlof; - artikel 49 - tijdelijke werkloosheid omwille van technische stoornis; - artikel 50 - tijdelijke werkloosheid omwille van slecht weer; - artikel 51 - tijdelijke werkloosheid omwille van economische redenen, van de wet van 3 juli 1978 betreffende de arbeidsovereenkomsten op de vergoeding voorzien in artikel 7, § 2 van deze statuten, voor zover zij volgende voorwaarden vervullen : - werkloosheidsuitkeringen genieten in toepassing van de reglementering op de werkloosheidsverzekering; - op het ogenblik van de werkloosheid in dienst van de werkgever zijn.  § 2. Het bedrag van de aanvullende vergoeding bij tijdelijke werkloosheid werd vanaf 1 december 2021 geïndexeerd met 1,52 pct. en vastgesteld op : - 12,89 EUR per werkloosheidsuitkering betaald in toepassing van de reglementering op de werkloosheidsverzekering; - 6,45 EUR per halve werkloosheidsuitkering betaald in toepassing van de reglementering op de werkloosheidsverzekering. Vanaf 1 januari 2024 wordt het bedrag van de vergoeding geïndexeerd met 16,13 pct. en vastgesteld op : - 14,97 EUR per werkloosheidsuitkering betaald in toepassing van de reglementering op de werkloosheidsverzekering; - 7,49 EUR per halve werkloosheidsuitkering betaald in toepassing van de reglementering op de werkloosheidsverzekering. Art. 8. De aanvullende vergoeding bij tijdelijke werkloosheid dient te worden betaald bij jeugdvakantie en bij seniorenvakantie. 2.2. Aanvullende vergoeding bij volledige werkloosheid Art. 9.  § 1. De bij artikel 5 bedoelde arbeiders hebben ten laste van het fonds, voor elke werkloosheidsuitkering recht op de bij artikel 9, § 2 voorziene vergoeding, met een maximum respectievelijk van 200 dagen en 300 dagen per geval, al naargelang zij op de eerste dag van de werkloosheid minder dan 45 jaar oud zijn of 45 jaar en ouder zijn, en voor zover zij volgende voorwaarden vervullen : 1. werkloosheidsuitkeringen genieten in toepassing van de wetgeving op de werkloosheidsverzekering; 2. door een in artikel 5 bedoelde werkgever ontslagen geweest zijn; 3. op het ogenblik van het ontslag, ten minste vijf jaar tewerkgesteld zijn in één of meerdere ondernemingen die onder één van de volgende paritair comités ressorteren : - voor de ijzernijverheid (Paritair Comité 104); - voor de non-ferrometalen (Paritair Comité 105); - voor de metaal-, machine- en elektrische bouw (Paritair Comité 111); - voor de sectoren verwant aan de metaal-, machine- en elektrische bouw (Paritair Subcomités 149.01, 149.02, 149.03 en 149.04); - voor de garage (Paritair Comité 112); - voor de terugwinning van metalen (Paritair Subcomité 142.01); 4. een wachttijd van vijftien kalenderdagen hebben vervuld. Voor de berekening van de wachttijd, worden de dagen werkloosheid en ziekte, in voorkomend geval, gelijkgesteld.  § 2. Het bedrag van de aanvullende werkloosheidsvergoeding werd vanaf 1 december 2021 geïndexeerd met 1,52 pct. en vastgesteld op : - 6,64 EUR per volledige werkloosheidsuitkering betaald in toepassing van de reglementering op de werkloosheidsverzekering; - 3,32 EUR per halve werkloosheidsuitkering betaald in toepassing van de reglementering op de werkloosheidsverzekering. Vanaf 1 januari 2024 wordt het bedrag van de vergoeding geïndexeerd met 16,13 pct. en vastgesteld op : - 7,71 EUR per werkloosheidsuitkering betaald in toepassing van de reglementering op de werkloosheidsverzekering; - 3,86 EUR per halve werkloosheidsuitkering betaald in toepassing van de reglementering op de werkloosheidsverzekering.  § 3. De aanvullende vergoeding bij volledige werkloosheid wordt betaald in de volgende gevallen :- de beëindiging van de arbeidsovereenkomst is niet het gevolg van een eenzijdige beëindiging van de arbeidsovereenkomst door de werkgever (bijvoorbeeld bij einde contract van bepaalde duur of duidelijk omschreven werk, bij medische overmacht,...); - aan de arbeiders die zijn ontslagen na 1 januari 2014 in het kader van collectieve ontslagen tot 31 december 2013; - aan de arbeiders die reeds aanvullende vergoedingen bij volledige werkloosheid ontvangen op 30 juni 2015 en hun saldo nog kunnen uitputten. 2.3. Aanvullende ziektevergoeding Art. 10. Voor arbeidsongeschiktheden die aanvingen vóór 1 juli 2019  § 1. De bij artikel 5 bedoelde arbeiders hebben na ten minste zestig dagen ononderbroken arbeidsongeschiktheid ten gevolge van ziekte of ongeval, met uitsluiting van de arbeidsongeschiktheid ten gevolge van beroepsziekte of arbeidsongeval, recht, ten laste van het fonds, op een aanvullende vergoeding die de uitkeringen van de ziekte- en invaliditeitsverzekering aanvult, voor zover de arbeiders volgende voorwaarden vervullen : - de ongeschiktheidsuitkeringen van de ziekte- en invaliditeitsverzekering genieten in toepassing van de wetgeving ter zake; - op het ogenblik waarop de ongeschiktheid aanvangt, in dienst zijn van een in artikel 5 bedoelde werkgever.  § 2. Het forfaitair bedrag van de bij artikel 10, § 1 bedoelde vergoeding wordt vastgesteld op : - 98,78 EUR na de eerste 60 dagen ononderbroken ongeschiktheid; - 98,78 EUR meer na de eerste 120 dagen ononderbroken ongeschiktheid; - 128,62 EUR meer na de eerste 180 dagen ononderbroken ongeschiktheid; - 128,62 EUR meer na de eerste 240 dagen ononderbroken ongeschiktheid; - 128,62 EUR meer na de eerste 300 dagen ononderbroken ongeschiktheid; - 128,62 EUR meer na de eerste 365 dagen ononderbroken ongeschiktheid; - 128,62 EUR meer na de eerste 455 dagen ononderbroken ongeschiktheid; - 128,62 EUR meer na de eerste 545 dagen ononderbroken ongeschiktheid; - 128,62 EUR meer na de eerste 635 dagen ononderbroken ongeschiktheid; - 128,62 EUR meer na de eerste 725 dagen ononderbroken ongeschiktheid; - 128,62 EUR meer na de eerste 815 dagen ononderbroken ongeschiktheid; - 128,62 EUR meer na de eerste 905 dagen ononderbroken ongeschiktheid; - 128,62 EUR meer na de eerste 995 dagen ononderbroken ongeschiktheid.  § 3. Een arbeidsongeschiktheid kan, ongeacht de duur ervan, slechts aanleiding geven tot de toekenning van een enkele reeks vergoedingen; het hervallen in eenzelfde ziekte wordt beschouwd als integraal deel uitmakend van de vorige ongeschiktheid wanneer die zich voordoet binnen de eerste veertien dagen volgend op het einde van die periode van arbeidsongeschiktheid.  § 4. Een arbeider die tijdens de ziekteperiode het werk deeltijds hervat en nog uitkeringen ontvangt van de ziekte- en invaliditeitsverzekering, heeft recht op een pro rata aanvullende ziektevergoeding. Vanaf 1 januari 2024 worden de bovenvermelde forfaitaire bedragen van 98,78 EUR na 60 en 120 dagen en 128,62 EUR na een langere ziekteperiode geïndexeerd met 16,13 pct. en vastgesteld op 114,71 EUR en 149,37 EUR. Art. 10bis. Voor arbeidsongeschiktheden die aanvangen vanaf 1 juli 2019  § 1. De bij artikel 5 bedoelde arbeiders hebben na ten minste 30 dagen ononderbroken arbeidsongeschiktheid ten gevolge van ziekte of ongeval, met uitsluiting van de arbeidsongeschiktheid ten gevolge van beroepsziekte of arbeidsongeval, recht, ten laste van het fonds, op een vergoeding die de uitkeringen van de ziekte- en invaliditeitsverzekering aanvult, met een maximum van 36 maanden, voor zover de arbeiders volgende voorwaarden vervullen : - de ongeschiktheiduitkeringen van de ziekte- en invaliditeitsverzekering genieten in toepassing van de wetgeving ter zake; - op het ogenblik waarop de ongeschiktheid aanvangt, in dienst zijn van een in artikel 5 bedoelde werkgever.  § 2. Het bedrag van de bij artikel 10bis, § 1 bedoelde aanvullende vergoeding wordt vastgesteld op : - 2,48 EUR per volledige ziekte-uitkering betaald in toepassing van de reglementering op de ziekteverzekering; - 1,24 EUR per halve ziekte-uitkering betaald in toepassing van de reglementering op de ziekteverzekering. Vanaf 1 januari 2024 wordt het bedrag van de bij artikel 10bis, § 1 bedoelde aanvullende vergoeding geïndexeerd met 16,13 pct. en vastgesteld op : - 2,88 EUR per volledige ziekte-uitkering betaald in toepassing van de reglementering op de ziekteverzekering; - 1,44 EUR per halve ziekte-uitkering betaald in toepassing van de reglementering op de ziekteverzekering.  § 3. Een arbeidsongeschiktheid kan, ongeacht de duur ervan, slechts aanleiding geven tot de toekenning van een enkele reeks vergoedingen; het hervallen in eenzelfde ziekte wordt beschouwd als integraal deel uitmakend van de vorige ongeschiktheid wanneer die zich voordoet binnen de eerste veertien dagen volgend op het einde van die periode van arbeidsongeschiktheid.  § 4. Een arbeider die tijdens de ziekteperiode het werk deeltijds hervat en nog uitkeringen ontvangt van de ziekte- en invaliditeitsverzekering, heeft recht op een pro rata aanvullende ziektevergoeding. 2.4. Aanvullende vergoeding voor oudere werklozen Art. 11. § 1. De in artikel 5 bedoelde arbeiders die volledig werkloos worden gesteld, hebben voor elke werkloosheidsdag recht op de bij artikel 11, § 2 voorziene vergoeding, onder volgende voorwaarden : - ten minste 55 jaar oud zijn op de eerste dag van de werkloosheid; - uitkeringen voor volledige werkloosheid genieten; - 20 jaar beroepsverleden kunnen bewijzen waarvan 5 jaar in de sector van de metaalhandel (PSC 149.04).  § 2. Het bedrag van de aanvullende werkloosheidsvergoeding werd vanaf 1 december 2021 geïndexeerd met 1,52 pct. en vastgesteld op : - 6,64 EUR per volledige werkloosheidsuitkering betaald in toepassing van de reglementering op de werkloosheidsverzekering; - 3,32 EUR per halve werkloosheidsuitkering betaald in toepassing van de reglementering op de werkloosheidsverzekering. Vanaf 1 januari 2024 wordt het bedrag van de aanvullende werkloosheidsvergoeding geïndexeerd met 16,13 pct. en vastgesteld op : - 7,71 EUR per volledige werkloosheidsuitkering betaald in toepassing van de reglementering op de werkloosheidsverzekering; - 3,86 EUR per halve werkloosheidsuitkering betaald in toepassing van de reglementering op de werkloosheidsverzekering.  § 3. Arbeiders die zijn ontslagen en een aanvullende vergoeding ontvangen conform de bepalingen van artikel 11, § 1 en § 2, behouden het recht op deze aanvullende vergoeding : - wanneer ze het werk hervatten als loontrekkende bij een andere werkgever dan de werkgever die hen heeft ontslagen en die niet behoort tot dezelfde technische bedrijfseenheid als de werkgever die hen heeft ontslagen; - ingeval een zelfstandige activiteit in hoofdberoep wordt uitgeoefend op voorwaarde dat die activiteit niet wordt uitgeoefend voor rekening van de werkgever die hen heeft ontslagen of voor rekening van een werkgever die behoort tot dezelfde technische bedrijfseenheid als de werkgever die hen heeft ontslagen.  § 4. De aanvullende vergoeding voor oudere werklozen wordt betaald in de volgende gevallen : - de beëindiging van de arbeidsovereenkomst is niet het gevolg van een eenzijdige beëindiging van de arbeidsovereenkomst door de werkgever (bijvoorbeeld bij einde contract van bepaalde duur of duidelijk omschreven werk, bij medische overmacht,...); - aan de arbeiders die zijn ontslagen na 1 januari 2014 in het kader van collectieve ontslagen tot 31 december 2013;- aan de arbeiders die reeds aanvullende vergoedingen bij volledige werkloosheid op 30 juni 2015 ontvangen en hun saldo nog kunnen uitputten. 2.5. Aanvullende vergoeding voor oudere zieken Art. 12. § 1. De in artikel 5 bedoelde arbeiders die verkeren in een toestand van blijvende arbeidsongeschiktheid wegens ziekte of ongeval, met uitsluiting van arbeidsongeschiktheid wegens beroepsziekte of arbeidsongeval, hebben voor elke ziekte-uitkering recht op de bij artikel 12, § 2 voorziene vergoeding, onder de volgende voorwaarden : - ten minste 55 jaar oud zijn op de eerste dag van de arbeidsongeschiktheid; - uitkeringen van ziekte- en invaliditeitsverzekering genieten; - een carenztijd van dertig kalenderdagen hebben vervuld, ingaande op de eerste dag van de ongeschiktheid; - 20 jaar beroepsverleden kunnen bewijzen waarvan 5 jaar in de sector van de metaalhandel (PSC 149.04).  § 2. Het bedrag van de aanvullende ziektevergoeding werd vanaf 1 december 2021 geïndexeerd met 1,52 pct. en vastgesteld op : - 8,46 EUR per volledige ziekte-uitkering betaald in toepassing van de reglementering op de ziekteverzekering; - 4,23 EUR per halve ziekte-uitkering betaald in toepassing van de reglementering op de ziekteverzekering. Vanaf 1 januari 2024 wordt het bedrag van de aanvullende ziektevergoeding geïndexeerd met 16,13 pct. en vastgesteld op : - 9,82 EUR per volledige ziekte-uitkering betaald in toepassing van de reglementering op de ziekteverzekering; - 4,91 EUR per halve ziekte-uitkering betaald in toepassing van de reglementering op de ziekteverzekering.  § 3. Een arbeider die tijdens de ziekteperiode het werk deeltijds hervat en nog uitkeringen ontvangt van de ziekte- en invaliditeitsverzekering, heeft recht op een pro rata aanvullende ziektevergoeding. Art. 13. De arbeiders die de bij artikel 11 en 12 bedoelde vergoeding genieten, hebben geen recht op bij de artikels 9, 10 en 15 voorziene vergoedingen. 2.6. Aanvullende vergoeding bij sluiting van de onderneming Art. 14. § 1. De in artikel 5 bedoelde arbeiders hebben recht op een aanvullende vergoeding in geval van sluiting van onderneming volgens de hierna bepaalde voorwaarden : 1. op het ogenblik van de sluiting van onderneming, ten minste 45 jaar oud zijn; 2. op het ogenblik van de sluiting van onderneming, een anciënniteit hebben van ten minste vijf jaar in de onderneming; 3. het bewijs leveren niet opnieuw, krachtens een arbeidsovereenkomst, te zijn aangeworven binnen een termijn van 30 kalenderdagen te rekenen vanaf de dag van het ontslag.  § 2. Onder "sluiting van onderneming" zoals bedoeld bij de eerste paragraaf van dit artikel, wordt verstaan : de volledige en definitieve stopzetting van de werkzaamheden van de onderneming of van de metaalhandel-afdeling, behorende tot een grotere entiteit die deel uitmaakt van een ander paritair comité.  § 3. Het bedrag van de aanvullende vergoeding werd vanaf 1 december 2021 geïndexeerd met 1,52 pct. en vastgesteld op 328,83 EUR. Dit bedrag wordt met 16,57 EUR verhoogd per jaar anciënniteit, met een maximum van 1 084,60 EUR. Vanaf 1 januari 2024 wordt het bedrag van de aanvullende vergoeding in geval van sluiting geïndexeerd met 16,13 pct. en vastgesteld op 381,87 EUR. Dit bedrag wordt vanaf 1 januari 2024 met 19,24 EUR verhoogd per jaar anciënniteit met een maximum van 1 259,54 EUR. 2.7. Aanvullende vergoeding bij stelsel van werkloosheid met bedrijfstoeslag Art. 15. § 1. In toepassing van en overeenkomstig : - de collectieve arbeidsovereenkomst nr. 17 gesloten op 19 december 1974, in de Nationale Arbeidsraad, tot invoering van een regeling van aanvullende vergoeding ten gunste van sommige bejaarde werknemers indien zij worden ontslagen, algemeen verbindend verklaard bij koninklijk besluit van 16 januari 1975 (Belgisch Staatsblad van 31 januari 1975);- de bestaande collectieve arbeidsovereenkomsten inzake stelsel van werkloosheid met bedrijfstoeslag, gesloten in het Paritair Subcomité voor de metaalhandel; - de collectieve arbeidsovereenkomst van 5 oktober 1998 betreffende de berekeningswijze van de aanvullende vergoeding brugpensioen, afgesloten in het Paritair Subcomité voor de metaalhandel, neemt het fonds de helft van het verschil tussen het nettoreferteloon en de werkloosheidsuitkering ten laste. Deze aanvullende vergoeding wordt berekend op het ogenblik dat het stelsel van werkloosheid met bedrijfstoeslag een aanvang neemt en blijft ongewijzigd, onder voorbehoud van de koppeling aan de evolutie van het indexcijfer van de consumptieprijzen, volgens de modaliteiten van toepassing op de werkloosheidsuitkeringen overeenkomstig de bepalingen van de wet van 2 augustus 1971. Bovendien wordt het bedrag van deze aanvullende vergoeding elk jaar op 1 januari herzien door de Nationale Arbeidsraad, in functie van de conventionele evolutie van de lonen.  § 2. De aanvullende uitkering voor volledige werkloosheid voorzien in artikel 9 van de statuten wordt in aanmerking genomen voor de berekening van de aanvullende uitkering voorzien in artikel 15, § 1.  § 3. Om te kunnen genieten van het stelsel van werkloosheid met bedrijfstoeslag zoals vermeld in de vorige paragrafen, moeten de betrokkenen vanaf 1 juli 2003 bewijzen dat zijn ten minste 5 jaar hebben gewerkt als arbeiders in één of meerdere ondernemingen ressorterend onder het Paritair Subcomité voor de metaalhandel. Indien een arbeider een anciënniteit heeft opgebouwd in eenzelfde onderneming, die een bepaalde periode niet tot het Paritair Subcomité voor de metaalhandel behoorde of die opgedeeld is in verschillende technische entiteiten behorende tot verschillende paritair comités, dan wordt deze anciënniteit als een geheel beschouwd.  § 4. Onder de voorwaarden bepaald in de collectieve arbeidsovereenkomst nr. 17 en volgens de daarin bepaalde modaliteiten, behouden de arbeiders die zijn ontslagen met het oog op het stelsel van werkloosheid met bedrijfstoeslag in het kader van deze collectieve arbeidsovereenkomsten of in het kader van een op ondernemingsniveau gesloten collectieve arbeidsovereenkomst inzake het stelsel van werkloosheid met bedrijfstoeslag, het recht op de aanvullende vergoeding : - wanneer ze het werk hervatten als loontrekkende bij een andere werkgever dan de werkgever die hen heeft ontslagen en die niet behoort tot dezelfde technische bedrijfseenheid als de werkgever die hen heeft ontslagen; - ingeval een zelfstandige activiteit in hoofdberoep wordt uitgeoefend op voorwaarde dat die activiteit niet wordt uitgeoefend voor rekening van de werkgever die hen heeft ontslagen of voor rekening van een werkgever die behoort tot dezelfde technische bedrijfseenheid als de werkgever die hen heeft ontslagen.  § 5. Sinds 1 juli 2003 neemt het fonds de toepassing van voormelde collectieve arbeidsovereenkomst van 19 december 1974 op zich indien een ondernemingsakkoord de uitbreiding van deze voordelen voorziet tot de arbeiders die een lagere leeftijd hebben dan deze bepaald in de collectieve arbeidsovereenkomsten omtrent het stelsel van werkloosheid met bedrijfstoeslag binnen de sector. Het fonds neemt dit voordeel ten laste vanaf de eerste dag van de maand volgend op de maand waarin de arbeider de leeftijd van 60 jaar bereikt, op voorwaarde dat de werkgever, op het ogenblik van het sluiten van het ondernemingsakkoord, kopie hiervan gestuurd heeft aan het fonds en dat hij de forfaitaire bijdrage, voorzien bij artikel 35, heeft vereffend.  § 6. Indien een arbeider in het kader van een stelsel van werkloosheid met bedrijfstoeslag, zijn rechten hieromtrent bij de Rijksdienst voor Arbeidsvoorziening heeft vastgeklikt, wordt ook de uitbetaling van de aanvullende vergoeding in dit kader bij het fonds vastgeklikt. 2.8. Aanvullende vergoeding bij vermindering van arbeidsprestaties, landingsbaan en zachte landingsbaan Art. 16. § 1. Het fonds betaalt een aanvullende vergoeding van 82,20 EUR per maand gedurende 60 maanden aan arbeiders van 53 jaar en meer die hun arbeidsprestaties verminderen tot een halftijdse betrekking overeenkomstig de collectieve arbeidsovereenkomsten nr. 77bis van 19 december 2001 en nr. 103 van 27 juni 2012 en de hieraan aangebrachte wijzigingen, en die in dit kader van de Rijksdienst voor Arbeidsvoorziening een uitkering ontvangen.  § 2. Een aanvullende vergoeding bij een landingsbaan zal toegekend worden aan de oudere werknemers die, uiterlijk op 30 juni 2025, hun prestaties met 1/5de of de helft in het kader van de collectieve arbeidsovereenkomst nr. 103 van 27 juni 2012 verminderen.De aanvullende vergoeding wordt toegekend vanaf 60 jaar en, overeenkomstig collectieve arbeidsovereenkomsten nr. 156 en nr. 157 van 15 juli 2021, vanaf 55 jaar voor een 1/5de en halftijdse loopbaanvermindering, en dit tot de wettelijke pensioenleeftijd. Vanaf 1 december 2021 werd het bedrag van de aanvullende vergoeding geïndexeerd met 1,52 pct. en vastgesteld op : - 82,20 EUR per maand voor een vermindering van de arbeidsprestaties met 1/2; - 32,87 EUR voor een vermindering van de arbeidsprestaties met 1/5de. Vanaf 1 januari 2024 wordt het bedrag van de aanvullende vergoeding geïndexeerd met 16,13 pct. en vastgesteld op : - 95,46 EUR per maand voor een vermindering van de arbeidsprestaties met 1/2; - 38,17 EUR per maand voor een vermindering van de arbeidsprestaties met 1/5de. Art. 16bis. § 1. Dit artikel wordt gesloten in toepassing van de collectieve arbeidsovereenkomst nr. 104 van 27 juni 2012 over de uitvoering van een werkgelegenheidsplan voor oudere werknemers in de onderneming en van het koninklijk besluit van 9 januari 2018 tot wijziging van artikel 19 van het koninklijk besluit van 28 november 1969 tot uitvoering van de wet van 27 juni 1969 tot herziening van de besluitwet van 28 december 1944 betreffende de maatschappelijke zekerheid der arbeiders (Belgisch Staatsblad van 25 januari 2018).  § 2. De arbeiders die in de periode van 1 januari 2024 tot en met 30 juni 2025 instappen in een zachte landingsbaan, overeenkomstig artikel 5 van het nationaal akkoord 2023-2024 van 4 oktober 2023, hebben ten laste van het fonds recht op een aanvullende vergoeding.  § 3. De aanvullende vergoeding is gelijk aan het verschil tussen het brutoloon na aanpassing van de loopbaan en het brutoloon voor normale prestaties van de maand voorafgaand aan de aanpassing van de loopbaan, met een maximum van 162,43 EUR bruto per maand (bedrag op 1 februari 2021). Vanaf 1 januari 2024 bedraagt het bedrag van de aanvullende vergoeding 188,63 EUR.  § 4. De toekenning van de vergoeding mag niet tot gevolg hebben dat het nettoloon van de arbeider hoger is dan voor de aanpassing van de loopbaan. In voorkomend geval wordt ze hiertoe begrensd.  § 5. De vergoeding wordt jaarlijks geïndexeerd volgens de bepalingen van de collectieve arbeidsovereenkomst van 18 juni 2009 betreffende de loonvorming, en de in voege zijnde wettelijke bepalingen.  § 6. De vergoeding kan niet worden gecumuleerd met een onderbrekingsuitkering, toegekend in het kader van een tijdskrediet, een loopbaanvermindering, landingsbanen of thematische verlofregelingen. De vergoeding kan niet worden gecumuleerd met de vergoedingen toegekend op basis van artikel 16 van deze collectieve arbeidsovereenkomst. De vergoedingen voor verschillende vormen van loopbaanwijzingen kunnen niet worden gecumuleerd.  § 7. Het recht op vergoeding vervalt onmiddellijk bij de beëindiging van de arbeidsovereenkomst of bij de stopzetting van de overeengekomen loopbaanwijziging.  § 8. Het fonds wordt belast met de praktische uitwerking van de aanvraagprocedure en de betalingsmodaliteiten. Het fonds stelt hiertoe de nodige richtlijnen ter beschikking van de arbeiders en werkgevers. 2.9. Terugbetaling van loopbaanbegeleiding Art. 16ter. § 1. Vanaf 1 juli 2023 tot en met 30 juni 2025 kan de arbeider die als gevolg van het loopbaangesprek of op eigen initiatief een beroep doet op loopbaanbegeleiding, ten laste van het fonds aanspraak maken op een terugbetaling en dit voor onbepaalde duur. Deze terugbetaling stemt overeen met de kostprijs van de door de arbeider bij de VDAB bestelde loopbaancheque(s). Voor arbeiders die geen recht hebben op loopbaancheques, bedraagt de tussenkomst maximum 80 EUR per periode van 6 jaar.  § 2. Het fonds wordt belast met de praktische uitwerking van de aanvraagprocedure en de betalingsmodaliteiten. Het fonds stelt hiertoe de nodige richtlijnen ter beschikking van de arbeiders. 2.10. Terugbetaling van de kosten voor kinderopvang Art. 16quater. § 1. Het "Sociaal Fonds voor de metaalhandel" betaalt de kosten voor kinderopvang terug aan de arbeider, die op het moment van de aanvraag van de terugbetaling, ressorteert onder de bevoegdheid van het Paritair Subcomité voor de metaalhandel, onder de volgende voorwaarden :1° De terugbetaling geldt voor de kosten voor opvang van kinderen tot de leeftijd van 3 jaar die plaatsvond in de periode van 1 januari 2022 tot en met 31 december 2023 in een gezins- of groepsopvang die wordt erkend door Kind &amp; Gezin of l'Office de la Naissance et de l'Enfance; 2° De terugbetaling bedraagt 4 EUR per dag/per kind, met een maximum van 400 EUR per jaar/per kind en gebeurt op basis van het door de opvang uitgereikte fiscaal attest waarop het dagbedrag en het aantal dagen opvang worden vermeld voor het jaar voorafgaand aan het jaar waarin het attest werd uitgereikt; 3° De terugbetaling moet worden aangevraagd vóór 31 december 2027.  § 2. Het fonds wordt belast met de praktische uitwerking van de aanvraagprocedure en de betalingsmodaliteiten. Het fonds stelt hiertoe de nodige richtlijnen ter beschikking van de arbeiders en werkgevers. Vanaf 1 januari 2024 tot en met 31 december 2025 bedraagt de terugbetaling 5 EUR per dag/per kind, met een maximum van 500 EUR per jaar/per kind tot de leeftijd van 14 jaar, voor voorschoolse en naschoolse opvang inclusief vakantiekampen mits fiscaal attest voor de kosten die in 2024 en 2025 plaatsvonden. De terugbetaling moet worden aangevraagd vóór 31 december 2030. Op 30 juni 2025 zal de raad van bestuur een uitbreiding naar na- en voorschoolse opvang evalueren, voor kinderen die op de dag van de opvangactiviteit jonger zijn dan 14 jaar (of jonger dan 21 jaar, als het kind een zware handicap heeft), voor opvang voorzien door een instelling of opvangvoorziening die rechtstreeks, gesubsidieerd of gecontroleerd wordt door een openbaar bestuur. 2.11. Syndicale premie Art. 17. § 1. De bij artikel 5 bedoelde arbeiders, die sedert ten minste een jaar lid zijn van één van de representatieve interprofessionele werknemersorganisaties welke op nationaal niveau verbonden zijn, hebben recht, ten laste van het fonds, op een syndicale premie, voor zover zij op 1 oktober van het lopende jaar ingeschreven zijn in het personeelsregister van de bij hetzelfde artikel 5, bedoelde ondernemingen.  § 2. Het bedrag van de bij artikel 17, § 1 bedoelde syndicale premie wordt vastgelegd, op voorstel van de raad van bestuur van het fonds, in een algemeen verbindend verklaarde collectieve arbeidsovereenkomst. 2.12. Betalingsmodaliteiten van de bovengenoemde aanvullende vergoedingen Art. 18. § 1. De in artikelen 7 en 8 (aanvullende werkloosheidsvergoeding in geval van tijdelijke werkloosheid), 9 (aanvullende werkloosheidsvergoeding in geval van volledige werkloosheid), 10 en 10bis (aanvullende ziektevergoeding), 11 (aanvullende vergoeding voor oudere werkloze), 12 (aanvullende vergoeding voor oudere zieken), 14 (vergoeding voor sluiting van onderneming), 15 (aanvullende vergoeding voor stelsel van werkloosheid met bedrijfstoeslag), 16 en 16bis (aanvullende vergoeding bij vermindering van arbeidsprestaties, landingsbaan en zachte landingsbaan), 16ter (terugbetaling van loopbaanbegeleiding) en 16quater (terugbetaling van de kosten voor kinderopvang) bedoelde vergoedingen worden rechtstreeks door het fonds aan de betrokken arbeiders uitbetaald, voor zover zij het bewijs leveren van hun recht op de vergoedingen voorzien door voormelde artikelen en volgens de modaliteiten bepaald door de raad van bestuur.  § 2. De in artikel 17 bedoelde vergoeding wordt uitbetaald door de interprofessionele werknemersorganisaties die op nationaal vlak verbonden zijn. Art. 19. De raad van bestuur bepaalt de datum en de modaliteiten van de betaling van de door het fonds toegekende vergoedingen. In geen geval mag de betaling van de vergoeding afh</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de landbouw; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor de landbouw, betreffende de loon- en arbeidsvoorwaarden (vlas). Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 11 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de landbouw Collectieve arbeidsovereenkomst van 17 december 2024 Loon- en arbeidsvoorwaarden (vlas) (Overeenkomst geregistreerd op 7 januari 2025 onder het nummer 191334/CO/144) Preambule Betreft de aanpassing van de lonen en de premies aan de indexering met 1,9 pct. op 1 oktober 2024. HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de door hen tewerkgestelde werknemers, die ressorteren onder het Paritair Comité voor de landbouw en waarvan de hoofdactiviteit bestaat uit de vlasteelt, de hennepteelt, de eerste verwerking van vlas en/of hennep. Onder "eerste verwerking" wordt verstaan: het scheiden van de verschillende onderdelen van de plant. Zijn uitgesloten: de werknemers die tewerkgesteld worden in de sector en die bedoeld worden in artikel 8bis van het koninklijk besluit van 28 november 1969, Belgisch Staatsblad van 5 december 1969, inzake sociale zekerheid van de arbeiders. Met de term "werknemers" worden de arbeiders bedoeld zonder onderscheid naar gender. HOOFDSTUK II. - Beroepenclassificatie Art. 2. De functieclassificatie en de loonschalen zijn de volgende:   </t>
         </is>
       </c>
     </row>
@@ -2141,29 +2140,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2025003378</t>
+          <t>2025002984</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>20 mei 2025</t>
+          <t>30 mei 2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>13 april 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 11 juni 2018 tot vaststelling van het bedrag en de betalingsmodaliteiten van de vergoeding voor de stagemeesters in de geneeskunde van kandidaat-specialisten</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor het tuinbouwbedrijf, tot vaststelling van de werkgeversbijdrage in de vervoerskosten van de werknemers (1)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-20&amp;numac_search=2025003378&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003378=53&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-30&amp;numac_search=2025002984&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025002984=53&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, artikel 55, § 1, ingevoegd bij de wet van 11 augustus 2017 en § 3 gewijzigd bij de wet van 29 november 2022;Gelet op het koninklijk besluit van 11 juni 2018 tot vaststelling van het bedrag en de betalingsmodaliteiten van de vergoeding voor de stagemeesters in de geneeskunde van kandidaat-specialisten;Gelet op het advies van de Nationale Commissie artsen- ziekenfondsen, gedaan op 18 oktober 2024;Gelet op het advies van de Commissie voor begrotingscontrole, gegeven op 8 januari 2025;Gelet op het advies van het Comité van de verzekering voor geneeskundige verzorging, gegeven op 13 januari 2025;Gelet op het advies van de Inspectie van Financiën, gegeven op 23 januari 2025;Gelet op de akkoordbevinding van de Minister voor Begroting van 8 april 2025;Op de voordracht van Onze Minister van Sociale Zaken,Hebben Wij besloten en besluiten Wij :Artikel 1. Artikel 4, tweede lid van het koninklijk besluit van 11 juni 2018 tot vaststelling van het bedrag en de betalingsmodaliteiten van de vergoeding voor de stagemeesters in de geneeskunde van kandidaat specialisten, laatstelijk gewijzigd bij het koninklijk besluit van 6 februari 2024 wordt aangevuld met de volgende zin: « Voor het referentiejaar 2024 wordt dit bedrag vastgesteld op 686,78 EUR. »Art. 2. De minister bevoegd voor Sociale Zaken is belast met de uitvoering van dit besluit.Gegeven te Brussel, 13 april 2025..FILIPVan Koningswege :De Minister van Sociale Zaken en Volksgezondheid,F. VANDENBROUCKE 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor het tuinbouwbedrijf;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor het tuinbouwbedrijf, tot vaststelling van de werkgeversbijdrage in de vervoerskosten van de werknemers.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het tuinbouwbedrijfCollectieve arbeidsovereenkomst van 17 december 2024Vaststelling van de werkgeversbijdrage in de vervoerskosten van de werknemers (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191537/CO/145)HOOFDSTUK I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de werknemers van de ondernemingen die ressorteren onder het Paritair Comité voor het tuinbouwbedrijf.Onder "werknemers" wordt verstaan : de arbeiders en bedienden zonder onderscheid naar gender.HOOFDSTUK II. - Vergoeding bij openbaar vervoerArt. 2. De werknemers die gebruik maken van om het even welk gemeenschappelijk openbaar vervoer hebben recht ten laste van de werkgever op de terugbetaling van de gedragen kosten aan 100 pct. en dit voor de afstand afgelegd door de gemeenschappelijke vervoerdienst, tussen de woonplaats en de werkplaats.HOOFDSTUK III. - FietsvergoedingArt. 3. De werknemers die voor het woon-werkverkeer gebruik maken van de fiets hebben vanaf 1 januari 2024 recht op een vergoeding van 0,27 EUR per kilometer ten laste van de werkgever.HOOFDSTUK IV. -Vergoeding voor andere vervoermiddelenArt. 4. De werknemers die woonachtig zijn op 5 km en meer van de werkplaats, en die gebruik maken van andere dan in artikelen 2 en 3 bedoelde vervoermiddelen, hebben per begonnen arbeidsdag eveneens recht, ten laste van de werkgever, op een terugbetaling van de gedragen kosten. Deze terugbetaling bedraagt per begonnen arbeidsdag 70 pct. van 1/65ste van de effectieve prijs aan 139 pct. voor de driemaandelijkse treinkaart en dit voor de afgelegde afstand tussen de woonplaats en de werkplaats.Er is een maximum van 65/65sten per 3 maanden.Een tabel met de effectieve bedragen vanaf 1 februari 2025 is opgenomen als bijlage bij deze collectieve arbeidsovereenkomst.Voor de berekening van de afstand wordt het aantal kilometers langs de baan in aanmerking genomen, berekend van de werkplaats tot de woonplaats.Art. 5. Wanneer werknemers via carpooling naar het werk komen wordt onder de volgende voorwaarden de tussenkomst in het driemaandelijks sociaal abonnement gebracht op 139 pct., op de volgende voorwaarden :- er zijn ten minste 3 werknemers die carpooling doen;- de carpooling gebeurt permanent gedurende het ganse jaar;- de organisatie van het collectief vervoer is fiscaal aftrekbaar in de hoofde van de werkgever a rato van 120 pct.Art. 6. De terugbetaling van de gedragen kosten, waarvan sprake in de artikelen 2, 3, 4 en 5, geschiedt minstens om de maand.Art. 7. Onverminderd de regelingen vastgesteld bij de artikelen 2, 3, 4 en 5, blijven de gunstigere voorwaarden inzake vervoer en de terugbetaling van vervoerskosten die op het vlak van de onderneming bestaan, behouden.HOOFDSTUK V. - HandelsvertegenwoordigersArt. 8.  § 1. Wat de handelsvertegenwoordigers betreft, is de werkgever verplicht een vergoeding te betalen voor verplaatsingskosten, gedragen tijdens dienstprestaties indien de bediende niet over een bedrijfswagen beschikt. De tussenkomst voor de federale ambtenaren kan hier als richtlijn dienen. § 2. Verder wordt aanbevolen een dagelijkse forfaitaire baanvergoeding te betalen; dit kan een toeslag per gewerkte dag zijn ten titel van tussenkomst in de kosten voortvloeiend uit het werk op de baan (bijvoorbeeld drank, restauratie, telefoon,...) wanneer deze ontstaan buiten de privéwoonst en de zetel van de onderneming. De hierboven vermelde aanbeveling is niet van toepassing voor de ondernemingen die aan hun handelsvertegenwoordigers één of meerdere tussenkomsten voorzien die gelijk aan of hoger is dan bovenvermelde aanbeveling.HOOFDSTUK VI. - GeldigheidArt. 9. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van 1 februari 2025 en is gesloten voor een onbepaalde duur.Zij vervangt de collectieve arbeidsovereenkomst van 15 december 2023, geregistreerd onder het nummer 185565/CO/145.Zij kan door elk van de ondertekenende partijen worden opgezegd met een opzeg van drie maanden, betekend bij een ter post aangetekende brief, gericht aan de voorzitter van het Paritair Comité voor het tuinbouwbedrijf.Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025.De Minister van Werk,D. CLARINVALBijlage bij de collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor het tuinbouwbedrijf, tot vaststelling van de werkgeversbijdrage in de vervoerskosten van de werknemers  </t>
         </is>
       </c>
     </row>
@@ -2173,28 +2171,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2025004018</t>
+          <t>2025201163</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>26 mei 2025</t>
+          <t>30 mei 2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>11 april 2025. - Koninklijk besluit betreffende de benoeming van de regeringscommissaris van defensie en zijn plaatsvervanger bij het War Heritage Institute</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de orthopedische technologieën, betreffende de bestaanszekerheid van de werknemers (1)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-26&amp;numac_search=2025004018&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025004018=54&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-30&amp;numac_search=2025201163&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201163=54&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 16 maart 1954 betreffende de controle op sommige instellingen van openbaar nut, de artikelen 9 en 13;Gelet op de wet van 28 april 2017 tot oprichting van het "War Heritage Institute" en houdende integratie van de opdrachten, de middelen en het personeel van het Instituut voor veteranen - Nationaal Instituut voor oorlogsinvaliden, oud-strijders en oorlogsslachtoffers, het Koninklijk Museum van het Leger en de Krijgsgeschiedenis, het Nationaal Gedenkteken van het Fort van Breendonk en de Historische Pool van Defensie, artikel 21;Gelet op het koninklijk besluit van 2 september 2024 betreffende de benoeming van de regeringscommissaris van Defensie bij het War Heritage Institute;Overwegende dat er dient te worden voorzien in de vervanging van de heer Kurt Parreyn als regeringscommissaris van Defensie bij het War Heritage Institute;Op de voordracht van Onze Minister van Defensie,Hebben Wij besloten en besluiten Wij :Artikel 1. De heer Kurt Parreyn wordt eervol ontslag verleend als regeringscommissaris van Defensie bij het War Heritage Institute.Art. 2. De heer Joachim Pohlmann wordt benoemd tot regeringscommissaris van Defensie bij het War Heritage Institute.Art. 3. De heer Harold Van Pee wordt benoemd als plaatsvervanger van de regeringscommissaris van Defensie bij het War Heritage Institute.Art. 4. Dit besluit heeft uitwerking met ingang van 1 april 2025.Art. 5. De minister bevoegd voor Defensie is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 april 2025.FILIPVan Koningswege :De Minister van Defensie,T. FRANCKEN 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de orthopedische technologieën; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de orthopedische technologieën, betreffende de bestaanszekerheid van de werknemers. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 11 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.Bijlage Paritair Comité voor de orthopedische technologieën Collectieve arbeidsovereenkomst van 18 december 2024 Bestaanszekerheid van de werknemers (Overeenkomst geregistreerd op 23 januari 2025 onder het nummer 191610/CO/340) Toepassingsgebied Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en werknemers van de ondernemingen die behoren tot de bevoegdheid van het Paritair Comité voor de orthopedische technologieën (PC 340).  § 2. Onder "werknemers" wordt verstaan : alle arbeiders en bedienden verbonden met een arbeidsovereenkomst. Aanvullende werkloosheidsuitkering Art. 2. De werknemers die tijdelijk werkloos gesteld worden hebben recht op een aanvullende werkloosheidsuitkering van 22,73 EUR (index oktober 2024) per dag werkloosheid. Het bedrag van deze aanvullende werkloosheidsvergoeding wordt geïndexeerd volgens het indexsysteem dat van toepassing is bij de arbeiders. Slotbepalingen Art. 3.  § 1. Deze collectieve arbeidsovereenkomst treedt inwerking op 1 januari 2025 en is gesloten voor onbepaalde tijd.  § 2. Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst van 5 juli 2024 betreffende bestaanszekerheid, geregistreerd onder nr. 189899/CO/340. Laatstgenoemde collectieve arbeidsovereenkomst zal niet in werking treden.  § 3. Vanaf de inwerkingtreding van deze collectieve arbeidsovereenkomst, zal de collectieve arbeidsovereenkomst van 30 november 2011 betreffende de bestaanszekerheid van de werklieden en werksters, gesloten in het Paritair Subcomité voor de orthopedische schoeisels (108622/CO/128.06) de werkgevers en werknemers niet meer binden (cfr. artikel 27 van de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités).  § 4. Zij kan worden opgezegd door één van de partijen met inachtneming van een opzeggingstermijn van drie maanden bij een ter post aangetekende brief, gericht aan de voorzitter van het Paritair Comité voor de orthopedische technologieën. Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -2205,29 +2203,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2025004019</t>
+          <t>2025201170</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>26 mei 2025</t>
+          <t>30 mei 2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>11 april 2025. - Koninklijk besluit betreffende de benoeming van een regeringscommissaris van Defensie en zijn plaatsvervanger bij het Nationaal Geografisch Instituut</t>
+          <t>11 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden, betreffende het sectoraal pensioen- en solidariteitsstelsel voor de werknemers tewerkgesteld in een onderneming die behoort tot de bevoegdheid van het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden (1)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-26&amp;numac_search=2025004019&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025004019=55&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-30&amp;numac_search=2025201170&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201170=55&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 16 maart 1954 betreffende de controle op sommige instellingen van openbaar nut, artikel 9;Gelet op de wet van 8 juni 1976 houdende oprichting van het Nationaal Geografisch Instituut, artikel 10, § 1 en § 2;Gelet op het koninklijk besluit van 21 januari 2019 betreffende de benoeming van de regeringscommissaris van Defensie bij het Nationaal Geografisch Instituut;Gelet op het koninklijk besluit van 16 december 2020 betreffende de benoeming van de plaatsvervanger van de regeringscommissaris van Defensie bij het Nationaal Geografisch Instituut;Overwegende dat er dient te worden voorzien in de vervanging van de heer Sven De Mey als regeringscommissaris van Defensie bij het Nationaal Geografisch Instituut;Overwegende dat er dient te worden voorzien in de vervanging van de heer Yves Beaurain als plaatsvervanger van de regeringscommissaris van Defensie bij het Nationaal Geografisch Instituut;Op voordracht van de Minister van Landsverdediging,Hebben Wij besloten en besluiten Wij :Artikel 1. De heer Sven De Mey wordt eervol ontslag verleend als regeringscommissaris van Defensie bij het Nationaal Geografisch Instituut.Art. 2. De heer Yves Beaurain wordt eervol ontslag verleend als plaatsvervanger van de regeringscommissaris van Defensie bij het Nationaal Geografisch Instituut.Art. 3. De heer Bernard Phaleg wordt benoemd tot regeringscommissaris van Defensie bij het Nationaal Geografisch Instituut.Art. 4. De heer Jozef Desmedt wordt benoemd als plaatsvervanger van de regeringscommissaris van Defensie bij het Nationaal Geografisch Instituut.Art. 5. Dit besluit heeft uitwerking met ingang van 1 april 2025.Art. 6. De Minister bevoegd voor Defensie is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 april 2025.FILIPVan Koningswege :De Minister van Defensie,T. FRANCKEN 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden;Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden, betreffende het sectoraal pensioen- en solidariteitsstelsel voor de werknemers tewerkgesteld in een onderneming die behoort tot de bevoegdheid van het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 11 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden Collectieve arbeidsovereenkomst van 17 december 2024 Sectoraal pensioen- en solidariteitsstelsel voor de werknemers tewerkgesteld in een onderneming die behoort tot de bevoegdheid van het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden (Overeenkomst geregistreerd op 23 januari 2025 onder het nummer 191611/CO/323) Voorwoord Ingevolge de wet van 26 december 2022 tot wijziging van verscheidene bepalingen ter versterking van de transparantie in het kader van de tweede pensioenpijler ("Transparantiewet"), is vanaf 1 januari 2025, overeenkomstig de wet van 28 april 2003 betreffende de aanvullende pensioenen het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid, bij niet naleving door de pensioeninstelling van de betalingstermijn voor de in het pensioenreglement bedoelde prestaties, de wettelijke intrestvoet zoals bepaald in artikel 2, § 1 van de wet van 5 mei 1865 betreffende de lening tegen intrest, verschuldigd op de uit te keren prestaties. Teneinde laattijdige betaling van deze prestaties te voorkomen, dringen zich een aantal wijzigingen op aan het pensioen- en solidariteitsreglement. Verder dient, ingevolge de verhoging van de wettelijke pensioenleeftijd vanaf 2025, de einddatum van de pensioentoezegging aangepast te worden. Tot slot worden een aantal bepalingen geactualiseerd. HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst nr. 188083/CO/323 van 28 mei 2024, betreffende het sectoraal pensioen- en solidariteitsstelsel voor de werknemers tewerkgesteld in een van onderneming die behoort tot de bevoegdheid van het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en werknemers van de ondernemingen welke tot de bevoegdheid behoren van het Paritair Comité voor het beheer van gebouwen de vastgoedmakelaars en de dienstboden. Onder "werknemers" wordt verstaan: de mannelijke en vrouwelijke bedienden, arbeiders dienstboden aangegeven in de DmfA in de RSZ categorieën 037, 112 en 113. Art. 2. Deze collectieve arbeidsovereenkomst is evenwel niet van toepassing op: a) de werknemers tewerkgesteld met een overeenkomst van studentenarbeid, aangegeven in de DmfA met werknemerscode 840 en 841;b) de werknemers aangegeven in de DmfA in de RSZ categorieën 037, 112 en 113 met werknemerscode 035 en 439; c) de buiten België gevestigde werkgevers waarvan de werknemers in België gedetacheerd worden in de zin van de bepalingen van titel II van de EEG verordening nr. 1408/71 van de Raad. Art. 3. De voordelen, omschreven in deze collectieve arbeidsovereenkomst vallen onder toepassing van artikel 12 van de wet van 24 juli 1987 betreffende de tijdelijke arbeid. Art. 4. De partijen vragen de algemeen verbindend verklaring van deze collectieve arbeidsovereenkomst aan. HOOFDSTUK II. - Definities Art. 5. De begrippen die in deze collectieve arbeidsovereenkomst en haar bijlagen zijn opgenomen moeten worden opgevat in hun betekenis zoals verduidelijkt in de wet op de aanvullende pensioenen van 28 april 2003, hierna genoemd, en haar uitvoeringsbesluiten. HOOFDSTUK III. - Voorwerp Art. 6. Deze collectieve arbeidsovereenkomst regelt de omvorming van het sociaal sectoraal pensioenstelsel naar sectoraal pensioenstelsel met behoud van de solidariteitstoezegging. Het sociale karakter van het sectoraal pensioenstelsel wordt opgeheven. Overeenkomstig artikel 10, § 1, 3° van de WAP wordt deze beslissing tot opheffing van het sociale karakter genomen met 80 pct. van de stemmen van de in het paritair orgaan benoemde, gewone of plaatsvervangende leden die de werkgevers vertegenwoordigen en 80 pct. van de stemmen van de, in het paritair orgaan benoemde, gewone of plaatsvervangende leden die de werknemers vertegenwoordigen. Bijgevolg voldoet het sectoraal pensioenstelsel niet langer aan de voorwaarden voor een sociaal sectoraal pensioenstelsel zoals bepaald in artikel 10, § 1 van de WAP. Art. 7. Deze collectieve arbeidsovereenkomst voorziet een sectoraal pensioenplan dat twee luiken omvat: a) de pensioentoezegging; b) de solidariteitstoezegging. Art. 8. De mogelijkheid zoals voorzien in de WAP waardoor werkgevers de mogelijkheid zouden hebben om de uitvoering van het pensioenstelsel zelf te organiseren in een pensioenstelsel op het niveau van de onderneming ("opting out") wordt niet weerhouden. HOOFDSTUK IV. - Aanduiding van de inrichter Art. 9. Het "Fonds tweede pijler PC 323", opgericht door de collectieve arbeidsovereenkomst van 17 februari 2011, gewijzigd door de collectieve arbeidsovereenkomsten van 25 oktober 2011, van 25 juni 2014 en van 29 september 2020 tot oprichting van het "Fonds tweede pijler PC 323", wordt aangeduid als inrichter. Dit fonds, met maatschappelijke zetel te 1070 Anderlecht, Birminghamstraat 225 is een fonds voor bestaanszekerheid. Dit fonds zal hierna de inrichter genoemd worden. HOOFDSTUK V. Pensioentoezegging Art. 10. De regels en modaliteiten inzake de uitvoering van de pensioentoezegging, alsook de rechten en plichten van de inrichter, de pensioeninstelling, de aangeslotenen en hun begunstigden vastgelegd in het pensioenreglement, dat als bijlage 1 aan deze collectieve arbeidsovereenkomst is gevoegd. Art. 11. Het beheer van de pensioentoezegging omvat de volgende deelaspecten: administratief, financieel, boekhoudkundig en actuarieel beheer. Dit beheer wordt vanaf 1 oktober 2020 door de inrichter toevertrouwd aan AG Insurance NV, met maatschappelijke zetel te 1000 Brussel, Emile Jacqmainlaan 53, Belgische verzekeringsonderneming toegelaten onder code 0079, onder toezicht van de Nationale Bank van België, hierna de pensioeninstelling genoemd. Art. 12. Binnen de juridische structuur van de pensioeninstelling kan de inrichter ervoor opteren om één of meerdere deelaspecten van het beheer aan derden uit te besteden.HOOFDSTUK VI. - Solidariteitstoezegging Art. 13. De regels en modaliteiten inzake de uitvoering van de solidariteitstoezegging, alsook de rechten en plichten van de inrichter, de solidariteitsinstelling, de aangeslotenen en hun begunstigden zijn vastgelegd in het solidariteitsreglement, dat als bijlage 2 aan deze collectieve arbeidsovereenkomst is gevoegd. Art. 14. Beheer van de solidariteitstoezegging omvat de volgende deelaspecten: administratief, financieel, boekhoudkundig en actuarieel beheer. Dit beheer wordt door de inrichter toevertrouwd aan het "Waarborg- en Sociaal Fonds voor de vastgoedsector", met maatschappelijke zetel te 9000 Gent, Kortrijksesteenweg 1005, een fonds voor bestaanszekerheid, hierna de solidariteitsinstelling genoemd. Art. 15. Binnen de juridische structuur van de solidariteitsinstelling kan de inrichter ervoor opteren om één of meerdere deelaspecten van het beheer aan derden uit te besteden. HOOFDSTUK VII. - Financiering van het sectoraal pensioenplan Art. 16. De regels en de modaliteiten inzake de financiering van het sectoraal pensioenplan zijn vastgelegd in collectieve arbeidsovereenkomst. Voor de periode van 1 april 2010 tot 31 december 2011 wordt dit bepaald door de collectieve arbeidsovereenkomst van 25 februari 2010 betreffende de vaststelling van de forfaitaire bijdrage van het sectorale pensioenplan. Voor de periode van 1 januari 2012 tot 30 maart 2014 wordt dit bepaald door de collectieve arbeidsovereenkomst van 25 oktober 2011 betreffende de vaststelling van de bijdrage ter financiering van het sectorale pensioenplan. Voor de periode vanaf 1 april 2014 wordt dit bepaald door de collectieve arbeidsovereenkomst van 11 december 2013 betreffende de vaststelling van de bijdrage ter financiering van het sectorale pensioenplan. HOOFDSTUK VIII. - Inwerkingtreding van het sectoraal pensioenplan Art. 17. Het sociaal sectoraal pensioenstelsel is in werking getreden op 1 april 2010. Vanaf 1 oktober 2020 werd het sociaal sectoraal pensioenstelsel omgevormd naar een sectoraal pensioenstelsel met een solidariteitsluik. HOOFDSTUK IX. - Inwerkingtreding, geldigheidsduur en opzeggingsprocedure van deze collectieve arbeidsovereenkomst Art. 18. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025 en wordt gesloten voor onbepaalde duur. Zij vervangt de collectieve arbeidsovereenkomst nr. 188083/CO/323 van 28 mei 2024, afgesloten binnen het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden, ter invoering van een sociaal sectoraal pensioenplan voor de werknemers tewerkgesteld in een onderneming die behoort tot de bevoegdheid van het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden. Art. 19. Deze collectieve arbeidsovereenkomst kan opgezegd worden mits naleving van een opzeggingstermijn van zes maanden, betekend bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden. HOOFDSTUK X. - Bijlagen Art. 20. De volgende bijlagen maken integraal deel uit van deze collectieve arbeidsovereenkomst: a) bijlage 1: pensioenreglement; b) bijlage 2: solidariteitsreglement. Gezien om te worden gevoegd bij het koninklijk besluit van 11 mei 2025. De Minister van Werk, D. CLARINVALBijlage 1 aan de collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden, betreffende het sectoraal pensioen- en solidariteitsstelsel voor de werknemers tewerkgesteld in een onderneming die behoort tot de bevoegdheid van het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden Pensioenreglement 1. Voorwerp De pensioentoezegging heeft tot doel om een kapitaal samen te stellen dat aan de aangeslotene uitgekeerd wordt, of aan zijn rechthebbende(n) ingeval de aangeslotene overlijdt vóór de voorziene einddatum. Het kapitaal kan op vraag van de begunstigde(n) omgezet worden in een lijfrente. Dit pensioenreglement bepaalt, samen met de algemene voorwaarden, de rechten en verplichtingen van de inrichter, de pensioeninstelling, de ondernemingen, de aangeslotenen en hun rechthebbenden, en de voorwaarden waaronder deze rechten uitgeoefend kunnen worden. Dit pensioenreglement is een onderdeel van de collectieve arbeidsovereenkomst van 17 december 2024 betreffende het sectoraal pensioenstelsel. 2. Begripsomschrijving In dit reglement worden een aantal begrippen gebruikt, die de volgende betekenis hebben: Inrichter Het fonds voor bestaanszekerheid "Fonds 2de pijler PC 323" met zetel te 1070 Anderlecht, Birminghamstraat 225. Collectieve arbeidsovereenkomst die het pensioenstelsel invoert De collectieve arbeidsovereenkomst van 17 februari 2011 tot invoering van een aanvullend sectoraal pensioenstelsel voor de werknemers tewerkgesteld in de ondernemingen die behoren tot de bevoegdheid van het Paritair Comité 323 voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden. Van 1 januari 2012 tot 31 maart 2014 wordt deze collectieve arbeidsovereenkomst vervangen door de collectieve arbeidsovereenkomst van 25 oktober 2011 betreffende het sociaal sectoraal pensioenplan voor de werknemers tewerkgesteld in een onderneming die behoort tot de bevoegdheid van het Paritair Comité 323 voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden. Voor de periode vanaf 1 april 2014 wordt deze collectieve arbeidsovereenkomst vervangen door de collectieve arbeidsovereenkomst van 25 juni 2014 betreffende het sociaal sectoraal pensioenplan voor de werknemers tewerkgesteld in een onderneming die behoort tot de bevoegdheid van het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden. Vanaf 1 maart 2020 tot en met 30 september 2020 wordt de collectieve arbeidsovereenkomst van 25 juni 2014 vervangen door de collectieve arbeidsovereenkomst van 11 maart 2021 betreffende het sectoraal pensioenplan voor de werknemers tewerkgesteld in een onderneming die behoort tot de bevoegdheid van het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden. Voor de periode vanaf 1 oktober 2020 wordt de collectieve arbeidsovereenkomst van 11 maart 2021 vervangen door de collectieve arbeidsovereenkomst van 31 mei 2021 betreffende het sectoraal pensioenplan voor de werknemers tewerkgesteld in een onderneming die behoort tot de bevoegdheid van het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden. Voor de periode vanaf 1 januari 2024 wordt de collectieve arbeidsovereenkomst van 31 mei 2021 vervangen door de collectieve arbeidsovereenkomst van 28 mei 2024 betreffende het sectoraal pensioenplan voor de werknemers tewerkgesteld in een onderneming die behoort tot de bevoegdheid van het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden. Onderneming De onderneming die valt binnen het toepassingsgebied van de collectieve arbeidsovereenkomst van 28 mei 2024 betreffende het sectoraal pensioenplan voor de werknemers tewerkgesteld in een onderneming die behoort tot de bevoegdheid van het Paritair Comité voor het beheer van gebouwen, de vastgoedmakelaars en de dienstboden. Aangeslotene 1. De werknemer waarvoor de inrichter een pensioenstelsel heeft ingevoerd, en die aan de aansluitingsvoorwaarden van het pensioenreglement voldoet (de "actieve aangeslotene" genoemd);2. Het gewezen personeelslid dat nog steeds actuele of uitgestelde rechten geniet overeenkomstig het pensioenreglement (de "slaper" genoemd). Pensioeninstelling AG Insurance NV, met maatschappelijke zetel te 1000 Brussel, Emile Jacqmainlaan 53, RPR Brussel, BE 0404.494.849, Belgische verzekeringsonderneming toegelaten onder code 0079, onder toezicht van de Nationale Bank van België, hierna de pensioeninstelling genoemd. Einddatum De einddatum is de datum waarop het bedrag dat op de pensioenrekening opgebouwd werd opeisbaar is en kan omgezet worden in een rente. Tot en met 31 december 2024 is de einddatum vastgesteld op de eerste van de maand volgend op de maand waarin de aangeslotene de leeftijd van 65 jaar bereikt. Met ingang van 1 januari 2025 is de einddatum vastgesteld op de eerste dag van de maand volgend op de maand waarin de aangeslotene de wettelijke pensioenleeftijd bereikt, behoudens vervroeging of verdaging van de einddatum. Pensionering De effectieve ingang van het rustpensioen, al dan niet vervroegd, in het wettelijk pensioenstelsel voor werknemers. Pensioenstelsel De collectieve pensioentoezegging beschreven in de collectieve arbeidsovereenkomst die het sectoraal pensioenstelsel invoert. Pensioentoezegging De toezegging van de inrichter om een aanvullend pensioen ten voordele van de aangeslotene en/of zijn begunstigde samen te stellen. Verworven reserve Met "verworven reserve" wordt de reserve waarop de aangeslotene op een bepaald ogenblik recht heeft overeenkomstig dit pensioenreglement bedoeld. Gezien deze pensioentoezegging een integrerend onderdeel uitmaakt van het sectoraal pensioenstelsel, dienen in het pensioenreglement gehanteerde termen die niet zouden opgenomen zijn in de hiervoor vermelde begrippenlijst te worden opgevat in hun betekenis in het licht van de wet betreffende de aanvullende pensioenen van 28 april 2003, hierna WAP genoemd. WAP De wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en sommige aanvullende voordelen inzake sociale zekerheid. Refertekwartalen De 4 aaneensluitende kwartalen onmiddellijk voorafgaand aan de 2 kwartalen voorafgaand aan het kwartaal van pensionering of van overlijden. Deze kwartalen vormen samen een vaste periode: indien voor een kwartaal geen bijdrage werd gestort, blijven de refertekwartalen ongewijzigd. 3. Aansluiting De aansluiting is verplicht voor alle werknemers die zijn tewerkgesteld met een arbeidsovereenkomst bij een onderneming waarop de collectieve arbeidsovereenkomst tot invoering van het aanvullend sectoraal pensioenstelsel van toepassing is. Worden evenwel uitgesloten: - werknemers met een arbeidsovereenkomst voor uitzendarbeid, zoals geregeld door hoofdstuk II van de wet van 24 juli 1987 betreffende de tijdelijke arbeid, de uitzendarbeid en het ter beschikking stellen van werknemers ten behoeve van gebruikers; - werknemers met een arbeidsovereenkomst die gesloten werd in het kader van een speciaal door of met steun van de overheid gevoerd opleidings-, arbeidsinpassings- en omscholingsprogramma. - werknemers met vakantie-, studenten- en IBO-contracten (individuele beroepsopleiding); - werknemers die al een wettelijk pensioen genieten op het ogenblik dat ze aangesloten zouden moeten worden. De aansluiting heeft plaats op de datum waarop de werknemer aan de aansluitingsvoorwaarden voldoet en ten vroegste op 1 april 2010.4. De pensioentoelage en hoe ze aangewend wordt 4.1. Het bedrag van de pensioentoelage De uitbetalingen op de einddatum en in geval van vroegtijdig overlijden voor de einddatum, worden gefinancierd door trimestriële pensioentoelagen die door de onderneming ten gunste van de aangeslotene gestort worden aan de pensioeninstelling. De Rijksdienst voor Sociale Zekerheid (RSZ) wordt belast met de inning van deze pensioentoelagen. De regels en de modaliteiten inzake de financiering van het aanvullend pensioenplan worden vastgelegd in een collectieve arbeidsovereenkomst. Van 1 april 2010 tot 31 december 2011 is dit de collectieve arbeidsovereenkomst van 25 februari 2010. Bij de toekenning van de bijdragen op de individuele pensioenrekening wordt evenwel geen rekening gehouden met de hierna vermelde DmfA "gelijkgestelde" prestatiecodes: 004, 012, 020, 024, 030, 073 en de codes aangegeven met de "indicatieve codes". Voor de periode van 1 januari 2012 tot 31 maart 2014 wordt dit bepaald door de collectieve arbeidsovereenkomst van 25 oktober 2011 betreffende de vaststelling van de bijdrage ter financiering van het sectorale pensioenplan. Voor de periode vanaf 1 april 2014 wordt dit bepaald door de collectieve arbeidsovereenkomst van 11 december 2013 betreffende de vaststelling van de bijdrage ter financiering van het sectorale pensioenplan. 4.2. De aanwending van de pensioentoelage  § 1. De pensioentoelage wordt voor iedere aangeslotene op een individuele pensioenrekening gestort voor een verzekering van een "uitgesteld kapitaal met terugbetaling van de reserve in het geval van overlijden" (UKMTR). De oprenting gebeurt vanaf de 1ste dag van het 2de trimester volgend op het einde van het trimester waarop de pensioentoelagen betrekking hebben. Voor wat betreft de pensioentoelagen dewelke betrekking hebben op het jaar 2010 gebeurt de oprenting vanaf de 1ste dag volgend op de storting van de pensioentoelagen in het financieringsfonds.  § 2. Voor pensioneringen vanaf 1 januari 2025 wijkt voor het kwartaal van pensionering en de twee daaraan voorafgaande kwartalen de pensioentoelage die, na afhouding van alle toepasselijke kosten en fiscale en parafiscale lasten, op de individuele pensioenrekening van de aangeslotene wordt gestort af van de pensioentoelage berekend conform de collectieve arbeidsovereenkomst van 11 december 2013 betreffende de vaststelling van de bijdrage ter financiering van het sectorale pensioenplan. Voor deze kwartalen wordt de pensioentoelage berekend zoals hierna beschreven: De pensioentoelage voor het kwartaal van pensionering wordt berekend op het gemiddelde over de refertekwartalen van het referteloon per kwartaal, pro rata het aantal verlopen maanden in het kwartaal van pensionering vóór de datum van pensionering. De bijdragen voor de twee kwartalen voorafgaand aan het kwartaal van pensionering worden eveneens berekend op het gemiddelde over de refertekwartalen van het referteloon per kwartaal. Het referteloon van de refertekwartalen die zich bevinden in het jaar/de jaren voor het jaar van pensionering zal voor de berekening van de bijdrage voor het kwartaal van pensionering en de twee daaraan voorafgaande kwartalen, aangepast worden aan de indexering en de sectoraal afgesproken baremaverhogingen van de lonen.  § 3. Voor overlijdens vanaf 1 januari 2025 wijkt voor het kwartaal van overlijden en de twee daaraan voorafgaande kwartalen de pensioentoelage die op de individuele pensioenrekening van de aangeslotene wordt gestort af van de pensioentoelage berekend conform de collectieve arbeidsovereenkomst van 11 december 2013 betreffende de vaststelling van de bijdrage ter financiering van het sectorale pensioenplan. Voor deze kwartalen wordt de bijdrage berekend op dezelfde wijze als de bijdragen voor het kwartaal van pensionering en de twee daaraan voorafgaande kwartalen, zoals beschreven in § 2.  § 4. De in § 2 en § 3 hiervoor beschreven berekening van de pensioentoelage is definitief. Voor zover als nodig worden alle aan onderhavig pensioenreglement verwante documenten naar analogie aangepast voor de berekening van de pensioentoelage van het kwartaal van pensionering en de twee daaraan voorafgaande kwartalen, en voor de berekening van de bijdrage voor het kwartaal van overlijden en de twee daaraan voorafgaande kwartalen. § 5. In afwijking van § 1 gebeurt de oprenting van de pensioentoelagen die betrekking hebben op het kwartaal van pensionering en op de twee daaraan voorafgaande kwartalen, alsook de pensioentoelagen die betrekking hebben op het kwartaal van overlijden en op de twee daaraan voorafgaande kwartalen, vanaf de eerste dag van de maand van pensionering dan wel overlijden. 4.3. Het rendement De pensioenrekening ontvangt een door de pensioeninstelling gewaarborgd rendement. De aanzuivering van eventuele tekorten ten opzichte van de minimumgarantie overeenkomstig de wetgeving en reglementering van toepassing op de aanvullende pensioenen (artikel 24 van de WAP) wordt ten laatste verricht op één van de volgende gebeurtenissen: - de overdracht van de verworven reserves naar een andere pensioeninstelling of de onthaalstructuur; - de pensionering van de aangeslotene; - de opheffing van het pensioenstelsel. Het ontbrekende deel wordt geput uit het financieringsfonds. 4.4. Winstdeelname De pensioeninstelling kan overgaan tot het toekennen van een winstdeelname. Deze winstdeelname zal op de individuele pensioenrekening gestort worden voor wat betreft de reserve die op de individuele rekening aanwezig is, en in het financieringsfonds voor wat betreft de daar aanwezige reserve. 5. Uitbetaling op de einddatum 5.1. De einddatum De einddatum waarop het bedrag dat op de pensioenrekening opgebouwd werd opeisbaar is, is vastgesteld op de eerste dag van de maand volgend op de maand waarin de aangeslotene de wettelijke pensioenleeftijd bereikt, tenzij verdaging of vervroeging van de einddatum. De uitbetaling kan gebeuren onder de vorm van een kapitaal of rente. 5.2. Verdaging van de einddatum Indien de actieve aangeslotene nog niet zijn (wettelijk) pensioen heeft opgenomen op de einddatum, blijft de pensioentoelage verschuldigd zo lang hij in dienst blijft, en er wordt een nieuwe einddatum vastgesteld door de eerdere einddatum telkens met 1 jaar te verlengen. Deze verdaging zal plaatsvinden volgens de door de pensioeninstelling bij de bevoegde controleautoriteit ingediende tarieven die in voege zijn op de datum van de verdaging. Voor de aangeslotene die is uitgetreden vóór de einddatum en zijn verworven reserve bij de pensioeninstelling gelaten heeft (de slaper), worden de reserves verder door de pensioeninstelling beheerd. De aangeslotene zal dan de uitbetaling van zijn pensioenrekening bekomen: - wanneer hij zijn wettelijk pensioen opneemt; of - wanneer de aangeslotene hierom verzoekt. 5.3. Vervroeging van de einddatum (vervroegde uitbetaling) De vervroeging van de einddatum leidt tot de uitbetaling van de pensioenrechten aan de aangeslotene vóór de einddatum (vervroegde uitbetaling). De aangeslotene kan de vervoegde uitbetaling van de pensioenrechten ten vroegste vanaf de leeftijd van 60 jaar bekomen: - wanneer hij voldoet aan de voorwaarden om met vervroegd wettelijk pensioen te gaan; - of bij zijn brugpensioen (stelsel van werkloosheid met bedrijfstoeslag) in het kader van een herstructureringsplan opgemaakt en gecommuniceerd aan de regionale en federale minister van werk vóór 1 oktober 2015, conform artikel 63/3 van de WAP. De vervroegde uitbetaling brengt het verval van het recht op een uitkering bij overlijden vóór de einddatum mee. 6. Uitkering in geval van overlijden vóór de einddatum Wanneer een aangeslotene overlijdt, heeft de begunstigde recht op de op het ogenblik van het overlijden opgebouwde waarde op de individuele pensioenrekening. 7. Verworven rechten van de aangeslotene op de reserves De reserves opgebouwd vóór 1 januari 2019 op de individuele rekeningen, zijn verworven door de aangeslotene indien gedurende minstens vier, niet noodzakelijk opeenvolgende, trimesters bijdragen betaald werden aan het sectoraal pensioenstelsel. Voor de aangeslotene in dienst van een werkgever onderworpen aan onderhavig pensioenreglement in de loop van het vierde kwartaal 2018, wordt deze voorwaarde tevens als vervuld beschouwd en de vóór 1 januari 2019 opgebouwde reserves als verworven indien deze aangeslotene in de loop van het eerste kwartaal van 2019 nog steeds in dienst is van een werkgever onderworpen aan onderhavig pensioenreglement. De reserves opgebouwd vanaf 1 januari 2019 op de individuele rekeningen, zijn onmiddellijk verworven door de aangeslotene. Een aangeslotene die ervoor gekozen heeft zijn verworven reserves over te dragen naar een andere pensioeninstelling en die nadien opnieuw wordt aangesloten, wordt eveneens als een nieuwe aangeslotene beschouwd. De pensioenrekening kan niet in pand gegeven worden, en de begunstiging ervan kan niet overgedragen worden. Er kan geen voorschot op toegekend worden. De bedragen van de niet verworven reserves worden in het financieringsfonds gestort. Deze bepaling houdt op uitwerking te hebben voor reserves opgebouwd vanaf 1 januari 2019. 8. De aangeslotene verlaat de sector vóór de einddatum De uittreding wordt geacht te hebben plaatsgevonden: - In geval van beëindiging van de arbeidsovereenkomst met een werkgever op wie dit pensioenreglement van toepassing is, anders dan door overlijden of pensionering; - In geval van beëindiging van de aansluiting vanwege het feit dat de aangeslotene niet langer de aansluitingsvoorwaarden van het pensioenstelsel vervult, zonder dat dit samenvalt met de beëindiging van de arbeidsovereenkomst, anders dan door overlijden of pensionering; - In geval van beëindiging van de aansluiting vanwege het feit dat de werkgever of, in geval van de overgang van de arbeidsovereenkomst, de nieuwe werkgever niet langer valt onder het toepassingsgebied van de collectieve arbeidsovereenkomst die het pensioenstelsel heeft ingevoerd. In geval van beëindiging van de aansluiting vanwege het feit dat de aangeslotene niet langer de aansluitingsvoorwaarden van het pensioenstelsel vervult, zonder dat dit samenvalt met de beëindiging van de arbeidsovereenkomst, anders dan door overlijden of pensionering, worden de verworven reserves bij de pensioeninstelling behouden en worden bij overlijden de verworven reserves uitgekeerd aan de begunstigden overeenkomstig de voorrangsorde bepaald in het pensioenreglement. In de twee andere gevallen heeft de aangeslotene een aantal keuzemogelijkheden omtrent de bestemming van zijn verworven reserves, desgevallend aangevuld tot de bedragen van de minimumgarantie overeenkomstig de wetgeving en reglementering van toepassing op de aanvullende pensioenen. Hij kan opteren voor een overdracht naar een andere pensioeninstelling. Hij kan daarbij kiezen voor: - de overdracht naar de pensioeninstelling van zijn nieuwe werkgever met inbegrip van de pensioeninstelling van de sector waaronder zijn nieuwe werkgever ressorteert, voor zover hij bij de pensioentoezegging van die werkgever of sector wordt aangesloten; - de overdacht naar een pensioeninstelling die de totale winst onder de aangeslotenen in verhouding tot hun reserves verdeelt en de kosten beperkt volgens de regels vastgesteld door de Koning. De pensioeninstelling voert de overdracht uit binnen de dertig dagen nadat zij van de beslissing tot overdracht werd ingelicht. Indien de aangeslotene niet kiest voor de overdracht naar een andere pensioeninstelling, kan hij: - zijn verworven reserves in het pensioenstelsel laten zonder wijziging. In dat geval geniet hij van een overlijdensdekking gelijk aan het bedrag van de verworven reserves; - opteren om zijn verworven reserves vervroegd te ontvangen voor zover dit niet strijdig is met de wetgeving en reglementering van toepassing op de aanvullende pensioenen. Indien de aangeslotene zijn keuze niet schriftelijk heeft meegedeeld binnen de dertig dagen vanaf dat hij van de diverse keuzemogelijkheden op de hoogte werd gebracht, wordt hij geacht te hebben gekozen voor het behoud van zijn verworven reserves bij de pensioeninstelling zonder wijziging van de pensioentoezegging. Na afloop van die termijn kan hij ten alle tijd alsnog kiezen voor de overdracht van zijn verworven reserves naar een andere pensioeninstelling. 9. De manier van uitbetalen De begunstigde(n) kan (kunnen) evenwel vragen om het kapitaal dat aan hem(n) toekomt, om te vormen in een lijfrente. De hoogte van de lijfrente wordt bepaald op basis van de op het moment van de omzetting door de pensioeninstelling gehanteerde tarieven. Een keuze voor een vereffening als lijfrente moet bij de aanvraag van de uitbetaling schriftelijk door de begunstigde meegedeeld worden.Het kan volgens de keuze van de begunstigde gaan om een lijfrente die enkel aan hem betaald wordt, of om een lijfrente die in geval van overlijden van de begunstigde voor 50 pct. of 75 pct. overdraagbaar is op de overlevende echtgeno(o)t(e) of op de partner waarmee hij wettelijk samenwoont. De renten worden in maandelijkse delen betaald op de laatste dag van elke maand tot en met de laatste vervaldag die voorafgaat aan het overlijden van de begunstigde(n). Wanneer de lijfrente bij aanvang lager is dan 500 EUR per jaar, wordt het pensioenkapitaal uitgekeerd en heeft de begunstigde geen optie tot omzetting in lijfrente. De in deze paragraaf vermelde drempels worden geïndexeerd volgens de bepalingen van de wet van 2 augustus 1971 houdende inrichting van een stelsel waarbij de wedden, lonen, pensioenen, toelagen en tegemoetkomingen ten laste van de openbare schatkist geïndexeerd worden. Alle bedragen, voordelen en uitkeringen die voortvloeien uit onderhavig pensioenreglement vormen brutobedragen, waarop alle bij wet verschuldigde inhoudingen, heffingen, bijdragen en belastingen in mindering gebracht moeten worden. Al deze inhoudingen, heffingen, bijdragen en belastingen zijn ten laste van de aangeslotene(n) of de begunstigde(n). 10. Begunstigden 10.1. De begunstigde van de uitkering op de einddatum Indien de aangeslotene in leven is op de einddatum, wordt het kapitaal uitgekeerd aan de aangeslotene zelf. Alle rechtsvorderingen tussen een werknemer en/of een aangeslotene, enerzijds, en een inrichter en/of een pensioeninstelling, anderzijds, die voortvloeien uit of verband houden met een aanvullend pensioen of het beheer ervan, verjaren door verloop van vijf jaar vanaf de dag volgend op die waarop de benadeelde werknemer of aangeslotene kennis heeft gekregen of redelijkerwijze kennis had moeten krijgen, hetzij van het voorval dat het vorderingsrecht doet ontstaan, hetzij van de schade</t>
         </is>
       </c>
     </row>
@@ -2237,29 +2234,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2025004020</t>
+          <t>2025003102</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>26 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>11 april 2025. - Koninklijk besluit betreffende de benoeming van een regeringscommissaris en zijn plaatsvervanger bij de Centrale Dienst voor Sociale en Culturele Actie van het Ministerie van Landsverdediging</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor de landbouw, tot vaststelling van de werkgeversbijdrage in de vervoerskosten van de werknemers (1)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-26&amp;numac_search=2025004020&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025004020=56&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025003102&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003102=56&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 16 maart 1954 betreffende de controle op sommige instellingen van openbaar nut, artikel 9;Gelet op de wet van 10 april 1973 houdende oprichting van een Centrale Dienst voor Sociale en Culturele actie van het Ministerie van Landsverdediging, artikel 13;Gelet op het koninklijk besluit van 30 september 2024 betreffende de benoeming van de regeringscommissaris van Defensie bij de Centrale Dienst voor Sociale en Culturele Actie van het Ministerie van Landsverdediging;Overwegende dat er dient te worden voorzien in de vervanging van de heer Kurt Parreyn als regeringscommissaris van Defensie bij de Centrale Dienst voor Sociale en Culturele Actie van het Ministerie van Landsverdediging;Op voordracht van de Minister van Landsverdediging,Hebben Wij besloten en besluiten Wij :Artikel 1. De heer Kurt PARREYN wordt eervol ontslag verleend als regeringscommissaris van Defensie bij de Centrale Dienst voor Sociale en Culturele Actie van het Ministerie van Landsverdediging.Art. 2. De heer Jozef Desmedt wordt benoemd tot regeringscommissaris van Defensie bij de Centrale Dienst voor Sociale en Culturele actie ten behoeve van de leden van de militaire gemeenschap.Art. 3. Mevrouw Pascale Van Leeuwen wordt benoemd als plaatsvervanger van de regeringscommissaris van Defensie bij de Centrale Dienst voor Sociale en Culturele actie ten behoeve van de leden van de militaire gemeenschap.Art. 4. Dit besluit heeft uitwerking met ingang van 1 april 2025.Art. 5. De Minister bevoegd voor Defensie is belast met de uitvoering van dit besluit.Gegeven te Brussel, 11 april 2025.FILIPVan Koningswege :De Minister van Defensie,T. FRANCKEN 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de landbouw;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor de landbouw, tot vaststelling van de werkgeversbijdrage in de vervoerskosten van de werknemers.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 7 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de landbouwCollectieve arbeidsovereenkomst van 17 december 2024Vaststelling van de werkgeversbijdrage in de vervoerskosten van de werknemers (Overeenkomst geregistreerd op 7 januari 2025 onder het nummer 191335/CO/144)HOOFDSTUK I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de werknemers van de ondernemingen die ressorteren onder het Paritair Comité voor de landbouw.Onder "werknemers" worden verstaan : de arbeiders en bedienden zonder onderscheid naar gender.HOOFDSTUK II. - Vergoeding bij openbaar vervoerArt. 2. De werknemers die gebruik maken van om het even welk gemeenschappelijk openbaar vervoer hebben recht, ten laste van de werkgever, op de terugbetaling van de gedragen kosten aan 100 pct. en dit voor de afstand afgelegd door de gemeenschappelijke vervoerdienst, tussen de woonplaats en de werkplaats.HOOFDSTUK III. - FietsvergoedingArt. 3. De werknemers die voor het woon-werkverkeer gebruik maken van de fiets hebben vanaf 1 januari 2024 recht, ten laste van de werkgever, op een vergoeding van 0,27 EUR per kilometer.HOOFDSTUK IV. - Vergoeding voor andere vervoermiddelenArt. 4. De werknemers die woonachtig zijn op 5 km en meer van de werkplaats, en die gebruik maken van andere dan in artikelen 2 en 3 bedoelde vervoermiddelen, hebben per begonnen arbeidsdag eveneens recht, ten laste van de werkgever, op een terugbetaling van de gedragen kosten. Deze terugbetaling bedraagt per begonnen arbeidsdag 70 pct. van 1/65ste van de effectieve prijs aan 139 pct. voor de driemaandelijkse treinkaart en dit voor de afgelegde afstand tussen de woonplaats en de werkplaats. Er is een maximum van 65/65sten per 3 maanden.Een tabel met de effectieve bedragen vanaf 1 februari 2025 is opgenomen als bijlage bij deze collectieve arbeidsovereenkomst.Voor de berekening van de afstand wordt het aantal kilometers langs de baan in aanmerking genomen, berekend van de werkplaats tot de woonplaats.Art. 5. Wanneer werknemers via carpooling naar het werk komen wordt onder de volgende voorwaarden de tussenkomst in het driemaandelijks sociaal abonnement gebracht op 139 pct., op de volgende voorwaarden :- er zijn ten minste 3 werknemers die carpooling doen;- de carpooling gebeurt permanent gedurende het ganse jaar;- de organisatie van het collectief vervoer is fiscaal aftrekbaar in de hoofde van de werkgever a rato van 120 pct.Art. 6. De terugbetaling van de gedragen kosten, waarvan sprake in de artikelen 2, 3, 4 en 5, geschiedt minstens om de maand.Art. 7. Onverminderd de regelingen vastgesteld bij de artikelen 2, 3, 4 en 5, blijven de gunstigere voorwaarden inzake vervoer en de terugbetaling van vervoerskosten die op het vlak van de onderneming bestaan, behouden.HOOFDSTUK V. - HandelsvertegenwoordigersArt. 8.  § 1. Wat de handelsvertegenwoordigers betreft, is de werkgever verplicht een vergoeding te betalen voor verplaatsingskosten, gedragen tijdens dienstprestaties indien de bediende niet over een bedrijfswagen beschikt. De tussenkomst voor de federale ambtenaren kan hier als richtlijn dienen. § 2. Verder wordt aanbevolen een dagelijkse forfaitaire baanvergoeding te betalen; dit kan een toeslag per gewerkte dag zijn ten titel van tussenkomst in de kosten voortvloeiend uit het werk op de baan (bijvoorbeeld drank, restauratie, telefoon,...) wanneer deze ontstaan buiten de privéwoonst en de zetel van de onderneming. De hierboven vermelde aanbeveling is niet van toepassing voor de ondernemingen die aan hun handelsvertegenwoordigers één of meerdere tussenkomsten voorzien die gelijk aan of hoger is dan bovenvermelde aanbeveling.HOOFDSTUK VI. - GeldigheidArt. 9. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van 1 februari 2025 en is gesloten voor een onbepaalde duur.Zij vervangt de collectieve arbeidsovereenkomst van 15 december 2023, gesloten in hetzelfde paritair comité, tot vaststelling van de werkgeversbijdrage in de vervoerskosten van de werknemers (registratienummer : 185622/CO/144).Zij kan door elk van de ondertekenende partijen worden opgezegd met een opzeg van drie maanden, betekend bij een ter post aangetekende brief, gericht aan de voorzitter van het Paritair Comité voor de landbouw.Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025.De Minister van Werk,D. CLARINVALBijlage aan de collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor de landbouw, tot vaststelling van de werkgeversbijdrage in de vervoerskosten van de werknemers  </t>
         </is>
       </c>
     </row>
@@ -2269,28 +2265,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2025200242</t>
+          <t>2025201253</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>05 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 26 november 2024, gesloten in het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf, tot wijziging van de collectieve arbeidsovereenkomst van 14 mei 1980 tot vaststelling van de arbeidsvoorwaarden (registratienummer 6406/CO/130 - koninklijk besluit van 30 januari 1981 - Belgisch Staatsblad van 24 maart 1981) (1)</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 15 januari 2025, gesloten in het Paritair Comité voor de handel in voedingswaren, betreffende de lonen (dranken) (verhoging met 0,4 pct. vanaf 1 januari 2022) (1)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-05&amp;numac_search=2025200242&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200242=57&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025201253&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201253=57&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 26 november 2024, gesloten in het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf, tot wijziging van de collectieve arbeidsovereenkomst van 14 mei 1980 tot vaststelling van de arbeidsvoorwaarden (registratienummer 6406/CO/130 - koninklijk besluit van 30 januari 1981 - Belgisch Staatsblad van 24 maart 1981). Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 10 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf Collectieve arbeidsovereenkomst van 26 november 2024 Wijziging van de collectieve arbeidsovereenkomst van 14 mei 1980 tot vaststelling van de arbeidsvoorwaarden (registratienummer 6406/CO/130 - koninklijk besluit van 30 januari 1981 - Belgisch Staatsblad van 24 maart 1981) (Overeenkomst geregistreerd op 5 december 2024 onder het nummer 190889/CO/130) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werknemers en werkgevers die onder de bevoegdheid vallen van het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf. Zij geldt niet voor de werknemers en werkgevers die onder de toepassing vallen van de collectieve arbeidsovereenkomst afgesloten op 18 oktober 2007 in het voornoemd paritair comité, tot vaststelling van de arbeidsvoorwaarden in de ondernemingen van de dagbladpers (koninklijk besluit van 1 juli 2008, Belgisch Staatsblad van 14 oktober 2008), met registratienummer 85853/CO/130 (gewijzigd bij collectieve arbeidsovereenkomst van 19 november 2009). Onder "werknemers" worden zowel werknemers als werkneemsters verstaan. Art. 2.  "Hoofdstuk V - Koppeling van de lonen aan het indexcijfer van de consumptieprijzen" van de collectieve arbeidsovereenkomst van 14 mei 1980 tot vaststelling van de arbeidsvoorwaarden wordt vervangen door volgende bepaling:"HOOFDSTUK V. - Koppeling van de lonen aan het gezondheidsindexcijfer Art. 15. Met ingang van 1 januari 2025 worden de wekelijkse minimumlonen bepaald door artikel 8, elk jaar op 1 januari en op 1 juli aangepast in functie van de reële evolutie van het afgevlakte gezondheidsindexcijfer. De berekening gebeurt als volgt: - Op 1 januari: Het afgevlakte gezondheidsindexcijfer van december van het jaar -1 in verhouding tot het afgevlakte gezondheidsindexcijfer van juni van het jaar -1. - Op 1 juli: Het afgevlakte gezondheidsindexcijfer van juni van het lopende jaar in verhouding tot de afgevlakte gezondheidsindexcijfer van december van het jaar -1. De afgevlakte gezondheidsindex is gelijk aan het rekenkundige gemiddelde van de gezondheidsindexen van de laatste vier maanden, welke berekend worden zoals bepaald in artikel 2, § 2, 1ste lid van het koninklijk besluit van 24 december 1993 ter uitvoering van de wet van 6 januari 1989 tot vrijwaring van 's lands concurrentievermogen (gewijzigd door de wet van 23 april 2015 tot verbetering van de werkgelegenheid). Voor de berekening van de afgevlakte gezondheidsindex wordt een tijdsafhankelijke vermenigvuldigingsfactor toegepast zoals bepaald in de artikelen 2bis en 2quater van hetzelfde koninklijk besluit. Art. 16. De nachttoeslag, zoals overeengekomen in artikel 10 van de collectieve arbeidsovereenkomst van 30 november 1990 betreffende het collectief contract (27157/CO/130, koninklijk besluit van 14 september 1992, Belgisch Staatsblad van 9 oktober 1992), die verbonden is aan het minimumloon volgt dezelfde evolutie. Art. 17. De verhogingen ingevolge de indexevolutie worden toegepast op het deel van het loon dat gelijk is aan het minimumloon, bepaald door artikel 8, ongeacht het bedrag van het werkelijk betaalde loon. Bij negatieve inflatie worden de lonen niet verlaagd maar wordt de negatieve index in rekening gebracht bij de volgende positieve index. Het minimum weekloon wordt afgerond op drie cijfers na de komma, waarbij het derde decimaal naar boven wordt afgerond als het vierde decimaal groter of gelijk is aan vijf. Art. 18. Om de overgang van het loonindexmechanisme te waarborgen, namelijk van de spilindex gekoppeld aan het indexcijfer van de consumptieprijzen naar de indexquotiëntberekening in functie van de reële evolutie van het afgevlakte gezondheidscijfer, wordt er per 1 januari 2025 een eenmalige overgangsmaatregel gehanteerd. De afgevlakte gezondheidsindex van december 2024 wordt vergeleken met de laatst overschreden spilindex van het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf. Het resultaat hiervan wordt uitgedrukt in een percentage. Art. 19. Per 1 januari 2025 worden de minimumlonen, bepaald door artikel 8, en de nachttoeslag, zoals vermeld in artikel 16, verhoogd met het percentage bepaald in artikel 18. Vanaf 1 juli 2025 worden de minimumlonen, bepaald door artikel 8, en de nachttoeslag, zoals vermeld in artikel 16, verhoogd zoals bepaald in artikel 15.". Art. 3. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025. Zij is gesloten voor dezelfde geldigheidsduur en volgens dezelfde opzeggingsmodaliteiten en -termijnen als de collectieve arbeidsovereenkomst loonvoorwaarden van 14 mei 1980 (registratienummer 6406/CO/130). Gezien om te worden gevoegd bij het koninklijk besluit van 10 april 2025. De Minister van Werk, D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de handel in voedingswaren; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 15 januari 2025, gesloten in het Paritair Comité voor de handel in voedingswaren, betreffende de lonen (dranken) (verhoging met 0,4 pct. vanaf 1 januari 2022). Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.Bijlage Paritair Comité voor de handel in voedingswaren Collectieve arbeidsovereenkomst van 15 januari 2025 Lonen (dranken) (verhoging met 0,4 pct. vanaf 1 januari 2022) (Overeenkomst geregistreerd op 31 januari 2025 onder het nummer 191691/CO/119) HOOFDSTUK I. - Toepassingsgebied Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de arbeiders tewerkgesteld in de handel in bier en drinkwaters.  § 2. Met "arbeiders" worden de mannelijke en de vrouwelijke arbeiders bedoeld. HOOFDSTUK II. - Loonschalen I Art. 2.  § 1. In ondernemingen waar de ecocheques, toe te kennen op grond van de collectieve arbeidsovereenkomst van 28 mei 2009 betreffende de ecocheques, werden omgezet in een ander voordeel en in ondernemingen waar de ecocheques, op grond van de collectieve arbeidsovereenkomst van 6 oktober 2011 betreffende de omzetting van de ecocheques, werden omgezet in een ander voordeel of in een verhoging van de maaltijdcheque met 1,08 EUR, blijven de gemaakte afspraken onverkort gelden.  § 2. Voor een arbeidstijdregeling van 38 uur per week zijn deze ondernemingen gehouden de lagere loonschalen te betalen : loonschalen I (ecocheques omgezet in een ander voordeel). De werknemers- en werkgeversorganisaties verbinden er zich toe om deze afspraken niet opnieuw in vraag te stellen. HOOFDSTUK III. - Loonschalen II Art. 3. Voor een arbeidstijdregeling van 38 uur per week zijn de volgende ondernemingen gehouden vanaf 1 januari 2016 de verhoogde loonschalen te betalen : loonschalen II (loonschalen I + 0,0875 EUR/uur) : - De ondernemingen waar de ecocheques, toe te kennen op grond van de collectieve arbeidsovereenkomst van 28 mei 2009 betreffende de ecocheques, niet werden omgezet in een ander voordeel en in ondernemingen waar de ecocheques, op grond van de collectieve arbeidsovereenkomst van 6 oktober 2011 betreffende de omzetting van de ecocheques, niet werden omgezet in een ander voordeel of in een verhoging van de maaltijdcheque met 1,08 EUR; - De ondernemingen opgericht vanaf 1 januari 2016; - De reeds vóór 1 januari 2016 bestaande ondernemingen die pas vanaf 1 januari 2016 voor het eerst arbeiders in dienst genomen hebben. HOOFDSTUK IV. - Beroepsclassificatie Art. 4. De in deze collectieve arbeidsovereenkomst vastgestelde minimumuurlonen stemmen overeen met de categorieën bepaald in de collectieve arbeidsovereenkomst van 1 oktober 1973, gesloten in het Paritair Comité voor de handel in voedingswaren, betreffende de classificatie van de arbeiders tewerkgesteld in de handel in bier en drinkwaters. HOOFDSTUK V. - Jongerenbarema's Art. 5.  § 1. De arbeiders - uitgezonderd de studenten, leerlingen en stagiaires - die minder dan 21 jaar oud zijn, hebben, afhankelijk van hun leeftijd, recht op een bepaald percentage van de minimumuurlonen van de arbeiders van 21 jaar zoals vastgesteld in de loonschalen I : 20 jaar : 100 pct.; 19 jaar : 100 pct.; 18 jaar : 100 pct.; 17 jaar : 77,5 pct.; 16 jaar : 70 pct.; 15 jaar : 70 pct.  § 2. Ingeval de loonschalen II van toepassing zijn, worden de toepasselijke bedragen van loonschaal I vermeerderd met 0,0875 EUR per uur. Art. 6.  § 1. De studenten, leerlingen en stagiaires die minder dan 21 jaar oud zijn, hebben, afhankelijk van hun leeftijd, recht op een bepaald percentage van de minimumuurlonen van de arbeiders van 21 jaar zoals vastgesteld in de loonschalen I : 20 jaar : 97,5 pct.; 19 jaar : 92,5 pct.; 18 jaar : 85 pct.;17 jaar : 77,5 pct.; 16 jaar : 70 pct.; 15 jaar : 70 pct.  § 2. Ingeval de loonschalen II van toepassing zijn, worden de toepasselijke bedragen van loonschaal I vermeerderd met 0,0875 EUR per uur. HOOFDSTUK VI Koppeling van de lonen aan de gezondheidsindex Art. 7. De minimumuurlonen vastgesteld in artikel 2, § 2 worden gekoppeld aan het indexcijfer van de gezondheidsindex overeenkomstig de collectieve arbeidsovereenkomst van 8 juni 2009 betreffende de indexering van de lonen. HOOFDSTUK VII Conventionele verhoging in toepassing van het sectorakkoord 2021-2022 Art. 8. De minimumbarema's en de werkelijk betaalde lonen zijn vanaf 1 januari 2022 verhoogd met 0,4 pct. Een gelijkwaardig voordeel kan ook op bedrijfsniveau worden toegekend. HOOFDSTUK VIII. - Slotbepalingen Art. 9. Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst van 27 maart 2019, geregistreerd onder het nummer 151751/CO/119, betreffende de lonen (dranken). Art. 10. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2022. Zij is gesloten voor onbepaalde tijd. Zij kan door elk van de ondertekenende partijen worden opgezegd mits een opzeggingstermijn van drie maanden gegeven bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Comité voor de handel in voedingswaren. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -2301,28 +2297,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2025200280</t>
+          <t>2025201191</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>06 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 6 december 2023, gesloten in het Paritair Comité voor de makelarij en verzekeringsagentschappen, in uitvoering van de collectieve arbeidsovereenkomst nr. 170 van 30 mei 2023 van de Nationale Arbeidsraad tot vaststelling, van 1 juli 2023 tot 30 juni 2025, van het interprofessioneel kader voor de aanpassing naar 55 jaar van de leeftijdsgrens, wat de toegang tot het recht op uitkeringen voor een landingsbaan betreft, voor werknemers met een lange loopbaan, zwaar beroep of uit een onderneming in moeilijkheden of herstructurering (1)</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 23 januari 2025, gesloten in het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf, betreffende de bepaling van het bedrag, de wijzen van toekenning en vereffening van een sluitingstoelage aan de werknemers getroffen door de sluiting van een onderneming waar minder dan 20 werknemers (minder dan 5 in geval van faillissement) zijn tewerkgesteld op het ogenblik dat de onderneming haar activiteit stillegt (1)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-06&amp;numac_search=2025200280&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200280=58&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025201191&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201191=58&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de makelarij en verzekeringsagentschappen; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 6 december 2023, gesloten in het Paritair Comité voor de makelarij en verzekeringsagentschappen, in uitvoering van de collectieve arbeidsovereenkomst nr. 170 van 30 mei 2023 van de Nationale Arbeidsraad tot vaststelling, van 1 juli 2023 tot 30 juni 2025, van het interprofessioneel kader voor de aanpassing naar 55 jaar van de leeftijdsgrens, wat de toegang tot het recht op uitkeringen voor een landingsbaan betreft, voor werknemers met een lange loopbaan, zwaar beroep of uit een onderneming in moeilijkheden of herstructurering. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 10 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de makelarij en verzekeringsagentschappen Collectieve arbeidsovereenkomst van 6 december 2023 Uitvoering van de collectieve arbeidsovereenkomst nr. 170 van 30 mei 2023 van de Nationale Arbeidsraad tot vaststelling, van 1 juli 2023 tot 30 juni 2025, van het interprofessioneel kader voor de aanpassing naar 55 jaar van de leeftijdsgrens, wat de toegang tot het recht op uitkeringen voor een landingsbaan betreft, voor werknemers met een lange loopbaan, zwaar beroep of uit een onderneming in moeilijkheden of herstructurering (Overeenkomst geregistreerd op 8 januari 2024 onder het nummer 184987/CO/307) Artikel 1. Toepassingsgebied Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de werkneemsters en werknemers van de ondernemingen die onder de bevoegdheid van het Paritair Comité voor de makelarij en verzekeringsagentschappen vallen. Art. 2. Deze collectieve arbeidsovereenkomst wordt afgesloten in toepassing van de collectieve arbeidsovereenkomst nr. 170 van 30 mei 2023 van de Nationale Arbeidsraad tot vaststelling, van 1 juli 2023 tot 30 juni 2025, van het interprofessioneel kader voor de aanpassing naar 55 jaar van de leeftijdsgrens, wat de toegang tot het recht op uitkeringen voor een landingsbaan betreft, voor werknemers met een lange loopbaan, die een zwaar beroep uitoefenen of tewerkgesteld zijn in een onderneming in moeilijkheden of herstructurering. Art. 3. In toepassing van artikel 3 van de collectieve arbeidsovereenkomst nr. 170 van 30 mei 2023, gesloten in de Nationale Arbeidsraad, wordt de leeftijdsgrens op 55 jaar gebracht voor de werknemers die in toepassing van artikel 8, § 1 van de collectieve arbeidsovereenkomst nr. 103 van 27 juni 2012 hun arbeidsprestaties verminderen tot een halftijdse betrekking, of met 1/5de, en die voldoen aan de voorwaarden zoals bepaald in artikel 6, § 5, lid 1, 2° en 3° van het koninklijk besluit van 12 december 2001, zoals gewijzigd door artikel 4 van het koninklijk besluit van 30 december 2014.Art. 4. Deze collectieve arbeidsovereenkomst wordt afgesloten voor bepaalde duur. Ze treedt in werking op 1 juli 2023 en houdt op van kracht te zijn op 30 juni 2025. Gezien om te worden gevoegd bij het koninklijk besluit van 10 april 2025. De Minister van Werk, D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 23 januari 2025, gesloten in het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf, betreffende de bepaling van het bedrag, de wijzen van toekenning en vereffening van een sluitingstoelage aan de werknemers getroffen door de sluiting van een onderneming waar minder dan 20 werknemers (minder dan 5 in geval van faillissement) zijn tewerkgesteld op het ogenblik dat de onderneming haar activiteit stillegt.Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf Collectieve arbeidsovereenkomst van 23 januari 2025 Bepaling van het bedrag, de wijzen van toekenning en vereffening van een sluitingstoelage aan de werknemers getroffen door de sluiting van een onderneming waar minder dan 20 werknemers (minder dan 5 in geval van faillissement) zijn tewerkgesteld op het ogenblik dat de onderneming haar activiteit stillegt (Overeenkomst geregistreerd op 31 januari 2025 onder het nummer 191705/CO/130) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de werknemers die onder het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf ressorteren. Art. 2. Deze collectieve arbeidsovereenkomst heeft tot doel de uitvoeringswijzen vast te leggen betreffende de toekenning van de sluitingstoelage bepaald in artikel 3, § 1, A, 3 van de statuten van het fonds voor bestaans- zekerheid, genaamd "Grafica Fonds", zoals vastgesteld in de bijlage 2 bij de collectieve arbeidsovereenkomst van 19 oktober 2023 houdende wijziging en coördinatie van de statuten van het fonds voor bestaanszekerheid, het "Bijzonder Fonds voor het grafische en dagbladbedrijf", in het kader van de integratie van de sectorfondsen. Art. 3. De toelage voor sluiting van ondernemingen wordt toegekend aan alle werknemers vermeld in artikel 6, § 1 van de statuten, die het slachtoffer zijn van de sluiting van een onderneming en die, op grond van het aantal tewerkgestelde werknemers, niet in aanmerking komen voor de ontslagvergoeding toegekend krachtens artikel 23 van de wet van 26 juni 2002 betreffende de sluiting van ondernemingen. Art. 4. De sluiting van onderneming betekent de definitieve stopzetting van iedere economische activiteit van een onderneming in één der sectoren vermeld in artikel 1 van het koninklijk besluit van 26 maart 1974 tot oprichting en tot vaststelling van de benaming en van de bevoegdheid van het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf, gewijzigd bij het koninklijk besluit van 1 juli 1974. Art. 5. De toelage voorzien bij deze collectieve arbeidsovereenkomst wordt niet toegekend aan de werknemers, slachtoffers van een sluiting van onderneming, die uit hoofde hiervan vergoedingen ontvangen vanwege het Fonds tot vergoeding van de in geval van sluiting van ondernemingen ontslagen werknemers, vanwege de werkgever zelf of vanwege enig andere organisatie. Art. 6. Het bedrag van de toelage bij sluiting van ondernemingen wordt als volgt berekend : a) een toelage van 90,29 EUR per jaar anciënniteit in de onderneming met een maximum van 20 jaar; b) een toelage van 90,29 EUR per leeftijdsjaar boven de 45 jaar met een maximum van 20 jaar. Art. 7. Aan de anciënniteitvoorwaarde moet voldaan zijn de dag waarop de opzegging ingaat, of in geval van contractverbreking zonder opzegging, de dag van de contractverbreking of van de sluiting van de onderneming.Art. 8. Het aantal jaren wordt berekend met ingang van de datum van tewerkstelling in de onderneming. De toelage is evenwel slechts verschuldigd na één jaar anciënniteit en wordt berekend per volledig verstreken jaar. Art. 9. De bedragen opgegeven in hogervermeld artikel 6 zijn geldig voor bedrijfssluitingen die plaatsvinden van 1 januari 2025 tot 31 december 2025. Deze bedragen worden jaarlijks per 1 januari aangepast door het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf op voorstel van het bestuursorgaan van Grafica, waarbij de toelagen vermeld in a) en b) van artikel 6, overeenstemmen met het bedrag vastgesteld krachtens artikel 23 van de wet van 26 juni 2002 betreffende de sluiting van de ondernemingen. Art. 10. De bij artikel 3 van deze collectieve arbeidsovereenkomst bedoelde werknemers vullen het daartoe door Grafica opgesteld document in en ondertekenen het. Dit document wordt vervolledigd door de werkgever, door de gemachtigde persoon die hem opvolgt, door de curator of door de diensten van het gemeentebestuur naargelang het gaat om een stopzetting van bedrijvigheid of om een faling. Dit document, behoorlijk ingevuld, vermeldt de geboortedatum van de werknemer, de periode waarin hij zonder onderbreking ingeschreven was in het personeelsregister van de onderneming, evenals de sluitingsdatum van het bedrijf. Art. 11. Het document wordt door de werknemer overhandigd aan de syndicale organisatie waarvan hij lid is of aan Grafica. Deze bepalen het bedrag waarop de werknemer krachtens deze collectieve arbeidsovereenkomst aanspraak kan maken en controleren of de werknemer aangesloten is bij één van de beroepsorganisaties zoals bepaald in artikel 6, § 1 van de statuten van Grafica. Art. 12. Grafica stort de nodige bedragen om de betaling aan de begunstigden van de toelage voor sluiting van ondernemingen te verzekeren aan het "Intersyndicaal Fonds van de grafische nijverheid en de dagbladen". Art. 13. De uitbetaling van de toelage voor sluiting van ondernemingen gebeurt overeenkomstig de bepalingen zoals beschreven in de statuten van Grafica. Art. 14. De aanvragen moeten door de betrokken werknemers worden ingediend vóór 31 maart van het jaar volgend op dit waarin de sluiting plaats vond. Art. 15. Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst van 15 februari 2024 tot bepaling van het bedrag, de wijzen van toekenning en vereffening van een sluitingstoelage aan de werknemers getroffen door de sluiting van een onderneming waar minder dan 20 werknemers (minder dan 5 in geval van faillissement) zijn tewerkgesteld op het ogenblik dat de onderneming haar activiteit stillegt (registratienummer 186303). Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025. Zij wordt voor onbepaalde tijd gesloten en kan door één van de partijen met drie maanden worden opgezegd bij een ter post aangetekende brief, gericht aan de voorzitter van het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf en aan de erin vertegenwoordigde organisaties. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -2333,29 +2329,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2025200203</t>
+          <t>2025003103</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>06 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10 april 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 24 november 2024, gesloten in het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf, betreffende de oprichting van een nieuw "Intersyndicaal Fonds van de grafische nijverheid en de dagbladen" (1)</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 28 januari 2025, gesloten in het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren, betreffende de pensioenpremie voor de uitzendkrachten (1)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-06&amp;numac_search=2025200203&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200203=59&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025003103&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003103=59&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 24 november 2024, gesloten in het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf, betreffende de oprichting van een nieuw "Intersyndicaal Fonds van de grafische nijverheid en de dagbladen". Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 10 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf Collectieve arbeidsovereenkomst van 24 november 2024 Oprichting van een nieuw "Intersyndicaal Fonds van de grafische nijverheid en de dagbladen" (Overeenkomst geregistreerd op 5 december 2024 onder het nummer 190885/CO/130) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en werknemers tewerkgesteld in de ondernemingen die onder de bevoegdheid vallen van het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf.Art. 2. Het fonds voor bestaanszekerheid voor werknemers die onder het paritair comité voor het drukkerij-, grafische kunst- en dagbladbedrijf vallen, genaamd "Grafica Fonds", voorziet in haar statuten en de bijhorende collectieve arbeidsovereenkomsten, dat er taken verdeeld worden naar de vzw "Intersyndicaal Sociaal Fonds". Art. 3. De vzw "Intersyndicaal Sociaal Fonds", met ondernemingsnummer 0414.569.585, wordt vervangen door de vzw "Intersyndicaal Fonds van de grafische nijverheid en de dagbladen", met ondernemingsnummer 1015.138.751. Art. 4. In alle collectieve arbeidsovereenkomsten afgesloten in het Paritair Comité voor het druk-kerij-, grafische kunst- en dagbladbedrijf, dienen verwijzingen naar de vzw "Intersyndicaal Sociaal Fonds", voortaan gelezen te worden als "Intersyndicaal Fonds van de grafische nijverheid en de dagbladen". Een lijst van de betreffende collectieve de arbeidsovereenkomsten is aangehecht als de bijlage aan deze collectieve arbeidsovereenkomst. Art. 5. Deze collectieve arbeidsovereenkomst treedt in werking op 20 november 2024. Zij wordt voor onbepaalde tijd gesloten en kan door één van de partijen met drie maanden worden opgezegd bij een ter post aangetekende brief, gericht aan de voorzitter van het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf en aan de erin vertegenwoordigde organisaties. Gezien om te worden gevoegd bij het koninklijk besluit van 10 april 2025. De Minister van Werk, D. CLARINVALBijlage bij de collectieve arbeidsovereenkomst van 24 november 2024, gesloten in het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf, betreffende de oprichting van een nieuw "Intersyndicaal Fonds van de grafische nijverheid en de dagbladen" Artikel 1. De collectieve arbeidsovereenkomsten afgesloten in het Paritair Comité voor het drukkerij-, grafische kunst- en dagbladbedrijf die naar : het "Intersyndicaal Sociaal Fonds" verwijzen, zijn de volgende : a) collectieve arbeidsovereenkomst van 19 oktober 2023 tot wijziging en coördinatie van het Fonds voor bestaanszekerheid, "Bijzonder Fonds voor het grafische en dagbladbedrijf", in het kader van de integratie van de sectorfondsen (registratienummer 185340/CO/130, koninklijk besluit van 24 oktober 2024, nog niet gepubliceerd in het Belgisch Staatsblad); b) collectieve arbeidsovereenkomst van 21 december 2023 betreffende de bepaling van het bedrag; de wijzen van toekenning en vereffening van een jaarlijkse syndicale toelage (registratienummer 184965/CO/130, koninklijk besluit van 1 september 2024, Belgisch Staatsblad van 27 september 2024); c) collectieve arbeidsovereenkomst van 15 februari 2024 betreffende de bepaling van het bedrag, de wijzen van toekenning en vereffening van een sluitingstoelage aan de werknemers getroffen door een sluiting van een onderneming waar minder dan 20 werknemers (minder dan 5 in geval van faillissement) zijn tewerkgesteld op het ogenblik dat de onderneming haar activiteit stillegt (registratienummer 186303/CO/130, koninklijk besluit van 1 oktober 2024, nog niet gepubliceerd in het Belgisch Staatsblad); d) collectieve arbeidsovereenkomst van 18 april 2024 tot bepaling van het bedrag, de wijzen van toekenning en vereffening van een opleidingstoelage (registratienummer 187718/CO/130, nog niet gepubliceerd in een koninklijk besluit, nog niet gepubliceerd in het Belgisch Staatsblad). Gezien om te worden gevoegd bij het koninklijk besluit van 10 april 2025. De Minister van Werk, D. CLARINVAL 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 28 januari 2025, gesloten in het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren, betreffende de pensioenpremie voor de uitzendkrachten.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 7 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leverenCollectieve arbeidsovereenkomst van 28 januari 2025Pensioenpremie voor de uitzendkrachten (Overeenkomst geregistreerd op 10 februari 2025 onder het nummer 191978/CO/322)PreambuleEen groeiend aantal sectoren waar de uitzendkrachten tewerkgesteld zijn, hebben een eigen sectorale pensioenpijler uitgewerkt.Daarbij betalen de bedrijven van deze sectoren een bijdrage aan een sectoraal orgaan ter dekking van de betaling van dit sectoraal pensioen.Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op :1°  de uitzendbureaus, bedoeld bij artikel 7, 1°  van de wet van 24 juli 1987 betreffende de tijdelijke arbeid, de uitzendarbeid en het ter beschikking stellen van werknemers ten behoeve van gebruikers;2°  de uitzendkrachten, bedoeld bij artikel 7, 3°  van genoemde wet van 24 juli 1987, die door de uitzendbureaus worden tewerkgesteld.Zijn uitgesloten uit het toepassingsgebied van onderhavige collectieve arbeidsovereenkomst :- de studenten uitzendkrachten onderworpen aan de solidariteitsbijdrage.Art. 2.  § 1. Partijen komen overeen voor de periode van 1 februari 2025 tot 30 juni 2026 de brutolonen van de uitzendkrachten, die tewerkgesteld zijn in sectoren met een sectorale pensioenregeling, te verhogen met een percentage dat overeenkomt met de in deze sectoren betaalde bijdrage, omgezet op basis van een reconversie coëfficiënt. § 2. Deze coëfficiënt houdt rekening met de patronale Rijksdienst voor Sociale Zekerheidsbijdragen.Deze reconversiecoëfficiënt bedraagt 0,6943 voor de arbeiders en 0,7158 voor de bedienden. § 3. De in § 1 genoemde percentages die van toepassing zijn voor de periode van 1 februari 2025 tot en met 30 juni 2026 zijn de percentages die opgenomen zijn in de bijlage bij deze collectieve arbeidsovereenkomst. § 4. De premie wordt berekend op het loon van de uitzendkracht en wordt toegekend per loonafrekening.De premie wordt afzonderlijk vermeld op de loonfiche van de uitzendkracht onder de uniforme benaming "pensioenpremie".Evenwaardig is de vermelding dat de "pensioenpremie" inbegrepen is in het brutoloon. § 5. Deze regeling maakt toepassing van artikel 12, tweede lid van de wet van 24 juli 1987 en geniet derhalve voorrang op de eventuele sectorale aanvullende pensioenregelingen van de gebruikende ondernemingen. § 6. De partijen komen overeen dat de volgende procedure wordt toegepast :Van zodra de voorzitter van het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren van de uitzendsector ervan verwittigd wordt dat er in een bepaalde sector een regeling inzake een sectorale pensioenpijler is overeengekomen, zal hij aan de voorzitter van het betrokken paritair comité vragen om de modaliteiten van deze regeling over te maken en zal hij deze informatie bezorgen aan de leden van het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren.Het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren sluit vervolgens een collectieve arbeidsovereenkomst af die voorziet in een regeling zoals hierboven overeengekomen.Een dergelijke regeling kan niet ingevoerd worden met terugwerkende kracht.Art. 3. Partijen engageren zich om het onderzoek verder te zetten met het oog op de creatie van een intersectoraal systeem op het niveau van de uitzendsector.Art. 4. Deze collectieve arbeidsovereenkomst treedt in werking op 1 februari 2025.Ze vervangt de collectieve arbeidsovereenkomst van 19 november 2024 betreffende de pensioenpremie voor de uitzendkrachten geregistreerd onder nummer 190880/CO/322 op 5 december 2024.Zij wordt gesloten voor een bepaalde duur en verstrijkt op 30 juni 2026.Zij kan, mits een opzeggingstermijn van 3 maanden wordt in acht genomen, door elk van de partijen worden opgezegd met een aangetekend schrijven gericht aan de voorzitter van het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren.Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025.De Minister van Werk,D. CLARINVALBijlage bij de collectieve arbeidsovereenkomst van 28 januari 2025, gesloten in het Paritair Comité voor de uitzendarbeid en de erkende ondernemingen die buurtwerken of -diensten leveren, betreffende de pensioenpremie voor de uitzendkrachten  </t>
         </is>
       </c>
     </row>
@@ -2365,28 +2360,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2025003574</t>
+          <t>2025201180</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>15 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10 april 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 23 maart 1982 tot vaststelling van het persoonlijk aandeel van de rechthebbenden of van de tegemoetkoming van de verzekering voor geneeskundige verzorging in het honorarium voor bepaalde verstrekkingen</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 16 januari 2025, gesloten in het Paritair Comité voor de bedienden van de textielnijverheid, betreffende het leven lang leren, het werkbaar werk en de arbeidsmarktwerking in de textielsector (1)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-15&amp;numac_search=2025003574&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003574=60&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025201180&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201180=60&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, artikel 37, § 1, derde lid, gewijzigd bij de wet van 20 december 1995, bij het koninklijk besluit van 16 april 1997, bekrachtigd bij de wet van 12 december 1997 en bij de wetten van 22 augustus 2002, 27 december 2006 en 29 maart 2012;Gelet op het koninklijk besluit van 23 maart 1982 tot vaststelling van het persoonlijk aandeel van de rechthebbenden of van de tegemoetkoming van de verzekering voor geneeskundige verzorging in het honorarium voor bepaalde verstrekkingen;Gelet op het advies van het Comité van de verzekering voor geneeskundige verzorging van het Rijksinstituut voor ziekte- en invaliditeitsverzekering, gegeven op 16 december 2024;Gelet op het advies van de inspecteur van financiën, gegeven op 7 januari 2025;Gelet op de akkoordbevinding van de Staatssecretaris voor Begroting, gegeven op 29 januari 2025;Gelet op het advies 77.515/2 van de Raad van State, gegeven op 17 maart 2025, met toepassing van artikel 84, § 1, eerste lid, 2°  van de wetten op de Raad van State gecoördineerd op 12 januari 1973;Overwegende het voorstel van de Overeenkomstencommissie kinesitherapeuten - verzekeringsinstellingen, gedaan op 26 november 2024;Overwegende het advies van de Commissie voor begrotingscontrole van 11 december 2024;Op de voordracht van de Minister van Sociale Zaken,Hebben Wij besloten en besluiten Wij :Artikel 1. In het koninklijk besluit van 23 maart 1982 tot vaststelling van het persoonlijk aandeel van de rechthebbenden of van de tegemoetkoming van de verzekering voor geneeskundige verzorging in het honorarium voor bepaalde verstrekkingen, wordt bijlage 2, die vervangen is bij het koninklijk besluit 9 oktober 2022, vervangen door de bijlage gevoegd bij dit besluit.Art. 2. Dit besluit treedt in werking op de eerste dag van de tweede maand na die waarin het is bekendgemaakt in het Belgisch Staatsblad.Art. 3. De minister bevoegd voor Sociale zaken is belast met uitvoering van dit besluitGegeven te Brussel 10 april 2025.FILIPVan Koningswege :De Minister van Sociale Zaken en Volksgezondheid,F. VANDENBROUCKEAnnexe à l'arrêté royal du 10 avril 2025 modifiant l'arrêté royal du 23 mars 1982 portant fixation de l'intervention personnelle des bénéficiaires ou de l'intervention de l'assurance soins de santé dans les honoraires pour certaines prestationsAnnexe 2.L'intervention personnelle du bénéficiaire dans l'honoraire des prestations reprises à l'article 7, § 1 de l'annexe à l'arrêté royal du 14 septembre 1984 (montants en euros).   </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de bedienden van de textielnijverheid; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 16 januari 2025, gesloten in het Paritair Comité voor de bedienden van de textielnijverheid, betreffende het leven lang leren, het werkbaar werk en de arbeidsmarktwerking in de textielsector.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de bedienden van de textielnijverheid Collectieve arbeidsovereenkomst van 16 januari 2025 Leven lang leren, het werkbaar werk en de arbeidsmarktwerking in de textielsector (Overeenkomst geregistreerd op 10 februari 2025 onder het nummer 191983/CO/214) I. Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op alle werkgevers die onder de bevoegdheid vallen van het Paritair Comité voor de bedienden van de textielnijverheid (PC nr. 214) en op de bedienden die ze tewerkstellen. Met "bedienden" worden de mannelijke en vrouwelijke bedienden bedoeld. II. Draagwijdte van de overeenkomst Art. 2. Deze collectieve arbeidsovereenkomst strekt ertoe de inspanningen die de sector in het kader van het paritair uitgebouwde sectoraal opleidingsbeleid de voorbije jaren heeft geleverd, minstens verder te zetten en waar mogelijk te verhogen. Deze collectieve arbeidsovereenkomst wordt gesloten voor de jaren 2025 en 2026 in toepassing van hoofdstuk 9 en 12 van de wet van 3 oktober 2022 houdende diverse arbeidsbepalingen. III. Werkbaar werk Art. 3. Vanuit Cobot en Cefret wordt de dienstverlening, begeleiding en ondersteuning met betrekking tot werkbaar werk verder uitgebouwd, ten dienste van de ondernemingen en de werknemers in de textielsector. Hiertoe wordt zowel voor 2025 als voor 2026 een budget voorzien dat overeenstemt met het budget van 2024. De sectorale sociale partners bepalen in de Permanente Beleidsgroep Opleiding de opdracht om hieromtrent sectorale expertise op te bouwen, waartoe de nodige middelen, zoals hiervoor aangeduid vanuit het "Fonds voor bestaanszekerheid van de bedienden van de textielnijverheid" worden ingezet. De sectorale sociale partners bepalen in de Permanente Beleidsgroep Opleiding de nodige modaliteiten en voorwaarden voor deze dienstverlening, begeleiding en ondersteuning met betrekking tot werkbaar werk. In geval van betwisting over de validatie van een project werkbaar werk, neemt de Permanente Beleidsgroep Opleiding de eindbeslissing. Eind 2026 zullen de sectorale sociale partners de stand van zaken betreffende het werkbaar werk evalueren. De statuten van het "Fonds voor bestaanszekerheid voor de bedienden van de textielnijverheid" worden in deze zin aangepast. De sectorale sociale partners zullen eveneens werken aan een globale toekomstvisie betreffende het werkbaar werk. IV. Sectorale en arbeidsmarktgerichte opleidingen Art. 4.  § 1. Om de participatiegraad aan opleiding te verhogen, zullen door Cobot vzw/Cefret asbl aanvragen ingediend worden bij het Paritair Comité voor de bedienden van de textielnijverheid voor de erkenning van sectorale beroepsopleidingen in het stelsel betaald educatief verlof (herstelwet van 22 januari 1985) of voor goedkeuring door het Paritair Comité voor de bedienden van de textielnijverheid van arbeidsmarktgerichte opleidingen in het stelsel van het Vlaams opleidingsverlof (decreet van 12 oktober 2018).  § 2. Voor de uren waarop de bediende deelneemt aan sectorale opleidingen, erkend door het Paritair Comité voor de bedienden van de textielnijverheid als beroepsopleiding in het stelsel van het betaald educatief verlof (herstelwet van 22 januari 1985) of arbeidsmarktgerichte opleidingen, goedgekeurd door het Paritair Comité voor de bedienden van de textielnijverheid in het stelsel van het Vlaams opleidingsverlof (decreet van 12 oktober 2018), heeft hij recht op zijn normaal loon, zonder toepassing van de loongrens, zoals voorzien in artikel 114 van de herstelwet van 22 januari 1985 houdende sociale bepalingen.  § 3. Voor de dagen dat de bediende deelneemt aan sectorale opleidingen, erkend door het Paritair Comité voor de bedienden van de textielnijverheid in het stelsel van het betaald educatief verlof (herstelwet van 22 januari 1985) of arbeidsmarktgerichte opleidingen, goedgekeurd door het Paritair Comité voor de bedienden van de textielnijverheid in het stelsel van het Vlaams opleidingsverlof (decreet van 12 oktober 2018), heeft hij recht op maaltijdcheques. V. Opleidingsplan Art. 5. In uitvoering van artikel 39 van de wet van 3 oktober 2022 houdende diverse arbeidsbepalingen wordt door Cobot vzw en Cefret asbl een webapplicatie "opleidingsplan" gebouwd ten dienste van de ondernemingen en de werknemers in de textielsector. De sectorale sociale partners bepalen in de Permanente Beleidsgroep Opleiding de opdracht en de inhoud hieromtrent alsook de nodige middelen die hiervoor vanuit het "Fonds voor bestaanszekerheid van de bedienden van de textielnijverheid" worden ingezet. De sectorale sociale partners wijzen op het belang van de uitvoering van de bepalingen opgenomen in artikel 36 van de wet van 3 oktober 2022 houdende diverse bepalingen. De werkgevers stellen één keer per burgerlijk jaar, vóór 31 maart, een opleidingsplan op voor hun werknemers in de schoot van de onderneming. Hiertoe legt de werkgever elk jaar een ontwerp van opleidingsplan voor aan de ondernemingsraad, of bij ontstentenis ervan, aan de vakbondsafvaardiging, ten minste vijftien dagen vóór de vergadering die wordt gepland met het oog op het onderzoeken ervan. De ondernemingsraad, of bij ontstentenis ervan, de vakbondsafvaardiging, geeft advies over het ontwerp tegen uiterlijk 15 maart. Bij ontstentenis van een ondernemingsraad en een vakbondsafvaardiging in de onderneming legt de werkgever het opleidingsplan voor aan de werknemers tegen uiterlijk 15 maart. De werkgever stelt het opleidingsplan op, met dien verstande dat bijzondere aandacht zal gaan naar personen komende uit de in artikel 35 van de wet van 3 oktober 2022 gedefinieerde risicogroepen, in het bijzonder de werknemers van minstens 50 jaar oud en naar knelpuntberoepen en naar de wijze van evaluatie met de werknemers. Een bijzondere aandacht zal tevens gaan naar de werknemers, bedoeld in artikel 1, 3°, g) van het koninklijk besluit van 19 februari 2013 tot uitvoering van artikel 189, 4de lid van de wet van 27 december 2006 houdende diverse bepalingen (I) alsook naar de werknemers met een handicap zoals bedoeld in artikel 1, 4° van het voormelde koninklijk besluit van 19 februari 2013. Bij de uitwerking van het opleidingsplan dient de genderdimensie in aanmerking te worden genomen. Het plan moet minimaal de bij artikel 6 bedoelde formele en informele opleidingen bevatten en uitleggen op welke wijze het bijdraagt aan de investeringen in opleiding, bedoeld in artikel 6. Het plan wordt voor een minimumduurtijd van één jaar gesloten. VI. Investeren in opleiding en groeipas Art. 6. Dit artikel 6 wordt gesloten in uitvoering van hoofdstuk 12 van de wet van 3 oktober 2022 betreffende diverse arbeidsbepalingen. In de ondernemingen die ten minste 20 werknemers tewerkstellen, uitgedrukt in voltijdse equivalenten, wordt voorzien in een individueel opleidingsrecht voor een voltijds tewerkgestelde werknemer met volgend groeipad : - vanaf 2023 : 2 dagen; - vanaf 2024 : 3 dagen;- vanaf 2026 : 4 dagen; - vanaf 2028 : 5 dagen. De werkgevers die minimum tien en minder dan twintig werknemers tewerkstellen, uitgedrukt in voltijdse equivalenten, voorzien in een individueel opleidingsrecht voor een voltijdse werknemer met volgend groeipad : - vanaf 2023 : 1 dag; - vanaf 2026 : 2 dagen. De werkgevers die minder dan tien werknemers tewerkstellen, worden uitgesloten van de toepassing van dit artikel 6. De sociale partners wijzen op het belang van opleiding en vorming en bevelen deze ondernemingen die minder dan 10 werknemers tewerkstellen, aan om hun werknemers te stimuleren om hun positie op de arbeidsmarkt door middel van vorming en opleiding te verstevigen. Voor de toepassing van dit artikel wordt het aantal tewerkgestelde werknemers berekend in voltijdse equivalenten op basis van de gemiddelde tewerkstelling van de referteperiode voorafgaand aan de tweejaarlijkse periode die voor de eerste keer op 1 januari 2022 begint. De referteperiode is de periode bestaande uit het vierde kwartaal van het voorlaatste jaar (n-2) en de eerste drie kwartalen van het jaar (n-1) voorafgaand aan de tweejaarlijkse periode. Om het gemiddeld aantal tewerkgestelde werknemers in voltijdse equivalenten tijdens de referteperiode te berekenen, wordt het totaal van de op het einde van elk kwartaal van de referteperiode aangegeven werknemers in voltijdse equivalenten, gedeeld door het aantal kwartalen waarvoor de werkgever, aan de Rijksdienst voor Sociale Zekerheid, werknemers aangegeven heeft die onderworpen zijn aan de wet van 27 juni 1969 tot herziening van de besluitwet van 28 december 1944 betreffende de maatschappelijke zekerheid der arbeiders. Indien de werkgever voor de bedoelde referteperiode geen aangiftes diende over te maken aan de rijksdienst, wordt voor de bepaling van het gemiddelde verwezen naar het aantal werknemers tewerkgesteld op de laatste dag van het kwartaal waarbinnen de eerste tewerkstelling volgend op de referteperiode plaatsgreep. De praktische tenuitvoerlegging van het individueel opleidingsrecht en de verwezenlijking van het groeipad wordt nagestreefd door : - het opleidingsaanbod van Cobot vzw en Cefret asbl beter en ruimer bekend te maken aan werkgevers en werknemers; - het opleidingsaanbod van Cobot vzw en Cefret asbl verder uit te breiden; - via Cobot vzw en Cefret asbl acties te ondernemen om de participatiegraad aan opleidingen te verhogen; - werkgevers aan te moedigen om alle, zowel formele als informele opleidingsinspanningen nauwgezet te registreren. Om het aantal individuele opleidingsdagen te bepalen worden minstens volgende opleidingen in aanmerking genomen : a) formele opleiding : door lesgevers of sprekers ontwikkelde cursussen en stages. Deze opleidingen worden gekenmerkt door een hoge graad van organisatie van de opleider of opleidingsinstelling. Ze gaan door op een plaats die duidelijk van de werkplek gescheiden is. Ze richten zich tot een groep leerlingen. Die opleidingen kunnen ontwikkeld en beheerd worden door de onderneming zelf of door een extern organisme; b) informele opleiding : de opleidingsactiviteiten, andere dan deze bedoeld onder a) die rechtstreeks betrekking hebben op het werk. Deze opleidingen worden gekenmerkt door een hoge graad van zelforganisatie door de individuele leerling of door een groep leerlingen met betrekking tot de tijd, de plaats en de inhoud, een inhoud die gekozen wordt volgens de individuele behoeften van de leerling op de werkplek, en met een rechtstreeks verband met het werk en de werkplek, met inbegrip van deelname aan conferenties of beurzen voor leerdoeleinden; c) de opleidingen die betrekking hebben op de materies inzake het welzijnsbeleid bedoeld in de wet van 4 augustus 1996 betreffende het welzijn van de werknemers bij de uitvoering van hun werk. Het saldo van de niet-opgebruikte opleidingsdagen wordt op het einde van het jaar overgedragen naar het daaropvolgende jaar, zonder dat dit saldo in mindering mag gebracht worden van het opleidingskrediet van de werknemer in dat volgende jaar. Het doel is dat op het einde van elke periode van vijf jaar, die ten vroegste kan beginnen op 1 januari 2024, of voor het einde van de arbeidsovereenkomst indien die eindigt voordat de voormelde periode van vijf jaar afloopt, de voltijds tewerkgestelde werknemer gemiddeld het minimum aantal opleidingsdagen per jaar zoals bepaald in dit artikel heeft opgenomen. Op het einde van de voormelde periode van vijf jaar, wordt het saldo van het beschikbare opleidingskrediet op nul gezet. VII. Eindbepalingen Art. 7. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025 en is gesloten voor de periode van 1 januari 2025 tot en met 31 december 2026, met uitzondering van artikel 4 dat van toepassing is gedurende de periode van 1 september 2025 tot en met 31 augustus 2027 alsook bijgevolg met uitzondering van artikel 1 waarvan de duurtijd eveneens verder loopt tot en met 31 augustus 2027. Art. 8. De ondertekenende partijen vragen dat deze collectieve arbeidsovereenkomst algemeen verbindend zou verklaard worden per koninklijk besluit. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
+</t>
         </is>
       </c>
     </row>
@@ -2396,28 +2392,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2025003575</t>
+          <t>2025201246</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>15 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10 april 2025. - Koninklijk besluit tot wijziging van artikel 7 van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 3 februari 2025, gesloten in het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Vlaamse Gemeenschap, betreffende de vaststelling van het percentage van de bijdragen voor het jaar 2025 voor het fonds voor bestaanszekerheid genaamd "Sociaal Fonds 319.01 tot financiering tweede pensioenpijler" en tot bepaling van de datum van aanvraag tot vrijstelling van de bijdragen voor het jaar 2025 (1)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-15&amp;numac_search=2025003575&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003575=61&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025201246&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201246=61&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, artikel 35, § 1, vijfde lid en § 2, eerste lid, 1°,  gewijzigd bij het koninklijk besluit van 25 april 1997, bekrachtigd bij de wet van 12 december 1997;Gelet op het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen;Gelet op de voorstellen van de Technische raad voor kinesitherapie, gedaan op 12 januari 2024, 27 juni 2024 en 8 november 2024;Gelet op de adviezen van de Dienst voor geneeskundige evaluatie en controle gegeven op 12 januari 2024, 27 juni 2024 en 8 november 2024;Gelet op de beslissing van de Overeenkomstencommissie kinesitherapeuten - verzekeringsinstellingen van 26 november 2024;Gelet op het advies van de Commissie voor begrotingscontrole van 11 december 2024;Gelet op de beslissing van het Comité van de verzekering voor geneeskundige verzorging van het Rijksinstituut voor ziekte- en invaliditeitsverzekering van 16 décember 2024;Gelet op het advies van de inspecteur van financiën, gegeven op 7 januari 2025;Gelet op de akkoordbevinding van de Staatssecretaris voor Begroting, gegeven op 29 januari 2025;Gelet op het advies 77.513/2 van de Raad van State, gegeven op 17 maart 2025, met toepassing van artikel 84, § 1, eerste lid, 2°  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Op de voordracht van de Minister van Sociale Zaken,Hebben Wij besloten en besluiten Wij :Artikel 1. In artikel 7 van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen, vervangen bij het koninklijk besluit van 18 december 2002 en gewijzigd bij de koninklijk besluiten van 25 april 2004, 17 februari 2005, 23 november 2005, 24 mei 2006, 1 juli 2006, 26 november 2006, 7 juni 2007, 20 oktober 2008, 26 april 2009, 29 april 2009, 29 augustus 2009, 22 juli 2010, 5 april 2011, 22 maart 2012, 19 september 2013, 21 februari 2014, 3 september 2015, 17 oktober 2016, 19 september 2017, 25 september 2018, 3 februari 2019, 3 maart 2021, 9 mei 2021, 20 mei 2021, 19 december 2021, 18 april 2022, 17 juni 2022, 9 februari 2023, 22 juni 2023, 1 oktober 2023 en 29 mei 2024 worden de volgende wijzigingen aangebracht :1°  § 1, 1°,  I. a) wordt aangevuld als volgt :  </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Vlaamse Gemeenschap; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 3 februari 2025, gesloten in het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Vlaamse Gemeenschap, betreffende de vaststelling van het percentage van de bijdragen voor het jaar 2025 voor het fonds voor bestaanszekerheid genaamd "Sociaal Fonds 319.01 tot financiering tweede pensioenpijler" en tot bepaling van de datum van aanvraag tot vrijstelling van de bijdragen voor het jaar 2025. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.Bijlage Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Vlaamse Gemeenschap Collectieve arbeidsovereenkomst van 3 februari 2025 Vaststelling van het percentage van de bijdragen voor het jaar 2025 voor het fonds voor bestaanszekerheid genaamd "Sociaal Fonds 319.01 tot financiering tweede pensioenpijler" en bepaling van de datum van aanvraag tot vrijstelling van de bijdragen voor het jaar 2025 (Overeenkomst geregistreerd op 10 februari 2025 onder het nummer 192003/CO/319.01) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de werknemers die ressorteren onder het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Vlaamse Gemeenschap (319.01). Onder "werknemers" wordt verstaan : het vrouwelijk en mannelijk werklieden- en bediendepersoneel. Art. 2. In toepassing van artikel 7 van de collectieve arbeidsovereenkomst van 7 februari 2011 tot wijziging van de statuten en de benaming van het fonds voor bestaanszekerheid genaamd "Sociaal Fonds 319.01 tot aanvullende financiering tweede pensioenpijler", gesloten in het Paritair subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Vlaamse Gemeenschap (319.01) (registratienummer 103830/CO/319.01, algemeen verbindend verklaard bij koninklijk besluit op 6 juli 2011, gepubliceerd in het Belgisch Staatsblad op 25 augustus 2011), wordt het percentage van de bijdragen voor het jaar 2025 op jaarbasis bepaald als volgt : per kwartaal 0,22 pct. van het brutobedrag van de bezoldigingen, vóór inhouding van de persoonlijke socialezekerheidsbijdragen. De inning van deze bijdragen geschiedt voor het jaar 2025 als volgt : - geen inning in het eerste en het tweede kwartaal; - 0,44 pct. van het brutobedrag van de bezoldigingen, vóór inhouding van de persoonlijke socialezekerheidsbijdragen, tijdens het derde en het vierde kwartaal. Art. 3.  § 1. In toepassing van artikel 7 van de hoger vermelde collectieve arbeidsovereenkomst wordt de datum waarop het attest van de actuaris aangetekend of per e-mail met ontvangstbevestiging aan het sociaal fonds moet worden overgemaakt voor het jaar 2025 vastgesteld op 15 april.  § 2. De vrijstelling van de bijdragen voor het jaar 2025 wordt enkel toegekend aan de ondernemingen die een door het sociaal fonds erkende vrijstelling van de bijdragen genoten in één of meer van de kalenderjaren 2008, 2009, 2010, 2011 en/of 2012 én die vanaf het kalenderjaar 2013 jaarlijks de aanvraag tot vrijstelling van de bijdragen indienen conform de geldende voorwaarden en procedures. Art. 4. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van de datum van ondertekening en is gesloten voor onbepaalde tijd. Zij kan worden opgezegd door elk van de partijen, mits een opzeggingstermijn van zes maanden, gericht bij een ter post aangetekend schrijven aan de voorzitter van het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Vlaamse Gemeenschap (319.01). Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
+</t>
         </is>
       </c>
     </row>
@@ -2427,28 +2424,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2025003917</t>
+          <t>2025201185</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>23 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10 april 2025. - Koninklijk besluit betreffende de toekenning van een subsidie aan 24 sociale actoren die werden geselecteerd uit de kandidaturen van de projectoproep "e-inclusion for Belgium - Sociale Actoren 2023" voor het tweede werkingsjaar van de uitvoering van een project gericht op de digitale inclusie van kwetsbare groepen in het kader van het project "e-inclusion for Belgium" van het Europees herstel- en veerkrachtplan</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 17 februari 2025, gesloten in het Paritair Comité voor de binnenscheepvaart, betreffende de eindejaarspremie (1)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-23&amp;numac_search=2025003917&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003917=62&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025201185&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201185=62&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 22 mei 2003 betreffende de organisatie van de begroting en van de comptabiliteit van de federale Staat, artikelen 121 tot 124 ;Gelet op de programmawet van 20 december 2020, artikel 91;Gelet op de wet van 23 december 2021 betreffende de Algemene uitgavenbegroting voor het begrotingsjaar 2022, artikel 2.06.4 ;Gelet op de wet van 26 december 2022 betreffende de Algemene uitgavenbegroting voor het begrotingsjaar 2023, artikel 2.06.4 ;Gelet op de wet van 22 december 2023 betreffende de Algemene uitgavenbegroting voor het begrotingsjaar 2024, artikel 2.06.4 ;Gelet op de financiënwet van 20 december 2024 voor het begrotingsjaar 2025 ;Gelet op de financiënwet van 25 maart 2025 voor het begrotingsjaar 2025 ;Gelet op het koninklijk besluit van 20 mei 2022 betreffende de administratieve, begrotings- en beheerscontrole, artikel 20 ;Gelet op de verordening (EU) 2021/241 van het Europees parlement en van de Raad van de Europese unie van 12 februari 2021 tot instelling van de herstel- en veerkrachtfaciliteit.Gelet op het Nationaal herstel- en veerkrachtplan zoals goedgekeurd door de Ministerraad op 30 april 2021.Gelet op de verordening (EU) 2023/435 van het Europees parlement en de Raad van 27 februari 2023 tot wijziging van Verordening (EU) 2021/241 wat betreft REPowerEU-hoofdstukken in herstel- en veerkrachtplannen en tot wijziging van Verordeningen (EU) nr. 1303/2013, (EU) 2021/1060 en (EU) 2021/1755 en Richtlijn 2003/87/EGGelet op de uitvoeringsbeslissing van de Raad van de Europese unie van 6 juli 2021 betreffende de goedkeuring van de evaluatie van het Belgische herstel- en veerkrachtplan;Gelet op de uitvoeringsbeslissing van de Europese Raad van 13 juli 2021 (en zijn bijlage) met betrekking tot de goedkeuring van de evaluatie van het Belgische plan voor Herstel en Veerkracht;Gelet op de uitvoeringsbeslissing van de Europese Raad van 13 juli 2021 (en zijn bijlage) met betrekking tot de goedkeuring van de evaluatie van het Belgische plan voor Herstel en Veerkracht;Gelet op het uitvoeringsbesluit van de Raad van de Unie van 8 december 2023 (en bijlage) dat het uitvoeringsbesluit van 13 juli 2021 wijzigt betreffende de goedkeuring van de beoordeling van het plan voor herstel en veerkracht voor België.Gelet op de verordening (EU) 2021/241 van het Europees parlement en van de Raad van de Europese unie van 12 februari 2021 tot instelling van de herstel- en veerkrachtfaciliteit.Gelet op de uitvoeringsbeslissing van de Europese Raad van 13 juli 2021 (en zijn bijlage) met betrekking tot de goedkeuring van de evaluatie van het Belgische plan voor Herstel en Veerkracht;Gelet op het uitvoeringsbesluit van de Raad van de Unie van 8 december 2023 (en bijlage) dat het uitvoeringsbesluit van 13 juli 2021 wijzigt betreffende de goedkeuring van de beoordeling van het plan voor herstel en veerkracht voor België.Gelet op het advies van de Inspectie van Financiën, gegeven op 2 juni 2023 ;Gelet op het advies van de Inspectie van Financiën, gegeven op 21 december 2023;Gelet op het advies van de Inspectie van Financiën, gegeven op 3 januari 2024;Gelet op het advies van de Inspectie van Financiën, gegeven op 31 januari 2024;Gelet op het advies van de Inspectie van Financiën, gegeven op 27 januari 2025;Gelet op het advies van de Inspectie van Financiën, gegeven op 28 maart 2025;Overwegende het belang van een snelle uitvoering van het project dat is opgenomen in het door de Ministerraad van 30 april 2021 goedgekeurde Nationaal Plan voor Herstel en Veerkracht betreffende de investeringen in digitaliseringOp de voordracht van de Minister van Asiel en Migratie, en Maatschappelijke Integratie, belast met Grootstedenbeleid;Hebben Wij besloten en besluiten Wij :Artikel 1.  § 1. Er wordt in het kader van het "e-inclusion for Belgium" project (referentie I408034vBE-C[42]-I[I-4.08]) van het Europees herstel- en veerkrachtplan aan 24 sociale actoren een subsidie van samen maximaal drie miljoen negenhonderdnegen duizend vierhonderdnegenenzestig euro en vierendertig cent (3.909.469,34 EUR) toegekend ter dekking van de kosten die gepaard gaan met de verwezenlijking van het tweede jaar van projecten inzake digitale inclusie van kwetsbare groepen in onze maatschappij. § 2. De subsidie van drie miljoen negenhonderdnegen duizend vierhonderdnegenenzestig euro en vierendertig cent (3.909.469,34 EUR) wordt aan de 24 sociale actoren verdeeld zoals vermeld in de bijlage van dit Koninklijk Besluit. § 3. Het bedrag van de subsidie komt overeen met het goedgekeurde bedrag voor het laatste werkingsjaar van het uit te voeren project. § 4. Het subsidiebedrag werd uitgesplitst in een bedrag exclusief en een bedrag inclusief btw. In geval van onduidelijkheid werd een correctie doorgevoerd om de btw te berekenen zonder het maximumbedrag van de toegekende subsidiebedrag te overschrijden. § 5. Alleen bedragen exclusief btw kunnen ten laste van het herstel- en veerkrachtplan worden gebracht. De btw wordt gedragen door de Belgische staat. § 6. Het subsidiebedrag zal worden aangerekend op de basisallocatie 06.41.14.33.00.44 van de Algemene uitgavenbegroting van het begrotingsjaar 2025.Art. 2. Het Digilab team van de POD Maatschappelijke Integratie, Administratief Centrum Kruidtuin - Finance Tower, Kruidtuinlaan 50 bus 165, 1000 Brussel, is belast met het administratieve beheer van het project "e-inclusion for Belgium".Art. 3.  § 1. Binnen drie maanden na de ondertekening van dit koninklijk besluit wordt een protocol, opgesteld op basis van de gegevens in het aanvraagdossier, gesloten tussen de begunstigde van de subsidie en de minister bevoegd voor maatschappelijke integratie en armoedebestrijding. Daarin worden de doelstellingen van het project,de wijze van uitvoering, de samenwerking tussen de partijen, de sancties, de verslaglegging en de verplichtingen van de begunstigde gespecificeerd. § 2. De uitvoering van het project moet geschieden op de in het protocol beschreven wijze.Art. 4. De subsidie dekt de uitgaven in de periode van 1 januari 2025 tot en met 31 december 2025.Art. 5.  § 1. De subsidie kan alleen de kosten in verband met het project dekken die zijn aangegeven in het aanvraagdossier ingediende financiële plan of waarvoor een wijzigingsverzoek is goedgekeurd door Digilab en die kunnen worden gefinancierd in het kader van het Europees herstel- en veerkrachtplan. § 2. Dubbele financiering van projectkosten is strikt verboden. § 3. Het betreft kosten die verband houden met de uitvoering van volgende goedgekeurde projecten:1. Het project "DigiFutures" van de vzw Alpha 50002. Het project "Le réseau des IP Wallons" van de vzw ARC3. Het project "Brigade Numérique Mobile" van de vzw Bibliothèques sans frontières (BSF)4. Het project "Soutien Informatique Mutualisé" van de vzw CALIF5. Het project "EPN Mobile et Connecté" van de vzw CEDEG6. Het project "LabNPlay" van de vzw CodeNPlay7. Het project "Tous connectés" van het Franstalige Rode Kruis van België8. Het project "EPN Upgrade" van de vzw Fobagra9. Het project "SocioConnect" van de vzw Interface3.Namur10. Het project "Diversi'Clic" van de vzw La Scientothèque11. Het project "PAW e-inclusion" van de vzw P.A.W.12. Het project "Tous.tes e-concerné.e.s" van vzw Pôle Beaurinois13. Het project "Migralink" van de vzw Le Monde des Possibles14. Het project "Digi You" van de vzw Pour la Solidarite15. Het project "Clic pour elles" van Réso vzw16. Het project "123 Digit" van de vzw WeTechCare17. Het project "Digiboost" van de vzw Yambi18. Het project van Amal vzw, "Digi-beetjes"19. Het project van IMEC vzw, "Digivaardig in zorg en welzijn (DiZW)20. Het project van Maks vzw, "Na de muis en het klavier komt ChatGPT"21. Het project van vzw Pegode, "Digihelden"22. Het project van SAAMO West-Vlaanderen, "E-inclusie als sociale hefboom"23. Het project van vzw Het Portaal, "Naar een e-inclusive zorg"24. Het project "Inclume" van de vzw Choq § 4. De organisaties zijn verplicht naast de subsidie een cofinanciering te voorzien. Deze cofinanciering moet bijdragen aan de verduurzaming van het project na afloop van de subsidie, zoals beoogd in de doelstellingen van de projectoproep "e-inclusion for Belgium" uit 2023 gericht op sociale actoren. Het bedrag van de cofinanciering dient 20% te bedragen van de totaal gemaakte uitgaven die in het lopende jaar voor dit project. § 5. Het niet voorzien in de vereiste cofinanciering zal resulteren in een vermindering van de toegekende subsidie. De vermindering zal proportioneel worden berekend op basis van het tekort aan de vereiste cofinanciering. § 6. Het inzetten van cofinanciering afkomstig uit andere Europese bronnen is strikt verboden.Art. 6.  § 1. Aan de begunstigde kan een voorschot van maximaal 30% van het via het RRF toegekende subsidiebedrag worden verstrekt. Bij de berekening van het voorschot wordt geen rekening gehouden met de btw. Het exacte voorschotbedrag per project wordt vermeld in de bijlage van dit koninklijk besluit.Dit voorschot wordt enkel toegekend op verzoek van de gesubsidieerde organisatie, dat moet worden ingediend vóór de eerste terugbetalingsaanvraag en uiterlijk op 1 juli 2025. § 2. Het resterende bedrag van de subsidie wordt aan de begunstigde betaald, evenredig met de gedane uitgaven en met inachtneming van de bepalingen in artikel 7 en artikel 8, onder voorbehoud van :a) de verwezenlijking van de in het protocol opgenomen doelstellingen van het project en de conformiteit ervan met betrekking tot de in het herstel- en veerkrachtplan bepaalde mijlpalen/doelstellingen van het project "e-inclusion for Belgium";b) De verwezenlijking van gepaste maatregelen om de financiële belangen van de Unie te beschermen en erover waken dat het gebruik van de fondsen in het kader van de door de faciliteit ondersteunde maatregelen het Belgisch en Europees juridisch kader respecteren, in het bijzonder wat de preventie, de opsporing en de bestrijding van de fraude, de corruptie en de belangenconflicten in artikel 22 van het Europees reglement (EU) 2021/241 betreft, vormt een verplichting en een voorwaarde voor de toekenning van de toelage.c) In geval van fraude, corruptie, belangenconflicten en dubbele financiering ten nadele van de financiële belangen van de Unie wordt de subsidie in haar geheel of gedeeltelijk verminderd. Bij de vaststelling van het bedrag van de terugvordering en de verlaging, of van het bedrag dat vroegtijdig moet worden terugbetaald, neemt de staat het evenredigheidsbeginsel in acht en houdt hij rekening met de ernst van de fraude, de corruptie en de belangenconflicten die de financiële belangen van de Unie schaden, of met de niet-nakoming van een verplichting. Bij het vaststellen van de toe te passen financiële correcties zal rekening worden gehouden met de richtsnoeren van de Europese Commissie voor het bepalen van de financiële correcties die moeten worden toegepast in geval van niet-naleving van de regels inzake overheidsopdrachten.d) het opmaken van terugbetalingsaanvragen vergezeld van de in artikel 7 paragraaf 4 genoemde documenten, waaruit onder meer de materialiteit en het bedrag van de aangegeven kosten blijkt.Art. 7.  § 1. Om het resterende bedrag van de subsidie (d.w.z. het bedrag boven het voorschot van 30%) te verkrijgen, moet de organisatie twee terugbetalingsaanvragen indienen. § 2. De eerste terugbetalingsaanvraag heeft betrekking op uitgaven tussen 1 januari 2025 en 30 juni 2025. Deze moet uiterlijk op 12 juli 2025 aan Digilab worden verzonden.Deze eerste terugbetalingsaanvraag moet vergezeld gaan van de in artikel 7 paragraaf 4 beschreven documenten om verificatie van die uitgaven mogelijk te maken.Het bedrag van de eerste terugbetalingsaanvraag wordt betaald, na goedkeuring van de door de begunstigde ingediende documenten en mits aan de in artikel 7 paragraaf 8 genoemde eisen wordt voldaan.De hoogte van het bedrag van de eerste terugbetalingsaanvraag mag niet meer bedragen dan 60% van het totale subsidiebedrag.De door de administratie goedgekeurde kosten worden in voorkomend geval verminderd met het reeds toegekende voorschot, conform artikel 6, § 1.Het voorschot van 30% van het bedrag van de RRF-subsidie + het resterend bedrag dat door de administratie wordt goedgekeurd op basis van de onkosten die worden ingediend in kader van de eerste terugbetalingsaanvraag, mag samen niet hoger zijn dan 60%.Als de begunstigde op het moment van de eerste terugbetalingsaanvraag nog niet het volledige voorschotbedrag heeft gebruikt, of als hij geen terugbetaling wenst te vragen, is hij niettemin verplicht om Digilab uiterlijk 12 juli 2025 de documenten toe te sturen die zijn opgesomd in artikel 7 lid 4. Deze documenten moeten betrekking hebben op alle uitgaven die zijn betaald tussen 1 januari 2025 en 30 juni 2025 en waarvoor de diensten volledig zijn geleverd. § 3. De tweede terugbetalingsaanvraag heeft betrekking op uitgaven die zijn gedaan tussen 1 januari 2025 en 31 december 2025, die niet zijn betaald met het bedrag van het voorschot, noch zijn opgenomen in de eerste terugbetalingsaanvraag.Deze tweede terugbetalingsaanvraag moet uiterlijk op 15 januari 2026 aan Digilab worden verzonden. Deze moet ook vergezeld gaan van de in artikel 7 paragraaf 4 beschreven documenten met betrekking tot de in deze terugbetalingsaanvraag opgegeven uitgaven (om verificatie van die uitgaven mogelijk te maken).Het bedrag van de tweede terugbetalingsaanvraag, dat ten hoogste overeenkomt met het saldo van de subsidie, wordt na goedkeuring van de door de begunstigde ingediende documenten en mits aan de in artikel 7 paragraaf 8 genoemde eisen wordt voldaan. § 4. Om ontvankelijk te zijn moet elke aanvraag vergezeld gaan van de volgende documenten :- een financieel verslag over de uitgaven die in het kader van het project zijn gedaan. De inhoud van het financieel verslag wordt in artikel 7 paragraaf 5 nader toegelicht;- alle boekhoudkundige documenten, originelen of leesbare kopieën, die de in het financieel verslag vermelde uitgaven rechtvaardigen. Al deze documenten moeten worden genummerd volgens een voorgeschreven methode (toegelicht in het protocol) zodat deze gemakkelijk gelinkt kunnen worden met de gegevens in het financieel verslag. De aanvrager verbindt zich ertoe de originelen gedurende de wettelijk voorgeschreven termijnen te bewaren en op verzoek van de administratie ter beschikking te stellen.- alle aanvullende bewijsstukken die nodig zijn om aan te tonen dat de gedane uitgaven rechtstreeks verband houden met de mijlpalen/doelstellingen van het "e-inclusion for Belgium" project zoals goedgekeurd in het herstel- en veerkrachtplan ;- een verklaring op eer dat :a) de projectuitgaven niet dubbel worden gefinancierd ;b) alle ingediende facturen zijn betaald.Indien dit niet het geval is, moet Digilab hiervan onverwijld in kennis worden gesteld. Dit deel van de subsidie wordt dan niet betaald of moet worden terugbetaald.- een document met de naam, voornaam en geboortedatum van de wettelijke vertegenwoordigers van de dienstverleners aan wie in het kader van het project een betaling is gedaan en wie vrijgesteld zijn van registratie in het UBO register.een activiteitenverslag in waarin onder meer de in het kader van het project ondernomen acties en de mate waarin de doelstellingen en resultaten zijn bereikt, worden aangetoond. § 5. De financiële verslagen dienen een gedetailleerde overzichtstabel te bevatten van de totaal gemaakte uitgaven, inclusief de bijbehorende betalingsbewijzen, waarmee de organisaties waaraan de betalingen zijn verricht kunnen worden geïdentificeerd (naam, KBO-nummer, adres), met vermelding van het bedrag exclusief btw en het btw-bedrag. Daarnaast dient een grondige toelichting te worden verstrekt over de relevantie van de totaal gemaakte uitgaven en het verband met het project. § 6. De financiële verslagen en activiteitenverslagen worden uitsluitend opgesteld op basis van het door Digilab verstrekte modellen en voldoen aan de in het protocol gespecifieerde vereisten. § 7. Terugbetalingsaanvragen en andere in artikel 7 paragraaf 4 genoemde documenten moeten bij Digilab worden ingediend via het elektronische systeem voor projecttoezicht. § 8. De uitbetaling van de terugbetalingsaanvraag zal worden geweigerd of het gevorderde bedrag zal niet volledig worden betaald:- in geval van niet-naleving van de bepalingen van dit koninklijk besluit ;- in geval van één of meerdere ontbrekende, onvolledige of buiten de termijn verzonden document (in het kader van de in artikel 7 paragraaf 4 gevraagde documenten) ;in geval van één of meerdere bewijsstukken, financiële verslagen of activiteitenverslagen die geen onweerlegbaar bewijs leveren dat de subsidie overeenkomstig de voorschriften is gebruikt.Art. 8. De begunstigde van de subsidie is verplicht de betaalde bedragen onverwijld terug te betalen :- in geval van onaanvaardbare, onvolledige of niet-conforme uitvoering van het project met betrekking tot de mijlpalen/doelstellingen van het project "e-inclusion for Belgium" zoals goedgekeurd in het herstel- en veerkrachtplan;- in geval van niet-naleving van de voorwaarden van dit koninklijk besluit of het protocol.Art. 9.  § 1. Digilab zal één of meer controles ter plaatse uitvoeren om na te gaan of de uitvoering van het project beantwoordt aan de in het protocol omschreven doelstellingen en dat de subsidie wordt gebruikt overeenkomstig de geldende regelgeving. § 2. Een externe audit kan worden verricht door de bevoegde federale of Europese autoriteiten. § 3. Indien de begunstigde van de subsidie de controle(s) belemmert, is hij verplicht de betaalde bedragen onverwijld terug te betalen.Art. 10. Op het einde van het laatste jaar van het project vindt een evaluatie plaats. Digilab is belast met deze evaluatie.Art. 11.  § 1. Het Belgische en Europese juridische kader betreffende het gebruik van middelen in het kader van het herstel- en herstelplan moeten door de organisatie en diens partners worden nageleefd.Het is de verantwoordelijkheid van organisatie ervoor te zorgen dat de wettelijke kaders door diens partners worden nageleefd. § 2. Bij de uitvoering van het project moet met name het DNSH-beginsel ("Do No Significant Harm") in acht worden genomen.Het niet naleven van het DNSH-beginsel kan ertoe leiden dat de subsidie moet worden terugbetaald.Art. 12. De Minister an Asiel en Migratie, en Maatschappelijke Integratie, belast met Grootstedenbeleid is belast met de uitvoering van dit besluit.Gegeven te Brussel, op 10 april 2025.FILIPVan Koningswege :De Minister van Asiel en Migratie, en Maatschappelijke Integratie, belast met Grootstedenbeleid,A VAN BOSSUYT  </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de binnenscheepvaart; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 17 februari 2025, gesloten in het Paritair Comité voor de binnenscheepvaart, betreffende de eindejaarspremie. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de binnenscheepvaart Collectieve arbeidsovereenkomst van 17 februari 2025 Eindejaarspremie (Overeenkomst geregistreerd op 13 maart 2025 onder het nummer 192563/CO/139) Artikel 1. Toepassingsgebied Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de werknemers van de ondernemingen die onder het Paritair Comité voor de binnenscheepvaart ressorteren, uitgezonderd de ondernemingen met als activiteit sleepdiensten. Tevens zijn uitgezonderd uit het toepassingsgebied van deze collectieve arbeidsovereenkomst de studenten onderworpen aan de solidariteitsbijdrage en leerlingen. Deze collectieve arbeidsovereenkomst is ook van toepassing op alle werknemers tewerkgesteld onder het stelsel van flexi-job in het Paritair Comité voor de binnenscheepvaart. Art. 2. Bedrag van de eindejaarspremie De in artikel 1 bedoelde werknemers hebben ten laste van het "Fonds voor de Rijn- en binnenscheepvaart" recht op een eindejaarspremie. De eindejaarspremie is gelijk aan 8,05 pct. berekend op het brutoloon zoals gekend in de DmfA onder de looncodes 1, 3 en 4 welke verdiend werd tijdens de referentieperiode welke loopt van 1 oktober van het voorgaande jaar tot 30 september van het jaar waarop de premie betrekking heeft. Het bedrag van de eindejaarspremie dient minima al 30 EUR te bedragen. Voor de werknemers die tewerkgesteld worden in de systeemvaart, is de eindejaarspremie eveneens gelijk aan 9,50 pct., berekend op het brutoloon zoals gekend in de DmfA onder de looncodes 1, 3 en 4 welke verdiend werd tijdens de referentieperiode welke loopt van 1 oktober van het voorgaande jaar tot 30 september van het jaar waarop de premie betrekking heeft. Het in aanmerking te ne men loon wordt tevens verhoogd met een forfaitair bedrag van 30 EUR per dag, ook voor deeltijdsen waar de prestaties in uren worden aangegeven, afwezigheid wegens : - Code 50 DmfA : ziekte of ongeval van gemeen recht; - Code 51 DmfA : moederschapbescherming en borstvoedingspauzes; - Code 52 DmfA : vaderschaps- of geboorteverlof, adoptieverlof en pleegouderverlof; - Code 53 DmfA : profylactisch verlof; - Code 60 DmfA : arbeidsongeval;- Code 61 DmfA : beroepsziekte; - Code 77 DmfA : crisismaatregel COVID-19 : tijdelijke werkloosheid wegens overmacht-corona, welke zich tijdens de referentieperiode heeft voorgedaan en niet is gedekt door het gewaarborgd weekloon voor werknemers. Voor de werkgevers die hun loonaangiften bij de Rijksdienst voor Sociale Zekerheid indienen volgens het stelsel van de vijfdagenweek, worden de bedoelde afwezigheidsdagen vermeerderd met de breuk 6/5den. Het forfaitair bedrag kan op 1 januari van elk jaar worden herzien. Het "Fonds voor de Rijn- en binnenscheepvaart" betaalt de eindejaarspremie uiterlijk vóór 8 januari van het jaar volgend op dit waarop de premie betrekking heeft. Art. 3. Ondernemingen met een gunstigere regeling In de ondernemingen waar gunstigere regelingen inzake de eindejaarspremie bestaan, blijven deze behouden, met dien verstande dat het bedrag van de eindejaarspremie bedoeld in artikel 2 in mindering mag worden gebracht van de bestaande eindejaarspremie. Art. 4. Financiering van de eindejaarspremie In uitvoering van artikel 5 van de collectieve arbeidsovereenkomst betreffende de statuten van het fonds voor bestaanszekerheid van 22 oktober 2020 en ter financiering van deze eindejaarspremie zijn de in artikel 1 bedoelde werkgevers, een procentuele bijdrage van 11,02 pct., berekend op het brutoloon berekend aan 108 pct., zoals gekend in de DmfA onder de looncodes 1, 3 en 4, verschuldigd aan het "Fonds voor de Rijn- en binnenscheepvaart". Voor de werkgevers die personeel tewerkstellen in de systeemvaart, wordt de procentuele bijdrage vastgesteld op 13,05 pct. berekend op het brutoloon berekend aan 108 pct., zoals gekend in de DmfA onder de looncodes 1, 3 en 4. De eindejaarspremie betaald door het "Fonds voor de Rijn- en binnenscheepvaart" wordt berekend op basis van de brutolonen aan 108 pct. aangegeven in de DmfA-aangifte onder de looncodes 1, 3 en 4 tijdens de referentieperiode welke loopt van 1 oktober van het voorgaande jaar tot 30 september van het jaar waarop de premie betrekking heeft. Voor de werknemers tewerkgesteld onder het stelsel van flexi-job wordt de bijdrage berekend op de brutolonen aan 100 pct. aangegeven onder de looncodes 22 (prestaties in het kader van een "flexi-job") en 23 (premies en andere voordelen voortvloeiend uit prestaties in het kader van een "flexi-job"). Art. 5. Opheffing bestaande collectieve arbeidsovereenkomst Deze collectieve arbeidsovereenkomst heft de collectieve arbeidsovereenkomst voor 16 maart 2022 (registratienummer 173809/CO/139) op. Art. 6. Slotbepalingen Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van 1 april 2025 en is gesloten voor onbepaalde tijd. Elk van de ondertekenende partijen kan ze opzeggen mits een opzeggingstermijn van 6 maanden in acht wordt genomen. De opzegging wordt bij een ter post aangetekende brief aan de voorzitter van het Paritair Comité voor de binnenscheepvaart en aan elk van de ondertekenende partijen betekend en heeft uitwerking de derde werkdag na de datum van verzending. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
+</t>
         </is>
       </c>
     </row>
@@ -2458,28 +2456,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2025200962</t>
+          <t>2025201186</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>05 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>8 april 2025. - Koninklijk besluit houdende benoeming van raadsheren en rechters in sociale zaken (1)</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 17 februari 2025, gesloten in het Paritair Comité voor de binnenscheepvaart, betreffende de opt-in van het toepassingsgebied van de flexi-jobs (1)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-05&amp;numac_search=2025200962&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200962=63&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025201186&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201186=63&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op het Gerechtelijk Wetboek inzonderheid op de artikelen 198 tot 201, 202, gewijzigd bij de wet van 6 mei 1982, 206, gewijzigd bij de wet van 15 mei 1987, en 216; Gelet op het koninklijk besluit van 7 april 1970 tot vaststelling van het aantal rechters en raadsheren in sociale zaken en van de wijze van voordracht van de kandidaten, gewijzigd bij de koninklijke besluiten van 16 juni 2006 en 25 maart 2014; Gelet op de kandidatenlijsten voorgedragen door de representatieve werkgevers- en werknemersorganisaties; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Tot werkend raadsheer in sociale zaken, als werknemer-arbeider bij het Arbeidshof van Brussel wordt benoemd : - behorend tot het Nederlandse taalstelsel : Mevr. VAN BUGGENHOUT Sofie, te BRUSSEL. Art. 2. Dit besluit heeft uitwerking met ingang van 1 november 2024. Art. 3. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 8 april 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzingen naar het Belgisch Staatsblad : Koninklijk besluit van 7 april 1970, Belgisch Staatsblad van 24 april 1970. Koninklijk besluit van 16 juni 2006, Belgisch Staatsblad van 28 juni 2006. Koninklijk besluit van 25 maart 2014, Belgisch Staatsblad van 28 maart 2014. 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet. Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de binnenscheepvaart; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 17 februari 2025, gesloten in het Paritair Comité voor de binnenscheepvaart, betreffende de opt-in van het toepassingsgebied van de flexi-jobs. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de binnenscheepvaart Collectieve arbeidsovereenkomst van 17 februari 2025 Opt-in van het toepassingsgebied van de flexi-jobs (Overeenkomst geregistreerd op 13 maart 2025 onder het nummer 192564/CO/139) Artikel 1. Toepassingsgebied Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en werknemers van de ondernemingen die ressorteren onder het Paritair Comité voor de binnenscheepvaart. Onder "werknemers" wordt verstaan : de mannelijke en vrouwelijke werknemers (arbeiders en bedienden) Deze collectieve arbeidsovereenkomst is ook van toepassing op alle werknemers tewerkgesteld onder het stelsel van flexi-job in het Paritair Comité voor de binnenscheepvaart. Art. 2. Wettelijke basissen Deze collectieve arbeidsovereenkomst wordt gesloten in uitvoering van : - de wet van 16 november 2015 houdende diverse bepalingen inzake sociale zaken (Belgisch Staatsblad van 26 november 2015); - artikel 182 programmawet van 22 december 2023 (Belgisch Staatsblad van 29 december 2023).Art. 3. Opt-in van de sector van de binnenscheepvaart bij een in de Ministerraad overlegd koninklijk besluit. De sociale partners van het Paritair Comité voor de binnenscheepvaart vragen unaniem de opt-in van de sector van de binnenscheepvaart in het toepassingsgebied van de flexi-jobs bij een in de Ministerraad overlegd koninklijk besluit. Er wordt een opt-in gevraagd voor alle ondernemingen. Toelatingen (opt-in) worden pas actief via een koninklijk besluit dat in werking treedt op 1 januari van het volgende jaar (een overgangsmaatregel voorziet dat in 2024 toelatingen op kwartaalbasis in plaats van op jaarbasis mogelijk zijn). De sector van de binnenscheepvaart vraagt voor 2024 de toelating vanaf kwartaal 3 van 2024. Art. 4. Bijdragen aan het fonds De werknemers op wie deze collectieve arbeidsovereenkomst van toepassing is zullen eveneens onderworpen zijn aan alle bijdragen en rechten zoals voorzien in : - de gecoördineerde collectieve arbeidsovereenkomst van 22 oktober 2020 inzake de arbeidsduur en de rechtsopvolgers ervan; - de collectieve arbeidsovereenkomst van 16 maart 2022 tot opheffing van de collectieve arbeidsovereenkomst van 22 oktober 2020 betreffende de eindejaarspremie; - de collectieve arbeidsovereenkomst van 22 oktober 2020 inzake vaststelling van de werkgeversbijdragen voor vormingskosten en de rechtsopvolgers ervan; - de collectieve arbeidsovereenkomst van 22 oktober 2020 inzake de syndicale premie en de rechtsopvolgers ervan; - de collectieve arbeidsovereenkomst van 22 oktober 2020 tot wijziging van de collectieve arbeidsovereenkomst van 10 oktober 2016 inzake vaststelling van de werkgeversbijdragen voor administratiekosten en de rechtsopvolgers ervan; - de gecoördineerde collectieve arbeidsovereenkomst van 22 oktober 2020 inzake de waarborg van een compenserende vergoeding - bijkomend pensioen en de rechtsopvolgers ervan. De bijdragen bedoeld in artikel 4 van deze collectieve arbeidsovereenkomst worden geïnd en ingevorderd door de Rijksdienst voor Sociale Zekerheid, in toepassing van artikel 6 van de Sociale Zekerheidswet van 27 juni 1969 en artikel 7 van de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid binnen de termijnen vastgesteld voor de betaling van de bijdragen voor de sociale zekerheid. Op eenvoudige vraag van het "Fonds voor de Rijn- en binnenscheepvaart" moet de werkgever alle gegevens, nodig voor een goede werking, over hemzelf of zijn werknemers verstrekken. Art. 5. Jaarlijks overleg Elk kalenderjaar waarin flexi-job werknemers worden tewerkgesteld wordt er een overleg over de toepassing van de flexi-jobs georganiseerd tussen de werkgeversvertegenwoordigers en de vertegenwoordigers van de werknemers op sectoraal vlak. Art. 6. Duurtijd en opzegging Deze collectieve arbeidsovereenkomst wordt gesloten voor onbepaalde duur met ingang van 1 april 2025. Deze collectieve arbeidsovereenkomst heft de collectieve arbeidsovereenkomst van 18 maart 2024 (registratienummer 187006/CO/139) op. Elk van de ondertekenende partijen kan ze opzeggen mits een opzeggingstermijn van 6 maanden in acht wordt genomen. De opzegging wordt bij een ter post aangetekende brief aan de voorzitter van het Paritair Comité voor de binnenscheepvaart en aan elk van de ondertekenende partijen betekend en heeft uitwerking de derde werkdag na de datum van verzending. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -2490,28 +2488,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2025002137</t>
+          <t>2025201188</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>02 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6 april 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 11 juli 2001 betreffende de weging van de management- en staffuncties in de federale overheidsdiensten en tot vaststelling van hun wedde, het koninklijk besluit van 29 oktober 2001 betreffende de aanduiding en de uitoefening van de managementfuncties in de federale overheidsdiensten en de programmatorische federale overheidsdiensten, het koninklijk besluit van 19 maart 2003 tot vaststelling van het organieke statuut van het Instituut voor de gelijkheid van vrouwen en mannen en het koninklijk besluit van 16 november 2006 betreffende de aanduiding en de uitoefening van de management- en staffuncties in sommige instellingen van openbaar nut</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 12 december 2024, gesloten in het Paritair Comité voor de vrije beroepen, betreffende de opheffing van de collectieve arbeidsovereenkomst nr. 121380/CO/336 (1)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-02&amp;numac_search=2025002137&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025002137=64&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025201188&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201188=64&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de artikelen 37 en 107, tweede lid, van de Grondwet;Gelet op de wet van 16 maart 1954 betreffende de controle op sommige instellingen van openbaar nut;Gelet op de wet van 4 februari 2000 houdende oprichting van het federaal Agentschap voor de Veiligheid van de voedselketen;Gelet op het koninklijk besluit van 6 december 2001 betreffende de aanduiding en de uitoefening van de management en staffuncties in het Federaal Agentschap voor de Veiligheid van de Voedselketen;Gelet op het koninklijk besluit van 16 november 2006 betreffende de aanduiding en de uitoefening van de managementfuncties in sommige instellingen van openbaar nut;Gelet op het koninklijk besluit van 10 juli 2024 tot wijziging van het koninklijk besluit van 11 juli 2001 betreffende de weging van de management- en staffuncties in de federale overheidsdiensten en tot vaststelling van hun wedde, het koninklijk besluit van 29 oktober 2001 betreffende de aanduiding en de uitoefening van de managementfuncties in de federale overheidsdiensten en de programmatorische federale overheidsdiensten, het koninklijk besluit van 19 maart 2003 tot vaststelling van het organieke statuut van het Instituut voor de gelijkheid van vrouwen en mannen en het koninklijk besluit van 16 november 2006 betreffende de aanduiding en de uitoefening van de management- en staffuncties in sommige instellingen van openbaar nut;Gelet op de adviezen van de inspecteurs van Financiën, gegeven op 18 december 2024 en op 6 januari 2025;Gelet op de akkoordbevinding van de Staatssecretaris voor Begroting, gegeven op 9 januari 2025;Gelet op het protocol nr. 2025/001 van 31 januari 2025 van het Sectorcomité XII - Volksgezondheid;Gelet op het advies 77.525/4 van de Raad van State, gegeven op 28 februari 2025, met toepaassing van artikel 84, § 1, eerste lid, 3°  van de wetten op Raad van State, gecoordineerd op 12 januari 1973;Gelet op de vrijstelling van de impactanalyse op basis van artikel 8, § 1, 4°  van de wet van 15 december 2013 houdende diverse bepalingen inzake administratieve vereenvoudiging;Overwegende dat de aanstelling in de leidinggevende functies die vacant zijn verklaard in het Federaal Agentschap voor de Veiligheid van de Voedselketen, hierna het Agentschap genoemd, noodzakelijk is om de continuïteit van de openbare dienstverlening te waarborgen;Dat de vacantverklaring van de betrekking door de overheid die bevoegd is voor de leidinggevende functies in de beheersdiensten van het Agentschap gebeurd is in tempore non suspecto in toepassing van artikel 2 van het koninklijk besluit van 6 december 2001 betreffende de aanduiding en de uitoefening van de management- en staffuncties in het Federaal Agentschap voor de Veiligheid van de Voedselketen;Dat het opstarten van de vergelijkende selectieprocedures voor de leidinggevende functies van het Agentschap op de bestaande reglementaire basis van artikel 2 van het koninklijk besluit van 6 december 2001 steunt;Overwegende dat het koninklijk besluit van 10 juli 2024, daar het in zijn artikel 81, eerste streepje het voormelde koninklijk besluit van 6 december 2001 opheft, op 6 september 2024 in het Belgisch Staatsblad werd gepubliceerd en dat het koninklijk besluit van 10 juli 2024 op 1 oktober 2024 in werking trad;Overwegende dat de wil van de bevoegde overheid om, met inachtneming van de oprichtingsakte, te voorzien in leidinggevende functies in het Agentschap duidelijk en onbetwistbaar is en blijft;Dat de opheffing van het koninklijk besluit van 6 december 2001 in zijn geheel derhalve betrekking heeft op een technische fout die de voortzetting van het op gang gebrachte proces niet mag schaden en die op termijn moet leiden tot de aanstelling van mandaathouders in het Agentschap;Dat het noodzakelijk is om artikel 2 van het koninklijk besluit van 6 december 2001 zo snel mogelijk te herstellen met het oog op de rechtszekerheid en de samenhang met het koninklijk besluit van 16 november 2006 betreffende de aanduiding en de uitoefening van de managementfuncties in sommige instellingen van openbaar nut.Overwegende dat de bepalingen die bedoeld zijn om de opdrachten van een federale dienst vast te stellen of om de regels inzake de organisatie van deze federale dienst vast te stellen niet het "reglementaire" karakter hebben dat vereist is door artikel 3, § 1, eerste lid van de gecoördineerde wetten op de Raad van State, zodat ze vallen onder de adviserende bevoegdheid van de afdeling Wetgeving;Op de voordracht van de Minister van Ambtenarenzaken en de Minister van Landbouw en op het advies van de in Raad vergaderde Ministers,Hebben Wij besloten en besluiten Wij :Artikel 1. In het koninklijk besluit van 10 juli 2024 tot wijziging van het koninklijk besluit van 11 juli 2001 betreffende de weging van de management- en staffuncties in de federale overheidsdiensten en tot vaststelling van hun wedde, het koninklijk besluit van 29 oktober 2001 betreffende de aanduiding en de uitoefening van de managementfuncties in de federale overheidsdiensten en de programmatorische federale overheidsdiensten, het koninklijk besluit van 19 maart 2003 tot vaststelling van het organieke statuut van het Instituut voor de gelijkheid van vrouwen en mannen en het koninklijk besluit van 16 november 2006 betreffende de aanduiding en de uitoefening van de management- en staffuncties in sommige instellingen van openbaar nut wordt artikel 81, eerste streepje ingetrokken.Art. 2. In artikel 81 van hetzelfde koninklijk besluit wordt het eerste streepje van artikel 81 van hetzelfde koninklijk besluit hersteld als volgt:- het koninklijk besluit van 6 december 2001 betreffende de aanduiding en de uitoefening van de management- en staffuncties in het Federaal Agentschap voor de Veiligheid van de Voedselketen, gewijzigd bij de besluiten van 20 september 2012, van 31 maart 2014, van 30 september 2021 en van 21 december 2021, uitgezonderd artikel 2.Art. 3. Dit besluit heeft uitwerking met ingang van 1 oktober 2024.Art. 4. Onze Minister van Ambtenarenzaken en Onze Minister van Landbouw zijn belast met de uitvoering van dit besluit.Gegeven te Brussel, op 6 april 2025.FILIPVan Koningswege :De Minister van Landbouw,D. CLARINVALDe Minister van Ambtenarenzaken,V. MATZ 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de vrije beroepen; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 12 december 2024, gesloten in het Paritair Comité voor de vrije beroepen, betreffende de opheffing van de collectieve arbeidsovereenkomst nr. 121380/CO/336. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de vrije beroepen Collectieve arbeidsovereenkomst van 12 december 2024 Opheffing van de collectieve arbeidsovereenkomst nr. 121380/CO/336 (Overeenkomst geregistreerd op 20 maart 2025 onder het nummer 192672/CO/336) Artikel 1. Toepassingsgebied Deze collectieve arbeidsovereenkomst heeft hetzelfde toepassingsgebied als de collectieve arbeidsovereenkomst die zij opheft. Art. 2.  Opheffing De collectieve arbeidsovereenkomst van 27 februari 2014 betreffende het minimum maandloon, geregistreerd onder het nummer 121380/CO/336, wordt opgeheven. Art. 3.  Geldigheidsduur Deze collectieve arbeidsovereenkomst treedt in werking op 12 december 2024 en geldt voor een onbepaalde duur. Zij kan door elk der partijen worden opgezegd middels een opzeggingstermijn van 12 maanden. De opzegging dient per ter post aangetekend schrijven te gebeuren, gericht aan de voorzitter van het paritair comité. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -2522,28 +2520,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2025200881</t>
+          <t>2025003698</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>07 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6 april 2025. - Koninklijk besluit tot machtiging om de eretitel van raadsheer en rechter in sociale zaken te voeren</t>
+          <t>7 mei 2025. - Koninklijk besluit tot omzetting van de amendementen van 2022 aan het MLC-Verdrag</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-07&amp;numac_search=2025200881&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025200881=65&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025003698&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003698=65&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op het Gerechtelijk Wetboek; Gelet op het advies van de gerechtelijke overheden; Overwegende dat op 31 oktober 2024 het mandaat van de raadsheren en rechters in sociale zaken een einde heeft genomen; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  De hierna genoemde personen worden gemachtigd de eretitel van hun ambt van raadsheer in sociale zaken te voeren: - bij het Arbeidshof van Antwerpen: - als werkgever: De heren: D'HONT Eric, te Kalmthout; VANKRUNKELSVEN Guy, te Hove; - als werknemer-arbeider: De heren: KERKHOFS Joris, te Kontich; NESKENS Andre, te Lummen; - als werknemer-bediende: Mevrouw HOUBRECHTS An, te Genk. - bij het Arbeidshof van Gent: - als werkgever: Mevrouwen: DESMIT Anne, te Brugge; NIMMEGEERS Sabine, te Lochristi; De heren: BLOMME Marc, te Brugge; BONTINCK Guy, te Mariakerke; - als werknemer-bediende: Mevrouw BOSTEELS Marianne, te Haaltert: De heren: DOISE Stefan, te Sint-Amandsberg; DUMORTIER Johan, te Denderleeuw. - bij het Arbeidshof van Brussel: - van het Nederlands taalstelsel: - als werkgever: Mevrouw MORIAU Hilde, te Sint-Pieters-Leeuw; De heer ARDIES Luc, te Bonheiden; - als werknemer-bediende: De heren: HENDRICKX Koenraad, te Bonheiden; LEURS André, te Mechelen. Art. 2.  De hierna genoemde personen worden gemachtigd de eretitel van hun ambt van rechter in sociale zaken te voeren: - bij de Arbeidsrechtbank van Antwerpen arrondissement Antwerpen: - als werkgever: Mevrouw VERHEYEN Adelheidis, te Grobbendonk;De heren: RUYS Marc, te Grobbendonk; VAN LOON Johan, te Deurne; - als werknemer-bediende: De heren: QUISTHOUDT, Erik, te Wuustwezel; SCHRAUWEN Erik, te Brasschaat. - bij de Arbeidsrechtbank van Antwerpen arrondissement Limburg: - als werkgever: De heer DELMOTTE Jacques, te Diepenbeek; - als werknemer-arbeider: Mevrouwen: HOUBRECHTS Nicole, te Ulbeek; JAENEN Gabrielle, te Geel; De heer PAULUSSEN Ronald, te Diepenbeek; - als werknemer-bediende: Mevrouw STEEGMANS Kristel, te Martenslinde; De heer NOURI Kareme, te Hasselt. - bij de Arbeidsrechtbank van Gent arrondissement Oost-Vlaanderen: - als werkgever: Mevrouwen: NEERINCKX Kristel, te Sint-Amandsberg; SNOECK Martine, te Nederzwalm-Hermelgem; VAN DER MEULEN Ann, te Ronse; De heren: DOOMS Hugo, te Buggenhout; VAN HEE Franky, te Erpe-Mere; VERGOTE Jan, te Ledeberg; - als werknemer-arbeider: De heer VAN DE WALLE Luc, te Wondelgem; - als werknemer-bediende: De heren: DE KEYSER André, te Hamme; DE VOS Guy, te Kluisbergen. - bij de Arbeidsrechtbank van Gent arrondissement West-Vlaanderen: - als werkgever: Mevrouwen: FLIPTS Caroline, te Roeselare; VERSTRAETE Annick, te Aalter; De heren: CALLEWIER Dominiek, te Zwevegem; DEKLERCK Thijs, te Veldegem; - als werknemer-arbeider: Mevrouw GOUSSAERT Nathalie, te Harelbeke; De heren: MAXY Paul, te Menen; MINNE Olaf, te Zedelgem; - als werknemer-bediende: Mevrouwen: DEVRIESE Griet, te Tielt; LAMBERT Erika, te Ieper; VANSINTJAN Lieze, te Bellem; De heren: BOUCKAERT Jean-Pierre, te Vlamertinge; VANRAES Joris, te Kortrijk.- bij de Nederlandstalige Arbeidsrechtbank van Brussel: - als werkgever: Mevrouwen: BETTENS Anneleen, te Roosdaal; HUINEN Jeanine, te Oostende; - als werknemer-bediende: Mevrouwen: VAN HORENBEECK Natascha, te Mechelen; VERSCHOOTEN Marleen, te Westerlo; De heren: LEFERE Geert, te Eeklo; VUCHELEN Thierry, te Denderleeuw. - bij de Arbeidsrechtbank van Leuven: - als werknemer-arbeider: De heer GODTS Ronald, te Vilvoorde; - als werknemer-bediende: Mevrouw VANSWEEVELT Sofie, te Aarschot. Art. 3.  Dit besluit heeft uitwerking met ingang van 1 november 2024. Art. 4.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 6 april 2025.FILIPVan Koningswege :  De Minister van Werk, D. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op het Belgisch Scheepvaartwetboek, artikelen 2.2.3.9, 1°,  h), 2.7.7.10, § 2, ingevoegd bij wet van 25 december 2024;Gelet op het koninklijk besluit van 20 juli 1973 houdende zeevaartinspectiereglement;Gelet op het van het koninklijk besluit van 30 juli 2021 tot optimalisatie van de maritieme arbeidsbepalingen;Gelet op het koninklijk besluit van 15 november 2021 inzake essentiële middelen aan boord van schepen;Gelet op de betrokkenheid van de gewestregeringen;Gelet op standaardadvies 65/2023 van de Gegevensbeschermingsautoriteit van 24 maart 2023 waarnaar de Autoriteit verwijst bij beslissing van 20 oktober 2023 in het dossier CO/A/2023/451;Gelet op het advies van de Inspecteur van Financiën, gegeven op 5 februari 2024;Gelet op het advies 77.345/4 van de Raad van State gegeven op 15 januari 2025 met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Overwegende dat dit besluit in de periode van lopende zaken genomen kan worden doordat dit besluit voorziet in de omzetting van amendementen aan een internationaal verdrag, namelijk het MLC-Verdrag, waarbij België Partij is; de omzetting van de amendementen is noodzakelijk om de verplichtingen van België als Verdragspartij bij het MLC-Verdrag na te leven;Op de voordracht van de Minister van Noordzee en de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. In artikel 7 van Bijlage XIV van het koninklijk besluit van 20 juli 1973 houdende zeevaartinspectiereglement, gewijzigd bij besluit van 29 februari 2004 en 30 september 2014, wordt het laatste lid van punt 2. A. a) opgeheven.Art. 2. Artikel 9 van Bijlage XIV van het koninklijk besluit van 20 juli 1973 houdende zeevaartinspectiereglement wordt vervangen als volgt:" 1. Geschikte ontspanningsvoorzieningen en diensten, met inbegrip van sociale connectiviteit, dienen aan boord beschikbaar te zijn voor zeevarenden, teneinde tegemoet te komen aan de bijzondere behoeften van zeevarenden die op schepen moeten wonen en werken, met inachtneming van voorschrift 4.3 van het MLC-Verdrag en de daarmee verband houdende bepalingen van de overeenstemmende Code met betrekking tot de bescherming van de gezondheid en veiligheid en ongevallenpreventie.2. Rederijen moeten, voor zover dit redelijkerwijs uitvoerbaar is, internet ter beschikking stellen van de zeevarenden aan boord van hun schepen, indien nodig kan hiervoor een redelijke kostprijs worden aangerekend.3. Aan boord van elk schip en rekening gehouden met zijn afmetingen en bemanning, moet in voldoende open dekruimte worden voorzien ten behoeve van de niet op dienst zijnde zeevarenden.4. Behoorlijk gemeubeld en op een geschikte plaats gelegen ontspanningslokalen dienen aan boord beschikbaar te zijn voor de zeevarenden. Zijn er geen dergelijke lokalen buiten de refters, dan moeten deze laatste zodanig ingericht en gemeubeld worden dat zij als ontspanningslokaal kunnen dienen.Art. 3. In punt 1 van artikel 13 van Bijlage XIV van hetzelfde besluit, gewijzigd bij besluit van 7 januari 1998, 29 februari 2004 en 15 november 2021, worden de woorden "waarvan de brutotonnenmaat meer bedraagt dan 500, " opgeheven.Art. 4. Artikel 2.4 van het koninklijk besluit van 30 juli 2021 tot optimalisatie van de maritieme arbeidsbepalingen wordt hernummerd naar artikel 2.4.1.Art. 5. In hetzelfde besluit wordt een artikel 2.4.2 ingevoegd, luidende:"Art. 2.4.2. De reder rapporteert onverwijld de gegevens overeenkomstig norm A4.3, paragraaf 5, a) en richtlijn B4.3.5, paragrafen 4 en 5 van het MLC-Verdrag en de nationale bepalingen tot uitvoering van de bepalingen van het MLC-Verdrag aan de FOSO."Art. 6. Artikel 3.6 van het koninklijk besluit van 15 november 2021 inzake essentiële middelen aan boord van schepen wordt vervangen als volgt:De organisatie en uitrusting van de cateringafdeling zijn zodanig dat aan de zeevarenden goede, gevarieerde, gebalanceerde en voedzame maaltijden kunnen worden verstrekt die onder hygiënische omstandigheden worden bereid en opgediend.Art. 7. In artikel 3.7, paragraaf 1, van hetzelfde besluit wordt 1°  aangevuld met de woorden "overeenkomstig artikel 3.6 en norm A3.2, paragraaf 2, b) van het MLC-Verdrag".Art. 8. De minister bevoegd voor maritieme mobiliteit is belast met de uitvoering van dit besluit.Gegeven te Brussel, 7 mei 2025.FILIPVan Koningswege :De Minister van Noordzee,VERLINDEN De Minister van Werk,D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -2554,28 +2552,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2025201359</t>
+          <t>2025201182</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>09 mei 2025</t>
+          <t>20 mei 2025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>25 maart 2025. - Koninklijk besluit houdende vaststelling van de taalkaders van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 3 februari 2025, gesloten in het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Vlaamse Gemeenschap, betreffende de bekwame helper (1)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-09&amp;numac_search=2025201359&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025201359=66&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-20&amp;numac_search=2025201182&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201182=66&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wetten op het gebruik van de talen in bestuurszaken, gecoördineerd op 18 juli 1966, inzonderheid op artikel 43ter, § 4, ingevoegd bij de wet van 12 juni 2002; Gelet op het koninklijk besluit van 3 februari 2002 houdende oprichting van de FOD Werkgelegenheid, Arbeid en Sociaal Overleg, gewijzigd door het koninklijk besluit van 18 april 2021; Gelet op het koninklijk besluit van 19 september 2005 tot vaststelling, met het oog op de toepassing van artikel 43ter van de wetten op het gebruik van de talen in bestuurszaken, gecoördineerd op 18 juli 1966, van de betrekkingen van de ambtenaren van de centrale diensten van de federale overheidsdiensten, die eenzelfde trap van de hiërarchie vormen; Gelet op het koninklijk besluit van 17 augustus 2018 tot vaststelling van de taalkaders van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg; Gelet op het akkoord van de Inspectie van Financiën op het personeelsplan 2023, gegeven op 26 januari 2024; Gelet op de opmerkingen die door de vakorganisaties werden geformuleerd overeenkomstig artikel 54, tweede lid, van voormelde wetten; Gelet op het advies n°56.265 van de Vaste commissie voor taaltoezicht, gegeven op 20 september 2024;Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Bij de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg wordt de verdeling van de betrekkingen van de centrale diensten over de taalkaders vastgesteld volgens de bij dit besluit gevoegde tabel. Art. 2. Het koninklijk besluit van 17 augustus 2018 houdende vaststelling van de taalkaders van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg, wordt opgeheven. Art. 3. Dit besluit heeft uitwerking met ingang van 5 augustus 2024. Art. 4. De Minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 25 maart 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVALBijlage bij het koninklijk besluit van 25 maart 2025 tot vastelling van de taalkaders van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg   </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Vlaamse Gemeenschap; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 3 februari 2025, gesloten in het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Vlaamse Gemeenschap, betreffende de bekwame helper. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Vlaamse Gemeenschap Collectieve arbeidsovereenkomst van 3 februari 2025 Bekwame helper (Overeenkomst geregistreerd op 13 maart 2025 onder het nummer 192554/CO/319.01) Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de werknemers die ressorteren onder het Paritair Subcomité voor de Vlaamse opvoedings- en huisvestingsinstellingen en -diensten. Onder "werknemers" wordt verstaan : de mannelijke en vrouwelijke werknemers. Voorwerp Art. 2. Deze collectieve arbeidsovereenkomst wordt gesloten in het kader van artikel 4 van de wet van 18 juni 2023 tot invoering van een overlegprocedure in het kader van de uitoefening van technische verstrekkingen door bekwame helpers bedoeld in artikel 124, 1°, 6de lid van de wet betreffende de uitoefening van de gezondheidszorgberoepen, gecoördineerd op 10 mei 2015. Instructies en/of opleiding, praktisch implementatie en impact op arbeidsorganisatie Art. 3. In elke organisatie waar werknemers ais bekwame helpers technische verstrekkingen zullen uitvoeren, zullen in onderling akkoord met de werknemersvertegenwoordigers nadere regels en afspraken worden vastgelegd.Deze regels en afspraken betreffen minstens : - opleidings- en instructiebeleid vereist in kader van de uitoefening van technische verstrekkingen door bekwame helpers; - communicatie en informatie-uitwisseling tussen de bekwame helper en arts en/of verpleegkundige verantwoordelijk voor algemene zorg en/of een basisverpleegkundige; - de impact op de arbeidsorganisatie. Art. 4.  Conform artikel 5 van de wet van 18 juni 2023 tot invoering van een overlegprocedure in het kader van de uitoefening van technische verstrekkingen door bekwame helpers bedoeld in artikel 124, 1°, 6de lid van de wet betreffende de uitoefening van de gezondheidszorgberoepen, gecoördineerd op 10 mei 2015 wordt jaarlijks een bespreking binnen het lokaal sociaal overlegorgaan geagendeerd zolang het gebruik aanhoudt. Met oog op deze bespreking bezorgt de werkgever minstens 15 dagen vóór de vergadering minstens de volgende informatie : - het aantal betrokken werknemers; - het aantal betrokken patiënten; - de aard van de verstrekkingen; - de gevolgde opleiding en/of de ontvangen instructies; - de impact op de arbeidsorganisatie. Art. 5.  Wanneer toegelaten technische verstrekkingen worden uitgeoefend door bekwame helpers, zorgt de werkgever voor de nodige kwaliteitsvolle instructies en/of opleiding. De opleiding kan zowel intern ols extern worden georganiseerd. De werkgever ziet er op toe dot de instructies en/of opleiding zo nodig worden opgevolgd en geactualiseerd. Art. 6. De werkgever gaat na dot de bekwame helper voldoet aan de opleidingsvoorwaarden zoals voorzien in artikel 9 van het koninklijk besluit van 29 februari 2024 tot vaststelling van de datum van inwerkingtreding van de wet van 11 juni 2023 tot wijziging van artikel 124, 1° van de wet betreffende de uitoefening van de gezondheidszorgberoepen, gecoördineerd op 10 mei 2015. De aanwezigheid van een door een arts en/of verpleegkundige verantwoordelijk voor algemene zorg en/of een basisverpleegkundige opgesteld zorgplan bevestigt dot de werknemer aan deze opleidingsvoorwaarden voldoet. Art. 7. De werkgever voorziet de nodige maatregelen zodat een bekwame helper contact kan opnemen met een arts of verpleegkundige verantwoordelijk voor algemene zorg of basisverpleegkundige. Art. 8. De werkgever informeert de verzekeringsinstelling over het stellen van technische verpleegkundige handelingen als bekwame helper zodat de burgerlijke aansprakelijkheid van de bekwame helper in het kader van het stellen van de toegelaten verpleegkundige handelingen verzekerd is. Ook de kosten verbonden aan een gebeurlijke juridische procedure tegen de bekwame helper betreffende (de gevolgen van) het stellen van toegelaten technische verstrekkingen zijn ten laste van de werkgever of diens verzekeringsinstelling. Art. 9. De werkgever legt vast welke functies het uitoefenen van technische verstrekkingen als bekwame helper kunnen opnemen. Het engagement van de werknemer om de uitoefening van technische verstrekkingen ols bekwame helper op te nemen, wordt vastgesteld in een schriftelijk akkoord vóór aanvang van deze uitoefening. Zoals bepaald in artikel 124, 1°, 14de lid van de wet van 10 mei 2015 betreffende de uitoefening van de gezondheidszorgberoepen kan een werknemer niet verplicht worden om zich te engageren als bekwame helper of om het aangegane engagement aan te houden. Slotbepalingen en inwerkingtreding Art. 10.  § 1. Deze collectieve arbeidsovereenkomst treedt in werking op de datum van ondertekening en is gesloten voor onbepaalde duur.  § 2. Zij kan door elk van de partijen opgezegd worden mits een opzeggingstermijn van zes maanden, bij een ter post aangetekend schrijven gericht aan de voorzitter van het Paritair Subcomité voor de opvoedings- en huisvestingsinrichtingen en -diensten van de Vlaamse Gemeenschap (319.01). Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
+</t>
         </is>
       </c>
     </row>
@@ -2585,29 +2584,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2025004076</t>
+          <t>2025000793</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>27 mei 2025</t>
+          <t>23 mei 2025</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4 maart 2025. - Koninklijk besluit houdende gedeeltelijke hernieuwing van de Hoge Raad voor oorlogsinvaliden, oud-strijders en oorlogsslachtoffers</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 30 oktober 2023, gesloten in het Paritair Subcomité voor de terugwinning van papier, betreffende de arbeids- en loonvoorwaarden (1)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-27&amp;numac_search=2025004076&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025004076=67&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-23&amp;numac_search=2025000793&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025000793=67&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 8 augustus 1981 tot oprichting van het Instituut voor veteranen - het Nationaal Instituut voor oorlogsinvaliden, oud-strijders en oorlogsslachtoffers en van de Hoge Raad voor oorlogsinvaliden, oud-strijders en oorlogsslachtoffers, artikel 30;Gelet op het koninklijk besluit van 29 november 1982 houdende uitvoering van de wet van 8 augustus 1981 tot oprichting van het Instituut voor veteranen - het Nationaal Instituut voor oorlogsinvaliden, oud-strijders en oorlogsslachtoffers en van de Hoge Raad voor oorlogsinvaliden, oud-strijders en oorlogsslachtoffers, artikel 22, derde lid;Gelet op het koninklijk besluit van 14 juni 2021 houdende gedeeltelijke hernieuwing van de Hoge Raad voor oorlogsinvaliden, oud-strijders en oorlogsslachtoffers, artikels 2 en 3;Overwegende dat er dient te worden voorzien in de vervanging van overleden leden van de Hoge Raad voor oorlogsinvaliden, oud-strijders en oorlogsslachtoffers ;Overwegende de unanieme beslissing van de Hoge Raad voor oorlogsinvaliden, oud-strijders en oorlogsslachtoffers tijdens de vergadering van 17 december 2024;Overwegende het voorstel van de Hoge Raad voor oorlogsinvaliden, oud-strijders en oorlogsslachtoffers van 20 januari 2025;Op de voordracht van de Minister van Defensie,Hebben Wij besloten en besluiten Wij :Artikel 1. Wordt benoemd tot lid van de Hoge Raad voor oorlogsinvaliden, oud-strijders en oorlogsslachtoffers, de heer Renaud de TERWANGNE ter vervanging van de heer Raymond BEHR, overleden, waarvan hij het mandaat zal voleindigen.Art. 2. Wordt benoemd tot lid van de Hoge Raad voor oorlogsinvaliden, oud-strijders en oorlogsslachtoffers, mevrouw Danielle IWENS ter vervanging van de heer André MOUTHUY, overleden, waarvan zij het mandaat zal voleindigen.Art. 3. Wordt benoemd tot lid van de Hoge Raad voor oorlogsinvaliden, oud-strijders en oorlogsslachtoffers, de heer Yves COLLIN ter vervanging van de heer Martin AEGTEN, overleden, waarvan hij het mandaat zal voleindigen.Art. 4. Dit besluit heeft uitwerking met ingang van 1 januari 2025.Art. 5. De Minister bevoegd voor Oorlogsslachtoffers is belast met de uitvoering van dit besluit.Brussel, 4 maart 2025.FILIPVan Koningswege :De Minister van Defensie,T. FRANCKEN 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Subcomité voor de terugwinning van papier;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 30 oktober 2023, gesloten in het Paritair Subcomité voor de terugwinning van papier, betreffende de arbeids- en loonvoorwaarden.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 7 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Subcomité voor de terugwinning van papierCollectieve arbeidsovereenkomst van 30 oktober 2023Arbeids- en loonvoorwaarden (Overeenkomst geregistreerdop 21 november 2023 onder het nummer 184004/CO/142.03)HOOFDSTUK I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de arbeiders en arbeidsters van de ondernemingen die ressorteren onder het Paritair Subcomité voor de terugwinning van papier.Voor de toepassing van deze collectieve arbeidsovereenkomst wordt onder "arbeiders" verstaan : de mannelijke en vrouwelijke werklieden.HOOFDSTUK II. - BeroepenclassificatieArt. 2. De beroepenclassificatie wordt als volgt vastgesteld :  </t>
         </is>
       </c>
     </row>
@@ -2617,7 +2615,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2025003649</t>
+          <t>2025201204</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2627,18 +2625,18 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6 oktober 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 16 april 2023 betreffende het rijbewijs vereist voor door waterstof of met een elektrische motor aangedreven bestelwagens. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de handel in voedingswaren, betreffende de arbeidsduur van sommige werklieden die onder het Paritair Comité voor de handel in voedingswaren ressorteren (1)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-23&amp;numac_search=2025003649&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003649=68&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-23&amp;numac_search=2025201204&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201204=68&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 6 oktober 2024 tot wijziging van het koninklijk besluit van 16 april 2023 betreffende het rijbewijs vereist voor door waterstof of met een elektrische motor aangedreven bestelwagens (Belgisch Staatsblad van 15 oktober 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST MOBILITÄT UND TRANSPORTWESEN6. OKTOBER 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 16. April 2023 über den Führerschein für Kleintransporter mit Wasserstoff- oder ElektromotorPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des am 16. März 1968 koordinierten Gesetzes über die Straßenverkehrspolizei, des Artikels 1 Absatz 1 und des Artikels 26, ersetzt durch das Gesetz vom 9. Juli 1976;Aufgrund des Königlichen Erlasses vom 16. April 2023 über den Führerschein für Kleintransporter mit Wasserstoff- oder Elektromotor;In Erwägung des Königlichen Erlasses vom 15. März 1968 zur Festlegung der allgemeinen Regelung über die technischen Anforderungen an Kraftfahrzeuge, ihre Anhänger, ihre Bestandteile und ihr Sicherheitszubehör;In Erwägung des Königlichen Erlasses vom 23. März 1998 über den Führerschein;Aufgrund der Beteiligung der Regionalregierungen;Aufgrund des Gutachtens Nr. 76.981/2/V des Staatsrates vom 26. August 2024, abgegeben in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Auf Vorschlag des Ministers der MobilitätHaben Wir beschloßen und erlassen Wir:Artikel 1. In Artikel 2 des Königlichen Erlasses vom 16. April 2023 über den Führerschein für Kleintransporter mit Wasserstoff- oder Elektromotor werden die Wörter "zur Güterbeförderung ohne Anhänger verwendet werden," durch die Wörter "zur Güterbeförderung verwendet werden, ohne Anhänger," ersetzt.Art. 2.  desselben Erlasses wird wie folgt abgeändert:a) In Absatz 1 werden zwischen den Wörtern "und die Logistik ist" und den Wörtern "und die an dem" die Wörter "oder auf deren Namen mehr als neun Fahrzeuge der Führerscheinklasse C1 oder C oder der Fahrzeugklasse N1 zugelassen sind" eingefügt.b) In Absatz 2 werden zwischen den Wörtern "dem in Absatz 1 erwähnten Sektor angehören" und den Wörtern ", und zwar gemäß" die Wörter "oder dass die in Absatz 1 erwähnten Fahrzeuge auf ihren Namen zugelassen sind" eingefügt.Art. 3. Der für den Straßenverkehr zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 6. Oktober 2024PHILIPPEVon Königs wegen:Der Minister der MobilitätG. GILKINET 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de handel in voedingswaren; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de handel in voedingswaren, betreffende de arbeidsduur van sommige werklieden die onder het Paritair Comité voor de handel in voedingswaren ressorteren. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de handel in voedingswaren Collectieve arbeidsovereenkomst van 18 december 2024 Arbeidsduur van sommige werklieden die onder het Paritair Comité voor de handel in voedingswaren ressorteren (Overeenkomst geregistreerd op 7 januari 2025 onder het nummer 191336/CO/119) HOOFDSTUK I. - Toepassingsgebied Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is toepasselijk op de werkgevers en op de arbeiders van de ondernemingen die ressorteren onder het Paritair Comité voor de handel in voedingswaren, met uitsluiting van de slagerijen, spekslagerijen en penserijen.  § 2. Met "arbeiders" worden de mannelijke en vrouwelijke arbeiders bedoeld. HOOFDSTUK II. - Bepalingen Art. 2. De werkgever is, wat de aan werken van vervoer tewerkgestelde werklieden betreft, ertoe gehouden het bedongen loon voor de volledige aanwezigheidstijd te betalen. Hij mag de rechtvaardiging vragen van de rusttijden welke onder meer met het oog op de verkeersveiligheid werden genomen door de werklieden die in vorig lid beoogde werken verrichten. Voor de toepassing van artikel 29 van de arbeidswet van 16 maart 1971 (Belgisch Staatsblad van 30 maart 1971) worden de overuren berekend in verhouding tot de aanwezigheidstijd. De bij het arbeidsreglement bepaalde rusttijden gedurende welke de werkman het voertuig niet hoeft te bewaken, worden niet als aanwezigheidstijd aangezien.HOOFDSTUK III. - Duur Art. 3. Deze collectieve arbeidsovereenkomst heeft uitwerking met ingang van 1 november 2023 en treedt buiten werking op 31 oktober 2025. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -2649,7 +2647,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2025003647</t>
+          <t>2025200925</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2659,18 +2657,18 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>22 september 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 19 april 2014 betreffende de inning en de consignatie van een som bij de vaststelling van de overtredingen inzake het wegverkeer. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst nr. 32/8 van 17 december 2024, tot wijziging van de collectieve arbeidsovereenkomst nr. 32bis van 7 juni 1985 betreffende het behoud van de rechten van de werknemers bij wijziging van werkgever ingevolge de overgang van ondernemingen krachtens overeenkomst en tot regeling van de rechten van de werknemers die overgenomen worden bij overname van activa na faillissement (1)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-23&amp;numac_search=2025003647&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003647=69&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-23&amp;numac_search=2025200925&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025200925=69&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 22 september 2024 tot wijziging van het koninklijk besluit van 19 april 2014 betreffende de inning en de consignatie van een som bij de vaststelling van de overtredingen inzake het wegverkeer (Belgisch Staatsblad van 4 oktober 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST MOBILITÄT UND TRANSPORTWESEN22. SEPTEMBER 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 19. April 2014 über die Erhebung und die Hinterlegung eines Geldbetrags bei der Feststellung der Verstöße in Sachen StraßenverkehrPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des am 16. März 1968 koordinierten Gesetzes über die Straßenverkehrspolizei, des Artikels 1 Absatz 1 und des Artikels 65;Aufgrund des Königlichen Erlasses vom 19. April 2014 über die Erhebung und die Hinterlegung eines Geldbetrags bei der Feststellung der Verstöße in Sachen Straßenverkehr;Aufgrund der Beteiligung der Regionalregierungen;Aufgrund der Stellungnahmen der Finanzinspektoren vom 8. Februar 2024, 26. Februar 2024, 29. Februar 2024 und 17. April 2024;Aufgrund des Einverständnisses des Ministers des Haushalts vom 18. Juni 2024;Aufgrund des Gutachtens Nr. 76.890/2/V des Staatsrates vom 1. August 2024, abgegeben in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Auf Vorschlag des Ministers der Mobilität, des Ministers der Finanzen, des Ministers der Justiz und der Ministerin des InnernHaben Wir beschloßen und erlassen Wir:Artikel 1 - In Artikel 2 einziger Absatz Nr. 4 des Königlichen Erlasses vom 19. April 2014 über die Erhebung und die Hinterlegung eines Geldbetrags bei der Feststellung der Verstöße in Sachen Straßenverkehr, abgeändert durch den Königlichen Erlass vom 23. April 2017, wird der vierte Satz, der mit den Wörtern "Ein Verstoß" beginnt und mit den Wörtern "einer sofortigen Erhebung von 1.260 EUR geben." endet, aufgehoben.Art. 2 - In Artikel 17 § 1 desselben Erlasses, zuletzt abgeändert durch den Königlichen Erlass vom 23. April 2017, wird Absatz 2 wie folgt ersetzt:"Gemäß Artikel 65 § 3 Absatz 2 des Gesetzes über die Straßenverkehrspolizei ist bei folgenden Verstößen ein Betrag von 1.260 EUR zu hinterlegen, auch wenn durch die Tat ein Schaden für Dritte entstanden ist:1. Verstoß gegen Artikel 34 § 2 Nr. 1 des Gesetzes über die Straßenverkehrspolizei, wenn bei der Atemanalyse eine Alkoholkonzentration von mindestens 0,50 Milligramm pro Liter ausgeatmeter Alveolarluft gemessen wird,2. Verstoß gegen Artikel 34 § 2 Nr. 3 desselben Gesetzes,3. Verstoß gegen Artikel 37bis § 1 Nr. 1 und 5 desselben Gesetzes,4. als Führer bei einem in Artikel 61ter § 1 Nr. 1 desselben Gesetzes erwähnten Speicheltest,5. bei einer in Artikel 63 § 1 Nr. 1, 2 und 4 desselben Gesetzes erwähnten Blutprobe,6. bei einer in Artikel 63 § 1 Nr. 5 desselben Gesetzes erwähnten Blutprobe, wenn die Artikel 61bis § 2 Nr. 1 desselben Gesetzes erwähnte standardisierte Checkliste Hinweise auf Anzeichen eines kürzlichen Konsums einer der in Artikel 37bis § 1 Nr. 1 desselben Gesetzes erwähnten Substanzen liefert."Art. 3 - Vorliegender Erlass tritt am ersten Tag des dritten Monats nach Ablauf einer Frist von zehn Tagen, die am Tag nach seiner Veröffentlichung im Belgischen Staatsblatt beginnt, in Kraft.Art. 4 - Der für den Straßenverkehr zuständige Minister, der Minister der Finanzen, der Minister der Justiz und der Minister des Innern sind, jeweils für ihren Bereich, mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 22. September 2024PHILIPPEVon Königs wegen:Der Minister der MobilitätG. GILKINETDer Minister der FinanzenV. VAN PETEGHEMDer Minister der JustizP. VAN TIGCHELTDie Ministerin des InnernA. VERLINDEN 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van de Nationale Arbeidsraad; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst nr. 32/8 van 17 december 2024, tot wijziging van de collectieve arbeidsovereenkomst nr. 32bis van 7 juni 1985 betreffende het behoud van de rechten van de werknemers bij wijziging van werkgever ingevolge de overgang van ondernemingen krachtens overeenkomst en tot regeling van de rechten van de werknemers die overgenomen worden bij overname van activa na faillissement. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageNationale Arbeidsraad Collectieve arbeidsovereenkomst nr. 32/8 van 17 december 2024 Wijziging van de collectieve arbeidsovereenkomst nr. 32bis van 7 juni 1985 betreffende het behoud van de rechten van de werknemers bij wijziging van werkgever ingevolge de overgang van ondernemingen krachtens overeenkomst en tot regeling van de rechten van de werknemers die overgenomen worden bij overname van activa na faillissement (Overeenkomst geregistreerd op 31 januari 2025 onder het nummer 191690/CO/300) Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités; Gelet op de collectieve arbeidsovereenkomst nr. 32bis van 7 juni 1985 betreffende het behoud van de rechten van de werknemers bij wijziging van werkgever ingevolge de overgang van ondernemingen krachtens overeenkomst en tot regeling van de rechten van de werknemers die overgenomen worden bij overname van activa na faillissement, geregistreerd op 26 juni 1985 onder het nummer 13290/CO/300;Gelet op de vorige wijzigingen van de collectieve arbeidsovereenkomst nr. 32bis : - de collectieve arbeidsovereenkomst nr. 32ter van 2 december 1986, geregistreerd op 11 december 1986 onder het nummer 16933/CO/300; - nr. 32quater van 19 december 1989, geregistreerd op 29 december 1989 onder het nummer 24677/CO/300; - nr. 32quinquies van 13 maart 2002, geregistreerd op 13 maart 2002 onder het nummer 61472/CO/300; - nr. 32sexies van 27 september 2016 geregistreerd op 7 oktober 2016 onder het nummer 135343/CO/300; en - nr. 32/7 van 23 april 2019, geregistreerd op 24 april 2019 onder het nummer 151408/CO/300. Overwegende dat de Nationale Arbeidsraad op 17 december 2019 de aanbeveling nr. 28 inzake herstructureringen heeft gericht aan alle paritaire comités en ondernemingen, waarbij aanbevelingen worden gedaan om te komen tot een kwalitatieve en efficiënte informatie en consultatie van werknemers(vertegenwoordigers); Overwegende dat de Nationale Arbeidsraad op 19 december 2023 het advies nr. 2.395 heeft uitgebracht betreffende de herstructureringen en de evaluatie van de aanbeveling nr. 28; Overwegende dat de sociale partners in dit kader overgekomen zijn om de collectieve arbeidsovereenkomst nr. 32bis aan te passen; Hebben de navolgende interprofessionele organisaties van werkgevers en van werknemers : - Het Verbond van Belgische Ondernemingen; - De organisaties voorgedragen door de Hoge Raad voor de Zelfstandigen en de Kleine en Middelgrote Ondernemingen; - De Boerenbond; - "La Fédération wallonne de l'Agriculture"; - De Unie van socialprofitondernemingen; - Het Algemeen Christelijk Vakverbond van België; - Het Algemeen Belgisch Vakverbond; - De Algemene Centrale der Liberale Vakbonden van België; op 17 december 2024 in de Nationale Arbeidsraad de volgende collectieve arbeidsovereenkomst gesloten. Artikel 1. Artikel 3 van deze collectieve arbeidsovereenkomst heeft hetzelfde toepassingsgebied als hoofdstuk IV van de collectieve arbeidsovereenkomst nr. 32bis van 7 juni 1985 betreffende het behoud van de rechten van de werknemers bij wijziging van werkgever ingevolge de overgang van ondernemingen krachtens overeenkomst en tot regeling van de rechten van de werknemers die overgenomen worden bij overname van activa na faillissement. Artikel 4 van deze collectieve arbeidsovereenkomst heeft hetzelfde toepassingsgebied als hoofdstuk II van de collectieve arbeidsovereenkomst nr. 32bis van 7 juni 1985. Art. 2. Artikel 1 van de collectieve arbeidsovereenkomst nr. 32bis van 7 juni 1985 wordt aangevuld met het volgende lid : "Deze collectieve arbeidsovereenkomst regelt eveneens de informatie die de vervreemder op verzoek dient te bezorgen aan de geïdentificeerde verkrijger in geval van overgang van ondernemingen krachtens overeenkomst." Art. 3. De aanhef van artikel 15bis van dezelfde collectieve arbeidsovereenkomst, dat hernummerd wordt als artikel 15/1, wordt vervangen door wat volgt : "In de ondernemingen waar noch een ondernemingsraad, noch een vakbondsafvaardiging, noch een comité voor preventie en bescherming op het werk bestaat, moeten de betrokken werknemers vooraf in kennis worden gesteld van : " Art. 4.  § 1. In dezelfde collectieve arbeidsovereenkomst wordt vóór de hoofdstukken V en VI, die respectievelijk de hoofdstukken VI en VII worden, een nieuw hoofdstuk V ingevoegd, met als opschrift: "Informatie mee te delen aan de geïdentificeerde verkrijger in geval van overgang van ondernemingen krachtens overeenkomst".  § 2. Onder het nieuwe hoofdstuk V wordt in dezelfde collectieve arbeidsovereenkomst een artikel 15/2 ingevoegd met een commentaar, luidend als volgt: "Artikel 15/2 Op verzoek van de vertegenwoordigers van de werknemers die bij de overgang van ondernemingen krachtens overeenkomst betrokken zijn, deelt de vervreemder de inhoud van de informatie en raadpleging mee aan de geïdentificeerde verkrijger en nodigt hem uit om zich aan hen voor te stellen tijdens die informatie en raadpleging.In de ondernemingen waar noch een ondernemingsraad, noch een vakbondsafvaardiging, noch een comité voor preventie en bescherming op het werk bestaat, deelt de vervreemder op verzoek van de werknemers die bij de overgang van ondernemingen krachtens overeenkomst betrokken zijn, de inhoud van de informatie mee aan de geïdentificeerde verkrijger en nodigt hem uit om zich aan hen voor te stellen vóór de overgang. Commentaar 1. De in artikel 15/2, eerste lid, van deze collectieve arbeidsovereenkomst vermelde informatie en raadpleging zijn die welke worden bedoeld in de voornoemde collectieve arbeidsovereenkomst nr. 9, in de voornoemde collectieve arbeidsovereenkomst nr. 5 en in de voornoemde wet van 4 augustus 1996. De in artikel 15/2, tweede lid, van deze collectieve arbeidsovereenkomst vermelde informatie is die welke wordt bedoeld in artikel 15/1 van deze collectieve arbeidsovereenkomst. 2. Zodra het verzoek door de werknemers(vertegenwoordigers) is gedaan, moet de inhoud van de informatie (en raadpleging) in alle gevallen aan de geïdentificeerde verkrijger worden bezorgd, ongeacht of deze al dan niet positief heeft gereageerd op de uitnodiging van de vervreemder overeenkomstig dit artikel. De vervreemder doet dit tijdig, tijdens de informatie (en raadpleging) van de werknemers(vertegenwoordigers) en vóór de overgang. De uitnodiging gebeurt tijdig en in ieder geval vóór de overgang. 3. De geïdentificeerde verkrijger is diegene die ingevolge de overgang de hoedanigheid van werkgever zal verkrijgen ten aanzien van de werknemers van de onderneming die overgaat of het gedeelte van de onderneming dat overgaat." Art. 5. Deze collectieve arbeidsovereenkomst wordt voor onbepaalde tijd gesloten. Ze treedt in werking op 1 februari 2025. Zij kan op verzoek van de meest gerede ondertekenende partij geheel of gedeeltelijk worden herzien of opgezegd, met inachtneming van een opzeggingstermijn van zes maanden. De organisatie die het initiatief tot herziening of opzegging neemt, moet in een gewone brief aan de voorzitter van de Nationale Arbeidsraad de redenen ervan aangeven en amendementsvoorstellen indienen. De andere organisaties verbinden zich ertoe deze binnen een maand na ontvangst ervan in de Nationale Arbeidsraad te bespreken. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL BijlageBijlage aan de de collectieve arbeidsovereenkomst nr. 32/8 van 17 december 2024, tot wijziging van de collectieve arbeidsovereenkomst nr. 32bis van 7 juni 1985 betreffende het behoud van de rechten van de werknemers bij wijziging van werkgever ingevolge de overgang van ondernemingen krachtens overeenkomst en tot regeling van de rechten van de werknemers die overgenomen worden bij overname van activa na faillissement WIJZIGING VAN DE COMMENTAAR VAN DE COLLECTIEVE ARBEIDSOVEREENKOMST NR. 32BIS VAN 7 JUNI 1985 BETREFFENDE HET BEHOUD VAN DE RECHTEN VAN DE WERKNEMERS BIJ WIJZIGING VAN WERKGEVER INGEVOLGE DE OVERGANG VAN ONDERNEMINGEN KRACHTENS OVEREENKOMST EN TOT REGELING VAN DE RECHTEN VAN DE WERKNEMERS DIE OVERGENOMEN WORDEN BIJ OVERNAME VAN ACTIVA NA FAILLISSEMENT Op 17 december 2024 hebben de in de Nationale Arbeidsraad vertegenwoordigde werkgevers- en werknemersorganisaties de collectieve arbeidsovereenkomst nr. 32/8 gesloten tot wijziging van de collectieve arbeidsovereenkomst nr. 32bis van 7 juni 1985 betreffende het behoud van de rechten van de werknemers bij wijziging van werkgever ingevolge de overgang van ondernemingen krachtens overeenkomst en tot regeling van de rechten van de werknemers die overgenomen worden bij overname van activa na faillissement. De wijzigingen in de collectieve arbeidsovereenkomst nr. 32bis beogen in eerste instantie om uitvoering te geven aan het advies nr. 2.395 dat de Raad op 19 december 2023 heeft uitgebracht betreffende de herstructureringen.Ook wordt het artikel 15bis van de collectieve arbeidsovereenkomst nr. 32bis, hernummerd als artikel 15/1, gewijzigd omdat het nog geen rekening houdt met de invoeging in 2008 van het artikel 65decies in de wet van 4 augustus 1996 betreffende het welzijn van de werknemers bij de uitvoering van hun werk. Het artikel 65decies stelt dat het comité voor preventie en bescherming op het werk "bij ontstentenis van een ondernemingsraad en een vakbondsafvaardiging de plaats inneemt van de ondernemingsraad, of, bij ontstentenis, de vakbondsafvaardiging", onder andere voor het recht op informatie en consultatie voorzien in de collectieve arbeidsovereenkomst nr. 9 van 9 maart 1972 houdende ordening van de in de Nationale Arbeidsraad gesloten nationale akkoorden en collectieve arbeidsovereenkomsten betreffende de ondernemingsraden en in de collectieve arbeidsovereenkomst nr. 32bis. Daarnaast wordt een derde lid aan de commentaar bij artikel 15/1 van de collectieve arbeidsovereenkomst nr. 32bis toegevoegd om te verduidelijken wat met het woord "vooraf" in dit artikel bedoeld wordt, op basis van hetgeen hieromtrent is opgenomen in de richtlijn 2001/23/EG van 12 maart 2001. De in de Nationale Arbeidsraad vertegenwoordigde werkgevers- en werknemersorganisaties hebben het dan ook noodzakelijk geacht om, ter verduidelijking, de commentaar bij artikel 15/1 van de collectieve arbeidsovereenkomst nr. 32bis als volgt aan te vullen : 1. Het tweede lid van de commentaar bij artikel 15/1 wordt als volgt aangevuld: "en in de wet van 4 augustus 1996 betreffende het welzijn van de werknemers bij de uitvoering van hun werk." 2. Er wordt een derde lid toegevoegd aan de commentaar bij artikel 15/1: "De vervreemder moet die informatie tijdig vóór de totstandkoming van de overgang verstrekken." Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -2681,28 +2679,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2025003025</t>
+          <t>2025201193</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>30 mei 2025</t>
+          <t>23 mei 2025</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16 september 2024. - Koninklijk besluit tot uitvoering van artikel 85/1, § 4, van de wet van 4 april 2014 betreffende de verzekeringen. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 9 januari 2025, gesloten in het Paritair Comité voor de koopvaardij, betreffende de goedkeuring van de bedragen vastgesteld in uitvoering van artikel 13 van de collectieve arbeidsovereenkomsten van 18 oktober 2004 (72990/CO/316) en 20 april 2005 (74708/CO/316) tot wijziging en coördinatie van de statuten van het "Bedrijfsfonds voor de koopvaardij" en tot vaststelling van de bedragen van de tewerkstellingspremies en de te innen werkgeversbijdragen in uitvoering van de collectieve arbeidsovereenkomst van 20 april 2005 betreffende de uitbetaling van tewerkstellingspremies voor de tewerkstelling van scheepsgezellen ingeschreven in de Belgische Pool der Zeelieden (1)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-30&amp;numac_search=2025003025&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003025=70&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-23&amp;numac_search=2025201193&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201193=70&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 16 september 2024 tot uitvoering van artikel 85/1, § 4, van de wet van 4 april 2014 betreffende de verzekeringen (Belgisch Staatsblad van 3 oktober 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST WIRTSCHAFT, KMB, MITTELSTAND UND ENERGIE16. SEPTEMBER 2024 - Königlicher Erlass zur Ausführung von Artikel 85/1 § 4 des Gesetzes vom 4. April 2014 über die VersicherungenPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des Gesetzes vom 4. April 2014 über die Versicherungen, des Artikels 85/1 § 4, eingefügt durch das Gesetz vom 9. Oktober 2023, und des Artikels 85/2, eingefügt durch das Gesetz vom 3. Mai 2024;Aufgrund der Stellungnahme des Versicherungsausschusses vom 9. Februar 2024;Aufgrund der Stellungnahme der FSMA vom 26. März 2024;Aufgrund der Stellungnahme des Finanzinspektors vom 10. April 2024;Aufgrund des Einverständnisses der Staatssekretärin für Haushalt vom 23. April 2024;Aufgrund der Stellungnahme Nr. 73/2024 der Datenschutzbehörde vom 26. Juli 2024;Aufgrund der Auswirkungsanalyse beim Erlass von Vorschriften, die gemäß Artikel 6 § 1 des Gesetzes vom 15. Dezember 2013 zur Festlegung verschiedener Bestimmungen in Sachen administrative Vereinfachung durchgeführt worden ist;Aufgrund des Antrags auf Begutachtung binnen einer Frist von dreißig Tagen, der in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat beim Staatsrat eingereicht worden ist;In der Erwägung, dass der Antrag auf Begutachtung am 29. Mai 2024 unter der Nummer 76.624/1 in die Liste der Gesetzgebungsabteilung des Staatsrates eingetragen worden ist;Aufgrund des Beschlusses der Gesetzgebungsabteilung vom 31. Mai 2024 in Anwendung von Artikel 84 § 5 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat, binnen der gesetzten Frist kein Gutachten abzugeben;In der Erwägung, dass zur Vereinfachung der Kündigungsformalitäten bestimmt wird, dass Versicherungsnehmer, die im Hinblick auf den Abschluss eines Vertrags mit einem neuen Versicherer einen Vertrag kündigen, von diesem neuen Versicherer oder gegebenenfalls einem Versicherungsvermittler verlangen können, für ihre Rechnung die zur Ausübung des Kündigungsrechts erforderlichen Formalitäten zu erledigen;In der Erwägung, dass ein neuer Versicherer oder ein Versicherungsvermittler bestimmte Informationen benötigt, um die für die Ausübung des Kündigungsrechts erforderlichen Formalitäten erledigen zu können;In der Erwägung, dass beim Austausch von Informationen, die für die Erledigung der Formalitäten für die Ausübung des Kündigungsrechts erforderlich sind, sowohl der Versicherungsnehmer als auch der neue Versicherer oder ein Versicherungsvermittler für die durch sie übermittelten Informationen auf der Grundlage des allgemeinen Rechts verantwortlich sind;In der Erwägung, dass es wichtig ist, dass der neue Versicherer oder der Versicherungsvermittler nachweisen kann, dass der ursprüngliche Antrag auf Kündigung vom Versicherungsnehmer des aktuellen Versicherungsvertrags stammt;Auf Vorschlag des Ministers der Wirtschaft, des Ministers der Justiz und der Staatssekretärin für Verbraucherschutz und aufgrund der Stellungnahme der Minister, die im Rat darüber beraten haben,Haben Wir beschloßen und erlassen Wir:Artikel 1 - Vorliegender Erlass findet Anwendung auf die Kündigung von stillschweigend erneuerbaren Versicherungsverträgen wie in Artikel 85/1 § 3 des Gesetzes vom 4. April 2014 über die Versicherungen erwähnt.Art. 2 - Im Hinblick auf die Anwendung von Artikel 85/1 § 3 desselben Gesetzes teilt der Versicherungsnehmer dem neuen Versicherer oder gegebenenfalls dem Versicherungsvermittler im Rahmen der in den Artikeln 85/1 und 85/2 desselben Gesetzes festgelegten Datenkategorien zumindest folgende Informationen mit:1. Name, Vorname und Postadresse des Versicherungsnehmers,2. Identifizierung des derzeitigen Versicherers oder des Versicherungsvermittlers, der als Bevollmächtigter eines oder mehrerer Versicherungsunternehmen befugt ist, im Namen und für Rechnung dieser Unternehmen den Versicherungsvertrag zu verwalten, einschließlich der Unternehmensnummer,3. Policenummer des zu kündigenden Vertrags und betreffender Versicherungsschutz,4. Datum der Vertragseinsetzung und jährliches Fälligkeitsdatum des zu kündigenden Vertrags.Art. 3 - Der Antrag des Versicherungsnehmers, für seine Rechnung die für die Ausübung des in Artikel 85/1 § 3 desselben Gesetzes erwähnten Kündigungsrechts erforderlichen Formalitäten zu erledigen, wird vom Versicherungsnehmer an den neuen Versicherer oder gegebenenfalls einen Versicherungsvermittler auf einem unterzeichneten dauerhaften Datenträger gestellt, durch den sich der Unterzeichner identifiziert und seine Willenserklärung abgibt, den aktuellen Versicherungsvertrag zu kündigen und einen neuen Versicherungsvertrag abzuschließen.Art. 4 - Vorliegender Erlass tritt am 1. Oktober 2024 in Kraft.Art. 5 - Die für Versicherungen, Justiz beziehungsweise Verbraucherschutz zuständigen Minister sind, jeweils für ihren Bereich, mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 16. September 2024PHILIPPEVon Königs wegen:Der Minister der WirtschaftP.-Y. DERMAGNEDer Minister der JustizP. VAN TIGCHELTDie Staatssekretärin für VerbraucherschutzA. BERTRAND 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de koopvaardij; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 9 januari 2025, gesloten in het Paritair Comité voor de koopvaardij, betreffende de goedkeuring van de bedragen vastgesteld in uitvoering van artikel 13 van de collectieve arbeidsovereenkomsten van 18 oktober 2004 (72990/CO/316) en 20 april 2005 (74708/CO/316) tot wijziging en coördinatie van de statuten van het "Bedrijfsfonds voor de koopvaardij" en tot vaststelling van de bedragen van de tewerkstellingspremies en de te innen werkgeversbijdragen in uitvoering van de collectieve arbeidsovereenkomst van 20 april 2005 betreffende de uitbetaling van tewerkstellingspremies voor de tewerkstelling van scheepsgezellen ingeschreven in de Belgische Pool der Zeelieden.Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de koopvaardij Collectieve arbeidsovereenkomst van 9 januari 2025 Goedkeuring van de bedragen vastgesteld in uitvoering van artikel 13 van de collectieve arbeidsovereenkomsten van 18 oktober 2004 (72990/CO/316) en 20 april 2005 (74708/CO/316) tot wijziging en coördinatie van de statuten van het "Bedrijfsfonds voor de koopvaardij" en vaststelling van de bedragen van de tewerkstellingspremies en de te innen werkgeversbijdragen in uitvoering van de collectieve arbeidsovereenkomst van 20 april 2005 betreffende de uitbetaling van tewerkstellingspremies voor de tewerkstelling van scheepsgezellen ingeschreven in de Belgische Pool der Zeelieden (Overeenkomst geregistreerd op 31 januari 2025 onder het nummer 191696/CO/316) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op: a) de werkgevers van de ondernemingen waarvan de activiteit tot de bevoegdheid van het Paritair Comité voor de koopvaardij behoort met uit zondering van de werkgevers van de ondernemingen die sleepboten exploiteren, waarvan de verrichte sleepactiviteit "zeevervoer" is; b) de zeelieden en shoregangers, mannen en vrouwen, die onder de toepassing vallen van artikel 3 van de collectieve arbeidsovereenkomst van 18 oktober 2004 tot wijziging en coördinatie van de statuten van het "Bedrijfsfonds voor de koopvaardij". Art. 2. Vaststelling van de bedragen in toepassing van artikel 13 van de collectieve arbeidsovereenkomsten van 18 oktober 2004 en 20 april 2005 tot wijziging en coördinatie van de statuten van het "Bedrijfsfonds voor de koopvaardij" Voor de tegemoetkoming in de kosten voor vakbondsvorming en in de financiering van sociale doeleinden, vermeld onder artikel 3, 2° van de collectieve arbeidsovereenkomst van 18 oktober 2004 tot wijziging en coördinatie van de statuten van het "Bedrijfsfonds voor de koopvaardij" wordt de bijdrage van de werkgevers met ingang van 1 januari 2025 vastgesteld op: - 0,90 EUR per dag en per zeevarende/shoreganger tewerkgesteld op Belgische vlagschepen en waarvoor aangifte moet worden gedaan bij de Hulp- en Voorzorgskas voor Zeevarenden; - 0,90 EUR per dag en per zeevarende ingeschreven op de Poollijst zoals bedoeld in artikel 1bis, 1° van de besluitwet van 7 februari 1945 betreffende de maatschappelijke veiligheid van de zeelieden ter koopvaardij, tewerkgesteld op vreemde vlagschepen en waarvoor socialezekerheidsbijdragen verschuldigd zijn. Voor de tegemoetkoming in de uitkering van een toeslag bij de wachtgelden van sommige zeevarenden, vermeld onder artikel 3, 3° van de collectieve arbeidsovereenkomst van 18 oktober 2004 tot wijziging en coördinatie van de statuten van het "Bedrijfsfonds voor de koopvaardij" wordt de bijdrage van de werkgevers met ingang van 1 januari 2025 vastgesteld op 0,90 EUR per zeevarende/shoreganger en per dag waarvoor de socialezekerheidsbijdragen verschuldigd zijn. Voor de tegemoetkoming in de uitkering van een gewaarborgd maandloon voor shoregangers, vermeld onder artikel 3, 6° van de collectieve arbeidsovereenkomst van 18 oktober 2004 tot wijziging en coördinatie van de statuten van het "Bedrijfsfonds voor de koopvaardij", wordt de bijdrage van de werkgevers met ingang van 1 januari 2025 vastgesteld op 0 EUR per zeevarende/shoreganger en per dag waarvoor de socialezekerheidsbijdragen verschuldigd zijn. Art. 3. Vaststelling van de bedragen van de tewerkstellingspremies en de te innen werkgeversbijdragen in uitvoering van de collectieve arbeidsovereenkomst van 20 april 2005 (74708/CO/316) Voor de tegemoetkoming in de kosten van die uitbetaling van tewerkstellingspremies aan werkgevers die scheepsgezellen tewerkstellen ingeschreven op de Poollijst zoals bedoeld in artikel 1bis, 1° van de besluitwet van 7 februari 1945 betreffende de maatschappelijke veiligheid van de zeelieden ter koopvaardij, zoals bepaald in artikel 3, 7° van de collectieve arbeidsovereenkomst van 18 oktober 2004 tot wijziging en coördinatie van de statuten van het "Bedrijfsfonds voor de koopvaardij", gewijzigd bij collectieve arbeidsovereenkomst van 20 april 2005 tot wijziging en coördinatie van de statuten van het "Bedrijfsfonds voor de koopvaardij", wordt de bijdrage van de werkgevers met ingang van 1 januari 2025 vastgesteld op: - 0,00 EUR per dag en per zeevarende tewerkgesteld op Belgische vlagschepen; - 0,00 EUR per dag en per zeevarende ingeschreven op de Poollijst zoals bedoeld in artikel 1bis, 1° van de besluitwet van 7 februari 1945 betreffende de maatschappelijke veiligheid van de zeelieden ter koopvaardij, tewerkgesteld op vreemde vlagschepen. Het bedrag van de tewerkstellingspremie bedraagt met ingang van 1 januari 2025 108,00 EUR per dag tewerkstelling van een scheepsgezel ingeschreven op de Poollijst zoals bedoeld in artikel 1bis, 1° van de besluitwet van 7 februari 1945 betreffende de maatschappelijke veiligheid van de zeelieden ter koopvaardij. Art. 4. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025 en wordt gesloten voor onbepaalde tijd. Zij kan door elk van de partijen worden opgezegd, met een opzeggingstermijn van zes maanden, per aangetekende brief gericht aan de voorzitter van het Paritair Comité voor de koopvaardij en aan de ondertekenende partijen. De termijn van zes maanden begint te lopen vanaf de datum waarop de aangetekende brief aan de voorzitter van het paritair comité is toegestuurd. Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst van 20 januari 2022 (registratienummer 176065/CO/316) betreffende de goedkeuring van de bedragen vastgesteld in uitvoering van artikel 13 van de collectieve arbeidsovereenkomsten van 18 oktober 2004 (72990/CO/316) en 20 april 2005 (74708/CO/316) tot wijziging en coördinatie van de statuten van het "Bedrijfsfonds voor de koopvaardij" en tot vaststelling van de bedragen van de tewerkstellingspremies en de te innen werkgeversbijdragen, in uitvoering van de collectieve arbeidsovereenkomst van 20 april 2005 betreffende de uitbetaling van tewerkstellingspremies voor de tewerkstelling van scheepsgezellen ingeschreven in de Belgische Pool der Zeelieden. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -2713,7 +2711,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2025003653</t>
+          <t>2025002976</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2723,19 +2721,18 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>3 september 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 17 september 2010 betreffende het model en de toepassingsregels van de gestandaardiseerde checklist tot vaststelling van indicaties van tekenen van recent druggebruik in het verkeer. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de textielnijverheid, tot wijziging en coördinatie van de statuten van het "Waarborg- en Sociaal Fonds der textielnijverheid" (1)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-23&amp;numac_search=2025003653&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003653=71&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-23&amp;numac_search=2025002976&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025002976=71&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 3 september 2024 tot wijziging van het koninklijk besluit van 17 september 2010 betreffende het model en de toepassingsregels van de gestandaardiseerde checklist tot vaststelling van indicaties van tekenen van recent druggebruik in het verkeer (Belgisch Staatsblad van 18 september 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST MOBILITÄT UND TRANSPORTWESEN3. SEPTEMBER 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 17. September 2010 über das Muster und die Anwendungsvorschriften der standardisierten Checkliste zur Feststellung von Hinweisen auf Anzeichen eines kürzlichen Drogenkonsums im VerkehrPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des am 16. März 1968 koordinierten Gesetzes über die Straßenverkehrspolizei, insbesondere des Artikels 61bis § 2 Nr. 1, ersetzt durch das Gesetz vom 31. Juli 2009;Aufgrund des Königlichen Erlasses vom 17. September 2010 über das Muster und die Anwendungsvorschriften der standardisierten Checkliste zur Feststellung von Hinweisen auf Anzeichen eines kürzlichen Drogenkonsums im Verkehr;Aufgrund der Beteiligung der Regionalregierungen;Aufgrund der Stellungnahmen der Finanzinspektoren vom 2. April 2024 und 30. April 2024;Aufgrund des Gutachtens Nr. 76.582/4 des Staatsrates vom 19. Juni 2024, abgegeben in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Auf Vorschlag des Ministers der Wirtschaft und des Ministers der JustizHaben Wir beschloßen und erlassen Wir:Artikel 1 -  Artikel 2 Absatz 2 des Königlichen Erlasses vom 17. September 2010 über das Muster und die Anwendungsvorschriften der standardisierten Checkliste zur Feststellung von Hinweisen auf Anzeichen eines kürzlichen Drogenkonsums im Verkehr wird wie folgt ersetzt:"Als Hinweis auf Anzeichen für kürzlich erfolgten Konsum einer der in Artikel 37bis § 1 Nr. 1 des Gesetzes vom 16. März 1968 über die Straßenverkehrspolizei erwähnten Substanzen gelten:1. mindestens drei angekreuzte Anzeichen auf der standardisierten Checkliste, verteilt auf mindestens zwei verschiedene Rubriken in Teil A; oder2. mindestens ein angekreuztes Anzeichen in Teil B der standardisierten Checkliste."Art. 2 -  Die Anlage um selben Erlass wird wie folgt ersetzt:"Anlage zum Königlichen Erlass vom 17. September 2010 über das Muster und die Anwendungsvorschriften der standardisierten Checkliste zur Feststellung von Hinweisen auf Anzeichen eines kürzlichen Drogenkonsums im Verkehr  Voor de raadpleging van de tabel, zie beeld  Art. 3 -  Vorliegender Erlass tritt am ersten Tag des Monats nach Ablauf einer Frist von zehn Tagen, die am Tag nach seiner Veröffentlichung im Belgischen Staatsblatt beginnt, in Kraft.Art. 4 - Die für Straßenverkehr beziehungsweise Justiz zuständigen Minister sind, jeweils für ihren Bereich, mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 3. September 2024PHILIPPEVon Königs wegen:Der Minister der MobilitätG. GILKINETDer Minister der JustizP. VAN TIGCHELT 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de textielnijverheid;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de textielnijverheid, tot wijziging en coördinatie van de statuten van het "Waarborg- en Sociaal Fonds der textielnijverheid".Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 7 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de textielnijverheidCollectieve arbeidsovereenkomst van 18 december 2024Wijziging en coördinatie van de statuten van het "Waarborg- en Sociaal Fonds der textielnijverheid" (Overeenkomst geregistreerd op 31 januari 2025 onder het nummer 191707/CO/120)HOOFDSTUK I. - ToepassingsgebiedArtikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op alle werkgevers die onder de bevoegdheid vallen van het Paritair Comité voor de textielnijverheid (PC 120) en op de arbeiders die ze tewerkstellen, met uitzondering van de ondernemingen en de erin tewerkgestelde arbeiders die onder de bevoegdheid vallen van het Paritair Subcomité voor de textielnijverheid uit het administratief arrondissement Verviers (PSC 120.01) en het Paritair Subcomité voor het vervaardigen van en de handel in zakken in jute of in vervangingsmaterialen (PSC 120.03). § 2. Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst van 29 juni 2022 tot wijziging en coördinatie van de statuten van het "Waarborg- en Sociaal Fonds der textielnijverheid" (registratienummer 175230/CO/120).HOOFDSTUK II. - VoorwerpArt. 2. Deze collectieve arbeidsovereenkomst wijzigt en coördineert de statuten van het "Waarborg- en Sociaal Fonds der textielnijverheid". De gewijzigde en gecoördineerde statuten worden opgenomen in de bijlage aan deze collectieve arbeidsovereenkomst.HOOFDSTUK III. - Duur van de overeenkomstArt. 3.  § 1. Deze collectieve arbeidsovereenkomst is van onbepaalde duur en treedt in werking op 1 januari 2024, zonder dat zij evenwel afbreuk doet aan de nog geldende bepalingen omtrent de in deze statuten opgenomen aanvullende sociale voordelen, zoals bepaald in eerdere (Algemene nationale) collectieve arbeidsovereenkomsten gesloten in het Paritair Comité voor de textielnijverheid (PC 120). § 2. Deze collectieve arbeidsovereenkomst kan opgezegd worden door elk van de ondertekenende partijen mits inachtneming van een opzeggingstermijn van zes maanden per aangetekend schrijven aan de voorzitter van het paritair comité en aan elk van de andere ondertekenende partijen.HOOFDSTUK IV. - Algemeen verbindend verklaringArt. 4. De ondertekenende partijen vragen dat deze collectieve arbeidsovereenkomst algemeen verbindend zou verklaard worden per koninklijk besluit.Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025.De Minister van Werk,D. CLARINVALBijlage aan de collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de textielnijverheid, tot wijziging en coördinatie van de statuten van het "Waarborg- en Sociaal Fonds der Textielnijverheid"StatutenBenaming en maatschappelijke zetelArtikel 1. Deze statuten hebben betrekking op een fonds voor bestaanszekerheid, genaamd "Waarborg- en Sociaal Fonds der textielnijverheid", hierna het "fonds".Art. 2. De maatschappelijke zetel van het fonds is gevestigd te Gent op het volgende adres : Poortakkerstraat 100, 9051 Gent (Sint-Denijs-Westrem). De zetel van het fonds kan bij beslissing van het Paritair Comité voor de textielnijverheid worden overgebracht naar elke andere plaats in België.DoelArt. 3. Het fonds heeft tot doel :1°  het innen van de bijdragen, nodig voor zijn werking;2°  het innen van de bijdragen in naam en voor rekening van het "Fonds voor Bestaanszekerheid voor de textielnijverheid" en het "Fonds voor Bestaanszekerheid - Sectoraal Aanvullend Pensioen" (geheroriënteerde bijdrage);3°  het innen van de bijdragen in naam en voor rekening van Vacantex vzw met betrekking tot de supplementaire vakantiedagen (Vacantexdagen);4°  het toekennen van de sociale voordelen aan de arbeiders en de uitkering van deze voordelen te verzekeren;5°  de terugbetaling aan de werkgevers en/of het ten laste nemen van de aanvullende sociale voordelen voor de arbeiders, vastgelegd bij collectieve arbeidsovereenkomst gesloten in het Paritair Comité voor de textielnijverheid en algemeen verbindend verklaard bij koninklijk besluit;6°  het financieren van de opleidings- en tewerkstellingsbevorderende initiatieven voor de arbeiders, georganiseerd door de in het Paritair Comité voor de textielnijverheid vertegenwoordigde organisaties;7°  het financieren van sectorale initiatieven in het kader van werkbaar werk;8°  de financiering van de syndicale en socio-professionele vorming van de arbeiders uit de textielnijverheid, evenals van de informatieopdracht met betrekking tot de toepassing van de wettelijke en conventionele bepalingen voor de werkgevers van de textielnijverheid;9°  de financiering van de lasten met betrekking tot de verbetering van de industriële relaties en de promotie van werkgelegenheid in de textielnijverheid;10°  de bestuurs- en beheerslasten met betrekking tot de uitbetaling van de sociale voordelen aan de vertegenwoordigde organisaties vergoeden.ToepassingsgebiedArt. 4.  § 1. Deze statuten zijn van toepassing op alle textielondernemingen en op alle erin tewerkgestelde arbeiders die onder de bevoegdheid vallen van het Paritair Comité voor de textielnijverheid, met uitzondering van de ondernemingen en de erin tewerkgestelde arbeiders die onder de bevoegdheid vallen van het Paritair Subcomité voor de textielnijverheid uit het administratief arrondissement Verviers (PSC 120.01) en het Paritair Subcomité voor het vervaardigen en de handel in zakken in jute of in vervangingsmaterialen (PSC 120.03) (hierna "de arbeider(s)" enerzijds en "de textielonderneming(en)" of "de werkgever(s)" anderzijds). § 2. In afwijking op § 1 hierboven is de afdeling syndicale premie (artikel 5) enkel van toepassing op de arbeiders die lid zijn van één van de in het Paritair Comité voor de textielnijverheid vertegenwoordigde werknemersorganisaties. § 3. In afwijking op § 1 hierboven zijn de artikelen 5 tot en met 14 niet van toepassing op Celanese Production Belgium BV en Celanese BV en de erin tewerkgestelde arbeiders.Aanvullende sociale voordelenSectie I. - Syndicale premie - aanvullende sociale toelage - syndicale vorming - internationale solidariteitAfdeling I. - Syndicale premieArt. 5.  § 1. Aan de arbeiders die zijn gesyndikeerd wordt jaarlijks een syndicale premie toegekend ten belope van 145 EUR op voorwaarde dat zij tewerkgesteld zijn in een textielonderneming op de referentiedatum, jaarlijks vastgesteld door de raad van beheer. § 2. De arbeiders die zijn gesyndikeerd met inbegrip van de langdurig zieken en die ouder zijn dan of gelijk aan 50 jaar op het ogenblik van de uitdiensttreding en die zijn ontslagen om andere dan dringende redenen, hebben in totaal gedurende 6 jaren recht op de syndicale premie op voorwaarde dat zij gedurende die tijd ononderbroken volledig werkloos of arbeidsongeschikt blijven. § 3. De arbeiders die zijn gesyndikeerd met inbegrip van de langdurig zieken en die jonger zijn dan 50 jaar op het ogenblik van de uitdiensttreding en die zijn ontslagen om andere dan dringende redenen, hebben in totaal gedurende 3 jaren recht op de syndicale premie op voorwaarde dat zij gedurende die tijd ononderbroken volledig werkloos of arbeidsongeschikt blijven. § 4. De arbeiders die zijn gesyndikeerd en die toetreden tot het SWT hebben recht op de syndicale premie tot het bereiken van de pensioengerechtigde leeftijd en minstens gedurende 6 jaren indien de pensioengerechtigde leeftijd eerder wordt bereikt. § 5. De arbeiders die zijn gesyndikeerd en die met (vervroegd) wettelijk rustpensioen gaan, hebben in totaal gedurende 6 jaren recht op de syndicale premie. § 6. De arbeiders die zijn gesyndikeerd en worden tewerkgesteld met een arbeidsovereenkomst van bepaalde tijd worden uitgesloten uit de paragrafen 2 tot en met 5 van dit artikel. Zij hebben na het verstrijken van de overeengekomen duur van hun arbeidsovereenkomst of na voortijdig ontslag om andere redenen dan dringende redenen gedurende 1 jaar recht op de syndicale premie op voorwaarde dat zij gedurende die tijd ononderbroken volledig werkloos of arbeidsongeschikt blijven.Afdeling II. - De aanvullende sociale toelage (aanvulling bij de werkloosheidsvergoeding bij tijdelijke werkloosheid om economische redenen)Art. 6.  § 1. De arbeiders hebben in geval van tijdelijke werkloosheid om economische redenen zoals bedoeld in artikel 51 van de wet van 3 juli 1978 betreffende de arbeidsovereenkomsten, recht op een supplement of een aanvullende vergoeding die hetzij door de werkgever hetzij door het fonds ten laste wordt genomen. § 2. Met ingang van 1 januari 2024 wordt het supplement van 3,00 EUR per dag (vijfdagenweek) tijdelijke werkloosheid bedoeld in artikel 51, § 8 van de wet van 3 juli 1978 betreffende de arbeidsovereenkomsten, verhoogd met 0,60 EUR naar 3,60 EUR per dag (vijfdagenweek).Voor de arbeiders, tewerkgesteld in de (halve) overbruggingsploegen wordt het bedrag van 3,60 EUR per dag (vijfdagenweek) omgezet naar 8,00 EUR per dag in de overbruggingsploegen. § 3. De regeling zoals ze geldt vanaf 1 januari 2024 wordt samengevat in volgend schema :  </t>
         </is>
       </c>
     </row>
@@ -2745,29 +2742,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2025003452</t>
+          <t>2025003101</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>19 mei 2025</t>
+          <t>23 mei 2025</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1 september 2024. - Koninklijk besluit van waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 15 december 2023, gesloten in het Paritair Comité voor de landbouw, tot vaststelling van de sectorale minimumloonschalen voor de bedienden op basis van beroepservaring. - Erratum</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 21 januari 2025, gesloten in het Paritair Comité voor de voedingsnijverheid, betreffende de bijdrage van de werkgevers in de verplaatsingskosten van de arbeiders (1)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-19&amp;numac_search=2025003452&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003452=72&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-23&amp;numac_search=2025003101&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003101=72&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
           <t xml:space="preserve">
-In het Belgisch Staatsblad van 6 januari 2025, pagina 382 :Tabel van de loonschaal II, lijnen van 18 tot 26 jaar ervaring :lezen : "2 394,35"in plaats van : "2 294,35". 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de voedingsnijverheid;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 21 januari 2025, gesloten in het Paritair Comité voor de voedingsnijverheid, betreffende de bijdrage van de werkgevers in de verplaatsingskosten van de arbeiders.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 7 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de voedingsnijverheidCollectieve arbeidsovereenkomst van 21 januari 2025Bijdrage van de werkgevers in de verplaatsingskosten van de arbeiders (Overeenkomst geregistreerd op 10 februari 2025 onder het nummer 191986/CO/118)HOOFDSTUK I. - ToepassingsgebiedArtikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de arbeiders van de voedingsindustrie. § 2. Met "arbeiders" worden alle arbeiders bedoeld, zonder onderscheid naar gender.HOOFDSTUK II. - Bijdrage van de werkgeverArt. 2. De bijdrage van de werkgever in de verplaatsingskosten van de arbeiders wordt als volgt vastgesteld :a) Vervoer per spoorwegen (Nationale Maatschappij der Belgische Spoorwegen) :De tussenkomst van de werkgever in de prijs van het gebruikte vervoerbewijs wordt berekend op basis van de treinkaarttarieven van de NMBS.De bijdrage bedraagt gemiddeld 80 pct. van het treinkaarttarief.In bijlage 1 worden de bedragen vermeld die van toepassing zijn vanaf 1 februari 2025.Dit barema zal jaarlijks automatisch en proportioneel aangepast worden aan de verhoging van de treintarieven.b) Gemeenschappelijk openbaar vervoer met uitzondering van het treinvervoer :Voor wat betreft het gemeenschappelijk openbaar vervoer, met uitzondering van het treinvervoer, zal de bijdrage van de werkgever in de prijs van de abonnementen vastgesteld worden volgens de hierna vastgestelde modaliteiten :- wanneer de prijs van het vervoer in verhouding tot de afstand staat, wordt de tussenkomst van de werkgever in de prijs van het gebruikte vervoerbewijs berekend op basis van de treinkaarttarieven van de NMBS. De bijdrage bedraagt gemiddeld 80 pct. van het treinkaarttarief. Deze tabel is in bijlage 1 van deze collectieve arbeidsovereenkomst opgenomen;- wanneer de prijs een eenheidsprijs is, ongeacht de afstand, wordt de bijdrage van de werkgever forfaitair vastgesteld en bedraagt zij 80 pct. van de effectief door de werknemer betaalde prijs, zonder evenwel het bedrag van de werkgeverstussenkomst voor een afstand van 7 kilometer uit de tabel van bijlage 1 te overschrijden.Deze barema's zullen jaarlijks automatisch en proportioneel aangepast worden aan de verhoging van de treintarieven.c) Verplaatsingen met de fiets :Werknemers die zich volledig of gedeeltelijk met de fiets verplaatsen, ontvangen vanaf 1 februari 2025 een fietsvergoeding van 0,27 EUR per afgelegde kilometer (heen en terug, van en naar het werk), voor de volledige afstand.Onder het begrip "fiets" verstaan we drie types :- Het rijwiel :Elk voertuig met 2 of meer wielen :- dat via pedalen of handgrepen met spierkracht wordt aangedreven;- dat uitgerust is met een elektrische hulpmotor tot 250 W en geen ondersteuning meer biedt vanaf 25 km per uur (of eerder, indien de bestuurder ophoudt met trappen);- Het gemotoriseerd rijwiel :Elk twee-, drie- of vierwielig voertuig met pedalen :- uitgerust met een elektrische hulpaandrijving met als hoofddoel trapondersteuning waarvan de aandrijfkracht wordt onderbroken bij een voertuigsnelheid van maximum 25 km per uur, met uitsluiting van de hierboven vermelde rijwielen.Het nominaal continu maximumvermogen van de elektrische motor bedraagt ten hoogste 1 kW;- De speed pedelec :Elk tweewielig voertuig met pedalen (met uitsluiting van de gemotoriseerde rijwielen) :- met een elektrische hulpaandrijving met als hoofddoel trapondersteuning waarvan de aandrijfkracht wordt onderbroken bij een voertuigsnelheid van maximum 45 km per uur.Het nominaal continu maximumvermogen van de elektrische motor bedraagt ten hoogste 4 kW.Paritair commentaarDe werkgever moet, met het oog op de fiscale en parafiscale vrijstelling van deze vergoeding, de passende maatregelen nemen opdat hij met zekerheid zowel het aantal daadwerkelijke verplaatsingen per fiets als de van belasting en socialezekerheidsbijdragen vrijgestelde vergoeding zou kunnen bepalen.De vergoeding voorzien in dit artikel 2, c) is een fietsvergoeding en geen bromfietsvergoeding. Zij is ook niet van toepassing op de werknemers die zich te voet naar het werk begeven.d) Andere verplaatsingsmiddelen :De tussenkomst van de werkgever wordt berekend op basis van het barema opgenomen in bijlage 2 van deze collectieve arbeidsovereenkomst, geldend vanaf 1 februari 2025, op voorwaarde dat de afstand volgens de kortste weg tussen het vertrekpunt en het aankomstpunt minstens 1 kilometer bedraagt.Dit barema zal jaarlijks automatisch en proportioneel aangepast worden aan de verhoging van de treintarieven. Deze aanpassing brengt het bedrag van de tussenkomst van de werkgever elk jaar op gemiddeld 80 pct. van de prijs van de treinkaart voor eenzelfde afstand.HOOFDSTUK III. - Tijdstip van terugbetalingArt. 3. De terugbetaling van de vervoerkosten waarvan sprake in deze collectieve arbeidsovereenkomst moet eenmaal per maand geschieden.Art. 4. Onverminderd de bepalingen voorzien in deze collectieve arbeidsovereenkomst, blijven de gunstigere toestanden inzake vervoer en terugbetaling van de vervoerkosten op het vlak van de onderneming behouden.Art. 5. De praktische modaliteiten tot uitvoering van deze collectieve arbeidsovereenkomst worden vastgelegd op het vlak van de onderneming.HOOFDSTUK IV. - GeldigheidsduurArt. 6.  § 1. Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst van 23 januari 2024 (registratienummer 185870/CO/118), gesloten in het Paritair Comité 118 voor de voedingsnijverheid, betreffende de bijdrage van de werkgevers in de verplaatsingskosten van de arbeiders. § 2. Zij treedt in werking op 1 februari 2025 en is gesloten voor onbepaalde duur. Zij kan opgezegd worden mits een opzeggingstermijn van drie maanden, bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Comité voor de voedingsnijverheid en aan de erin vertegenwoordigde organisaties.Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk,D. CLARINVALBijlage 1 aan de collectieve arbeidsovereenkomst van 21 januari 2025, gesloten in het Paritair Comité voor de voedingsnijverheid, betreffende de bijdrage van de werkgevers in de verplaatsingskosten van de arbeidersGeldig vanaf 1 februari 2025 :Bedrag van de patronale tussenkomst  </t>
         </is>
       </c>
     </row>
@@ -2777,7 +2773,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024011608</t>
+          <t>2025201194</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2787,18 +2783,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1 september 2024. - Koninklijk besluit tot wijziging van het Koninklijk Besluit van 21 november 2022 betreffende de toekenning van een subsidie aan het OCMW van Eigenbrakel voor de uitvoering van een project gericht op de digitale inclusie van kwetsbare groepen in het kader van het project "e-inclusion for Belgium" van het Europees herstel- en veerkrachtplan</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 22 januari 2025, gesloten in het Paritair Comité voor de bedienden van het kleding- en confectiebedrijf, betreffende het statuut van de syndicale afvaardiging (1)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-23&amp;numac_search=2024011608&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2024011608=73&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-23&amp;numac_search=2025201194&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201194=73&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 22 mei 2003 betreffende de organisatie van de begroting en van de comptabiliteit van de federale Staat, artikelen 121 tot 124 ;Gelet op de programmawet van 20 december 2020, artikel 91;Gelet op de wet van 26 december 2022 betreffende de Algemene uitgavenbegroting voor het begrotingsjaar 2023, artikel 2.06.4 ;Gelet op de wet van 22 december 2023 betreffende de Algemene uitgavenbegroting voor het begrotingsjaar 2024, artikel 2.06.4 ;Gelet op het koninklijk besluit van 20 mei 2022 betreffende de administratieve, begrotings- en beheerscontrole, artikel 20 ;Gelet op het Nationaal herstel- en veerkrachtplan zoals goedgekeurd door de Ministerraad op 30 april 2021.Gelet op de verordening (EU) 2021/241 van het Europees parlement en van de Raad van de Europese unie van 12 februari 2021 tot instelling van de herstel- en veerkrachtfaciliteit. Gelet op de verordening (EU) 2023/435 van het Europees parlement en de Raad van 27 februari 2023 tot wijziging van Verordening (EU) 2021/241 wat betreft REPowerEU-hoofdstukken in herstel- en veerkrachtplannen en tot wijziging van Verordeningen (EU) nr. 1303/2013, (EU) 2021/1060 en (EU) 2021/1755 en Richtlijn 2003/87/EGGelet op de uitvoeringsbeslissing van de Raad van de Europese unie van 6 juli 2021 betreffende de goedkeuring van de evaluatie van het Belgische herstel- en veerkrachtplan;Gelet op de uitvoeringsbeslissing van de Europese Raad van 13 juli 2021 (en zijn bijlage) met betrekking tot de goedkeuring van de evaluatie van het Belgische plan voor Herstel en Veerkracht;Gelet op het uitvoeringsbesluit van de Raad van de Unie van 8 december 2023 (en bijlage) dat het uitvoeringsbesluit van 13 juli 2021 wijzigt betreffende de goedkeuring van de beoordeling van het plan voor herstel en veerkracht voor België.Gelet op het advies van de Inspectie van Financiën, gegeven op 10 oktober 2022 ;Gelet op het advies van de Inspectie van Financiën, gegeven op 18 oktober 2022 ;Gelet op het advies van de Inspectie van Financiën, gegeven op 7 november 2022 ;Gelet op het advies van de Inspectie van Financiën, gegeven op 25 juli 2024;Op de voordracht van de Minister Karine Lalieux ;Hebben Wij besloten en besluiten Wij :Artikel 1. Artikel 1 van het Koninklijk Besluit van 21 november 2022 betreffende de toekenning van een subsidie aan het OCMW van Eigenbrakel voor de uitvoering van een project gericht op de digitale inclusie van kwetsbare groepen in het kader van het project "e-inclusion for Belgium" van het Europees herstel- en veerkrachtplan, wordt als volgt gewijzigd :" § 1. Er wordt aan het OCMW van Eigenbrakel, Avenue du 21 Juillet, 1 - 1420 Braine-l'Alleud, KBO-nummer 0212.362.197, een subsidie toegekend van maximaal zestigduizend honderdvierentachtig komma zeventig euro (60.184,70 EUR) ter dekking van de kosten inclusief btw die gepaard gaan met de verwezenlijking van het project "Cyber(wo)man" in het kader van het "e-inclusion for Belgium" project (referentie I408034vBE-C[42]-I[I-4.08]) van het Europees herstel- en veerkrachtplan.Het subsidiebedrag van zestigduizend honderdvierentachtig komma zeventig euro (60.184,70 EUR) dat werd toegekend, kan niet worden overschreden.Het subsidiebedrag van zestigduizend honderdvierentachtig komma zeventig euro (60.184,70 EUR) is btw inclusief. § 2. Alleen bedragen exclusief btw kunnen ten laste van het herstel- en veerkrachtplan worden gebracht. De btw wordt gedragen door de Belgische staat. § 3. Daar er bij toekenning van de subsidie geen rekening werd gehouden met het feit dat alleen bedragen exclusief btw ten laste van het herstel- en veerkrachtplan kunnen worden gebracht, moet een technische correctie worden doorgevoerd op het subsidiebedrag zonder de totaliteit van de subsidie te overschrijden. Hierdoor zal het vastgelegde bedrag in 2022 worden verminderd, evenredig met het bedrag van de btw dat zal worden aangerekend op de algemene uitgavenbegroting van het begrotingsjaar 2024. § 4. Het subsidiebedrag exclusief btw werd aangerekend op de basisallocatie 06.41.14.43.52 van de Algemene uitgavenbegroting van het begrotingsjaar 2022.Het subsidiebedrag van de btw zal worden aangerekend op de basisallocatie 06.41.14.43.52 van de Algemene uitgavenbegroting van het begrotingsjaar 2024 op basis van de door de subsidieontvanger ingediende en door Digilab gecontroleerde terugbetalingsaanvraag en dit zonder het maximale subsidiebedrag te overschrijden. »Art. 2. Artikel 11 van het Koninklijk Besluit van 21 november 2022 betreffende de toekenning van een subsidie aan het OCMW van Eigenbrakel voor de uitvoering van een project gericht op de digitale inclusie van kwetsbare groepen in het kader van het project "e-inclusion for Belgium" van het Europees herstel- en veerkrachtplan, wordt als volgt gewijzigd :" § 1. Op het einde van het eerste en enige jaar van het project "Cyber(wo)man" vindt een evaluatie plaats. § 2. Digilab zal op basis van de controle van het inhoudelijk en financieel verslag, het plaatsbezoek en de controle van alle bewijsstukken een afrekening maken van de gemaakte kosten om het finale subsidiebedrag te bepalen, verdeeld in een bedrag exclusief btw en een bedrag voor de btw. § 3. De som van het bedrag exclusief btw en het bedrag voor de btw mag het totaal bedrag van de toegekende subsidie niet overschrijden. § 4. Het finale subsidiebedrag wordt toegevoegd als bijlage aan dit Besluit. "Art. 3. De Minister Karine Lalieux is belast met de uitvoering van dit besluit.Gegeven te Brussel, 1 september 2024.FILIPVan Koningswege :De Minister van Maatschappelijke Integratie en armoedebestrijding,K. LALIEUX  </t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de bedienden van het kleding- en confectiebedrijf; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 22 januari 2025, gesloten in het Paritair Comité voor de bedienden van het kleding- en confectiebedrijf, betreffende het statuut van de syndicale afvaardiging. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de bedienden van het kleding- en confectiebedrijf Collectieve arbeidsovereenkomst van 22 januari 2025 Statuut van de syndicale afvaardiging (Overeenkomst geregistreerd op 10 februari 2025 onder het nummer 192000/CO/215) HOOFDSTUK I. - Algemene bepalingen en toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is gesloten volgens de algemene principes van het statuut van de syndicale afvaardiging, die het voorwerp uitmaken van de collectieve arbeidsovereenkomst nr. 5, gesloten op 24 mei 1971 in de Nationale Arbeidsraad betreffende het statuut van de syndicale afvaardigingen van het personeel der ondernemingen, gewijzigd en aangevuld door de collectieve arbeidsovereenkomsten nr. 5bis van 30 juni 1971, nr. 5ter van 21 december 1978 en nr. 5quater van 5 oktober 2011.Ze verbindt de representatieve organisaties van bedienden en werkgevers vertegenwoordigd in het Paritair Comité voor de bedienden van het kleding- en confectiebedrijf. Rekening houdend met de bekommernis het aantal beschermde personeelsleden binnen redelijke perken te houden, duiden de syndicale organisaties hun afgevaardigden bij voorkeur en zoveel mogelijk aan onder de personeelsleden die reeds een wettelijke bescherming tegen afdanking genieten in het kader van de wet van 20 september 1948 houdende organisatie van het bedrijfsleven of van de wet van 4 augustus 1996 betreffende het welzijn van de werknemers bij de uitvoering van hun werk. Art. 2. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers die ressorteren onder de bevoegdheid van het Paritair Comité voor de bedienden van het kleding- en confectiebedrijf en op de bedienden die zij tewerkstellen. HOOFDSTUK II. - Ondernemingen waar een syndicale delegatie kan opgericht worden Art. 3. In elke onderneming van het kleding- en confectiebedrijf, waar gewoonlijk gemiddeld ten minste 25 bedienden worden tewerkgesteld en waarvan de functies onder de classificatie vallen voorzien door de collectieve arbeidsovereenkomst van 21 mei 2008 betreffende de functieclassificatie, moet een syndicale afvaardiging worden opgericht. Om na te gaan in hoeverre vijfentwintig bedienden tewerkgesteld zijn, wordt de berekening toegepast, voorzien door de wettelijke en reglementaire bepalingen inzake de comités voor preventie en bescherming op het werk. Deze syndicale afvaardiging wordt door de werkgever aanzien als de vertegenwoordiging van het bij een werknemersorganisatie aangesloten bediendepersoneel, behorende tot de classificatie voorzien door de in artikel 3, eerste lid, vermelde collectieve arbeidsovereenkomst. HOOFDSTUK III. - Samenstelling van de syndicale afvaardiging Art. 4.  § 1. De syndicale afvaardiging bestaat uit volgend aantal leden, in verhouding tot het aantal bedienden die bedoeld zijn bij artikel 3, eerste lid : - 2, wanneer 25 tot 49 bedienden in de onderneming tewerkgesteld zijn; - 3, wanneer 50 tot 74 bedienden in de onderneming tewerkgesteld zijn; - 4, wanneer 75 en meer bedienden in de onderneming tewerkgesteld zijn. In de bedrijven die tussen 25 en 49 bedienden tellen, bedraagt het aantal afgevaardigden drie, indien een derde werknemersorganisatie een afgevaardigde aanduidt.  § 2. De in het Paritair Comité voor de bedienden van het kleding- en confectiebedrijf vertegenwoordigde werknemersorganisaties stellen zich onderling akkoord - eventueel doen zij daartoe een beroep op het verzoeningsinitiatief van de voorzitter van dat paritair comité - tot toekenning aan elke werknemersorganisatie, van het aantal leden van de syndicale afvaardiging, in verhouding tot het respectief aantal mandaten behaald bij de laatste sociale verkiezingen voor de comités voor preventie en bescherming op het werk, of tot hun respectievelijk ledenaantal in de ondernemingen. Geen syndicaal afgevaardigde kan in de onderneming worden aangeduid, zolang op grond van de in § 2 van dit artikel bedoelde procedure niet is uitgemaakt hoeveel afgevaardigden elke betrokken werknemersorganisatie mag aanduiden.  § 3. Binnen de drie maanden die volgen op de sociale verkiezingen wordt nagegaan of het aantal leden van de syndicale afvaardiging nog in verhouding staat tot het aantal bedienden dat in de onderneming is tewerkgesteld. Zo de verhouding niet meer overeenstemt met de getallen die voorkomen in § 1 van dit artikel, wordt overgegaan tot een vermeerdering of een vermindering van het aantal leden van de syndicale afvaardiging, volgens de modaliteiten voorzien in § 2 van dit artikel.  § 4. Voor de vaststelling van het aantal in de onderneming tewerkgestelde bedienden, wordt rekening gehouden met het gemiddeld aantal bedienden tewerkgesteld gedurende de vier kwartalen die voorafgaan aan het kwartaal tijdens hetwelk de oprichting van een syndicale afvaardiging werd ingediend.HOOFDSTUK IV. - Te vervullen voorwaarden om als syndicale afgevaardigde te worden aangeduid Art. 5. Om syndicale afgevaardigde te kunnen zijn, moet aan volgende voorwaarden worden voldaan op de datum van verzending van het aangetekend schrijven bedoeld in § 2 van artikel 6 : a) ten minste 18 jaar oud zijn; b) de burgerlijke rechten genieten; c) sedert ten minste één jaar voltijds in de onderneming tewerkgesteld zijn of eventueel sedert de oprichting van de onderneming; d) behoren tot de categorie bedienden die onder de classificatie ressorteren voorzien door de in artikel 3, eerste lid, vermelde collectieve arbeidsovereenkomst; e) niet door zijn werkgever rechtsgeldig ontslagen zijn. HOOFDSTUK V. - Aanduiding van de syndicale afgevaardigde Art. 6.  § 1. De syndicale afgevaardigden worden aangeduid door de werknemersorganisatie waarbij ze aangesloten zijn. Deze duidt zijn syndicale afgevaardigden zo aan, dat in de mate van het mogelijke, rekening wordt gehouden met het ploegwerk in de onderneming en met de verschillende departementen die in de onderneming bestaan.  § 2. De namen van de syndicale afgevaardigden worden door de werknemersorganisatie bij aangetekend schrijven aan de werkgever overgemaakt. In bovenvermeld schrijven vermeldt de betrokken werknemersorganisatie het aantal leden van de syndicale afvaardiging dat zij mag aanduiden, met verwijzing naar het akkoord bedoeld in artikel 4, § 2.  § 3. Elk geschil betreffende het al dan niet vervullen van de voorwaarden gesteld in artikel 5 van deze collectieve arbeidsovereenkomst, mag worden voorgelegd aan het paritair comité. HOOFDSTUK VI. - Duur en einde van het mandaat van de syndicale afgevaardigden Art. 7.  § 1. De syndicale afgevaardigden worden aangeduid voor een termijn van vier jaar. Hun mandaat loopt stilzwijgend verder, zolang het geen einde heeft genomen ingevolge één van de in § 2 van dit artikel vermelde bepalingen.  § 2. Het mandaat van de syndicale afgevaardigde neemt een einde : 1. door de beslissing van de werknemersorganisatie die de afgevaardigde heeft aangeduid; 2. wanneer de afgevaardigde afstand doet van zijn mandaat; 3. bij uitdiensttreding van de afgevaardigde; 4. wanneer, in toepassing van artikel 4, § 3 van deze collectieve arbeidsovereenkomst, mandaten moeten worden afgeschaft; 5. wanneer de afgevaardigde één van de voorwaarden, voorzien onder artikel 5, niet meer vervult. HOOFDSTUK VII. - Vervanging van de syndicale afgevaardigde Art. 8. Wanneer een plaats van syndicale afgevaardigde in de onderneming vacant komt door één van de oorzaken voorzien in artikel 7, § 2, wordt een nieuwe syndicale afgevaardigde aangeduid door de werknemersorganisatie die de te vervangen syndicale afgevaardigde had aangeduid. De betrokken werknemersorganisatie stelt, bij aangetekend schrijven, de werkgever in kennis van deze nieuwe aanduiding. HOOFDSTUK VIII. - Procedure inzake het behandelen van klachten in de onderneming Art. 9.  § 1. Elke individuele klacht wordt langs de gewone hiërarchische weg door de betrokken bediende ingediend. Deze kan zich, op zijn verzoek, laten bijstaan door zijn syndicale afgevaardigde. Elke collectieve klacht wordt door de syndicale afvaardiging langs de gewone hiërarchische weg ingediend.  § 2. Indien de bediende geen beroep heeft gedaan op zijn syndicale afgevaardigde bij het indienen van de klacht en er binnen een redelijke termijn geen voldoende gevolg wordt gegeven aan de klacht, kan de bediende alsnog een beroep doen op de syndicale afvaardiging.  § 3. Bij gebrek aan overeenstemming binnen een redelijke termijn tussen werkgever en syndicale afvaardiging, wordt een beroep gedaan op de secretarissen van de werknemersorganisaties en de werkgeversorganisatie om de besprekingen verder te zetten. § 4. Indien binnen een redelijke termijn geen regeling kan getroffen worden in uitvoering van de in § 2 en § 3 van dit artikel voorziene procedure, kunnen de werknemersorganisaties of de werkgeversorganisatie de zaak aan het verzoeningscomité van het paritair comité voorleggen. HOOFDSTUK IX. - Procedure inzake de werking van de syndicale delegatie Art. 10.  § 1. De syndicale afvaardiging wordt door de werkgever of door zijn vertegenwoordigers ontvangen zo dikwijls als zij er om verzoekt, mits tijdige verwittiging en onder opgave van gegronde redenen.  § 2. De syndicale afvaardiging wordt door de werkgever ontboden zo dikwijls hij erom verzoekt, mits tijdige verwittiging en onder opgave van gegronde redenen. De syndicale afvaardiging komt met de werkgever overeen wanneer en hoe zij wordt ingelicht omtrent de bedoeling van de werkgever wijzigingen aan de contractuele of gebruikelijke loons- en arbeidsvoorwaarden aan te brengen.  § 3. Indien de besprekingen tussen de werkgever en de syndicale afvaardiging gehouden worden buiten de normale arbeidsuren, worden deze prestaties als normale arbeidsprestaties vergoed.  § 4. Zonder afbreuk te doen aan de goede werkorganisatie, beschikt de syndicale afvaardiging, tijdens de werkuren, over de nodige tijd om zonder loonverlies haar taak te vervullen. Naargelang de aard van de opdracht en de het belang van de tussenkomst, komen de werkgever en de syndicale afvaardiging overeen welke tijd nodig is om haar taak naar behoren uit te voeren, hetzij collectief door de afvaardiging, hetzij individueel door één of meerdere leden van de afvaardiging. De vraag wordt tijdig aan de werkgever gericht, zodat deze de nodige maatregelen kan treffen om de goede gang van de onderneming te verzekeren. Bovendien, wanneer de syndicale afvaardiging overleg wenst te plegen, wordt, op haar aanvraag, door de werkgever een geschikt lokaal ter beschikking gesteld waar dit overleg vrij en ongestoord kan plaatshebben. Bij betwisting tussen de werkgever en de betrokken syndicale afvaardiging over het toestaan van de nodige vrije tijd of het ogenblik waarop die tijd wordt genomen, wordt er een beroep gedaan op de bemiddeling van de secretarissen van de werknemersorganisaties en de afgevaardigde van de werkgeversorganisatie. Indien geen vergelijk kan gevonden worden, treft het verzoeningsbureau een beslissing, waarbij de waarborg van een minimum aan vrije tijd wordt verleend, rekening houdend met de specifieke omstandigheden van het voorgelegde geval.  § 5. In de ondernemingen met twee of meer vestigingen in België, bestaat de mogelijkheid om, wanneer de omstandigheden het vereisen en zonder loonverlies, een gemeenschappelijke bijeenkomst te houden van de syndicale afvaardiging van de betrokken vestigingen, met het oog op de bespreking van problemen van gezamenlijk belang. Daartoe richten de syndicale afvaardiging of de werknemersorganisaties een gemotiveerde aanvraag aan de werkgever. De werkgever maakt de gemeenschappelijke bijeenkomst mogelijk binnen de kortst mogelijke termijn en ten laatste binnen de maand na het indienen van de aanvraag. HOOFDSTUK X. - Actiedomein van de syndicale afvaardiging Art. 11. Het optreden van de syndicale afvaardiging heeft betrekking op volgende punten : 1. de arbeidsverhoudingen; 2. de naleving van de algemene beginselen, bepaald in de artikelen 2 tot 5 van de collectieve arbeidsovereenkomst nr. 5 gesloten op 24 mei 1971 in de Nationale Arbeidsraad betreffende het statuut van de syndicale afvaardiging en van de grondbeginselen in dit statuut vastgelegd; 3. de eerbiediging van het arbeidsreglement en de arbeidsvoorwaarden; 4. de toepassing van de sociale wetgeving, van de collectieve arbeidsovereenkomsten en van de individuele arbeidsovereenkomsten. Art. 12. Bij ontstentenis van de ondernemingsraad, oefent de syndicale afvaardiging de taken, rechten en opdrachten uit die aan deze raad worden toegekend door de artikelen 4, 5, 6, 7 en 11 van de collectieve arbeidsovereenkomst nr. 9, gesloten op 9 maart 1972 in de Nationale Arbeidsraad.Art. 13. De syndicale afvaardiging kan mondeling of schriftelijk overgaan tot alle inlichtingen die nuttig zijn voor het personeel, zonder dat dit de organisatie van het werk mag storen. Deze inlichtingen hebben betrekking op de collectieve arbeidsverhoudingen en moeten de goedkeuring wegdragen van de werknemersorganisaties. Wanneer de syndicale afvaardiging gebruik maakt van dit recht, licht zij vooraf de werkgever ervan in. Bovendien, telkens als daartoe een grondige reden bestaat en met instemming van de werkgever of zijn vertegenwoordiger, kan de syndicale afvaardiging een voorlichtingsvergadering houden voor het personeel of een gedeelte ervan waarvoor de informatie bestemd is, in een daartoe bestemd lokaal en eventueel in het bijzijn van de secretaris van de werknemersorganisatie. De werkgever kan hiertoe niet willekeurig zijn instemming weigeren. Wanneer het mogelijk is, wordt deze vergadering - gedeeltelijk of geheel - tijdens de rusttijden gehouden. HOOFDSTUK XI. - Arbeidsvoorwaarden van de syndicale afvaardiging Art. 14.  § 1. De werkgever behandelt de leden van de syndicale afvaardiging in elk opzicht en in alle omstandigheden op gelijke voet als de andere bedienden die tot dezelfde beroepscategorie in de onderneming behoren.  § 2. De werknemersorganisaties zullen tevens geen eisen stellen aan de ondernemingen die ertoe zouden leiden leden van de syndicale afvaardiging te bevoordeligen ten overstaan van de andere bedienden die tot dezelfde beroepscategorie behoren in de onderneming. HOOFDSTUK XII. - Bescherming van de syndicale afgevaardigden Art. 15.  § 1. Vanaf het ogenblik waarop, overeenkomstig artikel 6 van deze collectieve arbeidsovereenkomst, de werkgever van de aanduiding van de syndicale afgevaardigden op de hoogte wordt gebracht en tot het verstrijken van de periode van zes maanden volgend op het einde van het mandaat, mogen de leden van de syndicale afvaardiging niet worden afgedankt om redenen die eigen zijn aan de uitoefening van hun mandaat.  § 2. De werkgever die van plan is een syndicale afgevaardigde te ontslaan, verwittigt voorafgaandelijk de syndicale afvaardiging, evenals de werknemersorganisatie die de kandidatuur van deze afgevaardigde heeft voorgedragen. Deze verwittiging gebeurt bij aangetekend schrijven dat uitwerking heeft op de derde dag volgend op de datum van de verzending. De betrokken werknemersorganisatie beschikt over een termijn van zeven dagen om mee te delen dat zij de geldigheid van de voorgenomen afdanking weigert te aanvaarden. Deze mededeling gebeurt bij aangetekend schrijven. De periode van zeven dagen neemt een aanvang op de dag waarop de brief die de werkgever verstuurde, uitwerking heeft. Het uitblijven van reactie van de werknemersorganisatie moet beschouwd worden als een aanvaarding van de geldigheid van de voorgenomen afdanking. Indien de werknemersorganisatie weigert de geldigheid van de voorgenomen afdanking te aanvaarden, heeft de meest gerede partij de mogelijkheid het geval aan het oordeel van het verzoeningsbureau van het paritair comité voor te leggen. De maatregel tot afdanking mag niet worden uitgevoerd gedurende de duur van deze procedure. Indien het verzoeningsbureau tot geen eenparige beslissing is kunnen komen binnen de dertig dagen van de aanvraag tot tussenkomst, kan het geschil betreffende de geldigheid van de redenen die door de werkgever worden ingeroepen om de afdanking te verantwoorden, aan de arbeidsrechtbank worden voorgelegd.  § 3. De in de voorgaande § 2 bedoelde verplichting bestaat niet bij ontslag om dringende redenen. Art. 16. Bij ontslag van een syndicale afgevaardigde wegens dringende redenen, moet de syndicale afvaardiging daarvan onmiddellijk en uiterlijk binnen de drie dagen op de hoogte worden gebracht. Bovendien zendt de werkgever, binnen de drie dagen na het ontslag, aan de werknemersorganisatie die deze syndicale afgevaardigde heeft aangeduid, aangetekend een afschrift van het schrijven bedoeld bij het laatste lid van artikel 35 van de wet van 3 juli 1978 betreffende de arbeidsovereenkomsten. Art. 17. Een forfaitaire vergoeding is door de werkgever verschuldigd in volgende gevallen : 1. indien hij een syndicale afgevaardigde afdankt, zonder de in voornoemd artikel 15 bepaalde procedure na te leven;2. indien, op het einde van deze procedure, de geldigheid van de redenen van afdanking, rekening houdend met de bepaling van artikel 15, niet wordt erkend door het verzoeningsbureau of de arbeidsrechtbank; 3. indien de werkgever een syndicale afgevaardigde heeft ontslagen wegens dringende reden en de arbeidsrechtbank het ontslag ongegrond heeft verklaard; 4. indien de arbeidsovereenkomst wordt beëindigd wegens zware fout van de werkgever, die voor de afgevaardigde een reden is tot onmiddellijke beëindiging van de overeenkomst. De forfaitaire vergoeding is gelijk aan de brutobezoldiging van één jaar, onverminderd de toepassing van de artikelen 39 en 40 van de wet van 3 juli 1978 betreffende de arbeidsovereenkomsten. Deze vergoeding is niet verschuldigd wanneer de syndicale afgevaardigde de vergoeding ontvangt, bepaald in hoofdstuk IV van de wet van 19 maart 1991 houdende bijzondere ontslagregeling voor de personeelsafgevaardigden in de ondernemingsraden en in de comités voor veiligheid, gezondheid en verfraaiing van de werkplaatsen alsmede voor de kandidaat-personeelsafgevaardigden. HOOFDSTUK XIII. - Regeling der geschillen Art. 18. Elk geschil betreffende de toepassing van deze collectieve arbeidsovereenkomst wordt voorgelegd aan het verzoeningsbureau van het Paritair Comité voor de bedienden van het kleding- en confectiebedrijf. HOOFDSTUK XIV. - Geldigheid en opzegging van de overeenkomst Art. 19. Deze collectieve arbeidsovereenkomst treedt in werking op 22 januari 2025 en wordt gesloten voor onbepaalde duur. Zij kan door één der ondertekenende partijen worden opgezegd, met een opzeggingstermijn van drie maanden, per aangetekende brief aan de voorzitter van het Paritair Comité voor de bedienden van het kleding- en confectiebedrijf en aan de in dit paritair comité vertegenwoordigde organisaties. Tijdens de geldigheid zullen, noch op het vlak van de bedrijfstak, noch op het vlak van de ondernemingen, eisen gesteld worden tot wijziging of aanvulling van deze collectieve arbeidsovereenkomst. HOOFDSTUK XV. - Slotbepalingen Art. 20. Deze collectieve arbeidsovereenkomst vervangt vanaf 22 januari 2025 de collectieve arbeidsovereenkomst van 2 juni 1975 gesloten in het Paritair Comité voor de bedienden van het kleding- en confectiebedrijf betreffende het statuut van de syndicale afvaardiging, registratienummer 3379/CO/215, algemeen verbindend verklaard bij koninklijk besluit van 19 september 1975. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
+</t>
         </is>
       </c>
     </row>
@@ -2808,28 +2805,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2025003266</t>
+          <t>2025201192</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>15 mei 2025</t>
+          <t>23 mei 2025</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>12 augustus 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 14 januari 2013 tot bepaling van de algemene uitvoeringsregels van de overheidsopdrachten, wat de betalingsregels betreft. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 4 februari 2025, gesloten in het Paritair Comité voor de schoonmaak, tot wijziging van de collectieve arbeidsovereenkomst van 11 juni 2009 betreffende de classificatie (geregistreerd op 5 oktober 2009 onder het nummer 94699/CO/121 en algemeen verbindend verklaard bij koninklijk besluit van 19 april 2010, Belgisch Staatsblad van 6 juli 2010) (1)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-15&amp;numac_search=2025003266&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003266=74&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-23&amp;numac_search=2025201192&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201192=74&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 12 augustus 2024 tot wijziging van het koninklijk besluit van 14 januari 2013 tot bepaling van de algemene uitvoeringsregels van de overheidsopdrachten, wat de betalingsregels betreft (Belgisch Staatsblad van 16 september 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST KANZLEI DES PREMIERMINISTERS12. AUGUST 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 14. Januar 2013 zur Festlegung der allgemeinen Regeln für die Ausführung öffentlicher Aufträge hinsichtlich der ZahlungsregelnPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des Gesetzes vom 13. August 2011 über öffentliche Aufträge und bestimmte Bau-, Liefer- und Dienstleistungsaufträge in den Bereichen Verteidigung und Sicherheit, des Artikels 35 Absatz 1;Aufgrund des Gesetzes vom 17. Juni 2016 über die öffentlichen Aufträge, der Artikel 86 Absatz 1 und 156 § 1 Absatz 1;Aufgrund der Stellungnahme der Kommission für die Öffentlichen Aufträge vom 26. Mai 2023;Aufgrund der Auswirkungsanalyse beim Erlass von Vorschriften, die am 4. August 2023 gemäß den Artikeln 6 § 1 und 7 § 1 des Gesetzes vom 15. Dezember 2013 zur Festlegung verschiedener Bestimmungen in Sachen administrative Vereinfachung durchgeführt worden ist;Aufgrund der Stellungnahme des Finanzinspektors vom 3. Oktober 2023;Aufgrund des Einverständnisses der Staatssekretärin für Haushalt vom 29. April 2024;Aufgrund des Gutachtens Nr. 76.540/1 des Staatsrates vom 17. Juni 2024, abgegeben in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Auf Vorschlag des Premierministers und aufgrund der Stellungnahme der Minister, die im Rat darüber beraten haben,Haben Wir beschloßen und erlassen Wir:Artikel 1 - Vorliegender Erlass dient der Teilumsetzung der Richtlinie 2011/7/EU des Europäischen Parlaments und des Rates vom 16. Februar 2011 zur Bekämpfung von Zahlungsverzug im Geschäftsverkehr.Art. 2 - In Artikel 2 des Königlichen Erlasses vom 14. Januar 2013 zur Festlegung der allgemeinen Regeln für die Ausführung öffentlicher Aufträge, abgeändert durch die Königlichen Erlasse vom 7. Februar 2014 und 22. Juni 2017, wird eine Nr. 27 mit folgendem Wortlaut eingefügt:"27. Bearbeitungsfrist: die Frist, in der die Vergabestellen die Überprüfungs- und Zahlungsvorgänge vornehmen."Art. 3 - Artikel 9 desselben Erlasses, abgeändert durch die Königlichen Erlasse vom 22. Mai 2014, 22. Juni 2017 und 15. April 2018, wird wie folgt abgeändert:a) Die Paragraphen 2 und 3 werden wie folgt ersetzt:" § 2 - Außer im Hinblick auf die in § 3/1 erwähnten Abweichungsmöglichkeiten darf in den Auftragsunterlagen nicht von der in den Artikeln 95 §§ 3 und 4, 127 und 160 erwähnten Frist abgewichen werden; jegliche anders lautende Bestimmung gilt als nicht geschrieben. Unbeschadet der Paragraphen 1 und 4 ist vorliegender Absatz jedoch nicht anwendbar, wenn alle folgenden Bedingungen erfüllt sind:1. In den Auftragsunterlagen ist ausdrücklich eine längere Bearbeitungsfrist vereinbart.2. Diese Abweichung ist aufgrund der besonderen Natur oder der Merkmale des Auftrags sachlich gerechtfertigt.3. Die Bearbeitungsfrist überschreitet in keinem Fall sechzig Tage.4. Diese Verlängerung ist für den Auftragnehmer nicht grob nachteilig im Sinne von § 3. § 3 - Eine für den Auftragnehmer grob nachteilige Vertragsklausel oder Praxis im Hinblick auf den Bearbeitungstermin oder die Bearbeitungsfrist, auf den für Verzugszinsen geltenden Zinssatz oder auf die Entschädigung für Beitreibungskosten gilt als nicht geschrieben.Bei der Entscheidung darüber, ob eine Vertragsklausel oder eine Praxis grob nachteilig für den Auftragnehmer ist, werden alle Umstände des Falles geprüft, einschließlich folgender Aspekte:1. jede grobe Abweichung von der guten Handelspraxis, die gegen den Grundsatz des guten Glaubens und der Redlichkeit verstößt,2. die Art der Bauleistungen, Lieferungen oder Dienstleistungen,3. ob die Vergabestelle einen objektiven Grund für die Abweichung von der in den Artikeln 95 §§ 3 und 4, 127 und 160 erwähnten Bearbeitungsfrist hat.Für die Anwendung des vorliegenden Paragraphen:1. ist eine Vertragsklausel oder eine Praxis als grob nachteilig anzusehen, wenn in ihr Verzugszinsen ausgeschlossen werden,2. wird vermutet, dass eine Vertragsklausel oder Praxis grob nachteilig ist, wenn in ihr die Entschädigung für Beitreibungskosten ausgeschlossen wird."b) Ein § 3/1 mit folgendem Wortlaut wird eingefügt:" § 3/1 - Für öffentliche Aufträge, die von Vergabestellen vergeben werden, die Gesundheitsdienste anbieten und für diesen Zweck ordnungsgemäß anerkannt sind, kann die Vergabestelle - ausschließlich für Aufträge, die mit der Ausübung dieser Tätigkeit verbunden sind - durch eine entsprechende Bestimmung in den Auftragsunterlagen von den in den Artikeln 95 §§ 3 und 4, 127 oder 160 erwähnten Fristen abweichen und eine gesonderte Überprüfungsfrist von höchstens dreißig Tagen und eine gesonderte Zahlungsfrist von sechzig Tagen vorsehen, wobei die letztgenannte Frist erst ab dem Datum der Beendigung der Überprüfung zu laufen beginnt, insofern der Vergabestelle die ordnungsgemäß aufgestellte Rechnung und andere erforderliche Unterlagen übergeben worden sind. In diesem Fall legt die Vergabestelle die Dauer der Überprüfungsfrist, die dreißig Tage nicht überschreiten darf, in den Auftragsunterlagen fest.Von der in Absatz 1 erwähnten Abweichungsmöglichkeit darf nur Gebrauch gemacht werden, wenn in den Auftragsunterlagen tatsächlich ein Überprüfungsverfahren vorgesehen ist. Darüber hinaus darf die in Absatz 1 erwähnte Überprüfungsfrist nicht lediglich dazu verwendet werden, die Gesamtzahlungsfrist zu verlängern.Macht die Vergabestelle von der in Absatz 1 erwähnten Abweichungsmöglichkeit für einen Bauauftrag Gebrauch, läuft die Überprüfungsfrist ab dem Datum, an dem die Vergabestelle die Schuldforderung und den detaillierten Baufortschrittsbericht wie in Artikel 95 § 1 erwähnt empfangen hat. Macht die Vergabestelle von der in Absatz 1 erwähnten Abweichungsmöglichkeit für einen Lieferauftrag Gebrauch, läuft die Überprüfungsfrist ab der gemäß Artikel 120 festgestellten Lieferung. Macht die Vergabestelle von der in Absatz 1 erwähnten Abweichungsmöglichkeit für einen Dienstleistungsauftrag Gebrauch, läuft die Überprüfungsfrist ab dem Datum der vollständigen oder partiellen Beendigung der Dienstleistungen, das gemäß den in den Auftragsunterlagen festgelegten Modalitäten festgestellt wird.Wird von der vorerwähnten Abweichungsmöglichkeit Gebrauch gemacht, wird die Zahlungsfrist bei Überschreitung der anwendbaren Überprüfungsfrist im Verhältnis zu der Anzahl Tage verringert, um die die Überprüfungsfrist überschritten wird. Im umgekehrten Fall wird die Zahlungsfrist ausgesetzt im Verhältnis zu der Anzahl Tage:1. um die die Frist, die dem Auftragnehmer zur Einreichung seiner Rechnung eingeräumt wird, überschritten wird,2. die erforderlich ist, um eine Antwort des Auftragnehmers zu erhalten, wenn die Vergabestelle ihn im Zusammenhang mit der gesamtschuldnerischen Haftung über den Realbetrag seiner Sozial- oder Steuerschulden im Sinne der Artikel 30bis § 4 und 30ter § 4 des Gesetzes vom 27. Juni 1969 zur Revision des Erlassgesetzes vom 28. Dezember 1944 über die soziale Sicherheit der Arbeitnehmer und des Artikels 55 des Gesetzbuches über die gütliche Beitreibung und die Zwangsbeitreibung von Steuerforderungen und nichtsteuerlichen Forderungen befragen muss."Art. 4 - In denselben Königlichen Erlass wird ein Artikel 66/1 mit folgendem Wortlaut eingefügt:"Art. 66/1 - Vergabestellen füllen die Felder in Bezug auf die in den Artikeln 95 §§ 3 und 4, 127 und 160 erwähnte Frist aus, die in einem elektronischen Formular vorgesehen sind, das zu diesem Zweck vom Föderalen Öffentlichen Dienst Politik und Unterstützung erstellt wird.Sie geben an, ob sie sich für die Anwendung der Frist entscheiden, die in den im vorhergehenden Absatz erwähnten Bestimmungen vorgesehen ist, oder ob sie sich für eine der in Artikel 9 §§ 2 oder 3/1 erwähnten Abweichungen entscheiden. In letzterem Fall geben sie die in den Auftragsunterlagen enthaltene Frist an.Dieses Formular muss im Anschluss an die in den Artikeln 62 Absatz 1 und 143 § 1 Absatz 1 des Gesetzes erwähnte Vergabebekanntmachung oder im Anschluss an die in den Artikeln 62 Absatz 2 und 143 § 1 Absatz 2 des Gesetzes erwähnte vereinfachte Vergabebekanntmachung ausgefüllt werden."Art. 5 - In Artikel 68 desselben Erlasses, abgeändert durch die Königlichen Erlasse vom 22. Mai 2014 und 22. Juni 2017, wird das Wort "Zahlungsfrist" durch das Wort "Bearbeitungsfrist" ersetzt.Art. 6 - In Artikel 69 § 1 desselben Erlasses, abgeändert durch den Königlichen Erlass vom 22. Mai 2014, werden die Wörter "Werden die aufgrund der Artikel 95 §§ 3 bis 5, 127 und 160 festgelegten Zahlungsfristen überschritten" durch die Wörter "Hat der Auftragnehmer seine vertraglichen und gesetzlichen Pflichten erfüllt und wird die in den Artikeln 95 §§ 3 und 4, 127 und 160 erwähnte Bearbeitungsfrist überschritten, ohne dass die Zahlung getätigt wird" ersetzt.Art. 7 - In Artikel 70 desselben Erlasses, abgeändert durch den Königlichen Erlass vom 22. Juni 2017, wird das Wort "Zahlungsfrist" durch das Wort "Bearbeitungsfrist" und das Wort "Zahlungsfristen" durch das Wort "Bearbeitungsfristen" ersetzt.Art. 8 - Artikel 95 desselben Erlasses, abgeändert durch die Königlichen Erlasse vom 22. Mai 2014 und 22. Juni 2017, wird wie folgt ersetzt:"Art. 95 - § 1 - Sowohl bei Anzahlungen als auch bei Restzahlung oder einmaliger Zahlung des Auftragswerts müssen Unternehmer eine datierte und unterzeichnete Schuldforderung mit detailliertem Baufortschrittsbericht, der ihrer Ansicht nach die beantragte Zahlung rechtfertigt, einreichen.Dieser detaillierte Bericht kann folgende Angaben umfassen:1. Mengen, die auf der Grundlage der Posten des zusammenfassenden Aufmaßes ausgeführt wurden,2. Mengen, die über die in den Posten des zusammenfassenden Aufmaßes vermerkten wahrscheinlichen Mengen hinaus ausgeführt wurden,3. zusätzliche Bauleistungen, die aufgrund einer schriftlichen Anweisung ausgeführt wurden,4. Bauleistungen, die zu Einheitspreisen ausgeführt wurden, die vom Unternehmer vorgeschlagen, von der Vergabestelle jedoch noch nicht angenommen worden sind. § 2 - Nach Empfang jeder Schuldforderung nimmt die Vergabestelle innerhalb der in § 3 Absatz 1 erwähnten Bearbeitungsfrist folgende Handlungen vor:1. Sie überprüft den eingereichten Baufortschrittsbericht und berichtigt ihn gegebenenfalls. Kommen darin Einheitspreise vor, die noch nicht zwischen den Parteien vereinbart worden sind, legt sie diese Preise unbeschadet der Rechte des Unternehmers von Amts wegen fest.2. Sie erstellt ein Protokoll mit Angabe der Bauleistungen, die sie im Hinblick auf ihre Bezahlung annimmt, und des Betrags, den sie ihrer Ansicht nach schuldet. Sie setzt den Unternehmer schriftlich von diesem Protokoll in Kenntnis und ersucht ihn, innerhalb fünf Tagen eine Rechnung über den angegebenen Betrag einzureichen. § 3 - Die Vergabestelle tätigt die Überprüfung und die Zahlung der dem Unternehmer geschuldeten Beträge innerhalb einer Bearbeitungsfrist von dreißig Tagen ab dem Datum, an dem die Vergabestelle die Schuldforderung und den detaillierten Baufortschrittsbericht wie in § 1 erwähnt empfangen hat. Die Zahlung kann jedoch nur getätigt werden, insofern der Vergabestelle die ordnungsgemäß aufgestellte Rechnung und andere eventuell erforderliche Unterlagen übergeben worden sind.Die in Absatz 1 erwähnte Bearbeitungsfrist beträgt sechzig Tage für Aufträge, die von Vergabestellen vergeben werden, die Gesundheitsdienste anbieten - ausschließlich für Bauleistungen, die mit der Ausübung dieser Tätigkeit verbunden sind - und für diesen Zweck ordnungsgemäß anerkannt sind.In folgenden Fällen wird von Absatz 1 abgewichen:- Wenn der Zeitpunkt des Eingangs der Schuldforderung unsicher ist, werden Überprüfung und Zahlung in einer Frist von dreißig Tagen ab dem Zeitpunkt des Eingangs des detaillierten Baufortschrittsberichts getätigt.- Wenn die Vergabestelle die Schuldforderung vor Ausführung der durch den detaillierten Baufortschrittsbericht festgestellten Bauleistungen erhält, werden Überprüfung und Zahlung in einer Frist von dreißig Tagen ab Ausführung der Bauleistungen getätigt. § 4 - Die Bearbeitungsfrist wird ausgesetzt im Verhältnis zu der Anzahl Tage:1. um die die Frist von fünf Tagen überschritten wird, die dem Unternehmer aufgrund von § 2 Nr. 2 zur Einreichung seiner Rechnung eingeräumt wird,2. die erforderlich ist, um eine Antwort des Unternehmers zu erhalten, wenn die Vergabestelle ihn im Zusammenhang mit der gesamtschuldnerischen Haftung über den Realbetrag seiner Sozial- oder Steuerschulden im Sinne der Artikel 30bis § 4 und 30ter § 4 des Gesetzes vom 27. Juni 1969 zur Revision des Erlassgesetzes vom 28. Dezember 1944 über die soziale Sicherheit der Arbeitnehmer und des Artikels 55 des Gesetzbuches über die gütliche Beitreibung und die Zwangsbeitreibung von Steuerforderungen und nichtsteuerlichen Forderungen befragen muss."Art. 9 - In Artikel 120 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 22. Mai 2014 und abgeändert durch den Königlichen Erlass vom 22. Juni 2017, werden die Absätze 2 und 3 aufgehoben.Art. 10 - Artikel 127 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 22. Mai 2014 und abgeändert durch den Königlichen Erlass vom 22. Juni 2017, wird wie folgt ersetzt:"Art. 127 - Die Vergabestelle tätigt die Überprüfung und die Zahlung der dem Lieferanten geschuldeten Beträge innerhalb der Bearbeitungsfrist von dreißig Tagen ab der Lieferung, insofern der Vergabestelle die ordnungsgemäß aufgestellte Rechnung und andere eventuell erforderliche Unterlagen übergeben worden sind.Die in Absatz 1 erwähnte Bearbeitungsfrist beträgt sechzig Tage für Aufträge, die von Vergabestellen vergeben werden, die Gesundheitsdienste anbieten - ausschließlich für Lieferungen, die mit der Ausübung dieser Tätigkeit verbunden sind - und für diesen Zweck ordnungsgemäß anerkannt sind.In folgenden Fällen wird von Absatz 1 abgewichen:- Wenn der Zeitpunkt des Eingangs der Rechnung bei der Vergabestelle unsicher ist, werden Überprüfung und Zahlung in einer Frist von dreißig Tagen ab der Lieferung getätigt.- Wenn die Vergabestelle die Rechnung vor der Lieferung erhält, werden Überprüfung und Zahlung in einer Frist von dreißig Tagen ab der Lieferung getätigt.Erfolgt die Lieferung in mehreren Malen, läuft die Bearbeitungsfrist ab dem Datum der Lieferung für jede Teillieferung.Die Bearbeitungsfrist wird ausgesetzt im Verhältnis zu der Anzahl Tage:1. um die die Frist überschritten wird, über die der Lieferant zur Einreichung seiner Rechnung verfügt, wenn die Vergabestelle eine Überprüfung auf der Grundlage des Lieferscheins oder einer gesonderten Schuldforderung und die Einreichung der Rechnung nach der Überprüfung vorgesehen hat,2. die erforderlich ist, um eine Antwort des Lieferanten zu erhalten, wenn die Vergabestelle ihn im Zusammenhang mit der gesamtschuldnerischen Haftung über den Realbetrag seiner Sozial- oder Steuerschulden im Sinne der Artikel 30bis § 4 und 30ter § 4 des Gesetzes vom 27. Juni 1969 zur Revision des Erlassgesetzes vom 28. Dezember 1944 über die soziale Sicherheit der Arbeitnehmer und des Artikels 55 des Gesetzbuches über die gütliche Beitreibung und die Zwangsbeitreibung von Steuerforderungen und nichtsteuerlichen Forderungen befragen muss."Art. 11 - In Artikel 129 desselben Königlichen Erlasses, abgeändert durch den Königlichen Erlass vom 22. Mai 2014, werden die Wörter "der in Artikel 120 Absatz 2 vorgesehenen Frist von dreißig Tagen" durch die Wörter "der Frist von dreißig Tagen, die ab dem Datum der Lieferung zu laufen beginnt," ersetzt.Art. 12 - In Artikel 131 desselben Königlichen Erlasses, abgeändert durch den Königlichen Erlass vom 22. Juni 2017, werden die Wörter "in Artikel 120" durch die Wörter "in Artikel 127" ersetzt.Art. 13 - Artikel 156 desselben Königlichen Erlasses, ersetzt durch den Königlichen Erlass vom 22. Mai 2014 und abgeändert durch den Königlichen Erlass vom 22. Juni 2017, wird wie folgt ersetzt:"Art. 156 - Verfügt die Vergabestelle über die Liste der erbrachten Dienstleistungen oder die Rechnung und ist die vollständige oder partielle Beendigung der Dienstleistungen gemäß den in den Auftragsunterlagen festgelegten Modalitäten festgestellt worden, tätigt die Vergabestelle die Überprüfung, erfüllt sie die Abnahmeformalitäten und notifiziert sie dem Dienstleistungserbringer ihr Ergebnis. Auf jeden Fall erfolgt die Überprüfung innerhalb der in Artikel 160 Absatz 1 erwähnten Bearbeitungsfrist.Werden die Dienstleistungen vor oder nach diesem Datum vollendet, so benachrichtigt der Dienstleistungserbringer den leitenden Beamten davon per Einschreibesendung oder elektronische Sendung, mit der das genaue Datum der Versendung in gleichwertiger Weise sichergestellt wird, und beantragt die Abnahme."Art. 14 - Artikel 160 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 22. Mai 2014 und abgeändert durch den Königlichen Erlass vom 22. Juni 2017, wird wie folgt ersetzt:"Art. 160 - Die Vergabestelle tätigt die Überprüfung und die Zahlung der dem Dienstleistungserbringer geschuldeten Beträge innerhalb der Bearbeitungsfrist von dreißig Tagen ab der Feststellung der vollständigen oder partiellen Beendigung der Dienstleistungen gemäß den in den Auftragsunterlagen festgelegten Modalitäten. Die Zahlung kann jedoch nur getätigt werden, insofern der Vergabestelle die ordnungsgemäß aufgestellte Rechnung, die Liste der erbrachten Dienstleistungen und andere eventuell erforderliche Unterlagen übergeben worden sind.Die in Absatz 1 erwähnte Bearbeitungsfrist beträgt sechzig Tage für Aufträge, die von Vergabestellen vergeben werden, die Gesundheitsdienste anbieten - ausschließlich für Dienstleistungen, die mit der Ausübung dieser Tätigkeit verbunden sind - und für diesen Zweck ordnungsgemäß anerkannt sind.In folgenden Fällen wird von Absatz 1 abgewichen:- Wenn der Zeitpunkt des Eingangs der Rechnung unsicher ist, werden Überprüfung und Zahlung in einer Frist von dreißig Tagen ab dem Zeitpunkt der Beendigung der Dienstleistungen getätigt.- Wenn die Vergabestelle die Rechnung vor Beendigung der Dienstleistungen erhält, werden Überprüfung und Zahlung in einer Frist von dreißig Tagen ab Beendigung der Dienstleistungen getätigt.Die Bearbeitungsfrist wird ausgesetzt im Verhältnis zu der Anzahl Tage:1. um die die Frist überschritten wird, über die der Dienstleistungserbringer zur Einreichung seiner Rechnung verfügt, wenn die Vergabestelle eine Überprüfung auf der Grundlage der Liste der erbrachten Dienstleistungen oder einer gesonderten Schuldforderung und die Einreichung der Rechnung nach der Überprüfung vorgesehen hat,2. die erforderlich ist, um eine Antwort des Dienstleistungserbringers zu erhalten, wenn die Vergabestelle ihn im Zusammenhang mit der gesamtschuldnerischen Haftung über den Realbetrag seiner Sozial- oder Steuerschulden im Sinne der Artikel 30bis § 4 und 30ter § 4 des Gesetzes vom 27. Juni 1969 zur Revision des Erlassgesetzes vom 28. Dezember 1944 über die soziale Sicherheit der Arbeitnehmer und des Artikels 55 des Gesetzbuches über die gütliche Beitreibung und die Zwangsbeitreibung von Steuerforderungen und nichtsteuerlichen Forderungen befragen muss."Art. 15 - Für Aufträge, deren geschätzter Wert unter den Schwellenwerten für die europäische Bekanntmachung liegt, tritt vorliegender Erlass am 1. Januar 2025 in Kraft, sofern ihre Auftragsbekanntmachungen ab diesem Datum veröffentlicht werden oder sofern für sie in Ermangelung einer Verpflichtung zur vorherigen Bekanntmachung ab diesem Datum zur Abgabe eines Angebots aufgefordert wird.Für Aufträge, deren geschätzter Wert mindestens die Schwellenwerte für die europäische Bekanntmachung erreicht, tritt vorliegender Erlass am 1. Januar 2025 in Kraft, sofern ihre Auftragsbekanntmachungen ab diesem Datum veröffentlicht werden oder sofern für sie in Ermangelung einer Verpflichtung zur vorherigen Bekanntmachung ab diesem Datum zur Abgabe eines Angebots aufgefordert wird. Für diese Aufträge gilt das Datum der Versendung der Bekanntmachung über die e-Procurement-Plattform an das Amtsblatt der Europäischen Union als Datum der Veröffentlichung der Auftragsbekanntmachung.Art. 16 - Der Premierminister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Ile-d'Yeu, den 12. August 2024PHILIPPEVon Königs wegen:Der PremierministerA. DE CROO 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de schoonmaak; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 4 februari 2025, gesloten in het Paritair Comité voor de schoonmaak, tot wijziging van de collectieve arbeidsovereenkomst van 11 juni 2009 betreffende de classificatie (geregistreerd op 5 oktober 2009 onder het nummer 94699/CO/121 en algemeen verbindend verklaard bij koninklijk besluit van 19 april 2010, Belgisch Staatsblad van 6 juli 2010). Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de schoonmaak Collectieve arbeidsovereenkomst van 4 februari 2025 Wijziging van de collectieve arbeidsovereenkomst van 11 juni 2009 betreffende de classificatie (geregistreerd op 5 oktober 2009 onder het nummer 94699/CO/121 en algemeen verbindend verklaard bij koninklijk besluit van 19 april 2010, Belgisch Staatsblad van 6 juli 2010) (Overeenkomst geregistreerd op 10 februari 2025 onder het nummer 192006/CO/121) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de werklieden en werksters uit de ondernemingen welke onder het Paritair Comité voor de schoonmaak ressorteren, kleine en middelgrote ondernemingen en anderen. Deze collectieve arbeidsovereenkomst zal eveneens van toepassing zijn op elke arbeider of werkster in loondienst, met een onbeperkt of tijdelijk contract, voor werkzaamheden die in België worden uitgevoerd, welke ook het vestigingsland van de werkgever weze. Art. 2. In artikel 2 van de collectieve arbeidsovereenkomst van 11 juni 2009 betreffende de classificatie, wordt het punt 3 Opleiding van de beschrijving van de categorie 8 Industriële reiniging : onderhoud, reiniging en behandeling in de scheepvaart, de industrie en het milieu aangevuld met volgende bepaling : "Werknemers in opleiding mogen aan de vereiste bezetting worden toegevoegd en staan onder toezicht van de operator. Zij mogen echter geen apparatuur zelfstandig bedienen, zoals pompen, hogedrukinstallaties, etc.". Art. 3. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025 en heeft dezelfde geldigheidsduur, dezelfde opzeggingsmodaliteiten en -termijnen als collectieve arbeidsovereenkomst welke zij wijzigt. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -2840,7 +2837,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2025003651</t>
+          <t>2025003002</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2850,19 +2847,18 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>9 juli 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 8 november 2007 betreffende de preventie en het herstel van milieuschade tengevolge van het vervoer over de weg, per spoor, over de binnenwateren of in de lucht van: uitheemse plantensoorten evenals van uitheemse diersoorten en hun krengen, naar aanleiding van de in-, de uit- en de doorvoer ervan; alsook van afvalstoffen bij hun doorvoer. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 20 februari 2025, gesloten in het Paritair Comité voor het vervoer en de logistiek, betreffende de anciënniteitspremie en het anciënniteitsverlof voor werklieden en werksters tewerkgesteld door werkgevers behorend tot het Paritair Subcomité voor de verhuizing (1)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-23&amp;numac_search=2025003651&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003651=75&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-23&amp;numac_search=2025003002&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003002=75&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 9 juli 2024 tot wijziging van het koninklijk besluit van 8 november 2007 betreffende de preventie en het herstel van milieuschade tengevolge van het vervoer over de weg, per spoor, over de binnenwateren of in de lucht van: uitheemse plantensoorten evenals van uitheemse diersoorten en hun krengen, naar aanleiding van de in-, de uit- en de doorvoer ervan; alsook van afvalstoffen bij hun doorvoer (Belgisch Staatsblad van 18 juli 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST MOBILITÄT UND TRANSPORTWESEN9. JULI 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 8. November 2007 über die Vermeidung und Sanierung von Umweltschäden verursacht durch Transporte über die Straße, über den Schienenweg, über die Binnengewässer oder über den Luftweg von gebietsfremden Pflanzenarten sowie gebietsfremden Tierarten und deren Überresten, als Folge ihres Imports, Exports und ihrer Durchfuhr, sowie von Abfällen bei ihrer DurchfuhrPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des Gesetzes vom 25. April 2007 zur Festlegung verschiedener Bestimmungen (IV), des Artikels 224;Aufgrund des Königlichen Erlasses vom 8. November 2007 über die Vermeidung und Sanierung von Umweltschäden verursacht durch Transporte über die Straße, über den Schienenweg, über die Binnengewässer oder über den Luftweg von gebietsfremden Pflanzenarten sowie gebietsfremden Tierarten und deren Überresten, als Folge ihres Imports, Exports und ihrer Durchfuhr, sowie von Abfällen bei ihrer Durchfuhr;Aufgrund der Stellungnahme des Finanzinspektors vom 5. Juli 2021;Aufgrund des Einverständnisses der Staatssekretärin für Haushalt vom 14. Dezember 2023;Aufgrund der Beteiligung der Regionalregierungen;Aufgrund der Auswirkungsanalyse beim Erlass von Vorschriften, die gemäß den Artikeln 6 und 7 des Gesetzes vom 15. Dezember 2013 zur Festlegung verschiedener Bestimmungen in Sachen administrative Vereinfachung durchgeführt worden ist;Aufgrund des Antrags auf Begutachtung binnen einer Frist von dreißig Tagen, der am 25. April 2024 beim Staatsrat eingereicht worden ist, in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;In Erwägung der Notifizierung der Gesetzgebungsabteilung des Staatsrates vom 29. April 2024, den Begutachtungsantrag, der unter der Nummer 76.251/16 in die Liste der Gesetzgebungsabteilung des Staatsrates eingetragen wurde, gemäß Artikel 84 § 5 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat von der Liste zu streichen;In Erwägung des Mahnschreibens der Europäischen Kommission vom 2. Juli 2020 und der entsprechenden mit Gründen versehenen Stellungnahme vom 28. September 2023, die in Anwendung von Artikel 258 des Vertrags über die Arbeitsweise der Europäischen Union abgegeben wurde, aufgrund der nicht ordnungsgemäßen Umsetzung von Artikel 12 Absatz 1 der Richtlinie 2004/35/EG des Europäischen Parlaments und des Rates vom 21. April 2004 über Umwelthaftung zur Vermeidung und Sanierung von Umweltschäden in Artikel 13 des Königlichen Erlasses vom 8. November 2007 über die Vermeidung und Sanierung von Umweltschäden verursacht durch Transporte über die Straße, über den Schienenweg, über die Binnengewässer oder über den Luftweg von gebietsfremden Pflanzenarten sowie gebietsfremden Tierarten und deren Überresten, als Folge ihres Imports, Exports und ihrer Durchfuhr, sowie von Abfällen bei ihrer Durchfuhr;Auf Vorschlag des Ministers der Mobilität und aufgrund der Stellungnahme der Minister, die im Rat darüber beraten haben,Haben Wir beschloßen und erlassen Wir:Artikel 1 - Mit vorliegendem Erlass wird die Richtlinie 2004/35/EG des Europäischen Parlaments und des Rates vom 21. April 2004 über Umwelthaftung zur Vermeidung und Sanierung von Umweltschäden teilweise umgesetzt.Art. 2 -  In Artikel 13 des Königlichen Erlasses vom 8. November 2007 über die Vermeidung und Sanierung von Umweltschäden verursacht durch Transporte über die Straße, über den Schienenweg, über die Binnengewässer oder über den Luftweg von gebietsfremden Pflanzenarten sowie gebietsfremden Tierarten und deren Überresten, als Folge ihres Imports, Exports und ihrer Durchfuhr, sowie von Abfällen bei ihrer Durchfuhr, zuletzt abgeändert durch den Königlichen Erlass vom 3. September 2017, wird Paragraph 1 wie folgt ersetzt:" § 1 - Natürliche und juristische Personen, die von einem Umweltschaden betroffen oder wahrscheinlich betroffen sind oder ein ausreichendes Interesse an einem umweltbezogenen Entscheidungsverfahren bezüglich des Schadens haben oder eine Verletzung ihrer Rechte geltend machen, können der zuständigen Behörde Bemerkungen zu einem unmittelbar drohenden oder bereits eingetretenen Umweltschaden unterbreiten und die zuständige Behörde auffordern, Maßnahmen gemäß dem vorliegenden Kapitel zu ergreifen.Unbeschadet des vorhergehenden Absatzes wird davon ausgegangen, dass juristische Personen, deren Ziel der Schutz der Umwelt ist und die in ihrer Satzung das Gebiet festgelegt haben, auf das sich ihre Tätigkeit erstreckt, ein ausreichendes Interesse haben und Träger von Rechten sind, die verletzt werden können."Art. 3 -  Der für Mobilität zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 9. Juli 2024PHILIPPEVon Königs wegen:Der Minister der MobilitätG. GILKINETDer Minister der VolksgesundheitF. VANDENBROUCKEDer Minister der UmweltZ. KHATTABI 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor het vervoer en de logistiek;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 20 februari 2025, gesloten in het Paritair Comité voor het vervoer en de logistiek, betreffende de anciënniteitspremie en het anciënniteitsverlof voor werklieden en werksters tewerkgesteld door werkgevers behorend tot het Paritair Subcomité voor de verhuizing.Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te00 Brussel, 7 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het vervoer en de logistiekCollectieve arbeidsovereenkomst van 20 februari 2025Anciënniteitspremie en anciënniteitsverlof voor werklieden en werksters tewerkgesteld door werkgevers behorend tot het Paritair Subcomité voor de verhuizing (Overeenkomst geregistreerd op 20 maart 2025 onder het nummer 192664/CO/140)I. ToepassingsgebiedArtikel 1.  Deze collectieve arbeidsovereenkomst is van toepassing :1) op de werkgevers die ressorteren onder het Paritair Comité voor het vervoer en de logistiek en die behoren tot het Paritair Subcomité 140.05 voor de verhuizing;2) op de werklieden en werksters die worden tewerkgesteld door de in 1) bedoelde werkgevers.Art. 2.  Met "anciënniteit" wordt bedoeld : elke periode van tewerkstelling die niet onderbroken wordt door een periode van meer dan 22 werkdagen gedurende dewelke hij niet meer via een arbeidsovereenkomst of interimcontract aan de werkgever verbonden is.II. AnciënniteitsverlofArt. 3.  De werklieden en werksters genieten vanaf 1 januari 2023 ingevolge de collectieve arbeidsovereenkomst van 21 november 2019, gesloten in het Paritair Comité voor het vervoer en de logistiek, betreffende de berekening van het anciënniteitsverlof van de werklieden en werksters tewerkgesteld in de verhuisondernemingen, meubelbewaring en hun aanverwante activiteiten (registratienummer 155926/CO/140), gewijzigd door de collectieve arbeidsovereenkomst van 19 oktober 2023 (registratienummer 183991/CO/140), van een anciënniteitsverlof dat als volgt berekend wordt : 1 betaalde dag per 5 jaar tewerkstelling in de sector (met inbegrip van de periode interimtewerkstelling van maximum 1 jaar), met een maximum van 5 dagen.Het loon dat voor elke dag anciënniteitsverlof dient betaald te worden, is het loon dat volgens de arbeidsovereenkomst die dag verschuldigd is.III. AnciënniteitspremieArt. 4.  Berekening van de anciënniteitspremieArtikel 3 van de collectieve arbeidsovereenkomst van 20 oktober 2011, gesloten in het Paritair Comité voor het vervoer en de logistiek, betreffende de berekening van de anciënniteit van de werklieden en werksters tewerkgesteld in de verhuisondernemingen, meubelbewaring en hun aanverwante activiteiten (Registratienummer 107044/CO/140) gewijzigd door de collectieve arbeidsovereenkomst van 19 oktober 2023 (registratienummer 183992/CO/140), wordt gewijzigd als volgt :Een brutopremie wordt jaarlijks toegekend aan elke werknemer die een ononderbroken anciënniteit van minstens 3 jaar op sectorniveau kan voorleggen (met inbegrip van een periode interim-tewerkstelling van maximum 1 jaar).De anciënniteit van de interimtewerkstelling is niet van toepassing bij de bepaling van de opzegtermijn.Art. 5.  Bedrag van de anciënniteitspremie  </t>
         </is>
       </c>
     </row>
@@ -2872,29 +2868,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2025003635</t>
+          <t>2025201165</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>16 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4 juli 2024. - Koninklijk besluit tot aanvulling van de lijsten van oneerlijke marktpraktijken tussen ondernemingen in de landbouw- en voedselvoorzieningsketen. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 28 juni 2024, gesloten in het Nationaal Paritair Comité voor de sport, betreffende de arbeids- en loonvoorwaarden van de betaalde voetbalspelers (1)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-16&amp;numac_search=2025003635&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003635=76&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025201165&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201165=76&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 4 juli 2024 tot aanvulling van de lijsten van oneerlijke marktpraktijken tussen ondernemingen in de landbouw- en voedselvoorzieningsketen (Belgisch Staatsblad van 25 juli 2024, err. van 3 september 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST WIRTSCHAFT, KMB, MITTELSTAND UND ENERGIE4. JULI 2024 - Königlicher Erlass zur Ergänzung der Listen unlauterer Handelspraktiken in den Geschäftsbeziehungen zwischen Unternehmen in der Agrar- und LebensmittelversorgungskettePHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des Wirtschaftsgesetzbuches, des Artikels VI.109/7 Absatz 1, eingefügt durch das Gesetz vom 28. November 2021;Aufgrund der Stellungnahme des Zentralen Wirtschaftsrates vom 29. März 2024;Aufgrund der Stellungnahme des Hohen Rates für Selbständige und KMB vom 2. April 2024;Aufgrund der Stellungnahme des Finanzinspektors vom 10. April 2024;Aufgrund der Auswirkungsanalyse beim Erlass von Vorschriften, die gemäß Artikel 6 § 1 des Gesetzes vom 15. Dezember 2013 zur Festlegung verschiedener Bestimmungen in Sachen administrative Vereinfachung durchgeführt worden ist;Aufgrund des Gutachtens Nr. 76.469/1 des Staatsrates vom 6. Juni 2024, abgegeben in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Auf Vorschlag des Ministers der Wirtschaft und des Ministers des Mittelstands und der Landwirtschaft und aufgrund der Stellungnahme der Minister, die im Rat darüber beraten haben,Haben Wir beschloßen und erlassen Wir:Artikel 1 - Vorliegender Erlass ist anwendbar auf Beziehungen in der Agrar- und Lebensmittelversorgungskette zwischen Käufern einerseits und Lieferanten mit einem Jahresumsatz von höchstens 350 000 000 EUR andererseits im Sinne von Artikel VI.109/4 des Wirtschaftsgesetzbuches.Art. 2 - Unbeschadet des Artikels VI.109/5 des Wirtschaftsgesetzbuches gelten folgende Marktpraktiken ebenfalls als unlauter und gemäß Artikel VI.109/8 des Wirtschaftsgesetzbuches verboten:1. Androhung einer unlauteren Auslistung der Erzeugnisse des Lieferanten durch den Käufer oder Vornahme einer solchen Auslistung durch den Käufer, wenn der Lieferant seine vertraglichen oder gesetzlichen Rechte ausübt, und Vornahme einer Auslistung durch den Käufer ohne vorherige schriftliche Rechtfertigung und Mitteilung,2. automatische Anrechnung von Schadenersatz durch den Käufer ohne vorherige schriftliche Rechtfertigung der Unzulänglichkeit und des Schadens, der den geforderten Betrag rechtfertigt, unbeschadet der Anwendung von Artikel 5.88 § 1 des Zivilgesetzbuches,3. einseitige Aufrechnung von Schadenersatz durch den Käufer ohne vorherige schriftliche Rechtfertigung der Unzulänglichkeit und des Schadens, der den geforderten Betrag rechtfertigt, unbeschadet der Anwendung von Artikel 5.88 § 1 des Zivilgesetzbuches,4. einseitige Aufrechnung von Vertragsstrafen ohne Entschädigungscharakter durch den Käufer, unbeschadet der Anwendung von Artikel 5.88 § 1 des Zivilgesetzbuches.Art. 3 - Unbeschadet des Artikels VI.109/6 Absatz 1 desselben Gesetzbuches gelten folgende Marktpraktiken ebenfalls als unlauter, es sei denn, sie sind zuvor klar und eindeutig in der Liefervereinbarung oder in einer Folgevereinbarung zwischen dem Lieferanten und dem Käufer vereinbart worden:1. Kauf der Erzeugnisse beim Lieferanten durch den Käufer zu einem Preis, der unter den Herstellungskosten des Lieferanten liegt. Für die Anwendung der vorliegenden Nummer werden die Herstellungskosten zum Zeitpunkt des Kaufs der Erzeugnisse berücksichtigt.Betrifft der Verkauf ein Erzeugnis, für das ein Herstellungskostenindex validiert worden ist innerhalb eines anerkannten Branchenverbands im Sinne von Artikel 157 der Verordnung (EU) Nr. 1308/2013 des Europäischen Parlaments und des Rates vom 17. Dezember 2013 über eine gemeinsame Marktorganisation für landwirtschaftliche Erzeugnisse und zur Aufhebung der Verordnungen (EWG) Nr. 922/72, (EWG) Nr. 234/79, (EG) Nr. 1037/2001 und (EG) Nr. 1234/2007 des Rates, dem Käufer und Verkäufer angeschlossen sind, dient dieser Index als Referenz für die Bestimmung der Herstellungskosten.Ist kein Herstellungskostenindex innerhalb eines anerkannten Branchenverbands validiert worden oder sind entweder der Käufer oder der Lieferant oder beide nicht einem anerkannten Branchenverband angeschlossen, werden die Herstellungskosten auf individueller Basis bestimmt,2. Weigerung einer der Parteien, den Vertrag neu zu verhandeln, wenn eine Änderung der Umstände, die nicht den Vertragsparteien zuzuschreiben ist und bei Vertragsabschluss nicht vorhersehbar war, die Erfüllung des Vertrags übermäßig teuer macht, so dass sie nach vernünftigem Ermessen nicht zuzumuten ist.Art. 4 - Vorliegender Erlass tritt am ersten Tag des dritten Monats nach seiner Veröffentlichung im Belgischen Staatsblatt für Liefervereinbarungen in Kraft, die nach diesem Datum geschlossen, erneuert oder geändert werden.Art. 5 - Liefervereinbarungen, die vor dem Datum der Veröffentlichung des vorliegenden Erlasses geschlossen wurden, werden innerhalb sechs Monaten ab diesem Datum mit vorliegendem Erlass in Einklang gebracht.Art. 6 - Die für Wirtschaft, Mittelstand beziehungsweise Landwirtschaft zuständigen Minister sind, jeweils für ihren Bereich, mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 4. Juli 2024PHILIPPEVon Königs wegen:Der Minister der WirtschaftP.-Y. DERMAGNEDer Minister des Mittelstands und der LandwirtschaftD. CLARINVAL 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Nationaal Paritair Comité voor de sport; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 28 juni 2024, gesloten in het Nationaal Paritair Comité voor de sport, betreffende de arbeids- en loonvoorwaarden van de betaalde voetbalspelers. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Nationaal Paritair Comité voor de sport Collectieve arbeidsovereenkomst van 28 juni 2024 Arbeids- en loonvoorwaarden van de betaalde voetbalspelers (Overeenkomst geregistreerd op 25 juli 2024 onder het nummer 189027/CO/223) HOOFDSTUK I. - Toepassingsgebied Artikel 1. De collectieve arbeidsovereenkomst is van toepassing op de voetbalclubs en de betaalde voetbalspelers die ressorteren onder de wet van 24 februari 1978. HOOFDSTUK II. - Duurtijd Art. 2.  De collectieve arbeidsovereenkomst wordt afgesloten voor een bepaalde duur, te weten van 1 juli 2024 tot en met 30 juni 2026, doch met uitzondering voor artikel 38 en bijgevolg ook artikel 1 die op 1 juli 2022 in werking treden en van onbepaalde duur zijn. Deze twee artikelen van onbepaalde duur kunnen opgezegd worden door elk van de ondertekenende partijen mits inachtneming van een opzeggingstermijn van zes maanden per aangetekend schrijven aan de voorzitter van het Nationaal Paritair Comité voor de sport. HOOFDSTUK III. - Arbeids- en loononderhandelingen Art. 3.  De partijen erkennen dat de arbeids- en loononderhandelingen gebeuren tussen de werkgevers/clubs en werknemers/vakbonden zoals vertegenwoordigd in het paritair comité.De partijen erkennen het belang van het sociaal overleg en onderschrijven dat reglementaire bepalingen die een invloed hebben op het statuut of de arbeidssituatie van de betaalde voetballer, steeds voorafgaand aan de reglementaire goedkeuring dienen te worden overlegd tussen de sociale partners als belangrijkste stakeholders. Dit houdt ook in dat sociale partners er zich toe verbinden geen reglementaire bepalingen goed te keuren, te onderschrijven of te bevestigen die in strijd zijn met wettelijke of conventionele bepalingen. Een reglementaire bepaling in strijd met wettelijke of conventionele bepalingen is niet geldig en in strijd met deze collectieve arbeidsovereenkomst. HOOFDSTUK IV Discriminatie, racisme en integriteit van speler of club Art. 4.  Noch de club noch de speler zullen zich inlaten met kwetsende, provocerende en/of discriminerende (racistische, xenofobe, homofobe, enz.) uitspraken, teksten, symbolen, gebaren en uitlatingen, in het kader van de relatie werkgever-werknemer. Deze raken personen in hun identiteit en hebben geen plaats in onze sport. De ondertekenende partijen veroordelen elke kwetsende, discriminatoire of racistische handeling van de werkgever en/of de werknemer in het kader van hun activiteiten binnen de voetbalsector. De sociale partners veroordelen ook alle inbreuken tegen de integriteit van de speler en/of club. HOOFDSTUK V. - Recht op arbeid Art. 5.  De betaalde voetballer heeft recht op arbeid (dit wil zeggen tewerkgesteld worden bij een voetbalclub onder de voorwaarden van de wet van 24 februari 1978 en speelgerechtigd zijn voor het eerste elftal van die club) : - Als hij eenzijdig door de club behorende tot de KBVB, VFV of ACFF wordt ontslagen. In dit geval zal de speler slechts speelgerechtigd zijn voor zover hij aangesloten is vóór 15 maart van het lopende seizoen, tenzij het ontslag een gevolg is van een vereffening/faillissement van de werkgever-club, in welk geval de aansluiting ook na 15 maart kan plaatsvinden; - Als hem een contract wordt aangeboden als betaalde sportbeoefenaar en hij geen lid is van een bij de KBVB, VFV of ACFF aangesloten club; - Als hem een contract wordt aangeboden als betaalde sportbeoefenaar en hij dit statuut in een andere club van de KBVB, VFV of ACFF niet bezit. In dit geval zal steeds voorafgaandelijk aan de ondertekening van de overeenkomst de goedkeuring van de arbitragecommissie voor de betaalde sportbeoefenaar zoals beschreven in artikel B2.60 en verdere van het bondsreglement vereist zijn. Er is geen goedkeuring vereist voor spelers die de leeftijd van 18 jaar hebben bereikt; - Als een bestaande overeenkomst tussen een speler en een club behorende tot de KBVB, VFV of ACFF in onderling akkoord wordt verbroken. In dit geval zal de speler speelgerechtigd zijn bij zijn nieuwe club als betaalde voetballer indien de overeenkomst in onderling overleg werd verbroken tijdens de lopende transferperiode. In geval van onderlinge verbreking buiten de transferperiode is de speler slechts speelgerechtigd van bij de aanvang van de eerstvolgende transferperiode. De transferperiodes zijn vastgelegd in de maanden januari (wintertransferperiode) en juli en augustus (zomertransferperiode); - Als de speler zelf ontslag neemt omwille van een impliciete fout van de werkgever. Een impliciete fout van de werkgever houdt in dat de werkgever eenzijdig belangrijke wijzigingen van een essentieel element van de arbeidsovereenkomst doorvoert. In casu wordt de ontstentenis van betaling van het loon gedurende uiterlijk de 30ste kalenderdag volgend op de opeisbaarheid als een impliciete fout van de werkgever beschouwd voor zover de werkgever voorafgaand in gebreke wordt gesteld en de kans werd gegeven om het nog verschuldigde loon te voldoen binnen een termijn van minimum 10 dagen. Er kan door de club of de federatie waartoe de club behoort geen beperking van dit recht worden opgelegd. HOOFDSTUK VI. - Loon en statuut Art. 6.  § 1. Het loon van de betaalde voetballer (in arbeidsrechtelijke zin) bestaat uit de volgende elementen : - het vast brutomaandsalaris; - de wedstrijdpremies; - andere contractuele vergoedingen; - de contractuele vergoedingen in natura, onder meer het beschikken over een woning, een voertuig of andere voordelen in natura; - de werkgeversbijdragen in het pensioenfonds.Alle vergoedingen moeten verplicht overgeschreven worden op het rekeningnummer van de speler. Dit rekeningnummer wordt vermeld in het contract tussen speler en club. De speler draagt de verantwoordelijkheid voor de schriftelijke kennisgeving aan de werkgever in geval van wijziging van rekeningnummer waarop de vergoedingen moeten worden overgeschreven.  § 2. Het loon moet contractueel voldoende bepaalbaar zijn (vaste wedde, voordelen in natura, premies,...) zodat reeds uit het contract blijkt of het minimumloon gerespecteerd werd. De werkgeversbijdragen voor de groepsverzekering, de collectieve arbeidsovereenkomstpremie en het vakantiegeld worden niet meegerekend voor de bepaling van de verschillende minimumlonen (deeltijds betaalde sportbeoefenaar-voltijds betaalde sportbeoefenaar - sportbeoefenaar van buiten de Europese Economische Ruimte). Dit betekent dat het minimumloon moet worden behaald met de andere loonelementen dan de werkgeversbijdragen voor de groepsverzekering, de collectieve arbeidsovereenkomstpremie en het vakantiegeld. Daarnaast wordt uitdrukkelijk overeengekomen dat voor het bereiken van het minimumloon enkel rekening kan worden gehouden met de loonelementen opgesomd in de loonbeschermingswet.  § 3. De betaalde voetballer dient elke maand van het contract, dat minimaal loopt tot het einde van het seizoen (30 juni), verloond te worden. Het effectieve maandloon moet minstens gelijk zijn aan het theoretisch minimum maandloon. Het jaarlijks minimumloon wordt vastgelegd door het Nationaal Paritair Comité voor de sport. Maandelijks dient minstens 1/12de van dit vastgelegde minimumloon te worden betaald. Tevens moet bijkomend rekening gehouden worden met de bepalingen van artikel 10. Art. 7.  Elke club (exclusief U23-teams) moet verplicht een aantal spelers onder arbeidsovereenkomst hebben, afhankelijk van de afdeling waarin de club uitkomt. Volgend minimum is van toepassing : - Nationale afdeling 1A : 23; - Nationale afdeling 1B : 19. Art. 8.  § 1. De betaalde voetbalspeler waarvan het contractueel vast brutomaandloon lager is dan 10 200 EUR en die per 1 februari langer dan 16 maanden ononderbroken bij de club is en minstens 16 jaar is, heeft recht op een collectieve arbeidsovereenkomstpremie op basis van de volgende modaliteiten : - meer dan één seizoen in dienst als betaalde voetbalspeler : 538,56 EUR; - meer dan 2 seizoenen in dienst als betaalde voetbalspeler : 807,85 EUR; - meer dan 3 seizoenen in dienst als betaalde voetbalspeler : 1 346,41 EUR; - meer dan 5 seizoenen in dienst als betaalde voetbalspeler : 1 615,69 EUR; - meer dan 7 seizoenen in dienst als betaalde voetbalspeler : 1 884,98 EUR; - meer dan 9 seizoenen in dienst als betaalde voetbalspeler : 2 154,26 EUR. Het ononderbroken in dienst zijn wordt bepaald door de in het (de) contract(en) vooropgestelde duurtijd. Een definitieve overgang naar een andere club vormt hierop de uitzondering.  § 2. De bedragen worden respectievelijk verhoogd tot 1 077,13 EUR (meer dan 2 seizoenen), 1 615,69 EUR (meer dan 3 seizoenen) en 2 154,26 EUR (meer dan 4 seizoenen) voor zover het op het moment van uitbetaling een club uit Nationale afdeling 1A betreft.  § 3. De maand van uitbetaling is februari van het seizoen waarin de respectievelijke voorwaarden voldaan zijn. De betaalde sportbeoefenaar die in februari niet meer in dienst is, heeft hierop geen recht meer.  § 4. De collectieve arbeidsovereenkomstpremie is niet inbegrepen in de normale bezoldiging. Hier kan contractueel niet van worden afgeweken. De arbeidsovereenkomstpremie is met andere woorden steeds verschuldigd bovenop eventuele andere contractuele premies of loonsverhogingen. Art. 9.  Partijen komen overeen dat de clubs aan de deeltijds en voltijds betaalde voetballers bovenop het jaarlijks geïndexeerd minimumloon voor de deeltijds en voltijds betaalde sportbeoefenaar : - 323,14 EUR waarborgen per seizoen voor de duurtijd van deze collectieve arbeidsovereenkomst.Art. 10.  § 1. De ondertekenende vakorganisaties hebben het recht op een dubbel van het geregistreerde contract van de betaalde voetballer op te vragen bij de KBVB, de Pro League of de betrokken voetballiga in zoverre zij daartoe gemandateerd worden door de speler.  § 2. De ondertekenende vakorganisaties hebben het recht de bijdragen in de groepsverzekering voor de betaalde voetballer op te vragen bij de club-werkgever of de desbetreffende verzekeringsmaatschappij waar de groepsverzekering is afgesloten in zoverre zij daartoe gemandateerd worden door de speler. Art. 11.  Indien een groepsverzekering voorzien is, dient dit berekend te worden binnen het wettelijk kader. De desbetreffende groepsverzekeringsbijdrage, die loon is, dient minimaal berekend te worden op de respectievelijke minimumlonen voor deeltijdse werknemers, voltijdse werknemers en werknemers buiten de Europese Economische Ruimte. Deze bepaling geldt enkel voor de arbeidscontracten vanaf 2018-2019. Art. 12.  § 1. Er kunnen wedstrijdpremies voorzien worden voor competitiewedstrijden, vriendschappelijke wedstrijden, bekerwedstrijden, eindrondewedstrijden en wedstrijden georganiseerd door de UEFA. Er kan een onderscheid gemaakt worden per categorie en per competitiefase. Club en speler zijn echter volledig vrij om te bepalen of er voor een bepaalde categorie wedstrijden al dan niet premies verschuldigd zijn.  § 2. Indien er premies worden overeengekomen voor bepaalde wedstrijden dienen deze voldoende bepaalbaar te zijn. Dit houdt in dat per categorie (zie § 1) telkens dient aangegeven te worden of en welke premie er verschuldigd is. Indien er geen premie verschuldigd is voor een bepaalde categorie of subcategorie, dient dit ook zo aangegeven te worden. Wanneer voor een bepaalde categorie van wedstrijden de premies onvoldoende bepaalbaar zijn (of niet aangegeven is dat er geen verschuldigd zijn), geldt een vaste premie van 80,78 EUR per punt per officiële wedstrijd in de competitie en van 242,35 EUR per wedstrijd voor de club die doorstoot in de Beker van België vanaf de 1/16de finales waarbij de speler op het wedstrijdblad stond ingeschreven. HOOFDSTUK VII. - Contractstabiliteit Art. 13.  De contracten van bepaalde duur tussen clubs en betaalde voetballers worden afgesloten voor maximum 5 jaar en minimum voor een periode die loopt tot het einde van het seizoen (30 juni) in de loop waarvan ze getekend worden. Bij niet-naleving van het minimum is de speler gerechtigd op de betaling tot het einde van dat seizoen. Art. 14.  § 1. De speler van wie het contract afloopt overeenkomstig de contractuele bepalingen is vrij om een arbeidsovereenkomst af te sluiten met een andere club naar zijn keuze. De onderhandelingsvrijheid van de speler kan dan ook op geen enkele wijze belemmerd worden.  § 2. Betaalde voetballers die einde contract zijn worden vrijgesteld van arbeidsprestaties met behoud van loon vanaf de eerste dag van de maand juni waarin het contract verstrijkt, behoudens indien er nog officiële matchen van de eerste ploeg zijn voorzien in de kalender. Deze bepaling geldt eveneens indien een speler wiens contract datzelfde seizoen afloopt nog meetraint met een andere club waarmee hij een arbeidsovereenkomst afsloot ingaande het volgend seizoen.  § 3. Spelers (1) waarvan hun contract afloopt op het einde van het seizoen of (2) getransfereerd worden vóór het einde van het seizoen en wiens arbeidscontract met hun nieuwe club begint te lopen vanaf 1 juli van het daaropvolgende seizoen, kunnen met hun nieuwe club deelnemen aan de trainingen en de trainingswedstrijden vanaf 10 juni van het lopende seizoen, mits de voorafgaande ondertekening van de Trainingsovereenkomst, afzonderlijk van de overeenkomst voor betaalde sportbeoefenaar. Deze periode van maximaal 20 dagen ("Trainingsperiode") wordt niet aanzien als het begin van uitvoering van de nieuwe overeenkomst voor betaalde sportbeoefenaar. De Trainingsovereenkomst is geen proefbeding en is enkel geldig indien een overeenkomst voor betaalde sportbeoefenaar werd afgesloten. De oude club van de speler kan zich niet verzetten tegen het afsluiten van de Trainingsovereenkomst en blijft schuldenaar van de verschuldigde sommen tot op de vervaldag van 30 juni. De speler voor clubs uit 1A en 1B (Pro League) zal gedurende de Trainingsperiode recht hebben op een forfaitaire trainingsvergoeding, niet onderworpen aan de groepsverzekering, van 1 077,13 EUR bruto per begonnen week, die betaald zal worden door de nieuwe club van de speler. § 4. Zonder afbreuk te doen aan de bepalingen van de wet van 24 februari 1978 en haar uitvoeringsbesluiten, verbinden de partijen er zich toe om geen voortijdige verbreking van arbeidsovereenkomsten te begaan, tenzij in geval van gegronde redenen te beoordelen door de rechter of de bevoegde instanties.  § 5. De betaalde voetbalspeler toegewezen aan de kern van het eerste elftal moet maximale kansen krijgen om te spelen en te trainen in deze kern. De minimale voorwaarden betreffende training en trainingsfaciliteiten waaraan de club moet voldoen zijn : - Trainingen onder leiding van een gediplomeerde coach die deel uitmaakt van de technische staf. Kwalitatieve trainingen zijn noodzakelijk om de carrière van de betrokken speler niet te hypothekeren; - De trainingen dienen plaats te vinden binnen de in het arbeidsreglement voorziene arbeidstijd; - Groepstrainingen bij een spelerskern waarvoor hij gekwalificeerd is om wedstrijden te spelen. Een individueel programma kan worden opgelegd in geval van blessure, revalidatie en, voor zover gestaafd door de club, wegens fysieke achterstand; - Dezelfde voorzieningen aangaande kledij te waarborgen. Bovendien zal de club eenzelfde of vergelijkbare kleedkamer voorzien. Geen substantiële wijziging van de trainingsvoorwaarden van de betaalde sportbeoefenaar kan als disciplinaire maatregel worden toegestaan tenzij de speler hiervan in kennis wordt gesteld op de wijze en volgens de procedure zoals voorzien in deze collectieve arbeidsovereenkomst aangaande het opleggen van boetes of sancties. Een miskenning door de club van de in artikel 14, § 5 toegekende rechten aan de speler kan leiden tot schade in hoofde van die speler. De exacte omvang van deze schade dient te worden bepaald door de rechter of de bevoegde instanties. HOOFDSTUK VIII. - Contractuele clausules Art. 15.  De optie is een contractuele clausule die specifiek is aan de voetbalsector. De partijen verklaren dat een eenzijdige optie niet rechtsgeldig is. De optieclausule is echter niet als eenzijdig te beschouwen indien aan alle onderstaande voorwaarden is voldaan :  § 1. Vormvereisten De optie moet schriftelijk worden opgesteld en integraal deel uitmaken van het contract, voor iedere werknemer (betaalde sportbeoefenaar) afzonderlijk en ten laatste op het ogenblik van de indiensttreding van de werknemer. Het contract moet bij de ondertekening verplicht de duurtijd, de toepasselijke salarisverhoging en de uiterste datum van de optielichting vermelden (ten laatste op 31 maart). Bij een loutere verwijzing naar de toepasselijke collectieve arbeidsovereenkomst zal de optielichting gepaard gaan met een verhoging van 20 pct. van de vaste bezoldiging, zonder dat deze verhoging meer dan 25 500 EUR moet bedragen.  § 2. Duurtijd Maximale duurtijd van het contract De maximale duurtijd van het contract, met inbegrip van de duurtijd van een eventuele optie in de overeenkomst, kan nooit langer bedragen dan een duurtijd van : - 5 jaar voor spelers boven 18 jaar; - 5 jaar voor spelers onder 18 jaar, met een loon van meer dan 25 000 EUR op seizoensbasis; - 3 jaar voor spelers onder de 18 jaar, met een loon die gelijk is of minder bedraagt dan 25 000 EUR op seizoensbasis. Een contract ingaand tijdens het lopend seizoen wordt voor de bepaling van de contractduur gelijkgesteld met één volledig seizoen. Dit geldt niet voor de Trainingsovereenkomst bepaald in artikel 14, § 3. Maximale duurtijd van de optie De duurtijd van een optie opgenomen in een overeenkomst, kan nooit langer bedragen dan de effectieve contractuele duurtijd bedongen in de overeenkomst (bijvoorbeeld wanneer een speler een contract tekent met een duurtijd van 2 jaar, kan de optie maximaal 2 jaar bedragen). Op deze regel bestaan 2 uitzonderingen : - Contracten afgesloten in de loop van het seizoen voor een duurtijd tot het einde van het seizoen, mogen een optie bevatten ten belope van 1 jaar. Bijvoorbeeld, speler X tekent contract met een duurtijd van 6 maanden tijdens de wintertransferperiode, dan mag een optie van 1 jaar in het contract worden ingeschreven;- Contracten afgesloten met zelfopgeleide jeugdspelers (drie al of niet aaneengesloten seizoenen aangesloten bij de club als amateur of als contractspeler - eventueel ter beschikking gesteld aan een andere club) jonger dan 18 jaar, mogen een optie bevatten ten belope van 2 jaar. Bijvoorbeeld, speler X, 15 jaar, tekent contract met een duurtijd van 1 jaar, dan mag een optie van 2 jaar in het contract worden ingeschreven. Onder geen beding kunnen de voorgaande 2 uitzonderingen afbreuk doen aan de maximale duurtijd van een contract van respectievelijk 5 en 3 jaar zoals bepaald in artikel 15, § 2, eerste lid van de collectieve arbeidsovereenkomst.  § 3. Salarisverhoging De optielichting gaat minstens gepaard met een verhoging van 15 pct. van de vaste bezoldiging en 5 pct. van de wedstrijd- en/of selectiepremies of 20 pct. van de vaste bezoldiging. Voor de berekening van de vaste bezoldiging zal, indien een tekenpremie werd afgesloten bij de originele overeenkomst, deze tekenpremie pro rata temporis bij de vaste bezoldiging moeten worden toegevoegd. De verhoging van het salaris moet in geen geval 25 500 EUR per seizoen overschrijden. In ieder geval is bij optielichting het gewaarborgd inkomen voor voltijds betaalde sportbeoefenaars verschuldigd.  § 4. Optielichting De optie moet door de club gelicht worden bij aangetekend schrijven ten laatste op 31 maart van het seizoen waarin het contract normaal verstrijkt, de datum van poststempel rechtsgeldig zijnde. Een meerjarig optiebeding kan niet opgesplitst worden en moet bijgevolg steeds in zijn geheel gelicht worden. De club kan geen optie lichten en/of de speler kan niet verplicht worden de optielichting na te leven als de club op 15 maart van het lopend seizoen een loonachterstand heeft van twee maanden of meer voor de speler wiens optie gelicht wordt. De speler dient de niet-naleving per aangetekend schrijven te bevestigen aan de club vóór 16 april van het lopende seizoen.  § 5. Sancties Sanctie bij niet-naleving : de speler kan de nietigheid inroepen en het contract als beëindigd beschouwen ofwel de duur van de optie bevestigen met toepassing van de in § 4 voorziene salarisverhoging. In geval van betwisting wordt de zaak verplicht voorgelegd aan de bevoegde rechtbank of arbitragecommissie voor de betaalde voetballer. Art. 16.  Het risico van degradatie is een inherent risico specifiek aan de sportsector. Toch zijn de, partijen akkoord om dit risico te beperken en in geval van degradatie om sportieve redenen een salarisvermindering te aanvaarden indien aan alle onderstaande voorwaarden is voldaan. De zuiver ontbindende voorwaarde bij degradatie wordt door de partijen niet aanvaard en de meest benadeelde partij kan de nietigheid ervan inroepen.  § 1. Toepassingsgebied Onderstaande regeling geldt enkel voor de voetbalclubs en voor spelers die een deeltijdse of voltijdse arbeidsovereenkomst voor betaalde sportbeoefenaar hebben ondertekend.  § 2. Vormvereisten De salarisvermindering bij degradatie moet schriftelijk worden opgesteld en integraal deel uitmaken van het contract, voor iedere werknemer (betaalde sportbeoefenaar) afzonderlijk en ten laatste op het ogenblik van de indiensttreding van de werknemer. Het contract moet verplicht de toepasselijke salarisvermindering vermelden, al dan niet beperkt tot 10 pct.  § 3. Salarisvermindering De salarisvermindering bedraagt maximaal 20 pct. van de vaste bezoldiging en 20 pct. van de wedstrijd- en/of selectiepremies mits het gemiddeld minimum maandinkomen wordt gegarandeerd. Ingeval in het contract een salarisvermindering bij degradatie wordt voorzien, heeft de speler op het ogenblik van de effectieve degradatie de keuze om ofwel de overeengekomen salarisvermindering te aanvaarden ofwel zijn vrijheid te vragen ingaand vanaf het seizoen volgend op de degradatie en dit zonder verder financiële verplichtingen tussen beide partijen vanaf het seizoen volgend op de degradatie. De speler die gebruik wenst te maken van de mogelijkheid om zijn vrijheid aan te vragen behoudt uiteraard zijn financiële aanspraken voor het volledig lopende seizoen en moet bij aangetekend schrijven zijn vrijheid aanvragen vanaf 15 mei en ten laatste op 7 juni, de datum van de poststempel rechtsgeldig zijnde, van het seizoen waarin de club degradeert.Na deze termijn wordt de speler geacht de salarisvermindering te hebben aanvaard. Ingeval in het contract een salarisvermindering omwille van de gradatie wordt voorzien die beperkt blijft tot 10 pct. van de vaste bezoldiging en 10 pct. van de wedstrijd- en/of selectiepremies, is de mogelijkheid voor de speler om zijn vrijheid aan te vragen niet voorzien, tenzij partijen contractueel anders overeenkomen. Voor spelers die behoren tot een U23-team is de referentie de moederclub van de speler en niet het U23-team. De salarisvermindering zelf gaat in vanaf 1 juli volgend op het seizoen waarin de club sportief degradeert.  § 4. Sancties Sancties bij niet-naleving : de clausule salarisvermindering is nietig en de speler kan ofwel de overeengekomen contractduur respecteren met toepassing van de bestaande loonvoorwaarden zonder salarisvermindering, ofwel zijn contract als beëindigd beschouwen. In geval van betwisting wordt de zaak voorgelegd aan de bevoegde rechtbank of de arbitragecommissie voor de betaalde voetballer. Art. 17.  Bij stijging naar een hogere afdeling zullen de vaste bezoldiging en de wedstrijd- en selectiepremies voor de betaalde voetballer met minimaal 10 pct. verhoogd worden, tenzij een verhoging van minimaal 10 pct. reeds contractueel werd vastgelegd. Voor spelers die behoren tot een U23-team is de referentie de moederclub van de speler en niet het U23-team. HOOFDSTUK IX. - Arbeidsongeschiktheid Art. 18.  De club kent de speler kosteloze medische bijstand toe door bemiddeling van haar medische staf en door haar aangeduide externe specialisten. Het staat de speler vrij geneesheren of specialisten van zijn keuze te raadplegen en zich door hen te laten verzorgen, op eigen kosten en risico's met name wat betreft een langdurige onbeschikbaarheid. De club neemt in geen geval de kosten of aansprakelijkheid ten laste van behandelingen, medische verzorging en in het algemeen, alle andere ingrepen dan deze welke door de geneesheren van de club of door haar aangeduide externe specialisten worden verstrekt of toegelaten. Art. 19.  Werkgevers/clubs verbinden zich ertoe in geval van arbeidsongeschiktheid wegens arbeidsongeval voor de eerste maand van de ongeschiktheid aan de speler het gewaarborgd loon uit te betalen, vanaf de tweede tot en met de zesde maand van de ongeschiktheid het contractuele vast loon en vanaf de zevende tot en met de twaalfde maand bovenop de tussenkomst van de arbeidsongevallenverzekeraar een aanvullende vergoeding zodat het contractueel vast loon van de betrokken speler wordt bereikt met een maximale bijpassing van 2 000 EUR per maand. Indien tijdens de duur van de arbeidsongeschiktheid de overeengekomen contractuele duurtijd verstrijkt, waarborgt de club bijkomend aan de speler het contractueel vast loon gedurende maximum twee maanden na het einde van de arbeidsovereenkomst zonder het totale maximum van zes maanden te overschrijden en valt de speler nadien terug op de wettelijke tussenkomst van de arbeidsongevallenverzekeraar. Indien tijdens de periode van arbeidsongeschiktheid een nieuw contract met een andere werkgever wordt gesloten, gaat er een nieuwe periode van arbeidsongeschiktheid in, met inbegrip van het gewaarborgd loon. Art. 20.  Werkgevers/clubs verbinden zich ertoe in het geval van arbeidsongeschiktheid wegens ziekte of ongeval voor de eerste maand van de ongeschiktheid aan de speler het gewaarborgd loon uit te betalen en voor de tweede maand (1A en 1B) en derde maand (enkel 1A) van de ongeschiktheid een aanvullende vergoeding bestaande uit het verschil tussen het contractuele vast loon en de tussenkomst van het ziekenfonds. Ingeval de speler geen recht heeft op tussenkomst van het ziekenfonds omwille van het feit dat hij nog een andere beroepsactiviteit uitoefent, is de club enkel gehouden tot de "fictieve" opleg en niet tot de betaling van het bedrag dat overeenstemt met de tussenkomst van het ziekenfonds zelf. Dit geldt niet wanneer de speler aangesloten is bij een ziekenfonds, maar niet uitkeringsgerechtigd is omwille van de te doorlopen wachttijd. Indien tijdens de duur van de arbeidsongeschiktheid de overeengekomen contractuele duurtijd verstrijkt, blijft de hierboven vermelde regeling voor de eerste twee maanden van de arbeidsongeschiktheid onverkort van toepassing en valt de speler nadien volledig terug op de wettelijke tussenkomst van het ziekenfonds. Indien tijdens de periode van arbeidsongeschiktheid een nieuw contract met een andere werkgever wordt gesloten, gaat er een nieuwe periode van arbeidsongeschiktheid in met inbegrip van het gewaarborgd loon.Art. 21.  De clubs zijn verplicht om hun arbeidsongevallenverzekering al of niet bij hun wetsverzekeraar, uit te breiden tot ongevallen overkomen aan hun spelers die ter beschikking gesteld worden aan de nationale selectie, behoudens gelijkwaardige dekking door de respectievelijke federatie. HOOFDSTUK X. - Spelersafvaardiging Art. 22.  § 1. De werkgevers/clubs erkennen dat de spelers vertegenwoordigd worden door een spelersvakbond.  § 2. Per werkgever/club wordt er, bij het begin van elk seizoen, een spelersraad gehouden die uit haar rangen minstens twee spelersafgevaardigden kiest.  § 3. De vertegenwoordigers van de spelersvakbonden kunnen uitgenodigd worden op deze spelersraad en krijgen het recht om de spelers in te lichten over de vakbondswerking.  § 4. Het mandaat van spelersafgevaardigde mag geen aanleiding geven tot enig voordeel noch nadeel voor degene die het uitoefent.  § 5. Een vertegenwoordiger van de spelersvakbond zal mondeling of schriftelijk kunnen overgaan tot alle mededelingen die nuttig zijn voor de spelers.  § 6. De werkgevers verklaren zich akkoord dat er op de installaties van de club voorlichtingsvergaderingen voor de spelers kunnen worden gehouden door de vertegenwoordigers van een spelersvakbond na voorafgaande kennisgeving aan de betrokken club. HOOFDSTUK XI. - Tijdelijk uitlenen van spelers Art. 23.  Het uitlenen van spelers tussen Belgische clubs is mogelijk onder de voorwaarden zoals bepaald in artikel 24 en volgende van deze collectieve arbeidsovereenkomst. Een binnenlandse uitleenbeurt die voldoet aan de voorwaarden zoals bepaald in artikel 24 kwalificeert niet als een terbeschikkingstelling in de zin van de wet van 24 juli 1987 betreffende de tijdelijke arbeid, de uitzendarbeid en het ter beschikking stellen van werknemers ten behoeve van gebruikers. Art. 24.  De partijen aanvaarden dat Belgische clubs spelers kunnen uitlenen onder de volgende cumulatieve voorwaarden : - De uitlenende club en de speler sluiten een schriftelijke bijlage tot schorsing van de tussen hen bestaande arbeidsovereenkomst. Deze bijlage moet door beide partijen ondertekend worden uiterlijk op het ogenblik dat de schorsing van de arbeidsovereenkomst een aanvang neemt. Deze bijlage bevat de volgende vermeldingen : 1. de duurtijd van de schorsing; 2. indien van toepassing, de omstandigheden waarin de club en de speler voortijdig een einde kunnen maken aan de schorsing van de arbeidsovereenkomst en de toepasselijke modaliteiten van dergelijke voortijdige beëindiging; 3. de uitdrukkelijke vermelding dat het gaat om een tijdelijke schorsing van de arbeidsovereenkomst overeenkomstig hoofdstuk XI van deze collectieve arbeidsovereenkomst; 4. de uitdrukkelijke vermelding dat de wederzijdse rechten en verplichtingen die voortvloeien uit de toepasselijke wettelijke en contractuele bepalingen, met inbegrip van de rechten en verplichtingen zoals uiteengezet in de arbeidsovereenkomst, integraal geschorst worden gedurende de duurtijd van de schorsing; - De ontlenende club en de speler sluiten een arbeidsovereenkomst van bepaalde tijd overeenkomstig de toepasselijke wettelijke en sectorale bepalingen. Deze arbeidsovereenkomst moet door beide partijen ondertekend worden uiterlijk op het ogenblik dat de arbeidsovereenkomst een aanvang neemt. Deze arbeidsovereenkomst vermeldt uitdrukkelijk dat het gaat om een arbeidsovereenkomst afgesloten overeenkomstig hoofdstuk XI van deze collectieve arbeidsovereenkomst. Indien hierover geen akkoord wordt gevonden binnen de 7 werkdagen na de schorsing van de arbeidsovereenkomst tussen de speler en de uitlenende club, zal de schorsing van de overeenkomst tussen de uitlenende club en de speler van rechtswege nietig worden verklaard; - Gedurende de schorsing van de arbeidsovereenkomst oefent de uitlenende club op geen enkele wijze enig werkgeversgezag uit over de speler. Gedurende de schorsing van de arbeidsovereenkomst wordt het werkgeversgezag uitsluitend uitgeoefend door de ontlenende club op basis van de arbeidsovereenkomst afgesloten tussen de ontlenende club en de speler. Art. 25.  Evenwel zal de uitlenende club de speler een bijkomende premie betalen ter vergoeding van de voor de uitlenende club bewezen prestaties die berekend wordt als het verschil tussen 75 pct. van de totale brutomaandlonen (exclusief werkgeversbijdragen) zou verdienen bij de uitlenende club in vergelijking met de totale brutomaandlonen dat de speler zal verdienen bij de ontlenende club.Art. 26.  De uitlenende club en de speler kunnen overeenkomen om een tijdelijke uitleenbeurt te verlengen. Dergelijke verlenging moet voldoen aan de voorwaarden zoals vermeld in hoofdstuk XI van deze collectieve arbeidsovereenkomst, met inbegrip van de verplichting om de respectievelijke vakorganisaties op de hoogte te brengen van de verlenging, overeenkomstig artikel 26 van deze collectieve arbeidsovereenkomst. Art. 27.  De uitlenende club brengt de respecti</t>
         </is>
       </c>
     </row>
@@ -2904,29 +2899,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2025003723</t>
+          <t>2025000796</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>23 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>20 juni 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 28 september 2009 tot vaststelling van de algemene voorwaarden waaraan de banken voor menselijk lichaamsmateriaal, de intermediaire structuren en de productie-instellingen moeten voldoen om te worden erkend en tot wijziging van het koninklijk besluit van 9 januari 2018 betreffende de biobanken. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 18 oktober 2024, gesloten in het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap, betreffende de vaststelling van de loon-, arbeids- en loonindexeringsvoorwaarden voor het personeel van de diensten voor gezins- en bejaardenhulp gesubsidieerd door het Waalse Gewest (1)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-23&amp;numac_search=2025003723&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003723=77&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025000796&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025000796=77&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 20 juni 2024 tot wijziging van het koninklijk besluit van 28 september 2009 tot vaststelling van de algemene voorwaarden waaraan de banken voor menselijk lichaamsmateriaal, de intermediaire structuren en de productie-instellingen moeten voldoen om te worden erkend en tot wijziging van het koninklijk besluit van 9 januari 2018 betreffende de biobanken (Belgisch Staatsblad van 1 juli 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALAGENTUR FÜR ARZNEIMITTEL UND GESUNDHEITSPRODUKTE20. JUNI 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 28. September 2009 zur Festlegung der allgemeinen Bedingungen, die die Banken für menschliches Körpermaterial, die Zwischenstrukturen und die Produktionseinrichtungen im Hinblick auf ihre Zulassung erfüllen müssen, und zur Abänderung des Königlichen Erlasses vom 9. Januar 2018 über BiobankenPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund der Verfassung, des Artikels 108;Aufgrund des Gesetzes vom 20. Juli 2006 über die Schaffung und die Arbeitsweise der Föderalagentur für Arzneimittel und Gesundheitsprodukte, des Artikels 4 § 1 Absatz 2 und 3 Nr. 6 Buchstabe a) vierter Gedankenstrich;Aufgrund des Gesetzes vom 19. Dezember 2008 über die Gewinnung und Verwendung menschlichen Körpermaterials im Hinblick auf medizinische Anwendungen beim Menschen oder zu wissenschaftlichen Forschungszwecken, der Artikel 7 § 2 Absatz 2, 10 § 7 Absatz 1 und 2, ersetzt durch das Gesetz vom 18. Mai 2022, und 22 § 1 Absatz 2, ersetzt durch das Gesetz vom 19. März 2013;Aufgrund des Königlichen Erlasses vom 28. September 2009 zur Festlegung der allgemeinen Bedingungen, die die Banken für menschliches Körpermaterial, die Zwischenstrukturen und die Produktionseinrichtungen im Hinblick auf ihre Zulassung erfüllen müssen;Aufgrund des Königlichen Erlasses vom 9. Januar 2018 über Biobanken;Aufgrund der Stellungnahme der Finanzinspektion vom 20. März 2024;Aufgrund des Einverständnisses des Staatssekretärs für Haushalt vom 8. April 2024;Aufgrund der Auswirkungsanalyse beim Erlass von Vorschriften, die gemäß den Artikeln 6 und 7 des Gesetzes vom 15. Dezember 2013 zur Festlegung verschiedener Bestimmungen in Sachen administrative Vereinfachung durchgeführt worden ist;Aufgrund der Gutachten Nr. 66.450/1/V und Nr. 76.240/3 des Staatsrates vom 2. September 2019 beziehungsweise 24. Mai 2024, abgegeben in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Auf Vorschlag des Ministers der Volksgesundheit und aufgrund der Stellungnahme der Minister, die im Rat darüber beraten haben,Haben Wir beschloßen und erlassen Wir:Artikel 1 - In Artikel 2 § 2 des Königlichen Erlasses vom 28. September 2009 zur Festlegung der allgemeinen Bedingungen, die die Banken für menschliches Körpermaterial, die Zwischenstrukturen und die Produktionseinrichtungen im Hinblick auf ihre Zulassung erfüllen müssen, werden in Nr. 7, eingefügt durch den Königlichen Erlass vom 31. Juli 2017, zwischen den Wörtern "die Bank für menschliches Körpermaterial" und den Wörtern "oder die Produktionseinrichtung," die Wörter ", die Zwischenstruktur für menschliches Körpermaterial" eingefügt.Art. 2 - Artikel 3 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 31. Juli 2017, wird wie folgt abgeändert:1. In Absatz 2 Nr. 2 wird zwischen den Wörtern "menschlichem Körpermaterial" und den Wörtern "in Zusammenarbeit mit einer Bank für menschliches Körpermaterial" das Wort "gegebenenfalls" eingefügt.2. In Absatz 3 werden zwischen den Wörtern "die Banken für menschliches Körpermaterial" und den Wörtern "und die Produktionseinrichtungen," die Wörter ", die Zwischenstrukturen für menschliches Körpermaterial" eingefügt.Art. 3 - In Artikel 4 Absatz 4 desselben Erlasses, eingefügt durch den Königlichen Erlass vom 31. Juli 2017, werden die Wörter "oder als Produktionseinrichtung" durch die Wörter ", als Zwischenstruktur für menschliches Körpermaterial oder als Produktionseinrichtung" ersetzt.Art. 4 - In Artikel 5/1 desselben Erlasses, eingefügt durch den Königlichen Erlass vom 31. Juli 2017, werden in § 1 Absatz 1 zwischen den Wörtern "Die Banken für menschliches Körpermaterial" und den Wörtern "und die Produktionseinrichtungen," die Wörter ", die Zwischenstrukturen für menschliches Körpermaterial" eingefügt.Art. 5 - In Artikel 6 § 1 Absatz 1 desselben Erlasses, abgeändert durch den Königlichen Erlass vom 31. Juli 2017, wird Nr. 2 wie folgt ersetzt:"2. wenn es sich bei der Einrichtung um eine Zwischenstruktur handelt: die in den Artikeln 3 § 4 Absatz 8, 8 §  1/1 Absatz 1 und 8 § 2 Absatz 3 des Gesetzes erwähnten Zusammenarbeitsabkommen, die diese mit Banken für menschliches Körpermaterial abgeschlossen hat,".Art. 6 - Artikel 8 desselben Erlasses, abgeändert durch den Königlichen Erlass vom 31. Juli 2017 und den Königlichen Erlass vom 9. Januar 2018, wird wie folgt abgeändert:1. In § 1 wird das Wort "Erteilung" durch das Wort "Verlängerung" ersetzt.2. In § 1 werden zwischen den Wörtern "einführende Bank für menschliches Körpermaterial" und den Wörtern "oder einführende Produktionseinrichtung" die Wörter ", einführende Zwischenstruktur für menschliches Körpermaterial" eingefügt.3. In § 3 Absatz 2 Nr. 12 werden die Wörter "für Zelltherapien bestimmtes" aufgehoben.4. Paragraph 5 wird wie folgt ersetzt:" § 5 - Ist das menschliche Körpermaterial ganz oder teilweise zur Zubereitung eines im Gesetz vom 25. März 1964 über Humanarzneimittel erwähnten Arzneimittels bestimmt, wird in dem in § 1 erwähnten Erlass angegeben, ob es sich um ein Gentherapeutikum, ein somatisches Zelltherapeutikum, ein Tissue-Engineering-Produkt, ein kombiniertes Arzneimittel für neuartige Therapien oder ein anderes Arzneimittel handelt."Art. 7 - In Artikel 9 Absatz 1 desselben Erlasses werden zwischen den Wörtern "der Artikel" und den Wörtern "5, 6, 7 § 1," die Wörter "3 § 4 Absatz 7 und 8, 4 §§ 1 und 2," eingefügt.Art. 8 - Artikel 11 desselben Erlasses, abgeändert durch den Königlichen Erlass vom 25. April 2014, wird wie folgt abgeändert:1. Paragraph 1 wird aufgehoben.2. Paragraph 5 Absatz 3 wird aufgehoben.Art. 9 - In Anlage 3 Punkt 2 zum selben Erlass werden die Wörter "Arten menschlichen Körpermaterials" wie folgt ergänzt: "sowie gegebenenfalls Vermerk, dass das Material ganz oder teilweise zur Zubereitung eines Gentherapeutikums, eines somatischen Zelltherapeutikums, eines Tissue-Engineering-Produkts, eines kombinierten Arzneimittels für neuartige Therapien oder eines anderen Arzneimittels bestimmt ist".Art. 10 - [Abänderung des Königlichen Erlasses vom 9. Januar 2018 über Biobanken]Art. 11 - Der für die Volksgesundheit zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 20. Juni 2024PHILIPPEVon Königs wegen:Der Minister der VolksgesundheitF. VANDENBROUCKE 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 18 oktober 2024, gesloten in het Paritair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap, betreffende de vaststelling van de loon-, arbeids- en loonindexeringsvoorwaarden voor het personeel van de diensten voor gezins- en bejaardenhulp gesubsidieerd door het Waalse Gewest.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 7 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Subcomité voor de diensten voor gezins- en bejaardenhulp van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige GemeenschapCollectieve arbeidsovereenkomst van 18 oktober 2024Vaststelling van de loon-, arbeids- en loonindexeringsvoorwaarden voor het personeel van de diensten voor gezins- en bejaardenhulp gesubsidieerd door het Waalse Gewest (Overeenkomst geregistreerd op 22 november 2024 onder het nummer 190712/CO/318.01)HOOFDSTUK I. - ToepassingsgebiedArtikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werknemers en werkgevers van de diensten voor gezins- en bejaardenhulp die erkend en gesubsidieerd zijn door het Waalse Gewest die vallen onder de bevoegdheid van het Paritair subcomité voor de diensten voor gezins- en bejaardenhulp van de Franse Gemeenschap, het Waalse Gewest en de Duitstalige Gemeenschap. § 2. Voor de toepassing van deze collectieve arbeidsovereenkomst, wordt onder "werknemer" verstaan : het arbeiders- en bediendenpersoneel, zonder onderscheid van geslacht, in dienst genomen in het kader van een arbeidsovereenkomst in de zin van de wet van 3 juli 1978.In deze collectieve arbeidsovereenkomst wordt het mannelijk geslacht gebruikt als soortnaam, enkel om de tekst niet te verzwaren. § 3. Deze collectieve arbeidsovereenkomst geeft uitvoering aan het intersectoraal tripartiete raamakkoord van de Waalse non-profitsector 2021-2024 van 26 mei 2021.Art. 2. De bepalingen van deze collectieve arbeidsovereenkomst stellen de regels vast die toepasbaar zijn op alle werknemers opgenomen in artikel 1, en bepalen enkel de minimumlonen, waarbij alle vrijheid aan de partijen wordt gelaten om overeen te komen over gunstigere voorwaarden voor de werknemers. Zij mogen bovendien geen afbreuk doen aan de bepalingen die gunstiger zijn voor de werknemers, daar waar een dergelijke situatie bestaat.Art. 3. De opsomming van de beroepen die gerangschikt zijn in de verschillende hierna vastgestelde categorieën moet als voorbeeld en als niet-beperkend worden beschouwd.Art. 4. Technisch personeel (3 categorieën)Eerste categorie- OnderhoudstechnicusWerknemer wiens functie bestaat in het reinigen van de lokalen van de diensten.ProfielBlijk geven van een algemene technische basiskennis betreffende het huishoudelijk onderhoud.StatuutArbeiderTweede categorie- Polyvalent arbeider, chauffeura) Polyvalent arbeiderWerknemer wiens functie erin bestaat om uitsluitend eenvoudige manuele en technische werkzaamheden uit te voeren, teneinde het levensmilieu van de hulpbehoevenden te verbeteren:1. de lokalen waar de gezinnen, de bejaarden, gehandicapten en/of zieken wonen inrichten en/of aanpassen;2. het personen alarmeringsmateriaal plaatsen, onderhouden;3. het sanitair materiaal vervoeren en onderhouden.De arbeider zal op geen enkelogenblik een privé-onderneming vervangen. De polyvalente arbeider wordt ertoe aangezet om:1. nauw samen te werken met de verantwoordelijke;2. zich in te passen in een interdisciplinaire hulp- en zorgarbeid en zich te wenden tot de verantwoordelijke van de dienst of tot de coördinator voor alle handelingen die buiten zijn bevoegdheid vallen;3. deelnemen aan de opleidingen die voor hem bestemd zijn.ProfielBij gebreke van een bestaande reglementering ter zake, blijk geven van :- een algemene en technische basiskennis;- kwaliteiten inzake openheid en werken in ploegverband;- aanpassingsvermogen om zich in de context van het dagelijks leven van de rechthebbenden te verplaatsen;- interpersoonlijke vaardigheden.StatuutArbeiderb) ChauffeurWerknemer wiens functie bestaat in het besturen van de voertuigen die bestemd zijn voor het vervoer van personen van hun woonplaats naar een ziekenhuisinstelling of een gezondheidsdienst. De functie wordt gekenmerkt door :1. de ter beschikking gestelde voertuigen besturen, met naleving van de wegcode en in alle veiligheid, en als een "goede huisvader" toe te zien op het algemeen onderhoud ervan;2. nauw samenwerken met de dienstverantwoordelijke;3. zich inpassen in een interdisciplinaire hulp- en zorgarbeid en zich wenden tot de verantwoordelijke van de dienst of tot de coördinator voor alle handelingen die buiten zijn bevoegdheid vallen;4. deelnemen aan de opleidingen die voor hem bestemd zijn.ProfielBij gebreke van een reglementering ter zake :- in bezit zijn van het diploma van hulpverlener en van het passende rijbewijs - de medische selectie hebben die noodzakelijk is voor de activiteit;- blijk geven van kwaliteiten inzake openheid en werken in ploegverband;- blijk geven van aanpassingsvermogen om zich in de context van het dagelijks leven van de rechthebbenden te verplaatsen;- blijk geven van interpersoonlijke vaardigheden.StatuutArbeiderDerde categorie- Sociale huishoudhulpWerknemer wiens functie erin bestaat om uitsluitend huishoudelijke werkzaamheden uit te voeren. Zij maken het voor de hulpbehoevenden mogelijk om thuis te blijven in een verzorgd en net kader. Deze functie wordt gekenmerkt door :1. onderhouden, handhaven en verbeteren van de hygiëne van de woning;2. zich integreren in een ploeg van huishoudhulpen en in nauwe samenwerking werken met de sociaal assistente of de verantwoordelijke die de ploeg van huishoudhulpen omkadert waarvan zij deel uitmaakt;3. zich inpassen in een interdisciplinaire hulp- en zorgarbeid en zich wenden tot de verantwoordelijke van de dienst of tot de coördinator voor alle handelingen die buiten zijn bevoegdheid vallen;4. deelnemen aan de opleidingen die voor hem bestemd zijn.ProfielBij gebreke van een bestaande reglementering ter zake, blijk geven van :- vaardigheid op het gebied van huishoudelijke taken;- kwaliteiten inzake openheid en werken in ploegverband;- aanpassingsvermogen om zich in de context van het dagelijks leven van de rechthebbenden te verplaatsen;- interpersoonlijke vaardigheden.StatuutArbeiderArt. 5. Administratief personeel (4 categorieën)Eerste categorie- KlerkBedienden waarvan de functie wordt gekenmerkt door :1. de gelijkstelling ofwel door onderwijs, ofwel in de praktijk, van kennis die overeenstemt met de 3 jaren van het lager secundair onderwijs;2. het uitvoeren van eenvoudige, weinig gediversifieerde taken waarvan de verantwoordelijkheid beperkt wordt door direct en constant toezicht;3. een beperkte assimilatietijd die het mogelijk maakt om een bekwaamheid te verwerven binnen een bepaalde tijd.Voorbeelden :Administratief- telefonist van de centrale die op eigen initiatief eenvoudige antwoorden moet verstrekken aan de correspondenten of telefonist van een coördinatiecentrum voor thuiszorg en -diensten - archivist-klasseerder die blijk moet geven van beoordelings- en onderscheidingsvermogen;- ervaren typist die 40 woorden/minuut kan typen, een correcte spelling heeft en zijn werk goed kan opmaken;- bediende (m/v) belast met eenvoudig redactioneel werk, rekenwerk, invoeren van lijsten, opmaken van staten of andere bijkomstige taken van hetzelfde niveau die enig gezond verstand vereisen en onder rechtstreeks toezicht worden uitgevoerd;- hulpbediende bij de loonadministratie (onder toezicht);- bediende boekhouding (invoeren van boekhoudkundige elementen zonder bepaling van de boeking);- facturatiebediende belast met het opmaken van de lopende facturen en van de statistieken.Informatica- codeerder;- gebruiker van directe registratie.StatuutBediendeTweede categorie- OpstellerBedienden waarvan de functie wordt gekenmerkt door :1. een opleiding die gelijkwaardig is aan de 6 jaar van het hoger secundair onderwijs - of een praktische opleiding verworven door stages of door het uitoefenen van dezelfde of soortgelijke functies;2. een beperkte assimilatietijd;3. autonoom, gevarieerd werk dat van diegene die het uitvoert een bovengemiddelde beroepswaarde, initiatief en verantwoordelijkheidszin vereist;4. de mogelijkheid :- om alle taken lager dan zijn specialiteit uit te voeren;- om alle elementen samen te brengen van de taken die hem worden toevertrouwd, eventueel met de hulp van de bedienden van de vorige categorie.Voorbeelden :Administratief- typist die eveneens met een secretariaatstaak is belast;- bediende die belast is met de berekening van de lonen en de gangbare toepassing van de sociale wetgeving ter zake; hij voert eveneens de betaling van de lonen uit, de verdeling van de arbeidsuren met het oog op het vaststellen van de kostprijzen en voert af en toe berekeningen uit voor de toepassing van de sociale wetgeving;- hulpboekhouder (algemene, analytische of industriële boekhouding) belast met het opmaken, met behulp van boekhoudkundige aanvangsdocumenten, van een gedeelte van de boekhouding of van de lopende boekingen die echter een homogeen geheel vormen, voorafgaand aan de centralisatie, zoals bijvoorbeeld de lopende rekeningen van klanten en leveranciers, tussentijdse rekeningen. Deze verrichtingen kunnen zowel manueel als machinaal worden uitgevoerd;- bediende belast met het opstellen van niet-repetitieve brieven;- bediende die, niet enkel bij afwezigheid van de sociaal assistenten, de wijzigingen moet ten laste nemen inzake toewijzing van taken van de gezinshulpen, in verband met de afwezigheid van de gezinshulpen en de evolutie van de vragen van de bejaarden;- bediende (m/v) die regelmatig moet aanwezig zijn op het secretariaat.InformaticaExploitatie- monitor : verdeelt en ziet toe op het werk van de codeerders; bovendien begeleidt hij het nieuwe personeel tijdens de proefperiode;- operator : persoon die belast is met de uitrusting en inwerkingstelling van de randapparatuur van de computer, volgens de uitvoeringsaanwijzingen.StatuutBediendeDerde categorie- Administratief bediende in bezit van een graduaat vereist bij de indienstnemingWerknemer die houder is van een diploma dat uitgereikt is door een school uit het hoger onderwijs en vereist is bij de indienstneming.Voorbeelden :Administratief- boekhouder, dat wil zeggen bediende belast met het omzetten van alle verrichtingen in boekhoudkundige termen, met het bijeenbrengen ervan en het samenstellen teneinde de algemene balans ervan op te maken, voorafgaandelijk aan de vooruitzichten, balansen, resultaten;- bediende belast met het boekhoudkundig inschrijven van alle verrichtingen die verband houden met de productie, deze samen te stellen en bijeen te brengen teneinde de kostprijs te kunnen berekenen;- bediende verantwoordelijk voor de toepassing van elke loon- en sociale bepaling - secretaris op een directieniveau.InformaticaExploitatie- deskoperator : leidt een grote eonfiguratie van heel het informaticasysteem door middel van het besturingssysteem (software van de machine);- voorbereider van de dragers en van de planning : staat in voor de planning van de werkzaamheden en de aanvoer van gegevensdragers.Ontwikkeling- programmeur : ontwerpt de gedetailleerde toepassingsprogramma's en werkt ze uit op basis van het analysedossier; hij maakt het exploitatiedossier klaar; hij zorgt voor de opvolging van de tests.StatuutBediendeVierde categorie- Administratief bediende in bezit van een licentie vereist bij de indienstnemingWerknemer houder van een diploma uitgereikt door een school uit het hoger onderwijs van het lange type (universiteit) en voor wie het bezit van deze titel vereist is.Voorbeelden : Informaticus analist, jurist.StatuutBediendeArt. 6. Sociaal personeel (4 categorieën)Eerste categorie- Thuisoppas en gezinshelpera) ThuisoppasIn het Waalse Gewest is het statuut van de thuisoppas opgenomen in artikel 323 van de Waalse regelgevingscode voor sociale actie en gezondheid.Heeft de opdracht samen te werken en het mentaal, fysiek en sociaal welzijn te optimaliseren van de rechthebbende van de dienst, die een voortdurende aanwezigheid nodig heeft, in samenwerking met de omgeving van deze laatste :1. instaan voor het actief toezicht tijdens de dag en/of de nacht van een rechthebbende van de dienst, samen met de nabije omgeving;2. ervoor zorgen dat de rechthebbende in optimale omstandigheden op het gebied van veiligheid en hygiëne kan blijven wonen;3. toezien op de correcte inname van de geneesmiddelen volgens het voorschrift van de behandelende geneesheer;4. De gerechtigde van de dienst helpen en hem leren, in functie van zijn fysieke en mentale capaciteiten, de "tijd" kwalitatief te gebruiken;5. de maaltijden klaarmaken en geven aan de gerechtigde;6. zich inpassen in een interdisciplinaire arbeid en zich wenden tot de verantwoordelijke van de dienst of tot de coördinator voor alle handelingen die buiten zijn bevoegdheid vallen;7. deelnemen aan de opleidingen die worden georganiseerd;8. de hoofdbegeleider ondersteunen.ProfielKennis :- ofwel een opleiding die toegang geeft tot het beroep van gezinshulp of gelijkwaardig beoordeeld wordt;- ofwel geen enkele overeenstemmende maar gelijkgestelde opleiding met toepassing van de besluiten van de Waalse Regering van 29 januari 2004 en 15 april 2005;- ofwel een door het Europees Sociaal Fonds of in het kader van het NOW-project (Onderwijs voor Sociale Promotie) gesubsidieerde kwalificatie-opleiding tot thuisoppas;- ofwel een opleiding van thuisoppas of een gelijkwaardige opleiding die in de toekomst zou worden goedgekeurd door het onderwijs voor sociale promotie en die zou beantwoorden aan het beroepsprofiel dat op 24 mei 1996 werd aangenomen door de Hoge Raad van het Onderwijs voor Sociale Promotie.Bekwaamheden :- blijk geven van zin voor openheid en samenwerken in ploegverband, analyse van situaties en terugschakelen naar de diensten;- blijk geven van bekwaamheid om de mogelijk heden van de rechthebbende te evalueren en deze te stimuleren opdat deze laatste actief blijft in de zorg voor zijn dagelijkse leefwereld;- blijk geven van bekwaamheid om mee te werken met de omgeving.StatuutBediendeb) GezinshelperIn het Waalse Gewest, personeel van wie de functie bepaald is in punt A van het statuut dat als bijlage gevoegd is bij het besluit van de Waalse Regering van 16 juli 1998 (Belgisch Staatsblad van 8 september 1998) houdende goedkeuring van het statuut van gezinshelper - en van wie het profiel bepaald is in punt B van hetzelfde besluit - gewijzigd door het besluit van de Waalse Regering van 8 april 2000 (Belgisch Staatsblad van 19 april 2000) - gewijzigd door het besluit van de Waalse Regering van 30 april 2009 (Belgisch Staatsblad van 22 juli 2009).StatuutBediendeTweede categorie- Thuisoppas voor zieke kinderenWerknemer die als taak heeft, door zijn aanwezigheid, mee te werken aan het welzijn en het fysiek en mentaal comfort van het zieke kind, wanneer een voortdurende aanwezigheid vereist is en wiens functie wordt gekenmerkt door :1. omstandigheden van veiligheid en hygiëne bewaren voor het zieke kind en het helpen om de tijd kwalitatief te gebruiken;2. toezien op de correcte inname van de geneesmiddelen;3. de maaltijden klaarmaken en geven aan het zieke kind;4. zich inpassen in een interdisciplinaire taak en zich wenden tot andere beroepskrachten voor alle handelingen die zijn bevoegdheid overschrijden;5. deelnemen aan de opleidingen die voor hem worden georganiseerd.ProfielKennis :- ofwel een diploma van kinderverzorger;- ofwel een opleiding die toegang geeft tot de uitoefening van het beroep van gezinshelper op voorwaarde dat hij een specifieke voortgezette opleiding heeft gevolgd voor de opvang van zieke kinderen.Bekwaamheden :- blijk geven van zin voor openheid en samenwerken in ploegverband, analyse van situaties en terugschakelen naar de diensten;- blijk geven van bekwaamheid om een relatie op te bouwen met de zieke kinderen en zich ermee bezig te houden - een bekwaamheid voor educatieve omkadering aantonen;- blijk geven van bekwaamheid om mee te werken met de omgeving.StatuutBediendeDerde categorie- Maatschappelijk assistentWerknemer van wie de functie bestaat in de omkadering en de organisatie van de voortgezette opleiding van de gezins- en bejaardenhelpers en/of andere zorgaanbieders en in de begeleiding van de rechthebbenden.Vereiste diploma's : sociaal assistent, gegradueerd sociaal verpleegkundige.StatuutBediendeVierde categorie- Sociaal personeel houder van een licentie vereist bij de indienstnemingSociaal werknemer houder van een diploma uitgereikt door een school van het hoger onderwijs van het lange type (universiteit) en voor wie het bezit van deze titel vereist is bij de indienstneming.Voorbeelden : psycholoog, socioloog,...StatuutBediendeHOOFDSTUK II. - Loonschalen - omzettingBijlage : loonschalen van januari 2024Art. 7.  § 1. Op 1 januari 2024 is een baremieke verhoging van toepassing, overeenkomstig de nieuwe loonschaal als bijlage 1. Deze past in een traject van herwaardering van de loonschalen, die zelf past in het budgettair traject van de NPA 2021-2024. § 2. De omzetting naar de referentieloonschalen gebeurt volgens de volgende tabellen :Technisch personeel  </t>
         </is>
       </c>
     </row>
@@ -2936,28 +2930,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2025003565</t>
+          <t>2025201171</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>15 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3 juni 2024. - Koninklijk besluit tot vaststelling van de communicatiemodaliteiten, het formaat van de herstelbaarheidsindex en de toegankelijkheid van de technische normen. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 12 december 2024, gesloten in het Paritair Comité voor de grote kleinhandelszaken, ter bepaling voor 2025 van de modaliteiten van toekenning en afrekening van de korting op de syndicale bijdrage en van de syndicale vorming (1)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-15&amp;numac_search=2025003565&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003565=78&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025201171&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201171=78&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 3 juni 2024 tot vaststelling van de communicatiemodaliteiten, het formaat van de herstelbaarheidsindex en de toegankelijkheid van de technische normen (Belgisch Staatsblad van 4 september 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST VOLKSGESUNDHEIT,SICHERHEIT DER NAHRUNGSMITTELKETTE UND UMWELT3. JUNI 2024 - Königlicher Erlass zur Festlegung der Modalitäten für die Mitteilung des Reparierbarkeitsindex, zur Festlegung dessen Formats und der Zugänglichkeit der technischen NormenPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des Artikels 4 § 3 des Gesetzes vom 17. März 2024 zur Förderung der Reparierbarkeit und Haltbarkeit von Waren;Aufgrund des Artikels 108 der Verfassung;Aufgrund des Königlichen Erlasses vom 25. Mai 2024 zur Bestimmung der Waren, für die der Reparierbarkeitsindex gilt, der technischen Normen zur Festlegung der Punktzahlen für jedes der Kriterien und der Methode zur Berechnung des Reparierbarkeitsindex;Aufgrund der gemeinsame Stellungnahme des Zentralen Wirtschaftsrates, des Föderalen Rates für Nachhaltige Entwicklung und des Besonderen Beratungsausschusses "Verbraucherschutz" vom 15. November 2022;Aufgrund der Stellungnahme des Finanzinspektors vom 16. März 2023;Aufgrund des Einverständnisses der Staatssekretärin für Haushalt vom 5. Mai 2023;Aufgrund des Gutachtens Nr. 75.678/16 des Staatsrates vom 21. März 2024, abgegeben in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Auf Vorschlag der Ministerin der UmweltHaben Wir beschloßen und erlassen Wir:Artikel 1 - Durch vorliegenden Erlass werden die Modalitäten für die Mitteilung und das Format des Reparierbarkeitsindex sowie die Zugänglichkeit der Berechnungen der in Artikel 3 des Königlichen Erlasses vom 25. Mai 2024 zur Bestimmung der Waren, für die der Reparierbarkeitsindex gilt, der technischen Normen zur Festlegung der Punktzahlen für jedes der Kriterien und der Methode zur Berechnung des Reparierbarkeitsindex erwähnten Produkte bestimmt.Art. 2 - Für die Anwendung des vorliegenden Erlasses gilt folgende Begriffsbestimmung:"grafische Gestaltung": Gestaltung, die auf die Realisierung einer visuellen Kommunikation abzielt, bei der Bild und Text kombiniert werden.Art. 3 - § 1 - Hersteller oder Importeure legen den Reparierbarkeitsindex der Waren fest, die sie gemäß den Artikeln 2, 3 und 4 des Königlichen Erlasses vom 25. Mai 2024 zur Bestimmung der Waren, für die der Reparierbarkeitsindex gilt, der technischen Normen zur Festlegung der Punktzahlen für jedes der Kriterien und der Methode zur Berechnung des Reparierbarkeitsindex in Verkehr bringen. § 2 - Hersteller oder Importeure teilen Verkäufern und Vertreibern zum Zeitpunkt der Registrierung und Lieferung von Waren kostenlos den Reparierbarkeitsindex und die technischen Normen zur Festlegung der Punktzahlen für jedes der Kriterien des Index mit. § 3 - Wenn die Vertreiber nicht mit den Verkäufern identisch sind, teilen sie den Verkäufern zum Zeitpunkt der Registrierung und Lieferung von Waren kostenlos den Reparierbarkeitsindex und die technischen Normen zur Festlegung der Punktzahlen für jedes der Kriterien des Index mit. § 4 - Hersteller oder Importeure teilen allen Interessehabenden kostenlos über eine Website den Reparierbarkeitsindex, die technischen Normen zur Festlegung der Punktzahlen für jedes der Kriterien des Reparierbarkeitsindex und die Einzelheiten der Berechnung, anhand der der Reparierbarkeitsindex bestimmt worden ist mit.Art. 4 - § 1 - Verkäufer informieren Verbraucher gemäß Artikel 5 des vorliegenden Erlasses kostenlos über den Reparierbarkeitsindex anhand eines gut sichtbaren Aushangs in der Nähe des Preises. § 2 - Verkäufer machen den Verbrauchern die technischen Normen zur Festlegung der Punktzahlen für jedes der Kriterien des Reparierbarkeitsindex und die Einzelheiten der Berechnung, anhand der der Reparierbarkeitsindex bestimmt worden ist, zugänglich, indem sie auf die in Artikel 3 § 4 des vorliegenden Erlasses erwähnte Website verweisen. Verkäufer geben in der Nähe des Preises die URL oder den QR-Code an, über die man auf die Website zugreifen kann.Art. 5 - § 1 - Der Minister bestimmt durch einen Ministeriellen Erlass den in Artikel 4 des vorliegenden Erlasses erwähnten Aushang, was die grafische Gestaltung, den Wortlaut und das Piktogramm betrifft. § 2 - Der Minister bestimmt durch einen Ministeriellen Erlass den Farbcode auf der Grundlage der erhaltenen Punktzahl des Reparierbarkeitsindex. § 3 - Die Schriftgröße der Ziffern der Punktzahl des Index muss mindestens der Schriftgröße der Ziffern des Preises im Verkaufsregal oder auf der Website entsprechen. Jede Anpassung der Größe dieser Angabe muss unter Einhaltung der Proportionen erfolgen. § 4 - Der Reparierbarkeitsindex wird in Form einer Note auf einer Skala von 1 bis 10 dargestellt, wobei eine Dezimalstelle zulässig ist. Wenn die Ziffer nach der ersten Dezimalstelle kleiner als fünf ist, wird die Note auf die niedrigere Dezimalstelle abgerundet. Wenn die Ziffer nach der ersten Dezimalstelle größer oder gleich fünf ist, wird die Note auf die höhere Dezimalstelle aufgerundet.Art. 6 - § 1 - Der Minister bestimmt durch einen Ministeriellen Erlass das Format der URL und des QR-Codes, die in Artikel 4 § 2 des vorliegenden Erlasses erwähnt sind. § 2 - Die Schriftgröße der URL und des QR-Codes, die in Artikel 4 § 2 des vorliegenden Erlasses erwähnt sind, muss mindestens der Schriftgröße der Ziffern des Preises entsprechen.Art. 7 - Vorliegender Erlass tritt am 2. Mai 2025 in Kraft.Art. 8 - Der für Umwelt zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 3. Juni 2024PHILIPPEVon Königs wegen:Die Ministerin der UmweltZ. KHATTABIDer Minister der WirtschaftP-Y. DERMAGNEDie Staatssekretärin für Verbraucherschutz, dem Minister der Justiz und der Nordsee beigeordnetA. BERTRANDDer Minister der Justiz und der NordseeP. VAN TIGCHELT 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de grote kleinhandelszaken; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 12 december 2024, gesloten in het Paritair Comité voor de grote kleinhandelszaken, ter bepaling voor 2025 van de modaliteiten van toekenning en afrekening van de korting op de syndicale bijdrage en van de syndicale vorming. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de grote kleinhandelszaken Collectieve arbeidsovereenkomst van 12 december 2024 Bepaling voor 2025 van de modaliteiten van toekenning en afrekening van de korting op de syndicale bijdrage en van de syndicale vorming (Overeenkomst geregistreerd op 7 januari 2025 onder het nummer 191327/CO/311) HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de werknemers van de ondernemingen welke ressorteren onder het Paritair Comité voor de grote kleinhandelszaken. HOOFDSTUK II. - Sociale voordelen Afdeling 1. - Korting op de syndicale bijdrage A. Aard van het voordeel Art. 2. De werknemers die tewerkgesteld zijn in een onderneming bedoeld in artikel 1 hebben recht op een korting op de syndicale bijdrage ten laste van het "Sociaal Fonds voor de grote kleinhandelszaken", onder de voorwaarden vastgesteld bij deze collectieve arbeidsovereenkomst. B. Bedrag Art. 3. Het bedrag van de korting werd als volgt vastgelegd : a) 145 EUR per jaar voor werknemers die een normale syndicale bijdrage in de vereiste vormen betaald hebben op het ogenblik van de betaling van de korting; b) 72,5 EUR per jaar voor werknemers die een beperkte syndicale bijdrage in de vereiste vormen betaald hebben op het ogenblik van de betaling van de korting, evenals voor de werknemers die op brugpensioen zijn. C. Toekenningsvoorwaarden Art. 4. Om recht te hebben op de korting moeten de werknemers, bedoeld in artikel 2 aan de volgende voorwaarden voldoen : 1° Vóór 1 januari 2025 aangesloten zijn bij één van de representatieve interprofessionele werknemersorganisaties, welke op nationaal plan zijn verbonden en vertegenwoordigd in het paritair comité, namelijk : - het Algemeen Belgisch Vakverbond (ABVV); - het Algemeen Christelijk Vakverbond (ACV); - de Algemene Centrale der Liberale Vakbonden van België (ACLVB); 2° Hetzij, op 15 juni 2025 tewerkgesteld zijn in één van de in artikel 2 bedoelde ondernemingen, of eventueel, op deze datum zijn gedekt door het stelsel van de gelijkgestelde dagen voorzien in de artikelen 16 en 18 en 41 tot 43 van het koninklijk besluit van 30 maart 1967 tot bepaling van de algemene uitvoeringsmodaliteiten van de wetten betreffende de jaarlijkse vakantie der loonarbeiders, hetzij op brugpensioen gesteld zijn volgens het regime, voorzien door de collectieve arbeidsovereenkomst, gesloten op 19 december 1974 in de Nationale Arbeidsraad, tot instelling van een regime voor aanvullende vergoedingen voor bepaalde oudere werknemers in geval zij zijn ontslagen, algemeen verbindend verklaard bij koninklijk besluit van 16 januari 1975, en niet de wettelijke pensioenleeftijd bereikt hebben, ofwel ingeschreven zijn in een tewerkstellingscel of daarvan vrijgesteld zijn in het kader van de erkenning als onderneming in herstructurering of in moeilijkheden.D. Betalings- en controlemodaliteiten Art. 5. Het sociaal fonds stort aan elke representatieve interprofessionele werknemersorganisatie de nodige bedragen om de betaling van de ristorno's te verzekeren. Art. 6. De werkgevers van de ondernemingen bedoeld in artikel 2, overhandigen met de loonfiche voor de maand mei, aan elke in hun onderneming op 15 juni tewerkgestelde werknemer alsook aan hen die gedekt zijn door het regime van de gelijkgestelde dagen, bepaald in artikel 4, 2° een behoorlijk ingevuld formulier waarvan het model wordt opgemaakt door de raad van bestuur van het sociaal fonds. De werkgevers zenden aan de werknemers die op brugpensioen werden gesteld, bedoeld in artikel 4, 2° het formulier toe, voor zover zij de wettelijke pensioenleeftijd niet bereikt hebben. Deze formulieren worden ambtshalve of op hun verzoek ter beschikking gesteld van de werkgevers door het beheer van het sociaal fonds, gevestigd in de Edmond Van Nieuwenhuyselaan, 8 te 1160 Brussel. Art. 7. De werknemers die de in artikel 4 bedoelde toekenningsvoorwaarden vervullen bezorgen aan de in artikel 4, 1° vermelde organisatie, waarvan zij lid zijn, het in artikel 6 bedoelde formulier in tweevoud. Deze organisatie onderzoekt de effectieve aansluiting van de werknemer en of hij een recht kan doen gelden en betaalt het bedrag van de korting. De verificatie en de betaling gebeuren tussen 16 juni en 30 september van het lopende dienstjaar. Art. 8. Vóór 31 oktober van het lopende dienstjaar, bezorgt iedere in artikel 4, 1° bedoelde organisatie aan het sociaal fonds een afrekening met vermelding van het bedrag van de ontvangen sommen, het aantal door de begunstigden ondertekende formulieren en het bedrag dat ermee overeenstemt. De organisaties zijn verplicht het dubbel van de terugbetalingsformulieren gedurende 5 jaar te bewaren, welke worden gecontroleerd door de expert-boekhouder van het sociaal fonds. Art. 9. De nadere modaliteiten van betaling en controle van de korting op de syndicale bijdrage verlopen volgens het "Reglement van de betaling van de syndicale premies" vastgesteld door de raad van bestuur van het sociaal fonds. Afdeling 2. - Syndicale vorming A. Aard van het voordeel Art. 10. De onder artikel 4, 1° bepaalde representatieve interprofessionele werknemersorganisaties hebben recht op en financiële deelneming ten laste van het "Sociaal Fonds voor de grote kleinhandelszaken" voor de onkosten die ze dragen bij de organisatie van cursussen of seminaries met het oog op de verbetering van de kennis van de werknemers op economisch, sociaal en technisch vlak, zoals bepaald door de collectieve arbeidsovereenkomst van 5 juli 1978 betreffende de syndicale vorming, gesloten in het Paritair Comité voor de grote kleinhandelszaken en verbindend verklaard bij koninklijk besluit van 2 maart 1979. B. Bedrag Art. 11. De globale financiële deelneming van het sociaal fonds is gelijk aan 137 481,76 EUR. Dit bedrag wordt over de onder artikel 4, 1° bedoelde representatieve interprofessionele werknemersorganisaties verdeeld naar rato van het aantal kortingen op de syndicale bijdrage dat het sociaal fonds tijdens het jaar 2024 voor elk van hen heeft betaald. C. Afrekening Art. 12. De betaling van de financiële deelneming aan de werknemersorganisaties die vallen onder artikel 4, 1° gebeurt gedurende de maand augustus volgens de modaliteiten die vastgelegd zijn door de raad van beheer van het sociaal fonds. HOOFDSTUK III. - Financiering A. Bedrag van de bijdrage van de werkgevers Art. 13. Om het "Sociaal Fonds voor de grote kleinhandelszaken" de mogelijkheid te bieden de definitieve sociale voordelen af te rekenen overeenkomstig hoofdstuk II van deze collectieve arbeidsovereenkomst, wordt de bijdrage die door de werkgevers aan het sociaal fonds moet worden betaald, bepaald op 90 EUR per tewerkgestelde werknemer en per bruggepensioneerde op datum van 30 september 2024. De aangifte bij de Rijksdienst voor Sociale Zekerheid voor het derde kwartaal 2023 is een rechtsgeldig bewijs voor de berekening van het tewerkgestelde effectief op 30 september 2024.Het sociaal fonds houdt zich het recht voor om informaties bij de RSZ op te vragen. Indien het aantal werknemers tewerkgesteld op 15 mei 2025 gewijzigd wordt met meer dan 10 pct. ten opzichte van het aantal werknemers meegedeeld op 30 september 2024, zal de bijdrage van de onderneming aangepast worden in functie van deze wijziging. B. Inning van de bijdrage van de werkgevers Art. 14. De inning van de bijdrage van de werkgevers door het sociaal fonds, berekend overeenkomstig artikel 13, gebeurt in de maand april. De werkgevers moeten de verschuldigde bedragen uiterlijk op 31 mei storten aan het sociaal fonds. HOOFDSTUK IV. - Slotbepalingen Art. 15.  Onderhavige collectieve arbeidsovereenkomst wordt van kracht op 1 januari 2025 en loopt ten einde op 31 december 2025. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -2968,28 +2962,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2025003362</t>
+          <t>2025201172</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>06 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>3 mei 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 27 november 2016 betreffende de identificatie van de eindgebruiker van mobiele openbare elektronische-communicatiediensten die worden geleverd op basis van een voorafbetaalde kaart. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 11 december 2024, gesloten in het Paritair Comité voor het hotelbedrijf, tot wijziging van de collectieve arbeidsovereenkomst van 27 juli 2010 tot wijziging en coördinatie van de collectieve arbeidsovereenkomsten tot toekenning van een eindejaarspremie (1)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-06&amp;numac_search=2025003362&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003362=79&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025201172&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201172=79&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 3 mei 2024 tot wijziging van het koninklijk besluit van 27 november 2016 betreffende de identificatie van de eindgebruiker van mobiele openbare elektronische-communicatiediensten die worden geleverd op basis van een voorafbetaalde kaart (Belgisch Staatsblad van 30 mei 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST WIRTSCHAFT, KMB, MITTELSTAND UND ENERGIE, FÖDERALER ÖFFENTLICHER DIENST JUSTIZ UND MINISTERIUM DER LANDESVERTEIDIGUNG3. MAI 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 27. November 2016 über die Identifizierung des Endnutzers öffentlich zugänglicher elektronischer Mobilfunkdienste, die über eine Guthabenkarte abgerechnet werdenPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des Gesetzes vom 13. Juni 2005 über die elektronische Kommunikation, des Artikels 127, wie durch das Gesetz vom 20. Juli 2022 über die Sammlung und Speicherung von Identifizierungsdaten und Metadaten im Bereich der elektronischen Kommunikation und die Übermittlung dieser Daten an Behörden ersetzt;Aufgrund der Auswirkungsanalyse beim Erlass von Vorschriften, die gemäß den Artikeln 6 und 7 des Gesetzes vom 15. Dezember 2013 zur Festlegung verschiedener Bestimmungen in Sachen administrative Vereinfachung durchgeführt worden ist;Aufgrund der öffentlichen Anhörung vom 21. November 2022 bis zum 22. Dezember 2023;Aufgrund der Stellungnahme des Finanzinspektors vom 13. Juni 2023;Aufgrund des Einverständnisses der Staatssekretärin für Haushalt vom 25. Juni 2023;Aufgrund der Stellungnahme des Belgischen Instituts für Post- und Fernmeldewesen vom 11. August 2023;Aufgrund der Stellungnahme Nr. 141/2023 der Datenschutzbehörde vom 29. September 2023;Aufgrund des Antrags auf Begutachtung binnen einer von Rechts wegen bis zum 4. September 2023 verlängerten Frist von dreißig Tagen, der am 19. Juli 2023 beim Staatsrat eingereicht worden ist, in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;In der Erwägung, dass kein Gutachten binnen dieser Frist übermittelt worden ist;Aufgrund von Artikel 84 § 4 Absatz 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Aufgrund der Konsultierung des Interministeriellen Ausschusses für Telekommunikation, Rundfunk und Fernsehen vom 5. bis zum 12. Juli 2023;Aufgrund der Zustimmung des Konzertierungsausschusses vom 18. Juli 2023;Auf Vorschlag der Ministerin des Fernmeldewesens, des Ministers der Justiz, der Ministerin der Landesverteidigung und aufgrund der Stellungnahme der Minister, die im Rat darüber beraten haben,Haben Wir beschloßen und erlassen Wir:Artikel 1 - [Abänderung des französischen und niederländischen Textes der Überschrift des Königlichen Erlasses vom 27. November 2016 über die Identifizierung des Endnutzers öffentlich zugänglicher elektronischer Mobilfunkdienste, die über eine Guthabenkarte abgerechnet werden]Art. 2 - Artikel 1 desselben Erlasses wird wie folgt ersetzt:"Artikel 1 - Vorliegender Erlass findet Anwendung auf Guthabenkarten, mit denen ein öffentlich zugänglicher elektronischer Mobilfunkdienst genutzt werden kann.Er findet Anwendung auf Guthabenkarten, die verbunden sind mit:- einer belgischen Telefonnummer oder einer belgischen IMSI oder- einer ausländischen Telefonnummer oder einer ausländischen IMSI, wenn die Guthabenkarten in Belgien mit Zustimmung des Betreibers vertrieben werden.Er findet keine Anwendung auf Guthabenkarten, mit denen nur Maschine-zu-Maschine-Anwendungen (M2M) oder Internet-der-Dinge-Anwendungen (IoT) genutzt werden können, sofern diese Anwendungen nicht die Nutzung eines Internetzugangsdienstes oder eines interpersonellen Kommunikationsdienstes eines Betreibers ermöglichen.Wenn eine Person, die in einem geschlossenen Zentrum oder Unterbringungsort im Sinne der Artikel 74/8 und 74/9 des Gesetzes vom 15. Dezember 1980 über die Einreise ins Staatsgebiet, den Aufenthalt, die Niederlassung und das Ausweisen von Ausländern wohnt, sich gemäß Artikel 127 § 10 Nr. 5 des Gesetzes vom 13. Juni 2005 über die elektronische Kommunikation bei einem elektronischen Kommunikationsdienst anmeldet, der über eine Guthabenkarte abgerechnet wird, finden nur Artikel 5 Absatz 3, Artikel 6 und Artikel 8 Anwendung.Wenn die Guthabenkarte für Rechnung der Nachrichten- und Sicherheitsdienste, der Polizeidienste oder der vom Minister bestimmten öffentlichen Behörden gekauft worden ist, findet nur Artikel 8 Anwendung."Art. 3 - Artikel 2 desselben Erlasses wird wie folgt abgeändert:1. Die Nummern 2 bis 6 werden aufgehoben.2. Der Artikel wird durch eine Nummer 7 mit folgendem Wortlaut ergänzt:"7. "sich identifizierende Person": die natürliche Person, die sich beim Betreiber identifiziert, und zwar:- die natürliche Person, die der Teilnehmer ist, oder- die natürliche Person, die gemäß Artikel 127 § 8 des Gesetzes für Rechnung der juristischen Person handelt, die der Teilnehmer ist, oder- die natürliche Person, die gemäß Artikel 127 § 10 Nr. 6 des Gesetzes für Rechnung der juristischen Person handelt, die sich bei einem elektronischen Kommunikationsdienst im Namen und für Rechnung einer natürlichen Person anmeldet, die Schwierigkeiten hat, diese Anmeldung vorzunehmen."Art. 4 - In der Überschrift von Kapitel 2 desselben Erlasses wird das Wort "Endnutzer" durch das Wort "Teilnehmer" ersetzt.Art. 5 - Artikel 3 desselben Erlasses wird wie folgt abgeändert:1. Absatz 1 wird wie folgt abgeändert:a) Die Wörter "Endnutzer einer Guthabenkarte müssen sich jedes Mal identifizieren," werden durch die Wörter "Die Person, die sich identifiziert, tut dies jedes Mal," ersetzt.b) Die Wörter "das betreffende Unternehmen" werden durch die Wörter "der Betreiber" ersetzt.2. Absatz 2 wird wie folgt ersetzt:"Die sich identifizierende Person ist verpflichtet, ein in Artikel 127 § 6 des Gesetzes erwähntes Identifizierungsdokument vorzulegen, wenn ein solches Dokument gemäß den Artikeln 14 bis 19 verlangt wird."Art. 6 - Artikel 4 desselben Erlasses wird wie folgt ersetzt:"Art. 4 - Die Person identifiziert sich spätestens bei Aktivierung der Karte nach einer der im vorliegenden Erlass beschriebenen Identifizierungsmethoden."Art. 7 - Artikel 5 desselben Erlasses wird wie folgt abgeändert:1. Absatz 1 wird wie folgt abgeändert:a) Der erste Satz wird wie folgt abgeändert:Die Wörter "Natürliche oder juristische Personen, die sich bei dem betreffenden Unternehmen identifizieren, dürfen eine aktive Guthabenkarte keinem Dritten überlassen," werden durch die Wörter "Sich identifizierende Personen, dürfen eine aktive Guthabenkarte keiner anderen Person übertragen," ersetzt.b) Nummer 1 wird wie folgt ersetzt:"1. ihrem Ehepartner, ihrem gesetzlich Zusammenwohnenden oder ihren Zusammenwohnenden, die in derselben Haushaltszusammensetzung aufgelistet sind,".c) Nummer 2 wird wie folgt ersetzt:"2. ihren Eltern, Großeltern, Kindern, Enkelkindern, Brüdern oder Schwestern oder denen der in Nr. 1 erwähnten Personen,".d) In Nr. 5 werden die Wörter "dem betreffenden Unternehmen" durch die Wörter "dem Betreiber" ersetzt.e) Nummer 6 wird wie folgt ersetzt:"6. der natürlichen Person, für die sich gemäß Artikel 127 § 10 Nr. 6 des Gesetzes eine juristische Person bei einem elektronischen Kommunikationsdienst angemeldet hat."2. In Absatz 2 wird das Wort "Geburtsort" durch das Wort "Vornamen" ersetzt und werden die Wörter "dem betreffenden Unternehmen" durch die Wörter "dem Betreiber" ersetzt.3. Der Artikel wird durch einen Absatz mit folgendem Wortlaut ergänzt:"Die in Absatz 1 Nr. 1 bis 6 erwähnten Personen, denen eine Guthabenkarte gemäß Absatz 1 überlassen worden ist, und die Personen, die in einem geschlossenen Zentrum oder Unterbringungsort im Sinne der Artikel 74/8 und 74/9 des Gesetzes vom 15. Dezember 1980 über die Einreise ins Staatsgebiet, den Aufenthalt, die Niederlassung und das Ausweisen von Ausländern wohnen und die eine Guthabenkarte gemäß Artikel 127 § 10 Nr. 5 des Gesetzes erhalten haben, dürfen eine aktive Guthabenkarte nur einer in Absatz 1 Nr. 1 bis 6 erwähnten Person überlassen."Art. 8 - Artikel 6 wird wie folgt abgeändert:1. Das Wort "Endnutzer" wird durch das Wort "Teilnehmer" ersetzt.2. Die Wörter "das betreffende Unternehmen" werden durch die Wörter "den Betreiber" ersetzt.Art. 9 - Die Überschrift von Kapitel 3 desselben Erlasses wird wie folgt ersetzt:"KAPITEL 3 - Maßnahmen der Betreiber, die Guthabenkarten bereitstellen".Art. 10 - In Kapitel 3 desselben Erlasses wird die Überschrift von Abschnitt 1 wie folgt ersetzt:"Abschnitt 1 - Allgemeine Bestimmungen".Art. 11 - Artikel 7 desselben Erlasses wird wie folgt ersetzt:"Art. 7 - Der Betreiber kann die Guthabenkarte erst aktivieren, nachdem die Identifizierung erfolgt ist."Art. 12 - Artikel 8 wird wie folgt abgeändert:1. Das Wort "Endnutzer" wird durch das Wort "Teilnehmer" ersetzt.2. Die Wörter "das betreffende Unternehmen" werden durch die Wörter "den Betreiber" ersetzt und das Wort "es" wird durch das Wort "er" ersetzt.Art. 13 - Artikel 9 wird wie folgt abgeändert:1. Absatz 1 wird wie folgt abgeändert:a) Die Wörter "das betreffende Unternehmen" werden durch die Wörter "der Betreiber" ersetzt.b) Das Wort "gültigen" wird durch die Wörter "im vorliegenden Erlass beschriebenen" ersetzt.c) Die Wörter "natürlichen Person, die die Aktivierung der Karte beantragt" werden durch die Wörter "sich identifizierenden Person" ersetzt.2. Absatz 2 wird aufgehoben.Art. 14 - Abschnitt 2 desselben Erlasses, der Artikel 10 umfasst, wird aufgehoben.Art. 15 - Artikel 11 desselben Erlasses wird wie folgt ersetzt:"Art. 11 - § 1 - Wenn Personen zu ihrer Identifizierung einen belgischen Personalausweis vorlegen, überprüft der Betreiber systematisch vor Aktivierung der Guthabenkarte und anhand des EDV-Instruments von checkdoc oder eines anderen vom Minister der Justiz und vom Minister zugelassenen EDV-Instruments, ob dieser Personalausweis bei den öffentlichen Behörden als gestohlen, verloren, abgelaufen oder ungültig gemeldet ist oder nicht ausgestellt wurde.Wenn dies der Fall ist, erlauben der Betreiber und der Vertriebsweg nicht die Aktivierung der Guthabenkarte auf der Grundlage der Vorlage des Personalausweises.Die in Absatz 1 erwähnte Zulassung wird nur erteilt, sofern das EDV-Instrument als zuverlässig angesehen werden kann.Diese Zuverlässigkeit wird vom Institut, von den Nachrichten- und Sicherheitsdiensten und der NTSU, das heißt der National Technical and Tactical Support Unit der Spezialeinheiten der föderalen Polizei, überprüft.Letztere überprüfen Folgendes:1. die Fähigkeit des EDV-Instruments, seine in Absatz 1 erwähnte Funktion zu erfüllen, unter anderem auf der Grundlage von Tests, die sie oder Dritte durchführen,2. die Zuverlässigkeit des Anbieters des Instruments,3. die Einhaltung der in Artikel 12 des Gesetzes vom 11. Dezember 1998 über die Klassifizierung und die Sicherheitsermächtigungen, -bescheinigungen und -stellungnahmen erwähnten Interessen für die nationale Sicherheit,4. jedes andere relevante Element auf der Grundlage des Einzelfalls.Die in Absatz 1 erwähnte Zulassung wird nach Stellungnahme des Instituts erteilt. § 2 - Wurde die Guthabenkarte bereits aktiviert und stellt der Betreiber im Nachhinein eine Unregelmäßigkeit in Bezug auf die Identifizierung der sich identifizierenden Person fest, wie fehlende oder widersprüchliche Daten, oder dass die Identifizierung dieser Person betrügerisch sein könnte, befolgt er folgendes Verfahren:1. Er prüft unverzüglich erneut die Identifizierungsdaten dieser Person anhand der Daten und Dokumente, über die er verfügt.2. Wenn nach dieser erneuten Überprüfung immer noch Zweifel an der genauen Identität dieser Person bestehen, fordert er sie unverzüglich auf, sich spätestens binnen eines Monats nach dieser Aufforderung erneut zu identifizieren.3. Wenn diese Person sich nicht binnen dieser Frist identifiziert hat, macht er die Guthabenkarte unbrauchbar, vorbehaltlich anders lautenden Befehls der Gerichtsbehörden oder der Nachrichten- und Sicherheitsdienste. § 3 - Wurde die Guthabenkarte bereits aktiviert und stellt der Betreiber im Nachhinein fest oder wird er darüber informiert, dass die Identifizierung der sich identifizierenden Person betrügerisch ist, macht er die Guthabenkarte unverzüglich unbrauchbar, vorbehaltlich anders lautenden Befehls der Gerichtsbehörden oder der Nachrichten- und Sicherheitsdienste. § 4 - Wenn der Betreiber eine Guthabenkarte in Anwendung der Paragraphen 2 und 3 unbrauchbar macht, wird der Teilnehmer nicht entschädigt."Art. 16 - Artikel 12 desselben Erlasses wird wie folgt ersetzt:"Art. 12 - Die Betreiber speichern die Informationen über die Art der Identifizierungsmethode, die für jede Identifizierung unter den in Abschnitt 5 erwähnten Methoden verwendet wird, solange die Identifizierungsdaten aufgrund von Artikel 127 § 4 Absatz 4 des Gesetzes auf Vorrat gespeichert werden müssen.Hat der Betreiber eine Person anhand der in Artikel 19 erwähnten Methode identifiziert, speichert er zudem die Informationen über die Art des zur Identifizierung der Person verwendeten Instruments zur Identitätsüberprüfung während derselben Frist wie der in Absatz 1 erwähnten Frist."Art. 17 - Artikel 13 desselben Erlasses wird wie folgt ersetzt:"Art. 13 - Der Betreiber muss der sich identifizierenden Person mindestens eine der im vorliegenden Abschnitt erwähnten Identifizierungsmethoden anbieten.Bietet der Betreiber als Identifizierungsmethode die in Artikel 127 § 5 Absatz 4 des Gesetzes erwähnte Gesichtsvergleichsmethode an, bietet er auch eine im vorliegenden Erlass vorgesehene alternative Identifizierungsmethode an."Art. 18 - In Abschnitt 5 desselben Erlasses wird die Überschrift von Unterabschnitt 1 wie folgt ersetzt:"Unterabschnitt 1 - Vorlage eines Identifizierungsdokuments beim Vertriebsweg".Art. 19 - Artikel 14 desselben Erlasses wird wie folgt ersetzt:"Art. 14 - Ein Betreiber darf eine Person identifizieren, wenn diese ein in Artikel 127 § 6 des Gesetzes erwähntes Identifizierungsdokument bei einem in Artikel 127 § 2 Nr. 5 desselben Gesetzes erwähnten Vertriebsweg vorlegt.Wenn dem Betreiber erlaubt worden ist, ein Gesichtsvergleichsinstrument gemäß Artikel 127 § 5 Absatz 4 Nr. 1 desselben Gesetzes einzusetzen, darf er eine Person nur mit deren Zustimmung anhand dieses Instruments identifizieren.Bei Vorlage eines belgischen elektronischen Personalausweises, wenn das Gesichtsvergleichsinstrument nicht verwendet wird und auf Verlangen eines Mitglieds des Vertriebswegs muss die sich identifizierende Person den PIN-Code des elektronischen Personalausweises eingeben."Art. 20 - In Abschnitt 5 desselben Erlasses wird die Überschrift von Unterabschnitt 2 wie folgt ersetzt:"Unterabschnitt 2 - Fernidentifizierung anhand eines Identifizierungsdokuments".Art. 21 - Artikel 15 desselben Erlasses wird wie folgt abgeändert:1. Paragraph 1 wird wie folgt abgeändert:a) Absatz 1 wird wie folgt ersetzt:"Art. 15 - § 1 - Ein Betreiber kann eine Person durch das Auslesen der Daten ihres elektronischen Personalausweises identifizieren. Ihre Identität wird nach Authentifizierung validiert."b) In Absatz 2 Nr. 2 werden zwischen den Wörtern "Der PIN-Code" und den Wörtern "muss eingegeben werden" die Wörter "des elektronischen Personalausweises" eingefügt.2. Paragraph 2 wird wie folgt ersetzt:" § 2 - Wenn dem Betreiber erlaubt worden ist, ein Gesichtsvergleichsinstrument gemäß Artikel 127 § 5 Absatz 4 Nr. 1 desselben Gesetzes einzusetzen, darf er eine Person anhand dieses Instruments und eines in Artikel 127 §  6 des Gesetzes erwähnten Identifizierungsdokuments identifizieren."Art. 22 - In Abschnitt 5 desselben Erlasses wird die Überschrift von Unterabschnitt 3 wie folgt ersetzt:"Unterabschnitt 3 - Identifizierung anhand eines Instruments, das die Identifizierung bei einer digitalen Anwendung der belgischen Behörden ermöglicht".Art. 23 - Artikel 16 desselben Erlasses wird wie folgt ersetzt:"Art. 16 - Ein Betreiber kann eine Person identifizieren, wenn diese ein Instrument verwendet, das es ermöglicht, sich bei einer digitalen Anwendung der belgischen Behörden zu identifizieren.Der Minister und der Minister der Justiz können jederzeit verbieten, dass ein in Absatz 1 erwähntes Instrument für die Identifizierung der Teilnehmer der Betreiber verwendet wird.Die Identifizierungsdaten müssen dem Betreiber vor Aktivierung der Guthabenkarte übermittelt worden sein."Art. 24 - Artikel 17 desselben Erlasses wird wie folgt abgeändert:1. Paragraph 1, der der einzige Paragraph wird, wird wie folgt abgeändert:a) Absatz 1 wird wie folgt abgeändert:i) Die Wörter "Betreffende Unternehmen können den Endnutzer auf der Grundlage eines elektronischen Online-Zahlungsvorgangs identifizieren," werden durch die Wörter "Der Betreiber kann die Identifizierung einer Person auf der Grundlage eines elektronischen Online-Zahlungsvorgangs ermöglichen," ersetzt.ii) Der Absatz wird wie folgt ergänzt: ", indem die in Artikel 127 § 10 Nr. 3 des Gesetzes erwähnten Informationen, einschließlich der Zahlungsreferenz, gespeichert werden."b) Absatz 2 wird wie folgt abgeändert:i) Im einleitenden Satz wird das Wort "Methode" durch das Wort "Identifizierungsmethode" ersetzt.ii) [Abänderung des niederländischen Textes von Nr. 2 und 3]iii) Nummer 4 wird aufgehoben.2. Paragraph 2 wird aufgehoben.Art. 25 - In Unterabschnitt 5 desselben Erlasses wird Artikel 18 wie folgt abgeändert:1. Paragraph 1 wird wie folgt abgeändert:a) Absatz 1 wird wie folgt ersetzt:"Art. 18 - § 1 - Der Betreiber kann eine Person identifizieren, indem er die bei diesem Betreiber erworbene Guthabenkarte mit einem Produkt desselben Betreibers, bei dem sie angemeldet ist, verbindet."b) In Absatz 2 werden die Wörter "Das betreffende Unternehmen" durch die Wörter "Der Betreiber" ersetzt.2. In § 2 werden die Wörter "Das betreffende Unternehmen" durch die Wörter "Der Betreiber" ersetzt.Art. 26 - In Unterabschnitt 6 desselben Erlasses wird Artikel 19 wie folgt abgeändert:1. Paragraph 1 wird wie folgt abgeändert:a) Absatz 1 wird wie folgt abgeändert:i) Die Wörter "Wenn Endnutzer" werden durch die Wörter "Der Betreiber kann Personen identifizieren, die ihm" ersetzt und die Wörter "dem betreffenden Unternehmen" werden gestrichen.ii) Die Wörter "überprüft Letzteres" werden durch die Wörter "indem er" ersetzt und der Satz wird durch das Wort "überprüft" ergänzt.b) Absatz 2 wird wie folgt abgeändert:i) Im einleitenden Satz wird das Wort "Methode" durch das Wort "Identifizierungsmethode" ersetzt.ii) Nummer 2 wird wie folgt ersetzt:"2. Die von einem Unternehmen bereitgestellte Identifizierungsmethode muss vorher auf Antrag eines Betreibers oder des Unternehmens hin vom Minister und vom Minister der Justiz nach Stellungnahme des Instituts, das sich zuvor mit den Nachrichten- und Sicherheitsdiensten und der NTSU, das heißt der National Technical and Tactical Support Unit der Spezialeinheiten der föderalen Polizei, konzertiert, zugelassen werden."2. Paragraph 2 wird wie folgt abgeändert: a) [Abänderung des französischen und niederländischen Textes von Absatz 1]b) In Absatz 2 werden die Wörter "Das betreffende Unternehmen" durch die Wörter "Der Betreiber" ersetzt.c) Absatz 3 wird wie folgt ersetzt:"Als Kriterien für die Gewährung oder den Entzug der Zulassung gelten:- der Grad der Zuverlässigkeit der Identifizierung unter Berücksichtigung der Richtigkeit, Vollständigkeit und Kohärenz der Identifizierungsdaten zum Zeitpunkt der Identifizierung sowie der Sicherheit und Unversehrtheit dieser Daten und- die Auswirkungen des Überprüfungsinstruments auf die nationale Sicherheit."3. Paragraph 3 wird aufgehoben.Art. 27 - In Kapitel 4 desselben Erlasses wird Artikel 20 aufgehoben.Art. 28 - Der für Fernmeldewesen zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 3. Mai 2024PHILIPPEVon Königs wegen:Die Ministerin des FernmeldewesensP. DE SUTTERDer Minister der JustizP. VAN TIGCHELTDie Ministerin der LandesverteidigungL. DEDONDER 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het hotelbedrijf; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 11 december 2024, gesloten in het Paritair Comité voor het hotelbedrijf, tot wijziging van de collectieve arbeidsovereenkomst van 27 juli 2010 tot wijziging en coördinatie van de collectieve arbeidsovereenkomsten tot toekenning van een eindejaarspremie. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota (1) Verwijzing naar het Belgisch Staatsblad: Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.Bijlage Paritair Comité voor het hotelbedrijf Collectieve arbeidsovereenkomst van 11 december 2024 Wijziging van de collectieve arbeidsovereenkomst van 27 juli 2010 tot wijziging en coördinatie van de collectieve arbeidsovereenkomsten tot toekenning van een eindejaarspremie (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191530/CO/302) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en werknemers van de ondernemingen die ressorteren onder het Paritair Comité voor het hotelbedrijf. Art. 2. In de collectieve arbeidsovereenkomst van 27 juli 2010, gesloten in het Paritair Comité voor het hotelbedrijf, tot wijziging en coördinatie van de collectieve arbeidsovereenkomsten tot toekenning van een eindejaarspremie, geregistreerd onder het nummer 101764/CO/302 en algemeen verbindend verklaard bij koninklijk besluit van 12 januari 2011, diverse malen gewijzigd, wordt in artikel 9, een punt 10c ingevoegd: "10c. de dagen begrepen in een ononderbroken ziekteperiode van maximum één week (zeven kalenderdagen) in de loop van het kalenderjaar waarop de eindejaarspremie betrekking heeft, op voorwaarde dat deze afwezigheid gerechtvaardigd is conform artikel 31 van de wet van 3 juli 1978 betreffende de arbeidsovereenkomsten. De gelijkstelling duurt zolang de gecumuleerde ziekteperiodes niet meer bedragen dan één week (7 kalenderdagen) gedurende het kalenderjaar. Voor werknemers met meer dan één jaar anciënniteit in de onderneming blijft de periode van 7 dagen gelijkstelling bij arbeidsongeschiktheid behouden, zelfs wanneer over het verloop van één jaar door gecumuleerde periodes van ziekte, de zeven dagen ongeschiktheid overschreden worden, en dit tot een periode van zes maanden onafgebroken arbeidsongeschiktheid bereikt wordt. De gelijkstelling voorzien in onderhavig artikel 10c geldt uitsluitend voor de berekening van de eindejaarspremie met als refertejaar 2024 en refertejaar 2025;". Art. 3. Deze collectieve arbeidsovereenkomst treedt in werking op de dag van ondertekening. Zij wordt gesloten voor een onbepaalde tijd en kan door elk van de partijen worden opgezegd op 1 januari van ieder kalenderjaar middels een opzegtermijn van 6 maand. De opzegging wordt bij een ter post aangetekende brief, gericht aan de voorzitter van het Paritair Comité voor het hotelbedrijf en aan de daarin vertegenwoordigde organisaties betekend voor 1 oktober van het voorafgaande kalenderjaar. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -3000,29 +2994,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2025201445</t>
+          <t>2025002978</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>12 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>28 april 2024. - Koninklijk besluit houdende ontslag en benoeming van een ondervoorzitster van de Nationale Hoge Raad voor Personen met een handicap</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor het tuinbouwbedrijf, betreffende de vaststelling van de loon- en arbeidsvoorwaarden (1)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-12&amp;numac_search=2025201445&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025201445=80&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025002978&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025002978=80&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op artikel 37 van de Grondwet; Gelet op het koninklijk besluit van 9 juli 1981 tot oprichting van een Nationale Hoge Raad voor Personen met een handicap, artikel 3, gewijzigd bij koninklijk besluit van 14 december 2006; Gelet op het koninklijk besluit van 25 juli 2024 houdende ontslag en benoeming van een ondervoorzitster van de Nationale Hoge Raad voor Personen met een handicap, artikel 2; Op de voordracht van de Minister van Personen met een handicap, Hebben Wij besloten en besluiten Wij :Artikel 1. Eervol ontslag uit haar mandaat als lid van de Nationale Hoge Raad voor Personen met een handicap wordt verleend aan mevrouw PARIJ, Corinne.Art. 2. Mevrouw TAMDITI, Khadija, wordt benoemd tot lid van de Nationale Hoge Raad voor Personen met een handicap ter vervanging van mevrouw PARIJ, Corinne, van wie zij het mandaat zal voltooien. Art. 3. Dit besluit heeft uitwerking met ingang van 1 februari 2025. Art. 4. De minister bevoegd voor personen met een handicap is belast met de uitvoering van dit besluit. Gegeven te Brussel, 28 april 2025.FILIPVan Koningswege : De Minister van Personen met een handicap, R. BEENDERS 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor het tuinbouwbedrijf;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 17 december 2024, gesloten in het Paritair Comité voor het tuinbouwbedrijf, betreffende de vaststelling van de loon- en arbeidsvoorwaarden.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het tuinbouwbedrijfCollectieve arbeidsovereenkomst van 17 december 2024Vaststelling van de loon- en arbeidsvoorwaarden (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191538/CO/145)PreambuleBetreft de aanpassing van de lonen en de premies aan de indexering met 3,57 pct. vanaf 1 januari 2025.HOOFDSTUK I. - ToepassingsgebiedArtikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de werknemers van de ondernemingen die ressorteren onder het Paritair Comité voor het tuinbouwbedrijf met inbegrip van de ondernemingen waarvan de hoofdactiviteit bestaat in de aanleg en het onderhoud van parken en tuinen.Zijn uitgesloten :- het seizoens- en gelegenheidspersoneel zoals bedoeld in artikel 8bis van het koninklijk besluit van 28 november 1969;- de bedienden. § 2. Met de term "werknemers" worden de arbeiders bedoeld zonder onderscheid naar gender.HOOFDSTUK II. - Toewijzing van de loonbarema'sArt. 2.  § 1. Onderhavige collectieve arbeidsovereenkomst heeft tot doel voor elke activiteit die in het koninklijk besluit dat het toepassingsgebied van het Paritair Comité voor het tuinbouwbedrijf omschrijft is opgenomen, een toepasselijk loonbarema aan te wijzen. § 2. Onderhavige collectieve overeenkomst vertrekt van het koninklijk besluit van 17 maart 1972 inzake het toepassingsgebied van het Paritair Comité voor het tuinbouwbedrijf (Belgisch Staatsblad van 5 mei 1972). Dit koninklijk besluit is opeenvolgend gewijzigd door de volgende koninklijke besluiten :(1) koninklijk besluit van 29 januari 1991 - Belgisch Staatsblad van 12 februari 1991;(2) koninklijk besluit van 12 augustus 1991 - Belgisch Staatsblad van 29 augustus 1991;(3) koninklijk besluit van 13 november 1996 - Belgisch Staatsblad van 29 november 1996;(4) koninklijk besluit van 7 april 2005 - Belgisch Staatsblad van 26 april 2005;(5) koninklijk besluit van 20 september 2009 - Belgisch Staatsblad van 30 september 2009;(6) koninklijk besluit van 13 maart 2011 - Belgisch Staatsblad van 1 april 2011;(7) koninklijk besluit van 9 januari 2014 - Belgisch Staatsblad van 30 januari 2014;(8) koninklijk besluit van 22 november 2022 - Belgisch Staatsblad van 15 december 2022.Art. 3. Voor de verschillende activiteiten die ressorteren onder het toepassingsgebied van het Paritair Comité voor het tuinbouwbedrijf gelden de volgende loonbarema's :- Barema bloemisterij : 145.1;- Barema bosboomkwekerij : 145.2;- Barema boomkwekerij : 145.3;- Barema tuinaanleg : 145.4;- Barema fruitteelt : 145.5;- Barema groenteteelt : 145.6;- Barema champignonteelt : 145.7.Art. 4. Voor de in de hierboven vermelde koninklijke besluiten opgenomen activiteiten die ressorteren onder het toepassingsgebied van het Paritair Comité voor het tuinbouwbedrijf, dienen respectievelijk de volgende loonbarema's te worden toegepast :1. De groenteteelt, met inbegrip van de speciale teelten, zoals de witloofteelt : barema groenteteelt - 145.6.Voor de paddenstoelenteelt geldt : het barema champignonteelt - 145.7.2. De fruitteelt, met inbegrip van de speciale teelten, zoals druiven-, perziken- en aardbeienteelt : barema fruitteelt - 145.5.3. De bloemen- en sierplantenteelt, alle specialiteiten inbegrepen : barema bloemisterij - 145.1.4. De boomkwekerij, met inbegrip van de rozen en sierheesterteelt : barema boomkwekerij - 145.3.Voor de bosboomkwekerij geldt : het barema bosboomkwekerij - 145.2.5. De teelt van de tuinbouwzaden : één van de hierboven vermelde barema's in functie van de tuinbouwzaden waar het precies over gaat.6. Het aanleggen en/of onderhouden van parken, tuinen, sportterreinen, recreatieterreinen, groene zones, begraafplaatsen, met inbegrip van begraafplaatsen van vreemde militairen in België : barema tuinaanleg - 145.4.7. Het aanleggen en/of onderhouden in eigen beheer van parken, tuinen, sportterreinen, recreatieterreinen of groene zones, wanneer de werklieden van de onderneming hoofdzakelijk aan deze activiteiten zijn tewerkgesteld : barema tuinaanleg - 145.4.8. Het verrichten van onderzoek in verband met tuinbouwgewassen en organiseren van voorlichting in de tuinbouwsector : één van de hierboven vermelde barema's in functie van het tuinbouwgewas waarop het onderzoek en de voorlichting betrekking hebben.9. De ondernemingen waarvan de hoofdactiviteit bestaat uit het sorteren van tuinbouwproducten en die niet ressorteren onder een ander daarvoor specifiek bevoegd paritair comité : één van de hierboven vermelde barema's in functie van de tuinbouwproducten waar het precies over gaat.10. De productie van potgrond, turf, schors en bodem verbeterende producten, voor zover geen ander paritair comité bevoegd is : barema bloemisterij - 145.1.11. Het manueel oogsten van tuinbouwproducten : één van de hierboven vermelde barema's in functie van de tuinbouwproducten waarop de oogst betrekking heeft.12. Het kweken van graszoden, voor zover het Paritair Comité voor de textielnijverheid of het Paritair Comité voor de scheikundige nijverheid niet bevoegd is : barema boomkwekerij - 145.3.13. Het verhuren en onderhouden van planten en/of bloemen bij derden. Voor zover de hoofdactiviteit van de onderneming bestaat in het conditioneren en verhuren van planten : barema - 145.4.Voor zover het verhuren en onderhouden van planten een nevenactiviteit is van het kweken van planten of bloemen : barema bloemisterij - 145.1 of barema boomkwekerij - 145.3 in functie van de planten of bloemen waar het in hoofdzaak over gaat.14. Het snoeien van fruitbomen voor rekening van derden : barema fruitteelt - 145.5.HOOFDSTUK III. - FunctieclassificatieBloemisterijArt. 5. De functies van de werknemers die werkzaam zijn in de bloemisterij (barema 145.1) worden als volgt ingedeeld :Categorie 1Dit is de categorie waar werknemers zonder ervaring starten. Het is bijgevolg per definitie een tijdelijke categorie. Wie maximum 18 maanden deze functie heeft uitgeoefend en bijgevolg de nodige kennis/ervaring heeft opgedaan zal automatisch overgaan naar de hogere categorie. Via een inhoudelijke weging die de effectiviteit van de prestaties beoordeelt, kunnen werknemers vroeger overgaan naar categorie 2.Categorie 2Hiertoe behoren de basismedewerkers met ervaring. Zij beoefenen hun job onder de verantwoordelijkheid van een andere persoon die de eindverantwoordelijkheid draagt. Desalniettemin wordt van hen een zekere zelfstandigheid inzake de uitvoering van het werk verwacht. Zij worden niet geacht om polyvalent inzetbaar te zijn.Categorie 3Hiertoe behoren de werknemers die zelfstandig technische functies uitoefenen en hiertoe over een zekere polyvalentie inzake plantengroepen en taken moeten beschikken. Zij hebben verantwoordelijkheid over de kwaliteit van de resultaten van hun eigen werk.Categorie 4Tot deze categorie behoren de werknemers die zelf leiding geven aan een groep van medewerkers uit de lagere categorieën. Behoren ook tot deze categorie : de werknemers die door de aard van de producten waarmee ze werken (bijvoorbeeld plantenbeschermingsmiddelen) een grote verantwoordelijkheid dragen voor de planten enerzijds en voor hun collega's anderzijds.Categorie 5Voor bedrijven groter dan 50 werknemers kan via onderhandelingen op bedrijfsvlak bovenop de sectorale afspraken een extra categorie worden toegevoegd. Het gaat hier om werknemers met de hoogste verantwoordelijkheid. Deze werknemers ontvangen hun order rechtstreeks van de leiding van de onderneming. Ze zijn bovendien eindverantwoordelijk voor de opdrachten en het product. Dit houdt ook in dat zij leiding moeten geven aan andere werknemers van categorie 3 en categorie 4 (die zelf reeds leiding geven aan een groep van medewerkers uit de lagere categorieën), en de verantwoordelijkheid hiervoor dragen. (Bos)BoomkwekerijArt. 6. De functies van de werknemers die werkzaam zijn in de bosboomkwekerij (barema 145.2) en boomkwekerij (barema 145.3) worden als volgt ingedeeld :Categorie 1De werknemers met de nodige ervaring. Zij beoefenen hun job onder de verantwoordelijkheid van een andere persoon die de eindverantwoordelijkheid draagt. Er wordt van deze medewerkers een zekere zelfstandigheid gevraagd inzake de uitvoering van het werk. Zij worden geacht over een zekere polyvalentie te beschikken.Categorie 2De werknemers die zelfstandig technische functies kunnen uitoefenen en hiertoe over een polyvalentie beschikken inzake plantengroepen en taken.Zij hebben verantwoordelijkheid over de kwaliteit van de resultaten van hun eigen werk. De werknemer moet over een degelijke assortimentskennis beschikken.Categorie 3De werknemers die over een grotere polyvalentie beschikken en die zelf leiding geven aan een groep van medewerkers uit de lagere categorieën. Behoren eveneens tot deze categorie : de werknemers die door de aard van het werk een eindverantwoordelijkheid dragen voor de totale afwerking van een gegeven opdracht en voor hun collega's anderzijds.Categorie 4De werknemers met de hoogste verantwoordelijkheid. Zij zijn bovendien eindverantwoordelijk voor een groot gedeelte van de productie gebonden bedrijfsvoering en/of logistiek. Dit houdt in dat zij leiding moeten geven aan andere werknemers van alle lagere categorieën en de verantwoordelijkheid hiervoor dragen.Parken en tuinenArt. 7. De functies van de werknemers die werkzaam zijn in de ondernemingen voor het inplanten en onderhouden van parken en tuinen (barema 145.4) worden als volgt ingedeeld :Categorie 1Hiertoe behoren de werknemers die starten zonder ervaring en zonder opleiding in de groensector en die niet zelfstandig kunnen werken.Wie maximum 18 maanden deze functie heeft uitgeoefend, gaat over naar categorie 2.Categorie 2Tot deze categorie behoren de basiswerknemers met ervaring. Zij beoefenen hun job onder de verantwoordelijkheid van een andere persoon die de eindverantwoordelijkheid draagt. Desalniettemin wordt van hen een zekere zelfstandigheid inzake de uitvoering van het werk verwacht. Zij worden niet geacht polyvalent inzetbaar te zijn.Categorie 3Hiertoe behoren de werknemers die zelfstandig alle technische functies uitoefenen en hiertoe over een zekere polyvalentie inzake taken moeten beschikken. Bijvoorbeeld :- grondwerkzaamheden : bewerkingen, bemestingen, chemische en/of mechanische onkruidbeheersing,...- beplantingswerkzaamheden : snoeien, maaien, aanplanten, zaaien, aanbinden, gewasbescherming,...- constructiewerkzaamheden : bestratingen, tuinmuurtjes en -trappen, afsluitingen,...Zij hebben verantwoordelijkheid over de kwaliteit van de resultaten van hun eigen werk.Categorie 4Tot deze categorie behoren de werknemers die zelfstandig alle technische functies uitoefenen en hiertoe over een zekere polyvalentie inzake taken moeten beschikken. Bijvoorbeeld :- grondwerkzaamheden : bewerkingen, bemestingen, chemische en/of mechanische onkruidbeheersing,...- beplantingswerkzaamheden : snoeien, maaien, aanplanten, zaaien, aanbinden, gewasbescherming,...- constructiewerkzaamheden : bestratingen, tuinmuurtjes en -trappen, afsluitingen,...Zij geven bovendien zelf leiding aan één of meerdere medewerkers uit de lagere categorieën, en hebben verantwoordelijkheid over de kwaliteit van de resultaten van hun eigen werk en dat van hun medewerkers waaraan zij leiding geven.Behoren ook tot deze categorie :a) de werknemers uit de categorie 3 die in hoofdzaak onderhoudswerkzaamheden verrichten langs wegen aangeduid met de verkeerstekens F5 en F9 en langs wegen met twee of meer baanvakken, gescheiden door een bezaaide of beplante middenberm;b) de werknemers uit de categorie 3 die regelmatig of in hoofdzaak boomverzorgingswerkzaamheden verrichten;c) de werknemers die regelmatig of in hoofdzaak gevaarlijke machines besturen of bedienen (cfr. graafmachine, klepelmaaier, hoogtewerker,...).Categorie 5Tot deze categorie behoren de werknemers die leiding moeten geven aan werknemers van de categorie 4.Zij hebben verantwoordelijkheid over de kwaliteit van de resultaten van hun eigen werk en dat van hun medewerkers waaraan zij leiding geven.FruitteeltArt. 8. De functies van de werknemers die werkzaam zijn in de fruitteelt (barema 145.5) worden als volgt ingedeeld :Categorie 1De werknemers met de nodige ervaring. De job wordt uitgevoerd onder verantwoordelijkheid van een andere persoon.De volgende kenmerken zijn van belang :- Zelfstandigheid;- Kwaliteitsbewustzijn;- Handigheid;- Inzetbaarheid voor meerdere taken.Categorie 2De werknemers die :- Zelfstandig technische functies uitoefenen en/of- Leiding geven over een (kleine) groep werknemers uit categorie 1.De volgende kenmerken zijn van belang : basis van teelt technische kennis.Als voorbeeld verstaat men hieronder herkennen van ziekten en plagen en/of kennis hebben van gebruik van gewasbeschermingsmiddelen.Categorie 3De werknemers die :- Zelf leiding geven aan een groep medewerkers van categorie 1 en categorie 2.Deze categorie is ook van toepassing voor werknemers die eindverantwoordelijkheid dragen.Deze werknemers kunnen de werkgever vervangen gedurende korte tijd en nemen bijvoorbeeld zelf kleine beslissingen inzake teelt, werk en arbeiders.Categorie 4De werknemers met de hoogste verantwoordelijkheid. Deze werknemers zijn eindverantwoordelijk voor een groot gedeelte van de productie gebonden bedrijfsvoering en/of logistiek.De volgende kenmerken zijn van belang :- Leiding geven aan andere werknemers;- Volledige kennis teelt, ziekte en plagen;- Kennis van de kwaliteitsvereisten;- Vervanging van de werkgever gedurende langere tijd mogelijk.GroenteteeltArt. 9. De functies van de werknemers die werkzaam zijn in de glastuinbouw, groenten open lucht en witloofteelt (barema 145.6) worden als volgt ingedeeld :Categorie 1De werknemers met de nodige ervaring. De job wordt uitgevoerd onder verantwoordelijkheid van een andere persoon.De volgende kenmerken zijn van belang :- Zelfstandigheid;- Kwaliteitsbewustzijn;- Handigheid;- Inzetbaarheid voor meerdere taken.Categorie 2De werknemers die :- Zelfstandig technische functies uitoefenen en/of- Leiding geven over een (kleine) groep werknemers uit categorie 1.De volgende kenmerken zijn van belang : basis van teelt technische kennis.Als voorbeeld verstaat men hieronder herkennen van ziekten en plagen en/of kennis hebben van gebruik van gewasbeschermingsmiddelen.Categorie 3De werknemers die :- Zelf leiding geven aan een groep medewerkers van categorie 1 en categorie 2.Deze categorie is ook van toepassing voor werknemers die eindverantwoordelijkheid dragen.Deze werknemers kunnen de werkgever vervangen gedurende korte tijd en nemen bijvoorbeeld zelf kleine beslissingen inzake teelt, werk en arbeiders.Categorie 4Bedrijven van meer dan vijftig werknemers kunnen via onderhandelingen op bedrijfsvlak bovenop de sectorale afspraken een extra categorie toevoegen.Deze categorie is voor werknemers met de hoogste verantwoordelijkheid.Deze werknemers zijn eindverantwoordelijk voor een groot gedeelte van de productie gebonden bedrijfsvoering en/of logistiek.De volgende kenmerken zijn van belang :- Leiding geven aan andere werknemers;- Volledige kennis teelt, ziekten en plagen;- Kennis van de kwaliteitsvereisten;- Vervanging van de werkgever gedurende langere tijd mogelijk.ChampignonteeltArt. 10. De functies van de werknemers die werkzaam zijn in de ondernemingen in de champignonteelt (barema 145.7) worden als volgt ingedeeld :Categorie 1De werknemers die basiswerkzaamheden kunnen uitvoeren en die geen ervaring hebben in de champignonsector. Na afloop van deze opleidingsperiode gedurende 6 maanden gaan deze werknemers over naar categorie 2.Categorie 2De werknemers die instaan voor de volgende werkzaamheden of die de volgende hoedanigheid hebben : plukmedewerkers, werkvoorbereiders, inpakkers, kantinemedewerkers, fustmedewerkers, afwegers, poetspersoneel tijdens de teelt,...Categorie 3De werknemers van wie tot de essentie van hun takenpakket behoort om leiding te geven aan een groep van medewerkers-werknemers die behoren tot categorie 1 of 2. Deze werknemers kunnen tevens instaan voor kwaliteitscontrole van het geplukte product, voor de afweging en voor de praktische werkorganisatie.In functie hiervan kunnen zij instructies geven aan medewerkers van categorie 1 en 2 aangaande plukwijze, de kwaliteit, de werkplanning en -organisatie.Commentaar : In de ondernemingen met 50 en meer werknemers kan de werknemer die instaat voor het afwegen en het uitoefenen van een controle op de kwaliteit van het product tot categorie 3 behoren volgens de modaliteiten die in dit verband op ondernemingsvlak werden afgesproken.Categorie 4De werknemers die beschikken over een technische kennis (elektriciteit, klimatiseren, mechanica,...) en die tewerkgesteld zijn aan onder meer de volgende werken : grote schoonmaak tussen de teelten, meehelpen bij de uitvoering van de teelt, voertuigen (of heftrucks) besturen, machines die voor teelt nodig zijn besturen, onderhoud van machines en installaties, uitvoeren van herstellingen.Categorie 5In de ondernemingen met 50 en meer werknemers kan via onderhandelingen op ondernemingsvlak voorzien worden in een vijfde categorie van werknemers.De drempel van 50 werknemers wordt berekend zoals voor wat betreft de organisatie van de sociale verkiezingen.Tot deze categorie behoren de werknemers met de hoogste verantwoordelijkheid onder de productiechef en ontvangen er hun orders rechtstreeks van. Zij geven leiding aan andere werknemers en dragen hiervoor de verantwoordelijkheid.HOOFDSTUK IV. - LoonvoorwaardenBloemisterijArt. 11. Op 1 januari 2025 worden de minimumuurlonen en de werkelijk betaalde lonen voor de werknemers van 18 jaar en ouder die werkzaam zijn in de bloemisterij (barema 145.1) geïndexeerd met 3,57 pct. Op basis van een wekelijkse arbeidsduur van 38 uren bedragen de minimumuurlonen vanaf 1 januari 2025 :  </t>
         </is>
       </c>
     </row>
@@ -3032,28 +3025,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2025003634</t>
+          <t>2025201196</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>16 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>25 april 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 20 oktober 2011 tot uitvoering van de wet van 15 mei 2007 betreffende de bestraffing van namaak en piraterij van intellectuele eigendomsrechten. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 14 januari 2025, gesloten in het Paritair Comité voor de ondernemingen van technische land- en tuinbouwwerken, met betrekking tot de loon- en arbeidsvoorwaarden (1)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-16&amp;numac_search=2025003634&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003634=81&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025201196&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201196=81&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
           <t xml:space="preserve">
- De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 25 april 2024 tot wijziging van het koninklijk besluit van 20 oktober 2011 tot uitvoering van de wet van 15 mei 2007 betreffende de bestraffing van namaak en piraterij van intellectuele eigendomsrechten (Belgisch Staatsblad van 23 mei 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST WIRTSCHAFT, KMB, MITTELSTAND UND ENERGIE25. APRIL 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 20. Oktober 2011 zur Ausführung des Gesetzes vom 15. Mai 2007 über die Ahndung der Nachahmung und der Piraterie von geistigen EigentumsrechtenPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund der Verfassung, des Artikels 108;Aufgrund des Wirtschaftsgesetzbuches, des Artikels XV.62 § 2, eingefügt durch das Gesetz vom 19. April 2014;Aufgrund des Gesetzes vom 15. Mai 2007 über die Ahndung der Nachahmung und der Piraterie von geistigen Eigentumsrechten, der Artikel 3 und 4 Absatz 2;Aufgrund des Königlichen Erlasses vom 20. Oktober 2011 zur Ausführung des Gesetzes vom 15. Mai 2007 über die Ahndung der Nachahmung und der Piraterie von geistigen Eigentumsrechten;Aufgrund der Stellungnahme des Finanzinspektors vom 22. Juni 2023;Aufgrund des Einverständnisses der Staatssekretärin für Haushalt vom 19. September 2023;Aufgrund der Auswirkungsanalyse beim Erlass von Vorschriften, die gemäß den Artikeln 6 und 7 des Gesetzes vom 15. Dezember 2013 zur Festlegung verschiedener Bestimmungen in Sachen administrative Vereinfachung durchgeführt worden ist;Aufgrund des Antrags auf Begutachtung binnen einer Frist von dreißig Tagen, der in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat beim Staatsrat eingereicht worden ist;In der Erwägung, dass der Antrag auf Begutachtung am 21. Dezember 2023 unter der Nummer 75.186/1 in die Liste der Gesetzgebungsabteilung des Staatsrates eingetragen worden ist;Aufgrund des Beschlusses der Gesetzgebungsabteilung vom 27. Dezember 2023 in Anwendung von Artikel 84 § 5 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat, binnen der gesetzten Frist kein Gutachten abzugeben;Auf Vorschlag des Ministers der Wirtschaft, des Ministers der Finanzen und des Ministers der Justiz und aufgrund der Stellungnahme der Minister, die im Rat darüber beraten haben,Haben Wir beschloßen und erlassen Wir:Artikel 1 - Die Überschrift des Königlichen Erlasses vom 20. Oktober 2011 zur Ausführung des Gesetzes vom 15. Mai 2007 über die Ahndung der Nachahmung und der Piraterie von geistigen Eigentumsrechten wird wie folgt ersetzt: "Königlicher Erlass über bestimmte Modalitäten in Bezug auf die Ahndung der Nachahmung und der Piraterie von geistigen Eigentumsrechten".Art. 2 - In Artikel 1 desselben Erlasses wird Nr. 2 wie folgt ersetzt:"2. Verordnung: die Verordnung (EU) Nr. 608/2013 des Europäischen Parlaments und des Rates vom 12. Juni 2013 zur Durchsetzung der Rechte geistigen Eigentums durch die Zollbehörden und zur Aufhebung der Verordnung (EG) Nr. 1383/2003 des Rates."Art. 3 - In Artikel 2 desselben Erlasses werden zwischen den Wörtern "Der Generalverwalter" und den Wörtern "Zoll und Akzisen" die Wörter "der Generalverwaltung" eingefügt und werden im zweiten Gedankenstrich die Wörter "Artikel 5 Absatz 7" durch die Wörter "Artikel 9 Absatz 1 und 2" ersetzt.Art. 4 - In der Überschrift von Kapitel 3 Abschnitt 1 desselben Erlasses werden die Wörter "13/1, 16 und 17 des Gesetzes" durch die Wörter "XV.25/3, XV.31 und XV.62 des Wirtschaftsgesetzbuches" ersetzt.Art. 5 - Artikel 4 desselben Erlasses wird wie folgt ersetzt:"Art. 4 - Unbeschadet der in den Artikeln XV.34, XV.58 und XV.59 des Wirtschaftsgesetzbuches vorgesehenen Koordinierung und Zusammenarbeit werden Protokolle zur Feststellung von Verstößen, die in den Artikeln XV.103, XV.107 und XV.108 sowie in den Artikeln XI.293, XI.304 und XI.318 des Wirtschaftsgesetzbuches erwähnt sind, für die Anwendung von Artikel XV.62 § 1 des Wirtschaftsgesetzbuches übermittelt an den vom Minister bestellten Bediensteten gemäß Artikel XV.2 § 1 des Wirtschaftsgesetzbuches, im Hinblick auf die Anwendung von Artikel XV.62:1. an den Regionaldirektor der Generalverwaltung Zoll und Akzisen, der für den Ort zuständig ist, an dem der Verstoß begangen wurde, wenn das Protokoll von Bediensteten der Generalverwaltung Zoll und Akzisen aufgenommen wird, die in Artikel XV.25/1 Absatz 1 des Wirtschaftsgesetzbuches erwähnt sind,2. oder an den Generaldirektor der Generaldirektion Wirtschaftsinspektion des Föderalen Öffentlichen Dienstes Wirtschaft, KMB, Mittelstand und Energie, wenn das Protokoll von Bediensteten der Generaldirektion Wirtschaftsinspektion aufgenommen wird, die in Anwendung von Artikel XV.25/1 Absatz 1 des Wirtschaftsgesetzbuches bestellt werden,3. oder an einen zu diesem Zweck durch Ministeriellen Erlass bestimmten Bediensteten, wenn das Protokoll von Bediensteten aufgenommen wird, die in Anwendung von Artikel XV.25/1 Absatz 1 des Wirtschaftsgesetzbuches zu diesem Zweck von dem für Wirtschaft zuständigen Minister oder dem für Finanzen zuständigen Minister bestellt werden."Art. 6 - In Artikel 5 desselben Erlasses werden die Wörter "in Artikel 18 des Gesetzes" durch die Wörter "in den Artikeln XV.2 und XV.25/1 des Wirtschaftsgesetzbuches" und die Wörter "in Ausführung dieses Artikels" durch die Wörter "gemäß vorliegendem Artikel" ersetzt.Art. 7 - In Artikel 6 Absatz 1 und 2 desselben Erlasses werden die Wörter "des Artikels 17 des Gesetzes" jeweils durch die Wörter "des Artikels XV.62 des Wirtschaftsgesetzbuches" ersetzt.Art. 8 - Artikel 7 desselben Erlasses wird wie folgt ersetzt:"Art. 7 - § 1 - Beträge, die einem Zuwiderhandelnden im Rahmen einer Vergleichsregelung im Sinne des Artikels XV.62 des Wirtschaftsgesetzbuches zur Zahlung vorgeschlagen werden, dürfen folgende Beträge nicht unterschreiten:1. 50 EUR für die in Artikel XV.103 des Wirtschaftsgesetzbuches erwähnten Verstöße,2. 50 EUR für die in Artikel XV.107 des Wirtschaftsgesetzbuches erwähnten Verstöße,3. 100 EUR für die in Artikel XV.108 des Wirtschaftsgesetzbuches erwähnten Verstöße.In Anwendung der Artikel XV.2 § 2 und XV.25/1 des Wirtschaftsgesetzbuches ist Absatz 1 Nr. 1 ebenfalls anwendbar auf Verstöße, die in den Artikeln XI.293, XI.304 und XI.318 des Wirtschaftsgesetzbuches erwähnt sind. § 2 - Beträge, die einem Zuwiderhandelnden im Rahmen einer Vergleichsregelung im Sinne des Artikels XV.62 des Wirtschaftsgesetzbuches zur Zahlung vorgeschlagen werden, dürfen folgende Beträge nicht überschreiten:1. 275.000 EUR für die in Artikel XV.103 des Wirtschaftsgesetzbuches erwähnten Verstöße,2. 13.750 EUR für die in Artikel XV.107 des Wirtschaftsgesetzbuches erwähnten Verstöße,3. 27.500 EUR für die in Artikel XV.108 des Wirtschaftsgesetzbuches erwähnten Verstöße.In Anwendung der Artikel XV.2 § 2 und XV.25/1 des Wirtschaftsgesetzbuches ist Absatz 1 ebenfalls anwendbar auf Verstöße, die in den Artikeln XI.293, XI.304 und XI.318 des Wirtschaftsgesetzbuches erwähnt sind. § 3 - Bei Zusammentreffen mehrerer solcher Verstöße werden die verschiedenen Beträge zusammengerechnet, ohne dass der Gesamtbetrag 550.000 EUR übersteigen darf.In Anwendung der Artikel XV.2 § 2 und XV.25/1 des Wirtschaftsgesetzbuches ist Absatz 1 ebenfalls anwendbar auf Verstöße, die in den Artikeln XI.293, XI.304 und XI.318 des Wirtschaftsgesetzbuches erwähnt sind."Art. 9 - In Artikel 10 desselben Erlasses werden die Wörter "Artikel 17 § 1 des Gesetzes" durch die Wörter "Artikel XV.62 § 1 des Wirtschaftsgesetzbuches" und die Wörter "den in Artikel 17 des Gesetzes erwähnten Bediensteten" durch die Wörter "den eigens zu diesem Zweck bestimmten Bediensteten wie in Artikel XV.62 des Wirtschaftsgesetzbuches erwähnt" ersetzt.Art. 10 - Artikel 11 desselben Erlasses wird wie folgt abgeändert:1. In Absatz 1 werden die Wörter "die in Artikel 17 des Gesetzes erwähnten Bediensteten" durch die Wörter "die eigens zu diesem Zweck bestimmten Bediensteten wie in Artikel XV.62 des Wirtschaftsgesetzbuches erwähnt" ersetzt.2. [Abänderung des französischen Textes von Absatz 1]3. In Absatz 1 werden die Wörter "in Artikel 18 des Gesetzes" durch die Wörter "in den Artikeln XV.2 § 2 und XV.25/1 des Wirtschaftsgesetzbuches" ersetzt.4. In Absatz 2 werden die Wörter "in den Artikeln 17 und 18 des Gesetzes" durch die Wörter "in den Artikeln XV.2, XV.25/1 und XV.62 des Wirtschaftsgesetzbuches" ersetzt.Art. 11 - Artikel 12 desselben Erlasses wird wie folgt abgeändert:1. In § 1 Absatz 1 werden die Wörter "des Artikels 17 § 1 Absatz 1 des Gesetzes" durch die Wörter "des Artikels XV.62 § 1 Absatz 1 des Wirtschaftsgesetzbuches" ersetzt.2. In § 1 Absatz 1 werden die Wörter "des Artikels 13/1 Absatz 3 des Gesetzes" durch die Wörter "des Artikels XV.25/3 des Wirtschaftsgesetzbuches" ersetzt.3. In § 1 Absatz 3 werden die Wörter "in Artikel 16" durch die Wörter "in Artikel XV.31 des Wirtschaftsgesetzbuches" ersetzt.4. In § 2 Absatz 1 werden die Wörter "des Artikels 17 § 1 Absatz 3 des Gesetzes" durch die Wörter "des Artikels XV.62 § 1 des Wirtschaftsgesetzbuches" ersetzt.Art. 12 - In der Überschrift von Kapitel 3 Abschnitt 2 desselben Erlasses werden die Wörter "Artikel 13 § 3 des Gesetzes" durch die Wörter "Artikel XV.30/1 des Wirtschaftsgesetzbuches" ersetzt.Art. 13 - Artikel 13 desselben Erlasses wird wie folgt abgeändert:1. In Absatz 1 werden die Wörter "des Artikels 13 § 3 Absatz 1 des Gesetzes" durch die Wörter "des Artikels XV.30/1 des Wirtschaftsgesetzbuches" und die Wörter "in Artikel 18 des Gesetzes" durch die Wörter "in den Artikeln XV.2 § 2 und XV.25/1 des Wirtschaftsgesetzbuches" ersetzt.2. In Absatz 2 werden die Wörter "in den Artikeln 17 und 18 des Gesetzes" durch die Wörter "in den Artikeln XV.2, XV.25/1 und XV.62 des Wirtschaftsgesetzbuches" ersetzt.Art. 14 - In Artikel 14 desselben Erlasses werden die Wörter "befugt, in Anwendung des Artikels 13 § 3 Absatz 4 des Gesetzes und des Artikels 13 § 4 Absatz 1 des Gesetzes die" durch die Wörter "in Anwendung von Artikel XV.30/1 § 1 Absatz 3 und Artikel XV.30/1 § 2 Absatz 1 des Wirtschaftsgesetzbuches befugt, die" ersetzt.Art. 15 - In Artikel 15 § 1 Absatz 1 desselben Erlasses werden die Wörter "der Artikel 13 § 3 Absatz 6, 13/1 Absatz 5 und 19 § 1 Nr. 2 Buchstabe e) des Gesetzes" durch die Wörter "der Artikel XV.25/3 Absatz 5 und XV.30/1 § 1 Absatz 6 des Wirtschaftsgesetzbuches" ersetzt.Art. 16 - Vorliegender Erlass tritt am ersten Tag des zweiten Monats nach dem Monat seiner Veröffentlichung im Belgischen Staatsblatt in Kraft.Art. 17 - Die für Wirtschaft, Finanzen beziehungsweise Justiz zuständigen Minister sind, jeweils für ihren Bereich, mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 25. April 2024PHILIPPEVon Königs wegen:Der Minister der WirtschaftP.-Y. DERMAGNEDer Minister der FinanzenV. VAN PETEGHEMDer Minister der JustizP. VAN TIGCHELT 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de ondernemingen van technische land- en tuinbouwwerken; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 14 januari 2025, gesloten in het Paritair Comité voor de ondernemingen van technische land- en tuinbouwwerken, met betrekking tot de loon- en arbeidsvoorwaarden. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de ondernemingen van technische land- en tuinbouwwerken Collectieve arbeidsovereenkomst van 14 januari 2025 Loon- en arbeidsvoorwaarden (Overeenkomst geregistreerd op 31 januari 2025 onder het nummer 191695/CO/132) Preambule Deze collectieve arbeidsovereenkomst heeft als doel het in artikel 2 (loon van de categorie 1A) schrappen van de verwijzing naar de lonen van de seizoenwerknemers in de landbouwsector. Tegelijk worden de op 1 januari 2025 geïndexeerde lonen vastgesteld. HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en hun werknemers van de ondernemingen die ressorteren onder het Paritair Comité voor de ondernemingen van technische land- en tuinbouwwerken. Onder "werknemers" wordt verstaan : de arbeiders zonder onderscheid naar gender. HOOFDSTUK II. Omschrijving van de categorieën Art. 2.  Categorie 1. Dit is de categorie waar ongeschoolden zonder ervaring starten. 1A. De tijdelijke werknemers die enkel bijspringen in drukke periodes, die werken op basis van schriftelijke dagcontracten en die aangemeld worden via Dimona. Deze werknemers werken maximum 25 dagen op jaarbasis in de sector. 1B. Nieuw aangeworven werknemers, ongeschoold en zonder ervaring, evenals de werknemers die niet ressorteren onder categorie 1A. Toepassingsmodaliteiten van categorieën 1A en 1B : - Bij dagcontracten zijn de eerste 25 dagen aan categorie 1A; vanaf de 26ste dag aan categorie 1B; - Dagcontracten die vanaf de 26ste dag nog steeds categorie 1A vermelden vallen automatisch onder categorie 1B vanaf de 1ste dag van tewerkstelling; - Contracten van onbepaalde duur vallen steeds onder minimaal categorie 1B vanaf de eerste dag van tewerkstelling. Categorie 2. Hiertoe behoren de basismedewerkers met minimum één jaar ervaring. Zij beoefenen de job onder de verantwoordelijkheid van een teamleider of bedrijfsleider die de eindverantwoordelijkheid draagt. Ze zijn niet polyvalent inzetbaar en voeren steeds dezelfde functie uit. Categorie 3. Hiertoe behoren de volgende werknemers : - arbeiders die technische functies uitoefenen; - arbeiders die over een zekere polyvalentie inzake besturen van machines en mechanisatie beschikken. Behoren bijvoorbeeld tot categorie 3 : polyvalente chauffeurs en mecaniciens. Categorie 4. Tot deze categorie behoren de werknemers die rechtstreeks ressorteren onder de verantwoordelijken categorie 5 en die zelf ook leiding geven. Behoren ook tot categorie 4 : de werknemers die door de aard van de producten waarmee ze werken (bijvoorbeeld sproeistoffen,...) een grote verantwoordelijkheid dragen voor hun collega's enerzijds en voor de landbouwproducten anderzijds. Categorie 5. Tot deze categorie behoren de verantwoordelijken. Deze werknemers kunnen volledig zelfstandig werken. Ze werken rechtstreeks onder de bedrijfsleiding en ze dragen de eindverantwoordelijkheid voor de opdrachten. Dit houdt in dat ze leiding geven over andere werknemers. HOOFDSTUK III. - Minimumuurlonen Art. 3. De minimumuurlonen van de in artikel 1 bedoelde werknemers werden op 1 januari 2008, vóór indexatie, als volgt vastgesteld : - Categorie 1A : 7,50 EUR; - Categorie 1B : 9,16 EUR; - Categorie 2 : 9,62 EUR; - Categorie 3 : 10,12 EUR; - Categorie 4 : 11,13 EUR;- Categorie 5 : 12,24 EUR. De minimumlonen van toepassing vanaf 1 januari 2025 na indexering zijn dan als volgt : - Categorie 1A : 12,01 EUR; - Categorie 1B : 14,11 EUR; - Categorie 2 : 14,85 EUR; - Categorie 3 : 15,58 EUR; - Categorie 4 : 17,13 EUR; - Categorie 5 : 18,78 EUR. De lonen gelden voor een maximum wekelijkse arbeidsduur van 38 uren. HOOFDSTUK IV. - Anciënniteitstoeslag Art. 4. De werkgever is ertoe gehouden aan de werknemers een anciënniteitstoeslag te betalen, als volgt vastgesteld : - voor werknemers die 1 tot 5 jaar anciënniteit hebben in de onderneming : toeslag van 0,03 EUR per uur; - voor werknemers die 5 tot 10 jaar anciënniteit hebben in de onderneming : toeslag van 0,05 EUR per uur; - voor werknemers die 10 tot 15 jaar anciënniteit hebben in de onderneming : toeslag van 0,15 EUR per uur; - voor werknemers die 15 tot 20 jaar anciënniteit hebben in de onderneming : toeslag van 0,25 EUR per uur; - voor werknemers die 20 tot 25 jaar anciënniteit hebben in de onderneming : toeslag van 0,38 EUR per uur; - voor werknemers die 25 tot 30 jaar anciënniteit hebben in de onderneming : toeslag van 0,50 EUR per uur; - voor werknemers die 30 tot 35 jaar anciënniteit hebben in de onderneming : toeslag van 0,65 EUR per uur; - voor werknemers die 35 tot 40 jaar anciënniteit hebben in de onderneming : toeslag van 0,80 EUR per uur; - voor werknemers vanaf 40 jaar anciënniteit in de onderneming : toeslag van 1,00 EUR per uur. Art. 5. Voor de berekening van het loon worden al de uren in aanmerking genomen gedurende welke de werknemer ter beschikking van de werkgever zijn mits aftrek van de duur der schafttijden. HOOFDSTUK V. - Minimumweekloon Art. 6. Een minimumweekloon, gelijk aan het gemiddeld loon verdiend gedurende de voorgaande twee weken, dat niet minder mag bedragen dan het loon voor het van kracht zijnde aantal wekelijkse arbeidsuren, is gewaarborgd aan de werknemers. Het minimumweekloon wordt aan de werknemers gewaarborgd voor elke week tijdens dewelke zij niet meer dan één dag onvrijwillig werkloos zijn. HOOFDSTUK VI. - Nachtwerk Art. 7. Voor de arbeid verricht tussen 22 uur en 6 uur (23 uur en 7 uur in de zomeruurregeling), is de werkgever verplicht de betrokken werknemers een toeslag van 20 pct. op het loon te betalen. Art. 8. De werkhervatting mag voor de werknemers die nachtwerk hebben verricht slechts volgen na een rustperiode van minstens acht uren wanneer dit nachtwerk zich uitzonderlijk voordoet en geen normaal en vastgesteld arbeidsstelsel is en wat de werkneemsters betreft. HOOFDSTUK VII. - Koppeling van de lonen en vergoedingen aan het indexcijfer van de consumptieprijzen Art. 9. Het minimumuurloon evenals de werkelijk betaalde lonen en vergoedingen worden gekoppeld aan de evolutie van de afgevlakte gezondheidsindex, overeenkomstig de bepalingen van de collectieve arbeidsovereenkomst van 1 september 2023, gesloten in het Paritair Comité voor de ondernemingen van technische land- en tuinbouwwerken, tot koppeling van de lonen en vergoedingen aan de evolutie van de afgevlakte gezondheidsindex. HOOFDSTUK VIII. - Bijzondere bepalingen Art. 10. Onverminderd de bepalingen van deze collectieve arbeidsovereenkomst, blijven de gunstigere loon- en arbeidsvoorwaarden, voorzien bij particuliere akkoorden gesloten op het vlak van de onderneming behouden.HOOFDSTUK IX. - Geldigheid Art. 11. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025 en is gesloten voor een onbepaalde duur. Zij vervangt de collectieve arbeidsovereenkomst van 22 mei 2024, geregistreerd onder het nr. 187916/CO/132 betreffende de loon- en arbeidsvoorwaarden. Zij kan door elk van de ondertekenende partijen worden opgezegd mits een opzegging van ten minste drie maanden, betekend bij een ter post aangetekende brief, gericht aan de voorzitter van het Paritair Comité voor de ondernemingen van technische land- en tuinbouwwerken. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -3064,28 +3057,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2025003308</t>
+          <t>2025003005</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>05 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>24 april 2024. - Koninklijk besluit tot wijziging van het Koninklijk besluit van 30 december 2009 tot het bepalen van de definitie en de voorwaarden waaraan een geregistreerd kassasysteem in de horecasector moet voldoen. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 21 januari 2025, gesloten in het Paritair Comité voor de scheikundige nijverheid, met betrekking tot een suppletieve regeling deconnectie tot vaststelling van sommige arbeidsvoorwaarden voor de kunststofverwerkende nijverheid van de provincie West-Vlaanderen (1)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-05&amp;numac_search=2025003308&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003308=82&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025003005&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003005=82&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 24 april 2024 tot wijziging van het Koninklijk besluit van 30 december 2009 tot het bepalen van de definitie en de voorwaarden waaraan een geregistreerd kassasysteem in de horecasector moet voldoen (Belgisch Staatsblad van 21 mei 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de scheikundige nijverheid;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 21 januari 2025, gesloten in het Paritair Comité voor de scheikundige nijverheid, met betrekking tot een suppletieve regeling deconnectie tot vaststelling van sommige arbeidsvoorwaarden voor de kunststofverwerkende nijverheid van de provincie West-Vlaanderen.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 7 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de scheikundige nijverheidCollectieve arbeidsovereenkomst van 21 januari 2025Betrekking tot een suppletieve regeling deconnectie tot vaststelling van sommige arbeidsvoorwaarden voor de kunststofverwerkende nijverheid van de provincie West-Vlaanderen (Overeenkomst geregistreerd op 31 januari 2025 onder het nummer 191697/CO/116)HOOFDSTUK I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers, die 20 of meer werknemers tewerkstellen en de arbeiders, hierna "de werknemers" genoemd, van de ondernemingen die gelegen zijn in de provincie West-Vlaanderen en ressorteren onder het Paritair Comité voor de scheikundige nijverheid uit hoofde van hun bedrijvigheid inzake verwerking van kunststoffen en die op datum van het afsluiten van onderhavige collectieve arbeidsovereenkomst of op een latere datum, geen eigen regeling rond deconnectie hebben op ondernemingsvlak.Met "werknemers" wordt verstaan : de mannelijke en vrouwelijke werknemers.Met "de onderneming" wordt verstaan : de werkgever.Art. 2. Deze suppletieve collectieve arbeidsovereenkomst komt tot stand in toepassing van de artikelen 16, 17, 17/1 en 17/2 van de wet van 26 maart 2018 betreffende de versterking van de economische groei en de sociale cohesie (Belgisch Staatsblad van 30 maart 2018), evenals hoofdstuk 8 van de wet van 3 oktober 2022 houdende diverse arbeidsbepalingen (Belgisch Staatsblad van 10 november 2022).Zij strekt ertoe de modaliteiten van het recht op deconnectie in hoofde van de werknemers te bepalen alsook om mechanismen voor de regulering van het gebruik van digitale hulpmiddelen met het oog op de eerbiediging van de rusttijden en het evenwicht tussen privé- en beroepsleven, in te voeren.Art. 3. Algemeen - Recht op deconnectieHet recht op deconnectie is het recht voor werknemers om buiten de overeengekomen arbeidstijd afstand te kunnen doen van het werk en af te zien van werkgerelateerde elektronische communicatie zoals e-mails of andere berichten (telefoon, Teams,...).De uitbreiding van de professionele digitale hulpmiddelen en de verankering van telewerk en andere flexibele werkvormen binnen de ondernemingen en in de maatschappij, brengt nieuwe uitdagingen met zich mee. Het kan leiden tot een gevoel van "permanente connectie", wat een negatieve invloed heeft op het respecteren van de rust, op het mentaal welzijn van werknemers en op de balans tussen werk en privé.Om over dit evenwicht te waken en om psychosociale risico's te verkleinen, worden bij de ondernemingen vanaf 1 januari 2025 enkele maatregelen getroffen die het recht op deconnectie voor de werknemers veiligstellen.Deze maatregelen doen geen afbreuk aan de regels inzake arbeidsduur en arbeidstijden in de wetgeving, in collectieve arbeidsovereenkomsten, het arbeidsreglement, arbeidsovereenkomsten en eventuele andere contractuele bepalingen. Tijdens deze uren is de werknemer beschikbaar (= effectief aan het werk) en bereikbaar (= hij kan gecontacteerd worden) tenzij uitdrukkelijk anders afgesproken (bijvoorbeeld bij focustijd of klantentijd).Evenmin doen deze maatregelen afbreuk aan de bevoegdheden van het comité voor preventie en bescherming op het werk zoals vervat in titel VII van de Codex Welzijn op het Werk.Art. 4. Basisprincipes1. De ondernemingen willen vooral inzetten op het recht op connectie en houden van verbinding met werknemers, klanten, leveranciers,...2. De ondernemingen zetten in op flexibel werken. De ondernemingen geloven in de sterktes daarvan, flexibiliteit werkt motiverend. De ondernemingen beseffen tegelijkertijd dat de moderne tijden uitdagend zijn en dat sommige werknemers echt hulp nodig hebben om grenzen te stellen. Werknemers mogen grenzen stellen rond bereikbaarheid en connectiviteit buiten hun arbeidsuren. Hierin is vrije keuze belangrijk, dat is de sterkte. Flexibiliteit mag geen last worden. Werknemers kunnen kiezen om bereikbaar te zijn (buiten de arbeidsuren), maar mogen niet het gevoel hebben van de hele tijd te moeten bereikbaar zijn. Werknemers zijn niet verplicht om bereikbaar of geconnecteerd te zijn buiten de arbeidsuren.3. Voor de meeste werknemers zijn het hybride werken en de digitalisering een goede zaak en ze hebben hier geen problemen mee. Ze kunnen flexibel werken en dit heeft een positieve impact op hun productiviteit, de kwaliteit van hun werk, hun worklife balance,...Een groep van mensen ervaart dit evenwel als eerder negatief, omdat ze het gevoel hebben altijd bereikbaar en geconnecteerd te moeten zijn. Deze collectieve arbeidsovereenkomst focust op het grote en ruimere kader. Voor de mensen die het hier wellastig mee hebben en ondersteuning nodig hebben, gaan ondernemingen dit direct, gericht en op maat doen. De ondernemingen gaan bovendien niet voor de technische ingrepen - net omdat ze de voordelen van autonomie en het flexibel werken niet willen wegnemen.4. Om organisatiedoelstellingen te bereiken, is het niet nodig om buiten de arbeidsuren bereikbaar of geconnecteerd te moeten zijn. Ondernemingen kunnen hun doelen halen binnen vastgestelde arbeidsuren en afgesproken arbeidstijd.5. Onderneming willen ook inzetten op mentale deconnectie. Werknemers hebben het recht om fysiek los te koppelen, maar het is ook de bedoeling dat ze mentaal kunnen loskoppelen. Het werk moet op het werk kunnen blijven, het is niet de bedoeling dat werknemers buiten hun arbeidstijd mentale hinder ondervinden (bijvoorbeeld door stress, slecht slapen,...) van hun werk.6. Werknemers hebben binnen de onderneming recht op duidelijkheid over de verwachtingen die er zijn rond (on)bereikbaarheid, connectie en het gebruik van digitale hulpmiddelen.7. Afspraken rond deconnectie zijn geen pleister op de wonde. Bij gemelde of vastgestelde problemen zullen ondernemingen ook inzetten op analyse van de werksituatie. Als een werknemer het gevoel heeft dat hij/zij altijd geconnecteerd of bereikbaar moet zijn, heeft dit vaak een andere oorzaak. Dan moeten de onderneming en de werknemers samen kijken naar mogelijke onderliggende redenen (bijvoorbeeld onduidelijke processen of workflows, onduidelijke taakverdeling, gebrekkige of laattijdige informatiestroom, moeilijke samenwerking, competenties,...).Art. 5. Praktische modaliteiten rond de toepassing van het recht op deconnectie buiten de normale arbeidstijdDe bepalingen rond arbeidstijd binnen de onderneming zijn in de meeste ondernemingen terug te vinden in het arbeidsreglement.Behoudens de bepalingen vermeldt in artikel 3, 4de lid is de werknemer niet verondersteld en niet verplicht om bereikbaar of geconnecteerd te zijn buiten zijn arbeidstijd. Hij is dus niet verplicht om werkgerelateerde e-mails, berichten, telefoons of andere vormen van communicatie te beantwoorden buiten de werkuren en ook niet om buiten de werkuren werk te verrichten of op te volgen.De werknemers hebben het recht om buiten de arbeidsuren, in het weekend, op feest- en verlofdagen en ook tijdens ziekte te deconnecteren en los te koppelen van de werkgerelateerde digitale informatie- en communicatiestroom.Tijdens de werkuren zijn de werknemers beschikbaar (= effectief aan het werk) en bereikbaar (= kunnen gecontacteerd worden), tenzij uitdrukkelijk anders afgesproken.Voor werknemers die zich regelmatig buiten het bedrijf bevinden, worden afspraken gemaakt binnen het team en met de leidinggevende over hun bereikbaarheid en onbereikbaarheid tijdens de werkuren. Er vindt ook regelmatig overleg plaats tussen de leidinggevende en de werknemers, en met het team, om het werk en de organisatie ervan te bespreken.In het geval dat een werknemer ingeschakeld is in een permanentie of wachtdienst, gelden de afspraken inzake bereikbaarheid die in dat kader werden gemaakt.Art. 6. Richtlijnen voor een aangewezen gebruik van digitale communicatiemiddelenOnder "communicatiemiddelen- en vormen" wordt verstaan : telefoons, PC, tablet, slimme horloges en andere middelen die het mogelijk maken om e-mails, voicemails, video's en berichten te sturen en te ontvangen en gebruik te maken van, of toegang te krijgen tot, intranet en apps zoals WhatsApp, Linkedin,...De ondernemingen engageren zich om volgende tips aan hun werknemers meegeven :- Ga steeds na of een e-mail of een ander bericht de meeste passende en effectieve manier is om contact op te nemen met een collega;- Ga zorgvuldig en spaarzaam om met de functie "(B)CC";- Vermijd het gebruik van de "reply to all" functie tenzij de boodschap ook iedereen aanbelangt;- Zorg voor een duidelijke onderwerpregel zodat de ontvanger onmiddellijk de inhoud kan identificeren;- Als er antwoord wordt verwacht, geef dan in de mail aan tegen wanneer;- Gebruik de functie "hoge prioriteit" enkel voor urgente en belangrijke berichten;- Overweeg het gebruik van andere communicatiemiddelen (in persoon, telefoon) voor zaken die echt prioritair zijn;- Stel in geval van geplande afwezigheid een out-of-office = automatisch antwoord in. Een goed out-of-office bericht bevat de melding dat je momenteel niet beschikbaar bent, wanneer je weer terug bent en wie gecontacteerd kan worden in jouw plaats. Een automatisch antwoord kan ook gebruikt worden om te bevestigen dat een e-mail is ontvangen maar momenteel niet behandeld kan worden.- Probeer je mails te behandelen op afgebakende tijdstippen;- Er wordt aangeraden om buiten de werkuren de status op de communicatiekanalen (mail, Teams,...) op offline te zetten, jouw bereikbaarheidsinstellingen aan te passen en jouw notificaties/meldingen op smartphone, laptop,... uit te schakelen.Art. 7. Vormings- en sensibiliseringsactiesDe ondernemingen engageren zich om werknemers en leidinggevenden te sensibiliseren en op te leiden met betrekking tot het verstandig gebruik van digitale hulpmiddelen en de risico's die verbonden zijn aan overmatige connectie.Deze vormings- en sensibiliseringsacties kunnen onder meer gaan over :- De basisprincipes van de arbeidstijdenreglementering, en specifiek het nut en het belang van de grenzen aan werktijden en het respecteren van voldoende rust voor het mentaal en fysiek welzijn en de work-life balance van werknemers;- De fysieke en mentale impact van het langdurig en actief geconnecteerd zijn zowel in werk- als privésituaties;- De richtlijnen voor het gebruik van (digitale) communicatiemiddelen en -vormen;- Mentale deconnectie en het leren "loslaten" van je werk.Deze vormings- en sensibiliseringsacties kunnen de vorm aannemen van :- Informatiemomenten, gezamenlijk en/of in teamverband;- Infoaffiches;- Een gepaste vorming, al dan niet digitaal, in functie van de noden en competenties van de betrokken werknemers;- Individuele info op maat aan de werknemers.De vormings- en sensibiliseringsacties worden op gezette tijdstippen geëvalueerd en indien nodig aangepast en bijgestuurd met inachtneming van de regels van het sociaal overleg binnen de onderneming overeenkomstig de wettelijke en conventionele bevoegdheden van de bevoegde instanties.Art. 8. Garanties ten aanzien van de werknemersWerknemers zullen geen nadeel ondervinden in hun keuze om niet bereikbaar of geconnecteerd te zijn buiten de arbeidstijd.De ondernemingen waken erover dat een werknemer die zich op zijn recht op deconnectie beroept (bijvoorbeeld als hij buiten zijn normale arbeidstijd de telefoon niet opneemt of werkgerelateerde e-mails of berichten niet leest) hiervan geen negatieve impact mag ervaren, zoals bijvoorbeeld negatieve feedback, beperking van loopbaanmogelijkheden, discriminatie of ontslag als rechtstreeks of onrechtstreeks gevolg van het zich beroepen op het recht op deconnectie.Art. 9. OndersteuningWerknemers die toch problemen ondervinden bij het toepassen van deze principes, kunnen vrijblijvend gebruik maken van ondersteuningsmogelijkheden om het probleem aan te kaarten en oplossingen te zoeken, zoals daar zijn :- Het eerste aanspreekpunt blijft de leidinggevende die rechtstreeks bevoegd is een oplossing te bieden voor het gestelde probleem;- Werknemers kunnen om overleg of een verzoek om steun en advies specifiek gericht op de problematiek van (on)bereikbaarheid en/of (de)connectie vragen bij de HR-dienst;- Ook bij specifieke vragen kunnen ze terecht bij hun interne vertrouwenspersoon of de arbeidsgeneesheer.Art. 10. Evaluatie en bijsturingDe ondernemingen verbinden zich ertoe om het afsprakenkader en de principes rond (de)connectie die moeten leiden tot een betere afstemming van gezondheids- en veiligheidsoverwegingen met de arbeidsorganisatie op regelmatige basis te evalueren en indien nodig bij te sturen binnen het comité voor preventie en bescherming op het werk.Art. 11. DuurtijdDeze collectieve arbeidsovereenkomst is gesloten voor onbepaalde duur. Zij treedt in werking op 1 februari 2025.Zij kan door elk der partijen worden opgezegd mits een opzeggingstermijn van drie maanden betekend bij een ter post aangetekende brief, gericht aan de voorzitter van het Paritair Comité voor de scheikundige nijverheid. De termijn van drie maanden begint te lopen vanaf de datum waarop de aangetekende brief aan de voorzitter wordt toegezonden. De poststempel geldt als bewijs.Deze collectieve arbeidsovereenkomst zal worden neergelegd ter Griffie van de Algemene Directie Collectieve Arbeidsbetrekkingen van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg en de algemeen verbindende kracht bij koninklijk besluit wordt gevraagd.Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025.De Minister van Werk,D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -3096,28 +3089,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2025003646</t>
+          <t>2025003007</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>23 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>14 april 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 21 april 2007 betreffende de ademtesttoestellen en de ademanalysetoestellen. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 21 januari 2025, gesloten in het Paritair Comité voor de bedienden uit de scheikundige nijverheid, met betrekking tot een suppletieve regeling deconnectie tot vaststelling van sommige arbeidsvoorwaarden voor de bedienden van de kunststofverwerkende nijverheid van de provincie West-Vlaanderen (1)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-23&amp;numac_search=2025003646&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003646=83&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025003007&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003007=83&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 14 april 2024 tot wijziging van het koninklijk besluit van 21 april 2007 betreffende de ademtesttoestellen en de ademanalysetoestellen (Belgisch Staatsblad van 19 april 2024, err. van 2 mei 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy. FÖDERALER ÖFFENTLICHER DIENST MOBILITÄT UND TRANSPORTWESEN14. APRIL 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 21. April 2007 über die Atemtestgeräte und die AtemanalysegerätePHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des am 16. März 1968 koordinierten Gesetzes über die Straßenverkehrspolizei, insbesondere des Artikels 59 § 4, abgeändert durch das Gesetz vom 18. Juli 1990;Aufgrund des Gesetzes vom 28. Februar 2013 zur Einführung des Wirtschaftsgesetzbuches, des Artikels 8;Aufgrund des Königlichen Erlasses vom 21. April 2007 über die Atemtestgeräte und die Atemanalysegeräte;Aufgrund der Mitteilung an die Europäische Kommission vom 17. November 2023 in Anwendung von Artikel 5 Absatz 1 der Richtlinie (EU) 2015/1535 des Europäischen Parlaments und des Rates vom 9. September 2015 über ein Informationsverfahren auf dem Gebiet der technischen Vorschriften und der Vorschriften für die Dienste der Informationsgesellschaft;Aufgrund der Beteiligung der Regionalregierungen;Aufgrund der Stellungnahmen der Finanzinspektoren vom 9. Januar 2023, 31. März 2023 und 18. April 2023;Aufgrund des Einverständnisses der Staatssekretärin für Haushalt vom 12. September 2023;Aufgrund des Antrags auf Begutachtung binnen einer Frist von dreißig Tagen, der am 4. Dezember 2023 beim Staatsrat eingereicht worden ist, in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Aufgrund des Beschlusses 75.015/4 des Staatsrats vom 4. Dezember 2023 in Anwendung von Artikel 84 § 5 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Auf Vorschlag des Ministers der Wirtschaft, des Ministers der Mobilität und des Ministers der JustizHaben Wir beschloßen und erlassen Wir:Artikel 1 - In Artikel 5 des Königlichen Erlasses vom 21. April 2007 über die Atemtestgeräte und die Atemanalysegeräte werden die Wörter "im Gesetz vom 16. Juni 1970 über die Maßeinheiten, Eichmaße und Messgeräte" durch die Wörter "in Buch VIII Titel 3 Kapitel 2 Abschnitt 2 des Wirtschaftsgesetzbuches vom 28. Februar 2013" ersetzt.Art. 2 - Artikel 23 desselben Erlasses wird aufgehoben.Art. 3 - In Artikel 24 Absatz 2 desselben Erlasses werden die Wörter "in das Gerät zu blasen bis das Gerät das Ende einer gültigen Probenahme anzeigt" durch die Wörter "und so lange wie möglich in das Gerät zu blasen" ersetzt.Art. 4 - Punkt 3.14.2 von Anlage 2 zum selben Erlass, abgeändert durch Artikel 6 des Königlichen Erlasses vom 10. Juni 2014, wird wie folgt abgeändert:1. In Absatz 1 werden die Wörter "1,9" durch die Wörter "1,2" ersetzt.2. In Absatz 3 werden die Worte ", ab dem Zeitpunkt, an dem das minimale erforderliche Volumen 1,9 l erreicht hat" durch die Wörter "ab dem Zeitpunkt, an dem die Person maximal ausgeatmet hat und das minimal erforderliche Volumen von 1,2 l erreicht wird" ersetzt.Art. 5 - ÜbergangsbestimmungenAtemanalysegeräte, die zum Zeitpunkt des Inkrafttretens des vorliegenden Erlasses gültig sind, dürfen weiter verwendet werden, sofern sie bei ihrer nächsten Nacheichung an die abgeänderten Bestimmungen von Punkt 3.14.2 von Anhang 2 zum vorerwähnten Erlass angepasst werden.Art. 6 - Die Artikel 1 und 2 des vorliegenden Erlasses treten am ersten Tag des Monats nach Ablauf einer Frist von zehn Tagen, die am Tag nach seiner Veröffentlichung im Belgischen Staatsblatt beginnt, in Kraft.Die Artikel 3, 4 und 5 des vorliegenden Erlasses treten am ersten Tag des dritten Monats nach Ablauf einer Frist von zehn Tagen, die am Tag nach seiner Veröffentlichung im Belgischen Staatsblatt beginnt, in Kraft.Art. 7 - Der Minister der Wirtschaft, der Minister der Justiz und der für den Straßenverkehr zuständige Minister sind mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 14. April 2024PHILIPPEVon Königs wegen:Der Minister der WirtschaftP.-Y. DERMAGNEDer Minister der MobilitätG. GILKINETDer Minister der JustizP. VAN TIGCHELT 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de bedienden uit de scheikundige nijverheid;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 21 januari 2025, gesloten in het Paritair Comité voor de bedienden uit de scheikundige nijverheid, met betrekking tot een suppletieve regeling deconnectie tot vaststelling van sommige arbeidsvoorwaarden voor de bedienden van de kunststofverwerkende nijverheid van de provincie West-Vlaanderen.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 7 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de bedienden uit de scheikundige nijverheidCollectieve arbeidsovereenkomst van 21 januari 2025Suppletieve regeling deconnectie tot vaststelling van sommige arbeidsvoorwaarden voor de bedienden van de kunststofverwerkende nijverheid van de provincie West-Vlaanderen (Overeenkomst geregistreerd op 31 januari 2025 onder het nummer 191699/CO/207)HOOFDSTUK I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers, die 20 of meer werknemers tewerkstellen en de bedienden, hierna "de werknemers" genoemd, van de ondernemingen die gelegen zijn in de provincie West-Vlaanderen en ressorteren onder het Paritair Comité voor de bedienden uit de scheikundige nijverheid uit hoofde van hun bedrijvigheid inzake verwerking van kunststoffen en die op datum van het afsluiten van onderhavige collectieve arbeidsovereenkomst of op een latere datum, geen eigen regeling rond deconnectie hebben op ondernemingsvlak.Met "werknemers" wordt verstaan : de mannelijke en vrouwelijke werknemers.Met "de onderneming" wordt verstaan : de werkgever.Art. 2. Deze suppletieve collectieve arbeidsovereenkomst komt tot stand in toepassing van de artikelen 16, 17, 17/1 en 17/2 van de wet van 26 maart 2018 betreffende de versterking van de economische groei en de sociale cohesie (Belgisch Staatsblad van 30 maart 2018), evenals hoofdstuk 8 van de wet van 3 oktober 2022 houdende diverse arbeidsbepalingen (Belgisch Staatsblad van 10 november 2022).Zij strekt ertoe de modaliteiten van het recht op deconnectie in hoofde van de werknemers te bepalen alsook om mechanismen voor de regulering van het gebruik van digitale hulpmiddelen met het oog op de eerbiediging van de rusttijden en het evenwicht tussen privé en beroepsleven, in te voeren.Art. 3. Algemeen - Recht op deconnectieHet recht op deconnectie is het recht voor werknemers om buiten de overeengekomen arbeidstijd afstand te kunnen doen van het werk en af te zien van werkgerelateerde elektronische communicatie zoals e-mails of andere berichten (telefoon, Teams,...).De uitbreiding van de professionele digitale hulpmiddelen en de verankering van telewerk en andere flexibele werkvormen binnen de ondernemingen en in de maatschappij, brengt nieuwe uitdagingen met zich mee. Het kan leiden tot een gevoel van "permanente connectie", wat een negatieve invloed heeft op het respecteren van de rust, op het mentaal welzijn van werknemers en op de balans tussen werk en privé.Om over dit evenwicht te waken en om psychosociale risico's te verkleinen, worden bij de ondernemingen vanaf 1 januari 2025 enkele maatregelen getroffen die het recht op deconnectie voor de werknemers veiligstellen.Deze maatregelen doen geen afbreuk aan de regels inzake arbeidsduur en arbeidstijden in de wetgeving, in collectieve arbeidsovereenkomsten, het arbeidsreglement, arbeidsovereenkomsten en eventuele andere contractuele bepalingen. Tijdens deze uren is de werknemer beschikbaar (= effectief aan het werk) en bereikbaar (= hij kan gecontacteerd worden) tenzij uitdrukkelijk anders afgesproken (bijvoorbeeld bij focustijd of klantentijd).Evenmin doen deze maatregelen afbreuk aan de bevoegdheden van het comité voor preventie en bescherming op het werk zoals vervat in Titel VII van de Codex Welzijn op het werk.Art. 4. Basisprincipes1. De ondernemingen willen vooral inzetten op het recht op connectie en houden van verbinding met werknemers, klanten, leveranciers,...2. De ondernemingen zetten in op flexibel werken. De ondernemingen geloven in de sterktes daarvan, flexibiliteit werkt motiverend. De ondernemingen beseffen tegelijkertijd dat de moderne tijden uitdagend zijn en dat sommige werknemers echt hulp nodig hebben om grenzen te stellen. Werknemers mogen grenzen stellen rond bereikbaarheid en connectiviteit buiten hun arbeidsuren. Hierin is vrije keuze belangrijk, dat is de sterkte. Flexibiliteit mag geen last worden. Werknemers kunnen kiezen om bereikbaar te zijn (buiten de arbeidsuren), maar mogen niet het gevoel hebben van de hele tijd te moeten bereikbaar zijn. Werknemers zijn niet verplicht om bereikbaar of geconnecteerd te zijn buiten de arbeidsuren.3. Voor de meeste werknemers zijn het hybride werken en de digitalisering een goede zaak en ze hebben hier geen problemen mee. Ze kunnen flexibel werken en dit heeft een positieve impact op hun productiviteit, de kwaliteit van hun werk, hun worklife balance,...Een groep van mensen ervaart dit evenwel als eerder negatief, omdat ze het gevoel hebben altijd bereikbaar en geconnecteerd te moeten zijn. Deze collectieve arbeidsovereenkomst focust op het grote en ruimere kader. Voor de mensen die het hier wel lastig mee hebben en ondersteuning nodig hebben, gaan ondernemingen dit direct, gericht en op maat doen. De ondernemingen gaan bovendien niet voor de technische ingrepen - net omdat ze de voordelen van autonomie en het flexibel werken niet willen wegnemen.4. Om organisatiedoelstellingen te bereiken, is het niet nodig om buiten de arbeidsuren bereikbaar of geconnecteerd te moeten zijn. Ondernemingen kunnen hun doelen halen binnen vastgestelde arbeidsuren en afgesproken arbeidstijd.5. Ondernemingen willen ook inzetten op mentale deconnectie. Werknemers hebben het recht om fysiek los te koppelen, maar het is ook de bedoeling dat ze mentaal kunnen loskoppelen. Het werk moet op het werk kunnen blijven, het is niet de bedoeling dat werknemers buiten hun arbeidstijd mentale hinder ondervinden (bijvoorbeeld door stress, slecht slapen,...) van hun werk.6. Werknemers hebben binnen de onderneming recht op duidelijkheid over de verwachtingen die er zijn rond (on)bereikbaarheid, connectie en het gebruik van digitale hulpmiddelen.7. Afspraken rond deconnectie zijn geen pleister op de wonde. Bij gemelde of vastgestelde problemen zullen ondernemingen ook inzetten op analyse van de werksituatie. Als een werknemer het gevoel heeft dat hij/zij altijd geconnecteerd of bereikbaar moet zijn, heeft dit vaak een andere oorzaak. Dan moeten de onderneming en de werknemers samen kijken naar mogelijke onderliggende redenen (bijvoorbeeld onduidelijke processen of workflows, onduidelijke taakverdeling, gebrekkige of laattijdige informatiestroom, moeilijke samenwerking, competenties,...).Art. 5. Praktische modaliteiten rond de toepassing van het recht op deconnectie buiten de normale arbeidstijdDe bepalingen rond arbeidstijd binnen de onderneming zijn in de meeste ondernemingen terug te vinden in het arbeidsreglement.Behoudens de uitzonderingen vermeldt in artikel 3, 4de lid is de werknemer niet verondersteld en niet verplicht om bereikbaar of geconnecteerd te zijn buiten zijn arbeidstijd. Hij is dus niet verplicht om werkgerelateerde e-mails, berichten, telefoons of andere vormen van communicatie te beantwoorden buiten de werkuren en ook niet om buiten de werkuren werk te verrichten of op te volgen.De werknemers hebben het recht om buiten de arbeidsuren, in het weekend, op feest- en verlofdagen en ook tijdens ziekte te deconnecteren en los te koppelen van de werkgerelateerde digitale informatie- en communicatiestroom.Tijdens de werkuren zijn de werknemers beschikbaar (= effectief aan het werk) en bereikbaar (= kunnen gecontacteerd worden), tenzij uitdrukkelijk anders afgesproken.Voor werknemers die zich regelmatig buiten het bedrijf bevinden, worden afspraken gemaakt binnen het team en met de leidinggevende over hun bereikbaarheid en onbereikbaarheid tijdens de werkuren. Er vindt ook regelmatig overleg plaats tussen de leidinggevende en de werknemers, en met het team, om het werk en de organisatie ervan te bespreken.In het geval dat een werknemer ingeschakeld is in een permanentie of wachtdienst, gelden de afspraken inzake bereikbaarheid die in dat kader werden gemaakt.Art. 6. Richtlijnen voor een aangewezen gebruik van digitale communicatiemiddelenOnder communicatiemiddelen en -vormen wordt verstaan : telefoons, PC, tablet, slimme horloges en andere middelen die het mogelijk maken om e-mails, voicemails, video's en berichten te sturen en te ontvangen en gebruik te maken van, of toegang te krijgen tot, intranet en apps zoals WhatsApp, Linkedin,...De ondernemingen engageren zich om volgende tips aan hun werknemers mee te geven :- Ga steeds na of een e-mail of een ander bericht de meeste passende en effectieve manier is om contact op te nemen met een collega;- Ga zorgvuldig en spaarzaam om met de functie "(B)CC";- Vermijd het gebruik van de "reply to all" functie tenzij de boodschap ook iedereen aanbelangt;- Zorg voor een duidelijke onderwerpregel zodat de ontvanger onmiddellijk de inhoud kan identificeren;- Als er antwoord wordt verwacht, geef dan in de mail aan tegen wanneer;- Gebruik de functie "hoge prioriteit" enkel voor urgente en belangrijke berichten;- Overweeg het gebruik van andere communicatiemiddelen (in persoon, telefoon) voor zaken die echt prioritair zijn;- Stel in geval van geplande afwezigheid een out-of-office = automatisch antwoord in. Een goed out-of-office bericht bevat de melding dat je momenteel niet beschikbaar bent, wanneer je weer terug bent en wie gecontacteerd kan worden in jouw plaats. Een automatisch antwoord kan ook gebruikt worden om te bevestigen dat een e-mail is ontvangen maar momenteel niet behandeld kan worden.- Probeer je mails te behandelen op afgebakende tijdstippen;- Er wordt aangeraden om buiten de werkuren de status op de communicatiekanalen (mail, Teams,...) op offline te zetten, jouw bereikbaarheidsinstellingen aan te passen en jouw notificaties/meldingen op smartphone, laptop,... uit te schakelen.Art. 7. Vormings - en sensibiliseringsactiesDe ondernemingen engageren zich om werknemers en leidinggevenden te sensibiliseren en op te leiden met betrekking tot het verstandig gebruik van digitale hulpmiddelen en de risico's die verbonden zijn aan overmatige connectie.Deze vormings- en sensibiliseringsacties kunnen onder meer gaan over :- De basisprincipes van de arbeidstijdenreglementering, en specifiek het nut en het belang van de grenzen aan werktijden en het respecteren van voldoende rust voor het mentaal en fysiek welzijn en de worklife balance van werknemers;- De fysieke en mentale impact van het langdurig en actief geconnecteerd zijn zowel in werk- als privésituaties;- De richtlijnen voor het gebruik van (digitale) communicatiemiddelen en -vormen;- Mentale deconnectie en het leren "loslaten" van je werk.Deze vormings- en sensibiliseringsacties kunnen de vorm aannemen van :- Informatiemomenten, gezamenlijk en/of in teamverband;- Infoaffiches;- Een gepaste vorming, al dan niet digitaal, in functie van de noden en competenties van de betrokken werknemers;- Individuele info op maat aan de werknemers.De vormings- en sensibiliseringsacties worden op gezette tijdstippen geëvalueerd en indien nodig aangepast en bijgestuurd met inachtneming van de regels van het sociaal overleg binnen de onderneming overeenkomstig de wettelijke en conventionele bevoegdheden van de bevoegde instanties.Art. 8. Garanties ten aanzien van de werknemersWerknemers zullen geen nadeel ondervinden in hun keuze om niet bereikbaar of geconnecteerd te zijn buiten de arbeidstijd.De ondernemingen waken erover dat een werknemer die zich op zijn recht op deconnectie beroept (bijvoorbeeld als hij buiten zijn normale arbeidstijd de telefoon niet opneemt of werkgerelateerde e-mails of berichten niet leest) hiervan geen negatieve impact mag ervaren, zoals bijvoorbeeld negatieve feedback, beperking van loopbaanmogelijkheden, discriminatie of ontslag als rechtstreeks of onrechtstreeks gevolg van het zich beroepen op het recht op deconnectie.Art. 9. OndersteuningWerknemers die toch problemen ondervinden bij het toepassen van deze principes, kunnen vrijblijvend gebruik maken van ondersteuningsmogelijkheden om het probleem aan te kaarten en oplossingen te zoeken, zoals daar zijn :- Het eerste aanspreekpunt blijft de leidinggevende die rechtstreeks bevoegd is een oplossing te bieden voor het gestelde probleem;- Werknemers kunnen om overleg of een verzoek om steun en advies specifiek gericht op de problematiek van (on)bereikbaarheid en/of (de)connectie vragen bij de HR dienst;- Ook bij specifieke vragen kunnen ze terecht bij hun interne vertrouwenspersoon of de arbeidsgeneesheer.Art. 10. Evaluatie en bijsturingDe ondernemingen verbinden zich ertoe om het afsprakenkader en de principes rond (de)connectie die moeten leiden tot een betere afstemming van gezondheids- en veiligheidsoverwegingen met de arbeidsorganisatie op regelmatige basis te evalueren en indien nodig bij te sturen binnen het comité voor preventie en bescherming op het werk.Art. 11. DuurtijdDeze collectieve arbeidsovereenkomst is gesloten voor onbepaalde duur. Zij treedt in werking op 1 februari 2025.Zij kan door elk der partijen worden opgezegd mits een opzeggingstermijn van drie maanden betekend bij een ter post aangetekende brief, gericht aan de voorzitter van het paritair comité. De termijn van drie maanden begint te lopen vanaf de datum waarop de aangetekende brief aan de voorzitter wordt toegezonden. De poststempel geldt als bewijsDeze collectieve arbeidsovereenkomst zal worden neergelegd ter Griffie van de Algemene Directie Collectieve Arbeidsbetrekkingen van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg en de algemeen verbindende kracht bij koninklijk besluit wordt gevraagd.Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025.De Minister van Werk,D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -3128,28 +3121,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2025002854</t>
+          <t>2025201167</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>28 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>14 april 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 22 december 2020 tot oprichting van de Nationale Veiligheidsraad, het Strategisch Comité Inlichtingen en Veiligheid en het Coördinatiecomité Inlichtingen en Veiligheid. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de bedienden van de textielnijverheid, tot wijziging en coördinatie van de statuten van het "Fonds voor bestaanszekerheid voor de bedienden van de textielnijverheid" (1)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-28&amp;numac_search=2025002854&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025002854=84&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025201167&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201167=84&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 14 april 2024 tot wijziging van het koninklijk besluit van 22 december 2020 tot oprichting van de Nationale Veiligheidsraad, het Strategisch Comité Inlichtingen en Veiligheid en het Coördinatiecomité Inlichtingen en Veiligheid (Belgisch Staatsblad van 26 april 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST KANZLEI DES PREMIERMINISTERS14. APRIL 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 22. Dezember 2020 zur Schaffung des Nationalen Sicherheitsrates, des Strategischen Ausschusses für Nachrichten und Sicherheit und des Koordinierungsausschusses für Nachrichten und SicherheitPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des Artikels 37 der Verfassung;Aufgrund des Königlichen Erlasses vom 22. Dezember 2020 zur Schaffung des Nationalen Sicherheitsrates, des Strategischen Ausschusses für Nachrichten und Sicherheit und des Koordinierungsausschusses für Nachrichten und Sicherheit;Aufgrund der Stellungnahme des Finanzinspektors vom 21. März 2024;Aufgrund des Einverständnisses der Staatssekretärin für Haushalt vom 26. März 2024;Aufgrund des Artikels 8 § 1 Nr. 3 des Gesetzes vom 15. Dezember 2013 zur Festlegung verschiedener Bestimmungen in Sachen administrative Vereinfachung, durch den von der Auswirkungsanalyse beim Erlass von Vorschriften befreit wird, da es sich um einen Erlass mit formellem Charakter handelt;In der Erwägung, dass nach einer Evaluation festgestellt wurde, dass die Aufgabe des Vorsitzenden des Koordinierungsausschusses für Nachrichten und Sicherheit eine Verfügbarkeit und eine gewisse Arbeitslast erfordert, die nur schwer mit einer vollzeitigen leitenden Funktion zu vereinbaren sind;Dass darüber hinaus die Funktion des Vorsitzenden des Koordinierungsausschusses mittlerweile erweitert wurde, insbesondere im Rahmen des Verfahrens für die Überprüfung ausländischer Direktinvestitionen (FDI);Dass der Vorsitzende des Koordinierungsausschusses sich auch mit dem Vorsitzenden des Strategischen Ausschusses für Nachrichten und Sicherheit und den für diesen Bereich zuständigen Dienststellen des Föderalen Öffentlichen Dienstes Kanzlei des Premierministers abstimmen muss, um die Überwachung und das Monitoring der Ziele der nationalen Sicherheitsstrategie zu verbessern;Auf Vorschlag des Premierministers und aufgrund der Stellungnahme der Minister, die im Rat darüber beraten haben,Haben Wir beschloßen und erlassen Wir:Artikel 1 - In Artikel 12 § 1 des Königlichen Erlasses vom 22. Dezember 2020 zur Schaffung des Nationalen Sicherheitsrates, des Strategischen Ausschusses für Nachrichten und Sicherheit und des Koordinierungsausschusses für Nachrichten und Sicherheit, abgeändert durch den Königlichen Erlass vom 29. März 2022, wird Absatz 2 wie folgt ersetzt:"Der Vorsitz des Koordinierungsausschusses wird von einem Mitglied eines Dienstes oder einer Behörde geführt, das als ständiges Mitglied im Koordinierungsausschuss tagt. Der Vorsitzende wird vom Rat auf Vorschlag des Koordinierungsausschusses für einen erneuerbaren Zeitraum von zwei Jahren bestimmt."Art. 2 -  Der Premierminister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 14. April 2024PHILIPPEVon Königs wegen:Der PremierministerA. DE CROO 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de bedienden van de textielnijverheid; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de bedienden van de textielnijverheid, tot wijziging en coördinatie van de statuten van het "Fonds voor bestaanszekerheid voor de bedienden van de textielnijverheid". Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de bedienden van de textielnijverheid Collectieve arbeidsovereenkomst van 18 december 2024 Wijziging en coördinatie van de statuten van het "Fonds voor bestaanszekerheid voor de bedienden van de textielnijverheid" (Overeenkomst geregistreerd op 31 januari 2025 onder het nummer 191709/CO/214) HOOFDSTUK I. - Toepassingsgebied Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op alle werkgevers die onder de bevoegdheid vallen van het Paritair Comité voor de bedienden van de textielnijverheid (PC 214) en op de bedienden die ze tewerkstellen.  § 2. Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst van 29 juni 2022 tot wijziging en coördinatie van de statuten van het "Fonds voor bestaanszekerheid voor de bedienden van de textielnijverheid" (registratienummer 175232/CO/214). HOOFDSTUK II. - Voorwerp Art. 2. Deze collectieve arbeidsovereenkomst wijzigt de statuten van het "Fonds voor bestaanszekerheid voor de bedienden van de textielnijverheid". De gewijzigde en gecoördineerde statuten worden opgenomen in de bijlage aan deze collectieve arbeidsovereenkomst. HOOFDSTUK III. - Duur van de overeenkomst Art. 3.  § 1. Deze collectieve arbeidsovereenkomst is van onbepaalde duur en treedt in werking op 1 januari 2024, zonder dat zij evenwel afbreuk doet aan de nog geldende bepalingen omtrent de in deze statuten opgenomen aanvullende sociale voordelen, zoals bepaald in eerdere (algemene nationale) collectieve arbeidsovereenkomsten gesloten in het Paritair Comité voor de bedienden van de textielnijverheid (PC 214).  § 2. Deze collectieve arbeidsovereenkomst kan opgezegd worden door elk van de ondertekenende partijen mits inachtneming van een opzeggingstermijn van zes maanden per aangetekend schrijven aan de voorzitter van het paritair comité en aan elk van de andere ondertekenende partijen. HOOFDSTUK IV. - Algemeen verbindend verklaring Art. 4. De ondertekenende partijen vragen dat deze collectieve arbeidsovereenkomst algemeen verbindend zou verklaard worden per koninklijk besluit. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVALBijlage bij de collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de bedienden van de textielnijverheid, tot wijziging en coördinatie van de statuten van het "Fonds voor bestaanszekerheid voor de bedienden van de textielnijverheid" I. Benaming en maatschappelijke zetel Artikel 1. Met ingang van 1 januari 1981 is een fonds voor bestaanszekerheid opgericht, genaamd "Fonds voor bestaanszekerheid voor de bedienden van de textielnijverheid", hierna "het fonds". Art. 2. De maatschappelijke zetel van het fonds is gevestigd te Poortakkerstraat 100, 9051 Gent (Sint-Denijs-Westrem). De zetel kan bij beslissing van het Paritair Comité voor de bedienden van de textielnijverheid worden overgebracht naar elke andere plaats in België. II. Doel Art. 3. Het fonds heeft tot doel : 1° het innen of laten innen van de bijdragen, nodig voor zijn werking; 2° het innen van de bijdragen bestemd voor de financiering van het sectoraal aanvullend pensioenstelsel voor de bedienden van het Paritair Comité voor de bedienden van de textielnijverheid in naam en voor rekening van het "Fonds voor Bestaanszekerheid - Sectoraal Aanvullend Pensioen voor de Textielnijverheid" (FBZ-SAP Textiel), de sectorale inrichter van dit sectoraal aanvullend pensioenstelsel alsook het aanleggen en eventueel doorstorten van een buffer vanuit de reserves van het fonds in het geval van een tekort ten opzichte van de wettelijke rendementsgarantie voorzien in artikel 24, § 2 van de wet van 28 april 2003 betreffende de aanvullende pensioenen (WAP) overeenkomstig de toepasselijke collectieve arbeidsovereenkomst gesloten in het Paritair Comité voor de bedienden van de textielnijverheid over het sectoraal aanvullend pensioenstelsel; 3° het toekennen van de sociale voordelen aan de bedienden en de uitkering van deze sociale voordelen verzekeren; 4° de terugbetaling aan de werkgevers en het ten laste nemen van de aanvullende vergoedingen en de bijzondere werkgeversbijdragen in het kader van de stelsels van werkloosheid met bedrijfstoeslag; 5° het financieren van opleidings- en tewerkstellingsbevorderende initiatieven voor de bedienden en georganiseerd door de in het Paritair Comité voor de bedienden van de textielnijverheid vertegenwoordigde organisaties; 6° het financieren van sectorale initiatieven in het kader van werkbaar werk; 7° het financieren van de lasten met betrekking tot de verbetering van de industriële relaties en de promotie van de werkgelegenheid in de textielnijverheid; 8° de bestuurs- en beheerslasten met betrekking tot de uitbetaling van de sociale voordelen aan de vertegenwoordigde organisaties vergoeden. III. Toepassingsgebied Art. 4.  § 1. Deze statuten zijn van toepassing op alle textielondernemingen en op alle erin tewerkgestelde bedienden die onder de bevoegdheid vallen van het Paritair Comité voor de bedienden van de textielnijverheid (hierna "de bediende(n)" enerzijds en "de textielonderneming(en)" of "de werkgever(s)" anderzijds).  § 2. In afwijking van § 1, is artikel 7, § 3 van deze statuten niet van toepassing op de textielondernemingen en de erin tewerkgestelde bedienden die, wat hun arbeiders betreft, onder de bevoegdheid vallen van het Paritair Subcomité voor het vervaardigen van en de handel in zakken in jute of in vervangingsmaterialen (PSC 120.03). IV. Toekenning en uitkering van de aanvullende sociale voordelen Art. 5.  § 1. De bedienden hebben recht op de aanvullende sociale voordelen ten laste van het fonds waarvan de aard, het bedrag, de toekenningsvoorwaarden en de uitkeringsmodaliteiten worden vastgesteld bij collectieve arbeidsovereenkomst, gesloten in het Paritair Comité voor de bedienden van de textielnijverheid en algemeen verbindend verklaard bij koninklijk besluit. Deze aanvullende sociale voordelen worden in eerste instantie gedragen door de werkgever, die deze met inbegrip van de capitatieve bijdragen vervolgens kan terugvorderen bij het fonds. § 2. Meer in het bijzonder gaat het om de volgende aanvullende sociale voordelen : - de aanvullende vergoedingen in het kader van de verschillende stelsels van werkloosheid met bedrijfstoeslag, zoals bepaald in de betrokken collectieve arbeidsovereenkomsten gesloten in het Paritair Comité voor de bedienden van de textielnijverheid en algemeen verbindend verklaard bij koninklijk besluit. Art. 6.  § 1. Het fonds betaalt aan de bediende een sectorale tegemoetkoming in de kinderopvang vanaf 1 januari 2024 van 1 EUR per dag met een maximum van 150 EUR per jaar en per kind tot de leeftijd van 3 jaar. Deze sectorale tegemoetkoming geldt alleen voor kinderopvang in een gezins- of groepsopvang die wordt erkend door Kind &amp; Gezin of l'Office de la Naissance et de l'Enfance.  § 2. De terugbetaling gebeurt door het fonds op basis van het door de opvang uitgereikte fiscaal attest waarop het dagbedrag en het aantal dagen opvang wordt vermeld voor het jaar voorafgaand aan het jaar waarin het attest werd uitgereikt. Het jaar 2024 is het eerste jaar waarvoor een fiscaal attest (afgeleverd in 2025) het recht op de sectorale tegemoetkoming kan openen. De sectorale tegemoetkoming geldt voor de periode van tewerkstelling in de textielsector. In geval van onvolledige tewerkstelling (bijvoorbeeld door indiensttreding of uitdiensttreding in de loop van het jaar) wordt het plafond van de tegemoetkoming pro rata beperkt.  § 3. De raad van beheer van het fonds wordt belast met de praktische uitwerking van de aanvraagprocedure en de betalingsmodaliteiten. Art. 7.  § 1. In uitvoering van artikel 3 van de collectieve arbeidsovereenkomst van 25 september 2024 betreffende preventieve maatregelen inzake de gezondheid en veiligheid op het werk en/of maatregelen inzake duurzame herinschakeling van langdurig zieken in de textielsector, wordt het fonds vanaf 1 oktober 2024 aangeduid als instelling belast met de aanvraag, de besteding en het gebruik van de gelden zoals bedoeld in artikel 147, § 1 van de programmawet van 27 december 2021.  § 2. Deze gelden worden aangewend voor de uitvoering van artikel 4 (cf. dienstverlening van Cobot en Cefret) van de collectieve arbeidsovereenkomst van 25 september 2024.  § 3. Het fonds maakt jaarlijks een verslag op over de besteding van deze gelden en maakt dat over aan de Federale Overheidsdienstdienst Werkgelegenheid, Arbeid en Sociaal Overleg. Art. 8.  § 1. Jaarlijks wordt een globale werkingstoelage toegekend aan de representatieve werknemersorganisaties en de representatieve werkgeversorganisatie die vastgesteld wordt op 0,125 pct. van de onbegrensde brutojaarlonen waarop de bijdragen worden geïnd, zoals bepaald in artikel 9, § 2. De werkingstoelage voor de werknemersorganisaties wordt onder de werknemersorganisaties verdeeld volgens de sinds 2007 bepaalde verdeelsleutel.  § 2. De werknemersorganisaties kunnen deze werkingstoelage besteden voor de toekenning van een syndicale premie van maximum 145 EUR per gesyndiceerde en per jaar. V. Financiering Art. 9.  § 1. De financiering van de aanvullende sociale voordelen zoals bepaald in hoofdstuk IV gebeurt door middel van een werkgeversbijdrage van 0,80 pct. op de begrensde brutolonen. Met ingang vanaf 1 januari 2022 (dit wil zeggen op de lonen betaald vanaf 1 januari 2022) wordt een bijdrageschorsing van 0,20 procentpunt toegepast voor een periode van drie jaar (dit is tot 1 januari 2025). Met ingang van 1 januari 2025 zullen de sociale partners tweejaarlijks evalueren of deze bijdrageschorsing voor een periode van 2 jaar kan verdergezet worden rekening houdend met de financiële situatie van het fonds. Deze bijdrage wordt geïnd op de brutolonen waarbij enkel de onder DmfA looncode 1 aangegeven lonen in aanmerking komen, die op kwartaalbasis worden begrensd tot een kwartaalloongrens. Deze kwartaalloongrens is gelijk aan 3 x de maandgrens die op 1 januari van het betrokken jaar is vastgelegd overeenkomstig de collectieve arbeidsovereenkomst nr. 17, gesloten op 19 december 1974 in de Nationale Arbeidsraad.  § 2. De financiering van de opleidings- en tewerkstellingsbevorderende initiatieven zoals bepaald in artikel 3, 5° van deze statuten gebeurt door middel van een werkgeversbijdrage van 0,30 pct. Deze bijdrage wordt geïnd op de onbegrensde brutolonen die aangegeven worden onder de DmfA looncodes 1, 2, 3, 4, 6 en 7. § 3. Met ingang van 1 januari 2021 (dit wil zeggen op de lonen betaald vanaf 1 januari 2021) wordt een patronale bijdrage van 1,20 pct. geïnd op de onbegrensde brutolonen onderworpen aan de gewone RSZ-bijdragen en aangegeven onder DmfA looncode 1, verminderd met het enkel vakantiegeld. Deze patronale bijdrage dient ter financiering voor het sectoraal aanvullend pensioenplanstelsel voor de bedienden van het Paritair Comité voor de bedienden van de textielnijverheid, zoals bepaald in artikel 3, 2° van deze statuten en in de toepasselijke collectieve arbeidsovereenkomsten gesloten in het Paritair Comité voor de bedienden van de textielnijverheid en algemeen verbindend verklaard per koninklijk besluit. Deze patronale bijdrage is niet van toepassing op de ondernemingen die in het kader van het sectoraal aanvullend pensioenstelsel gebruik maken van de mogelijkheid tot uitsluiting uit het toepassingsgebied zoals bepaald in de toepasselijke collectieve arbeidsovereenkomsten gesloten in het Paritair Comité voor de bedienden van de textielnijverheid, en algemeen verbindend verklaard per koninklijk besluit. In het kader van het sectoraal aanvullend pensioenstelsel en in uitvoering van artikel 7, § 4 van de collectieve arbeidsovereenkomst van 22 december 2021 tot wijziging en coördinatie van het sociaal sectoraal pensioenstelsel en overgang van solidariteitsinstelling met overdracht van het solidariteitsfonds wordt vanuit de reserves van het fonds jaarlijks - indien er sprake is van een tekort ten opzichte van de wettelijke rendementsgarantie zoals voorzien in artikel 24, § 2 van de WAP - een buffer aangelegd ten belope van het verschil tussen de bedragen ingeschreven op de individuele rekeningen van de aangeslotenen bij de pensioeninstelling (Sefoplus OFP) en deze bedragen aangevuld tot de wettelijke rendementsgarantie voorzien in artikel 24, § 2 van de WAP. De totale som overeenstemmend met het hiervoor vermelde verschil zal jaarlijks overgemaakt worden aan het "Fonds voor Bestaanszekerheid - Sectoraal Aanvullend Pensioen voor de Textielnijverheid", volgens de afspraken vastgelegd in de overeenkomst hieromtrent tussen het "Fonds voor Bestaanszekerheid - Sectoraal Aanvullend Pensioen voor de Textielnijverheid" en het fonds. Art. 10.  § 1. De werkgeversbijdragen worden door het fonds geïnd en ingevorderd.  § 2. De werkgeversbijdragen zijn op trimestriële basis door de werkgevers verschuldigd en worden berekend op de begrensde en onbegrensde brutolonen van de respectieve refertekwartalen die overeenstemmen met de vier kalenderkwartalen. De werkgevers moeten ervoor zorgen dat deze werkgeversbijdragen uiterlijk op de volgende vervaldata effectief op de bankrekening van het fonds staan : - eerste kwartaal lopende jaar : 31 juli van het lopende jaar; - tweede kwartaal lopende jaar : 31 oktober van het lopende jaar; - derde kwartaal lopende jaar : 31 januari van het jaar volgend op het lopende jaar; - vierde kwartaal lopende jaar : 30 april van het jaar volgend op het lopende jaar. Indien een vervaldag samenvalt met een inactiviteitsdag (wettelijke feestdag, zaterdag of zondag) wordt deze verschoven naar de eerstvolgende werkdag. Art. 11.  § 1. Bij laattijdige betaling moet de werkgever voor elk kwartaal waarop de bijdragen betrekking hebben, vanaf de eerste dag volgend op de in artikel 10, § 2 bepaalde vervaldag, verplicht een verhoging van 10 pct. op het bedrag van de verschuldigde werkgeversbijdragen betalen. Daarenboven is de werkgever een nalatigheidsintrest verschuldigd, zonder dat hiervoor een ingebrekestelling vereist is, die gelijk is aan de nalatigheidsintrest van toepassing op de RSZ-bijdragen.  § 2. Voor de inning van de bijdragen geldt de verjaringstermijn toegepast door de Rijksdienst voor Sociale Zekerheid. Art. 12.  Onverminderd de toepassing van artikel 14 van de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid, kunnen de percentages van de bijdragevoeten van de werkgeversbijdragen slechts gewijzigd worden per collectieve arbeidsovereenkomst, gesloten in het Paritair Comité voor de bedienden van de textielnijverheid en algemeen verbindend verklaard bij koninklijk besluit. VI. Beheer Art. 13. Het fonds wordt beheerd door een raad van beheer die paritair is samengesteld uit vertegenwoordigers van de werkgevers en de bedienden, vertegenwoordigd in het Paritair Comité voor de bedienden van de textielnijverheid. Deze raad bestaat uit tien leden, met name : vijf vertegenwoordigers van de werkgevers en vijf vertegenwoordigers van de bedienden.De leden van de raad van beheer worden aangeduid door het Paritair Comité voor de bedienden van de textielnijverheid onder de gewone of de plaatsvervangende leden van dit comité. Hun mandaat eindigt wanneer zij ophouden lid te zijn van het Paritair Comité voor de bedienden van de textielnijverheid. In dat geval worden zij vervangen door een lid van het Paritair Comité voor de bedienden van de textielnijverheid dat behoort tot dezelfde groep als het lid van wie het mandaat een einde nam. Art. 14. Ieder jaar duidt de raad van beheer onder de leden van de raad van beheer een voorzitter en twee ondervoorzitters aan. Er zal voor het voorzitterschap en het eerste ondervoorzitterschap een beurtregeling worden toegepast onder de vertegenwoordigers van de werkgevers en van de bedienden. De tweede ondervoorzitter behoort steeds tot de groep van de vertegenwoordigers van de bedienden. Art. 15. De raad van beheer vergadert minstens eenmaal per semester en telkens wanneer twee leden van de raad hierom verzoeken. De uitnodigingen moeten de agenda vermelden. De notulen worden opgemaakt door de administratie van het fonds en ondertekend door diegene die de vergadering heeft voorgezeten. De uittreksels uit de notulen worden ondertekend door de voorzitter of door twee leden van de raad van beheer. De beslissingen worden genomen bij volstrekte meerderheid van stemmen der aanwezige leden. De stemming is geldig indien eraan deelgenomen wordt door ten minste één lid van iedere groep en op voorwaarde dat het ter stemming gebrachte punt duidelijk vermeld werd op de agenda van de bijeenroeping van de vergadering. Art. 16. De raad van beheer heeft tot opdracht het fonds te beheren en alle maatregelen te treffen die nodig blijken voor zijn goede werking. Hij beschikt over de meest uitgebreide bevoegdheden voor het beheer van het fonds. Hij treedt in rechte op in naam van het fonds. Art. 17. De raad van beheer kan bijzondere bevoegdheden aan één of meer van zijn leden of aan derden overdragen. Voor alle andere handelingen dan die waarvoor door de raad van beheer bijzondere opdrachten werden gegeven, volstaat de gezamenlijke handtekening van twee leden van de raad van beheer, één van iedere groep opdat het fonds geldig vertegenwoordigd zou zijn tegenover derden, zonder dat zij enige rechtvaardiging aan derden hoeven voor te leggen van voorafgaande beraadslaging of machtiging. Art. 18. De beheerders zijn slechts verantwoordelijk voor de uitvoering van hun mandaat en zij gaan geen enkele persoonlijke verplichting aan ten gevolge van de uitvoering van hun mandaat van beheerder, ten opzichte der verbintenissen van het fonds. VII. Begrotingen en rekeningen Art. 19. Het dienstjaar neemt een aanvang op 1 januari en sluit op 31 december. Art. 20. Elk jaar, uiterlijk tijdens de maand december, wordt een begroting voor het volgende jaar ter goedkeuring aan het Paritair Comité voor de bedienden van de textielnijverheid voorgelegd. Op 31 december worden de rekeningen van het verlopen jaar afgesloten. De boekhouding wordt gevoerd en de jaarrekeningen worden opgesteld in overeenstemming met het koninklijk besluit van 15 januari 1999 betreffende de boekhouding en de jaarrekening met betrekking tot de fondsen voor bestaanszekerheid. VIII. Toezicht Art. 21. De raad van beheer, alsmede bij toepassing van artikel 12 van de wet van 7 januari 1958 betreffende de fondsen voor bestaanszekerheid de door het Paritair Comité voor de bedienden van de textielnijverheid aangewezen revisor, brengen jaarlijks ieder een schriftelijk verslag uit over het vervullen van hun opdracht tijdens het verlopen jaar. Art. 22. De jaarrekening, het jaarverslag en het verslag van de revisor dienen uiterlijk tijdens de maand juni ter goedkeuring aan het Paritair Comité voor de bedienden van de textielnijverheid voorgelegd te worden. IX. Ontbinding en vereffening Art. 23. Het fonds kan slechts ontbonden worden bij eenparige beslissing van het Paritair Comité voor de bedienden van de textielnijverheid. Art. 24.  Ingeval bij de ontbinding van het fonds gelden beschikbaar blijven, wijst het Paritair Comité voor de bedienden van de textielnijverheid de vereffenaars aan, bepaalt hun bevoegdheden en bezoldiging en beslist over de bestemming van het overblijvende vermogen van het fonds (na vereffening van alle schulden). Deze bestemming zal zo nauw mogelijk aansluiten bij het doel waarvoor het fonds werd opgericht, zoals bepaald in artikel 3 van deze statuten. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -3160,28 +3153,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2025003395</t>
+          <t>2025201179</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>06 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>9 april 2024. - Koninklijk besluit tot wijziging van diverse bepalingen betreffende arbeidsongevallen in de overheidssector. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 16 januari 2025, gesloten in het Paritair Comité voor de textielnijverheid, betreffende het leven lang leren, het werkbaar werk en de arbeidsmarktwerking in de textielsector (1)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-06&amp;numac_search=2025003395&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003395=85&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025201179&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201179=85&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 9 april 2024 tot wijziging van diverse bepalingen betreffende arbeidsongevallen in de overheidssector (Belgisch Staatsblad van 26 april 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST POLITIK UND UNTERSTÜTZUNG9. APRIL 2024 - Königlicher Erlass zur Abänderung verschiedener Bestimmungen in Bezug auf Arbeitsunfälle im öffentlichen SektorPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des Gesetzes vom 3. Juli 1967 über die Vorbeugung von oder den Schadenersatz für Arbeitsunfälle, Wegeunfälle und Berufskrankheiten im öffentlichen Sektor;Aufgrund des Königlichen Erlasses vom 24. Januar 1969 über den Schadenersatz für Arbeitsunfälle und Wegeunfälle zugunsten von Personalmitgliedern des öffentlichen Sektors;Aufgrund des Königlichen Erlasses vom 12. Juni 1970 über den Schadenersatz für Arbeitsunfälle und Wegeunfälle zugunsten der Personalmitglieder der Einrichtungen öffentlichen Interesses, juristischen Personen des öffentlichen Rechts und autonomen öffentlichen Unternehmen;Aufgrund des Königlichen Erlasses vom 13. Juli 1970 über den Schadenersatz für Arbeitsunfälle und Wegeunfälle zugunsten bestimmter Personalmitglieder von öffentlichen Diensten oder Einrichtungen des lokalen Sektors;Aufgrund der Stellungnahmen der Finanzinspektoren des Öffentlichen Dienstes, der Volksgesundheit und des Innern vom 16. Oktober 2023, 18. Oktober 2023 beziehungsweise 18. Oktober 2023;Aufgrund des Einverständnisses der Staatssekretärin für Haushalt vom 23. Oktober 2023;Aufgrund von Artikel 8 § 1 Nr. 4 des Gesetzes vom 15. Dezember 2013 zur Festlegung verschiedener Bestimmungen in Sachen administrative Vereinfachung ist vorliegender Erlass von der Auswirkungsanalyse beim Erlass von Vorschriften befreit, da es sich um Selbstregulierungsbestimmungen handelt;Aufgrund des Protokolls Nr. 241/8 des Gemeinsamen Ausschusses für alle öffentlichen Dienste vom 8. Februar 2024;Aufgrund des Antrags auf Begutachtung binnen einer Frist von dreißig Tagen, der in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat eingereicht worden ist;In der Erwägung, dass der Antrag auf Begutachtung am 5. März 2024 unter der Nummer 75.812/4 in die Liste der Gesetzgebungsabteilung des Staatsrates eingetragen worden ist;Aufgrund des Beschlusses der Gesetzgebungsabteilung vom 5. März 2024 in Anwendung von Artikel 84 § 5 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat, binnen der gesetzten Frist kein Gutachten abzugeben;Auf Vorschlag der Ministerin des Öffentlichen Dienstes, des Ministers der Sozialen Angelegenheiten und der Volksgesundheit und der Ministerin des Innern und aufgrund der Stellungnahme der Minister, die im Rat darüber beraten haben,Haben Wir beschloßen und erlassen Wir:KAPITEL 1 - Abänderung des Königlichen Erlasses vom 24. Januar 1969 über den Schadenersatz für Arbeitsunfälle und Wegeunfälle zugunsten von Personalmitgliedern des öffentlichen SektorsArtikel 1 -  Artikel 1 des Königlichen Erlasses vom 24. Januar 1969 über den Schadenersatz für Arbeitsunfälle und Wegeunfälle zugunsten von Personalmitgliedern des öffentlichen Sektors, ersetzt durch den Königlichen Erlass vom 7. Juni 2006 und abgeändert durch die Königlichen Erlasse vom 25. Februar 2017 und 29. Juli 2019, wird wie folgt abgeändert:a) In Nr. 5 werden die Wörter ", einschließlich der von oder im Namen der Französischen Gemeinschaftskommission organisierten Lehranstalten" aufgehoben.b) In Nr. 6 werden die Wörter "oder der Französischen Gemeinschaftskommission" aufgehoben.c) Nummer 7 wird wie folgt ersetzt:"7. der psycho-medizinisch-sozialen Zentren, Zentren für Schülerbetreuung, Schul- und Berufsberatungsdienste und Dienste für pädagogische Begleitung, die von einer der Gemeinschaften organisiert oder subventioniert werden,".Art. 2 - Artikel 2 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 20. September 1998 und abgeändert durch den Königlichen Erlass vom 7. Juni 2006, wird wie folgt abgeändert:a) In Nr. 3 werden die Wörter "weder eine Gehaltssubvention noch einen Lohn zu Lasten einer Gemeinschaft oder Gemeinschaftskommission beziehen" durch die Wörter "keine Gehaltssubvention zu Lasten einer Gemeinschaft beziehen" ersetzt.b) Nr. 4 wird aufgehoben.c) In Nr. 5 werden die Wörter "oder Gemeinschaftskommission" aufgehoben.Art. 3 - In Artikel 3 Absatz 1 Nr. 2 Buchstabe e) desselben Erlasses, ersetzt durch den Königlichen Erlass vom 20. September 1998, werden die Wörter "oder das Kollegium, der beziehungsweise dem sie unterstehen" durch die Wörter ", der sie unterstehen" ersetzt.Art. 4 - In denselben Erlass wird ein Artikel 3bis mit folgendem Wortlaut eingefügt:"Art. 3bis - § 1 - Beschlüsse, Vorschläge, Aufforderungen, Vorladungen und Ministerielle Erlasse werden dem Opfer oder seinen Berechtigten auf eine der folgenden Weisen übermittelt:1. auf elektronischem Weg mit Empfangsbestätigung,2. durch persönliche Aushändigung gegen datierte und unterzeichnete Empfangsbestätigung,3. per Einschreibesendung an die letzte mitgeteilte Adresse.Wenn die Übermittlung auf mehrere der in Absatz 1 erwähnten Weisen erfolgt ist, gilt die Frist, die für das Opfer oder seine Berechtigten am günstigsten ist. § 2 - Das Opfer oder seine Berechtigten reichen ihren Antrag, ihre Erklärung, ihr ärztliches Attest mit ersten Feststellungen und ihren ausführlichen medizinischen Bericht auf eine der in § 1 Absatz 1 Nr. 1 bis 3 erwähnten Weisen ein. § 3 - Anträge und medizinische Befunde, die zwischen dem in Artikel 6 erwähnten Dienst und der Verwaltung der medizinischen Expertise ausgetauscht werden, werden auf eine der folgenden Weisen übermittelt:1. auf elektronischem Weg mit Empfangsbestätigung,2. per gewöhnliche Post,3. per Einschreibesendung."Art. 5 - Artikel 5 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 7. Juni 2007, wird wie folgt abgeändert:1. Absatz 1 wird wie folgt ersetzt:"Bestattungsgeld wird gemäß den Artikeln 92 bis 95 des Königlichen Erlasses vom 13. Juli 2017 zur Festlegung der Zulagen und Entschädigungen der Personalmitglieder des föderalen öffentlichen Dienstes gewährt."2. Absatz 2 wird aufgehoben.Art. 6 - Artikel 5bis desselben Erlasses, eingefügt durch den Königlichen Erlass vom 7. Juni 2007 und abgeändert durch die Königlichen Erlasse vom 26. November 2012 und 1. Dezember 2013, wird wie folgt abgeändert:1. In § 1 werden die Wörter "der Arbeitsunfähigkeitsgrad" durch die Wörter "der Prozentsatz bleibender Arbeitsunfähigkeit" ersetzt.2. In § 2 Absatz 1 Nr. 1 wird der Begriff "Grad" jeweils durch den Begriff "Prozentsatz" ersetzt.3. [Abänderung des niederländischen Textes von § 2 Absatz 1 Nr. 1]4. In § 3 werden die Wörter "bleibender Unfähigkeit" durch die Wörter "bleibender Arbeitsunfähigkeit" ersetzt.5. Die Paragraphen 4 und 5 werden wie folgt ersetzt:" § 4 - Das Opfer reicht seinen Antrag, dem alle Belege beiliegen, bei dem in Artikel 6 erwähnten Dienst ein. Dieser Dienst übermittelt ihn binnen achtundvierzig Stunden der Verwaltung der medizinischen Expertise. Diese untersucht das Opfer spätestens drei Monate nach Einreichung des Antrags.Die Verwaltung der medizinischen Expertise behält den Prozentsatz bleibender Arbeitsunfähigkeit bei oder erhöht ihn und legt im Falle einer Verschlimmerung das Datum fest. Sie notifiziert dem in Artikel 6 erwähnten Dienst ihre medizinischen Befunde. Der Minister oder sein Beauftragter hält diese medizinischen Befunde in einem Ministeriellen Erlass fest und notifiziert ihn dem Opfer. § 5 - Der Zuschlag ist ab dem ersten Tag des Monats der Verschlimmerung, auf die er sich bezieht, auszuzahlen. Ab dem Datum der Gewährung des Zuschlags wird dieser zusammen mit der Rente ausgezahlt."6. [Abänderung des französischen Textes von § 6]Art. 7 - Artikel 5ter desselben Erlasses, eingefügt durch den Königlichen Erlass vom 7. Juni 2007 und abgeändert durch die Königlichen Erlasse vom 26. November 2012 und 1. Dezember 2013, wird wie folgt abgeändert:1. In § 5 Absatz 1 werden die Wörter "per Einschreiben" aufgehoben.2. In § 5 werden die Absätze 2 und 3 wie folgt ersetzt:"Dieser Dienst übermittelt ihn binnen achtundvierzig Stunden der Verwaltung der medizinischen Expertise. Diese notifiziert dem in Artikel 6 erwähnten Dienst spätestens drei Monate nach Einreichung des Antrags ihre aufgrund der Aktenlage getroffenen medizinischen Befunde.Der Minister oder sein Beauftragter hält diese medizinischen Befunde in einem Ministeriellen Erlass fest und notifiziert ihn den Berechtigten."3. In § 6 werden die Wörter "nach der Notifizierung des Ministeriellen Erlasses" durch die Wörter "des Todes des Opfers" ersetzt.Art. 8 - Artikel 7 desselben Erlasses, abgeändert durch die Königlichen Erlasse vom 21. November 1991, 20. September 1998 und 1. Dezember 2013, wird wie folgt abgeändert:a) [Abänderung des niederländischen Textes von Absatz 1]b) In Absatz 2 werden die Wörter "des Formulars "Unfallerklärung", das in doppelter Ausfertigung erstellt wird" durch die Wörter "einer Arbeitsunfallerklärung" ersetzt.c) Absatz 3 wird wie folgt ersetzt:"Die Arbeitsunfallerklärung, der ein ärztliches Attest mit ersten Feststellungen beigefügt werden muss, wenn der Unfall eine zeitweilige Arbeitsunfähigkeit zur Folge hat oder haben kann, muss an den in Artikel 6 erwähnten Dienst geschickt werden. Dieser Dienst übermittelt sie binnen achtundvierzig Stunden der Fedris-Datenbank über das Portal der sozialen Sicherheit."d) In Absatz 4 werden die Wörter "dieses Formulars und des ärztlichen Attestes" durch die Wörter "der Arbeitsunfallerklärung" ersetzt.e) Artikel 7 wird durch einen Absatz mit folgendem Wortlaut ergänzt:"Im ärztlichen Attest mit ersten Feststellungen wird Folgendes angegeben:1. Name, Vorname und Adresse des Arztes,2. Name, Vorname und Adresse des Opfers,3. Datum des Unfalls,4. Art und Lage der Verletzungen,5. Folgen der Verletzungen,6. Beginndatum der Arbeitsunfähigkeit und ihre voraussichtliche Dauer in Anzahl Tagen,7. Ort, an dem die Pflege erfolgt,8. Datum und Ort der Ausstellung des ärztlichen Attests,9. Unterschrift und Stempel des Arztes."Art. 9 - Artikel 8 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 8. Mai 2014, wird wie folgt abgeändert:1. Absatz 1 erster Gedankenstrich wird durch die Wörter "oder gegebenenfalls Tod" ergänzt.2. In Absatz 1 zweiter Gedankenstrich wird das Wort "Arbeitsunfähigkeitszeiträumen" durch die Wörter "Zeiträumen zeitweiliger Arbeitsunfähigkeit" ersetzt.3. [Abänderung des niederländischen Textes von Absatz 1 dritter Gedankenstrich]4. [Abänderung des französischen Textes von Absatz 1 dritter Gedankenstrich]5. [Abänderung des niederländischen Textes von Absatz 2]6. In Absatz 2 wird das Wort "Arbeitsunfähigkeitszeiträumen" durch die Wörter "Zeiträumen zeitweiliger Arbeitsunfähigkeit" ersetzt.7. Artikel 8 wird durch einen Absatz mit folgendem Wortlaut ergänzt:"Die Verwaltung der medizinischen Expertise notifiziert dem in Artikel 6 erwähnten Dienst binnen dreißig Tagen ab der letzten ärztlichen Untersuchung ihre medizinischen Befunde."Art. 10 - Artikel 8bis desselben Erlasses, eingefügt durch den Königlichen Erlass vom 8. Mai 2014, wird aufgehoben.Art. 11 - Artikel 9 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 8. Mai 2014 und abgeändert durch den Königlichen Erlass vom 7. November 2021, wird wie folgt ersetzt:"Art. 9 - § 1 - Bei zeitweiliger Arbeitsunfähigkeit von mindestens dreißig Tagen wird das Opfer von Amts wegen bei der Verwaltung der medizinischen Expertise vorgeladen. § 2 - Bei zeitweiliger Arbeitsunfähigkeit von weniger als dreißig Tagen wird das Opfer, wenn es dem in Artikel 6 erwähnten Dienst binnen sechs Monaten nach dem Unfall einen ausführlichen medizinischen Bericht des von ihm konsultierten Arztes zur Bescheinigung einer bleibenden Arbeitsunfähigkeit übermittelt, von Amts wegen bei der Verwaltung der medizinischen Expertise vorgeladen.Der in Artikel 6 erwähnte Dienst übermittelt der Verwaltung der medizinischen Expertise den ausführlichen medizinischen Bericht binnen achtundvierzig Stunden.Wenn das Opfer binnen sechs Monaten nach dem Unfall keinen ausführlichen medizinischen Bericht übermittelt, wie in Absatz 1 erwähnt, notifiziert der Minister oder sein Beauftragter ihm seinen Beschluss zur Genesungserklärung. Das Konsolidierungsdatum entspricht dem Datum der Notifizierung des Beschlusses zur Genesungserklärung. § 3 - Wenn die Verwaltung der medizinischen Expertise das Opfer untersucht hat, notifiziert sie dem in Artikel 6 erwähnten Dienst ihre medizinischen Befunde.Wenn der Unfall einen Prozentsatz bleibender Arbeitsunfähigkeit zur Folge hat, überprüft der Minister oder sein Beauftragter, ob die Bedingungen für die Gewährung von Entschädigungen erfüllt sind, und schlägt dem Opfer die Zahlung einer Rente vor. In diesem Vorschlag werden die Entlohnung, die als Grundlage für die Berechnung der Rente dient, die Art der Verletzung, der Prozentsatz bleibender Arbeitsunfähigkeit und das Konsolidierungsdatum gemäß den medizinischen Befunden der Verwaltung der medizinischen Expertise angegeben.Wenn der Unfall keinen Prozentsatz bleibender Arbeitsunfähigkeit zur Folge hat, notifiziert der Minister oder sein Beauftragter dem Opfer einen Beschluss zur Genesungserklärung, der die medizinischen Befunde der Verwaltung der medizinischen Expertise enthält.Falls das Opfer nach zwei aufeinanderfolgenden Aufforderungen ohne triftigen Grund nicht bei der Verwaltung der medizinischen Expertise vorstellig wird, benachrichtigt diese den in Artikel 6 erwähnten Dienst. Der Minister oder sein Beauftragter notifiziert dem Opfer seinen Beschluss zur Genesungserklärung. Das Konsolidierungsdatum entspricht dem Datum der Notifizierung des Beschlusses zur Genesungserklärung. § 4 - Wenn das Opfer mit dem in § 3 Absatz 2 erwähnten Vorschlag einverstanden ist, hält der Minister oder sein Beauftragter ihn in einem Ministeriellen Erlass fest und notifiziert diesen dem Opfer. § 5 - Wenn das Opfer vor der Notifizierung des in den Paragraphen 2 und 3 erwähnten Beschlusses zur Genesungserklärung oder des in § 4 erwähnten Ministeriellen Erlasses stirbt, können die in den Artikeln 8 bis 10 des Gesetzes erwähnten Berechtigten bei dem in Artikel 6 erwähnten Dienst einen Antrag, dem alle Belege beiliegen, zur Feststellung des Kausalzusammenhangs zwischen Unfall und Tod des Opfers einreichen.Dieser Dienst übermittelt den Antrag binnen achtundvierzig Stunden der Verwaltung der medizinischen Expertise. Diese notifiziert dem in Artikel 6 erwähnten Dienst spätestens drei Monate nach Einreichung des Antrags ihre aufgrund der Aktenlage getroffenen medizinischen Befunde.Wenn der Kausalzusammenhang zwischen Unfall und Tod feststeht, überprüft der Minister oder sein Beauftragter, ob die in den Artikeln 8 bis 10 des Gesetzes erwähnten Bedingungen für die Gewährung der Renten erfüllt sind, und schlägt den Berechtigten die Zahlung einer Rente vor. In diesem Vorschlag wird die Entlohnung, auf deren Grundlage die Rente berechnet wird, angegeben. Wenn die Berechtigten mit dem Vorschlag einverstanden sind, hält der Minister oder sein Beauftragter ihn in einem Ministeriellen Erlass fest und notifiziert diesen den Berechtigten.Wenn der Kausalzusammenhang zwischen Unfall und Tod nicht feststeht, notifiziert der Minister oder sein Beauftragter den Berechtigten seinen Beschluss mit den medizinischen Befunden der Verwaltung der medizinischen Expertise."Art. 12 - Artikel 10 desselben Erlasses, zuletzt abgeändert durch den Königlichen Erlass vom 8. Mai 2014, wird wie folgt abgeändert:1. In § 1 Absatz 1 werden die Wörter "der Arbeitsunfähigkeit" durch die Wörter "des Prozentsatzes bleibender Arbeitsunfähigkeit" ersetzt.2. In § 1 Absatz 1 werden die Wörter "der Notwendigkeit der regelmäßigen Hilfe einer Drittperson" durch die Wörter "des Prozentsatzes der Hilfe einer Drittperson" ersetzt.3. In § 1 Absatz 1 erster Gedankenstrich werden die Wörter "Artikel 9 § 2 Absatz 1 oder § 3 Absatz 3" durch die Wörter "Artikel 9 § 2 Absatz 3 oder §  3 Absatz 3 oder Absatz 4" ersetzt.4. Paragraph 1 Absatz 2 wird aufgehoben.5. Die Paragraphen 2 und 3 werden wie folgt ersetzt:" § 2 - Das Opfer oder seine Berechtigten richten ihren Revisionsantrag, dem alle Belege beiliegen, an den in Artikel 6 erwähnten Dienst. § 3 - Der Minister oder sein Beauftragter setzt das Opfer unverzüglich von der Einreichung seines Revisionsantrags in Kenntnis."6. Artikel 10 wird durch einen Paragraphen 4 mit folgendem Wortlaut ergänzt:" § 4 - Der in Artikel 6 erwähnte Dienst übermittelt den Revisionsantrag binnen achtundvierzig Stunden der Verwaltung der medizinischen Expertise."Art. 13 - Artikel 11 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 1. Dezember 2013, wird wie folgt ersetzt:"Art. 11 - § 1 - Spätestens drei Monate nach Einreichung des Revisionsantrags untersucht die Verwaltung der medizinischen Expertise das Opfer.Die Verwaltung der medizinischen Expertise behält den Prozentsatz bleibender Arbeitsunfähigkeit und gegebenenfalls den Prozentsatz der Hilfe einer Drittperson bei oder ändert ihn und legt im Falle einer Änderung das Datum fest. § 2 - Im Falle eines Revisionsantrags aufgrund des Todes des Opfers trifft die Verwaltung der medizinischen Expertise spätestens drei Monate nach Einreichung des Revisionsantrags ihre medizinischen Befunde aufgrund der Aktenlage. § 3 - Die Verwaltung der medizinischen Expertise notifiziert dem in Artikel 6 erwähnten Dienst ihre medizinischen Befunde.Der Minister oder sein Beauftragter hält diese medizinischen Befunde in einem Ministeriellen Erlass fest und notifiziert ihn dem Opfer oder seinen Berechtigten. § 4 - Die Revision wirkt ab dem ersten Tag des Monats der Verschlimmerung oder dem ersten Tag des Monats nach der Verringerung. § 5 - Falls das Opfer nach zwei aufeinanderfolgenden Aufforderungen ohne triftigen Grund nicht bei der Verwaltung der medizinischen Expertise vorstellig wird, nachdem der in Artikel 10 § 3 erwähnte Revisionsantrag eingereicht wurde, wird die Auszahlung der Entschädigungen und Renten ab dem ersten Tag des Monats nach dem Datum der zweiten Aufforderung ausgesetzt.Die Verwaltung der medizinischen Expertise beurteilt die Relevanz der Gründe für das Nichterscheinen des Opfers, sofern es eine schriftliche Rechtfertigung einreicht.Die Auszahlung wird ohne rückwirkende Kraft am ersten Tag des Monats nach dem Datum des Erscheinens des Opfers, das zuvor ohne triftigen Grund nicht bei der Verwaltung der medizinischen Expertise vorstellig geworden war, wieder aufgenommen."Art. 14 - In Artikel 28 § 1 Absatz 2 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 7. Juni 2007 und abgeändert durch den Königlichen Erlass vom 1. Dezember 2013, werden die Wörter "von Formularen zur Unfallerklärung" durch die Wörter "der Arbeitsunfallerklärung" ersetzt.Art. 15 - Anlage 1 zu demselben Erlass wird aufgehoben.KAPITEL 2 - Abänderung des Königlichen Erlasses vom 12. Juni 1970 über den Schadenersatz für Arbeitsunfälle und Wegeunfälle zugunsten der Personalmitglieder der Einrichtungen öffentlichen Interesses, juristischen Personen des öffentlichen Rechts und autonomen öffentlichen UnternehmenArt. 16 - Artikel 8 des Königlichen Erlasses vom 12. Juni 1970 über den Schadenersatz für Arbeitsunfälle und Wegeunfälle zugunsten der Personalmitglieder der Einrichtungen öffentlichen Interesses, juristischen Personen des öffentlichen Rechts und autonomen öffentlichen Unternehmen, abgeändert durch den Königlichen Erlass vom 27. Mai 2004, wird wie folgt abgeändert:1. Absatz 1 wird wie folgt ersetzt:"Das Muster der Arbeitsunfallerklärung wird von dem für den föderalen öffentlichen Dienst zuständigen Minister festgelegt."2. In Absatz 2 werden die Wörter "des Formulars, anhand dessen der Unfall gemeldet wird, und das Muster des beizufügenden ärztlichen Attestes" durch die Wörter "der Arbeitsunfallerklärung" ersetzt.KAPITEL 3 - Abänderung des Königlichen Erlasses vom 13. Juli 1970 über den Schadenersatz für Arbeitsunfälle und Wegeunfälle zugunsten bestimmter Personalmitglieder von öffentlichen Diensten oder Einrichtungen des lokalen SektorsArt. 17 - Artikel 1 des Königlichen Erlasses vom 13. Juli 1970 über den Schadenersatz für Arbeitsunfälle und Wegeunfälle zugunsten bestimmter Personalmitglieder von öffentlichen Diensten oder Einrichtungen des lokalen Sektors, ersetzt durch den Königlichen Erlass vom 26. November 2012 und abgeändert durch die Königlichen Erlasse vom 25. Februar 2017 und 29. Juli 2019, wird wie folgt abgeändert:a) In Nr. 5 werden die Wörter "der Dienststellen des Kollegiums der Französischen Gemeinschaftskommission und" aufgehoben.b) Eine Nr. 5bis mit folgendem Wortlaut wird eingefügt:"5bis. der Bildungseinrichtungen, der psycho-medizinisch-sozialen Zentren, der Schul- und Berufsberatungsstellen, der Dienste für pädagogische Begleitung und der Zentren für Schülerbetreuung des Kollegiums der Französischen Gemeinschaftskommission,".Art. 18 - In denselben Erlass wird ein Artikel 3bis mit folgendem Wortlaut eingefügt:"Art. 3bis - § 1 - Beschlüsse, Vorschläge, Aufforderungen und Vorladungen werden dem Opfer oder seinen Berechtigten auf eine der folgenden Weisen übermittelt:1. auf elektronischem Weg mit Empfangsbestätigung,2. durch persönliche Aushändigung gegen datierte und unterzeichnete Empfangsbestätigung,3. per Einschreibesendung an die letzte mitgeteilte Adresse.Wenn die Übermittlung auf mehrere der in Absatz 1 erwähnten Weisen erfolgt ist, gilt die Frist, die für das Opfer oder seine Berechtigten am günstigsten ist. § 2 - Das Opfer oder seine Berechtigten reichen ihren Antrag, ihre Erklärung, ihr ärztliches Attest mit ersten Feststellungen und ihren ausführlichen medizinischen Bericht auf eine der in § 1 Absatz 1 Nr. 1 bis 3 erwähnten Weisen ein. § 3 - Anträge und medizinische Befunde, die zwischen dem in Artikel 6 erwähnten Dienst oder Beamten und dem medizinischen Dienst ausgetauscht werden, werden auf eine der folgenden Weisen übermittelt:1. auf elektronischem Weg mit Empfangsbestätigung,2. per gewöhnliche Post,3. per Einschreibesendung."Art. 19 - Artikel 5 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 26. November 2012, wird wie folgt abgeändert:1. Absatz 1 wird wie folgt ersetzt:"Bestattungsgeld wird gemäß den Artikeln 92 bis 95 des Königlichen Erlasses vom 13. Juli 2017 zur Festlegung der Zulagen und Entschädigungen der Personalmitglieder des föderalen öffentlichen Dienstes gewährt."2. Absatz 2 wird aufgehoben.Art. 20 - Artikel 5bis desselben Erlasses, eingefügt durch den Königlichen Erlass vom 26. November 2012, wird wie folgt abgeändert:1. [Abänderung des niederländischen Textes von § 1]2. In § 1 werden die Wörter "der Arbeitsunfähigkeitsgrad" durch die Wörter "der Prozentsatz bleibender Arbeitsunfähigkeit" ersetzt.3. In § 2 Absatz 1 Nr. 1 wird der Begriff "Grad" jeweils durch den Begriff "Prozentsatz" ersetzt.4. [Abänderung des niederländischen Textes von § 2 Absatz 1 Nr. 1]5. In § 3 werden die Wörter "bleibender Unfähigkeit" durch die Wörter "bleibender Arbeitsunfähigkeit" ersetzt.6. Die Paragraphen 4 und 5 werden wie folgt ersetzt:" § 4 - Das Opfer reicht seinen Antrag, dem alle Belege beiliegen, bei dem in Artikel 6 erwähnten Dienst oder Beamten ein. Dieser Dienst beziehungsweise Beamte übermittelt ihn binnen achtundvierzig Stunden dem medizinischen Dienst. Dieser untersucht das Opfer spätestens drei Monate nach Einreichung des Antrags.Der medizinische Dienst behält den Prozentsatz bleibender Arbeitsunfähigkeit bei oder erhöht ihn und legt im Falle einer Verschlimmerung das Datum fest. Er notifiziert dem in Artikel 6 erwähnten Dienst beziehungsweise Beamten seine medizinischen Befunde. Die Behörde hält diese medizinischen Befunde in einem Beschluss fest und notifiziert ihn dem Opfer. § 5 - Der Zuschlag ist ab dem ersten Tag des Monats der Verschlimmerung, auf die er sich bezieht, auszuzahlen. Ab dem Datum der Gewährung des Zuschlags wird dieser zusammen mit der Rente ausgezahlt."7. [Abänderung des französischen Textes von § 6]Art. 21 - Artikel 5ter desselben Erlasses, eingefügt durch den Königlichen Erlass vom 26. November 2012, wird wie folgt abgeändert:1. [Abänderung des niederländischen Textes von § 3 Absatz 1 vierter Gedankenstrich]2. Paragraph 5 wird wie folgt ersetzt:" § 5 - Die Berechtigten des Opfers reichen einen Antrag, dem alle Belege beiliegen, bei dem in Artikel 6 erwähnten Dienst beziehungsweise Beamten ein.Dieser Dienst beziehungsweise Beamte übermittelt ihn binnen achtundvierzig Stunden dem medizinischen Dienst. Dieser notifiziert dem in Artikel 6 erwähnten Dienst beziehungsweise Beamten spätestens drei Monate nach Einreichung des Antrags seine aufgrund der Aktenlage getroffenen medizinischen Befunde.Die Behörde hält diese medizinischen Befunde in einem Beschluss fest und notifiziert ihn den Berechtigten."3. In § 6 werden die Wörter "nach Notifizierung des Beschlusses der Behörde" durch die Wörter "des Todes des Opfers" ersetzt.Art. 22 - Artikel 7 desselben Erlasses wird wie folgt abgeändert:a) In Absatz 1 werden die Wörter "des Formulars "Unfallerklärung", das vorliegendem Erlass beiliegt" durch die Wörter "einer Arbeitsunfallerklärung" ersetzt.b) Absatz 2 wird wie folgt ersetzt:"Die Arbeitsunfallerklärung, der ein ärztliches Attest mit ersten Feststellungen beigefügt werden muss, wenn der Unfall eine zeitweilige Arbeitsunfähigkeit zur Folge hat oder haben kann, muss an den in Artikel 6 erwähnten Dienst beziehungsweise Beamten geschickt werden. Dieser Dienst beziehungsweise Beamte übermittelt sie binnen achtundvierzig Stunden der Fedris-Datenbank über das Portal der sozialen Sicherheit."c) Artikel 7 wird durch zwei Absätze mit folgendem Wortlaut ergänzt:"Das Muster dieser Erklärung wird von dem für den föderalen öffentlichen Dienst zuständigen Minister festgelegt.Im ärztlichen Attest mit ersten Feststellungen wird Folgendes angegeben:1. Name, Vorname und Adresse des Arztes,2. Name, Vorname und Adresse des Opfers,3. Datum des Unfalls,4. Art und Lage der Verletzungen,5. Folgen der Verletzungen,6. Beginndatum der Arbeitsunfähigkeit und ihre voraussichtliche Dauer in Anzahl Tagen,7. Ort, an dem die Pflege erfolgt,8. Datum und Ort der Ausstellung des ärztlichen Attests,9. Unterschrift und Stempel des Arztes."Art. 23 - Artikel 8 desselben Erlasses, eingefügt durch den Königlichen Erlass vom 8. Mai 2014, wird wie folgt abgeändert:1. [Abänderung des niederländischen Textes von Absatz 1]2. Absatz 1 erster Gedankenstrich wird durch die Wörter "oder gegebenenfalls Tod" ergänzt.3. In Absatz 1 zweiter Gedankenstrich wird das Wort "Arbeitsunfähigkeitszeiträumen" durch die Wörter "Zeiträumen zeitweiliger Arbeitsunfähigkeit" ersetzt.4. [Abänderung des niederländischen Textes von Absatz 1 dritter Gedankenstrich]5. [Abänderung des französischen Textes von Absatz 1 dritter Gedankenstrich]6. In Absatz 2 zweiter Gedankenstrich wird das Wort "Arbeitsunfähigkeitszeiträumen" durch die Wörter "Zeiträumen zeitweiliger Arbeitsunfähigkeit" ersetzt.7. Absatz 3 wird wie folgt ersetzt:"Der medizinische Dienst notifiziert dem in Artikel 6 erwähnten Dienst beziehungsweise Beamten binnen dreißig Tagen ab der letzten ärztlichen Untersuchung seine medizinischen Befunde."8. Absatz 4 wird aufgehoben.Art. 24 - Artikel 9 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 8. Mai 2014 und abgeändert durch den Königlichen Erlass vom 7. November 2021, wird wie folgt ersetzt:"Art. 9 - § 1 - Bei zeitweiliger Arbeitsunfähigkeit von mindestens dreißig Tagen wird das Opfer von Amts wegen beim medizinischen Dienst vorgeladen. § 2 - Bei zeitweiliger Arbeitsunfähigkeit von weniger als dreißig Tagen wird das Opfer, wenn es dem in Artikel 6 erwähnten Dienst beziehungsweise Beamten binnen sechs Monaten nach dem Unfall einen ausführlichen medizinischen Bericht des von ihm konsultierten Arztes zur Bescheinigung einer bleibenden Arbeitsunfähigkeit übermittelt, von Amts wegen beim medizinischen Dienst vorgeladen.Der in Artikel 6 erwähnte Dienst beziehungsweise Beamte übermittelt dem medizinischen Dienst den ausführlichen Bericht binnen achtundvierzig Stunden.Wenn das Opfer binnen sechs Monaten nach dem Unfall keinen ausführlichen medizinischen Bericht übermittelt, wie in Absatz 1 erwähnt, notifiziert die Behörde ihm ihren Beschluss zur Genesungserklärung. Das Konsolidierungsdatum entspricht dem Datum der Notifizierung des Beschlusses zur Genesungserklärung. § 3 - Wenn der medizinische Dienst das Opfer untersucht hat, notifiziert er dem in Artikel 6 erwähnten Dienst beziehungsweise Beamten seine medizinischen Befunde.Wenn der Unfall einen Prozentsatz bleibender Arbeitsunfähigkeit zur Folge hat, überprüft die Behörde, ob die Bedingungen für die Gewährung von Entschädigungen erfüllt sind, und schlägt dem Opfer die Zahlung einer Rente vor. In diesem Vorschlag werden die Entlohnung, die als Grundlage für die Berechnung der Rente dient, die Art der Verletzung, der Prozentsatz bleibender Arbeitsunfähigkeit und das Konsolidierungsdatum gemäß den medizinischen Befunden des medizinischen Dienstes angegeben.Wenn der Unfall keinen Prozentsatz bleibender Arbeitsunfähigkeit zur Folge hat, notifiziert die Behörde dem Opfer einen Beschluss zur Genesungserklärung, der die medizinischen Befunde des medizinischen Dienstes enthält.Falls das Opfer nach zwei aufeinanderfolgenden Aufforderungen ohne triftigen Grund nicht beim medizinischen Dienst vorstellig wird, benachrichtigt dieser den in Artikel 6 erwähnten Dienst beziehungsweise Beamten. Die Behörde notifiziert dem Opfer ihren Beschluss zur Genesungserklärung. Das Konsolidierungsdatum entspricht dem Datum der Notifizierung des Beschlusses zur Genesungserklärung. § 4 - Wenn das Opfer mit dem in § 3 Absatz 2 erwähnten Vorschlag einverstanden ist, hält die Behörde ihn in einem Beschluss fest und notifiziert diesen dem Opfer. § 5 - Wenn das Opfer vor der Notifizierung des in den Paragraphen 2 und 3 erwähnten Beschlusses zur Genesungserklärung oder des in § 4 erwähnten Beschlusses stirbt, können die in den Artikeln 8 bis 10 des Gesetzes erwähnten Berechtigten bei dem in Artikel 6 erwähnten Dienst beziehungsweise Beamten einen Antrag, dem alle Belege beiliegen, zur Feststellung des Kausalzusammenhangs zwischen Unfall und Tod des Opfers einreichen.Dieser Dienst beziehungsweise Beamte übermittelt den Antrag binnen achtundvierzig Stunden dem medizinischen Dienst. Dieser notifiziert dem in Artikel 6 erwähnten Dienst beziehungsweise Beamten spätestens drei Monate nach Einreichung des Antrags seine aufgrund der Aktenlage getroffenen medizinischen Befunde.Wenn der Kausalzusammenhang zwischen Unfall und Tod feststeht, überprüft die Behörde, ob die in den Artikeln 8 bis 10 des Gesetzes erwähnten Bedingungen für die Gewährung der Renten erfüllt sind, und schlägt den Berechtigten die Zahlung einer Rente vor. In diesem Vorschlag wird die Entlohnung, auf deren Grundlage die Rente berechnet wird, angegeben. Wenn das Opfer mit dem Vorschlag einverstanden ist, hält die Behörde ihn in einem Ministeriellen Erlass fest und notifiziert diesen den Berechtigten.Wenn der Kausalzusammenhang zwischen Unfall und Tod nicht feststeht, notifiziert die Behörde den Berechtigten ihren Beschluss mit den medizinischen Befunden des medizinischen Dienstes."Art. 25 - Artikel 10 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 8. Mai 2014, wird aufgehoben.Art. 26 - Artikel 11 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 26. November 2012 und abgeändert durch den Königlichen Erlass vom 8. Mai 2014, wird wie folgt ersetzt:"Art. 11 - Anträge auf Revision der Entschädigungen, die auf eine Verschlimmerung oder Verringerung des Prozentsatzes bleibender Arbeitsunfähigkeit des Opfers, auf seinen durch die Folgen des Unfalls bedingten Tod oder auf eine Änderung des Prozentsatzes der Hilfe einer Drittperson gestützt sind, dürfen binnen drei Jahren ab einem der folgenden Zeitpunkte eingereicht werden:- der Notifizierung des in Artikel 9 § 2 Absatz 3 oder § 3 Absatz 3 oder Absatz 4 erwähnten Beschlusses,- der Notifizierung des in Artikel 9 § 4 erwähnten Beschlusses,- dem formell rechtskräftigen Beschluss."Art. 27 - Artikel 12 desselben Erlasses, abgeändert durch die Königlichen Erlasse vom 27. Januar 1988 und 26. November 2012, wird wie folgt ersetzt:"Art. 12 - Das Opfer oder seine Berechtigten richten ihren Revisionsantrag, dem alle Belege beiliegen, an den in Artikel 6 erwähnten Dienst beziehungsweise Beamten.Die Behörde setzt das Opfer unverzüglich von der Einreichung seines Revisionsantrags in Kenntnis.Der in Artikel 6 erwähnte Dienst beziehungsweise Beamte übermittelt den Revisionsantrag binnen achtundvierzig St</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de textielnijverheid; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 16 januari 2025, gesloten in het Paritair Comité voor de textielnijverheid, betreffende het leven lang leren, het werkbaar werk en de arbeidsmarktwerking in de textielsector. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor de textielnijverheid Collectieve arbeidsovereenkomst van 16 januari 2025 Leven lang leren, werkbaar werk en arbeidsmarktwerking in de textielsector (Overeenkomst geregistreerd op 10 februari 2025 onder het nummer 191979/CO/120) I. Toepassingsgebied Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op alle werkgevers die onder de bevoegdheid vallen van het Paritair Comité voor de textielnijverheid (PC 120) en op de arbeiders die ze tewerkstellen, met uitzondering van de ondernemingen en de erin tewerkgestelde arbeiders die onder de bevoegdheid vallen van het Paritair Subcomité voor de textielnijverheid uit het administratief arrondissement Verviers (PSC 120.01) en het Paritair Subcomité voor het vervaardigen van en de handel in zakken in jute of in vervangingsmaterialen (PSC 120.03).  § 2. Met "arbeiders" worden de mannelijke en vrouwelijke arbeiders bedoeld.II. Draagwijdte van de overeenkomst Art. 2. Deze collectieve arbeidsovereenkomst strekt ertoe de inspanningen die de sector in het kader van het paritair uitgebouwde sectoraal opleidingsbeleid de voorbije jaren heeft geleverd, minstens verder te zetten en waar mogelijk te verhogen. Deze collectieve arbeidsovereenkomst wordt gesloten voor de jaren 2025 en 2026 in toepassing van hoofdstuk 9 en 12 van de wet van 3 oktober 2022 houdende diverse arbeidsbepalingen. III. Werkbaar werk Art. 3. De werkgevers zijn voor de periode van 1 januari 2025 tot en met 31 december 2026 aan het "Waarborg- en Sociaal Fonds van de textielnijverheid", een bijdrage van 0,10 pct. (op de lonen aan 100 pct.) verschuldigd, berekend op grond van het volledig loon van de arbeiders, zoals bedoeld in artikel 23 van de wet van 29 juni 1981 houdende de algemene beginselen van de sociale zekerheid voor werknemers en de uitvoeringsbesluiten van deze wet. Deze bijdrage is per kwartaal verschuldigd op de lonen betaald gedurende de periode van 1 januari 2025 tot en met 31 december 2026 en wordt door het waarborg- en sociaal fonds geïnd en op de sectie "Werkbaar werk" gestort. De statuten van het "Waarborg- en Sociaal Fonds van de textielnijverheid" worden in deze zin aangepast. Art. 4. Vanuit Cobot vzw/Cefret asbl wordt de dienstverlening, begeleiding en projectmatige ondersteuning met betrekking tot werkbaar werk verder uitgebouwd, ten dienste van de ondernemingen en de werknemers in de textielsector. De sectorale sociale partners bepalen in de Permanente Beleidsgroep Opleiding de opdracht om hieromtrent sectorale expertise op te bouwen, waartoe de nodige middelen, zoals bedoeld in artikel 3 hiervoor, vanuit het waarborg- en sociaal fonds worden ingezet. De sectorale sociale partners bepalen in de Permanente Beleidsgroep Opleiding de nodige modaliteiten en voorwaarden voor deze dienstverlening, begeleiding en projectmatige ondersteuning met betrekking tot werkbaar werk. In geval van betwisting over de validatie van een project werkbaar werk, neemt de Permanente Beleidsgroep Opleiding de eindbeslissing. Eind 2026 zullen de sectorale sociale partners de stand van zaken betreffende het werkbaar werk evalueren. De sectorale sociale partners zullen eveneens werken aan een globale toekomstvisie betreffende het werkbaar werk. IV. Sectorale en arbeidsmarktgerichte opleidingen Art. 5. § 1. Om de participatiegraad aan opleiding te verhogen, zullen door Cobot vzw/Cefret asbl aanvragen ingediend worden bij het Paritair Comité voor de textielnijverheid voor de erkenning van sectorale beroepsopleidingen in het stelsel betaald educatief verlof (herstelwet van 22 januari 1985) of voor goedkeuring door het Paritair Comité voor de textielnijverheid van arbeidsmarktgerichte opleidingen in het stelsel van het Vlaams opleidingsverlof (decreet van 12 oktober 2018)  § 2. Voor de uren waarop de arbeider deelneemt aan sectorale opleidingen, erkend door het Paritair Comité voor de textielnijverheid als beroepsopleiding in het stelsel van het betaald educatief verlof (herstelwet van 22 januari 1985) of arbeidsmarktgerichte opleidingen, goedgekeurd door het paritair comité nr. 120 in het stelsel van het Vlaams opleidingsverlof (decreet van 12 oktober 2018), heeft hij recht op zijn normaal loon, zonder toepassing van de loongrens, zoals voorzien in artikel 114 van het herstelwet van 22 januari 1985 houdende sociale bepalingen.  § 3. Voor de dagen dat de arbeider deelneemt aan sectorale opleidingen, erkend door het Paritair Comité voor de textielnijverheid in het stelsel van het betaald educatief verlof (herstelwet van 22 januari 1985) of arbeidsmarktgerichte opleidingen, goedgekeurd door het paritair comité nr. 120 in het stelsel van het Vlaams opleidingsverlof (decreet van 12 oktober 2018), heeft hij recht op maaltijdcheques. V. Opleidingsplan Art. 6. In uitvoering van artikel 39 van de wet van 3 oktober 2022 houdende diverse arbeidsbepalingen wordt door Cobot vzw en Cefret asbl een webapplicatie "opleidingsplan" gebouwd ten dienste van de ondernemingen en de werknemers in de textielsector.De sectorale sociale partners bepalen in de Permanente Beleidsgroep Opleiding de opdracht en de inhoud hieromtrent alsook de nodige middelen die hiervoor vanuit het waarborg- en sociaal fonds worden ingezet. De werkgevers stellen één keer per burgerlijk jaar, vóór 31 maart, een opleidingsplan op voor hun werknemers in de schoot van de onderneming. Hiertoe legt de werkgever elk jaar een ontwerp van opleidingsplan voor aan de ondernemingsraad, of bij ontstentenis ervan aan de vakbondsafvaardiging, ten minste vijftien dagen vóór de vergadering die wordt gepland met het oog op het onderzoeken ervan. De ondernemingsraad, of bij ontstentenis ervan, de vakbondsafvaardiging, geeft advies over het ontwerp tegen uiterlijk 15 maart. Bij ontstentenis van een ondernemingsraad en een vakbondsafvaardiging in de onderneming legt de werkgever het opleidingsplan voor aan de werknemers tegen uiterlijk 15 maart. De werkgever stelt het opleidingsplan op, met dien verstande dat bijzondere aandacht zal gaan naar personen komende uit de in artikel 35 van de wet van 3 oktober 2022 gedefinieerde risicogroepen, in het bijzonder de werknemers van minstens 50 jaar oud en naar knelpuntberoepen en naar de wijze van evaluatie met de werknemers. Een bijzondere aandacht zal tevens gaan naar de werknemers, bedoeld in artikel 1, 3°, g) van het koninklijk besluit van 19 februari 2013 tot uitvoering van artikel 189, 4de lid van de wet van 27 december 2006 houdende diverse bepalingen (I) alsook naar de werknemers met een handicap zoals bedoeld in artikel 1, 4° van het voormelde koninklijk besluit van 19 februari 2013. Bij de uitwerking van het opleidingsplan dient de genderdimensie in aanmerking te worden genomen. Het plan moet minimaal de bij artikel 7 bedoelde formele en informele opleidingen bevatten, en uitleggen op welke wijze het bijdraagt aan de investeringen in opleiding, bedoeld in artikel 7. Het plan wordt voor een minimumduurtijd van één jaar gesloten. VI. Investeren in opleiding en groeipad Art. 7. Dit artikel 7 wordt gesloten in uitvoering van hoofdstuk 12 van de wet van 3 oktober 2022 betreffende diverse arbeidsbepalingen. In de ondernemingen die ten minste 20 werknemers tewerkstellen, uitgedrukt in voltijdse equivalenten, wordt voorzien in een individueel opleidingsrecht voor een voltijds tewerkgestelde werknemer met volgend groeipad : - vanaf 2023 : 2 dagen; - vanaf 2024 : 3 dagen; - vanaf 2026 : 4 dagen; - vanaf 2028 : 5 dagen. De werkgevers die minimum tien en minder dan twintig werknemers tewerkstellen, uitgedrukt in voltijdse equivalenten, voorzien in een individueel opleidingsrecht voor een voltijdse werknemer met volgend groeipad : - vanaf 2023 : 1 dag; - vanaf 2026 : 2 dagen. De werkgevers die minder dan tien werknemers tewerkstellen, worden uitgesloten van de toepassing van dit artikel 7. De sociale partners wijzen op het belang van opleiding en vorming en bevelen deze ondernemingen die minder dan tien werknemers tewerkstellen, aan om hun werknemers te stimuleren om hun positie op de arbeidsmarkt door middel van vorming en opleiding te verstevigen. Voor de toepassing van dit artikel wordt het aantal tewerkgestelde werknemers berekend in voltijdse equivalenten op basis van de gemiddelde tewerkstelling van de referteperiode voorafgaand aan de tweejaarlijkse periode die voor de eerste keer op 1 januari 2022 begint. De referteperiode is de periode bestaande uit het vierde kwartaal van het voorlaatste jaar (n-2) en de eerste drie kwartalen van het jaar (n-1) voorafgaand aan de tweejaarlijkse periode. Om het gemiddeld aantal tewerkgestelde werknemers in voltijdse equivalenten tijdens de referteperiode te berekenen, wordt het totaal van de op het einde van elk kwartaal van de referteperiode aangegeven werknemers in voltijdse equivalenten, gedeeld door het aantal kwartalen waarvoor de werkgever, aan de Rijksdienst voor Sociale Zekerheid, werknemers aangegeven heeft die onderworpen zijn aan de wet van 27 juni 1969 tot herziening van de besluitwet van 28 december 1944 betreffende de maatschappelijke zekerheid der arbeiders.Indien de werkgever voor de bedoelde referteperiode geen aangiftes diende over te maken aan de rijksdienst, wordt voor de bepaling van het gemiddelde verwezen naar het aantal werknemers tewerkgesteld op de laatste dag van het kwartaal waarbinnen de eerste tewerkstelling volgend op de referteperiode plaatsgreep. De praktische tenuitvoerlegging van het individueel opleidingsrecht en de verwezenlijking van het groeipad wordt nagestreefd door : - het opleidingsaanbod van Cobot vzw en Cefret asbl beter en ruimer bekend te maken aan werkgevers en werknemers; - het opleidingsaanbod van Cobot vzw en Cefret asbl verder uit te breiden; - via Cobot vzw en Cefret asbl acties te ondernemen om de participatiegraad aan opleidingen te verhogen; - werkgevers aan te moedigen om alle, zowel formele ais informele opleidingsinspanningen nauwgezet te registreren. Om het aantal individuele opleidingsdagen te bepalen worden minstens volgende opleidingen in aanmerking genomen : a) formele opleiding : door lesgevers of sprekers ontwikkelde cursussen en stages. Deze opleidingen worden gekenmerkt door een hoge graad van organisatie van de opleider of opleidingsinstelling. Ze gaan door op een plaats die duidelijk van de werkplek gescheiden is. Ze richten zich tot een groep leerlingen. Die opleidingen kunnen ontwikkeld en beheerd worden door de onderneming zelf of door een extern organisme; b) informele opleiding : de opleidingsactiviteiten, andere dan deze bedoeld onder a) die rechtstreeks betrekking hebben op het werk. Deze opleidingen worden gekenmerkt door een hoge graad van zelforganisatie door de individuele leerling of door een groep leerlingen met betrekking tot de tijd, de plaats en de inhoud, een inhoud die gekozen wordt volgens de individuele behoeften van de leerling op de werkplek, en met een rechtstreeks verband met het werk en de werkplek, met inbegrip van deelname aan conferenties of beurzen voor leerdoeleinden; c) de opleidingen die betrekking hebben op de materies inzake het welzijnsbeleid bedoeld in de wet van 4 augustus 1996 betreffende het welzijn van de werknemers bij de uitvoering van hun werk. Het saldo van de niet-opgebruikte opleidingsdagen wordt op het einde van het jaar overgedragen naar het daaropvolgende jaar, zonder dat dit saldo in mindering mag gebracht worden van het opleidingskrediet van de werknemer in dat volgende jaar. Het doel is dat op het einde van elke periode van vijf jaar, die ten vroegste kan beginnen op 1 januari 2024, of voor het einde van de arbeidsovereenkomst indien die eindigt voordat de voormelde periode van vijf jaar afloopt, de voltijds tewerkgestelde werknemer gemiddeld het minimum aantal opleidingsdagen per jaar zoals bepaald in dit artikel heeft opgenomen. Op het einde van de voormelde periode van vijf jaar, wordt het saldo van het beschikbare opleidingskrediet op nul gezet. VII. Eindbepalingen Art. 8. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025 en is gesloten voor de periode van 1 januari 2025 tot en met 31 december 2026, met uitzondering van artikel 5 dat van toepassing is gedurende de periode van 1 september 2025 tot en met 31 augustus 2027, alsook bijgevolg met uitzondering van artikel 1 waarvan de duurtijd eveneens verder loopt tot en met 31 augustus 2027. Art. 9. De ondertekenende partijen vragen dat deze collectieve arbeidsovereenkomst algemeen verbindend zou verklaard worden per koninklijk besluit. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
+</t>
         </is>
       </c>
     </row>
@@ -3191,28 +3185,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2025003968</t>
+          <t>2025201255</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>28 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>9 april 2024. - Koninklijk besluit betreffende de berekeningsmethode van de elementen van de minimumvergoeding voor pakjesbezorgers. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 15 januari 2025, gesloten in het Paritair Comité voor de stoffering en de houtbewerking, betreffende het sectoraal georganiseerd outplacement (arbeiders) (1)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-28&amp;numac_search=2025003968&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003968=86&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025201255&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201255=86&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 9 april 2024 betreffende de berekeningsmethode van de elementen van de minimumvergoeding voor pakjesbezorgers (Belgisch Staatsblad van 23 april 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST WIRTSCHAFT, KMB, MITTELSTAND UND ENERGIE9. APRIL 2024 - Königlicher Erlass zur Festlegung der Methode zur Berechnung der Bestandteile der Mindestvergütung für PaketzustellerPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund der Artikel 10/1 § 1 Absatz 3 und 22 § 8 Absatz 2 des Gesetzes vom 26. Januar 2018 über die Postdienste, eingefügt durch das Gesetz vom 17. Dezember 2023;Aufgrund der Auswirkungsanalyse beim Erlass von Vorschriften, die gemäß den Artikeln 6 und 7 des Gesetzes vom 15. Dezember 2013 zur Festlegung verschiedener Bestimmungen in Sachen administrative Vereinfachung durchgeführt worden ist;Aufgrund der Stellungnahme des Finanzinspektors vom 28. Oktober 2023;Aufgrund des Einverständnisses der Staatssekretärin für Haushalt vom 13. November 2023;Aufgrund des Gutachtens 74.984/4 des Staatsrates vom 22. Januar 2024, abgegeben in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Auf Vorschlag des Ministers der Wirtschaft, des Ministers der Selbständigen und der Ministerin der Post und aufgrund der Stellungnahme der Minister, die im Rat darüber beraten haben,Haben Wir beschloßen und erlassen Wir:Artikel 1 - Für die Anwendung des vorliegenden Erlasses versteht man unter:a) "Gesetz": das Gesetz vom 26. Januar 2018 über die Postdienste,b) "FÖD Wirtschaft": den Föderalen Öffentlichen Dienst Wirtschaft, KMB, Mittelstand und Energie,c) "Institut": das in Artikel 13 des Gesetzes vom 17. Januar 2003 über das Statut der Regulierungsinstanz des belgischen Post- und Telekommunikationssektors erwähnte Belgische Institut für Post- und Fernmeldewesen.Art. 2 - Die Mindestvergütung für Dienstleistungserbringer mit Fahrrad gilt für Dienstleistungserbringer, die ein Verkehrsmittel benutzen, für das kein Führerschein erforderlich ist oder für das ein Führerschein der Klasse AM, A, A1 oder A2 erforderlich ist.Die Mindestvergütung für Dienstleistungserbringer mit Motorfahrzeug gilt für Dienstleistungserbringer, die ein Transportmittel verwenden, für das ein Führerschein der Klasse B oder höher erforderlich ist.Art. 3 - § 1 - Zusätzlich zu den in Artikel 10/1 § 1 Absatz 2 des Gesetzes erwähnten Bestandteilen umfasst die Mindestvergütung:a) die Anzahl gefahrener Kilometer,b) die Anzahl geleisteter Stunden. § 2 - In Artikel 10/1 § 1 Absatz 2 Nr. 2 Buchstabe a) und Nr. 3 des Gesetzes erwähnte Transportkosten eines Dienstleistungserbringers mit Fahrrad umfassen:a) Abschreibung,b) Wartung,c) Versicherung,d) durchschnittliche Energiekosten in den sechs Monaten vor dem Monat der Veröffentlichung des in § 4 erwähnten Ministeriellen Erlasses,e) allgemeine Kosten. § 3 - In Artikel 10/1 § 1 Absatz 2 Nr. 2 Buchstabe b) und Nr. 3 des Gesetzes erwähnte Transportkosten eines Dienstleistungserbringers mit Motorfahrzeug umfassen:a) Abschreibung,b) Wartung,c) Versicherung,d) Reifenkosten,e) Kosten der technischen Kontrolle,f) Verkehrssteuer,g) durchschnittliche Kraftstoffkosten in den sechs Monaten vor dem Monat der Veröffentlichung des in § 4 erwähnten Ministeriellen Erlasses,h) allgemeine Kosten. § 4 - Der für Wirtschaft zuständige Minister legt den Zahlenwert jedes der in den Paragraphen 1, 2 und 3 aufgeführten Bestandteile ohne Mehrwertsteuer und den in Artikel 10/1 § 1 Absatz 2 Nr. 1 des Gesetzes erwähnten Betrag des Mindeststundenlohns fest. § 5 - Die Kosten der in den Paragraphen 2 und 3 erwähnten Bestandteile sind an den Betrag des abgeflachten Gesundheitsindexes für den Monat November 2023 gebunden, mit Ausnahme:a) der in § 2 Buchstabe d) erwähnten Energiekosten, die an den durchschnittlichen Verbraucherpreisindex für Strom während der sechs Monate vor dem Monat der Veröffentlichung des vorliegenden Erlasses gebunden sind,b) der in § 3 Buchstabe g) erwähnten Kraftstoffkosten, die an den durchschnittlichen Verbraucherpreisindex für Dieselkraftstoff während der sechs Monate vor dem Monat der Veröffentlichung des vorliegenden Erlasses gebunden sind. § 6 - Die Kosten der in den Paragraphen 2 und 3 erwähnten Bestandteile werden jährlich am 1. Januar an den abgeflachten Gesundheitsindex für den Monat November des Vorjahres angepasst.In Abweichung von Absatz 1 werden halbjährlich, am 1. Januar und am 1. Juli, angepasst:a) die in § 2 Buchstabe d) erwähnten Energiekosten, entsprechend dem durchschnittlichen Verbraucherpreisindex für Strom während der sechs Monate vor dem Monat der Veröffentlichung des in § 4 erwähnten Ministeriellen Erlasses,b) die in § 3 Buchstabe g) erwähnten Kraftstoffkosten, entsprechend dem durchschnittlichen Verbraucherpreisindex für Dieselkraftstoff während der sechs Monate vor dem Monat der Veröffentlichung des in § 4 erwähnten Ministeriellen Erlasses.In Abweichung von den Absätzen 1 und 2 kann der für Wirtschaft zuständige Minister den Zeitplan für die Indexierung aus den von ihm angegebenen Gründen ändern.Art. 4 - Der für Wirtschaft zuständige Minister legt die Methode zur Berechnung der Mindestvergütung und der verschiedenen Bestandteile, aus denen diese sich zusammensetzt, fest. Er veröffentlicht den Betrag der Mindestvergütung im Belgischen Staatsblatt.Über seine Website veröffentlicht der FÖD Wirtschaft auch den Betrag der Mindestvergütung und stellt allen Unternehmen ein Erläuterungsschreiben der Methode zur Berechnung der Mindestvergütung zur Verfügung, die gemäß Absatz 1 festgelegt wird.Art. 5 - § 1 - Alle drei Jahre werden in Zusammenarbeit mit dem Institut Umfragen bei den Unternehmen der Branche durchgeführt, um die Relevanz der Parameter für die Berechnung der Mindestvergütung zu evaluieren. § 2 - Der für Wirtschaft zuständige Minister legt fest, welche Daten abgefragt werden und nach welchen praktischen Modalitäten die Unternehmen der Branche an den Umfragen teilnehmen. Das Institut ist mit der Erhebung der erforderlichen Informationen bei den Unternehmen beauftragt. § 3 - Alle Föderalverwaltungen und alle Dienste oder Einrichtungen öffentlichen Interesses müssen bei der Durchführung der in § 1 erwähnten Umfragen unentgeltlich ihre Mitwirkung gewähren. Sie gewähren dem FÖD Wirtschaft kostenlosen Zugriff auf vertrauliche Informationen, von denen sie für die Ausübung ihrer Funktion Kenntnis haben, soweit diese Mitteilung für die Erfüllung seiner Aufträge notwendig ist.Art. 6 - Treten am 1. Juli 2024 in Kraft:a) Artikel 14 des Gesetzes vom 17. Dezember 2023 zur Festlegung verschiedener Bestimmungen zur Verbesserung der Arbeitsbedingungen von Paketzustellern,b) vorliegender Erlass.Art. 7 - Der für Wirtschaft zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 9. April 2024PHILIPPEVon Königs wegen:Der Minister der WirtschaftP.-Y. DERMAGNEDer Minister der SelbständigenD. CLARINVALDie Ministerin der PostP. DE SUTTER 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de stoffering en de houtbewerking; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 15 januari 2025, gesloten in het Paritair Comité voor de stoffering en de houtbewerking, betreffende het sectoraal georganiseerd outplacement (arbeiders). Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de stoffering en de houtbewerking Collectieve arbeidsovereenkomst van 15 januari 2025 Sectoraal georganiseerd outplacement (arbeiders) (Overeenkomst geregistreerd op 10 februari 2025 onder het nummer 191994/CO/126) Artikel 1. Toepassingsgebied en doel Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de werknemers tewerkgesteld in de ondernemingen die ressorteren onder het Paritair Comité voor de stoffering en de houtbewerking. Waar sprake is van "werknemers" worden steeds de arbeiders en de arbeidsters bedoeld. Deze collectieve arbeidsovereenkomst wordt gesloten in uitvoering van de wet van 5 september 2001 tot verbetering van de werkgelegenheidsgraad van de werknemers, hoofdstuk V, afdelingen 1 en 2, en van de collectieve arbeidsovereenkomst nr. 82, gesloten op 10 juli 2002 in de schoot van de Nationale Arbeidsraad. Deze collectieve arbeidsovereenkomst heeft tot doel aan bepaalde categorieën van werknemers die werden ontslagen, het recht te verlenen op een sectorale outplacementbegeleiding. Art. 2.  Toegang tot het sectoraal georganiseerd outplacement  § 1. Outplacement in de algemene regeling, conform afdeling 1 van hoofdstuk V van de wet van 5 september 2001 tot verbetering van de werkgelegenheidsgraad van de werknemers De werknemer van wie de arbeidsovereenkomst door de werkgever wordt beëindigd door middel van een opzeggingstermijn van minstens 30 weken of een vergoeding die gelijk is aan het lopend loon dat overeenstemt hetzij met de duur van een opzeggingstermijn van minstens 30 weken, hetzij met het resterende gedeelte van die termijn, heeft recht op outplacement.  § 2. Outplacement in de bijzondere regeling, conform afdeling 2 van hoofdstuk V van de wet van 5 september 2001 tot verbetering van de werkgelegenheidsgraad van de werknemers De werknemer die niet voldoet aan de voorwaarden van het outplacement in de algemene regeling ( § 1) heeft recht op outplacement, mits gelijktijdig voldaan is aan de volgende voorwaarden : - hij is niet ontslagen om dringende redenen; - op het ogenblik van het ontslag is hij minstens 45 jaar; - op het ogenblik van het ontslag heeft hij ten minste één jaar ononderbroken dienstanciënniteit bij de werkgever die ontslaat. Dit recht op outplacement wordt in de sector als volgt versoepeld : - hij is niet ontslagen om dringende redenen; - op het ogenblik van het ontslag is hij minstens 40 jaar; - op het ogenblik van het ontslag heeft hij ten minste 5 jaar ononderbroken dienstanciënniteit bij de werkgever die ontslaat.  § 3. Herstructurering, sluiting of faillissement Het sectoraal georganiseerd outplacement is, voor de werknemers die vallen onder § 1 of § 2, ook van toepassing in het geval van herstructurering, sluiting of faillissement. Het recht op een sectorale outplacementbegeleiding kan in dit geval, worden uitgebreid tot andere werknemers dan deze gevat door § 1 of § 2, op voorwaarde dat outplacementbegeleiding het voorwerp heeft uitgemaakt van een akkoord op ondernemingsvlak in het raam van een herstructurering of bij sluiting of faillissement van een onderneming. Voor deze uitbreiding is de goedkeuring vereist van het beheerscomité van het fonds voor bestaanszekerheid, op vraag van de partijen betrokken bij de opmaak van het herstructureringsplan. De eerste opvang en begeleiding van de werknemers betrokken bij een herstructurering, sluiting of faillissement gebeuren in de tewerkstellingscellen die daartoe worden opgericht. Woodwize duidt ook het outplacementbureau aan conform artikel 7 van deze collectieve arbeidsovereenkomst. In dit kader worden tussen Woodwize en de gewestelijke overheden de nodige samenwerkingsovereenkomsten gesloten. Art. 3.  Procedure Voor de onder artikel 2, § 1 en § 2 vermelde vormen van outplacement volstaat het dat de werkgever aan de werknemer meldt dat hij recht heeft op het sectoraal georganiseerd outplacement, en dat hij zich daarvoor dient te richten tot Woodwize, het opleidingscentrum van de houtsector. De werkgever dient de contactgegevens van Woodwize aan de betrokken werknemer te bezorgen, evenals de manier waarop en de timing waarbinnen hij contact met Woodwize dient op te nemen. De volgende standaardzin kan daartoe in de ontslagbrief worden opgenomen : Wij melden u dat u recht heeft op outplacement en dat u daarvoor gebruik kan maken van het sectorale aanbod. U dient zich daarvoor te richten tot : Woodwize vzw, Hof ter Vleestdreef 3 1070 Brussel Tel. 02 558 15 51 info@woodwize.be U heeft er in dit kader alle belang bij zo spoedig mogelijk contact op te nemen met Woodwize. De daarvoor aangestelde consulenten van Woodwize zullen de betrokken werknemer op zijn vraag verder begeleiden en hem in contact brengen met één van de erkende outplacementkantoren waarmee de sector samenwerkt. Voor het collectief outplacement in geval van herstructurering (artikel 2, § 3) wordt de aanvraag en de uitvoering van het outplacementproject gecentraliseerd in uitvoering van het herstructureringsplan.Art. 4.  Inhoud van de outplacementbegeleiding De ontslagen werknemer heeft recht op een outplacementbegeleiding in drie fasen. De eerste fase (een termijn van 2 maanden ten belope van in het totaal 20 uur begeleiding) houdt in : - Kennismaking en psychologische begeleiding voor het verwerken van het ontslag en het opmaken van een balans voor de werknemer; - Sollicitatietraining en het geven van hulp bij het zoeken naar een nieuwe dienstbetrekking; - Opvolging en ondersteuning bij sollicitaties. Indien de werknemer binnen de eerste fase geen betrekking heeft gevonden of geen zelfstandige activiteit heeft aangevat, wordt de begeleiding voortgezet gedurende een tweede fase (de daaropvolgende termijn van vier maanden) ten belope van in het totaal 20 uur. Indien de werknemer op het einde van de tweede fase geen nieuwe betrekking heeft gevonden of geen zelfstandige activiteit heeft aangevat, wordt de begeleiding voortgezet gedurende een derde fase (de daaropvolgende termijn van 6 maanden), opnieuw ten belope van in het totaal 20 uur. Wanneer de outplacementbegeleiding plaatsheeft tijdens de opzeggingstermijn, worden de begeleidingsuren aangerekend op de tijd dat de werknemer op grond van artikel 41 van de wet van 3 juli 1978 op de arbeidsovereenkomsten afwezig mag zijn om een nieuwe betrekking te zoeken. Art. 5.  Engagementen van de werknemer die een beroep doet op outplacement Om recht te hebben op de outplacementbegeleiding verbindt de ontslagen werknemer zich ertoe, zich bij de VDAB, Actiris of Forem in te schrijven als werkzoekende en hiervan het bewijs te leveren. Om in fase 2 en 3 recht te hebben op verdere opvolging en begeleiding, verbindt de ontslagen werknemer zich ertoe te goeder trouw mee te werken aan de begeleiding en de aangeboden opleidingen te volgen. Zodra de werknemer zonder voldoende rechtvaardiging afwezig is, vervalt het recht op verdere ontslagbegeleiding van de sector. De begeleiding wordt eveneens stopgezet zodra de werknemer een nieuwe betrekking in loondienst of als zelfstandige heeft gevonden. Wanneer de werknemer een nieuwe betrekking heeft gevonden, doch die verliest binnen drie maanden na de indiensttreding, kan op zijn verzoek de outplacementbegeleiding worden hervat in de fase waarin ze was onderbroken. Art. 6.  Engagement van de werkgever De werkgever dient de ontslagen werknemer te informeren over diens recht op het sectoraal outplacement en zal hem de nodige gegevens daartoe mededelen, zoals omschreven in artikel 3. Art. 7.  Organisatie Woodwize vzw is aangesteld om de coördinatie van het sectoraal georganiseerd outplacement te verzorgen. Het doet daarvoor een beroep op erkende outplacementkantoren die door het fonds voor bestaanszekerheid worden aangesteld. Het paritair beheerscomité van het fonds voor bestaanszekerheid bevraagt daartoe om de 2 jaar de outplacementkantoren die hun interesse tot (vernieuwing van) samenwerking hebben laten blijken. Deze bevraging resulteert in samenwerkingsovereenkomsten voor een bepaalde duur van 2 jaar, met maximaal 6 outplacementkantoren. Het beheerscomité beslist tot samenwerking op basis van het dossier dat daartoe door de outplacementkantoren wordt ingediend, en desgevallend op basis van een rapportering door Woodwize vzw over de voorbije samenwerkingsperiode. Samenwerking is enkel mogelijk met outplacementkantoren die door de gewesten zijn erkend en die de verbintenissen naleven die hen krachtens de wetgeving en de collectieve arbeidsovereenkomst nr. 82 worden opgelegd. Eenmaal per jaar zal de evaluatie van het sectoraal outplacement op de agenda van het paritair comité worden gebracht. Art. 8.  Financiering De kosten aangerekend door de outplacementkantoren worden ten laste genomen door het fonds voor bestaanszekerheid, en aangerekend op zijn balansprovisie "vormingsactiviteiten".Indien de werkgever bij toepassing van artikel 81 van de wet van 26 december 2013 de vermindering van 4 weken loon toepast op de verbrekingsvergoeding, en voor het outplacement een beroep doet op artikel 2, § 1 van deze collectieve arbeidsovereenkomst, is hij hiervoor een vergoeding ten belope van 4 weken loon verschuldigd. Deze bijdrage wordt geïnd door het fonds voor bestaanszekerheid, waar ze zal worden toegevoegd aan de balansprovisie "vormingsactiviteiten". Tussen Woodwize en het fonds zullen voor het innen van deze bijdrage de nodige afspraken worden gemaakt. In geval van versoepeling van de voorwaarden tot outplacement, zoals mogelijk op basis van artikel 2, § 3, kan een evenredige inspanning van de werkgever worden gevraagd, te bepalen door het beheerscomité van het fonds voor bestaanszekerheid. In voorkomend geval wordt ook deze bijdrage toegevoegd aan de balansprovisie "vormingsactiviteiten" van het fonds voor bestaanszekerheid. Waar mogelijk zal een beroep worden gedaan op de publieke middelen die voor herplaatsing en outplacement ter beschikking worden gesteld, zo bijvoorbeeld via het Sociaal Interventiefonds bij de VDAB, voor ontslagen ten gevolge van een faillissement. Art. 9.  Conformiteit met de wetgeving en de collectieve arbeidsovereenkomst nr. 82 De ondertekenaars van deze overeenkomst verklaren dat de werkgevers die een beroep doen op het sectoraal georganiseerd outplacement, voldoen aan de wettelijke en conventionele verplichtingen ten aanzien van de doelgroep zoals omschreven in artikel 1 en 2. Ten aanzien van artikel 11/5, § 1 van de wet van 5 september 2001 verklaren de sectorale sociale partners dat de waarde van het sectoraal aangeboden outplacement overeenstemt met minstens 1/12de van het jaarloon van het kalenderjaar dat het ontslag voorafgaat. Toekenning van deze outplacementbegeleiding doet geen afbreuk aan de bepalingen van de wet op de arbeidsovereenkomsten in verband met het ontslag noch aan de aanvullende voordelen die door de andere sectorale collectieve arbeidsovereenkomsten worden verleend. Art. 10. Duur van de overeenkomst Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025 en houdt op van kracht te zijn op 31 december 2025. Art. 11. De ondertekenende partijen vragen dat deze collectieve arbeidsovereenkomst algemeen verbindend zou verklaard worden per koninklijk besluit. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -3223,29 +3217,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2025003692</t>
+          <t>2025003012</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>16 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>17 maart 2024. - Koninklijk besluit tot uitvoering van het hoofdstuk 2 van de wet van 29 november 2022 houdende diverse bepalingen inzake gezondheidszorg, wat betreft de toepassing van het verbod op ereloonsupplementen voor geneeskundige verzorging verleend door tandheelkundigen aan rechthebbenden op de verhoogde verzekeringstegemoetkoming. - Erratum</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 11 december 2024, gesloten in het Paritair Subcomité voor de beschutte werkplaatsen van het Waalse Gewest en van de Duitstalige Gemeenschap, betreffende de vaststelling van de minimumlooncategorieën voor het productiepersoneel in de Waalse beschutte werkplaatsen (1)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-16&amp;numac_search=2025003692&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003692=87&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025003012&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003012=87&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
           <t xml:space="preserve">
-In het Belgisch Staatsblad nr. 65 van 22 maart 2024 (Ed. 1), boven de tabel op pagina 35209, wordt de titel "Annexe : Liste des prestations pour lesquelles en exécution de l'article 2, l'interdiction des suppléments pour les bénéficiaires de l'intervention majorée entre en vigueur le 1er janvier 2025 :" toegevoegd ; 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Subcomité voor de beschutte werkplaatsen van het Waalse Gewest en van de Duitstalige Gemeenschap;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 11 december 2024, gesloten in het Paritair Subcomité voor de beschutte werkplaatsen van het Waalse Gewest en van de Duitstalige Gemeenschap, betreffende de vaststelling van de minimumlooncategorieën voor het productiepersoneel in de Waalse beschutte werkplaatsen.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 7 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Subcomité voor de beschutte werkplaatsen van het Waalse Gewest en van de Duitstalige GemeenschapCollectieve arbeidsovereenkomst van 11 december 2024Vaststelling van de minimumlooncategorieën voor het productiepersoneel in de Waalse beschutte werkplaatsen (Overeenkomst geregistreerd op 14 februari 2025 onder het nummer 192050/CO/327.03)Vervanging van de collectieve arbeidsovereenkomst van 29 maart 2010 (nr. 99420/CO/327.03) betreffende de vaststelling van de minimumlooncategorieën voor het productiepersoneel in de beschutte werkplaatsen die worden gesubsidieerd door het Waalse Gewest.HOOFDSTUK I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is uitsluitend van toepassing op de werkgevers en op de werknemers van de beschutte werkplaatsen (BW) die worden gesubsidieerd door het Waalse Gewest en die ressorteren onder het Paritair Subcomité voor de beschutte werkplaatsen van het Waalse Gewest en van de Duitstalige Gemeenschap, met uitzondering van de beschutte werkplaatsen die gevestigd zijn in de Duitstalige Gemeenschap.Onder "werknemers" wordt verstaan : de mannelijke en vrouwelijke, invalide en valide, productiewerknemers.Onder "productiepersoneel" worden de werknemers verstaan die worden beoogd door de bepalingen van de collectieve arbeidsovereenkomst van 29 maart 2010 betreffende het herstel van de loonspanning van het productiepersoneel in de beschutte werkplaatsen en niet die welke worden beoogd door de collectieve arbeidsovereenkomst van 24 januari 2007 betreffende de harmonisering van de loonschalen voor het kaderpersoneel tewerkgesteld in de beschutte werkplaatsen die gevestigd zijn in het Waalse Gewest.Deze collectieve arbeidsovereenkomst is van toepassing op de werknemers die tewerkgesteld zijn op 1 december 2024 en op de werknemers die worden in dienst genomen vanaf 1 december 2024.Art. 2. Voor de terugwerkende kracht van deze maatregel tot 1 januari 2024 is deze collectieve arbeidsovereenkomst van toepassing op de werknemers tewerkgesteld op 1 december 2024 en op de werknemers in SWT en gepensioneerd vanaf 1 januari 2024.HOOFDSTUK II. - Algemene bepalingenArt. 3. Deze collectieve arbeidsovereenkomst heeft als doel om een evolutierooster vast te stellen van de minimumlonen van de zeven looncategorieën die bepaald zijn voor de productiewerknemers.Zo zullen de uurlonen van de minimumroosters worden verhoogd volgens de anciënniteit ten belope van 0,13 EUR bruto per 5 jaar sectorale anciënniteit tot 25 jaar anciënniteit (ofwel 0,13 EUR/5 jaar, 0,26 EUR/10 jaar, 0,39 EUR/15 jaar, 0,52 EUR/20 jaar, 0,65 EUR/25 jaar).Art. 4. Onder "erkende sectorale anciënniteit" wordt verstaan : de jaarlijkse anciënniteit die werd verworven per voltooid jaar in de ondernemingen die ressorteren onder Paritair Subcomité voor de beschutte werkplaatsen van het Waalse Gewest en van de Duitstalige Gemeenschap, met uitsluiting van de stageovereenkomsten.Onder "bedrijfsanciënniteit" wordt verstaan : de onderbroken tewerkstellingsperiodes binnen eenzelfde BW. Deze worden gecumuleerd om de anciënniteit van de werknemer te bepalen.De toepassing van de uurlonen van de minimumroosters wordt gekoppeld aan de verjaardag van de indiensttreding van de werknemer in de onderneming en wordt toegepast op de 1ste dag van de maand die volgt op de maand van de verjaardag.Art. 5. Twee evolutieroosters worden als bijlage bij deze collectieve arbeidsovereenkomst gevoegd, het ene tot vaststelling van de minimumuurlonen op 1 januari 2024, het andere tot vaststelling van de minimumuurlonen vanaf 1 mei 2024 na indexering.Art. 6. Deze nieuwe minima worden gerealiseerd in het kader van het Waalse non-profit akkoord 2021-2024 overeenkomstig het protocolakkoord van 30 juni 2021. Zij worden dus niet in aanmerking genomen in het kader van de loonnorm.Art. 7. Voor de BW die al hebben geanticipeerd op de maatregelen en/of al een evolutierooster van de loonschalen hebben dat gekoppeld is aan de gelijke of hogere anciënniteit vermeld in een collectieve ondernemingsovereenkomst of in het arbeidsreglement of een lokaal protocolakkoord of elke andere vorm van lokaal akkoord, zal lokaal worden onderhandeld in plaats van deze collectieve arbeidsovereenkomst toe te passen.Het zal aan de partijen op lokaal niveau toekomen om de nodige maatregelen te nemen om aan de betrokken werknemers een gelijkwaardig voordeel toe te kennen.In geval van betwisting zal een beroep worden gedaan op een verzoeningsbureau.HOOFDSTUK III. - SlotbepalingenArt. 8. Alle lonen die zijn vastgelegd in deze collectieve arbeidsovereenkomst zijn gekoppeld aan het indexcijfer van de consumptieprijzen van het Koninkrijk, overeenkomstig de toepassing van de collectieve arbeidsovereenkomst van 30 mei 2002 betreffende de koppeling van de lonen aan het indexcijfer van de consumptieprijzen.Art. 9. De doelstelling is dat de lonen van de werknemers worden verhoogd door de maatregel op de loonfiches van de maand januari 2025.De terugwerkende kracht van de maatregel zal uiterlijk 2 maanden na de effectieve ontvangst van de bedragen gestort door het AViQ moeten worden toegepast voor de betrokken werknemers.Art. 10. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2024.Ze wordt gesloten voor onbepaalde duur. Ze kan door elke partij worden opgezegd met een opzeggingstermijn van drie maanden die met een ter post aangetekend schrijven (poststempel geldt als bewijs) wordt gericht tot de voorzitter van het Paritair Subcomité voor de beschutte werkplaatsen van het Waalse Gewest en van de Duitstalige Gemeenschap.Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025.De Minister van Werk,D. CLARINVALBijlage 1 aan de collectieve arbeidsovereenkomst van 11 december 2024, gesloten in het Paritair Subcomité voor de beschutte werkplaatsen van het Waalse Gewest en van de Duitstalige Gemeenschap, betreffende de vaststelling van de minimumlooncategorieën voor het productiepersoneel in de Waalse beschutte werkplaatsenHistoriekHerwaardering van 1 juni 2001, indexering van 1 februari 2002, verhoging betreffende het herstel van de loonspanning van 1 januari 2003, indexering van 1 juni 2003, verhoging betreffende het herstel van de loonspanning van 1 januari 2004, indexering van 1 oktober 2004, verhoging met 0,25 pct. van 1 juli 2005, indexering van 1 augustus 2005, indexering van 1 oktober 2006, verhoging ingevolge het interprofessioneel akkoord (IPA) voor de periode 2007-2008 (enkel voor de categorie 5) van 1 april 2007, verhoging met 1 pct. enkel voor de categorieën 1 tot 4 ingevolge het sectoraal akkoord 2007-2008 van 1 juli 2007, indexering op 1 januari 2008, indexering op 1 mei 2008 en indexering op 1 september 2008, herwaardering van het minimummaandloon van de 5de categorie (GGMMI) van het productiepersoneel verhoogd met 25 EUR vanaf 1 oktober, categorie (GGMMI) van het productiepersoneel verhoogd met 25 EUR vanaf 1 oktober 2008; nieuwe functieclassificatie op 1 januari 2010, indexering op 1 september 2010, verhoging functieclassificatie op 1 januari 2011, indexering op 1 mei 2011, verhoging - classificatie op 1 juli 2011, indexeringen op 1 februari 2012, op 1 december 2012, op 1 juni 2016, op 1 juni 2017, verhoging op 1 juli 2017, indexering op 1 september 2018, verhoging ingevolge het interprofessioneel akkoord (IPA) voor de periode 2019-2020, indexeringen : 1 maart 2020, op 1 september 2021, verhoging ingevolge het non-profitakkoord (NPA) voor de periode 2021-2024, indexeringen : op 1 januari 2022, op 1 maart 2022, op 1 mei 2022, op 1 augustus 2022, op 1 november 2022, op 1 december 2022, op 1 november 2023, herwaardering van 13 c. op 1 januari 2024 per schijf van 5 jaar anciënniteit (NPA 2021-2024)  </t>
         </is>
       </c>
     </row>
@@ -3255,28 +3248,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2025003950</t>
+          <t>2025201183</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>28 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>3 maart 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 24 december 1987 betreffende de koopvernietigende gebreken bij verkoop of ruiling van huisdieren. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 20 februari 2025, gesloten in het Paritair Comité voor het vervoer en de logistiek, betreffende de digitalisering van het dagelijks prestatieblad voor werklieden en werksters tewerkgesteld door werkgevers behorend tot het Paritair Subcomité voor de verhuizing (1)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-28&amp;numac_search=2025003950&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003950=88&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025201183&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201183=88&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 3 maart 2024 tot wijziging van het koninklijk besluit van 24 december 1987 betreffende de koopvernietigende gebreken bij verkoop of ruiling van huisdieren (Belgisch Staatsblad van 22 maart 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST VOLKSGESUNDHEIT, SICHERHEIT DER NAHRUNGSMITTELKETTE UND UMWELT3. MÄRZ 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 24. Dezember 1987 über Wandlungsmängel bei Verkauf oder Tausch von HaustierenPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des Gesetzes vom 25. August 1885 zur Revision der Rechtsvorschriften über Wandlungsmängel, der Artikel 1 und 2;Aufgrund des Königlichen Erlasses vom 24. Dezember 1987 über Wandlungsmängel bei Verkauf oder Tausch von Haustieren;Aufgrund der Stellungnahme des Rates des Haushaltsfonds für Gesundheit und Qualität der Tiere und tierischen Erzeugnisse vom 31. August 2023;Aufgrund der Konzertierung zwischen den Regionalregierungen und der Föderalbehörde vom 20. Juli 2023;Aufgrund der Stellungnahme des Finanzinspektors vom 9. November 2023;Aufgrund des Antrags auf Begutachtung binnen einer Frist von dreißig Tagen, der in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat beim Staatsrat eingereicht worden ist;In der Erwägung, dass der Antrag auf Begutachtung am 12. Februar 2024 unter der Nummer 75.633/3 in die Liste der Gesetzgebungsabteilung des Staatsrates eingetragen worden ist;Aufgrund des Beschlusses der Gesetzgebungsabteilung vom 14. Februar 2024 in Anwendung von Artikel 84 § 5 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat, binnen der gesetzten Frist kein Gutachten abzugeben;Auf Vorschlag des Ministers der LandwirtschaftHaben Wir beschloßen und erlassen Wir:Artikel 1 - In Artikel 1 des Königlichen Erlasses vom 24. Dezember 1987 über Wandlungsmängel bei Verkauf oder Tausch von Haustieren wird Nr. 2, abgeändert durch den Königlichen Erlass vom 1. Februar 2012, durch eine Bestimmung mit folgendem Wortlaut ergänzt:"- Rind mit nichtnegativem Ergebnis bei einem ELISA-Test zur Diagnose der Besnoitiose,".Art. 2 - In Artikel 6 desselben Erlasses, abgeändert durch die Königlichen Erlasse vom 1. Februar 2012 und 19. Juli 2019 werden zwischen dem Wort "bei" und den Wörtern "mit BHV1 infizierten Rindern" die Wörter "Rindern mit nichtnegativem Ergebnis bei einem ELISA-Test zur Diagnose der Besnoitiose," eingefügt.Art. 3 - Der für Landwirtschaft zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 3. März 2024PHILIPPEVon Königs wegen:Der Minister der LandwirtschaftD. CLARINVAL 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet. Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het vervoer en de logistiek; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 20 februari 2025, gesloten in het Paritair Comité voor het vervoer en de logistiek, betreffende de digitalisering van het dagelijks prestatieblad voor werklieden en werksters tewerkgesteld door werkgevers behorend tot het Paritair Subcomité voor de verhuizing. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor het vervoer en de logistiek Collectieve arbeidsovereenkomst van 20 februari 2025 Digitalisering van het dagelijks prestatieblad voor werklieden en werksters tewerkgesteld door werkgevers behorend tot het Paritair Subcomité voor de verhuizing (Overeenkomst geregistreerd op 13 maart 2025 onder het nummer 192559/CO/140) HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing : 1) op de werkgevers die ressorteren onder het Paritair Comité voor het vervoer en de logistiek en die behoren tot het Paritair Subcomité voor de verhuizing; 2) op de werklieden en werksters die worden tewerkgesteld door de in 1) bedoelde werkgevers. HOOFDSTUK II. - Wettelijk kader Art. 2. Deze collectieve arbeidsovereenkomst wordt afgesloten in uitvoering van het sectoraal protocolakkoord van 27 september 2023. HOOFDSTUK III. - Digitalisering van het dagelijks prestatieblad Art. 3.  Principe De digitalisering en automatisering van gegevensstromen hebben tot resultaat dat steeds meer werknemers en werkgevers ervoor opteren om de loonbrief digitaal te laten bezorgen. Deze collectieve arbeidsovereenkomst heeft tot doel de werknemer de mogelijkheid te bieden ook het verplichte dagelijkse prestatieblad digitaal te ontvangen.Art. 4.  Keuzerecht Werkgevers die gebruik wensen te maken van het digitaal dagelijks prestatieblad, moeten bij de werknemers die in dienst zijn van de onderneming en/of in dienst treden van de onderneming, het mailadres en/of het digitaal platform opvragen waarlangs het digitaal dagelijks prestatieblad kan bezorgd worden. Iedere werknemer kan er evenwel voor kiezen om geen gebruik te maken van het digitaal dagelijks prestatieblad en kan verzoeken om de verdere fysieke aflevering van het dagelijks prestatieblad. Art. 5.  Voorwaarden  § 1. De inhoud van het digitaal prestatieblad moet voldoen aan de bepalingen van artikel 10 van de collectieve arbeidsovereenkomst van 13 juni 2005 betreffende de arbeidsduur in de subsector voor verhuisondernemingen, meubelbewaring en hun aanverwante activiteiten (registratienummer 75752/CO/140).  § 2. Het digitaal prestatieblad moet door de werkgever of zijn aangestelde uiterlijk bij de aflevering van de loonbrief over dezelfde periode, bezorgd worden.  § 3. Het digitaal prestatieblad wordt aan de werknemer bezorgd via een platform dat minstens aan onderstaande voorwaarden voldoet : - de werknemer ontvangt een melding wanneer een nieuw digitaal prestatieblad beschikbaar is; - de identificatie van de werknemer verloopt via een sluitend systeem, waarbij de inloggegevens op een unieke manier aan de werknemer gekoppeld zijn; - het systeem voorziet voor de werknemer een eenvoudige maar sluitende ondertekeningswijze. De plaatsing van het document op het digitaal platform door de werkgever geldt als ondertekening door de werkgever; - het systeem voorziet eveneens voor werkgever en werknemer de mogelijkheid om opmerkingen te formuleren. Hiervoor dient voldoende plaats te worden voorbehouden; - het voorziet tenslotte ook een systeem van herinnering wanneer de werknemer het prestatieblad nog niet binnen de 7 dagen na ontvangst ondertekend heeft.  § 4. Indien het exemplaar getekend is door beide contracterende partijen van de overeenkomst, is iedere betwisting ervan onontvankelijk. Betwistingen zijn slechts toegelaten indien één van de partijen weigert het prestatieblad te ondertekenen. Zonder wettige en nauwkeurige reden mogen werkgevers en werknemers echter niet weigeren het voorgelegde prestatieblad te ondertekenen.  § 5. Het gebruikte platform kan zowel extern als bedrijfseigen zijn. Het platform wordt voor gebruik voorgelegd aan het Paritair Subcomité voor de verhuizing dat zal beslissen of het al dan niet voldoet aan alle voorwaarden die in deze collectieve arbeidsovereenkomst worden opgesomd. De beslissing van het Paritair Subcomité voor de verhuizing zal door de voorzitter van dit subcomité schriftelijk aan de betrokken onderneming worden overgemaakt. Indien het platform echter reeds voor gebruik werd goedgekeurd door het Paritair Subcomité 140.03 voor het wegvervoer en de logistiek voor rekening van derden, moet het niet opnieuw voor goedkeuring worden voorgelegd aan het Paritair Subcomité voor de verhuizing. HOOFDSTUK IV. - Geldigheidsduur Art. 6. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025 en wordt gesloten voor onbepaalde tijd. Zij kan worden opgezegd door elk van de contracterende partijen met een opzeggingstermijn van drie maanden, betekend bij ter post aangetekende brief aan de voorzitter van het Paritair Comité voor het vervoer en de logistiek. De termijn van drie maanden begint te lopen vanaf de datum van verzending van bovengenoemde aangetekende brief. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -3287,28 +3280,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2025003967</t>
+          <t>2025201200</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>28 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>18 februari 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 29 mei 2018 betreffende de bescherming tegen insolventie bij de verkoop van pakketreizen, gekoppelde reisarrangementen en reisdiensten. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 3 maart 2025, gesloten in het Paritair Comité voor het verzekeringswezen, tot aanvulling van de statuten van FOPAS door de invoeging van een luik preventie van psychosociale risico's (1)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-28&amp;numac_search=2025003967&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003967=89&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025201200&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201200=89&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 18 februari 2024 tot wijziging van het koninklijk besluit van 29 mei 2018 betreffende de bescherming tegen insolventie bij de verkoop van pakketreizen, gekoppelde reisarrangementen en reisdiensten (Belgisch Staatsblad van 29 februari 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST WIRTSCHAFT, KMB, MITTELSTAND UND ENERGIE18. FEBRUAR 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 29. Mai 2018 über den Insolvenzschutz beim Verkauf von Pauschalreisen, verbundenen Reiseleistungen und ReiseleistungenPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des Gesetzes vom 21. November 2017 über den Verkauf von Pauschalreisen, verbundenen Reiseleistungen und Reiseleistungen, des Artikels 60 Absatz 2, eingefügt durch das Gesetz vom 5. Juni 2023, und des Artikels 74, ersetzt durch das Gesetz vom 5. Juni 2023;Aufgrund des Königlichen Erlasses vom 29. Mai 2018 über den Insolvenzschutz beim Verkauf von Pauschalreisen, verbundenen Reiseleistungen und Reiseleistungen;Aufgrund des Antrags auf Begutachtung binnen einer Frist von dreißig Tagen, der in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat beim Staatsrat eingereicht worden ist;In der Erwägung, dass der Antrag auf Begutachtung am 11. Dezember 2023 unter der Nummer 75.069/1 in die Liste der Gesetzgebungsabteilung des Staatsrates eingetragen worden ist;Aufgrund des Beschlusses der Gesetzgebungsabteilung vom 12. Dezember 2023 in Anwendung von Artikel 84 § 5 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat, binnen der gesetzten Frist kein Gutachten abzugeben;Auf Vorschlag des Ministers der Wirtschaft, des Ministers der Justiz und der Staatssekretärin für VerbraucherschutzHaben Wir beschloßen und erlassen Wir:Artikel 1 - Artikel 4 des Königlichen Erlasses vom 29. Mai 2018 über den Insolvenzschutz beim Verkauf von Pauschalreisen, verbundenen Reiseleistungen und Reiseleistungen, dessen heutiger Text § 1 bilden wird, wird durch einen Paragraphen 2 mit folgendem Wortlaut ergänzt:" § 2 - Bei Versicherungsnehmern, die ihre Tätigkeit gerade erst aufgenommen haben, müssen die Eigenmittel erst zwölf Monate nach der Gründung ihres Unternehmens mindestens 25.000 EUR betragen, wie in § 1 Nr. 1 vorgeschrieben."Art. 2 - Vorliegender Erlass tritt am 1. Januar 2025 in Kraft.Art. 3 - Die für Wirtschaft beziehungsweise Verbraucherschutz zuständigen Minister sind, jeweils für ihren Bereich, mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 18. Februar 2024PHILIPPEVon Königs wegen:Der Minister der WirtschaftP.-Y. DERMAGNEDer Minister der JustizP. VAN TIGCHELTDie Staatssekretärin für VerbraucherschutzA. BERTRAND 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het verzekeringswezen; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 3 maart 2025, gesloten in het Paritair Comité voor het verzekeringswezen, tot aanvulling van de statuten van FOPAS door de invoeging van een luik preventie van psychosociale risico's. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brusse, le 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. BijlageParitair Comité voor het verzekeringswezen Collectieve arbeidsovereenkomst van 3 maart 2025 Aanvulling van de statuten van FOPAS door de invoeging van een luik preventie van psychosociale risico's (Overeenkomst geregistreerd op 13 maart 2025 onder het nummer 192572/CO/306) Toelichting Deze overeenkomst voegt een derde pijler toe aan de opdrachten van FOPAS als vierde deel bis als een artikel 18bis na artikel 18 van de collectieve arbeidsovereenkomst van 30 juni 2022 tot vaststelling van de statuten van FOPAS (registratienummer 175796/CO/306). Aldus wordt aan FOPAS, naast zijn opdrachten inzake opleiding en beroepsherinschakeling/outplacement, een extra opdracht toevertrouwd : deze betreft preventie/de herinschakeling van langdurig zieken (burn-out,...). Artikel 1. Toepassingsgebied Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de werknemers van de ondernemingen die ressorteren onder het Paritair Comité voor het verzekeringswezen. Art. 2. Financiering FOPAS is belast met de ontvangst van de opbrengst van de responsabiliseringsbijdrage van de werkgevers (bedoeld in de programmawet van 27 december 2021) van de Rijksdienst voor Sociale Zekerheid, en dit overeenkomstig de collectieve arbeidsovereenkomst van 3 maart 2025 betreffende de responsabiliseringsbijdrage van de werkgevers inzake invaliditeit.Art. 3. Voorwerp FOPAS is belast met de uitvoering van de maatregelen waarin de collectieve arbeidsovereenkomst van 3 maart 2025 voorziet, namelijk : - Sensibiliseringsacties inzake psychosociale risico's; - De financiering van pilootprojecten in verband met herinschakeling; - Preventieve informatieprogramma's; - De verspreiding van preventieprogramma's (bijvoorbeeld : FEDRIS,...),... Art. 4. Geldigheidsduur Deze collectieve arbeidsovereenkomst treedt in werking op de dag van ondertekening en wordt voor onbepaalde duur gesloten. Elke ondertekenende partij kan deze collectieve arbeidsovereenkomst opzeggen met inachtneming van een opzeggingstermijn van drie maanden. Die opzegging moet, aangetekend per post, aan de voorzitter van het Paritair Comité voor het verzekeringswezen worden gericht. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -3319,28 +3312,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2025003654</t>
+          <t>2025201187</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>23 mei 2025</t>
+          <t>27 mei 2025</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>24 januari 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 2 oktober 2023 tot wijziging van het koninklijk besluit van 1 december 1975 houdende algemeen reglement op de politie van het wegverkeer en van het gebruik van de openbare weg. - Duitse vertaling</t>
+          <t>7 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 19 februari 2025, gesloten in het Paritair Comité voor het kleding- en confectiebedrijf, tot verlenging van een aantal bepalingen van het akkoord van sociale vrede 2023-2024 (1)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-23&amp;numac_search=2025003654&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003654=90&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025201187&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201187=90&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 24 januari 2024 tot wijziging van het koninklijk besluit van 2 oktober 2023 tot wijziging van het koninklijk besluit van 1 december 1975 houdende algemeen reglement op de politie van het wegverkeer en van het gebruik van de openbare weg (Belgisch Staatsblad van 26 januari 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST MOBILITÄT UND TRANSPORTWESEN24. JANUAR 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 2. Oktober 2023 zur Abänderung des Königlichen Erlasses vom 1. Dezember 1975 zur Festlegung der allgemeinen Ordnung über den Straßenverkehr und die Benutzung der öffentlichen StraßePHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des am 16. März 1968 koordinierten Gesetzes über die Straßenverkehrspolizei, des Artikels 1 Absatz 1;Aufgrund des Königlichen Erlasses vom 2. Oktober 2023 zur Abänderung des Königlichen Erlasses vom 1. Dezember 1975 zur Festlegung der allgemeinen Ordnung über den Straßenverkehr und die Benutzung der öffentlichen Straße;Aufgrund der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat, des Artikels 3 § 1;Aufgrund der Dringlichkeit;In der Erwägung des Inkrafttretens am 1. Februar 2024 von Artikel 3 des Erlasses vom 2. Oktober 2023 zur Abänderung des Königlichen Erlasses vom 1. Dezember 1975 zur Festlegung der allgemeinen Ordnung über den Straßenverkehr und die Benutzung der öffentlichen Straße, in dem bestimmt wird, dass Führer von vorfahrtsberechtigten Fahrzeugen, die einen dringenden Auftrag ausführen und nicht verpflichtet sind, die Straßenverkehrsordnung einzuhalten, von wenigen Ausnahmen abgesehen, die besondere akustische Warnvorrichtung benutzen müssen;In der Erwägung, dass diese Bestimmung von grundlegender Bedeutung ist, um die Sicherheit aller Verkehrsteilnehmer zu gewährleisten;Dass der Einsatz der Schallzeichenanlage die anderen Verkehrsteilnehmer auf ein vorfahrtsberechtigtes Fahrzeug aufmerksam macht, wenn die Benutzung des Blaulichts nicht ausreicht;Dass dies ferner dafür sorgt, dass zum Beispiel ein Fußgänger auf einem Fußgängerüberweg oder ein von rechts kommender Führer erkennen kann, wann das herannahende vorfahrtsberechtigte Fahrzeug von seinem Vorrang Gebrauch machen möchte;Dass bei Nichtbenutzung der Schallzeichenanlage bei anderen Verkehrsteilnehmern Zweifel über die Absichten des Führers eines vorfahrtsberechtigten Fahrzeugs entstehen können; dass diese Zweifel eine reale Unfallquelle darstellen;In der Erwägung, dass die Veröffentlichung dieser neuen Maßnahme jedoch eine Reihe von Fragen bezüglich ihrer praktischen Anwendung unter bestimmten spezifischen Umständen aufgeworfen hat;Dass unter diesen spezifischen Umständen der Einsatz der Schallzeichenanlage Nachteile mit sich bringen kann, die die ordnungsgemäße Durchführung des Auftrags gefährden (Einsatz am Ort eines laufenden Einbruchs) oder eine unverhältnismäßige Lärmbelästigung verursachen können (insbesondere nachts);Dass diese Sonderfälle daher zu berücksichtigen sind, um eine wirksame und verhältnismäßige Anwendung der Vorschrift zu gewährleisten;In der Erwägung, dass es jedoch nicht möglich ist, diese Ausnahmen vor dem ursprünglich vorgesehenen Datum des Inkrafttretens, nämlich dem 1. Februar 2024, festzulegen;Dass das Inkrafttreten der betreffenden Bestimmung an diesem Datum der Rechtssicherheit abträglich wäre und zu operativen Schwierigkeiten für die betreffenden Dienste (Polizei, Feuerwehr, Krankenwagen usw.) führen würde; dass ein Aufschub dieses Inkrafttretens eine Rückkehr zur vorher bestehenden Regelung zur Folge hätte und in der Zwischenzeit Rechtssicherheit gewährleistet wäre;Dass vorliegender Erlass daher dringend und auf jeden Fall spätestens am 1. Februar angenommen werden sollte;Auf Vorschlag des Ministers der MobilitätHaben Wir beschloßen und erlassen Wir:Artikel 1 -  Artikel 7 des Königlichen Erlasses vom 2. Oktober 2023 zur Abänderung des Königlichen Erlasses vom 1. Dezember 1975 zur Festlegung der allgemeinen Ordnung über den Straßenverkehr und die Benutzung der öffentlichen Straße wird durch folgende Bestimmung ersetzt:"Vorliegender Erlass tritt am ersten Tag des Monats nach Ablauf einer Frist von zehn Tagen ab dem Tag nach seiner Veröffentlichung im Belgischen Staatsblatt in Kraft, mit Ausnahme von Artikel 3, der an einem von Uns festzulegenden Datum in Kraft tritt."Art. 2 -  Vorliegender Erlass tritt am 1. Februar 2024 in Kraft.Art. 3 -  Der für den Straßenverkehr zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 24. Januar 2024PHILIPPEVon Königs wegen:Der Minister der MobilitätG. GILKINET 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet. Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor het kleding- en confectiebedrijf; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 19 februari 2025, gesloten in het Paritair Comité voor het kleding- en confectiebedrijf, tot verlenging van een aantal bepalingen van het akkoord van sociale vrede 2023-2024. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 7 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.Bijlage Paritair Comité voor het kleding- en confectiebedrijf Collectieve arbeidsovereenkomst van 19 februari 2025 Verlenging van een aantal bepalingen van het akkoord van sociale vrede 2023-2024 (Overeenkomst geregistreerd op 20 maart 2025 onder het nummer 192667/CO/109) HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de arbeid(st)ers, met inbegrip van de huisarbeid(st)ers, hiernavolgend "werknemers" genoemd, van de ondernemingen welke onder het Paritair Comité voor het kleding- en confectiebedrijf ressorteren. HOOFDSTUK II. - Duur Art. 2. Deze collectieve arbeidsovereenkomst is van toepassing van 1 januari 2025 tot en met 30 juni 2025. HOOFDSTUK III. - Bepalingen Art. 3.  Vlaamse aanmoedigingspremies De sector tekent verder in op het stelsel van de Vlaamse aanmoedigingspremies, bedoeld in hoofdstuk III van het besluit van de Vlaamse Regering van 1 maart 2002. Art. 4.  Flexibiliteit Tijdens de duurtijd van deze collectieve arbeidsovereenkomst wordt er geen sectorale uitbreiding van de flexibiliteitsregelingen voorzien. Op ondernemingsvlak moet constructief overleg kunnen gevoerd worden over maatregelen inzake arbeidsorganisatie die wenselijk zijn voor de onderneming. Dit overleg zal verlopen volgens de wettelijke procedure. Art. 5.  Aanbeveling starterslonen De sociale partners komen overeen om de aanbeveling van 26 juni 2019 betreffende de starterslonen verder te zetten voor de duurtijd van het akkoord. Art. 6.  Sociale vrede Tijdens de duur van deze collectieve arbeidsovereenkomst waarborgen de ondertekenende partijen de inachtneming van de sociale vrede, hetgeen het volgende inhoudt : 1. alle bepalingen betreffende de lonen en arbeidsvoorwaarden worden stipt nageleefd en kunnen niet in betwisting worden gebracht door de werknemers- of de werkgeversorganisaties, noch door de werknemers of de werkgevers; 2. de werknemersorganisaties en de werknemers verbinden er zich toe geen eisen te stellen op nationaal noch op gewestelijk vlak, noch op dat van de onderneming aangezien alle individuele normatieve bepalingen geregeld zijn door onderhavige collectieve arbeidsovereenkomst. Gezien om te worden gevoegd bij het koninklijk besluit van 7 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -3351,28 +3344,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2025003588</t>
+          <t>2025201297</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>15 mei 2025</t>
+          <t>09 mei 2025</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>21 januari 2024. - Koninklijk besluit houdende het scholingsbeding, heroriëntering om professionele redenen en het werkplekleertraject. - Erratum</t>
+          <t>5 mei 2025. - Koninklijk besluit tot vaststelling, voor de ondernemingen die onder het Paritair Comité voor de steenbakkerij (PC 114) ressorteren, van de voorwaarden waaronder het gebrek aan werk wegens economische oorzaken de uitvoering van de arbeidsovereenkomst voor werklieden schorst (1)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-15&amp;numac_search=2025003588&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003588=91&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-09&amp;numac_search=2025201297&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201297=91&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
           <t xml:space="preserve">
-In het Belgisch Staatsblad van 7 februari 2024, bladzijde 14859, akte 2024/000469, dient "In afwijking van artikel 6bis, § 1, van het koninklijk besluit van 2 oktober 1937 houdende het statuut van het Rijkspersoneel" te worden gelezen in de plaats van « In afwijking van artikel 6, § 1, van het koninklijk besluit van 2 oktober 1937".
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 3 juli 1978 betreffende de arbeidsovereenkomsten, artikel 51, § 1, vervangen bij de wet van 30 december 2001 en gewijzigd bij de wetten van 4 juli 2011 en 15 januari 2018; Gelet op het advies van het Paritair Comité voor de steenbakkerij, gegeven op 27 november 2024; Gelet op advies 77.585/16 van de Raad van State, gegeven op 14 april 2025, met toepassing van artikel 84, § 1, eerste lid, 2°, van de wetten op de Raad van State, gecoördineerd op 12 januari 1973; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Dit besluit is van toepassing op de werkgevers en op de werklieden van de ondernemingen die onder het Paritair Comité voor de steenbakkerij ressorteren. Art. 2. Bij gebrek aan werk wegens economische oorzaken mag de uitvoering van de arbeidsovereenkomst voor werklieden volledig worden geschorst op voorwaarde dat de schorsing door aanplakking op een goed zichtbare plaats in de lokalen van de onderneming, ten minste zeven dagen vooraf, ter kennis wordt gebracht. Wanneer de werkman de dag van de aanplakking afwezig is, wordt hem de kennisgeving dezelfde dag bij aangetekende brief gezonden.Art. 3. De duur van de volledige schorsing van de uitvoering van de arbeidsovereenkomst mag zesentwintig weken niet overschrijden. Wanneer de volledige schorsing van de uitvoering van de overeenkomst de maximumduur van zesentwintig weken heeft bereikt, moet de werkgever gedurende een volledige arbeidsweek de regeling van volledige arbeid opnieuw invoeren, alvorens een nieuwe volledige schorsing kan ingaan. Art. 4. Met toepassing van artikel 51, § 1, vijfde lid, van de wet van 3 juli 1978 betreffende de arbeidsovereenkomsten, vermeldt de in artikel 2 bedoelde kennisgeving de datum waarop de volledige schorsing van de uitvoering van de overeenkomst ingaat, de datum waarop deze schorsing een einde neemt, alsook de data waarop de werklieden werkloos worden gesteld. Art. 5. Dit besluit heeft uitwerking met ingang van 1 april 2025 en treedt buiten werking op 31 maart 2026. Art. 6. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 5 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzingen naar het Belgisch Staatsblad: Wet van 3 juli 1978, Belgisch Staatsblad van 22 augustus 1978. Wet van 30 december 2001, Belgisch Staatsblad van 31 december 2001. Programmawet van 4 juli 2011, Belgisch Staatsblad van 19 juli 2011. Wet van 15 januari 2018, Belgisch Staatsblad van 5 februari 2018. 
 </t>
         </is>
       </c>
@@ -3383,28 +3376,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2025003652</t>
+          <t>2025003629</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>23 mei 2025</t>
+          <t>12 mei 2025</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>21 januari 2024. - Koninklijk besluit tot wijziging van het koninklijk besluit van 15 maart 1968 houdende algemeen reglement op de technische eisen waaraan de auto's, hun aanhangwagens, hun onderdelen en hun veiligheidstoebehoren moeten voldoen en het koninklijk besluit van 1 december 1975 houdende algemeen reglement op de politie van het wegverkeer en van het gebruik van de openbare weg. - Duitse vertaling</t>
+          <t>5 mei 2025. - Koninklijk besluit tot benoeming van de eerste plaatsvervangend voorzitter van de Nederlandstalige Uitvoerende Kamer van het Beroepsinstituut van Vastgoedmakelaars</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-23&amp;numac_search=2025003652&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003652=92&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-12&amp;numac_search=2025003629&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003629=92&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 21 januari 2024 tot wijziging van het koninklijk besluit van 15 maart 1968 houdende algemeen reglement op de technische eisen waaraan de auto's, hun aanhangwagens, hun onderdelen en hun veiligheidstoebehoren moeten voldoen en het koninklijk besluit van 1 december 1975 houdende algemeen reglement op de politie van het wegverkeer en van het gebruik van de openbare weg (Belgisch Staatsblad van 1 februari 2024).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST MOBILITÄT UND TRANSPORTWESEN21. JANUAR 2024 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 15. März 1968 zur Festlegung der allgemeinen Regelung über die technischen Anforderungen an Kraftfahrzeuge, ihre Anhänger, ihre Bestandteile und ihr Sicherheitszubehör und des Königlichen Erlasses vom 1. Dezember 1975 zur Festlegung der allgemeinen Ordnung über den Straßenverkehr und die Benutzung der öffentlichen StraßePHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund von Artikel 1 Absatz 1 des Gesetzes vom 16. März 1968 über die Straßenverkehrspolizei, koordiniert durch den Königlichen Erlass vom 16. März 1968 zur Koordinierung der Gesetze über die Straßenverkehrspolizei;Aufgrund des Gesetzes vom 21. Juni 1985 über die technischen Anforderungen, denen jedes Fahrzeug für den Transport auf dem Landweg, seine Bestandteile und sein Sicherheitszubehör entsprechen müssen, des Artikels 1, abgeändert durch die Gesetze vom 18. Juli 1990, 5. April 1995, 4. August 1996 und 27. November 1996, den Königlichen Erlass vom 20. Juli 2000 und das Gesetz vom 31. Juli 2020;Aufgrund des Königlichen Erlasses vom 15. März 1968 zur Festlegung der allgemeinen Regelung über die technischen Anforderungen an Kraftfahrzeuge, ihre Anhänger, ihre Bestandteile und ihr Sicherheitszubehör;Aufgrund des Königlichen Erlasses vom 1. Dezember 1975 zur Festlegung der allgemeinen Ordnung über den Straßenverkehr und die Benutzung der öffentlichen Straße;Aufgrund der Stellungnahme des Beratungsausschusses "Verwaltung - Industrie" vom 17. April 2023;Aufgrund der Beteiligung der Regionalregierungen an der Ausarbeitung des vorliegenden Erlasses;Aufgrund des Gutachtens Nr. 74.734/4 des Staatsrates vom 22. November 2023, abgegeben in Anwendung von Artikel 84 §  1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Auf Vorschlag des Ministers der MobilitätHaben Wir beschloßen und erlassen Wir:KAPITEL 1 - Abänderung des Königlichen Erlasses vom 15. März 1968 zur Festlegung der allgemeinen Regelung über die technischen Anforderungen an Kraftfahrzeuge, ihre Anhänger, ihre Bestandteile und ihr SicherheitszubehörArtikel 1 -  Artikel 28 § 2 Nr. 1 Buchstabe c) Ziffer 4 Absatz 1 des Königlichen Erlasses vom 15. März 1968 zur Festlegung der allgemeinen Regelung über die technischen Anforderungen an Kraftfahrzeuge, ihre Anhänger, ihre Bestandteile und ihr Sicherheitszubehör, ersetzt durch den Königlichen Erlass vom 10. April 1995 und abgeändert durch die Königlichen Erlasse vom 17. März 2003, 13. September 2004 und 9. März 2022, wird wie folgt abgeändert:"4 Fahrzeuge der Polizeidienste, erkennbare Fahrzeuge des Straßenkontrolldienstes der Verwaltung der Verkehrsregelung und der Infrastruktur zu Land, vom Minister der Finanzen bestimmte erkennbare Fahrzeuge der Zoll und Akzisenverwaltung, vom Minister der Landesverteidigung bestimmte erkennbare Fahrzeuge der Militärpolizei und der Minenräumdienste der Streitkräfte, für den Transport von Häftlingen und für die Staatsanwaltschaft benutzte Fahrzeuge des Föderalen Öffentlichen Dienstes Justiz, das Dienstfahrzeug der Provinzgouverneure, erkennbare Fahrzeuge der Inspektionsdienste der Regionen und der Gesellschaften für öffentlichen Verkehr, die mit den Straßenkontrollen beauftragt sind, Krankenwagen, Fahrzeuge für dringende medizinische Einsätze des 112-Dienstes, Feuerwehrfahrzeuge, Fahrzeuge des Zivilschutzes, Rettungsfahrzeuge der Nationalen Gesellschaft der Belgischen Eisenbahnen, Rettungsfahrzeuge von Infrabel, Rettungsfahrzeuge bei durch Wasser, Gas, Strom oder radioaktive Stoffe verursachten schweren Zwischenfällen, erkennbare Fahrzeuge der Noteinsatzplanungskoordinatoren dürfen vorne oder auf dem Dach mit einem oder mehreren blauen Blinklichtern versehen sein."Art. 2 -  Artikel 43 § 2 Nr. 3 desselben Königlichen Erlasses vom 15. März 1968, ersetzt durch den Königlichen Erlass vom 10. April 1995 und abgeändert durch die Königlichen Erlasse vom 17. März 2003, 13. September 2004 und 9. März 2022, wird wie folgt ersetzt:"3. Fahrzeuge der Polizeidienste, erkennbare Fahrzeuge des Straßenkontrolldienstes der Verwaltung der Verkehrsregelung und der Infrastruktur zu Land, vom Minister der Finanzen bestimmte erkennbare Fahrzeuge der Zoll und Akzisenverwaltung, vom Minister der Landesverteidigung bestimmte erkennbare Fahrzeuge der Militärpolizei und der Minenräumdienste der Streitkräfte, für den Transport von Häftlingen und für die Staatsanwaltschaft benutzte Fahrzeuge des Föderalen Öffentlichen Dienstes Justiz, das Dienstfahrzeug der Provinzgouverneure, erkennbare Fahrzeuge der Inspektionsdienste der Regionen und der Gesellschaften für öffentlichen Verkehr, die mit den Straßenkontrollen beauftragt sind, Krankenwagen, Fahrzeuge für dringende medizinische Einsätze des 112-Dienstes, Feuerwehrfahrzeuge, Fahrzeuge des Zivilschutzes, Rettungsfahrzeuge der Nationalen Gesellschaft der Belgischen Eisenbahnen, Rettungsfahrzeuge von Infrabel, Rettungsfahrzeuge bei durch Wasser, Gas, Strom oder radioaktive Stoffe verursachten schweren Zwischenfällen, erkennbare Fahrzeuge der Noteinsatzplanungskoordinatoren dürfen mit einer besonderen akustischen Warnvorrichtung ausgestattet sein. Der für den Straßenverkehr zuständige Minister oder sein Beauftragter kann ausnahmsweise erlauben, dass andere für einen öffentlichen Dienst bestimmte Fahrzeuge mit einer besonderen akustischen Warnvorrichtung ausgestattet werden."KAPITEL 2 - Abänderung des Königlichen Erlasses vom 1. Dezember 1975 zur Festlegung der allgemeinen Ordnung über den Straßenverkehr und die Benutzung der öffentlichen StraßeArt. 3 -  Artikel 37.5 Buchstabe e) des Königlichen Erlasses vom 1. Dezember 1975 zur Festlegung der allgemeinen Ordnung über den Straßenverkehr und die Benutzung der öffentlichen Straße, eingefügt durch das Gesetz vom 16. Juli 2020 und abgeändert durch den Königlichen Erlass vom 2. Oktober 2023, wird wie folgt ersetzt:"e) Führer eines Rettungsfahrzeugs der Nationalen Gesellschaft der Belgischen Eisenbahnen,".KAPITEL 3 - SchlussbestimmungArt. 4 -  Der für den Straßenverkehr zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 21. Januar 2024PHILIPPEVon Königs wegen:Der Minister der MobilitätG. GILKINET
+Bij koninklijk besluit van 5 mei 2025 wordt dhr. Johan Timmermans voor een termijn van zes jaar benoemd tot eerste plaatsvervangend voorzitter van de Nederlandstalige Uitvoerende Kamer van het Beroepsinstituut van Vastgoedmakelaars.Dit besluit treedt in werking op 28 mei 2025.Binnen een termijn van zestig dagen vanaf deze bekendmaking kan een verzoekschrift tot nietigverklaring bij de Raad van State ingediend worden.Het verzoekschrift wordt ofwel per post aangetekend verzonden naar de griffie van de Raad van State, Wetenschapsstraat 33, te 1040 Brussel, ofwel wordt het ingediend volgens de elektronische procedure (zie daarvoor de rubriek "e-Procedure" op de website van de Raad van State). 
 </t>
         </is>
       </c>
@@ -3415,28 +3408,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2025003875</t>
+          <t>2025003680</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>28 mei 2025</t>
+          <t>14 mei 2025</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>3 december 2023. - Koninklijk besluit tot uitvoering van artikel 115, § 10, eerste lid, van de wet van 7 december 1998 tot organisatie van een geïntegreerde politiedienst, gestructureerd op twee niveaus. - Duitse vertaling</t>
+          <t>5 mei 2025. - Koninklijk besluit betreffende het ontslag en de benoeming van een regeringscommissaris bij de naamloze vennootschap van publiek recht A.S.T.R.I.D.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-28&amp;numac_search=2025003875&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003875=93&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-14&amp;numac_search=2025003680&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003680=93&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 3 december 2023 tot uitvoering van artikel 115, § 10, eerste lid, van de wet van 7 december 1998 tot organisatie van een geïntegreerde politiedienst, gestructureerd op twee niveaus (Belgisch Staatsblad van 27 december 2023).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST INNERES3. DEZEMBER 2023 - Königlicher Erlass zur Ausführung von Artikel 115 § 10 Absatz 1 des Gesetzes vom 7. Dezember 1998 zur Organisation eines auf zwei Ebenen strukturierten integrierten PolizeidienstesPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des Gesetzes vom 7. Dezember 1998 zur Organisation eines auf zwei Ebenen strukturierten integrierten Polizeidienstes, des Artikels 115 § 10 Absatz 1;Aufgrund der Stellungnahme des Generalinspektors der Finanzen vom 12. Januar 2023;Aufgrund des Einverständnisses der Staatssekretärin für Haushalt vom 13. März 2023;Aufgrund der Stellungnahme des Bürgermeisterrates vom 7. Juni 2023;Aufgrund des Antrags auf Begutachtung binnen einer um fünfzehn Tage verlängerten Frist von dreißig Tagen, der am 17. Juli 2023 beim Staatsrat eingereicht worden ist, in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;In der Erwägung, dass kein Gutachten binnen dieser Frist übermittelt worden ist;Aufgrund des Artikels 84 § 4 Absatz 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Auf Vorschlag der Ministerin des Innern und aufgrund der Stellungnahme der Minister, die im Rat darüber beraten haben,Haben Wir beschloßen und erlassen Wir:Artikel 1 - In vorliegendem Erlass wird die Art der in Artikel 115 § 10 Absatz 1 des Gesetzes vom 7. Dezember 1998 zur Organisation eines auf zwei Ebenen strukturierten integrierten Polizeidienstes erwähnten Unterstützungsaufträge bestimmt, die die föderale Polizei auf nichtoperativer Ebene zugunsten der lokalen Polizeizonen kostenlos erfüllt, und zwar unbeschadet der eigenen Aufträge der föderalen Polizei, die den Polizeizonen indirekt zugutekommen.Die in Absatz 1 erwähnten Unterstützungsaufträge werden im Rahmen der verfügbaren Haushaltsmittel und Ressourcen erfüllt, ohne dabei die gesetzlichen Aufträge der föderalen Polizei zu beeinträchtigen.Im Zweifelsfall entscheidet der Minister des Innern, ob es sich um einen in Absatz 1 erwähnten Auftrag handelt. Er holt hierzu die Stellungnahme des in Artikel 8ter desselben Gesetzes erwähnten Koordinierungsausschusses der integrierten Polizei ein.Art. 2 - Die Dienstleistungen, die die föderale Polizei den Polizeizonen im Rahmen der in Artikel 1 Absatz 1 erwähnten Unterstützungsaufträge anbietet, beruhen auf den vom Koordinierungsausschuss der integrierten Polizei validierten Standards der integrierten Polizei.Die in Absatz 1 erwähnten Standards betreffen mindestens die Typologie der angebotenen Dienstleistungen, die erforderlichen Bedingungen, um diese Dienstleistungen anzubieten, die Festlegung von Prioritäten sowie die damit verbundenen Richtlinien für den Haushaltsplan.Art. 3 - Die nichtoperative Unterstützung, die die föderale Polizei der lokalen Polizei kostenlos leistet, betrifft Dienstleistungen, die für die integrierte Arbeitsweise der Polizeidienste von wesentlicher Bedeutung sind, nachstehend "wesentliche Dienstleistungen" genannt.Art. 4 - Im Rahmen der nichtoperativen Unterstützung erfüllt die föderale Polizei zugunsten der Polizeizonen in den Bereichen Strategie, Politik und Kommunikation sowie in rechtlichen Angelegenheiten kostenlos folgende Aufträge:1. punktuelle Unterstützung im politischen Bereich, einschließlich der Erstellung strategischer Analysen, sowie im Bereich des polizeilichen Lagebildes,2. Unterstützung im Rahmen der Kommunikation innerhalb der integrierten Polizei, einschließlich der redaktionellen und visuellen Unterstützung und der Entwicklung von Kommunikationssystemen, die die Zurverfügungstellung operativer und nichtoperativer Dokumentation ermöglichen,3. Unterstützung im Rahmen von Werbemaßnahmen für die integrierte Polizei und Verleih von Werbematerial für die integrierte Polizei,4. Abfassung juristischer Gutachten und Bereitstellung technischer Unterstützung im Rahmen der Rechtsvorschriften in Bezug auf die Polizeidienste.Art. 5 - Im Rahmen der nichtoperativen Unterstützung erfüllt die föderale Polizei zugunsten der Polizeizonen im Bereich Personal kostenlos folgende Aufträge:1. medizinische Unterstützung, die Folgendes umfasst:a) Eingreifen des Stressteams in Krisensituationen, einschließlich derjenigen, die sich aus schweren Gewalttaten ergeben, die von Dritten gegen Polizeipersonal begangen werden,b) Verwaltung der in Artikel X.I.1 Absatz 1 RSPol erwähnten kostenlosen Gesundheitspflege,c) Verwaltung der in Artikel X.I.1 Absatz 3 RSPol erwähnten Krankenhausversicherungen,d) Verwaltung der in Teil X Titel II RSPol erwähnten medizinischen Kontrolle,e) Arbeitsweise der Kommission für die Eignung des Personals der Polizeidienste und der Berufungskommission für die Eignung des Personals der Polizeidienste, die in Artikel IX.II.1 RSPol erwähnt sind,f) operative medizinische Unterstützung bei Einsätzen, die von der föderalen Polizei gemeinsam mit der lokalen Polizei durchgeführt werden,g) Bereitstellung administrativer Informationen im Bereich Arbeitsunfähigkeit und Absentismus,h) ärztliche Tauglichkeitsuntersuchungen im Rahmen der Anwerbung und der Auswahl von Polizeianwärtern und für spezielle Funktionen, mit Ausnahme derjenigen, die im Rahmen von Anwerbungen durchgeführt werden, die direkt von einer Polizeizone vorgenommen werden,2. Unterstützung bei der Anwerbung und Auswahl der Personalmitglieder der Polizeidienste,3. Organisation der Auswahl im Rahmen des sozialen Aufstiegs,4. unbeschadet der Aufträge der zugelassenen Schulen,a) Koordinierung, Organisation und Begleitung der Ausbildungen und Trainings in Bezug auf die vereinbarte Kontrolle des öffentlichen Raums im Rahmen der belastbaren Kapazität,b) Bereitstellung bestimmter Ausbildungen, die in Ausführung der Rechtsvorschriften oder der vom Minister des Innern festgelegten nationalen Richtlinien durchgeführt werden,c) Bereitstellung funktionaler Ausbildungen und Fortbildungen,d) Bereitstellung von Beförderungsausbildungen, insbesondere des Direktionsbrevets,e) Bereitstellung bestimmter Ausbildungen in Ausführung von Protokollen und Verwaltungsverträgen, die auf der Grundlage des Gegenseitigkeitsprinzips mit den zugelassenen Polizeischulen, den Polizeizonen, dem Ständigen Ausschuss für die lokale Polizei oder Ausbildungseinrichtungen geschlossen wurden,5. Verwaltung der Verleihung von Ehrenauszeichnungen, Zuteilung von Identifizierungsnummern, Verteilung von Antragsformularen für den Erhalt einer Gewerkschaftsprämie und Verwaltung von Abonnements für die öffentlichen Verkehrsmittel im Rahmen der in Artikel XI.V.1 RSPol erwähnten Beteiligung,6. Verwaltung der Mobilität, der Aufrufe zur Bewerbung für ein Mandat,7. Ausführung von Kompetenzbilanzen und Coaching im Rahmen der Suche nach angepassten Stellen innerhalb der integrierten Polizei.Art. 6 - Im Rahmen der nichtoperativen Unterstützung erfüllt die föderale Polizei zugunsten der Polizeizonen im Bereich Logistik kostenlos folgende Aufträge:1. was die wesentliche Ausrüstung betrifft, einschließlich Dienstuniformen, persönlicher und kollektiver Waffenausrüstung, Identifizierungsmitteln und Polizeifahrzeugen:a) Abgabe von Stellungnahmen in Bezug auf diesbezügliche öffentliche Aufträge nur dann, wenn ein öffentlicher Auftrag für die Polizeizonen nicht zugänglich ist,b) Abgabe technischer Stellungnahmen nur dann, wenn ein öffentlicher Auftrag für die Polizeizonen nicht zugänglich ist,c) Vorbereitung, Vergabe und Öffnung diesbezüglicher öffentlicher Aufträge für die Polizeizonen,d) Festlegung und Bewertung der diesbezüglichen Normen,e) Bereitstellung von Legitimations- und Identifizierungskarten,2. was die Infrastruktur betrifft:a) Festlegung und Bewertung von Normen in Bezug auf Konzeption und Bau von Gebäuden,b) Unterrichtung der Polizeizonen in Bezug auf diese Normen.Art. 7 - Im Rahmen der nichtoperativen Unterstützung erfüllt die föderale Polizei zugunsten der Polizeizonen im Bereich Finanzen kostenlos folgende Aufträge:1. Verwaltung und Vorfinanzierung der Kosten, die bei den in Artikel XI.IV.38 RSPol erwähnten internationalen Rechtshilfeersuchen entstehen,2. Verwaltung des Haushalts in Bezug auf die integrierte Arbeitsweise der Polizeidienste.Art. 8 - Im Rahmen der nichtoperativen Unterstützung erfüllt die föderale Polizei zugunsten der Polizeizonen im Bereich polizeiliche Informationen und ICT-Mittel kostenlos folgende Aufträge:1. Aufträge im Zusammenhang mit der Verwaltung operativer polizeilicher Datenbanken, wenn sie für die gesamte integrierte Polizei erforderlich sind und eine der in Artikel 44/2 des Gesetzes über das Polizeiamt erwähnten Kategorien von Datenbanken betreffen, und zwar nur, was die besonderen Datenbanken betrifft, wenn die föderale Polizei allein oder gemeinsam für die Verarbeitung verantwortlich ist, und für die Teile, deren Zusammenlegung zugunsten der integrierten Polizei erfolgt, und, was die gemeinsamen Datenbanken betrifft, wenn die föderale Polizei die gemeinsame Datenbank verwaltet,2. Aufträge im Zusammenhang mit der Verwaltung und Entwicklung nichtoperativer polizeilicher Datenbanken, wenn sie für die gesamte integrierte Polizei erforderlich sind,3. Entwicklung, Verwaltung und Zurverfügungstellung von Datenbanken und Informationen, die sich aus den statutarischen Verpflichtungen im Bereich Personal ergeben,4. Entwicklung und Verwaltung von operativen und nichtoperativen Informations- und Kommunikationssystemen der Polizeidienste, wenn diese Systeme Standards für die integrierte Polizei darstellen und in den Informations- und Kommunikationsdiensten des Bezirks eingesetzt werden,5. Zurverfügungstellung und Verwaltung operativer oder nichtoperativer Daten, die von Dritten bereitgestellt werden, zugunsten der integrierten Polizei, sofern diese Daten der föderalen Polizei kostenlos zur Verfügung gestellt werden,6. Implementierung von ICT-Infrastrukturen und -Netzen und Bereitstellung der erforderlichen Lizenzen für die grundlegenden operativen Prozesse der integrierten Polizei gemäß den Standards der integrierten Polizei,7. Bestimmung von Normen, Grundsätzen, Entwicklungsprozessen, Mindeststandards, Bewertung der Effizienz des Systems und Qualitätskontrolle operativer und nichtoperativer Informationsflüsse, wenn sie für die Arbeitsweise der integrierten Polizei erforderlich sind,8. Bereitstellung von funktionalem oder technischem Fachwissen im Bereich Verwaltung operativer oder nichtoperativer Informationen, wenn dieses Fachwissen für die Arbeitsweise der integrierten Polizei erforderlich ist.Art. 9 - Im Rahmen der nichtoperativen Unterstützung erfüllt die föderale Polizei zugunsten der Polizeizonen im Bereich Datenverarbeitung und -schutz durch den Datenschutzbeauftragten der föderalen Polizei kostenlos folgende Aufträge:1. Abgabe von Stellungnahmen zu Verarbeitungen, für die der Minister des Innern und der Minister der Justiz verantwortlich sind,2. Beratung und Bereitstellung von Dokumentation.Art. 10 - Der für Inneres zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 3. Dezember 2023PHILIPPEVon Königs wegen:Die Ministerin des InnernA. VERLINDEN 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 8 juni 1998 betreffende de radiocommunicatie van de hulp- en veiligheidsdiensten, inzonderheid op artikel 17;Gelet op de bijlage bij het koninklijk besluit van 27 juli 1998 tot vaststelling van de statuten van A.S.T.R.I.D. inzonderheid op artikel 19;Gelet op het koninklijk besluit van 5 januari 2021 betreffende het ontslag en de benoeming van een regeringscommissaris bij de naamloze vennootschap van publiek recht A.S.T.R.I.D.;Overwegende dat er bij de naamloze vennootschap van publiek recht A.S.T.R.I.D. een nieuwe regeringscommissaris dient te worden benoemd, belast met de controle-uitoefening namens de Minister van Veiligheid en Binnenlandse Zaken;Overwegende dat de heer Jorn BRONSELAER de noodzakelijke kennis heeft om in het algemeen de wettelijke opdrachten van de regeringscommissarissen uit te oefenen, en om in het bijzonder te waken over de naleving van de wet, de statuten van A.S.T.R.I.D. en het beheerscontract dat tussen de Staat en A.S.T.R.I.D. is gesloten.Op de voordracht van de Minister van Binnenlandse Zaken,Hebben Wij besloten en besluiten Wij :Artikel 1. Eervol ontslag uit zijn mandaat van regeringscommissaris bij de naamloze vennootschap van publiek recht A.S.T.R.I.D. wordt verleend aan de heer Raf TRUYENS.Art. 2. De heer Jorn BRONSELAER wordt benoemd tot regeringscommissaris bij de naamloze vennootschap van publiek recht A.S.T.R.I.D.Art. 3. Dit besluit treedt in werking op 1 mei 2025.Art. 4. De Minister bevoegd voor Binnenlandse Zaken is belast met de uitvoering van dit besluit.Gegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister van Veiligheid en Binnenlandse zaken, belast met Beliris,B. QUINTIN 
 </t>
         </is>
       </c>
@@ -3447,28 +3440,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2025003566</t>
+          <t>2025201148</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>15 mei 2025</t>
+          <t>16 mei 2025</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>23 november 2023. - Koninklijk besluit tot wijziging van diverse besluiten inzake geneesmiddelen en medische hulpmiddelen. - Duitse vertaling van uittreksels</t>
+          <t>5 mei 2025. - Koninklijk besluit tot benoeming van de Voorzitter van de Hoge Raad voor Preventie en Bescherming op het Werk (1)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-15&amp;numac_search=2025003566&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003566=94&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-16&amp;numac_search=2025201148&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201148=94&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van de artikelen 6 en 15 van het koninklijk besluit van 23 november 2023 tot wijziging van diverse besluiten inzake geneesmiddelen en medische hulpmiddelen (Belgisch Staatsblad van 7 december 2023).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALAGENTUR FÜR ARZNEIMITTEL UND GESUNDHEITSPRODUKTE23. NOVEMBER 2023 - Königlicher Erlass zur Abänderung verschiedener Erlasse über Arzneimittel und Medizinprodukte(...)KAPITEL 3 - Wiederaufnahme einiger Bestimmungen des Königlichen Erlasses vom 18. März 1999 über MedizinprodukteArt. 6 - Artikel 9 des Königlichen Erlasses vom 18. März 1999 über Medizinprodukte, aufgehoben durch den Königlichen Erlass vom 13. September 2022, wird mit folgendem Wortlaut wieder aufgenommen:"Art. 9 - § 1 - Bei Produkten, die für klinische Prüfungen bestimmt sind, wendet der Hersteller oder sein Bevollmächtigter das in Anlage 8 bestimmte Verfahren an und meldet dies anhand der in Anlage 8 Nr. 2.2 erwähnten Erklärung der FAAG und den zuständigen Behörden der Mitgliedstaaten, in denen die Prüfungen eventuell durchgeführt werden sollen. Gegebenenfalls übermittelt die FAAG dem zuständigen Dienst die Information.Bei Produkten der Klasse III sowie bei implantierbaren und zur langzeitigen Anwendung bestimmten invasiven Produkten der Klasse IIa oder IIb notifiziert der Hersteller oder sein Bevollmächtigter seine Absicht, eine klinische Prüfung bei der FAAG durchzuführen, anhand der in Absatz 1 erwähnten Daten mindestens sechzig Tage vor Beginn der Prüfung.Binnen zwanzig Tagen ab dem in Absatz 2 erwähnten Notifizierungsdatum überprüft die FAAG, ob die eingereichte Akte die in Anlage 8 Nr. 2.2 erwähnten Elemente enthält. Ist die Akte unvollständig, schickt die FAAG sie dem Hersteller oder seinem Bevollmächtigten zurück und informiert ihn über die Unzulässigkeit, die dazu führt, dass die klinische Prüfung verweigert wird. Ist die Akte vollständig, teilt die FAAG dem Hersteller oder seinem Bevollmächtigten die Zulässigkeit mit.Der Generalverwalter der FAAG kann dem Hersteller oder seinem Bevollmächtigten erlauben, vor Ablauf der Frist von sechzig Tagen mit der notifizierten klinischen Prüfung zu beginnen, sofern die betreffende Ethik-Kommission, wie in Artikel 2 Nr. 4 erster oder zweiter Gedankenstrich des oben erwähnten Gesetzes vom 7. Mai 2007 erwähnt, eine günstige Stellungnahme zu dem entsprechenden Prüfungsprogramm, darin einbegriffen die Überprüfung des klinischen Prüfplans, abgegeben hat.Der Hersteller oder sein Bevollmächtigter kann nach Ablauf von sechzig Tagen ab dem in Absatz 2 erwähnten Notifizierungsdatum mit der notifizierten klinischen Prüfung beginnen, sofern die im vorhergehenden Absatz erwähnte betreffende Ethik-Kommission eine wie im vorhergehenden Absatz erwähnte günstige Stellungnahme abgegeben hat, außer wenn die FAAG ihm binnen dieser Frist einen gegenteiligen Beschluss aus Gründen der Volksgesundheit oder der öffentlichen Ordnung zukommen lässt. § 2 - Bei anderen als den in § 1 Absatz 2 genannten Produkten kann der Hersteller oder sein Bevollmächtigter sofort nach dem in § 1 Absatz 1 erwähnten Notifizierungsdatum mit der klinischen Prüfung beginnen, sofern die in § 1 Absatz 5 erwähnte zuständige Ethik-Kommission eine günstige Stellungnahme zu dem betreffenden Prüfungsprogramm, darin einbegriffen die Überprüfung des klinischen Prüfplans, abgegeben hat. § 3 - Die in den Paragraphen 1 und 2 erwähnten Produkte können den in Artikel 2 Nr. 17 des oben erwähnten Gesetzes vom 7. Mai 2004 erwähnten Prüfern nur zur Verfügung gestellt werden, sofern die in § 1 Absatz 5 erwähnte betreffende Ethik-Kommission eine günstige Stellungnahme zu dem notifizierten Prüfungsprogramm abgegeben hat. § 4 - Der für die Volksgesundheit zuständige Minister kann auf Stellungnahme der zuständigen Dienste die Form festlegen, in der der Hersteller oder sein Bevollmächtigter die in § 1 erwähnte Notifizierung oder die in § 2 erwähnten Informationen übermitteln muss. § 5 - Die klinischen Prüfungen müssen im Einklang mit den Bestimmungen von Anlage 10 durchgeführt werden. § 6 - Die Bestimmungen der Paragraphen 1 und 2 gelten nicht, wenn die klinischen Prüfungen mit Produkten durchgeführt werden, die die CE-Kennzeichnung tragen dürfen, es sei denn, diese Prüfungen haben eine andere Zweckbestimmung der Produkte zum Gegenstand als die in dem Verfahren zur Bewertung der Konformität vorgesehene Zweckbestimmung. Die einschlägigen Bestimmungen der Anlage 10 zu vorliegendem Erlass bleiben folglich anwendbar. § 7 - Der für die Volksgesundheit zuständige Minister kann begonnene klinische Prüfungen aussetzen oder verbieten sowie alle anderen notwendigen Maßnahmen treffen, um die Volksgesundheit und die öffentliche Ordnung zu gewährleisten.Die FAAG teilt allen anderen Mitgliedstaaten und der Europäischen Kommission die Ablehnungs- oder Aussetzungsentscheidung sowie die Gründe dafür mit. Hat die FAAG eine wesentliche Änderung oder vorübergehende Unterbrechung einer klinischen Prüfung angeordnet, informiert sie die anderen betreffenden Mitgliedstaaten über die von ihr getroffenen Maßnahmen und deren Gründe. § 8 - Der Hersteller oder sein Bevollmächtigter notifiziert der FAAG und der in § 1 Absatz 5 erwähnten Ethik-Kommission den Abschluss der klinischen Prüfung und begründet gegebenenfalls die vorzeitige Beendigung der Prüfung. Ist die klinische Prüfung aus Sicherheitsgründen vorzeitig abgebrochen worden, wird die Notifizierung an alle anderen Mitgliedstaaten und die Europäische Kommission gerichtet. Der Hersteller oder sein Beauftragter hält den in Anlage 10 Nr. 2.3.7 erwähnten Bericht der FAAG zur Verfügung."(...)KAPITEL 6 - Abänderung des Königlichen Erlasses vom 28. September 2009 zur Festlegung der Qualitäts- und Sicherheitsnormen für die Spende, Entnahme, Gewinnung, Testung, Verarbeitung, Lagerung und Verteilung von menschlichem Körpermaterial, denen die Banken für menschliches Körpermaterial, die Zwischenstrukturen für menschliches Körpermaterial und die Produktionseinrichtungen entsprechen müssenArt. 15 - In Anlage IV Punkt 4.2 zum Königlichen Erlass vom 28. September 2009 zur Festlegung der Qualitäts- und Sicherheitsnormen für die Spende, Entnahme, Gewinnung, Testung, Verarbeitung, Lagerung und Verteilung von menschlichem Körpermaterial, denen die Banken für menschliches Körpermaterial, die Zwischenstrukturen für menschliches Körpermaterial und die Produktionseinrichtungen entsprechen müssen, ersetzt durch den Königlichen Erlass vom 25. April 2014, werden die Wörter "sind die Blutproben" durch die Wörter "sind die Blut- und gegebenenfalls Urinproben" ersetzt.(...)Gegeben zu Brüssel, den 23. November 2023PHILIPPEVon Königs wegen:Der Minister der VolksgesundheitF. VANDENBROUCKE 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 4 augustus 1996 betreffende het welzijn van de werknemers bij de uitvoering van hun werk, artikel 44, gewijzigd bij de wetten van 13 februari 1998 en 30 december 2009, en artikel 45, gewijzigd bij de wet van 20 juli 2006; Gelet op boek II, titel 9 van de codex over het welzijn op het werk, artikel II.9-43; Gelet op het koninklijk besluit van 22 april 2019 tot benoeming van de Voorzitter van de Hoge Raad voor Preventie en Bescherming op het Werk; Overwegende dat de heer Karel Van Damme bij koninklijk besluit van 22 april 2019 tot voorzitter van de Hoge Raad werd benoemd, voor een periode van zes jaar, gestart op 1 juni 2019 en eindigend op 31 mei 2025; Overwegende dat het daarom nodig is om, met ingang van 1 juni 2025, het mandaat van de Voorzitter van de Hoge Raad met zes jaar te hernieuwen; Overwegende dat de heer Karel Van Damme nog steeds beantwoordt aan de voorwaarden bedoeld in artikel 45, § 2, eerste lid, van de wet van 4 augustus 1996 betreffende het welzijn van de werknemers bij de uitvoering van hun werk; Overwegende dat zijn curriculum vitae en zijn ervaring als Voorzitter van de Hoge Raad ruimschoots aantonen dat hij vertrouwd is met de activiteiten van de Hoge Raad en dat hij deskundig is op vlak van het welzijn van de werknemers bij de uitvoering van hun werk; Op de voordracht de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. De heer Karel Van Damme wordt benoemd tot Voorzitter van de Hoge Raad voor Preventie en Bescherming op het Werk voor een periode van zes jaar.Art. 2. Dit besluit treedt in werking op 1 juni 2025. Art. 3. Onze Minister van Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 5 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzingen naar het Belgisch Staatsblad: Wet van 4 augustus 1996, Belgisch Staatsblad van 18 september 1996; Wet van 13 februari 1998, Belgisch Staatsblad van 19 februari 1998; Wet van 20 juli 2006, Belgisch Staatsblad van 28 juli 2006; Wet van 30 december 2009, Belgisch Staatsblad van 31 december 2009; Codex over het welzijn op het werk, Belgisch Staatsblad van 2 juni 2017; Koninklijk besluit van 22 april 2019, Belgsich Staatsblad van 21 mei 2019. 
 </t>
         </is>
       </c>
@@ -3479,28 +3472,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2025003648</t>
+          <t>2025201149</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>23 mei 2025</t>
+          <t>16 mei 2025</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2 oktober 2023. - Koninklijk besluit tot wijziging van het koninklijk besluit van 1 december 1975 houdende algemeen reglement op de politie van het wegverkeer en van het gebruik van de openbare weg. - Duitse vertaling</t>
+          <t>5 mei 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 12 augustus 2024 tot benoeming van permanente deskundigen van de Hoge Raad voor Preventie en Bescherming op het Werk</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-23&amp;numac_search=2025003648&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003648=95&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-16&amp;numac_search=2025201149&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201149=95&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 2 oktober 2023 tot wijziging van het koninklijk besluit van 1 december 1975 houdende algemeen reglement op de politie van het wegverkeer en van het gebruik van de openbare weg (Belgisch Staatsblad van 8 januari 2024).Deze vertaling in het Duits is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST MOBILITÄT UND TRANSPORTWESEN2. OKTOBER 2023 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 1. Dezember 1975 zur Festlegung der allgemeinen Ordnung über den Straßenverkehr und die Benutzung der öffentlichen StraßePHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des am 16. März 1968 koordinierten Gesetzes über die Straßenverkehrspolizei, des Artikels 1 Absatz 1;Aufgrund des Königlichen Erlasses vom 1. Dezember 1975 zur Festlegung der allgemeinen Ordnung über den Straßenverkehr und die Benutzung der öffentlichen Straße;Aufgrund der Beteiligung der Regionalregierungen;Aufgrund von Artikel 84 § 4 Absatz 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Aufgrund der Übermittlung an die Europäische Kommission vom 8. Juni 2023 in Anwendung von Artikel 5 Absatz 1 der Richtlinie (EU) 2015/1535 des Europäischen Parlaments und des Rates vom 9. September 2015 über ein Informationsverfahren auf dem Gebiet der technischen Vorschriften und der Vorschriften für die Dienste der Informationsgesellschaft;Auf Vorschlag des Ministers der MobilitätHaben Wir beschloßen und erlassen Wir:Artikel 1 - In Artikel 2.20 Absatz 1 des Königlichen Erlasses vom 1. Dezember 1975 zur Festlegung der allgemeinen Ordnung über den Straßenverkehr und die Benutzung der öffentlichen Straße, eingefügt durch den Königlichen Erlass vom 16. Juli 1997 und abgeändert durch den Königlichen Erlass vom 21. Juli 2016, werden die Wörter ", und dessen maximale Nutzleistung des Motors 15 kW nicht überschreitet" aufgehoben.Art. 2 - In Artikel 36 Absatz 1 desselben Erlasses, ersetzt durch den Königlichen Erlass vom 24. Juni 2000 und abgeändert durch die Königlichen Erlasse vom 14. Mai 2002 und 21. Juli 2016, werden zwischen den Wörtern "vierrädrigen Fahrzeugen mit Motor" und den Wörtern "und Kleinkrafträdern" die Wörter ", mit Ausnahme von landwirtschaftlichen Fahrzeugen mit einer bauartbedingten Höchstgeschwindigkeit von 40 km/h, die nicht mit einem Lenker wie bei Motorrädern ausgestattet sind," eingefügt.Art. 3 - In Artikel 37.5 Absatz 1 desselben Erlasses, eingefügt durch das Gesetz vom 16. Juli 2020, werden zwischen den Wörtern "die vorliegende Verordnung" und den Wörtern "mit Ausnahme der" die Wörter ", unter der Bedingung, dass die blauen Blinklichter und die besondere akustische Warnvorrichtung benutzt werden," eingefügt.Art. 4 - Artikel 70.2.1 Nr. 3 desselben Erlasses wird durch einen Buchstaben k) mit folgendem Wortlaut ergänzt:"k) Ein Zusatzschild, auf dem das nachstehende Symbol abgebildet ist, zeigt an, dass der Platz für das Be- und Entladen von Gütern vorbehalten ist. Voor de raadpleging van de tabel, zie beeld  Art. 5 - In Artikel 82.1.5 desselben Erlasses, eingefügt durch den Königlichen Erlass vom 30. Juli 2022, wird zwischen den Wörtern "zusätzlich mit" und den Wörtern "gelben oder orangefarbenen" das Wort "weißen," eingefügt.Art. 6 - Artikel 82bis desselben Erlasses, eingefügt durch das Gesetz vom 15. Mai 2022, wird wie folgt abgeändert:1. In Artikel 82bis.1 Nr. 2 erster Gedankenstrich wird das Wort "weißen" durch die Wörter "gelben oder orangefarbenen" ersetzt.2. Artikel 82bis.1 wird durch eine Nummer 3 mit folgendem Wortlaut ergänzt:"3. Motorisierte Fortbewegungsgeräte dürfen mit zusätzlichen weißen, gelben oder orangefarbenen seitlichen Kennzeichnungsmitteln versehen sein."3. In Artikel 82bis.3 werden die Wörter "genügend wirksamen Bremsen" durch die Wörter "einem ausreichend wirksamen Bremssystem" ersetzt.Art. 7 - Vorliegender Erlass tritt am ersten Tag des Monats nach Ablauf einer Frist von zehn Tagen, die am Tag nach seiner Veröffentlichung im Belgischen Staatsblatt beginnt, in Kraft.Art. 8 - Der für den Straßenverkehr zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 2. Oktober 2023PHILIPPEVon Königs wegen:Der Minister der MobilitätG. GILKINET 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 4 augustus 1996 betreffende het welzijn van de werknemers bij de uitvoering van hun werk, artikel 44, gewijzigd bij de wetten van 13 februari 1998 en 30 december 2009, en artikel 45, § 1; Gelet op het artikel II.9-8 van de codex over het welzijn op het werk; Gelet op het koninklijk besluit van 12 augustus 2024 tot benoeming van permanente deskundigen van de Hoge Raad voor Preventie en Bescherming op het Werk; Gelet op de aanvraag tot vervanging en de voordracht ingediend door de betrokken instantie, overeenkomstig artikel II.9-8 van de codex over het welzijn op het werk; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1. Eervol ontslag wordt verleend aan de permanente deskundige van de Hoge Raad voor Preventie en Bescherming op het Werk, vertegenwoordiger van Co-Prev, Vereniging van externe diensten voor preventie en bescherming op het werk: - De heer Geert De Smet. Art. 2. Wordt benoemd tot permanente deskundige van de Hoge Raad voor Preventie en Bescherming op het Werk als vertegenwoordigster van Co-Prev, Vereniging van externe diensten voor preventie en bescherming op het werk: - Mevrouw Hanne Sanders, ter vervanging van de heer Geert De Smet; Art. 3. In artikel 1 van het koninklijk besluit van 12 augustus 2024 tot benoeming van permanente deskundigen van de Hoge Raad voor Preventie en Bescherming op het Werk worden de woorden "De heer Geert De Smet" vervangen door de woorden "Mevrouw Hanne Sanders". Art. 4. Dit besluit treedt in werking op 1 april 2025.Art. 5. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 5 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzingen naar het Belgisch Staatsblad: Wet van 4 augustus 1996, Belgisch Staatsblad van 18 september 1996; Wet van 13 februari 1998, Belgisch Staatsblad van 19 februari 1998; Wet van 30 december 2009, Belgisch Staatsblad van 31 december 2009; Codex over het welzijn op het werk, Belgisch Staatsblad van 2 juni 2017; Koninklijk besluit van 12 augustus 2024, Belgisch Staatsblad van 9 september 2024. 
 </t>
         </is>
       </c>
@@ -3511,28 +3504,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2025003725</t>
+          <t>2025201166</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>26 mei 2025</t>
+          <t>16 mei 2025</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>15 september 2023. - Koninklijk besluit tot wijziging van titel 1 van boek 2 met betrekking tot de algemene rechten en plichten van het koninklijk besluit van 19 april 2014 tot bepaling van het administratief statuut van het operationeel personeel van de hulpverleningszones. - Duitse vertaling</t>
+          <t>5 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de handel in voedingswaren, betreffende de bestaanszekerheid (1)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-26&amp;numac_search=2025003725&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003725=96&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-16&amp;numac_search=2025201166&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025201166=96&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 15 september 2023 tot wijziging van titel 1 van boek 2 met betrekking tot de algemene rechten en plichten van het koninklijk besluit van 19 april 2014 tot bepaling van het administratief statuut van het operationeel personeel van de hulpverleningszones (Belgisch Staatsblad van 27 oktober 2023).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de handel in voedingswaren; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 18 december 2024, gesloten in het Paritair Comité voor de handel in voedingswaren, betreffende de bestaanszekerheid. Art. 2.  De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 5 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL_______Nota (1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Comité voor de handel in voedingswaren Collectieve arbeidsovereenkomst van 18 december 2024 Bestaanszekerheid (Overeenkomst geregistreerd op 20 januari 2025 onder het nummer 191543/CO/119) HOOFDSTUK I. - Toepassingsgebied Artikel 1.  § 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en arbeiders van de ondernemingen die vallen onder het Paritair Comité voor de handel in voedingswaren.  § 2. Met "arbeiders" worden de mannelijke en de vrouwelijke arbeiders bedoeld. HOOFDSTUK II. - Collectief ontslag Art. 2.  § 1. Het "Waarborg- en Sociaal Fonds voor de handel in voedingswaren" kent aan de arbeiders die het slachtoffer zijn van een collectief ontslag, zoals gedefinieerd in de collectieve arbeidsovereenkomsten nr. 10 en nr. 24 van de Nationale Arbeidsraad, een uitkering toe van 3,80 EUR per dag ter aanvulling van de wettelijke vergoeding gedurende de eerste 120 door de RVA vergoedbare dagen volgend op het ontslag.  § 2. Vanaf 1 januari 2016, wordt de dagvergoeding vermeld in § 1, gebracht op 4,00 EUR.  § 3. Vanaf 1 januari 2018 wordt de dagvergoeding vermeld in § 1, gebracht op 4,20 EUR.  § 4. Vanaf 1 januari 2020 wordt de dagvergoeding vermeld in § 1, gebracht op 4,40 EUR.  § 5. Vanaf 1 januari 2022 wordt de dagvergoeding vermeld in § 1, gebracht op 4, 60 EUR.  § 6. Vanaf 1 januari 2024 wordt de dagvergoeding vermeld in § 1, gebracht op 5,10 EUR.HOOFDSTUK III. - Tijdelijke werkloosheid Art. 3.  § 1. Het "Waarborg- en Sociaal Fonds van de handel in voedingswaren" kent aan de arbeiders die het slachtoffer zijn van tijdelijke werkloosheid (om economische of technische reden) een aanvullende vergoeding op de RVA-uitkeringen toe van 3,80 EUR per dag gedurende de eerste 60 dagen per kalenderjaar die in aanmerking komen voor vergoeding.  § 2. Vanaf 1 januari 2016, wordt de dagvergoeding vermeld in § 1, gebracht op 4,00 EUR.  § 3. Vanaf 1 januari 2018, wordt de dagvergoeding vermeld in § 1, gebracht op 4,20 EUR.  § 4. Vanaf 1 januari 2020 wordt de dagvergoeding vermeld in § 1, gebracht op 4,40 EUR.  § 5. Vanaf 1 januari 2022 wordt de dagvergoeding vermeld in § 1, gebracht op 4,60 EUR.  § 6. Vanaf 1 januari 2024 wordt de dagvergoeding vermeld in § 1, gebracht op 5,10 EUR. HOOFDSTUK IV. - Langdurige ziekte Art. 4.  § 1. Het "Waarborg- en Sociaal Fonds voor de handel in voedingswaren" kent aan de arbeiders die langdurig ziek zijn een aanvullende uitkering toe van 3,80 EUR per dag bovenop de ziekte-uitkering gedurende 60 dagen te rekenen na de periode gedekt door het gewaarborgd loon. Voor deeltijdse arbeiders wordt de tussenkomst van het sociaal fonds berekend naar rata van de arbeidstijd.  § 2. Vanaf 1 januari 2016, wordt de dagvergoeding vermeld in § 1, gebracht op 4,00 EUR.  § 3. Vanaf 1 januari 2018, wordt de dagvergoeding vermeld in § 1, gebracht op 4,20 EUR.  § 4. Vanaf 1 januari 2020 wordt de dagvergoeding vermeld in § 1, gebracht op 4,40 EUR.  § 5. Vanaf 1 januari 2022 wordt de dagvergoeding vermeld in § 1, gebracht op 4,60 EUR.  § 6. Vanaf 1 januari 2024 wordt de dagvergoeding vermeld in § 1, gebracht op 5,10 EUR.  § 7. De toekenningsmodaliteiten van de aanvullende uitkering luiden als volgt : De arbeider moet langdurig ziek zijn, dit wil zeggen dat de periode gedekt door het gewaarborgd loon (30 kalenderdagen) voorbij is. Voor arbeiders die arbeidsongeschikt zijn als gevolg van Covid-19 wordt de aanvullende uitkering toegekend vanaf de 31ste dag van de arbeidsongeschiktheid en voor een maximum van 60 dagen, ongeacht of zij al dan niet recht hebben op het gewaarborgde loon. De aanvullende uitkering wordt ook toegekend in geval van verbod te werken of sommige werken uit te voeren tijdens de zwangerschap, voorgeschreven door de geneesheer. De tussenkomst wordt niet toegekend voor het zwangerschapsverlof. De arbeider, slachtoffer van een arbeidsongeval, die een uitkering van het ziekenfonds geniet (na de periode van erkenning van het ongeval) heeft recht op de aanvullende vergoeding, zonder wachtperiode van 30 dagen. Wordt als herval beschouwd, een arbeidsongeschiktheid die plaatsgrijpt binnen de 14 dagen volgend op het einde van een periode van arbeidsongeschiktheid die aanleiding gaf tot de betaling van het gewaarborgd loon. Het fonds zal deze twee periodes beschouwen als één enkele periode, zonder wachtperiode voor de tweede.  § 8. Indien de arbeider, om redenen eigen aan de ziekteuitkering, geen recht heeft op een vergoeding van de mutualiteit, dan wordt de aanvraag geval per geval onderzocht door het "Waarborg- en Sociaal Fonds voor de handel in voedingswaren". HOOFDSTUK V Beëindiging van de arbeidsovereenkomst wegens overmacht Art. 5.  § 1. Het "Waarborg- en Sociaal Fonds van de handel in voedingswaren" kent aan de arbeiders wier arbeidsovereenkomst ten einde kwam wegens overmacht, een aanvullende uitkering toe van 3,80 EUR per dag bovenop de werkloosheidsuitkering of ziekte-uitkering gedurende 60 dagen na het einde van de overeenkomst. Voor deeltijdse arbeiders wordt de tussenkomst van het sociaal fonds berekend naar rata van de arbeidstijd. § 2. Vanaf 1 januari 2016, wordt de dagvergoeding vermeld in § 1, gebracht op 4,00 EUR.  § 3. Vanaf 1 januari 2018, wordt de dagvergoeding vermeld in § 1, gebracht op 4,20 EUR.  § 4. Vanaf 1 januari 2020 wordt de dagvergoeding vermeld in § 1, gebracht op 4,40 EUR.  § 5. Vanaf 1 januari 2022 wordt de dagvergoeding vermeld in § 1, gebracht op 4,60 EUR.  § 6. Vanaf 1 januari 2024 wordt de dagvergoeding vermeld in § 1, gebracht op 5,10 EUR.  § 7. De toekenningsmodaliteiten van de aanvullende uitkering luiden als volgt : De arbeidsovereenkomst van de arbeider moet wegens overmacht verbroken worden. Er is sprake van "overmacht" bij de beëindiging van de arbeidsovereenkomst omwille van definitieve arbeidsongeschiktheid. Deze uitkering is niet cumuleerbaar met de uitkering wegens langdurige ziekte uit het vorige hoofdstuk. Indien de arbeider geniet van de toeslag bij langdurige ziekte voordat hij definitief arbeidsongeschikt verklaard wordt, zal de toeslag bij overmacht alleen voor het saldo van de 60 dagen uitbetaald worden (60 dagen verminderd met het aantal uitbetaalde dagen voor langdurige ziekte). HOOFDSTUK VI. - Slotbepalingen Art. 6. Deze collectieve arbeidsovereenkomst treedt in werking op 1 januari 2025 en houdt op van kracht te zijn op 31 december 2025. Gezien om te worden gevoegd bij het koninklijk besluit van 5 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -3543,29 +3536,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2025003866</t>
+          <t>2025003110</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>22 mei 2025</t>
+          <t>16 mei 2025</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>17 juni 2022. - Koninklijk besluit houdende de toekenning van subsidies in het kader van het Belgische herstel- en veerkrachtplan</t>
+          <t>5 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 21 januari 2025, gesloten in het Paritair Comité voor de bedienden uit de scheikundige nijverheid, betreffende het vervoer van de werknemers (1)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-22&amp;numac_search=2025003866&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003866=97&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-16&amp;numac_search=2025003110&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003110=97&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 22 mei 2003 houdende organisatie van de begroting en van de comptabiliteit van de federale Staat, de artikelen 121 tot 124;Gelet op de programmawet van 20 december 2020, artikel 91;Gelet op de wet van 23 december 2021 houdende de Algemene uitgavenbegroting voor het begrotingsjaar 2022, artikel 2.06.4;Gelet op het koninklijk besluit van 16 november 1994 betreffende de administratieve en begrotingscontrole;Gelet op de verordening (EU) 2021/241 van het Europees parlement en van de Raad van de Europese unie van 12 februari 2021 tot instelling van de herstel- en veerkrachtfaciliteit;Gelet op de uitvoeringsbeslissing van de Raad van de Europese unie van 6 juli houdende de goedkeuring van de evaluatie van het Belgische herstel- en veerkrachtplan;Gelet op het advies van de inspectie van Financiën, gegeven op 9.05.2022;Op de voordracht van de Minister van Binnenlandse Zaken, Institutionele Hervormingen en Democratische Vernieuwing, Annelies Verlinden,Hebben Wij besloten en besluiten Wij :Artikel 1. Er wordt aan het Agentschap voor de Opvang van Asielzoekers (Fedasil) Kartuizersstraat 21 - 1000 Brussel, 0860.737.913 een subsidie toegekend voor de verwezenlijking van het project `I205038 BE-C[C22]-I[I-205] - Digitalisation FPS : sub-measure 7- Digitalisation of asylum and immigration management processes' in het kader van de Faciliteit voor herstel en veerkracht:- van maximaal twee miljoen zesenzeventigduizend achthonderdtachtig euro (2.076.880 EUR) ter dekking van de kosten (excl. Btw);- van maximaal vierhonderdzesendertigduizend honderdvijfenveertig euro (436.145 EUR) ter dekking van niet-terugvorderbare btw-uitgaven.Art. 2.  De in artikel 1 bedoelde bedragen zullen worden aangerekend op:- de basisallocatie 06.41.12.414042 van de Algemene uitgavenbegroting voor het deel ter dekking van de kosten excl. btw van de begrotingsjaren 2022-2026;- de basisallocatie 06.41.10.414098 van de Algemene uitgavenbegroting voor het deel ter dekking van de niet-terugvorderbare btw van de begrotingsjaren 2022-2026.Art. 3.  Uiterlijk binnen drie maanden na de ondertekening van het koninklijk besluit zal een protocol worden gesloten tussen de begunstigde van de subsidie en Minister van Binnenlandse Zaken, Institutionele Hervormingen en Democratische Vernieuwing, Annelies Verlinden. Dit protocol specificeert de modaliteiten inzake de uitvoering, samenwerking tussen de partijen, sancties, klachten, meldingen en verplichtingen van de begunstigde in het kader van het herstel- en veerkrachtplan.Art. 4.  De eindbegunstigde ontvangt jaarlijks een voorschot dat overeenkomt met hoogstens 30% van de jaarlijkse begroting op voorlegging van een schuldvordering aan het begin van het kalenderjaar.Het saldo van de jaarlijkse subsidie wordt aan de begunstigde uitbetaald op voorlegging van een schuldvordering onder voorbehoud van:- het bewijs van de conformiteit en de volledige verwezenlijking van de in het herstel- en veerkrachtplan bepaalde mijlpalen/doelstellingen;- de verwezenlijking van de gepaste maatregelen om de belangen van de Unie te beschermen en ervoor waken dat het gebruik van de fondsen in het kader van de door de faciliteit ondersteunde maatregelen het Belgisch en Europees juridisch kader respecteren, in het bijzonder wat de preventie, de opsporing en de bestrijding van de fraude, de corruptie en de belangenconflicten in artikel 22 van het Europees reglement (EU) 2021/241 betreft;- het opmaken van een schuldvordering met de nodige bewijsstukken die de materialiteit en het bedrag van de aangegeven lasten aantonen.Bij onaanvaardbare, onvolledige of niet conforme gerealiseerde mijlpalen/doelstellingen kunnen alle uitbetaalde subsidies gerecupereerd worden. Art. 5.  De Minister van Binnenlandse Zaken, Institutionele Hervormingen en Democratische Vernieuwing is belast met de uitvoering van dit besluit.Gegeven te Brussel, 17 juni 2022.FILIPVan Koningswege :De Minister van Binnenlandse Zaken,A. VERLINDEN 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de bedienden uit de scheikundige nijverheid;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 21 januari 2025, gesloten in het Paritair Comité voor de bedienden uit de scheikundige nijverheid, betreffende het vervoer van de werknemers.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de bedienden uit de scheikundige nijverheidCollectieve arbeidsovereenkomst van 21 januari 2025Vervoer van de werknemers (Overeenkomst geregistreerdop 31 januari 2025 onder het nummer 191700/CO/207)Artikel 1. ToepassingsgebiedDeze collectieve arbeidsovereenkomst is van toepassing op de werkgevers van de ondernemingen welke ressorteren onder het Paritair Comité voor de bedienden uit de scheikundige nijverheid en op de bedienden waarvan de functies opgenomen zijn in de classificatie der functies opgesteld door dit paritair comité, hierna "de werknemer(s)" genoemd.Met "werknemer(s)" wordt verstaan : de mannelijke en vrouwelijke werknemers.Art. 2. Behalve in het geval waarin de werkgevers zelf het vervoer van hun werknemers organiseren en financieren wordt de bijdrage van de werkgevers in de vervoerkosten gedragen door de werknemers vanaf 1 februari 2025 vastgesteld overeenkomstig de bepalingen van artikelen 3 tot en met 6 van deze collectieve arbeidsovereenkomst.Art. 3. Bijdrage van de werkgevers § 1. Gemeenschappelijk openbaar treinvervoerWat het door de NMBS georganiseerde vervoer betreft, wordt de tussenkomst van de werkgever in de prijs van het gebruikte vervoerbewijs, vanaf 1 februari 2024, berekend op 80 pct. van de reële prijs van de treinkaarten in functie van de afstand. Deze tabel (bijlage 1) wordt jaarlijks op 1 februari aangepast aan de nieuwe tarieven van de NMBS. § 2. Gemeenschappelijk openbaar vervoer, met uitzondering van het treinvervoerVoor wat betreft het gemeenschappelijk openbaar vervoer, met uitzondering van het treinvervoer, wordt de tussenkomst van de werkgever in de prijs van de abonnementen bepaald volgens de modaliteiten als opgenomen in artikel 4 van de collectieve arbeidsovereenkomst nr. 19/9 afgesloten in de Nationale Arbeidsraad. § 3. Gecombineerd gemeenschappelijk openbaar vervoerVoor wat betreft het gecombineerd gemeenschappelijk openbaar vervoer wordt de tussenkomst van de werkgever in de prijs van het vervoersbewijs bepaald volgens de modaliteiten als opgenomen in artikel 5 en artikel 6 van de collectieve arbeidsovereenkomst nr. 19/9 afgesloten in de Nationale Arbeidsraad. § 4. Gemeenschappelijk openbaar vervoer op het grondgebied van een andere lidstaatVoor wat betreft het gemeenschappelijk openbaar vervoer op het grondgebied van een andere lidstaat, wordt de tussenkomst van de werkgever in de prijs van het vervoersbewijs bepaald volgens de modaliteiten als opgenomen in artikel 7 van de collectieve arbeidsovereenkomst nr. 19/9 afgesloten in de Nationale Arbeidsraad.Art. 4. Onmogelijkheid om in normale omstandigheden een openbaar gemeenschappelijk vervoermiddel te gebruikenIndien de werknemer onmogelijk in normale omstandigheden een openbaar gemeenschappelijk vervoermiddel kan gebruiken wegens de geografische ligging van de onderneming of ingevolge de toegepaste uurroosters, wordt de bijdrage van de werkgevers uitgebreid tot de werknemer die verplicht zijn een particulier vervoermiddel te gebruiken.De tussenkomst van de werkgevers bij gebruik van een ander vervoermiddel dan het openbaar vervoer voor een afgelegde afstand die minstens 5 km moet bedragen, blijft vanaf 1 februari 2009 gekoppeld aan de vroegere tabel (in uitvoering van de wet van 27 juli 1962 tot vaststelling van een werkgeversbijdrage in het verlies geleden door de NMBS ingevolge de uitgifte van abonnementen voor werklieden en bedienden) op basis van het gemiddelde van 70 pct. van de reële prijs van de treinkaarten in functie van de afstand, zoals opgenomen in bijlage (bijlage 2) en aangepast op 1 februari van ieder jaar (jaar N + 1) aan de nieuwe tarieven.Art. 5. In het geval dat de NMBS geen tarieven voor een weekkaart bekendmaakt, zullen de kolommen "tarieven weekkaart" en "tussenkomst weekkaart" van de tabel "Tussenkomst van de werkgever bij gebruik van een ander vervoermiddel dan het openbaar vervoer" (in bijlage 2), op 1 februari van elk jaar (jaar N + 1) (als de NMBS nieuwe tarieven bekend maakt) op de volgende manier worden bekomen :"Tarieven weekkaart"De tarieven van de weekkaart van het vorige jaar (jaar N) worden per afstand(en) verhoogd met het percentage van de prijsstijging voor dezelfde afstand(en) van de maandkaart van het huidige jaar (jaar N + 1) afgerond op 2 decimalen op basis van wiskundige afronding. Het percentage van de prijsstijging van de maandkaart wordt op zijn beurt verkregen door de tarieven van de maandkaart van het jaar N per afstand(en) te vergelijken met de tarieven van de maandkaart van het jaar N + 1 per afstand(en) (percentage met 2 decimalen op basis van wiskundige afronding)."Tussenkomst weekkaart"De tussenkomsten van de werkgever in de prijzen van de weekkaart zijn gebaseerd op het gemiddelde van 70 pct.Art. 6. In het geval dat de NMBS tarieven van maandkaarten, 3 maandkaarten en jaarkaarten beperkt tot 150 km bekendmaakt, zal de tabel van de NMBS aangevuld worden met tarieven vanaf 151 km tot en met 200 km en de daar bijhorende tussenkomsten van de werkgever, op 1 februari van elk jaar (jaar N + 1) (als de NMBS nieuwe tarieven bekend maakt), die op de volgende manier worden bekomen :"Prijzen vanaf 151 km tot en met 200 km voor de maandkaart, 3 maandkaart en jaarkaart"De tarieven van de maandkaarten, 3 maandkaarten en jaarkaarten beperkt tot 150 km worden aangevuld door de tarieven van de voornoemde kaarten vanaf 151 km tot en met 200 km van het vorige jaar (jaar N) te verhogen met het percentage van de gemiddelde prijsstijging bekeken over alle afstanden tot en met 150 km van de respectievelijke kaart van het huidige jaar (jaar N + 1), afgerond op 2 decimalen op basis van wiskundige afronding.Het percentage van de gemiddelde prijsstijging van het tarief van de hogergenoemde kaart wordt op zijn beurt verkregen door de tarieven bekeken over alle afstanden tot en met 150 km van de maandkaart, 3 maandkaart en jaarkaart van het jaar N (beperkt tot 150 km) te vergelijken met de tarieven bekeken over alle afstanden tot en met 150 km van de maandkaart, 3 maandkaart en jaarkaart van het jaar N + 1 (percentage met 2 decimalen op basis van wiskundige afronding)."Tussenkomst maandkaart, 3 maandkaart en jaarkaart"De tussenkomsten van de werkgever in de prijzen van de maandkaart, 3 maandkaart, jaarkaart zijn gebaseerd op het gemiddelde van 70 pct."Prijzen vanaf 151 km tot en met 200 km voor de weekkaart"De tarieven van de weekkaart, bekomen door toepassing van artikel 5, worden vanaf 151 km tot en met 200 km aangevuld op de volgende manier : de tarieven vanaf 151 km tot 200 km van het jaar N worden verhoogd met het percentage van de gemiddelde prijsstijging bekeken over alle afstanden tot en met 150 km van de maandkaart van het jaar N + 1, zoals verkregen in toepassing van dit artikel.Art. 7. De bepalingen van deze collectieve arbeidsovereenkomst doen geen afbreuk aan de gunstigere arbeidsvoorwaarden die in de ondernemingen bestaan.Art. 8. De bijdrage van de werkgevers in de vervoerskosten van de werknemers wordt ten minste maandelijks betaald.Art. 9. De bijdrage van de werkgevers in de vervoerkosten van de werknemers is afhankelijk van de aflevering door de werknemers van, naargelang het geval, één of meerdere van de hierna vermelde attesten :a) het speciaal getuigschrift uitgegeven door de Nationale Maatschappij der Belgische Spoorwegen voor de treinkaart voor vervoer per trein;b) een officieel document dat de afgelegde afstand vermeldt, voor het regelmatig gebruik van één of meerdere andere gemeenschappelijke openbaar vervoermiddelen dan de trein;c) een verklaring, ondertekend door de werknemers, waaruit blijkt dat zij regelmatig een ander vervoermiddel gebruiken dan deze vermeld onder a) en b) hierboven over een afstand die minstens 5 km bereikt.Art. 10. In aanvulling op de tussenkomst in de kostprijs van een treinabonnement, zoals bepaald in deze collectieve arbeidsovereenkomst, komt de werkgever sinds 1 juli 2023 tussen, in de parkingskosten van een maandabonnement op de NMBS-parkings a rato van 25 EUR per maand (werkgeverskost), mits voorlegging van stavingstukken, en pro rata de abonnementsformule.Art. 11. DuurDeze collectieve arbeidsovereenkomst is gesloten voor onbepaalde duur. Ze treedt in werking op 1 februari 2025.Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst van 16 januari 2024 gesloten in het Paritair Comité voor de bedienden uit scheikundige nijverheid, betreffende het vervoer van de werknemers (registratienummer : 186136/CO/207).Zij kan door elk der partijen worden opgezegd mits een opzegging van drie maanden, betekend bij een ter post aangetekende brief, gericht aan de voorzitter van het paritair comité. De termijn van drie maanden begint te lopen vanaf de datum waarop de aangetekende brief aan de voorzitter wordt toegezonden. De poststempel geldt als bewijs.Deze collectieve arbeidsovereenkomst zal worden neergelegd ter Griffie van de Algemene Directie Collectieve Arbeidsbetrekkingen van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg en de algemeen verbindende kracht bij koninklijk besluit wordt gevraagd.Gezien om te worden gevoegd bij het koninklijk besluit van 5 mei 2025.De Minister van Werk,D. CLARINVALBijlage 1 bij de collectieve arbeidsovereenkomst van 21 januari 2025, gesloten in het Paritair Comité voor de bedienden uit de scheikundige nijverheid, betreffende het vervoer van de werknemers  </t>
         </is>
       </c>
     </row>
@@ -3575,29 +3567,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2025004115</t>
+          <t>2025003109</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>28 mei 2025</t>
+          <t>16 mei 2025</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>14 januari 2022. - Koninklijk besluit houdende toekenning van een subsidie aan het Agentschap voor Buitenlandse Handel voor steun aan de export via de ontwikkeling van digitale instrumenten en toegenomen digitalisering van het Agentschap voor Buitenlandse Handel</t>
+          <t>5 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 19 februari 2025, gesloten in het Paritair Comité voor het kleding- en confectiebedrijf, betreffende de arbeidsvoorwaarden (1)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-28&amp;numac_search=2025004115&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025004115=98&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-16&amp;numac_search=2025003109&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003109=98&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 22 mei 2003 houdende organisatie van de begroting en van de comptabiliteit van de federale Staat, de artikelen 121 tot 124;Gelet op de programmawet van 20 december 2020, artikel 91;Gelet op de wet van 22 december 2020 houdende de Algemene uitgavenbegroting voor het begrotingsjaar 2021, artikel 2.06.4, zoals gewijzigd bij de wet van 2 april 2021 houdende de derde aanpassing van de Algemene uitgavenbegroting voor het begrotingsjaar 2021;Gelet op het koninklijk besluit van 16 november 1994 betreffende de administratieve en begrotingscontrole;Gelet op het advies van de inspecteur van Financiën, gegeven op 13 december 2021;Overwegende dat het Agentschap voor Buitenlandse Handel een projectfiche heeft ingediend voor steun aan de export via de ontwikkeling van digitale instrumenten en toegenomen digitalisering van het Agentschap voor Buitenlandse Handel in het kader van de Faciliteit voor herstel en veerkracht ;Op de voordracht van de Minister van Buitenlandse Zaken, Europese Zaken en Buitenlandse Handel,Hebben Wij besloten en besluiten Wij :Artikel 1. Er wordt aan het Agentschap voor Buitenlandse Handel, Montoyerstraat 3 1000 Brussel, 0858.355.275 een subsidie toegekend- van maximaal 130 000 euro (honderddertigduizend EUR) ter dekking van de kosten excl. btw die gepaard gaan met de verwezenlijk van het project `I205026 BE-C[C22]-I[I-205] - Digitalisering FOD, submaatregel 3: Steun aan de export via de ontwikkeling van digitale instrumenten en digitalisering van het agentschap voor buitenlandse handel" van de Federale Staat' in het kader van de Faciliteit voor herstel en veerkracht.Art. 2. Het in artikel 1 bedoelde bedrag zal worden aangerekend op de basisallocatie 06.41.12. 41.40.42 van de Algemene uitgavenbegroting van het begrotingsjaar 2021.Art. 3. De jaarlijks voorziene subsidie in vereffeningskredieten in 2021 wordt naar de begunstigde overgemaakt op voorlegging van een schuldvordering en bewijsstukken die de materialiteit en het bedrag van de opgegeven lasten staven.In 2022 zal 30% van het jaarlijkse bedrag dat wordt uitgetrokken op de vereffeningskredieten naar de begunstigde worden overgemaakt op voorlegging van een schuldvordering aan het begin van het kalenderjaar. Het saldo van de jaarlijkse subsidie ten laste van de vereffeningskredieten wordt overgemaakt na voorlegging van bewijsstukken die de materialiteit en het bedrag van de opgegeven lasten staven.Art. 4. Uiterlijk binnen drie maanden na de ondertekening van het koninklijk besluit zal een protocol worden gesloten tussen de begunstigde van de subsidie en de Minister bevoegd voor Buitenlandse Zaken, Europese Zaken en Buitenlandse Handel. Dit protocol specificeert de modaliteiten inzake de uitvoering en verslaglegging van de door het ontwerp beoogde activiteiten en de verantwoording van de aangegeven kosten.Art. 5. De Minister bevoegd voor Buitenlandse Zaken, Europese Zaken en Buitenlandse Handel is belast met de uitvoering van dit besluit.Gegeven te Brussel, 14 januari 2022.FILIPVan Koningswege :De Minister van Buitenlandse Zaken, Europese Zaken en Buitenlandse Handel,S. WILMES 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor het kleding- en confectiebedrijf;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 19 februari 2025, gesloten in het Paritair Comité voor het kleding- en confectiebedrijf, betreffende de arbeidsvoorwaarden.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het kleding- en confectiebedrijfCollectieve arbeidsovereenkomst van 19 februari 2025Arbeidsvoorwaarden (Overeenkomst geregistreerd op 20 maart 2025 onder het nummer 192662/CO/109)HOOFDSTUK I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers die ressorteren onder het Paritair Comité voor het kleding- en confectiebedrijf en op de arbeiders en arbeidsters, hierna werknemers genoemd, die zij tewerkstellen, met inbegrip van de huisarbeid(st)ers.HOOFDSTUK II. - Duur van de overeenkomst en verbintenissenArt. 2. Deze collectieve arbeidsovereenkomst wordt van kracht op 1 januari 2025 en houdt op van kracht te zijn op 31 december 2025. Zij volgt op de collectieve arbeidsovereenkomst van 24 november 2023 ter verlenging van de collectieve arbeidsovereenkomst van 18 januari 2023 betreffende de arbeidsvoorwaarden (registratienummer 184908/CO/109).Tijdens de duur van deze collectieve arbeidsovereenkomst waarborgen de ondertekenende partijen de inachtneming van de sociale vrede, hetgeen het volgende inhoudt :1) alle bepalingen betreffende de lonen en arbeidsvoorwaarden worden stipt nageleefd en kunnen niet in betwisting worden gebracht door de werknemers- of de werkgeversorganisaties, noch door de werknemers of de werkgevers;2) de werknemersorganisaties en de werknemers verbinden er zich toe geen eisen te stellen op nationaal noch op gewestelijk vlak, noch op dat van de onderneming, aangezien alle individuele normatieve bepalingen geregeld zijn door onderhavige collectieve arbeidsovereenkomst.HOOFDSTUK III. - Toepassingsdatum van de loonaanpassingenArt. 3. Alle loonaanpassingen in uitvoering van deze collectieve arbeidsovereenkomst worden toegepast vanaf de eerste dag van de maand, in de ondernemingen waar per maand of per halve maand wordt betaald.In de ondernemingen waar de loonperiode op een andere dag dan de eerste dag van de maand begint, worden, indien het aantal kalenderdagen vóór de eerste dag van de maand, kleiner is dan of gelijk is aan het aantal kalenderdagen te rekenen vanaf de eerste dag van de maand, de loonaanpassingen toegekend vanaf de eerste dag van de loonperiode waarin de eerste dag van de maand valt. In het tegengestelde geval worden de loonaanpassingen toegepast vanaf de eerste dag van de loonperiode die een aanvang neemt na de eerste dag van de maand.HOOFDSTUK IV. - LonenA. Lonen toepasselijk op werknemers die tewerkgesteld worden met een arbeidsovereenkomst voor studentenArt. 4. De minimumuurlonen worden toegekend volgens hun leeftijd en functie als volgt : de percentages worden berekend op loongroep 1 voor de studenten die behoren tot de laagste groep van de classificatie of op het loon van de groep voor de tewerkstelling waarvoor de student werd aangeworven.  </t>
         </is>
       </c>
     </row>
@@ -3607,29 +3598,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2025003472</t>
+          <t>2025003107</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>20 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>16 juni 2019. - Koninklijk besluit houdende benoeming van een Gouverneur en van een Plaatsvervangend Gouverneur voor België bij de Aziatische Infrastructuurinvesteringsbank</t>
+          <t>5 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 10 november 2023, gesloten in het Paritair Comité voor het glasbedrijf, betreffende de vervoerskosten (1)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-20&amp;numac_search=2025003472&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003472=99&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025003107&amp;page=1&amp;lg_txt=N&amp;caller=list&amp;2025003107=99&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
           <t xml:space="preserve">
-FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 29 juni 2018 houdende goedkeuring van de statuten en van de resolutie nr. 24 van de Raad van Gouverneurs van de Aziatische Infrastructuurinvesteringsbank ;Gelet op artikel 22, 1 van het Verdrag betreffende de Aziatische Infrastructuurinvesteringsbank ;Op de voordracht van de minister van Buitenlandse Zaken,Hebben Wij besloten en besluiten Wij :Artikel 1. De minister van Financiën treedt op als Gouverneur voor België bij de Aziatische Infrastructuurinvesteringsbank.Art. 2. De heer Ronald De Swert, adviseur-generaal, treedt op als Plaatsvervangend Gouverneur voor België bij de Aziatische Infrastructuurinvesteringsbank.Art. 3. Dit besluit heeft uitwerking met ingang van 1 juli 2019.Art. 4. De minister van Buitenlandse Zaken is belast met de uitvoering van dit besluit.Gegeven te Brussel, 16 juni 2019.FILIPVan Koningswege :De Minister van Buitenlandse Zaken,D. REYNDERS 
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor het glasbedrijf;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 10 november 2023, gesloten in het Paritair Comité voor het glasbedrijf, betreffende de vervoerskosten.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor het glasbedrijfCollectieve arbeidsovereenkomst van 10 november 2023Vervoerskosten (Overeenkomst geregistreerd op 30 november 2023 onder het nummer 184283/CO/115)TITEL I. - ToepassingsgebiedArtikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en arbeiders van de ondernemingen die ressorteren onder het Paritair Comité voor het glasbedrijf.Onder "arbeiders" verstaat men : zowel arbeiders als arbeidsters.Art. 2. Deze collectieve arbeidsovereenkomst is gesloten ter uitvoering van :- de collectieve arbeidsovereenkomst nr. 19ter, gesloten op 5 maart 1991 in de Nationale Arbeidsraad, betreffende de financiële bijdrage van de werkgever in de prijs van het vervoer van de werknemers en meermaals gewijzigd waarvan de laatste keer door de collectieve arbeidsovereenkomst nr. 19/9 van 23 april 2019;- de collectieve arbeidsovereenkomst nr. 164, gesloten op 24 januari 2023 in de Nationale Arbeidsraad, over de fietsvergoeding.TITEL II. - Vervoer per spoorArt. 3. Wat het vervoer georganiseerd door de Nationale Maatschappij der Belgische Spoorwegen, hierna genoemd N.M.B.S., betreft, wordt de tussenkomst van de werkgever in de prijs van het gebruikte vervoerbewijs berekend op basis van de onderstaande tabel met forfaitaire bedragen voor de afstand afgelegd tussen de woonplaats en de arbeidsplaats.Deze tabel wordt aangepast in overeenstemming met de nieuwe forfaitaire tarieven voorzien in de collectieve arbeidsovereenkomst nr. 19/9 voor de tussenkomst van de werkgever in het woon-werkverkeer per spoor, met uitzondering van minstens equivalente forfaitaire tarieven die vroeger in de sector werden voorzien (zie collectieve arbeidsovereenkomst van 21 juni 2017 afgesloten in het kader van het Paritair Comité voor het glasbedrijf (PC 115), met betrekking tot de vervoerkosten).  </t>
         </is>
       </c>
     </row>
@@ -3639,29 +3629,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2025003637</t>
+          <t>2025000798</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>23 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>17 januari 2019. - Koninklijk besluit tot wijziging van het koninklijk besluit van 3 december 2009 houdende regeling van de operationele diensten van de Federale Overheidsdienst Financiën. - Duitse vertaling</t>
+          <t>5 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 11 maart 2024, gesloten in het Paritair Comité voor de bedienden der metaalfabrikatennijverheid, betreffende de wijziging van het sociaal sectoraal pensioenstelsel en van de sectorale technische nota (1)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-23&amp;numac_search=2025003637&amp;page=3&amp;lg_txt=N&amp;caller=list&amp;2025003637=0&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025000798&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025000798=0&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 17 januari 2019 tot wijziging van het koninklijk besluit van 3 december 2009 houdende regeling van de operationele diensten van de Federale Overheidsdienst Financiën (Belgisch Staatsblad van 28 januari 2019).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST FINANZEN17. JANUAR 2019 - Königlicher Erlass zur Abänderung des Königlichen Grundlagenerlasses vom 3. Dezember 2009 über die operativen Dienste des Föderalen Öffentlichen Dienstes FinanzenPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund der Verfassung, der Artikel 37 und 107 Absatz 2;Aufgrund des Königlichen Grundlagenerlasses vom 3. Dezember 2009 über die operativen Dienste des Föderalen Öffentlichen Dienstes Finanzen;Aufgrund der Stellungnahme des Finanzinspektors vom 9. November 2018;Aufgrund der Stellungnahme des Direktionsausschusses des Föderalen Öffentlichen Dienstes Finanzen vom 9. November 2018;Aufgrund der mit Gründen versehenen Stellungnahme des Hohen Konzertierungsausschusses des Sektors II - Finanzen vom 21. Dezember 2018;In der Erwägung, dass der Königliche Grundlagenerlass vom 3. Dezember 2009 über die operativen Dienste des Föderalen Öffentlichen Dienstes Finanzen aktualisiert werden muss;Auf Vorschlag des Ministers der FinanzenHaben Wir beschloßen und erlassen Wir:Artikel 1 - Artikel 4 des Königlichen Grundlagenerlasses vom 3. Dezember 2009 über die operativen Dienste des Föderalen Öffentlichen Dienstes Finanzen, abgeändert durch den Königlichen Erlass vom 4. April 2014, wird wie folgt ersetzt:"Art. 4 - Die Generalverwaltung Einnahme und Beitreibung ist beauftragt mit:1. der Ausführung der Gesetzesbestimmungen über die Einnahme und Beitreibung der in Artikel 2 erwähnten Steuern, Gebühren und gleichgesetzten Steuern. Sie gewährleistet für jede Region die Einnahme und Beitreibung der in Artikel 3 Absatz 1 Nr. 1, 2, 5, 10, 11 und 12 des Sondergesetzes vom 16. Januar 1989 bezüglich der Finanzierung der Gemeinschaften und Regionen erwähnten Steuern nur, insofern die betreffende Region den Dienst in Bezug auf diese Steuern nicht übernommen hat,2. der Zuweisung der zugunsten der Provinzen, Gemeinden und Gemeindeagglomerationen erzielten durchlaufenden Einnahmen, abzüglich der Nachlasse, die für ihre Rechnung in dem Monat ausgezahlt wurden, in dem diese Einnahmen eingenommen wurden,3. der Bearbeitung der Erstattungen der in Artikel 2 erwähnten Steuern, Gebühren und gleichgesetzten Steuern und der Erstattungen in Bezug auf die in den Nummern 6 bis 9 erwähnten Einnahmen,4. der Zahlung der in Nr. 3 erwähnten Erstattungen, die aus rechtlichen oder administrativen Gründen nicht ausgeführt wurden,5. der Zahlung der in Nr. 3 erwähnten Erstattungen, die ausgezahlt wurden, aber auf das Finanzkonto des zentralisierenden Buchhalters zurückgekommen sind,6. der Ausführung von Titel 3 des Registrierungs-, Hypotheken- und Kanzleigebührengesetzbuches in Bezug auf die Einnahme und Beitreibung der Gebühren für die Eintragung in die Liste,7. der Einnahme und Beitreibung aller nichtsteuerlichen Forderungen des Staates, der Gemeinschaften und der Regionen und der Einrichtungen, die von ihnen abhängen, mit der sie durch oder aufgrund einer Gesetzes- oder Verordnungsbestimmung beauftragt ist oder für die keine andere Behörde ausdrücklich für zuständig erklärt wurde.Zu diesen nichtsteuerlichen Forderungen gehören insbesondere:- strafrechtliche Geldbußen und Gerichtskosten,- Vergleiche, die zum Erlöschen der Strafverfolgung führen,- Beitreibungen für Rechnung Dritter,- vom Staat als Schuldforderung festgesetzte Gebühren und gezahlte Vorschüsse in Ausführung der Bestimmungen des Gerichtsgesetzbuches über den weiterführenden juristischen Beistand und die Gerichtskostenhilfe,- als Schuldforderung festgesetzte Gebühren und andere Verfahrenskosten im Rahmen des Verfahrens mit Gerichtskostenhilfe vor dem Staatsrat,- verschiedene und gelegentliche Aktiva,8. der Ausführung der Aufgaben des durch das Gesetz vom 21. Februar 2003 geschaffenen Dienstes für Unterhaltsforderungen,9. allen Befugnissen, die durch eine Gesetzes- oder Verordnungsbestimmung der ehemaligen Mehrwertsteuer-, Registrierungs- und Domänenverwaltung, einem ihrer Rechtsvorgänger oder einem ihrer Beamten zugeteilt worden sind, insofern die betreffenden Angelegenheiten in den Nummern 7 bis 8 des vorliegenden Artikels erwähnt sind."Art. 2 - Artikel 6 desselben Erlasses, abgeändert durch den Königlichen Erlass vom 2. Dezember 2015, wird wie folgt ersetzt:"Art. 6 - Die Generalverwaltung Vermögensdokumentation ist beauftragt mit:1. der Ausführung des Registrierungs-, Hypotheken- und Kanzleigebührengesetzbuches außer Titel 3 hinsichtlich der Einnahme und Beitreibung der Gebühren für die Eintragung in die Liste, des Erbschaftssteuergesetzbuches außer Buch IIbis, des Gesetzbuches der verschiedenen Gebühren und Steuern außer Buch II und ihrer Ausführungserlasse. Sie gewährleistet für jede Region den Dienst in Bezug auf die in Artikel 3 Absatz 1 Nr. 4, 6, 7 und 8 des Sondergesetzes vom 16. Januar 1989 bezüglich der Finanzierung der Gemeinschaften und Regionen erwähnten Steuern nur, insofern die betreffende Region diesen Dienst nicht übernommen hat,2. der Verwaltung des privaten Eigentums des Staates, begrenzt auf die Güter, deren verwaltender Dienst der Verwaltung Vermögensdienste untersteht, einschließlich der Einnahme der mit diesen Gütern verbundenen Domanialerträge,3. der Veräußerung von unbeweglichen Gütern in Ausführung des Gesetzes vom 31. Mai 1923 über die Veräußerung von Domanialliegenschaften und der Veräußerung oder Übertragung von beweglichen oder unbeweglichen Gütern in Anwendung von Artikel 117 des Gesetzes vom 22. Mai 2003 zur Organisation des Haushaltsplans und der Buchführung des Föderalstaates,4. der Ausübung der Befugnisse, die den Erwerbsausschüssen zugeteilt worden sind (insbesondere durch den Königlichen Erlass vom 3. November 1960 über die Ausschüsse für den Erwerb von Immobilien für Rechnung des Staates, der staatlichen Einrichtungen und der Einrichtungen, an denen der Staat ein überwiegendes Interesse hat, Artikel 61 des Programmgesetzes vom 6. Juli 1989 und Artikel 15 des Gesetzes vom 1. April 1971 zur Gründung einer Gebäuderegie),5. der Ausführung von Titel IX des Einkommensteuergesetzbuches 1992 in Bezug auf die Festlegung des Katastereinkommens und die Bewahrung und Fortschreibung der Katasterdokumentation, einschließlich des Katasterplans, sowie die Ausfertigung und Ausstellung von Auszügen oder Kopien und der Ausführung des Königlichen Erlasses vom 30. Juli 2018 über die Anlage und Fortschreibung der Katasterdokumentation und zur Festlegung der Modalitäten für die Ausstellung von Katasterauszügen,6. der Ausführung der Rechtsvorschriften über Zusammenstellung, Fortschreibung und Bewahrung der Vermögensdokumentation, sowohl was bewegliche als auch unbewegliche Vermögensteile betrifft, darin einbegriffen:- die Verfolgung der aufeinanderfolgenden Wechsel der dinglichen Rechte an in Belgien gelegenen unbeweglichen Gütern, auch als Teil der Katasterdokumentation,- die Errichtung und Pflege einer Datenbank der registrierten Mietverträge,- der Dienst der Bekanntmachung von Urkunden und Schriftstücken und der Hypothekenbewahrung (Hypothekengesetz vom 16. Dezember 1851 und Hypothekenbekanntmachung wie in anderen Gesetzen, Dekreten und Ordonnanzen vorgesehen),- der Dienst der Aufbewahrung des Nationalen Pfandregisters (Gesetz vom 11. Juli 2013),- als Übergangsmaßnahme: die Formalitäten in Bezug auf die Verpfändung von Handelsgeschäften, den Diskont und die Verpfändung von Rechnungen (Gesetz vom 25. Oktober 1919), und zwar höchstens bis zum 31. Dezember 2018,7. der Festlegung und Beitreibung der Steuer der Gebietsfremden auf Mehrwerte auf unbewegliche Güter (Einkommensteuergesetzbuch 1992, Artikel 301, und Erlass zur Ausführung des Einkommensteuergesetzbuches 1992, Kapitel 3 Abschnitt 7 Artikel 177),8. der Einnahme des Berufssteuervorabzugs auf Mehrwerte, die von Gebietsfremden im Rahmen ihrer beruflichen Tätigkeit auf unbewegliche Güter verwirklicht werden (Einkommensteuergesetzbuch 1992, Artikel 412bis, und Erlass zur Ausführung des Einkommensteuergesetzbuches 1992, Kapitel 3 Abschnitt 13bis Artikel 210bis und 210ter),9. der Einnahme und Beitreibung der Gebühren in Bezug auf das Verfahren vor dem Staatsrat (Erlass des Regenten vom 23. August 1948 zur Festlegung des Verfahrens vor der Verwaltungsstreitsachenabteilung des Staatsrates, Artikel 71),10. der Ausstellung von Erbscheinen (Zivilgesetzbuch, Art. 1240bis),11. allen Befugnissen, die durch eine Gesetzes- oder Verordnungsbestimmung der ehemaligen Mehrwertsteuer-, Registrierungs- und Domänenverwaltung, einem ihrer Rechtsvorgänger oder einem ihrer Beamten zugeteilt worden sind, insofern die betreffenden Angelegenheiten zur Abteilung Registrierung und Domänen gehören, mit Ausnahme der in Artikel 4 Nr. 6 bis 9 des vorliegenden Erlasses erwähnten Aufgaben."Art. 3 - Artikel 7 desselben Erlasses wird wie folgt ersetzt:"Art. 7 - Die Generalverwaltung Schatzamt ist beauftragt mit:1. der Verwaltung und Koordinierung der Finanzbeziehungen (mit Ausnahme der Steuersachen) auf bilateraler, europäischer und multilateraler Ebene in Bezug auf Wirtschaftspolitik, Handel und Entwicklung,2. der Verwaltung des Schatzamtes des Staates, der Staatsschuld und der Behandlung von Angelegenheiten, die mit den Finanzvorschriften zu tun haben,3. allem, was Zahlungen zu Lasten der Staatskasse betrifft,4. der allgemeinen Buchführung des Staates, vorbehaltlich der Angelegenheiten, die durch das Gesetz dem Föderalen Öffentlichen Dienst Haushalt und Geschäftsführungskontrolle zugewiesen sind,5. der Verwaltung der Hinterlegungs- und Konsignationskasse und des Landesamts für Wertpapiere,6. der Verwaltung der verschiedenen Schutzsysteme für Einlagen und Finanzinstrumente und des Abwicklungsfonds,7. der Verwaltung der Königlichen Münze Belgien,8. der Kontrolle der Finanzinstitute wie durch Gesetz oder Verordnung zugeteilt,9. allen Befugnissen, die durch Gesetz oder Verordnung der ehemaligen Verwaltung des Schatzamtes oder einem ihrer Bediensteten zugeteilt sind."Art. 4 - Artikel 7/1 desselben Erlasses, eingefügt durch den Königlichen Erlass vom 6. September 2018, wird wie folgt ersetzt:"Art. 7/1 - Die Generalverwaltung Strategische Expertise und Unterstützung ist beauftragt mit:1. der Abfassung, Koordinierung, Umsetzung und Überwachung der Rechtsvorschriften in den Angelegenheiten, die in die Zuständigkeit des Föderalen Öffentlichen Dienstes Finanzen fallen,2. der Durchführung von Studien über die Auswirkungen politischer Leitlinien und der Analyse der Ergebnisse der verfolgten Politik,3. der Koordinierung der internationalen Beziehungen des FÖD und dem Abschluss und der Verwaltung von Sitzabkommen in steuerlicher Hinsicht,4. der Bereitstellung von näheren Angaben über die belgischen Steuervorschriften für ausländische Investoren,5. der Verwaltung und Zurverfügungstellung von relevanten Informationen und Informationsquellen."Art. 5 - Artikel 8 desselben Erlasses, abgeändert durch den Königlichen Erlass vom 19. Juli 2013, wird aufgehoben.Art. 6 - Vorliegender Erlass tritt am 1. Februar 2019 in Kraft.Art. 7 - Der für Finanzen zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 17. Januar 2019PHILIPPEVon Königs wegen:Der Vizepremierminister und Minister der FinanzenA. DE CROO
-</t>
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28;Gelet op het verzoek van het Paritair Comité voor de bedienden der metaalfabrikatennijverheid;Op de voordracht van de Minister van Werk,Hebben Wij besloten en besluiten Wij :Artikel 1. Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 11 maart 2024, gesloten in het Paritair Comité voor de bedienden der metaalfabrikatennijverheid, betreffende de wijziging van het sociaal sectoraal pensioenstelsel en van de sectorale technische nota.Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit.Gegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister van Werk,D. CLARINVAL_______Nota(1) Verwijzing naar het Belgisch Staatsblad :Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.BijlageParitair Comité voor de bedienden der metaalfabrikatennijverheidCollectieve arbeidsovereenkomst van 11 maart 2024Wijziging van het sociaal sectoraal pensioenstelsel en van de sectorale technische nota (Overeenkomst geregistreerd op 29 maart 2024 onder het nummer 187003/CO/209)HOOFDSTUK I. - ToepassingsgebiedArtikel 1.  § 1. Deze overeenkomst is van toepassing op de werkgevers, die onder de bevoegdheid vallen van het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid, en op de werknemers met een arbeidsovereenkomst voor bedienden die deze werkgevers tewerkstellen. § 2. Onder "werkgevers" wordt verstaan : zowel de juridische entiteit (op basis van het ondernemingsnummer) als de vestigingseenheden (op basis van het vestigingseenheidnummer) indien de juridische entiteit over meerdere vestigingseenheden beschikt.HOOFDSTUK II. - VoorwerpArt. 2. Deze collectieve arbeidsovereenkomst wijzigt de collectieve arbeidsovereenkomst van 4 juli 2022 (met registratienummer 174721/CO/209) tot wijziging van het sociaal sectoraal pensioenstelsel, het pensioenreglement, het solidariteitsreglement en van de sectorale technische nota.Deze collectieve arbeidsovereenkomst heeft als voorwerp :a) de coördinatie van de basiskenmerken en de regels inzake het beheer en de uitvoering van het sociaal sectoraal pensioenstelsel en de verduidelijking van een aantal aspecten van het sociaal sectoraal pensioenstelsel, zoals vastgelegd in de sectorale collectieve arbeidsovereenkomsten, opgesomd in artikel 18 van deze collectieve arbeidsovereenkomst;b) de wijziging met ingang van 1 september 2023 van de technische nota, opgenomen in bijlage 1 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174121/CO/209.Art. 3. Deze collectieve arbeidsovereenkomst wordt gesloten met toepassing van artikel 10 van de wet van 28 april 2003 betreffende de aanvullende pensioenen en het belastingstelsel van die pensioenen en van sommige aanvullende voordelen inzake sociale zekerheid.De wet van 28 april 2003 zal verder kortweg de "WAP" genoemd worden.Deze collectieve arbeidsovereenkomst wordt gesloten in uitvoering van de beslissing van de representatieve organisaties in het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid en heeft als enig voorwerp de instelling van een sectoraal pensioenstel :-vanaf 1 april 2002 voor de bedienden van de werkgevers, die niet vrijgesteld zijn van de deelname aan het sectoraal pensioenstelsel of geen gebruik hebben gemaakt van "opting-out" (zie hoofdstuk X van deze collectieve arbeidsovereenkomst);- vanaf 1 juli 2007 voor de kaderleden van de werkgevers, die niet vrijgesteld zijn van de deelname aan het sectoraal pensioenstelsel of geen gebruik hebben gemaakt van "opting-out" (zie hoofdstuk X van deze collectieve arbeidsovereenkomst).Met ingang van 1 januari 2017 werd het sectoraal pensioenstelsel omgevormd tot een sociaal sectoraal pensioenstelsel via de invoering van een solidariteitstoezegging. Vanaf 1 januari 2017 geldt de solidariteitstoezegging eveneens voor de bedienden en de kaderleden van de werkgevers die destijds gebruik hebben gemaakt van "opting-out" (zie hoofdstuk X van deze collectieve arbeidsovereenkomst).In artikel 18 van deze collectieve arbeidsovereenkomst wordt de historiek weergegeven van de verschillende sectorale collectieve arbeidsovereenkomsten die in de loop van de jaren binnen het Paritair Comité 209 voor de bedienden van metaalfabrikatennijverheid werden gesloten ter invoering, wijziging en verduidelijking van het sociaal sectoraal pensioenstelsel.HOOFDSTUK III. - Aanduiding van de InrichterArt. 4. Overeenkomstig artikel 3, § 1, 5°  van de WAP, wordt het "Sociaal Fonds voor de Bedienden Metaal-BIS - Fonds voor Bestaanszekerheid", afgekort SFBM-BIS, met ondernemingsnummer KBO 0682.891.282, opgericht op 1 januari 2017 via de collectieve arbeidsovereenkomst van 9 oktober 2017 van het Paritair Comité 209 (met registratienummer 142818/CO/209), aangeduid als Inrichter van het sociaal sectoraal pensioenstelsel.Het SFBM-BIS zal hierna de "Inrichter" genoemd worden.HOOFDSTUK IV. - De pensioentoezeggingArt. 5.  § 1. Het sociaal sectoraal pensioenstelsel bestaat enerzijds uit een pensioentoezegging die is vastgelegd in het pensioenreglement (zie sectie 1 met de bijzondere voorwaarden en de algemene voorwaarden van het groepsverzekeringsreglement, zoals opgenomen in bijlage 2 en bijlage 3 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209), en anderzijds uit een solidariteitstoezegging, die verbonden is aan de pensioentoezegging en is vastgelegd in het solidariteitsreglement (zie sectie 2 met de bijzondere voorwaarden en de algemene voorwaarden van het groepsverzekeringsreglement, opgenomen in bijlage 2 en in bijlage 3 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209). § 2. De pensioentoezegging is van het type vaste bijdragen zonder rendementsgarantie van de Inrichter, doch zonder afbreuk te doen aan het wettelijk minimum rendement opgelegd door de WAP.De sectorale pensioentoezegging moet sinds de aanvang beschouwd worden als één globale pensioentoezegging. De wettelijke minimum rendementsgarantie wordt berekend op de totaliteit van de verworven reserves, opgebouwd vanaf 1 januari 2004.Bij de kapitalisatie van de aanvullende pensioenpremies en de toepassing van de wettelijke minimum rendementsgarantie wordt de horizontale methode toegepast.De pensioentoezegging voorziet in :- de opbouw van een aanvullend pensioenkapitaal, dat overeenkomstig de regels en de modaliteiten van het pensioenreglement wordt uitbetaald aan de aangesloten werknemer op moment van pensionering (in zoverre de betrokken werknemer bij zijn uittreding uit de sector zijn verworven reserves niet heeft overgedragen naar een andere pensioeninstelling). Dit aanvullend pensioenkapitaal kan op verzoek van de aangesloten werknemer worden omgezet in een levenslange pensioenrente;- een overlijdenskapitaal in geval van overlijden van de aangesloten werknemer vóór pensionering, dat gelijk is aan de verworven reserves die de aangesloten werknemer heeft opgebouwd in het sociaal sectoraal pensioenstelsel tot op het moment van zijn overlijden en dat wordt uitbetaald aan de begunstigden van de overleden aangesloten werknemer, overeenkomstig de regels en modaliteiten van het pensioenreglement. § 3. Deze pensioentoezegging is een verbintenis van de Inrichter ten aanzien van de aangesloten werknemers. § 4. De regels en modaliteiten betreffende de pensioentoezegging worden verder vastgelegd in sectie 1 met de bijzondere en de algemene voorwaarden van het groepsverzekeringsreglement (het pensioenreglement), opgenomen in de bijlagen 2 en 3 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209. Het pensioenreglement moet steeds gelezen worden in overeenstemming met deze sectorale collectieve arbeidsovereenkomst, die voorrang heeft.HOOFDSTUK V. - Beheer en aanduiding van de pensioeninstellingArt. 6.  § 1. Het beheer en de uitvoering van de pensioentoezegging werden aanvankelijk door de Inrichter toevertrouwd aan de verzekeringsonderneming Integrale NV. Met ingang van 15 december 2021 heeft de verzekeringsonderneming Monument Assurance Belgium NV, met maatschappelijke zetel te 1210 Sint-Joost-ten-Node, Koning Albert II - Laan, 19 en onder het codenummer 1644 en met ondernemingsnummer 0478.291.162, alle rechten en verplichtingen met betrekking tot de pensioentoezegging overgenomen van Integrale NV. Monument Assurance Belgium NV vervangt met andere woorden Integrale NV met ingang van 15 december 2021 als pensioeninstelling en staat vanaf 15 december 2021 in voor het beheer en de uitvoering van de pensioentoezegging. § 2. De beheers- en werkingsregels die worden afgesproken tussen de Inrichter en Monument Assurance Belgium NV als pensioeninstelling evenals de door Monument Assurance Belgium NV aangerekende beheerskosten worden vastgelegd in een beheers- en verzekeringsovereenkomst, en zijn ook beschreven in de technische nota, opgenomen in bijlage 1 bij deze collectieve overeenkomst.HOOFDSTUK VI. - Verwerving van pensioenrechtenArt. 7. Overeenkomstig artikel 17 van de WAP en het pensioenreglement in sectie 1 met de bijzondere en de algemene voorwaarden van het groepsverzekeringsreglement (zoals bepaald in de bijlagen 2 en 3 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209), kunnen alle werknemers, tewerkgesteld bij een werkgever bedoeld in artikel 1, die niet aangesloten zijn bij een evenwaardig ondernemingspensioenstelsel in het kader van een opting-out of een buiten toepassingsgebied (zie hoofdstuk X van deze collectieve arbeidsovereenkomst), hun recht op een sectoraal aanvullend pensioen laten gelden binnen de voorwaarden van het pensioen- en solidariteitsreglement.HOOFDSTUK VII. - SolidariteitstoezeggingArt. 8.  § 1. De solidariteitstoezegging voorziet, in uitvoering van artikel 43 van de WAP en het koninklijk besluit van 14 november 2003 tot vaststelling van de solidariteitsprestaties verbonden met de sociale aanvullende pensioenstelsels in de volgende solidariteitsprestaties :- de financiering van de opbouw van het aanvullend pensioen tijdens de periodes van tijdelijke werkloosheid in de zin van hoofdstuk II/1 "Regeling van schorsing van de uitvoering van de overeenkomst en regeling van gedeeltelijke arbeid" van titel III van de wet van 3 juli 1978 betreffende de arbeidsovereenkomsten;- de financiering van de opbouw van het aanvullend pensioen tijdens de periodes van arbeidsongeschiktheid ten gevolge van ziekte of ongeval van gemeen recht (met uitzondering van een arbeidsongeval of een beroepsziekte);- de financiering van de opbouw van het aanvullend pensioen tijdens periodes voorafgaand aan het faillissement, de ontbinding en invereffeningstelling, sluiting of de gerechtelijke reorganisatie (in de zin van Boek XX van het Wetboek Economisch Recht) van de onderneming alsook de financiering van de opbouw van het aanvullend pensioen indien het faillissement of invereffeningstelling van de onderneming zich voordeed in de periode sinds 1 januari 2019 en de betrokken failliete/vereffende onderneming in de periode vóór 2019 de werknemers niet had aangesloten aan het sectoraal pensioenstelsel en geen aanvullende pensioenpremies had betaald, met dien verstande dat in alle gevallen deze solidariteitsprestatie slechts voor een maximumperiode van 12 maanden wordt toegekend;- de financiering van een extra uitkering in de vorm van een rente aan de begunstigden in geval van overlijden van de aangesloten werknemer tijdens zijn beroepsloopbaan in de sector vóór de datum van pensionering. § 2. De bedragen van deze solidariteitsprestaties worden door het Paritair Comité 209 bepaald in een aparte collectieve arbeidsovereenkomst. § 3. Deze solidariteitstoezegging is een verbintenis van de Inrichter ten aanzien van de aangesloten werknemers. § 4. De regels en de modaliteiten betreffende de solidariteitstoezegging worden verder vastgelegd in sectie 2 met de bijzondere en de algemene voorwaarden van het groepsverzekeringsreglement (het solidariteitsreglement), opgenomen in de bijlagen 2 en 3 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209. Het solidariteitsreglement moet steeds gelezen worden in overeenstemming met deze sectorale collectieve arbeidsovereenkomst, die voorrang heeft.HOOFDSTUK VIII. - Beheer en aanduiding van de solidariteitsinstellingArt. 9.  § 1. Het beheer en de uitvoering van de solidariteitstoezegging werden aanvankelijk door de Inrichter toevertrouwd aan de verzekeringsonderneming Integrale NV. Met ingang van 15 december 2021 heeft de verzekeringsonderneming Monument Assurance Belgium NV, met maatschappelijke zetel te 1210 Sint-Joost-ten-Node, Koning Albert II-Laan, 19, toegelaten onder het codenummer 1644 en met ondernemingsnummer 0478.291.162, alle rechten en verplichtingen met betrekking tot de solidariteitstoezegging overgenomen van Integrale NV. Monument Assurance Belgium NV vervangt met andere woorden Integrale NV met ingang van 15 december 2021 als solidariteitsinstelling en staat vanaf 15 december 2021 in voor het beheer en de uitvoering van de solidariteitstoezegging. § 2. De beheers- en werkingsregels die worden afgesproken tussen de Inrichter en Monument Assurance Belgium NV als solidariteitsinstelling evenals de door Monument Assurance Belgium NV aangerekende beheerskosten worden vastgelegd in een beheers- en verzekeringsovereenkomst, en zijn ook beschreven in de technische nota, opgenomen in bijlage 1 bij deze collectieve overeenkomst.HOOFDSTUK IX. - Bijdragen en inningsmodaliteitenArt. 10. Algemene principes § 1. In het voordeel van de werknemers, die rechten kunnen laten gelden met betrekking tot het sociaal sectoraal pensioenstelsel, zal het "Sociaal Fonds voor de Bedienden Metaal - Fonds voor Bestaanszekerheid", afgekort "SFBM", met ondernemingsnummer KBO 0541.831.805, opgericht op 1 januari 2014 via de collectieve arbeidsovereenkomst van 4 november 2013 van het Paritair Comité 209 (met registratienummer 118373/CO/209), met ingang van 1 januari 2019 zowel de aanvullende pensioenpremies als de solidariteitsbijdragen innen ter financiering van het sociaal sectoraal pensioenstelsel. § 2. Het SFBM int de aanvullende pensioenpremies en de solidariteitsbijdragen in naam en voor rekening van de Inrichter bij alle werkgevers op wie het sociaal sectoraal pensioenstelsel in haar geheel van toepassing is.Het SFBM int ook de solidariteitsbijdragen in naam en voor rekening van de Inrichter bij de werkgevers op wie enkel de solidariteitstoezegging van toepassing is (omdat ze voor wat betreft de pensioentoezegging genieten van een "opting-out").De premies tot financiering van de pensioentoezegging en de bijdragen tot financiering van de solidariteitstoezegging worden geïnd onder de vorm van procentuele kwartaalbijdragen.Dit betekent dat de aanvullende pensioenpremies en de solidariteitsbijdragen door het SFBM driemaandelijks worden geïnd bij de betrokken werkgevers op basis van de DmfA-aangiftes.Daarnaast int het SFBM bij de werkgever die de aangeslotene tewerkstelt op het moment van zijn uittreding, pensionering of overlijden, in naam en voor rekening van de Inrichter, de nodige premies die nodig zijn voor de aanzuivering van de tekorten van de gewaarborgde pensioenreserves alsook van de tekorten ten opzichte van de wettelijke rendementsgarantie, zoals bepaald in de artikelen 24 en 30 van de WAP. Dit omvat ook dat het SFBM, in naam en voor rekening van de Inrichter, de achterstallige pensioenpremies (verhoogd met een bijkomende administratiekost) int bij de werkgevers, die in het verleden nagelaten hebben om hun bedienden aan te sluiten bij het sociaal sectoraal pensioenstelsel en de nodige pensioenpremies te betalen, zoals bepaald in de sectorale collectieve arbeidsovereenkomsten met betrekking tot het sociaal sectoraal pensioenstelsel en uitgewerkt in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst (en in de vorige versies van de technische nota). § 3. De eventuele taksen en sociale bijdragen zijn ten laste van de werkgever en komen bovenop de aanvullende pensioenpremies.Het SFBM int, in naam en voor rekening van de Inrichter, bij de werkgevers de sociale bijdragen, met inbegrip van de eventuele Wijninckxbijdrage, zoals bedoeld in artikel 38, §  3duodecies en § 3terdecies van de wet van 29 juni 1981, die verschuldigd zijn op de aanvullende pensioenpremies en stort deze door aan de Rijksdienst voor Sociale Zekerheid (RSZ). § 4. Het percentage van de aanvullende pensioenpremies en de solidariteitsbijdragen, alsook de modaliteiten van de inning worden vastgelegd in de sectorale collectieve arbeidsovereenkomsten tot vaststelling van de statuten van het SFBM, en in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst. § 5. De concrete afspraken omtrent de inning en de doorstorting van deze aanvullende pensioenpremies en solidariteitsbijdragen worden verder uitgewerkt in een beheersovereenkomst tussen het SFBM en de Inrichter. Omdat het SFBM bij de inning ondersteuning krijgt van het "Fonds voor bestaanszekerheid van de metaalverwerkende nijverheid", met ondernemingsnummer KBO 0855.690.646, (opgericht bij beslissing van 13 januari 1965 van het Nationaal Paritair Comité 111, algemeen verbindend verklaard bij koninklijk besluit van 10 februari 1965), afgekort "FBZMN", is het FBZMN ook partij bij deze beheersovereenkomst. § 6. De praktische aspecten van de inning en de doorstorting van de aanvullende pensioenpremies en solidariteitsbijdragen naar de pensioen- en solidariteitsinstelling worden vastgelegd in een beheersovereenkomst tussen de Inrichter, het SFBM en Monument Assurance Belgium NV.Art. 11. Financiering van de pensioentoezegging § 1. De financiering van de pensioentoezegging zal gebeuren via een patronale pensioenpremie, die gelijk is aan een percentage van het referentieloon van de aangesloten werknemers. Het referentieloon is gelijk aan het bij de RSZ aangegeven brutojaarloon, exclusief het enkel en het dubbel vakantiegeld. § 2. Met ingang van 1 januari 2020 bedraagt de patronale pensioenpremie 2,29 pct. van het referentieloon.Meer concreet, betreft het 2,29 pct. op basis van de brutoloonmassa, waarbij de brutoloonmassa gelijk is aan de som van 1/1,08 op DmfA-bezoldigingscode 1 met de DmfA-bezoldigingscodes 2, 3, 4. § 3. De aanvullende pensioenpremies worden per kwartaal geïnd door het SFBM.Binnen de 4 maanden volgend op het einde van het betreffende kwartaal stort het SFBM de aanvullende pensioenpremies, na inhouding van de administratiekosten voor de inning ervan, in naam en voor rekening van de Inrichter, door naar de pensioeninstelling (Monument Assurance Belgium NV).Met ingang van 1 januari 2020 houdt het SFBM bij elk verlopen kwartaal een forfaitair percentage in op de geïnde aanvullende pensioenpremies. Dit forfaitair kostenpercentage wordt jaarlijks bepaald door de raad van bestuur van de Inrichter. Voor 2023 en 2024 is dit forfaitair kostenpercentage vastgelegd op 1 pct. van de geïnde aanvullende pensioenpremies.Art. 12. Financiering van de solidariteitstoezegging § 1. De financiering van de solidariteitstoezegging zal gebeuren via een solidariteitsbijdrage, die gelijk is aan een percentage van het referentieloon van de aangesloten werknemers. Het referentieloon is gelijk aan het bij de RSZ aangegeven brutojaarloon, exclusief het enkel en het dubbel vakantiegeld. § 2. Met ingang van 1 januari 2020 bedraagt de solidariteitsbijdrage 0,10 pct. van het referentieloon.Meer concreet, betreft het 0,10 pct. op basis van de brutoloonmassa, waarbij de brutoloonmassa gelijk is aan de som van 1/1,08 op DmfA-bezoldigingscode 1 met de DmfA-bezoldigingscodes 2, 3, 4. § 3. De solidariteitsbijdragen worden per kwartaal geïnd door het SFBM.Binnen de 4 maanden volgend op het einde van het betreffende kwartaal stort het SFBM 95 pct. en vanaf 1 januari 2021 96 pct. van de geïnde solidariteitsbijdragen, in naam en voor rekening van de Inrichter door naar de solidariteitsinstelling. De overige 5 pct. en vanaf 1 januari 2021 de overige 4 pct. van de geïnde solidariteitsbijdragen worden tegelijkertijd doorgestort naar de Inrichter ter dekking van de administratiekosten voor de inning van de solidariteitsbijdragen en diens algemene werkingskosten. Deze bepalingen zijn eveneens van toepassing indien de Inrichter (of het SFBM in naam en voor rekening van de Inrichter) nog bedragen zou ontvangen via het Fonds van Sluiting van Onderneming (FSO), de curator, de vereffenaar(s) of van de onderneming in gerechtelijke reorganisatie voor aangeslotenen voor wie de opbouw van het aanvullend pensioen tijdens periodes voorafgaand aan het faillissement, de ontbinding en invereffeningstelling, sluiting of de gerechtelijke reorganisatie (in de zin van Boek XX van het Wetboek Economisch Recht) van de onderneming reeds via de solidariteitspensioentoezegging gebeurde.HOOFDSTUK X. - Buiten toepassingsgebied en mogelijkheid tot opting-outArt. 13. Buiten toepassingsgebied § 1. Werkgevers, die voor hun bedienden een aanvullend pensioenstelsel op ondernemingsniveau hebben ingericht vóór 11 juni 2001, dat zonder onderbreking nog steeds van toepassing is en minstens evenwaardig is aan het sectoraal aanvullend pensioenstelsel, moeten niet deelnemen aan het sociaal sectoraal pensioenstelsel en worden bijgevolg uitgesloten uit het toepassingsgebied van het sociaal sectoraal pensioenstelsel in zoverre ze voldoen aan de jaarlijkse attesteringsplicht overeenkomstig § 3 van dit artikel.Werkgevers, die voor hun kaderleden een aanvullend pensioenstelsel op ondernemingsniveau hebben ingericht vóór 31 december 2006, dat zonder onderbreking nog steeds van toepassing is en minstens evenwaardig is aan het sectoraal pensioenstelsel, moeten niet deelnemen aan het sociaal sectoraal pensioenstelsel en worden bijgevolg uitgesloten uit het toepassingsgebied van het sociaal sectoraal pensioenstelsel in zoverre zij voldoen aan de jaarlijkse attesteringsplicht overeenkomstig § 3 van dit artikel.De vrijstelling van deelname aan het sociaal sectoraal pensioenstelsel wegens buiten toepassingsgebied geldt zowel voor de pensioentoezegging als voor de solidariteitstoezegging. § 2. De voorwaarden en modaliteiten omtrent het "buiten toepassingsgebied" worden verder vastgelegd in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst. § 3. Er geldt een jaarlijkse attesteringsplicht voor de werkgevers bedoeld in § 1 van dit artikel, waarvan de modaliteiten wordt vastgelegd in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst.Art. 14. Opting-out § 1. Werkgevers, die vóór 1 april 2011 op basis van de toepasselijke sectorale collectieve arbeidsovereenkomsten binnen het Paritair Comité 209, gebruik hebben gemaakt van de geboden mogelijkheid tot opting-out (dit wil zeggen de mogelijkheid om voor een deel of het geheel van de werknemers de uitvoering van sectoraal pensioenstelsel zelf te organiseren in een pensioenstelsel op het niveau van de onderneming, zoals bepaald in artikel 9 van de WAP), kunnen de opting-out verderzetten, op voorwaarde dat ze blijven voldoen aan de voorwaarden en modaliteiten met inbegrip van de jaarlijkse attesteringsplicht, zoals vastgelegd in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst. § 3. Werkgevers die vóór 1 april 2011 gebruik hebben gemaakt van de mogelijkheid tot opting-out, zijn wel verplicht om zich aan te sluiten bij de solidariteitstoezegging die werd ingevoerd door de Inrichter binnen de sector en dit voor alle werknemers, die aangesloten zijn bij het pensioenstelsel op het niveau van de onderneming.Art. 15. Reorganisaties - nieuwe ondernemingenIn het kader van de overgang van een onderneming, vestiging of deel van een onderneming of een vestiging, als gevolg van een conventionele overdracht of een fusie, splitsing of andere transactie in de zin van de collectieve arbeidsovereenkomst nr. 32bis van 7 juni 1985 betreffende het behoud van de rechten van de werknemers bij wijziging van werkgever ingevolge de overgang van ondernemingen krachtens overeenkomst en tot regeling van de rechten van de werknemers die overgenomen worden bij overname van activa na faillissement of gerechtelijk akkoord door boedelafstand (zoals nadien gewijzigd), kan de werkgever voor de overgenomen of bij de reorganisatie betrokken werknemers eveneens vrijgesteld worden van deelname aan het sociaal sectoraal pensioenstelsel, mits voldaan is aan de voorwaarden voor opting-out (hoofdstuk B) of van buiten toepassingsgebied (hoofdstuk C), zoals voorzien in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst.Indien een werkgever ten gevolge van een wijziging van paritair comité onder de bevoegdheid valt van het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid, kan de werkgever voor de betrokken werknemers eveneens vrijgesteld worden van deelname aan het sociaal sectoraal pensioenstelsel, mits voldaan is aan de voorwaarden van buiten toepassingsgebied (hoofdstuk C) op het moment dat de werkgever onder de bevoegdheid van het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid valt, zoals voorzien in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst.Indien de onderneming pas op moment van of na de inwerkingtreding van deze collectieve arbeidsovereenkomst is opgericht en onder de bevoegdheid valt van het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid, kan de werkgever voor de betrokken werknemers eveneens vrijgesteld worden van deelname aan het sociaal sectoraal pensioenstelsel indien deze vanaf de oprichting reeds een evenwaardig ondernemingsplan heeft en mits voldaan is aan de voorwaarden van buiten toepassingsgebied (hoofdstuk C) op het moment van de oprichting, zoals voorzien in de technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst.Art. 16. Alle werknemers van een werkgever, bedoeld in artikel 1 van deze collectieve arbeidsovereenkomst, die niet aangesloten zijn bij een ander evenwaardig ondernemingspensioenstelsel in het kader van een opting-out of een buiten toepassingsgebied, zijn verplicht aangesloten aan het sectoraal sociaal pensioenstelsel.HOOFDSTUK XI. - Wijziging van het pensioenreglement, solidariteitsreglement en de technische notaArt. 17.  § 1. Het reglement van de groepsverzekering die het sociaal sectoraal pensioenstelsel uitvoert, zoals opgenomen in bijlage 2 en bijlage 3 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209 blijft verder van toepassing. § 2. De technische nota, opgenomen in bijlage 1 bij de collectieve arbeidsovereenkomst van 4 juli 2022 met registratienummer 174721/CO/209, wordt met ingang van 1 september 2023 gewijzigd door de technische nota opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst. § 3. De technische nota, opgenomen in bijlage 1 bij deze collectieve arbeidsovereenkomst, maakt integraal deel uit van deze collectieve arbeidsovereenkomst.HOOFDSTUK XII. - Vervanging van de collectieve arbeidsovereenkomstArt. 18.  § 1. Deze collectieve arbeidsovereenkomst vervangt vanaf 1 september 2023 de collectieve arbeidsovereenkomst van 4 juli 2022 tot wijziging van het sociaal sectoraal pensioenstelsel, het pensioenreglement en het solidariteitsreglement en van de sectorale technische nota (met registratienummer 174721/CO/209), met uitzondering van de bijlagen 2 en 3, die ongewijzigd behouden blijven. § 2. Deze collectieve arbeidsovereenkomst coördineert de basiskenmerken en de regels inzake het beheer en uitvoering van het sociaal sectoraal pensioenstelsel en verduidelijkt een aantal aspecten van het sociaal sectoraal pensioenstelsel, zoals vastgelegd in de sectorale collectieve arbeidsovereenkomsten, die binnen het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid werden gesloten met betrekking tot het sociaal sectoraal pensioenstelsel, zoals onder meer :- de collectieve arbeidsovereenkomst van 11 juni 2001 (met registratienummer 57918/CO/209) betreffende het nationaal akkoord 2001-2002, gesloten in het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid;- de collectieve arbeidsovereenkomst van 17 december 2001 (met registratienummer 60649/CO/209) betreffende de uitvoering van artikel 4, §§ 2, 3 en 4 van de collectieve arbeidsovereenkomst van 11 juni 2001 betreffende het nationaal akkoord 2001-2002;- de collectieve arbeidsovereenkomst van 21 maart 2002 (met registratienummer 62481/CO/209) betreffende de uitvoering van hoofdstuk II, artikel 4, §§ 1 en 5 van de collectieve arbeidsovereenkomst van 11 juni 2001 betreffende het nationaal akkoord 2001-2002;- de collectieve arbeidsovereenkomst van 8 maart 2004 (met registratienummer 70726/CO/209) tot wijziging van de collectieve arbeidsovereenkomst van 21 maart 2002 betreffende de uitvoering van hoofdstuk II, artikel 4, §§ 1 en 5 van de collectieve arbeidsovereenkomst van 11 juni 2001 betreffende het nationaal akkoord 2001-2002;- de collectieve arbeidsovereenkomst van 18 januari 2007 (met registratienummer 82045/CO/209) gesloten in uitvoering van het nationaal akkoord 2007-2008, tot wijziging en vervanging van de collectieve arbeidsovereenkomst van 21 maart 2002 tot uitvoering van hoofdstuk II, artikel 4, §§ 1 en 5 van de collectieve arbeidsovereenkomst van 11 juni 2001 betreffende het nationaal akkoord 2001-2002 (sectoraal aanvullend pensioen);- de collectieve arbeidsovereenkomst van 24 september 2007 (met registratienummer 85840/CO/209) betreffende het nationaal akkoord 2007-2008, gesloten in het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid;- de collectieve arbeidsovereenkomst van 6 juli 2009 (met registratienummer 95215/CO/209) betreffende het nationaal akkoord 2009-2010, gesloten in het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid;- de collectieve arbeidsovereenkomst van 20 december 2010 (met registratienummer 102881/CO/209) tot wijziging van artikel 3, § 2b van het nationaal akkoord 2009-2010;- de collectieve arbeidsovereenkomst van 20 december 2010 (met registratienummer 102882/CO/209) tot uitvoering van artikel 3, § 4, 4de alinea van het nationaal akkoord 2009-2010;- de collectieve arbeidsovereenkomst van 4 juli 2011 (met registratienummer 105349/CO/209) betreffende het nationaal akkoord 2011-2012, gesloten in het Paritair Comité 209 voor de bedienden van de metaalfabrikatennijverheid;- de collectieve arbeidsovereenkomst van 5 maart 2012 (met registratienummer 109294/CO/209) tot wijziging van het reglement van de groepsverzekering die het sectorale pensioenstelsel uitvoert en van de sectorale technische nota;- de collectieve arbeidsovereenkomst van 10 juli 2013 (met registratienummer 116303/CO/209) tot wijziging van het reglement van de groepsverzekering die het sectorale pensioenstelsel uitvoert en van de sectorale technische nota;- de collectieve arbeidsovereenkomst van 4 november 2013 (met registratienummer 118405/CO/209) tot verhoging van het bedrag van de pensioenbijdragen;- de collectieve arbeidsovereenkomst van 4 juli 2016 (met registratienummer 134523/CO/209) tot wijziging van het reglement van de groepsverzekering die het sectorale pensioenstelsel uitvoert en van de sectorale technische nota, en opheffing van het nivelleringsfonds;- de collectieve arbeidsovereenkomst van 13 november 2017 (met registratienummer 144393/CO/209) tot wijziging van het reglement van de groepsverzekering die het sectorale pensioenstelsel uitvoert en van de sectorale technische nota;- de collectieve arbeidsovereenkomst van 11 december 2017 (met registratienummer 144375/CO/209) betreffende de solidariteitsuitkeringen;- de collectieve arbeidsovereenkomst van 9 december 2019 (met registratienummer 157451/CO/209) tot wijziging van het reglement van de groepsverzekering die het sociale sectorale pensioenstelsel uitvoert en van de sectorale technische nota en tot verduidelijking van een aantal aspecten van het sectorale pensioenstelsel;- de collectieve arbeidsovereenkomst van 14 december 2020 tot wijziging van het sociaal sectoraal pensioenstelsel, het pensioenreglement, het solidariteitsreglement en van de sectorale technische nota (met registratienummer 162728/CO/209);- de collectieve arbeidsovereenkomst van 4 juli 2022 tot wijziging van het sociaal sectoraal pensioenstelsel, het pensioenreglement, het solidariteitsreglement en van de sectorale technische nota (met registratienummer 17</t>
         </is>
       </c>
     </row>
@@ -3671,28 +3660,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2025003636</t>
+          <t>2025201258</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>23 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6 september 2018. - Koninklijk besluit tot wijziging van het koninklijk besluit van 3 december 2009 houdende regeling van de operationele diensten van de Federale Overheidsdienst Financiën. - Duitse vertaling</t>
+          <t>5 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 23 januari 2025, gesloten in het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap, betreffende het statuut van de zonale busbegeleiders (1)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-23&amp;numac_search=2025003636&amp;page=3&amp;lg_txt=N&amp;caller=list&amp;2025003636=1&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025201258&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025201258=1&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 6 september 2018 tot wijziging van het koninklijk besluit van 3 december 2009 houdende regeling van de operationele diensten van de Federale Overheidsdienst Financiën (Belgisch Staatsblad van 19 september 2018).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST FINANZEN6. SEPTEMBER 2018 - Königlicher Erlass zur Abänderung des Königlichen Grundlagenerlasses vom 3. Dezember 2009 über die operativen Dienste des Föderalen Öffentlichen Dienstes FinanzenPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund der Verfassung, des Artikels 37;Aufgrund des Königlichen Grundlagenerlasses vom 3. Dezember 2009 über die operativen Dienste des Föderalen Öffentlichen Dienstes Finanzen;Aufgrund der Stellungnahme des Direktionsausschusses des Föderalen Öffentlichen Dienstes Finanzen vom 29. September 2017;Aufgrund der Stellungnahme des Finanzinspektors vom 10. November 2017;Aufgrund der mit Gründen versehenen Stellungnahme des Hohen Konzertierungsausschusses des Sektors II - Finanzen vom 10. Juli 2018;Auf Vorschlag des Ministers der FinanzenHaben Wir beschloßen und erlassen Wir:Artikel 1 - Artikel 1 Absatz 1 des Königlichen Grundlagenerlasses vom 3. Dezember 2009 über die operativen Dienste des Föderalen Öffentlichen Dienstes Finanzen wird wie folgt abgeändert:1. Im einleitenden Satz wird das Wort "sechs" durch das Wort "sieben" ersetzt.2. Der Absatz wird durch eine Nr. 7 mit folgendem Wortlaut ergänzt:"7. Generalverwaltung Strategische Expertise und Unterstützung."Art. 2 - In Kapitel 1 desselben Erlasses, abgeändert durch die Königlichen Erlasse vom 19. Juli 2013, 4. April 2014 und 2. Dezember 2015, wird ein Artikel 7/1 mit folgendem Wortlaut eingefügt:"Art. 7/1 - Die Generalverwaltung Strategische Expertise und Unterstützung ist insbesondere beauftragt mit:1. der Abfassung, Koordinierung, Umsetzung und Überwachung der Rechtsvorschriften in den Angelegenheiten, die in die Zuständigkeit des Föderalen Öffentlichen Dienstes Finanzen fallen,2. der Durchführung von Studien über die Auswirkungen politischer Leitlinien und der Analyse der Ergebnisse der verfolgten Politik,3. der Umsetzung einer integralen Risikopolitik und einer koordinierten Zielgruppenstrategie,4. der Verwaltung und Zurverfügungstellung von relevanten Informationen und Informationsquellen."Art. 3 - Vorliegender Erlass tritt am ersten Tag des Monats nach Ablauf einer Frist von zehn Tagen, die am Tag nach seiner Veröffentlichung im Belgischen Staatsblatt beginnt, in Kraft.Art. 4 - Der für Finanzen zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 6. September 2018PHILIPPEVon Königs wegen:Der Minister der FinanzenJ. VAN OVERTVELDT
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 23 januari 2025, gesloten in het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap, betreffende het statuut van de zonale busbegeleiders. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 5 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969. Bijlage Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap Collectieve arbeidsovereenkomst van 23 januari 2025 Statuut van de zonale busbegeleiders (Overeenkomst geregistreerd op 31 januari 2025 onder het nummer 191704/CO/152.01) HOOFDSTUK I. - Toepassingsgebied Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en op de busbegeleiders en busbegeleidsters, hierna "busbegeleider" genoemd, die ressorteren onder het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap, en die behoren tot het zonaal leerlingenvervoer, zoals gedefinieerd bij wet van 15 juli 1983 houdende de oprichting van de Nationale Dienst voor Leerlingenvervoer. HOOFDSTUK II. - Duur van contracten Art. 2. Deze collectieve arbeidsovereenkomst is afgesloten ter verbetering van het statuut van de busbegeleider zoals gedefinieerd in artikel 1. Alle zonale busbegeleiders krijgen een arbeidsovereenkomst aangeboden van ten minste tien maanden met ingang van 1 september 2008. Met uitzondering van de jaarlijkse betaalde vakantiedagen worden volgende dagen doorbetaald zonder dat prestaties dienen geleverd te worden : - de schoolvakantiedagen die vallen tussen 1 september en 30 juni; - de facultatieve vrije dagen bepaald door de school, de inrichtende macht of het Vlaams Ministerie van Onderwijs; - de dagen waarop de school voorziet in een alternatief lessenpakket en er zodoende geen leerlingenvervoer nodig is. Art. 3. Deze collectieve arbeidsovereenkomst doet geen afbreuk aan de bestaande loon- en arbeidsvoorwaarden.Art. 4. Tijdens de maanden juli en augustus kan de busbegeleider aanspraak maken op een bestaanszekerheidsvergoeding indien voldaan is aan de voorwaarden zoals vastgelegd bij collectieve arbeidsovereenkomst van 28 september 2016 betreffende de bestaanszekerheidsvergoeding. HOOFDSTUK III. - Geldigheidsduur Art. 5. Deze collectieve arbeidsovereenkomst vervangt de collectieve arbeidsovereenkomst van 28 september 2016 betreffende het statuut van de zonale busbegeleiders (overeenkomst geregistreerd op 29 november 2016 onder het nummer 136155/CO/152.01) en treedt in werking op datum van sluiting en is gesloten voor onbepaalde duur. Elk van de partijen kan ze opzeggen mits een opzeggingstermijn van drie maanden. Deze opzegging wordt bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Subcomité voor de gesubsidieerde inrichtingen van het vrij onderwijs van de Vlaamse Gemeenschap. Art. 6. Overeenkomstig artikel 14 van de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités worden, voor wat betreft de ondertekening van deze collectieve arbeidsovereenkomst, de handtekeningen van de personen die deze aangaan namens de werknemersorganisaties enerzijds en namens de werkgeversorganisaties anderzijds, vervangen door de, door de voorzitter en de secretaris ondertekende en door de leden goedgekeurde notulen van de vergadering. Gezien om te worden gevoegd bij het koninklijk besluit van 5 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -3703,28 +3692,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2025003936</t>
+          <t>2025201248</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>28 mei 2025</t>
+          <t>19 mei 2025</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>31 januari 2018. - Koninklijk besluit tot wijziging van het koninklijk besluit van 20 november 2009 betreffende de erkenning van de dierenartsen. - Duitse vertaling</t>
+          <t>5 mei 2025. - Koninklijk besluit waarbij algemeen verbindend wordt verklaard de collectieve arbeidsovereenkomst van 10 februari 2025, gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, tot vaststelling van het percentage van de bijdragen tot bijkomende financiering van de tweede pensioenpijler voor het jaar 2025 (1)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-28&amp;numac_search=2025003936&amp;page=3&amp;lg_txt=N&amp;caller=list&amp;2025003936=2&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-19&amp;numac_search=2025201248&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025201248=2&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 31 januari 2018 tot wijziging van het koninklijk besluit van 20 november 2009 betreffende de erkenning van de dierenartsen (Belgisch Staatsblad van 14 februari 2018).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST VOLKSGESUNDHEIT, SICHERHEIT DER NAHRUNGSMITTELKETTE UND UMWELT31. JANUAR 2018 - Königlicher Erlass zur Abänderung des Königlichen Erlasses vom 20. November 2009 über die Zulassung von TierärztenPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund des Gesetzes vom 28. August 1991 über die Ausübung der Veterinärmedizin, des Artikels 4 Absatz 4, zuletzt abgeändert durch das Gesetz vom 19. März 2014;Aufgrund des Königlichen Erlasses vom 20. November 2009 über die Zulassung von Tierärzten;Aufgrund der Stellungnahme des Finanzinspektors vom 5. Dezember 2016;Aufgrund der Konzertierung zwischen den Regionalregierungen und der Föderalbehörde vom 1. April 2016;Aufgrund des Gutachtens Nr. 61.251/3 des Staatsrates vom 16. Mai 2017, abgegeben in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Auf Vorschlag des Ministers der Volksgesundheit und des Ministers der LandwirtschaftHaben Wir beschloßen und erlassen Wir:Artikel 1 - In Artikel 2 des Königlichen Erlasses vom 20. November 2009 über die Zulassung von Tierärzten, ersetzt durch den Königlichen Erlass vom 13. Juni 2014, wird § 1 durch eine Nr. 6 mit folgendem Wortlaut ergänzt:"6. Ihre Sprachkenntnisse einer Landessprache sind mindestens auf dem europäischen Niveau B1, wenn die Muttersprache des Tierarztes keine der Landessprachen ist oder wenn die Sprache, in der die Berufsqualifikation, die zur Ausübung der Veterinärmedizin berechtigt, erworben wurde, keine der Landessprachen ist."Art. 2 - Der für Volksgesundheit zuständige Minister und der für Landwirtschaft zuständige Minister sind, jeder für seinen Bereich, mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 31. Januar 2018PHILIPPEVon Königs wegen:Die Ministerin der VolksgesundheitM. DE BLOCKDer Minister der LandwirtschaftD. DUCARME 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 5 december 1968 betreffende de collectieve arbeidsovereenkomsten en de paritaire comités, inzonderheid op artikel 28; Gelet op het verzoek van het Paritair Comité voor de gezondheidsinrichtingen en -diensten; Op de voordracht van de Minister van Werk, Hebben Wij besloten en besluiten Wij : Artikel 1.  Algemeen verbindend wordt verklaard de als bijlage overgenomen collectieve arbeidsovereenkomst van 10 februari 2025, gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, tot vaststelling van het percentage van de bijdragen tot bijkomende financiering van de tweede pensioenpijler voor het jaar 2025. Art. 2. De minister bevoegd voor Werk is belast met de uitvoering van dit besluit. Gegeven te Brussel, 5 mei 2025. FILIPVan Koningswege : De Minister van Werk, D. CLARINVAL _______Nota(1) Verwijzing naar het Belgisch Staatsblad : Wet van 5 december 1968, Belgisch Staatsblad van 15 januari 1969.Bijlage Paritair Comité voor de gezondheidsinrichtingen en -diensten Collectieve arbeidsovereenkomst van 10 februari 2025 Vaststelling van het percentage van de bijdragen tot bijkomende financiering van de tweede pensioenpijler voor het jaar 2025 (Overeenkomst geregistreerd op 20 maart 2025 onder het nummer 192673/CO/330) Artikel 1. Deze collectieve arbeidsovereenkomst is van toepassing op de werkgevers en de werknemers die ressorteren onder het Paritair Comité voor de gezondheidsinrichtingen en -diensten en die behoren tot de onderstaande sectoren onder de bevoegdheid van de Vlaamse Gemeenschap en/of de Vlaamse Gemeenschapscommissie van het Brusselse Hoofdstedelijk Gewest : - de categorale ziekenhuizen (dit is elk ziekenhuis dat uitsluitend beschikt over een G-dienst (revalidatie van geriatrische patiënten) en/of een Sp-dienst (gespecialiseerde dienst voor behandeling en revalidatie) als vermeld in artikel 5, § 1, I, eerste lid, 3° en 4° van de bijzondere wet van 8 augustus 1980 tot hervorming der instellingen); - de rusthuizen voor bejaarden, de rust- en verzorgingstehuizen, de dagverzorgingscentra, de assistentiewoningen, de centra voor kortverblijf voor bejaarden; - de psychiatrische verzorgingstehuizen; - de initiatieven voor beschut wonen; - de revalidatiecentra met uitsluiting van de instellingen waarmee het Verzekeringscomité van het RIZIV op voorstel van het College van geneesheren-directeurs, in uitvoering van artikel 22, 6° van de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen gecoördineerd op 14 juli 1994, een overeenkomst heeft gesloten en die niet vallen onder de toepassing van artikel 5, § 1, I, 5° van de bijzondere wet van 8 augustus 1980 tot hervorming van de instellingen. Onder "werknemers" wordt verstaan : het mannelijk en vrouwelijk werklieden- en bediendepersoneel. Art. 2. In toepassing van artikelen 3 en 4 van de collectieve arbeidsovereenkomst van 12 november 2018 tot financiering van de tweede pensioenpijler en de jaarlijkse vaststelling van het percentage van de bijdragen (registratienummer 149441/CO/330), gesloten in het Paritair Comité voor de gezondheidsinrichtingen en -diensten, wordt het percentage van de bijdragen voor het jaar 2025 op jaarbasis bepaald als volgt : per kwartaal 0,22 pct. van het brutobedrag van de bezoldigingen, vóór inhouding van de persoonlijke socialezekerheidsbijdragen. De inning van deze bijdragen geschiedt voor het jaar 2025 als volgt : - geen inning in het eerste en het tweede kwartaal; - 0,44 pct. van het brutobedrag van de bezoldigingen, vóór inhouding van de persoonlijke socialezekerheidsbijdragen, tijdens het derde en het vierde kwartaal. Art. 3. Deze collectieve arbeidsovereenkomst gaat in vanaf de datum van ondertekening. Zij is gesloten voor onbepaalde tijd en kan worden opgezegd door elk van de partijen, mits een opzeggingstermijn van zes maanden, bij een ter post aangetekende brief gericht aan de voorzitter van het Paritair Comité voor de gezondheidsinrichtingen en -diensten die alle ondertekenende organisaties hiervan in kennis stelt. De opzeggingstermijn begint te lopen vanaf de eerste dag van de maand die volgt op de datum waarop de voorzitter van het Paritair Comité voor de gezondheidsinrichtingen en -diensten de betrokken organisaties in kennis heeft gesteld van de opzegging. Gezien om te worden gevoegd bij het koninklijk besluit van 5 mei 2025. De Minister van Werk, D. CLARINVAL 
 </t>
         </is>
       </c>
@@ -3735,28 +3724,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2025003563</t>
+          <t>2025003811</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>15 mei 2025</t>
+          <t>20 mei 2025</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>30 augustus 2016. - Koninklijk besluit houdende maatregelen betreffende de bestrijding van de vesiculaire varkensziekte. - Duitse vertaling</t>
+          <t>5 mei 2025. - Koninklijk besluit houdende toekenning van een toelage aan de vzw "Çavaria" voor het budgettair jaar 2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-19&amp;pd_search=2025-05-15&amp;numac_search=2025003563&amp;page=3&amp;lg_txt=N&amp;caller=list&amp;2025003563=3&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-20&amp;numac_search=2025003811&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003811=3&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
           <t xml:space="preserve">
-De hierna volgende tekst is de Duitse vertaling van het koninklijk besluit van 30 augustus 2016 houdende maatregelen betreffende de bestrijding van de vesiculaire varkensziekte (Belgisch Staatsblad van 7 oktober 2016).Deze vertaling is opgemaakt door de Centrale dienst voor Duitse vertaling in Malmedy.FÖDERALER ÖFFENTLICHER DIENST VOLKSGESUNDHEIT, SICHERHEIT DER NAHRUNGSMITTELKETTE UND UMWELT UND FÖDERALAGENTUR FÜR DIE SICHERHEIT DER NAHRUNGSMITTELKETTE30. AUGUST 2016 - Königlicher Erlass zur Festlegung tierseuchenrechtlicher Maßnahmen zur Bekämpfung der vesikulären SchweinekrankheitPHILIPPE, Konig der Belgier, Allen Gegenwartigen und Zukunftigen, Unser Gruß!Aufgrund der Verfassung, des Artikels 108;Aufgrund des Gesetzes vom 24. März 1987 über die Tiergesundheit, des Artikels 7, des Artikels 8, des Artikels 9 Nr. 1, 2, 3 und 4, des Artikels 15 Nr. 1 und 2, abgeändert durch das Gesetz vom 1. März 2007, und des Artikels 17, abgeändert durch die Gesetze vom 23. Dezember 2005 und 20. Juli 2006;Aufgrund des Gesetzes vom 23. März 1998 über die Schaffung eines Haushaltsfonds für Gesundheit und Qualität der Tiere und tierischen Erzeugnisse, des Artikels 4 Absatz 1 Nr. 1;Aufgrund des Gesetzes vom 4. Februar 2000 über die Schaffung der Föderalagentur für die Sicherheit der Nahrungsmittelkette, des Artikels 4 §§ 1 bis 3, abgeändert durch das Gesetz vom 22. Dezember 2003, und § 6, eingefügt durch das Gesetz vom 13. Juli 2001 und ergänzt durch das Gesetz vom 9. Juli 2004, und des Artikels 5 Absatz 2 Nr. 13, abgeändert durch das Gesetz vom 22. Dezember 2003;Aufgrund des Königlichen Erlasses vom 16. November 2001 zur Übertragung zusätzlicher Aufgaben an die Föderalagentur für die Sicherheit der Nahrungsmittelkette, des Artikels 2 Buchstabe d);Aufgrund der Stellungnahme des Finanzinspektors vom 18. August 2015;Aufgrund der Konzertierung zwischen den Regionalregierungen und der Föderalbehörde vom 10. Dezember 2015;Aufgrund des Einverständnisses der Ministerin des Haushalts vom 28. Januar 2016;Aufgrund des Gutachtens Nr. 59.303/3 des Staatsrates vom 20. Mai 2016, abgegeben in Anwendung von Artikel 84 § 1 Absatz 1 Nr. 2 der am 12. Januar 1973 koordinierten Gesetze über den Staatsrat;Auf Vorschlag des Ministers der LandwirtschaftHaben Wir beschloßen und erlassen Wir:KAPITEL 1 - Anwendungsbereich und BegriffsbestimmungenArtikel 1 - Vorliegender Erlass dient der Teilumsetzung der Richtlinie 92/119/EWG des Rates der Europäischen Gemeinschaften mit allgemeinen Gemeinschaftsmaßnahmen zur Bekämpfung bestimmter Tierseuchen sowie besonderen Maßnahmen bezüglich der vesikulären Schweinekrankheit.Art. 2 -  § 1 - Für die Anwendung des vorliegenden Erlasses gelten die Begriffsbestimmungen des Königlichen Erlasses vom 1. Juli 2014 zur Einführung eines Systems zur Kennzeichnung und Registrierung von Schweinen und zur Festlegung der Bedingungen für die Zulassung von Schweinehaltungsbetrieben. § 2 - Für die Anwendung des vorliegenden Erlasses gelten ferner folgende Begriffsbestimmungen:1.Seuche: vesikuläre Schweinekrankheit,2. Tier: Haustier einer Art, die zur Verschleppung der Seuche beitragen könnte,3. Schwein: Tier der Familie Suidae, ausgenommen wilde Schweine,4. ansteckungsverdächtiges Schwein: Schwein, das mit dem Seuchenerreger direkt oder indirekt in Kontakt gekommen sein kann,5. seuchenverdächtiges Schwein: Schwein, das klinische Symptome oder Läsionen aufweist, die den begründeten Verdacht nahelegen, dass dieses Schwein von der Seuche befallen ist,6. befallenes Schwein: Schwein, bei dem die Seuche anhand einer vom nationalen Referenzlabor durchgeführten Laboruntersuchung amtlich festgestellt worden ist,7. seropositives Schwein: Schwein, bei dem durch eine serologische Untersuchung nachgewiesen wird, dass es Träger von Antikörpern gegen die vesikuläre Schweinekrankheit ist,8. Seuchenbestätigung: die auf Laborbefunde gestützte Feststellung der Seuche durch die Agentur. Bei epidemischem Auftreten kann die Agentur die Seuchenbestätigung auch auf klinische und/oder epidemiologische Befunde stützen,9. Seuchenherd: Betrieb, in dem das Vorhandensein der Seuche bestätigt ist,10. Nachbar- oder Kontaktbetrieb: Betrieb, in dem Schweine gehalten werden und der durch seine Lage oder durch den Verkehr von Personen oder Fahrzeugen oder die Verbringung von Tieren oder Material mit einem seuchenverdächtigen Betrieb oder mit einem Seuchenherd in Kontakt gekommen ist und in den der Seuchenerreger eingeschleppt werden konnte,11. Vektor: Wirbeltier oder wirbelloses Tier, das den Seuchenerreger auf mechanischem oder biologischem Weg übertragen und verschleppen könnte,12. Inkubationszeit: die voraussichtliche Zeitspanne zwischen der Infektion und dem Auftreten der ersten klinischen Krankheitssymptome. Die Inkubationszeit beträgt achtundzwanzig Tage,13. Agentur: Föderalagentur für die Sicherheit der Nahrungsmittelkette,14. amtlicher Tierarzt: Tierarzt der Agentur,15. Minister: Minister, zu dessen Zuständigkeit die Landwirtschaft gehört,16. Besitzer/Verantwortlicher: jede natürliche oder juristische Person, die rechtmäßiger Besitzer der Schweine beziehungsweise entgeltlich oder unentgeltlich für deren Haltung zuständig ist,17. Sentinel-Schweine: Schweine, bei denen die Untersuchung auf Antikörper gegen das Virus der vesikulären Schweinekrankheit einen negativen Befund ergeben hat.KAPITEL 2 - Allgemeine BestimmungenArt. 3 - In vorliegendem Erlass werden die bei Seuchenverdacht oder -bestätigung anzuwendenden Bekämpfungsmaßnahmen bestimmt.KAPITEL 3 - SeuchenverdachtArt. 4 - Befinden sich in einem Betrieb ansteckungs- oder seuchenverdächtige Schweine, stellt der amtliche Tierarzt den Betrieb unverzüglich unter Verdacht und führt er eine Untersuchung vor Ort durch, um diesen Verdacht zu erhärten beziehungsweise zu entkräften. Insbesondere entnimmt er geeignete Proben beziehungsweise veranlasst er deren Entnahme für die Laboruntersuchungen.Art. 5 - In Betrieben, in denen sich seropositive Schweine befinden, die nicht den Bestimmungen von Artikel 9 entsprechen, werden nach einem Zeitraum von mindestens achtundzwanzig Tagen zusätzliche serologische Untersuchungen durchgeführt. Die Bestimmungen von Kapitel 3 bleiben bis zum Abschluss dieser zusätzlichen Untersuchungen anwendbar. Sind bei den weiteren Untersuchungen keine eindeutigen Anzeichen der Krankheit festzustellen und sind die Schweine weiterhin seropositiv, werden sie getötet und unschädlich beseitigt oder unter Überwachung in einem vom amtlichen Tierarzt bestimmten Schlachthof geschlachtet.Art. 6 -  § 1 - In dem seuchenverdächtigen Betrieb führt der amtliche Tierarzt folgende Maßnahmen durch:1. Ermittlung aller Kategorien von Schweinen, und für jede Kategorie Zählung der bereits verendeten oder ansteckungs- oder seuchenverdächtigen Schweine. Diese Zählung wird vom Verantwortlichen unter Berücksichtigung der während des Verdachtszeitraums geborenen oder verendeten Schweine täglich auf den neuesten Stand gebracht. Diese Angaben müssen auf Verlangen des amtlichen Tierarztes vorgelegt werden,2. eine epizootiologische Untersuchung gemäß Kapitel 5. § 2 - Folgende Maßnahmen sind in einem seuchenverdächtigen Betrieb anwendbar:1. Alle Schweine werden dort in Stallungen verwahrt oder an einem anderen Ort, der eine gesonderte Aufstallung ermöglicht, abgesondert.2. Die Verbringung von Schweinen aus und zu dem Seuchenbetrieb ist untersagt.3. Der Verkehr von Personen und Fahrzeugen sowie die Verbringung anderer Tiere als Schweine aus dem und zum Seuchenbetrieb sowie der Transport von Fleisch und Tierkörpern, Futtermitteln, Gegenständen, Abfällen, Dung, Einstreu, Mist und sonstigen Materialien, die Träger von Ansteckungsstoffen sein könnten, aus dem und zum Seuchenbetrieb, unterliegt der Genehmigung des amtlichen Tierarztes. Der amtliche Tierarzt legt die Bedingungen fest, die erfüllt werden müssen, um jegliche Gefahr der Seuchenverschleppung zu vermeiden.4. An den Ein- und Ausgängen von Gebäuden, Räumlichkeiten oder sonstigen Orten zur Unterbringung von Schweinen und der Wirtschaftsgebäude müssen geeignete Desinfektionsmittel gemäß den Anweisungen des amtlichen Tierarztes verwendet werden.Art. 7 - Bis die in Artikel 6 vorgesehenen Maßnahmen ergriffen sind, trifft der Verantwortliche für ansteckungs- oder seuchenverdächtige Schweine alle zweckmäßigen Vorkehrungen, um den Bestimmungen von Artikel 6 mit Ausnahme des Paragraphen 1 Nr. 2 nachzukommen.Art. 8 - Der amtliche Tierarzt hebt die in den Artikeln 4 und 6 vorgesehenen Maßnahmen erst auf, wenn der Verdacht entkräftet wurde.KAPITEL 4 - Maßnahmen innerhalb des SeuchenherdsArt. 9 - Die Seuchenbestätigung erfolgt in Betrieben:1. in denen das Virus dieser Seuche entweder bei den Schweinen selbst oder in der Umgebung isoliert worden ist,2. in denen sich seropositive Schweine befinden, sofern diese Schweine oder andere im Betrieb befindliche Schweine die für diese Seuche charakteristischen Schädigungen und/oder Symptome aufweisen,3. in denen sich Schweine befinden, die seropositiv sind oder klinische Anzeichen aufweisen, und wenn diese Betriebe Nachbar- oder Kontaktbetriebe sind.Art. 10 -  § 1 - Sobald der Seuchenverdacht in einem Betrieb bestätigt wird, erklärt der amtliche Tierarzt diesen zu einem Seuchenherd. Er notifiziert dem Verantwortlichen die Erklärung als Seuchenherd. § 2 - Zusätzlich zu den in Artikel 6 vorgesehenen Maßnahmen trifft der amtliche Tierarzt ebenfalls folgende Maßnahmen:1. unverzügliche Tötung und Vernichtung aller Schweine,2. Vernichtung oder angemessene Behandlung aller Stoffe und Abfälle wie Futtermittel, Einstreu, Mist und Gülle, die Träger von Ansteckungsstoffen sein könnten, gemäß seinen Anweisungen,3. nach Ausführung der in Nr. 1 und Nr. 2 erwähnten Maßnahmen Reinigung und Desinfektion der für die Unterbringung der Schweine verwendeten Stallungen und ihrer unmittelbaren Umgebung, der Transportmittel sowie aller anderen Gegenstände und Materialien, die Träger von Ansteckungsstoffen sein könnten, gemäß Artikel 25.Art. 11 -  § 1 - Der amtliche Tierarzt genehmigt die Wiederbelegung des Betriebs mit Schweinen unter folgenden Bedingungen:1. frühestens vier Wochen nach der ersten vollständigen Reinigung und Desinfektion der Räumlichkeiten, wie in Artikel 26 bestimmt,2. alle angelieferten Schweine müssen vorab einer klinischen und serologischen Untersuchung gemäß den Empfehlungen der Agentur unterzogen werden und seronegativ sein,3. alle Schweine müssen innerhalb von acht Tagen in den Betrieb gebracht werden,4. während eines Zeitraums von sechzig Tagen nach Aufnahme des letzten Schweins darf kein Schwein den Betrieb verlassen,5. nach frühestens achtundzwanzig Tagen müssen alle Schweine einer klinischen Untersuchung und muss eine repräsentative Anzahl von Schweinen einer serologischen Untersuchung gemäß den Empfehlungen der Agentur unterzogen werden. § 2 - Wenn in einem Betrieb Schweine im Freien gehalten werden, muss vorab eine Wiederbelegung mit Sentinel-Schweinen gemäß den Anweisungen der Agentur erfolgen. § 3 - Fleisch von Schweinen aus einem Seuchenherd, die in dem Zeitraum zwischen der mutmaßlichen Einschleppung der Seuche und der Durchführung amtlicher Maßnahmen geschlachtet wurden, wird unter amtlicher Überwachung ermittelt und unschädlich beseitigt, um die Verschleppung des Virus der vesikulären Schweinekrankheit zu vermeiden.KAPITEL 5 - Epizootiologische UntersuchungArt. 12 - Die epizootiologische Untersuchung betrifft:1. den Zeitraum, während dessen die Seuche im Betrieb möglicherweise präsent war,2. die Ermittlung der mutmaßlichen Ansteckungsquelle im Seuchenbetrieb und die Identifizierung von Nachbar- oder Kontaktbetrieben,3. den Verkehr von Personen und Fahrzeugen sowie die Verbringung von Tieren, Tierkörpern, Material und sonstigen Stoffen, durch die der Seuchenerreger zu oder aus einem Betrieb vermutlich verschleppt worden ist,4. das Vorhandensein und die Weiterverschleppung von Vektoren.Art. 13 - Zur Koordinierung dieser Untersuchung richtet die Agentur ein Bekämpfungszentrum ein.KAPITEL 6 - Maßnahmen in Nachbar- oder KontaktbetriebenArt. 14 -  § 1 - Der amtliche Tierarzt stellt alle Nachbar- oder Kontaktbetriebe unter Verdacht und wendet die Maßnahmen von Kapitel 3 auf sie an. § 2 - Der amtliche Tierarzt kann ebenfalls die in Artikel 10 § 2 vorgesehenen Maßnahmen in den Nachbar- oder Kontaktbetrieben ausführen, wenn das Vorhandensein einer Seuche angesichts ihrer Lage und/oder der Art der Kontakte ernsthaft zu befürchten ist.Art. 15 - Wenn Artikel 14 für einen Nachbar- oder Kontaktbetrieb anwendbar ist, gelten die Bestimmungen von Kapitel 3 mindestens für einen Zeitraum von achtundzwanzig Tagen ab dem mutmaßlichen Zeitpunkt der Seucheneinschleppung.Ist der Zeitpunkt der Seucheneinschleppung nicht bekannt, gilt der Zeitpunkt der Erklärung als Seuchenherd.Art. 16 -  § 1 - In Nachbar- und Kontaktbetrieben gelten die Bestimmungen der Artikel 14 und 15. § 2 - Diese Bestimmungen bleiben anwendbar bis:1. eine klinische Untersuchung der Schweine mit negativem Befund erfolgt ist,2. eine statistisch repräsentative Anzahl von Proben der Schweine gemäß den Empfehlungen der Agentur einer serologischen Untersuchung unterzogen worden ist, bei der keine Antikörper gegen das Virus der vesikulären Schweinekrankheit nachgewiesen werden konnten. § 3 - Die in § 2 erwähnten Untersuchungen können erst achtundzwanzig Tage nach dem Kontakt oder der Erklärung als Seuchenherd erfolgen.KAPITEL 7 - Maßnahmen in Schutz- und ÜberwachungszonenArt. 17 - Sobald der Seuchenverdacht bestätigt ist, grenzt die Agentur um den Seuchenherd innerhalb einer Überwachungszone mit einem Mindestradius von zehn Kilometern eine Schutzzone mit einem Mindestradius von drei Kilometern ab. Sie notifiziert dem Verantwortlichen das Vorhandensein der Seuche.Art. 18 - Wenn die in Artikel 19 Nr. 3 und in Artikel 22 Nr. 2 erwähnten Verbotsbestimmungen länger als dreißig Tage aufrechterhalten werden und dadurch Schwierigkeiten bei der Unterbringung der Schweine entstehen, kann der amtliche Tierarzt auf begründeten Antrag des Verantwortlichen hin Abgang und Verbringung der Schweine aus einem Betrieb in der Schutz- beziehungsweise der Überwachungszone genehmigen, sofern:1. die Sachlage überprüft worden ist,2. alle im Betrieb befindlichen Schweine untersucht worden sind,3. die zu verbringenden Schweine einer klinischen Untersuchung unterzogen worden sind und kein Schwein seuchenverdächtig ist,4. die Schweine gemäß den Bestimmungen des Königlichen Erlasses vom 1. Juli 2014 zur Einführung eines Systems zur Kennzeichnung und Registrierung von Schweinen und zur Festlegung der Bedingungen für die Zulassung von Schweinehaltungsbetrieben gekennzeichnet sind,5. der Bestimmungsbetrieb sich in der Schutz- oder der Überwachungszone befindet.Es müssen alle erforderlichen Vorkehrungen getroffen werden, insbesondere für die Reinigung und Desinfektion der Fahrzeuge nach jedem Transport, um die Gefahr einer Verschleppung des Seuchenerregers zu vermeiden.KAPITEL 8 - Maßnahmen gegen die vesikuläre Schweinekrankheit in der SchutzzoneArt. 19 - Folgende Maßnahmen sind in der Schutzzone anwendbar:1. Die Agentur erstellt ein Inventar der Betriebe und der dort gehaltenen Schweine.2. Unbeschadet des Königlichen Erlasses vom 15. Februar 1995 zur Festlegung besonderer Maßnahmen in Bezug auf die epidemiologische Überwachung und die Vorbeugung meldepflichtiger Schweinekrankheiten werden alle Betriebe, die Schweine halten, regelmäßig besucht. Die Häufigkeit dieser Besuche richtet sich nach der Schwere der Seuche in den Betrieben, in denen die Risiken am größten sind, und wird von der Agentur näher bestimmt. Die Schweine werden klinisch untersucht und gegebenenfalls werden Proben für Laboruntersuchungen entnommen. Die Angaben und Resultate dieser Besuche werden registriert.3. Verbringung und Transport von Schweinen über öffentliche Straßen oder Privatwege sind verboten. Die Agentur kann jedoch Abweichungen für die Durchfuhr der Schweine im Straßen- oder Schienenverkehr gewähren, wenn die Schweine ohne Entladung oder Fahrtunterbrechung transportiert werden.4. Fahrzeuge und Ausrüstungen, die innerhalb der Schutzzone zum Transport von Tieren beziehungsweise von Materialien, die zu Trägern von Ansteckungsstoffen werden können, insbesondere Futtermittel, Mist oder Gülle, verwendet werden, dürfen einen innerhalb der Schutzzone gelegenen Betrieb, die Schutzzone selbst oder einen Schlachthof erst verlassen, wenn sie gemäß den Anweisungen der Agentur vorher gereinigt und desinfiziert worden sind.5. Die Schweine dürfen den Haltungsbetrieb nach Abschluss der in Artikel 26 vorgesehenen ersten Maßnahmen zur Reinigung und Desinfektion des Seuchenherds einundzwanzig Tage lang nicht verlassen. Nach Ablauf dieser Frist kann der amtliche Tierarzt die Erlaubnis erteilen, dass Schweine den genannten Betrieb verlassen, um: a) unmittelbar in einen von der Agentur bestimmten Schlachthof, vorzugsweise innerhalb der Schutz- oder Überwachungszone, verbracht zu werden, sofern: - alle im Betrieb befindlichen Schweine vorab untersucht worden sind, - die zur Schlachtung zu verbringenden Schweine einer klinischen Untersuchung unterzogen worden sind und kein Schwein seuchenverdächtig ist, - jedes einzelne Schwein gemäß den Bestimmungen des Königlichen Erlasses vom 1. Juli 2014 zur Einführung eines Systems zur Kennzeichnung und Registrierung von Schweinen und zur Festlegung der Bedingungen für die Zulassung von Schweinehaltungsbetrieben gekennzeichnet ist, - die Fahrzeuge verplombt sind. Die Fahrzeuge und Ausrüstungen, in denen die Schweine befördert wurden, sind gemäß den Anweisungen der Agentur zu reinigen und zu desinfizieren, b) unter außergewöhnlichen Umständen - unmittelbar in andere innerhalb der Schutzzone gelegene Betriebe verbracht zu werden, sofern: - alle im Betrieb befindlichen Schweine vorab untersucht worden sind, - alle zu verbringenden Schweine einer klinischen Untersuchung unterzogen worden sind und kein Schwein seuchenverdächtig ist, - jedes einzelne Schwein gemäß den Bestimmungen des Königlichen Erlasses vom 1. Juli 2014 zur Einführung eines Systems zur Kennzeichnung und Registrierung von Schweinen und zur Festlegung der Bedingungen für die Zulassung von Schweinehaltungsbetrieben gekennzeichnet ist.6. Frisches Fleisch der unter Nr. 5 Buchstabe a) erwähnten Schweine: - darf nicht in den innergemeinschaftlichen oder internationalen Handel gelangen und wird mit dem für frisches Fleisch vorgesehenen Genusstauglichkeitskennzeichen im Sinne von Anhang II der Richtlinie 2002/99/EG versehen, - wird von Fleisch, das für den innergemeinschaftlichen und internationalen Handel bestimmt ist, separat erzeugt, zerlegt, befördert und gelagert und darf nicht in Fleischerzeugnisse gelangen, die für den innergemeinschaftlichen oder internationalen Handel bestimmt sind, es sei denn, es wurde einer Behandlung gemäß Anhang III der Richtlinie 2002/99/EG unterzogen.Art. 20 - Die Maßnahmen in der Schutzzone gelten mindestens, bis:1. alle in Artikel 26 vorgesehenen Maßnahmen abgeschlossen sind,2. in allen Betrieben der Zone: a) die Schweine einer klinischen Untersuchung unterzogen worden sind und kein Schwein seuchenverdächtig ist, b) eine statistisch repräsentative Anzahl von Schweinen einer serologischen Untersuchung unterzogen worden ist, bei der eine Infektion ausgeschlossen werden konnte.Die Untersuchung und die Probenahme gemäß den Buchstaben a) und b) dürfen erst nach Ablauf von achtundzwanzig Tagen nach Abschluss der in Artikel 26 vorgesehenen ersten Maßnahmen zur Reinigung und Desinfektion des Seuchenherds erfolgen.Art. 21 - Nach Ablauf des in Artikel 20 Nr. 2 erwähnten Zeitraums finden die in der Überwachungszone geltenden Bestimmungen, wie in Artikel 23 angegeben, auch auf die Schutzzone Anwendung.KAPITEL 9 - Maßnahmen gegen die vesikuläre Schweinekrankheit in der ÜberwachungszoneArt. 22 - Folgende Maßnahmen sind in der Überwachungszone anwendbar:1. Die Agentur erstellt ein Inventar der Betriebe der Zone und der dort gehaltenen Schweine.2. Der Transport von Schweinen über öffentliche Straßen oder Privatwege ist verboten. Die Agentur kann jedoch Abweichungen für die Durchfuhr der Schweine gewähren, wenn die Schweine ohne Entladung oder Fahrtunterbrechung transportiert werden. Mit der Genehmigung der Agentur können jedoch Schlachtschweine von außerhalb der Überwachungszone in einen in dieser Zone gelegenen Schlachthof verbracht werden.3. In Abweichung von Nr. 2 kann der amtliche Tierarzt die Verbringung von Schweinen aus einem Betrieb in der Überwachungszone genehmigen, sofern: a) alle im Betrieb befindlichen Schweine in der Zeitspanne von achtundvierzig Stunden vor der Verbringung untersucht worden sind, b) die zu verbringenden Schweine in der Zeitspanne von achtundvierzig Stunden vor der Verbringung einer klinischen Untersuchung unterzogen worden sind und kein Schwein seuchenverdächtig ist, c) in der Zeitspanne von vierzehn Tagen vor der Verbringung eine statistisch repräsentative Anzahl von Proben der zu verbringenden Schweine serologisch untersucht wurde und dabei keine Antikörper gegen das Virus der vesikulären Schweinekrankheit festgestellt wurden, d) jedes einzelne Schwein gemäß den Bestimmungen des Königlichen Erlasses vom 1. Juli 2014 zur Einführung eines Systems zur Kennzeichnung und Registrierung von Schweinen und zur Festlegung der Bedingungen für die Zulassung von Schweinehaltungsbetrieben gekennzeichnet ist, e) während der vorangegangenen einundzwanzig Tage dem Betrieb keine Schweine zugeführt wurden. Diese Bestimmung gilt nicht für die unmittelbare Verbringung von Schlachtschweinen zu einem Schlachthof, f) die Fahrzeuge und anderen Ausrüstungen, die zur Verbringung dieser Schweine verwendet wurden, nach jedem Transport gemäß den Anweisungen der Agentur gereinigt und desinfiziert werden.4. Die innerhalb der Überwachungszone zur Verbringung von Schweinen, anderen Tieren oder Materialien, die Träger von Ansteckungsstoffen sein könnten, verwendeten Fahrzeuge und Ausrüstungen dürfen diese Zone erst verlassen, wenn sie gemäß den Anweisungen des amtlichen Tierarztes gereinigt und desinfiziert worden sind.Art. 23 -  § 1 - Die Maßnahmen in der Überwachungszone gelten mindestens, bis:1. alle in Artikel 26 vorgesehenen Maßnahmen abgeschlossen sind,2. alle Maßnahmen in der Schutzzone abgeschlossen sind. § 2 - In Anwendung von Artikel 11 § 2 können die Maßnahmen in der Überwachungszone verlängert werden, und zwar solange, bis die Befunde der Untersuchungen an den Sentinel-Schweinen negativ ausfallen.KAPITEL 10 - Maßnahmen in SchlachthöfenArt. 24 - Bestätigt sich das Auftreten der vesikulären Schweinekrankheit in einem Schlachthof, gelten folgende Maßnahmen:1. alle im Schlachthof befindlichen Schweine werden unverzüglich geschlachtet,2. die Tierkörper der infizierten und mit Ansteckungsstoffen in Kontakt gekommenen Schweine sowie die Nebenprodukte der Schlachtung werden unter amtlicher Aufsicht unschädlich beseitigt, damit die Gefahr einer Verschleppung des Virus der vesikulären Schweinekrankheit ausgeschlossen ist,3. die Reinigung und Desinfektion der Gebäude und Einrichtungen, einschließlich der Fahrzeuge, erfolgen gemäß den Anweisungen des amtlichen Tierarztes,4. eine epizootiologische Untersuchung wird gemäß Artikel 12 durchgeführt,5. Schlachtschweine dürfen frühestens vierundzwanzig Stunden nach Abschluss der gemäß Nr. 3 durchgeführten Reinigungs- und Desinfektionsmaßnahmen wieder in den Schlachthof verbracht werden.KAPITEL 11 - Reinigung und DesinfektionArt. 25 - Es gelten folgende Maßnahmen:1. Reinigungs-, Desinfektions- und Entwesungsarbeiten werden nach Anweisung der Agentur durchgeführt, um eine Verschleppung beziehungsweise das Überleben des Seuchenerregers auszuschließen.2. Die zu verwendenden Desinfektions- und Insektenvertilgungsmittel sowie gegebenenfalls ihre Konzentrationen sind amtlich zugelassen.3. Der amtliche Tierarzt vergewissert sich nach Durchführung der in Nr. 2 erwähnten Maßnahmen, dass die Maßnahmen ordnungsgemäß durchgeführt worden sind.Art. 26 -  § 1 - Verfahren der Vorreinigung und Desinfektion:1. Sobald die Schweinetierkörper entfernt worden sind, um unschädlich beseitigt zu werden, sind die Räumlichkeiten, in denen die Schweine untergebracht waren, sowie alle anderen Teile von während der Tötung verunreinigten Räumlichkeiten mit einem Desinfektionsmittel in der der vesikulären Schweinekrankheit angemessenen Konzentration zu besprühen. Das verwendete Desinfektionsmittel muss mindestens vierundzwanzig Stunden einwirken können.2. Eventuelle Gewebe- oder Blutrückstände sind sorgfältig zu entfernen und unschädlich zu beseitigen. § 2 - Verfahren der Zwischenreinigung und -desinfektion:1. Dung, Einstreu und Futter, die Träger von Ansteckungsstoffen sein könnten, sind aus den Gebäuden zu entfernen, aufzuschichten und mit einem zugelassenen Desinfektionsmittel zu besprühen. Gülle ist mit einer Methode zu behandeln, die eine Abtötung des Virus ermöglicht.2. Alle beweglichen Zubehörteile sind aus den Räumlichkeiten zu entfernen und gesondert zu reinigen und zu desinfizieren.3. Von allen Flächen sind mit Hilfe eines Entfettungsmittels Fett und andere Verunreinigungen zu entfernen; sie sind sodann mit Druckwasser abzuspritzen.4. Anschließend sind alle Flächen erneut mit einem Desinfektionsmittel zu besprühen.5. Hermetisch abgeschlossene Räume sind durch Begasung zu desinfizieren.6. Instandsetzungen von Boden, Wänden und anderen beschädigten Teilen sind sofort durchzuführen. Es ist nachzuprüfen, ob die Instandsetzungsarbeiten in zufriedenstellender Weise durchgeführt worden sind.7. Alle Teile der Räumlichkeiten, die von brennbarem Material vollständig frei sind, können einer Hitzebehandlung mit Hilfe eines Flammenwerfers unterzogen werden.8. Alle Flächen sind mit einem alkalischen Desinfektionsmittel mit einem pH-Wert von mehr als 12,5 oder einem anderen zugelassenen Desinfektionsmittel zu besprühen. Das Desinfektionsmittel ist achtundvierzig Stunden danach mit Wasser abzuspülen. § 3 - Endreinigung und -desinfektion:Die Behandlung mit Flammenwerfern oder einem alkalischen Desinfektionsmittel gemäß § 2 Nr. 7 oder 8 ist nach vierzehn Tagen erneut vorzunehmen.KAPITEL 12 - LabordiagnoseArt. 27 -  § 1 - Allein das nationale Referenzlabor ist für die Labordiagnose der Seuche zuständig. § 2 - Das nationale Referenzlabor hält die Virusisolate der Seuche aus bestätigten Seuchenfällen des nationalen Hoheitsgebiets vorrätig. § 3 - Das nationale Referenzlabor arbeitet mit den gemeinschaftlichen Referenzlaboratorien zusammen.KAPITEL 13 - ImpfungArt. 28 - Die Impfung gegen die Seuche und deren Behandlung sind verboten.Art. 29 - In Abweichung von Artikel 28 kann der Minister beschließen, die Impfung gegen die Seuche ergänzend zu den Maßnahmen des vorliegenden Erlasses einzuführen, vorausgesetzt, dass alle geimpften Schweine:1. mit einer eindeutigen Kennzeichnung versehen sind,2. in der Impfzone bleiben, außer wenn sie mit Genehmigung des amtlichen Tierarztes zwecks sofortiger Schlachtung in einen von ihm bestimmten Schlachthof verbracht werden. Die Verbringung darf erst genehmigt werden, nachdem alle Schweine in dem Betrieb untersucht worden sind und jeglicher Seuchenverdacht entkräftet worden ist.KAPITEL 14 - EntschädigungenArt. 30 - Im Rahmen des dazu vorgesehenen Haushaltsplanartikels und zu Lasten des Haushaltsfonds für Gesundheit und Qualität der Tiere und tierischen Erzeugnisse wird dem Besitzer von Schweinen, die auf Anordnung getötet worden sind, eine Entschädigung in Höhe des Wertes der Schweine gewährt, sofern der Besitzer die Bestimmungen des vorliegenden Erlasses eingehalten hat.In keinem Fall darf diese Entschädigung 1.000 EUR pro Schwein übersteigen.Die Schätzung der Schweine erfolgt gemäß dem in den Artikeln 77 und 78 des Königlichen Erlasses vom 10. Oktober 2005 über die Bekämpfung der Maul- und Klauenseuche festgelegten Verfahren.KAPITEL 15 - SanktionenArt. 31 - Verstöße gegen die Bestimmungen des vorliegenden Erlasses werden gemäß dem Königlichen Erlass vom 22. Februar 2001 zur Organisation der von der Föderalagentur für die Sicherheit der Nahrungsmittelkette durchgeführten Kontrollen und zur Abänderung verschiedener Gesetzesbestimmungen ermittelt, festgestellt und verfolgt und gemäß Kapitel VI des Gesetzes vom 24. März 1987 über die Tiergesundheit bestraft.KAPITEL 16 - SchlussbestimmungenArt. 32 - Der für die Sicherheit der Nahrungsmittelkette zuständige Minister ist mit der Ausführung des vorliegenden Erlasses beauftragt.Gegeben zu Brüssel, den 30. August 2016PHILIPPEVon Königs wegen:Der Minister der LandwirtschaftW. BORSUS 
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 22 mei 2003 houdende organisatie van de begroting en van de comptabiliteit van de federale Staat, op de artikelen 121 tot 124;Gelet op de wet van 10 mei 2007 ter bestrijding van bepaalde vormen van discriminatie, artikel 32/1;Gelet op de financiewet voor begrotingsjaar van 20 december 2024 op sectie 12 - FOD Justitie, programma 58/5 - Diversiteit, Interculturaliteit en Gelijkheid van Kansen;Gelet op het koninklijk besluit van 20 mei 2022 betreffende de administratieve, begrotings- en beheerscontrole;Gelet op het koninklijk besluit van 2 oktober 2023 betreffende de modaliteiten voor de toekenning van de jaarlijkse subsidies voor de koepels van niet-gouvernementele organisaties die actief zijn in het domein van de bestrijding van discriminatie op grond van seksuele oriëntatie voor wat betreft de materies die behoren tot de bevoegdheid van de federale overheid;Gelet op het ministerieel besluit van 22 maart 2024 tot erkenning van de koepels van niet-gouvernementele organisaties die actief zijn in het domein van de bestrijding van discriminatie op grond van seksuele oriëntatie voor wat betreft de materies die behoren tot de bevoegdheid van de federale overheid, voor de erkenningscyclus van 2024-2028;Gelet de instemming van de Minister van Begroting gegeven op 4 april 2025;Gelet op het advies van de inspecteur van Financiën, gegeven op 10 januari 2025;Overwegende dat een krediet van vierhonderdéénennegentigduizend euro (491.000,00 euro) op de organisatieafdeling 12.58.52, activiteitenprogramma 58/5, basisallocatie 33.00.41 van de administratieve begroting van de FOD justitie voor het begrotingsjaar 2025 is ingeschreven;Overwegende de aanvraag voor een subsidie die de vzw "Çavaria" indiende op 1 oktober 2024 overeenkomstig artikel 13 van het voornoemde koninklijk besluit van 2 oktober 2023;Overwegende dat de vzw "Çavaria" voldoet aan de criteria vastgelegd in artikelen 8 en 10 van het voornoemde koninklijk besluit van 2 oktober 2023 en is erkend als een koepel van organisaties;Op de voordracht van de Minister van Gelijke Kansen;Hebben Wij besloten en besluiten Wij :Artikel 1.  § 1. Een toelage van zevenenveertigduizend tweehonderdtweeënvijftig euro en zeventig cent (47.252,70 euro) wordt toegekend aan de vzw "Çavaria", met zetel gevestigd te Kammerstraat 22, 9000 Gent (ondernemingsnummer 0415 652 423 en rekeningnummer IBAN BE 84 0682 1326 7459). § 2. De toelage is bedoeld ter financiële ondersteuning van de jaarlijkse werkingskosten in verband met de uitvoering van een werkprogramma in het kader van het federale beleid inzake bestrijding van discriminatie op grond van seksuele oriëntatie. Art. 2. De toelage bedoeld in artikel 1, wordt aangerekend op het activiteitenprogramma 58/5, basisallocatie 33.00.41, organisatieafdeling 12.58.52 van de administratieve begroting van de FOD Justitie voor het begrotingsjaar 2025.Art. 3. De periode waarop de toelage betrekking heeft, begint op 1 januari 2025 en eindigt op 31 maart 2025.Art. 4. De toelage bedoeld in artikel 1 wordt in twee schijven betaald, verdeeld op de volgende wijze:- een eerste schijf van negentig percent na ondertekening van dit besluit;- het saldo van tien percent na de voorlegging van het eindverslag van de activiteiten en de bewijsstukken voor de volledige toelage. Art. 5.  § 1. Worden aanvaard als subsidieerbare kosten:1°  de kosten voor de huur, de huurlasten en het onderhoud van de gebouwen;2°  de personeelskosten en de kosten voor de aanwerving van het personeel en voor het personeelsbeheer;3°  de missiekosten en reiskosten;4°  de opleidingskosten;5°  de kosten voor administratief en boekhoudkundig beheer;6°  de kantoor- en informaticakosten;7°  de kosten inzake logistiek, communicatie en kantooruitrusting. § 2. De subsidie dekt geen kosten die reeds gedekt zijn door een andere vorm van subsidiering.Art. 6.  § 1. De vereniging verstuurt uiterlijk op 3A maart 2026 het eindverslag van de activiteiten alsook de financiële bewijsstukken naar de dienst Gelijke Kansen (Waterloolaan 115, 1000 Brussel of naar het e-mailadres: equal@just.fgov.be). § 2. Het eindverslag van de activiteiten bevat minstens een algemene beschrijving van de verwezenlijkte werkzaamheden, een synthese van de gevoerde acties, een evaluatie van de behaalde doelstellingen, een beschrijving van de eventuele ondervonden problemen met inbegrip van de obstakels bij de tenuitvoerlegging van de acties, een beschrijving van de faciliterende factoren, alsook alle noodzakelijke informatie die de dienst Gelijke Kansen in staat moet stellen om de verwezenlijking van die activiteiten te evalueren. § 3. De vereniging verstuurt eveneens een samenvattende tabel van alle bewijsstukken van de op deze toelage aangerekende uitgaven, met referentie naar de uitgavencategorieën. § 4. Bij ontstentenis van de volledige overlevering van de documenten, namelijk het eindverslag van de activiteiten en de bewijsstukken voor de volledige toelage, wordt de tweede schijf van de toelage niet uitbetaald en wordt, in voorkomend geval, de eerste schijf teruggevorderd voor het gedeelte van het bedrag dat niet naar behoren, overeenkomstig dit artikel, is gemotiveerd.Art. 7.  § 1. De begunstigde moet:- de bepalingen van de toekenning van de toelage volledig nakomen. Indien dat niet het geval is, kan hem een volledige of gedeeltelijke terugbetaling van de toegekende toelage worden gevraagd;- met betrekking tot het goede besteding van deze toelage enige controle van stukken en/of ter plekke aanvaarden;- het publiek in elk bericht of bij elke publiciteit op de hoogte brengen van de financiële hulp die ze in het kader van deze toelage hebben ontvangen. § 2. In het geval dat de toelage onrechtmatig werd gebruikt, is de dienst Gelijke Kansen van de FOD Justitie belast met de terugvordering van de bedragen. § 3. Indien blijkt dat te veel toelage werd toegekend voor het afgelopen jaar, wordt een beslissing tot terugvordering ter kennis gebracht bij aangetekende brief. Na verloop van een termijn van dertig dagen wordt de beslissing tot terugvordering definitief, tenzij de vereniging opmerkingen heeft laten toekomen. In dat geval wordt de definitieve beslissing uiterlijk twee maanden na ontvangst van de opmerkingen ter kennis van de vereniging gebracht. De vereniging stort het verschuldigde bedrag uiterlijk drie maanden na de definitieve beslissing tot terugvordering terug.Art. 8. Dit besluit heeft uitwerking met ingang van 1 januari 2025.Art. 9. Het lid van de regering dat bevoegd is voor Gelijke Kansen is belast met de uitvoering van dit besluitGegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister voor Gelijke Kansen,R. BEENDERS 
 </t>
         </is>
       </c>
@@ -3767,25 +3756,3204 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
+          <t>2025003812</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>20 mei 2025</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>5 mei 2025. - Koninklijk besluit houdende toekenning van een toelage aan de vzw "Prisme" voor het budgettair jaar 2025</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-20&amp;numac_search=2025003812&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003812=4&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 22 mei 2003 houdende organisatie van de begroting en van de comptabiliteit van de federale Staat, op de artikelen 121 tot 124;Gelet op de wet van 10 mei 2007 ter bestrijding van bepaalde vormen van discriminatie, artikel 32/1;Gelet op de financiewet voor begrotingsjaar van 20 december 2024 op sectie 12 - FOD Justitie, programma 58/5 - Diversiteit, Interculturaliteit en Gelijkheid van Kansen;Gelet op het koninklijk besluit van 20 mei 2022 betreffende de administratieve, begrotings- en beheerscontrole;Gelet op het koninklijk besluit van 2 oktober 2023 betreffende de modaliteiten voor de toekenning van de jaarlijkse subsidies voor de koepels van niet-gouvernementele organisaties die actief zijn in het domein van de bestrijding van discriminatie op grond van seksuele oriëntatie voor wat betreft de materies die behoren tot de bevoegdheid van de federale overheid;Gelet op het ministerieel besluit van 22 maart 2024 tot erkenning van de koepels van niet-gouvernementele organisaties die actief zijn in het domein van de bestrijding van discriminatie op grond van seksuele oriëntatie voor wat betreft de materies die behoren tot de bevoegdheid van de federale overheid, voor de erkenningscyclus van 2024-2028;Gelet de instemming van de Minister van Begroting gegeven op 4 april 2025;Gelet op het advies van de inspecteur van Financiën, gegeven op 10 januari 2025;Overwegende dat een krediet van vierhonderdéénennegentigduizend euro (491.000,00 euro) op de organisatieafdeling 12.58.52, activiteitenprogramma 58/5, basisallocatie 33.00.41 van de administratieve begroting van de FOD justitie voor het begrotingsjaar 2025 is ingeschreven;Overwegende de aanvraag voor een subsidie die de vzw "Prisme" indiende op 1 oktober 2024 overeenkomstig artikel 13 van het voornoemde koninklijk besluit van 2 oktober 2023;Overwegende dat de vzw "Prisme" voldoet aan de criteria vastgelegd in artikelen 8 en 10 van het voornoemde koninklijk besluit van 2 oktober 2023 en is erkend als een koepel van organisaties;Op de voordracht van de Minister van Gelijke Kansen;Hebben Wij besloten en besluiten Wij :Artikel 1.  § 1. Een toelage van vierenveertigduizend zeshonderdzevenentwintig euro en vijfenvijftig cent euro (44.627,55 euro) wordt toegekend aan de vzw "Prisme", met zetel gevestigd te Rue Pierreuse 25, 4000 Luik (ondernemingsnummer 0890 447 429 en rekeningnummer IBAN BE 82 0682 4796 5268). § 2. De toelage is bedoeld ter financiële ondersteuning van de jaarlijkse werkingskosten in verband met de uitvoering van een werkprogramma in het kader van het federale beleid inzake bestrijding van discriminatie op grond van seksuele oriëntatie. Art. 2. De toelage bedoeld in artikel 1, wordt aangerekend op het activiteitenprogramma 58/5, basisallocatie 33.00.41, organisatieafdeling 12.58.52 van de administratieve begroting van de FOD Justitie voor het begrotingsjaar 2025.Art. 3. De periode waarop de toelage betrekking heeft, begint op 1 januari 2025 en eindigt op 31 maart 2025.Art. 4. De toelage bedoeld in artikel 1 wordt in twee schijven betaald, verdeeld op de volgende wijze:- een eerste schijf van negentig procent na ondertekening van dit besluit;- de tweede schijf van tien procent na de voorlegging van het eindverslag van de activiteiten en de bewijsstukken voor de volledige toelage. Art. 5.  § 1. Worden aanvaard als subsidieerbare kosten:1°  de kosten voor de huur, de huurlasten en het onderhoud van de gebouwen;2°  de personeelskosten en de kosten voor de aanwerving van het personeel en voor het personeelsbeheer;3°  de missiekosten en reiskosten;4°  de opleidingskosten;5°  de kosten voor administratief en boekhoudkundig beheer;6°  de kantoor- en informaticakosten;7°  de kosten inzake logistiek, communicatie en kantooruitrusting. § 2. De subsidie dekt geen kosten die reeds gedekt zijn door een andere vorm van subsidiering.Art. 6.  § 1. De vereniging verstuurt uiterlijk op 31 maart 2026 het eindverslag van de activiteiten alsook de financiële bewijsstukken naar de dienst Gelijke Kansen (Waterloolaan 115, 1000 Brussel of naar het e-mailadres: equal@just.fgov.be). § 2. Het eindverslag van de activiteiten bevat minstens een algemene beschrijving van de verwezenlijkte werkzaamheden, een synthese van de gevoerde acties, een evaluatie van de behaalde doelstellingen, een beschrijving van de eventuele ondervonden problemen met inbegrip van de obstakels bij de tenuitvoerlegging van de acties, een beschrijving van de faciliterende factoren, alsook alle noodzakelijke informatie die de dienst Gelijke Kansen in staat moet stellen om de verwezenlijking van die activiteiten te evalueren. § 3. De vereniging verstuurt eveneens een samenvattende tabel van alle bewijsstukken van de op deze toelage aangerekende uitgaven, met referentie naar de uitgavencategorieën. § 4. Bij ontstentenis van de volledige overlevering van de documenten, namelijk het eindverslag van de activiteiten en de bewijsstukken voor de volledige toelage, wordt de tweede schijf van de toelage niet uitbetaald en wordt, in voorkomend geval, de eerste schijf teruggevorderd voor het gedeelte van het bedrag dat niet naar behoren, overeenkomstig dit artikel, is gemotiveerd.Art. 7.  § 1. De begunstigde moet:- de bepalingen van de toekenning van de toelage volledig nakomen. Indien dat niet het geval is, kan hem een volledige of gedeeltelijke terugbetaling van de toegekende toelage worden gevraagd;- met betrekking tot het goede besteding van deze toelage enige controle van stukken en/of ter plekke aanvaarden;- het publiek in elk bericht of bij elke publiciteit op de hoogte brengen van de financiële hulp die ze in het kader van deze toelage hebben ontvangen. § 2. In het geval dat de toelage onrechtmatig werd gebruikt, is de dienst Gelijke Kansen van de FOD Justitie belast met de terugvordering van de bedragen. § 3. Indien blijkt dat te veel toelage werd toegekend voor het afgelopen jaar, wordt een beslissing tot terugvordering ter kennis gebracht bij aangetekende brief. Na verloop van een termijn van dertig dagen wordt de beslissing tot terugvordering definitief, tenzij de vereniging opmerkingen heeft laten toekomen. In dat geval wordt de definitieve beslissing uiterlijk twee maanden na ontvangst van de opmerkingen ter kennis van de vereniging gebracht. De vereniging stort het verschuldigde bedrag uiterlijk drie maanden na de definitieve beslissing tot terugvordering terug.Art. 8. Dit besluit heeft uitwerking met ingang van 1 januari 2025.Art. 9. Het lid van de regering dat bevoegd is voor Gelijke Kansen is belast met de uitvoering van dit besluitGegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister voor Gelijke Kansen,R. BEENDERS 
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2025003735</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>21 mei 2025</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>5 mei 2025. - Koninklijk besluit houdende benoeming van de vertegenwoordiger van de Minister van Financiën bij de Nationale Bank van België</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-21&amp;numac_search=2025003735&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003735=5&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 22 februari 1998 tot vaststelling van het organiek statuut van de Nationale Bank van België, artikel 22;Gelet op artikel 41 van de statuten van de Nationale Bank van België, goedgekeurd bij koninklijk besluit van 18 september 2022;Gelet op het koninklijk besluit van 9 februari 2024 houdende benoeming van de vertegenwoordiger van de Minister van Financiën bij de Nationale Bank van België;Op de voordracht van de Vice-eersteminister en Minister van Financiën,Hebben Wij besloten en besluiten Wij :Artikel 1. Wesley De Visscher wordt benoemd tot vertegenwoordiger van de Minister van Financiën bij de Nationale Bank van België ter vervanging van de heer Filip Van de Velde.Art. 2. Dit besluit treedt in werking op 1 mei 2025.Art. 3. De Minister bevoegd voor Financiën is belast met de uitvoering van dit besluit.Gegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Vice-eersteminister en Minister van Financiën,J. JAMBON 
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2025003813</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>26 mei 2025</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>5 mei 2025. - Koninklijk besluit houdende toekenning van een toelage aan de vzw "Rainbow House" voor het budgettair jaar 2025</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-26&amp;numac_search=2025003813&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003813=6&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 22 mei 2003 houdende organisatie van de begroting en van de comptabiliteit van de federale Staat, op de artikelen 121 tot 124;Gelet op de wet van 10 mei 2007 ter bestrijding van bepaalde vormen van discriminatie, artikel 32/1;Gelet op de financiewet voor begrotingsjaar van 20 december 2024 op sectie 12 - FOD Justitie, programma 58/5 - Diversiteit, Interculturaliteit en Gelijkheid van Kansen;Gelet op het koninklijk besluit van 20 mei 2022 betreffende de administratieve, begrotings- en beheerscontrole;Gelet op het koninklijk besluit van 2 oktober 2023 betreffende de modaliteiten voor de toekenning van de jaarlijkse subsidies voor de koepels van niet-gouvernementele organisaties die actief zijn in het domein van de bestrijding van discriminatie op grond van seksuele oriëntatie voor wat betreft de materies die behoren tot de bevoegdheid van de federale overheid;Gelet op het ministerieel besluit van 22 maart 2024 tot erkenning van de koepels van niet-gouvernementele organisaties die actief zijn in het domein van de bestrijding van discriminatie op grond van seksuele oriëntatie voor wat betreft de materies die behoren tot de bevoegdheid van de federale overheid, voor de erkenningscyclus van 2024-2028;Gelet de instemming van de Minister van Begroting gegeven op 4 april 2025;Gelet op het advies van de inspecteur van Financiën, gegeven op 10 januari 2025;Overwegende dat een krediet van vierhonderdéénennegentigduizend euro (491.000,00 euro) op de organisatieafdeling 12.58.52, activiteitenprogramma 58/5, basisallocatie 33.00.41 van de administratieve begroting van de FOD justitie voor het begrotingsjaar 2025 is ingeschreven;Overwegende de aanvraag voor een subsidie die de vzw "Rainbow House" indiende op 1 oktober 2024 overeenkomstig artikel 13 van het voornoemde koninklijk besluit van 2 oktober 2023;Overwegende dat de vzw "Rainbow House" voldoet aan de criteria vastgelegd in artikelen 8 en 10 van het voornoemde koninklijk besluit van 2 oktober 2023 en is erkend als een koepel van organisaties;Op de voordracht van de Minister van Gelijke Kansen;Hebben Wij besloten en besluiten Wij :Artikel 1.  § 1. Een toelage van negenendertigduizend driehonderdzevenenzeventig euro en vijfentwintig cent (39.377,25 euro) wordt toegekend aan de vzw "Rainbow House", met zetel gevestigd te Kolenmarkt 42, 1000 Brussel (ondernemings-nummer 478 920 276 en rekeningnummer IBAN BE91 0689 4623 0276). § 2. De toelage is bedoeld ter financiële ondersteuning van de jaarlijkse werkingskosten in verband met de uitvoering van een werkprogramma in het kader van het federale beleid inzake bestrijding van discriminatie op grond van seksuele oriëntatie.Art. 2. De toelage bedoeld in artikel 1, wordt aangerekend op het activiteitenprogramma 58/5, basisallocatie 33.00.41, organisatieafdeling 12.58.52 van de administratieve begroting van de FOD Justitie voor het begrotingsjaar 2025.Art. 3. De periode waarop de toelage betrekking heeft, begint op 1 januari 2025 en eindigt op 31 maart 2025.Art. 4. De toelage bedoeld in artikel 1 wordt in twee schijven betaald, verdeeld op de volgende wijze:- een eerste schijf van negentig procent na ondertekening van dit besluit;- de tweede schijf van tien procent na de voorlegging van het eindverslag van de activiteiten en de bewijsstukken voor de volledige toelage.Art. 5.  § 1. Worden aanvaard als subsidieerbare kosten:1°  de kosten voor de huur, de huurlasten en het onderhoud van de gebouwen;2°  de personeelskosten en de kosten voor de aanwerving van het personeel en voor het personeelsbeheer;3°  de missiekosten en reiskosten;4°  de opleidingskosten;5°  de kosten voor administratief en boekhoudkundig beheer;6°  de kantoor- en informaticakosten;7°  de kosten inzake logistiek, communicatie en kantooruitrusting. § 2. De subsidie dekt geen kosten die reeds gedekt zijn door een andere vorm van subsidiering.Art. 6.  § 1. De vereniging verstuurt uiterlijk op 31 maart 2026 het eindverslag van de activiteiten alsook de financiële bewijsstukken naar de dienst Gelijke Kansen (Waterloolaan 115, 1000 Brussel of naar het e-mailadres: equal@just.fgov.be). § 2. Het eindverslag van de activiteiten bevat minstens een algemene beschrijving van de verwezenlijkte werkzaamheden, een synthese van de gevoerde acties, een evaluatie van de behaalde doelstellingen, een beschrijving van de eventuele ondervonden problemen met inbegrip van de obstakels bij de tenuitvoerlegging van de acties, een beschrijving van de faciliterende factoren, alsook alle noodzakelijke informatie die de dienst Gelijke Kansen in staat moet stellen om de verwezenlijking van die activiteiten te evalueren. § 3. De vereniging verstuurt eveneens een samenvattende tabel van alle bewijsstukken van de op deze toelage aangerekende uitgaven, met referentie naar de uitgavencategorieën. § 4. Bij ontstentenis van de volledige overlevering van de documenten, namelijk het eindverslag van de activiteiten en de bewijsstukken voor de volledige toelage, wordt de tweede schijf van de toelage niet uitbetaald en wordt, in voorkomend geval, de eerste schijf teruggevorderd voor het gedeelte van het bedrag dat niet naar behoren, overeenkomstig dit artikel, is gemotiveerd.Art. 7.  § 1. De begunstigde moet:- de bepalingen van de toekenning van de toelage volledig nakomen. Indien dat niet het geval is, kan hem een volledige of gedeeltelijke terugbetaling van de toegekende toelage worden gevraagd;- met betrekking tot het goede besteding van deze toelage enige controle van stukken en/of ter plekke aanvaarden;- het publiek in elk bericht of bij elke publiciteit op de hoogte brengen van de financiële hulp die ze in het kader van deze toelage hebben ontvangen. § 2. In het geval dat de toelage onrechtmatig werd gebruikt, is de dienst Gelijke Kansen van de FOD Justitie belast met de terugvordering van de bedragen. § 3. Indien blijkt dat te veel toelage werd toegekend voor het afgelopen jaar, wordt een beslissing tot terugvordering ter kennis gebracht bij aangetekende brief. Na verloop van een termijn van dertig dagen wordt de beslissing tot terugvordering definitief, tenzij de vereniging opmerkingen heeft laten toekomen. In dat geval wordt de definitieve beslissing uiterlijk twee maanden na ontvangst van de opmerkingen ter kennis van de vereniging gebracht. De vereniging stort het verschuldigde bedrag uiterlijk drie maanden na de definitieve beslissing tot terugvordering terug.Art. 8. Dit besluit heeft uitwerking met ingang van 1 januari 2025.Art. 9. Het lid van de regering dat bevoegd is voor Gelijke Kansen is belast met de uitvoering van dit besluitGegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister voor Gelijke Kansen,R. BEENDERS 
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2025003893</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>27 mei 2025</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>5 mei 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur en van het koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-27&amp;numac_search=2025003893&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003893=7&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+VERSLAG AAN DE KONINGSire,AlgemeenHet koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur (hierna "KB toegankelijkheid"), zette richtlijn (EU) 2019/882 van het Europees Parlement en de Raad van 17 april 2019 betreffende de toegankelijkheidsvoorschriften voor producten en diensten, gedeeltelijk om. Volgens artikel 31 van deze richtlijn diende deze tegen 28 juni 2022 te zijn omgezet en vanaf 28 juni 2025 te worden toegepast.Het koninklijk besluit van 13 maart 2024 tot wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur (hierna "KB universele lader"), zette Richtlijn (EU) 2022/2380 van het Europees Parlement en de Raad van 23 november 2022 tot wijziging van Richtlijn 2014/53/EU betreffende de harmonisatie van de wetgevingen van de lidstaten inzake het op de markt aanbieden van radioapparatuur, gedeeltelijk om. Volgens artikel 2 van deze richtlijn diende deze tegen 28 december 2023 te zijn omgezet en vanaf 28 december 2024 te worden toegepast (voor bepaalde radioapparatuur).Er worden dus twee Europese richtlijnen omgezet door wijziging van hetzelfde koninklijk besluit, waarbij de volgens de Europese deadline eerste omzetting later moet in werking treden dan de tweede. Aangezien de eerste omzetting nog niet in werking was ten tijde van de tweede omzetting, kon het niet anders dan bij de tweede omzetting uit te gaan van het koninklijk besluit zoals nog niet gewijzigd door de eerste omzetting. Tegen dat de eerste omzetting in werking treedt, is echter ook de tweede omzetting al in werking getreden. Bijgevolg is het uitgangspunt bij de inwerkingtreding van de eerste omzetting het koninklijk besluit zoals gewijzigd door de tweede omzetting. Daardoor klopt de formulering van bepaalde wijzigingen van de eerste omzetting niet meer. Die was immers gebaseerd op de tekst zoals nog niet gewijzigd door de tweede omzetting. Vandaar wijzigt het voorliggende koninklijk besluit die formulering (artikelen 5 en 6) en laat deze in werking treden samen met de eerste omzetting. Ook wordt het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur zelf (hierna "KB radioapparatuur") gewijzigd om de tekst ingevoegd door de tweede omzetting waar nodig aan te passen aan de eerste omzetting. Aangezien ten tijde van de tweede omzetting de eerste omzetting nog niet in werking was getreden, kon daar geen rekening mee worden gehouden (artikelen 2 en 4). Verder worden met het voorliggende koninklijk besluit ook een paar materiële vergissingen rechtgezet (artikelen 1, 3, 7 en 8). Het gaat hier dus louter om wetstechnische wijzigingen en niet om inhoudelijke.Advies 77.399/4 van de Raad van State van 12 februari 2025 werd integraal gevolgd.Artikelsgewijze besprekingArtikel 1 Dit artikel zet een vergissing in de Franse tekst van het KB radioapparatuur recht: er dient te worden verwezen naar "alinéa" en niet naar "paragraphe". Artikelen 2 en 4In de tekst van het KB radioapparatuur die toegevoegd werd door het KB universele lader wordt op verschillende plaatsen verwezen naar artikel 4 § 8, derde lid ervan. Aangezien het KB toegankelijkheid een nieuw lid invoegt tussen het eerste en tweede lid van artikel 4 § 8, wijzigt vanaf dan het derde lid in het vierde lid en dient dus de verwijzing naar artikel 4, § 8, derde lid te wijzigen naar artikel 4, § 8, vierde lid. Waar in de Franse tekst per vergissing naar « paragraphe » in plaats van naar « alinéa » verwezen werd, wordt dit ook rechtgezet (artikel 2).Artikel 3Dit artikel wijzigt artikel 26, § 7, van het KB radioapparatuur. In artikel 26, § 7, wordt verwezen naar paragraaf 4, tweede lid. Het KB toegankelijkheid voegt een nieuw lid in tussen het eerste en tweede lid van paragraaf 4 zodat het tweede lid het derde lid wordt. De verwijzing in artikel 26, § 7, wordt in die zin aangepast.Artikel 5Het lid van artikel 4, § 8, dat gewijzigd wordt door artikel 5, 9°,  c) van het KB toegankelijkheid werd eerder al gewijzigd door het KB universele lader. De wijziging die het KB toegankelijkheid doorvoert, dient dus te gebeuren op de tekst zoals gewijzigd door het KB universele lader. Aangezien dat niet het geval was, wordt de formulering van de wijziging die artikel 5, 9°,  c) van het KB toegankelijkheid doorvoert in die zin aangepast.Artikel 6Dit betreft de rechtzetting van een vergissing in het KB toegankelijkheid. De aangegeven wijziging is bedoeld voor het opschrift van hoofdstuk 3, afdeling 5 van het KB radioapparatuur en niet hoofdstuk 4. Artikel 7Door de toepassing van artikel 23, 1°,  van het KB toegankelijkheid in zijn huidige vorm zouden in de Franse tekst van artikel 28 § 1 van het KB radioapparatuur de woorden "l'article 26" twee keer na elkaar komen te staan, wat niet de bedoeling is. Deze wijziging dient dus om dit te voorkomen.Artikel 8Deze rechtzettingen i.v.m. het KB toegankelijkheid krijgen logischerwijze dezelfde datum van inwerkingtreding als het KB toegankelijkheid zelf. Enkel artikel 1 dient vroeger in werking te treden rekening houdend met de opmerking van de Raad van State (voetnoot 7 van zijn advies). Dit om verwarring te vermijden over de in artikel 1 bedoelde verbetering. Deze slaat op artikel 4, § 8, derde lid, van het KB radioapparatuur dat door de inwerkingtreding van het KB toegankelijkheid echter het vierde lid zal worden. Artikel 9Deze bepaling behoeft geen commentaar.Ik heb de eer te zijn,Sire,Van Uwe Majesteit,de zeer eerbiedige en zeer getrouwe dienaar,De Minister van Telecommunicatie,V. MATZRAAD VAN STATEAfdeling WetgevingAdvies 77.399/4 van 12 februari 2025 over een ontwerp van koninklijk besluit `houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur en van het koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur'Op 14 januari 2025 is de Raad van State, afdeling Wetgeving, door de Vice-eersteminister en Minister van Ambtenarenzaken, Overheidsbedrijven, Telecommunicatie en Post verzocht binnen een termijn van dertig dagen een advies te verstrekken over een ontwerp van koninklijk besluit `houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur en van het koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur'.Het ontwerp is door de vierde kamer onderzocht op 12 februari 2025. De kamer was samengesteld uit Bernard BLERO, kamervoorzitter, Géraldine ROSOUX en Dimitri YERNAULT, staatsraden, Christian BEHRENDT en Jacques ENGLEBERT, assessoren, en Anne-Catherine VAN GEERSDAELE, griffier.Het verslag is uitgebracht door Julien GAUL, auditeur.De overeenstemming tussen de Franse en de Nederlandse tekst van het advies is nagezien onder toezicht van Géraldine ROSOUX.Het advies, waarvan de tekst hierna volgt, is gegeven op 12 februari 2025.Aangezien de adviesaanvraag ingediend is op basis van artikel 84, § 1, eerste lid, 2°,  van de wetten `op de Raad van State', gecoördineerd op 12 januari 1973, beperkt de afdeling Wetgeving zich, overeenkomstig artikel 84, § 3, van de gecoördineerde wetten, voornamelijk tot het onderzoek van de bevoegdheid van de steller van de handeling, de rechtsgrond en de vraag of de voorgeschreven vormvereisten zijn vervuld.VOORAFGAANDE VORMVEREISTEN1. De gemachtigde beaamt dat sommige bepalingen van het ontwerp rechtsgrond vinden in artikel 32, § 3, tweede lid, en § 4, derde lid, van de wet van 13 juni 2005 `betreffende de elektronische communicatie', welk artikel ertoe verplicht het advies in te winnen van het Belgisch Instituut voor postdiensten en telecommunicatie.Er moet op toegezien worden dat dit vormvereiste naar behoren vervuld wordt.2. Artikel 9, tweede lid, van het samenwerkingsakkoord van 17 november 2006 `tussen de Federale Staat, de Vlaamse Gemeenschap, de Franstalige Gemeenschap en de Duitstalige Gemeenschap betreffende het wederzijds consulteren bij het opstellen van regelgeving inzake elektronische communicatienetwerken, het uitwisselen van informatie en de uitoefening van de bevoegdheden met betrekking tot elektronische communicatienetwerken door de regulerende instanties bevoegd voor telecommunicatie of radio-omroep en televisie' luidt als volgt:"Het Interministerieel Comité voor Telecommunicatie en Radio-omroep en Televisie heeft tot taak om in onderling overleg en met respect voor ieders bevoegdheid, volgens de modaliteiten en procedures zoals vastgelegd binnen het Overlegcomité, de wederzijdse consultatie te organiseren omtrent mekaars initiatieven inzake het opstellen van ontwerpregelgeving met betrekking tot omroep en telecommunicatie."Aangezien het ontwerp het op de markt aanbieden van radioapparatuur betreft, vormt het een "ontwerpregelgeving met betrekking tot omroep en telecommunicatie" in de zin van het samenwerkingsakkoord van 17 november 2006.De afdeling Wetgeving heeft aan de hand van het dossier dat haar voorgelegd is niet kunnen vaststellen of die wederzijdse consultatie plaatsgevonden heeft.Er moet op toegezien worden dat dit vormvereiste naar behoren vervuld wordt.3. Indien de aan de Raad van State voorgelegde tekst naar aanleiding van het vervullen van die vormvereisten nog wijzigingen zou ondergaan die niet louter vormelijk zijn en die niet het resultaat zijn van het gevolg dat aan dit advies wordt gegeven, moeten de gewijzigde of toegevoegde bepalingen op hun beurt om advies aan de afdeling Wetgeving worden voorgelegd, overeenkomstig artikel 3, § 1, eerste lid, van de gecoördineerde wetten `op de Raad van State'.De vervulling van die vormvereisten moet bovendien in de aanhef vermeld worden.ALGEMENE OPMERKINGEN1. Voor elk gewijzigd artikel dienen de opeenvolgende vroegere wijzigingen daarvan opgegeven te worden, overeenkomstig de regels opgenomen in de Handleiding voor het opstellen van wetgevende en reglementaire teksten.1 Bijgevolg dienen de volgende preciseringen aangebracht te worden:- artikel 4, § 8, derde lid, van het koninklijk besluit van 25 maart 2016 `betreffende het op de markt aanbieden van radioapparatuur' is ingevoegd bij het koninklijk besluit van 13 maart 2024 `tot wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur'2 (artikel 1 van het ontwerp);- de artikelen 6, § 4, tweede lid, en 7, § 2, tweede lid (lees derde lid), van het koninklijk besluit van 25 maart 2016 zijn ingevoegd bij het koninklijk besluit van 13 maart 20243 (artikel 2 van het ontwerp);- artikel 28, eerste lid, h), van het koninklijk besluit van 25 maart 2016 is vervangen bij het koninklijk besluit van 13 maart 20244 (artikel 4 van het ontwerp);- artikel 4, § 8, tweede lid5, van het koninklijk besluit van 25 maart 2016 is gewijzigd bij het koninklijk besluit van 13 maart 20246 (artikel 5 van het ontwerp).2. Gelet op de wijze waarop het ontwerpbesluit gesteld is7, moet de steller zich ervan vergewissen of het feit dat de inwerkingtreding van dat besluit samenvalt met die van het koninklijk besluit van 13 september 2023 `houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur', te weten 28 juni 2025, een duidelijke en coherente samenhang waarborgt tussen de wijzigingen die respectievelijk aangebracht worden bij het ontwerp en bij het koninklijk besluit van 13 september 2023.BIJZONDERE OPMERKINGENAANHEFIn het eerste lid moet eveneens verwezen worden naar artikel 32, § 3, tweede lid, en § 4, derde lid, van de wet van 13 juni 2005, dat vervangen is bij de wet van 18 december 2015.DISPOSITIEFArtikel 6Bij artikel 6 van het koninklijk besluit van 13 maart 2024 wordt geen tweede lid ingevoegd in artikel 7, § 2, van het koninklijk besluit van 25 maart 2016 maar wordt dat artikel aangevuld met een lid. De gemachtigde is het ermee eens dat de bij artikel 6 van het ontwerp beoogde wijziging geen bestaansgrond heeft. De bepaling moet weggelaten worden.De Griffier   De VoorzitterAnne-Catherine VAN GEERSDAELE   Bernard BLERO_______Nota's1 Beginselen van de wetgevingstechniek-Handleiding voor het opstellen van wetgevende en reglementaire teksten, www.raadvst-consetat.be, tab "Wetgevingstechniek", aanbeveling 113 en volgende.2 Artikel 4, 2°,  van het koninklijk besluit van 13 maart 2024. Behalve wat laptops betreft, is dat koninklijk besluit van 13 maart 2024 in werking getreden op 28 december 2024 (zie artikel 12 van dat besluit).3 Respectievelijk bij de artikelen 5 en 6 van het koninklijk besluit van 13 maart 2024.4 Artikel 10, 2°,  van het koninklijk besluit van 13 maart 2024.5 Dat het derde lid zal worden bij de inwerkingtreding van artikel 5, 9°,  b), van het koninklijk besluit van 13 september 2023 `houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur'.6 Artikel 4, 1°,  van het koninklijk besluit van 13 maart 2024.7 Zo worden bij artikel 1 van het ontwerp wijzigingen aangebracht in artikel 4, § 8, derde lid, van het koninklijk besluit van 25 maart 2016 (ingevoegd bij artikel 4, 2°,  van het koninklijk besluit van 13 maart 2024) terwijl bij artikel 5, 9°,  b), van het koninklijk besluit van 13 september 2023 een nieuw lid ingevoegd zal worden tussen het eerste lid en het tweede lid van artikel 4, § 8, waardoor het huidige derde lid het vierde lid zal worden. Bovendien worden bij het ontwerpbesluit wijzigingen aangebracht in het koninklijk besluit van 13 september 2023.5 MEI 2025. - Koninklijk besluit houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur en van het koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuurFILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 13 juni 2005 betreffende de elektronische communicatie, artikel 32, § 2/1, ingevoegd bij de wet van 6 februari 2024, § 3, tweede lid, § 4, derde lid, vervangen bij de wet van 18 december 2015 en artikel 38/1, ingevoegd bij de wet van 20 juli 2023;Gelet op het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur;Gelet op het koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur;Gelet op advies 77.399/4 van de Raad van State, gegeven op 12 februari 2025, met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Gelet op het advies van het Belgisch Instituut voor postdiensten en telecommunicatie van 7 april 2025;Gelet op de raadpleging van 16 april 2025 tot 25 april 2025 van het Interministerieel Comité voor Telecommunicatie en Radio-omroep en Televisie;Op de voordracht van de Minister van Telecommunicatie,Hebben Wij besloten en besluiten Wij :Artikel 1. In artikel 4, § 8, derde lid, van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur, ingevoegd bij het koninklijk besluit van 13 maart 2024, wordt in de Franse tekst het woord "paragraphe" vervangen door het woord "alinéa".Art. 2. In artikel 6, § 4, tweede lid en in artikel 7, § 2, derde lid, van hetzelfde besluit, ingevoegd bij het koninklijk besluit van 13 maart 2024, worden de woorden "derde lid" vervangen door de woorden "vierde lid".Art. 3. In artikel 26 § 7 van hetzelfde besluit, worden de woorden "tweede lid" vervangen door de woorden "derde lid".Art. 4. In artikel 28, eerste lid, bepaling onder h), van hetzelfde besluit, vervangen bij het koninklijk besluit van 13 maart 2024, worden de woorden "derde lid" vervangen door de woorden "vierde lid".Art. 5. Artikel 5, 9°,  c) van het koninklijk besluit van 13 september 2023 houdende wijziging van het koninklijk besluit van 25 maart 2016 betreffende het op de markt aanbieden van radioapparatuur wordt vervangen als volgt: "c) in het vroegere tweede lid, gewijzigd bij het koninklijk besluit van 13 maart 2024, dat het derde lid wordt, worden de woorden "De instructies bevatten" vervangen door de woorden "Wat de essentiële eisen betreft, bevatten de instructies".Art. 6. In artikel 9 van hetzelfde besluit worden de woorden "hoofdstuk 4" vervangen door de woorden "hoofdstuk 3".Art. 7. In artikel 23, 1°  van hetzelfde besluit worden in de Franse tekst de woorden "l'article 26" geschrapt.Art. 8. Artikel 1 treedt in werking op 27 juni 2025.De artikelen 2 tot 7 treden in werking op 28 juni 2025.Art. 9. De minister bevoegd voor Telecommunicatie wordt belast met de uitvoering van dit besluit.Gegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister van Telecommunicatie,V. MATZ 
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2025003755</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>28 mei 2025</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>5 mei 2025. - Koninklijk besluit houdende ontslag en benoeming van een regeringscommissaris en ontslag van een plaatsvervangend regeringscommissaris bij het Bureau voor Normalisatie</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-28&amp;numac_search=2025003755&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003755=8&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 16 maart 1954 betreffende de controle op sommige instellingen van openbaar nut, artikel 9, § 1, tweede lid;Overwegende het Wetboek van economisch recht, artikel VIII.3;Overwegende het koninklijk besluit van 10 augustus 2009 houdende ontslag en benoeming van een regeringscommissaris en van een plaatsvervangende regeringscommissaris bij het Bureau voor normalisatie;Overwegende het koninklijk besluit van 24 december 2020 houdende ontslag en benoeming van een plaatsvervangend regeringscommissaris bij het Bureau voor Normalisatie;Op de voordracht van de Minister van Economie,Hebben Wij besloten en besluiten Wij :Artikel 1. Aan dhr. Renaud Collette, adviseur, wordt eervol ontslag verleend als regeringscommissaris bij het Bureau voor Normalisatie.Art. 2. Dhr. Herman Van den Langenbergh, adviseur-generaal, wordt benoemd tot regeringscommissaris bij het Bureau voor Normalisatie.Art. 3. Aan dhr. Chris Van der Cruyssen, adviseur-generaal, wordt eervol ontslag verleend als plaatsvervangend regeringscommissaris bij het Bureau voor Normalisatie.Art. 4. De regeringscommissaris bij het Bureau voor Normalisatie oefent zijn bevoegdheden uit overeenkomstig de bepalingen van de wet van 16 maart 1954 betreffende de controle op sommige instellingen van openbaar nut. Hij brengt verslag uit aan de minister bevoegd voor Economie, in het bijzonder aangaande alle beslissingen van de Raad van Bestuur van het Bureau voor Normalisatie.Art. 5. De minister bevoegd voor Economie is belast met de uitvoering van dit besluit.Gegeven te Brussel, 5 mei 2025.FILIPVan Koningswege :De Minister van Economie,D. CLARINVAL 
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2025003802</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>21 mei 2025</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>29 april 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat wat betreft de concessie</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-21&amp;numac_search=2025003802&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003802=9&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+VERSLAG AAN DE KONINGSire, Het voorgestelde besluit beoogt de concessieprocedure, zoals bepaald in het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat, aan te passen rekening houdend met de wijzigingen aangebracht aan de milieuvergunningsprocedure. Deze laatste werd recent gewijzigd bij het koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden. De wet van 13 juni 1969 inzake de exploratie en de exploitatie van de niet-levende rijkdommen van de territoriale zee en het continentaal plat, schrijft immers dat er voor de exploratie en/of de exploitatie van minerale en andere niet-levende rijkdommen van de zeebodem zowel een milieuvergunning als een concessie vereist is. Deze kunnen dus afzonderlijk worden toegekend, maar beiden zijn noodzakelijk om te kunnen overgaan tot exploratie en/of exploitatie. Om de verschillende procedures betreffende milieuvergunning en concessie beter op elkaar te laten aansluiten, werden er een aantal specifieke wijzigingen aangebracht. De Raad van State adviseert in haar advies 77.319/1 van 14 januari 2025 om de samenhang tussen enkele van deze wijzigingen te verduidelijken. Hierbij refereert hij naar het ontworpen artikel 20, tweede lid, het nieuw artikel 22/1 en het artikel 26, eerste lid.In het oorspronkelijke artikel 20 werd er voorzien dat elke verlengingsaanvraag moest worden ingediend ten minste één jaar voor het verstrijken van de geldigheidsduur van de concessievergunning. In het verleden was deze termijn ingesteld om ervoor te zorgen dat de concessie werd verlengd voordat deze zou aflopen. Deze aansluiting is belangrijk omdat enkel een verlenging van concessie toelaat om rekening te blijven houden met de ontgonnen volumes van de laatste vijf jaar bij het bepalen van het jaarlijkse maximale exploitatievolume per concessiehouder overeenkomstig artikel 26, eerste lid. Indien er een onderbreking is tussen de aflopende concessievergunning en de vernieuwing ervan, moest de concessievernieuwing beschouwd worden als een `nieuwe' concessieaanvraag, waarbij er aan de concessiehouder slechts het minimale volume van 30.000 m3 kan worden toegekend, overeenkomstig artikel 26, tweede lid.Het koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden koppelt de procedure tot het bekomen van een milieuvergunning in het kader van de exploratie en/of exploitatie van de zeebodem los van de procedure tot het bekomen van een concessie. Dit betekent enerzijds dat moet worden voorzien in maatregelen die een verval van concessie voorzien indien de milieuvergunning wordt opgeheven of vervallen wordt verklaard, en anderzijds dat moet worden voorzien in maatregelen om de mogelijkheid op te vangen dat een verlenging van de milieuvergunning wordt aangevraagd en toegekend maar dat de verlenging van de concessievergunning niet bekomen kan worden voordat deze afloopt. In het ontworpen artikel 22/1 worden dus de gevolgen voor de concessie vastgelegd indien de milieuvergunning wordt opgeheven of vervallen worden verklaard.Artikel 20, tweede lid, heeft als doel om de concessiehouder te behoeden voor verlies van zijn ontginningsvolume omwille van procedurele redenen. Het koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden legt geen periode vast waarbinnen de milieuvergunning dient te worden aangevraagd. Het gevaar bestaat dus dat een verlenging van de milieuvergunning wordt aangevraagd en toegekend maar dat de verlenging van de concessievergunning niet bekomen kan worden vóór het verstrijken van de concessie. Het tweede lid van artikel 20 laat dan ook toe dat de concessiehouder die de milieuvergunningsprocedure succesvol heeft doorlopen en dus een milieuvergunning heeft verkregen en die een verlengingsaanvraag voor de concessie heeft ingediend voordat deze verstrijkt, de zekerheid heeft dat eens de concessieprocedure positief is beëindigd, de volumes die de laatste vijf jaar zijn ontgonnen onder zijn concessie in aanmerking worden genomen om het maximale jaarlijkse exploitatievolume te bepalen. Uiteraard zal er geen rekening gehouden kunnen worden met de ontgonnen hoeveelheden van de laatste vijf jaar indien de concessiehouder een verlening van concessie aanvraagt na het verstrijken van de geldigheidstermijn van deze of indien de verlengingsaanvraag van de concessie wordt afgewezen.Deze aansluiting van concessies is ook belangrijk voor de schatting van het beschikbare volume voor de andere concessiehouders. De volumes voor het volgende jaar worden overeenkomstig artikel 26, eerste lid, berekend en medegedeeld aan de concessiehouders vóór 01/08/X-1. Indien het tweede lid niet zou zijn voorzien, zouden de volumes meegedeeld aan de concessiehouders, onzeker zijn. De volumes zouden immers nog kunnen dalen of stijgen naargelang de procedure van een verlenging al dan niet op tijd zou afgerond geraken. Dergelijke onzekerheid zou niet getuigen van goed beheer vanwege de Belgische Staat.Een ander gevolg van het opsplitsen van de procedure in een milieuvergunningsprocedure en een concessieprocedure, is dat de bepalingen van de milieuvergunning in werking zijn getreden op 31 december 2024. De Raad van State raadde in zijn advies nr. 77.319/1 van 14 januari 2025 aan om te voorzien in overgangsmaatregelen om redenen van noodzaak voor de continuïteit en de goede werking van het bestuur. Artikel 26 van het wijzigingsbesluit voorziet dan ook in een overgangsbepaling voor de concessieaanvraag. Indien een aanvraag werd ingediend voor de inwerkingtreding van dit besluit, blijven de oude regels van kracht en wordt de vergunning verleend, verlengd, gewijzigd, uitgebreid, overgedragen of ingetrokken met toepassing van de oude regels. Zo dienen er niet halverwege een procedure nieuwe bepalingen te worden toegepast. Dit zou voor onnodige verwarring en rechtsonzekerheid zorgen. Dit betekent voor wat het luik milieueffectenbeoordeling betreft, dat de aanvragen die ingediend zijn vóór 31 december 2024 beoordeeld zullen worden op grond van het koninklijk besluit van 21 oktober 2018 houdende de regels betreffende de milieueffectenbeoordeling in toepassing van de wet van 13 juni 1969 inzake de exploratie en exploitatie van niet-levende rijkdommen van de territoriale zee en het continentaal plat. Indien dus deze aanvragen aanleiding geven tot een concessie, dan zullen deze toekenningen van concessie geen milieuvergunning inhouden, maar wel een beoordeling van de milieueffecten, zoals het geval was voor de inwerkingtreding van titel 5, hoofdstuk II, van het koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelatingen en Natura 2000-goedkeuringen en tot milieuvergunning in de Belgische zeegebieden. De aanvragen die ingediend worden na 31 december 2024 zullen dus wel moeten beschikken over een milieuvergunning, zoals bepaald in het hierboven vermelde koninklijk besluit van 26 april 2024.Deze aanvragen zullen voor wat het luik concessie wel nog beoordeeld worden op grond van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat, zoals deze gold voor de inwerkingtreding van het ontworpen besluit. Hierdoor wordt de continuïteit en de goede werking van het bestuur verzekerd.Ik heb de eer te zijn,Sire,Van Uwe Majesteit,de zeer eerbiedige en zeer getrouwe dienaar,De Minister van Economie,D. CLARINVALRAAD VAN STATEAfdeling WetgevingAdvies 77.319/1 van 14 januari 2025 over een ontwerp van koninklijk besluit `tot wijziging van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet levende rijkdommen in de territoriale zee en op het continentaal plat wat betreft de concessie'Op 18 december 2024 is de Raad van State, afdeling Wetgeving, Minister van Economie verzocht binnen een termijn van dertig dagen een advies te verstrekken over een ontwerp van koninklijk besluit `tot wijziging van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat wat betreft de concessie'.Het ontwerp is door de eerste kamer onderzocht op 7 januari 2025. De kamer was samengesteld uit Pierre LEFRANC, wnd. kamervoorzitter, Brecht STEEN en Tim CORTHAUT, staatsraden, Michel TISON, assessor, en Eline YOSHIMI, griffier.Het verslag is uitgebracht door Katrien DIDDEN, auditeur.De overeenstemming tussen de Franse en de Nederlandse tekst van het advies is nagezien onder toezicht van Tim CORTHAUT, staatsraad.Het advies, waarvan de tekst hierna volgt, is gegeven op 14 januari 2025.1. Met toepassing van artikel 84, § 3, eerste lid, van de wetten op de Raad van State, gecoördineerd op 12 januari 1973, heeft de afdeling Wetgeving zich toegespitst op het onderzoek van de bevoegdheid van de steller van de handeling, van de rechtsgrond, alsmede van de vraag of aan de te vervullen vormvereisten is voldaan.VOORAFGAANDE OPMERKING2. Rekening houdend met het ogenblik waarop dit advies wordt gegeven, vestigt de Raad van State de aandacht van de adviesaanvrager erop dat de ontbinding van de Wetgevende Kamers tot gevolg heeft dat de regering sedert die datum en totdat, na de verkiezing van de Kamer van volksvertegenwoordigers, een nieuwe regering is benoemd door de Koning, niet meer over de volheid van haar bevoegdheid beschikt. Dit advies wordt evenwel gegeven zonder dat wordt nagegaan of dit ontwerp in die beperkte bevoegdheid kan worden ingepast, aangezien de afdeling Wetgeving geen kennis heeft van het geheel van de feitelijke gegevens die de regering in aanmerking kan nemen als ze te oordelen heeft of het vaststellen of het wijzigen van verordeningen noodzakelijk is.STREKKING VAN HET ONTWERP3. Overeenkomstig artikel 3, § 1, van de wet van 13 juni 1969 `inzake de exploratie en de exploitatie van niet-levende rijkdommen van de territoriale zee en het continentaal plat' is voor de exploratie en/of de exploitatie van de minerale en andere niet-levende rijkdommen van de zeebodem en van de ondergrond zowel een concessie als een milieuvergunning vereist. Een dergelijke concessie kan slechts worden toegestaan mits een milieuvergunning wordt toegekend1.De milieuvergunningsprocedure werd recent gewijzigd bij het koninklijk besluit van 26 april 2024 `betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden' (hierna: milieuvergunningsbesluit).Het om advies voorgelegde ontwerp strekt er in hoofdzaak toe de concessieprocedure, zoals bepaald in het koninklijk besluit van 1 september 2004 `betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat' aan te passen in het licht van de wijzigingen in de milieuvergunningsprocedure.RECHTSGROND4. De ontworpen regeling vindt rechtsgrond in het in de aanhef vermelde artikel 3, § 2, van de wet van 13 juni 1969, dat de Koning machtigt om, op voordracht van de minister bevoegd voor Economie, de voorwaarden en nadere regels tot toekenning van de concessie voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen van de zeebodem vast te stellen.In de mate dat de ontworpen bepalingen bovendien verband houden met de nieuwe regeling voor de milieuvergunning, kan bijkomend rechtsgrond worden gevonden in artikel 3, § 3, van de wet van 13 juni 1969. ONDERZOEK VAN DE TEKSTAanhef5. Het eerste lid van de aanhef dient als volgt te worden geformuleerd:"Gelet op de wet van 13 juni 1969 inzake de exploratie en de exploitatie van de niet levende rijkdommen van de territoriale zee en het continentaal plat, artikel 3, §§ 2 en 3, vervangen bij de wet van 11 december 2022".Artikel 46.1. De invoering van het enkelvoud in het ontworpen artikel 8, § 1, eerste lid, van het koninklijk besluit van 1 september 2004 kan fout worden begrepen. Door te spreken van "de concessieaanvraag voor de exploratie en de exploitatie van de niet-levende rijkdommen van de territoriale zee en het continentaal plat" kan de indruk worden gewekt dat er voortaan maar één concessieaanvraag mogelijk is, en dat die bovendien op zowel de exploratie als de exploitatie betrekking moet hebben, terwijl meerdere concessies kunnen worden verleend en dit voor zowel exploratie, exploitatie als de combinatie van beide. De redactie van het ontworpen artikel 8 van het koninklijk besluit van 1 september 2004 moet worden heroverwogen teneinde op ondubbelzinnige en consistente wijze de bedoelde draagwijdte ervan tot uiting te brengen.6.2. In artikel 4, 4°,  van het ontwerp moet de te vervangen Nederlandse tekst als volgt luiden: "in het geval van een exploratie- en/of exploitatieaanvraag in de controlezones".6.3.De tekst van artikel 4, 5°,  van het ontwerp wordt beter als volgt verwoord: "paragraaf 2, eerste lid, 5°,  gewijzigd bij het koninklijk besluit van 19 april 2014, wordt opgeheven;"Artikel 77. Het ontworpen artikel 11, § 1, tweede lid, laatste zin, van het koninklijk besluit van 1 september 2004 stelt dat het besluit tot verlening van de milieuvergunning aan de commissie wordt bezorgd binnen de veertien dagen na ontvangst van het besluit zoals voorzien in artikel 103, § 6, van het milieuvergunningsbesluit2. Op de vraag wat precies moet worden verstaan onder de ontvangst "zoals voorzien in artikel 103, § 6, van het milieuvergunningsbesluit", nu dit artikel de betekening aan de dienst Continentaal plat regelt, antwoordde de gemachtigde:"De dienst Marien Milieu bezorgt het besluit van de minister wat betreft de milieuvergunning digitaal aan de leden van de Raadgevende Commissie overeenkomstig artikel 83, § 3, juncto artikel 102 van het koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden. Het besluit wordt eveneens aan de dienst Continentaal Plat verstuurd overeenkomstig artikel 78, § 2, juncto artikel 103, § 6 van hetzelfde koninklijk besluit van 26 april 2024. De dienst kan er dan ook over waken dat de beslissing wordt bezorgd aan de Raadgevende Commissie binnen de periode voorzien in het nieuwe artikel 11, § 1, tweede lid."Ter wille van de rechtszekerheid dient in de tekst te worden verduidelijkt door wie het besluit tot verlening van de milieuvergunning aan de commissie wordt bezorgd en op welk ogenblik de bedoelde termijn van veertien dagen ingaat.Artikel 128. In de inleidende zin van artikel 12 moet de verwijzing naar het koninklijk besluit van 21 oktober 2018 worden weggelaten.Meer algemeen verdient het aanbeveling om de nog relevante wetsgeschiedenis van de verschillende bepalingen die door het ontwerp worden gewijzigd te verifiëren.Artikel 149. Het ontworpen artikel 20, tweede lid, van het koninklijk besluit van 1 september 2004 luidt als volgt:"Indien het besluit tot verlening van milieuvergunning werd toegekend vóór het verstrijken van de geldigheidsduur van de exploratie- of exploitatieconcessie, wordt er bij het bepalen van de maximale toegestane jaarlijkse exploitatievolumes rekening gehouden met de ontgonnen hoeveelheden gedurende de vorige 5 jaar, overeenkomstig artikel 26, eerste lid."De noodzaak van het ontworpen artikel 20, tweede lid, van het koninklijk besluit van 1 september 2004 is niet evident, nu het ontworpen artikel 26, eerste lid, van dat koninklijk besluit erin voorziet dat de minister in elk geval jaarlijks het maximaal exploitatievolume per concessiehouder vaststelt, waarbij eveneens rekening moet worden gehouden met de ontgonnen hoeveelheden van de vorige vijf jaar en waarnaar in de ontworpen bepaling ook wordt verwezen. Daarbij lijkt het ook irrelevant wanneer de milieuvergunning werd verleend3. Bijgevolg worden de stellers van het ontwerp uitgenodigd om de samenhang tussen de ontworpen artikelen 20, tweede lid, 22/1 en 26, eerste lid, van het koninklijk besluit van 1 september 2004 beter tot uiting te brengen in het te nemen besluit.Artikelen 15 en 1610. De ontworpen artikelen 22 en 22/1 van het koninklijk besluit van 1 september 2004, voorzien in een "intrekking voor verval van de concessie", bij het niet naleven van de voorwaarden van de concessie, of indien de milieuvergunning is opgeheven of vervallen. Hoewel daarbij wordt aangesloten bij de bestaande terminologie van het koninklijk besluit van 1 september 2004,4 moet worden vastgesteld dat die term niet ondubbelzinnig is en tot rechtsonzekerheid aanleiding kan geven.Vooreerst moet worden opgemerkt dat de Nederlandse woordgroep "intrekking voor verval van de concessie" een slechte vertaling is van de Franse tekst, en er veeleer bedoeld wordt "intrekking wegens het verval van de concessie".Daarnaast moet worden vastgesteld dat met "de intrekking" ("le retrait") in kwestie eigenlijk iets anders wordt bedoeld dan wat in het administratief recht gebruikelijk onder de intrekking van een administratieve rechtshandeling wordt verstaan, met name het met terugwerkende kracht verwijderen van die handeling uit het rechtsverkeer zodat ze wordt geacht nooit uitwerking te hebben gehad5. In casu wordt de concessie immers niet met terugwerkende kracht ongedaan gemaakt, maar wordt ze slechts beëindigd voor de toekomst nadat de minister heeft vastgesteld dat daartoe aanleiding is wegens het niet naleven van de voorwaarden van de concessie (ontworpen artikel 22) of wegens de opheffing of het verval van de milieuvergunning (ontworpen artikel 22/1). In die zin is de "intrekking" te beschouwen als een opheffing.Het is bovendien dubbelop om te spreken van een intrekking (lees: opheffing) voor (lees: wegens) het verval van de concessie, aangezien het verval taalkundig zelf al het einde van de concessie impliceert, zodat een "opheffing wegens het verval van de concessie" beëindigt wat al beëindigd is.Correcter zou zijn om consistent de term "vervallenverklaring van de concessie" ("déclaration de déchéance de la concession") te gebruiken. Op die manier wordt beter tot uiting gebracht dat de beslissing van de minister leidt tot de beëindiging van de concessie.De ontworpen artikelen 22 en 22/1 van het koninklijk besluit van 1 september 2004 moeten in het licht daarvan worden aangepast. Dezelfde terminologische aanpassing moet dan ook worden doorgevoerd in het opschrift van hoofdstuk VII van dat besluit, evenals in artikel 21 van dat besluit.Artikel 2411. Artikel 24 van het ontwerp voorziet in de inwerkingtreding van onder meer titel 5, hoofdstuk II (artikel 24, 1° ) en artikel 111, 4°,  (artikel 24, 2° ) van het milieuvergunningsbesluit op de tiende dag na de bekendmaking ervan in het Belgisch Staatsblad.Overeenkomstig artikel 114 van het milieuvergunningsbesluit treden titel 5, hoofdstuk II en artikel 111, 4°,  van dit besluit in werking "op een door Ons vast te stellen datum en uiterlijk op 31 december 2024". Bij gebrek aan andere regeling zijn de in artikel 24, 1°  en 2°  vermelde bepalingen bijgevolg al in werking getreden op 31 december 2024, zodat de inwerkingtredingsbepaling in artikel 24, 1°  en 2°,  van het ontwerp geen doel meer kan treffen. Artikel 24, 3°,  van het ontwerp, dat de inwerkingtreding van het te nemen besluit bepaalt op de tiende dag na bekendmaking ervan in het Belgisch Staatsblad, bevestigt dan nog enkel de basisregel,6 en is dan verder overbodig.Hierop gewezen, verklaarde de gemachtigde het volgende:"Het dossier heeft helaas een langere doorlooptijd gekend alvorens het ingediend werd bij de Raad van State. Hierdoor is de oorspronkelijke doelstelling, namelijk een publicatie in het Belgisch Staatsblad alvorens de datum van 31 december 2024, helaas niet gehaald. We stellen dan ook voor om de inwerkingtreding van het betrokken besluit inderdaad te voorzien voor 31 december 2024, zodoende dat er geen vacuüm en rechtsonzekerheid ontstaat wat de procedures betreft en dus om artikel 24, 1°  en 2°  van het ontwerp te laten vallen. Artikel 24 van het ontwerp zou dan luiden: `Dit besluit heeft uitwerking met ingang van 31 december 2024.' (`Le présent arrêté produit ses effets le 31 décembre 2024.')."11.1. Met de weglating van artikel 24, 1°  en 2°,  van het ontwerp kan worden ingestemd.11.2. De suggestie van de gemachtigde om het besluit zelf uitwerking te geven met ingang van 31 december 2024 zou echter tot gevolg hebben dat aan het te nemen besluit terugwerkende kracht wordt verleend.Het verlenen van terugwerkende kracht aan besluiten kan slechts onder bepaalde voorwaarden toelaatbaar worden geacht, namelijk wanneer ofwel voor de retroactiviteit een wettelijke grondslag bestaat, ofwel de retroactiviteit betrekking heeft op een regeling waarbij, met inachtneming van het gelijkheidsbeginsel, voordelen worden toegekend ofwel de retroactiviteit noodzakelijk is voor de continuïteit of de goede werking van het bestuur en daardoor, in beginsel, geen verkregen situaties worden aangetast. Enkel indien de retroactiviteit van de ontworpen regeling in één van de opgesomde gevallen valt in te passen, kan deze worden gebillijkt.Volgens de gemachtigde is de terugwerkende kracht nodig om te vermijden dat er een vacuüm en rechtsonzekerheid zou ontstaan wat de procedures betreft. Aldus lijkt de gemachtigde te refereren aan de noodzaak voor de continuïteit of de goede werking van het bestuur.11.3. Niettemin moet worden vastgesteld dat verschillende bepalingen van het ontwerp betrekking hebben op procedurele voorschriften, die uit de aard ervan niet met terugwerkende kracht uitwerking kunnen hebben. Wat de materiële bepalingen betreft kan de terugwerkende kracht slechts worden aanvaard voor zover die in te passen is in de in opmerking 11.2 vermelde gevallen.11.4. Het komt de Raad van State echter voor dat de doelstelling van de gemachtigde ook bereikt kan worden zonder een beroep te doen op de terugwerkende kracht. Het lijkt feitelijk te volstaan om de bekendmaking en inwerkingtreding van het te nemen besluit te bespoedigen - bijvoorbeeld op de dag van die bekendmaking - en de inwerkingtredingsbepaling aan te vullen met een overgangsbepaling7 die stipuleert dat op de dag van inwerkingtreding van het te nemen besluit nog hangende aanvragen die werden ingediend voor de datum van inwerkingtreding van het te nemen besluit geacht worden te zijn ingediend onder het koninklijk besluit van 1 september 2004, zoals gewijzigd door het te nemen besluit, en in overeenstemming daarmee zullen worden beoordeeld.8De Griffier,   De Voorzitter,E. Yoshimi   P. Lefranc_______Nota's1 Artikel 3, § 2, tweede lid, van de wet van 13 juni 1969.Artikel 103, § 6, van het milieuvergunningsbesluit luidt als volgt:2 " § 6. De minister betekent het besluit waarvan sprake in artikel 78, § 2 en in artikel 91, § 4, eveneens aan de dienst Continentaal plat".3 Gelet op het ontworpen artikel 22/1 van het koninklijk besluit van 1 september 2004 is het immers niet evident dat er een verlenging van een concessie zou kunnen worden verleend zonder nog lopende (en dus per definitie vooraf toegekende) milieuvergunning, nu de opheffingof het verval van de milieuvergunning volgens die bepaling resulteert in de beëindiging van de concessie. 4 Naar aanleiding van eerdere opmerkingen van de Raad van State werd al het onderscheid tussen de verschillende gevallen van beëindiging van de concessie, namelijk het verstrijken van de concessie, het "intrekken" door de minister en de verzaking door de houder van de concessie, verduidelijkt, zie adv.RvS 75.402/1 van 20 februari 2024 over een ontwerp dat heeft geleid tot het koninklijk besluit van 4 juli 2024 `tot wijziging van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat wat betreft het registreersysteem', opmerking 7. 5 Daar komt bij dat volgens de leer van de intrekking een individuele administratieve rechtshandeling die rechten heeft verleend (zoals het geval is bij een concessie) slechts kan worden ingetrokken wanneer of omdat die onwettig of onregelmatig is; omgekeerd kan een bestuurshandeling die wettig is niet worden ingetrokken, zie bv. RvS nr. 260.429 van 12 juli 2024, T.P. e.a. /Vlaams Gewest en OVAM, punt 8.19. 6 Artikel 6 van de wet van 31 mei 1961 `betreffende het gebruik der talen in wetgevingszaken, het opmaken, bekendmaken en inwerkingtreden van wetten en verordeningen'.7 Voor een gelijkaardige overgangsregeling in deze materie, zie artikel 30 van het koninklijk besluit van 21 oktober 2018 `houdende de regels betreffende de milieueffectenbeoordeling in toepassing van de wet van 13 juni 1969 inzake de exploratie en exploitatie van niet-levende rijkdommen van de territoriale zee en het continentaal plat'.8 De afdeling Wetgeving heeft geen aanwijzingen dat er sinds 31 december 2024 al concessies zouden zijn verleend op basis van de nog aan te nemen regels. Mocht dat toch het geval zijn, zouden die beslissingen uitdrukkelijk moeten worden bevestigd in een bijkomende overgangsbepaling.29 APRIL 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat wat betreft de concessieFILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 13 juni 1969 inzake de exploratie en de exploitatie van de niet-levende rijkdommen van de territoriale zee en het continentaal plat, artikel 3, §§ 2 en 3, vervangen bij de wet van 11 december 2022;Gelet op het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat;Gelet op het advies van de inspecteur van Financiën, gegeven op 2 september 2024;Gelet op advies 77.319/1 van de Raad van State, gegeven op 14 januari 2025, met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Overwegende het koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden;Overwegende het advies van de raadgevende Commissie belast met de coördinatie tussen de administraties die betrokken zijn bij het beheer van de exploratie en de exploitatie van het continentaal plat en de territoriale zee, gegeven op 26 maart 2024;Op de voordracht van de Minister van Economie,Hebben Wij besloten en besluiten Wij :Artikel 1. In artikel 1 van het koninklijk besluit van 1 september 2004 betreffende de voorwaarden en de toekenningsprocedure van concessies voor de exploratie en de exploitatie van de minerale en andere niet-levende rijkdommen in de territoriale zee en op het continentaal plat, worden de volgende wijzigingen aangebracht:a) de bepaling onder 2°  wordt opgeheven;a) de bepaling onder 7°  wordt opgeheven;b) de bepaling onder 8°,  gewijzigd bij het koninklijk besluit van 21 oktober 2018, wordt vervangen als volgt:"8°  "milieuvergunningsbesluit": koninklijk besluit van 26 april 2024 betreffende de procedure tot instelling van mariene beschermde gebieden, tot Natura 2000-toelating en Natura 2000-goedkeuring en tot milieuvergunning in de Belgische zeegebieden;";c) de bepaling onder 8° /1 wordt ingevoegd, luidende:"8° /1 "milieuvergunning": milieuvergunning voor de exploratie en exploitatie van de minerale en andere niet-levende rijkdommen van de zeebodem en van de ondergrond toegekend krachtens titel 5, hoofdstuk II, van het milieuvergunningsbesluit;";d) in de bepaling onder 12°,  vervangen bij het koninklijk besluit van 19 april 2014, worden de woorden "de Beheerseenheid van het Mathematisch Model van de Noordzee en het Schelde-estuarium, zoals bedoeld in het koninklijk besluit van 29 september 1997 houdende de overdracht van de Beheerseenheid van het Mathematisch Model van de Noordzee en het Schelde-estuarium naar" vervangen door de woorden "de wetenschappelijke dienst Beheerseenheid Mathematisch model van de Noordzee van de Operationele Directie Natuurlijk Milieu van";f) in de bepaling onder 18°  wordt het woord "exploitatie" vervangen door de woorden "uitzonderlijke en onvoorzienbare exploitatie";g) de bepaling onder 29°,  vervangen bij het koninklijk besluit van 21 oktober 2018, wordt opgeheven;h) de bepaling onder 30°  wordt opgeheven;i) in de Nederlandstalige tekst van de bepaling onder 31°,  ingevoegd bij het koninklijk besluit van 19 april 2014, worden de woorden "behorende tot" vervangen door het woord "van";j) de bepaling onder 37°,  ingevoegd bij het koninklijk besluit van 21 oktober 2018, wordt opgeheven.Art. 2. In artikel 4 van hetzelfde besluit, vervangen bij het koninklijk besluit van 19 april 2014 en gewijzigd bij het koninklijk besluit van 12 juni 2024, worden de volgende wijzigingen aangebracht:1°  in het eerste lid worden de woorden ", met uitzondering van sectoren 3a en 3b" opgeheven;2°  het tweede lid wordt opgeheven.Art. 3. Artikel 6 van hetzelfde besluit, gewijzigd bij de koninklijke besluiten van 20 maart 2014 en van 12 juli 2022, wordt opgeheven.Art. 4. In artikel 8 van hetzelfde besluit, worden de volgende wijzigingen aangebracht:1°  in paragraaf 1, eerste lid, worden de woorden "worden aan de afgevaardigde van de minister betekend" vervangen door de woorden "worden ingediend bij de afgevaardigde van de minister";2°  in paragraaf 1, tweede lid, vervangen bij het koninklijk besluit van 19 april 2014 en gewijzigd bij het koninklijk besluit van 21 oktober 2018, wordt de zin "De aanvrager betekent het ingevulde formulier met zijn bijlagen, evenals het milieueffectbeoordelingsrapport, zoals beschreven in hoofdstuk 2 van het MEB-besluit, in één van de landstalen in één papieren en één elektronisch exemplaar aan de afgevaardigde van de minister." vervangen als volgt:"Het ingevulde formulier met eventuele bijlagen, wordt in één van de landstalen door de aanvrager betekend of digitaal verstuurd aan de afgevaardigde van de minister.";3°  in paragraaf 2, eerste lid, 4°  worden de woorden "in het geval van een exploratie- en of exploitatie-aanvraag in de controlezones," opgeheven;4°  paragraaf 2, eerste lid, 5°,  gewijzigd bij het koninklijk besluit van 19 april 2014, wordt opgeheven;5°  paragraaf 3, vervangen bij het koninklijk besluit van 19 april 2014, wordt vervangen als volgt:" § 3. De aanvrager kan de aanvraag ten vroegste indienen na ontvangst van het attest ter bevestiging van de volledigheid en ontvankelijkheid zoals bepaald in artikel 101, § 1, van het milieuvergunningsbesluit en moet deze ten laatste één maand na het verkrijgen van de milieuvergunning voor de gevraagde activiteit hebben ingediend.".Art. 5. In artikel 9 van hetzelfde besluit worden de volgende wijzigingen aangebracht:1°  in paragraaf 1 worden de woorden "van het dossier" vervangen door de woorden "van het betekend of ontvangen dossier";2°  in paragraaf 3, eerste lid, worden de woorden "na vaststelling van de volledigheid van het dossier" ingevoegd tussen de woorden "binnen de tien dagen" en de woorden "in een register van concessieaanvragen";3°  in paragraaf 3, derde lid, vervangen bij het koninklijk besluit van 19 april 2014, worden de woorden "en informeert de bevoegde minister en de BMM van deze inschrijving" opgeheven.Art. 6. In hetzelfde besluit worden de volgende artikelen opgeheven:1°  artikel 9/1, ingevoegd bij het koninklijk </t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2025003467</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>12 mei 2025</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>28 april 2025. - Koninklijk besluit tot wijziging van het koninklijk besluit van 12 december 2018 tot vaststelling van de tegemoetkoming van de verplichte verzekering in de verpleegdagprijs in geval van opneming in een ziekenhuis in het buitenland</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-12&amp;numac_search=2025003467&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003467=10&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, artikel 37, § 7;Gelet op het koninklijk besluit van 12 december 2018 tot vaststelling van de tegemoetkoming van de verplichte verzekering in de verpleegdagprijs in geval van opneming in een ziekenhuis in het buitenland;Gelet op het advies van de Commissie voor begrotingscontrole, gegeven op 8 januari 2025, met toepassing van artikel 2, eerste lid, van het koninklijk besluit nr. 20 van 13 mei 2020 houdende tijdelijke maatregelen in de strijd tegen de COVID-19 pandemie en ter verzekering van de continuïteit van zorg in de verplichte verzekering voor geneeskundige verzorging;Gelet op het advies van het Comité van de verzekering voor geneeskundige verzorging, gegeven op 13 januari 2025, met toepassing van artikel 2, eerste lid, van het koninklijk besluit nr. 20 van 13 mei 2020 houdende tijdelijke maatregelen in de strijd tegen de COVID-19 pandemie en ter verzekering van de continuïteit van zorg in de verplichte verzekering voor geneeskundige verzorging;Gelet op het advies van de inspecteur van Financiën, gegeven op 31 januari 2025;Gelet op de akkoordbevinding van de minister voor Begroting, gegeven op 27 februari 2025;Gelet op het advies 77.573/2 van de Raad van State, gegeven op 8 april 2025, met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Op de voordracht van de Minister van Sociale Zaken;Hebben Wij besloten en besluiten Wij :Artikel 1. Artikel 1, § 3 van het koninklijk besluit van 12 december 2018 tot vaststelling van de tegemoetkoming van de verplichte verzekering in de verpleegdagprijs in geval van opneming in een ziekenhuis in het buitenland wordt vervangen als volgt:"Voor het tijdvak van 1 januari 2025 tot en met 31 december 2025 is de in § 1 bedoelde verpleegdagprijs vastgesteld op 820,57 euro.".Art. 2. Dit besluit treedt in werking op 1 januari 2025.Art. 3. De minister bevoegd voor Sociale zaken is belast met de uitvoering van dit besluit.Gegeven te Brussel, 28 april 2025.FILIPVan Koningswege :De Minister van Sociale Zaken,F. VANDENBROUCKE 
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2025003470</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>13 mei 2025</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>28 april 2025. - Koninklijk besluit tot wijziging van artikel 25, § 3bis, van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-13&amp;numac_search=2025003470&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003470=11&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet betreffende de verplichte verzekering voor geneeskundige verzorging en uitkeringen, gecoördineerd op 14 juli 1994, artikel 35, § 1, vijfde lid, en § 2, eerste lid, 1°,  gewijzigd bij het koninklijk besluit van 25 april 1997, bekrachtigd bij de wet van 12 december 1997;Gelet op het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen;Gelet op het voorstel van de Technische geneeskundige raad, gedaan tijdens zijn vergadering van 25 oktober 2022 ;Gelet op het advies van de Dienst voor geneeskundige evaluatie en controle van het Rijksinstituut voor ziekte- en invaliditeitsverzekering, gegeven op 25 oktober 2022;Gelet op de beslissing van de Nationale commissie artsen-ziekenfondsen van 12 december 2022;Gelet op het advies van de Commissie voor begrotingscontrole, gegeven op 1 maart 2023;Gelet op de beslissing van het Comité van de verzekering voor geneeskundige verzorging van het Rijksinstituut voor ziekte- en invaliditeitsverzekering van 27 maart 2023;Gelet op het advies van de Inspecteur van Financiën, gegeven op 17 februari 2025;Gelet op de akkoordbevinding van de Minister van Begroting van 27 februari 2025;Gelet op advies 77.601/2 van de Raad van State, gegeven op 14 april 2025, met toepassing van artikel 84, § 1, eerste lid, 2°,  van de wetten op de Raad van State, gecoördineerd op 12 januari 1973;Op de voordracht van de Minister van Sociale Zaken,Hebben Wij besloten en besluiten Wij :Artikel 1. In artikel 25, § 3bis, van de bijlage bij het koninklijk besluit van 14 september 1984 tot vaststelling van de nomenclatuur van de geneeskundige verstrekkingen inzake verplichte verzekering voor geneeskundige verzorging en uitkeringen, laatstelijk gewijzigd bij het koninklijk besluit van 19 juli 2024, wordt in de vijfde toepassingsregel na de verstrekking 590450 het tweede lid van de bepaling onder 5°  vervangen als volgt:"Het verslag maakt deel uit van het medisch dossier van de patiënt en wordt overgemaakt aan de huisarts die het globaal medisch dossier beheert, en de verwijzende arts.".Art. 2. Dit besluit treedt in werking op de eerste dag van de tweede maand na die waarin het is bekendgemaakt in het Belgisch Staatsblad.Art. 3. De minister bevoegd voor Sociale Zaken is belast met de uitvoering van dit besluit.Gegeven te Brussel, 28 april 2025.FILIPVan Koningswege :De Minister van Sociale Zaken en Volksgezondheid,F. VANDENBROUCKE . 
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2025201342</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>02 mei 2025</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>27 april 2025. - Koninklijk besluit tot hernieuwing van de mandaten van de Wetenschappelijke Raad, ingesteld bij het Federaal agentschap voor beroepsrisico's</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-02&amp;numac_search=2025201342&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025201342=12&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wetten betreffende de preventie van beroepsziekten en de vergoeding van de schade die uit die ziekten voortvloeit, gecoördineerd op 3 juni 1970, artikel 6bis, gewijzigd bij de wet van 13 juli 2006; Gelet op het koninklijk besluit van 25 februari 2007 tot vaststelling van de samenstelling van de Wetenschappelijke Raad en de oprichting van Medische Commissies bij Fedris en tot bepaling van het bedrag van de vergoedingen en presentiegelden toegekend aan de voorzitter en de leden van deze verschillende organen; gewijzigd bij koninklijk besluit van 19 juli 2013; Gelet op het advies van het beheerscomité van het Federaal agentschap voor beroepsrisico's, gegeven op 12 maart 2025; Op de voordracht van de Minister van Sociale Zaken, Hebben Wij besloten en besluiten Wij :Artikel 1. : Worden benoemd, voor een termijn van zes jaar, ingaande op 1 mei 2025, in hoedanigheid van leden van de Wetenschappelijke Raad, ingesteld bij het Federaal agentschap voor beroepsrisico's: 1° In de hoedanigheid van artsen, gespecialiseerd inzake arbeidsgeneeskunde en/of beroepsziekten voorgedragen door de Faculteit geneeskunde van elk van de universiteiten die een specialisatie in de arbeidsgeneeskunde inricht: Université Catholique de Louvain Effectief lid: Mevr. Dahlqvist Caroline Plaatsvervangend lid: Mevr. Gohy SophieKatholieke Universiteit Leuven Effectief lid: Dhr. Godderis Lode Plaatsvervangend lid: Mevr. Lambreghts CharlotteUniversité libre de Bruxelles Effectief lid: Mevr. Haccuria Amaryllis Plaatsvervangend lid: Dhr. Leduc DimitriUniversité de Liège Effectief lid: Mevr. Rusu Donna Plaatsvervangend lid: Dhr. Borguet MarcVrije Universiteit Brussel Effectief lid: Dhr. Versée Mathieu Plaatsvervangend lid: Mevr. Hanon Shane Universiteit Gent Effectief lid: Mevr. Braeckman Lutgart Plaatsvervangend lid: Mevr. Schepens VeerleUniversiteit Antwerpen Effectief lid: Mevr. Acke Sofie Plaatsvervangend lid: Mevr. Claesen Bieke 2° In de hoedanigheid van ingenieurs gespecialiseerd inzake voorkoming van beroepsziekten: Effectieve leden: Dhr. Boogaerts Geert Dhr. Jaupart Samuel Plaatsvervangende leden: Dhr. Van Bouwel Jan 3° In de hoedanigheid van deskundigen in het domein van de scheikunde en twee plaatsvervangers, bijzonder bekwaam inzake industriële toxicologie: Effectieve leden: Dhr. Sanchez Diez Ernesto 4° In de hoedanigheid van artsen gespecialiseerd inzake beroepsziekten, verbonden aan de Algemene Directie Toezicht op het Welzijn op het Werk van de Federale Overheidsdienst Werkgelegenheid, Arbeid en Sociaal Overleg: Effectieve leden: Dhr. Reyntjes Paulo Dhr. Gahide Désiré Plaatsvervangende leden Dhr. D'Hondt Cynthia Mevr. Lysens Katrien 5° In de hoedanigheid van artsen van het Federaal agentschap voor beroepsrisico's: Effectieve leden: Mevr. Phillips Chantal Dhr. Henriquez Carlos Plaatsvervangende leden: Dhr. Poot Olivier Mevr Van Raemdonck Anuschka 6° In de hoedanigheid van preventieadviseurs-arbeidsartsen, waarvan de ene verbonden is aan een interne dienst voor preventie en bescherming op het werk en de andere aan een externe dienst voor preventie en bescherming op het werk, voorgedragen door de meest representatieve organisaties van preventieadviseurs-arbeidsartsen: Effectief lid: Mevr. Nana Nanjouo Carine Laure Plaatsvervangend lid: Dhr. Rotsaert Paul 7° In de hoedanigheid van deskundigen aangeduid door de representatieve organisaties die zetelen in het Beheerscomité van het Federaal agentschap voor beroepsrisico's: Effectieve leden: Dhr. De Meester Kris Dhr. Van Eyck Kris Plaatsvervangende leden: Mevr. Verdoot Caroline Art. 2. Wordt benoemd voor een termijn van zes jaar, ingaande op 1 mei 2025, in hoedanigheid van voorzitter van de Wetenschappelijke Raad, ingesteld bij het Federaal agentschap voor beroepsrisico's: Dhr. Godderis Lode Art. 3. Dit besluit treedt in werking op 1 mei 2025. Art. 4. De minister bevoegd voor Sociale Zaken is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege : De Minister van Sociale Zaken, F. VANDENBROUCKE 
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2025201150</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>06 mei 2025</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>27 april 2025. - Koninklijk besluit tot benoeming van de werkende en plaatsvervangende leden van het Comité overheidsbedrijven, bedoeld in artikel 31, § 6, derde en vierde lid, van de wet van 21 maart 1991 tot hervorming van sommige economische overheidsbedrijven</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-06&amp;numac_search=2025201150&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025201150=13&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 21 maart 1991 tot hervorming van sommige economische overheidsbedrijven, artikel 31, § 6, derde en vierde lid; Gelet op het koninklijk besluit van 13 januari 1997 betreffende de werking en de samenstelling van het Comité overheidsbedrijven, artikelen 1 en 2; Gelet op het koninklijk besluit van 22 mei 2014 houdende benoeming van de werkende en plaatsvervangende leden van het Comité overheidsbedrijven, bedoeld in artikel 31, § 6, derde en vierde lid, van de wet van 21 maart 1991 tot hervorming van sommige economische overheidsbedrijven;Gelet op het voorstel van de raad van bestuur van bpost van 8 mei 2024; Gelet op de voorstellen van de raad van bestuur van Proximus van 19 september 2024; Gelet op het voorstel van de raad van bestuur van HR Rail van 21 oktober 2024; Gelet op het voorstel van de raad van bestuur van skeyes van 28 november 2024; Gelet op het voorstel van de raad van bestuur van de Nationale Maatschappij voor Belgische Spoorwegen van 13 december 2024; Gelet op het voorstel van de raad van bestuur van Infrabel van 21 januari 2025; Gelet op het advies van de Inspecteur van Financiën, gegeven op 1 april 2025; Op de voordracht van de Eerste Minister en op advies van de in Raad vergaderde Ministers, Hebben Wij besloten en besluiten Wij : Artikel 1. Worden voor een termijn van zes jaar benoemd tot werkende leden van het Comité overheidsbedrijven: a) op voorstel van bpost: - Mevr. An Matthynssens - Mevr. Inge Wevers - De heer Arnaud Parent b) op voorstel van Proximus: - Mevr. Olivia Rolin - De heer Karel Meeusen c) op voorstel van skeyes: - De heer Geert Malfliet - De heer Réginald de Borman d) op voorstel van de Nationale Maatschappij voor Belgische Spoorwegen: - Mevr. Sofia Kolibos e) op voorstel van Infrabel: - De heer Lander Decorte f) op voorstel van HR Rail: - Mevr. Sarah Blancke Art. 2. Worden voor een termijn van zes jaar benoemd tot plaatsvervangende leden van het Comité overheidsbedrijven: a) op voorstel van bpost: - De heer Peter Claes - De heer Dominique Piret - Mevr. Céline Moreau b) op voorstel van Proximus: - Mevr. Kristel Jans - Mevr. Valérie Vermeire c) op voorstel van skeyes: - De heer Egon Michiels - Mevr. Audrey Dorigo d) op voorstel van de Nationale Maatschappij voor Belgische Spoorwegen: - De heer Erwin Deyaert e) op voorstel van Infrabel: - Mevr. Maud Storme f) op voorstel van HR Rail: - Mevr. Leen De Ridder Art. 3. Het koninklijk besluit van 22 mei 2014 houdende benoeming van de werkende en plaatsvervangende leden van het Comité overheidsbedrijven, bedoeld in artikel 31, § 6, derde en vierde lid, van de wet van 21 maart 1991 tot hervorming van sommige economische overheidsbedrijven, wordt opgeheven. Art. 4. Dit besluit treedt heden in werking. Art. 5. De Eerste Minister is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege : De Eerste Minister, B. DE WEVER 
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2025201385</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>07 mei 2025</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>27 april 2025. - Koninklijk besluit tot verlenging van de taalkaders voor het personeel van het Grondwettelijk Hof</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-07&amp;numac_search=2025201385&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025201385=14&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de bijzondere wet van 6 januari 1989 op het Grondwettelijk Hof, de artikelen 42 en 66; Gelet op de wetten op het gebruik van de talen in bestuurszaken, gecoördineerd op 18 juli 1966, artikel 43, § 3; Gelet op het koninklijk besluit van 25 februari 2007 tot vaststelling, met het oog op de toepassing van artikel 43 van de wetten op het gebruik van de talen in bestuurszaken, gecoördineerd op 18 juli 1966, van de betrekkingen van het personeel van het Grondwettelijk Hof die eenzelfde trap van de hiërarchie vormen en tot goedkeuring van de taalkaders voor het personeel van het Grondwettelijk Hof, gewijzigd bij het koninklijk besluit van 19 december 2014; Gelet op het koninklijk besluit van 28 juni 2019 tot verlenging van de taalkaders voor het personeel van het Grondwettelijk Hof; Gelet op de beschikking van het Grondwettelijk Hof van 18 december 2024 tot vaststelling van de taalkaders voor het personeel van het Grondwettelijk Hof; Overwegende dat voldaan werd aan de voorschriften van artikel 54, tweede lid, van de voormelde wetten op het gebruik van de talen in bestuurszaken; Gelet op het advies nr. 57.023 van de Vaste Commissie voor Taaltoezicht, gegeven op 28 februari 2025; Gelet op het advies van de Inspecteur van Financiën, gegeven op 4 april 2025; Gelet op het artikel 8, § 1, 3°, van de wet van 15 december 2013 houdende diverse bepalingen inzake administratieve vereenvoudiging, houdende de vrijstelling van een regelgevingsimpactanalyse omdat het een formele beslissing betreft; Op de voordracht van de Eerste Minister en op het advies van de in Raad vergaderde Ministers, Hebben Wij besloten en besluiten Wij : Artikel 1. De taalkaders voor het personeel van het Grondwettelijk Hof, vastgesteld bij artikel 2 van het koninklijk besluit van 25 februari 2007 tot vaststelling, met het oog op de toepassing van artikel 43 van de wetten op het gebruik van de talen in bestuurszaken, gecoördineerd op 18 juli 1966, van de betrekkingen van het personeel van het Grondwettelijk Hof die eenzelfde trap van de hiërarchie vormen en tot goedkeuring van de taalkaders voor het personeel van het Grondwettelijk Hof, en laatst verlengd bij koninklijk besluit van 28 juni 2019, worden verlengd. Art. 2. Dit besluit heeft uitwerking met ingang van 1 maart 2025. Art. 3. De Eerste Minister is belast met de uitvoering van dit besluit. Gegeven te Brussel, 27 april 2025. FILIPVan Koningswege : De Eerste Minister, B. DE WEVER 
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2025003537</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>07 mei 2025</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>27 april 2025. - Koninklijk besluit tot goedkeuring van het huishoudelijk reglement van de proefbank voor vuurwapens</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.ejustice.just.fgov.be/cgi/article.pl?language=nl&amp;sum_date=2026-02-20&amp;pd_search=2025-05-07&amp;numac_search=2025003537&amp;page=2&amp;lg_txt=N&amp;caller=list&amp;2025003537=15&amp;view_numac=&amp;dt=Koninklijk+besluit&amp;pdd=2025-05-01&amp;pdf=2025-05-31&amp;choix1=en&amp;choix2=en&amp;fr=f&amp;nl=n&amp;du=d&amp;trier=afkondiging</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+FILIP, Koning der Belgen, Aan allen die nu zijn en hierna wezen zullen, Onze Groet.Gelet op de wet van 8 juli 2018 houdende bepalingen inzake de proefbank voor vuurwapens, artikel 5, derde lid;Overwegende dat de organen van de proefbank voor vuurwapens op 13 juni 2024 in overleg hun huishoudelijk reglement hebben opgesteld;Op de voordracht van de Minister van Economie en de Minister van Justitie,Hebben Wij besloten en besluiten Wij :Artikel 1. Het bij dit besluit gevoegde huishoudelijk reglement van de proefbank voor vuurwapens wordt goedgekeurd.Art. 2. Dit besluit treedt in werking de dag waarop het in het Belgisch Staatsblad wordt bekendgemaakt.Art. 3. De minister bevoegd voor Economie en de minister bevoegd voor Justitie zijn, ieder wat hem betreft, belast met de uitvoering van dit besluit.Gegeven te Brussel, 27 april 2025.FILIPVan Koningswege :De Minister van Economie,D. CLARINVALDe Minister van Justitie,A. VERLINDENBijlageHuishoudelijk reglement van de proefbank voor vuurwapensDe wettelijke bepalingen (wetten en uitvoeringsbesluiten) die van toepassing zijn op de proefbank voor vuurwapens worden beschouwd als een integraal onderdeel van het huishoudelijk reglement. In geval van afwijking of tegenstrijdigheid tussen dit huishoudelijk reglement en de wettelijke bepalingen, hebben deze laatste voorrang.TITEL I. - Identificatie en lokalisatieArtikel 1. De zetel van de proefbank voor vuurwapens (hierna « PB  ») is gevestigd te 4000 Liège, rue Fond des Tawes, 45. Hij is ingeschreven bij de btw onder het nr. BE0206.607.129.Art. 2. De PB gebruikt voor zijn communicatie de Franse en Nederlandse benaming gezamenlijk: « Proefbank voor vuurwapens - Banc d'épreuves des armes à feu ».TITEL II. - Vergaderingen van de Raad van BestuurHOOFDSTUK I. - UitnodigingArt. 3. De Raad van Bestuur wordt bijeengeroepen door de voorzitter van de Raad van Bestuur (per e-mail) met verzoek om ontvangstbevestiging.Behoudens dringende en onvoorziene gevallen, gebeurt de bijeenroeping minimum tien kalenderdagen vóór de vastgestelde datum van de vergadering.De uitnodiging vermeldt de datum, het uur en de plaats van de vergadering, alsmede de agenda. Ze wordt verzonden met de werkdocumenten die verband houden met de punten van de agenda van de vergadering, waaronder de samenvatting van de dossiers betreffende deze punten, en die zich op de zetel van de PB bevinden.De Raad van Bestuur vergadert minstens om de twee maanden. Hij moet worden bijeengeroepen telkens wanneer minstens drie van zijn leden er schriftelijk om verzoeken. De voorzitter is ertoe gehouden de Raad van Bestuur bijeen te roepen binnen eenentwintig kalenderdagen volgend op de ontvangst van het verzoekschrift. In voorkomend geval zijn de leden, die een punt op de agenda wensen te plaatsen, ertoe gehouden, samen met hun aanvraag, een toelichtingsnota betreffende dit punt te overhandigen aan de voorzitter.De uitnodigingen, agenda en werkdocumenten met betrekking tot iedere vergadering worden per e-mail gestuurd naar het mailadres dat door ieder van de leden daartoe meegedeeld is aan de secretaris van de Raad van Bestuur. Iedere adreswijziging wordt ter kennis gebracht van de secretaris.HOOFDSTUK II. - DagordeArt. 4. De voorzitter van de Raad van Bestuur stelt na overleg met de directeur de dagorde van de vergaderingen vast.Art. 5. In geval van dringende noodzaak kunnen hetzij de voorzitter van de Raad van Bestuur, hetzij de directeur, hetzij minstens drie leden een bijkomend punt op de dagorde van de vergadering plaatsen.De dringende noodzaak, vereist om ter zitting bijkomende punten op de dagorde te plaatsen, kan alleen worden aangenomen wanneer dit wordt gevraagd ten laatste twee werkdagen voor de vergaderdatum en wanneer daartoe beslist wordt door de meerderheid van de aanwezige leden. De notulen dienen in dat geval deze beslissing uitdrukkelijk te vermelden, alsmede de volgorde van de punten van de dagorde die wordt vastgesteld volgens de bepalingen van artikel 9.HOOFDSTUK III. - Manier van vergaderen, beraadslagen en beslissenArt. 6. Enkel de bestuurders zetelen in de Raad van Bestuur. De directeur en de regeringscommissarissen wonen de Raad van Bestuur bij. Laatstgenoemden beschikken uitsluitend over een raadgevende stem, in overeenstemming met artikel 41.Art. 7. De Raad van Bestuur vergadert onder het voorzitterschap van zijn voorzitter of, bij zijn ontstentenis, van een onafhankelijke bestuurder aangewezen door de voorzitter of, bij afwezigheid, van een onafhankelijke bestuurder aangesteld door de andere aanwezige bestuurders. Hij is dan de voorzitter van de zitting in kwestie.De vergaderingen van de Raad van Bestuur worden voor geopend en voor gesloten verklaard door de voorzitter van de zitting.Art. 8. De Ra